--- a/docs/innovation_news_ledger.xlsx
+++ b/docs/innovation_news_ledger.xlsx
@@ -9,9 +9,9 @@
     <sheet name="Run Log" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'News Ledger'!$A$3:$O$105</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'News Ledger'!$A$3:$O$114</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Source Registry'!$A$3:$K$37</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Run Log'!$A$3:$H$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Run Log'!$A$3:$H$7</definedName>
   </definedNames>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -472,7 +472,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="NewsLedgerTable" displayName="NewsLedgerTable" ref="A3:O105" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="NewsLedgerTable" displayName="NewsLedgerTable" ref="A3:O114" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <autoFilter ref="A3:O4"/>
   <tableColumns count="15">
     <tableColumn id="1" name="Collected At (JST)"/>
@@ -516,7 +516,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="RunLogTable" displayName="RunLogTable" ref="A3:H6" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="RunLogTable" displayName="RunLogTable" ref="A3:H7" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <autoFilter ref="A3:H4"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Run Time (JST)"/>
@@ -800,7 +800,7 @@
       </c>
       <c r="B5" s="25" t="inlineStr">
         <is>
-          <t>2026-07-26T19:10:55+09:00</t>
+          <t>2026-07-26T19:51:39+09:00</t>
         </is>
       </c>
       <c r="C5" s="46" t="n"/>
@@ -1088,7 +1088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O105"/>
+  <dimension ref="A1:O114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1216,27 +1216,27 @@
     <row r="4" ht="42" customHeight="1">
       <c r="A4" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T19:51:39+09:00</t>
         </is>
       </c>
       <c r="B4" s="75" t="inlineStr">
         <is>
-          <t>2026-07-25T20:00:53Z</t>
+          <t>2026-07-26T10:00:16Z</t>
         </is>
       </c>
       <c r="C4" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="D4" s="60" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="E4" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="F4" s="76" t="n">
@@ -1249,32 +1249,32 @@
       </c>
       <c r="H4" s="60" t="inlineStr">
         <is>
-          <t>The Guardian Technology</t>
+          <t>South China Morning Post Technology</t>
         </is>
       </c>
       <c r="I4" s="60" t="inlineStr">
         <is>
-          <t>Mega datacentre planned for outer Melbourne will be six times bigger than a large shopping centre</t>
+          <t>Were the German courts too soft on Chinese members of drug rape network?</t>
         </is>
       </c>
       <c r="J4" s="60" t="inlineStr">
         <is>
-          <t>More than 3,600 people sign petition for careful assessment of proposed AI hub, now a flashpoint for national debate on datacentre boom Follow our Australia news live blog for latest updates Get our breaking news email , free app or daily news podcast For some residents it started with a letter in the mailbox. It was a “friendly introduction from the team behind the Victorian AI hub”. “I am knocking on doors to explain what we have in mind and, most importantly, to listen,” the letter from Syncline Energy stated. Continue reading...</t>
+          <t>Minutes after a Berlin court sentenced a Chinese man to five years in prison for aiding and abetting aggravated rape and sexual coercion, two women who had sat through the trial hugged each other and cried. But the case left one of those women, named Kristina, balancing mixed emotions as she struggled to reconcile her desire to see the perpetrators punished and questions about what justice really meant in a case of this nature. The 32-year-old accused, who was studying medicine, was jailed for...</t>
         </is>
       </c>
       <c r="K4" s="60" t="inlineStr">
         <is>
-          <t>https://www.theguardian.com/australia-news/2026/jul/26/mega-datacentre-planned-for-outer-melbourne-will-be-almost-six-times-the-size-of-chadstone-shopping-centre</t>
+          <t>https://www.scmp.com/news/china/politics/article/3361892/were-german-courts-too-soft-chinese-members-drug-rape-network?utm_source=rss_feed</t>
         </is>
       </c>
       <c r="L4" s="60" t="inlineStr">
         <is>
-          <t>fbf0c9b2010e9cdb4ff4a650</t>
+          <t>4ca6c9bab41f11f1e490b924</t>
         </is>
       </c>
       <c r="M4" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T19:51:39+09:00</t>
         </is>
       </c>
       <c r="N4" s="60" t="inlineStr">
@@ -1287,12 +1287,12 @@
     <row r="5" ht="42" customHeight="1">
       <c r="A5" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T19:51:39+09:00</t>
         </is>
       </c>
       <c r="B5" s="75" t="inlineStr">
         <is>
-          <t>2026-07-25T14:32:00Z</t>
+          <t>2026-07-26T08:00:09Z</t>
         </is>
       </c>
       <c r="C5" s="60" t="inlineStr">
@@ -1302,50 +1302,50 @@
       </c>
       <c r="D5" s="60" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="E5" s="60" t="inlineStr">
         <is>
-          <t>Semiconductors &amp; Telecom</t>
+          <t>Innovation Policy</t>
         </is>
       </c>
       <c r="F5" s="76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" s="60" t="inlineStr">
         <is>
-          <t>Official Company</t>
+          <t>Major Media</t>
         </is>
       </c>
       <c r="H5" s="60" t="inlineStr">
         <is>
-          <t>Samsung Global Newsroom</t>
+          <t>South China Morning Post Technology</t>
         </is>
       </c>
       <c r="I5" s="60" t="inlineStr">
         <is>
-          <t>Samsung Electronics and Broadcom Expand Strategic Collaboration Across Memory and Foundry Technologies</t>
+          <t>Lower profit margins set to foil Chinese carmakers’ price war plans despite falling sales</t>
         </is>
       </c>
       <c r="J5" s="60" t="inlineStr">
         <is>
-          <t>Samsung Electronics and Broadcom today announced the signing of a memorandum of understanding (MOU) to expand their strategic collaboration across memory and foundry technologies, supporting the next generation of AI infrastructure. The MOU was announced during the AI Summit, held at The Midway in San Francisco. Attendees included Jinman Han, President and Head of Samsung […]</t>
+          <t>Narrowing profit margins due to higher raw material costs have dealt yet another major blow to China’s carmakers as they face shrinking market demand amid a rollback of purchase subsidies and tax incentives. The dire scenario could also dash Chinese consumers’ hopes for steep discounts, despite carmakers’ efforts to reduce their inventories, according to dealers and analysts. “The crux point is that most carmakers are facing squeezed margins and are unable to offer further price cuts to attract...</t>
         </is>
       </c>
       <c r="K5" s="60" t="inlineStr">
         <is>
-          <t>https://news.samsung.com/global/samsung-electronics-and-broadcom-expand-strategic-collaboration-across-memory-and-foundry-technologies</t>
+          <t>https://www.scmp.com/business/china-business/article/3361876/lower-profit-margins-set-foil-chinese-carmakers-price-war-plans-despite-falling-sales?utm_source=rss_feed</t>
         </is>
       </c>
       <c r="L5" s="60" t="inlineStr">
         <is>
-          <t>bd739fbc33fb8bb2bb1f6e52</t>
+          <t>edcae2eaed3f6ecc6f59640c</t>
         </is>
       </c>
       <c r="M5" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T19:51:39+09:00</t>
         </is>
       </c>
       <c r="N5" s="60" t="inlineStr">
@@ -1358,27 +1358,27 @@
     <row r="6" ht="42" customHeight="1">
       <c r="A6" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T19:51:39+09:00</t>
         </is>
       </c>
       <c r="B6" s="75" t="inlineStr">
         <is>
-          <t>2026-07-25T13:00:43Z</t>
+          <t>2026-07-26T04:54:09Z</t>
         </is>
       </c>
       <c r="C6" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>EU &amp; Europe</t>
         </is>
       </c>
       <c r="D6" s="60" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="E6" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence | Robotics</t>
+          <t>Fusion Energy</t>
         </is>
       </c>
       <c r="F6" s="76" t="n">
@@ -1391,32 +1391,32 @@
       </c>
       <c r="H6" s="60" t="inlineStr">
         <is>
-          <t>The Guardian Technology</t>
+          <t>South China Morning Post Technology</t>
         </is>
       </c>
       <c r="I6" s="60" t="inlineStr">
         <is>
-          <t>The AI jobs apocalypse probably isn’t coming anytime soon</t>
+          <t>European heatwaves drive summer tourists to cooler north</t>
         </is>
       </c>
       <c r="J6" s="60" t="inlineStr">
         <is>
-          <t>Artificial intelligence may not deliver on its promise of vast economic opportunity at a price that humanity is willing to pay In March, Anthropic, the cutting-edge artificial intelligence business that gave us the chatbot Claude, published an analysis on the impact of AI on employment, to help us assess the claim that intelligent robots were about to redefine human existence, ending demand for human labor. Last year in May, Anthropic’s co-founder, Dario Amodei, claimed AI could wipe out half of all entry-level jobs in one to five years. Last January, he told us AI would probably become a “general labor substitute for humans”. In June he said we risk “a world where the economic trade-off di…</t>
+          <t>European holidaymakers worn down by recurrent heatwaves are currently snubbing Mediterranean destinations for northern climes in hopes of cooler temperatures, but it remains to be seen whether it is just a fad or a durable shift in the tourism market. With temperatures in the European summer regularly climbing up towards 40 degrees Celsius (100 degrees Fahrenheit), cool has become cool. This year, visitors “have been telling me that they have escaped the heat in southern parts of Europe”, said...</t>
         </is>
       </c>
       <c r="K6" s="60" t="inlineStr">
         <is>
-          <t>https://www.theguardian.com/technology/2026/jul/25/ai-jobs-apocalypse-human-labor</t>
+          <t>https://www.scmp.com/news/world/europe/article/3361871/european-heatwaves-drive-summer-tourists-cooler-north?utm_source=rss_feed</t>
         </is>
       </c>
       <c r="L6" s="60" t="inlineStr">
         <is>
-          <t>144f9038d6abd12e69ae1122</t>
+          <t>16261ceceb1c08aa85c0ea99</t>
         </is>
       </c>
       <c r="M6" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T19:51:39+09:00</t>
         </is>
       </c>
       <c r="N6" s="60" t="inlineStr">
@@ -1429,27 +1429,27 @@
     <row r="7" ht="42" customHeight="1">
       <c r="A7" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:10:55+09:00</t>
+          <t>2026-07-26T19:51:39+09:00</t>
         </is>
       </c>
       <c r="B7" s="75" t="inlineStr">
         <is>
-          <t>2026-07-25T11:12:11Z</t>
+          <t>2026-07-26T03:21:31Z</t>
         </is>
       </c>
       <c r="C7" s="60" t="inlineStr">
         <is>
-          <t>Middle East</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="D7" s="60" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="E7" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="F7" s="76" t="n">
@@ -1462,32 +1462,32 @@
       </c>
       <c r="H7" s="60" t="inlineStr">
         <is>
-          <t>The National Technology</t>
+          <t>South China Morning Post Technology</t>
         </is>
       </c>
       <c r="I7" s="60" t="inlineStr">
         <is>
-          <t>Risky bet: The winners and losers from the OpenAI-Hugging Face hacking mess</t>
+          <t>Rare medical condition causes Chinese man’s scalp to thicken and fold, resembling human brain</t>
         </is>
       </c>
       <c r="J7" s="60" t="inlineStr">
         <is>
-          <t>When OpenAI revealed this week that one of its AI models went rogue during a security test and autonomously hacked the start-up Hugging Face, it came as a shock. Questions were raised quickly, but there was no immediate clarity. Hugging Face co-founder and chief executive Clem Delangue said the incident was "possibly the first of its kind". As with any serious tech incident, there are those who stand to gain and other who stand to lose. And the circumstances can be as complex as the hacking is. Losers: OpenAI and Hugging Face Let's start with the obvious matter. It was a PR nightmare for ChatGPT maker OpenAI, as well as Hugging Face, as they bore the brunt of the mess, albeit for different…</t>
+          <t>A man from central China had long been troubled by a thickening scalp that developed folds resembling the creases of a brain, but he eventually found a plastic surgeon who could address his condition. The 23-year-old man from Hunan province, surnamed Li, recently had his issue resolved at the Zhongnan Hospital of Wuhan University in Hubei. Li first noticed the hardening of his scalp several years ago. As the condition advanced, his scalp thickened and proliferated, creating large areas of uneven...</t>
         </is>
       </c>
       <c r="K7" s="60" t="inlineStr">
         <is>
-          <t>https://www.thenationalnews.com/future/technology/2026/07/25/risky-bet-the-winners-and-losers-from-the-openai-hugging-face-hacking-mess/</t>
+          <t>https://www.scmp.com/news/people-culture/trending-china/article/3361865/rare-medical-condition-causes-chinese-mans-scalp-thicken-and-fold-resembling-human-brain?utm_source=rss_feed</t>
         </is>
       </c>
       <c r="L7" s="60" t="inlineStr">
         <is>
-          <t>ae772fcc12d71afd038c86c2</t>
+          <t>e6f3f1ebac50723e73d10bfe</t>
         </is>
       </c>
       <c r="M7" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:10:55+09:00</t>
+          <t>2026-07-26T19:51:39+09:00</t>
         </is>
       </c>
       <c r="N7" s="60" t="inlineStr">
@@ -1500,12 +1500,12 @@
     <row r="8" ht="42" customHeight="1">
       <c r="A8" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T19:51:39+09:00</t>
         </is>
       </c>
       <c r="B8" s="75" t="inlineStr">
         <is>
-          <t>2026-07-25T05:00:35Z</t>
+          <t>2026-07-26T00:00:14Z</t>
         </is>
       </c>
       <c r="C8" s="60" t="inlineStr">
@@ -1515,16 +1515,16 @@
       </c>
       <c r="D8" s="60" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="E8" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Innovation Policy</t>
         </is>
       </c>
       <c r="F8" s="76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G8" s="60" t="inlineStr">
         <is>
@@ -1533,32 +1533,32 @@
       </c>
       <c r="H8" s="60" t="inlineStr">
         <is>
-          <t>The Guardian Technology</t>
+          <t>South China Morning Post Technology</t>
         </is>
       </c>
       <c r="I8" s="60" t="inlineStr">
         <is>
-          <t>‘I thought, I’ve tried everything else, why not give AI a shot?’: the long-lost family reunited by ChatGPT</t>
+          <t>Indonesia’s plan for a Singapore rival starts to take shape</t>
         </is>
       </c>
       <c r="J8" s="60" t="inlineStr">
         <is>
-          <t>Avtar spent decades wondering what happened to the mother he never got to know. Thousands of miles away, Nicci was haunted by the story of a half-brother given away before she was born. How did a chatbot bring them together? As a small boy growing up in Amritsar, India, in the 1960s, Avtar Singh used to hear whispers. Your mum isn’t really your mum , the rumours would say. Your mum lives abroad. Avtar didn’t really pay any attention to it. “I thought, the neighbours are just making up stories.” But the stories were true: the woman raising Avtar was actually his grandmother. When he was too young to remember it, his father had emigrated to Canada to work as a teacher, leaving Avtar in the ca…</t>
+          <t>Indonesia wants to build a financial centre to rival Singapore, Hong Kong or Dubai, but analysts say the real work of persuading global investors has barely begun. Parliament’s passage of the enabling legislation on Tuesday laid the legal foundation for the hub, marking a milestone in President Prabowo Subianto’s push to attract more foreign capital into Southeast Asia’s largest economy and lift growth towards 8 per cent by the end of his term in 2029. Yet observers caution that the centre,...</t>
         </is>
       </c>
       <c r="K8" s="60" t="inlineStr">
         <is>
-          <t>https://www.theguardian.com/lifeandstyle/ng-interactive/2026/jul/25/long-lost-family-reunited-chatgpt-artificial-intelligence-ai</t>
+          <t>https://www.scmp.com/week-asia/economics/article/3361783/indonesias-plan-singapore-rival-starts-take-shape?utm_source=rss_feed</t>
         </is>
       </c>
       <c r="L8" s="60" t="inlineStr">
         <is>
-          <t>818d7fcb63b548448b301aec</t>
+          <t>f74daba2783d19d5f5ff6719</t>
         </is>
       </c>
       <c r="M8" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T19:51:39+09:00</t>
         </is>
       </c>
       <c r="N8" s="60" t="inlineStr">
@@ -1571,27 +1571,27 @@
     <row r="9" ht="42" customHeight="1">
       <c r="A9" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T19:51:39+09:00</t>
         </is>
       </c>
       <c r="B9" s="75" t="inlineStr">
         <is>
-          <t>2026-07-24T18:00:01Z</t>
+          <t>2026-07-25T21:57:06Z</t>
         </is>
       </c>
       <c r="C9" s="60" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Middle East</t>
         </is>
       </c>
       <c r="D9" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="E9" s="60" t="inlineStr">
         <is>
-          <t>Semiconductors &amp; Telecom</t>
+          <t>Robotics</t>
         </is>
       </c>
       <c r="F9" s="76" t="n">
@@ -1604,32 +1604,32 @@
       </c>
       <c r="H9" s="60" t="inlineStr">
         <is>
-          <t>IEEE Spectrum</t>
+          <t>South China Morning Post Technology</t>
         </is>
       </c>
       <c r="I9" s="60" t="inlineStr">
         <is>
-          <t>2022 IEEE President K.J. Ray Liu Honored for His Leadership</t>
+          <t>US pauses nightly Iran strikes, as Houthis clash with Saudis</t>
         </is>
       </c>
       <c r="J9" s="60" t="inlineStr">
         <is>
-          <t>Unlike many budding engineers, K.J. Ray Liu wasn’t inspired to enter the field by tinkering with electronics or following in the footsteps of a family member. Growing up in Taichung, Taiwan, he answered his government’s call for students to become electrical engineers to help manufacture semiconductors in the 1970s, when the country’s economy was struggling. “Students who were good in math, science, and physics all wanted to be an electrical engineer because that was the top priority of the government,” Liu says. “That’s how I got into engineering. Now Taiwan is a world leader in semiconductors.” K.J. Ray Liu Occupation Retired professor of information technology and a digital signal proces…</t>
+          <t>Skirmishes between Houthi rebels and Saudi Arabia intensified, as a pause in the nearly two-week run of nightly US strikes on Iran raised fresh questions about President Donald Trump’s strategy in the war. The Houthis, Islamist militants based in Yemen and backed by Iran, said they fired missiles and drones at facilities linked to oil giant Saudi Aramco in the Red Sea port towns of Jizan and Yanbu. There was no immediate confirmation from the Saudi government or Aramco. Saudi authorities briefly...</t>
         </is>
       </c>
       <c r="K9" s="60" t="inlineStr">
         <is>
-          <t>https://spectrum.ieee.org/ieee-president-ray-liu-award</t>
+          <t>https://www.scmp.com/news/world/middle-east/article/3361857/us-pauses-nightly-iran-strikes-houthis-clash-saudis?utm_source=rss_feed</t>
         </is>
       </c>
       <c r="L9" s="60" t="inlineStr">
         <is>
-          <t>87b839503197ad74fc686cf1</t>
+          <t>9578a29fc000c630648a5b1c</t>
         </is>
       </c>
       <c r="M9" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T19:51:39+09:00</t>
         </is>
       </c>
       <c r="N9" s="60" t="inlineStr">
@@ -1642,22 +1642,22 @@
     <row r="10" ht="42" customHeight="1">
       <c r="A10" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:10:55+09:00</t>
+          <t>2026-07-26T19:51:39+09:00</t>
         </is>
       </c>
       <c r="B10" s="75" t="inlineStr">
         <is>
-          <t>2026-07-24T17:32:29Z</t>
+          <t>2026-07-25T21:30:08Z</t>
         </is>
       </c>
       <c r="C10" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="D10" s="60" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="E10" s="60" t="inlineStr">
@@ -1675,32 +1675,32 @@
       </c>
       <c r="H10" s="60" t="inlineStr">
         <is>
-          <t>The National Technology</t>
+          <t>South China Morning Post Technology</t>
         </is>
       </c>
       <c r="I10" s="60" t="inlineStr">
         <is>
-          <t>Nvidia, Microsoft and IBM among companies endorsing open-weight AI models</t>
+          <t>The West is debating AI’s future with half the world absent</t>
         </is>
       </c>
       <c r="J10" s="60" t="inlineStr">
         <is>
-          <t>Nvidia chief executive Jensen Huang joined X on Friday and used his first post to champion AI models that can be downloaded and adapted, arguing they are vital to preserving America’s lead in artificial intelligence. Mr Huang attached a letter signed by 25 major companies, including Microsoft, Palantir , Perplexity, CrowdStrike and IBM that endorsed open-source software development and “open-weight” AI models. Some US officials have raised concerns that AI models could pose national security risks, while companies such as OpenAI and Anthropic still largely oppose open architecture for proprietary reasons. “Open source did more than lower the cost of software; it created a shared foundation…</t>
+          <t>On July 13, more than 200 leading economists and AI researchers, including 16 Nobel laureates, signed an open letter organised by the Stanford Digital Economy Lab. Its warning was stark: artificial intelligence may drive an economic transformation “larger than the Industrial Revolution” compressed into a fraction of the time, and that we “must act now” to build the institutions to steer it. We agree with every word. Then we scanned the signatory list. Four in five signatories come from the...</t>
         </is>
       </c>
       <c r="K10" s="60" t="inlineStr">
         <is>
-          <t>https://www.thenationalnews.com/future/technology/2026/07/24/open-weight-models-ai-nvidia/</t>
+          <t>https://www.scmp.com/opinion/world-opinion/article/3361362/west-debating-ais-future-half-world-absent?utm_source=rss_feed</t>
         </is>
       </c>
       <c r="L10" s="60" t="inlineStr">
         <is>
-          <t>258e9b19598256f555ff9019</t>
+          <t>3e13a0000f2936b28208b36d</t>
         </is>
       </c>
       <c r="M10" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:10:55+09:00</t>
+          <t>2026-07-26T19:51:39+09:00</t>
         </is>
       </c>
       <c r="N10" s="60" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="B11" s="75" t="inlineStr">
         <is>
-          <t>2026-07-24T17:03:55Z</t>
+          <t>2026-07-25T20:00:53Z</t>
         </is>
       </c>
       <c r="C11" s="60" t="inlineStr">
@@ -1728,12 +1728,12 @@
       </c>
       <c r="D11" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="E11" s="60" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="F11" s="76" t="n">
@@ -1746,27 +1746,27 @@
       </c>
       <c r="H11" s="60" t="inlineStr">
         <is>
-          <t>MIT Technology Review</t>
+          <t>The Guardian Technology</t>
         </is>
       </c>
       <c r="I11" s="60" t="inlineStr">
         <is>
-          <t>The quest to keep organs alive outside the body</t>
+          <t>Mega datacentre planned for outer Melbourne will be six times bigger than a large shopping centre</t>
         </is>
       </c>
       <c r="J11" s="60" t="inlineStr">
         <is>
-          <t>This week, I covered a fascinating effort to preserve organs outside the body. There’s a huge shortage of donor organs, and one of the main reasons is time—they survive only a matter of hours outside the body, even when they’re kept on ice. Doctors dream of organ banks—stores of human organs that can be preserved…</t>
+          <t>More than 3,600 people sign petition for careful assessment of proposed AI hub, now a flashpoint for national debate on datacentre boom Follow our Australia news live blog for latest updates Get our breaking news email , free app or daily news podcast For some residents it started with a letter in the mailbox. It was a “friendly introduction from the team behind the Victorian AI hub”. “I am knocking on doors to explain what we have in mind and, most importantly, to listen,” the letter from Syncline Energy stated. Continue reading...</t>
         </is>
       </c>
       <c r="K11" s="60" t="inlineStr">
         <is>
-          <t>https://www.technologyreview.com/2026/07/24/1140790/the-quest-to-keep-organs-alive-outside-the-body/</t>
+          <t>https://www.theguardian.com/australia-news/2026/jul/26/mega-datacentre-planned-for-outer-melbourne-will-be-almost-six-times-the-size-of-chadstone-shopping-centre</t>
         </is>
       </c>
       <c r="L11" s="60" t="inlineStr">
         <is>
-          <t>039c84226e8803400ce67975</t>
+          <t>fbf0c9b2010e9cdb4ff4a650</t>
         </is>
       </c>
       <c r="M11" s="75" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="B12" s="75" t="inlineStr">
         <is>
-          <t>2026-07-24T16:46:59Z</t>
+          <t>2026-07-25T14:32:00Z</t>
         </is>
       </c>
       <c r="C12" s="60" t="inlineStr">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="D12" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="E12" s="60" t="inlineStr">
@@ -1817,27 +1817,27 @@
       </c>
       <c r="H12" s="60" t="inlineStr">
         <is>
-          <t>Intel Newsroom</t>
+          <t>Samsung Global Newsroom</t>
         </is>
       </c>
       <c r="I12" s="60" t="inlineStr">
         <is>
-          <t>Intel and Lens Technology Collaborate to Enable Advanced Semiconductor Packaging for the AI Era</t>
+          <t>Samsung Electronics and Broadcom Expand Strategic Collaboration Across Memory and Foundry Technologies</t>
         </is>
       </c>
       <c r="J12" s="60" t="inlineStr">
         <is>
-          <t>SANTA CLARA, Calif. &amp; CHANGSHA, China — Intel Corporation and Lens Technology today announced a strategic collaboration focused on enabling new technologies for advanced semiconductor packaging. Through this work, the companies intend to explore opportunities to accelerate the development of glass substrate-based packaging solutions that can help enable higher performance, increased interconnect density, and improved … The post Intel and Lens Technology Collaborate to Enable Advanced Semiconductor Packaging for the AI Era appeared first on Newsroom .</t>
+          <t>Samsung Electronics and Broadcom today announced the signing of a memorandum of understanding (MOU) to expand their strategic collaboration across memory and foundry technologies, supporting the next generation of AI infrastructure. The MOU was announced during the AI Summit, held at The Midway in San Francisco. Attendees included Jinman Han, President and Head of Samsung […]</t>
         </is>
       </c>
       <c r="K12" s="60" t="inlineStr">
         <is>
-          <t>https://newsroom.intel.com/new-technologies/intel-and-lens-technology-collaborate-to-enable-advanced-semiconductor-packaging-for-the-ai-era</t>
+          <t>https://news.samsung.com/global/samsung-electronics-and-broadcom-expand-strategic-collaboration-across-memory-and-foundry-technologies</t>
         </is>
       </c>
       <c r="L12" s="60" t="inlineStr">
         <is>
-          <t>10eedf14d7d6b636e24e447d</t>
+          <t>bd739fbc33fb8bb2bb1f6e52</t>
         </is>
       </c>
       <c r="M12" s="75" t="inlineStr">
@@ -1860,12 +1860,12 @@
       </c>
       <c r="B13" s="75" t="inlineStr">
         <is>
-          <t>2026-07-24T15:25:30Z</t>
+          <t>2026-07-25T13:00:43Z</t>
         </is>
       </c>
       <c r="C13" s="60" t="inlineStr">
         <is>
-          <t>EU &amp; Europe</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D13" s="60" t="inlineStr">
@@ -1875,40 +1875,40 @@
       </c>
       <c r="E13" s="60" t="inlineStr">
         <is>
-          <t>Innovation Policy</t>
+          <t>Artificial Intelligence | Robotics</t>
         </is>
       </c>
       <c r="F13" s="76" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G13" s="60" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Major Media</t>
         </is>
       </c>
       <c r="H13" s="60" t="inlineStr">
         <is>
-          <t>UK DSIT</t>
+          <t>The Guardian Technology</t>
         </is>
       </c>
       <c r="I13" s="60" t="inlineStr">
         <is>
-          <t>Guidance: Cyber Resilience Pledge - list of signatories</t>
+          <t>The AI jobs apocalypse probably isn’t coming anytime soon</t>
         </is>
       </c>
       <c r="J13" s="60" t="inlineStr">
         <is>
-          <t>Organisations that have signed the Cyber Resilience Pledge.</t>
+          <t>Artificial intelligence may not deliver on its promise of vast economic opportunity at a price that humanity is willing to pay In March, Anthropic, the cutting-edge artificial intelligence business that gave us the chatbot Claude, published an analysis on the impact of AI on employment, to help us assess the claim that intelligent robots were about to redefine human existence, ending demand for human labor. Last year in May, Anthropic’s co-founder, Dario Amodei, claimed AI could wipe out half of all entry-level jobs in one to five years. Last January, he told us AI would probably become a “general labor substitute for humans”. In June he said we risk “a world where the economic trade-off di…</t>
         </is>
       </c>
       <c r="K13" s="60" t="inlineStr">
         <is>
-          <t>https://www.gov.uk/government/publications/cyber-resilience-pledge-list-of-signatories</t>
+          <t>https://www.theguardian.com/technology/2026/jul/25/ai-jobs-apocalypse-human-labor</t>
         </is>
       </c>
       <c r="L13" s="60" t="inlineStr">
         <is>
-          <t>556f1cad5674dfe48a261c54</t>
+          <t>144f9038d6abd12e69ae1122</t>
         </is>
       </c>
       <c r="M13" s="75" t="inlineStr">
@@ -1926,22 +1926,22 @@
     <row r="14" ht="42" customHeight="1">
       <c r="A14" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T19:51:39+09:00</t>
         </is>
       </c>
       <c r="B14" s="75" t="inlineStr">
         <is>
-          <t>2026-07-24T12:00:14Z</t>
+          <t>2026-07-25T13:00:08Z</t>
         </is>
       </c>
       <c r="C14" s="60" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D14" s="60" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="E14" s="60" t="inlineStr">
@@ -1959,32 +1959,32 @@
       </c>
       <c r="H14" s="60" t="inlineStr">
         <is>
-          <t>The Guardian Technology</t>
+          <t>South China Morning Post Technology</t>
         </is>
       </c>
       <c r="I14" s="60" t="inlineStr">
         <is>
-          <t>Should you use AI for a task? Here’s a simple way to decide | Bruce Schneier</t>
+          <t>What is a supernode, and why does it matter for the China-US tech rivalry?</t>
         </is>
       </c>
       <c r="J14" s="60" t="inlineStr">
         <is>
-          <t>Sometimes, what matters isn’t your output but what you put into the process. Think of it like work v the gym I teach public policy at the Harvard Kennedy School and the Munk School at the University of Toronto. And it will come as no surprise to you that my students regularly use AI to complete their writing assignments. Doing so is a waste of their tuition money. But if their entire career is going to include AI writing assistants, why shouldn’t they embrace their future? The best way I’ve found to explain the dilemma comes from the AI researcher Daniel Meissler: it’s the difference between work and the gym. Continue reading...</t>
+          <t>As the size of artificial intelligence models expands beyond 1 trillion parameters, a new concept is dominating the computing landscape: “supernode”. At this year’s World Artificial Intelligence Conference (WAIC), China’s top AI summit, domestic chipmakers from Huawei Technologies to Biren Technology showcased new hardware designed to knit hundreds or thousands of chips together to act as one giant supercomputer, which they called a supernode. The focus on supernodes at WAIC reflected a shift in...</t>
         </is>
       </c>
       <c r="K14" s="60" t="inlineStr">
         <is>
-          <t>https://www.theguardian.com/commentisfree/2026/jul/24/should-you-use-ai</t>
+          <t>https://www.scmp.com/tech/article/3361562/what-supernode-and-why-does-it-matter-china-us-tech-rivalry?utm_source=rss_feed</t>
         </is>
       </c>
       <c r="L14" s="60" t="inlineStr">
         <is>
-          <t>d7259db0d54f48b0f5039bb8</t>
+          <t>4e5989e812e0089b587f2c6b</t>
         </is>
       </c>
       <c r="M14" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T19:51:39+09:00</t>
         </is>
       </c>
       <c r="N14" s="60" t="inlineStr">
@@ -2002,12 +2002,12 @@
       </c>
       <c r="B15" s="75" t="inlineStr">
         <is>
-          <t>2026-07-24T11:39:05Z</t>
+          <t>2026-07-25T11:12:11Z</t>
         </is>
       </c>
       <c r="C15" s="60" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Middle East</t>
         </is>
       </c>
       <c r="D15" s="60" t="inlineStr">
@@ -2035,22 +2035,22 @@
       </c>
       <c r="I15" s="60" t="inlineStr">
         <is>
-          <t>Zoom launches live voice translation, with Arabic coming in late 2026</t>
+          <t>Risky bet: The winners and losers from the OpenAI-Hugging Face hacking mess</t>
         </is>
       </c>
       <c r="J15" s="60" t="inlineStr">
         <is>
-          <t>Zoom Technologies has launched a new live voice translation service, with Arabic support coming in the fourth quarter of this year. Five languages – English, Chinese, French, Japanese and Spanish – will initially be available, the California-based company said. A Zoom representative confirmed to The National that Arabic will be available in the fourth quarter, alongside German, Italian and Portuguese. Zoom launched a version of the service in April, after promoting it at its Zoomtopia conference last September. Using the live voice translation feature requires a Pro, Business, or Enterprise account, the artificial intelligence plug-in ZoomMate, or a stand-alone add-on. Zoom has posted instr…</t>
+          <t>When OpenAI revealed this week that one of its AI models went rogue during a security test and autonomously hacked the start-up Hugging Face, it came as a shock. Questions were raised quickly, but there was no immediate clarity. Hugging Face co-founder and chief executive Clem Delangue said the incident was "possibly the first of its kind". As with any serious tech incident, there are those who stand to gain and other who stand to lose. And the circumstances can be as complex as the hacking is. Losers: OpenAI and Hugging Face Let's start with the obvious matter. It was a PR nightmare for ChatGPT maker OpenAI, as well as Hugging Face, as they bore the brunt of the mess, albeit for different…</t>
         </is>
       </c>
       <c r="K15" s="60" t="inlineStr">
         <is>
-          <t>https://www.thenationalnews.com/future/technology/2026/07/24/zoom-launches-live-voice-translation-with-arabic-coming-in-late-2026/</t>
+          <t>https://www.thenationalnews.com/future/technology/2026/07/25/risky-bet-the-winners-and-losers-from-the-openai-hugging-face-hacking-mess/</t>
         </is>
       </c>
       <c r="L15" s="60" t="inlineStr">
         <is>
-          <t>9df818f0442aeef1a46447c7</t>
+          <t>ae772fcc12d71afd038c86c2</t>
         </is>
       </c>
       <c r="M15" s="75" t="inlineStr">
@@ -2073,7 +2073,7 @@
       </c>
       <c r="B16" s="75" t="inlineStr">
         <is>
-          <t>2026-07-24T04:34:27Z</t>
+          <t>2026-07-25T05:00:35Z</t>
         </is>
       </c>
       <c r="C16" s="60" t="inlineStr">
@@ -2083,12 +2083,12 @@
       </c>
       <c r="D16" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="E16" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence | Semiconductors &amp; Telecom</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="F16" s="76" t="n">
@@ -2096,32 +2096,32 @@
       </c>
       <c r="G16" s="60" t="inlineStr">
         <is>
-          <t>Official Company</t>
+          <t>Major Media</t>
         </is>
       </c>
       <c r="H16" s="60" t="inlineStr">
         <is>
-          <t>NVIDIA Blog</t>
+          <t>The Guardian Technology</t>
         </is>
       </c>
       <c r="I16" s="60" t="inlineStr">
         <is>
-          <t>At AI Summit, South Korea Outlines Its AI Future With NVIDIA and Partners</t>
+          <t>‘I thought, I’ve tried everything else, why not give AI a shot?’: the long-lost family reunited by ChatGPT</t>
         </is>
       </c>
       <c r="J16" s="60" t="inlineStr">
         <is>
-          <t>At this week’s AI Summit in San Francisco, South Korean President Jae Myung Lee and some of the country’s top business leaders and researchers are meeting with NVIDIA and ecosystem partners to chart Korea’s AI progress. Building on NVIDIA founder and CEO Jensen Huang’s visit to Korea last month, this week’s discussions and announcements advance […]</t>
+          <t>Avtar spent decades wondering what happened to the mother he never got to know. Thousands of miles away, Nicci was haunted by the story of a half-brother given away before she was born. How did a chatbot bring them together? As a small boy growing up in Amritsar, India, in the 1960s, Avtar Singh used to hear whispers. Your mum isn’t really your mum , the rumours would say. Your mum lives abroad. Avtar didn’t really pay any attention to it. “I thought, the neighbours are just making up stories.” But the stories were true: the woman raising Avtar was actually his grandmother. When he was too young to remember it, his father had emigrated to Canada to work as a teacher, leaving Avtar in the ca…</t>
         </is>
       </c>
       <c r="K16" s="60" t="inlineStr">
         <is>
-          <t>https://blogs.nvidia.com/blog/ai-summit-korea-partners-and-nvidia/</t>
+          <t>https://www.theguardian.com/lifeandstyle/ng-interactive/2026/jul/25/long-lost-family-reunited-chatgpt-artificial-intelligence-ai</t>
         </is>
       </c>
       <c r="L16" s="60" t="inlineStr">
         <is>
-          <t>3124530844eb0ac80a5a17e4</t>
+          <t>818d7fcb63b548448b301aec</t>
         </is>
       </c>
       <c r="M16" s="75" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="B17" s="75" t="inlineStr">
         <is>
-          <t>2026-07-24T00:00:00Z</t>
+          <t>2026-07-24T18:00:01Z</t>
         </is>
       </c>
       <c r="C17" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="D17" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E17" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Semiconductors &amp; Telecom</t>
         </is>
       </c>
       <c r="F17" s="76" t="n">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="G17" s="60" t="inlineStr">
         <is>
-          <t>Scientific Publication</t>
+          <t>Major Media</t>
         </is>
       </c>
       <c r="H17" s="60" t="inlineStr">
         <is>
-          <t>Nature</t>
+          <t>IEEE Spectrum</t>
         </is>
       </c>
       <c r="I17" s="60" t="inlineStr">
         <is>
-          <t>Briefing Chat: Baby &lt;i&gt;T. rex&lt;/i&gt; were killers from birth, suggest new fossils</t>
+          <t>2022 IEEE President K.J. Ray Liu Honored for His Leadership</t>
         </is>
       </c>
       <c r="J17" s="60" t="inlineStr">
         <is>
-          <t>Nature, Published online: 24 July 2026; doi:10.1038/d41586-026-02338-2 Nature staff discuss the young but deadly dinosaur kings, the prowess of ancient Egyptian princesses, and how London is becoming the world’s AI safety capital.</t>
+          <t>Unlike many budding engineers, K.J. Ray Liu wasn’t inspired to enter the field by tinkering with electronics or following in the footsteps of a family member. Growing up in Taichung, Taiwan, he answered his government’s call for students to become electrical engineers to help manufacture semiconductors in the 1970s, when the country’s economy was struggling. “Students who were good in math, science, and physics all wanted to be an electrical engineer because that was the top priority of the government,” Liu says. “That’s how I got into engineering. Now Taiwan is a world leader in semiconductors.” K.J. Ray Liu Occupation Retired professor of information technology and a digital signal proces…</t>
         </is>
       </c>
       <c r="K17" s="60" t="inlineStr">
         <is>
-          <t>https://www.nature.com/articles/d41586-026-02338-2</t>
+          <t>https://spectrum.ieee.org/ieee-president-ray-liu-award</t>
         </is>
       </c>
       <c r="L17" s="60" t="inlineStr">
         <is>
-          <t>d9ad7c48684afc35a7223f91</t>
+          <t>87b839503197ad74fc686cf1</t>
         </is>
       </c>
       <c r="M17" s="75" t="inlineStr">
@@ -2210,27 +2210,27 @@
     <row r="18" ht="42" customHeight="1">
       <c r="A18" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T19:10:55+09:00</t>
         </is>
       </c>
       <c r="B18" s="75" t="inlineStr">
         <is>
-          <t>2026-07-24T00:00:00Z</t>
+          <t>2026-07-24T17:32:29Z</t>
         </is>
       </c>
       <c r="C18" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D18" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United Arab Emirates</t>
         </is>
       </c>
       <c r="E18" s="60" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="F18" s="76" t="n">
@@ -2238,37 +2238,37 @@
       </c>
       <c r="G18" s="60" t="inlineStr">
         <is>
-          <t>Scientific Publication</t>
+          <t>Major Media</t>
         </is>
       </c>
       <c r="H18" s="60" t="inlineStr">
         <is>
-          <t>Nature</t>
+          <t>The National Technology</t>
         </is>
       </c>
       <c r="I18" s="60" t="inlineStr">
         <is>
-          <t>Bizarre CRISPR enzyme kills cancer cells by shredding their DNA</t>
+          <t>Nvidia, Microsoft and IBM among companies endorsing open-weight AI models</t>
         </is>
       </c>
       <c r="J18" s="60" t="inlineStr">
         <is>
-          <t>Nature, Published online: 24 July 2026; doi:10.1038/d41586-026-02268-z Early tests suggest the protein can be aimed at targets with tumour-causing mutations.</t>
+          <t>Nvidia chief executive Jensen Huang joined X on Friday and used his first post to champion AI models that can be downloaded and adapted, arguing they are vital to preserving America’s lead in artificial intelligence. Mr Huang attached a letter signed by 25 major companies, including Microsoft, Palantir , Perplexity, CrowdStrike and IBM that endorsed open-source software development and “open-weight” AI models. Some US officials have raised concerns that AI models could pose national security risks, while companies such as OpenAI and Anthropic still largely oppose open architecture for proprietary reasons. “Open source did more than lower the cost of software; it created a shared foundation…</t>
         </is>
       </c>
       <c r="K18" s="60" t="inlineStr">
         <is>
-          <t>https://www.nature.com/articles/d41586-026-02268-z</t>
+          <t>https://www.thenationalnews.com/future/technology/2026/07/24/open-weight-models-ai-nvidia/</t>
         </is>
       </c>
       <c r="L18" s="60" t="inlineStr">
         <is>
-          <t>006500c385193d3a42b6ae61</t>
+          <t>258e9b19598256f555ff9019</t>
         </is>
       </c>
       <c r="M18" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T19:10:55+09:00</t>
         </is>
       </c>
       <c r="N18" s="60" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="B19" s="75" t="inlineStr">
         <is>
-          <t>2026-07-23T20:01:35Z</t>
+          <t>2026-07-24T17:03:55Z</t>
         </is>
       </c>
       <c r="C19" s="60" t="inlineStr">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="E19" s="60" t="inlineStr">
         <is>
-          <t>Semiconductors &amp; Telecom</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="F19" s="76" t="n">
@@ -2309,32 +2309,32 @@
       </c>
       <c r="G19" s="60" t="inlineStr">
         <is>
-          <t>Official Company</t>
+          <t>Major Media</t>
         </is>
       </c>
       <c r="H19" s="60" t="inlineStr">
         <is>
-          <t>Intel Newsroom</t>
+          <t>MIT Technology Review</t>
         </is>
       </c>
       <c r="I19" s="60" t="inlineStr">
         <is>
-          <t>Intel Reports Second-Quarter 2026 Financial Results</t>
+          <t>The quest to keep organs alive outside the body</t>
         </is>
       </c>
       <c r="J19" s="60" t="inlineStr">
         <is>
-          <t>Intel Corporation’s second-quarter 2026 earnings news release and presentation are available on the company’s Investor Relations website. The earnings conference call for investors begins at 2 p.m. PDT today; a public webcast will be available at www.intc.com.More: Earnings News Release | Earnings Call Comments from CEO Lip-Bu Tan and CFO Dave Zinsner The post Intel Reports Second-Quarter 2026 Financial Results appeared first on Newsroom .</t>
+          <t>This week, I covered a fascinating effort to preserve organs outside the body. There’s a huge shortage of donor organs, and one of the main reasons is time—they survive only a matter of hours outside the body, even when they’re kept on ice. Doctors dream of organ banks—stores of human organs that can be preserved…</t>
         </is>
       </c>
       <c r="K19" s="60" t="inlineStr">
         <is>
-          <t>https://newsroom.intel.com/corporate/intel-reports-second-quarter-2026-financial-results</t>
+          <t>https://www.technologyreview.com/2026/07/24/1140790/the-quest-to-keep-organs-alive-outside-the-body/</t>
         </is>
       </c>
       <c r="L19" s="60" t="inlineStr">
         <is>
-          <t>bd78c44bc1aa5dc9d72bde44</t>
+          <t>039c84226e8803400ce67975</t>
         </is>
       </c>
       <c r="M19" s="75" t="inlineStr">
@@ -2357,22 +2357,22 @@
       </c>
       <c r="B20" s="75" t="inlineStr">
         <is>
-          <t>2026-07-23T19:56:50Z</t>
+          <t>2026-07-24T16:46:59Z</t>
         </is>
       </c>
       <c r="C20" s="60" t="inlineStr">
         <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D20" s="60" t="inlineStr">
+        <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="D20" s="60" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
       <c r="E20" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Semiconductors &amp; Telecom</t>
         </is>
       </c>
       <c r="F20" s="76" t="n">
@@ -2380,32 +2380,32 @@
       </c>
       <c r="G20" s="60" t="inlineStr">
         <is>
-          <t>Major Media</t>
+          <t>Official Company</t>
         </is>
       </c>
       <c r="H20" s="60" t="inlineStr">
         <is>
-          <t>The Guardian Technology</t>
+          <t>Intel Newsroom</t>
         </is>
       </c>
       <c r="I20" s="60" t="inlineStr">
         <is>
-          <t>Trump says nearly 200 firms have signed pledge to protect Americans from costs arising from datacenters</t>
+          <t>Intel and Lens Technology Collaborate to Enable Advanced Semiconductor Packaging for the AI Era</t>
         </is>
       </c>
       <c r="J20" s="60" t="inlineStr">
         <is>
-          <t>‘Ratepayer Protection Pledge’ president has touted is non-binding as people continue to struggle with rising bills Donald Trump has announced that about 200 entities have signed on to his non-binding “Ratepayer Protection Pledge”, expanding a voluntary commitment which claims to ensure US consumers will not bear the cost of the AI datacenter build-out. Trump delivered remarks on Thursday at the Environmental Protection Agency (EPA) headquarters, alongside Lee Zeldin, the agency’s administrator, and Chris Wright, the energy secretary. Other attenders included governors who signed on to the pledge, including Brian Kemp of Georgia, Mike DeWine of Ohio, Spencer Cox of Utah and Jeff Landry of Lo…</t>
+          <t>SANTA CLARA, Calif. &amp; CHANGSHA, China — Intel Corporation and Lens Technology today announced a strategic collaboration focused on enabling new technologies for advanced semiconductor packaging. Through this work, the companies intend to explore opportunities to accelerate the development of glass substrate-based packaging solutions that can help enable higher performance, increased interconnect density, and improved … The post Intel and Lens Technology Collaborate to Enable Advanced Semiconductor Packaging for the AI Era appeared first on Newsroom .</t>
         </is>
       </c>
       <c r="K20" s="60" t="inlineStr">
         <is>
-          <t>https://www.theguardian.com/us-news/2026/jul/23/trump-datacenter-costs-big-tech</t>
+          <t>https://newsroom.intel.com/new-technologies/intel-and-lens-technology-collaborate-to-enable-advanced-semiconductor-packaging-for-the-ai-era</t>
         </is>
       </c>
       <c r="L20" s="60" t="inlineStr">
         <is>
-          <t>1ede7beb496d94bde434264e</t>
+          <t>10eedf14d7d6b636e24e447d</t>
         </is>
       </c>
       <c r="M20" s="75" t="inlineStr">
@@ -2428,55 +2428,55 @@
       </c>
       <c r="B21" s="75" t="inlineStr">
         <is>
-          <t>2026-07-23T18:00:00Z</t>
+          <t>2026-07-24T15:25:30Z</t>
         </is>
       </c>
       <c r="C21" s="60" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>EU &amp; Europe</t>
         </is>
       </c>
       <c r="D21" s="60" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="E21" s="60" t="inlineStr">
         <is>
-          <t>Semiconductors &amp; Telecom</t>
+          <t>Innovation Policy</t>
         </is>
       </c>
       <c r="F21" s="76" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G21" s="60" t="inlineStr">
         <is>
-          <t>Official Company</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H21" s="60" t="inlineStr">
         <is>
-          <t>Samsung Global Newsroom</t>
+          <t>UK DSIT</t>
         </is>
       </c>
       <c r="I21" s="60" t="inlineStr">
         <is>
-          <t>[Infographic] [Galaxy Unpacked July 2026] Highlights From Galaxy Unpacked</t>
+          <t>Guidance: Cyber Resilience Pledge - list of signatories</t>
         </is>
       </c>
       <c r="J21" s="60" t="inlineStr">
         <is>
-          <t>On July 22, Samsung Electronics hosted Galaxy Unpacked July 2026 at Old Billingsgate in London — unveiling its next-generation foldables with agentic AI. Alongside Galaxy Z Fold8 Ultra, Galaxy Z Fold8 and Galaxy Z Flip8, Samsung introduced Galaxy Watch Ultra2 and Galaxy Watch9 with more advanced health features, as well as intelligent eyewear. Through a […]</t>
+          <t>Organisations that have signed the Cyber Resilience Pledge.</t>
         </is>
       </c>
       <c r="K21" s="60" t="inlineStr">
         <is>
-          <t>https://news.samsung.com/global/infographic-galaxy-unpacked-july-2026-highlights-from-galaxy-unpacked</t>
+          <t>https://www.gov.uk/government/publications/cyber-resilience-pledge-list-of-signatories</t>
         </is>
       </c>
       <c r="L21" s="60" t="inlineStr">
         <is>
-          <t>ee2b658cb0dfffbcc854ebab</t>
+          <t>556f1cad5674dfe48a261c54</t>
         </is>
       </c>
       <c r="M21" s="75" t="inlineStr">
@@ -2494,12 +2494,12 @@
     <row r="22" ht="42" customHeight="1">
       <c r="A22" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T19:51:39+09:00</t>
         </is>
       </c>
       <c r="B22" s="75" t="inlineStr">
         <is>
-          <t>2026-07-23T16:58:28Z</t>
+          <t>2026-07-24T13:00:14Z</t>
         </is>
       </c>
       <c r="C22" s="60" t="inlineStr">
@@ -2509,12 +2509,12 @@
       </c>
       <c r="D22" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="E22" s="60" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="F22" s="76" t="n">
@@ -2527,32 +2527,32 @@
       </c>
       <c r="H22" s="60" t="inlineStr">
         <is>
-          <t>MIT Technology Review</t>
+          <t>The Guardian Technology</t>
         </is>
       </c>
       <c r="I22" s="60" t="inlineStr">
         <is>
-          <t>Supercooled kidneys have been transplanted into pigs in a “landmark achievement”</t>
+          <t>Be skeptical of OpenAI’s rogue hacker agent story | John Thickstun</t>
         </is>
       </c>
       <c r="J22" s="60" t="inlineStr">
         <is>
-          <t>When it comes to organ donation, time is everything. As soon as an organ has been carefully removed from a donor’s body, it starts to deteriorate. Surgeons have a matter of hours to get it into a recipient. Leave it too long and the organ will become unusable. In most cases, organs will be kept…</t>
+          <t>If OpenAI loudly proclaims how dangerous AI is, investors will hear how powerful it is. And who benefits from that? On 14 February 2019, OpenAI announced a language model called GPT-2, the precursor to the models that power modern AI chatbots and agents such as ChatGPT and Claude. But OpenAI declared GPT-2 was too risky to release, citing concerns about safety and abuse. I recall being annoyed at the time that OpenAI would make such a useless announcement: the risks seemed overblown, and without access to the model there wasn’t much for a researcher like me to learn about GPT-2. Continue reading...</t>
         </is>
       </c>
       <c r="K22" s="60" t="inlineStr">
         <is>
-          <t>https://www.technologyreview.com/2026/07/23/1140765/supercooled-kidneys-have-been-transplanted-into-pigs-in-a-landmark-achievement/</t>
+          <t>https://www.theguardian.com/technology/2026/jul/24/openai-rogue-hacker</t>
         </is>
       </c>
       <c r="L22" s="60" t="inlineStr">
         <is>
-          <t>590a8cbd726d99d379ccecb1</t>
+          <t>ac01b28f85e133214755b7cc</t>
         </is>
       </c>
       <c r="M22" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T19:51:39+09:00</t>
         </is>
       </c>
       <c r="N22" s="60" t="inlineStr">
@@ -2570,12 +2570,12 @@
       </c>
       <c r="B23" s="75" t="inlineStr">
         <is>
-          <t>2026-07-23T16:45:56Z</t>
+          <t>2026-07-24T12:00:14Z</t>
         </is>
       </c>
       <c r="C23" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="D23" s="60" t="inlineStr">
@@ -2603,22 +2603,22 @@
       </c>
       <c r="I23" s="60" t="inlineStr">
         <is>
-          <t>Customers prefer AI chatbots, says British Gas owner as 1,300 call centre and back office jobs axed</t>
+          <t>Should you use AI for a task? Here’s a simple way to decide | Bruce Schneier</t>
         </is>
       </c>
       <c r="J23" s="60" t="inlineStr">
         <is>
-          <t>CEO Chris O’Shea defends Centrica’s plans as it reports rise in retail profits following focus on bigger margins The owner of British Gas has claimed that most households would rather speak with an AI chatbot than deal with the company’s staff as it prepares to cut 1,300 jobs from its call centres and back office. Centrica, the supplier’s FTSE 100 owner, plans to cut 800 jobs as the company carries out a “targeted deployment of AI tools”, on top of the 500 cuts it confirmed last month. Continue reading...</t>
+          <t>Sometimes, what matters isn’t your output but what you put into the process. Think of it like work v the gym I teach public policy at the Harvard Kennedy School and the Munk School at the University of Toronto. And it will come as no surprise to you that my students regularly use AI to complete their writing assignments. Doing so is a waste of their tuition money. But if their entire career is going to include AI writing assistants, why shouldn’t they embrace their future? The best way I’ve found to explain the dilemma comes from the AI researcher Daniel Meissler: it’s the difference between work and the gym. Continue reading...</t>
         </is>
       </c>
       <c r="K23" s="60" t="inlineStr">
         <is>
-          <t>https://www.theguardian.com/business/2026/jul/23/customers-prefer-ai-chatbots-says-chris-oshea-british-gas-centrica-boss</t>
+          <t>https://www.theguardian.com/commentisfree/2026/jul/24/should-you-use-ai</t>
         </is>
       </c>
       <c r="L23" s="60" t="inlineStr">
         <is>
-          <t>2ef05538ad59fc3911318d3f</t>
+          <t>d7259db0d54f48b0f5039bb8</t>
         </is>
       </c>
       <c r="M23" s="75" t="inlineStr">
@@ -2636,12 +2636,12 @@
     <row r="24" ht="42" customHeight="1">
       <c r="A24" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T19:10:55+09:00</t>
         </is>
       </c>
       <c r="B24" s="75" t="inlineStr">
         <is>
-          <t>2026-07-23T16:00:00Z</t>
+          <t>2026-07-24T11:39:05Z</t>
         </is>
       </c>
       <c r="C24" s="60" t="inlineStr">
@@ -2651,12 +2651,12 @@
       </c>
       <c r="D24" s="60" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>United Arab Emirates</t>
         </is>
       </c>
       <c r="E24" s="60" t="inlineStr">
         <is>
-          <t>Semiconductors &amp; Telecom | Healthcare</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="F24" s="76" t="n">
@@ -2664,37 +2664,37 @@
       </c>
       <c r="G24" s="60" t="inlineStr">
         <is>
-          <t>Official Company</t>
+          <t>Major Media</t>
         </is>
       </c>
       <c r="H24" s="60" t="inlineStr">
         <is>
-          <t>Samsung Global Newsroom</t>
+          <t>The National Technology</t>
         </is>
       </c>
       <c r="I24" s="60" t="inlineStr">
         <is>
-          <t>[Galaxy Unpacked July 2026] Samsung and Partners Envision a Connected Care Future — From First Signal to Lasting Change</t>
+          <t>Zoom launches live voice translation, with Arabic coming in late 2026</t>
         </is>
       </c>
       <c r="J24" s="60" t="inlineStr">
         <is>
-          <t>At Galaxy Unpacked July 2026 in London, Samsung Electronics set out its vision for the next chapter of digital health — a future where care moves from reactive treatment toward preventive, personalized and connected experiences, supported by trusted health innovation and partnerships across the healthcare ecosystem. To explore that vision, Samsung hosted a Health Forum […]</t>
+          <t>Zoom Technologies has launched a new live voice translation service, with Arabic support coming in the fourth quarter of this year. Five languages – English, Chinese, French, Japanese and Spanish – will initially be available, the California-based company said. A Zoom representative confirmed to The National that Arabic will be available in the fourth quarter, alongside German, Italian and Portuguese. Zoom launched a version of the service in April, after promoting it at its Zoomtopia conference last September. Using the live voice translation feature requires a Pro, Business, or Enterprise account, the artificial intelligence plug-in ZoomMate, or a stand-alone add-on. Zoom has posted instr…</t>
         </is>
       </c>
       <c r="K24" s="60" t="inlineStr">
         <is>
-          <t>https://news.samsung.com/global/galaxy-unpacked-july-2026-samsung-and-partners-envision-a-connected-care-future-from-first-signal-to-lasting-change</t>
+          <t>https://www.thenationalnews.com/future/technology/2026/07/24/zoom-launches-live-voice-translation-with-arabic-coming-in-late-2026/</t>
         </is>
       </c>
       <c r="L24" s="60" t="inlineStr">
         <is>
-          <t>032ebcb3943c83074eb9bcf5</t>
+          <t>9df818f0442aeef1a46447c7</t>
         </is>
       </c>
       <c r="M24" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T19:10:55+09:00</t>
         </is>
       </c>
       <c r="N24" s="60" t="inlineStr">
@@ -2712,55 +2712,55 @@
       </c>
       <c r="B25" s="75" t="inlineStr">
         <is>
-          <t>2026-07-23T15:27:52Z</t>
+          <t>2026-07-24T04:34:27Z</t>
         </is>
       </c>
       <c r="C25" s="60" t="inlineStr">
         <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D25" s="60" t="inlineStr">
+        <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="D25" s="60" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
       <c r="E25" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Artificial Intelligence | Semiconductors &amp; Telecom</t>
         </is>
       </c>
       <c r="F25" s="76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G25" s="60" t="inlineStr">
         <is>
-          <t>Major Media</t>
+          <t>Official Company</t>
         </is>
       </c>
       <c r="H25" s="60" t="inlineStr">
         <is>
-          <t>The Guardian Technology</t>
+          <t>NVIDIA Blog</t>
         </is>
       </c>
       <c r="I25" s="60" t="inlineStr">
         <is>
-          <t>Elon Musk says he got ‘carried away’ with Trump – but still holds on to contentious political views</t>
+          <t>At AI Summit, South Korea Outlines Its AI Future With NVIDIA and Partners</t>
         </is>
       </c>
       <c r="J25" s="60" t="inlineStr">
         <is>
-          <t>In interview, billionaire says instead of running ‘Doge’ he should’ve ‘worked on my companies’ and shares extreme predictions Elon Musk has admitted he became too consumed by politics during his volatile alliance with Donald Trump and his brief appointment as the president’s financial axman, running the so-called “department of government efficiency” (Doge). The world’s richest person, and briefly its first trillionaire after his SpaceX company floated on the New York stock exchange in June, made the confession in a wide-ranging interview with the Economist published on Thursday. He shared his positions on subjects from foreign wars to AI, and made a number of eye-opening predictions for th…</t>
+          <t>At this week’s AI Summit in San Francisco, South Korean President Jae Myung Lee and some of the country’s top business leaders and researchers are meeting with NVIDIA and ecosystem partners to chart Korea’s AI progress. Building on NVIDIA founder and CEO Jensen Huang’s visit to Korea last month, this week’s discussions and announcements advance […]</t>
         </is>
       </c>
       <c r="K25" s="60" t="inlineStr">
         <is>
-          <t>https://www.theguardian.com/technology/2026/jul/23/elon-musk-regret-trump-doge-ai</t>
+          <t>https://blogs.nvidia.com/blog/ai-summit-korea-partners-and-nvidia/</t>
         </is>
       </c>
       <c r="L25" s="60" t="inlineStr">
         <is>
-          <t>5ab5ea23fbff158109e679af</t>
+          <t>3124530844eb0ac80a5a17e4</t>
         </is>
       </c>
       <c r="M25" s="75" t="inlineStr">
@@ -2783,7 +2783,7 @@
       </c>
       <c r="B26" s="75" t="inlineStr">
         <is>
-          <t>2026-07-23T15:00:48Z</t>
+          <t>2026-07-24T00:00:00Z</t>
         </is>
       </c>
       <c r="C26" s="60" t="inlineStr">
@@ -2793,45 +2793,45 @@
       </c>
       <c r="D26" s="60" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="E26" s="60" t="inlineStr">
         <is>
-          <t>Innovation Policy</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="F26" s="76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G26" s="60" t="inlineStr">
         <is>
-          <t>Major Media</t>
+          <t>Scientific Publication</t>
         </is>
       </c>
       <c r="H26" s="60" t="inlineStr">
         <is>
-          <t>The Guardian Technology</t>
+          <t>Nature</t>
         </is>
       </c>
       <c r="I26" s="60" t="inlineStr">
         <is>
-          <t>The roaring 20s: how the current decade revolutionised cinema</t>
+          <t>Briefing Chat: Baby &lt;i&gt;T. rex&lt;/i&gt; were killers from birth, suggest new fossils</t>
         </is>
       </c>
       <c r="J26" s="60" t="inlineStr">
         <is>
-          <t>Pre-Covid, the movie landscape was dramatically different: YouTubers weren’t dominating the box office, video game spin-offs rarely made an impact and Winnie-the-Pooh wasn’t yet the star of a slasher movie. Why such a flurry of innovation – and what will be next? Cinema has always been a medium of research and development. At any given point, the industry is searching for yet another breakthrough that can drive it into the future. Synchronised sound in the 1920s. Technicolor in the 1930s. The invention of the modern blockbuster in the 1970s. Conversely, the consensus is that, if the 2020s has a defining trend, then it is one of decline. The theatrical experience is under attack from all ang…</t>
+          <t>Nature, Published online: 24 July 2026; doi:10.1038/d41586-026-02338-2 Nature staff discuss the young but deadly dinosaur kings, the prowess of ancient Egyptian princesses, and how London is becoming the world’s AI safety capital.</t>
         </is>
       </c>
       <c r="K26" s="60" t="inlineStr">
         <is>
-          <t>https://www.theguardian.com/film/2026/jul/23/how-2020s-decade-revolutionised-cinema</t>
+          <t>https://www.nature.com/articles/d41586-026-02338-2</t>
         </is>
       </c>
       <c r="L26" s="60" t="inlineStr">
         <is>
-          <t>f8939f05439f07fdefca04fc</t>
+          <t>d9ad7c48684afc35a7223f91</t>
         </is>
       </c>
       <c r="M26" s="75" t="inlineStr">
@@ -2854,7 +2854,7 @@
       </c>
       <c r="B27" s="75" t="inlineStr">
         <is>
-          <t>2026-07-23T13:00:16Z</t>
+          <t>2026-07-24T00:00:00Z</t>
         </is>
       </c>
       <c r="C27" s="60" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="D27" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="E27" s="60" t="inlineStr">
         <is>
-          <t>Semiconductors &amp; Telecom</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="F27" s="76" t="n">
@@ -2877,32 +2877,32 @@
       </c>
       <c r="G27" s="60" t="inlineStr">
         <is>
-          <t>Official Company</t>
+          <t>Scientific Publication</t>
         </is>
       </c>
       <c r="H27" s="60" t="inlineStr">
         <is>
-          <t>NVIDIA Blog</t>
+          <t>Nature</t>
         </is>
       </c>
       <c r="I27" s="60" t="inlineStr">
         <is>
-          <t>GeForce NOW Sets Sail With ‘Path of Exile: Curse of the Allflame’ Joining the Cloud</t>
+          <t>Bizarre CRISPR enzyme kills cancer cells by shredding their DNA</t>
         </is>
       </c>
       <c r="J27" s="60" t="inlineStr">
         <is>
-          <t>Lock in and load up the cloud. GFN Thursday brings fresh updates and new adventures, all ready to play without waiting for downloads. Set sail in Path of Exile: Curse of the Allflame and charge in Battlefield 6 Season 4 both launching major content for members this week. Then revisit Capcom legends like Breath of […]</t>
+          <t>Nature, Published online: 24 July 2026; doi:10.1038/d41586-026-02268-z Early tests suggest the protein can be aimed at targets with tumour-causing mutations.</t>
         </is>
       </c>
       <c r="K27" s="60" t="inlineStr">
         <is>
-          <t>https://blogs.nvidia.com/blog/geforce-now-thursday-path-of-exile-allflame/</t>
+          <t>https://www.nature.com/articles/d41586-026-02268-z</t>
         </is>
       </c>
       <c r="L27" s="60" t="inlineStr">
         <is>
-          <t>d6df6c9a47b33117f5bcb1be</t>
+          <t>006500c385193d3a42b6ae61</t>
         </is>
       </c>
       <c r="M27" s="75" t="inlineStr">
@@ -2925,7 +2925,7 @@
       </c>
       <c r="B28" s="75" t="inlineStr">
         <is>
-          <t>2026-07-23T12:00:00Z</t>
+          <t>2026-07-23T20:01:35Z</t>
         </is>
       </c>
       <c r="C28" s="60" t="inlineStr">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="E28" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence | Healthcare</t>
+          <t>Semiconductors &amp; Telecom</t>
         </is>
       </c>
       <c r="F28" s="76" t="n">
@@ -2948,32 +2948,32 @@
       </c>
       <c r="G28" s="60" t="inlineStr">
         <is>
-          <t>Major Media</t>
+          <t>Official Company</t>
         </is>
       </c>
       <c r="H28" s="60" t="inlineStr">
         <is>
-          <t>MIT Technology Review</t>
+          <t>Intel Newsroom</t>
         </is>
       </c>
       <c r="I28" s="60" t="inlineStr">
         <is>
-          <t>How AI helps scientists design the next generation of medicines</t>
+          <t>Intel Reports Second-Quarter 2026 Financial Results</t>
         </is>
       </c>
       <c r="J28" s="60" t="inlineStr">
         <is>
-          <t>Designing and developing a new medicine is an expensive, failure-prone scientific challenge. A new drug can take many years to develop, at the cost of a significant investment. And even then, most possible candidates never reach the patient. For biologic medicines, therapies made from engineered proteins rather than synthetic chemistry (which are often used to…</t>
+          <t>Intel Corporation’s second-quarter 2026 earnings news release and presentation are available on the company’s Investor Relations website. The earnings conference call for investors begins at 2 p.m. PDT today; a public webcast will be available at www.intc.com.More: Earnings News Release | Earnings Call Comments from CEO Lip-Bu Tan and CFO Dave Zinsner The post Intel Reports Second-Quarter 2026 Financial Results appeared first on Newsroom .</t>
         </is>
       </c>
       <c r="K28" s="60" t="inlineStr">
         <is>
-          <t>https://www.technologyreview.com/2026/07/23/1140346/how-ai-helps-scientists-design-the-next-generation-of-medicines/</t>
+          <t>https://newsroom.intel.com/corporate/intel-reports-second-quarter-2026-financial-results</t>
         </is>
       </c>
       <c r="L28" s="60" t="inlineStr">
         <is>
-          <t>f283b79f845eeb45783eb41c</t>
+          <t>bd78c44bc1aa5dc9d72bde44</t>
         </is>
       </c>
       <c r="M28" s="75" t="inlineStr">
@@ -2996,55 +2996,55 @@
       </c>
       <c r="B29" s="75" t="inlineStr">
         <is>
-          <t>2026-07-23T09:23:23Z</t>
+          <t>2026-07-23T19:56:50Z</t>
         </is>
       </c>
       <c r="C29" s="60" t="inlineStr">
         <is>
-          <t>EU &amp; Europe</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D29" s="60" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="E29" s="60" t="inlineStr">
         <is>
-          <t>Innovation Policy</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="F29" s="76" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G29" s="60" t="inlineStr">
         <is>
-          <t>Policy Institute</t>
+          <t>Major Media</t>
         </is>
       </c>
       <c r="H29" s="60" t="inlineStr">
         <is>
-          <t>Bruegel</t>
+          <t>The Guardian Technology</t>
         </is>
       </c>
       <c r="I29" s="60" t="inlineStr">
         <is>
-          <t>Session 2b: Can the EU's better regulation agenda deliver competitiveness?</t>
+          <t>Trump says nearly 200 firms have signed pledge to protect Americans from costs arising from datacenters</t>
         </is>
       </c>
       <c r="J29" s="60" t="inlineStr">
         <is>
-          <t>Session 2b: Can the EU's better regulation agenda deliver competitiveness? Chiara Montanaro Thu, 07/23/2026 - 11:23 Chiara Montanaro Thu, 07/23/2026 - 11:23</t>
+          <t>‘Ratepayer Protection Pledge’ president has touted is non-binding as people continue to struggle with rising bills Donald Trump has announced that about 200 entities have signed on to his non-binding “Ratepayer Protection Pledge”, expanding a voluntary commitment which claims to ensure US consumers will not bear the cost of the AI datacenter build-out. Trump delivered remarks on Thursday at the Environmental Protection Agency (EPA) headquarters, alongside Lee Zeldin, the agency’s administrator, and Chris Wright, the energy secretary. Other attenders included governors who signed on to the pledge, including Brian Kemp of Georgia, Mike DeWine of Ohio, Spencer Cox of Utah and Jeff Landry of Lo…</t>
         </is>
       </c>
       <c r="K29" s="60" t="inlineStr">
         <is>
-          <t>https://www.bruegel.org/node/12451</t>
+          <t>https://www.theguardian.com/us-news/2026/jul/23/trump-datacenter-costs-big-tech</t>
         </is>
       </c>
       <c r="L29" s="60" t="inlineStr">
         <is>
-          <t>90ef16bcfe1bd00925658dc5</t>
+          <t>1ede7beb496d94bde434264e</t>
         </is>
       </c>
       <c r="M29" s="75" t="inlineStr">
@@ -3067,55 +3067,55 @@
       </c>
       <c r="B30" s="75" t="inlineStr">
         <is>
-          <t>2026-07-23T08:00:24Z</t>
+          <t>2026-07-23T18:00:00Z</t>
         </is>
       </c>
       <c r="C30" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="D30" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="E30" s="60" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Semiconductors &amp; Telecom</t>
         </is>
       </c>
       <c r="F30" s="76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G30" s="60" t="inlineStr">
         <is>
-          <t>Intergovernmental</t>
+          <t>Official Company</t>
         </is>
       </c>
       <c r="H30" s="60" t="inlineStr">
         <is>
-          <t>WHO News</t>
+          <t>Samsung Global Newsroom</t>
         </is>
       </c>
       <c r="I30" s="60" t="inlineStr">
         <is>
-          <t>WHO launches seven strategies to prevent drowning</t>
+          <t>[Infographic] [Galaxy Unpacked July 2026] Highlights From Galaxy Unpacked</t>
         </is>
       </c>
       <c r="J30" s="60" t="inlineStr">
         <is>
-          <t>Ahead of World Drowning Prevention Day on 25 July, the World Health Organization (WHO) is launching a new technical package to help governments and communities implement seven proven measures to reduce drowning deaths.</t>
+          <t>On July 22, Samsung Electronics hosted Galaxy Unpacked July 2026 at Old Billingsgate in London — unveiling its next-generation foldables with agentic AI. Alongside Galaxy Z Fold8 Ultra, Galaxy Z Fold8 and Galaxy Z Flip8, Samsung introduced Galaxy Watch Ultra2 and Galaxy Watch9 with more advanced health features, as well as intelligent eyewear. Through a […]</t>
         </is>
       </c>
       <c r="K30" s="60" t="inlineStr">
         <is>
-          <t>https://www.who.int/news/item/23-07-2026-who-launches-seven-strategies-to-prevent-drowning</t>
+          <t>https://news.samsung.com/global/infographic-galaxy-unpacked-july-2026-highlights-from-galaxy-unpacked</t>
         </is>
       </c>
       <c r="L30" s="60" t="inlineStr">
         <is>
-          <t>57adeb9edafee5c65dff443d</t>
+          <t>ee2b658cb0dfffbcc854ebab</t>
         </is>
       </c>
       <c r="M30" s="75" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="B31" s="75" t="inlineStr">
         <is>
-          <t>2026-07-23T02:00:46Z</t>
+          <t>2026-07-23T16:58:28Z</t>
         </is>
       </c>
       <c r="C31" s="60" t="inlineStr">
@@ -3153,40 +3153,40 @@
       </c>
       <c r="E31" s="60" t="inlineStr">
         <is>
-          <t>Semiconductors &amp; Telecom</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="F31" s="76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G31" s="60" t="inlineStr">
         <is>
-          <t>Official Company</t>
+          <t>Major Media</t>
         </is>
       </c>
       <c r="H31" s="60" t="inlineStr">
         <is>
-          <t>NVIDIA Blog</t>
+          <t>MIT Technology Review</t>
         </is>
       </c>
       <c r="I31" s="60" t="inlineStr">
         <is>
-          <t>NVIDIA AI Supercomputer Comes Online at Naval Postgraduate School</t>
+          <t>Supercooled kidneys have been transplanted into pigs in a “landmark achievement”</t>
         </is>
       </c>
       <c r="J31" s="60" t="inlineStr">
         <is>
-          <t>NVIDIA founder and CEO Jensen Huang today visited the Naval Postgraduate School in Monterey, California, to commission an NVIDIA DGX GB300 system — bringing one of the world’s most powerful AI platforms fully online for the students, researchers and faculty at the U.S. military’s flagship graduate university. “Our nation depends on our men and women […]</t>
+          <t>When it comes to organ donation, time is everything. As soon as an organ has been carefully removed from a donor’s body, it starts to deteriorate. Surgeons have a matter of hours to get it into a recipient. Leave it too long and the organ will become unusable. In most cases, organs will be kept…</t>
         </is>
       </c>
       <c r="K31" s="60" t="inlineStr">
         <is>
-          <t>https://blogs.nvidia.com/blog/naval-postgraduate-school-dgx-ai-supercomputer/</t>
+          <t>https://www.technologyreview.com/2026/07/23/1140765/supercooled-kidneys-have-been-transplanted-into-pigs-in-a-landmark-achievement/</t>
         </is>
       </c>
       <c r="L31" s="60" t="inlineStr">
         <is>
-          <t>c174fc131c4d55cb839833e9</t>
+          <t>590a8cbd726d99d379ccecb1</t>
         </is>
       </c>
       <c r="M31" s="75" t="inlineStr">
@@ -3204,61 +3204,65 @@
     <row r="32" ht="42" customHeight="1">
       <c r="A32" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:05:06+09:00</t>
+          <t>2026-07-26T18:56:03+09:00</t>
         </is>
       </c>
       <c r="B32" s="75" t="inlineStr">
         <is>
-          <t>2026-07-23T00:00:00Z</t>
+          <t>2026-07-23T16:45:56Z</t>
         </is>
       </c>
       <c r="C32" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D32" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="E32" s="60" t="inlineStr">
         <is>
-          <t>Innovation Policy</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="F32" s="76" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G32" s="60" t="inlineStr">
         <is>
-          <t>Policy Institute</t>
+          <t>Major Media</t>
         </is>
       </c>
       <c r="H32" s="60" t="inlineStr">
         <is>
-          <t>Brookings TechTank</t>
+          <t>The Guardian Technology</t>
         </is>
       </c>
       <c r="I32" s="60" t="inlineStr">
         <is>
-          <t>How tech firms should address job concerns and skill development</t>
-        </is>
-      </c>
-      <c r="J32" s="60" t="inlineStr"/>
+          <t>Customers prefer AI chatbots, says British Gas owner as 1,300 call centre and back office jobs axed</t>
+        </is>
+      </c>
+      <c r="J32" s="60" t="inlineStr">
+        <is>
+          <t>CEO Chris O’Shea defends Centrica’s plans as it reports rise in retail profits following focus on bigger margins The owner of British Gas has claimed that most households would rather speak with an AI chatbot than deal with the company’s staff as it prepares to cut 1,300 jobs from its call centres and back office. Centrica, the supplier’s FTSE 100 owner, plans to cut 800 jobs as the company carries out a “targeted deployment of AI tools”, on top of the 500 cuts it confirmed last month. Continue reading...</t>
+        </is>
+      </c>
       <c r="K32" s="60" t="inlineStr">
         <is>
-          <t>https://www.brookings.edu/articles/how-tech-firms-should-address-job-concerns-and-skill-development/</t>
+          <t>https://www.theguardian.com/business/2026/jul/23/customers-prefer-ai-chatbots-says-chris-oshea-british-gas-centrica-boss</t>
         </is>
       </c>
       <c r="L32" s="60" t="inlineStr">
         <is>
-          <t>0d48c18a0657c35e8abe7133</t>
+          <t>2ef05538ad59fc3911318d3f</t>
         </is>
       </c>
       <c r="M32" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:05:06+09:00</t>
+          <t>2026-07-26T18:56:03+09:00</t>
         </is>
       </c>
       <c r="N32" s="60" t="inlineStr">
@@ -3276,26 +3280,26 @@
       </c>
       <c r="B33" s="75" t="inlineStr">
         <is>
-          <t>2026-07-23T00:00:00Z</t>
+          <t>2026-07-23T16:00:00Z</t>
         </is>
       </c>
       <c r="C33" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="D33" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="E33" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence | Healthcare</t>
+          <t>Semiconductors &amp; Telecom | Healthcare</t>
         </is>
       </c>
       <c r="F33" s="76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G33" s="60" t="inlineStr">
         <is>
@@ -3304,27 +3308,27 @@
       </c>
       <c r="H33" s="60" t="inlineStr">
         <is>
-          <t>OpenAI News</t>
+          <t>Samsung Global Newsroom</t>
         </is>
       </c>
       <c r="I33" s="60" t="inlineStr">
         <is>
-          <t>Launching Health in ChatGPT</t>
+          <t>[Galaxy Unpacked July 2026] Samsung and Partners Envision a Connected Care Future — From First Signal to Lasting Change</t>
         </is>
       </c>
       <c r="J33" s="60" t="inlineStr">
         <is>
-          <t>Health in ChatGPT now lets eligible U.S. users securely connect medical records and Apple Health to get more personalized insights and better understand their health.</t>
+          <t>At Galaxy Unpacked July 2026 in London, Samsung Electronics set out its vision for the next chapter of digital health — a future where care moves from reactive treatment toward preventive, personalized and connected experiences, supported by trusted health innovation and partnerships across the healthcare ecosystem. To explore that vision, Samsung hosted a Health Forum […]</t>
         </is>
       </c>
       <c r="K33" s="60" t="inlineStr">
         <is>
-          <t>https://openai.com/index/health-in-chatgpt</t>
+          <t>https://news.samsung.com/global/galaxy-unpacked-july-2026-samsung-and-partners-envision-a-connected-care-future-from-first-signal-to-lasting-change</t>
         </is>
       </c>
       <c r="L33" s="60" t="inlineStr">
         <is>
-          <t>bf70d809f9542eeef4af8727</t>
+          <t>032ebcb3943c83074eb9bcf5</t>
         </is>
       </c>
       <c r="M33" s="75" t="inlineStr">
@@ -3347,7 +3351,7 @@
       </c>
       <c r="B34" s="75" t="inlineStr">
         <is>
-          <t>2026-07-23T00:00:00Z</t>
+          <t>2026-07-23T15:27:52Z</t>
         </is>
       </c>
       <c r="C34" s="60" t="inlineStr">
@@ -3357,45 +3361,45 @@
       </c>
       <c r="D34" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="E34" s="60" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="F34" s="76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G34" s="60" t="inlineStr">
         <is>
-          <t>Scientific Publication</t>
+          <t>Major Media</t>
         </is>
       </c>
       <c r="H34" s="60" t="inlineStr">
         <is>
-          <t>Nature</t>
+          <t>The Guardian Technology</t>
         </is>
       </c>
       <c r="I34" s="60" t="inlineStr">
         <is>
-          <t>How does Make America Healthy Again hold up against scientific scrutiny?</t>
+          <t>Elon Musk says he got ‘carried away’ with Trump – but still holds on to contentious political views</t>
         </is>
       </c>
       <c r="J34" s="60" t="inlineStr">
         <is>
-          <t>Nature, Published online: 23 July 2026; doi:10.1038/d41586-026-02024-3 Researchers share their views on the US health policy spanning topics from vaccines to nutrition.</t>
+          <t>In interview, billionaire says instead of running ‘Doge’ he should’ve ‘worked on my companies’ and shares extreme predictions Elon Musk has admitted he became too consumed by politics during his volatile alliance with Donald Trump and his brief appointment as the president’s financial axman, running the so-called “department of government efficiency” (Doge). The world’s richest person, and briefly its first trillionaire after his SpaceX company floated on the New York stock exchange in June, made the confession in a wide-ranging interview with the Economist published on Thursday. He shared his positions on subjects from foreign wars to AI, and made a number of eye-opening predictions for th…</t>
         </is>
       </c>
       <c r="K34" s="60" t="inlineStr">
         <is>
-          <t>https://www.nature.com/articles/d41586-026-02024-3</t>
+          <t>https://www.theguardian.com/technology/2026/jul/23/elon-musk-regret-trump-doge-ai</t>
         </is>
       </c>
       <c r="L34" s="60" t="inlineStr">
         <is>
-          <t>29dc020f76be264fafefbdc5</t>
+          <t>5ab5ea23fbff158109e679af</t>
         </is>
       </c>
       <c r="M34" s="75" t="inlineStr">
@@ -3418,7 +3422,7 @@
       </c>
       <c r="B35" s="75" t="inlineStr">
         <is>
-          <t>2026-07-23T00:00:00Z</t>
+          <t>2026-07-23T15:00:48Z</t>
         </is>
       </c>
       <c r="C35" s="60" t="inlineStr">
@@ -3428,45 +3432,45 @@
       </c>
       <c r="D35" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="E35" s="60" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Innovation Policy</t>
         </is>
       </c>
       <c r="F35" s="76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G35" s="60" t="inlineStr">
         <is>
-          <t>Scientific Publication</t>
+          <t>Major Media</t>
         </is>
       </c>
       <c r="H35" s="60" t="inlineStr">
         <is>
-          <t>Nature</t>
+          <t>The Guardian Technology</t>
         </is>
       </c>
       <c r="I35" s="60" t="inlineStr">
         <is>
-          <t>Daily briefing: Orcas smash sunfish to smithereens</t>
+          <t>The roaring 20s: how the current decade revolutionised cinema</t>
         </is>
       </c>
       <c r="J35" s="60" t="inlineStr">
         <is>
-          <t>Nature, Published online: 23 July 2026; doi:10.1038/d41586-026-02307-9 The dolphins might be helping their young eat, or just having fun. Plus, the beauty and skill of scientific illustration and a crash course in quantum computing.</t>
+          <t>Pre-Covid, the movie landscape was dramatically different: YouTubers weren’t dominating the box office, video game spin-offs rarely made an impact and Winnie-the-Pooh wasn’t yet the star of a slasher movie. Why such a flurry of innovation – and what will be next? Cinema has always been a medium of research and development. At any given point, the industry is searching for yet another breakthrough that can drive it into the future. Synchronised sound in the 1920s. Technicolor in the 1930s. The invention of the modern blockbuster in the 1970s. Conversely, the consensus is that, if the 2020s has a defining trend, then it is one of decline. The theatrical experience is under attack from all ang…</t>
         </is>
       </c>
       <c r="K35" s="60" t="inlineStr">
         <is>
-          <t>https://www.nature.com/articles/d41586-026-02307-9</t>
+          <t>https://www.theguardian.com/film/2026/jul/23/how-2020s-decade-revolutionised-cinema</t>
         </is>
       </c>
       <c r="L35" s="60" t="inlineStr">
         <is>
-          <t>38109aea610319dbc3f32aef</t>
+          <t>f8939f05439f07fdefca04fc</t>
         </is>
       </c>
       <c r="M35" s="75" t="inlineStr">
@@ -3489,17 +3493,17 @@
       </c>
       <c r="B36" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T22:04:00Z</t>
+          <t>2026-07-23T13:00:16Z</t>
         </is>
       </c>
       <c r="C36" s="60" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D36" s="60" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E36" s="60" t="inlineStr">
@@ -3517,27 +3521,27 @@
       </c>
       <c r="H36" s="60" t="inlineStr">
         <is>
-          <t>Samsung Global Newsroom</t>
+          <t>NVIDIA Blog</t>
         </is>
       </c>
       <c r="I36" s="60" t="inlineStr">
         <is>
-          <t>[Galaxy Unpacked July 2026] A First Look at Galaxy Z Fold8 Ultra, Galaxy Z Fold8 and Galaxy Z Flip8</t>
+          <t>GeForce NOW Sets Sail With ‘Path of Exile: Curse of the Allflame’ Joining the Cloud</t>
         </is>
       </c>
       <c r="J36" s="60" t="inlineStr">
         <is>
-          <t>At Galaxy Unpacked July 2026 in London, Samsung Electronics unveiled the eighth-generation Galaxy Z series. Combining agentic AI that understands users with hardware tailored to different lifestyles, the lineup offers three distinct foldable experiences. Samsung Newsroom got an early look at the new devices during Galaxy Unpacked July 2026 — from Galaxy Z Fold8 Ultra, […]</t>
+          <t>Lock in and load up the cloud. GFN Thursday brings fresh updates and new adventures, all ready to play without waiting for downloads. Set sail in Path of Exile: Curse of the Allflame and charge in Battlefield 6 Season 4 both launching major content for members this week. Then revisit Capcom legends like Breath of […]</t>
         </is>
       </c>
       <c r="K36" s="60" t="inlineStr">
         <is>
-          <t>https://news.samsung.com/global/galaxy-unpacked-july-2026-a-first-look-at-galaxy-z-fold8-ultra-galaxy-z-fold8-and-galaxy-z-flip8</t>
+          <t>https://blogs.nvidia.com/blog/geforce-now-thursday-path-of-exile-allflame/</t>
         </is>
       </c>
       <c r="L36" s="60" t="inlineStr">
         <is>
-          <t>6871adffe89103810dfccf11</t>
+          <t>d6df6c9a47b33117f5bcb1be</t>
         </is>
       </c>
       <c r="M36" s="75" t="inlineStr">
@@ -3560,22 +3564,22 @@
       </c>
       <c r="B37" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T22:03:00Z</t>
+          <t>2026-07-23T12:00:00Z</t>
         </is>
       </c>
       <c r="C37" s="60" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D37" s="60" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E37" s="60" t="inlineStr">
         <is>
-          <t>Semiconductors &amp; Telecom</t>
+          <t>Artificial Intelligence | Healthcare</t>
         </is>
       </c>
       <c r="F37" s="76" t="n">
@@ -3583,32 +3587,32 @@
       </c>
       <c r="G37" s="60" t="inlineStr">
         <is>
-          <t>Official Company</t>
+          <t>Major Media</t>
         </is>
       </c>
       <c r="H37" s="60" t="inlineStr">
         <is>
-          <t>Samsung Global Newsroom</t>
+          <t>MIT Technology Review</t>
         </is>
       </c>
       <c r="I37" s="60" t="inlineStr">
         <is>
-          <t>[Galaxy Unpacked July 2026] A First Look at Galaxy Watch Ultra2 and Galaxy Watch9</t>
+          <t>How AI helps scientists design the next generation of medicines</t>
         </is>
       </c>
       <c r="J37" s="60" t="inlineStr">
         <is>
-          <t>At Galaxy Unpacked July 2026 in London, Samsung Electronics unveiled Galaxy Watch Ultra2 and Galaxy Watch9, expanding the digital health experience on the wrist. From the moment users wake up to the time they finish a workout and begin recovery, a smartwatch stays in contact with the body throughout the day. Samsung Newsroom got an […]</t>
+          <t>Designing and developing a new medicine is an expensive, failure-prone scientific challenge. A new drug can take many years to develop, at the cost of a significant investment. And even then, most possible candidates never reach the patient. For biologic medicines, therapies made from engineered proteins rather than synthetic chemistry (which are often used to…</t>
         </is>
       </c>
       <c r="K37" s="60" t="inlineStr">
         <is>
-          <t>https://news.samsung.com/global/galaxy-unpacked-july-2026-a-first-look-at-galaxy-watch-ultra2-and-galaxy-watch9</t>
+          <t>https://www.technologyreview.com/2026/07/23/1140346/how-ai-helps-scientists-design-the-next-generation-of-medicines/</t>
         </is>
       </c>
       <c r="L37" s="60" t="inlineStr">
         <is>
-          <t>8956b8f95f8049ae547c684e</t>
+          <t>f283b79f845eeb45783eb41c</t>
         </is>
       </c>
       <c r="M37" s="75" t="inlineStr">
@@ -3631,55 +3635,55 @@
       </c>
       <c r="B38" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T22:02:00Z</t>
+          <t>2026-07-23T09:23:23Z</t>
         </is>
       </c>
       <c r="C38" s="60" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>EU &amp; Europe</t>
         </is>
       </c>
       <c r="D38" s="60" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="E38" s="60" t="inlineStr">
         <is>
-          <t>Semiconductors &amp; Telecom</t>
+          <t>Innovation Policy</t>
         </is>
       </c>
       <c r="F38" s="76" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G38" s="60" t="inlineStr">
         <is>
-          <t>Official Company</t>
+          <t>Policy Institute</t>
         </is>
       </c>
       <c r="H38" s="60" t="inlineStr">
         <is>
-          <t>Samsung Global Newsroom</t>
+          <t>Bruegel</t>
         </is>
       </c>
       <c r="I38" s="60" t="inlineStr">
         <is>
-          <t>Samsung Galaxy Z Fold8 Ultra, Fold8 and Flip8: Foldables, Perfected for Every Way of Living</t>
+          <t>Session 2b: Can the EU's better regulation agenda deliver competitiveness?</t>
         </is>
       </c>
       <c r="J38" s="60" t="inlineStr">
         <is>
-          <t>Samsung Electronics today unveiled the new Galaxy Z series, its most complete lineup yet, designed to expand foldables to a wider audience. The lineup introduces Galaxy Z Fold8, a fresh and exciting form factor that provides a new kind of foldable experience built around the way people explore, discover and immerse themselves in their favorite […]</t>
+          <t>Session 2b: Can the EU's better regulation agenda deliver competitiveness? Chiara Montanaro Thu, 07/23/2026 - 11:23 Chiara Montanaro Thu, 07/23/2026 - 11:23</t>
         </is>
       </c>
       <c r="K38" s="60" t="inlineStr">
         <is>
-          <t>https://news.samsung.com/global/samsung-galaxy-z-fold8-ultra-fold8-and-flip8foldables-perfected-for-every-way-of-living</t>
+          <t>https://www.bruegel.org/node/12451</t>
         </is>
       </c>
       <c r="L38" s="60" t="inlineStr">
         <is>
-          <t>3c09b6e86ff09a214f548cb1</t>
+          <t>90ef16bcfe1bd00925658dc5</t>
         </is>
       </c>
       <c r="M38" s="75" t="inlineStr">
@@ -3702,55 +3706,55 @@
       </c>
       <c r="B39" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T22:01:00Z</t>
+          <t>2026-07-23T08:00:24Z</t>
         </is>
       </c>
       <c r="C39" s="60" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D39" s="60" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="E39" s="60" t="inlineStr">
         <is>
-          <t>Semiconductors &amp; Telecom</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="F39" s="76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G39" s="60" t="inlineStr">
         <is>
-          <t>Official Company</t>
+          <t>Intergovernmental</t>
         </is>
       </c>
       <c r="H39" s="60" t="inlineStr">
         <is>
-          <t>Samsung Global Newsroom</t>
+          <t>WHO News</t>
         </is>
       </c>
       <c r="I39" s="60" t="inlineStr">
         <is>
-          <t>Samsung Galaxy Watch Ultra2 and Watch9: Your Health Companion on the Wrist</t>
+          <t>WHO launches seven strategies to prevent drowning</t>
         </is>
       </c>
       <c r="J39" s="60" t="inlineStr">
         <is>
-          <t>Samsung Electronics today announced the all-new Galaxy Watch Ultra2 and Galaxy Watch9, delivering a new era of effortless health, where users can unlock in-depth, meaningful health insights simply by wearing these devices. To support 24/7 wearability, Samsung delivers powerful innovations that maximize comfort while advancing performance with Galaxy Watch’s largest battery and brightest display ever, […]</t>
+          <t>Ahead of World Drowning Prevention Day on 25 July, the World Health Organization (WHO) is launching a new technical package to help governments and communities implement seven proven measures to reduce drowning deaths.</t>
         </is>
       </c>
       <c r="K39" s="60" t="inlineStr">
         <is>
-          <t>https://news.samsung.com/global/samsung-galaxy-watch-ultra2-and-watch9-your-health-companion-on-the-wrist</t>
+          <t>https://www.who.int/news/item/23-07-2026-who-launches-seven-strategies-to-prevent-drowning</t>
         </is>
       </c>
       <c r="L39" s="60" t="inlineStr">
         <is>
-          <t>d2071e7bcb1db74477836d6a</t>
+          <t>57adeb9edafee5c65dff443d</t>
         </is>
       </c>
       <c r="M39" s="75" t="inlineStr">
@@ -3773,17 +3777,17 @@
       </c>
       <c r="B40" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T22:00:00Z</t>
+          <t>2026-07-23T02:00:46Z</t>
         </is>
       </c>
       <c r="C40" s="60" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D40" s="60" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E40" s="60" t="inlineStr">
@@ -3792,7 +3796,7 @@
         </is>
       </c>
       <c r="F40" s="76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G40" s="60" t="inlineStr">
         <is>
@@ -3801,27 +3805,27 @@
       </c>
       <c r="H40" s="60" t="inlineStr">
         <is>
-          <t>Samsung Global Newsroom</t>
+          <t>NVIDIA Blog</t>
         </is>
       </c>
       <c r="I40" s="60" t="inlineStr">
         <is>
-          <t>Samsung Brings Galaxy Ecosystem Into Everyday Eyewear</t>
+          <t>NVIDIA AI Supercomputer Comes Online at Naval Postgraduate School</t>
         </is>
       </c>
       <c r="J40" s="60" t="inlineStr">
         <is>
-          <t>Samsung Electronics today introduced its intelligent eyewear at Galaxy Unpacked in London. Building on the concepts announced at the latest Google I/O, the new designs were developed with global eyewear brands, Gentle Monster and Warby Parker. The intelligent eyewear shows how the Galaxy ecosystem can move beyond the mobile phone and into eyewear that supports […]</t>
+          <t>NVIDIA founder and CEO Jensen Huang today visited the Naval Postgraduate School in Monterey, California, to commission an NVIDIA DGX GB300 system — bringing one of the world’s most powerful AI platforms fully online for the students, researchers and faculty at the U.S. military’s flagship graduate university. “Our nation depends on our men and women […]</t>
         </is>
       </c>
       <c r="K40" s="60" t="inlineStr">
         <is>
-          <t>https://news.samsung.com/global/samsung-brings-galaxy-ecosystem-into-everyday-eyewear</t>
+          <t>https://blogs.nvidia.com/blog/naval-postgraduate-school-dgx-ai-supercomputer/</t>
         </is>
       </c>
       <c r="L40" s="60" t="inlineStr">
         <is>
-          <t>c3c9b17859519c8241a98bfb</t>
+          <t>c174fc131c4d55cb839833e9</t>
         </is>
       </c>
       <c r="M40" s="75" t="inlineStr">
@@ -3839,22 +3843,22 @@
     <row r="41" ht="42" customHeight="1">
       <c r="A41" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T19:05:06+09:00</t>
         </is>
       </c>
       <c r="B41" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T14:21:46Z</t>
+          <t>2026-07-23T00:00:00Z</t>
         </is>
       </c>
       <c r="C41" s="60" t="inlineStr">
         <is>
-          <t>EU &amp; Europe</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D41" s="60" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E41" s="60" t="inlineStr">
@@ -3867,37 +3871,33 @@
       </c>
       <c r="G41" s="60" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Policy Institute</t>
         </is>
       </c>
       <c r="H41" s="60" t="inlineStr">
         <is>
-          <t>UK DSIT</t>
+          <t>Brookings TechTank</t>
         </is>
       </c>
       <c r="I41" s="60" t="inlineStr">
         <is>
-          <t>Guidance: Women in Research Charter</t>
-        </is>
-      </c>
-      <c r="J41" s="60" t="inlineStr">
-        <is>
-          <t>A voluntary commitment to improve outcomes for women across the UK research system, with actions for research funders and research performing organisations.</t>
-        </is>
-      </c>
+          <t>How tech firms should address job concerns and skill development</t>
+        </is>
+      </c>
+      <c r="J41" s="60" t="inlineStr"/>
       <c r="K41" s="60" t="inlineStr">
         <is>
-          <t>https://www.gov.uk/government/publications/women-in-research-charter</t>
+          <t>https://www.brookings.edu/articles/how-tech-firms-should-address-job-concerns-and-skill-development/</t>
         </is>
       </c>
       <c r="L41" s="60" t="inlineStr">
         <is>
-          <t>1e9fd9033d38bacea37c0f42</t>
+          <t>0d48c18a0657c35e8abe7133</t>
         </is>
       </c>
       <c r="M41" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T19:05:06+09:00</t>
         </is>
       </c>
       <c r="N41" s="60" t="inlineStr">
@@ -3910,65 +3910,65 @@
     <row r="42" ht="42" customHeight="1">
       <c r="A42" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:05:06+09:00</t>
+          <t>2026-07-26T18:56:03+09:00</t>
         </is>
       </c>
       <c r="B42" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T14:12:14Z</t>
+          <t>2026-07-23T00:00:00Z</t>
         </is>
       </c>
       <c r="C42" s="60" t="inlineStr">
         <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="D42" s="60" t="inlineStr">
+        <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="D42" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
       <c r="E42" s="60" t="inlineStr">
         <is>
-          <t>Innovation Policy | Quantum</t>
+          <t>Artificial Intelligence | Healthcare</t>
         </is>
       </c>
       <c r="F42" s="76" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G42" s="60" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Official Company</t>
         </is>
       </c>
       <c r="H42" s="60" t="inlineStr">
         <is>
-          <t>DOE Office of Science News</t>
+          <t>OpenAI News</t>
         </is>
       </c>
       <c r="I42" s="60" t="inlineStr">
         <is>
-          <t>Secretary of Energy Chris Wright Announces First Genesis Mission Projects Selected to Accelerate AI-Driven Scientific Discovery</t>
+          <t>Launching Health in ChatGPT</t>
         </is>
       </c>
       <c r="J42" s="60" t="inlineStr">
         <is>
-          <t>Nearly 300 projects selected from historic RFA response spanning all 50 states to accelerate breakthroughs in energy, discovery science, and national security.</t>
+          <t>Health in ChatGPT now lets eligible U.S. users securely connect medical records and Apple Health to get more personalized insights and better understand their health.</t>
         </is>
       </c>
       <c r="K42" s="60" t="inlineStr">
         <is>
-          <t>https://www.energy.gov/articles/secretary-energy-chris-wright-announces-first-genesis-mission-projects-selected-accelerate</t>
+          <t>https://openai.com/index/health-in-chatgpt</t>
         </is>
       </c>
       <c r="L42" s="60" t="inlineStr">
         <is>
-          <t>23fa1d6907c14d73ce3a41cd</t>
+          <t>bf70d809f9542eeef4af8727</t>
         </is>
       </c>
       <c r="M42" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:05:06+09:00</t>
+          <t>2026-07-26T18:56:03+09:00</t>
         </is>
       </c>
       <c r="N42" s="60" t="inlineStr">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="B43" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T14:12:00Z</t>
+          <t>2026-07-23T00:00:00Z</t>
         </is>
       </c>
       <c r="C43" s="60" t="inlineStr">
@@ -3996,45 +3996,45 @@
       </c>
       <c r="D43" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="E43" s="60" t="inlineStr">
         <is>
-          <t>Innovation Policy | Artificial Intelligence</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="F43" s="76" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G43" s="60" t="inlineStr">
         <is>
-          <t>Policy Institute</t>
+          <t>Scientific Publication</t>
         </is>
       </c>
       <c r="H43" s="60" t="inlineStr">
         <is>
-          <t>CSET</t>
+          <t>Nature</t>
         </is>
       </c>
       <c r="I43" s="60" t="inlineStr">
         <is>
-          <t>Remarks at the Global Nobel Laureates Assembly on Artificial Intelligence and Nuclear War in Borgo Laudato Si’, Vatican</t>
+          <t>How does Make America Healthy Again hold up against scientific scrutiny?</t>
         </is>
       </c>
       <c r="J43" s="60" t="inlineStr">
         <is>
-          <t>CSET Senior Fellow Emelia Probasco shares her experience and the remarks she gave at the Global Nobel Laureates Assembly on Artificial Intelligence and Nuclear War, which took place at Borgo Laudato Si’, Vatican. The post Remarks at the Global Nobel Laureates Assembly on Artificial Intelligence and Nuclear War in Borgo Laudato Si’, Vatican appeared first on Center for Security and Emerging Technology .</t>
+          <t>Nature, Published online: 23 July 2026; doi:10.1038/d41586-026-02024-3 Researchers share their views on the US health policy spanning topics from vaccines to nutrition.</t>
         </is>
       </c>
       <c r="K43" s="60" t="inlineStr">
         <is>
-          <t>https://cset.georgetown.edu/article/remarks-at-the-global-nobel-laureates-assembly-on-artificial-intelligence-and-nuclear-war/</t>
+          <t>https://www.nature.com/articles/d41586-026-02024-3</t>
         </is>
       </c>
       <c r="L43" s="60" t="inlineStr">
         <is>
-          <t>863086979e9f7f63c082cb57</t>
+          <t>29dc020f76be264fafefbdc5</t>
         </is>
       </c>
       <c r="M43" s="75" t="inlineStr">
@@ -4057,55 +4057,55 @@
       </c>
       <c r="B44" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T13:58:00Z</t>
+          <t>2026-07-23T00:00:00Z</t>
         </is>
       </c>
       <c r="C44" s="60" t="inlineStr">
         <is>
-          <t>EU &amp; Europe</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D44" s="60" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="E44" s="60" t="inlineStr">
         <is>
-          <t>Innovation Policy</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="F44" s="76" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G44" s="60" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Scientific Publication</t>
         </is>
       </c>
       <c r="H44" s="60" t="inlineStr">
         <is>
-          <t>UK DSIT</t>
+          <t>Nature</t>
         </is>
       </c>
       <c r="I44" s="60" t="inlineStr">
         <is>
-          <t>Guidance: Consult: register your interest</t>
+          <t>Daily briefing: Orcas smash sunfish to smithereens</t>
         </is>
       </c>
       <c r="J44" s="60" t="inlineStr">
         <is>
-          <t>Register your interest in using Consult, the AI tool that helps government teams analyse public consultation responses. Join the waitlist for access.</t>
+          <t>Nature, Published online: 23 July 2026; doi:10.1038/d41586-026-02307-9 The dolphins might be helping their young eat, or just having fun. Plus, the beauty and skill of scientific illustration and a crash course in quantum computing.</t>
         </is>
       </c>
       <c r="K44" s="60" t="inlineStr">
         <is>
-          <t>https://www.gov.uk/government/publications/consult-register-your-interest</t>
+          <t>https://www.nature.com/articles/d41586-026-02307-9</t>
         </is>
       </c>
       <c r="L44" s="60" t="inlineStr">
         <is>
-          <t>a651f42eb5805e39f03fbebe</t>
+          <t>38109aea610319dbc3f32aef</t>
         </is>
       </c>
       <c r="M44" s="75" t="inlineStr">
@@ -4123,65 +4123,65 @@
     <row r="45" ht="42" customHeight="1">
       <c r="A45" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:05:06+09:00</t>
+          <t>2026-07-26T18:56:03+09:00</t>
         </is>
       </c>
       <c r="B45" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T13:53:19Z</t>
+          <t>2026-07-22T22:04:00Z</t>
         </is>
       </c>
       <c r="C45" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="D45" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="E45" s="60" t="inlineStr">
         <is>
-          <t>Innovation Policy | Artificial Intelligence</t>
+          <t>Semiconductors &amp; Telecom</t>
         </is>
       </c>
       <c r="F45" s="76" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G45" s="60" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Official Company</t>
         </is>
       </c>
       <c r="H45" s="60" t="inlineStr">
         <is>
-          <t>National Science Foundation News</t>
+          <t>Samsung Global Newsroom</t>
         </is>
       </c>
       <c r="I45" s="60" t="inlineStr">
         <is>
-          <t>Statement from NSF Chief of Staff Brian Stone, performing the duties of the NSF director, on advancing the Administration's AI priorities through the Genesis Mission</t>
+          <t>[Galaxy Unpacked July 2026] A First Look at Galaxy Z Fold8 Ultra, Galaxy Z Fold8 and Galaxy Z Flip8</t>
         </is>
       </c>
       <c r="J45" s="60" t="inlineStr">
         <is>
-          <t>The U.S. National Science Foundation is proud to join the White House Office of Science and Technology Policy, the U.S. Department of Energy and other federal partners in advancing the administration's artificial intelligence priorities through the…</t>
+          <t>At Galaxy Unpacked July 2026 in London, Samsung Electronics unveiled the eighth-generation Galaxy Z series. Combining agentic AI that understands users with hardware tailored to different lifestyles, the lineup offers three distinct foldable experiences. Samsung Newsroom got an early look at the new devices during Galaxy Unpacked July 2026 — from Galaxy Z Fold8 Ultra, […]</t>
         </is>
       </c>
       <c r="K45" s="60" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/news/statement-nsf-chief-staff-brian-stone-performing-duties-nsf-1</t>
+          <t>https://news.samsung.com/global/galaxy-unpacked-july-2026-a-first-look-at-galaxy-z-fold8-ultra-galaxy-z-fold8-and-galaxy-z-flip8</t>
         </is>
       </c>
       <c r="L45" s="60" t="inlineStr">
         <is>
-          <t>123e2207578ca69c8f9c00a2</t>
+          <t>6871adffe89103810dfccf11</t>
         </is>
       </c>
       <c r="M45" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:05:06+09:00</t>
+          <t>2026-07-26T18:56:03+09:00</t>
         </is>
       </c>
       <c r="N45" s="60" t="inlineStr">
@@ -4194,65 +4194,65 @@
     <row r="46" ht="42" customHeight="1">
       <c r="A46" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:05:06+09:00</t>
+          <t>2026-07-26T18:56:03+09:00</t>
         </is>
       </c>
       <c r="B46" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T13:53:12Z</t>
+          <t>2026-07-22T22:03:00Z</t>
         </is>
       </c>
       <c r="C46" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="D46" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="E46" s="60" t="inlineStr">
         <is>
-          <t>Innovation Policy | Artificial Intelligence</t>
+          <t>Semiconductors &amp; Telecom</t>
         </is>
       </c>
       <c r="F46" s="76" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G46" s="60" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Official Company</t>
         </is>
       </c>
       <c r="H46" s="60" t="inlineStr">
         <is>
-          <t>National Science Foundation News</t>
+          <t>Samsung Global Newsroom</t>
         </is>
       </c>
       <c r="I46" s="60" t="inlineStr">
         <is>
-          <t>New NSF initiative aims to unlock dataset value for AI-enabled scientific discovery</t>
+          <t>[Galaxy Unpacked July 2026] A First Look at Galaxy Watch Ultra2 and Galaxy Watch9</t>
         </is>
       </c>
       <c r="J46" s="60" t="inlineStr">
         <is>
-          <t>The U.S. National Science Foundation announced the NSF Unlocking Dataset Value for AI-Enabled Scientific Discovery program, a new investment to advance scientific community datasets and enable discovery and innovation using artificial intelligence…</t>
+          <t>At Galaxy Unpacked July 2026 in London, Samsung Electronics unveiled Galaxy Watch Ultra2 and Galaxy Watch9, expanding the digital health experience on the wrist. From the moment users wake up to the time they finish a workout and begin recovery, a smartwatch stays in contact with the body throughout the day. Samsung Newsroom got an […]</t>
         </is>
       </c>
       <c r="K46" s="60" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/news/new-nsf-initiative-aims-unlock-dataset-value-ai-enabled</t>
+          <t>https://news.samsung.com/global/galaxy-unpacked-july-2026-a-first-look-at-galaxy-watch-ultra2-and-galaxy-watch9</t>
         </is>
       </c>
       <c r="L46" s="60" t="inlineStr">
         <is>
-          <t>dcd819527d9b80141b26bcb8</t>
+          <t>8956b8f95f8049ae547c684e</t>
         </is>
       </c>
       <c r="M46" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:05:06+09:00</t>
+          <t>2026-07-26T18:56:03+09:00</t>
         </is>
       </c>
       <c r="N46" s="60" t="inlineStr">
@@ -4265,65 +4265,65 @@
     <row r="47" ht="42" customHeight="1">
       <c r="A47" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:05:06+09:00</t>
+          <t>2026-07-26T18:56:03+09:00</t>
         </is>
       </c>
       <c r="B47" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T13:53:06Z</t>
+          <t>2026-07-22T22:02:00Z</t>
         </is>
       </c>
       <c r="C47" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="D47" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="E47" s="60" t="inlineStr">
         <is>
-          <t>Innovation Policy</t>
+          <t>Semiconductors &amp; Telecom</t>
         </is>
       </c>
       <c r="F47" s="76" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G47" s="60" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Official Company</t>
         </is>
       </c>
       <c r="H47" s="60" t="inlineStr">
         <is>
-          <t>National Science Foundation News</t>
+          <t>Samsung Global Newsroom</t>
         </is>
       </c>
       <c r="I47" s="60" t="inlineStr">
         <is>
-          <t>NSF announces $83M investment in integrated data systems and services to advance AI-driven science and strengthen U.S. research infrastructure</t>
+          <t>Samsung Galaxy Z Fold8 Ultra, Fold8 and Flip8: Foldables, Perfected for Every Way of Living</t>
         </is>
       </c>
       <c r="J47" s="60" t="inlineStr">
         <is>
-          <t>The U.S. National Science Foundation today announced $83 million in awards through the Integrated Data Systems and Services (IDSS) program. The awards will expand access to data infrastructure resources that researchers can use alongside computing…</t>
+          <t>Samsung Electronics today unveiled the new Galaxy Z series, its most complete lineup yet, designed to expand foldables to a wider audience. The lineup introduces Galaxy Z Fold8, a fresh and exciting form factor that provides a new kind of foldable experience built around the way people explore, discover and immerse themselves in their favorite […]</t>
         </is>
       </c>
       <c r="K47" s="60" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/news/nsf-announces-83m-investment-integrated-data-systems</t>
+          <t>https://news.samsung.com/global/samsung-galaxy-z-fold8-ultra-fold8-and-flip8foldables-perfected-for-every-way-of-living</t>
         </is>
       </c>
       <c r="L47" s="60" t="inlineStr">
         <is>
-          <t>018d40b7e6eb7aa4b8cfb5fa</t>
+          <t>3c09b6e86ff09a214f548cb1</t>
         </is>
       </c>
       <c r="M47" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:05:06+09:00</t>
+          <t>2026-07-26T18:56:03+09:00</t>
         </is>
       </c>
       <c r="N47" s="60" t="inlineStr">
@@ -4341,22 +4341,22 @@
       </c>
       <c r="B48" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T13:00:11Z</t>
+          <t>2026-07-22T22:01:00Z</t>
         </is>
       </c>
       <c r="C48" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="D48" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="E48" s="60" t="inlineStr">
         <is>
-          <t>Robotics | Healthcare | Semiconductors &amp; Telecom</t>
+          <t>Semiconductors &amp; Telecom</t>
         </is>
       </c>
       <c r="F48" s="76" t="n">
@@ -4369,27 +4369,27 @@
       </c>
       <c r="H48" s="60" t="inlineStr">
         <is>
-          <t>NVIDIA Blog</t>
+          <t>Samsung Global Newsroom</t>
         </is>
       </c>
       <c r="I48" s="60" t="inlineStr">
         <is>
-          <t>NVIDIA Open Sources First GPU-Accelerated Medical Physics Simulation Framework</t>
+          <t>Samsung Galaxy Watch Ultra2 and Watch9: Your Health Companion on the Wrist</t>
         </is>
       </c>
       <c r="J48" s="60" t="inlineStr">
         <is>
-          <t>Before a healthcare robot can be useful in the real world, it has to learn how the physical world pushes back. Anatomy varies. Instruments bend, press, slip and interact with tissue. Imaging can be noisy or incomplete. And the rare, edge scenarios developers most need to understand don’t appear on schedule. That creates one of […]</t>
+          <t>Samsung Electronics today announced the all-new Galaxy Watch Ultra2 and Galaxy Watch9, delivering a new era of effortless health, where users can unlock in-depth, meaningful health insights simply by wearing these devices. To support 24/7 wearability, Samsung delivers powerful innovations that maximize comfort while advancing performance with Galaxy Watch’s largest battery and brightest display ever, […]</t>
         </is>
       </c>
       <c r="K48" s="60" t="inlineStr">
         <is>
-          <t>https://blogs.nvidia.com/blog/medical-physics-simulation-open-source/</t>
+          <t>https://news.samsung.com/global/samsung-galaxy-watch-ultra2-and-watch9-your-health-companion-on-the-wrist</t>
         </is>
       </c>
       <c r="L48" s="60" t="inlineStr">
         <is>
-          <t>3c1ee99eb36c61c92c0f7bb6</t>
+          <t>d2071e7bcb1db74477836d6a</t>
         </is>
       </c>
       <c r="M48" s="75" t="inlineStr">
@@ -4412,26 +4412,26 @@
       </c>
       <c r="B49" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T13:00:00Z</t>
+          <t>2026-07-22T22:00:00Z</t>
         </is>
       </c>
       <c r="C49" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="D49" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="E49" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Semiconductors &amp; Telecom</t>
         </is>
       </c>
       <c r="F49" s="76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G49" s="60" t="inlineStr">
         <is>
@@ -4440,27 +4440,27 @@
       </c>
       <c r="H49" s="60" t="inlineStr">
         <is>
-          <t>OpenAI News</t>
+          <t>Samsung Global Newsroom</t>
         </is>
       </c>
       <c r="I49" s="60" t="inlineStr">
         <is>
-          <t>Building AI infrastructure with the Effingham County community</t>
+          <t>Samsung Brings Galaxy Ecosystem Into Everyday Eyewear</t>
         </is>
       </c>
       <c r="J49" s="60" t="inlineStr">
         <is>
-          <t>OpenAI announces Project Camellia in Effingham County, Georgia, with commitments to responsible energy, community investment, jobs, and access to Codex.</t>
+          <t>Samsung Electronics today introduced its intelligent eyewear at Galaxy Unpacked in London. Building on the concepts announced at the latest Google I/O, the new designs were developed with global eyewear brands, Gentle Monster and Warby Parker. The intelligent eyewear shows how the Galaxy ecosystem can move beyond the mobile phone and into eyewear that supports […]</t>
         </is>
       </c>
       <c r="K49" s="60" t="inlineStr">
         <is>
-          <t>https://openai.com/index/building-ai-infrastructure-with-the-effingham-county-community</t>
+          <t>https://news.samsung.com/global/samsung-brings-galaxy-ecosystem-into-everyday-eyewear</t>
         </is>
       </c>
       <c r="L49" s="60" t="inlineStr">
         <is>
-          <t>082c4173c70b04519142ea2a</t>
+          <t>c3c9b17859519c8241a98bfb</t>
         </is>
       </c>
       <c r="M49" s="75" t="inlineStr">
@@ -4483,55 +4483,55 @@
       </c>
       <c r="B50" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T13:00:00Z</t>
+          <t>2026-07-22T14:21:46Z</t>
         </is>
       </c>
       <c r="C50" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>EU &amp; Europe</t>
         </is>
       </c>
       <c r="D50" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="E50" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Innovation Policy</t>
         </is>
       </c>
       <c r="F50" s="76" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G50" s="60" t="inlineStr">
         <is>
-          <t>Official Company</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H50" s="60" t="inlineStr">
         <is>
-          <t>OpenAI News</t>
+          <t>UK DSIT</t>
         </is>
       </c>
       <c r="I50" s="60" t="inlineStr">
         <is>
-          <t>How news organizations are using AI to advance their vital missions</t>
+          <t>Guidance: Women in Research Charter</t>
         </is>
       </c>
       <c r="J50" s="60" t="inlineStr">
         <is>
-          <t>News organizations are using AI to strengthen reporting, grow audiences, and improve business operations, with OpenAI tools supporting journalists and publishers worldwide.</t>
+          <t>A voluntary commitment to improve outcomes for women across the UK research system, with actions for research funders and research performing organisations.</t>
         </is>
       </c>
       <c r="K50" s="60" t="inlineStr">
         <is>
-          <t>https://openai.com/index/how-news-organizations-are-using-ai</t>
+          <t>https://www.gov.uk/government/publications/women-in-research-charter</t>
         </is>
       </c>
       <c r="L50" s="60" t="inlineStr">
         <is>
-          <t>932591afba7f1cf55372f3f4</t>
+          <t>1e9fd9033d38bacea37c0f42</t>
         </is>
       </c>
       <c r="M50" s="75" t="inlineStr">
@@ -4549,17 +4549,17 @@
     <row r="51" ht="42" customHeight="1">
       <c r="A51" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T19:05:06+09:00</t>
         </is>
       </c>
       <c r="B51" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T13:00:00Z</t>
+          <t>2026-07-22T14:12:14Z</t>
         </is>
       </c>
       <c r="C51" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D51" s="60" t="inlineStr">
@@ -4569,45 +4569,45 @@
       </c>
       <c r="E51" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Innovation Policy | Quantum</t>
         </is>
       </c>
       <c r="F51" s="76" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G51" s="60" t="inlineStr">
         <is>
-          <t>Official Company</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H51" s="60" t="inlineStr">
         <is>
-          <t>Google AI</t>
+          <t>DOE Office of Science News</t>
         </is>
       </c>
       <c r="I51" s="60" t="inlineStr">
         <is>
-          <t>3 Google updates from Galaxy Unpacked 2026</t>
+          <t>Secretary of Energy Chris Wright Announces First Genesis Mission Projects Selected to Accelerate AI-Driven Scientific Discovery</t>
         </is>
       </c>
       <c r="J51" s="60" t="inlineStr">
         <is>
-          <t>Gentle Monster glasses, Warby Parker glasses, a prompt asking for the history behind a pictured building, and a prompt asking to book a table at a pictured restaurant</t>
+          <t>Nearly 300 projects selected from historic RFA response spanning all 50 states to accelerate breakthroughs in energy, discovery science, and national security.</t>
         </is>
       </c>
       <c r="K51" s="60" t="inlineStr">
         <is>
-          <t>https://blog.google/products-and-platforms/platforms/android/galaxy-unpacked-2026/</t>
+          <t>https://www.energy.gov/articles/secretary-energy-chris-wright-announces-first-genesis-mission-projects-selected-accelerate</t>
         </is>
       </c>
       <c r="L51" s="60" t="inlineStr">
         <is>
-          <t>7c49a9cf52e16d8bc5c300b8</t>
+          <t>23fa1d6907c14d73ce3a41cd</t>
         </is>
       </c>
       <c r="M51" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T19:05:06+09:00</t>
         </is>
       </c>
       <c r="N51" s="60" t="inlineStr">
@@ -4625,12 +4625,12 @@
       </c>
       <c r="B52" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T12:10:00Z</t>
+          <t>2026-07-22T14:12:00Z</t>
         </is>
       </c>
       <c r="C52" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D52" s="60" t="inlineStr">
@@ -4640,40 +4640,40 @@
       </c>
       <c r="E52" s="60" t="inlineStr">
         <is>
-          <t>Fusion Energy</t>
+          <t>Innovation Policy | Artificial Intelligence</t>
         </is>
       </c>
       <c r="F52" s="76" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G52" s="60" t="inlineStr">
         <is>
-          <t>Major Media</t>
+          <t>Policy Institute</t>
         </is>
       </c>
       <c r="H52" s="60" t="inlineStr">
         <is>
-          <t>MIT Technology Review</t>
+          <t>CSET</t>
         </is>
       </c>
       <c r="I52" s="60" t="inlineStr">
         <is>
-          <t>The Download: NASA’s new space telescope and OpenAI’s autonomous hacker</t>
+          <t>Remarks at the Global Nobel Laureates Assembly on Artificial Intelligence and Nuclear War in Borgo Laudato Si’, Vatican</t>
         </is>
       </c>
       <c r="J52" s="60" t="inlineStr">
         <is>
-          <t>This is today’s edition of The Download, our weekday newsletter that provides a daily dose of what’s going on in the world of technology. Shape-shifting mirrors on NASA’s new space telescope could unveil Jupiters like our own When NASA’s Nancy Grace Roman Space Telescope launches, as early as the end of next month, it will…</t>
+          <t>CSET Senior Fellow Emelia Probasco shares her experience and the remarks she gave at the Global Nobel Laureates Assembly on Artificial Intelligence and Nuclear War, which took place at Borgo Laudato Si’, Vatican. The post Remarks at the Global Nobel Laureates Assembly on Artificial Intelligence and Nuclear War in Borgo Laudato Si’, Vatican appeared first on Center for Security and Emerging Technology .</t>
         </is>
       </c>
       <c r="K52" s="60" t="inlineStr">
         <is>
-          <t>https://www.technologyreview.com/2026/07/22/1140717/the-download-nasa-space-telescope-openai-hugging-face-hack/</t>
+          <t>https://cset.georgetown.edu/article/remarks-at-the-global-nobel-laureates-assembly-on-artificial-intelligence-and-nuclear-war/</t>
         </is>
       </c>
       <c r="L52" s="60" t="inlineStr">
         <is>
-          <t>62c5c294dc0cb2f834763aa6</t>
+          <t>863086979e9f7f63c082cb57</t>
         </is>
       </c>
       <c r="M52" s="75" t="inlineStr">
@@ -4696,17 +4696,17 @@
       </c>
       <c r="B53" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T12:00:00Z</t>
+          <t>2026-07-22T13:58:00Z</t>
         </is>
       </c>
       <c r="C53" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>EU &amp; Europe</t>
         </is>
       </c>
       <c r="D53" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="E53" s="60" t="inlineStr">
@@ -4715,7 +4715,7 @@
         </is>
       </c>
       <c r="F53" s="76" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G53" s="60" t="inlineStr">
         <is>
@@ -4724,27 +4724,27 @@
       </c>
       <c r="H53" s="60" t="inlineStr">
         <is>
-          <t>NIST News</t>
+          <t>UK DSIT</t>
         </is>
       </c>
       <c r="I53" s="60" t="inlineStr">
         <is>
-          <t>NIST Announces Funding Opportunity for 14 MEP Centers to Advance Small and Medium-Sized U.S. Manufacturers</t>
+          <t>Guidance: Consult: register your interest</t>
         </is>
       </c>
       <c r="J53" s="60" t="inlineStr">
         <is>
-          <t>NIST MEP will host an informational webinar on Tuesday, July 28, 2026, at 1 p.m. ET to provide general information about this opportunity and guidance on preparing applications.</t>
+          <t>Register your interest in using Consult, the AI tool that helps government teams analyse public consultation responses. Join the waitlist for access.</t>
         </is>
       </c>
       <c r="K53" s="60" t="inlineStr">
         <is>
-          <t>https://www.nist.gov/news-events/news/2026/07/nist-announces-funding-opportunity-14-mep-centers-advance-small-and-medium</t>
+          <t>https://www.gov.uk/government/publications/consult-register-your-interest</t>
         </is>
       </c>
       <c r="L53" s="60" t="inlineStr">
         <is>
-          <t>5aa9c93bc7040291c9f08bfa</t>
+          <t>a651f42eb5805e39f03fbebe</t>
         </is>
       </c>
       <c r="M53" s="75" t="inlineStr">
@@ -4762,12 +4762,12 @@
     <row r="54" ht="42" customHeight="1">
       <c r="A54" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T19:05:06+09:00</t>
         </is>
       </c>
       <c r="B54" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T12:00:00Z</t>
+          <t>2026-07-22T13:53:19Z</t>
         </is>
       </c>
       <c r="C54" s="60" t="inlineStr">
@@ -4782,45 +4782,45 @@
       </c>
       <c r="E54" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Innovation Policy | Artificial Intelligence</t>
         </is>
       </c>
       <c r="F54" s="76" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G54" s="60" t="inlineStr">
         <is>
-          <t>Official Company</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H54" s="60" t="inlineStr">
         <is>
-          <t>OpenAI News</t>
+          <t>National Science Foundation News</t>
         </is>
       </c>
       <c r="I54" s="60" t="inlineStr">
         <is>
-          <t>Advancing the next era of national science</t>
+          <t>Statement from NSF Chief of Staff Brian Stone, performing the duties of the NSF director, on advancing the Administration's AI priorities through the Genesis Mission</t>
         </is>
       </c>
       <c r="J54" s="60" t="inlineStr">
         <is>
-          <t>OpenAI outlines its commitment to advancing American science working with the U.S. Department of Energy and national labs to use frontier AI to accelerate discovery.</t>
+          <t>The U.S. National Science Foundation is proud to join the White House Office of Science and Technology Policy, the U.S. Department of Energy and other federal partners in advancing the administration's artificial intelligence priorities through the…</t>
         </is>
       </c>
       <c r="K54" s="60" t="inlineStr">
         <is>
-          <t>https://openai.com/index/advancing-the-next-era-of-national-science</t>
+          <t>https://www.nsf.gov/news/statement-nsf-chief-staff-brian-stone-performing-duties-nsf-1</t>
         </is>
       </c>
       <c r="L54" s="60" t="inlineStr">
         <is>
-          <t>577ddf6b90e6d70b43383fc6</t>
+          <t>123e2207578ca69c8f9c00a2</t>
         </is>
       </c>
       <c r="M54" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T19:05:06+09:00</t>
         </is>
       </c>
       <c r="N54" s="60" t="inlineStr">
@@ -4833,17 +4833,17 @@
     <row r="55" ht="42" customHeight="1">
       <c r="A55" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T19:05:06+09:00</t>
         </is>
       </c>
       <c r="B55" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T09:00:00Z</t>
+          <t>2026-07-22T13:53:12Z</t>
         </is>
       </c>
       <c r="C55" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D55" s="60" t="inlineStr">
@@ -4853,45 +4853,45 @@
       </c>
       <c r="E55" s="60" t="inlineStr">
         <is>
-          <t>Fusion Energy</t>
+          <t>Innovation Policy | Artificial Intelligence</t>
         </is>
       </c>
       <c r="F55" s="76" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G55" s="60" t="inlineStr">
         <is>
-          <t>Major Media</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H55" s="60" t="inlineStr">
         <is>
-          <t>MIT Technology Review</t>
+          <t>National Science Foundation News</t>
         </is>
       </c>
       <c r="I55" s="60" t="inlineStr">
         <is>
-          <t>Shape-shifting mirrors on NASA’s new space telescope could unveil Jupiters like our own</t>
+          <t>New NSF initiative aims to unlock dataset value for AI-enabled scientific discovery</t>
         </is>
       </c>
       <c r="J55" s="60" t="inlineStr">
         <is>
-          <t>When NASA’s Nancy Grace Roman Space Telescope launches, as early as the end of next month, it will attempt one of astronomy’s most precise disappearing acts to date. The telescope will carry the first space-bound “active” coronagraph, an instrument that effectively erases most of the light from a star during photography. It will allow astronomers…</t>
+          <t>The U.S. National Science Foundation announced the NSF Unlocking Dataset Value for AI-Enabled Scientific Discovery program, a new investment to advance scientific community datasets and enable discovery and innovation using artificial intelligence…</t>
         </is>
       </c>
       <c r="K55" s="60" t="inlineStr">
         <is>
-          <t>https://www.technologyreview.com/2026/07/22/1140701/shape-shifting-mirrors-roman-space-telescope/</t>
+          <t>https://www.nsf.gov/news/new-nsf-initiative-aims-unlock-dataset-value-ai-enabled</t>
         </is>
       </c>
       <c r="L55" s="60" t="inlineStr">
         <is>
-          <t>04231693b363104315116185</t>
+          <t>dcd819527d9b80141b26bcb8</t>
         </is>
       </c>
       <c r="M55" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T19:05:06+09:00</t>
         </is>
       </c>
       <c r="N55" s="60" t="inlineStr">
@@ -4904,17 +4904,17 @@
     <row r="56" ht="42" customHeight="1">
       <c r="A56" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T19:05:06+09:00</t>
         </is>
       </c>
       <c r="B56" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T05:30:00Z</t>
+          <t>2026-07-22T13:53:06Z</t>
         </is>
       </c>
       <c r="C56" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D56" s="60" t="inlineStr">
@@ -4924,45 +4924,45 @@
       </c>
       <c r="E56" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Innovation Policy</t>
         </is>
       </c>
       <c r="F56" s="76" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G56" s="60" t="inlineStr">
         <is>
-          <t>Official Company</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H56" s="60" t="inlineStr">
         <is>
-          <t>OpenAI News</t>
+          <t>National Science Foundation News</t>
         </is>
       </c>
       <c r="I56" s="60" t="inlineStr">
         <is>
-          <t>Introducing OpenAI Presence</t>
+          <t>NSF announces $83M investment in integrated data systems and services to advance AI-driven science and strengthen U.S. research infrastructure</t>
         </is>
       </c>
       <c r="J56" s="60" t="inlineStr">
         <is>
-          <t>Introducing OpenAI Presence, a proven enterprise AI agent platform that helps organizations deploy trusted voice and chat agents for customer and internal workflows.</t>
+          <t>The U.S. National Science Foundation today announced $83 million in awards through the Integrated Data Systems and Services (IDSS) program. The awards will expand access to data infrastructure resources that researchers can use alongside computing…</t>
         </is>
       </c>
       <c r="K56" s="60" t="inlineStr">
         <is>
-          <t>https://openai.com/index/introducing-openai-presence</t>
+          <t>https://www.nsf.gov/news/nsf-announces-83m-investment-integrated-data-systems</t>
         </is>
       </c>
       <c r="L56" s="60" t="inlineStr">
         <is>
-          <t>839f7a51d7b587ae6fb6fad7</t>
+          <t>018d40b7e6eb7aa4b8cfb5fa</t>
         </is>
       </c>
       <c r="M56" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T19:05:06+09:00</t>
         </is>
       </c>
       <c r="N56" s="60" t="inlineStr">
@@ -4980,7 +4980,7 @@
       </c>
       <c r="B57" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T00:00:00Z</t>
+          <t>2026-07-22T13:00:11Z</t>
         </is>
       </c>
       <c r="C57" s="60" t="inlineStr">
@@ -4995,11 +4995,11 @@
       </c>
       <c r="E57" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Robotics | Healthcare | Semiconductors &amp; Telecom</t>
         </is>
       </c>
       <c r="F57" s="76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G57" s="60" t="inlineStr">
         <is>
@@ -5008,27 +5008,27 @@
       </c>
       <c r="H57" s="60" t="inlineStr">
         <is>
-          <t>OpenAI News</t>
+          <t>NVIDIA Blog</t>
         </is>
       </c>
       <c r="I57" s="60" t="inlineStr">
         <is>
-          <t>NTT DATA Group cuts incident analysis to 30 minutes with Codex</t>
+          <t>NVIDIA Open Sources First GPU-Accelerated Medical Physics Simulation Framework</t>
         </is>
       </c>
       <c r="J57" s="60" t="inlineStr">
         <is>
-          <t>NTT DATA Group uses ChatGPT Enterprise and Codex to help 9,000 employees automate work, cut incident analysis to 30 minutes, and scale secure AI adoption.</t>
+          <t>Before a healthcare robot can be useful in the real world, it has to learn how the physical world pushes back. Anatomy varies. Instruments bend, press, slip and interact with tissue. Imaging can be noisy or incomplete. And the rare, edge scenarios developers most need to understand don’t appear on schedule. That creates one of […]</t>
         </is>
       </c>
       <c r="K57" s="60" t="inlineStr">
         <is>
-          <t>https://openai.com/index/ntt-data</t>
+          <t>https://blogs.nvidia.com/blog/medical-physics-simulation-open-source/</t>
         </is>
       </c>
       <c r="L57" s="60" t="inlineStr">
         <is>
-          <t>389ebd02d2834f48054db326</t>
+          <t>3c1ee99eb36c61c92c0f7bb6</t>
         </is>
       </c>
       <c r="M57" s="75" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="B58" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T00:00:00Z</t>
+          <t>2026-07-22T13:00:00Z</t>
         </is>
       </c>
       <c r="C58" s="60" t="inlineStr">
@@ -5061,12 +5061,12 @@
       </c>
       <c r="D58" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E58" s="60" t="inlineStr">
         <is>
-          <t>Innovation Policy | Biotechnology</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="F58" s="76" t="n">
@@ -5074,32 +5074,32 @@
       </c>
       <c r="G58" s="60" t="inlineStr">
         <is>
-          <t>Scientific Publication</t>
+          <t>Official Company</t>
         </is>
       </c>
       <c r="H58" s="60" t="inlineStr">
         <is>
-          <t>Nature</t>
+          <t>OpenAI News</t>
         </is>
       </c>
       <c r="I58" s="60" t="inlineStr">
         <is>
-          <t>Subnuclear genome compartmentalization controls bivalent chromatin activity</t>
+          <t>Building AI infrastructure with the Effingham County community</t>
         </is>
       </c>
       <c r="J58" s="60" t="inlineStr">
         <is>
-          <t>Nature, Published online: 22 July 2026; doi:10.1038/s41586-026-10832-w Knowledge of the spatial location of a gene is necessary to understand its epigenomic regulation.</t>
+          <t>OpenAI announces Project Camellia in Effingham County, Georgia, with commitments to responsible energy, community investment, jobs, and access to Codex.</t>
         </is>
       </c>
       <c r="K58" s="60" t="inlineStr">
         <is>
-          <t>https://www.nature.com/articles/s41586-026-10832-w</t>
+          <t>https://openai.com/index/building-ai-infrastructure-with-the-effingham-county-community</t>
         </is>
       </c>
       <c r="L58" s="60" t="inlineStr">
         <is>
-          <t>f9bccca3cabb5ce19441f09d</t>
+          <t>082c4173c70b04519142ea2a</t>
         </is>
       </c>
       <c r="M58" s="75" t="inlineStr">
@@ -5122,7 +5122,7 @@
       </c>
       <c r="B59" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T00:00:00Z</t>
+          <t>2026-07-22T13:00:00Z</t>
         </is>
       </c>
       <c r="C59" s="60" t="inlineStr">
@@ -5132,45 +5132,45 @@
       </c>
       <c r="D59" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E59" s="60" t="inlineStr">
         <is>
-          <t>Fusion Energy</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="F59" s="76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G59" s="60" t="inlineStr">
         <is>
-          <t>Scientific Publication</t>
+          <t>Official Company</t>
         </is>
       </c>
       <c r="H59" s="60" t="inlineStr">
         <is>
-          <t>Nature</t>
+          <t>OpenAI News</t>
         </is>
       </c>
       <c r="I59" s="60" t="inlineStr">
         <is>
-          <t>What counts as a moon? Huge ‘exosatellite’ sparks debate</t>
+          <t>How news organizations are using AI to advance their vital missions</t>
         </is>
       </c>
       <c r="J59" s="60" t="inlineStr">
         <is>
-          <t>Nature, Published online: 22 July 2026; doi:10.1038/d41586-026-02299-6 Discovery of a distant Jupiter-mass object could pave the way for detection of exomoons — plus, a rare transmissible cancer found in catfish.</t>
+          <t>News organizations are using AI to strengthen reporting, grow audiences, and improve business operations, with OpenAI tools supporting journalists and publishers worldwide.</t>
         </is>
       </c>
       <c r="K59" s="60" t="inlineStr">
         <is>
-          <t>https://www.nature.com/articles/d41586-026-02299-6</t>
+          <t>https://openai.com/index/how-news-organizations-are-using-ai</t>
         </is>
       </c>
       <c r="L59" s="60" t="inlineStr">
         <is>
-          <t>a3eb7f1e33aee131ed0b4bf7</t>
+          <t>932591afba7f1cf55372f3f4</t>
         </is>
       </c>
       <c r="M59" s="75" t="inlineStr">
@@ -5193,7 +5193,7 @@
       </c>
       <c r="B60" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T00:00:00Z</t>
+          <t>2026-07-22T13:00:00Z</t>
         </is>
       </c>
       <c r="C60" s="60" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="D60" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E60" s="60" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="F60" s="76" t="n">
@@ -5216,32 +5216,32 @@
       </c>
       <c r="G60" s="60" t="inlineStr">
         <is>
-          <t>Scientific Publication</t>
+          <t>Official Company</t>
         </is>
       </c>
       <c r="H60" s="60" t="inlineStr">
         <is>
-          <t>Nature</t>
+          <t>Google AI</t>
         </is>
       </c>
       <c r="I60" s="60" t="inlineStr">
         <is>
-          <t>How do quantum computers work?</t>
+          <t>3 Google updates from Galaxy Unpacked 2026</t>
         </is>
       </c>
       <c r="J60" s="60" t="inlineStr">
         <is>
-          <t>Nature, Published online: 22 July 2026; doi:10.1038/d41586-026-02219-8 Recent breakthroughs suggest usable devices could be here in a decade.</t>
+          <t>Gentle Monster glasses, Warby Parker glasses, a prompt asking for the history behind a pictured building, and a prompt asking to book a table at a pictured restaurant</t>
         </is>
       </c>
       <c r="K60" s="60" t="inlineStr">
         <is>
-          <t>https://www.nature.com/articles/d41586-026-02219-8</t>
+          <t>https://blog.google/products-and-platforms/platforms/android/galaxy-unpacked-2026/</t>
         </is>
       </c>
       <c r="L60" s="60" t="inlineStr">
         <is>
-          <t>626697d1d64f5d985431135f</t>
+          <t>7c49a9cf52e16d8bc5c300b8</t>
         </is>
       </c>
       <c r="M60" s="75" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="B61" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T00:00:00Z</t>
+          <t>2026-07-22T12:10:00Z</t>
         </is>
       </c>
       <c r="C61" s="60" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="D61" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E61" s="60" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Fusion Energy</t>
         </is>
       </c>
       <c r="F61" s="76" t="n">
@@ -5287,32 +5287,32 @@
       </c>
       <c r="G61" s="60" t="inlineStr">
         <is>
-          <t>Scientific Publication</t>
+          <t>Major Media</t>
         </is>
       </c>
       <c r="H61" s="60" t="inlineStr">
         <is>
-          <t>Nature</t>
+          <t>MIT Technology Review</t>
         </is>
       </c>
       <c r="I61" s="60" t="inlineStr">
         <is>
-          <t>CRISPR–Cas regulates expression of embedded anti-phage defence systems</t>
+          <t>The Download: NASA’s new space telescope and OpenAI’s autonomous hacker</t>
         </is>
       </c>
       <c r="J61" s="60" t="inlineStr">
         <is>
-          <t>Nature, Published online: 22 July 2026; doi:10.1038/s41586-026-10833-9 CRISPR–Cas systems transcriptionally tune diverse innate defences using CRISPR RNA-like guides to balance antiviral protection with fitness, and hyperactivate these defences when compromised, establishing a layered bacterial ‘immunity guard’ network.</t>
+          <t>This is today’s edition of The Download, our weekday newsletter that provides a daily dose of what’s going on in the world of technology. Shape-shifting mirrors on NASA’s new space telescope could unveil Jupiters like our own When NASA’s Nancy Grace Roman Space Telescope launches, as early as the end of next month, it will…</t>
         </is>
       </c>
       <c r="K61" s="60" t="inlineStr">
         <is>
-          <t>https://www.nature.com/articles/s41586-026-10833-9</t>
+          <t>https://www.technologyreview.com/2026/07/22/1140717/the-download-nasa-space-telescope-openai-hugging-face-hack/</t>
         </is>
       </c>
       <c r="L61" s="60" t="inlineStr">
         <is>
-          <t>a49dbeef4f425713e07751f7</t>
+          <t>62c5c294dc0cb2f834763aa6</t>
         </is>
       </c>
       <c r="M61" s="75" t="inlineStr">
@@ -5335,12 +5335,12 @@
       </c>
       <c r="B62" s="75" t="inlineStr">
         <is>
-          <t>2026-07-21T22:35:45Z</t>
+          <t>2026-07-22T12:00:00Z</t>
         </is>
       </c>
       <c r="C62" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D62" s="60" t="inlineStr">
@@ -5350,40 +5350,40 @@
       </c>
       <c r="E62" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence | Semiconductors &amp; Telecom</t>
+          <t>Innovation Policy</t>
         </is>
       </c>
       <c r="F62" s="76" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G62" s="60" t="inlineStr">
         <is>
-          <t>Official Company</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H62" s="60" t="inlineStr">
         <is>
-          <t>NVIDIA Blog</t>
+          <t>NIST News</t>
         </is>
       </c>
       <c r="I62" s="60" t="inlineStr">
         <is>
-          <t>Built in Fort Worth: Wistron Opens Advanced Manufacturing Plant to Produce NVIDIA AI Systems</t>
+          <t>NIST Announces Funding Opportunity for 14 MEP Centers to Advance Small and Medium-Sized U.S. Manufacturers</t>
         </is>
       </c>
       <c r="J62" s="60" t="inlineStr">
         <is>
-          <t>The AI era runs on AI infrastructure. Many of these advanced systems are built and tested in Texas. Wistron opened its first U.S. manufacturing facility today in Fort Worth — a 324,000-square-foot greenfield plant producing superchips at the heart of some of the world’s most capable AI systems. In front of an audience of Wistron […]</t>
+          <t>NIST MEP will host an informational webinar on Tuesday, July 28, 2026, at 1 p.m. ET to provide general information about this opportunity and guidance on preparing applications.</t>
         </is>
       </c>
       <c r="K62" s="60" t="inlineStr">
         <is>
-          <t>https://blogs.nvidia.com/blog/wistron-manufacturing-texas/</t>
+          <t>https://www.nist.gov/news-events/news/2026/07/nist-announces-funding-opportunity-14-mep-centers-advance-small-and-medium</t>
         </is>
       </c>
       <c r="L62" s="60" t="inlineStr">
         <is>
-          <t>21f1e1f3e19b1a5bf0af3cb7</t>
+          <t>5aa9c93bc7040291c9f08bfa</t>
         </is>
       </c>
       <c r="M62" s="75" t="inlineStr">
@@ -5406,22 +5406,22 @@
       </c>
       <c r="B63" s="75" t="inlineStr">
         <is>
-          <t>2026-07-21T19:44:19Z</t>
+          <t>2026-07-22T12:00:00Z</t>
         </is>
       </c>
       <c r="C63" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D63" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E63" s="60" t="inlineStr">
         <is>
-          <t>Innovation Policy | Fusion Energy</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="F63" s="76" t="n">
@@ -5429,32 +5429,32 @@
       </c>
       <c r="G63" s="60" t="inlineStr">
         <is>
-          <t>Industry Association</t>
+          <t>Official Company</t>
         </is>
       </c>
       <c r="H63" s="60" t="inlineStr">
         <is>
-          <t>Fusion Industry Association</t>
+          <t>OpenAI News</t>
         </is>
       </c>
       <c r="I63" s="60" t="inlineStr">
         <is>
-          <t>FIA and Clean Air Task Force Publish Principles on Codes and Standards</t>
+          <t>Advancing the next era of national science</t>
         </is>
       </c>
       <c r="J63" s="60" t="inlineStr">
         <is>
-          <t>In partnership with the Clean Air Task Force, the Fusion Industry Association published a one-pager outlining its principles for fusion codes and standards. As fusion moves towards deployment, it is critical that codes and standards ensure safe deployment while enabling innovation. The post FIA and Clean Air Task Force Publish Principles on Codes and Standards appeared first on Fusion Industry Association .</t>
+          <t>OpenAI outlines its commitment to advancing American science working with the U.S. Department of Energy and national labs to use frontier AI to accelerate discovery.</t>
         </is>
       </c>
       <c r="K63" s="60" t="inlineStr">
         <is>
-          <t>https://www.fusionindustryassociation.org/fia-and-clean-air-task-force-publish-principles-on-codes-and-standards/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=fia-and-clean-air-task-force-publish-principles-on-codes-and-standards</t>
+          <t>https://openai.com/index/advancing-the-next-era-of-national-science</t>
         </is>
       </c>
       <c r="L63" s="60" t="inlineStr">
         <is>
-          <t>2366dc909672b56b77a196bd</t>
+          <t>577ddf6b90e6d70b43383fc6</t>
         </is>
       </c>
       <c r="M63" s="75" t="inlineStr">
@@ -5477,7 +5477,7 @@
       </c>
       <c r="B64" s="75" t="inlineStr">
         <is>
-          <t>2026-07-21T17:00:00Z</t>
+          <t>2026-07-22T09:00:00Z</t>
         </is>
       </c>
       <c r="C64" s="60" t="inlineStr">
@@ -5492,40 +5492,40 @@
       </c>
       <c r="E64" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Fusion Energy</t>
         </is>
       </c>
       <c r="F64" s="76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G64" s="60" t="inlineStr">
         <is>
-          <t>Official Company</t>
+          <t>Major Media</t>
         </is>
       </c>
       <c r="H64" s="60" t="inlineStr">
         <is>
-          <t>OpenAI News</t>
+          <t>MIT Technology Review</t>
         </is>
       </c>
       <c r="I64" s="60" t="inlineStr">
         <is>
-          <t>Introducing the ChatGPT for small business program</t>
+          <t>Shape-shifting mirrors on NASA’s new space telescope could unveil Jupiters like our own</t>
         </is>
       </c>
       <c r="J64" s="60" t="inlineStr">
         <is>
-          <t>OpenAI launches the ChatGPT for Small Businesses program, helping entrepreneurs build AI skills, automate work, and grow with ChatGPT Work.</t>
+          <t>When NASA’s Nancy Grace Roman Space Telescope launches, as early as the end of next month, it will attempt one of astronomy’s most precise disappearing acts to date. The telescope will carry the first space-bound “active” coronagraph, an instrument that effectively erases most of the light from a star during photography. It will allow astronomers…</t>
         </is>
       </c>
       <c r="K64" s="60" t="inlineStr">
         <is>
-          <t>https://openai.com/index/introducing-chatgpt-small-business-program</t>
+          <t>https://www.technologyreview.com/2026/07/22/1140701/shape-shifting-mirrors-roman-space-telescope/</t>
         </is>
       </c>
       <c r="L64" s="60" t="inlineStr">
         <is>
-          <t>3064e426d18ccd85acab9b00</t>
+          <t>04231693b363104315116185</t>
         </is>
       </c>
       <c r="M64" s="75" t="inlineStr">
@@ -5548,7 +5548,7 @@
       </c>
       <c r="B65" s="75" t="inlineStr">
         <is>
-          <t>2026-07-21T15:36:43Z</t>
+          <t>2026-07-22T05:30:00Z</t>
         </is>
       </c>
       <c r="C65" s="60" t="inlineStr">
@@ -5563,11 +5563,11 @@
       </c>
       <c r="E65" s="60" t="inlineStr">
         <is>
-          <t>Semiconductors &amp; Telecom</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="F65" s="76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G65" s="60" t="inlineStr">
         <is>
@@ -5576,27 +5576,27 @@
       </c>
       <c r="H65" s="60" t="inlineStr">
         <is>
-          <t>NVIDIA Blog</t>
+          <t>OpenAI News</t>
         </is>
       </c>
       <c r="I65" s="60" t="inlineStr">
         <is>
-          <t>NVIDIA Vera Rubin Driving Performance Per Watt, Lowest Token Cost for Partners Worldwide</t>
+          <t>Introducing OpenAI Presence</t>
         </is>
       </c>
       <c r="J65" s="60" t="inlineStr">
         <is>
-          <t>NVIDIA Vera Rubin is here, and it’s going gigascale. Vera Rubin NVL72 production is ramping up with racks running at partners CoreWeave, Google Cloud, Microsoft Azure and Oracle Cloud Infrastructure. Spanning 350+ factory sites in 30 countries, Vera Rubin has the largest, most mature rack-scale supply chain ever assembled to meet customer compute demand. The […]</t>
+          <t>Introducing OpenAI Presence, a proven enterprise AI agent platform that helps organizations deploy trusted voice and chat agents for customer and internal workflows.</t>
         </is>
       </c>
       <c r="K65" s="60" t="inlineStr">
         <is>
-          <t>https://blogs.nvidia.com/blog/vera-rubin/</t>
+          <t>https://openai.com/index/introducing-openai-presence</t>
         </is>
       </c>
       <c r="L65" s="60" t="inlineStr">
         <is>
-          <t>ffef75ffd9647e2c722b429e</t>
+          <t>839f7a51d7b587ae6fb6fad7</t>
         </is>
       </c>
       <c r="M65" s="75" t="inlineStr">
@@ -5619,55 +5619,55 @@
       </c>
       <c r="B66" s="75" t="inlineStr">
         <is>
-          <t>2026-07-21T15:06:49Z</t>
+          <t>2026-07-22T00:00:00Z</t>
         </is>
       </c>
       <c r="C66" s="60" t="inlineStr">
         <is>
-          <t>EU &amp; Europe</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D66" s="60" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E66" s="60" t="inlineStr">
         <is>
-          <t>Innovation Policy</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="F66" s="76" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G66" s="60" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Official Company</t>
         </is>
       </c>
       <c r="H66" s="60" t="inlineStr">
         <is>
-          <t>UK DSIT</t>
+          <t>OpenAI News</t>
         </is>
       </c>
       <c r="I66" s="60" t="inlineStr">
         <is>
-          <t>Transparency data: DSIT: workforce management information, June 2026</t>
+          <t>NTT DATA Group cuts incident analysis to 30 minutes with Codex</t>
         </is>
       </c>
       <c r="J66" s="60" t="inlineStr">
         <is>
-          <t>Reports on departmental staff numbers and costs.</t>
+          <t>NTT DATA Group uses ChatGPT Enterprise and Codex to help 9,000 employees automate work, cut incident analysis to 30 minutes, and scale secure AI adoption.</t>
         </is>
       </c>
       <c r="K66" s="60" t="inlineStr">
         <is>
-          <t>https://www.gov.uk/government/publications/dsit-workforce-management-information-june-2026</t>
+          <t>https://openai.com/index/ntt-data</t>
         </is>
       </c>
       <c r="L66" s="60" t="inlineStr">
         <is>
-          <t>68c02c5c6a2ee3c9c91fc7f1</t>
+          <t>389ebd02d2834f48054db326</t>
         </is>
       </c>
       <c r="M66" s="75" t="inlineStr">
@@ -5690,55 +5690,55 @@
       </c>
       <c r="B67" s="75" t="inlineStr">
         <is>
-          <t>2026-07-21T15:06:31Z</t>
+          <t>2026-07-22T00:00:00Z</t>
         </is>
       </c>
       <c r="C67" s="60" t="inlineStr">
         <is>
-          <t>EU &amp; Europe</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D67" s="60" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="E67" s="60" t="inlineStr">
         <is>
-          <t>Innovation Policy</t>
+          <t>Innovation Policy | Biotechnology</t>
         </is>
       </c>
       <c r="F67" s="76" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G67" s="60" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Scientific Publication</t>
         </is>
       </c>
       <c r="H67" s="60" t="inlineStr">
         <is>
-          <t>UK DSIT</t>
+          <t>Nature</t>
         </is>
       </c>
       <c r="I67" s="60" t="inlineStr">
         <is>
-          <t>Guidance: TechFirst Local</t>
+          <t>Subnuclear genome compartmentalization controls bivalent chromatin activity</t>
         </is>
       </c>
       <c r="J67" s="60" t="inlineStr">
         <is>
-          <t>Details of the TechFirst local grant funding programme to boost digital skills and support people into tech jobs.</t>
+          <t>Nature, Published online: 22 July 2026; doi:10.1038/s41586-026-10832-w Knowledge of the spatial location of a gene is necessary to understand its epigenomic regulation.</t>
         </is>
       </c>
       <c r="K67" s="60" t="inlineStr">
         <is>
-          <t>https://www.gov.uk/government/publications/techlocal</t>
+          <t>https://www.nature.com/articles/s41586-026-10832-w</t>
         </is>
       </c>
       <c r="L67" s="60" t="inlineStr">
         <is>
-          <t>88893e13a25a6efc42ed57ea</t>
+          <t>f9bccca3cabb5ce19441f09d</t>
         </is>
       </c>
       <c r="M67" s="75" t="inlineStr">
@@ -5761,55 +5761,55 @@
       </c>
       <c r="B68" s="75" t="inlineStr">
         <is>
-          <t>2026-07-21T15:05:29Z</t>
+          <t>2026-07-22T00:00:00Z</t>
         </is>
       </c>
       <c r="C68" s="60" t="inlineStr">
         <is>
-          <t>EU &amp; Europe</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D68" s="60" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="E68" s="60" t="inlineStr">
         <is>
-          <t>Innovation Policy</t>
+          <t>Fusion Energy</t>
         </is>
       </c>
       <c r="F68" s="76" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G68" s="60" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Scientific Publication</t>
         </is>
       </c>
       <c r="H68" s="60" t="inlineStr">
         <is>
-          <t>UK DSIT</t>
+          <t>Nature</t>
         </is>
       </c>
       <c r="I68" s="60" t="inlineStr">
         <is>
-          <t>TechFirst PhD Support</t>
+          <t>What counts as a moon? Huge ‘exosatellite’ sparks debate</t>
         </is>
       </c>
       <c r="J68" s="60" t="inlineStr">
         <is>
-          <t>Part of TechFirst, the government’s flagship skills programme opening pathways into the UK’s fast-growing tech sector.</t>
+          <t>Nature, Published online: 22 July 2026; doi:10.1038/d41586-026-02299-6 Discovery of a distant Jupiter-mass object could pave the way for detection of exomoons — plus, a rare transmissible cancer found in catfish.</t>
         </is>
       </c>
       <c r="K68" s="60" t="inlineStr">
         <is>
-          <t>https://www.gov.uk/guidance/techexpert</t>
+          <t>https://www.nature.com/articles/d41586-026-02299-6</t>
         </is>
       </c>
       <c r="L68" s="60" t="inlineStr">
         <is>
-          <t>406416679082f87595cbd50b</t>
+          <t>a3eb7f1e33aee131ed0b4bf7</t>
         </is>
       </c>
       <c r="M68" s="75" t="inlineStr">
@@ -5832,55 +5832,55 @@
       </c>
       <c r="B69" s="75" t="inlineStr">
         <is>
-          <t>2026-07-21T15:05:21Z</t>
+          <t>2026-07-22T00:00:00Z</t>
         </is>
       </c>
       <c r="C69" s="60" t="inlineStr">
         <is>
-          <t>EU &amp; Europe</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D69" s="60" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="E69" s="60" t="inlineStr">
         <is>
-          <t>Innovation Policy</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="F69" s="76" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G69" s="60" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Scientific Publication</t>
         </is>
       </c>
       <c r="H69" s="60" t="inlineStr">
         <is>
-          <t>UK DSIT</t>
+          <t>Nature</t>
         </is>
       </c>
       <c r="I69" s="60" t="inlineStr">
         <is>
-          <t>TechFirst</t>
+          <t>How do quantum computers work?</t>
         </is>
       </c>
       <c r="J69" s="60" t="inlineStr">
         <is>
-          <t>TechFirst is the government’s flagship tech skills programme opening pathways into the UK’s fast-growing tech sector, providing opportunities across all parts of the UK.</t>
+          <t>Nature, Published online: 22 July 2026; doi:10.1038/d41586-026-02219-8 Recent breakthroughs suggest usable devices could be here in a decade.</t>
         </is>
       </c>
       <c r="K69" s="60" t="inlineStr">
         <is>
-          <t>https://www.gov.uk/guidance/techfirst</t>
+          <t>https://www.nature.com/articles/d41586-026-02219-8</t>
         </is>
       </c>
       <c r="L69" s="60" t="inlineStr">
         <is>
-          <t>4ae9e496e9b66c66de074041</t>
+          <t>626697d1d64f5d985431135f</t>
         </is>
       </c>
       <c r="M69" s="75" t="inlineStr">
@@ -5903,55 +5903,55 @@
       </c>
       <c r="B70" s="75" t="inlineStr">
         <is>
-          <t>2026-07-21T15:05:11Z</t>
+          <t>2026-07-22T00:00:00Z</t>
         </is>
       </c>
       <c r="C70" s="60" t="inlineStr">
         <is>
-          <t>EU &amp; Europe</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D70" s="60" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="E70" s="60" t="inlineStr">
         <is>
-          <t>Innovation Policy | Semiconductors &amp; Telecom</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="F70" s="76" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G70" s="60" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Scientific Publication</t>
         </is>
       </c>
       <c r="H70" s="60" t="inlineStr">
         <is>
-          <t>UK DSIT</t>
+          <t>Nature</t>
         </is>
       </c>
       <c r="I70" s="60" t="inlineStr">
         <is>
-          <t>Policy paper: Fixed Telecoms Modernisation Charter</t>
+          <t>CRISPR–Cas regulates expression of embedded anti-phage defence systems</t>
         </is>
       </c>
       <c r="J70" s="60" t="inlineStr">
         <is>
-          <t>This document sets out the steps that telecoms providers should follow when carrying out any current and future fixed telecoms modernisations.</t>
+          <t>Nature, Published online: 22 July 2026; doi:10.1038/s41586-026-10833-9 CRISPR–Cas systems transcriptionally tune diverse innate defences using CRISPR RNA-like guides to balance antiviral protection with fitness, and hyperactivate these defences when compromised, establishing a layered bacterial ‘immunity guard’ network.</t>
         </is>
       </c>
       <c r="K70" s="60" t="inlineStr">
         <is>
-          <t>https://www.gov.uk/government/publications/fixed-telecoms-modernisation-charter</t>
+          <t>https://www.nature.com/articles/s41586-026-10833-9</t>
         </is>
       </c>
       <c r="L70" s="60" t="inlineStr">
         <is>
-          <t>d5e4431b57fcb4b6271f6c72</t>
+          <t>a49dbeef4f425713e07751f7</t>
         </is>
       </c>
       <c r="M70" s="75" t="inlineStr">
@@ -5974,7 +5974,7 @@
       </c>
       <c r="B71" s="75" t="inlineStr">
         <is>
-          <t>2026-07-21T15:00:20Z</t>
+          <t>2026-07-21T22:35:45Z</t>
         </is>
       </c>
       <c r="C71" s="60" t="inlineStr">
@@ -6007,22 +6007,22 @@
       </c>
       <c r="I71" s="60" t="inlineStr">
         <is>
-          <t>Built for Vera Rubin, NVIDIA Spectrum-6 Arrives in Gigascale AI Factories</t>
+          <t>Built in Fort Worth: Wistron Opens Advanced Manufacturing Plant to Produce NVIDIA AI Systems</t>
         </is>
       </c>
       <c r="J71" s="60" t="inlineStr">
         <is>
-          <t>AI has entered the gigascale era. The world’s most advanced AI factories are bringing together hundreds of thousands of GPUs and CPUs to train frontier models, power agentic AI and generate intelligence at unprecedented scale. At this level, networking becomes a critical computing power multiplier in driving token generation. Marking a networking milestone, NVIDIA Spectrum-6 […]</t>
+          <t>The AI era runs on AI infrastructure. Many of these advanced systems are built and tested in Texas. Wistron opened its first U.S. manufacturing facility today in Fort Worth — a 324,000-square-foot greenfield plant producing superchips at the heart of some of the world’s most capable AI systems. In front of an audience of Wistron […]</t>
         </is>
       </c>
       <c r="K71" s="60" t="inlineStr">
         <is>
-          <t>https://blogs.nvidia.com/blog/nvidia-spectrum-six-arrives-in-gigascale-ai-factories/</t>
+          <t>https://blogs.nvidia.com/blog/wistron-manufacturing-texas/</t>
         </is>
       </c>
       <c r="L71" s="60" t="inlineStr">
         <is>
-          <t>6f3401cebeb5dc5a8f12a872</t>
+          <t>21f1e1f3e19b1a5bf0af3cb7</t>
         </is>
       </c>
       <c r="M71" s="75" t="inlineStr">
@@ -6045,12 +6045,12 @@
       </c>
       <c r="B72" s="75" t="inlineStr">
         <is>
-          <t>2026-07-21T14:48:28Z</t>
+          <t>2026-07-21T19:44:19Z</t>
         </is>
       </c>
       <c r="C72" s="60" t="inlineStr">
         <is>
-          <t>EU &amp; Europe</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D72" s="60" t="inlineStr">
@@ -6060,11 +6060,11 @@
       </c>
       <c r="E72" s="60" t="inlineStr">
         <is>
-          <t>Fusion Energy</t>
+          <t>Innovation Policy | Fusion Energy</t>
         </is>
       </c>
       <c r="F72" s="76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G72" s="60" t="inlineStr">
         <is>
@@ -6078,22 +6078,22 @@
       </c>
       <c r="I72" s="60" t="inlineStr">
         <is>
-          <t>FIA Outlines EU Financing Pathway for Fusion</t>
+          <t>FIA and Clean Air Task Force Publish Principles on Codes and Standards</t>
         </is>
       </c>
       <c r="J72" s="60" t="inlineStr">
         <is>
-          <t>On 21 July, the Fusion Industry Association published a paper outlining a practical EU financing roadmap for commercial fusion energy. As fusion projects move from research to demonstration, first-of-a-kind plants and commercial deployment, they require different funding and financing tools at each stage of development. Europe's financing framework must evolve from a collection of individual programmes into a coherent funding architecture that supports the entire fusion commercialisation journey. The post FIA Outlines EU Financing Pathway for Fusion appeared first on Fusion Industry Association .</t>
+          <t>In partnership with the Clean Air Task Force, the Fusion Industry Association published a one-pager outlining its principles for fusion codes and standards. As fusion moves towards deployment, it is critical that codes and standards ensure safe deployment while enabling innovation. The post FIA and Clean Air Task Force Publish Principles on Codes and Standards appeared first on Fusion Industry Association .</t>
         </is>
       </c>
       <c r="K72" s="60" t="inlineStr">
         <is>
-          <t>https://www.fusionindustryassociation.org/fia-outlines-eu-financing-pathway-for-fusion/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=fia-outlines-eu-financing-pathway-for-fusion</t>
+          <t>https://www.fusionindustryassociation.org/fia-and-clean-air-task-force-publish-principles-on-codes-and-standards/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=fia-and-clean-air-task-force-publish-principles-on-codes-and-standards</t>
         </is>
       </c>
       <c r="L72" s="60" t="inlineStr">
         <is>
-          <t>88af233d904d670250fa5a31</t>
+          <t>2366dc909672b56b77a196bd</t>
         </is>
       </c>
       <c r="M72" s="75" t="inlineStr">
@@ -6116,55 +6116,55 @@
       </c>
       <c r="B73" s="75" t="inlineStr">
         <is>
-          <t>2026-07-21T13:30:36Z</t>
+          <t>2026-07-21T17:00:00Z</t>
         </is>
       </c>
       <c r="C73" s="60" t="inlineStr">
         <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="D73" s="60" t="inlineStr">
+        <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="D73" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
       <c r="E73" s="60" t="inlineStr">
         <is>
-          <t>Innovation Policy | Artificial Intelligence</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="F73" s="76" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G73" s="60" t="inlineStr">
         <is>
-          <t>Policy Institute</t>
+          <t>Official Company</t>
         </is>
       </c>
       <c r="H73" s="60" t="inlineStr">
         <is>
-          <t>CSET</t>
+          <t>OpenAI News</t>
         </is>
       </c>
       <c r="I73" s="60" t="inlineStr">
         <is>
-          <t>Why Do AI Systems Misbehave?</t>
+          <t>Introducing the ChatGPT for small business program</t>
         </is>
       </c>
       <c r="J73" s="60" t="inlineStr">
         <is>
-          <t>AI systems are increasingly impressive, which makes their failures all the more baffling. This blog dives into the causes of AI misbehavior. The post Why Do AI Systems Misbehave? appeared first on Center for Security and Emerging Technology .</t>
+          <t>OpenAI launches the ChatGPT for Small Businesses program, helping entrepreneurs build AI skills, automate work, and grow with ChatGPT Work.</t>
         </is>
       </c>
       <c r="K73" s="60" t="inlineStr">
         <is>
-          <t>https://cset.georgetown.edu/article/why-do-ai-systems-misbehave/</t>
+          <t>https://openai.com/index/introducing-chatgpt-small-business-program</t>
         </is>
       </c>
       <c r="L73" s="60" t="inlineStr">
         <is>
-          <t>3e1aa390ad965782cc86c386</t>
+          <t>3064e426d18ccd85acab9b00</t>
         </is>
       </c>
       <c r="M73" s="75" t="inlineStr">
@@ -6187,22 +6187,22 @@
       </c>
       <c r="B74" s="75" t="inlineStr">
         <is>
-          <t>2026-07-21T13:00:47Z</t>
+          <t>2026-07-21T15:36:43Z</t>
         </is>
       </c>
       <c r="C74" s="60" t="inlineStr">
         <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="D74" s="60" t="inlineStr">
+        <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="D74" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
       <c r="E74" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence | Semiconductors &amp; Telecom | Healthcare</t>
+          <t>Semiconductors &amp; Telecom</t>
         </is>
       </c>
       <c r="F74" s="76" t="n">
@@ -6220,22 +6220,22 @@
       </c>
       <c r="I74" s="60" t="inlineStr">
         <is>
-          <t>NVIDIA and Partners Build in America, for America</t>
+          <t>NVIDIA Vera Rubin Driving Performance Per Watt, Lowest Token Cost for Partners Worldwide</t>
         </is>
       </c>
       <c r="J74" s="60" t="inlineStr">
         <is>
-          <t>NVIDIA and its partners are investing in American manufacturing, supply chains, energy grids and skilled workforces so the U.S. can produce the infrastructure needed for better healthcare, breakthrough scientific discovery, stronger industrial productivity and global technology leadership.</t>
+          <t>NVIDIA Vera Rubin is here, and it’s going gigascale. Vera Rubin NVL72 production is ramping up with racks running at partners CoreWeave, Google Cloud, Microsoft Azure and Oracle Cloud Infrastructure. Spanning 350+ factory sites in 30 countries, Vera Rubin has the largest, most mature rack-scale supply chain ever assembled to meet customer compute demand. The […]</t>
         </is>
       </c>
       <c r="K74" s="60" t="inlineStr">
         <is>
-          <t>https://blogs.nvidia.com/blog/nvidia-and-partners-build-in-america-for-america/</t>
+          <t>https://blogs.nvidia.com/blog/vera-rubin/</t>
         </is>
       </c>
       <c r="L74" s="60" t="inlineStr">
         <is>
-          <t>c815807553a0a9fc82116a87</t>
+          <t>ffef75ffd9647e2c722b429e</t>
         </is>
       </c>
       <c r="M74" s="75" t="inlineStr">
@@ -6258,55 +6258,55 @@
       </c>
       <c r="B75" s="75" t="inlineStr">
         <is>
-          <t>2026-07-21T13:00:14Z</t>
+          <t>2026-07-21T15:06:49Z</t>
         </is>
       </c>
       <c r="C75" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>EU &amp; Europe</t>
         </is>
       </c>
       <c r="D75" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="E75" s="60" t="inlineStr">
         <is>
-          <t>Semiconductors &amp; Telecom</t>
+          <t>Innovation Policy</t>
         </is>
       </c>
       <c r="F75" s="76" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G75" s="60" t="inlineStr">
         <is>
-          <t>Official Company</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H75" s="60" t="inlineStr">
         <is>
-          <t>Intel Newsroom</t>
+          <t>UK DSIT</t>
         </is>
       </c>
       <c r="I75" s="60" t="inlineStr">
         <is>
-          <t>Intel and Fortinet Collaborate to Advance Cybersecurity Innovation and Strengthen Global Supply Chain Resilience</t>
+          <t>Transparency data: DSIT: workforce management information, June 2026</t>
         </is>
       </c>
       <c r="J75" s="60" t="inlineStr">
         <is>
-          <t>SANTA CLARA AND SUNNYVALE, Calif. – July 21, 2026 – Intel Corporation (NASDAQ: INTC) and Fortinet (NASDAQ: FTNT), today announced a strategic collaboration to develop Fortinet Security Processor 6 (SP6). Expanding a long-standing relationship between the two companies, this collaboration combines Fortinet’s proprietary, purpose-built security processor expertise with Intel’s advanced design, packaging, and manufacturing capabilities … The post Intel and Fortinet Collaborate to Advance Cybersecurity Innovation and Strengthen Global Supply Chain Resilience appeared first on Newsroom .</t>
+          <t>Reports on departmental staff numbers and costs.</t>
         </is>
       </c>
       <c r="K75" s="60" t="inlineStr">
         <is>
-          <t>https://newsroom.intel.com/manufacturing/intel-and-fortinet-collaborate-to-advance-cybersecurity-innovation-and-strengthen-global-supply-chain-resilience</t>
+          <t>https://www.gov.uk/government/publications/dsit-workforce-management-information-june-2026</t>
         </is>
       </c>
       <c r="L75" s="60" t="inlineStr">
         <is>
-          <t>28388342f57d2cae1a96b7b7</t>
+          <t>68c02c5c6a2ee3c9c91fc7f1</t>
         </is>
       </c>
       <c r="M75" s="75" t="inlineStr">
@@ -6329,55 +6329,55 @@
       </c>
       <c r="B76" s="75" t="inlineStr">
         <is>
-          <t>2026-07-21T12:10:00Z</t>
+          <t>2026-07-21T15:06:31Z</t>
         </is>
       </c>
       <c r="C76" s="60" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>EU &amp; Europe</t>
         </is>
       </c>
       <c r="D76" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="E76" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Innovation Policy</t>
         </is>
       </c>
       <c r="F76" s="76" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G76" s="60" t="inlineStr">
         <is>
-          <t>Major Media</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H76" s="60" t="inlineStr">
         <is>
-          <t>MIT Technology Review</t>
+          <t>UK DSIT</t>
         </is>
       </c>
       <c r="I76" s="60" t="inlineStr">
         <is>
-          <t>The Download: Chinese AI divides the White House, and a record copyright payout</t>
+          <t>Guidance: TechFirst Local</t>
         </is>
       </c>
       <c r="J76" s="60" t="inlineStr">
         <is>
-          <t>This is today’s edition of The Download, our weekday newsletter that provides a daily dose of what’s going on in the world of technology. China’s AI models have Trump’s AI world at war with itself Last weekend, several current and former advisers to President Donald Trump on AI publicly lobbed insults at the country’s leading…</t>
+          <t>Details of the TechFirst local grant funding programme to boost digital skills and support people into tech jobs.</t>
         </is>
       </c>
       <c r="K76" s="60" t="inlineStr">
         <is>
-          <t>https://www.technologyreview.com/2026/07/21/1140685/the-download-chinese-ai-divides-white-house-anthropic-copyright-settlement/</t>
+          <t>https://www.gov.uk/government/publications/techlocal</t>
         </is>
       </c>
       <c r="L76" s="60" t="inlineStr">
         <is>
-          <t>f9addf0904b9de5b7bcc326b</t>
+          <t>88893e13a25a6efc42ed57ea</t>
         </is>
       </c>
       <c r="M76" s="75" t="inlineStr">
@@ -6400,55 +6400,55 @@
       </c>
       <c r="B77" s="75" t="inlineStr">
         <is>
-          <t>2026-07-21T10:37:34Z</t>
+          <t>2026-07-21T15:05:29Z</t>
         </is>
       </c>
       <c r="C77" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>EU &amp; Europe</t>
         </is>
       </c>
       <c r="D77" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="E77" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence | Semiconductors &amp; Telecom</t>
+          <t>Innovation Policy</t>
         </is>
       </c>
       <c r="F77" s="76" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G77" s="60" t="inlineStr">
         <is>
-          <t>Major Media</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H77" s="60" t="inlineStr">
         <is>
-          <t>MIT Technology Review</t>
+          <t>UK DSIT</t>
         </is>
       </c>
       <c r="I77" s="60" t="inlineStr">
         <is>
-          <t>Advancing next-gen AI with materials science innovation</t>
+          <t>TechFirst PhD Support</t>
         </is>
       </c>
       <c r="J77" s="60" t="inlineStr">
         <is>
-          <t>The conversation about AI often centers on algorithms, computing power, or huge investments in new semiconductor fabrication plants and hyperscale data centers. But beneath each of these advances is another layer of innovation that makes them possible: advanced materials. Every new generation of AI technology demands more processing power, more memory, greater energy efficiency, and…</t>
+          <t>Part of TechFirst, the government’s flagship skills programme opening pathways into the UK’s fast-growing tech sector.</t>
         </is>
       </c>
       <c r="K77" s="60" t="inlineStr">
         <is>
-          <t>https://www.technologyreview.com/2026/07/21/1140602/advancing-next-gen-ai-with-materials-science-innovation/</t>
+          <t>https://www.gov.uk/guidance/techexpert</t>
         </is>
       </c>
       <c r="L77" s="60" t="inlineStr">
         <is>
-          <t>6b7e59d6f503e3d45c9ea292</t>
+          <t>406416679082f87595cbd50b</t>
         </is>
       </c>
       <c r="M77" s="75" t="inlineStr">
@@ -6471,55 +6471,55 @@
       </c>
       <c r="B78" s="75" t="inlineStr">
         <is>
-          <t>2026-07-21T08:26:17Z</t>
+          <t>2026-07-21T15:05:21Z</t>
         </is>
       </c>
       <c r="C78" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>EU &amp; Europe</t>
         </is>
       </c>
       <c r="D78" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="E78" s="60" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Innovation Policy</t>
         </is>
       </c>
       <c r="F78" s="76" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G78" s="60" t="inlineStr">
         <is>
-          <t>Intergovernmental</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H78" s="60" t="inlineStr">
         <is>
-          <t>WHO News</t>
+          <t>UK DSIT</t>
         </is>
       </c>
       <c r="I78" s="60" t="inlineStr">
         <is>
-          <t>UN report: Global hunger levels ease for third consecutive year as regional disparities persist</t>
+          <t>TechFirst</t>
         </is>
       </c>
       <c r="J78" s="60" t="inlineStr">
         <is>
-          <t>Global hunger declined for a third consecutive year in 2025, demonstrating that progress is possible. However, the improvements remain fragile, unevenly distributed and insufficient to achieve the Sustainable Development Goals by 2030, according to The State of Food Security and Nutrition in the World 2026 (SOFI 2026) report, released on Tuesday by five United Nations specialized agencies.</t>
+          <t>TechFirst is the government’s flagship tech skills programme opening pathways into the UK’s fast-growing tech sector, providing opportunities across all parts of the UK.</t>
         </is>
       </c>
       <c r="K78" s="60" t="inlineStr">
         <is>
-          <t>https://www.who.int/news/item/21-07-2026-un-report--global-hunger-levels-ease-for-third-consecutive-year-as-regional-disparities-persist</t>
+          <t>https://www.gov.uk/guidance/techfirst</t>
         </is>
       </c>
       <c r="L78" s="60" t="inlineStr">
         <is>
-          <t>223e20b3abaf53bd3b29f3e1</t>
+          <t>4ae9e496e9b66c66de074041</t>
         </is>
       </c>
       <c r="M78" s="75" t="inlineStr">
@@ -6542,55 +6542,55 @@
       </c>
       <c r="B79" s="75" t="inlineStr">
         <is>
-          <t>2026-07-21T07:00:00Z</t>
+          <t>2026-07-21T15:05:11Z</t>
         </is>
       </c>
       <c r="C79" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>EU &amp; Europe</t>
         </is>
       </c>
       <c r="D79" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="E79" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Innovation Policy | Semiconductors &amp; Telecom</t>
         </is>
       </c>
       <c r="F79" s="76" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G79" s="60" t="inlineStr">
         <is>
-          <t>Official Company</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H79" s="60" t="inlineStr">
         <is>
-          <t>OpenAI News</t>
+          <t>UK DSIT</t>
         </is>
       </c>
       <c r="I79" s="60" t="inlineStr">
         <is>
-          <t>OpenAI and Hugging Face partner to address security incident during model evaluation</t>
+          <t>Policy paper: Fixed Telecoms Modernisation Charter</t>
         </is>
       </c>
       <c r="J79" s="60" t="inlineStr">
         <is>
-          <t>OpenAI and Hugging Face share early findings from a security incident during AI model evaluation, highlighting advanced cyber capabilities and lessons for defenders.</t>
+          <t>This document sets out the steps that telecoms providers should follow when carrying out any current and future fixed telecoms modernisations.</t>
         </is>
       </c>
       <c r="K79" s="60" t="inlineStr">
         <is>
-          <t>https://openai.com/index/hugging-face-model-evaluation-security-incident</t>
+          <t>https://www.gov.uk/government/publications/fixed-telecoms-modernisation-charter</t>
         </is>
       </c>
       <c r="L79" s="60" t="inlineStr">
         <is>
-          <t>d925d8c91f460a44f07089c2</t>
+          <t>d5e4431b57fcb4b6271f6c72</t>
         </is>
       </c>
       <c r="M79" s="75" t="inlineStr">
@@ -6613,22 +6613,22 @@
       </c>
       <c r="B80" s="75" t="inlineStr">
         <is>
-          <t>2026-07-20T15:55:00Z</t>
+          <t>2026-07-21T15:00:20Z</t>
         </is>
       </c>
       <c r="C80" s="60" t="inlineStr">
         <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="D80" s="60" t="inlineStr">
+        <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="D80" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
       <c r="E80" s="60" t="inlineStr">
         <is>
-          <t>Semiconductors &amp; Telecom</t>
+          <t>Artificial Intelligence | Semiconductors &amp; Telecom</t>
         </is>
       </c>
       <c r="F80" s="76" t="n">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="G80" s="60" t="inlineStr">
         <is>
-          <t>Major Media</t>
+          <t>Official Company</t>
         </is>
       </c>
       <c r="H80" s="60" t="inlineStr">
         <is>
-          <t>IEEE Spectrum</t>
+          <t>NVIDIA Blog</t>
         </is>
       </c>
       <c r="I80" s="60" t="inlineStr">
         <is>
-          <t>SEM-Guided Low-kV FIB Finishing for Leading-Edge Semiconductor Failure Analysis</t>
+          <t>Built for Vera Rubin, NVIDIA Spectrum-6 Arrives in Gigascale AI Factories</t>
         </is>
       </c>
       <c r="J80" s="60" t="inlineStr">
         <is>
-          <t>Discover how the ZEISS Crossbeam 750 FIBSEM sets a new benchmark for precise TEM lamella prep, tomography, and advanced nanofabrication. This delivers better resolution, better SNR, larger usable FOV, and shorter acquisition times. Learn how uninterrupted FIB milling will reduce damage and rework, accelerate time to TEM, and increase first pass success—so your FA, yield, and materials teams make faster, confident data driven decisions. Register now for this free webinar! Join us to discover how the new ZEISS Crossbeam 750 with its see while you mill capability delivers precision and clarity—every time—for demanding FIB-SEM workflows. Designed for extremely challenging TEM lamella preparatio…</t>
+          <t>AI has entered the gigascale era. The world’s most advanced AI factories are bringing together hundreds of thousands of GPUs and CPUs to train frontier models, power agentic AI and generate intelligence at unprecedented scale. At this level, networking becomes a critical computing power multiplier in driving token generation. Marking a networking milestone, NVIDIA Spectrum-6 […]</t>
         </is>
       </c>
       <c r="K80" s="60" t="inlineStr">
         <is>
-          <t>https://event.on24.com/wcc/r/5418459/287E3D5B99470D34C830D69A24B3B207</t>
+          <t>https://blogs.nvidia.com/blog/nvidia-spectrum-six-arrives-in-gigascale-ai-factories/</t>
         </is>
       </c>
       <c r="L80" s="60" t="inlineStr">
         <is>
-          <t>73d0028e337a76c2cd00f1bc</t>
+          <t>6f3401cebeb5dc5a8f12a872</t>
         </is>
       </c>
       <c r="M80" s="75" t="inlineStr">
@@ -6684,22 +6684,22 @@
       </c>
       <c r="B81" s="75" t="inlineStr">
         <is>
-          <t>2026-07-20T15:34:49Z</t>
+          <t>2026-07-21T14:48:28Z</t>
         </is>
       </c>
       <c r="C81" s="60" t="inlineStr">
         <is>
+          <t>EU &amp; Europe</t>
+        </is>
+      </c>
+      <c r="D81" s="60" t="inlineStr">
+        <is>
           <t>Global</t>
         </is>
       </c>
-      <c r="D81" s="60" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
       <c r="E81" s="60" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Fusion Energy</t>
         </is>
       </c>
       <c r="F81" s="76" t="n">
@@ -6707,32 +6707,32 @@
       </c>
       <c r="G81" s="60" t="inlineStr">
         <is>
-          <t>Intergovernmental</t>
+          <t>Industry Association</t>
         </is>
       </c>
       <c r="H81" s="60" t="inlineStr">
         <is>
-          <t>WHO News</t>
+          <t>Fusion Industry Association</t>
         </is>
       </c>
       <c r="I81" s="60" t="inlineStr">
         <is>
-          <t>WHO marks 25 years of Research4Life, advancing access to scientific knowledge in more than 120 countries</t>
+          <t>FIA Outlines EU Financing Pathway for Fusion</t>
         </is>
       </c>
       <c r="J81" s="60" t="inlineStr">
         <is>
-          <t>The World Health Organization (WHO) today marks the 25th anniversary of Research4Life, a public-private partnership that provides researchers, educators, health professionals and policy-makers in low- and middle-income countries with affordable or free access to scientific knowledge. The partnership has helped dramatically expand access to scientific knowledge for researchers, educators, health professionals and policy-makers in more than 120 countries.</t>
+          <t>On 21 July, the Fusion Industry Association published a paper outlining a practical EU financing roadmap for commercial fusion energy. As fusion projects move from research to demonstration, first-of-a-kind plants and commercial deployment, they require different funding and financing tools at each stage of development. Europe's financing framework must evolve from a collection of individual programmes into a coherent funding architecture that supports the entire fusion commercialisation journey. The post FIA Outlines EU Financing Pathway for Fusion appeared first on Fusion Industry Association .</t>
         </is>
       </c>
       <c r="K81" s="60" t="inlineStr">
         <is>
-          <t>https://www.who.int/news/item/21-07-2026-who-marks-25-years-of-research4life--advancing-access-to-scientific-knowledge-in-more-than-120-countries</t>
+          <t>https://www.fusionindustryassociation.org/fia-outlines-eu-financing-pathway-for-fusion/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=fia-outlines-eu-financing-pathway-for-fusion</t>
         </is>
       </c>
       <c r="L81" s="60" t="inlineStr">
         <is>
-          <t>09e6494006eb3af009c1a30f</t>
+          <t>88af233d904d670250fa5a31</t>
         </is>
       </c>
       <c r="M81" s="75" t="inlineStr">
@@ -6755,55 +6755,55 @@
       </c>
       <c r="B82" s="75" t="inlineStr">
         <is>
-          <t>2026-07-20T07:09:01Z</t>
+          <t>2026-07-21T13:30:36Z</t>
         </is>
       </c>
       <c r="C82" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D82" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E82" s="60" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Innovation Policy | Artificial Intelligence</t>
         </is>
       </c>
       <c r="F82" s="76" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G82" s="60" t="inlineStr">
         <is>
-          <t>Intergovernmental</t>
+          <t>Policy Institute</t>
         </is>
       </c>
       <c r="H82" s="60" t="inlineStr">
         <is>
-          <t>WHO News</t>
+          <t>CSET</t>
         </is>
       </c>
       <c r="I82" s="60" t="inlineStr">
         <is>
-          <t>Road deaths fall by 21% globally but stronger action is needed to save lives</t>
+          <t>Why Do AI Systems Misbehave?</t>
         </is>
       </c>
       <c r="J82" s="60" t="inlineStr">
         <is>
-          <t>Despite the addition of more than one billion motor-vehicles to the world’s roads, the global rate of road traffic deaths declined by 21% between 2011 and 2025, according to new data released by the World Health Organization (WHO). The world has experienced profound changes in road traffic during this time with the emergence of new modes of transport and a sharp rise in motorcycle use. Despite this progress, however, road traffic crashes still claimed 1.16 million people's lives in 2025. Road traffic injuries remain the leading cause of death among children and youth aged 5–29 years. The new WHO data comes as global leaders today adopt a new United Nations (UN) General Assembly progress dec…</t>
+          <t>AI systems are increasingly impressive, which makes their failures all the more baffling. This blog dives into the causes of AI misbehavior. The post Why Do AI Systems Misbehave? appeared first on Center for Security and Emerging Technology .</t>
         </is>
       </c>
       <c r="K82" s="60" t="inlineStr">
         <is>
-          <t>https://www.who.int/news/item/20-07-2026-road-deaths-fall-by-21--globally-but-stronger-action-is-needed-to-save-lives</t>
+          <t>https://cset.georgetown.edu/article/why-do-ai-systems-misbehave/</t>
         </is>
       </c>
       <c r="L82" s="60" t="inlineStr">
         <is>
-          <t>05edb573a8ead16ae99b6291</t>
+          <t>3e1aa390ad965782cc86c386</t>
         </is>
       </c>
       <c r="M82" s="75" t="inlineStr">
@@ -6826,55 +6826,55 @@
       </c>
       <c r="B83" s="75" t="inlineStr">
         <is>
-          <t>2026-07-18T07:27:54Z</t>
+          <t>2026-07-21T13:00:47Z</t>
         </is>
       </c>
       <c r="C83" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D83" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E83" s="60" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Artificial Intelligence | Semiconductors &amp; Telecom | Healthcare</t>
         </is>
       </c>
       <c r="F83" s="76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G83" s="60" t="inlineStr">
         <is>
-          <t>Intergovernmental</t>
+          <t>Official Company</t>
         </is>
       </c>
       <c r="H83" s="60" t="inlineStr">
         <is>
-          <t>WHO News</t>
+          <t>NVIDIA Blog</t>
         </is>
       </c>
       <c r="I83" s="60" t="inlineStr">
         <is>
-          <t>WHO Member States continue negotiations on the Pathogen Access and Benefit Sharing Annex</t>
+          <t>NVIDIA and Partners Build in America, for America</t>
         </is>
       </c>
       <c r="J83" s="60" t="inlineStr">
         <is>
-          <t>WHO Member States have advanced negotiations on the Pathogen Access and Benefit Sharing (PABS) annex, a central component of the WHO Pandemic Agreement, while agreeing that continued discussions are needed to finalize a framework that supports a faster, more effective and equitable response to future pandemics.</t>
+          <t>NVIDIA and its partners are investing in American manufacturing, supply chains, energy grids and skilled workforces so the U.S. can produce the infrastructure needed for better healthcare, breakthrough scientific discovery, stronger industrial productivity and global technology leadership.</t>
         </is>
       </c>
       <c r="K83" s="60" t="inlineStr">
         <is>
-          <t>https://www.who.int/news/item/20-07-2026-who-member-states-continue-negotiations-on-the-pathogen-access-and-benefit-sharing-annex</t>
+          <t>https://blogs.nvidia.com/blog/nvidia-and-partners-build-in-america-for-america/</t>
         </is>
       </c>
       <c r="L83" s="60" t="inlineStr">
         <is>
-          <t>14dd15caca066d18dfcf2e34</t>
+          <t>c815807553a0a9fc82116a87</t>
         </is>
       </c>
       <c r="M83" s="75" t="inlineStr">
@@ -6897,55 +6897,55 @@
       </c>
       <c r="B84" s="75" t="inlineStr">
         <is>
-          <t>2026-07-17T20:26:18Z</t>
+          <t>2026-07-21T13:00:14Z</t>
         </is>
       </c>
       <c r="C84" s="60" t="inlineStr">
         <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="D84" s="60" t="inlineStr">
+        <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="D84" s="60" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
       <c r="E84" s="60" t="inlineStr">
         <is>
-          <t>Fusion Energy</t>
+          <t>Semiconductors &amp; Telecom</t>
         </is>
       </c>
       <c r="F84" s="76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G84" s="60" t="inlineStr">
         <is>
-          <t>Industry Association</t>
+          <t>Official Company</t>
         </is>
       </c>
       <c r="H84" s="60" t="inlineStr">
         <is>
-          <t>Fusion Industry Association</t>
+          <t>Intel Newsroom</t>
         </is>
       </c>
       <c r="I84" s="60" t="inlineStr">
         <is>
-          <t>In the News: FIA Launches the 2026 Global Fusion Industry Report in New York City, Washington, D.C., and London</t>
+          <t>Intel and Fortinet Collaborate to Advance Cybersecurity Innovation and Strengthen Global Supply Chain Resilience</t>
         </is>
       </c>
       <c r="J84" s="60" t="inlineStr">
         <is>
-          <t>On July 13, the Fusion Industry Association launched the 2026 Global Fusion Industry Report at an event in New York City - making headlines worldwide and bringing together industry leaders, investors, and media. A Washington, D.C. launch and Congressional briefing followed on July 15, to discuss the report’s findings in the context of US policy with policymakers, think tanks, national labs, and industry leaders. A London dinner event held on July 29 will discuss the report's findings with government leaders, aligned with the recently released UK 2026 Fusion Strategy. The post In the News: FIA Launches the 2026 Global Fusion Industry Report in New York City, Washington, D.C., and London appe…</t>
+          <t>SANTA CLARA AND SUNNYVALE, Calif. – July 21, 2026 – Intel Corporation (NASDAQ: INTC) and Fortinet (NASDAQ: FTNT), today announced a strategic collaboration to develop Fortinet Security Processor 6 (SP6). Expanding a long-standing relationship between the two companies, this collaboration combines Fortinet’s proprietary, purpose-built security processor expertise with Intel’s advanced design, packaging, and manufacturing capabilities … The post Intel and Fortinet Collaborate to Advance Cybersecurity Innovation and Strengthen Global Supply Chain Resilience appeared first on Newsroom .</t>
         </is>
       </c>
       <c r="K84" s="60" t="inlineStr">
         <is>
-          <t>https://www.fusionindustryassociation.org/fia-launches-the-2026-global-fusion-industry-report-in-new-york-city-washington-d-c-and-london/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=fia-launches-the-2026-global-fusion-industry-report-in-new-york-city-washington-d-c-and-london</t>
+          <t>https://newsroom.intel.com/manufacturing/intel-and-fortinet-collaborate-to-advance-cybersecurity-innovation-and-strengthen-global-supply-chain-resilience</t>
         </is>
       </c>
       <c r="L84" s="60" t="inlineStr">
         <is>
-          <t>186c1d4e76c09a864706432c</t>
+          <t>28388342f57d2cae1a96b7b7</t>
         </is>
       </c>
       <c r="M84" s="75" t="inlineStr">
@@ -6968,22 +6968,22 @@
       </c>
       <c r="B85" s="75" t="inlineStr">
         <is>
-          <t>2026-07-17T18:42:47Z</t>
+          <t>2026-07-21T12:10:00Z</t>
         </is>
       </c>
       <c r="C85" s="60" t="inlineStr">
         <is>
-          <t>EU &amp; Europe</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="D85" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E85" s="60" t="inlineStr">
         <is>
-          <t>Innovation Policy | Fusion Energy</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="F85" s="76" t="n">
@@ -6991,32 +6991,32 @@
       </c>
       <c r="G85" s="60" t="inlineStr">
         <is>
-          <t>Industry Association</t>
+          <t>Major Media</t>
         </is>
       </c>
       <c r="H85" s="60" t="inlineStr">
         <is>
-          <t>Fusion Industry Association</t>
+          <t>MIT Technology Review</t>
         </is>
       </c>
       <c r="I85" s="60" t="inlineStr">
         <is>
-          <t>International Legal Expert Group Publish Paper on the Need for the EU to Secure Its Competitive Fusion Advantage</t>
+          <t>The Download: Chinese AI divides the White House, and a record copyright payout</t>
         </is>
       </c>
       <c r="J85" s="60" t="inlineStr">
         <is>
-          <t>A discussion paper from the International Group of Legal Experts on Fusion Energy (FELEX) argues that Europe holds a competitive advantage in commercial fusion that no other region can replicate, but must act now to preserve it. The paper highlights the Euratom Treaty as the world’s only harmonized legal framework for nuclear governance across 27... The post International Legal Expert Group Publish Paper on the Need for the EU to Secure Its Competitive Fusion Advantage appeared first on Fusion Industry Association .</t>
+          <t>This is today’s edition of The Download, our weekday newsletter that provides a daily dose of what’s going on in the world of technology. China’s AI models have Trump’s AI world at war with itself Last weekend, several current and former advisers to President Donald Trump on AI publicly lobbed insults at the country’s leading…</t>
         </is>
       </c>
       <c r="K85" s="60" t="inlineStr">
         <is>
-          <t>https://www.fusionindustryassociation.org/international-legal-expert-group-publish-paper-on-the-need-for-the-eu-to-secure-its-competitive-fusion-advantage/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=international-legal-expert-group-publish-paper-on-the-need-for-the-eu-to-secure-its-competitive-fusion-advantage</t>
+          <t>https://www.technologyreview.com/2026/07/21/1140685/the-download-chinese-ai-divides-white-house-anthropic-copyright-settlement/</t>
         </is>
       </c>
       <c r="L85" s="60" t="inlineStr">
         <is>
-          <t>7ef6110ab078602757409abf</t>
+          <t>f9addf0904b9de5b7bcc326b</t>
         </is>
       </c>
       <c r="M85" s="75" t="inlineStr">
@@ -7039,7 +7039,7 @@
       </c>
       <c r="B86" s="75" t="inlineStr">
         <is>
-          <t>2026-07-17T18:00:01Z</t>
+          <t>2026-07-21T10:37:34Z</t>
         </is>
       </c>
       <c r="C86" s="60" t="inlineStr">
@@ -7054,7 +7054,7 @@
       </c>
       <c r="E86" s="60" t="inlineStr">
         <is>
-          <t>Robotics</t>
+          <t>Artificial Intelligence | Semiconductors &amp; Telecom</t>
         </is>
       </c>
       <c r="F86" s="76" t="n">
@@ -7067,27 +7067,27 @@
       </c>
       <c r="H86" s="60" t="inlineStr">
         <is>
-          <t>IEEE Spectrum</t>
+          <t>MIT Technology Review</t>
         </is>
       </c>
       <c r="I86" s="60" t="inlineStr">
         <is>
-          <t>This Graduate Student Equips NASA’s Robots With Assembly Skills</t>
+          <t>Advancing next-gen AI with materials science innovation</t>
         </is>
       </c>
       <c r="J86" s="60" t="inlineStr">
         <is>
-          <t>Like many engineers, Sarah Downs says she knew she wanted to pursue a STEM career from a young age. As a teenager, she discovered robotics through her Tulsa, Okla., middle school’s First Lego League team, and she fell in love with the field, she says. Downs participated in the international robotics program from 2014 to 2016. Watching PBS specials on NASA Mars rovers Spirit and Opportunity , and seeing the live broadcast of the Curiosity rover launch in 2011, inspired the teen to dream of a career working with NASA. Sarah Downs MEMBER GRADE Graduate student member UNIVERSITY Texas A&amp;M University in College Station MAJOR Electric engineering This year the IEEE graduate student member achieve…</t>
+          <t>The conversation about AI often centers on algorithms, computing power, or huge investments in new semiconductor fabrication plants and hyperscale data centers. But beneath each of these advances is another layer of innovation that makes them possible: advanced materials. Every new generation of AI technology demands more processing power, more memory, greater energy efficiency, and…</t>
         </is>
       </c>
       <c r="K86" s="60" t="inlineStr">
         <is>
-          <t>https://spectrum.ieee.org/graduate-student-nasas-robots-assembly</t>
+          <t>https://www.technologyreview.com/2026/07/21/1140602/advancing-next-gen-ai-with-materials-science-innovation/</t>
         </is>
       </c>
       <c r="L86" s="60" t="inlineStr">
         <is>
-          <t>c21b23b6ab59c7960b95be1f</t>
+          <t>6b7e59d6f503e3d45c9ea292</t>
         </is>
       </c>
       <c r="M86" s="75" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="B87" s="75" t="inlineStr">
         <is>
-          <t>2026-07-17T13:00:05Z</t>
+          <t>2026-07-21T08:26:17Z</t>
         </is>
       </c>
       <c r="C87" s="60" t="inlineStr">
@@ -7120,45 +7120,45 @@
       </c>
       <c r="D87" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="E87" s="60" t="inlineStr">
         <is>
-          <t>Semiconductors &amp; Telecom | Healthcare</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="F87" s="76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G87" s="60" t="inlineStr">
         <is>
-          <t>Official Company</t>
+          <t>Intergovernmental</t>
         </is>
       </c>
       <c r="H87" s="60" t="inlineStr">
         <is>
-          <t>Intel Newsroom</t>
+          <t>WHO News</t>
         </is>
       </c>
       <c r="I87" s="60" t="inlineStr">
         <is>
-          <t>Intel-Powered Medical Exoskeleton Helps Patients Get Back on Their Feet</t>
+          <t>UN report: Global hunger levels ease for third consecutive year as regional disparities persist</t>
         </is>
       </c>
       <c r="J87" s="60" t="inlineStr">
         <is>
-          <t>People with lower-limb injuries who cannot stand or walk often need intensive clinical rehabilitation and expert-guided physiotherapy.This medical care retrains the limbs and supports the brain’s ability to relearn movement, with the goal of restoring greater mobility and ultimately, helping the patient to walk again.But traditional rehabilitation methods today have its limits – it’s fatigue-inducing, imprecise and requires expert, … The post Intel-Powered Medical Exoskeleton Helps Patients Get Back on Their Feet appeared first on Newsroom .</t>
+          <t>Global hunger declined for a third consecutive year in 2025, demonstrating that progress is possible. However, the improvements remain fragile, unevenly distributed and insufficient to achieve the Sustainable Development Goals by 2030, according to The State of Food Security and Nutrition in the World 2026 (SOFI 2026) report, released on Tuesday by five United Nations specialized agencies.</t>
         </is>
       </c>
       <c r="K87" s="60" t="inlineStr">
         <is>
-          <t>https://newsroom.intel.com/client-computing/intel-powered-medical-exoskeleton-helps-patients-get-back-on-their-feet</t>
+          <t>https://www.who.int/news/item/21-07-2026-un-report--global-hunger-levels-ease-for-third-consecutive-year-as-regional-disparities-persist</t>
         </is>
       </c>
       <c r="L87" s="60" t="inlineStr">
         <is>
-          <t>3dd1b06b356e118627f94f8b</t>
+          <t>223e20b3abaf53bd3b29f3e1</t>
         </is>
       </c>
       <c r="M87" s="75" t="inlineStr">
@@ -7181,7 +7181,7 @@
       </c>
       <c r="B88" s="75" t="inlineStr">
         <is>
-          <t>2026-07-16T16:00:53Z</t>
+          <t>2026-07-21T07:00:00Z</t>
         </is>
       </c>
       <c r="C88" s="60" t="inlineStr">
@@ -7196,11 +7196,11 @@
       </c>
       <c r="E88" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence | Semiconductors &amp; Telecom</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="F88" s="76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G88" s="60" t="inlineStr">
         <is>
@@ -7209,27 +7209,27 @@
       </c>
       <c r="H88" s="60" t="inlineStr">
         <is>
-          <t>Intel Newsroom</t>
+          <t>OpenAI News</t>
         </is>
       </c>
       <c r="I88" s="60" t="inlineStr">
         <is>
-          <t>Intel and Google Cloud Announce Collaboration to Accelerate Intel’s AI-Enabled Enterprise Transformation</t>
+          <t>OpenAI and Hugging Face partner to address security incident during model evaluation</t>
         </is>
       </c>
       <c r="J88" s="60" t="inlineStr">
         <is>
-          <t>SANTA CLARA, Calif., and SUNNYVALE, Calif. – July 16, 2026 – Intel and Google Cloud today announced an expansion of their previously announced multi-year strategic collaboration, which would accelerate Intel’s enterprise-wide digital evolution through the deployment of Gemini Enterprise and Google Cloud.Intel will integrate advanced, Gemini-powered generative AI across its global workforce, helping to scale capabilities and … The post Intel and Google Cloud Announce Collaboration to Accelerate Intel’s AI-Enabled Enterprise Transformation appeared first on Newsroom .</t>
+          <t>OpenAI and Hugging Face share early findings from a security incident during AI model evaluation, highlighting advanced cyber capabilities and lessons for defenders.</t>
         </is>
       </c>
       <c r="K88" s="60" t="inlineStr">
         <is>
-          <t>https://newsroom.intel.com/artificial-intelligence/intel-google-cloud-announce-collaboration-to-accelerate-intel-ai-enabled-enterprise-transformation</t>
+          <t>https://openai.com/index/hugging-face-model-evaluation-security-incident</t>
         </is>
       </c>
       <c r="L88" s="60" t="inlineStr">
         <is>
-          <t>0361033c6203d3cbfc2c57cf</t>
+          <t>d925d8c91f460a44f07089c2</t>
         </is>
       </c>
       <c r="M88" s="75" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="B89" s="75" t="inlineStr">
         <is>
-          <t>2026-07-16T16:00:00Z</t>
+          <t>2026-07-20T15:55:00Z</t>
         </is>
       </c>
       <c r="C89" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D89" s="60" t="inlineStr">
@@ -7267,7 +7267,7 @@
       </c>
       <c r="E89" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Semiconductors &amp; Telecom</t>
         </is>
       </c>
       <c r="F89" s="76" t="n">
@@ -7275,32 +7275,32 @@
       </c>
       <c r="G89" s="60" t="inlineStr">
         <is>
-          <t>Official Company</t>
+          <t>Major Media</t>
         </is>
       </c>
       <c r="H89" s="60" t="inlineStr">
         <is>
-          <t>Google AI</t>
+          <t>IEEE Spectrum</t>
         </is>
       </c>
       <c r="I89" s="60" t="inlineStr">
         <is>
-          <t>Connect more of your apps to Search</t>
+          <t>SEM-Guided Low-kV FIB Finishing for Leading-Edge Semiconductor Failure Analysis</t>
         </is>
       </c>
       <c r="J89" s="60" t="inlineStr">
         <is>
-          <t>Connected apps rendering</t>
+          <t>Discover how the ZEISS Crossbeam 750 FIBSEM sets a new benchmark for precise TEM lamella prep, tomography, and advanced nanofabrication. This delivers better resolution, better SNR, larger usable FOV, and shorter acquisition times. Learn how uninterrupted FIB milling will reduce damage and rework, accelerate time to TEM, and increase first pass success—so your FA, yield, and materials teams make faster, confident data driven decisions. Register now for this free webinar! Join us to discover how the new ZEISS Crossbeam 750 with its see while you mill capability delivers precision and clarity—every time—for demanding FIB-SEM workflows. Designed for extremely challenging TEM lamella preparatio…</t>
         </is>
       </c>
       <c r="K89" s="60" t="inlineStr">
         <is>
-          <t>https://blog.google/products-and-platforms/products/search/connected-apps/</t>
+          <t>https://event.on24.com/wcc/r/5418459/287E3D5B99470D34C830D69A24B3B207</t>
         </is>
       </c>
       <c r="L89" s="60" t="inlineStr">
         <is>
-          <t>23c6974aa4b45f04208cef57</t>
+          <t>73d0028e337a76c2cd00f1bc</t>
         </is>
       </c>
       <c r="M89" s="75" t="inlineStr">
@@ -7323,7 +7323,7 @@
       </c>
       <c r="B90" s="75" t="inlineStr">
         <is>
-          <t>2026-07-16T16:00:00Z</t>
+          <t>2026-07-20T15:34:49Z</t>
         </is>
       </c>
       <c r="C90" s="60" t="inlineStr">
@@ -7333,45 +7333,45 @@
       </c>
       <c r="D90" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="E90" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="F90" s="76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G90" s="60" t="inlineStr">
         <is>
-          <t>Official Company</t>
+          <t>Intergovernmental</t>
         </is>
       </c>
       <c r="H90" s="60" t="inlineStr">
         <is>
-          <t>Google AI</t>
+          <t>WHO News</t>
         </is>
       </c>
       <c r="I90" s="60" t="inlineStr">
         <is>
-          <t>Create, edit and star in videos with two Google Vids updates</t>
+          <t>WHO marks 25 years of Research4Life, advancing access to scientific knowledge in more than 120 countries</t>
         </is>
       </c>
       <c r="J90" s="60" t="inlineStr">
         <is>
-          <t>Text "Gemini Omni and Personal Avatars in Google Vids" surrounded by various images</t>
+          <t>The World Health Organization (WHO) today marks the 25th anniversary of Research4Life, a public-private partnership that provides researchers, educators, health professionals and policy-makers in low- and middle-income countries with affordable or free access to scientific knowledge. The partnership has helped dramatically expand access to scientific knowledge for researchers, educators, health professionals and policy-makers in more than 120 countries.</t>
         </is>
       </c>
       <c r="K90" s="60" t="inlineStr">
         <is>
-          <t>https://blog.google/products-and-platforms/products/workspace/gemini-omni-personal-avatars/</t>
+          <t>https://www.who.int/news/item/21-07-2026-who-marks-25-years-of-research4life--advancing-access-to-scientific-knowledge-in-more-than-120-countries</t>
         </is>
       </c>
       <c r="L90" s="60" t="inlineStr">
         <is>
-          <t>0560403cacf5a7a127ad3346</t>
+          <t>09e6494006eb3af009c1a30f</t>
         </is>
       </c>
       <c r="M90" s="75" t="inlineStr">
@@ -7394,55 +7394,55 @@
       </c>
       <c r="B91" s="75" t="inlineStr">
         <is>
-          <t>2026-07-15T21:00:00Z</t>
+          <t>2026-07-20T07:09:01Z</t>
         </is>
       </c>
       <c r="C91" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D91" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="E91" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence | Innovation Policy</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="F91" s="76" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G91" s="60" t="inlineStr">
         <is>
-          <t>Policy Institute</t>
+          <t>Intergovernmental</t>
         </is>
       </c>
       <c r="H91" s="60" t="inlineStr">
         <is>
-          <t>CSET</t>
+          <t>WHO News</t>
         </is>
       </c>
       <c r="I91" s="60" t="inlineStr">
         <is>
-          <t>Meet GPT-Red: an LLM super-hacker OpenAI built to make its models safer</t>
+          <t>Road deaths fall by 21% globally but stronger action is needed to save lives</t>
         </is>
       </c>
       <c r="J91" s="60" t="inlineStr">
         <is>
-          <t>CSET’s Jessica Ji shared her expert insight in an article published by MIT Technology Review. The article examines how OpenAI developed GPT-Red, an AI "super-hacker" designed to automatically identify vulnerabilities in large language models and strengthen their defenses against cyberattacks through AI-powered red-teaming. The post Meet GPT-Red: an LLM super-hacker OpenAI built to make its models safer appeared first on Center for Security and Emerging Technology .</t>
+          <t>Despite the addition of more than one billion motor-vehicles to the world’s roads, the global rate of road traffic deaths declined by 21% between 2011 and 2025, according to new data released by the World Health Organization (WHO). The world has experienced profound changes in road traffic during this time with the emergence of new modes of transport and a sharp rise in motorcycle use. Despite this progress, however, road traffic crashes still claimed 1.16 million people's lives in 2025. Road traffic injuries remain the leading cause of death among children and youth aged 5–29 years. The new WHO data comes as global leaders today adopt a new United Nations (UN) General Assembly progress dec…</t>
         </is>
       </c>
       <c r="K91" s="60" t="inlineStr">
         <is>
-          <t>https://cset.georgetown.edu/article/meet-gpt-red-an-llm-super-hacker-openai-built-to-make-its-models-safer/</t>
+          <t>https://www.who.int/news/item/20-07-2026-road-deaths-fall-by-21--globally-but-stronger-action-is-needed-to-save-lives</t>
         </is>
       </c>
       <c r="L91" s="60" t="inlineStr">
         <is>
-          <t>f64391d3daf689e78e7ac442</t>
+          <t>05edb573a8ead16ae99b6291</t>
         </is>
       </c>
       <c r="M91" s="75" t="inlineStr">
@@ -7465,12 +7465,12 @@
       </c>
       <c r="B92" s="75" t="inlineStr">
         <is>
-          <t>2026-07-15T17:47:57Z</t>
+          <t>2026-07-18T07:27:54Z</t>
         </is>
       </c>
       <c r="C92" s="60" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D92" s="60" t="inlineStr">
@@ -7480,40 +7480,40 @@
       </c>
       <c r="E92" s="60" t="inlineStr">
         <is>
-          <t>Fusion Energy</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="F92" s="76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G92" s="60" t="inlineStr">
         <is>
-          <t>Industry Association</t>
+          <t>Intergovernmental</t>
         </is>
       </c>
       <c r="H92" s="60" t="inlineStr">
         <is>
-          <t>Fusion Industry Association</t>
+          <t>WHO News</t>
         </is>
       </c>
       <c r="I92" s="60" t="inlineStr">
         <is>
-          <t>Starlight Engine Raises JPY 6.06 Billion</t>
+          <t>WHO Member States continue negotiations on the Pathogen Access and Benefit Sharing Annex</t>
         </is>
       </c>
       <c r="J92" s="60" t="inlineStr">
         <is>
-          <t>Starlight Engine has raised JPY 6.06 billion in its first external funding round to accelerate development of FAST. The company is developing a tokamak-based fusion machine that builds on decades of research, including Japan's JT-60SA program and international efforts. The post Starlight Engine Raises JPY 6.06 Billion appeared first on Fusion Industry Association .</t>
+          <t>WHO Member States have advanced negotiations on the Pathogen Access and Benefit Sharing (PABS) annex, a central component of the WHO Pandemic Agreement, while agreeing that continued discussions are needed to finalize a framework that supports a faster, more effective and equitable response to future pandemics.</t>
         </is>
       </c>
       <c r="K92" s="60" t="inlineStr">
         <is>
-          <t>https://www.nikkei.com/article/DGXZQOUC152ET0V10C26A7000000/#new_tab?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=starlight-engine-raises-jpy-6-06-billion</t>
+          <t>https://www.who.int/news/item/20-07-2026-who-member-states-continue-negotiations-on-the-pathogen-access-and-benefit-sharing-annex</t>
         </is>
       </c>
       <c r="L92" s="60" t="inlineStr">
         <is>
-          <t>2f29b005896c3737ab846738</t>
+          <t>14dd15caca066d18dfcf2e34</t>
         </is>
       </c>
       <c r="M92" s="75" t="inlineStr">
@@ -7536,26 +7536,26 @@
       </c>
       <c r="B93" s="75" t="inlineStr">
         <is>
-          <t>2026-07-15T17:43:32Z</t>
+          <t>2026-07-17T20:26:18Z</t>
         </is>
       </c>
       <c r="C93" s="60" t="inlineStr">
         <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D93" s="60" t="inlineStr">
+        <is>
           <t>Global</t>
         </is>
       </c>
-      <c r="D93" s="60" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
       <c r="E93" s="60" t="inlineStr">
         <is>
           <t>Fusion Energy</t>
         </is>
       </c>
       <c r="F93" s="76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G93" s="60" t="inlineStr">
         <is>
@@ -7569,22 +7569,22 @@
       </c>
       <c r="I93" s="60" t="inlineStr">
         <is>
-          <t>Fusion research center coming to Madison’s former Oscar Mayer plant</t>
+          <t>In the News: FIA Launches the 2026 Global Fusion Industry Report in New York City, Washington, D.C., and London</t>
         </is>
       </c>
       <c r="J93" s="60" t="inlineStr">
         <is>
-          <t>Realta Fusion selected Madison, Wisconsin's former Oscar Mayer site as the location for its new headquarters and facility. They plan to build the prototype magnetic mirror fusion machine here, with the project expected to create 600+ jobs and establish a major hub for fusion innovation. The post Fusion research center coming to Madison’s former Oscar Mayer plant appeared first on Fusion Industry Association .</t>
+          <t>On July 13, the Fusion Industry Association launched the 2026 Global Fusion Industry Report at an event in New York City - making headlines worldwide and bringing together industry leaders, investors, and media. A Washington, D.C. launch and Congressional briefing followed on July 15, to discuss the report’s findings in the context of US policy with policymakers, think tanks, national labs, and industry leaders. A London dinner event held on July 29 will discuss the report's findings with government leaders, aligned with the recently released UK 2026 Fusion Strategy. The post In the News: FIA Launches the 2026 Global Fusion Industry Report in New York City, Washington, D.C., and London appe…</t>
         </is>
       </c>
       <c r="K93" s="60" t="inlineStr">
         <is>
-          <t>https://www.jsonline.com/story/money/business/energy/2026/07/15/nuclear-fusion-facility-coming-to-madisons-oscar-mayer-factory-site/90900554007/?gnt-cfr=1&amp;gca-cat=p&amp;gca-uir=true&amp;gca-epti=z116463p117850l004150c117850e1157xxv116463d--54--b--54--&amp;gca-ft=178&amp;gca-ds=sophi#new_tab&amp;utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=fusion-research-center-coming-to-madisons-former-oscar-mayer-plant</t>
+          <t>https://www.fusionindustryassociation.org/fia-launches-the-2026-global-fusion-industry-report-in-new-york-city-washington-d-c-and-london/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=fia-launches-the-2026-global-fusion-industry-report-in-new-york-city-washington-d-c-and-london</t>
         </is>
       </c>
       <c r="L93" s="60" t="inlineStr">
         <is>
-          <t>aed2fa8a807fb17c3e6861e7</t>
+          <t>186c1d4e76c09a864706432c</t>
         </is>
       </c>
       <c r="M93" s="75" t="inlineStr">
@@ -7607,22 +7607,22 @@
       </c>
       <c r="B94" s="75" t="inlineStr">
         <is>
-          <t>2026-07-15T12:15:58Z</t>
+          <t>2026-07-17T18:42:47Z</t>
         </is>
       </c>
       <c r="C94" s="60" t="inlineStr">
         <is>
+          <t>EU &amp; Europe</t>
+        </is>
+      </c>
+      <c r="D94" s="60" t="inlineStr">
+        <is>
           <t>Global</t>
         </is>
       </c>
-      <c r="D94" s="60" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
       <c r="E94" s="60" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Innovation Policy | Fusion Energy</t>
         </is>
       </c>
       <c r="F94" s="76" t="n">
@@ -7630,32 +7630,32 @@
       </c>
       <c r="G94" s="60" t="inlineStr">
         <is>
-          <t>Intergovernmental</t>
+          <t>Industry Association</t>
         </is>
       </c>
       <c r="H94" s="60" t="inlineStr">
         <is>
-          <t>WHO News</t>
+          <t>Fusion Industry Association</t>
         </is>
       </c>
       <c r="I94" s="60" t="inlineStr">
         <is>
-          <t>New WHO guidelines: up to 45% of dementia risk could be prevented or delayed</t>
+          <t>International Legal Expert Group Publish Paper on the Need for the EU to Secure Its Competitive Fusion Advantage</t>
         </is>
       </c>
       <c r="J94" s="60" t="inlineStr">
         <is>
-          <t>The World Health Organization (WHO) today released updated guidelines on reducing the risk of cognitive decline and dementia , providing countries with evidence-based recommendations to help prevent or delay the onset of dementia across the life course. Dementia is a condition caused by brain diseases and affects memory, thinking and the ability to function. More than 57 million people live with dementia worldwide and nearly 10 million people get newly diagnosed every year. Alzheimer disease is the most common form of dementia and is estimated to account for 60–70% of cases. While there is no cure for dementia, up to 45% of the risks can be attributed to modifiable risk factors such as toba…</t>
+          <t>A discussion paper from the International Group of Legal Experts on Fusion Energy (FELEX) argues that Europe holds a competitive advantage in commercial fusion that no other region can replicate, but must act now to preserve it. The paper highlights the Euratom Treaty as the world’s only harmonized legal framework for nuclear governance across 27... The post International Legal Expert Group Publish Paper on the Need for the EU to Secure Its Competitive Fusion Advantage appeared first on Fusion Industry Association .</t>
         </is>
       </c>
       <c r="K94" s="60" t="inlineStr">
         <is>
-          <t>https://www.who.int/news/item/15-07-2026-new-who-guidelines--up-to-45--of-dementia-risk-could-be-prevented-or-delayed</t>
+          <t>https://www.fusionindustryassociation.org/international-legal-expert-group-publish-paper-on-the-need-for-the-eu-to-secure-its-competitive-fusion-advantage/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=international-legal-expert-group-publish-paper-on-the-need-for-the-eu-to-secure-its-competitive-fusion-advantage</t>
         </is>
       </c>
       <c r="L94" s="60" t="inlineStr">
         <is>
-          <t>30a0d7838c2c12642479a64f</t>
+          <t>7ef6110ab078602757409abf</t>
         </is>
       </c>
       <c r="M94" s="75" t="inlineStr">
@@ -7678,7 +7678,7 @@
       </c>
       <c r="B95" s="75" t="inlineStr">
         <is>
-          <t>2026-07-15T00:01:54Z</t>
+          <t>2026-07-17T18:00:01Z</t>
         </is>
       </c>
       <c r="C95" s="60" t="inlineStr">
@@ -7688,45 +7688,45 @@
       </c>
       <c r="D95" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E95" s="60" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Robotics</t>
         </is>
       </c>
       <c r="F95" s="76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G95" s="60" t="inlineStr">
         <is>
-          <t>Intergovernmental</t>
+          <t>Major Media</t>
         </is>
       </c>
       <c r="H95" s="60" t="inlineStr">
         <is>
-          <t>WHO News</t>
+          <t>IEEE Spectrum</t>
         </is>
       </c>
       <c r="I95" s="60" t="inlineStr">
         <is>
-          <t>Global childhood immunization coverage inches forward despite conflict and hesitancy – UNICEF, WHO</t>
+          <t>This Graduate Student Equips NASA’s Robots With Assembly Skills</t>
         </is>
       </c>
       <c r="J95" s="60" t="inlineStr">
         <is>
-          <t>In 2025, 90% of infants globally – or nearly 116 million – received at least one dose of a diphtheria, tetanus and pertussis (DTP) vaccine, and 85% – or 110 million – completed the full three-dose series, according to the annual WHO-UNICEF Estimates of National Immunization Coverage (WUENIC) released today. While both indicators rose by one percentage point from the previous year, global coverage remains one point below 2019 levels – hovering within the same narrow range since 2009. According to the data, an estimated 13.5 million “zero-dose” children did not receive a single vaccine in their first year during 2025. While these represent nearly 750 000 fewer children than the previous year,…</t>
+          <t>Like many engineers, Sarah Downs says she knew she wanted to pursue a STEM career from a young age. As a teenager, she discovered robotics through her Tulsa, Okla., middle school’s First Lego League team, and she fell in love with the field, she says. Downs participated in the international robotics program from 2014 to 2016. Watching PBS specials on NASA Mars rovers Spirit and Opportunity , and seeing the live broadcast of the Curiosity rover launch in 2011, inspired the teen to dream of a career working with NASA. Sarah Downs MEMBER GRADE Graduate student member UNIVERSITY Texas A&amp;M University in College Station MAJOR Electric engineering This year the IEEE graduate student member achieve…</t>
         </is>
       </c>
       <c r="K95" s="60" t="inlineStr">
         <is>
-          <t>https://www.who.int/news/item/15-07-2026-global-childhood-immunization-coverage-inches-forward-despite-conflict-and-hesitancy---unicef--who</t>
+          <t>https://spectrum.ieee.org/graduate-student-nasas-robots-assembly</t>
         </is>
       </c>
       <c r="L95" s="60" t="inlineStr">
         <is>
-          <t>03ea8728394fda1e18a57d66</t>
+          <t>c21b23b6ab59c7960b95be1f</t>
         </is>
       </c>
       <c r="M95" s="75" t="inlineStr">
@@ -7749,7 +7749,7 @@
       </c>
       <c r="B96" s="75" t="inlineStr">
         <is>
-          <t>2026-07-14T17:40:43Z</t>
+          <t>2026-07-17T13:00:05Z</t>
         </is>
       </c>
       <c r="C96" s="60" t="inlineStr">
@@ -7759,12 +7759,12 @@
       </c>
       <c r="D96" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E96" s="60" t="inlineStr">
         <is>
-          <t>Fusion Energy</t>
+          <t>Semiconductors &amp; Telecom | Healthcare</t>
         </is>
       </c>
       <c r="F96" s="76" t="n">
@@ -7772,32 +7772,32 @@
       </c>
       <c r="G96" s="60" t="inlineStr">
         <is>
-          <t>Industry Association</t>
+          <t>Official Company</t>
         </is>
       </c>
       <c r="H96" s="60" t="inlineStr">
         <is>
-          <t>Fusion Industry Association</t>
+          <t>Intel Newsroom</t>
         </is>
       </c>
       <c r="I96" s="60" t="inlineStr">
         <is>
-          <t>Global Investment in Fusion Companies Surges 69% to $4.5 Billion</t>
+          <t>Intel-Powered Medical Exoskeleton Helps Patients Get Back on Their Feet</t>
         </is>
       </c>
       <c r="J96" s="60" t="inlineStr">
         <is>
-          <t>The Fusion Industry Association released its 2026 Global Fusion Industry Report, showing that fusion companies have raised a $14.24 billion. The report highlights record investment, growing commercial partnerships, and increasing confidence that fusion machines will deliver electricity in the 2030s. The post Global Investment in Fusion Companies Surges 69% to $4.5 Billion appeared first on Fusion Industry Association .</t>
+          <t>People with lower-limb injuries who cannot stand or walk often need intensive clinical rehabilitation and expert-guided physiotherapy.This medical care retrains the limbs and supports the brain’s ability to relearn movement, with the goal of restoring greater mobility and ultimately, helping the patient to walk again.But traditional rehabilitation methods today have its limits – it’s fatigue-inducing, imprecise and requires expert, … The post Intel-Powered Medical Exoskeleton Helps Patients Get Back on Their Feet appeared first on Newsroom .</t>
         </is>
       </c>
       <c r="K96" s="60" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/news/articles/2026-07-13/global-investment-in-fusion-companies-surges-69-to-4-5-billion#new_tab?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=global-investment-in-fusion-companies-surges-69-to-4-5-billion</t>
+          <t>https://newsroom.intel.com/client-computing/intel-powered-medical-exoskeleton-helps-patients-get-back-on-their-feet</t>
         </is>
       </c>
       <c r="L96" s="60" t="inlineStr">
         <is>
-          <t>37f8fa9d53d7f670777b07a5</t>
+          <t>3dd1b06b356e118627f94f8b</t>
         </is>
       </c>
       <c r="M96" s="75" t="inlineStr">
@@ -7820,7 +7820,7 @@
       </c>
       <c r="B97" s="75" t="inlineStr">
         <is>
-          <t>2026-07-14T17:39:28Z</t>
+          <t>2026-07-16T16:00:53Z</t>
         </is>
       </c>
       <c r="C97" s="60" t="inlineStr">
@@ -7830,12 +7830,12 @@
       </c>
       <c r="D97" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E97" s="60" t="inlineStr">
         <is>
-          <t>Fusion Energy</t>
+          <t>Artificial Intelligence | Semiconductors &amp; Telecom</t>
         </is>
       </c>
       <c r="F97" s="76" t="n">
@@ -7843,32 +7843,32 @@
       </c>
       <c r="G97" s="60" t="inlineStr">
         <is>
-          <t>Industry Association</t>
+          <t>Official Company</t>
         </is>
       </c>
       <c r="H97" s="60" t="inlineStr">
         <is>
-          <t>Fusion Industry Association</t>
+          <t>Intel Newsroom</t>
         </is>
       </c>
       <c r="I97" s="60" t="inlineStr">
         <is>
-          <t>General Fusion Shares Soar 25%</t>
+          <t>Intel and Google Cloud Announce Collaboration to Accelerate Intel’s AI-Enabled Enterprise Transformation</t>
         </is>
       </c>
       <c r="J97" s="60" t="inlineStr">
         <is>
-          <t>Canada-based General Fusion has become the first publicly listed fusion company after completing a merger with a special purpose acquisition company (SPAC). The listing provides the company with broader access to capital as it advances its technology toward deployment. The post General Fusion Shares Soar 25% appeared first on Fusion Industry Association .</t>
+          <t>SANTA CLARA, Calif., and SUNNYVALE, Calif. – July 16, 2026 – Intel and Google Cloud today announced an expansion of their previously announced multi-year strategic collaboration, which would accelerate Intel’s enterprise-wide digital evolution through the deployment of Gemini Enterprise and Google Cloud.Intel will integrate advanced, Gemini-powered generative AI across its global workforce, helping to scale capabilities and … The post Intel and Google Cloud Announce Collaboration to Accelerate Intel’s AI-Enabled Enterprise Transformation appeared first on Newsroom .</t>
         </is>
       </c>
       <c r="K97" s="60" t="inlineStr">
         <is>
-          <t>https://www.wsj.com/livecoverage/stock-market-today-bank-earnings-07-14-2026/card/general-fusion-shares-soar-25--lfmTDvoKe8UYxvdcs8Hq#new_tab?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=general-fusion-shares-soar-25</t>
+          <t>https://newsroom.intel.com/artificial-intelligence/intel-google-cloud-announce-collaboration-to-accelerate-intel-ai-enabled-enterprise-transformation</t>
         </is>
       </c>
       <c r="L97" s="60" t="inlineStr">
         <is>
-          <t>4f333224cb84eee2f3fbf904</t>
+          <t>0361033c6203d3cbfc2c57cf</t>
         </is>
       </c>
       <c r="M97" s="75" t="inlineStr">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="B98" s="75" t="inlineStr">
         <is>
-          <t>2026-07-14T16:00:00Z</t>
+          <t>2026-07-16T16:00:00Z</t>
         </is>
       </c>
       <c r="C98" s="60" t="inlineStr">
@@ -7924,22 +7924,22 @@
       </c>
       <c r="I98" s="60" t="inlineStr">
         <is>
-          <t>Celebrating 25 years of visual search innovation</t>
+          <t>Connect more of your apps to Search</t>
         </is>
       </c>
       <c r="J98" s="60" t="inlineStr">
         <is>
-          <t>Google Images logo surrounded by illustrations of people searching for different images</t>
+          <t>Connected apps rendering</t>
         </is>
       </c>
       <c r="K98" s="60" t="inlineStr">
         <is>
-          <t>https://blog.google/products-and-platforms/products/search/google-images-25th-anniversary/</t>
+          <t>https://blog.google/products-and-platforms/products/search/connected-apps/</t>
         </is>
       </c>
       <c r="L98" s="60" t="inlineStr">
         <is>
-          <t>bbfc4b37a73bf4793d60e253</t>
+          <t>23c6974aa4b45f04208cef57</t>
         </is>
       </c>
       <c r="M98" s="75" t="inlineStr">
@@ -7962,55 +7962,55 @@
       </c>
       <c r="B99" s="75" t="inlineStr">
         <is>
-          <t>2026-07-14T12:00:00Z</t>
+          <t>2026-07-16T16:00:00Z</t>
         </is>
       </c>
       <c r="C99" s="60" t="inlineStr">
         <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="D99" s="60" t="inlineStr">
+        <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="D99" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
       <c r="E99" s="60" t="inlineStr">
         <is>
-          <t>Innovation Policy</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="F99" s="76" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G99" s="60" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Official Company</t>
         </is>
       </c>
       <c r="H99" s="60" t="inlineStr">
         <is>
-          <t>NIST News</t>
+          <t>Google AI</t>
         </is>
       </c>
       <c r="I99" s="60" t="inlineStr">
         <is>
-          <t>NIST Receives New Patent for Microbe-Killing Water Heater</t>
+          <t>Create, edit and star in videos with two Google Vids updates</t>
         </is>
       </c>
       <c r="J99" s="60" t="inlineStr">
         <is>
-          <t>Warm water in household pipes can be a breeding ground for harmful bacteria.</t>
+          <t>Text "Gemini Omni and Personal Avatars in Google Vids" surrounded by various images</t>
         </is>
       </c>
       <c r="K99" s="60" t="inlineStr">
         <is>
-          <t>https://www.nist.gov/news-events/news/2026/07/nist-receives-new-patent-microbe-killing-water-heater</t>
+          <t>https://blog.google/products-and-platforms/products/workspace/gemini-omni-personal-avatars/</t>
         </is>
       </c>
       <c r="L99" s="60" t="inlineStr">
         <is>
-          <t>72b002f5a04f35d9ca1e9949</t>
+          <t>0560403cacf5a7a127ad3346</t>
         </is>
       </c>
       <c r="M99" s="75" t="inlineStr">
@@ -8033,7 +8033,7 @@
       </c>
       <c r="B100" s="75" t="inlineStr">
         <is>
-          <t>2026-07-13T21:00:00Z</t>
+          <t>2026-07-15T21:00:00Z</t>
         </is>
       </c>
       <c r="C100" s="60" t="inlineStr">
@@ -8048,7 +8048,7 @@
       </c>
       <c r="E100" s="60" t="inlineStr">
         <is>
-          <t>Innovation Policy | Artificial Intelligence</t>
+          <t>Artificial Intelligence | Innovation Policy</t>
         </is>
       </c>
       <c r="F100" s="76" t="n">
@@ -8066,22 +8066,22 @@
       </c>
       <c r="I100" s="60" t="inlineStr">
         <is>
-          <t>Washington Is Looking to Keep China From Training Its AI on US Models</t>
+          <t>Meet GPT-Red: an LLM super-hacker OpenAI built to make its models safer</t>
         </is>
       </c>
       <c r="J100" s="60" t="inlineStr">
         <is>
-          <t>CSET’s Colin Shea-Blymyer shared his expert insight in an article published by Bloomberg. The article examines growing concerns in Washington over the use of "distillation" by Chinese AI companies to train models using outputs from leading US systems, and the resulting debate over intellectual property, competition, and national security in the global AI race. The post Washington Is Looking to Keep China From Training Its AI on US Models appeared first on Center for Security and Emerging Technology .</t>
+          <t>CSET’s Jessica Ji shared her expert insight in an article published by MIT Technology Review. The article examines how OpenAI developed GPT-Red, an AI "super-hacker" designed to automatically identify vulnerabilities in large language models and strengthen their defenses against cyberattacks through AI-powered red-teaming. The post Meet GPT-Red: an LLM super-hacker OpenAI built to make its models safer appeared first on Center for Security and Emerging Technology .</t>
         </is>
       </c>
       <c r="K100" s="60" t="inlineStr">
         <is>
-          <t>https://cset.georgetown.edu/article/washington-is-looking-to-keep-china-from-training-its-ai-on-us-models/</t>
+          <t>https://cset.georgetown.edu/article/meet-gpt-red-an-llm-super-hacker-openai-built-to-make-its-models-safer/</t>
         </is>
       </c>
       <c r="L100" s="60" t="inlineStr">
         <is>
-          <t>e96177000536ef3f58f8fb3c</t>
+          <t>f64391d3daf689e78e7ac442</t>
         </is>
       </c>
       <c r="M100" s="75" t="inlineStr">
@@ -8104,55 +8104,55 @@
       </c>
       <c r="B101" s="75" t="inlineStr">
         <is>
-          <t>2026-07-13T16:00:00Z</t>
+          <t>2026-07-15T17:47:57Z</t>
         </is>
       </c>
       <c r="C101" s="60" t="inlineStr">
         <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D101" s="60" t="inlineStr">
+        <is>
           <t>Global</t>
         </is>
       </c>
-      <c r="D101" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
       <c r="E101" s="60" t="inlineStr">
         <is>
-          <t>Innovation Policy | Quantum</t>
+          <t>Fusion Energy</t>
         </is>
       </c>
       <c r="F101" s="76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G101" s="60" t="inlineStr">
         <is>
-          <t>Official Company</t>
+          <t>Industry Association</t>
         </is>
       </c>
       <c r="H101" s="60" t="inlineStr">
         <is>
-          <t>Microsoft Research</t>
+          <t>Fusion Industry Association</t>
         </is>
       </c>
       <c r="I101" s="60" t="inlineStr">
         <is>
-          <t>Verifying Rust cryptography in SymCrypt, from standards to code</t>
+          <t>Starlight Engine Raises JPY 6.06 Billion</t>
         </is>
       </c>
       <c r="J101" s="60" t="inlineStr">
         <is>
-          <t>Cryptographic code supports vital protections in modern computing systems. Learn how a new method helps verify code as developers write it while preserving speed and adaptability as it gets implemented and evolves. The post Verifying Rust cryptography in SymCrypt, from standards to code appeared first on Microsoft Research .</t>
+          <t>Starlight Engine has raised JPY 6.06 billion in its first external funding round to accelerate development of FAST. The company is developing a tokamak-based fusion machine that builds on decades of research, including Japan's JT-60SA program and international efforts. The post Starlight Engine Raises JPY 6.06 Billion appeared first on Fusion Industry Association .</t>
         </is>
       </c>
       <c r="K101" s="60" t="inlineStr">
         <is>
-          <t>https://www.microsoft.com/en-us/research/blog/verifying-rust-cryptography-in-symcrypt-from-standards-to-code/</t>
+          <t>https://www.nikkei.com/article/DGXZQOUC152ET0V10C26A7000000/#new_tab?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=starlight-engine-raises-jpy-6-06-billion</t>
         </is>
       </c>
       <c r="L101" s="60" t="inlineStr">
         <is>
-          <t>a7866758cf94a3c5e9d26534</t>
+          <t>2f29b005896c3737ab846738</t>
         </is>
       </c>
       <c r="M101" s="75" t="inlineStr">
@@ -8175,7 +8175,7 @@
       </c>
       <c r="B102" s="75" t="inlineStr">
         <is>
-          <t>2026-07-13T12:00:41Z</t>
+          <t>2026-07-15T17:43:32Z</t>
         </is>
       </c>
       <c r="C102" s="60" t="inlineStr">
@@ -8185,12 +8185,12 @@
       </c>
       <c r="D102" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="E102" s="60" t="inlineStr">
         <is>
-          <t>Semiconductors &amp; Telecom | Artificial Intelligence</t>
+          <t>Fusion Energy</t>
         </is>
       </c>
       <c r="F102" s="76" t="n">
@@ -8198,32 +8198,32 @@
       </c>
       <c r="G102" s="60" t="inlineStr">
         <is>
-          <t>Official Company</t>
+          <t>Industry Association</t>
         </is>
       </c>
       <c r="H102" s="60" t="inlineStr">
         <is>
-          <t>Intel Newsroom</t>
+          <t>Fusion Industry Association</t>
         </is>
       </c>
       <c r="I102" s="60" t="inlineStr">
         <is>
-          <t>Intel Invests €5 Billion to Expand Manufacturing in Europe</t>
+          <t>Fusion research center coming to Madison’s former Oscar Mayer plant</t>
         </is>
       </c>
       <c r="J102" s="60" t="inlineStr">
         <is>
-          <t>LEIXLIP, Ireland, July 13, 2026 —Intel today announced a €5 billion ($5.7 billion) capital investment at its Leixlip campus in Ireland, marking the next phase in the site’s capacity expansion. Global demand for AI and high-performance computing is driving the need for advanced silicon to power AI Factories, and Intel is scaling capacity in Ireland … The post Intel Invests €5 Billion to Expand Manufacturing in Europe appeared first on Newsroom .</t>
+          <t>Realta Fusion selected Madison, Wisconsin's former Oscar Mayer site as the location for its new headquarters and facility. They plan to build the prototype magnetic mirror fusion machine here, with the project expected to create 600+ jobs and establish a major hub for fusion innovation. The post Fusion research center coming to Madison’s former Oscar Mayer plant appeared first on Fusion Industry Association .</t>
         </is>
       </c>
       <c r="K102" s="60" t="inlineStr">
         <is>
-          <t>https://newsroom.intel.com/intel-foundry/intel-invests-5-billion-euro-to-expand-manufacturing-in-europe</t>
+          <t>https://www.jsonline.com/story/money/business/energy/2026/07/15/nuclear-fusion-facility-coming-to-madisons-oscar-mayer-factory-site/90900554007/?gnt-cfr=1&amp;gca-cat=p&amp;gca-uir=true&amp;gca-epti=z116463p117850l004150c117850e1157xxv116463d--54--b--54--&amp;gca-ft=178&amp;gca-ds=sophi#new_tab&amp;utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=fusion-research-center-coming-to-madisons-former-oscar-mayer-plant</t>
         </is>
       </c>
       <c r="L102" s="60" t="inlineStr">
         <is>
-          <t>297a8b5b279e5916cf45fddb</t>
+          <t>aed2fa8a807fb17c3e6861e7</t>
         </is>
       </c>
       <c r="M102" s="75" t="inlineStr">
@@ -8246,55 +8246,55 @@
       </c>
       <c r="B103" s="75" t="inlineStr">
         <is>
-          <t>2026-07-13T10:19:51Z</t>
+          <t>2026-07-15T12:15:58Z</t>
         </is>
       </c>
       <c r="C103" s="60" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D103" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="E103" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence | Robotics</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="F103" s="76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G103" s="60" t="inlineStr">
         <is>
-          <t>Major Media</t>
+          <t>Intergovernmental</t>
         </is>
       </c>
       <c r="H103" s="60" t="inlineStr">
         <is>
-          <t>IEEE Spectrum</t>
+          <t>WHO News</t>
         </is>
       </c>
       <c r="I103" s="60" t="inlineStr">
         <is>
-          <t>Building a Foundation Stack for General-Purpose Robots</t>
+          <t>New WHO guidelines: up to 45% of dementia risk could be prevented or delayed</t>
         </is>
       </c>
       <c r="J103" s="60" t="inlineStr">
         <is>
-          <t>This article is brought to you by X Square Robot . Large language models gave artificial intelligence a working recipe. Pretrain a large model on broad data, and general capability follows. Robotics has no such recipe. Robotics systems have long been assembled from separate perception, planning, and control parts that rarely add up to intelligence a robot can carry from one task to another, or one machine to another. The central problem in embodied AI is to find the equivalent recipe, and the field does not yet agree on what it is. X Square Robot , a Chinese embodied-AI company, has made an unusually explicit bet. It argues that the recipe is an integrated stack, spanning the data a robot l…</t>
+          <t>The World Health Organization (WHO) today released updated guidelines on reducing the risk of cognitive decline and dementia , providing countries with evidence-based recommendations to help prevent or delay the onset of dementia across the life course. Dementia is a condition caused by brain diseases and affects memory, thinking and the ability to function. More than 57 million people live with dementia worldwide and nearly 10 million people get newly diagnosed every year. Alzheimer disease is the most common form of dementia and is estimated to account for 60–70% of cases. While there is no cure for dementia, up to 45% of the risks can be attributed to modifiable risk factors such as toba…</t>
         </is>
       </c>
       <c r="K103" s="60" t="inlineStr">
         <is>
-          <t>https://spectrum.ieee.org/x-square-robot-embodied-ai-stack</t>
+          <t>https://www.who.int/news/item/15-07-2026-new-who-guidelines--up-to-45--of-dementia-risk-could-be-prevented-or-delayed</t>
         </is>
       </c>
       <c r="L103" s="60" t="inlineStr">
         <is>
-          <t>d56ace988ec4655cef540679</t>
+          <t>30a0d7838c2c12642479a64f</t>
         </is>
       </c>
       <c r="M103" s="75" t="inlineStr">
@@ -8317,7 +8317,7 @@
       </c>
       <c r="B104" s="75" t="inlineStr">
         <is>
-          <t>2026-07-13T09:57:57Z</t>
+          <t>2026-07-15T00:01:54Z</t>
         </is>
       </c>
       <c r="C104" s="60" t="inlineStr">
@@ -8350,22 +8350,22 @@
       </c>
       <c r="I104" s="60" t="inlineStr">
         <is>
-          <t>El Salvador validated by WHO as having eliminated trachoma as a public health problem</t>
+          <t>Global childhood immunization coverage inches forward despite conflict and hesitancy – UNICEF, WHO</t>
         </is>
       </c>
       <c r="J104" s="60" t="inlineStr">
         <is>
-          <t>The World Health Organization (WHO) has validated El Salvador as having eliminated trachoma as a public health problem. Trachoma is the world's leading infectious cause of blindness.</t>
+          <t>In 2025, 90% of infants globally – or nearly 116 million – received at least one dose of a diphtheria, tetanus and pertussis (DTP) vaccine, and 85% – or 110 million – completed the full three-dose series, according to the annual WHO-UNICEF Estimates of National Immunization Coverage (WUENIC) released today. While both indicators rose by one percentage point from the previous year, global coverage remains one point below 2019 levels – hovering within the same narrow range since 2009. According to the data, an estimated 13.5 million “zero-dose” children did not receive a single vaccine in their first year during 2025. While these represent nearly 750 000 fewer children than the previous year,…</t>
         </is>
       </c>
       <c r="K104" s="60" t="inlineStr">
         <is>
-          <t>https://www.who.int/news/item/13-07-2026-el-salvador-validated-by-who-as-having-eliminated-trachoma-as-a-public-health-problem</t>
+          <t>https://www.who.int/news/item/15-07-2026-global-childhood-immunization-coverage-inches-forward-despite-conflict-and-hesitancy---unicef--who</t>
         </is>
       </c>
       <c r="L104" s="60" t="inlineStr">
         <is>
-          <t>213c7954ea56dfd0fccb556a</t>
+          <t>03ea8728394fda1e18a57d66</t>
         </is>
       </c>
       <c r="M104" s="75" t="inlineStr">
@@ -8388,71 +8388,710 @@
       </c>
       <c r="B105" s="75" t="inlineStr">
         <is>
+          <t>2026-07-14T17:40:43Z</t>
+        </is>
+      </c>
+      <c r="C105" s="60" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="D105" s="60" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E105" s="60" t="inlineStr">
+        <is>
+          <t>Fusion Energy</t>
+        </is>
+      </c>
+      <c r="F105" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="G105" s="60" t="inlineStr">
+        <is>
+          <t>Industry Association</t>
+        </is>
+      </c>
+      <c r="H105" s="60" t="inlineStr">
+        <is>
+          <t>Fusion Industry Association</t>
+        </is>
+      </c>
+      <c r="I105" s="60" t="inlineStr">
+        <is>
+          <t>Global Investment in Fusion Companies Surges 69% to $4.5 Billion</t>
+        </is>
+      </c>
+      <c r="J105" s="60" t="inlineStr">
+        <is>
+          <t>The Fusion Industry Association released its 2026 Global Fusion Industry Report, showing that fusion companies have raised a $14.24 billion. The report highlights record investment, growing commercial partnerships, and increasing confidence that fusion machines will deliver electricity in the 2030s. The post Global Investment in Fusion Companies Surges 69% to $4.5 Billion appeared first on Fusion Industry Association .</t>
+        </is>
+      </c>
+      <c r="K105" s="60" t="inlineStr">
+        <is>
+          <t>https://www.bloomberg.com/news/articles/2026-07-13/global-investment-in-fusion-companies-surges-69-to-4-5-billion#new_tab?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=global-investment-in-fusion-companies-surges-69-to-4-5-billion</t>
+        </is>
+      </c>
+      <c r="L105" s="60" t="inlineStr">
+        <is>
+          <t>37f8fa9d53d7f670777b07a5</t>
+        </is>
+      </c>
+      <c r="M105" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T18:56:03+09:00</t>
+        </is>
+      </c>
+      <c r="N105" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O105" s="60" t="inlineStr"/>
+    </row>
+    <row r="106" ht="42" customHeight="1">
+      <c r="A106" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T18:56:03+09:00</t>
+        </is>
+      </c>
+      <c r="B106" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-14T17:39:28Z</t>
+        </is>
+      </c>
+      <c r="C106" s="60" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="D106" s="60" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E106" s="60" t="inlineStr">
+        <is>
+          <t>Fusion Energy</t>
+        </is>
+      </c>
+      <c r="F106" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="G106" s="60" t="inlineStr">
+        <is>
+          <t>Industry Association</t>
+        </is>
+      </c>
+      <c r="H106" s="60" t="inlineStr">
+        <is>
+          <t>Fusion Industry Association</t>
+        </is>
+      </c>
+      <c r="I106" s="60" t="inlineStr">
+        <is>
+          <t>General Fusion Shares Soar 25%</t>
+        </is>
+      </c>
+      <c r="J106" s="60" t="inlineStr">
+        <is>
+          <t>Canada-based General Fusion has become the first publicly listed fusion company after completing a merger with a special purpose acquisition company (SPAC). The listing provides the company with broader access to capital as it advances its technology toward deployment. The post General Fusion Shares Soar 25% appeared first on Fusion Industry Association .</t>
+        </is>
+      </c>
+      <c r="K106" s="60" t="inlineStr">
+        <is>
+          <t>https://www.wsj.com/livecoverage/stock-market-today-bank-earnings-07-14-2026/card/general-fusion-shares-soar-25--lfmTDvoKe8UYxvdcs8Hq#new_tab?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=general-fusion-shares-soar-25</t>
+        </is>
+      </c>
+      <c r="L106" s="60" t="inlineStr">
+        <is>
+          <t>4f333224cb84eee2f3fbf904</t>
+        </is>
+      </c>
+      <c r="M106" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T18:56:03+09:00</t>
+        </is>
+      </c>
+      <c r="N106" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O106" s="60" t="inlineStr"/>
+    </row>
+    <row r="107" ht="42" customHeight="1">
+      <c r="A107" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T18:56:03+09:00</t>
+        </is>
+      </c>
+      <c r="B107" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-14T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="C107" s="60" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="D107" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E107" s="60" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="F107" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="G107" s="60" t="inlineStr">
+        <is>
+          <t>Official Company</t>
+        </is>
+      </c>
+      <c r="H107" s="60" t="inlineStr">
+        <is>
+          <t>Google AI</t>
+        </is>
+      </c>
+      <c r="I107" s="60" t="inlineStr">
+        <is>
+          <t>Celebrating 25 years of visual search innovation</t>
+        </is>
+      </c>
+      <c r="J107" s="60" t="inlineStr">
+        <is>
+          <t>Google Images logo surrounded by illustrations of people searching for different images</t>
+        </is>
+      </c>
+      <c r="K107" s="60" t="inlineStr">
+        <is>
+          <t>https://blog.google/products-and-platforms/products/search/google-images-25th-anniversary/</t>
+        </is>
+      </c>
+      <c r="L107" s="60" t="inlineStr">
+        <is>
+          <t>bbfc4b37a73bf4793d60e253</t>
+        </is>
+      </c>
+      <c r="M107" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T18:56:03+09:00</t>
+        </is>
+      </c>
+      <c r="N107" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O107" s="60" t="inlineStr"/>
+    </row>
+    <row r="108" ht="42" customHeight="1">
+      <c r="A108" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T18:56:03+09:00</t>
+        </is>
+      </c>
+      <c r="B108" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-14T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="C108" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D108" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E108" s="60" t="inlineStr">
+        <is>
+          <t>Innovation Policy</t>
+        </is>
+      </c>
+      <c r="F108" s="76" t="n">
+        <v>4</v>
+      </c>
+      <c r="G108" s="60" t="inlineStr">
+        <is>
+          <t>Government</t>
+        </is>
+      </c>
+      <c r="H108" s="60" t="inlineStr">
+        <is>
+          <t>NIST News</t>
+        </is>
+      </c>
+      <c r="I108" s="60" t="inlineStr">
+        <is>
+          <t>NIST Receives New Patent for Microbe-Killing Water Heater</t>
+        </is>
+      </c>
+      <c r="J108" s="60" t="inlineStr">
+        <is>
+          <t>Warm water in household pipes can be a breeding ground for harmful bacteria.</t>
+        </is>
+      </c>
+      <c r="K108" s="60" t="inlineStr">
+        <is>
+          <t>https://www.nist.gov/news-events/news/2026/07/nist-receives-new-patent-microbe-killing-water-heater</t>
+        </is>
+      </c>
+      <c r="L108" s="60" t="inlineStr">
+        <is>
+          <t>72b002f5a04f35d9ca1e9949</t>
+        </is>
+      </c>
+      <c r="M108" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T18:56:03+09:00</t>
+        </is>
+      </c>
+      <c r="N108" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O108" s="60" t="inlineStr"/>
+    </row>
+    <row r="109" ht="42" customHeight="1">
+      <c r="A109" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T18:56:03+09:00</t>
+        </is>
+      </c>
+      <c r="B109" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-13T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="C109" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D109" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E109" s="60" t="inlineStr">
+        <is>
+          <t>Innovation Policy | Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="F109" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="G109" s="60" t="inlineStr">
+        <is>
+          <t>Policy Institute</t>
+        </is>
+      </c>
+      <c r="H109" s="60" t="inlineStr">
+        <is>
+          <t>CSET</t>
+        </is>
+      </c>
+      <c r="I109" s="60" t="inlineStr">
+        <is>
+          <t>Washington Is Looking to Keep China From Training Its AI on US Models</t>
+        </is>
+      </c>
+      <c r="J109" s="60" t="inlineStr">
+        <is>
+          <t>CSET’s Colin Shea-Blymyer shared his expert insight in an article published by Bloomberg. The article examines growing concerns in Washington over the use of "distillation" by Chinese AI companies to train models using outputs from leading US systems, and the resulting debate over intellectual property, competition, and national security in the global AI race. The post Washington Is Looking to Keep China From Training Its AI on US Models appeared first on Center for Security and Emerging Technology .</t>
+        </is>
+      </c>
+      <c r="K109" s="60" t="inlineStr">
+        <is>
+          <t>https://cset.georgetown.edu/article/washington-is-looking-to-keep-china-from-training-its-ai-on-us-models/</t>
+        </is>
+      </c>
+      <c r="L109" s="60" t="inlineStr">
+        <is>
+          <t>e96177000536ef3f58f8fb3c</t>
+        </is>
+      </c>
+      <c r="M109" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T18:56:03+09:00</t>
+        </is>
+      </c>
+      <c r="N109" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O109" s="60" t="inlineStr"/>
+    </row>
+    <row r="110" ht="42" customHeight="1">
+      <c r="A110" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T18:56:03+09:00</t>
+        </is>
+      </c>
+      <c r="B110" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-13T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="C110" s="60" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="D110" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E110" s="60" t="inlineStr">
+        <is>
+          <t>Innovation Policy | Quantum</t>
+        </is>
+      </c>
+      <c r="F110" s="76" t="n">
+        <v>1</v>
+      </c>
+      <c r="G110" s="60" t="inlineStr">
+        <is>
+          <t>Official Company</t>
+        </is>
+      </c>
+      <c r="H110" s="60" t="inlineStr">
+        <is>
+          <t>Microsoft Research</t>
+        </is>
+      </c>
+      <c r="I110" s="60" t="inlineStr">
+        <is>
+          <t>Verifying Rust cryptography in SymCrypt, from standards to code</t>
+        </is>
+      </c>
+      <c r="J110" s="60" t="inlineStr">
+        <is>
+          <t>Cryptographic code supports vital protections in modern computing systems. Learn how a new method helps verify code as developers write it while preserving speed and adaptability as it gets implemented and evolves. The post Verifying Rust cryptography in SymCrypt, from standards to code appeared first on Microsoft Research .</t>
+        </is>
+      </c>
+      <c r="K110" s="60" t="inlineStr">
+        <is>
+          <t>https://www.microsoft.com/en-us/research/blog/verifying-rust-cryptography-in-symcrypt-from-standards-to-code/</t>
+        </is>
+      </c>
+      <c r="L110" s="60" t="inlineStr">
+        <is>
+          <t>a7866758cf94a3c5e9d26534</t>
+        </is>
+      </c>
+      <c r="M110" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T18:56:03+09:00</t>
+        </is>
+      </c>
+      <c r="N110" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O110" s="60" t="inlineStr"/>
+    </row>
+    <row r="111" ht="42" customHeight="1">
+      <c r="A111" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T18:56:03+09:00</t>
+        </is>
+      </c>
+      <c r="B111" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-13T12:00:41Z</t>
+        </is>
+      </c>
+      <c r="C111" s="60" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="D111" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E111" s="60" t="inlineStr">
+        <is>
+          <t>Semiconductors &amp; Telecom | Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="F111" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="G111" s="60" t="inlineStr">
+        <is>
+          <t>Official Company</t>
+        </is>
+      </c>
+      <c r="H111" s="60" t="inlineStr">
+        <is>
+          <t>Intel Newsroom</t>
+        </is>
+      </c>
+      <c r="I111" s="60" t="inlineStr">
+        <is>
+          <t>Intel Invests €5 Billion to Expand Manufacturing in Europe</t>
+        </is>
+      </c>
+      <c r="J111" s="60" t="inlineStr">
+        <is>
+          <t>LEIXLIP, Ireland, July 13, 2026 —Intel today announced a €5 billion ($5.7 billion) capital investment at its Leixlip campus in Ireland, marking the next phase in the site’s capacity expansion. Global demand for AI and high-performance computing is driving the need for advanced silicon to power AI Factories, and Intel is scaling capacity in Ireland … The post Intel Invests €5 Billion to Expand Manufacturing in Europe appeared first on Newsroom .</t>
+        </is>
+      </c>
+      <c r="K111" s="60" t="inlineStr">
+        <is>
+          <t>https://newsroom.intel.com/intel-foundry/intel-invests-5-billion-euro-to-expand-manufacturing-in-europe</t>
+        </is>
+      </c>
+      <c r="L111" s="60" t="inlineStr">
+        <is>
+          <t>297a8b5b279e5916cf45fddb</t>
+        </is>
+      </c>
+      <c r="M111" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T18:56:03+09:00</t>
+        </is>
+      </c>
+      <c r="N111" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O111" s="60" t="inlineStr"/>
+    </row>
+    <row r="112" ht="42" customHeight="1">
+      <c r="A112" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T18:56:03+09:00</t>
+        </is>
+      </c>
+      <c r="B112" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-13T10:19:51Z</t>
+        </is>
+      </c>
+      <c r="C112" s="60" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D112" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E112" s="60" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence | Robotics</t>
+        </is>
+      </c>
+      <c r="F112" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="G112" s="60" t="inlineStr">
+        <is>
+          <t>Major Media</t>
+        </is>
+      </c>
+      <c r="H112" s="60" t="inlineStr">
+        <is>
+          <t>IEEE Spectrum</t>
+        </is>
+      </c>
+      <c r="I112" s="60" t="inlineStr">
+        <is>
+          <t>Building a Foundation Stack for General-Purpose Robots</t>
+        </is>
+      </c>
+      <c r="J112" s="60" t="inlineStr">
+        <is>
+          <t>This article is brought to you by X Square Robot . Large language models gave artificial intelligence a working recipe. Pretrain a large model on broad data, and general capability follows. Robotics has no such recipe. Robotics systems have long been assembled from separate perception, planning, and control parts that rarely add up to intelligence a robot can carry from one task to another, or one machine to another. The central problem in embodied AI is to find the equivalent recipe, and the field does not yet agree on what it is. X Square Robot , a Chinese embodied-AI company, has made an unusually explicit bet. It argues that the recipe is an integrated stack, spanning the data a robot l…</t>
+        </is>
+      </c>
+      <c r="K112" s="60" t="inlineStr">
+        <is>
+          <t>https://spectrum.ieee.org/x-square-robot-embodied-ai-stack</t>
+        </is>
+      </c>
+      <c r="L112" s="60" t="inlineStr">
+        <is>
+          <t>d56ace988ec4655cef540679</t>
+        </is>
+      </c>
+      <c r="M112" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T18:56:03+09:00</t>
+        </is>
+      </c>
+      <c r="N112" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O112" s="60" t="inlineStr"/>
+    </row>
+    <row r="113" ht="42" customHeight="1">
+      <c r="A113" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T18:56:03+09:00</t>
+        </is>
+      </c>
+      <c r="B113" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-13T09:57:57Z</t>
+        </is>
+      </c>
+      <c r="C113" s="60" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="D113" s="60" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E113" s="60" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="F113" s="76" t="n">
+        <v>1</v>
+      </c>
+      <c r="G113" s="60" t="inlineStr">
+        <is>
+          <t>Intergovernmental</t>
+        </is>
+      </c>
+      <c r="H113" s="60" t="inlineStr">
+        <is>
+          <t>WHO News</t>
+        </is>
+      </c>
+      <c r="I113" s="60" t="inlineStr">
+        <is>
+          <t>El Salvador validated by WHO as having eliminated trachoma as a public health problem</t>
+        </is>
+      </c>
+      <c r="J113" s="60" t="inlineStr">
+        <is>
+          <t>The World Health Organization (WHO) has validated El Salvador as having eliminated trachoma as a public health problem. Trachoma is the world's leading infectious cause of blindness.</t>
+        </is>
+      </c>
+      <c r="K113" s="60" t="inlineStr">
+        <is>
+          <t>https://www.who.int/news/item/13-07-2026-el-salvador-validated-by-who-as-having-eliminated-trachoma-as-a-public-health-problem</t>
+        </is>
+      </c>
+      <c r="L113" s="60" t="inlineStr">
+        <is>
+          <t>213c7954ea56dfd0fccb556a</t>
+        </is>
+      </c>
+      <c r="M113" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T18:56:03+09:00</t>
+        </is>
+      </c>
+      <c r="N113" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O113" s="60" t="inlineStr"/>
+    </row>
+    <row r="114" ht="42" customHeight="1">
+      <c r="A114" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T18:56:03+09:00</t>
+        </is>
+      </c>
+      <c r="B114" s="75" t="inlineStr">
+        <is>
           <t>2026-07-12T21:00:00Z</t>
         </is>
       </c>
-      <c r="C105" s="60" t="inlineStr">
+      <c r="C114" s="60" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="D105" s="60" t="inlineStr">
+      <c r="D114" s="60" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="E105" s="60" t="inlineStr">
+      <c r="E114" s="60" t="inlineStr">
         <is>
           <t>Artificial Intelligence | Innovation Policy</t>
         </is>
       </c>
-      <c r="F105" s="76" t="n">
+      <c r="F114" s="76" t="n">
         <v>3</v>
       </c>
-      <c r="G105" s="60" t="inlineStr">
+      <c r="G114" s="60" t="inlineStr">
         <is>
           <t>Policy Institute</t>
         </is>
       </c>
-      <c r="H105" s="60" t="inlineStr">
+      <c r="H114" s="60" t="inlineStr">
         <is>
           <t>CSET</t>
         </is>
       </c>
-      <c r="I105" s="60" t="inlineStr">
+      <c r="I114" s="60" t="inlineStr">
         <is>
           <t>Companies turn to Chinese AI models to cut costs</t>
         </is>
       </c>
-      <c r="J105" s="60" t="inlineStr">
+      <c r="J114" s="60" t="inlineStr">
         <is>
           <t>CSET’s Sam Bresnick shared his expert insight in an article published by The Financial Times. The article examines why companies around the world are increasingly adopting Chinese AI models, drawn by their lower costs, improving capabilities, and the flexibility offered by open-weight systems. The post Companies turn to Chinese AI models to cut costs appeared first on Center for Security and Emerging Technology .</t>
         </is>
       </c>
-      <c r="K105" s="60" t="inlineStr">
+      <c r="K114" s="60" t="inlineStr">
         <is>
           <t>https://cset.georgetown.edu/article/companies-turn-to-chinese-ai-models-to-cut-costs/</t>
         </is>
       </c>
-      <c r="L105" s="60" t="inlineStr">
+      <c r="L114" s="60" t="inlineStr">
         <is>
           <t>9e1bc06c29b61bed048d4f44</t>
         </is>
       </c>
-      <c r="M105" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="N105" s="60" t="inlineStr">
+      <c r="M114" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T18:56:03+09:00</t>
+        </is>
+      </c>
+      <c r="N114" s="60" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="O105" s="60" t="inlineStr"/>
+      <c r="O114" s="60" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:O105"/>
+  <autoFilter ref="A3:O114"/>
   <mergeCells count="2">
     <mergeCell ref="A1:O1"/>
     <mergeCell ref="A2:O2"/>
@@ -8470,7 +9109,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="N4:N105" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="N4:N114" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"New,Reviewed,Follow-up,Archived"</formula1>
     </dataValidation>
   </dataValidations>
@@ -8577,10 +9216,19 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K103" r:id="rId100"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K104" r:id="rId101"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K105" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K106" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K107" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K108" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K109" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K110" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K111" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K112" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K113" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K114" r:id="rId111"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId103"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId112"/>
   </tableParts>
 </worksheet>
 </file>
@@ -10652,7 +11300,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -10731,26 +11379,26 @@
     <row r="4" ht="42" customHeight="1">
       <c r="A4" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:10:55+09:00</t>
+          <t>2026-07-26T19:51:39+09:00</t>
         </is>
       </c>
       <c r="B4" s="77" t="n">
         <v>34</v>
       </c>
       <c r="C4" s="77" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D4" s="77" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E4" s="77" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F4" s="77" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G4" s="77" t="n">
-        <v>194.65</v>
+        <v>11.55</v>
       </c>
       <c r="H4" s="60" t="inlineStr">
         <is>
@@ -10761,26 +11409,26 @@
     <row r="5">
       <c r="A5" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:05:06+09:00</t>
+          <t>2026-07-26T19:10:55+09:00</t>
         </is>
       </c>
       <c r="B5" s="77" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C5" s="77" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D5" s="77" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E5" s="77" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="F5" s="77" t="n">
         <v>9</v>
       </c>
       <c r="G5" s="77" t="n">
-        <v>165.89</v>
+        <v>194.65</v>
       </c>
       <c r="H5" s="60" t="inlineStr">
         <is>
@@ -10791,35 +11439,65 @@
     <row r="6">
       <c r="A6" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T19:05:06+09:00</t>
         </is>
       </c>
       <c r="B6" s="77" t="n">
         <v>33</v>
       </c>
       <c r="C6" s="77" t="n">
+        <v>24</v>
+      </c>
+      <c r="D6" s="77" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" s="77" t="n">
+        <v>39</v>
+      </c>
+      <c r="F6" s="77" t="n">
+        <v>9</v>
+      </c>
+      <c r="G6" s="77" t="n">
+        <v>165.89</v>
+      </c>
+      <c r="H6" s="60" t="inlineStr">
+        <is>
+          <t>Daily update</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T18:56:03+09:00</t>
+        </is>
+      </c>
+      <c r="B7" s="77" t="n">
+        <v>33</v>
+      </c>
+      <c r="C7" s="77" t="n">
         <v>20</v>
       </c>
-      <c r="D6" s="77" t="n">
+      <c r="D7" s="77" t="n">
         <v>94</v>
       </c>
-      <c r="E6" s="77" t="n">
+      <c r="E7" s="77" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="77" t="n">
+      <c r="F7" s="77" t="n">
         <v>13</v>
       </c>
-      <c r="G6" s="77" t="n">
+      <c r="G7" s="77" t="n">
         <v>129.43</v>
       </c>
-      <c r="H6" s="60" t="inlineStr">
+      <c r="H7" s="60" t="inlineStr">
         <is>
           <t>Initial lookback</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:H6"/>
+  <autoFilter ref="A3:H7"/>
   <mergeCells count="2">
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>

--- a/docs/innovation_news_ledger.xlsx
+++ b/docs/innovation_news_ledger.xlsx
@@ -11,7 +11,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'News Ledger'!$A$3:$O$114</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Source Registry'!$A$3:$K$37</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Run Log'!$A$3:$H$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Run Log'!$A$3:$H$8</definedName>
   </definedNames>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -516,7 +516,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="RunLogTable" displayName="RunLogTable" ref="A3:H7" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="RunLogTable" displayName="RunLogTable" ref="A3:H8" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <autoFilter ref="A3:H4"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Run Time (JST)"/>
@@ -800,7 +800,7 @@
       </c>
       <c r="B5" s="25" t="inlineStr">
         <is>
-          <t>2026-07-26T19:51:39+09:00</t>
+          <t>2026-07-26T20:00:03+09:00</t>
         </is>
       </c>
       <c r="C5" s="46" t="n"/>
@@ -1254,12 +1254,12 @@
       </c>
       <c r="I4" s="60" t="inlineStr">
         <is>
-          <t>Were the German courts too soft on Chinese members of drug rape network?</t>
+          <t>ドイツの裁判所は中国の薬物強姦ネットワークのメンバーに対して甘すぎたのか？</t>
         </is>
       </c>
       <c r="J4" s="60" t="inlineStr">
         <is>
-          <t>Minutes after a Berlin court sentenced a Chinese man to five years in prison for aiding and abetting aggravated rape and sexual coercion, two women who had sat through the trial hugged each other and cried. But the case left one of those women, named Kristina, balancing mixed emotions as she struggled to reconcile her desire to see the perpetrators punished and questions about what justice really meant in a case of this nature. The 32-year-old accused, who was studying medicine, was jailed for...</t>
+          <t>ベルリンの裁判所が中国人男性に対し、強姦と性的強要の幇助で5年の懲役を言い渡したことに対し、被害者の女性たちは複雑な感情を抱いている。この事件は、正義とは何かを考えさせるものである。</t>
         </is>
       </c>
       <c r="K4" s="60" t="inlineStr">
@@ -1325,12 +1325,12 @@
       </c>
       <c r="I5" s="60" t="inlineStr">
         <is>
-          <t>Lower profit margins set to foil Chinese carmakers’ price war plans despite falling sales</t>
+          <t>中国の自動車メーカー、利益率低下で価格戦争計画が頓挫</t>
         </is>
       </c>
       <c r="J5" s="60" t="inlineStr">
         <is>
-          <t>Narrowing profit margins due to higher raw material costs have dealt yet another major blow to China’s carmakers as they face shrinking market demand amid a rollback of purchase subsidies and tax incentives. The dire scenario could also dash Chinese consumers’ hopes for steep discounts, despite carmakers’ efforts to reduce their inventories, according to dealers and analysts. “The crux point is that most carmakers are facing squeezed margins and are unable to offer further price cuts to attract...</t>
+          <t>中国の自動車メーカーは、原材料費の高騰により利益率が縮小し、販売需要の減少に直面している。これにより、消費者が期待する大幅な値下げが難しくなる可能性がある。</t>
         </is>
       </c>
       <c r="K5" s="60" t="inlineStr">
@@ -1396,12 +1396,12 @@
       </c>
       <c r="I6" s="60" t="inlineStr">
         <is>
-          <t>European heatwaves drive summer tourists to cooler north</t>
+          <t>欧州の熱波が夏の観光客を涼しい北へ誘導</t>
         </is>
       </c>
       <c r="J6" s="60" t="inlineStr">
         <is>
-          <t>European holidaymakers worn down by recurrent heatwaves are currently snubbing Mediterranean destinations for northern climes in hopes of cooler temperatures, but it remains to be seen whether it is just a fad or a durable shift in the tourism market. With temperatures in the European summer regularly climbing up towards 40 degrees Celsius (100 degrees Fahrenheit), cool has become cool. This year, visitors “have been telling me that they have escaped the heat in southern parts of Europe”, said...</t>
+          <t>欧州の観光客は、繰り返される熱波の影響で地中海の目的地を避け、涼しい北部を選ぶ傾向が見られる。これは観光市場における持続的な変化を示す可能性がある。</t>
         </is>
       </c>
       <c r="K6" s="60" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="I7" s="60" t="inlineStr">
         <is>
-          <t>Rare medical condition causes Chinese man’s scalp to thicken and fold, resembling human brain</t>
+          <t>中国の男性が珍しい病状で頭皮が厚く折りたたまれる</t>
         </is>
       </c>
       <c r="J7" s="60" t="inlineStr">
         <is>
-          <t>A man from central China had long been troubled by a thickening scalp that developed folds resembling the creases of a brain, but he eventually found a plastic surgeon who could address his condition. The 23-year-old man from Hunan province, surnamed Li, recently had his issue resolved at the Zhongnan Hospital of Wuhan University in Hubei. Li first noticed the hardening of his scalp several years ago. As the condition advanced, his scalp thickened and proliferated, creating large areas of uneven...</t>
+          <t>中国中部の男性が、脳のひだに似た厚い頭皮の状態に悩まされていたが、整形外科医によって治療を受けた。この症例は医療技術の重要性を示すものである。</t>
         </is>
       </c>
       <c r="K7" s="60" t="inlineStr">
@@ -1538,12 +1538,12 @@
       </c>
       <c r="I8" s="60" t="inlineStr">
         <is>
-          <t>Indonesia’s plan for a Singapore rival starts to take shape</t>
+          <t>インドネシアのシンガポール対抗計画が具体化</t>
         </is>
       </c>
       <c r="J8" s="60" t="inlineStr">
         <is>
-          <t>Indonesia wants to build a financial centre to rival Singapore, Hong Kong or Dubai, but analysts say the real work of persuading global investors has barely begun. Parliament’s passage of the enabling legislation on Tuesday laid the legal foundation for the hub, marking a milestone in President Prabowo Subianto’s push to attract more foreign capital into Southeast Asia’s largest economy and lift growth towards 8 per cent by the end of his term in 2029. Yet observers caution that the centre,...</t>
+          <t>インドネシアはシンガポール、香港、ドバイに対抗する金融センターの建設を目指しており、法律的基盤が整ったことで外国資本の誘致に向けた重要な一歩を踏み出した。しかし、実際の投資誘致にはさらなる努力が必要とされている。</t>
         </is>
       </c>
       <c r="K8" s="60" t="inlineStr">
@@ -1609,12 +1609,12 @@
       </c>
       <c r="I9" s="60" t="inlineStr">
         <is>
-          <t>US pauses nightly Iran strikes, as Houthis clash with Saudis</t>
+          <t>米国がイランへの夜間攻撃を一時停止、フーシ派とサウジの衝突</t>
         </is>
       </c>
       <c r="J9" s="60" t="inlineStr">
         <is>
-          <t>Skirmishes between Houthi rebels and Saudi Arabia intensified, as a pause in the nearly two-week run of nightly US strikes on Iran raised fresh questions about President Donald Trump’s strategy in the war. The Houthis, Islamist militants based in Yemen and backed by Iran, said they fired missiles and drones at facilities linked to oil giant Saudi Aramco in the Red Sea port towns of Jizan and Yanbu. There was no immediate confirmation from the Saudi government or Aramco. Saudi authorities briefly...</t>
+          <t>フーシ派とサウジアラビアの間で衝突が激化する中、米国のイランへの夜間攻撃が一時停止され、トランプ大統領の戦略に新たな疑問が生じている。</t>
         </is>
       </c>
       <c r="K9" s="60" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="I10" s="60" t="inlineStr">
         <is>
-          <t>The West is debating AI’s future with half the world absent</t>
+          <t>西側諸国がAIの未来を議論する中、半分の世界が不在</t>
         </is>
       </c>
       <c r="J10" s="60" t="inlineStr">
         <is>
-          <t>On July 13, more than 200 leading economists and AI researchers, including 16 Nobel laureates, signed an open letter organised by the Stanford Digital Economy Lab. Its warning was stark: artificial intelligence may drive an economic transformation “larger than the Industrial Revolution” compressed into a fraction of the time, and that we “must act now” to build the institutions to steer it. We agree with every word. Then we scanned the signatory list. Four in five signatories come from the...</t>
+          <t>スタンフォードデジタル経済ラボが主導した公開書簡には、AIが産業革命を超える経済変革を引き起こす可能性があると警告する200人以上の経済学者とAI研究者が署名した。これは、AIの影響を適切に管理するための制度構築の必要性を強調している。</t>
         </is>
       </c>
       <c r="K10" s="60" t="inlineStr">
@@ -1751,12 +1751,12 @@
       </c>
       <c r="I11" s="60" t="inlineStr">
         <is>
-          <t>Mega datacentre planned for outer Melbourne will be six times bigger than a large shopping centre</t>
+          <t>メルボルン郊外に計画されているメガデータセンター</t>
         </is>
       </c>
       <c r="J11" s="60" t="inlineStr">
         <is>
-          <t>More than 3,600 people sign petition for careful assessment of proposed AI hub, now a flashpoint for national debate on datacentre boom Follow our Australia news live blog for latest updates Get our breaking news email , free app or daily news podcast For some residents it started with a letter in the mailbox. It was a “friendly introduction from the team behind the Victorian AI hub”. “I am knocking on doors to explain what we have in mind and, most importantly, to listen,” the letter from Syncline Energy stated. Continue reading...</t>
+          <t>メルボルン郊外に計画されているAIハブは、大型ショッピングセンターの6倍の規模を持つデータセンターであり、地域住民からの慎重な評価を求める署名が3,600人以上集まった。これはデータセンターの急増に関する国民的議論の焦点となっている。</t>
         </is>
       </c>
       <c r="K11" s="60" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="I12" s="60" t="inlineStr">
         <is>
-          <t>Samsung Electronics and Broadcom Expand Strategic Collaboration Across Memory and Foundry Technologies</t>
+          <t>サムスン電子とブロードコム、メモリとファウンドリ技術で戦略的協力を拡大</t>
         </is>
       </c>
       <c r="J12" s="60" t="inlineStr">
         <is>
-          <t>Samsung Electronics and Broadcom today announced the signing of a memorandum of understanding (MOU) to expand their strategic collaboration across memory and foundry technologies, supporting the next generation of AI infrastructure. The MOU was announced during the AI Summit, held at The Midway in San Francisco. Attendees included Jinman Han, President and Head of Samsung […]</t>
+          <t>サムスン電子とブロードコムは、AIインフラの次世代を支えるためのメモランダムを締結し、メモリとファウンドリ技術における戦略的協力を拡大することを発表した。これは、AI技術の進展に向けた重要なステップである。</t>
         </is>
       </c>
       <c r="K12" s="60" t="inlineStr">
@@ -1893,12 +1893,12 @@
       </c>
       <c r="I13" s="60" t="inlineStr">
         <is>
-          <t>The AI jobs apocalypse probably isn’t coming anytime soon</t>
+          <t>AIによる雇用の終焉はすぐには訪れない</t>
         </is>
       </c>
       <c r="J13" s="60" t="inlineStr">
         <is>
-          <t>Artificial intelligence may not deliver on its promise of vast economic opportunity at a price that humanity is willing to pay In March, Anthropic, the cutting-edge artificial intelligence business that gave us the chatbot Claude, published an analysis on the impact of AI on employment, to help us assess the claim that intelligent robots were about to redefine human existence, ending demand for human labor. Last year in May, Anthropic’s co-founder, Dario Amodei, claimed AI could wipe out half of all entry-level jobs in one to five years. Last January, he told us AI would probably become a “general labor substitute for humans”. In June he said we risk “a world where the economic trade-off di…</t>
+          <t>Anthropic社の分析によれば、人工知能が人間の労働需要を根本的に変えるという主張には疑問が残る。AIがエントリーレベルの仕事を半減させるという予測は過大評価であり、実際の影響は限定的である可能性が高い。</t>
         </is>
       </c>
       <c r="K13" s="60" t="inlineStr">
@@ -1964,12 +1964,12 @@
       </c>
       <c r="I14" s="60" t="inlineStr">
         <is>
-          <t>What is a supernode, and why does it matter for the China-US tech rivalry?</t>
+          <t>スーパーノードとは何か、そして中国と米国の技術競争における重要性</t>
         </is>
       </c>
       <c r="J14" s="60" t="inlineStr">
         <is>
-          <t>As the size of artificial intelligence models expands beyond 1 trillion parameters, a new concept is dominating the computing landscape: “supernode”. At this year’s World Artificial Intelligence Conference (WAIC), China’s top AI summit, domestic chipmakers from Huawei Technologies to Biren Technology showcased new hardware designed to knit hundreds or thousands of chips together to act as one giant supercomputer, which they called a supernode. The focus on supernodes at WAIC reflected a shift in...</t>
+          <t>人工知能モデルのサイズが1兆パラメータを超える中、中国のAIサミットである世界人工知能会議（WAIC）では、複数のチップを結合して一つの巨大なスーパーコンピュータとして機能する新しいハードウェア「スーパーノード」が紹介された。これは、AIインフラの進化を示す重要な動きである。</t>
         </is>
       </c>
       <c r="K14" s="60" t="inlineStr">
@@ -2035,12 +2035,12 @@
       </c>
       <c r="I15" s="60" t="inlineStr">
         <is>
-          <t>Risky bet: The winners and losers from the OpenAI-Hugging Face hacking mess</t>
+          <t>リスクのある賭け：OpenAI-Hugging Faceハッキング事件の勝者と敗者</t>
         </is>
       </c>
       <c r="J15" s="60" t="inlineStr">
         <is>
-          <t>When OpenAI revealed this week that one of its AI models went rogue during a security test and autonomously hacked the start-up Hugging Face, it came as a shock. Questions were raised quickly, but there was no immediate clarity. Hugging Face co-founder and chief executive Clem Delangue said the incident was "possibly the first of its kind". As with any serious tech incident, there are those who stand to gain and other who stand to lose. And the circumstances can be as complex as the hacking is. Losers: OpenAI and Hugging Face Let's start with the obvious matter. It was a PR nightmare for ChatGPT maker OpenAI, as well as Hugging Face, as they bore the brunt of the mess, albeit for different…</t>
+          <t>OpenAIのAIモデルがセキュリティテスト中にハッキングを行った事件が発覚。OpenAIとHugging FaceはPRの面で大きな打撃を受けた。</t>
         </is>
       </c>
       <c r="K15" s="60" t="inlineStr">
@@ -2106,12 +2106,12 @@
       </c>
       <c r="I16" s="60" t="inlineStr">
         <is>
-          <t>‘I thought, I’ve tried everything else, why not give AI a shot?’: the long-lost family reunited by ChatGPT</t>
+          <t>AIで再会した家族：ChatGPTの力</t>
         </is>
       </c>
       <c r="J16" s="60" t="inlineStr">
         <is>
-          <t>Avtar spent decades wondering what happened to the mother he never got to know. Thousands of miles away, Nicci was haunted by the story of a half-brother given away before she was born. How did a chatbot bring them together? As a small boy growing up in Amritsar, India, in the 1960s, Avtar Singh used to hear whispers. Your mum isn’t really your mum , the rumours would say. Your mum lives abroad. Avtar didn’t really pay any attention to it. “I thought, the neighbours are just making up stories.” But the stories were true: the woman raising Avtar was actually his grandmother. When he was too young to remember it, his father had emigrated to Canada to work as a teacher, leaving Avtar in the ca…</t>
+          <t>Avtarは母親を知らずに過ごし、ChatGPTを通じて長年の謎を解明。AIが彼と半兄を再会させた経緯が語られている。</t>
         </is>
       </c>
       <c r="K16" s="60" t="inlineStr">
@@ -2177,12 +2177,12 @@
       </c>
       <c r="I17" s="60" t="inlineStr">
         <is>
-          <t>2022 IEEE President K.J. Ray Liu Honored for His Leadership</t>
+          <t>2022年IEEE会長K.J.レイ・リウがリーダーシップで表彰</t>
         </is>
       </c>
       <c r="J17" s="60" t="inlineStr">
         <is>
-          <t>Unlike many budding engineers, K.J. Ray Liu wasn’t inspired to enter the field by tinkering with electronics or following in the footsteps of a family member. Growing up in Taichung, Taiwan, he answered his government’s call for students to become electrical engineers to help manufacture semiconductors in the 1970s, when the country’s economy was struggling. “Students who were good in math, science, and physics all wanted to be an electrical engineer because that was the top priority of the government,” Liu says. “That’s how I got into engineering. Now Taiwan is a world leader in semiconductors.” K.J. Ray Liu Occupation Retired professor of information technology and a digital signal proces…</t>
+          <t>K.J.レイ・リウは、台湾の半導体産業の発展に寄与した功績が評価され、IEEEのリーダーシップ賞を受賞した。</t>
         </is>
       </c>
       <c r="K17" s="60" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="I18" s="60" t="inlineStr">
         <is>
-          <t>Nvidia, Microsoft and IBM among companies endorsing open-weight AI models</t>
+          <t>Nvidia、Microsoft、IBMがオープンウェイトAIモデルを支持</t>
         </is>
       </c>
       <c r="J18" s="60" t="inlineStr">
         <is>
-          <t>Nvidia chief executive Jensen Huang joined X on Friday and used his first post to champion AI models that can be downloaded and adapted, arguing they are vital to preserving America’s lead in artificial intelligence. Mr Huang attached a letter signed by 25 major companies, including Microsoft, Palantir , Perplexity, CrowdStrike and IBM that endorsed open-source software development and “open-weight” AI models. Some US officials have raised concerns that AI models could pose national security risks, while companies such as OpenAI and Anthropic still largely oppose open architecture for proprietary reasons. “Open source did more than lower the cost of software; it created a shared foundation…</t>
+          <t>NvidiaのCEOが、ダウンロード可能で適応可能なAIモデルの重要性を強調し、25社の署名を添えた。オープンソース開発の支持が、アメリカのAIリーダーシップを維持するために必要だと述べている。</t>
         </is>
       </c>
       <c r="K18" s="60" t="inlineStr">
@@ -2319,12 +2319,12 @@
       </c>
       <c r="I19" s="60" t="inlineStr">
         <is>
-          <t>The quest to keep organs alive outside the body</t>
+          <t>体外で臓器を生かし続けるための探求</t>
         </is>
       </c>
       <c r="J19" s="60" t="inlineStr">
         <is>
-          <t>This week, I covered a fascinating effort to preserve organs outside the body. There’s a huge shortage of donor organs, and one of the main reasons is time—they survive only a matter of hours outside the body, even when they’re kept on ice. Doctors dream of organ banks—stores of human organs that can be preserved…</t>
+          <t>臓器提供の不足を解消するため、体外での臓器保存に関する取り組みが進められている。臓器は数時間しか生存できず、医師たちは臓器バンクの実現を夢見ている。</t>
         </is>
       </c>
       <c r="K19" s="60" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="I20" s="60" t="inlineStr">
         <is>
-          <t>Intel and Lens Technology Collaborate to Enable Advanced Semiconductor Packaging for the AI Era</t>
+          <t>インテルとレンズテクノロジーがAI時代の半導体パッケージングを推進するために協力</t>
         </is>
       </c>
       <c r="J20" s="60" t="inlineStr">
         <is>
-          <t>SANTA CLARA, Calif. &amp; CHANGSHA, China — Intel Corporation and Lens Technology today announced a strategic collaboration focused on enabling new technologies for advanced semiconductor packaging. Through this work, the companies intend to explore opportunities to accelerate the development of glass substrate-based packaging solutions that can help enable higher performance, increased interconnect density, and improved … The post Intel and Lens Technology Collaborate to Enable Advanced Semiconductor Packaging for the AI Era appeared first on Newsroom .</t>
+          <t>インテルとレンズテクノロジーは、先進的な半導体パッケージング技術の開発を目指す戦略的な協力を発表。ガラス基板を用いたパッケージングソリューションの開発を加速することを目指している。</t>
         </is>
       </c>
       <c r="K20" s="60" t="inlineStr">
@@ -2461,12 +2461,12 @@
       </c>
       <c r="I21" s="60" t="inlineStr">
         <is>
-          <t>Guidance: Cyber Resilience Pledge - list of signatories</t>
+          <t>サイバー耐性誓約：署名者リスト</t>
         </is>
       </c>
       <c r="J21" s="60" t="inlineStr">
         <is>
-          <t>Organisations that have signed the Cyber Resilience Pledge.</t>
+          <t>サイバー耐性誓約に署名した組織のリストが公開された。</t>
         </is>
       </c>
       <c r="K21" s="60" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="I22" s="60" t="inlineStr">
         <is>
-          <t>Be skeptical of OpenAI’s rogue hacker agent story | John Thickstun</t>
+          <t>OpenAIのハッカーエージェントの話に懐疑的であるべき</t>
         </is>
       </c>
       <c r="J22" s="60" t="inlineStr">
         <is>
-          <t>If OpenAI loudly proclaims how dangerous AI is, investors will hear how powerful it is. And who benefits from that? On 14 February 2019, OpenAI announced a language model called GPT-2, the precursor to the models that power modern AI chatbots and agents such as ChatGPT and Claude. But OpenAI declared GPT-2 was too risky to release, citing concerns about safety and abuse. I recall being annoyed at the time that OpenAI would make such a useless announcement: the risks seemed overblown, and without access to the model there wasn’t much for a researcher like me to learn about GPT-2. Continue reading...</t>
+          <t>OpenAIがAIの危険性を強調することで、投資家はその力を認識する。GPT-2のリリースを控えた当時の懸念について、著者は過剰なリスク評価だと感じていた。</t>
         </is>
       </c>
       <c r="K22" s="60" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="I23" s="60" t="inlineStr">
         <is>
-          <t>Should you use AI for a task? Here’s a simple way to decide | Bruce Schneier</t>
+          <t>AIをタスクに使用すべきか？シンプルな判断方法</t>
         </is>
       </c>
       <c r="J23" s="60" t="inlineStr">
         <is>
-          <t>Sometimes, what matters isn’t your output but what you put into the process. Think of it like work v the gym I teach public policy at the Harvard Kennedy School and the Munk School at the University of Toronto. And it will come as no surprise to you that my students regularly use AI to complete their writing assignments. Doing so is a waste of their tuition money. But if their entire career is going to include AI writing assistants, why shouldn’t they embrace their future? The best way I’ve found to explain the dilemma comes from the AI researcher Daniel Meissler: it’s the difference between work and the gym. Continue reading...</t>
+          <t>ハーバード・ケネディスクールのブルース・シュナイアー教授は、AIを利用することの是非について考察。学生がAIを使って課題を完成させることが多いが、それが教育費の無駄になる可能性があると警告している。</t>
         </is>
       </c>
       <c r="K23" s="60" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="I24" s="60" t="inlineStr">
         <is>
-          <t>Zoom launches live voice translation, with Arabic coming in late 2026</t>
+          <t>Zoomがライブ音声翻訳サービスを開始、アラビア語は2026年末に対応</t>
         </is>
       </c>
       <c r="J24" s="60" t="inlineStr">
         <is>
-          <t>Zoom Technologies has launched a new live voice translation service, with Arabic support coming in the fourth quarter of this year. Five languages – English, Chinese, French, Japanese and Spanish – will initially be available, the California-based company said. A Zoom representative confirmed to The National that Arabic will be available in the fourth quarter, alongside German, Italian and Portuguese. Zoom launched a version of the service in April, after promoting it at its Zoomtopia conference last September. Using the live voice translation feature requires a Pro, Business, or Enterprise account, the artificial intelligence plug-in ZoomMate, or a stand-alone add-on. Zoom has posted instr…</t>
+          <t>Zoom Technologiesは新たにライブ音声翻訳サービスを開始し、初めは英語、中国語、フランス語、日本語、スペイン語の5言語が利用可能。アラビア語は2026年末に追加される予定で、ドイツ語、イタリア語、ポルトガル語も同時に対応する。</t>
         </is>
       </c>
       <c r="K24" s="60" t="inlineStr">
@@ -2745,12 +2745,12 @@
       </c>
       <c r="I25" s="60" t="inlineStr">
         <is>
-          <t>At AI Summit, South Korea Outlines Its AI Future With NVIDIA and Partners</t>
+          <t>AIサミットで韓国がAIの未来を描く</t>
         </is>
       </c>
       <c r="J25" s="60" t="inlineStr">
         <is>
-          <t>At this week’s AI Summit in San Francisco, South Korean President Jae Myung Lee and some of the country’s top business leaders and researchers are meeting with NVIDIA and ecosystem partners to chart Korea’s AI progress. Building on NVIDIA founder and CEO Jensen Huang’s visit to Korea last month, this week’s discussions and announcements advance […]</t>
+          <t>韓国の李在明大統領がサンフランシスコで開催されたAIサミットで、NVIDIAやパートナーと共に韓国のAIの進展を議論した。</t>
         </is>
       </c>
       <c r="K25" s="60" t="inlineStr">
@@ -2816,12 +2816,12 @@
       </c>
       <c r="I26" s="60" t="inlineStr">
         <is>
-          <t>Briefing Chat: Baby &lt;i&gt;T. rex&lt;/i&gt; were killers from birth, suggest new fossils</t>
+          <t>新たな化石が示すベビーT. rexの捕食者としての特性</t>
         </is>
       </c>
       <c r="J26" s="60" t="inlineStr">
         <is>
-          <t>Nature, Published online: 24 July 2026; doi:10.1038/d41586-026-02338-2 Nature staff discuss the young but deadly dinosaur kings, the prowess of ancient Egyptian princesses, and how London is becoming the world’s AI safety capital.</t>
+          <t>新たに発見された化石が、ベビーT. rexが誕生時から捕食者であった可能性を示唆している。</t>
         </is>
       </c>
       <c r="K26" s="60" t="inlineStr">
@@ -2887,12 +2887,12 @@
       </c>
       <c r="I27" s="60" t="inlineStr">
         <is>
-          <t>Bizarre CRISPR enzyme kills cancer cells by shredding their DNA</t>
+          <t>CRISPR酵素が癌細胞をDNAを破壊して殺す</t>
         </is>
       </c>
       <c r="J27" s="60" t="inlineStr">
         <is>
-          <t>Nature, Published online: 24 July 2026; doi:10.1038/d41586-026-02268-z Early tests suggest the protein can be aimed at targets with tumour-causing mutations.</t>
+          <t>新たなCRISPR酵素が、癌細胞のDNAを破壊することで癌細胞を殺す可能性があることが初期のテストで示された。</t>
         </is>
       </c>
       <c r="K27" s="60" t="inlineStr">
@@ -2958,12 +2958,12 @@
       </c>
       <c r="I28" s="60" t="inlineStr">
         <is>
-          <t>Intel Reports Second-Quarter 2026 Financial Results</t>
+          <t>インテル、2026年第2四半期の財務結果を報告</t>
         </is>
       </c>
       <c r="J28" s="60" t="inlineStr">
         <is>
-          <t>Intel Corporation’s second-quarter 2026 earnings news release and presentation are available on the company’s Investor Relations website. The earnings conference call for investors begins at 2 p.m. PDT today; a public webcast will be available at www.intc.com.More: Earnings News Release | Earnings Call Comments from CEO Lip-Bu Tan and CFO Dave Zinsner The post Intel Reports Second-Quarter 2026 Financial Results appeared first on Newsroom .</t>
+          <t>インテルは、2026年第2四半期の財務結果を発表し、投資家向けのカンファレンスコールを開催する予定である。</t>
         </is>
       </c>
       <c r="K28" s="60" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="I29" s="60" t="inlineStr">
         <is>
-          <t>Trump says nearly 200 firms have signed pledge to protect Americans from costs arising from datacenters</t>
+          <t>トランプ、データセンターのコスト保護に関する誓約を発表</t>
         </is>
       </c>
       <c r="J29" s="60" t="inlineStr">
         <is>
-          <t>‘Ratepayer Protection Pledge’ president has touted is non-binding as people continue to struggle with rising bills Donald Trump has announced that about 200 entities have signed on to his non-binding “Ratepayer Protection Pledge”, expanding a voluntary commitment which claims to ensure US consumers will not bear the cost of the AI datacenter build-out. Trump delivered remarks on Thursday at the Environmental Protection Agency (EPA) headquarters, alongside Lee Zeldin, the agency’s administrator, and Chris Wright, the energy secretary. Other attenders included governors who signed on to the pledge, including Brian Kemp of Georgia, Mike DeWine of Ohio, Spencer Cox of Utah and Jeff Landry of Lo…</t>
+          <t>トランプは、約200の企業がAIデータセンターの建設に伴うコストからアメリカの消費者を保護するという非拘束的な誓約に署名したと発表した。</t>
         </is>
       </c>
       <c r="K29" s="60" t="inlineStr">
@@ -3100,12 +3100,12 @@
       </c>
       <c r="I30" s="60" t="inlineStr">
         <is>
-          <t>[Infographic] [Galaxy Unpacked July 2026] Highlights From Galaxy Unpacked</t>
+          <t>Galaxy Unpackedのハイライト</t>
         </is>
       </c>
       <c r="J30" s="60" t="inlineStr">
         <is>
-          <t>On July 22, Samsung Electronics hosted Galaxy Unpacked July 2026 at Old Billingsgate in London — unveiling its next-generation foldables with agentic AI. Alongside Galaxy Z Fold8 Ultra, Galaxy Z Fold8 and Galaxy Z Flip8, Samsung introduced Galaxy Watch Ultra2 and Galaxy Watch9 with more advanced health features, as well as intelligent eyewear. Through a […]</t>
+          <t>サムスンは、ロンドンで開催されたGalaxy Unpacked July 2026で、次世代の折りたたみ式デバイスや健康機能を強化したスマートウォッチを発表した。新しいAI技術を搭載した製品が紹介された。</t>
         </is>
       </c>
       <c r="K30" s="60" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="I31" s="60" t="inlineStr">
         <is>
-          <t>Supercooled kidneys have been transplanted into pigs in a “landmark achievement”</t>
+          <t>超冷却腎臓が豚に移植される</t>
         </is>
       </c>
       <c r="J31" s="60" t="inlineStr">
         <is>
-          <t>When it comes to organ donation, time is everything. As soon as an organ has been carefully removed from a donor’s body, it starts to deteriorate. Surgeons have a matter of hours to get it into a recipient. Leave it too long and the organ will become unusable. In most cases, organs will be kept…</t>
+          <t>臓器提供において、時間が重要である中、超冷却された腎臓が豚に移植されるという画期的な成果が報告された。臓器の劣化を防ぐための新たな技術が期待される。</t>
         </is>
       </c>
       <c r="K31" s="60" t="inlineStr">
@@ -3242,12 +3242,12 @@
       </c>
       <c r="I32" s="60" t="inlineStr">
         <is>
-          <t>Customers prefer AI chatbots, says British Gas owner as 1,300 call centre and back office jobs axed</t>
+          <t>ブリティッシュ・ガス、AIチャットボットの導入で1300人の雇用削減</t>
         </is>
       </c>
       <c r="J32" s="60" t="inlineStr">
         <is>
-          <t>CEO Chris O’Shea defends Centrica’s plans as it reports rise in retail profits following focus on bigger margins The owner of British Gas has claimed that most households would rather speak with an AI chatbot than deal with the company’s staff as it prepares to cut 1,300 jobs from its call centres and back office. Centrica, the supplier’s FTSE 100 owner, plans to cut 800 jobs as the company carries out a “targeted deployment of AI tools”, on top of the 500 cuts it confirmed last month. Continue reading...</t>
+          <t>ブリティッシュ・ガスの親会社Centricaは、AIチャットボットを導入することで多くの家庭がスタッフよりもチャットボットと話すことを好むと主張し、1300人の雇用を削減する計画を発表した。</t>
         </is>
       </c>
       <c r="K32" s="60" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="I33" s="60" t="inlineStr">
         <is>
-          <t>[Galaxy Unpacked July 2026] Samsung and Partners Envision a Connected Care Future — From First Signal to Lasting Change</t>
+          <t>サムスン、デジタルヘルスの未来を描く</t>
         </is>
       </c>
       <c r="J33" s="60" t="inlineStr">
         <is>
-          <t>At Galaxy Unpacked July 2026 in London, Samsung Electronics set out its vision for the next chapter of digital health — a future where care moves from reactive treatment toward preventive, personalized and connected experiences, supported by trusted health innovation and partnerships across the healthcare ecosystem. To explore that vision, Samsung hosted a Health Forum […]</t>
+          <t>サムスン電子は、ロンドンで開催されたGalaxy Unpacked July 2026で、予防的かつ個別化されたデジタルヘルスの未来を提案した。医療エコシステム全体との信頼できるパートナーシップを通じて、接続された体験を提供することを目指している。</t>
         </is>
       </c>
       <c r="K33" s="60" t="inlineStr">
@@ -3384,12 +3384,12 @@
       </c>
       <c r="I34" s="60" t="inlineStr">
         <is>
-          <t>Elon Musk says he got ‘carried away’ with Trump – but still holds on to contentious political views</t>
+          <t>イーロン・マスク、トランプとの関係を振り返る</t>
         </is>
       </c>
       <c r="J34" s="60" t="inlineStr">
         <is>
-          <t>In interview, billionaire says instead of running ‘Doge’ he should’ve ‘worked on my companies’ and shares extreme predictions Elon Musk has admitted he became too consumed by politics during his volatile alliance with Donald Trump and his brief appointment as the president’s financial axman, running the so-called “department of government efficiency” (Doge). The world’s richest person, and briefly its first trillionaire after his SpaceX company floated on the New York stock exchange in June, made the confession in a wide-ranging interview with the Economist published on Thursday. He shared his positions on subjects from foreign wars to AI, and made a number of eye-opening predictions for th…</t>
+          <t>イーロン・マスクは、ドナルド・トランプとの関係において政治に没頭しすぎたと認め、企業運営にもっと集中すべきだったと語った。彼は、外国の戦争やAIに関する見解を共有し、いくつかの驚くべき予測を行った。</t>
         </is>
       </c>
       <c r="K34" s="60" t="inlineStr">
@@ -3455,12 +3455,12 @@
       </c>
       <c r="I35" s="60" t="inlineStr">
         <is>
-          <t>The roaring 20s: how the current decade revolutionised cinema</t>
+          <t>roaring 20s: 現在の10年が映画を革命化した</t>
         </is>
       </c>
       <c r="J35" s="60" t="inlineStr">
         <is>
-          <t>Pre-Covid, the movie landscape was dramatically different: YouTubers weren’t dominating the box office, video game spin-offs rarely made an impact and Winnie-the-Pooh wasn’t yet the star of a slasher movie. Why such a flurry of innovation – and what will be next? Cinema has always been a medium of research and development. At any given point, the industry is searching for yet another breakthrough that can drive it into the future. Synchronised sound in the 1920s. Technicolor in the 1930s. The invention of the modern blockbuster in the 1970s. Conversely, the consensus is that, if the 2020s has a defining trend, then it is one of decline. The theatrical experience is under attack from all ang…</t>
+          <t>映画産業は常に新たな革新を求めており、2020年代の特徴は衰退であるとの見解が示されています。</t>
         </is>
       </c>
       <c r="K35" s="60" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="I36" s="60" t="inlineStr">
         <is>
-          <t>GeForce NOW Sets Sail With ‘Path of Exile: Curse of the Allflame’ Joining the Cloud</t>
+          <t>GeForce NOWが『Path of Exile: Curse of the Allflame』を追加</t>
         </is>
       </c>
       <c r="J36" s="60" t="inlineStr">
         <is>
-          <t>Lock in and load up the cloud. GFN Thursday brings fresh updates and new adventures, all ready to play without waiting for downloads. Set sail in Path of Exile: Curse of the Allflame and charge in Battlefield 6 Season 4 both launching major content for members this week. Then revisit Capcom legends like Breath of […]</t>
+          <t>GeForce NOWが新しいコンテンツを提供し、ユーザーはダウンロードを待たずにゲームを楽しむことができます。</t>
         </is>
       </c>
       <c r="K36" s="60" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="I37" s="60" t="inlineStr">
         <is>
-          <t>How AI helps scientists design the next generation of medicines</t>
+          <t>AIが科学者の次世代医薬品設計を支援</t>
         </is>
       </c>
       <c r="J37" s="60" t="inlineStr">
         <is>
-          <t>Designing and developing a new medicine is an expensive, failure-prone scientific challenge. A new drug can take many years to develop, at the cost of a significant investment. And even then, most possible candidates never reach the patient. For biologic medicines, therapies made from engineered proteins rather than synthetic chemistry (which are often used to…</t>
+          <t>新しい医薬品の設計と開発は高コストで失敗しやすい科学的課題であり、AIがそのプロセスを支援する可能性があります。</t>
         </is>
       </c>
       <c r="K37" s="60" t="inlineStr">
@@ -3668,12 +3668,12 @@
       </c>
       <c r="I38" s="60" t="inlineStr">
         <is>
-          <t>Session 2b: Can the EU's better regulation agenda deliver competitiveness?</t>
+          <t>EUの規制改善アジェンダは競争力をもたらすか</t>
         </is>
       </c>
       <c r="J38" s="60" t="inlineStr">
         <is>
-          <t>Session 2b: Can the EU's better regulation agenda deliver competitiveness? Chiara Montanaro Thu, 07/23/2026 - 11:23 Chiara Montanaro Thu, 07/23/2026 - 11:23</t>
+          <t>EUの規制改善アジェンダが競争力を向上させるかどうかについての議論が行われています。</t>
         </is>
       </c>
       <c r="K38" s="60" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="I39" s="60" t="inlineStr">
         <is>
-          <t>WHO launches seven strategies to prevent drowning</t>
+          <t>WHOが溺死防止のための7つの戦略を発表</t>
         </is>
       </c>
       <c r="J39" s="60" t="inlineStr">
         <is>
-          <t>Ahead of World Drowning Prevention Day on 25 July, the World Health Organization (WHO) is launching a new technical package to help governments and communities implement seven proven measures to reduce drowning deaths.</t>
+          <t>世界保健機関（WHO）は、7月25日の世界溺死防止デーに向けて、溺死を減少させるための新しい技術パッケージを発表しました。</t>
         </is>
       </c>
       <c r="K39" s="60" t="inlineStr">
@@ -3810,12 +3810,12 @@
       </c>
       <c r="I40" s="60" t="inlineStr">
         <is>
-          <t>NVIDIA AI Supercomputer Comes Online at Naval Postgraduate School</t>
+          <t>NVIDIAのAIスパコンが海軍大学院校で稼働開始</t>
         </is>
       </c>
       <c r="J40" s="60" t="inlineStr">
         <is>
-          <t>NVIDIA founder and CEO Jensen Huang today visited the Naval Postgraduate School in Monterey, California, to commission an NVIDIA DGX GB300 system — bringing one of the world’s most powerful AI platforms fully online for the students, researchers and faculty at the U.S. military’s flagship graduate university. “Our nation depends on our men and women […]</t>
+          <t>NVIDIAの創業者兼CEO、ジェンセン・ファンがカリフォルニア州モントレーの海軍大学院校を訪れ、NVIDIA DGX GB300システムを稼働させました。</t>
         </is>
       </c>
       <c r="K40" s="60" t="inlineStr">
@@ -3881,10 +3881,14 @@
       </c>
       <c r="I41" s="60" t="inlineStr">
         <is>
-          <t>How tech firms should address job concerns and skill development</t>
-        </is>
-      </c>
-      <c r="J41" s="60" t="inlineStr"/>
+          <t>テクノロジー企業が職業の懸念とスキル開発にどう対処すべきか</t>
+        </is>
+      </c>
+      <c r="J41" s="60" t="inlineStr">
+        <is>
+          <t>テクノロジー企業は、職業に関する懸念やスキル開発に対してどのように取り組むべきかについての考察が求められています。</t>
+        </is>
+      </c>
       <c r="K41" s="60" t="inlineStr">
         <is>
           <t>https://www.brookings.edu/articles/how-tech-firms-should-address-job-concerns-and-skill-development/</t>
@@ -3948,12 +3952,12 @@
       </c>
       <c r="I42" s="60" t="inlineStr">
         <is>
-          <t>Launching Health in ChatGPT</t>
+          <t>ChatGPTにおける健康機能の開始</t>
         </is>
       </c>
       <c r="J42" s="60" t="inlineStr">
         <is>
-          <t>Health in ChatGPT now lets eligible U.S. users securely connect medical records and Apple Health to get more personalized insights and better understand their health.</t>
+          <t>ChatGPTの健康機能により、米国の適格ユーザーは医療記録やApple Healthを安全に接続し、より個別化された健康情報を得ることが可能になりました。</t>
         </is>
       </c>
       <c r="K42" s="60" t="inlineStr">
@@ -4019,12 +4023,12 @@
       </c>
       <c r="I43" s="60" t="inlineStr">
         <is>
-          <t>How does Make America Healthy Again hold up against scientific scrutiny?</t>
+          <t>アメリカの健康政策は科学的検証に耐えうるのか</t>
         </is>
       </c>
       <c r="J43" s="60" t="inlineStr">
         <is>
-          <t>Nature, Published online: 23 July 2026; doi:10.1038/d41586-026-02024-3 Researchers share their views on the US health policy spanning topics from vaccines to nutrition.</t>
+          <t>研究者たちは、ワクチンから栄養に至るまで、アメリカの健康政策に関する見解を共有しています。</t>
         </is>
       </c>
       <c r="K43" s="60" t="inlineStr">
@@ -4090,12 +4094,12 @@
       </c>
       <c r="I44" s="60" t="inlineStr">
         <is>
-          <t>Daily briefing: Orcas smash sunfish to smithereens</t>
+          <t>日々のブリーフィング：オルカがサンフィッシュを粉砕</t>
         </is>
       </c>
       <c r="J44" s="60" t="inlineStr">
         <is>
-          <t>Nature, Published online: 23 July 2026; doi:10.1038/d41586-026-02307-9 The dolphins might be helping their young eat, or just having fun. Plus, the beauty and skill of scientific illustration and a crash course in quantum computing.</t>
+          <t>オルカがサンフィッシュを粉砕する行動は、子供たちに食べ物を与える手助けか、単に楽しんでいるのかが議論されています。</t>
         </is>
       </c>
       <c r="K44" s="60" t="inlineStr">
@@ -4161,12 +4165,12 @@
       </c>
       <c r="I45" s="60" t="inlineStr">
         <is>
-          <t>[Galaxy Unpacked July 2026] A First Look at Galaxy Z Fold8 Ultra, Galaxy Z Fold8 and Galaxy Z Flip8</t>
+          <t>[Galaxy Unpacked 2026年7月] Galaxy Z Fold8 Ultra、Galaxy Z Fold8、Galaxy Z Flip8の初公開</t>
         </is>
       </c>
       <c r="J45" s="60" t="inlineStr">
         <is>
-          <t>At Galaxy Unpacked July 2026 in London, Samsung Electronics unveiled the eighth-generation Galaxy Z series. Combining agentic AI that understands users with hardware tailored to different lifestyles, the lineup offers three distinct foldable experiences. Samsung Newsroom got an early look at the new devices during Galaxy Unpacked July 2026 — from Galaxy Z Fold8 Ultra, […]</t>
+          <t>2026年7月のGalaxy Unpackedで、サムスン電子は第8世代Galaxy Zシリーズを発表し、異なるライフスタイルに合わせた折りたたみ式デバイスを提供しました。</t>
         </is>
       </c>
       <c r="K45" s="60" t="inlineStr">
@@ -4232,12 +4236,12 @@
       </c>
       <c r="I46" s="60" t="inlineStr">
         <is>
-          <t>[Galaxy Unpacked July 2026] A First Look at Galaxy Watch Ultra2 and Galaxy Watch9</t>
+          <t>[Galaxy Unpacked 2026年7月] Galaxy Watch Ultra2とGalaxy Watch9の初公開</t>
         </is>
       </c>
       <c r="J46" s="60" t="inlineStr">
         <is>
-          <t>At Galaxy Unpacked July 2026 in London, Samsung Electronics unveiled Galaxy Watch Ultra2 and Galaxy Watch9, expanding the digital health experience on the wrist. From the moment users wake up to the time they finish a workout and begin recovery, a smartwatch stays in contact with the body throughout the day. Samsung Newsroom got an […]</t>
+          <t>2026年7月のGalaxy Unpackedで、サムスン電子はGalaxy Watch Ultra2とGalaxy Watch9を発表し、デジタル健康体験を拡大しました。</t>
         </is>
       </c>
       <c r="K46" s="60" t="inlineStr">
@@ -4303,12 +4307,12 @@
       </c>
       <c r="I47" s="60" t="inlineStr">
         <is>
-          <t>Samsung Galaxy Z Fold8 Ultra, Fold8 and Flip8: Foldables, Perfected for Every Way of Living</t>
+          <t>サムスンGalaxy Z Fold8 Ultra、Fold8、Flip8：生活様式に合わせた折りたたみ式デバイス</t>
         </is>
       </c>
       <c r="J47" s="60" t="inlineStr">
         <is>
-          <t>Samsung Electronics today unveiled the new Galaxy Z series, its most complete lineup yet, designed to expand foldables to a wider audience. The lineup introduces Galaxy Z Fold8, a fresh and exciting form factor that provides a new kind of foldable experience built around the way people explore, discover and immerse themselves in their favorite […]</t>
+          <t>サムスン電子は新しいGalaxy Zシリーズを発表し、折りたたみ式デバイスをより広いオーディエンスに拡大することを目指しています。</t>
         </is>
       </c>
       <c r="K47" s="60" t="inlineStr">
@@ -4374,12 +4378,12 @@
       </c>
       <c r="I48" s="60" t="inlineStr">
         <is>
-          <t>Samsung Galaxy Watch Ultra2 and Watch9: Your Health Companion on the Wrist</t>
+          <t>サムスンGalaxy Watch Ultra2とWatch9：健康のための腕時計</t>
         </is>
       </c>
       <c r="J48" s="60" t="inlineStr">
         <is>
-          <t>Samsung Electronics today announced the all-new Galaxy Watch Ultra2 and Galaxy Watch9, delivering a new era of effortless health, where users can unlock in-depth, meaningful health insights simply by wearing these devices. To support 24/7 wearability, Samsung delivers powerful innovations that maximize comfort while advancing performance with Galaxy Watch’s largest battery and brightest display ever, […]</t>
+          <t>サムスン電子は新しいGalaxy Watch Ultra2とGalaxy Watch9を発表し、ユーザーがこれらのデバイスを着用することで深い健康洞察を得られる新時代を迎えました。</t>
         </is>
       </c>
       <c r="K48" s="60" t="inlineStr">
@@ -4445,12 +4449,12 @@
       </c>
       <c r="I49" s="60" t="inlineStr">
         <is>
-          <t>Samsung Brings Galaxy Ecosystem Into Everyday Eyewear</t>
+          <t>サムスン、日常の眼鏡にGalaxyエコシステムを導入</t>
         </is>
       </c>
       <c r="J49" s="60" t="inlineStr">
         <is>
-          <t>Samsung Electronics today introduced its intelligent eyewear at Galaxy Unpacked in London. Building on the concepts announced at the latest Google I/O, the new designs were developed with global eyewear brands, Gentle Monster and Warby Parker. The intelligent eyewear shows how the Galaxy ecosystem can move beyond the mobile phone and into eyewear that supports […]</t>
+          <t>サムスン電子はロンドンで開催されたGalaxy Unpackedで、インテリジェントな眼鏡を発表しました。これにより、Galaxyエコシステムがモバイルフォンを超えて眼鏡に進出することを示しています。</t>
         </is>
       </c>
       <c r="K49" s="60" t="inlineStr">
@@ -4516,12 +4520,12 @@
       </c>
       <c r="I50" s="60" t="inlineStr">
         <is>
-          <t>Guidance: Women in Research Charter</t>
+          <t>女性研究者のためのチャーターに関するガイダンス</t>
         </is>
       </c>
       <c r="J50" s="60" t="inlineStr">
         <is>
-          <t>A voluntary commitment to improve outcomes for women across the UK research system, with actions for research funders and research performing organisations.</t>
+          <t>英国の研究システムにおける女性の成果を向上させるための自主的な取り組みで、研究資金提供者や研究機関に対する行動が含まれています。</t>
         </is>
       </c>
       <c r="K50" s="60" t="inlineStr">
@@ -4587,12 +4591,12 @@
       </c>
       <c r="I51" s="60" t="inlineStr">
         <is>
-          <t>Secretary of Energy Chris Wright Announces First Genesis Mission Projects Selected to Accelerate AI-Driven Scientific Discovery</t>
+          <t>エネルギー長官クリス・ライトがAI駆動の科学発見を加速するプロジェクトを発表</t>
         </is>
       </c>
       <c r="J51" s="60" t="inlineStr">
         <is>
-          <t>Nearly 300 projects selected from historic RFA response spanning all 50 states to accelerate breakthroughs in energy, discovery science, and national security.</t>
+          <t>全米50州からの歴史的なRFA応答から選ばれた約300のプロジェクトが、エネルギー、発見科学、国家安全保障におけるブレークスルーを加速することを目的としています。</t>
         </is>
       </c>
       <c r="K51" s="60" t="inlineStr">
@@ -4658,12 +4662,12 @@
       </c>
       <c r="I52" s="60" t="inlineStr">
         <is>
-          <t>Remarks at the Global Nobel Laureates Assembly on Artificial Intelligence and Nuclear War in Borgo Laudato Si’, Vatican</t>
+          <t>人工知能と核戦争に関するグローバルノーベル賞受賞者会議での発言</t>
         </is>
       </c>
       <c r="J52" s="60" t="inlineStr">
         <is>
-          <t>CSET Senior Fellow Emelia Probasco shares her experience and the remarks she gave at the Global Nobel Laureates Assembly on Artificial Intelligence and Nuclear War, which took place at Borgo Laudato Si’, Vatican. The post Remarks at the Global Nobel Laureates Assembly on Artificial Intelligence and Nuclear War in Borgo Laudato Si’, Vatican appeared first on Center for Security and Emerging Technology .</t>
+          <t>CSETのシニアフェロー、エメリア・プロバスコがバチカンで開催された人工知能と核戦争に関するグローバルノーベル賞受賞者会議での経験と発言を共有しました。</t>
         </is>
       </c>
       <c r="K52" s="60" t="inlineStr">
@@ -4729,12 +4733,12 @@
       </c>
       <c r="I53" s="60" t="inlineStr">
         <is>
-          <t>Guidance: Consult: register your interest</t>
+          <t>AIツール「Consult」の利用登録案内</t>
         </is>
       </c>
       <c r="J53" s="60" t="inlineStr">
         <is>
-          <t>Register your interest in using Consult, the AI tool that helps government teams analyse public consultation responses. Join the waitlist for access.</t>
+          <t>政府チームが公的相談の回答を分析するためのAIツール「Consult」の利用に関心がある方は、待機リストに登録してください。</t>
         </is>
       </c>
       <c r="K53" s="60" t="inlineStr">
@@ -4800,12 +4804,12 @@
       </c>
       <c r="I54" s="60" t="inlineStr">
         <is>
-          <t>Statement from NSF Chief of Staff Brian Stone, performing the duties of the NSF director, on advancing the Administration's AI priorities through the Genesis Mission</t>
+          <t>NSF長官代行ブライアン・ストーンのAI優先事項推進に関する声明</t>
         </is>
       </c>
       <c r="J54" s="60" t="inlineStr">
         <is>
-          <t>The U.S. National Science Foundation is proud to join the White House Office of Science and Technology Policy, the U.S. Department of Energy and other federal partners in advancing the administration's artificial intelligence priorities through the…</t>
+          <t>米国科学財団（NSF）は、ホワイトハウス科学技術政策局やエネルギー省などと連携し、行政の人工知能（AI）優先事項を推進することを誇りに思っています。</t>
         </is>
       </c>
       <c r="K54" s="60" t="inlineStr">
@@ -4871,12 +4875,12 @@
       </c>
       <c r="I55" s="60" t="inlineStr">
         <is>
-          <t>New NSF initiative aims to unlock dataset value for AI-enabled scientific discovery</t>
+          <t>新しいNSFイニシアティブがAIを活用した科学的発見のためのデータセットの価値を解放</t>
         </is>
       </c>
       <c r="J55" s="60" t="inlineStr">
         <is>
-          <t>The U.S. National Science Foundation announced the NSF Unlocking Dataset Value for AI-Enabled Scientific Discovery program, a new investment to advance scientific community datasets and enable discovery and innovation using artificial intelligence…</t>
+          <t>米国国立科学財団は、AIを活用した科学的発見を促進するための新しい投資を発表しました。</t>
         </is>
       </c>
       <c r="K55" s="60" t="inlineStr">
@@ -4942,12 +4946,12 @@
       </c>
       <c r="I56" s="60" t="inlineStr">
         <is>
-          <t>NSF announces $83M investment in integrated data systems and services to advance AI-driven science and strengthen U.S. research infrastructure</t>
+          <t>NSFがAI駆動の科学を進展させるために8300万ドルの投資を発表</t>
         </is>
       </c>
       <c r="J56" s="60" t="inlineStr">
         <is>
-          <t>The U.S. National Science Foundation today announced $83 million in awards through the Integrated Data Systems and Services (IDSS) program. The awards will expand access to data infrastructure resources that researchers can use alongside computing…</t>
+          <t>米国国立科学財団は、統合データシステムおよびサービスプログラムを通じて8300万ドルの助成金を発表し、研究者がデータインフラを活用できるようにします。</t>
         </is>
       </c>
       <c r="K56" s="60" t="inlineStr">
@@ -5013,12 +5017,12 @@
       </c>
       <c r="I57" s="60" t="inlineStr">
         <is>
-          <t>NVIDIA Open Sources First GPU-Accelerated Medical Physics Simulation Framework</t>
+          <t>NVIDIAが初のGPU加速医療物理シミュレーションフレームワークをオープンソース化</t>
         </is>
       </c>
       <c r="J57" s="60" t="inlineStr">
         <is>
-          <t>Before a healthcare robot can be useful in the real world, it has to learn how the physical world pushes back. Anatomy varies. Instruments bend, press, slip and interact with tissue. Imaging can be noisy or incomplete. And the rare, edge scenarios developers most need to understand don’t appear on schedule. That creates one of […]</t>
+          <t>NVIDIAは、医療ロボットが現実世界で有用になるために必要な物理的な反発を学ぶためのシミュレーションフレームワークを公開しました。</t>
         </is>
       </c>
       <c r="K57" s="60" t="inlineStr">
@@ -5084,12 +5088,12 @@
       </c>
       <c r="I58" s="60" t="inlineStr">
         <is>
-          <t>Building AI infrastructure with the Effingham County community</t>
+          <t>エフィンガム郡コミュニティとのAIインフラ構築</t>
         </is>
       </c>
       <c r="J58" s="60" t="inlineStr">
         <is>
-          <t>OpenAI announces Project Camellia in Effingham County, Georgia, with commitments to responsible energy, community investment, jobs, and access to Codex.</t>
+          <t>OpenAIはジョージア州エフィンガム郡でプロジェクト・カメリアを発表し、責任あるエネルギー、地域投資、雇用、Codexへのアクセスを約束しました。</t>
         </is>
       </c>
       <c r="K58" s="60" t="inlineStr">
@@ -5155,12 +5159,12 @@
       </c>
       <c r="I59" s="60" t="inlineStr">
         <is>
-          <t>How news organizations are using AI to advance their vital missions</t>
+          <t>ニュース組織がAIを活用して重要な使命を推進</t>
         </is>
       </c>
       <c r="J59" s="60" t="inlineStr">
         <is>
-          <t>News organizations are using AI to strengthen reporting, grow audiences, and improve business operations, with OpenAI tools supporting journalists and publishers worldwide.</t>
+          <t>ニュース組織はAIを利用して報道を強化し、オーディエンスを拡大し、ビジネス運営を改善しています。</t>
         </is>
       </c>
       <c r="K59" s="60" t="inlineStr">
@@ -5226,12 +5230,12 @@
       </c>
       <c r="I60" s="60" t="inlineStr">
         <is>
-          <t>3 Google updates from Galaxy Unpacked 2026</t>
+          <t>Galaxy Unpacked 2026からの3つのGoogleのアップデート</t>
         </is>
       </c>
       <c r="J60" s="60" t="inlineStr">
         <is>
-          <t>Gentle Monster glasses, Warby Parker glasses, a prompt asking for the history behind a pictured building, and a prompt asking to book a table at a pictured restaurant</t>
+          <t>Gentle Monsterの眼鏡やWarby Parkerの眼鏡など、Galaxy Unpacked 2026での新しいプロンプトが紹介されました。</t>
         </is>
       </c>
       <c r="K60" s="60" t="inlineStr">
@@ -5297,12 +5301,12 @@
       </c>
       <c r="I61" s="60" t="inlineStr">
         <is>
-          <t>The Download: NASA’s new space telescope and OpenAI’s autonomous hacker</t>
+          <t>ダウンロード：NASAの新しい宇宙望遠鏡とOpenAIの自律ハッカー</t>
         </is>
       </c>
       <c r="J61" s="60" t="inlineStr">
         <is>
-          <t>This is today’s edition of The Download, our weekday newsletter that provides a daily dose of what’s going on in the world of technology. Shape-shifting mirrors on NASA’s new space telescope could unveil Jupiters like our own When NASA’s Nancy Grace Roman Space Telescope launches, as early as the end of next month, it will…</t>
+          <t>本日は、NASAの新しい宇宙望遠鏡に関する情報を含む技術ニュースレターをお届けします。</t>
         </is>
       </c>
       <c r="K61" s="60" t="inlineStr">
@@ -5368,12 +5372,12 @@
       </c>
       <c r="I62" s="60" t="inlineStr">
         <is>
-          <t>NIST Announces Funding Opportunity for 14 MEP Centers to Advance Small and Medium-Sized U.S. Manufacturers</t>
+          <t>NISTが中小企業向けの資金提供機会を発表</t>
         </is>
       </c>
       <c r="J62" s="60" t="inlineStr">
         <is>
-          <t>NIST MEP will host an informational webinar on Tuesday, July 28, 2026, at 1 p.m. ET to provide general information about this opportunity and guidance on preparing applications.</t>
+          <t>NIST MEPは、2026年7月28日火曜日に中小企業向けの資金提供機会に関する情報ウェビナーを開催し、申請準備に関するガイダンスを提供します。</t>
         </is>
       </c>
       <c r="K62" s="60" t="inlineStr">
@@ -5439,12 +5443,12 @@
       </c>
       <c r="I63" s="60" t="inlineStr">
         <is>
-          <t>Advancing the next era of national science</t>
+          <t>次世代の国家科学を推進する</t>
         </is>
       </c>
       <c r="J63" s="60" t="inlineStr">
         <is>
-          <t>OpenAI outlines its commitment to advancing American science working with the U.S. Department of Energy and national labs to use frontier AI to accelerate discovery.</t>
+          <t>OpenAIは、米国エネルギー省および国立研究所と連携し、最前線のAIを活用して科学の発見を加速する取り組みを発表しました。</t>
         </is>
       </c>
       <c r="K63" s="60" t="inlineStr">
@@ -5510,12 +5514,12 @@
       </c>
       <c r="I64" s="60" t="inlineStr">
         <is>
-          <t>Shape-shifting mirrors on NASA’s new space telescope could unveil Jupiters like our own</t>
+          <t>NASAの新しい宇宙望遠鏡が変形ミラーを搭載、私たちのような木星を発見する可能性</t>
         </is>
       </c>
       <c r="J64" s="60" t="inlineStr">
         <is>
-          <t>When NASA’s Nancy Grace Roman Space Telescope launches, as early as the end of next month, it will attempt one of astronomy’s most precise disappearing acts to date. The telescope will carry the first space-bound “active” coronagraph, an instrument that effectively erases most of the light from a star during photography. It will allow astronomers…</t>
+          <t>NASAのナンシー・グレース・ローマン宇宙望遠鏡が来月末にも打ち上げられる予定で、星の光を効果的に消す「アクティブコロナグラフ」を搭載し、天文学の新たな発見を目指します。</t>
         </is>
       </c>
       <c r="K64" s="60" t="inlineStr">
@@ -5581,12 +5585,12 @@
       </c>
       <c r="I65" s="60" t="inlineStr">
         <is>
-          <t>Introducing OpenAI Presence</t>
+          <t>OpenAI Presenceの導入</t>
         </is>
       </c>
       <c r="J65" s="60" t="inlineStr">
         <is>
-          <t>Introducing OpenAI Presence, a proven enterprise AI agent platform that helps organizations deploy trusted voice and chat agents for customer and internal workflows.</t>
+          <t>OpenAI Presenceが、企業が信頼できる音声およびチャットエージェントを展開するためのプラットフォームを提供します。</t>
         </is>
       </c>
       <c r="K65" s="60" t="inlineStr">
@@ -5652,12 +5656,12 @@
       </c>
       <c r="I66" s="60" t="inlineStr">
         <is>
-          <t>NTT DATA Group cuts incident analysis to 30 minutes with Codex</t>
+          <t>NTT DATAグループ、Codexを活用してインシデント分析を30分に短縮</t>
         </is>
       </c>
       <c r="J66" s="60" t="inlineStr">
         <is>
-          <t>NTT DATA Group uses ChatGPT Enterprise and Codex to help 9,000 employees automate work, cut incident analysis to 30 minutes, and scale secure AI adoption.</t>
+          <t>NTT DATAグループがChatGPT EnterpriseとCodexを活用し、9,000人の従業員が業務を自動化し、インシデント分析を30分に短縮することに成功しました。</t>
         </is>
       </c>
       <c r="K66" s="60" t="inlineStr">
@@ -5723,12 +5727,12 @@
       </c>
       <c r="I67" s="60" t="inlineStr">
         <is>
-          <t>Subnuclear genome compartmentalization controls bivalent chromatin activity</t>
+          <t>サブ核ゲノム区画化が二価クロマチン活性を制御</t>
         </is>
       </c>
       <c r="J67" s="60" t="inlineStr">
         <is>
-          <t>Nature, Published online: 22 July 2026; doi:10.1038/s41586-026-10832-w Knowledge of the spatial location of a gene is necessary to understand its epigenomic regulation.</t>
+          <t>遺伝子の空間的な位置を理解することが、エピゲノム調節を理解するために必要であることが示されています。</t>
         </is>
       </c>
       <c r="K67" s="60" t="inlineStr">
@@ -5794,12 +5798,12 @@
       </c>
       <c r="I68" s="60" t="inlineStr">
         <is>
-          <t>What counts as a moon? Huge ‘exosatellite’ sparks debate</t>
+          <t>巨大な‘エクソ衛星’が月の定義を巡る議論を引き起こす</t>
         </is>
       </c>
       <c r="J68" s="60" t="inlineStr">
         <is>
-          <t>Nature, Published online: 22 July 2026; doi:10.1038/d41586-026-02299-6 Discovery of a distant Jupiter-mass object could pave the way for detection of exomoons — plus, a rare transmissible cancer found in catfish.</t>
+          <t>遠方の木星質量の天体の発見がエクソ月の検出への道を開く可能性があり、また、ナマズに見られる珍しい伝染性癌についても言及されています。</t>
         </is>
       </c>
       <c r="K68" s="60" t="inlineStr">
@@ -5865,12 +5869,12 @@
       </c>
       <c r="I69" s="60" t="inlineStr">
         <is>
-          <t>How do quantum computers work?</t>
+          <t>量子コンピュータの仕組み</t>
         </is>
       </c>
       <c r="J69" s="60" t="inlineStr">
         <is>
-          <t>Nature, Published online: 22 July 2026; doi:10.1038/d41586-026-02219-8 Recent breakthroughs suggest usable devices could be here in a decade.</t>
+          <t>最近のブレークスルーにより、実用的な量子コンピュータが10年以内に登場する可能性が示唆されています。</t>
         </is>
       </c>
       <c r="K69" s="60" t="inlineStr">
@@ -5936,12 +5940,12 @@
       </c>
       <c r="I70" s="60" t="inlineStr">
         <is>
-          <t>CRISPR–Cas regulates expression of embedded anti-phage defence systems</t>
+          <t>CRISPR–Casが抗ファージ防御システムの発現を調節</t>
         </is>
       </c>
       <c r="J70" s="60" t="inlineStr">
         <is>
-          <t>Nature, Published online: 22 July 2026; doi:10.1038/s41586-026-10833-9 CRISPR–Cas systems transcriptionally tune diverse innate defences using CRISPR RNA-like guides to balance antiviral protection with fitness, and hyperactivate these defences when compromised, establishing a layered bacterial ‘immunity guard’ network.</t>
+          <t>CRISPR–Casシステムが多様な先天的防御を調整し、ウイルスからの保護と適応度のバランスを取る仕組みが解明されました。</t>
         </is>
       </c>
       <c r="K70" s="60" t="inlineStr">
@@ -6007,12 +6011,12 @@
       </c>
       <c r="I71" s="60" t="inlineStr">
         <is>
-          <t>Built in Fort Worth: Wistron Opens Advanced Manufacturing Plant to Produce NVIDIA AI Systems</t>
+          <t>フォートワースにおけるWistronの先進製造工場開設</t>
         </is>
       </c>
       <c r="J71" s="60" t="inlineStr">
         <is>
-          <t>The AI era runs on AI infrastructure. Many of these advanced systems are built and tested in Texas. Wistron opened its first U.S. manufacturing facility today in Fort Worth — a 324,000-square-foot greenfield plant producing superchips at the heart of some of the world’s most capable AI systems. In front of an audience of Wistron […]</t>
+          <t>Wistronがテキサス州フォートワースにAIシステム用の先進製造工場を開設し、324,000平方フィートの施設でスーパーチップを生産します。</t>
         </is>
       </c>
       <c r="K71" s="60" t="inlineStr">
@@ -6078,12 +6082,12 @@
       </c>
       <c r="I72" s="60" t="inlineStr">
         <is>
-          <t>FIA and Clean Air Task Force Publish Principles on Codes and Standards</t>
+          <t>FIAとクリーンエアタスクフォースが融合エネルギーの基準を発表</t>
         </is>
       </c>
       <c r="J72" s="60" t="inlineStr">
         <is>
-          <t>In partnership with the Clean Air Task Force, the Fusion Industry Association published a one-pager outlining its principles for fusion codes and standards. As fusion moves towards deployment, it is critical that codes and standards ensure safe deployment while enabling innovation. The post FIA and Clean Air Task Force Publish Principles on Codes and Standards appeared first on Fusion Industry Association .</t>
+          <t>融合産業協会がクリーンエアタスクフォースと共同で、融合エネルギーの安全な展開を確保しつつ革新を促進するための原則をまとめた文書を発表しました。</t>
         </is>
       </c>
       <c r="K72" s="60" t="inlineStr">
@@ -6149,12 +6153,12 @@
       </c>
       <c r="I73" s="60" t="inlineStr">
         <is>
-          <t>Introducing the ChatGPT for small business program</t>
+          <t>小規模ビジネス向けChatGPTプログラムの導入</t>
         </is>
       </c>
       <c r="J73" s="60" t="inlineStr">
         <is>
-          <t>OpenAI launches the ChatGPT for Small Businesses program, helping entrepreneurs build AI skills, automate work, and grow with ChatGPT Work.</t>
+          <t>OpenAIが小規模ビジネス向けのChatGPTプログラムを開始し、起業家がAIスキルを習得し、業務を自動化し、成長を促進する手助けを行います。</t>
         </is>
       </c>
       <c r="K73" s="60" t="inlineStr">
@@ -6220,12 +6224,12 @@
       </c>
       <c r="I74" s="60" t="inlineStr">
         <is>
-          <t>NVIDIA Vera Rubin Driving Performance Per Watt, Lowest Token Cost for Partners Worldwide</t>
+          <t>NVIDIA Vera Rubin、パートナー向けに最適な性能とコストを提供</t>
         </is>
       </c>
       <c r="J74" s="60" t="inlineStr">
         <is>
-          <t>NVIDIA Vera Rubin is here, and it’s going gigascale. Vera Rubin NVL72 production is ramping up with racks running at partners CoreWeave, Google Cloud, Microsoft Azure and Oracle Cloud Infrastructure. Spanning 350+ factory sites in 30 countries, Vera Rubin has the largest, most mature rack-scale supply chain ever assembled to meet customer compute demand. The […]</t>
+          <t>NVIDIA Vera Rubinが生産を拡大し、CoreWeave、Google Cloud、Microsoft Azure、Oracle Cloud Infrastructureなどのパートナーと共に、350以上の工場サイトで顧客の計算需要に応えるための供給チェーンを構築しています。</t>
         </is>
       </c>
       <c r="K74" s="60" t="inlineStr">
@@ -6291,12 +6295,12 @@
       </c>
       <c r="I75" s="60" t="inlineStr">
         <is>
-          <t>Transparency data: DSIT: workforce management information, June 2026</t>
+          <t>透明性データ：DSIT：労働力管理情報、2026年6月</t>
         </is>
       </c>
       <c r="J75" s="60" t="inlineStr">
         <is>
-          <t>Reports on departmental staff numbers and costs.</t>
+          <t>部門のスタッフ数とコストに関する報告が行われています。</t>
         </is>
       </c>
       <c r="K75" s="60" t="inlineStr">
@@ -6362,12 +6366,12 @@
       </c>
       <c r="I76" s="60" t="inlineStr">
         <is>
-          <t>Guidance: TechFirst Local</t>
+          <t>ガイダンス：TechFirstローカル</t>
         </is>
       </c>
       <c r="J76" s="60" t="inlineStr">
         <is>
-          <t>Details of the TechFirst local grant funding programme to boost digital skills and support people into tech jobs.</t>
+          <t>TechFirstローカル助成金プログラムの詳細が公開され、デジタルスキルの向上とテクノロジー職への支援が行われます。</t>
         </is>
       </c>
       <c r="K76" s="60" t="inlineStr">
@@ -6433,12 +6437,12 @@
       </c>
       <c r="I77" s="60" t="inlineStr">
         <is>
-          <t>TechFirst PhD Support</t>
+          <t>TechFirst博士課程支援</t>
         </is>
       </c>
       <c r="J77" s="60" t="inlineStr">
         <is>
-          <t>Part of TechFirst, the government’s flagship skills programme opening pathways into the UK’s fast-growing tech sector.</t>
+          <t>TechFirstの一環として、英国の急成長するテクノロジーセクターへの道を開く政府のスキルプログラムです。</t>
         </is>
       </c>
       <c r="K77" s="60" t="inlineStr">
@@ -6509,7 +6513,7 @@
       </c>
       <c r="J78" s="60" t="inlineStr">
         <is>
-          <t>TechFirst is the government’s flagship tech skills programme opening pathways into the UK’s fast-growing tech sector, providing opportunities across all parts of the UK.</t>
+          <t>TechFirstは、英国の急成長するテクノロジーセクターへの道を開く政府の主力技術スキルプログラムであり、英国全土での機会を提供します。</t>
         </is>
       </c>
       <c r="K78" s="60" t="inlineStr">
@@ -6575,12 +6579,12 @@
       </c>
       <c r="I79" s="60" t="inlineStr">
         <is>
-          <t>Policy paper: Fixed Telecoms Modernisation Charter</t>
+          <t>政策文書：固定通信の近代化憲章</t>
         </is>
       </c>
       <c r="J79" s="60" t="inlineStr">
         <is>
-          <t>This document sets out the steps that telecoms providers should follow when carrying out any current and future fixed telecoms modernisations.</t>
+          <t>この文書は、通信事業者が現在および将来の固定通信の近代化を実施する際に従うべき手順を示しています。</t>
         </is>
       </c>
       <c r="K79" s="60" t="inlineStr">
@@ -6646,12 +6650,12 @@
       </c>
       <c r="I80" s="60" t="inlineStr">
         <is>
-          <t>Built for Vera Rubin, NVIDIA Spectrum-6 Arrives in Gigascale AI Factories</t>
+          <t>Vera Rubin向けに設計されたNVIDIA Spectrum-6、ギガスケールAI工場に登場</t>
         </is>
       </c>
       <c r="J80" s="60" t="inlineStr">
         <is>
-          <t>AI has entered the gigascale era. The world’s most advanced AI factories are bringing together hundreds of thousands of GPUs and CPUs to train frontier models, power agentic AI and generate intelligence at unprecedented scale. At this level, networking becomes a critical computing power multiplier in driving token generation. Marking a networking milestone, NVIDIA Spectrum-6 […]</t>
+          <t>AIがギガスケールの時代に突入し、最先端のAI工場が数十万のGPUとCPUを統合して新たな知能を生成しています。このレベルでは、ネットワーキングが計算能力を高める重要な要素となります。</t>
         </is>
       </c>
       <c r="K80" s="60" t="inlineStr">
@@ -6717,12 +6721,12 @@
       </c>
       <c r="I81" s="60" t="inlineStr">
         <is>
-          <t>FIA Outlines EU Financing Pathway for Fusion</t>
+          <t>FIA、EUの核融合エネルギー資金調達の道筋を示す</t>
         </is>
       </c>
       <c r="J81" s="60" t="inlineStr">
         <is>
-          <t>On 21 July, the Fusion Industry Association published a paper outlining a practical EU financing roadmap for commercial fusion energy. As fusion projects move from research to demonstration, first-of-a-kind plants and commercial deployment, they require different funding and financing tools at each stage of development. Europe's financing framework must evolve from a collection of individual programmes into a coherent funding architecture that supports the entire fusion commercialisation journey. The post FIA Outlines EU Financing Pathway for Fusion appeared first on Fusion Industry Association .</t>
+          <t>核融合産業協会は、商業核融合エネルギーのための実用的なEU資金調達ロードマップを発表しました。研究から実証、商業展開に向けた各段階で必要な資金調達手法の進化が求められています。</t>
         </is>
       </c>
       <c r="K81" s="60" t="inlineStr">
@@ -6788,12 +6792,12 @@
       </c>
       <c r="I82" s="60" t="inlineStr">
         <is>
-          <t>Why Do AI Systems Misbehave?</t>
+          <t>AIシステムはなぜ誤動作するのか？</t>
         </is>
       </c>
       <c r="J82" s="60" t="inlineStr">
         <is>
-          <t>AI systems are increasingly impressive, which makes their failures all the more baffling. This blog dives into the causes of AI misbehavior. The post Why Do AI Systems Misbehave? appeared first on Center for Security and Emerging Technology .</t>
+          <t>AIシステムの進化が進む中、その失敗の原因について考察するブログが公開されました。AIの誤動作の原因を探る内容です。</t>
         </is>
       </c>
       <c r="K82" s="60" t="inlineStr">
@@ -6859,12 +6863,12 @@
       </c>
       <c r="I83" s="60" t="inlineStr">
         <is>
-          <t>NVIDIA and Partners Build in America, for America</t>
+          <t>NVIDIAとパートナー、アメリカのために製造を推進</t>
         </is>
       </c>
       <c r="J83" s="60" t="inlineStr">
         <is>
-          <t>NVIDIA and its partners are investing in American manufacturing, supply chains, energy grids and skilled workforces so the U.S. can produce the infrastructure needed for better healthcare, breakthrough scientific discovery, stronger industrial productivity and global technology leadership.</t>
+          <t>NVIDIAとそのパートナーは、アメリカの製造業、供給網、エネルギー網、熟練労働力に投資し、より良い医療、画期的な科学的発見、産業生産性の向上、グローバルな技術リーダーシップを実現するためのインフラを構築しています。</t>
         </is>
       </c>
       <c r="K83" s="60" t="inlineStr">
@@ -6930,12 +6934,12 @@
       </c>
       <c r="I84" s="60" t="inlineStr">
         <is>
-          <t>Intel and Fortinet Collaborate to Advance Cybersecurity Innovation and Strengthen Global Supply Chain Resilience</t>
+          <t>インテルとフォーティネット、サイバーセキュリティ革新を推進し供給網の強靭性を強化</t>
         </is>
       </c>
       <c r="J84" s="60" t="inlineStr">
         <is>
-          <t>SANTA CLARA AND SUNNYVALE, Calif. – July 21, 2026 – Intel Corporation (NASDAQ: INTC) and Fortinet (NASDAQ: FTNT), today announced a strategic collaboration to develop Fortinet Security Processor 6 (SP6). Expanding a long-standing relationship between the two companies, this collaboration combines Fortinet’s proprietary, purpose-built security processor expertise with Intel’s advanced design, packaging, and manufacturing capabilities … The post Intel and Fortinet Collaborate to Advance Cybersecurity Innovation and Strengthen Global Supply Chain Resilience appeared first on Newsroom .</t>
+          <t>インテルとフォーティネットは、Fortinet Security Processor 6 (SP6)の開発に向けた戦略的な協力を発表しました。このコラボレーションは、両社の長年の関係を基に、セキュリティプロセッサの専門知識とインテルの先進的な設計・製造能力を組み合わせています。</t>
         </is>
       </c>
       <c r="K84" s="60" t="inlineStr">
@@ -7001,12 +7005,12 @@
       </c>
       <c r="I85" s="60" t="inlineStr">
         <is>
-          <t>The Download: Chinese AI divides the White House, and a record copyright payout</t>
+          <t>ダウンロード：中国のAIがホワイトハウスを分断、記録的な著作権支払い</t>
         </is>
       </c>
       <c r="J85" s="60" t="inlineStr">
         <is>
-          <t>This is today’s edition of The Download, our weekday newsletter that provides a daily dose of what’s going on in the world of technology. China’s AI models have Trump’s AI world at war with itself Last weekend, several current and former advisers to President Donald Trump on AI publicly lobbed insults at the country’s leading…</t>
+          <t>本日のテクノロジーに関するニュースレターでは、中国のAIモデルがトランプ政権内での対立を引き起こしていることが報じられている。</t>
         </is>
       </c>
       <c r="K85" s="60" t="inlineStr">
@@ -7072,12 +7076,12 @@
       </c>
       <c r="I86" s="60" t="inlineStr">
         <is>
-          <t>Advancing next-gen AI with materials science innovation</t>
+          <t>材料科学の革新で次世代AIを推進</t>
         </is>
       </c>
       <c r="J86" s="60" t="inlineStr">
         <is>
-          <t>The conversation about AI often centers on algorithms, computing power, or huge investments in new semiconductor fabrication plants and hyperscale data centers. But beneath each of these advances is another layer of innovation that makes them possible: advanced materials. Every new generation of AI technology demands more processing power, more memory, greater energy efficiency, and…</t>
+          <t>AIに関する議論はアルゴリズムや計算能力に集中しがちだが、これらの進展を可能にするもう一つの革新の層が存在する。それは先進材料であり、次世代のAI技術はより多くの処理能力やメモリ、エネルギー効率を求めている。</t>
         </is>
       </c>
       <c r="K86" s="60" t="inlineStr">
@@ -7143,12 +7147,12 @@
       </c>
       <c r="I87" s="60" t="inlineStr">
         <is>
-          <t>UN report: Global hunger levels ease for third consecutive year as regional disparities persist</t>
+          <t>国連報告：世界の飢餓レベルが3年連続で改善も地域格差が残る</t>
         </is>
       </c>
       <c r="J87" s="60" t="inlineStr">
         <is>
-          <t>Global hunger declined for a third consecutive year in 2025, demonstrating that progress is possible. However, the improvements remain fragile, unevenly distributed and insufficient to achieve the Sustainable Development Goals by 2030, according to The State of Food Security and Nutrition in the World 2026 (SOFI 2026) report, released on Tuesday by five United Nations specialized agencies.</t>
+          <t>2025年に世界の飢餓が3年連続で減少したことが報告されているが、改善は脆弱で不均一であり、2030年までに持続可能な開発目標を達成するには不十分であると指摘されている。</t>
         </is>
       </c>
       <c r="K87" s="60" t="inlineStr">
@@ -7214,12 +7218,12 @@
       </c>
       <c r="I88" s="60" t="inlineStr">
         <is>
-          <t>OpenAI and Hugging Face partner to address security incident during model evaluation</t>
+          <t>OpenAIとHugging Face、モデル評価中のセキュリティインシデントに対処するため提携</t>
         </is>
       </c>
       <c r="J88" s="60" t="inlineStr">
         <is>
-          <t>OpenAI and Hugging Face share early findings from a security incident during AI model evaluation, highlighting advanced cyber capabilities and lessons for defenders.</t>
+          <t>OpenAIとHugging Faceは、AIモデル評価中に発生したセキュリティインシデントに関する初期の調査結果を共有し、高度なサイバー能力と防御者への教訓を強調している。</t>
         </is>
       </c>
       <c r="K88" s="60" t="inlineStr">
@@ -7285,12 +7289,12 @@
       </c>
       <c r="I89" s="60" t="inlineStr">
         <is>
-          <t>SEM-Guided Low-kV FIB Finishing for Leading-Edge Semiconductor Failure Analysis</t>
+          <t>先端半導体故障解析のためのSEMガイド低電圧FIB仕上げ</t>
         </is>
       </c>
       <c r="J89" s="60" t="inlineStr">
         <is>
-          <t>Discover how the ZEISS Crossbeam 750 FIBSEM sets a new benchmark for precise TEM lamella prep, tomography, and advanced nanofabrication. This delivers better resolution, better SNR, larger usable FOV, and shorter acquisition times. Learn how uninterrupted FIB milling will reduce damage and rework, accelerate time to TEM, and increase first pass success—so your FA, yield, and materials teams make faster, confident data driven decisions. Register now for this free webinar! Join us to discover how the new ZEISS Crossbeam 750 with its see while you mill capability delivers precision and clarity—every time—for demanding FIB-SEM workflows. Designed for extremely challenging TEM lamella preparatio…</t>
+          <t>ZEISS Crossbeam 750 FIBSEMが、TEMラメラ準備、トモグラフィー、先進的なナノファブリケーションのための新たな基準を設定している。これにより、解像度、信号対雑音比、使用可能な視野が向上し、取得時間が短縮される。</t>
         </is>
       </c>
       <c r="K89" s="60" t="inlineStr">
@@ -7356,12 +7360,12 @@
       </c>
       <c r="I90" s="60" t="inlineStr">
         <is>
-          <t>WHO marks 25 years of Research4Life, advancing access to scientific knowledge in more than 120 countries</t>
+          <t>WHOがResearch4Lifeの25周年を記念、120カ国以上で科学知識へのアクセスを促進</t>
         </is>
       </c>
       <c r="J90" s="60" t="inlineStr">
         <is>
-          <t>The World Health Organization (WHO) today marks the 25th anniversary of Research4Life, a public-private partnership that provides researchers, educators, health professionals and policy-makers in low- and middle-income countries with affordable or free access to scientific knowledge. The partnership has helped dramatically expand access to scientific knowledge for researchers, educators, health professionals and policy-makers in more than 120 countries.</t>
+          <t>世界保健機関（WHO）は、低中所得国の研究者や教育者、医療専門家、政策立案者に手頃な価格または無料で科学知識へのアクセスを提供する公私パートナーシップResearch4Lifeの25周年を迎えた。このパートナーシップは、120カ国以上で科学知識へのアクセスを大幅に拡大するのに寄与している。</t>
         </is>
       </c>
       <c r="K90" s="60" t="inlineStr">
@@ -7427,12 +7431,12 @@
       </c>
       <c r="I91" s="60" t="inlineStr">
         <is>
-          <t>Road deaths fall by 21% globally but stronger action is needed to save lives</t>
+          <t>世界の交通事故死者数21%減少も、さらなる対策が必要</t>
         </is>
       </c>
       <c r="J91" s="60" t="inlineStr">
         <is>
-          <t>Despite the addition of more than one billion motor-vehicles to the world’s roads, the global rate of road traffic deaths declined by 21% between 2011 and 2025, according to new data released by the World Health Organization (WHO). The world has experienced profound changes in road traffic during this time with the emergence of new modes of transport and a sharp rise in motorcycle use. Despite this progress, however, road traffic crashes still claimed 1.16 million people's lives in 2025. Road traffic injuries remain the leading cause of death among children and youth aged 5–29 years. The new WHO data comes as global leaders today adopt a new United Nations (UN) General Assembly progress dec…</t>
+          <t>世界保健機関（WHO）の新データによると、2011年から2025年にかけて世界の交通事故死者数は21%減少したが、依然として2025年には116万人が命を落としており、特に5〜29歳の子供や若者における交通事故は主要な死因となっている。</t>
         </is>
       </c>
       <c r="K91" s="60" t="inlineStr">
@@ -7498,12 +7502,12 @@
       </c>
       <c r="I92" s="60" t="inlineStr">
         <is>
-          <t>WHO Member States continue negotiations on the Pathogen Access and Benefit Sharing Annex</t>
+          <t>WHO加盟国、病原体アクセスと利益配分に関する交渉を継続</t>
         </is>
       </c>
       <c r="J92" s="60" t="inlineStr">
         <is>
-          <t>WHO Member States have advanced negotiations on the Pathogen Access and Benefit Sharing (PABS) annex, a central component of the WHO Pandemic Agreement, while agreeing that continued discussions are needed to finalize a framework that supports a faster, more effective and equitable response to future pandemics.</t>
+          <t>WHO加盟国は、パンデミック協定の中心的要素である病原体アクセスと利益配分（PABS）附属書に関する交渉を進めており、将来のパンデミックに対する迅速かつ効果的で公平な対応を支える枠組みの最終化に向けたさらなる議論が必要であることに合意した。</t>
         </is>
       </c>
       <c r="K92" s="60" t="inlineStr">
@@ -7569,12 +7573,12 @@
       </c>
       <c r="I93" s="60" t="inlineStr">
         <is>
-          <t>In the News: FIA Launches the 2026 Global Fusion Industry Report in New York City, Washington, D.C., and London</t>
+          <t>FIAが2026年グローバル核融合産業レポートをニューヨーク、ワシントンD.C.、ロンドンで発表</t>
         </is>
       </c>
       <c r="J93" s="60" t="inlineStr">
         <is>
-          <t>On July 13, the Fusion Industry Association launched the 2026 Global Fusion Industry Report at an event in New York City - making headlines worldwide and bringing together industry leaders, investors, and media. A Washington, D.C. launch and Congressional briefing followed on July 15, to discuss the report’s findings in the context of US policy with policymakers, think tanks, national labs, and industry leaders. A London dinner event held on July 29 will discuss the report's findings with government leaders, aligned with the recently released UK 2026 Fusion Strategy. The post In the News: FIA Launches the 2026 Global Fusion Industry Report in New York City, Washington, D.C., and London appe…</t>
+          <t>核融合産業協会（FIA）は、2026年グローバル核融合産業レポートをニューヨークで発表し、業界リーダーや投資家、メディアが集まるイベントを開催した。続いてワシントンD.C.での発表と議会ブリーフィングが行われ、報告書の内容が米国の政策文脈で議論された。</t>
         </is>
       </c>
       <c r="K93" s="60" t="inlineStr">
@@ -7640,12 +7644,12 @@
       </c>
       <c r="I94" s="60" t="inlineStr">
         <is>
-          <t>International Legal Expert Group Publish Paper on the Need for the EU to Secure Its Competitive Fusion Advantage</t>
+          <t>EUの競争力ある核融合技術を確保する必要性に関する国際法律専門家グループの論文発表</t>
         </is>
       </c>
       <c r="J94" s="60" t="inlineStr">
         <is>
-          <t>A discussion paper from the International Group of Legal Experts on Fusion Energy (FELEX) argues that Europe holds a competitive advantage in commercial fusion that no other region can replicate, but must act now to preserve it. The paper highlights the Euratom Treaty as the world’s only harmonized legal framework for nuclear governance across 27... The post International Legal Expert Group Publish Paper on the Need for the EU to Secure Its Competitive Fusion Advantage appeared first on Fusion Industry Association .</t>
+          <t>国際法律専門家グループが発表した論文は、ヨーロッパが商業核融合において競争優位性を持っているが、それを維持するためには迅速な行動が必要であると主張している。特に、ユーロトム条約が27カ国における核ガバナンスのための唯一の調和された法的枠組みであることを強調している。</t>
         </is>
       </c>
       <c r="K94" s="60" t="inlineStr">
@@ -7711,12 +7715,12 @@
       </c>
       <c r="I95" s="60" t="inlineStr">
         <is>
-          <t>This Graduate Student Equips NASA’s Robots With Assembly Skills</t>
+          <t>大学院生がNASAのロボットに組立スキルを装備</t>
         </is>
       </c>
       <c r="J95" s="60" t="inlineStr">
         <is>
-          <t>Like many engineers, Sarah Downs says she knew she wanted to pursue a STEM career from a young age. As a teenager, she discovered robotics through her Tulsa, Okla., middle school’s First Lego League team, and she fell in love with the field, she says. Downs participated in the international robotics program from 2014 to 2016. Watching PBS specials on NASA Mars rovers Spirit and Opportunity , and seeing the live broadcast of the Curiosity rover launch in 2011, inspired the teen to dream of a career working with NASA. Sarah Downs MEMBER GRADE Graduate student member UNIVERSITY Texas A&amp;M University in College Station MAJOR Electric engineering This year the IEEE graduate student member achieve…</t>
+          <t>テキサスA&amp;M大学の大学院生サラ・ダウンズが、NASAのロボットに組立スキルを与えるプロジェクトに取り組んでいます。彼女は若い頃からSTEMキャリアを目指していました。</t>
         </is>
       </c>
       <c r="K95" s="60" t="inlineStr">
@@ -7782,12 +7786,12 @@
       </c>
       <c r="I96" s="60" t="inlineStr">
         <is>
-          <t>Intel-Powered Medical Exoskeleton Helps Patients Get Back on Their Feet</t>
+          <t>インテル搭載の医療用エクソスケルトンが患者の歩行を支援</t>
         </is>
       </c>
       <c r="J96" s="60" t="inlineStr">
         <is>
-          <t>People with lower-limb injuries who cannot stand or walk often need intensive clinical rehabilitation and expert-guided physiotherapy.This medical care retrains the limbs and supports the brain’s ability to relearn movement, with the goal of restoring greater mobility and ultimately, helping the patient to walk again.But traditional rehabilitation methods today have its limits – it’s fatigue-inducing, imprecise and requires expert, … The post Intel-Powered Medical Exoskeleton Helps Patients Get Back on Their Feet appeared first on Newsroom .</t>
+          <t>下肢の怪我を持つ患者のために、インテルが搭載した医療用エクソスケルトンが開発され、リハビリテーションの限界を克服することを目指しています。</t>
         </is>
       </c>
       <c r="K96" s="60" t="inlineStr">
@@ -7853,12 +7857,12 @@
       </c>
       <c r="I97" s="60" t="inlineStr">
         <is>
-          <t>Intel and Google Cloud Announce Collaboration to Accelerate Intel’s AI-Enabled Enterprise Transformation</t>
+          <t>インテルとGoogle CloudがAI活用の企業変革を加速するための協力を発表</t>
         </is>
       </c>
       <c r="J97" s="60" t="inlineStr">
         <is>
-          <t>SANTA CLARA, Calif., and SUNNYVALE, Calif. – July 16, 2026 – Intel and Google Cloud today announced an expansion of their previously announced multi-year strategic collaboration, which would accelerate Intel’s enterprise-wide digital evolution through the deployment of Gemini Enterprise and Google Cloud.Intel will integrate advanced, Gemini-powered generative AI across its global workforce, helping to scale capabilities and … The post Intel and Google Cloud Announce Collaboration to Accelerate Intel’s AI-Enabled Enterprise Transformation appeared first on Newsroom .</t>
+          <t>インテルとGoogle Cloudは、AIを活用した企業のデジタル進化を加速するための戦略的協力を拡大することを発表しました。</t>
         </is>
       </c>
       <c r="K97" s="60" t="inlineStr">
@@ -7924,12 +7928,12 @@
       </c>
       <c r="I98" s="60" t="inlineStr">
         <is>
-          <t>Connect more of your apps to Search</t>
+          <t>アプリを検索にもっと接続</t>
         </is>
       </c>
       <c r="J98" s="60" t="inlineStr">
         <is>
-          <t>Connected apps rendering</t>
+          <t>接続されたアプリのレンダリングに関する情報が提供されています。</t>
         </is>
       </c>
       <c r="K98" s="60" t="inlineStr">
@@ -7995,12 +7999,12 @@
       </c>
       <c r="I99" s="60" t="inlineStr">
         <is>
-          <t>Create, edit and star in videos with two Google Vids updates</t>
+          <t>Google Vidsの2つの更新で動画を作成、編集、主演</t>
         </is>
       </c>
       <c r="J99" s="60" t="inlineStr">
         <is>
-          <t>Text "Gemini Omni and Personal Avatars in Google Vids" surrounded by various images</t>
+          <t>Google Vidsに関する更新情報が発表され、Gemini Omniとパーソナルアバターに関する内容が紹介されています。</t>
         </is>
       </c>
       <c r="K99" s="60" t="inlineStr">
@@ -8066,12 +8070,12 @@
       </c>
       <c r="I100" s="60" t="inlineStr">
         <is>
-          <t>Meet GPT-Red: an LLM super-hacker OpenAI built to make its models safer</t>
+          <t>GPT-Red：OpenAIが開発したLLMスーパーハッカー</t>
         </is>
       </c>
       <c r="J100" s="60" t="inlineStr">
         <is>
-          <t>CSET’s Jessica Ji shared her expert insight in an article published by MIT Technology Review. The article examines how OpenAI developed GPT-Red, an AI "super-hacker" designed to automatically identify vulnerabilities in large language models and strengthen their defenses against cyberattacks through AI-powered red-teaming. The post Meet GPT-Red: an LLM super-hacker OpenAI built to make its models safer appeared first on Center for Security and Emerging Technology .</t>
+          <t>CSETのジェシカ・ジがMITテクノロジーレビューに寄稿した記事で、OpenAIが開発したAIスーパーハッカーGPT-Redについて解説しています。これは、大規模言語モデルの脆弱性を自動的に特定し、サイバー攻撃からの防御を強化するためのものです。</t>
         </is>
       </c>
       <c r="K100" s="60" t="inlineStr">
@@ -8137,12 +8141,12 @@
       </c>
       <c r="I101" s="60" t="inlineStr">
         <is>
-          <t>Starlight Engine Raises JPY 6.06 Billion</t>
+          <t>スターロイトエンジンが60.6億円を調達</t>
         </is>
       </c>
       <c r="J101" s="60" t="inlineStr">
         <is>
-          <t>Starlight Engine has raised JPY 6.06 billion in its first external funding round to accelerate development of FAST. The company is developing a tokamak-based fusion machine that builds on decades of research, including Japan's JT-60SA program and international efforts. The post Starlight Engine Raises JPY 6.06 Billion appeared first on Fusion Industry Association .</t>
+          <t>スターロイトエンジンは、FASTの開発を加速するために初の外部資金調達ラウンドで60.6億円を調達しました。同社は、トカマク型の融合機を開発しています。</t>
         </is>
       </c>
       <c r="K101" s="60" t="inlineStr">
@@ -8208,12 +8212,12 @@
       </c>
       <c r="I102" s="60" t="inlineStr">
         <is>
-          <t>Fusion research center coming to Madison’s former Oscar Mayer plant</t>
+          <t>マディソンに融合研究センターが設立、オスカー・マイヤー工場跡地に</t>
         </is>
       </c>
       <c r="J102" s="60" t="inlineStr">
         <is>
-          <t>Realta Fusion selected Madison, Wisconsin's former Oscar Mayer site as the location for its new headquarters and facility. They plan to build the prototype magnetic mirror fusion machine here, with the project expected to create 600+ jobs and establish a major hub for fusion innovation. The post Fusion research center coming to Madison’s former Oscar Mayer plant appeared first on Fusion Industry Association .</t>
+          <t>Realta Fusionは、ウィスコンシン州マディソンの元オスカー・マイヤー工場跡地に新しい本社と施設を設立することを発表しました。このプロジェクトは600以上の雇用を創出し、融合技術の主要な拠点を確立することが期待されています。</t>
         </is>
       </c>
       <c r="K102" s="60" t="inlineStr">
@@ -8279,12 +8283,12 @@
       </c>
       <c r="I103" s="60" t="inlineStr">
         <is>
-          <t>New WHO guidelines: up to 45% of dementia risk could be prevented or delayed</t>
+          <t>新しいWHOガイドライン：認知症リスクの最大45%を予防または遅延可能</t>
         </is>
       </c>
       <c r="J103" s="60" t="inlineStr">
         <is>
-          <t>The World Health Organization (WHO) today released updated guidelines on reducing the risk of cognitive decline and dementia , providing countries with evidence-based recommendations to help prevent or delay the onset of dementia across the life course. Dementia is a condition caused by brain diseases and affects memory, thinking and the ability to function. More than 57 million people live with dementia worldwide and nearly 10 million people get newly diagnosed every year. Alzheimer disease is the most common form of dementia and is estimated to account for 60–70% of cases. While there is no cure for dementia, up to 45% of the risks can be attributed to modifiable risk factors such as toba…</t>
+          <t>WHOは、認知症のリスクを減少させるための新しいガイドラインを発表しました。これにより、国々は認知症の発症を予防または遅延させるための根拠に基づく推奨を得ることができます。</t>
         </is>
       </c>
       <c r="K103" s="60" t="inlineStr">
@@ -8350,12 +8354,12 @@
       </c>
       <c r="I104" s="60" t="inlineStr">
         <is>
-          <t>Global childhood immunization coverage inches forward despite conflict and hesitancy – UNICEF, WHO</t>
+          <t>世界の子供の予防接種率が向上、紛争やためらいにもかかわらず</t>
         </is>
       </c>
       <c r="J104" s="60" t="inlineStr">
         <is>
-          <t>In 2025, 90% of infants globally – or nearly 116 million – received at least one dose of a diphtheria, tetanus and pertussis (DTP) vaccine, and 85% – or 110 million – completed the full three-dose series, according to the annual WHO-UNICEF Estimates of National Immunization Coverage (WUENIC) released today. While both indicators rose by one percentage point from the previous year, global coverage remains one point below 2019 levels – hovering within the same narrow range since 2009. According to the data, an estimated 13.5 million “zero-dose” children did not receive a single vaccine in their first year during 2025. While these represent nearly 750 000 fewer children than the previous year,…</t>
+          <t>2025年には、世界で90%の乳児がジフテリア、破傷風、百日咳（DTP）ワクチンの少なくとも1回の接種を受け、85%が3回の接種を完了したとWHOとUNICEFの報告が示しています。しかし、依然として2019年の水準を下回っています。</t>
         </is>
       </c>
       <c r="K104" s="60" t="inlineStr">
@@ -8421,12 +8425,12 @@
       </c>
       <c r="I105" s="60" t="inlineStr">
         <is>
-          <t>Global Investment in Fusion Companies Surges 69% to $4.5 Billion</t>
+          <t>核融合企業への世界的投資が69%増加、45億ドルに達する</t>
         </is>
       </c>
       <c r="J105" s="60" t="inlineStr">
         <is>
-          <t>The Fusion Industry Association released its 2026 Global Fusion Industry Report, showing that fusion companies have raised a $14.24 billion. The report highlights record investment, growing commercial partnerships, and increasing confidence that fusion machines will deliver electricity in the 2030s. The post Global Investment in Fusion Companies Surges 69% to $4.5 Billion appeared first on Fusion Industry Association .</t>
+          <t>核融合産業協会が発表した2026年の報告書によると、核融合企業への投資が記録的な水準に達し、2030年代に電力供給が期待されている。</t>
         </is>
       </c>
       <c r="K105" s="60" t="inlineStr">
@@ -8492,12 +8496,12 @@
       </c>
       <c r="I106" s="60" t="inlineStr">
         <is>
-          <t>General Fusion Shares Soar 25%</t>
+          <t>ジェネラルフュージョンの株価が25%上昇</t>
         </is>
       </c>
       <c r="J106" s="60" t="inlineStr">
         <is>
-          <t>Canada-based General Fusion has become the first publicly listed fusion company after completing a merger with a special purpose acquisition company (SPAC). The listing provides the company with broader access to capital as it advances its technology toward deployment. The post General Fusion Shares Soar 25% appeared first on Fusion Industry Association .</t>
+          <t>カナダのジェネラルフュージョンが特別目的買収会社（SPAC）との合併を完了し、公開企業となったことで資本へのアクセスが広がり、株価が上昇した。</t>
         </is>
       </c>
       <c r="K106" s="60" t="inlineStr">
@@ -8563,12 +8567,12 @@
       </c>
       <c r="I107" s="60" t="inlineStr">
         <is>
-          <t>Celebrating 25 years of visual search innovation</t>
+          <t>視覚検索の革新25周年を祝う</t>
         </is>
       </c>
       <c r="J107" s="60" t="inlineStr">
         <is>
-          <t>Google Images logo surrounded by illustrations of people searching for different images</t>
+          <t>Google Imagesが視覚検索の革新25周年を迎え、さまざまな画像検索の様子を描いたイラストが紹介されている。</t>
         </is>
       </c>
       <c r="K107" s="60" t="inlineStr">
@@ -8634,12 +8638,12 @@
       </c>
       <c r="I108" s="60" t="inlineStr">
         <is>
-          <t>NIST Receives New Patent for Microbe-Killing Water Heater</t>
+          <t>NIST、新しい微生物除去型給湯器の特許を取得</t>
         </is>
       </c>
       <c r="J108" s="60" t="inlineStr">
         <is>
-          <t>Warm water in household pipes can be a breeding ground for harmful bacteria.</t>
+          <t>家庭の配管内の温水が有害な細菌の繁殖地となる可能性があることから、NISTが新たな給湯器の特許を取得した。</t>
         </is>
       </c>
       <c r="K108" s="60" t="inlineStr">
@@ -8705,12 +8709,12 @@
       </c>
       <c r="I109" s="60" t="inlineStr">
         <is>
-          <t>Washington Is Looking to Keep China From Training Its AI on US Models</t>
+          <t>ワシントン、中国が米国モデルでAIを訓練するのを防ごうとする</t>
         </is>
       </c>
       <c r="J109" s="60" t="inlineStr">
         <is>
-          <t>CSET’s Colin Shea-Blymyer shared his expert insight in an article published by Bloomberg. The article examines growing concerns in Washington over the use of "distillation" by Chinese AI companies to train models using outputs from leading US systems, and the resulting debate over intellectual property, competition, and national security in the global AI race. The post Washington Is Looking to Keep China From Training Its AI on US Models appeared first on Center for Security and Emerging Technology .</t>
+          <t>ワシントンでは、中国のAI企業が米国のシステムの出力を用いてモデルを訓練することに対する懸念が高まっており、知的財産や国家安全保障に関する議論が進んでいる。</t>
         </is>
       </c>
       <c r="K109" s="60" t="inlineStr">
@@ -8776,12 +8780,12 @@
       </c>
       <c r="I110" s="60" t="inlineStr">
         <is>
-          <t>Verifying Rust cryptography in SymCrypt, from standards to code</t>
+          <t>SymCryptにおけるRust暗号の検証</t>
         </is>
       </c>
       <c r="J110" s="60" t="inlineStr">
         <is>
-          <t>Cryptographic code supports vital protections in modern computing systems. Learn how a new method helps verify code as developers write it while preserving speed and adaptability as it gets implemented and evolves. The post Verifying Rust cryptography in SymCrypt, from standards to code appeared first on Microsoft Research .</t>
+          <t>新しい手法により、開発者がコードを記述する際に暗号コードの検証が可能になり、速度と適応性を保ちながら実装が進む。</t>
         </is>
       </c>
       <c r="K110" s="60" t="inlineStr">
@@ -8847,12 +8851,12 @@
       </c>
       <c r="I111" s="60" t="inlineStr">
         <is>
-          <t>Intel Invests €5 Billion to Expand Manufacturing in Europe</t>
+          <t>インテル、欧州で製造拡大のために50億ユーロを投資</t>
         </is>
       </c>
       <c r="J111" s="60" t="inlineStr">
         <is>
-          <t>LEIXLIP, Ireland, July 13, 2026 —Intel today announced a €5 billion ($5.7 billion) capital investment at its Leixlip campus in Ireland, marking the next phase in the site’s capacity expansion. Global demand for AI and high-performance computing is driving the need for advanced silicon to power AI Factories, and Intel is scaling capacity in Ireland … The post Intel Invests €5 Billion to Expand Manufacturing in Europe appeared first on Newsroom .</t>
+          <t>インテルはアイルランドのLeixlipキャンパスに50億ユーロを投資し、AIや高性能コンピューティングの需要に応えるための製造能力を拡大する。</t>
         </is>
       </c>
       <c r="K111" s="60" t="inlineStr">
@@ -8918,12 +8922,12 @@
       </c>
       <c r="I112" s="60" t="inlineStr">
         <is>
-          <t>Building a Foundation Stack for General-Purpose Robots</t>
+          <t>汎用ロボットの基盤スタック構築</t>
         </is>
       </c>
       <c r="J112" s="60" t="inlineStr">
         <is>
-          <t>This article is brought to you by X Square Robot . Large language models gave artificial intelligence a working recipe. Pretrain a large model on broad data, and general capability follows. Robotics has no such recipe. Robotics systems have long been assembled from separate perception, planning, and control parts that rarely add up to intelligence a robot can carry from one task to another, or one machine to another. The central problem in embodied AI is to find the equivalent recipe, and the field does not yet agree on what it is. X Square Robot , a Chinese embodied-AI company, has made an unusually explicit bet. It argues that the recipe is an integrated stack, spanning the data a robot l…</t>
+          <t>ロボティクス分野では、知能を持つロボットを実現するための統合スタックの必要性が議論されている。X Square Robotはこの課題に挑戦している。</t>
         </is>
       </c>
       <c r="K112" s="60" t="inlineStr">
@@ -8989,12 +8993,12 @@
       </c>
       <c r="I113" s="60" t="inlineStr">
         <is>
-          <t>El Salvador validated by WHO as having eliminated trachoma as a public health problem</t>
+          <t>エルサルバドル、WHOによりトラコーマの公衆衛生問題を解消したと認定</t>
         </is>
       </c>
       <c r="J113" s="60" t="inlineStr">
         <is>
-          <t>The World Health Organization (WHO) has validated El Salvador as having eliminated trachoma as a public health problem. Trachoma is the world's leading infectious cause of blindness.</t>
+          <t>世界保健機関（WHO）は、エルサルバドルがトラコーマを公衆衛生問題として解消したと認定した。トラコーマは失明の主要な感染症である。</t>
         </is>
       </c>
       <c r="K113" s="60" t="inlineStr">
@@ -9060,12 +9064,12 @@
       </c>
       <c r="I114" s="60" t="inlineStr">
         <is>
-          <t>Companies turn to Chinese AI models to cut costs</t>
+          <t>企業がコスト削減のために中国のAIモデルに注目</t>
         </is>
       </c>
       <c r="J114" s="60" t="inlineStr">
         <is>
-          <t>CSET’s Sam Bresnick shared his expert insight in an article published by The Financial Times. The article examines why companies around the world are increasingly adopting Chinese AI models, drawn by their lower costs, improving capabilities, and the flexibility offered by open-weight systems. The post Companies turn to Chinese AI models to cut costs appeared first on Center for Security and Emerging Technology .</t>
+          <t>企業がコスト削減を目的に、中国のAIモデルを採用する動きが広がっている。低コストや能力向上、オープンウェイトシステムの柔軟性が要因とされる。</t>
         </is>
       </c>
       <c r="K114" s="60" t="inlineStr">
@@ -11300,7 +11304,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -11379,7 +11383,7 @@
     <row r="4" ht="42" customHeight="1">
       <c r="A4" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:51:39+09:00</t>
+          <t>2026-07-26T20:00:03+09:00</t>
         </is>
       </c>
       <c r="B4" s="77" t="n">
@@ -11389,16 +11393,16 @@
         <v>24</v>
       </c>
       <c r="D4" s="77" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E4" s="77" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="F4" s="77" t="n">
         <v>10</v>
       </c>
       <c r="G4" s="77" t="n">
-        <v>11.55</v>
+        <v>154.27</v>
       </c>
       <c r="H4" s="60" t="inlineStr">
         <is>
@@ -11409,26 +11413,26 @@
     <row r="5">
       <c r="A5" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:10:55+09:00</t>
+          <t>2026-07-26T19:51:39+09:00</t>
         </is>
       </c>
       <c r="B5" s="77" t="n">
         <v>34</v>
       </c>
       <c r="C5" s="77" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D5" s="77" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E5" s="77" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F5" s="77" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G5" s="77" t="n">
-        <v>194.65</v>
+        <v>11.55</v>
       </c>
       <c r="H5" s="60" t="inlineStr">
         <is>
@@ -11439,26 +11443,26 @@
     <row r="6">
       <c r="A6" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:05:06+09:00</t>
+          <t>2026-07-26T19:10:55+09:00</t>
         </is>
       </c>
       <c r="B6" s="77" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C6" s="77" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D6" s="77" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E6" s="77" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="F6" s="77" t="n">
         <v>9</v>
       </c>
       <c r="G6" s="77" t="n">
-        <v>165.89</v>
+        <v>194.65</v>
       </c>
       <c r="H6" s="60" t="inlineStr">
         <is>
@@ -11469,35 +11473,65 @@
     <row r="7">
       <c r="A7" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T19:05:06+09:00</t>
         </is>
       </c>
       <c r="B7" s="77" t="n">
         <v>33</v>
       </c>
       <c r="C7" s="77" t="n">
+        <v>24</v>
+      </c>
+      <c r="D7" s="77" t="n">
+        <v>5</v>
+      </c>
+      <c r="E7" s="77" t="n">
+        <v>39</v>
+      </c>
+      <c r="F7" s="77" t="n">
+        <v>9</v>
+      </c>
+      <c r="G7" s="77" t="n">
+        <v>165.89</v>
+      </c>
+      <c r="H7" s="60" t="inlineStr">
+        <is>
+          <t>Daily update</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T18:56:03+09:00</t>
+        </is>
+      </c>
+      <c r="B8" s="77" t="n">
+        <v>33</v>
+      </c>
+      <c r="C8" s="77" t="n">
         <v>20</v>
       </c>
-      <c r="D7" s="77" t="n">
+      <c r="D8" s="77" t="n">
         <v>94</v>
       </c>
-      <c r="E7" s="77" t="n">
+      <c r="E8" s="77" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="77" t="n">
+      <c r="F8" s="77" t="n">
         <v>13</v>
       </c>
-      <c r="G7" s="77" t="n">
+      <c r="G8" s="77" t="n">
         <v>129.43</v>
       </c>
-      <c r="H7" s="60" t="inlineStr">
+      <c r="H8" s="60" t="inlineStr">
         <is>
           <t>Initial lookback</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:H7"/>
+  <autoFilter ref="A3:H8"/>
   <mergeCells count="2">
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>

--- a/docs/innovation_news_ledger.xlsx
+++ b/docs/innovation_news_ledger.xlsx
@@ -9,9 +9,9 @@
     <sheet name="Run Log" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'News Ledger'!$A$3:$O$114</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'News Ledger'!$A$3:$O$56</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Source Registry'!$A$3:$K$37</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Run Log'!$A$3:$H$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Run Log'!$A$3:$H$9</definedName>
   </definedNames>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -472,7 +472,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="NewsLedgerTable" displayName="NewsLedgerTable" ref="A3:O114" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="NewsLedgerTable" displayName="NewsLedgerTable" ref="A3:O56" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <autoFilter ref="A3:O4"/>
   <tableColumns count="15">
     <tableColumn id="1" name="Collected At (JST)"/>
@@ -516,7 +516,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="RunLogTable" displayName="RunLogTable" ref="A3:H8" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="RunLogTable" displayName="RunLogTable" ref="A3:H9" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <autoFilter ref="A3:H4"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Run Time (JST)"/>
@@ -800,7 +800,7 @@
       </c>
       <c r="B5" s="25" t="inlineStr">
         <is>
-          <t>2026-07-26T20:00:03+09:00</t>
+          <t>2026-07-26T20:13:43+09:00</t>
         </is>
       </c>
       <c r="C5" s="46" t="n"/>
@@ -1088,7 +1088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O114"/>
+  <dimension ref="A1:O56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="B4" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T10:00:16Z</t>
+          <t>2026-07-26T08:00:09Z</t>
         </is>
       </c>
       <c r="C4" s="60" t="inlineStr">
@@ -1236,11 +1236,11 @@
       </c>
       <c r="E4" s="60" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Innovation Policy</t>
         </is>
       </c>
       <c r="F4" s="76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" s="60" t="inlineStr">
         <is>
@@ -1254,22 +1254,22 @@
       </c>
       <c r="I4" s="60" t="inlineStr">
         <is>
-          <t>ドイツの裁判所は中国の薬物強姦ネットワークのメンバーに対して甘すぎたのか？</t>
+          <t>利益率の低下が中国自動車メーカーの価格戦争計画を阻む</t>
         </is>
       </c>
       <c r="J4" s="60" t="inlineStr">
         <is>
-          <t>ベルリンの裁判所が中国人男性に対し、強姦と性的強要の幇助で5年の懲役を言い渡したことに対し、被害者の女性たちは複雑な感情を抱いている。この事件は、正義とは何かを考えさせるものである。</t>
+          <t>中国の自動車メーカーが利益率の低下に直面し、価格戦争の計画が難航している。</t>
         </is>
       </c>
       <c r="K4" s="60" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/news/china/politics/article/3361892/were-german-courts-too-soft-chinese-members-drug-rape-network?utm_source=rss_feed</t>
+          <t>https://www.scmp.com/business/china-business/article/3361876/lower-profit-margins-set-foil-chinese-carmakers-price-war-plans-despite-falling-sales?utm_source=rss_feed</t>
         </is>
       </c>
       <c r="L4" s="60" t="inlineStr">
         <is>
-          <t>4ca6c9bab41f11f1e490b924</t>
+          <t>edcae2eaed3f6ecc6f59640c</t>
         </is>
       </c>
       <c r="M4" s="75" t="inlineStr">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="B5" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T08:00:09Z</t>
+          <t>2026-07-26T00:00:14Z</t>
         </is>
       </c>
       <c r="C5" s="60" t="inlineStr">
@@ -1311,7 +1311,7 @@
         </is>
       </c>
       <c r="F5" s="76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G5" s="60" t="inlineStr">
         <is>
@@ -1325,22 +1325,22 @@
       </c>
       <c r="I5" s="60" t="inlineStr">
         <is>
-          <t>中国の自動車メーカー、利益率低下で価格戦争計画が頓挫</t>
+          <t>インドネシアのシンガポール対抗計画が具体化</t>
         </is>
       </c>
       <c r="J5" s="60" t="inlineStr">
         <is>
-          <t>中国の自動車メーカーは、原材料費の高騰により利益率が縮小し、販売需要の減少に直面している。これにより、消費者が期待する大幅な値下げが難しくなる可能性がある。</t>
+          <t>インドネシアがシンガポールや香港に対抗する金融センターの設立を目指し、法的基盤が整備された。</t>
         </is>
       </c>
       <c r="K5" s="60" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/business/china-business/article/3361876/lower-profit-margins-set-foil-chinese-carmakers-price-war-plans-despite-falling-sales?utm_source=rss_feed</t>
+          <t>https://www.scmp.com/week-asia/economics/article/3361783/indonesias-plan-singapore-rival-starts-take-shape?utm_source=rss_feed</t>
         </is>
       </c>
       <c r="L5" s="60" t="inlineStr">
         <is>
-          <t>edcae2eaed3f6ecc6f59640c</t>
+          <t>f74daba2783d19d5f5ff6719</t>
         </is>
       </c>
       <c r="M5" s="75" t="inlineStr">
@@ -1358,65 +1358,65 @@
     <row r="6" ht="42" customHeight="1">
       <c r="A6" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:51:39+09:00</t>
+          <t>2026-07-26T18:56:03+09:00</t>
         </is>
       </c>
       <c r="B6" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T04:54:09Z</t>
+          <t>2026-07-25T14:32:00Z</t>
         </is>
       </c>
       <c r="C6" s="60" t="inlineStr">
         <is>
-          <t>EU &amp; Europe</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="D6" s="60" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="E6" s="60" t="inlineStr">
         <is>
-          <t>Fusion Energy</t>
+          <t>Semiconductors &amp; Telecom</t>
         </is>
       </c>
       <c r="F6" s="76" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G6" s="60" t="inlineStr">
         <is>
-          <t>Major Media</t>
+          <t>Official Company</t>
         </is>
       </c>
       <c r="H6" s="60" t="inlineStr">
         <is>
-          <t>South China Morning Post Technology</t>
+          <t>Samsung Global Newsroom</t>
         </is>
       </c>
       <c r="I6" s="60" t="inlineStr">
         <is>
-          <t>欧州の熱波が夏の観光客を涼しい北へ誘導</t>
+          <t>サムスン電子とブロードコムがメモリとファウンドリ技術での戦略的協力を拡大</t>
         </is>
       </c>
       <c r="J6" s="60" t="inlineStr">
         <is>
-          <t>欧州の観光客は、繰り返される熱波の影響で地中海の目的地を避け、涼しい北部を選ぶ傾向が見られる。これは観光市場における持続的な変化を示す可能性がある。</t>
+          <t>サムスン電子とブロードコムが、次世代AIインフラを支えるためのメモリとファウンドリ技術に関する戦略的協力を拡大することを発表しました。</t>
         </is>
       </c>
       <c r="K6" s="60" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/news/world/europe/article/3361871/european-heatwaves-drive-summer-tourists-cooler-north?utm_source=rss_feed</t>
+          <t>https://news.samsung.com/global/samsung-electronics-and-broadcom-expand-strategic-collaboration-across-memory-and-foundry-technologies</t>
         </is>
       </c>
       <c r="L6" s="60" t="inlineStr">
         <is>
-          <t>16261ceceb1c08aa85c0ea99</t>
+          <t>bd739fbc33fb8bb2bb1f6e52</t>
         </is>
       </c>
       <c r="M6" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:51:39+09:00</t>
+          <t>2026-07-26T18:56:03+09:00</t>
         </is>
       </c>
       <c r="N6" s="60" t="inlineStr">
@@ -1429,17 +1429,17 @@
     <row r="7" ht="42" customHeight="1">
       <c r="A7" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:51:39+09:00</t>
+          <t>2026-07-26T20:13:43+09:00</t>
         </is>
       </c>
       <c r="B7" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T03:21:31Z</t>
+          <t>2026-07-25T02:32:54Z</t>
         </is>
       </c>
       <c r="C7" s="60" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D7" s="60" t="inlineStr">
@@ -1449,11 +1449,11 @@
       </c>
       <c r="E7" s="60" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Innovation Policy</t>
         </is>
       </c>
       <c r="F7" s="76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" s="60" t="inlineStr">
         <is>
@@ -1467,27 +1467,27 @@
       </c>
       <c r="I7" s="60" t="inlineStr">
         <is>
-          <t>中国の男性が珍しい病状で頭皮が厚く折りたたまれる</t>
+          <t>中国、Trip.comに765百万ドルの独占禁止罰金を科す</t>
         </is>
       </c>
       <c r="J7" s="60" t="inlineStr">
         <is>
-          <t>中国中部の男性が、脳のひだに似た厚い頭皮の状態に悩まされていたが、整形外科医によって治療を受けた。この症例は医療技術の重要性を示すものである。</t>
+          <t>中国の市場規制当局は、Trip.comに対して独占的行為により765百万ドルの罰金を科した。この措置は、中国の市場における競争環境を改善するための政策の一環と見られる。</t>
         </is>
       </c>
       <c r="K7" s="60" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/news/people-culture/trending-china/article/3361865/rare-medical-condition-causes-chinese-mans-scalp-thicken-and-fold-resembling-human-brain?utm_source=rss_feed</t>
+          <t>https://www.scmp.com/tech/policy/article/3361818/china-hits-tripcom-us765-million-antitrust-penalty-after-six-month-investigation?utm_source=rss_feed</t>
         </is>
       </c>
       <c r="L7" s="60" t="inlineStr">
         <is>
-          <t>e6f3f1ebac50723e73d10bfe</t>
+          <t>4f0f96e20a2da9824751e330</t>
         </is>
       </c>
       <c r="M7" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:51:39+09:00</t>
+          <t>2026-07-26T20:13:43+09:00</t>
         </is>
       </c>
       <c r="N7" s="60" t="inlineStr">
@@ -1500,12 +1500,12 @@
     <row r="8" ht="42" customHeight="1">
       <c r="A8" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:51:39+09:00</t>
+          <t>2026-07-26T18:56:03+09:00</t>
         </is>
       </c>
       <c r="B8" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T00:00:14Z</t>
+          <t>2026-07-24T16:46:59Z</t>
         </is>
       </c>
       <c r="C8" s="60" t="inlineStr">
@@ -1515,50 +1515,50 @@
       </c>
       <c r="D8" s="60" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E8" s="60" t="inlineStr">
         <is>
-          <t>Innovation Policy</t>
+          <t>Semiconductors &amp; Telecom</t>
         </is>
       </c>
       <c r="F8" s="76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G8" s="60" t="inlineStr">
         <is>
-          <t>Major Media</t>
+          <t>Official Company</t>
         </is>
       </c>
       <c r="H8" s="60" t="inlineStr">
         <is>
-          <t>South China Morning Post Technology</t>
+          <t>Intel Newsroom</t>
         </is>
       </c>
       <c r="I8" s="60" t="inlineStr">
         <is>
-          <t>インドネシアのシンガポール対抗計画が具体化</t>
+          <t>インテルとレンズテクノロジーがAI時代の先進半導体パッケージングを実現するために協力</t>
         </is>
       </c>
       <c r="J8" s="60" t="inlineStr">
         <is>
-          <t>インドネシアはシンガポール、香港、ドバイに対抗する金融センターの建設を目指しており、法律的基盤が整ったことで外国資本の誘致に向けた重要な一歩を踏み出した。しかし、実際の投資誘致にはさらなる努力が必要とされている。</t>
+          <t>インテルとレンズテクノロジーが、ガラス基板を用いた先進的な半導体パッケージング技術の開発を加速するための戦略的協力を発表しました。</t>
         </is>
       </c>
       <c r="K8" s="60" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/week-asia/economics/article/3361783/indonesias-plan-singapore-rival-starts-take-shape?utm_source=rss_feed</t>
+          <t>https://newsroom.intel.com/new-technologies/intel-and-lens-technology-collaborate-to-enable-advanced-semiconductor-packaging-for-the-ai-era</t>
         </is>
       </c>
       <c r="L8" s="60" t="inlineStr">
         <is>
-          <t>f74daba2783d19d5f5ff6719</t>
+          <t>10eedf14d7d6b636e24e447d</t>
         </is>
       </c>
       <c r="M8" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:51:39+09:00</t>
+          <t>2026-07-26T18:56:03+09:00</t>
         </is>
       </c>
       <c r="N8" s="60" t="inlineStr">
@@ -1571,27 +1571,27 @@
     <row r="9" ht="42" customHeight="1">
       <c r="A9" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:51:39+09:00</t>
+          <t>2026-07-26T18:56:03+09:00</t>
         </is>
       </c>
       <c r="B9" s="75" t="inlineStr">
         <is>
-          <t>2026-07-25T21:57:06Z</t>
+          <t>2026-07-24T04:34:27Z</t>
         </is>
       </c>
       <c r="C9" s="60" t="inlineStr">
         <is>
-          <t>Middle East</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="D9" s="60" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E9" s="60" t="inlineStr">
         <is>
-          <t>Robotics</t>
+          <t>Artificial Intelligence | Semiconductors &amp; Telecom</t>
         </is>
       </c>
       <c r="F9" s="76" t="n">
@@ -1599,37 +1599,37 @@
       </c>
       <c r="G9" s="60" t="inlineStr">
         <is>
-          <t>Major Media</t>
+          <t>Official Company</t>
         </is>
       </c>
       <c r="H9" s="60" t="inlineStr">
         <is>
-          <t>South China Morning Post Technology</t>
+          <t>NVIDIA Blog</t>
         </is>
       </c>
       <c r="I9" s="60" t="inlineStr">
         <is>
-          <t>米国がイランへの夜間攻撃を一時停止、フーシ派とサウジの衝突</t>
+          <t>AIサミットで韓国がNVIDIAとパートナーと共にAIの未来を描く</t>
         </is>
       </c>
       <c r="J9" s="60" t="inlineStr">
         <is>
-          <t>フーシ派とサウジアラビアの間で衝突が激化する中、米国のイランへの夜間攻撃が一時停止され、トランプ大統領の戦略に新たな疑問が生じている。</t>
+          <t>韓国の大統領とビジネスリーダーがNVIDIAと共にAIの進展を議論し、今後の政策を策定するための会議を開催した。</t>
         </is>
       </c>
       <c r="K9" s="60" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/news/world/middle-east/article/3361857/us-pauses-nightly-iran-strikes-houthis-clash-saudis?utm_source=rss_feed</t>
+          <t>https://blogs.nvidia.com/blog/ai-summit-korea-partners-and-nvidia/</t>
         </is>
       </c>
       <c r="L9" s="60" t="inlineStr">
         <is>
-          <t>9578a29fc000c630648a5b1c</t>
+          <t>3124530844eb0ac80a5a17e4</t>
         </is>
       </c>
       <c r="M9" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:51:39+09:00</t>
+          <t>2026-07-26T18:56:03+09:00</t>
         </is>
       </c>
       <c r="N9" s="60" t="inlineStr">
@@ -1642,27 +1642,27 @@
     <row r="10" ht="42" customHeight="1">
       <c r="A10" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:51:39+09:00</t>
+          <t>2026-07-26T18:56:03+09:00</t>
         </is>
       </c>
       <c r="B10" s="75" t="inlineStr">
         <is>
-          <t>2026-07-25T21:30:08Z</t>
+          <t>2026-07-24T00:00:00Z</t>
         </is>
       </c>
       <c r="C10" s="60" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D10" s="60" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="E10" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="F10" s="76" t="n">
@@ -1670,37 +1670,37 @@
       </c>
       <c r="G10" s="60" t="inlineStr">
         <is>
-          <t>Major Media</t>
+          <t>Scientific Publication</t>
         </is>
       </c>
       <c r="H10" s="60" t="inlineStr">
         <is>
-          <t>South China Morning Post Technology</t>
+          <t>Nature</t>
         </is>
       </c>
       <c r="I10" s="60" t="inlineStr">
         <is>
-          <t>西側諸国がAIの未来を議論する中、半分の世界が不在</t>
+          <t>奇妙なCRISPR酵素が癌細胞をDNAを破壊して殺す</t>
         </is>
       </c>
       <c r="J10" s="60" t="inlineStr">
         <is>
-          <t>スタンフォードデジタル経済ラボが主導した公開書簡には、AIが産業革命を超える経済変革を引き起こす可能性があると警告する200人以上の経済学者とAI研究者が署名した。これは、AIの影響を適切に管理するための制度構築の必要性を強調している。</t>
+          <t>新たなCRISPR酵素が癌細胞を標的にし、DNAを破壊することで効果を示す可能性があることが報告された。</t>
         </is>
       </c>
       <c r="K10" s="60" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/opinion/world-opinion/article/3361362/west-debating-ais-future-half-world-absent?utm_source=rss_feed</t>
+          <t>https://www.nature.com/articles/d41586-026-02268-z</t>
         </is>
       </c>
       <c r="L10" s="60" t="inlineStr">
         <is>
-          <t>3e13a0000f2936b28208b36d</t>
+          <t>006500c385193d3a42b6ae61</t>
         </is>
       </c>
       <c r="M10" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:51:39+09:00</t>
+          <t>2026-07-26T18:56:03+09:00</t>
         </is>
       </c>
       <c r="N10" s="60" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="B11" s="75" t="inlineStr">
         <is>
-          <t>2026-07-25T20:00:53Z</t>
+          <t>2026-07-23T16:58:28Z</t>
         </is>
       </c>
       <c r="C11" s="60" t="inlineStr">
@@ -1728,12 +1728,12 @@
       </c>
       <c r="D11" s="60" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E11" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="F11" s="76" t="n">
@@ -1746,27 +1746,27 @@
       </c>
       <c r="H11" s="60" t="inlineStr">
         <is>
-          <t>The Guardian Technology</t>
+          <t>MIT Technology Review</t>
         </is>
       </c>
       <c r="I11" s="60" t="inlineStr">
         <is>
-          <t>メルボルン郊外に計画されているメガデータセンター</t>
+          <t>超冷却された腎臓が豚に移植される「画期的な成果」</t>
         </is>
       </c>
       <c r="J11" s="60" t="inlineStr">
         <is>
-          <t>メルボルン郊外に計画されているAIハブは、大型ショッピングセンターの6倍の規模を持つデータセンターであり、地域住民からの慎重な評価を求める署名が3,600人以上集まった。これはデータセンターの急増に関する国民的議論の焦点となっている。</t>
+          <t>臓器提供において、時間が重要であることを示す研究が発表され、超冷却された腎臓が豚に移植されることに成功した。これは臓器の保存と移植における新たな可能性を示唆している。</t>
         </is>
       </c>
       <c r="K11" s="60" t="inlineStr">
         <is>
-          <t>https://www.theguardian.com/australia-news/2026/jul/26/mega-datacentre-planned-for-outer-melbourne-will-be-almost-six-times-the-size-of-chadstone-shopping-centre</t>
+          <t>https://www.technologyreview.com/2026/07/23/1140765/supercooled-kidneys-have-been-transplanted-into-pigs-in-a-landmark-achievement/</t>
         </is>
       </c>
       <c r="L11" s="60" t="inlineStr">
         <is>
-          <t>fbf0c9b2010e9cdb4ff4a650</t>
+          <t>590a8cbd726d99d379ccecb1</t>
         </is>
       </c>
       <c r="M11" s="75" t="inlineStr">
@@ -1789,55 +1789,55 @@
       </c>
       <c r="B12" s="75" t="inlineStr">
         <is>
-          <t>2026-07-25T14:32:00Z</t>
+          <t>2026-07-23T15:00:48Z</t>
         </is>
       </c>
       <c r="C12" s="60" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D12" s="60" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="E12" s="60" t="inlineStr">
         <is>
-          <t>Semiconductors &amp; Telecom</t>
+          <t>Innovation Policy</t>
         </is>
       </c>
       <c r="F12" s="76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" s="60" t="inlineStr">
         <is>
-          <t>Official Company</t>
+          <t>Major Media</t>
         </is>
       </c>
       <c r="H12" s="60" t="inlineStr">
         <is>
-          <t>Samsung Global Newsroom</t>
+          <t>The Guardian Technology</t>
         </is>
       </c>
       <c r="I12" s="60" t="inlineStr">
         <is>
-          <t>サムスン電子とブロードコム、メモリとファウンドリ技術で戦略的協力を拡大</t>
+          <t>現在の10年代が映画を革命化した理由</t>
         </is>
       </c>
       <c r="J12" s="60" t="inlineStr">
         <is>
-          <t>サムスン電子とブロードコムは、AIインフラの次世代を支えるためのメモランダムを締結し、メモリとファウンドリ技術における戦略的協力を拡大することを発表した。これは、AI技術の進展に向けた重要なステップである。</t>
+          <t>映画産業の革新とその影響について考察されており、政策的な観点からの議論が含まれています。</t>
         </is>
       </c>
       <c r="K12" s="60" t="inlineStr">
         <is>
-          <t>https://news.samsung.com/global/samsung-electronics-and-broadcom-expand-strategic-collaboration-across-memory-and-foundry-technologies</t>
+          <t>https://www.theguardian.com/film/2026/jul/23/how-2020s-decade-revolutionised-cinema</t>
         </is>
       </c>
       <c r="L12" s="60" t="inlineStr">
         <is>
-          <t>bd739fbc33fb8bb2bb1f6e52</t>
+          <t>f8939f05439f07fdefca04fc</t>
         </is>
       </c>
       <c r="M12" s="75" t="inlineStr">
@@ -1855,12 +1855,12 @@
     <row r="13" ht="42" customHeight="1">
       <c r="A13" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T20:13:43+09:00</t>
         </is>
       </c>
       <c r="B13" s="75" t="inlineStr">
         <is>
-          <t>2026-07-25T13:00:43Z</t>
+          <t>2026-07-23T11:30:07Z</t>
         </is>
       </c>
       <c r="C13" s="60" t="inlineStr">
@@ -1870,16 +1870,16 @@
       </c>
       <c r="D13" s="60" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="E13" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence | Robotics</t>
+          <t>Robotics | Innovation Policy</t>
         </is>
       </c>
       <c r="F13" s="76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G13" s="60" t="inlineStr">
         <is>
@@ -1888,32 +1888,32 @@
       </c>
       <c r="H13" s="60" t="inlineStr">
         <is>
-          <t>The Guardian Technology</t>
+          <t>South China Morning Post Technology</t>
         </is>
       </c>
       <c r="I13" s="60" t="inlineStr">
         <is>
-          <t>AIによる雇用の終焉はすぐには訪れない</t>
+          <t>米国、中国製ヒューマノイドロボットの禁止を検討</t>
         </is>
       </c>
       <c r="J13" s="60" t="inlineStr">
         <is>
-          <t>Anthropic社の分析によれば、人工知能が人間の労働需要を根本的に変えるという主張には疑問が残る。AIがエントリーレベルの仕事を半減させるという予測は過大評価であり、実際の影響は限定的である可能性が高い。</t>
+          <t>米国の議会は、中国製のヒューマノイドロボットの軍事利用を禁止する防衛法案を進めており、国家安全保障やデータプライバシーの懸念から外国の自律システムの使用を制限する内容が含まれている。</t>
         </is>
       </c>
       <c r="K13" s="60" t="inlineStr">
         <is>
-          <t>https://www.theguardian.com/technology/2026/jul/25/ai-jobs-apocalypse-human-labor</t>
+          <t>https://www.scmp.com/tech/policy/article/3361622/us-eyes-ban-chinese-humanoid-robots-us-china-tech-rivalry-intensifies?utm_source=rss_feed</t>
         </is>
       </c>
       <c r="L13" s="60" t="inlineStr">
         <is>
-          <t>144f9038d6abd12e69ae1122</t>
+          <t>17c856708cfe91897e9a7d7c</t>
         </is>
       </c>
       <c r="M13" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T20:13:43+09:00</t>
         </is>
       </c>
       <c r="N13" s="60" t="inlineStr">
@@ -1926,17 +1926,17 @@
     <row r="14" ht="42" customHeight="1">
       <c r="A14" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:51:39+09:00</t>
+          <t>2026-07-26T20:13:43+09:00</t>
         </is>
       </c>
       <c r="B14" s="75" t="inlineStr">
         <is>
-          <t>2026-07-25T13:00:08Z</t>
+          <t>2026-07-23T10:00:17Z</t>
         </is>
       </c>
       <c r="C14" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="D14" s="60" t="inlineStr">
@@ -1964,27 +1964,27 @@
       </c>
       <c r="I14" s="60" t="inlineStr">
         <is>
-          <t>スーパーノードとは何か、そして中国と米国の技術競争における重要性</t>
+          <t>中国のテクノロジー企業、国内競争を背景にAIブームをチャンスに変える</t>
         </is>
       </c>
       <c r="J14" s="60" t="inlineStr">
         <is>
-          <t>人工知能モデルのサイズが1兆パラメータを超える中、中国のAIサミットである世界人工知能会議（WAIC）では、複数のチップを結合して一つの巨大なスーパーコンピュータとして機能する新しいハードウェア「スーパーノード」が紹介された。これは、AIインフラの進化を示す重要な動きである。</t>
+          <t>中国のテクノロジー企業は、AIへの投資が急増する中、国内の激しい競争を背景に国際的な展開を加速させている。特にクラウドベースのソフトウェアや基盤モデルを通じて、物理的な供給チェーンだけでなく、テクノロジーの輸出も増加している。</t>
         </is>
       </c>
       <c r="K14" s="60" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/tech/article/3361562/what-supernode-and-why-does-it-matter-china-us-tech-rivalry?utm_source=rss_feed</t>
+          <t>https://www.scmp.com/tech/tech-trends/article/3361596/chinas-tech-firms-turn-global-ai-boom-opportunity-amid-fierce-rivalry-home?utm_source=rss_feed</t>
         </is>
       </c>
       <c r="L14" s="60" t="inlineStr">
         <is>
-          <t>4e5989e812e0089b587f2c6b</t>
+          <t>2d5de96218ebc1a4b06e4e7c</t>
         </is>
       </c>
       <c r="M14" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:51:39+09:00</t>
+          <t>2026-07-26T20:13:43+09:00</t>
         </is>
       </c>
       <c r="N14" s="60" t="inlineStr">
@@ -1997,65 +1997,65 @@
     <row r="15" ht="42" customHeight="1">
       <c r="A15" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:10:55+09:00</t>
+          <t>2026-07-26T18:56:03+09:00</t>
         </is>
       </c>
       <c r="B15" s="75" t="inlineStr">
         <is>
-          <t>2026-07-25T11:12:11Z</t>
+          <t>2026-07-23T09:23:23Z</t>
         </is>
       </c>
       <c r="C15" s="60" t="inlineStr">
         <is>
-          <t>Middle East</t>
+          <t>EU &amp; Europe</t>
         </is>
       </c>
       <c r="D15" s="60" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="E15" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Innovation Policy</t>
         </is>
       </c>
       <c r="F15" s="76" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G15" s="60" t="inlineStr">
         <is>
-          <t>Major Media</t>
+          <t>Policy Institute</t>
         </is>
       </c>
       <c r="H15" s="60" t="inlineStr">
         <is>
-          <t>The National Technology</t>
+          <t>Bruegel</t>
         </is>
       </c>
       <c r="I15" s="60" t="inlineStr">
         <is>
-          <t>リスクのある賭け：OpenAI-Hugging Faceハッキング事件の勝者と敗者</t>
+          <t>EUの規制改善が競争力をもたらすか？</t>
         </is>
       </c>
       <c r="J15" s="60" t="inlineStr">
         <is>
-          <t>OpenAIのAIモデルがセキュリティテスト中にハッキングを行った事件が発覚。OpenAIとHugging FaceはPRの面で大きな打撃を受けた。</t>
+          <t>EUの規制改善が競争力に与える影響についてのセッションが行われ、政策の重要性が議論されています。</t>
         </is>
       </c>
       <c r="K15" s="60" t="inlineStr">
         <is>
-          <t>https://www.thenationalnews.com/future/technology/2026/07/25/risky-bet-the-winners-and-losers-from-the-openai-hugging-face-hacking-mess/</t>
+          <t>https://www.bruegel.org/node/12451</t>
         </is>
       </c>
       <c r="L15" s="60" t="inlineStr">
         <is>
-          <t>ae772fcc12d71afd038c86c2</t>
+          <t>90ef16bcfe1bd00925658dc5</t>
         </is>
       </c>
       <c r="M15" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:10:55+09:00</t>
+          <t>2026-07-26T18:56:03+09:00</t>
         </is>
       </c>
       <c r="N15" s="60" t="inlineStr">
@@ -2073,55 +2073,55 @@
       </c>
       <c r="B16" s="75" t="inlineStr">
         <is>
-          <t>2026-07-25T05:00:35Z</t>
+          <t>2026-07-23T02:00:46Z</t>
         </is>
       </c>
       <c r="C16" s="60" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D16" s="60" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E16" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Semiconductors &amp; Telecom</t>
         </is>
       </c>
       <c r="F16" s="76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16" s="60" t="inlineStr">
         <is>
-          <t>Major Media</t>
+          <t>Official Company</t>
         </is>
       </c>
       <c r="H16" s="60" t="inlineStr">
         <is>
-          <t>The Guardian Technology</t>
+          <t>NVIDIA Blog</t>
         </is>
       </c>
       <c r="I16" s="60" t="inlineStr">
         <is>
-          <t>AIで再会した家族：ChatGPTの力</t>
+          <t>NVIDIAのAIスパコンが海軍大学校で稼働開始</t>
         </is>
       </c>
       <c r="J16" s="60" t="inlineStr">
         <is>
-          <t>Avtarは母親を知らずに過ごし、ChatGPTを通じて長年の謎を解明。AIが彼と半兄を再会させた経緯が語られている。</t>
+          <t>NVIDIAの創業者が海軍大学校を訪れ、強力なAIプラットフォームを導入しました。これにより、学生や研究者が最新の技術を活用できる環境が整います。</t>
         </is>
       </c>
       <c r="K16" s="60" t="inlineStr">
         <is>
-          <t>https://www.theguardian.com/lifeandstyle/ng-interactive/2026/jul/25/long-lost-family-reunited-chatgpt-artificial-intelligence-ai</t>
+          <t>https://blogs.nvidia.com/blog/naval-postgraduate-school-dgx-ai-supercomputer/</t>
         </is>
       </c>
       <c r="L16" s="60" t="inlineStr">
         <is>
-          <t>818d7fcb63b548448b301aec</t>
+          <t>c174fc131c4d55cb839833e9</t>
         </is>
       </c>
       <c r="M16" s="75" t="inlineStr">
@@ -2139,17 +2139,17 @@
     <row r="17" ht="42" customHeight="1">
       <c r="A17" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T19:05:06+09:00</t>
         </is>
       </c>
       <c r="B17" s="75" t="inlineStr">
         <is>
-          <t>2026-07-24T18:00:01Z</t>
+          <t>2026-07-23T00:00:00Z</t>
         </is>
       </c>
       <c r="C17" s="60" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D17" s="60" t="inlineStr">
@@ -2159,45 +2159,45 @@
       </c>
       <c r="E17" s="60" t="inlineStr">
         <is>
-          <t>Semiconductors &amp; Telecom</t>
+          <t>Innovation Policy</t>
         </is>
       </c>
       <c r="F17" s="76" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G17" s="60" t="inlineStr">
         <is>
-          <t>Major Media</t>
+          <t>Policy Institute</t>
         </is>
       </c>
       <c r="H17" s="60" t="inlineStr">
         <is>
-          <t>IEEE Spectrum</t>
+          <t>Brookings TechTank</t>
         </is>
       </c>
       <c r="I17" s="60" t="inlineStr">
         <is>
-          <t>2022年IEEE会長K.J.レイ・リウがリーダーシップで表彰</t>
+          <t>技術企業が雇用問題とスキル開発にどのように対処すべきか</t>
         </is>
       </c>
       <c r="J17" s="60" t="inlineStr">
         <is>
-          <t>K.J.レイ・リウは、台湾の半導体産業の発展に寄与した功績が評価され、IEEEのリーダーシップ賞を受賞した。</t>
+          <t>技術企業が直面する雇用問題とスキル開発に関する提言が行われ、政策的な視点からのアプローチが求められています。</t>
         </is>
       </c>
       <c r="K17" s="60" t="inlineStr">
         <is>
-          <t>https://spectrum.ieee.org/ieee-president-ray-liu-award</t>
+          <t>https://www.brookings.edu/articles/how-tech-firms-should-address-job-concerns-and-skill-development/</t>
         </is>
       </c>
       <c r="L17" s="60" t="inlineStr">
         <is>
-          <t>87b839503197ad74fc686cf1</t>
+          <t>0d48c18a0657c35e8abe7133</t>
         </is>
       </c>
       <c r="M17" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T19:05:06+09:00</t>
         </is>
       </c>
       <c r="N17" s="60" t="inlineStr">
@@ -2210,65 +2210,65 @@
     <row r="18" ht="42" customHeight="1">
       <c r="A18" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:10:55+09:00</t>
+          <t>2026-07-26T18:56:03+09:00</t>
         </is>
       </c>
       <c r="B18" s="75" t="inlineStr">
         <is>
-          <t>2026-07-24T17:32:29Z</t>
+          <t>2026-07-23T00:00:00Z</t>
         </is>
       </c>
       <c r="C18" s="60" t="inlineStr">
         <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="D18" s="60" t="inlineStr">
+        <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="D18" s="60" t="inlineStr">
-        <is>
-          <t>United Arab Emirates</t>
-        </is>
-      </c>
       <c r="E18" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Artificial Intelligence | Healthcare</t>
         </is>
       </c>
       <c r="F18" s="76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18" s="60" t="inlineStr">
         <is>
-          <t>Major Media</t>
+          <t>Official Company</t>
         </is>
       </c>
       <c r="H18" s="60" t="inlineStr">
         <is>
-          <t>The National Technology</t>
+          <t>OpenAI News</t>
         </is>
       </c>
       <c r="I18" s="60" t="inlineStr">
         <is>
-          <t>Nvidia、Microsoft、IBMがオープンウェイトAIモデルを支持</t>
+          <t>ChatGPTにおける健康機能の導入</t>
         </is>
       </c>
       <c r="J18" s="60" t="inlineStr">
         <is>
-          <t>NvidiaのCEOが、ダウンロード可能で適応可能なAIモデルの重要性を強調し、25社の署名を添えた。オープンソース開発の支持が、アメリカのAIリーダーシップを維持するために必要だと述べている。</t>
+          <t>ChatGPTが米国のユーザー向けに医療記録とApple Healthを安全に接続し、個別化された健康情報を提供する新機能を発表しました。</t>
         </is>
       </c>
       <c r="K18" s="60" t="inlineStr">
         <is>
-          <t>https://www.thenationalnews.com/future/technology/2026/07/24/open-weight-models-ai-nvidia/</t>
+          <t>https://openai.com/index/health-in-chatgpt</t>
         </is>
       </c>
       <c r="L18" s="60" t="inlineStr">
         <is>
-          <t>258e9b19598256f555ff9019</t>
+          <t>bf70d809f9542eeef4af8727</t>
         </is>
       </c>
       <c r="M18" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:10:55+09:00</t>
+          <t>2026-07-26T18:56:03+09:00</t>
         </is>
       </c>
       <c r="N18" s="60" t="inlineStr">
@@ -2286,55 +2286,55 @@
       </c>
       <c r="B19" s="75" t="inlineStr">
         <is>
-          <t>2026-07-24T17:03:55Z</t>
+          <t>2026-07-22T14:21:46Z</t>
         </is>
       </c>
       <c r="C19" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>EU &amp; Europe</t>
         </is>
       </c>
       <c r="D19" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="E19" s="60" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Innovation Policy</t>
         </is>
       </c>
       <c r="F19" s="76" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G19" s="60" t="inlineStr">
         <is>
-          <t>Major Media</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H19" s="60" t="inlineStr">
         <is>
-          <t>MIT Technology Review</t>
+          <t>UK DSIT</t>
         </is>
       </c>
       <c r="I19" s="60" t="inlineStr">
         <is>
-          <t>体外で臓器を生かし続けるための探求</t>
+          <t>研究における女性のための憲章に関するガイダンス</t>
         </is>
       </c>
       <c r="J19" s="60" t="inlineStr">
         <is>
-          <t>臓器提供の不足を解消するため、体外での臓器保存に関する取り組みが進められている。臓器は数時間しか生存できず、医師たちは臓器バンクの実現を夢見ている。</t>
+          <t>英国の研究システムにおける女性の成果を改善するための自主的な取り組みが提案され、研究資金提供者や研究機関に対する具体的な行動が示されています。</t>
         </is>
       </c>
       <c r="K19" s="60" t="inlineStr">
         <is>
-          <t>https://www.technologyreview.com/2026/07/24/1140790/the-quest-to-keep-organs-alive-outside-the-body/</t>
+          <t>https://www.gov.uk/government/publications/women-in-research-charter</t>
         </is>
       </c>
       <c r="L19" s="60" t="inlineStr">
         <is>
-          <t>039c84226e8803400ce67975</t>
+          <t>1e9fd9033d38bacea37c0f42</t>
         </is>
       </c>
       <c r="M19" s="75" t="inlineStr">
@@ -2352,17 +2352,17 @@
     <row r="20" ht="42" customHeight="1">
       <c r="A20" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T19:05:06+09:00</t>
         </is>
       </c>
       <c r="B20" s="75" t="inlineStr">
         <is>
-          <t>2026-07-24T16:46:59Z</t>
+          <t>2026-07-22T14:12:14Z</t>
         </is>
       </c>
       <c r="C20" s="60" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D20" s="60" t="inlineStr">
@@ -2372,45 +2372,45 @@
       </c>
       <c r="E20" s="60" t="inlineStr">
         <is>
-          <t>Semiconductors &amp; Telecom</t>
+          <t>Innovation Policy</t>
         </is>
       </c>
       <c r="F20" s="76" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G20" s="60" t="inlineStr">
         <is>
-          <t>Official Company</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H20" s="60" t="inlineStr">
         <is>
-          <t>Intel Newsroom</t>
+          <t>DOE Office of Science News</t>
         </is>
       </c>
       <c r="I20" s="60" t="inlineStr">
         <is>
-          <t>インテルとレンズテクノロジーがAI時代の半導体パッケージングを推進するために協力</t>
+          <t>エネルギー長官クリス・ライトがAI駆動の科学的発見を加速するための最初のジェネシスミッションプロジェクトを発表</t>
         </is>
       </c>
       <c r="J20" s="60" t="inlineStr">
         <is>
-          <t>インテルとレンズテクノロジーは、先進的な半導体パッケージング技術の開発を目指す戦略的な協力を発表。ガラス基板を用いたパッケージングソリューションの開発を加速することを目指している。</t>
+          <t>エネルギー省は、全米から選ばれた約300のプロジェクトを発表し、エネルギー、発見科学、国家安全保障におけるブレークスルーを加速することを目指しています。</t>
         </is>
       </c>
       <c r="K20" s="60" t="inlineStr">
         <is>
-          <t>https://newsroom.intel.com/new-technologies/intel-and-lens-technology-collaborate-to-enable-advanced-semiconductor-packaging-for-the-ai-era</t>
+          <t>https://www.energy.gov/articles/secretary-energy-chris-wright-announces-first-genesis-mission-projects-selected-accelerate</t>
         </is>
       </c>
       <c r="L20" s="60" t="inlineStr">
         <is>
-          <t>10eedf14d7d6b636e24e447d</t>
+          <t>23fa1d6907c14d73ce3a41cd</t>
         </is>
       </c>
       <c r="M20" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T19:05:06+09:00</t>
         </is>
       </c>
       <c r="N20" s="60" t="inlineStr">
@@ -2428,22 +2428,22 @@
       </c>
       <c r="B21" s="75" t="inlineStr">
         <is>
-          <t>2026-07-24T15:25:30Z</t>
+          <t>2026-07-22T14:12:00Z</t>
         </is>
       </c>
       <c r="C21" s="60" t="inlineStr">
         <is>
-          <t>EU &amp; Europe</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D21" s="60" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E21" s="60" t="inlineStr">
         <is>
-          <t>Innovation Policy</t>
+          <t>Innovation Policy | Artificial Intelligence</t>
         </is>
       </c>
       <c r="F21" s="76" t="n">
@@ -2451,32 +2451,32 @@
       </c>
       <c r="G21" s="60" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Policy Institute</t>
         </is>
       </c>
       <c r="H21" s="60" t="inlineStr">
         <is>
-          <t>UK DSIT</t>
+          <t>CSET</t>
         </is>
       </c>
       <c r="I21" s="60" t="inlineStr">
         <is>
-          <t>サイバー耐性誓約：署名者リスト</t>
+          <t>人工知能と核戦争に関するグローバルノーベル賞受賞者会議での発言</t>
         </is>
       </c>
       <c r="J21" s="60" t="inlineStr">
         <is>
-          <t>サイバー耐性誓約に署名した組織のリストが公開された。</t>
+          <t>CSETのシニアフェローがAIと核戦争に関する会議での経験を共有。</t>
         </is>
       </c>
       <c r="K21" s="60" t="inlineStr">
         <is>
-          <t>https://www.gov.uk/government/publications/cyber-resilience-pledge-list-of-signatories</t>
+          <t>https://cset.georgetown.edu/article/remarks-at-the-global-nobel-laureates-assembly-on-artificial-intelligence-and-nuclear-war/</t>
         </is>
       </c>
       <c r="L21" s="60" t="inlineStr">
         <is>
-          <t>556f1cad5674dfe48a261c54</t>
+          <t>863086979e9f7f63c082cb57</t>
         </is>
       </c>
       <c r="M21" s="75" t="inlineStr">
@@ -2494,17 +2494,17 @@
     <row r="22" ht="42" customHeight="1">
       <c r="A22" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:51:39+09:00</t>
+          <t>2026-07-26T18:56:03+09:00</t>
         </is>
       </c>
       <c r="B22" s="75" t="inlineStr">
         <is>
-          <t>2026-07-24T13:00:14Z</t>
+          <t>2026-07-22T13:58:00Z</t>
         </is>
       </c>
       <c r="C22" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>EU &amp; Europe</t>
         </is>
       </c>
       <c r="D22" s="60" t="inlineStr">
@@ -2514,45 +2514,45 @@
       </c>
       <c r="E22" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Innovation Policy</t>
         </is>
       </c>
       <c r="F22" s="76" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G22" s="60" t="inlineStr">
         <is>
-          <t>Major Media</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H22" s="60" t="inlineStr">
         <is>
-          <t>The Guardian Technology</t>
+          <t>UK DSIT</t>
         </is>
       </c>
       <c r="I22" s="60" t="inlineStr">
         <is>
-          <t>OpenAIのハッカーエージェントの話に懐疑的であるべき</t>
+          <t>ガイダンス：Consultの利用登録</t>
         </is>
       </c>
       <c r="J22" s="60" t="inlineStr">
         <is>
-          <t>OpenAIがAIの危険性を強調することで、投資家はその力を認識する。GPT-2のリリースを控えた当時の懸念について、著者は過剰なリスク評価だと感じていた。</t>
+          <t>政府チームが公共の意見を分析するためのAIツールConsultの利用登録を呼びかけ。</t>
         </is>
       </c>
       <c r="K22" s="60" t="inlineStr">
         <is>
-          <t>https://www.theguardian.com/technology/2026/jul/24/openai-rogue-hacker</t>
+          <t>https://www.gov.uk/government/publications/consult-register-your-interest</t>
         </is>
       </c>
       <c r="L22" s="60" t="inlineStr">
         <is>
-          <t>ac01b28f85e133214755b7cc</t>
+          <t>a651f42eb5805e39f03fbebe</t>
         </is>
       </c>
       <c r="M22" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:51:39+09:00</t>
+          <t>2026-07-26T18:56:03+09:00</t>
         </is>
       </c>
       <c r="N22" s="60" t="inlineStr">
@@ -2565,65 +2565,65 @@
     <row r="23" ht="42" customHeight="1">
       <c r="A23" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T19:05:06+09:00</t>
         </is>
       </c>
       <c r="B23" s="75" t="inlineStr">
         <is>
-          <t>2026-07-24T12:00:14Z</t>
+          <t>2026-07-22T13:53:19Z</t>
         </is>
       </c>
       <c r="C23" s="60" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D23" s="60" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E23" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Innovation Policy | Artificial Intelligence</t>
         </is>
       </c>
       <c r="F23" s="76" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G23" s="60" t="inlineStr">
         <is>
-          <t>Major Media</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H23" s="60" t="inlineStr">
         <is>
-          <t>The Guardian Technology</t>
+          <t>National Science Foundation News</t>
         </is>
       </c>
       <c r="I23" s="60" t="inlineStr">
         <is>
-          <t>AIをタスクに使用すべきか？シンプルな判断方法</t>
+          <t>NSF長官代理によるAI優先事項の推進に関する声明</t>
         </is>
       </c>
       <c r="J23" s="60" t="inlineStr">
         <is>
-          <t>ハーバード・ケネディスクールのブルース・シュナイアー教授は、AIを利用することの是非について考察。学生がAIを使って課題を完成させることが多いが、それが教育費の無駄になる可能性があると警告している。</t>
+          <t>米国国立科学財団がホワイトハウスと連携し、AIに関する優先事項を推進することを発表。</t>
         </is>
       </c>
       <c r="K23" s="60" t="inlineStr">
         <is>
-          <t>https://www.theguardian.com/commentisfree/2026/jul/24/should-you-use-ai</t>
+          <t>https://www.nsf.gov/news/statement-nsf-chief-staff-brian-stone-performing-duties-nsf-1</t>
         </is>
       </c>
       <c r="L23" s="60" t="inlineStr">
         <is>
-          <t>d7259db0d54f48b0f5039bb8</t>
+          <t>123e2207578ca69c8f9c00a2</t>
         </is>
       </c>
       <c r="M23" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T19:05:06+09:00</t>
         </is>
       </c>
       <c r="N23" s="60" t="inlineStr">
@@ -2636,65 +2636,65 @@
     <row r="24" ht="42" customHeight="1">
       <c r="A24" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:10:55+09:00</t>
+          <t>2026-07-26T19:05:06+09:00</t>
         </is>
       </c>
       <c r="B24" s="75" t="inlineStr">
         <is>
-          <t>2026-07-24T11:39:05Z</t>
+          <t>2026-07-22T13:53:12Z</t>
         </is>
       </c>
       <c r="C24" s="60" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D24" s="60" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E24" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Innovation Policy | Artificial Intelligence</t>
         </is>
       </c>
       <c r="F24" s="76" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G24" s="60" t="inlineStr">
         <is>
-          <t>Major Media</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H24" s="60" t="inlineStr">
         <is>
-          <t>The National Technology</t>
+          <t>National Science Foundation News</t>
         </is>
       </c>
       <c r="I24" s="60" t="inlineStr">
         <is>
-          <t>Zoomがライブ音声翻訳サービスを開始、アラビア語は2026年末に対応</t>
+          <t>新しいNSFイニシアチブがAIによる科学的発見のためのデータセットの価値を解放</t>
         </is>
       </c>
       <c r="J24" s="60" t="inlineStr">
         <is>
-          <t>Zoom Technologiesは新たにライブ音声翻訳サービスを開始し、初めは英語、中国語、フランス語、日本語、スペイン語の5言語が利用可能。アラビア語は2026年末に追加される予定で、ドイツ語、イタリア語、ポルトガル語も同時に対応する。</t>
+          <t>米国国立科学財団がAIを活用した科学的発見を促進するための新しいプログラムを発表。</t>
         </is>
       </c>
       <c r="K24" s="60" t="inlineStr">
         <is>
-          <t>https://www.thenationalnews.com/future/technology/2026/07/24/zoom-launches-live-voice-translation-with-arabic-coming-in-late-2026/</t>
+          <t>https://www.nsf.gov/news/new-nsf-initiative-aims-unlock-dataset-value-ai-enabled</t>
         </is>
       </c>
       <c r="L24" s="60" t="inlineStr">
         <is>
-          <t>9df818f0442aeef1a46447c7</t>
+          <t>dcd819527d9b80141b26bcb8</t>
         </is>
       </c>
       <c r="M24" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:10:55+09:00</t>
+          <t>2026-07-26T19:05:06+09:00</t>
         </is>
       </c>
       <c r="N24" s="60" t="inlineStr">
@@ -2707,17 +2707,17 @@
     <row r="25" ht="42" customHeight="1">
       <c r="A25" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T19:05:06+09:00</t>
         </is>
       </c>
       <c r="B25" s="75" t="inlineStr">
         <is>
-          <t>2026-07-24T04:34:27Z</t>
+          <t>2026-07-22T13:53:06Z</t>
         </is>
       </c>
       <c r="C25" s="60" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D25" s="60" t="inlineStr">
@@ -2727,45 +2727,45 @@
       </c>
       <c r="E25" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence | Semiconductors &amp; Telecom</t>
+          <t>Innovation Policy</t>
         </is>
       </c>
       <c r="F25" s="76" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G25" s="60" t="inlineStr">
         <is>
-          <t>Official Company</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H25" s="60" t="inlineStr">
         <is>
-          <t>NVIDIA Blog</t>
+          <t>National Science Foundation News</t>
         </is>
       </c>
       <c r="I25" s="60" t="inlineStr">
         <is>
-          <t>AIサミットで韓国がAIの未来を描く</t>
+          <t>NSFがAI駆動の科学を進めるために8300万ドルの投資を発表</t>
         </is>
       </c>
       <c r="J25" s="60" t="inlineStr">
         <is>
-          <t>韓国の李在明大統領がサンフランシスコで開催されたAIサミットで、NVIDIAやパートナーと共に韓国のAIの進展を議論した。</t>
+          <t>米国国立科学財団が8300万ドルの助成金を発表し、研究者がデータインフラを利用できるようにする。</t>
         </is>
       </c>
       <c r="K25" s="60" t="inlineStr">
         <is>
-          <t>https://blogs.nvidia.com/blog/ai-summit-korea-partners-and-nvidia/</t>
+          <t>https://www.nsf.gov/news/nsf-announces-83m-investment-integrated-data-systems</t>
         </is>
       </c>
       <c r="L25" s="60" t="inlineStr">
         <is>
-          <t>3124530844eb0ac80a5a17e4</t>
+          <t>018d40b7e6eb7aa4b8cfb5fa</t>
         </is>
       </c>
       <c r="M25" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T19:05:06+09:00</t>
         </is>
       </c>
       <c r="N25" s="60" t="inlineStr">
@@ -2783,7 +2783,7 @@
       </c>
       <c r="B26" s="75" t="inlineStr">
         <is>
-          <t>2026-07-24T00:00:00Z</t>
+          <t>2026-07-22T13:00:00Z</t>
         </is>
       </c>
       <c r="C26" s="60" t="inlineStr">
@@ -2793,7 +2793,7 @@
       </c>
       <c r="D26" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E26" s="60" t="inlineStr">
@@ -2802,36 +2802,36 @@
         </is>
       </c>
       <c r="F26" s="76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26" s="60" t="inlineStr">
         <is>
-          <t>Scientific Publication</t>
+          <t>Official Company</t>
         </is>
       </c>
       <c r="H26" s="60" t="inlineStr">
         <is>
-          <t>Nature</t>
+          <t>OpenAI News</t>
         </is>
       </c>
       <c r="I26" s="60" t="inlineStr">
         <is>
-          <t>新たな化石が示すベビーT. rexの捕食者としての特性</t>
+          <t>エフィンガム郡コミュニティとのAIインフラ構築</t>
         </is>
       </c>
       <c r="J26" s="60" t="inlineStr">
         <is>
-          <t>新たに発見された化石が、ベビーT. rexが誕生時から捕食者であった可能性を示唆している。</t>
+          <t>OpenAIがエフィンガム郡でプロジェクトを発表し、責任あるエネルギー、地域投資、雇用、Codexへのアクセスを約束。</t>
         </is>
       </c>
       <c r="K26" s="60" t="inlineStr">
         <is>
-          <t>https://www.nature.com/articles/d41586-026-02338-2</t>
+          <t>https://openai.com/index/building-ai-infrastructure-with-the-effingham-county-community</t>
         </is>
       </c>
       <c r="L26" s="60" t="inlineStr">
         <is>
-          <t>d9ad7c48684afc35a7223f91</t>
+          <t>082c4173c70b04519142ea2a</t>
         </is>
       </c>
       <c r="M26" s="75" t="inlineStr">
@@ -2854,7 +2854,7 @@
       </c>
       <c r="B27" s="75" t="inlineStr">
         <is>
-          <t>2026-07-24T00:00:00Z</t>
+          <t>2026-07-22T13:00:00Z</t>
         </is>
       </c>
       <c r="C27" s="60" t="inlineStr">
@@ -2864,45 +2864,45 @@
       </c>
       <c r="D27" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E27" s="60" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="F27" s="76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G27" s="60" t="inlineStr">
         <is>
-          <t>Scientific Publication</t>
+          <t>Official Company</t>
         </is>
       </c>
       <c r="H27" s="60" t="inlineStr">
         <is>
-          <t>Nature</t>
+          <t>OpenAI News</t>
         </is>
       </c>
       <c r="I27" s="60" t="inlineStr">
         <is>
-          <t>CRISPR酵素が癌細胞をDNAを破壊して殺す</t>
+          <t>ニュース組織がAIを活用して重要な使命を推進</t>
         </is>
       </c>
       <c r="J27" s="60" t="inlineStr">
         <is>
-          <t>新たなCRISPR酵素が、癌細胞のDNAを破壊することで癌細胞を殺す可能性があることが初期のテストで示された。</t>
+          <t>ニュース組織がAIを利用して報道を強化し、オーディエンスを拡大し、ビジネス運営を改善している。</t>
         </is>
       </c>
       <c r="K27" s="60" t="inlineStr">
         <is>
-          <t>https://www.nature.com/articles/d41586-026-02268-z</t>
+          <t>https://openai.com/index/how-news-organizations-are-using-ai</t>
         </is>
       </c>
       <c r="L27" s="60" t="inlineStr">
         <is>
-          <t>006500c385193d3a42b6ae61</t>
+          <t>932591afba7f1cf55372f3f4</t>
         </is>
       </c>
       <c r="M27" s="75" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="B28" s="75" t="inlineStr">
         <is>
-          <t>2026-07-23T20:01:35Z</t>
+          <t>2026-07-22T12:00:00Z</t>
         </is>
       </c>
       <c r="C28" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D28" s="60" t="inlineStr">
@@ -2940,40 +2940,40 @@
       </c>
       <c r="E28" s="60" t="inlineStr">
         <is>
-          <t>Semiconductors &amp; Telecom</t>
+          <t>Innovation Policy</t>
         </is>
       </c>
       <c r="F28" s="76" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G28" s="60" t="inlineStr">
         <is>
-          <t>Official Company</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H28" s="60" t="inlineStr">
         <is>
-          <t>Intel Newsroom</t>
+          <t>NIST News</t>
         </is>
       </c>
       <c r="I28" s="60" t="inlineStr">
         <is>
-          <t>インテル、2026年第2四半期の財務結果を報告</t>
+          <t>NIST、米国の中小製造業者を支援するための資金提供機会を発表</t>
         </is>
       </c>
       <c r="J28" s="60" t="inlineStr">
         <is>
-          <t>インテルは、2026年第2四半期の財務結果を発表し、投資家向けのカンファレンスコールを開催する予定である。</t>
+          <t>NIST MEPは、米国の中小製造業者を支援するための資金提供機会についての情報ウェビナーを開催します。</t>
         </is>
       </c>
       <c r="K28" s="60" t="inlineStr">
         <is>
-          <t>https://newsroom.intel.com/corporate/intel-reports-second-quarter-2026-financial-results</t>
+          <t>https://www.nist.gov/news-events/news/2026/07/nist-announces-funding-opportunity-14-mep-centers-advance-small-and-medium</t>
         </is>
       </c>
       <c r="L28" s="60" t="inlineStr">
         <is>
-          <t>bd78c44bc1aa5dc9d72bde44</t>
+          <t>5aa9c93bc7040291c9f08bfa</t>
         </is>
       </c>
       <c r="M28" s="75" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="B29" s="75" t="inlineStr">
         <is>
-          <t>2026-07-23T19:56:50Z</t>
+          <t>2026-07-22T12:00:00Z</t>
         </is>
       </c>
       <c r="C29" s="60" t="inlineStr">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="D29" s="60" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E29" s="60" t="inlineStr">
@@ -3015,36 +3015,36 @@
         </is>
       </c>
       <c r="F29" s="76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G29" s="60" t="inlineStr">
         <is>
-          <t>Major Media</t>
+          <t>Official Company</t>
         </is>
       </c>
       <c r="H29" s="60" t="inlineStr">
         <is>
-          <t>The Guardian Technology</t>
+          <t>OpenAI News</t>
         </is>
       </c>
       <c r="I29" s="60" t="inlineStr">
         <is>
-          <t>トランプ、データセンターのコスト保護に関する誓約を発表</t>
+          <t>国家科学の次の時代を進める</t>
         </is>
       </c>
       <c r="J29" s="60" t="inlineStr">
         <is>
-          <t>トランプは、約200の企業がAIデータセンターの建設に伴うコストからアメリカの消費者を保護するという非拘束的な誓約に署名したと発表した。</t>
+          <t>OpenAIは、米国エネルギー省や国立研究所と協力し、フロンティアAIを活用して発見を加速することにコミットしています。</t>
         </is>
       </c>
       <c r="K29" s="60" t="inlineStr">
         <is>
-          <t>https://www.theguardian.com/us-news/2026/jul/23/trump-datacenter-costs-big-tech</t>
+          <t>https://openai.com/index/advancing-the-next-era-of-national-science</t>
         </is>
       </c>
       <c r="L29" s="60" t="inlineStr">
         <is>
-          <t>1ede7beb496d94bde434264e</t>
+          <t>577ddf6b90e6d70b43383fc6</t>
         </is>
       </c>
       <c r="M29" s="75" t="inlineStr">
@@ -3067,26 +3067,26 @@
       </c>
       <c r="B30" s="75" t="inlineStr">
         <is>
-          <t>2026-07-23T18:00:00Z</t>
+          <t>2026-07-22T05:30:00Z</t>
         </is>
       </c>
       <c r="C30" s="60" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D30" s="60" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E30" s="60" t="inlineStr">
         <is>
-          <t>Semiconductors &amp; Telecom</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="F30" s="76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G30" s="60" t="inlineStr">
         <is>
@@ -3095,27 +3095,27 @@
       </c>
       <c r="H30" s="60" t="inlineStr">
         <is>
-          <t>Samsung Global Newsroom</t>
+          <t>OpenAI News</t>
         </is>
       </c>
       <c r="I30" s="60" t="inlineStr">
         <is>
-          <t>Galaxy Unpackedのハイライト</t>
+          <t>OpenAI Presenceの紹介</t>
         </is>
       </c>
       <c r="J30" s="60" t="inlineStr">
         <is>
-          <t>サムスンは、ロンドンで開催されたGalaxy Unpacked July 2026で、次世代の折りたたみ式デバイスや健康機能を強化したスマートウォッチを発表した。新しいAI技術を搭載した製品が紹介された。</t>
+          <t>OpenAI Presenceは、組織が信頼できる音声およびチャットエージェントを展開するための企業向けAIエージェントプラットフォームです。</t>
         </is>
       </c>
       <c r="K30" s="60" t="inlineStr">
         <is>
-          <t>https://news.samsung.com/global/infographic-galaxy-unpacked-july-2026-highlights-from-galaxy-unpacked</t>
+          <t>https://openai.com/index/introducing-openai-presence</t>
         </is>
       </c>
       <c r="L30" s="60" t="inlineStr">
         <is>
-          <t>ee2b658cb0dfffbcc854ebab</t>
+          <t>839f7a51d7b587ae6fb6fad7</t>
         </is>
       </c>
       <c r="M30" s="75" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="B31" s="75" t="inlineStr">
         <is>
-          <t>2026-07-23T16:58:28Z</t>
+          <t>2026-07-22T00:00:00Z</t>
         </is>
       </c>
       <c r="C31" s="60" t="inlineStr">
@@ -3153,40 +3153,40 @@
       </c>
       <c r="E31" s="60" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="F31" s="76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G31" s="60" t="inlineStr">
         <is>
-          <t>Major Media</t>
+          <t>Official Company</t>
         </is>
       </c>
       <c r="H31" s="60" t="inlineStr">
         <is>
-          <t>MIT Technology Review</t>
+          <t>OpenAI News</t>
         </is>
       </c>
       <c r="I31" s="60" t="inlineStr">
         <is>
-          <t>超冷却腎臓が豚に移植される</t>
+          <t>NTTデータグループ、Codexでインシデント分析を30分に短縮</t>
         </is>
       </c>
       <c r="J31" s="60" t="inlineStr">
         <is>
-          <t>臓器提供において、時間が重要である中、超冷却された腎臓が豚に移植されるという画期的な成果が報告された。臓器の劣化を防ぐための新たな技術が期待される。</t>
+          <t>NTTデータグループは、ChatGPT EnterpriseとCodexを活用し、9,000人の従業員が業務を自動化し、インシデント分析を30分に短縮することに成功しました。</t>
         </is>
       </c>
       <c r="K31" s="60" t="inlineStr">
         <is>
-          <t>https://www.technologyreview.com/2026/07/23/1140765/supercooled-kidneys-have-been-transplanted-into-pigs-in-a-landmark-achievement/</t>
+          <t>https://openai.com/index/ntt-data</t>
         </is>
       </c>
       <c r="L31" s="60" t="inlineStr">
         <is>
-          <t>590a8cbd726d99d379ccecb1</t>
+          <t>389ebd02d2834f48054db326</t>
         </is>
       </c>
       <c r="M31" s="75" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="B32" s="75" t="inlineStr">
         <is>
-          <t>2026-07-23T16:45:56Z</t>
+          <t>2026-07-22T00:00:00Z</t>
         </is>
       </c>
       <c r="C32" s="60" t="inlineStr">
@@ -3219,45 +3219,45 @@
       </c>
       <c r="D32" s="60" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="E32" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="F32" s="76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G32" s="60" t="inlineStr">
         <is>
-          <t>Major Media</t>
+          <t>Scientific Publication</t>
         </is>
       </c>
       <c r="H32" s="60" t="inlineStr">
         <is>
-          <t>The Guardian Technology</t>
+          <t>Nature</t>
         </is>
       </c>
       <c r="I32" s="60" t="inlineStr">
         <is>
-          <t>ブリティッシュ・ガス、AIチャットボットの導入で1300人の雇用削減</t>
+          <t>サブニュクレアゲノム区画化が二価クロマチン活性を制御</t>
         </is>
       </c>
       <c r="J32" s="60" t="inlineStr">
         <is>
-          <t>ブリティッシュ・ガスの親会社Centricaは、AIチャットボットを導入することで多くの家庭がスタッフよりもチャットボットと話すことを好むと主張し、1300人の雇用を削減する計画を発表した。</t>
+          <t>遺伝子の空間的な位置を理解することは、そのエピゲノム調節を理解するために必要です。</t>
         </is>
       </c>
       <c r="K32" s="60" t="inlineStr">
         <is>
-          <t>https://www.theguardian.com/business/2026/jul/23/customers-prefer-ai-chatbots-says-chris-oshea-british-gas-centrica-boss</t>
+          <t>https://www.nature.com/articles/s41586-026-10832-w</t>
         </is>
       </c>
       <c r="L32" s="60" t="inlineStr">
         <is>
-          <t>2ef05538ad59fc3911318d3f</t>
+          <t>f9bccca3cabb5ce19441f09d</t>
         </is>
       </c>
       <c r="M32" s="75" t="inlineStr">
@@ -3280,22 +3280,22 @@
       </c>
       <c r="B33" s="75" t="inlineStr">
         <is>
-          <t>2026-07-23T16:00:00Z</t>
+          <t>2026-07-21T22:35:45Z</t>
         </is>
       </c>
       <c r="C33" s="60" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D33" s="60" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E33" s="60" t="inlineStr">
         <is>
-          <t>Semiconductors &amp; Telecom | Healthcare</t>
+          <t>Artificial Intelligence | Semiconductors &amp; Telecom</t>
         </is>
       </c>
       <c r="F33" s="76" t="n">
@@ -3308,27 +3308,27 @@
       </c>
       <c r="H33" s="60" t="inlineStr">
         <is>
-          <t>Samsung Global Newsroom</t>
+          <t>NVIDIA Blog</t>
         </is>
       </c>
       <c r="I33" s="60" t="inlineStr">
         <is>
-          <t>サムスン、デジタルヘルスの未来を描く</t>
+          <t>フォートワースにおけるウィストロンの先進製造工場開設</t>
         </is>
       </c>
       <c r="J33" s="60" t="inlineStr">
         <is>
-          <t>サムスン電子は、ロンドンで開催されたGalaxy Unpacked July 2026で、予防的かつ個別化されたデジタルヘルスの未来を提案した。医療エコシステム全体との信頼できるパートナーシップを通じて、接続された体験を提供することを目指している。</t>
+          <t>ウィストロンがテキサス州フォートワースにAIシステム用の先進製造工場を開設しました。この工場では、世界のAIシステムの中心となるスーパーチップが生産されます。</t>
         </is>
       </c>
       <c r="K33" s="60" t="inlineStr">
         <is>
-          <t>https://news.samsung.com/global/galaxy-unpacked-july-2026-samsung-and-partners-envision-a-connected-care-future-from-first-signal-to-lasting-change</t>
+          <t>https://blogs.nvidia.com/blog/wistron-manufacturing-texas/</t>
         </is>
       </c>
       <c r="L33" s="60" t="inlineStr">
         <is>
-          <t>032ebcb3943c83074eb9bcf5</t>
+          <t>21f1e1f3e19b1a5bf0af3cb7</t>
         </is>
       </c>
       <c r="M33" s="75" t="inlineStr">
@@ -3351,55 +3351,55 @@
       </c>
       <c r="B34" s="75" t="inlineStr">
         <is>
-          <t>2026-07-23T15:27:52Z</t>
+          <t>2026-07-21T19:44:19Z</t>
         </is>
       </c>
       <c r="C34" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D34" s="60" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="E34" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Innovation Policy | Fusion Energy</t>
         </is>
       </c>
       <c r="F34" s="76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G34" s="60" t="inlineStr">
         <is>
-          <t>Major Media</t>
+          <t>Industry Association</t>
         </is>
       </c>
       <c r="H34" s="60" t="inlineStr">
         <is>
-          <t>The Guardian Technology</t>
+          <t>Fusion Industry Association</t>
         </is>
       </c>
       <c r="I34" s="60" t="inlineStr">
         <is>
-          <t>イーロン・マスク、トランプとの関係を振り返る</t>
+          <t>FIAとクリーンエアタスクフォースが核融合の原則を発表</t>
         </is>
       </c>
       <c r="J34" s="60" t="inlineStr">
         <is>
-          <t>イーロン・マスクは、ドナルド・トランプとの関係において政治に没頭しすぎたと認め、企業運営にもっと集中すべきだったと語った。彼は、外国の戦争やAIに関する見解を共有し、いくつかの驚くべき予測を行った。</t>
+          <t>核融合産業協会は、クリーンエアタスクフォースと協力して、核融合のコードと基準に関する原則を発表しました。</t>
         </is>
       </c>
       <c r="K34" s="60" t="inlineStr">
         <is>
-          <t>https://www.theguardian.com/technology/2026/jul/23/elon-musk-regret-trump-doge-ai</t>
+          <t>https://www.fusionindustryassociation.org/fia-and-clean-air-task-force-publish-principles-on-codes-and-standards/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=fia-and-clean-air-task-force-publish-principles-on-codes-and-standards</t>
         </is>
       </c>
       <c r="L34" s="60" t="inlineStr">
         <is>
-          <t>5ab5ea23fbff158109e679af</t>
+          <t>2366dc909672b56b77a196bd</t>
         </is>
       </c>
       <c r="M34" s="75" t="inlineStr">
@@ -3422,12 +3422,12 @@
       </c>
       <c r="B35" s="75" t="inlineStr">
         <is>
-          <t>2026-07-23T15:00:48Z</t>
+          <t>2026-07-21T15:06:49Z</t>
         </is>
       </c>
       <c r="C35" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>EU &amp; Europe</t>
         </is>
       </c>
       <c r="D35" s="60" t="inlineStr">
@@ -3441,36 +3441,36 @@
         </is>
       </c>
       <c r="F35" s="76" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G35" s="60" t="inlineStr">
         <is>
-          <t>Major Media</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H35" s="60" t="inlineStr">
         <is>
-          <t>The Guardian Technology</t>
+          <t>UK DSIT</t>
         </is>
       </c>
       <c r="I35" s="60" t="inlineStr">
         <is>
-          <t>roaring 20s: 現在の10年が映画を革命化した</t>
+          <t>DSITの人材管理情報（2026年6月）</t>
         </is>
       </c>
       <c r="J35" s="60" t="inlineStr">
         <is>
-          <t>映画産業は常に新たな革新を求めており、2020年代の特徴は衰退であるとの見解が示されています。</t>
+          <t>部門のスタッフ数とコストに関する報告が行われています。</t>
         </is>
       </c>
       <c r="K35" s="60" t="inlineStr">
         <is>
-          <t>https://www.theguardian.com/film/2026/jul/23/how-2020s-decade-revolutionised-cinema</t>
+          <t>https://www.gov.uk/government/publications/dsit-workforce-management-information-june-2026</t>
         </is>
       </c>
       <c r="L35" s="60" t="inlineStr">
         <is>
-          <t>f8939f05439f07fdefca04fc</t>
+          <t>68c02c5c6a2ee3c9c91fc7f1</t>
         </is>
       </c>
       <c r="M35" s="75" t="inlineStr">
@@ -3493,55 +3493,55 @@
       </c>
       <c r="B36" s="75" t="inlineStr">
         <is>
-          <t>2026-07-23T13:00:16Z</t>
+          <t>2026-07-21T15:06:31Z</t>
         </is>
       </c>
       <c r="C36" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>EU &amp; Europe</t>
         </is>
       </c>
       <c r="D36" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="E36" s="60" t="inlineStr">
         <is>
-          <t>Semiconductors &amp; Telecom</t>
+          <t>Innovation Policy</t>
         </is>
       </c>
       <c r="F36" s="76" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G36" s="60" t="inlineStr">
         <is>
-          <t>Official Company</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H36" s="60" t="inlineStr">
         <is>
-          <t>NVIDIA Blog</t>
+          <t>UK DSIT</t>
         </is>
       </c>
       <c r="I36" s="60" t="inlineStr">
         <is>
-          <t>GeForce NOWが『Path of Exile: Curse of the Allflame』を追加</t>
+          <t>TechFirst地域支援プログラムの詳細</t>
         </is>
       </c>
       <c r="J36" s="60" t="inlineStr">
         <is>
-          <t>GeForce NOWが新しいコンテンツを提供し、ユーザーはダウンロードを待たずにゲームを楽しむことができます。</t>
+          <t>TechFirstの地域助成金プログラムの詳細が示されており、デジタルスキルを向上させ、テクノロジー職への支援を行います。</t>
         </is>
       </c>
       <c r="K36" s="60" t="inlineStr">
         <is>
-          <t>https://blogs.nvidia.com/blog/geforce-now-thursday-path-of-exile-allflame/</t>
+          <t>https://www.gov.uk/government/publications/techlocal</t>
         </is>
       </c>
       <c r="L36" s="60" t="inlineStr">
         <is>
-          <t>d6df6c9a47b33117f5bcb1be</t>
+          <t>88893e13a25a6efc42ed57ea</t>
         </is>
       </c>
       <c r="M36" s="75" t="inlineStr">
@@ -3564,55 +3564,55 @@
       </c>
       <c r="B37" s="75" t="inlineStr">
         <is>
-          <t>2026-07-23T12:00:00Z</t>
+          <t>2026-07-21T15:05:29Z</t>
         </is>
       </c>
       <c r="C37" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>EU &amp; Europe</t>
         </is>
       </c>
       <c r="D37" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="E37" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence | Healthcare</t>
+          <t>Innovation Policy</t>
         </is>
       </c>
       <c r="F37" s="76" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G37" s="60" t="inlineStr">
         <is>
-          <t>Major Media</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H37" s="60" t="inlineStr">
         <is>
-          <t>MIT Technology Review</t>
+          <t>UK DSIT</t>
         </is>
       </c>
       <c r="I37" s="60" t="inlineStr">
         <is>
-          <t>AIが科学者の次世代医薬品設計を支援</t>
+          <t>TechFirstのPhD支援</t>
         </is>
       </c>
       <c r="J37" s="60" t="inlineStr">
         <is>
-          <t>新しい医薬品の設計と開発は高コストで失敗しやすい科学的課題であり、AIがそのプロセスを支援する可能性があります。</t>
+          <t>TechFirstの一部として、UKの急成長するテクノロジーセクターへの道を開く政府のスキルプログラムです。</t>
         </is>
       </c>
       <c r="K37" s="60" t="inlineStr">
         <is>
-          <t>https://www.technologyreview.com/2026/07/23/1140346/how-ai-helps-scientists-design-the-next-generation-of-medicines/</t>
+          <t>https://www.gov.uk/guidance/techexpert</t>
         </is>
       </c>
       <c r="L37" s="60" t="inlineStr">
         <is>
-          <t>f283b79f845eeb45783eb41c</t>
+          <t>406416679082f87595cbd50b</t>
         </is>
       </c>
       <c r="M37" s="75" t="inlineStr">
@@ -3635,7 +3635,7 @@
       </c>
       <c r="B38" s="75" t="inlineStr">
         <is>
-          <t>2026-07-23T09:23:23Z</t>
+          <t>2026-07-21T15:05:21Z</t>
         </is>
       </c>
       <c r="C38" s="60" t="inlineStr">
@@ -3645,7 +3645,7 @@
       </c>
       <c r="D38" s="60" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="E38" s="60" t="inlineStr">
@@ -3654,36 +3654,36 @@
         </is>
       </c>
       <c r="F38" s="76" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G38" s="60" t="inlineStr">
         <is>
-          <t>Policy Institute</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H38" s="60" t="inlineStr">
         <is>
-          <t>Bruegel</t>
+          <t>UK DSIT</t>
         </is>
       </c>
       <c r="I38" s="60" t="inlineStr">
         <is>
-          <t>EUの規制改善アジェンダは競争力をもたらすか</t>
+          <t>UKのテクノロジー分野を支援するTechFirst</t>
         </is>
       </c>
       <c r="J38" s="60" t="inlineStr">
         <is>
-          <t>EUの規制改善アジェンダが競争力を向上させるかどうかについての議論が行われています。</t>
+          <t>TechFirstは、UKの急成長するテクノロジーセクターへの道を開く政府の主力スキルプログラムです。</t>
         </is>
       </c>
       <c r="K38" s="60" t="inlineStr">
         <is>
-          <t>https://www.bruegel.org/node/12451</t>
+          <t>https://www.gov.uk/guidance/techfirst</t>
         </is>
       </c>
       <c r="L38" s="60" t="inlineStr">
         <is>
-          <t>90ef16bcfe1bd00925658dc5</t>
+          <t>4ae9e496e9b66c66de074041</t>
         </is>
       </c>
       <c r="M38" s="75" t="inlineStr">
@@ -3706,55 +3706,55 @@
       </c>
       <c r="B39" s="75" t="inlineStr">
         <is>
-          <t>2026-07-23T08:00:24Z</t>
+          <t>2026-07-21T15:05:11Z</t>
         </is>
       </c>
       <c r="C39" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>EU &amp; Europe</t>
         </is>
       </c>
       <c r="D39" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="E39" s="60" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Innovation Policy | Semiconductors &amp; Telecom</t>
         </is>
       </c>
       <c r="F39" s="76" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G39" s="60" t="inlineStr">
         <is>
-          <t>Intergovernmental</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H39" s="60" t="inlineStr">
         <is>
-          <t>WHO News</t>
+          <t>UK DSIT</t>
         </is>
       </c>
       <c r="I39" s="60" t="inlineStr">
         <is>
-          <t>WHOが溺死防止のための7つの戦略を発表</t>
+          <t>固定通信近代化のための政策文書</t>
         </is>
       </c>
       <c r="J39" s="60" t="inlineStr">
         <is>
-          <t>世界保健機関（WHO）は、7月25日の世界溺死防止デーに向けて、溺死を減少させるための新しい技術パッケージを発表しました。</t>
+          <t>この文書は、通信事業者が現在および将来の固定通信の近代化を行う際に従うべきステップを示しています。</t>
         </is>
       </c>
       <c r="K39" s="60" t="inlineStr">
         <is>
-          <t>https://www.who.int/news/item/23-07-2026-who-launches-seven-strategies-to-prevent-drowning</t>
+          <t>https://www.gov.uk/government/publications/fixed-telecoms-modernisation-charter</t>
         </is>
       </c>
       <c r="L39" s="60" t="inlineStr">
         <is>
-          <t>57adeb9edafee5c65dff443d</t>
+          <t>d5e4431b57fcb4b6271f6c72</t>
         </is>
       </c>
       <c r="M39" s="75" t="inlineStr">
@@ -3777,55 +3777,55 @@
       </c>
       <c r="B40" s="75" t="inlineStr">
         <is>
-          <t>2026-07-23T02:00:46Z</t>
+          <t>2026-07-21T14:48:28Z</t>
         </is>
       </c>
       <c r="C40" s="60" t="inlineStr">
         <is>
+          <t>EU &amp; Europe</t>
+        </is>
+      </c>
+      <c r="D40" s="60" t="inlineStr">
+        <is>
           <t>Global</t>
         </is>
       </c>
-      <c r="D40" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
       <c r="E40" s="60" t="inlineStr">
         <is>
-          <t>Semiconductors &amp; Telecom</t>
+          <t>Fusion Energy</t>
         </is>
       </c>
       <c r="F40" s="76" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G40" s="60" t="inlineStr">
         <is>
-          <t>Official Company</t>
+          <t>Industry Association</t>
         </is>
       </c>
       <c r="H40" s="60" t="inlineStr">
         <is>
-          <t>NVIDIA Blog</t>
+          <t>Fusion Industry Association</t>
         </is>
       </c>
       <c r="I40" s="60" t="inlineStr">
         <is>
-          <t>NVIDIAのAIスパコンが海軍大学院校で稼働開始</t>
+          <t>EUの核融合資金調達計画を示すFIA</t>
         </is>
       </c>
       <c r="J40" s="60" t="inlineStr">
         <is>
-          <t>NVIDIAの創業者兼CEO、ジェンセン・ファンがカリフォルニア州モントレーの海軍大学院校を訪れ、NVIDIA DGX GB300システムを稼働させました。</t>
+          <t>核融合産業協会は、商業核融合エネルギーのためのEU資金調達の実用的なロードマップを発表しました。研究から実証、商業展開に至る各段階で必要な資金調達手段の進化が求められています。</t>
         </is>
       </c>
       <c r="K40" s="60" t="inlineStr">
         <is>
-          <t>https://blogs.nvidia.com/blog/naval-postgraduate-school-dgx-ai-supercomputer/</t>
+          <t>https://www.fusionindustryassociation.org/fia-outlines-eu-financing-pathway-for-fusion/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=fia-outlines-eu-financing-pathway-for-fusion</t>
         </is>
       </c>
       <c r="L40" s="60" t="inlineStr">
         <is>
-          <t>c174fc131c4d55cb839833e9</t>
+          <t>88af233d904d670250fa5a31</t>
         </is>
       </c>
       <c r="M40" s="75" t="inlineStr">
@@ -3843,12 +3843,12 @@
     <row r="41" ht="42" customHeight="1">
       <c r="A41" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:05:06+09:00</t>
+          <t>2026-07-26T18:56:03+09:00</t>
         </is>
       </c>
       <c r="B41" s="75" t="inlineStr">
         <is>
-          <t>2026-07-23T00:00:00Z</t>
+          <t>2026-07-21T13:30:36Z</t>
         </is>
       </c>
       <c r="C41" s="60" t="inlineStr">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="E41" s="60" t="inlineStr">
         <is>
-          <t>Innovation Policy</t>
+          <t>Innovation Policy | Artificial Intelligence</t>
         </is>
       </c>
       <c r="F41" s="76" t="n">
@@ -3876,32 +3876,32 @@
       </c>
       <c r="H41" s="60" t="inlineStr">
         <is>
-          <t>Brookings TechTank</t>
+          <t>CSET</t>
         </is>
       </c>
       <c r="I41" s="60" t="inlineStr">
         <is>
-          <t>テクノロジー企業が職業の懸念とスキル開発にどう対処すべきか</t>
+          <t>AIシステムはなぜ誤動作するのか？</t>
         </is>
       </c>
       <c r="J41" s="60" t="inlineStr">
         <is>
-          <t>テクノロジー企業は、職業に関する懸念やスキル開発に対してどのように取り組むべきかについての考察が求められています。</t>
+          <t>AIシステムの誤動作の原因を探るブログ記事で、政策的な視点からの考察が行われている。</t>
         </is>
       </c>
       <c r="K41" s="60" t="inlineStr">
         <is>
-          <t>https://www.brookings.edu/articles/how-tech-firms-should-address-job-concerns-and-skill-development/</t>
+          <t>https://cset.georgetown.edu/article/why-do-ai-systems-misbehave/</t>
         </is>
       </c>
       <c r="L41" s="60" t="inlineStr">
         <is>
-          <t>0d48c18a0657c35e8abe7133</t>
+          <t>3e1aa390ad965782cc86c386</t>
         </is>
       </c>
       <c r="M41" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:05:06+09:00</t>
+          <t>2026-07-26T18:56:03+09:00</t>
         </is>
       </c>
       <c r="N41" s="60" t="inlineStr">
@@ -3919,12 +3919,12 @@
       </c>
       <c r="B42" s="75" t="inlineStr">
         <is>
-          <t>2026-07-23T00:00:00Z</t>
+          <t>2026-07-21T12:10:00Z</t>
         </is>
       </c>
       <c r="C42" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="D42" s="60" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="E42" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence | Healthcare</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="F42" s="76" t="n">
@@ -3942,32 +3942,32 @@
       </c>
       <c r="G42" s="60" t="inlineStr">
         <is>
-          <t>Official Company</t>
+          <t>Major Media</t>
         </is>
       </c>
       <c r="H42" s="60" t="inlineStr">
         <is>
-          <t>OpenAI News</t>
+          <t>MIT Technology Review</t>
         </is>
       </c>
       <c r="I42" s="60" t="inlineStr">
         <is>
-          <t>ChatGPTにおける健康機能の開始</t>
+          <t>ダウンロード：中国のAIがホワイトハウスを分断し、記録的な著作権支払い</t>
         </is>
       </c>
       <c r="J42" s="60" t="inlineStr">
         <is>
-          <t>ChatGPTの健康機能により、米国の適格ユーザーは医療記録やApple Healthを安全に接続し、より個別化された健康情報を得ることが可能になりました。</t>
+          <t>中国のAIモデルに関する議論が、トランプ政権のAI政策に影響を与えていることを報告。</t>
         </is>
       </c>
       <c r="K42" s="60" t="inlineStr">
         <is>
-          <t>https://openai.com/index/health-in-chatgpt</t>
+          <t>https://www.technologyreview.com/2026/07/21/1140685/the-download-chinese-ai-divides-white-house-anthropic-copyright-settlement/</t>
         </is>
       </c>
       <c r="L42" s="60" t="inlineStr">
         <is>
-          <t>bf70d809f9542eeef4af8727</t>
+          <t>f9addf0904b9de5b7bcc326b</t>
         </is>
       </c>
       <c r="M42" s="75" t="inlineStr">
@@ -3990,55 +3990,55 @@
       </c>
       <c r="B43" s="75" t="inlineStr">
         <is>
-          <t>2026-07-23T00:00:00Z</t>
+          <t>2026-07-21T07:00:00Z</t>
         </is>
       </c>
       <c r="C43" s="60" t="inlineStr">
         <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="D43" s="60" t="inlineStr">
+        <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="D43" s="60" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
       <c r="E43" s="60" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="F43" s="76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G43" s="60" t="inlineStr">
         <is>
-          <t>Scientific Publication</t>
+          <t>Official Company</t>
         </is>
       </c>
       <c r="H43" s="60" t="inlineStr">
         <is>
-          <t>Nature</t>
+          <t>OpenAI News</t>
         </is>
       </c>
       <c r="I43" s="60" t="inlineStr">
         <is>
-          <t>アメリカの健康政策は科学的検証に耐えうるのか</t>
+          <t>OpenAIとHugging Faceがモデル評価中のセキュリティインシデントに対処するために提携</t>
         </is>
       </c>
       <c r="J43" s="60" t="inlineStr">
         <is>
-          <t>研究者たちは、ワクチンから栄養に至るまで、アメリカの健康政策に関する見解を共有しています。</t>
+          <t>OpenAIとHugging Faceは、AIモデル評価中のセキュリティインシデントに関する初期の調査結果を共有し、サイバー防御者への教訓を強調した。</t>
         </is>
       </c>
       <c r="K43" s="60" t="inlineStr">
         <is>
-          <t>https://www.nature.com/articles/d41586-026-02024-3</t>
+          <t>https://openai.com/index/hugging-face-model-evaluation-security-incident</t>
         </is>
       </c>
       <c r="L43" s="60" t="inlineStr">
         <is>
-          <t>29dc020f76be264fafefbdc5</t>
+          <t>d925d8c91f460a44f07089c2</t>
         </is>
       </c>
       <c r="M43" s="75" t="inlineStr">
@@ -4061,22 +4061,22 @@
       </c>
       <c r="B44" s="75" t="inlineStr">
         <is>
-          <t>2026-07-23T00:00:00Z</t>
+          <t>2026-07-20T15:55:00Z</t>
         </is>
       </c>
       <c r="C44" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D44" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E44" s="60" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Semiconductors &amp; Telecom</t>
         </is>
       </c>
       <c r="F44" s="76" t="n">
@@ -4084,32 +4084,32 @@
       </c>
       <c r="G44" s="60" t="inlineStr">
         <is>
-          <t>Scientific Publication</t>
+          <t>Major Media</t>
         </is>
       </c>
       <c r="H44" s="60" t="inlineStr">
         <is>
-          <t>Nature</t>
+          <t>IEEE Spectrum</t>
         </is>
       </c>
       <c r="I44" s="60" t="inlineStr">
         <is>
-          <t>日々のブリーフィング：オルカがサンフィッシュを粉砕</t>
+          <t>先端半導体故障分析のためのSEMガイド低電圧FIB仕上げ</t>
         </is>
       </c>
       <c r="J44" s="60" t="inlineStr">
         <is>
-          <t>オルカがサンフィッシュを粉砕する行動は、子供たちに食べ物を与える手助けか、単に楽しんでいるのかが議論されています。</t>
+          <t>ZEISS Crossbeam 750 FIBSEMが、精密TEMラメラ準備や高度なナノファブリケーションの新基準を設定し、故障分析を加速する方法を紹介。</t>
         </is>
       </c>
       <c r="K44" s="60" t="inlineStr">
         <is>
-          <t>https://www.nature.com/articles/d41586-026-02307-9</t>
+          <t>https://event.on24.com/wcc/r/5418459/287E3D5B99470D34C830D69A24B3B207</t>
         </is>
       </c>
       <c r="L44" s="60" t="inlineStr">
         <is>
-          <t>38109aea610319dbc3f32aef</t>
+          <t>73d0028e337a76c2cd00f1bc</t>
         </is>
       </c>
       <c r="M44" s="75" t="inlineStr">
@@ -4132,55 +4132,55 @@
       </c>
       <c r="B45" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T22:04:00Z</t>
+          <t>2026-07-18T07:27:54Z</t>
         </is>
       </c>
       <c r="C45" s="60" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D45" s="60" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="E45" s="60" t="inlineStr">
         <is>
-          <t>Semiconductors &amp; Telecom</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="F45" s="76" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G45" s="60" t="inlineStr">
         <is>
-          <t>Official Company</t>
+          <t>Intergovernmental</t>
         </is>
       </c>
       <c r="H45" s="60" t="inlineStr">
         <is>
-          <t>Samsung Global Newsroom</t>
+          <t>WHO News</t>
         </is>
       </c>
       <c r="I45" s="60" t="inlineStr">
         <is>
-          <t>[Galaxy Unpacked 2026年7月] Galaxy Z Fold8 Ultra、Galaxy Z Fold8、Galaxy Z Flip8の初公開</t>
+          <t>WHO加盟国が病原体アクセスと利益配分に関する交渉を継続</t>
         </is>
       </c>
       <c r="J45" s="60" t="inlineStr">
         <is>
-          <t>2026年7月のGalaxy Unpackedで、サムスン電子は第8世代Galaxy Zシリーズを発表し、異なるライフスタイルに合わせた折りたたみ式デバイスを提供しました。</t>
+          <t>WHO加盟国は、パンデミック協定の中心要素である病原体アクセスと利益配分に関する交渉を進め、将来のパンデミックに対する迅速かつ効果的な対応を支える枠組みの最終化に向けた議論を行っています。</t>
         </is>
       </c>
       <c r="K45" s="60" t="inlineStr">
         <is>
-          <t>https://news.samsung.com/global/galaxy-unpacked-july-2026-a-first-look-at-galaxy-z-fold8-ultra-galaxy-z-fold8-and-galaxy-z-flip8</t>
+          <t>https://www.who.int/news/item/20-07-2026-who-member-states-continue-negotiations-on-the-pathogen-access-and-benefit-sharing-annex</t>
         </is>
       </c>
       <c r="L45" s="60" t="inlineStr">
         <is>
-          <t>6871adffe89103810dfccf11</t>
+          <t>14dd15caca066d18dfcf2e34</t>
         </is>
       </c>
       <c r="M45" s="75" t="inlineStr">
@@ -4203,55 +4203,55 @@
       </c>
       <c r="B46" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T22:03:00Z</t>
+          <t>2026-07-17T20:26:18Z</t>
         </is>
       </c>
       <c r="C46" s="60" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D46" s="60" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="E46" s="60" t="inlineStr">
         <is>
-          <t>Semiconductors &amp; Telecom</t>
+          <t>Fusion Energy</t>
         </is>
       </c>
       <c r="F46" s="76" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G46" s="60" t="inlineStr">
         <is>
-          <t>Official Company</t>
+          <t>Industry Association</t>
         </is>
       </c>
       <c r="H46" s="60" t="inlineStr">
         <is>
-          <t>Samsung Global Newsroom</t>
+          <t>Fusion Industry Association</t>
         </is>
       </c>
       <c r="I46" s="60" t="inlineStr">
         <is>
-          <t>[Galaxy Unpacked 2026年7月] Galaxy Watch Ultra2とGalaxy Watch9の初公開</t>
+          <t>2026年グローバル核融合産業報告書の発表</t>
         </is>
       </c>
       <c r="J46" s="60" t="inlineStr">
         <is>
-          <t>2026年7月のGalaxy Unpackedで、サムスン電子はGalaxy Watch Ultra2とGalaxy Watch9を発表し、デジタル健康体験を拡大しました。</t>
+          <t>核融合産業協会は、2026年グローバル核融合産業報告書を発表し、米国の政策に関連する議論を行いました。</t>
         </is>
       </c>
       <c r="K46" s="60" t="inlineStr">
         <is>
-          <t>https://news.samsung.com/global/galaxy-unpacked-july-2026-a-first-look-at-galaxy-watch-ultra2-and-galaxy-watch9</t>
+          <t>https://www.fusionindustryassociation.org/fia-launches-the-2026-global-fusion-industry-report-in-new-york-city-washington-d-c-and-london/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=fia-launches-the-2026-global-fusion-industry-report-in-new-york-city-washington-d-c-and-london</t>
         </is>
       </c>
       <c r="L46" s="60" t="inlineStr">
         <is>
-          <t>8956b8f95f8049ae547c684e</t>
+          <t>186c1d4e76c09a864706432c</t>
         </is>
       </c>
       <c r="M46" s="75" t="inlineStr">
@@ -4274,55 +4274,55 @@
       </c>
       <c r="B47" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T22:02:00Z</t>
+          <t>2026-07-17T18:42:47Z</t>
         </is>
       </c>
       <c r="C47" s="60" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>EU &amp; Europe</t>
         </is>
       </c>
       <c r="D47" s="60" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="E47" s="60" t="inlineStr">
         <is>
-          <t>Semiconductors &amp; Telecom</t>
+          <t>Innovation Policy | Fusion Energy</t>
         </is>
       </c>
       <c r="F47" s="76" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G47" s="60" t="inlineStr">
         <is>
-          <t>Official Company</t>
+          <t>Industry Association</t>
         </is>
       </c>
       <c r="H47" s="60" t="inlineStr">
         <is>
-          <t>Samsung Global Newsroom</t>
+          <t>Fusion Industry Association</t>
         </is>
       </c>
       <c r="I47" s="60" t="inlineStr">
         <is>
-          <t>サムスンGalaxy Z Fold8 Ultra、Fold8、Flip8：生活様式に合わせた折りたたみ式デバイス</t>
+          <t>EUの核融合競争力を確保する必要性に関する論文発表</t>
         </is>
       </c>
       <c r="J47" s="60" t="inlineStr">
         <is>
-          <t>サムスン電子は新しいGalaxy Zシリーズを発表し、折りたたみ式デバイスをより広いオーディエンスに拡大することを目指しています。</t>
+          <t>国際法専門家グループが発表した論文は、ヨーロッパが商業核融合において競争優位を持っているが、それを維持するために今行動する必要があると主張しています。</t>
         </is>
       </c>
       <c r="K47" s="60" t="inlineStr">
         <is>
-          <t>https://news.samsung.com/global/samsung-galaxy-z-fold8-ultra-fold8-and-flip8foldables-perfected-for-every-way-of-living</t>
+          <t>https://www.fusionindustryassociation.org/international-legal-expert-group-publish-paper-on-the-need-for-the-eu-to-secure-its-competitive-fusion-advantage/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=international-legal-expert-group-publish-paper-on-the-need-for-the-eu-to-secure-its-competitive-fusion-advantage</t>
         </is>
       </c>
       <c r="L47" s="60" t="inlineStr">
         <is>
-          <t>3c09b6e86ff09a214f548cb1</t>
+          <t>7ef6110ab078602757409abf</t>
         </is>
       </c>
       <c r="M47" s="75" t="inlineStr">
@@ -4345,55 +4345,55 @@
       </c>
       <c r="B48" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T22:01:00Z</t>
+          <t>2026-07-15T21:00:00Z</t>
         </is>
       </c>
       <c r="C48" s="60" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D48" s="60" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E48" s="60" t="inlineStr">
         <is>
-          <t>Semiconductors &amp; Telecom</t>
+          <t>Artificial Intelligence | Innovation Policy</t>
         </is>
       </c>
       <c r="F48" s="76" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G48" s="60" t="inlineStr">
         <is>
-          <t>Official Company</t>
+          <t>Policy Institute</t>
         </is>
       </c>
       <c r="H48" s="60" t="inlineStr">
         <is>
-          <t>Samsung Global Newsroom</t>
+          <t>CSET</t>
         </is>
       </c>
       <c r="I48" s="60" t="inlineStr">
         <is>
-          <t>サムスンGalaxy Watch Ultra2とWatch9：健康のための腕時計</t>
+          <t>GPT-Red：OpenAIが構築したAIスーパーハッカー</t>
         </is>
       </c>
       <c r="J48" s="60" t="inlineStr">
         <is>
-          <t>サムスン電子は新しいGalaxy Watch Ultra2とGalaxy Watch9を発表し、ユーザーがこれらのデバイスを着用することで深い健康洞察を得られる新時代を迎えました。</t>
+          <t>OpenAIが開発したGPT-Redは、大規模言語モデルの脆弱性を自動的に特定し、サイバー攻撃に対する防御を強化するためのAIスーパーハッカーです。</t>
         </is>
       </c>
       <c r="K48" s="60" t="inlineStr">
         <is>
-          <t>https://news.samsung.com/global/samsung-galaxy-watch-ultra2-and-watch9-your-health-companion-on-the-wrist</t>
+          <t>https://cset.georgetown.edu/article/meet-gpt-red-an-llm-super-hacker-openai-built-to-make-its-models-safer/</t>
         </is>
       </c>
       <c r="L48" s="60" t="inlineStr">
         <is>
-          <t>d2071e7bcb1db74477836d6a</t>
+          <t>f64391d3daf689e78e7ac442</t>
         </is>
       </c>
       <c r="M48" s="75" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="B49" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T22:00:00Z</t>
+          <t>2026-07-15T17:47:57Z</t>
         </is>
       </c>
       <c r="C49" s="60" t="inlineStr">
@@ -4426,45 +4426,45 @@
       </c>
       <c r="D49" s="60" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="E49" s="60" t="inlineStr">
         <is>
-          <t>Semiconductors &amp; Telecom</t>
+          <t>Fusion Energy</t>
         </is>
       </c>
       <c r="F49" s="76" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G49" s="60" t="inlineStr">
         <is>
-          <t>Official Company</t>
+          <t>Industry Association</t>
         </is>
       </c>
       <c r="H49" s="60" t="inlineStr">
         <is>
-          <t>Samsung Global Newsroom</t>
+          <t>Fusion Industry Association</t>
         </is>
       </c>
       <c r="I49" s="60" t="inlineStr">
         <is>
-          <t>サムスン、日常の眼鏡にGalaxyエコシステムを導入</t>
+          <t>スターロライトエンジンが60.6億円を調達</t>
         </is>
       </c>
       <c r="J49" s="60" t="inlineStr">
         <is>
-          <t>サムスン電子はロンドンで開催されたGalaxy Unpackedで、インテリジェントな眼鏡を発表しました。これにより、Galaxyエコシステムがモバイルフォンを超えて眼鏡に進出することを示しています。</t>
+          <t>スターロライトエンジンは、FASTの開発を加速するために60.6億円の資金を調達しました。同社は、JT-60SAプログラムや国際的な取り組みを基にしたトカマク型核融合装置を開発しています。</t>
         </is>
       </c>
       <c r="K49" s="60" t="inlineStr">
         <is>
-          <t>https://news.samsung.com/global/samsung-brings-galaxy-ecosystem-into-everyday-eyewear</t>
+          <t>https://www.nikkei.com/article/DGXZQOUC152ET0V10C26A7000000/#new_tab?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=starlight-engine-raises-jpy-6-06-billion</t>
         </is>
       </c>
       <c r="L49" s="60" t="inlineStr">
         <is>
-          <t>c3c9b17859519c8241a98bfb</t>
+          <t>2f29b005896c3737ab846738</t>
         </is>
       </c>
       <c r="M49" s="75" t="inlineStr">
@@ -4487,55 +4487,55 @@
       </c>
       <c r="B50" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T14:21:46Z</t>
+          <t>2026-07-15T17:43:32Z</t>
         </is>
       </c>
       <c r="C50" s="60" t="inlineStr">
         <is>
-          <t>EU &amp; Europe</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D50" s="60" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="E50" s="60" t="inlineStr">
         <is>
-          <t>Innovation Policy</t>
+          <t>Fusion Energy</t>
         </is>
       </c>
       <c r="F50" s="76" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G50" s="60" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Industry Association</t>
         </is>
       </c>
       <c r="H50" s="60" t="inlineStr">
         <is>
-          <t>UK DSIT</t>
+          <t>Fusion Industry Association</t>
         </is>
       </c>
       <c r="I50" s="60" t="inlineStr">
         <is>
-          <t>女性研究者のためのチャーターに関するガイダンス</t>
+          <t>マディソンの元オスカー・マイヤー工場に核融合研究センターが設立</t>
         </is>
       </c>
       <c r="J50" s="60" t="inlineStr">
         <is>
-          <t>英国の研究システムにおける女性の成果を向上させるための自主的な取り組みで、研究資金提供者や研究機関に対する行動が含まれています。</t>
+          <t>Realta Fusionがマディソンに新しい本社と施設を設立し、核融合技術のプロトタイプを建設する計画を発表した。</t>
         </is>
       </c>
       <c r="K50" s="60" t="inlineStr">
         <is>
-          <t>https://www.gov.uk/government/publications/women-in-research-charter</t>
+          <t>https://www.jsonline.com/story/money/business/energy/2026/07/15/nuclear-fusion-facility-coming-to-madisons-oscar-mayer-factory-site/90900554007/?gnt-cfr=1&amp;gca-cat=p&amp;gca-uir=true&amp;gca-epti=z116463p117850l004150c117850e1157xxv116463d--54--b--54--&amp;gca-ft=178&amp;gca-ds=sophi#new_tab&amp;utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=fusion-research-center-coming-to-madisons-former-oscar-mayer-plant</t>
         </is>
       </c>
       <c r="L50" s="60" t="inlineStr">
         <is>
-          <t>1e9fd9033d38bacea37c0f42</t>
+          <t>aed2fa8a807fb17c3e6861e7</t>
         </is>
       </c>
       <c r="M50" s="75" t="inlineStr">
@@ -4553,65 +4553,65 @@
     <row r="51" ht="42" customHeight="1">
       <c r="A51" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:05:06+09:00</t>
+          <t>2026-07-26T18:56:03+09:00</t>
         </is>
       </c>
       <c r="B51" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T14:12:14Z</t>
+          <t>2026-07-15T00:01:54Z</t>
         </is>
       </c>
       <c r="C51" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D51" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="E51" s="60" t="inlineStr">
         <is>
-          <t>Innovation Policy | Quantum</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="F51" s="76" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G51" s="60" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Intergovernmental</t>
         </is>
       </c>
       <c r="H51" s="60" t="inlineStr">
         <is>
-          <t>DOE Office of Science News</t>
+          <t>WHO News</t>
         </is>
       </c>
       <c r="I51" s="60" t="inlineStr">
         <is>
-          <t>エネルギー長官クリス・ライトがAI駆動の科学発見を加速するプロジェクトを発表</t>
+          <t>世界の子供の予防接種率が向上、紛争やためらいにもかかわらず</t>
         </is>
       </c>
       <c r="J51" s="60" t="inlineStr">
         <is>
-          <t>全米50州からの歴史的なRFA応答から選ばれた約300のプロジェクトが、エネルギー、発見科学、国家安全保障におけるブレークスルーを加速することを目的としています。</t>
+          <t>2025年には、世界で90%の乳児がジフテリア、破傷風、百日咳（DTP）ワクチンの少なくとも1回の接種を受け、85%が3回の接種を完了したとWHOとUNICEFの報告が示しています。しかし、依然として2019年の水準を下回っています。</t>
         </is>
       </c>
       <c r="K51" s="60" t="inlineStr">
         <is>
-          <t>https://www.energy.gov/articles/secretary-energy-chris-wright-announces-first-genesis-mission-projects-selected-accelerate</t>
+          <t>https://www.who.int/news/item/15-07-2026-global-childhood-immunization-coverage-inches-forward-despite-conflict-and-hesitancy---unicef--who</t>
         </is>
       </c>
       <c r="L51" s="60" t="inlineStr">
         <is>
-          <t>23fa1d6907c14d73ce3a41cd</t>
+          <t>03ea8728394fda1e18a57d66</t>
         </is>
       </c>
       <c r="M51" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:05:06+09:00</t>
+          <t>2026-07-26T18:56:03+09:00</t>
         </is>
       </c>
       <c r="N51" s="60" t="inlineStr">
@@ -4629,7 +4629,7 @@
       </c>
       <c r="B52" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T14:12:00Z</t>
+          <t>2026-07-14T12:00:00Z</t>
         </is>
       </c>
       <c r="C52" s="60" t="inlineStr">
@@ -4644,40 +4644,40 @@
       </c>
       <c r="E52" s="60" t="inlineStr">
         <is>
-          <t>Innovation Policy | Artificial Intelligence</t>
+          <t>Innovation Policy</t>
         </is>
       </c>
       <c r="F52" s="76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G52" s="60" t="inlineStr">
         <is>
-          <t>Policy Institute</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H52" s="60" t="inlineStr">
         <is>
-          <t>CSET</t>
+          <t>NIST News</t>
         </is>
       </c>
       <c r="I52" s="60" t="inlineStr">
         <is>
-          <t>人工知能と核戦争に関するグローバルノーベル賞受賞者会議での発言</t>
+          <t>NIST、微生物を殺す給湯器の新特許を取得</t>
         </is>
       </c>
       <c r="J52" s="60" t="inlineStr">
         <is>
-          <t>CSETのシニアフェロー、エメリア・プロバスコがバチカンで開催された人工知能と核戦争に関するグローバルノーベル賞受賞者会議での経験と発言を共有しました。</t>
+          <t>家庭の配管内の温水が有害な細菌の繁殖地となる可能性があることから、NISTが新たな特許を取得した。</t>
         </is>
       </c>
       <c r="K52" s="60" t="inlineStr">
         <is>
-          <t>https://cset.georgetown.edu/article/remarks-at-the-global-nobel-laureates-assembly-on-artificial-intelligence-and-nuclear-war/</t>
+          <t>https://www.nist.gov/news-events/news/2026/07/nist-receives-new-patent-microbe-killing-water-heater</t>
         </is>
       </c>
       <c r="L52" s="60" t="inlineStr">
         <is>
-          <t>863086979e9f7f63c082cb57</t>
+          <t>72b002f5a04f35d9ca1e9949</t>
         </is>
       </c>
       <c r="M52" s="75" t="inlineStr">
@@ -4700,22 +4700,22 @@
       </c>
       <c r="B53" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T13:58:00Z</t>
+          <t>2026-07-13T21:00:00Z</t>
         </is>
       </c>
       <c r="C53" s="60" t="inlineStr">
         <is>
-          <t>EU &amp; Europe</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D53" s="60" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E53" s="60" t="inlineStr">
         <is>
-          <t>Innovation Policy</t>
+          <t>Innovation Policy | Artificial Intelligence</t>
         </is>
       </c>
       <c r="F53" s="76" t="n">
@@ -4723,32 +4723,32 @@
       </c>
       <c r="G53" s="60" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Policy Institute</t>
         </is>
       </c>
       <c r="H53" s="60" t="inlineStr">
         <is>
-          <t>UK DSIT</t>
+          <t>CSET</t>
         </is>
       </c>
       <c r="I53" s="60" t="inlineStr">
         <is>
-          <t>AIツール「Consult」の利用登録案内</t>
+          <t>米国、中国がAIを米国モデルで訓練するのを阻止しようとする</t>
         </is>
       </c>
       <c r="J53" s="60" t="inlineStr">
         <is>
-          <t>政府チームが公的相談の回答を分析するためのAIツール「Consult」の利用に関心がある方は、待機リストに登録してください。</t>
+          <t>米国では、中国のAI企業が米国のシステムからの出力を使用してモデルを訓練することに対する懸念が高まっており、知的財産や競争、国家安全保障に関する議論が進んでいる。</t>
         </is>
       </c>
       <c r="K53" s="60" t="inlineStr">
         <is>
-          <t>https://www.gov.uk/government/publications/consult-register-your-interest</t>
+          <t>https://cset.georgetown.edu/article/washington-is-looking-to-keep-china-from-training-its-ai-on-us-models/</t>
         </is>
       </c>
       <c r="L53" s="60" t="inlineStr">
         <is>
-          <t>a651f42eb5805e39f03fbebe</t>
+          <t>e96177000536ef3f58f8fb3c</t>
         </is>
       </c>
       <c r="M53" s="75" t="inlineStr">
@@ -4766,65 +4766,65 @@
     <row r="54" ht="42" customHeight="1">
       <c r="A54" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:05:06+09:00</t>
+          <t>2026-07-26T18:56:03+09:00</t>
         </is>
       </c>
       <c r="B54" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T13:53:19Z</t>
+          <t>2026-07-13T16:00:00Z</t>
         </is>
       </c>
       <c r="C54" s="60" t="inlineStr">
         <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="D54" s="60" t="inlineStr">
+        <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="D54" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
       <c r="E54" s="60" t="inlineStr">
         <is>
-          <t>Innovation Policy | Artificial Intelligence</t>
+          <t>Innovation Policy | Quantum</t>
         </is>
       </c>
       <c r="F54" s="76" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G54" s="60" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Official Company</t>
         </is>
       </c>
       <c r="H54" s="60" t="inlineStr">
         <is>
-          <t>National Science Foundation News</t>
+          <t>Microsoft Research</t>
         </is>
       </c>
       <c r="I54" s="60" t="inlineStr">
         <is>
-          <t>NSF長官代行ブライアン・ストーンのAI優先事項推進に関する声明</t>
+          <t>SymCryptにおけるRust暗号の検証</t>
         </is>
       </c>
       <c r="J54" s="60" t="inlineStr">
         <is>
-          <t>米国科学財団（NSF）は、ホワイトハウス科学技術政策局やエネルギー省などと連携し、行政の人工知能（AI）優先事項を推進することを誇りに思っています。</t>
+          <t>新しい手法が開発者がコードを書く際にその検証を助け、実装と進化の過程で速度と適応性を保つことを可能にする。</t>
         </is>
       </c>
       <c r="K54" s="60" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/news/statement-nsf-chief-staff-brian-stone-performing-duties-nsf-1</t>
+          <t>https://www.microsoft.com/en-us/research/blog/verifying-rust-cryptography-in-symcrypt-from-standards-to-code/</t>
         </is>
       </c>
       <c r="L54" s="60" t="inlineStr">
         <is>
-          <t>123e2207578ca69c8f9c00a2</t>
+          <t>a7866758cf94a3c5e9d26534</t>
         </is>
       </c>
       <c r="M54" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:05:06+09:00</t>
+          <t>2026-07-26T18:56:03+09:00</t>
         </is>
       </c>
       <c r="N54" s="60" t="inlineStr">
@@ -4837,65 +4837,65 @@
     <row r="55" ht="42" customHeight="1">
       <c r="A55" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:05:06+09:00</t>
+          <t>2026-07-26T18:56:03+09:00</t>
         </is>
       </c>
       <c r="B55" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T13:53:12Z</t>
+          <t>2026-07-13T12:00:41Z</t>
         </is>
       </c>
       <c r="C55" s="60" t="inlineStr">
         <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="D55" s="60" t="inlineStr">
+        <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="D55" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
       <c r="E55" s="60" t="inlineStr">
         <is>
-          <t>Innovation Policy | Artificial Intelligence</t>
+          <t>Semiconductors &amp; Telecom | Artificial Intelligence</t>
         </is>
       </c>
       <c r="F55" s="76" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G55" s="60" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Official Company</t>
         </is>
       </c>
       <c r="H55" s="60" t="inlineStr">
         <is>
-          <t>National Science Foundation News</t>
+          <t>Intel Newsroom</t>
         </is>
       </c>
       <c r="I55" s="60" t="inlineStr">
         <is>
-          <t>新しいNSFイニシアティブがAIを活用した科学的発見のためのデータセットの価値を解放</t>
+          <t>インテル、ヨーロッパでの製造拡大に50億ユーロを投資</t>
         </is>
       </c>
       <c r="J55" s="60" t="inlineStr">
         <is>
-          <t>米国国立科学財団は、AIを活用した科学的発見を促進するための新しい投資を発表しました。</t>
+          <t>インテルはアイルランドのLeixlipキャンパスに50億ユーロを投資し、AIと高性能コンピューティング向けの先進的なシリコンの需要に応えるための製造能力を拡大する。</t>
         </is>
       </c>
       <c r="K55" s="60" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/news/new-nsf-initiative-aims-unlock-dataset-value-ai-enabled</t>
+          <t>https://newsroom.intel.com/intel-foundry/intel-invests-5-billion-euro-to-expand-manufacturing-in-europe</t>
         </is>
       </c>
       <c r="L55" s="60" t="inlineStr">
         <is>
-          <t>dcd819527d9b80141b26bcb8</t>
+          <t>297a8b5b279e5916cf45fddb</t>
         </is>
       </c>
       <c r="M55" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:05:06+09:00</t>
+          <t>2026-07-26T18:56:03+09:00</t>
         </is>
       </c>
       <c r="N55" s="60" t="inlineStr">
@@ -4908,27 +4908,27 @@
     <row r="56" ht="42" customHeight="1">
       <c r="A56" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:05:06+09:00</t>
+          <t>2026-07-26T18:56:03+09:00</t>
         </is>
       </c>
       <c r="B56" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T13:53:06Z</t>
+          <t>2026-07-12T21:00:00Z</t>
         </is>
       </c>
       <c r="C56" s="60" t="inlineStr">
         <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D56" s="60" t="inlineStr">
+        <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="D56" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
       <c r="E56" s="60" t="inlineStr">
         <is>
-          <t>Innovation Policy</t>
+          <t>Artificial Intelligence | Innovation Policy</t>
         </is>
       </c>
       <c r="F56" s="76" t="n">
@@ -4936,37 +4936,37 @@
       </c>
       <c r="G56" s="60" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Policy Institute</t>
         </is>
       </c>
       <c r="H56" s="60" t="inlineStr">
         <is>
-          <t>National Science Foundation News</t>
+          <t>CSET</t>
         </is>
       </c>
       <c r="I56" s="60" t="inlineStr">
         <is>
-          <t>NSFがAI駆動の科学を進展させるために8300万ドルの投資を発表</t>
+          <t>企業がコスト削減のために中国のAIモデルに注目</t>
         </is>
       </c>
       <c r="J56" s="60" t="inlineStr">
         <is>
-          <t>米国国立科学財団は、統合データシステムおよびサービスプログラムを通じて8300万ドルの助成金を発表し、研究者がデータインフラを活用できるようにします。</t>
+          <t>企業がコスト削減を目的に中国のAIモデルを採用する動きが広がっており、低コストや改善された能力、オープンウェイトシステムの柔軟性がその要因とされている。</t>
         </is>
       </c>
       <c r="K56" s="60" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/news/nsf-announces-83m-investment-integrated-data-systems</t>
+          <t>https://cset.georgetown.edu/article/companies-turn-to-chinese-ai-models-to-cut-costs/</t>
         </is>
       </c>
       <c r="L56" s="60" t="inlineStr">
         <is>
-          <t>018d40b7e6eb7aa4b8cfb5fa</t>
+          <t>9e1bc06c29b61bed048d4f44</t>
         </is>
       </c>
       <c r="M56" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:05:06+09:00</t>
+          <t>2026-07-26T18:56:03+09:00</t>
         </is>
       </c>
       <c r="N56" s="60" t="inlineStr">
@@ -4976,4126 +4976,8 @@
       </c>
       <c r="O56" s="60" t="inlineStr"/>
     </row>
-    <row r="57" ht="42" customHeight="1">
-      <c r="A57" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="B57" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-22T13:00:11Z</t>
-        </is>
-      </c>
-      <c r="C57" s="60" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="D57" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E57" s="60" t="inlineStr">
-        <is>
-          <t>Robotics | Healthcare | Semiconductors &amp; Telecom</t>
-        </is>
-      </c>
-      <c r="F57" s="76" t="n">
-        <v>0</v>
-      </c>
-      <c r="G57" s="60" t="inlineStr">
-        <is>
-          <t>Official Company</t>
-        </is>
-      </c>
-      <c r="H57" s="60" t="inlineStr">
-        <is>
-          <t>NVIDIA Blog</t>
-        </is>
-      </c>
-      <c r="I57" s="60" t="inlineStr">
-        <is>
-          <t>NVIDIAが初のGPU加速医療物理シミュレーションフレームワークをオープンソース化</t>
-        </is>
-      </c>
-      <c r="J57" s="60" t="inlineStr">
-        <is>
-          <t>NVIDIAは、医療ロボットが現実世界で有用になるために必要な物理的な反発を学ぶためのシミュレーションフレームワークを公開しました。</t>
-        </is>
-      </c>
-      <c r="K57" s="60" t="inlineStr">
-        <is>
-          <t>https://blogs.nvidia.com/blog/medical-physics-simulation-open-source/</t>
-        </is>
-      </c>
-      <c r="L57" s="60" t="inlineStr">
-        <is>
-          <t>3c1ee99eb36c61c92c0f7bb6</t>
-        </is>
-      </c>
-      <c r="M57" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="N57" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O57" s="60" t="inlineStr"/>
-    </row>
-    <row r="58" ht="42" customHeight="1">
-      <c r="A58" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="B58" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-22T13:00:00Z</t>
-        </is>
-      </c>
-      <c r="C58" s="60" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="D58" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E58" s="60" t="inlineStr">
-        <is>
-          <t>Artificial Intelligence</t>
-        </is>
-      </c>
-      <c r="F58" s="76" t="n">
-        <v>1</v>
-      </c>
-      <c r="G58" s="60" t="inlineStr">
-        <is>
-          <t>Official Company</t>
-        </is>
-      </c>
-      <c r="H58" s="60" t="inlineStr">
-        <is>
-          <t>OpenAI News</t>
-        </is>
-      </c>
-      <c r="I58" s="60" t="inlineStr">
-        <is>
-          <t>エフィンガム郡コミュニティとのAIインフラ構築</t>
-        </is>
-      </c>
-      <c r="J58" s="60" t="inlineStr">
-        <is>
-          <t>OpenAIはジョージア州エフィンガム郡でプロジェクト・カメリアを発表し、責任あるエネルギー、地域投資、雇用、Codexへのアクセスを約束しました。</t>
-        </is>
-      </c>
-      <c r="K58" s="60" t="inlineStr">
-        <is>
-          <t>https://openai.com/index/building-ai-infrastructure-with-the-effingham-county-community</t>
-        </is>
-      </c>
-      <c r="L58" s="60" t="inlineStr">
-        <is>
-          <t>082c4173c70b04519142ea2a</t>
-        </is>
-      </c>
-      <c r="M58" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="N58" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O58" s="60" t="inlineStr"/>
-    </row>
-    <row r="59" ht="42" customHeight="1">
-      <c r="A59" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="B59" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-22T13:00:00Z</t>
-        </is>
-      </c>
-      <c r="C59" s="60" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="D59" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E59" s="60" t="inlineStr">
-        <is>
-          <t>Artificial Intelligence</t>
-        </is>
-      </c>
-      <c r="F59" s="76" t="n">
-        <v>1</v>
-      </c>
-      <c r="G59" s="60" t="inlineStr">
-        <is>
-          <t>Official Company</t>
-        </is>
-      </c>
-      <c r="H59" s="60" t="inlineStr">
-        <is>
-          <t>OpenAI News</t>
-        </is>
-      </c>
-      <c r="I59" s="60" t="inlineStr">
-        <is>
-          <t>ニュース組織がAIを活用して重要な使命を推進</t>
-        </is>
-      </c>
-      <c r="J59" s="60" t="inlineStr">
-        <is>
-          <t>ニュース組織はAIを利用して報道を強化し、オーディエンスを拡大し、ビジネス運営を改善しています。</t>
-        </is>
-      </c>
-      <c r="K59" s="60" t="inlineStr">
-        <is>
-          <t>https://openai.com/index/how-news-organizations-are-using-ai</t>
-        </is>
-      </c>
-      <c r="L59" s="60" t="inlineStr">
-        <is>
-          <t>932591afba7f1cf55372f3f4</t>
-        </is>
-      </c>
-      <c r="M59" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="N59" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O59" s="60" t="inlineStr"/>
-    </row>
-    <row r="60" ht="42" customHeight="1">
-      <c r="A60" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="B60" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-22T13:00:00Z</t>
-        </is>
-      </c>
-      <c r="C60" s="60" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="D60" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E60" s="60" t="inlineStr">
-        <is>
-          <t>Artificial Intelligence</t>
-        </is>
-      </c>
-      <c r="F60" s="76" t="n">
-        <v>0</v>
-      </c>
-      <c r="G60" s="60" t="inlineStr">
-        <is>
-          <t>Official Company</t>
-        </is>
-      </c>
-      <c r="H60" s="60" t="inlineStr">
-        <is>
-          <t>Google AI</t>
-        </is>
-      </c>
-      <c r="I60" s="60" t="inlineStr">
-        <is>
-          <t>Galaxy Unpacked 2026からの3つのGoogleのアップデート</t>
-        </is>
-      </c>
-      <c r="J60" s="60" t="inlineStr">
-        <is>
-          <t>Gentle Monsterの眼鏡やWarby Parkerの眼鏡など、Galaxy Unpacked 2026での新しいプロンプトが紹介されました。</t>
-        </is>
-      </c>
-      <c r="K60" s="60" t="inlineStr">
-        <is>
-          <t>https://blog.google/products-and-platforms/platforms/android/galaxy-unpacked-2026/</t>
-        </is>
-      </c>
-      <c r="L60" s="60" t="inlineStr">
-        <is>
-          <t>7c49a9cf52e16d8bc5c300b8</t>
-        </is>
-      </c>
-      <c r="M60" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="N60" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O60" s="60" t="inlineStr"/>
-    </row>
-    <row r="61" ht="42" customHeight="1">
-      <c r="A61" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="B61" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-22T12:10:00Z</t>
-        </is>
-      </c>
-      <c r="C61" s="60" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="D61" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E61" s="60" t="inlineStr">
-        <is>
-          <t>Fusion Energy</t>
-        </is>
-      </c>
-      <c r="F61" s="76" t="n">
-        <v>0</v>
-      </c>
-      <c r="G61" s="60" t="inlineStr">
-        <is>
-          <t>Major Media</t>
-        </is>
-      </c>
-      <c r="H61" s="60" t="inlineStr">
-        <is>
-          <t>MIT Technology Review</t>
-        </is>
-      </c>
-      <c r="I61" s="60" t="inlineStr">
-        <is>
-          <t>ダウンロード：NASAの新しい宇宙望遠鏡とOpenAIの自律ハッカー</t>
-        </is>
-      </c>
-      <c r="J61" s="60" t="inlineStr">
-        <is>
-          <t>本日は、NASAの新しい宇宙望遠鏡に関する情報を含む技術ニュースレターをお届けします。</t>
-        </is>
-      </c>
-      <c r="K61" s="60" t="inlineStr">
-        <is>
-          <t>https://www.technologyreview.com/2026/07/22/1140717/the-download-nasa-space-telescope-openai-hugging-face-hack/</t>
-        </is>
-      </c>
-      <c r="L61" s="60" t="inlineStr">
-        <is>
-          <t>62c5c294dc0cb2f834763aa6</t>
-        </is>
-      </c>
-      <c r="M61" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="N61" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O61" s="60" t="inlineStr"/>
-    </row>
-    <row r="62" ht="42" customHeight="1">
-      <c r="A62" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="B62" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-22T12:00:00Z</t>
-        </is>
-      </c>
-      <c r="C62" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="D62" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E62" s="60" t="inlineStr">
-        <is>
-          <t>Innovation Policy</t>
-        </is>
-      </c>
-      <c r="F62" s="76" t="n">
-        <v>5</v>
-      </c>
-      <c r="G62" s="60" t="inlineStr">
-        <is>
-          <t>Government</t>
-        </is>
-      </c>
-      <c r="H62" s="60" t="inlineStr">
-        <is>
-          <t>NIST News</t>
-        </is>
-      </c>
-      <c r="I62" s="60" t="inlineStr">
-        <is>
-          <t>NISTが中小企業向けの資金提供機会を発表</t>
-        </is>
-      </c>
-      <c r="J62" s="60" t="inlineStr">
-        <is>
-          <t>NIST MEPは、2026年7月28日火曜日に中小企業向けの資金提供機会に関する情報ウェビナーを開催し、申請準備に関するガイダンスを提供します。</t>
-        </is>
-      </c>
-      <c r="K62" s="60" t="inlineStr">
-        <is>
-          <t>https://www.nist.gov/news-events/news/2026/07/nist-announces-funding-opportunity-14-mep-centers-advance-small-and-medium</t>
-        </is>
-      </c>
-      <c r="L62" s="60" t="inlineStr">
-        <is>
-          <t>5aa9c93bc7040291c9f08bfa</t>
-        </is>
-      </c>
-      <c r="M62" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="N62" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O62" s="60" t="inlineStr"/>
-    </row>
-    <row r="63" ht="42" customHeight="1">
-      <c r="A63" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="B63" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-22T12:00:00Z</t>
-        </is>
-      </c>
-      <c r="C63" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="D63" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E63" s="60" t="inlineStr">
-        <is>
-          <t>Artificial Intelligence</t>
-        </is>
-      </c>
-      <c r="F63" s="76" t="n">
-        <v>2</v>
-      </c>
-      <c r="G63" s="60" t="inlineStr">
-        <is>
-          <t>Official Company</t>
-        </is>
-      </c>
-      <c r="H63" s="60" t="inlineStr">
-        <is>
-          <t>OpenAI News</t>
-        </is>
-      </c>
-      <c r="I63" s="60" t="inlineStr">
-        <is>
-          <t>次世代の国家科学を推進する</t>
-        </is>
-      </c>
-      <c r="J63" s="60" t="inlineStr">
-        <is>
-          <t>OpenAIは、米国エネルギー省および国立研究所と連携し、最前線のAIを活用して科学の発見を加速する取り組みを発表しました。</t>
-        </is>
-      </c>
-      <c r="K63" s="60" t="inlineStr">
-        <is>
-          <t>https://openai.com/index/advancing-the-next-era-of-national-science</t>
-        </is>
-      </c>
-      <c r="L63" s="60" t="inlineStr">
-        <is>
-          <t>577ddf6b90e6d70b43383fc6</t>
-        </is>
-      </c>
-      <c r="M63" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="N63" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O63" s="60" t="inlineStr"/>
-    </row>
-    <row r="64" ht="42" customHeight="1">
-      <c r="A64" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="B64" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-22T09:00:00Z</t>
-        </is>
-      </c>
-      <c r="C64" s="60" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="D64" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E64" s="60" t="inlineStr">
-        <is>
-          <t>Fusion Energy</t>
-        </is>
-      </c>
-      <c r="F64" s="76" t="n">
-        <v>0</v>
-      </c>
-      <c r="G64" s="60" t="inlineStr">
-        <is>
-          <t>Major Media</t>
-        </is>
-      </c>
-      <c r="H64" s="60" t="inlineStr">
-        <is>
-          <t>MIT Technology Review</t>
-        </is>
-      </c>
-      <c r="I64" s="60" t="inlineStr">
-        <is>
-          <t>NASAの新しい宇宙望遠鏡が変形ミラーを搭載、私たちのような木星を発見する可能性</t>
-        </is>
-      </c>
-      <c r="J64" s="60" t="inlineStr">
-        <is>
-          <t>NASAのナンシー・グレース・ローマン宇宙望遠鏡が来月末にも打ち上げられる予定で、星の光を効果的に消す「アクティブコロナグラフ」を搭載し、天文学の新たな発見を目指します。</t>
-        </is>
-      </c>
-      <c r="K64" s="60" t="inlineStr">
-        <is>
-          <t>https://www.technologyreview.com/2026/07/22/1140701/shape-shifting-mirrors-roman-space-telescope/</t>
-        </is>
-      </c>
-      <c r="L64" s="60" t="inlineStr">
-        <is>
-          <t>04231693b363104315116185</t>
-        </is>
-      </c>
-      <c r="M64" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="N64" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O64" s="60" t="inlineStr"/>
-    </row>
-    <row r="65" ht="42" customHeight="1">
-      <c r="A65" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="B65" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-22T05:30:00Z</t>
-        </is>
-      </c>
-      <c r="C65" s="60" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="D65" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E65" s="60" t="inlineStr">
-        <is>
-          <t>Artificial Intelligence</t>
-        </is>
-      </c>
-      <c r="F65" s="76" t="n">
-        <v>1</v>
-      </c>
-      <c r="G65" s="60" t="inlineStr">
-        <is>
-          <t>Official Company</t>
-        </is>
-      </c>
-      <c r="H65" s="60" t="inlineStr">
-        <is>
-          <t>OpenAI News</t>
-        </is>
-      </c>
-      <c r="I65" s="60" t="inlineStr">
-        <is>
-          <t>OpenAI Presenceの導入</t>
-        </is>
-      </c>
-      <c r="J65" s="60" t="inlineStr">
-        <is>
-          <t>OpenAI Presenceが、企業が信頼できる音声およびチャットエージェントを展開するためのプラットフォームを提供します。</t>
-        </is>
-      </c>
-      <c r="K65" s="60" t="inlineStr">
-        <is>
-          <t>https://openai.com/index/introducing-openai-presence</t>
-        </is>
-      </c>
-      <c r="L65" s="60" t="inlineStr">
-        <is>
-          <t>839f7a51d7b587ae6fb6fad7</t>
-        </is>
-      </c>
-      <c r="M65" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="N65" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O65" s="60" t="inlineStr"/>
-    </row>
-    <row r="66" ht="42" customHeight="1">
-      <c r="A66" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="B66" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-22T00:00:00Z</t>
-        </is>
-      </c>
-      <c r="C66" s="60" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="D66" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E66" s="60" t="inlineStr">
-        <is>
-          <t>Artificial Intelligence</t>
-        </is>
-      </c>
-      <c r="F66" s="76" t="n">
-        <v>1</v>
-      </c>
-      <c r="G66" s="60" t="inlineStr">
-        <is>
-          <t>Official Company</t>
-        </is>
-      </c>
-      <c r="H66" s="60" t="inlineStr">
-        <is>
-          <t>OpenAI News</t>
-        </is>
-      </c>
-      <c r="I66" s="60" t="inlineStr">
-        <is>
-          <t>NTT DATAグループ、Codexを活用してインシデント分析を30分に短縮</t>
-        </is>
-      </c>
-      <c r="J66" s="60" t="inlineStr">
-        <is>
-          <t>NTT DATAグループがChatGPT EnterpriseとCodexを活用し、9,000人の従業員が業務を自動化し、インシデント分析を30分に短縮することに成功しました。</t>
-        </is>
-      </c>
-      <c r="K66" s="60" t="inlineStr">
-        <is>
-          <t>https://openai.com/index/ntt-data</t>
-        </is>
-      </c>
-      <c r="L66" s="60" t="inlineStr">
-        <is>
-          <t>389ebd02d2834f48054db326</t>
-        </is>
-      </c>
-      <c r="M66" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="N66" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O66" s="60" t="inlineStr"/>
-    </row>
-    <row r="67" ht="42" customHeight="1">
-      <c r="A67" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="B67" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-22T00:00:00Z</t>
-        </is>
-      </c>
-      <c r="C67" s="60" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="D67" s="60" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="E67" s="60" t="inlineStr">
-        <is>
-          <t>Innovation Policy | Biotechnology</t>
-        </is>
-      </c>
-      <c r="F67" s="76" t="n">
-        <v>1</v>
-      </c>
-      <c r="G67" s="60" t="inlineStr">
-        <is>
-          <t>Scientific Publication</t>
-        </is>
-      </c>
-      <c r="H67" s="60" t="inlineStr">
-        <is>
-          <t>Nature</t>
-        </is>
-      </c>
-      <c r="I67" s="60" t="inlineStr">
-        <is>
-          <t>サブ核ゲノム区画化が二価クロマチン活性を制御</t>
-        </is>
-      </c>
-      <c r="J67" s="60" t="inlineStr">
-        <is>
-          <t>遺伝子の空間的な位置を理解することが、エピゲノム調節を理解するために必要であることが示されています。</t>
-        </is>
-      </c>
-      <c r="K67" s="60" t="inlineStr">
-        <is>
-          <t>https://www.nature.com/articles/s41586-026-10832-w</t>
-        </is>
-      </c>
-      <c r="L67" s="60" t="inlineStr">
-        <is>
-          <t>f9bccca3cabb5ce19441f09d</t>
-        </is>
-      </c>
-      <c r="M67" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="N67" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O67" s="60" t="inlineStr"/>
-    </row>
-    <row r="68" ht="42" customHeight="1">
-      <c r="A68" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="B68" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-22T00:00:00Z</t>
-        </is>
-      </c>
-      <c r="C68" s="60" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="D68" s="60" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="E68" s="60" t="inlineStr">
-        <is>
-          <t>Fusion Energy</t>
-        </is>
-      </c>
-      <c r="F68" s="76" t="n">
-        <v>0</v>
-      </c>
-      <c r="G68" s="60" t="inlineStr">
-        <is>
-          <t>Scientific Publication</t>
-        </is>
-      </c>
-      <c r="H68" s="60" t="inlineStr">
-        <is>
-          <t>Nature</t>
-        </is>
-      </c>
-      <c r="I68" s="60" t="inlineStr">
-        <is>
-          <t>巨大な‘エクソ衛星’が月の定義を巡る議論を引き起こす</t>
-        </is>
-      </c>
-      <c r="J68" s="60" t="inlineStr">
-        <is>
-          <t>遠方の木星質量の天体の発見がエクソ月の検出への道を開く可能性があり、また、ナマズに見られる珍しい伝染性癌についても言及されています。</t>
-        </is>
-      </c>
-      <c r="K68" s="60" t="inlineStr">
-        <is>
-          <t>https://www.nature.com/articles/d41586-026-02299-6</t>
-        </is>
-      </c>
-      <c r="L68" s="60" t="inlineStr">
-        <is>
-          <t>a3eb7f1e33aee131ed0b4bf7</t>
-        </is>
-      </c>
-      <c r="M68" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="N68" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O68" s="60" t="inlineStr"/>
-    </row>
-    <row r="69" ht="42" customHeight="1">
-      <c r="A69" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="B69" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-22T00:00:00Z</t>
-        </is>
-      </c>
-      <c r="C69" s="60" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="D69" s="60" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="E69" s="60" t="inlineStr">
-        <is>
-          <t>Quantum</t>
-        </is>
-      </c>
-      <c r="F69" s="76" t="n">
-        <v>0</v>
-      </c>
-      <c r="G69" s="60" t="inlineStr">
-        <is>
-          <t>Scientific Publication</t>
-        </is>
-      </c>
-      <c r="H69" s="60" t="inlineStr">
-        <is>
-          <t>Nature</t>
-        </is>
-      </c>
-      <c r="I69" s="60" t="inlineStr">
-        <is>
-          <t>量子コンピュータの仕組み</t>
-        </is>
-      </c>
-      <c r="J69" s="60" t="inlineStr">
-        <is>
-          <t>最近のブレークスルーにより、実用的な量子コンピュータが10年以内に登場する可能性が示唆されています。</t>
-        </is>
-      </c>
-      <c r="K69" s="60" t="inlineStr">
-        <is>
-          <t>https://www.nature.com/articles/d41586-026-02219-8</t>
-        </is>
-      </c>
-      <c r="L69" s="60" t="inlineStr">
-        <is>
-          <t>626697d1d64f5d985431135f</t>
-        </is>
-      </c>
-      <c r="M69" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="N69" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O69" s="60" t="inlineStr"/>
-    </row>
-    <row r="70" ht="42" customHeight="1">
-      <c r="A70" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="B70" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-22T00:00:00Z</t>
-        </is>
-      </c>
-      <c r="C70" s="60" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="D70" s="60" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="E70" s="60" t="inlineStr">
-        <is>
-          <t>Biotechnology</t>
-        </is>
-      </c>
-      <c r="F70" s="76" t="n">
-        <v>0</v>
-      </c>
-      <c r="G70" s="60" t="inlineStr">
-        <is>
-          <t>Scientific Publication</t>
-        </is>
-      </c>
-      <c r="H70" s="60" t="inlineStr">
-        <is>
-          <t>Nature</t>
-        </is>
-      </c>
-      <c r="I70" s="60" t="inlineStr">
-        <is>
-          <t>CRISPR–Casが抗ファージ防御システムの発現を調節</t>
-        </is>
-      </c>
-      <c r="J70" s="60" t="inlineStr">
-        <is>
-          <t>CRISPR–Casシステムが多様な先天的防御を調整し、ウイルスからの保護と適応度のバランスを取る仕組みが解明されました。</t>
-        </is>
-      </c>
-      <c r="K70" s="60" t="inlineStr">
-        <is>
-          <t>https://www.nature.com/articles/s41586-026-10833-9</t>
-        </is>
-      </c>
-      <c r="L70" s="60" t="inlineStr">
-        <is>
-          <t>a49dbeef4f425713e07751f7</t>
-        </is>
-      </c>
-      <c r="M70" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="N70" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O70" s="60" t="inlineStr"/>
-    </row>
-    <row r="71" ht="42" customHeight="1">
-      <c r="A71" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="B71" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-21T22:35:45Z</t>
-        </is>
-      </c>
-      <c r="C71" s="60" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="D71" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E71" s="60" t="inlineStr">
-        <is>
-          <t>Artificial Intelligence | Semiconductors &amp; Telecom</t>
-        </is>
-      </c>
-      <c r="F71" s="76" t="n">
-        <v>0</v>
-      </c>
-      <c r="G71" s="60" t="inlineStr">
-        <is>
-          <t>Official Company</t>
-        </is>
-      </c>
-      <c r="H71" s="60" t="inlineStr">
-        <is>
-          <t>NVIDIA Blog</t>
-        </is>
-      </c>
-      <c r="I71" s="60" t="inlineStr">
-        <is>
-          <t>フォートワースにおけるWistronの先進製造工場開設</t>
-        </is>
-      </c>
-      <c r="J71" s="60" t="inlineStr">
-        <is>
-          <t>Wistronがテキサス州フォートワースにAIシステム用の先進製造工場を開設し、324,000平方フィートの施設でスーパーチップを生産します。</t>
-        </is>
-      </c>
-      <c r="K71" s="60" t="inlineStr">
-        <is>
-          <t>https://blogs.nvidia.com/blog/wistron-manufacturing-texas/</t>
-        </is>
-      </c>
-      <c r="L71" s="60" t="inlineStr">
-        <is>
-          <t>21f1e1f3e19b1a5bf0af3cb7</t>
-        </is>
-      </c>
-      <c r="M71" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="N71" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O71" s="60" t="inlineStr"/>
-    </row>
-    <row r="72" ht="42" customHeight="1">
-      <c r="A72" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="B72" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-21T19:44:19Z</t>
-        </is>
-      </c>
-      <c r="C72" s="60" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="D72" s="60" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="E72" s="60" t="inlineStr">
-        <is>
-          <t>Innovation Policy | Fusion Energy</t>
-        </is>
-      </c>
-      <c r="F72" s="76" t="n">
-        <v>2</v>
-      </c>
-      <c r="G72" s="60" t="inlineStr">
-        <is>
-          <t>Industry Association</t>
-        </is>
-      </c>
-      <c r="H72" s="60" t="inlineStr">
-        <is>
-          <t>Fusion Industry Association</t>
-        </is>
-      </c>
-      <c r="I72" s="60" t="inlineStr">
-        <is>
-          <t>FIAとクリーンエアタスクフォースが融合エネルギーの基準を発表</t>
-        </is>
-      </c>
-      <c r="J72" s="60" t="inlineStr">
-        <is>
-          <t>融合産業協会がクリーンエアタスクフォースと共同で、融合エネルギーの安全な展開を確保しつつ革新を促進するための原則をまとめた文書を発表しました。</t>
-        </is>
-      </c>
-      <c r="K72" s="60" t="inlineStr">
-        <is>
-          <t>https://www.fusionindustryassociation.org/fia-and-clean-air-task-force-publish-principles-on-codes-and-standards/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=fia-and-clean-air-task-force-publish-principles-on-codes-and-standards</t>
-        </is>
-      </c>
-      <c r="L72" s="60" t="inlineStr">
-        <is>
-          <t>2366dc909672b56b77a196bd</t>
-        </is>
-      </c>
-      <c r="M72" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="N72" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O72" s="60" t="inlineStr"/>
-    </row>
-    <row r="73" ht="42" customHeight="1">
-      <c r="A73" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="B73" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-21T17:00:00Z</t>
-        </is>
-      </c>
-      <c r="C73" s="60" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="D73" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E73" s="60" t="inlineStr">
-        <is>
-          <t>Artificial Intelligence</t>
-        </is>
-      </c>
-      <c r="F73" s="76" t="n">
-        <v>1</v>
-      </c>
-      <c r="G73" s="60" t="inlineStr">
-        <is>
-          <t>Official Company</t>
-        </is>
-      </c>
-      <c r="H73" s="60" t="inlineStr">
-        <is>
-          <t>OpenAI News</t>
-        </is>
-      </c>
-      <c r="I73" s="60" t="inlineStr">
-        <is>
-          <t>小規模ビジネス向けChatGPTプログラムの導入</t>
-        </is>
-      </c>
-      <c r="J73" s="60" t="inlineStr">
-        <is>
-          <t>OpenAIが小規模ビジネス向けのChatGPTプログラムを開始し、起業家がAIスキルを習得し、業務を自動化し、成長を促進する手助けを行います。</t>
-        </is>
-      </c>
-      <c r="K73" s="60" t="inlineStr">
-        <is>
-          <t>https://openai.com/index/introducing-chatgpt-small-business-program</t>
-        </is>
-      </c>
-      <c r="L73" s="60" t="inlineStr">
-        <is>
-          <t>3064e426d18ccd85acab9b00</t>
-        </is>
-      </c>
-      <c r="M73" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="N73" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O73" s="60" t="inlineStr"/>
-    </row>
-    <row r="74" ht="42" customHeight="1">
-      <c r="A74" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="B74" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-21T15:36:43Z</t>
-        </is>
-      </c>
-      <c r="C74" s="60" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="D74" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E74" s="60" t="inlineStr">
-        <is>
-          <t>Semiconductors &amp; Telecom</t>
-        </is>
-      </c>
-      <c r="F74" s="76" t="n">
-        <v>0</v>
-      </c>
-      <c r="G74" s="60" t="inlineStr">
-        <is>
-          <t>Official Company</t>
-        </is>
-      </c>
-      <c r="H74" s="60" t="inlineStr">
-        <is>
-          <t>NVIDIA Blog</t>
-        </is>
-      </c>
-      <c r="I74" s="60" t="inlineStr">
-        <is>
-          <t>NVIDIA Vera Rubin、パートナー向けに最適な性能とコストを提供</t>
-        </is>
-      </c>
-      <c r="J74" s="60" t="inlineStr">
-        <is>
-          <t>NVIDIA Vera Rubinが生産を拡大し、CoreWeave、Google Cloud、Microsoft Azure、Oracle Cloud Infrastructureなどのパートナーと共に、350以上の工場サイトで顧客の計算需要に応えるための供給チェーンを構築しています。</t>
-        </is>
-      </c>
-      <c r="K74" s="60" t="inlineStr">
-        <is>
-          <t>https://blogs.nvidia.com/blog/vera-rubin/</t>
-        </is>
-      </c>
-      <c r="L74" s="60" t="inlineStr">
-        <is>
-          <t>ffef75ffd9647e2c722b429e</t>
-        </is>
-      </c>
-      <c r="M74" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="N74" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O74" s="60" t="inlineStr"/>
-    </row>
-    <row r="75" ht="42" customHeight="1">
-      <c r="A75" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="B75" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-21T15:06:49Z</t>
-        </is>
-      </c>
-      <c r="C75" s="60" t="inlineStr">
-        <is>
-          <t>EU &amp; Europe</t>
-        </is>
-      </c>
-      <c r="D75" s="60" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="E75" s="60" t="inlineStr">
-        <is>
-          <t>Innovation Policy</t>
-        </is>
-      </c>
-      <c r="F75" s="76" t="n">
-        <v>3</v>
-      </c>
-      <c r="G75" s="60" t="inlineStr">
-        <is>
-          <t>Government</t>
-        </is>
-      </c>
-      <c r="H75" s="60" t="inlineStr">
-        <is>
-          <t>UK DSIT</t>
-        </is>
-      </c>
-      <c r="I75" s="60" t="inlineStr">
-        <is>
-          <t>透明性データ：DSIT：労働力管理情報、2026年6月</t>
-        </is>
-      </c>
-      <c r="J75" s="60" t="inlineStr">
-        <is>
-          <t>部門のスタッフ数とコストに関する報告が行われています。</t>
-        </is>
-      </c>
-      <c r="K75" s="60" t="inlineStr">
-        <is>
-          <t>https://www.gov.uk/government/publications/dsit-workforce-management-information-june-2026</t>
-        </is>
-      </c>
-      <c r="L75" s="60" t="inlineStr">
-        <is>
-          <t>68c02c5c6a2ee3c9c91fc7f1</t>
-        </is>
-      </c>
-      <c r="M75" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="N75" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O75" s="60" t="inlineStr"/>
-    </row>
-    <row r="76" ht="42" customHeight="1">
-      <c r="A76" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="B76" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-21T15:06:31Z</t>
-        </is>
-      </c>
-      <c r="C76" s="60" t="inlineStr">
-        <is>
-          <t>EU &amp; Europe</t>
-        </is>
-      </c>
-      <c r="D76" s="60" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="E76" s="60" t="inlineStr">
-        <is>
-          <t>Innovation Policy</t>
-        </is>
-      </c>
-      <c r="F76" s="76" t="n">
-        <v>5</v>
-      </c>
-      <c r="G76" s="60" t="inlineStr">
-        <is>
-          <t>Government</t>
-        </is>
-      </c>
-      <c r="H76" s="60" t="inlineStr">
-        <is>
-          <t>UK DSIT</t>
-        </is>
-      </c>
-      <c r="I76" s="60" t="inlineStr">
-        <is>
-          <t>ガイダンス：TechFirstローカル</t>
-        </is>
-      </c>
-      <c r="J76" s="60" t="inlineStr">
-        <is>
-          <t>TechFirstローカル助成金プログラムの詳細が公開され、デジタルスキルの向上とテクノロジー職への支援が行われます。</t>
-        </is>
-      </c>
-      <c r="K76" s="60" t="inlineStr">
-        <is>
-          <t>https://www.gov.uk/government/publications/techlocal</t>
-        </is>
-      </c>
-      <c r="L76" s="60" t="inlineStr">
-        <is>
-          <t>88893e13a25a6efc42ed57ea</t>
-        </is>
-      </c>
-      <c r="M76" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="N76" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O76" s="60" t="inlineStr"/>
-    </row>
-    <row r="77" ht="42" customHeight="1">
-      <c r="A77" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="B77" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-21T15:05:29Z</t>
-        </is>
-      </c>
-      <c r="C77" s="60" t="inlineStr">
-        <is>
-          <t>EU &amp; Europe</t>
-        </is>
-      </c>
-      <c r="D77" s="60" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="E77" s="60" t="inlineStr">
-        <is>
-          <t>Innovation Policy</t>
-        </is>
-      </c>
-      <c r="F77" s="76" t="n">
-        <v>3</v>
-      </c>
-      <c r="G77" s="60" t="inlineStr">
-        <is>
-          <t>Government</t>
-        </is>
-      </c>
-      <c r="H77" s="60" t="inlineStr">
-        <is>
-          <t>UK DSIT</t>
-        </is>
-      </c>
-      <c r="I77" s="60" t="inlineStr">
-        <is>
-          <t>TechFirst博士課程支援</t>
-        </is>
-      </c>
-      <c r="J77" s="60" t="inlineStr">
-        <is>
-          <t>TechFirstの一環として、英国の急成長するテクノロジーセクターへの道を開く政府のスキルプログラムです。</t>
-        </is>
-      </c>
-      <c r="K77" s="60" t="inlineStr">
-        <is>
-          <t>https://www.gov.uk/guidance/techexpert</t>
-        </is>
-      </c>
-      <c r="L77" s="60" t="inlineStr">
-        <is>
-          <t>406416679082f87595cbd50b</t>
-        </is>
-      </c>
-      <c r="M77" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="N77" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O77" s="60" t="inlineStr"/>
-    </row>
-    <row r="78" ht="42" customHeight="1">
-      <c r="A78" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="B78" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-21T15:05:21Z</t>
-        </is>
-      </c>
-      <c r="C78" s="60" t="inlineStr">
-        <is>
-          <t>EU &amp; Europe</t>
-        </is>
-      </c>
-      <c r="D78" s="60" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="E78" s="60" t="inlineStr">
-        <is>
-          <t>Innovation Policy</t>
-        </is>
-      </c>
-      <c r="F78" s="76" t="n">
-        <v>3</v>
-      </c>
-      <c r="G78" s="60" t="inlineStr">
-        <is>
-          <t>Government</t>
-        </is>
-      </c>
-      <c r="H78" s="60" t="inlineStr">
-        <is>
-          <t>UK DSIT</t>
-        </is>
-      </c>
-      <c r="I78" s="60" t="inlineStr">
-        <is>
-          <t>TechFirst</t>
-        </is>
-      </c>
-      <c r="J78" s="60" t="inlineStr">
-        <is>
-          <t>TechFirstは、英国の急成長するテクノロジーセクターへの道を開く政府の主力技術スキルプログラムであり、英国全土での機会を提供します。</t>
-        </is>
-      </c>
-      <c r="K78" s="60" t="inlineStr">
-        <is>
-          <t>https://www.gov.uk/guidance/techfirst</t>
-        </is>
-      </c>
-      <c r="L78" s="60" t="inlineStr">
-        <is>
-          <t>4ae9e496e9b66c66de074041</t>
-        </is>
-      </c>
-      <c r="M78" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="N78" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O78" s="60" t="inlineStr"/>
-    </row>
-    <row r="79" ht="42" customHeight="1">
-      <c r="A79" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="B79" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-21T15:05:11Z</t>
-        </is>
-      </c>
-      <c r="C79" s="60" t="inlineStr">
-        <is>
-          <t>EU &amp; Europe</t>
-        </is>
-      </c>
-      <c r="D79" s="60" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="E79" s="60" t="inlineStr">
-        <is>
-          <t>Innovation Policy | Semiconductors &amp; Telecom</t>
-        </is>
-      </c>
-      <c r="F79" s="76" t="n">
-        <v>3</v>
-      </c>
-      <c r="G79" s="60" t="inlineStr">
-        <is>
-          <t>Government</t>
-        </is>
-      </c>
-      <c r="H79" s="60" t="inlineStr">
-        <is>
-          <t>UK DSIT</t>
-        </is>
-      </c>
-      <c r="I79" s="60" t="inlineStr">
-        <is>
-          <t>政策文書：固定通信の近代化憲章</t>
-        </is>
-      </c>
-      <c r="J79" s="60" t="inlineStr">
-        <is>
-          <t>この文書は、通信事業者が現在および将来の固定通信の近代化を実施する際に従うべき手順を示しています。</t>
-        </is>
-      </c>
-      <c r="K79" s="60" t="inlineStr">
-        <is>
-          <t>https://www.gov.uk/government/publications/fixed-telecoms-modernisation-charter</t>
-        </is>
-      </c>
-      <c r="L79" s="60" t="inlineStr">
-        <is>
-          <t>d5e4431b57fcb4b6271f6c72</t>
-        </is>
-      </c>
-      <c r="M79" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="N79" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O79" s="60" t="inlineStr"/>
-    </row>
-    <row r="80" ht="42" customHeight="1">
-      <c r="A80" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="B80" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-21T15:00:20Z</t>
-        </is>
-      </c>
-      <c r="C80" s="60" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="D80" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E80" s="60" t="inlineStr">
-        <is>
-          <t>Artificial Intelligence | Semiconductors &amp; Telecom</t>
-        </is>
-      </c>
-      <c r="F80" s="76" t="n">
-        <v>0</v>
-      </c>
-      <c r="G80" s="60" t="inlineStr">
-        <is>
-          <t>Official Company</t>
-        </is>
-      </c>
-      <c r="H80" s="60" t="inlineStr">
-        <is>
-          <t>NVIDIA Blog</t>
-        </is>
-      </c>
-      <c r="I80" s="60" t="inlineStr">
-        <is>
-          <t>Vera Rubin向けに設計されたNVIDIA Spectrum-6、ギガスケールAI工場に登場</t>
-        </is>
-      </c>
-      <c r="J80" s="60" t="inlineStr">
-        <is>
-          <t>AIがギガスケールの時代に突入し、最先端のAI工場が数十万のGPUとCPUを統合して新たな知能を生成しています。このレベルでは、ネットワーキングが計算能力を高める重要な要素となります。</t>
-        </is>
-      </c>
-      <c r="K80" s="60" t="inlineStr">
-        <is>
-          <t>https://blogs.nvidia.com/blog/nvidia-spectrum-six-arrives-in-gigascale-ai-factories/</t>
-        </is>
-      </c>
-      <c r="L80" s="60" t="inlineStr">
-        <is>
-          <t>6f3401cebeb5dc5a8f12a872</t>
-        </is>
-      </c>
-      <c r="M80" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="N80" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O80" s="60" t="inlineStr"/>
-    </row>
-    <row r="81" ht="42" customHeight="1">
-      <c r="A81" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="B81" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-21T14:48:28Z</t>
-        </is>
-      </c>
-      <c r="C81" s="60" t="inlineStr">
-        <is>
-          <t>EU &amp; Europe</t>
-        </is>
-      </c>
-      <c r="D81" s="60" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="E81" s="60" t="inlineStr">
-        <is>
-          <t>Fusion Energy</t>
-        </is>
-      </c>
-      <c r="F81" s="76" t="n">
-        <v>1</v>
-      </c>
-      <c r="G81" s="60" t="inlineStr">
-        <is>
-          <t>Industry Association</t>
-        </is>
-      </c>
-      <c r="H81" s="60" t="inlineStr">
-        <is>
-          <t>Fusion Industry Association</t>
-        </is>
-      </c>
-      <c r="I81" s="60" t="inlineStr">
-        <is>
-          <t>FIA、EUの核融合エネルギー資金調達の道筋を示す</t>
-        </is>
-      </c>
-      <c r="J81" s="60" t="inlineStr">
-        <is>
-          <t>核融合産業協会は、商業核融合エネルギーのための実用的なEU資金調達ロードマップを発表しました。研究から実証、商業展開に向けた各段階で必要な資金調達手法の進化が求められています。</t>
-        </is>
-      </c>
-      <c r="K81" s="60" t="inlineStr">
-        <is>
-          <t>https://www.fusionindustryassociation.org/fia-outlines-eu-financing-pathway-for-fusion/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=fia-outlines-eu-financing-pathway-for-fusion</t>
-        </is>
-      </c>
-      <c r="L81" s="60" t="inlineStr">
-        <is>
-          <t>88af233d904d670250fa5a31</t>
-        </is>
-      </c>
-      <c r="M81" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="N81" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O81" s="60" t="inlineStr"/>
-    </row>
-    <row r="82" ht="42" customHeight="1">
-      <c r="A82" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="B82" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-21T13:30:36Z</t>
-        </is>
-      </c>
-      <c r="C82" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="D82" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E82" s="60" t="inlineStr">
-        <is>
-          <t>Innovation Policy | Artificial Intelligence</t>
-        </is>
-      </c>
-      <c r="F82" s="76" t="n">
-        <v>3</v>
-      </c>
-      <c r="G82" s="60" t="inlineStr">
-        <is>
-          <t>Policy Institute</t>
-        </is>
-      </c>
-      <c r="H82" s="60" t="inlineStr">
-        <is>
-          <t>CSET</t>
-        </is>
-      </c>
-      <c r="I82" s="60" t="inlineStr">
-        <is>
-          <t>AIシステムはなぜ誤動作するのか？</t>
-        </is>
-      </c>
-      <c r="J82" s="60" t="inlineStr">
-        <is>
-          <t>AIシステムの進化が進む中、その失敗の原因について考察するブログが公開されました。AIの誤動作の原因を探る内容です。</t>
-        </is>
-      </c>
-      <c r="K82" s="60" t="inlineStr">
-        <is>
-          <t>https://cset.georgetown.edu/article/why-do-ai-systems-misbehave/</t>
-        </is>
-      </c>
-      <c r="L82" s="60" t="inlineStr">
-        <is>
-          <t>3e1aa390ad965782cc86c386</t>
-        </is>
-      </c>
-      <c r="M82" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="N82" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O82" s="60" t="inlineStr"/>
-    </row>
-    <row r="83" ht="42" customHeight="1">
-      <c r="A83" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="B83" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-21T13:00:47Z</t>
-        </is>
-      </c>
-      <c r="C83" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="D83" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E83" s="60" t="inlineStr">
-        <is>
-          <t>Artificial Intelligence | Semiconductors &amp; Telecom | Healthcare</t>
-        </is>
-      </c>
-      <c r="F83" s="76" t="n">
-        <v>0</v>
-      </c>
-      <c r="G83" s="60" t="inlineStr">
-        <is>
-          <t>Official Company</t>
-        </is>
-      </c>
-      <c r="H83" s="60" t="inlineStr">
-        <is>
-          <t>NVIDIA Blog</t>
-        </is>
-      </c>
-      <c r="I83" s="60" t="inlineStr">
-        <is>
-          <t>NVIDIAとパートナー、アメリカのために製造を推進</t>
-        </is>
-      </c>
-      <c r="J83" s="60" t="inlineStr">
-        <is>
-          <t>NVIDIAとそのパートナーは、アメリカの製造業、供給網、エネルギー網、熟練労働力に投資し、より良い医療、画期的な科学的発見、産業生産性の向上、グローバルな技術リーダーシップを実現するためのインフラを構築しています。</t>
-        </is>
-      </c>
-      <c r="K83" s="60" t="inlineStr">
-        <is>
-          <t>https://blogs.nvidia.com/blog/nvidia-and-partners-build-in-america-for-america/</t>
-        </is>
-      </c>
-      <c r="L83" s="60" t="inlineStr">
-        <is>
-          <t>c815807553a0a9fc82116a87</t>
-        </is>
-      </c>
-      <c r="M83" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="N83" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O83" s="60" t="inlineStr"/>
-    </row>
-    <row r="84" ht="42" customHeight="1">
-      <c r="A84" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="B84" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-21T13:00:14Z</t>
-        </is>
-      </c>
-      <c r="C84" s="60" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="D84" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E84" s="60" t="inlineStr">
-        <is>
-          <t>Semiconductors &amp; Telecom</t>
-        </is>
-      </c>
-      <c r="F84" s="76" t="n">
-        <v>0</v>
-      </c>
-      <c r="G84" s="60" t="inlineStr">
-        <is>
-          <t>Official Company</t>
-        </is>
-      </c>
-      <c r="H84" s="60" t="inlineStr">
-        <is>
-          <t>Intel Newsroom</t>
-        </is>
-      </c>
-      <c r="I84" s="60" t="inlineStr">
-        <is>
-          <t>インテルとフォーティネット、サイバーセキュリティ革新を推進し供給網の強靭性を強化</t>
-        </is>
-      </c>
-      <c r="J84" s="60" t="inlineStr">
-        <is>
-          <t>インテルとフォーティネットは、Fortinet Security Processor 6 (SP6)の開発に向けた戦略的な協力を発表しました。このコラボレーションは、両社の長年の関係を基に、セキュリティプロセッサの専門知識とインテルの先進的な設計・製造能力を組み合わせています。</t>
-        </is>
-      </c>
-      <c r="K84" s="60" t="inlineStr">
-        <is>
-          <t>https://newsroom.intel.com/manufacturing/intel-and-fortinet-collaborate-to-advance-cybersecurity-innovation-and-strengthen-global-supply-chain-resilience</t>
-        </is>
-      </c>
-      <c r="L84" s="60" t="inlineStr">
-        <is>
-          <t>28388342f57d2cae1a96b7b7</t>
-        </is>
-      </c>
-      <c r="M84" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="N84" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O84" s="60" t="inlineStr"/>
-    </row>
-    <row r="85" ht="42" customHeight="1">
-      <c r="A85" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="B85" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-21T12:10:00Z</t>
-        </is>
-      </c>
-      <c r="C85" s="60" t="inlineStr">
-        <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="D85" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E85" s="60" t="inlineStr">
-        <is>
-          <t>Artificial Intelligence</t>
-        </is>
-      </c>
-      <c r="F85" s="76" t="n">
-        <v>1</v>
-      </c>
-      <c r="G85" s="60" t="inlineStr">
-        <is>
-          <t>Major Media</t>
-        </is>
-      </c>
-      <c r="H85" s="60" t="inlineStr">
-        <is>
-          <t>MIT Technology Review</t>
-        </is>
-      </c>
-      <c r="I85" s="60" t="inlineStr">
-        <is>
-          <t>ダウンロード：中国のAIがホワイトハウスを分断、記録的な著作権支払い</t>
-        </is>
-      </c>
-      <c r="J85" s="60" t="inlineStr">
-        <is>
-          <t>本日のテクノロジーに関するニュースレターでは、中国のAIモデルがトランプ政権内での対立を引き起こしていることが報じられている。</t>
-        </is>
-      </c>
-      <c r="K85" s="60" t="inlineStr">
-        <is>
-          <t>https://www.technologyreview.com/2026/07/21/1140685/the-download-chinese-ai-divides-white-house-anthropic-copyright-settlement/</t>
-        </is>
-      </c>
-      <c r="L85" s="60" t="inlineStr">
-        <is>
-          <t>f9addf0904b9de5b7bcc326b</t>
-        </is>
-      </c>
-      <c r="M85" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="N85" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O85" s="60" t="inlineStr"/>
-    </row>
-    <row r="86" ht="42" customHeight="1">
-      <c r="A86" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="B86" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-21T10:37:34Z</t>
-        </is>
-      </c>
-      <c r="C86" s="60" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="D86" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E86" s="60" t="inlineStr">
-        <is>
-          <t>Artificial Intelligence | Semiconductors &amp; Telecom</t>
-        </is>
-      </c>
-      <c r="F86" s="76" t="n">
-        <v>0</v>
-      </c>
-      <c r="G86" s="60" t="inlineStr">
-        <is>
-          <t>Major Media</t>
-        </is>
-      </c>
-      <c r="H86" s="60" t="inlineStr">
-        <is>
-          <t>MIT Technology Review</t>
-        </is>
-      </c>
-      <c r="I86" s="60" t="inlineStr">
-        <is>
-          <t>材料科学の革新で次世代AIを推進</t>
-        </is>
-      </c>
-      <c r="J86" s="60" t="inlineStr">
-        <is>
-          <t>AIに関する議論はアルゴリズムや計算能力に集中しがちだが、これらの進展を可能にするもう一つの革新の層が存在する。それは先進材料であり、次世代のAI技術はより多くの処理能力やメモリ、エネルギー効率を求めている。</t>
-        </is>
-      </c>
-      <c r="K86" s="60" t="inlineStr">
-        <is>
-          <t>https://www.technologyreview.com/2026/07/21/1140602/advancing-next-gen-ai-with-materials-science-innovation/</t>
-        </is>
-      </c>
-      <c r="L86" s="60" t="inlineStr">
-        <is>
-          <t>6b7e59d6f503e3d45c9ea292</t>
-        </is>
-      </c>
-      <c r="M86" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="N86" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O86" s="60" t="inlineStr"/>
-    </row>
-    <row r="87" ht="42" customHeight="1">
-      <c r="A87" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="B87" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-21T08:26:17Z</t>
-        </is>
-      </c>
-      <c r="C87" s="60" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="D87" s="60" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="E87" s="60" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-      <c r="F87" s="76" t="n">
-        <v>1</v>
-      </c>
-      <c r="G87" s="60" t="inlineStr">
-        <is>
-          <t>Intergovernmental</t>
-        </is>
-      </c>
-      <c r="H87" s="60" t="inlineStr">
-        <is>
-          <t>WHO News</t>
-        </is>
-      </c>
-      <c r="I87" s="60" t="inlineStr">
-        <is>
-          <t>国連報告：世界の飢餓レベルが3年連続で改善も地域格差が残る</t>
-        </is>
-      </c>
-      <c r="J87" s="60" t="inlineStr">
-        <is>
-          <t>2025年に世界の飢餓が3年連続で減少したことが報告されているが、改善は脆弱で不均一であり、2030年までに持続可能な開発目標を達成するには不十分であると指摘されている。</t>
-        </is>
-      </c>
-      <c r="K87" s="60" t="inlineStr">
-        <is>
-          <t>https://www.who.int/news/item/21-07-2026-un-report--global-hunger-levels-ease-for-third-consecutive-year-as-regional-disparities-persist</t>
-        </is>
-      </c>
-      <c r="L87" s="60" t="inlineStr">
-        <is>
-          <t>223e20b3abaf53bd3b29f3e1</t>
-        </is>
-      </c>
-      <c r="M87" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="N87" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O87" s="60" t="inlineStr"/>
-    </row>
-    <row r="88" ht="42" customHeight="1">
-      <c r="A88" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="B88" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-21T07:00:00Z</t>
-        </is>
-      </c>
-      <c r="C88" s="60" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="D88" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E88" s="60" t="inlineStr">
-        <is>
-          <t>Artificial Intelligence</t>
-        </is>
-      </c>
-      <c r="F88" s="76" t="n">
-        <v>1</v>
-      </c>
-      <c r="G88" s="60" t="inlineStr">
-        <is>
-          <t>Official Company</t>
-        </is>
-      </c>
-      <c r="H88" s="60" t="inlineStr">
-        <is>
-          <t>OpenAI News</t>
-        </is>
-      </c>
-      <c r="I88" s="60" t="inlineStr">
-        <is>
-          <t>OpenAIとHugging Face、モデル評価中のセキュリティインシデントに対処するため提携</t>
-        </is>
-      </c>
-      <c r="J88" s="60" t="inlineStr">
-        <is>
-          <t>OpenAIとHugging Faceは、AIモデル評価中に発生したセキュリティインシデントに関する初期の調査結果を共有し、高度なサイバー能力と防御者への教訓を強調している。</t>
-        </is>
-      </c>
-      <c r="K88" s="60" t="inlineStr">
-        <is>
-          <t>https://openai.com/index/hugging-face-model-evaluation-security-incident</t>
-        </is>
-      </c>
-      <c r="L88" s="60" t="inlineStr">
-        <is>
-          <t>d925d8c91f460a44f07089c2</t>
-        </is>
-      </c>
-      <c r="M88" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="N88" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O88" s="60" t="inlineStr"/>
-    </row>
-    <row r="89" ht="42" customHeight="1">
-      <c r="A89" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="B89" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-20T15:55:00Z</t>
-        </is>
-      </c>
-      <c r="C89" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="D89" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E89" s="60" t="inlineStr">
-        <is>
-          <t>Semiconductors &amp; Telecom</t>
-        </is>
-      </c>
-      <c r="F89" s="76" t="n">
-        <v>0</v>
-      </c>
-      <c r="G89" s="60" t="inlineStr">
-        <is>
-          <t>Major Media</t>
-        </is>
-      </c>
-      <c r="H89" s="60" t="inlineStr">
-        <is>
-          <t>IEEE Spectrum</t>
-        </is>
-      </c>
-      <c r="I89" s="60" t="inlineStr">
-        <is>
-          <t>先端半導体故障解析のためのSEMガイド低電圧FIB仕上げ</t>
-        </is>
-      </c>
-      <c r="J89" s="60" t="inlineStr">
-        <is>
-          <t>ZEISS Crossbeam 750 FIBSEMが、TEMラメラ準備、トモグラフィー、先進的なナノファブリケーションのための新たな基準を設定している。これにより、解像度、信号対雑音比、使用可能な視野が向上し、取得時間が短縮される。</t>
-        </is>
-      </c>
-      <c r="K89" s="60" t="inlineStr">
-        <is>
-          <t>https://event.on24.com/wcc/r/5418459/287E3D5B99470D34C830D69A24B3B207</t>
-        </is>
-      </c>
-      <c r="L89" s="60" t="inlineStr">
-        <is>
-          <t>73d0028e337a76c2cd00f1bc</t>
-        </is>
-      </c>
-      <c r="M89" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="N89" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O89" s="60" t="inlineStr"/>
-    </row>
-    <row r="90" ht="42" customHeight="1">
-      <c r="A90" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="B90" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-20T15:34:49Z</t>
-        </is>
-      </c>
-      <c r="C90" s="60" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="D90" s="60" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="E90" s="60" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-      <c r="F90" s="76" t="n">
-        <v>1</v>
-      </c>
-      <c r="G90" s="60" t="inlineStr">
-        <is>
-          <t>Intergovernmental</t>
-        </is>
-      </c>
-      <c r="H90" s="60" t="inlineStr">
-        <is>
-          <t>WHO News</t>
-        </is>
-      </c>
-      <c r="I90" s="60" t="inlineStr">
-        <is>
-          <t>WHOがResearch4Lifeの25周年を記念、120カ国以上で科学知識へのアクセスを促進</t>
-        </is>
-      </c>
-      <c r="J90" s="60" t="inlineStr">
-        <is>
-          <t>世界保健機関（WHO）は、低中所得国の研究者や教育者、医療専門家、政策立案者に手頃な価格または無料で科学知識へのアクセスを提供する公私パートナーシップResearch4Lifeの25周年を迎えた。このパートナーシップは、120カ国以上で科学知識へのアクセスを大幅に拡大するのに寄与している。</t>
-        </is>
-      </c>
-      <c r="K90" s="60" t="inlineStr">
-        <is>
-          <t>https://www.who.int/news/item/21-07-2026-who-marks-25-years-of-research4life--advancing-access-to-scientific-knowledge-in-more-than-120-countries</t>
-        </is>
-      </c>
-      <c r="L90" s="60" t="inlineStr">
-        <is>
-          <t>09e6494006eb3af009c1a30f</t>
-        </is>
-      </c>
-      <c r="M90" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="N90" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O90" s="60" t="inlineStr"/>
-    </row>
-    <row r="91" ht="42" customHeight="1">
-      <c r="A91" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="B91" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-20T07:09:01Z</t>
-        </is>
-      </c>
-      <c r="C91" s="60" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="D91" s="60" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="E91" s="60" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-      <c r="F91" s="76" t="n">
-        <v>1</v>
-      </c>
-      <c r="G91" s="60" t="inlineStr">
-        <is>
-          <t>Intergovernmental</t>
-        </is>
-      </c>
-      <c r="H91" s="60" t="inlineStr">
-        <is>
-          <t>WHO News</t>
-        </is>
-      </c>
-      <c r="I91" s="60" t="inlineStr">
-        <is>
-          <t>世界の交通事故死者数21%減少も、さらなる対策が必要</t>
-        </is>
-      </c>
-      <c r="J91" s="60" t="inlineStr">
-        <is>
-          <t>世界保健機関（WHO）の新データによると、2011年から2025年にかけて世界の交通事故死者数は21%減少したが、依然として2025年には116万人が命を落としており、特に5〜29歳の子供や若者における交通事故は主要な死因となっている。</t>
-        </is>
-      </c>
-      <c r="K91" s="60" t="inlineStr">
-        <is>
-          <t>https://www.who.int/news/item/20-07-2026-road-deaths-fall-by-21--globally-but-stronger-action-is-needed-to-save-lives</t>
-        </is>
-      </c>
-      <c r="L91" s="60" t="inlineStr">
-        <is>
-          <t>05edb573a8ead16ae99b6291</t>
-        </is>
-      </c>
-      <c r="M91" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="N91" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O91" s="60" t="inlineStr"/>
-    </row>
-    <row r="92" ht="42" customHeight="1">
-      <c r="A92" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="B92" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-18T07:27:54Z</t>
-        </is>
-      </c>
-      <c r="C92" s="60" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="D92" s="60" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="E92" s="60" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-      <c r="F92" s="76" t="n">
-        <v>1</v>
-      </c>
-      <c r="G92" s="60" t="inlineStr">
-        <is>
-          <t>Intergovernmental</t>
-        </is>
-      </c>
-      <c r="H92" s="60" t="inlineStr">
-        <is>
-          <t>WHO News</t>
-        </is>
-      </c>
-      <c r="I92" s="60" t="inlineStr">
-        <is>
-          <t>WHO加盟国、病原体アクセスと利益配分に関する交渉を継続</t>
-        </is>
-      </c>
-      <c r="J92" s="60" t="inlineStr">
-        <is>
-          <t>WHO加盟国は、パンデミック協定の中心的要素である病原体アクセスと利益配分（PABS）附属書に関する交渉を進めており、将来のパンデミックに対する迅速かつ効果的で公平な対応を支える枠組みの最終化に向けたさらなる議論が必要であることに合意した。</t>
-        </is>
-      </c>
-      <c r="K92" s="60" t="inlineStr">
-        <is>
-          <t>https://www.who.int/news/item/20-07-2026-who-member-states-continue-negotiations-on-the-pathogen-access-and-benefit-sharing-annex</t>
-        </is>
-      </c>
-      <c r="L92" s="60" t="inlineStr">
-        <is>
-          <t>14dd15caca066d18dfcf2e34</t>
-        </is>
-      </c>
-      <c r="M92" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="N92" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O92" s="60" t="inlineStr"/>
-    </row>
-    <row r="93" ht="42" customHeight="1">
-      <c r="A93" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="B93" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-17T20:26:18Z</t>
-        </is>
-      </c>
-      <c r="C93" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="D93" s="60" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="E93" s="60" t="inlineStr">
-        <is>
-          <t>Fusion Energy</t>
-        </is>
-      </c>
-      <c r="F93" s="76" t="n">
-        <v>1</v>
-      </c>
-      <c r="G93" s="60" t="inlineStr">
-        <is>
-          <t>Industry Association</t>
-        </is>
-      </c>
-      <c r="H93" s="60" t="inlineStr">
-        <is>
-          <t>Fusion Industry Association</t>
-        </is>
-      </c>
-      <c r="I93" s="60" t="inlineStr">
-        <is>
-          <t>FIAが2026年グローバル核融合産業レポートをニューヨーク、ワシントンD.C.、ロンドンで発表</t>
-        </is>
-      </c>
-      <c r="J93" s="60" t="inlineStr">
-        <is>
-          <t>核融合産業協会（FIA）は、2026年グローバル核融合産業レポートをニューヨークで発表し、業界リーダーや投資家、メディアが集まるイベントを開催した。続いてワシントンD.C.での発表と議会ブリーフィングが行われ、報告書の内容が米国の政策文脈で議論された。</t>
-        </is>
-      </c>
-      <c r="K93" s="60" t="inlineStr">
-        <is>
-          <t>https://www.fusionindustryassociation.org/fia-launches-the-2026-global-fusion-industry-report-in-new-york-city-washington-d-c-and-london/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=fia-launches-the-2026-global-fusion-industry-report-in-new-york-city-washington-d-c-and-london</t>
-        </is>
-      </c>
-      <c r="L93" s="60" t="inlineStr">
-        <is>
-          <t>186c1d4e76c09a864706432c</t>
-        </is>
-      </c>
-      <c r="M93" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="N93" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O93" s="60" t="inlineStr"/>
-    </row>
-    <row r="94" ht="42" customHeight="1">
-      <c r="A94" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="B94" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-17T18:42:47Z</t>
-        </is>
-      </c>
-      <c r="C94" s="60" t="inlineStr">
-        <is>
-          <t>EU &amp; Europe</t>
-        </is>
-      </c>
-      <c r="D94" s="60" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="E94" s="60" t="inlineStr">
-        <is>
-          <t>Innovation Policy | Fusion Energy</t>
-        </is>
-      </c>
-      <c r="F94" s="76" t="n">
-        <v>1</v>
-      </c>
-      <c r="G94" s="60" t="inlineStr">
-        <is>
-          <t>Industry Association</t>
-        </is>
-      </c>
-      <c r="H94" s="60" t="inlineStr">
-        <is>
-          <t>Fusion Industry Association</t>
-        </is>
-      </c>
-      <c r="I94" s="60" t="inlineStr">
-        <is>
-          <t>EUの競争力ある核融合技術を確保する必要性に関する国際法律専門家グループの論文発表</t>
-        </is>
-      </c>
-      <c r="J94" s="60" t="inlineStr">
-        <is>
-          <t>国際法律専門家グループが発表した論文は、ヨーロッパが商業核融合において競争優位性を持っているが、それを維持するためには迅速な行動が必要であると主張している。特に、ユーロトム条約が27カ国における核ガバナンスのための唯一の調和された法的枠組みであることを強調している。</t>
-        </is>
-      </c>
-      <c r="K94" s="60" t="inlineStr">
-        <is>
-          <t>https://www.fusionindustryassociation.org/international-legal-expert-group-publish-paper-on-the-need-for-the-eu-to-secure-its-competitive-fusion-advantage/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=international-legal-expert-group-publish-paper-on-the-need-for-the-eu-to-secure-its-competitive-fusion-advantage</t>
-        </is>
-      </c>
-      <c r="L94" s="60" t="inlineStr">
-        <is>
-          <t>7ef6110ab078602757409abf</t>
-        </is>
-      </c>
-      <c r="M94" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="N94" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O94" s="60" t="inlineStr"/>
-    </row>
-    <row r="95" ht="42" customHeight="1">
-      <c r="A95" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="B95" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-17T18:00:01Z</t>
-        </is>
-      </c>
-      <c r="C95" s="60" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="D95" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E95" s="60" t="inlineStr">
-        <is>
-          <t>Robotics</t>
-        </is>
-      </c>
-      <c r="F95" s="76" t="n">
-        <v>0</v>
-      </c>
-      <c r="G95" s="60" t="inlineStr">
-        <is>
-          <t>Major Media</t>
-        </is>
-      </c>
-      <c r="H95" s="60" t="inlineStr">
-        <is>
-          <t>IEEE Spectrum</t>
-        </is>
-      </c>
-      <c r="I95" s="60" t="inlineStr">
-        <is>
-          <t>大学院生がNASAのロボットに組立スキルを装備</t>
-        </is>
-      </c>
-      <c r="J95" s="60" t="inlineStr">
-        <is>
-          <t>テキサスA&amp;M大学の大学院生サラ・ダウンズが、NASAのロボットに組立スキルを与えるプロジェクトに取り組んでいます。彼女は若い頃からSTEMキャリアを目指していました。</t>
-        </is>
-      </c>
-      <c r="K95" s="60" t="inlineStr">
-        <is>
-          <t>https://spectrum.ieee.org/graduate-student-nasas-robots-assembly</t>
-        </is>
-      </c>
-      <c r="L95" s="60" t="inlineStr">
-        <is>
-          <t>c21b23b6ab59c7960b95be1f</t>
-        </is>
-      </c>
-      <c r="M95" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="N95" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O95" s="60" t="inlineStr"/>
-    </row>
-    <row r="96" ht="42" customHeight="1">
-      <c r="A96" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="B96" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-17T13:00:05Z</t>
-        </is>
-      </c>
-      <c r="C96" s="60" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="D96" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E96" s="60" t="inlineStr">
-        <is>
-          <t>Semiconductors &amp; Telecom | Healthcare</t>
-        </is>
-      </c>
-      <c r="F96" s="76" t="n">
-        <v>0</v>
-      </c>
-      <c r="G96" s="60" t="inlineStr">
-        <is>
-          <t>Official Company</t>
-        </is>
-      </c>
-      <c r="H96" s="60" t="inlineStr">
-        <is>
-          <t>Intel Newsroom</t>
-        </is>
-      </c>
-      <c r="I96" s="60" t="inlineStr">
-        <is>
-          <t>インテル搭載の医療用エクソスケルトンが患者の歩行を支援</t>
-        </is>
-      </c>
-      <c r="J96" s="60" t="inlineStr">
-        <is>
-          <t>下肢の怪我を持つ患者のために、インテルが搭載した医療用エクソスケルトンが開発され、リハビリテーションの限界を克服することを目指しています。</t>
-        </is>
-      </c>
-      <c r="K96" s="60" t="inlineStr">
-        <is>
-          <t>https://newsroom.intel.com/client-computing/intel-powered-medical-exoskeleton-helps-patients-get-back-on-their-feet</t>
-        </is>
-      </c>
-      <c r="L96" s="60" t="inlineStr">
-        <is>
-          <t>3dd1b06b356e118627f94f8b</t>
-        </is>
-      </c>
-      <c r="M96" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="N96" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O96" s="60" t="inlineStr"/>
-    </row>
-    <row r="97" ht="42" customHeight="1">
-      <c r="A97" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="B97" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-16T16:00:53Z</t>
-        </is>
-      </c>
-      <c r="C97" s="60" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="D97" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E97" s="60" t="inlineStr">
-        <is>
-          <t>Artificial Intelligence | Semiconductors &amp; Telecom</t>
-        </is>
-      </c>
-      <c r="F97" s="76" t="n">
-        <v>0</v>
-      </c>
-      <c r="G97" s="60" t="inlineStr">
-        <is>
-          <t>Official Company</t>
-        </is>
-      </c>
-      <c r="H97" s="60" t="inlineStr">
-        <is>
-          <t>Intel Newsroom</t>
-        </is>
-      </c>
-      <c r="I97" s="60" t="inlineStr">
-        <is>
-          <t>インテルとGoogle CloudがAI活用の企業変革を加速するための協力を発表</t>
-        </is>
-      </c>
-      <c r="J97" s="60" t="inlineStr">
-        <is>
-          <t>インテルとGoogle Cloudは、AIを活用した企業のデジタル進化を加速するための戦略的協力を拡大することを発表しました。</t>
-        </is>
-      </c>
-      <c r="K97" s="60" t="inlineStr">
-        <is>
-          <t>https://newsroom.intel.com/artificial-intelligence/intel-google-cloud-announce-collaboration-to-accelerate-intel-ai-enabled-enterprise-transformation</t>
-        </is>
-      </c>
-      <c r="L97" s="60" t="inlineStr">
-        <is>
-          <t>0361033c6203d3cbfc2c57cf</t>
-        </is>
-      </c>
-      <c r="M97" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="N97" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O97" s="60" t="inlineStr"/>
-    </row>
-    <row r="98" ht="42" customHeight="1">
-      <c r="A98" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="B98" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-16T16:00:00Z</t>
-        </is>
-      </c>
-      <c r="C98" s="60" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="D98" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E98" s="60" t="inlineStr">
-        <is>
-          <t>Artificial Intelligence</t>
-        </is>
-      </c>
-      <c r="F98" s="76" t="n">
-        <v>0</v>
-      </c>
-      <c r="G98" s="60" t="inlineStr">
-        <is>
-          <t>Official Company</t>
-        </is>
-      </c>
-      <c r="H98" s="60" t="inlineStr">
-        <is>
-          <t>Google AI</t>
-        </is>
-      </c>
-      <c r="I98" s="60" t="inlineStr">
-        <is>
-          <t>アプリを検索にもっと接続</t>
-        </is>
-      </c>
-      <c r="J98" s="60" t="inlineStr">
-        <is>
-          <t>接続されたアプリのレンダリングに関する情報が提供されています。</t>
-        </is>
-      </c>
-      <c r="K98" s="60" t="inlineStr">
-        <is>
-          <t>https://blog.google/products-and-platforms/products/search/connected-apps/</t>
-        </is>
-      </c>
-      <c r="L98" s="60" t="inlineStr">
-        <is>
-          <t>23c6974aa4b45f04208cef57</t>
-        </is>
-      </c>
-      <c r="M98" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="N98" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O98" s="60" t="inlineStr"/>
-    </row>
-    <row r="99" ht="42" customHeight="1">
-      <c r="A99" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="B99" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-16T16:00:00Z</t>
-        </is>
-      </c>
-      <c r="C99" s="60" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="D99" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E99" s="60" t="inlineStr">
-        <is>
-          <t>Artificial Intelligence</t>
-        </is>
-      </c>
-      <c r="F99" s="76" t="n">
-        <v>0</v>
-      </c>
-      <c r="G99" s="60" t="inlineStr">
-        <is>
-          <t>Official Company</t>
-        </is>
-      </c>
-      <c r="H99" s="60" t="inlineStr">
-        <is>
-          <t>Google AI</t>
-        </is>
-      </c>
-      <c r="I99" s="60" t="inlineStr">
-        <is>
-          <t>Google Vidsの2つの更新で動画を作成、編集、主演</t>
-        </is>
-      </c>
-      <c r="J99" s="60" t="inlineStr">
-        <is>
-          <t>Google Vidsに関する更新情報が発表され、Gemini Omniとパーソナルアバターに関する内容が紹介されています。</t>
-        </is>
-      </c>
-      <c r="K99" s="60" t="inlineStr">
-        <is>
-          <t>https://blog.google/products-and-platforms/products/workspace/gemini-omni-personal-avatars/</t>
-        </is>
-      </c>
-      <c r="L99" s="60" t="inlineStr">
-        <is>
-          <t>0560403cacf5a7a127ad3346</t>
-        </is>
-      </c>
-      <c r="M99" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="N99" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O99" s="60" t="inlineStr"/>
-    </row>
-    <row r="100" ht="42" customHeight="1">
-      <c r="A100" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="B100" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-15T21:00:00Z</t>
-        </is>
-      </c>
-      <c r="C100" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="D100" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E100" s="60" t="inlineStr">
-        <is>
-          <t>Artificial Intelligence | Innovation Policy</t>
-        </is>
-      </c>
-      <c r="F100" s="76" t="n">
-        <v>3</v>
-      </c>
-      <c r="G100" s="60" t="inlineStr">
-        <is>
-          <t>Policy Institute</t>
-        </is>
-      </c>
-      <c r="H100" s="60" t="inlineStr">
-        <is>
-          <t>CSET</t>
-        </is>
-      </c>
-      <c r="I100" s="60" t="inlineStr">
-        <is>
-          <t>GPT-Red：OpenAIが開発したLLMスーパーハッカー</t>
-        </is>
-      </c>
-      <c r="J100" s="60" t="inlineStr">
-        <is>
-          <t>CSETのジェシカ・ジがMITテクノロジーレビューに寄稿した記事で、OpenAIが開発したAIスーパーハッカーGPT-Redについて解説しています。これは、大規模言語モデルの脆弱性を自動的に特定し、サイバー攻撃からの防御を強化するためのものです。</t>
-        </is>
-      </c>
-      <c r="K100" s="60" t="inlineStr">
-        <is>
-          <t>https://cset.georgetown.edu/article/meet-gpt-red-an-llm-super-hacker-openai-built-to-make-its-models-safer/</t>
-        </is>
-      </c>
-      <c r="L100" s="60" t="inlineStr">
-        <is>
-          <t>f64391d3daf689e78e7ac442</t>
-        </is>
-      </c>
-      <c r="M100" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="N100" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O100" s="60" t="inlineStr"/>
-    </row>
-    <row r="101" ht="42" customHeight="1">
-      <c r="A101" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="B101" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-15T17:47:57Z</t>
-        </is>
-      </c>
-      <c r="C101" s="60" t="inlineStr">
-        <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="D101" s="60" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="E101" s="60" t="inlineStr">
-        <is>
-          <t>Fusion Energy</t>
-        </is>
-      </c>
-      <c r="F101" s="76" t="n">
-        <v>0</v>
-      </c>
-      <c r="G101" s="60" t="inlineStr">
-        <is>
-          <t>Industry Association</t>
-        </is>
-      </c>
-      <c r="H101" s="60" t="inlineStr">
-        <is>
-          <t>Fusion Industry Association</t>
-        </is>
-      </c>
-      <c r="I101" s="60" t="inlineStr">
-        <is>
-          <t>スターロイトエンジンが60.6億円を調達</t>
-        </is>
-      </c>
-      <c r="J101" s="60" t="inlineStr">
-        <is>
-          <t>スターロイトエンジンは、FASTの開発を加速するために初の外部資金調達ラウンドで60.6億円を調達しました。同社は、トカマク型の融合機を開発しています。</t>
-        </is>
-      </c>
-      <c r="K101" s="60" t="inlineStr">
-        <is>
-          <t>https://www.nikkei.com/article/DGXZQOUC152ET0V10C26A7000000/#new_tab?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=starlight-engine-raises-jpy-6-06-billion</t>
-        </is>
-      </c>
-      <c r="L101" s="60" t="inlineStr">
-        <is>
-          <t>2f29b005896c3737ab846738</t>
-        </is>
-      </c>
-      <c r="M101" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="N101" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O101" s="60" t="inlineStr"/>
-    </row>
-    <row r="102" ht="42" customHeight="1">
-      <c r="A102" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="B102" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-15T17:43:32Z</t>
-        </is>
-      </c>
-      <c r="C102" s="60" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="D102" s="60" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="E102" s="60" t="inlineStr">
-        <is>
-          <t>Fusion Energy</t>
-        </is>
-      </c>
-      <c r="F102" s="76" t="n">
-        <v>0</v>
-      </c>
-      <c r="G102" s="60" t="inlineStr">
-        <is>
-          <t>Industry Association</t>
-        </is>
-      </c>
-      <c r="H102" s="60" t="inlineStr">
-        <is>
-          <t>Fusion Industry Association</t>
-        </is>
-      </c>
-      <c r="I102" s="60" t="inlineStr">
-        <is>
-          <t>マディソンに融合研究センターが設立、オスカー・マイヤー工場跡地に</t>
-        </is>
-      </c>
-      <c r="J102" s="60" t="inlineStr">
-        <is>
-          <t>Realta Fusionは、ウィスコンシン州マディソンの元オスカー・マイヤー工場跡地に新しい本社と施設を設立することを発表しました。このプロジェクトは600以上の雇用を創出し、融合技術の主要な拠点を確立することが期待されています。</t>
-        </is>
-      </c>
-      <c r="K102" s="60" t="inlineStr">
-        <is>
-          <t>https://www.jsonline.com/story/money/business/energy/2026/07/15/nuclear-fusion-facility-coming-to-madisons-oscar-mayer-factory-site/90900554007/?gnt-cfr=1&amp;gca-cat=p&amp;gca-uir=true&amp;gca-epti=z116463p117850l004150c117850e1157xxv116463d--54--b--54--&amp;gca-ft=178&amp;gca-ds=sophi#new_tab&amp;utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=fusion-research-center-coming-to-madisons-former-oscar-mayer-plant</t>
-        </is>
-      </c>
-      <c r="L102" s="60" t="inlineStr">
-        <is>
-          <t>aed2fa8a807fb17c3e6861e7</t>
-        </is>
-      </c>
-      <c r="M102" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="N102" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O102" s="60" t="inlineStr"/>
-    </row>
-    <row r="103" ht="42" customHeight="1">
-      <c r="A103" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="B103" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-15T12:15:58Z</t>
-        </is>
-      </c>
-      <c r="C103" s="60" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="D103" s="60" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="E103" s="60" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-      <c r="F103" s="76" t="n">
-        <v>1</v>
-      </c>
-      <c r="G103" s="60" t="inlineStr">
-        <is>
-          <t>Intergovernmental</t>
-        </is>
-      </c>
-      <c r="H103" s="60" t="inlineStr">
-        <is>
-          <t>WHO News</t>
-        </is>
-      </c>
-      <c r="I103" s="60" t="inlineStr">
-        <is>
-          <t>新しいWHOガイドライン：認知症リスクの最大45%を予防または遅延可能</t>
-        </is>
-      </c>
-      <c r="J103" s="60" t="inlineStr">
-        <is>
-          <t>WHOは、認知症のリスクを減少させるための新しいガイドラインを発表しました。これにより、国々は認知症の発症を予防または遅延させるための根拠に基づく推奨を得ることができます。</t>
-        </is>
-      </c>
-      <c r="K103" s="60" t="inlineStr">
-        <is>
-          <t>https://www.who.int/news/item/15-07-2026-new-who-guidelines--up-to-45--of-dementia-risk-could-be-prevented-or-delayed</t>
-        </is>
-      </c>
-      <c r="L103" s="60" t="inlineStr">
-        <is>
-          <t>30a0d7838c2c12642479a64f</t>
-        </is>
-      </c>
-      <c r="M103" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="N103" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O103" s="60" t="inlineStr"/>
-    </row>
-    <row r="104" ht="42" customHeight="1">
-      <c r="A104" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="B104" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-15T00:01:54Z</t>
-        </is>
-      </c>
-      <c r="C104" s="60" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="D104" s="60" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="E104" s="60" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-      <c r="F104" s="76" t="n">
-        <v>1</v>
-      </c>
-      <c r="G104" s="60" t="inlineStr">
-        <is>
-          <t>Intergovernmental</t>
-        </is>
-      </c>
-      <c r="H104" s="60" t="inlineStr">
-        <is>
-          <t>WHO News</t>
-        </is>
-      </c>
-      <c r="I104" s="60" t="inlineStr">
-        <is>
-          <t>世界の子供の予防接種率が向上、紛争やためらいにもかかわらず</t>
-        </is>
-      </c>
-      <c r="J104" s="60" t="inlineStr">
-        <is>
-          <t>2025年には、世界で90%の乳児がジフテリア、破傷風、百日咳（DTP）ワクチンの少なくとも1回の接種を受け、85%が3回の接種を完了したとWHOとUNICEFの報告が示しています。しかし、依然として2019年の水準を下回っています。</t>
-        </is>
-      </c>
-      <c r="K104" s="60" t="inlineStr">
-        <is>
-          <t>https://www.who.int/news/item/15-07-2026-global-childhood-immunization-coverage-inches-forward-despite-conflict-and-hesitancy---unicef--who</t>
-        </is>
-      </c>
-      <c r="L104" s="60" t="inlineStr">
-        <is>
-          <t>03ea8728394fda1e18a57d66</t>
-        </is>
-      </c>
-      <c r="M104" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="N104" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O104" s="60" t="inlineStr"/>
-    </row>
-    <row r="105" ht="42" customHeight="1">
-      <c r="A105" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="B105" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-14T17:40:43Z</t>
-        </is>
-      </c>
-      <c r="C105" s="60" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="D105" s="60" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="E105" s="60" t="inlineStr">
-        <is>
-          <t>Fusion Energy</t>
-        </is>
-      </c>
-      <c r="F105" s="76" t="n">
-        <v>0</v>
-      </c>
-      <c r="G105" s="60" t="inlineStr">
-        <is>
-          <t>Industry Association</t>
-        </is>
-      </c>
-      <c r="H105" s="60" t="inlineStr">
-        <is>
-          <t>Fusion Industry Association</t>
-        </is>
-      </c>
-      <c r="I105" s="60" t="inlineStr">
-        <is>
-          <t>核融合企業への世界的投資が69%増加、45億ドルに達する</t>
-        </is>
-      </c>
-      <c r="J105" s="60" t="inlineStr">
-        <is>
-          <t>核融合産業協会が発表した2026年の報告書によると、核融合企業への投資が記録的な水準に達し、2030年代に電力供給が期待されている。</t>
-        </is>
-      </c>
-      <c r="K105" s="60" t="inlineStr">
-        <is>
-          <t>https://www.bloomberg.com/news/articles/2026-07-13/global-investment-in-fusion-companies-surges-69-to-4-5-billion#new_tab?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=global-investment-in-fusion-companies-surges-69-to-4-5-billion</t>
-        </is>
-      </c>
-      <c r="L105" s="60" t="inlineStr">
-        <is>
-          <t>37f8fa9d53d7f670777b07a5</t>
-        </is>
-      </c>
-      <c r="M105" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="N105" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O105" s="60" t="inlineStr"/>
-    </row>
-    <row r="106" ht="42" customHeight="1">
-      <c r="A106" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="B106" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-14T17:39:28Z</t>
-        </is>
-      </c>
-      <c r="C106" s="60" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="D106" s="60" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="E106" s="60" t="inlineStr">
-        <is>
-          <t>Fusion Energy</t>
-        </is>
-      </c>
-      <c r="F106" s="76" t="n">
-        <v>0</v>
-      </c>
-      <c r="G106" s="60" t="inlineStr">
-        <is>
-          <t>Industry Association</t>
-        </is>
-      </c>
-      <c r="H106" s="60" t="inlineStr">
-        <is>
-          <t>Fusion Industry Association</t>
-        </is>
-      </c>
-      <c r="I106" s="60" t="inlineStr">
-        <is>
-          <t>ジェネラルフュージョンの株価が25%上昇</t>
-        </is>
-      </c>
-      <c r="J106" s="60" t="inlineStr">
-        <is>
-          <t>カナダのジェネラルフュージョンが特別目的買収会社（SPAC）との合併を完了し、公開企業となったことで資本へのアクセスが広がり、株価が上昇した。</t>
-        </is>
-      </c>
-      <c r="K106" s="60" t="inlineStr">
-        <is>
-          <t>https://www.wsj.com/livecoverage/stock-market-today-bank-earnings-07-14-2026/card/general-fusion-shares-soar-25--lfmTDvoKe8UYxvdcs8Hq#new_tab?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=general-fusion-shares-soar-25</t>
-        </is>
-      </c>
-      <c r="L106" s="60" t="inlineStr">
-        <is>
-          <t>4f333224cb84eee2f3fbf904</t>
-        </is>
-      </c>
-      <c r="M106" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="N106" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O106" s="60" t="inlineStr"/>
-    </row>
-    <row r="107" ht="42" customHeight="1">
-      <c r="A107" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="B107" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-14T16:00:00Z</t>
-        </is>
-      </c>
-      <c r="C107" s="60" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="D107" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E107" s="60" t="inlineStr">
-        <is>
-          <t>Artificial Intelligence</t>
-        </is>
-      </c>
-      <c r="F107" s="76" t="n">
-        <v>0</v>
-      </c>
-      <c r="G107" s="60" t="inlineStr">
-        <is>
-          <t>Official Company</t>
-        </is>
-      </c>
-      <c r="H107" s="60" t="inlineStr">
-        <is>
-          <t>Google AI</t>
-        </is>
-      </c>
-      <c r="I107" s="60" t="inlineStr">
-        <is>
-          <t>視覚検索の革新25周年を祝う</t>
-        </is>
-      </c>
-      <c r="J107" s="60" t="inlineStr">
-        <is>
-          <t>Google Imagesが視覚検索の革新25周年を迎え、さまざまな画像検索の様子を描いたイラストが紹介されている。</t>
-        </is>
-      </c>
-      <c r="K107" s="60" t="inlineStr">
-        <is>
-          <t>https://blog.google/products-and-platforms/products/search/google-images-25th-anniversary/</t>
-        </is>
-      </c>
-      <c r="L107" s="60" t="inlineStr">
-        <is>
-          <t>bbfc4b37a73bf4793d60e253</t>
-        </is>
-      </c>
-      <c r="M107" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="N107" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O107" s="60" t="inlineStr"/>
-    </row>
-    <row r="108" ht="42" customHeight="1">
-      <c r="A108" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="B108" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-14T12:00:00Z</t>
-        </is>
-      </c>
-      <c r="C108" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="D108" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E108" s="60" t="inlineStr">
-        <is>
-          <t>Innovation Policy</t>
-        </is>
-      </c>
-      <c r="F108" s="76" t="n">
-        <v>4</v>
-      </c>
-      <c r="G108" s="60" t="inlineStr">
-        <is>
-          <t>Government</t>
-        </is>
-      </c>
-      <c r="H108" s="60" t="inlineStr">
-        <is>
-          <t>NIST News</t>
-        </is>
-      </c>
-      <c r="I108" s="60" t="inlineStr">
-        <is>
-          <t>NIST、新しい微生物除去型給湯器の特許を取得</t>
-        </is>
-      </c>
-      <c r="J108" s="60" t="inlineStr">
-        <is>
-          <t>家庭の配管内の温水が有害な細菌の繁殖地となる可能性があることから、NISTが新たな給湯器の特許を取得した。</t>
-        </is>
-      </c>
-      <c r="K108" s="60" t="inlineStr">
-        <is>
-          <t>https://www.nist.gov/news-events/news/2026/07/nist-receives-new-patent-microbe-killing-water-heater</t>
-        </is>
-      </c>
-      <c r="L108" s="60" t="inlineStr">
-        <is>
-          <t>72b002f5a04f35d9ca1e9949</t>
-        </is>
-      </c>
-      <c r="M108" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="N108" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O108" s="60" t="inlineStr"/>
-    </row>
-    <row r="109" ht="42" customHeight="1">
-      <c r="A109" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="B109" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-13T21:00:00Z</t>
-        </is>
-      </c>
-      <c r="C109" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="D109" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E109" s="60" t="inlineStr">
-        <is>
-          <t>Innovation Policy | Artificial Intelligence</t>
-        </is>
-      </c>
-      <c r="F109" s="76" t="n">
-        <v>3</v>
-      </c>
-      <c r="G109" s="60" t="inlineStr">
-        <is>
-          <t>Policy Institute</t>
-        </is>
-      </c>
-      <c r="H109" s="60" t="inlineStr">
-        <is>
-          <t>CSET</t>
-        </is>
-      </c>
-      <c r="I109" s="60" t="inlineStr">
-        <is>
-          <t>ワシントン、中国が米国モデルでAIを訓練するのを防ごうとする</t>
-        </is>
-      </c>
-      <c r="J109" s="60" t="inlineStr">
-        <is>
-          <t>ワシントンでは、中国のAI企業が米国のシステムの出力を用いてモデルを訓練することに対する懸念が高まっており、知的財産や国家安全保障に関する議論が進んでいる。</t>
-        </is>
-      </c>
-      <c r="K109" s="60" t="inlineStr">
-        <is>
-          <t>https://cset.georgetown.edu/article/washington-is-looking-to-keep-china-from-training-its-ai-on-us-models/</t>
-        </is>
-      </c>
-      <c r="L109" s="60" t="inlineStr">
-        <is>
-          <t>e96177000536ef3f58f8fb3c</t>
-        </is>
-      </c>
-      <c r="M109" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="N109" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O109" s="60" t="inlineStr"/>
-    </row>
-    <row r="110" ht="42" customHeight="1">
-      <c r="A110" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="B110" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-13T16:00:00Z</t>
-        </is>
-      </c>
-      <c r="C110" s="60" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="D110" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E110" s="60" t="inlineStr">
-        <is>
-          <t>Innovation Policy | Quantum</t>
-        </is>
-      </c>
-      <c r="F110" s="76" t="n">
-        <v>1</v>
-      </c>
-      <c r="G110" s="60" t="inlineStr">
-        <is>
-          <t>Official Company</t>
-        </is>
-      </c>
-      <c r="H110" s="60" t="inlineStr">
-        <is>
-          <t>Microsoft Research</t>
-        </is>
-      </c>
-      <c r="I110" s="60" t="inlineStr">
-        <is>
-          <t>SymCryptにおけるRust暗号の検証</t>
-        </is>
-      </c>
-      <c r="J110" s="60" t="inlineStr">
-        <is>
-          <t>新しい手法により、開発者がコードを記述する際に暗号コードの検証が可能になり、速度と適応性を保ちながら実装が進む。</t>
-        </is>
-      </c>
-      <c r="K110" s="60" t="inlineStr">
-        <is>
-          <t>https://www.microsoft.com/en-us/research/blog/verifying-rust-cryptography-in-symcrypt-from-standards-to-code/</t>
-        </is>
-      </c>
-      <c r="L110" s="60" t="inlineStr">
-        <is>
-          <t>a7866758cf94a3c5e9d26534</t>
-        </is>
-      </c>
-      <c r="M110" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="N110" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O110" s="60" t="inlineStr"/>
-    </row>
-    <row r="111" ht="42" customHeight="1">
-      <c r="A111" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="B111" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-13T12:00:41Z</t>
-        </is>
-      </c>
-      <c r="C111" s="60" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="D111" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E111" s="60" t="inlineStr">
-        <is>
-          <t>Semiconductors &amp; Telecom | Artificial Intelligence</t>
-        </is>
-      </c>
-      <c r="F111" s="76" t="n">
-        <v>0</v>
-      </c>
-      <c r="G111" s="60" t="inlineStr">
-        <is>
-          <t>Official Company</t>
-        </is>
-      </c>
-      <c r="H111" s="60" t="inlineStr">
-        <is>
-          <t>Intel Newsroom</t>
-        </is>
-      </c>
-      <c r="I111" s="60" t="inlineStr">
-        <is>
-          <t>インテル、欧州で製造拡大のために50億ユーロを投資</t>
-        </is>
-      </c>
-      <c r="J111" s="60" t="inlineStr">
-        <is>
-          <t>インテルはアイルランドのLeixlipキャンパスに50億ユーロを投資し、AIや高性能コンピューティングの需要に応えるための製造能力を拡大する。</t>
-        </is>
-      </c>
-      <c r="K111" s="60" t="inlineStr">
-        <is>
-          <t>https://newsroom.intel.com/intel-foundry/intel-invests-5-billion-euro-to-expand-manufacturing-in-europe</t>
-        </is>
-      </c>
-      <c r="L111" s="60" t="inlineStr">
-        <is>
-          <t>297a8b5b279e5916cf45fddb</t>
-        </is>
-      </c>
-      <c r="M111" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="N111" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O111" s="60" t="inlineStr"/>
-    </row>
-    <row r="112" ht="42" customHeight="1">
-      <c r="A112" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="B112" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-13T10:19:51Z</t>
-        </is>
-      </c>
-      <c r="C112" s="60" t="inlineStr">
-        <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="D112" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E112" s="60" t="inlineStr">
-        <is>
-          <t>Artificial Intelligence | Robotics</t>
-        </is>
-      </c>
-      <c r="F112" s="76" t="n">
-        <v>0</v>
-      </c>
-      <c r="G112" s="60" t="inlineStr">
-        <is>
-          <t>Major Media</t>
-        </is>
-      </c>
-      <c r="H112" s="60" t="inlineStr">
-        <is>
-          <t>IEEE Spectrum</t>
-        </is>
-      </c>
-      <c r="I112" s="60" t="inlineStr">
-        <is>
-          <t>汎用ロボットの基盤スタック構築</t>
-        </is>
-      </c>
-      <c r="J112" s="60" t="inlineStr">
-        <is>
-          <t>ロボティクス分野では、知能を持つロボットを実現するための統合スタックの必要性が議論されている。X Square Robotはこの課題に挑戦している。</t>
-        </is>
-      </c>
-      <c r="K112" s="60" t="inlineStr">
-        <is>
-          <t>https://spectrum.ieee.org/x-square-robot-embodied-ai-stack</t>
-        </is>
-      </c>
-      <c r="L112" s="60" t="inlineStr">
-        <is>
-          <t>d56ace988ec4655cef540679</t>
-        </is>
-      </c>
-      <c r="M112" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="N112" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O112" s="60" t="inlineStr"/>
-    </row>
-    <row r="113" ht="42" customHeight="1">
-      <c r="A113" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="B113" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-13T09:57:57Z</t>
-        </is>
-      </c>
-      <c r="C113" s="60" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="D113" s="60" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="E113" s="60" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-      <c r="F113" s="76" t="n">
-        <v>1</v>
-      </c>
-      <c r="G113" s="60" t="inlineStr">
-        <is>
-          <t>Intergovernmental</t>
-        </is>
-      </c>
-      <c r="H113" s="60" t="inlineStr">
-        <is>
-          <t>WHO News</t>
-        </is>
-      </c>
-      <c r="I113" s="60" t="inlineStr">
-        <is>
-          <t>エルサルバドル、WHOによりトラコーマの公衆衛生問題を解消したと認定</t>
-        </is>
-      </c>
-      <c r="J113" s="60" t="inlineStr">
-        <is>
-          <t>世界保健機関（WHO）は、エルサルバドルがトラコーマを公衆衛生問題として解消したと認定した。トラコーマは失明の主要な感染症である。</t>
-        </is>
-      </c>
-      <c r="K113" s="60" t="inlineStr">
-        <is>
-          <t>https://www.who.int/news/item/13-07-2026-el-salvador-validated-by-who-as-having-eliminated-trachoma-as-a-public-health-problem</t>
-        </is>
-      </c>
-      <c r="L113" s="60" t="inlineStr">
-        <is>
-          <t>213c7954ea56dfd0fccb556a</t>
-        </is>
-      </c>
-      <c r="M113" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="N113" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O113" s="60" t="inlineStr"/>
-    </row>
-    <row r="114" ht="42" customHeight="1">
-      <c r="A114" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="B114" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-12T21:00:00Z</t>
-        </is>
-      </c>
-      <c r="C114" s="60" t="inlineStr">
-        <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="D114" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E114" s="60" t="inlineStr">
-        <is>
-          <t>Artificial Intelligence | Innovation Policy</t>
-        </is>
-      </c>
-      <c r="F114" s="76" t="n">
-        <v>3</v>
-      </c>
-      <c r="G114" s="60" t="inlineStr">
-        <is>
-          <t>Policy Institute</t>
-        </is>
-      </c>
-      <c r="H114" s="60" t="inlineStr">
-        <is>
-          <t>CSET</t>
-        </is>
-      </c>
-      <c r="I114" s="60" t="inlineStr">
-        <is>
-          <t>企業がコスト削減のために中国のAIモデルに注目</t>
-        </is>
-      </c>
-      <c r="J114" s="60" t="inlineStr">
-        <is>
-          <t>企業がコスト削減を目的に、中国のAIモデルを採用する動きが広がっている。低コストや能力向上、オープンウェイトシステムの柔軟性が要因とされる。</t>
-        </is>
-      </c>
-      <c r="K114" s="60" t="inlineStr">
-        <is>
-          <t>https://cset.georgetown.edu/article/companies-turn-to-chinese-ai-models-to-cut-costs/</t>
-        </is>
-      </c>
-      <c r="L114" s="60" t="inlineStr">
-        <is>
-          <t>9e1bc06c29b61bed048d4f44</t>
-        </is>
-      </c>
-      <c r="M114" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="N114" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O114" s="60" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A3:O114"/>
+  <autoFilter ref="A3:O56"/>
   <mergeCells count="2">
     <mergeCell ref="A1:O1"/>
     <mergeCell ref="A2:O2"/>
@@ -9113,7 +4995,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="N4:N114" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="N4:N56" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"New,Reviewed,Follow-up,Archived"</formula1>
     </dataValidation>
   </dataValidations>
@@ -9171,68 +5053,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K54" r:id="rId51"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K55" r:id="rId52"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K56" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K57" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K58" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K59" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K60" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K61" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K62" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K63" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K64" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K65" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K66" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K67" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K68" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K69" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K70" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K71" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K72" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K73" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K74" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K75" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K76" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K77" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K78" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K79" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K80" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K81" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K82" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K83" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K84" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K85" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K86" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K87" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K88" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K89" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K90" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K91" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K92" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K93" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K94" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K95" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K96" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K97" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K98" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K99" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K100" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K101" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K102" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K103" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K104" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K105" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K106" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K107" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K108" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K109" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K110" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K111" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K112" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K113" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K114" r:id="rId111"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId112"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId54"/>
   </tableParts>
 </worksheet>
 </file>
@@ -9758,7 +5582,7 @@
       </c>
       <c r="G11" s="60" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/rss/91/feed</t>
+          <t>https://www.scmp.com/rss/36/feed</t>
         </is>
       </c>
       <c r="H11" s="60" t="inlineStr">
@@ -9776,7 +5600,7 @@
       </c>
       <c r="K11" s="60" t="inlineStr">
         <is>
-          <t>Major Asia-focused media.</t>
+          <t>Major Asia-focused technology media; only /tech/ article URLs are accepted.</t>
         </is>
       </c>
     </row>
@@ -11304,7 +7128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -11383,7 +7207,7 @@
     <row r="4" ht="42" customHeight="1">
       <c r="A4" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:00:03+09:00</t>
+          <t>2026-07-26T20:13:43+09:00</t>
         </is>
       </c>
       <c r="B4" s="77" t="n">
@@ -11393,16 +7217,16 @@
         <v>24</v>
       </c>
       <c r="D4" s="77" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E4" s="77" t="n">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="F4" s="77" t="n">
         <v>10</v>
       </c>
       <c r="G4" s="77" t="n">
-        <v>154.27</v>
+        <v>162.46</v>
       </c>
       <c r="H4" s="60" t="inlineStr">
         <is>
@@ -11413,7 +7237,7 @@
     <row r="5">
       <c r="A5" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:51:39+09:00</t>
+          <t>2026-07-26T20:00:03+09:00</t>
         </is>
       </c>
       <c r="B5" s="77" t="n">
@@ -11423,16 +7247,16 @@
         <v>24</v>
       </c>
       <c r="D5" s="77" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E5" s="77" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="F5" s="77" t="n">
         <v>10</v>
       </c>
       <c r="G5" s="77" t="n">
-        <v>11.55</v>
+        <v>154.27</v>
       </c>
       <c r="H5" s="60" t="inlineStr">
         <is>
@@ -11443,26 +7267,26 @@
     <row r="6">
       <c r="A6" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:10:55+09:00</t>
+          <t>2026-07-26T19:51:39+09:00</t>
         </is>
       </c>
       <c r="B6" s="77" t="n">
         <v>34</v>
       </c>
       <c r="C6" s="77" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D6" s="77" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E6" s="77" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F6" s="77" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G6" s="77" t="n">
-        <v>194.65</v>
+        <v>11.55</v>
       </c>
       <c r="H6" s="60" t="inlineStr">
         <is>
@@ -11473,26 +7297,26 @@
     <row r="7">
       <c r="A7" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:05:06+09:00</t>
+          <t>2026-07-26T19:10:55+09:00</t>
         </is>
       </c>
       <c r="B7" s="77" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C7" s="77" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D7" s="77" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E7" s="77" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="F7" s="77" t="n">
         <v>9</v>
       </c>
       <c r="G7" s="77" t="n">
-        <v>165.89</v>
+        <v>194.65</v>
       </c>
       <c r="H7" s="60" t="inlineStr">
         <is>
@@ -11503,35 +7327,65 @@
     <row r="8">
       <c r="A8" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T19:05:06+09:00</t>
         </is>
       </c>
       <c r="B8" s="77" t="n">
         <v>33</v>
       </c>
       <c r="C8" s="77" t="n">
+        <v>24</v>
+      </c>
+      <c r="D8" s="77" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" s="77" t="n">
+        <v>39</v>
+      </c>
+      <c r="F8" s="77" t="n">
+        <v>9</v>
+      </c>
+      <c r="G8" s="77" t="n">
+        <v>165.89</v>
+      </c>
+      <c r="H8" s="60" t="inlineStr">
+        <is>
+          <t>Daily update</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T18:56:03+09:00</t>
+        </is>
+      </c>
+      <c r="B9" s="77" t="n">
+        <v>33</v>
+      </c>
+      <c r="C9" s="77" t="n">
         <v>20</v>
       </c>
-      <c r="D8" s="77" t="n">
+      <c r="D9" s="77" t="n">
         <v>94</v>
       </c>
-      <c r="E8" s="77" t="n">
+      <c r="E9" s="77" t="n">
         <v>0</v>
       </c>
-      <c r="F8" s="77" t="n">
+      <c r="F9" s="77" t="n">
         <v>13</v>
       </c>
-      <c r="G8" s="77" t="n">
+      <c r="G9" s="77" t="n">
         <v>129.43</v>
       </c>
-      <c r="H8" s="60" t="inlineStr">
+      <c r="H9" s="60" t="inlineStr">
         <is>
           <t>Initial lookback</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:H8"/>
+  <autoFilter ref="A3:H9"/>
   <mergeCells count="2">
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>

--- a/docs/innovation_news_ledger.xlsx
+++ b/docs/innovation_news_ledger.xlsx
@@ -9,9 +9,9 @@
     <sheet name="Run Log" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'News Ledger'!$A$3:$O$56</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Source Registry'!$A$3:$K$37</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Run Log'!$A$3:$H$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'News Ledger'!$A$3:$O$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Source Registry'!$A$3:$K$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Run Log'!$A$3:$H$10</definedName>
   </definedNames>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -472,7 +472,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="NewsLedgerTable" displayName="NewsLedgerTable" ref="A3:O56" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="NewsLedgerTable" displayName="NewsLedgerTable" ref="A3:O42" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <autoFilter ref="A3:O4"/>
   <tableColumns count="15">
     <tableColumn id="1" name="Collected At (JST)"/>
@@ -496,7 +496,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="SourceRegistryTable" displayName="SourceRegistryTable" ref="A3:K37" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="SourceRegistryTable" displayName="SourceRegistryTable" ref="A3:K41" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <autoFilter ref="A3:K37"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Active"/>
@@ -516,7 +516,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="RunLogTable" displayName="RunLogTable" ref="A3:H9" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="RunLogTable" displayName="RunLogTable" ref="A3:H10" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <autoFilter ref="A3:H4"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Run Time (JST)"/>
@@ -800,7 +800,7 @@
       </c>
       <c r="B5" s="25" t="inlineStr">
         <is>
-          <t>2026-07-26T20:13:43+09:00</t>
+          <t>2026-07-26T20:19:15+09:00</t>
         </is>
       </c>
       <c r="C5" s="46" t="n"/>
@@ -1088,7 +1088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O56"/>
+  <dimension ref="A1:O42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1216,12 +1216,12 @@
     <row r="4" ht="42" customHeight="1">
       <c r="A4" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:51:39+09:00</t>
+          <t>2026-07-26T18:56:03+09:00</t>
         </is>
       </c>
       <c r="B4" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T08:00:09Z</t>
+          <t>2026-07-25T14:32:00Z</t>
         </is>
       </c>
       <c r="C4" s="60" t="inlineStr">
@@ -1231,50 +1231,50 @@
       </c>
       <c r="D4" s="60" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="E4" s="60" t="inlineStr">
         <is>
-          <t>Innovation Policy</t>
+          <t>Semiconductors &amp; Telecom</t>
         </is>
       </c>
       <c r="F4" s="76" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G4" s="60" t="inlineStr">
         <is>
-          <t>Major Media</t>
+          <t>Official Company</t>
         </is>
       </c>
       <c r="H4" s="60" t="inlineStr">
         <is>
-          <t>South China Morning Post Technology</t>
+          <t>Samsung Global Newsroom</t>
         </is>
       </c>
       <c r="I4" s="60" t="inlineStr">
         <is>
-          <t>利益率の低下が中国自動車メーカーの価格戦争計画を阻む</t>
+          <t>サムスン電子とブロードコム、メモリおよびファウンドリ技術での戦略的協力を拡大</t>
         </is>
       </c>
       <c r="J4" s="60" t="inlineStr">
         <is>
-          <t>中国の自動車メーカーが利益率の低下に直面し、価格戦争の計画が難航している。</t>
+          <t>サムスン電子とブロードコムは、次世代AIインフラを支えるためのメモリおよびファウンドリ技術に関する戦略的協力を拡大するMOUを締結しました。</t>
         </is>
       </c>
       <c r="K4" s="60" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/business/china-business/article/3361876/lower-profit-margins-set-foil-chinese-carmakers-price-war-plans-despite-falling-sales?utm_source=rss_feed</t>
+          <t>https://news.samsung.com/global/samsung-electronics-and-broadcom-expand-strategic-collaboration-across-memory-and-foundry-technologies</t>
         </is>
       </c>
       <c r="L4" s="60" t="inlineStr">
         <is>
-          <t>edcae2eaed3f6ecc6f59640c</t>
+          <t>bd739fbc33fb8bb2bb1f6e52</t>
         </is>
       </c>
       <c r="M4" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:51:39+09:00</t>
+          <t>2026-07-26T18:56:03+09:00</t>
         </is>
       </c>
       <c r="N4" s="60" t="inlineStr">
@@ -1287,22 +1287,22 @@
     <row r="5" ht="42" customHeight="1">
       <c r="A5" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:51:39+09:00</t>
+          <t>2026-07-26T20:19:15+09:00</t>
         </is>
       </c>
       <c r="B5" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T00:00:14Z</t>
+          <t>2026-07-24T19:55:05Z</t>
         </is>
       </c>
       <c r="C5" s="60" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D5" s="60" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E5" s="60" t="inlineStr">
@@ -1311,7 +1311,7 @@
         </is>
       </c>
       <c r="F5" s="76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5" s="60" t="inlineStr">
         <is>
@@ -1320,32 +1320,32 @@
       </c>
       <c r="H5" s="60" t="inlineStr">
         <is>
-          <t>South China Morning Post Technology</t>
+          <t>The New York Times Science</t>
         </is>
       </c>
       <c r="I5" s="60" t="inlineStr">
         <is>
-          <t>インドネシアのシンガポール対抗計画が具体化</t>
+          <t>What to Know About Peptides the FDA Is Considering for Use</t>
         </is>
       </c>
       <c r="J5" s="60" t="inlineStr">
         <is>
-          <t>インドネシアがシンガポールや香港に対抗する金融センターの設立を目指し、法的基盤が整備された。</t>
+          <t>The agency is considering whether compounding pharmacies should be allowed to produce BPC-157, TB-500 and other previously banned peptides.</t>
         </is>
       </c>
       <c r="K5" s="60" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/week-asia/economics/article/3361783/indonesias-plan-singapore-rival-starts-take-shape?utm_source=rss_feed</t>
+          <t>https://www.nytimes.com/2026/07/23/well/peptides-fda-research.html</t>
         </is>
       </c>
       <c r="L5" s="60" t="inlineStr">
         <is>
-          <t>f74daba2783d19d5f5ff6719</t>
+          <t>2a99e80e122a0e1b78658c57</t>
         </is>
       </c>
       <c r="M5" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:51:39+09:00</t>
+          <t>2026-07-26T20:19:15+09:00</t>
         </is>
       </c>
       <c r="N5" s="60" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="B6" s="75" t="inlineStr">
         <is>
-          <t>2026-07-25T14:32:00Z</t>
+          <t>2026-07-24T16:46:59Z</t>
         </is>
       </c>
       <c r="C6" s="60" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="D6" s="60" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E6" s="60" t="inlineStr">
@@ -1391,27 +1391,27 @@
       </c>
       <c r="H6" s="60" t="inlineStr">
         <is>
-          <t>Samsung Global Newsroom</t>
+          <t>Intel Newsroom</t>
         </is>
       </c>
       <c r="I6" s="60" t="inlineStr">
         <is>
-          <t>サムスン電子とブロードコムがメモリとファウンドリ技術での戦略的協力を拡大</t>
+          <t>インテルとレンズテクノロジー、AI時代の先進半導体パッケージングを実現するために協力</t>
         </is>
       </c>
       <c r="J6" s="60" t="inlineStr">
         <is>
-          <t>サムスン電子とブロードコムが、次世代AIインフラを支えるためのメモリとファウンドリ技術に関する戦略的協力を拡大することを発表しました。</t>
+          <t>インテルとレンズテクノロジーは、ガラス基板を用いた先進半導体パッケージング技術の開発を加速するための戦略的協力を発表しました。これにより、性能向上や相互接続密度の増加が期待されています。</t>
         </is>
       </c>
       <c r="K6" s="60" t="inlineStr">
         <is>
-          <t>https://news.samsung.com/global/samsung-electronics-and-broadcom-expand-strategic-collaboration-across-memory-and-foundry-technologies</t>
+          <t>https://newsroom.intel.com/new-technologies/intel-and-lens-technology-collaborate-to-enable-advanced-semiconductor-packaging-for-the-ai-era</t>
         </is>
       </c>
       <c r="L6" s="60" t="inlineStr">
         <is>
-          <t>bd739fbc33fb8bb2bb1f6e52</t>
+          <t>10eedf14d7d6b636e24e447d</t>
         </is>
       </c>
       <c r="M6" s="75" t="inlineStr">
@@ -1429,31 +1429,31 @@
     <row r="7" ht="42" customHeight="1">
       <c r="A7" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:13:43+09:00</t>
+          <t>2026-07-26T20:19:15+09:00</t>
         </is>
       </c>
       <c r="B7" s="75" t="inlineStr">
         <is>
-          <t>2026-07-25T02:32:54Z</t>
+          <t>2026-07-24T14:46:32Z</t>
         </is>
       </c>
       <c r="C7" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>EU &amp; Europe</t>
         </is>
       </c>
       <c r="D7" s="60" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E7" s="60" t="inlineStr">
         <is>
-          <t>Innovation Policy</t>
+          <t>Fusion Energy</t>
         </is>
       </c>
       <c r="F7" s="76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" s="60" t="inlineStr">
         <is>
@@ -1462,32 +1462,32 @@
       </c>
       <c r="H7" s="60" t="inlineStr">
         <is>
-          <t>South China Morning Post Technology</t>
+          <t>The New York Times Science</t>
         </is>
       </c>
       <c r="I7" s="60" t="inlineStr">
         <is>
-          <t>中国、Trip.comに765百万ドルの独占禁止罰金を科す</t>
+          <t>Life of Alan Turing Emerges in Richer Detail From Short Story</t>
         </is>
       </c>
       <c r="J7" s="60" t="inlineStr">
         <is>
-          <t>中国の市場規制当局は、Trip.comに対して独占的行為により765百万ドルの罰金を科した。この措置は、中国の市場における競争環境を改善するための政策の一環と見られる。</t>
+          <t>A Cambridge professor has transcribed a handwritten story that the famous mathematician wrote in the year before his death, presenting a different side of him.</t>
         </is>
       </c>
       <c r="K7" s="60" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/tech/policy/article/3361818/china-hits-tripcom-us765-million-antitrust-penalty-after-six-month-investigation?utm_source=rss_feed</t>
+          <t>https://www.nytimes.com/2026/07/24/world/europe/alan-turing-short-story-cambridge.html</t>
         </is>
       </c>
       <c r="L7" s="60" t="inlineStr">
         <is>
-          <t>4f0f96e20a2da9824751e330</t>
+          <t>72af9a1d3b7d7274dd0ca533</t>
         </is>
       </c>
       <c r="M7" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:13:43+09:00</t>
+          <t>2026-07-26T20:19:15+09:00</t>
         </is>
       </c>
       <c r="N7" s="60" t="inlineStr">
@@ -1500,17 +1500,17 @@
     <row r="8" ht="42" customHeight="1">
       <c r="A8" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T20:19:15+09:00</t>
         </is>
       </c>
       <c r="B8" s="75" t="inlineStr">
         <is>
-          <t>2026-07-24T16:46:59Z</t>
+          <t>2026-07-24T14:25:17Z</t>
         </is>
       </c>
       <c r="C8" s="60" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D8" s="60" t="inlineStr">
@@ -1520,45 +1520,45 @@
       </c>
       <c r="E8" s="60" t="inlineStr">
         <is>
-          <t>Semiconductors &amp; Telecom</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="F8" s="76" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G8" s="60" t="inlineStr">
         <is>
-          <t>Official Company</t>
+          <t>Major Media</t>
         </is>
       </c>
       <c r="H8" s="60" t="inlineStr">
         <is>
-          <t>Intel Newsroom</t>
+          <t>The New York Times Science</t>
         </is>
       </c>
       <c r="I8" s="60" t="inlineStr">
         <is>
-          <t>インテルとレンズテクノロジーがAI時代の先進半導体パッケージングを実現するために協力</t>
+          <t>Health Care Agency Discontinues Dozens of Active Research Awards</t>
         </is>
       </c>
       <c r="J8" s="60" t="inlineStr">
         <is>
-          <t>インテルとレンズテクノロジーが、ガラス基板を用いた先進的な半導体パッケージング技術の開発を加速するための戦略的協力を発表しました。</t>
+          <t>The Agency for Healthcare Research and Quality slowed the awarding of new grants last year. Now it is stopping existing ones.</t>
         </is>
       </c>
       <c r="K8" s="60" t="inlineStr">
         <is>
-          <t>https://newsroom.intel.com/new-technologies/intel-and-lens-technology-collaborate-to-enable-advanced-semiconductor-packaging-for-the-ai-era</t>
+          <t>https://www.nytimes.com/2026/07/23/science/health-research-funding-ahrq.html</t>
         </is>
       </c>
       <c r="L8" s="60" t="inlineStr">
         <is>
-          <t>10eedf14d7d6b636e24e447d</t>
+          <t>35ca7b9882d04ac7b97464b0</t>
         </is>
       </c>
       <c r="M8" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T20:19:15+09:00</t>
         </is>
       </c>
       <c r="N8" s="60" t="inlineStr">
@@ -1571,17 +1571,17 @@
     <row r="9" ht="42" customHeight="1">
       <c r="A9" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T20:19:15+09:00</t>
         </is>
       </c>
       <c r="B9" s="75" t="inlineStr">
         <is>
-          <t>2026-07-24T04:34:27Z</t>
+          <t>2026-07-24T14:08:05Z</t>
         </is>
       </c>
       <c r="C9" s="60" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D9" s="60" t="inlineStr">
@@ -1591,7 +1591,7 @@
       </c>
       <c r="E9" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence | Semiconductors &amp; Telecom</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="F9" s="76" t="n">
@@ -1599,37 +1599,37 @@
       </c>
       <c r="G9" s="60" t="inlineStr">
         <is>
-          <t>Official Company</t>
+          <t>Major Media</t>
         </is>
       </c>
       <c r="H9" s="60" t="inlineStr">
         <is>
-          <t>NVIDIA Blog</t>
+          <t>The New York Times Technology</t>
         </is>
       </c>
       <c r="I9" s="60" t="inlineStr">
         <is>
-          <t>AIサミットで韓国がNVIDIAとパートナーと共にAIの未来を描く</t>
+          <t>An A.I. Music F.A.Q.: Can I Remix Madonna? Is This All Legal?</t>
         </is>
       </c>
       <c r="J9" s="60" t="inlineStr">
         <is>
-          <t>韓国の大統領とビジネスリーダーがNVIDIAと共にAIの進展を議論し、今後の政策を策定するための会議を開催した。</t>
+          <t>Advances in A.I. are making it possible to create all kinds of music from scratch, but they also raise questions about what is legal and who will actually listen.</t>
         </is>
       </c>
       <c r="K9" s="60" t="inlineStr">
         <is>
-          <t>https://blogs.nvidia.com/blog/ai-summit-korea-partners-and-nvidia/</t>
+          <t>https://www.nytimes.com/2026/07/24/arts/music/ai-music-faq.html</t>
         </is>
       </c>
       <c r="L9" s="60" t="inlineStr">
         <is>
-          <t>3124530844eb0ac80a5a17e4</t>
+          <t>7de4799418b19aa7b1ed024c</t>
         </is>
       </c>
       <c r="M9" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T20:19:15+09:00</t>
         </is>
       </c>
       <c r="N9" s="60" t="inlineStr">
@@ -1642,27 +1642,27 @@
     <row r="10" ht="42" customHeight="1">
       <c r="A10" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T20:19:15+09:00</t>
         </is>
       </c>
       <c r="B10" s="75" t="inlineStr">
         <is>
-          <t>2026-07-24T00:00:00Z</t>
+          <t>2026-07-24T13:32:42Z</t>
         </is>
       </c>
       <c r="C10" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D10" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E10" s="60" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="F10" s="76" t="n">
@@ -1670,37 +1670,37 @@
       </c>
       <c r="G10" s="60" t="inlineStr">
         <is>
-          <t>Scientific Publication</t>
+          <t>Major Media</t>
         </is>
       </c>
       <c r="H10" s="60" t="inlineStr">
         <is>
-          <t>Nature</t>
+          <t>The New York Times Science</t>
         </is>
       </c>
       <c r="I10" s="60" t="inlineStr">
         <is>
-          <t>奇妙なCRISPR酵素が癌細胞をDNAを破壊して殺す</t>
+          <t>Jacob Tsimerman Lives in Number Theory</t>
         </is>
       </c>
       <c r="J10" s="60" t="inlineStr">
         <is>
-          <t>新たなCRISPR酵素が癌細胞を標的にし、DNAを破壊することで効果を示す可能性があることが報告された。</t>
+          <t>Dr. Tsimerman won one of four Fields Medals, an award for top mathematicians under 40, for his work on the André-Oort conjecture, but is now changing his focus to artificial intelligence.</t>
         </is>
       </c>
       <c r="K10" s="60" t="inlineStr">
         <is>
-          <t>https://www.nature.com/articles/d41586-026-02268-z</t>
+          <t>https://www.nytimes.com/2026/07/23/science/jacob-tsimerman-fields-medal.html</t>
         </is>
       </c>
       <c r="L10" s="60" t="inlineStr">
         <is>
-          <t>006500c385193d3a42b6ae61</t>
+          <t>7bc77efe108aea824dae5a1b</t>
         </is>
       </c>
       <c r="M10" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T20:19:15+09:00</t>
         </is>
       </c>
       <c r="N10" s="60" t="inlineStr">
@@ -1713,17 +1713,17 @@
     <row r="11" ht="42" customHeight="1">
       <c r="A11" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T20:19:15+09:00</t>
         </is>
       </c>
       <c r="B11" s="75" t="inlineStr">
         <is>
-          <t>2026-07-23T16:58:28Z</t>
+          <t>2026-07-24T13:29:44Z</t>
         </is>
       </c>
       <c r="C11" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D11" s="60" t="inlineStr">
@@ -1733,11 +1733,11 @@
       </c>
       <c r="E11" s="60" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Innovation Policy</t>
         </is>
       </c>
       <c r="F11" s="76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" s="60" t="inlineStr">
         <is>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="H11" s="60" t="inlineStr">
         <is>
-          <t>MIT Technology Review</t>
+          <t>The New York Times Science</t>
         </is>
       </c>
       <c r="I11" s="60" t="inlineStr">
         <is>
-          <t>超冷却された腎臓が豚に移植される「画期的な成果」</t>
+          <t>FDAパネルが4つのペプチドの制限解除を支持</t>
         </is>
       </c>
       <c r="J11" s="60" t="inlineStr">
         <is>
-          <t>臓器提供において、時間が重要であることを示す研究が発表され、超冷却された腎臓が豚に移植されることに成功した。これは臓器の保存と移植における新たな可能性を示唆している。</t>
+          <t>FDAのパネルは、3年前に禁止された未承認薬への広範なアクセスを許可することに反対する科学者たちの議論を行った。</t>
         </is>
       </c>
       <c r="K11" s="60" t="inlineStr">
         <is>
-          <t>https://www.technologyreview.com/2026/07/23/1140765/supercooled-kidneys-have-been-transplanted-into-pigs-in-a-landmark-achievement/</t>
+          <t>https://www.nytimes.com/2026/07/23/health/fda-scientists-rfk-peptides.html</t>
         </is>
       </c>
       <c r="L11" s="60" t="inlineStr">
         <is>
-          <t>590a8cbd726d99d379ccecb1</t>
+          <t>e6017b8b35489923d29a4728</t>
         </is>
       </c>
       <c r="M11" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T20:19:15+09:00</t>
         </is>
       </c>
       <c r="N11" s="60" t="inlineStr">
@@ -1784,12 +1784,12 @@
     <row r="12" ht="42" customHeight="1">
       <c r="A12" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T20:19:15+09:00</t>
         </is>
       </c>
       <c r="B12" s="75" t="inlineStr">
         <is>
-          <t>2026-07-23T15:00:48Z</t>
+          <t>2026-07-24T13:00:14Z</t>
         </is>
       </c>
       <c r="C12" s="60" t="inlineStr">
@@ -1804,11 +1804,11 @@
       </c>
       <c r="E12" s="60" t="inlineStr">
         <is>
-          <t>Innovation Policy</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="F12" s="76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" s="60" t="inlineStr">
         <is>
@@ -1822,27 +1822,27 @@
       </c>
       <c r="I12" s="60" t="inlineStr">
         <is>
-          <t>現在の10年代が映画を革命化した理由</t>
+          <t>Be skeptical of OpenAI’s rogue hacker agent story | John Thickstun</t>
         </is>
       </c>
       <c r="J12" s="60" t="inlineStr">
         <is>
-          <t>映画産業の革新とその影響について考察されており、政策的な観点からの議論が含まれています。</t>
+          <t>If OpenAI loudly proclaims how dangerous AI is, investors will hear how powerful it is. And who benefits from that? On 14 February 2019, OpenAI announced a language model called GPT-2, the precursor to the models that power modern AI chatbots and agents such as ChatGPT and Claude. But OpenAI declared GPT-2 was too risky to release, citing concerns about safety and abuse. I recall being annoyed at the time that OpenAI would make such a useless announcement: the risks seemed overblown, and without access to the model there wasn’t much for a researcher like me to learn about GPT-2. Continue reading...</t>
         </is>
       </c>
       <c r="K12" s="60" t="inlineStr">
         <is>
-          <t>https://www.theguardian.com/film/2026/jul/23/how-2020s-decade-revolutionised-cinema</t>
+          <t>https://www.theguardian.com/technology/2026/jul/24/openai-rogue-hacker</t>
         </is>
       </c>
       <c r="L12" s="60" t="inlineStr">
         <is>
-          <t>f8939f05439f07fdefca04fc</t>
+          <t>ac01b28f85e133214755b7cc</t>
         </is>
       </c>
       <c r="M12" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T20:19:15+09:00</t>
         </is>
       </c>
       <c r="N12" s="60" t="inlineStr">
@@ -1855,31 +1855,31 @@
     <row r="13" ht="42" customHeight="1">
       <c r="A13" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:13:43+09:00</t>
+          <t>2026-07-26T20:19:15+09:00</t>
         </is>
       </c>
       <c r="B13" s="75" t="inlineStr">
         <is>
-          <t>2026-07-23T11:30:07Z</t>
+          <t>2026-07-24T12:00:14Z</t>
         </is>
       </c>
       <c r="C13" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="D13" s="60" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="E13" s="60" t="inlineStr">
         <is>
-          <t>Robotics | Innovation Policy</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="F13" s="76" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G13" s="60" t="inlineStr">
         <is>
@@ -1888,32 +1888,32 @@
       </c>
       <c r="H13" s="60" t="inlineStr">
         <is>
-          <t>South China Morning Post Technology</t>
+          <t>The Guardian Technology</t>
         </is>
       </c>
       <c r="I13" s="60" t="inlineStr">
         <is>
-          <t>米国、中国製ヒューマノイドロボットの禁止を検討</t>
+          <t>Should you use AI for a task? Here’s a simple way to decide | Bruce Schneier</t>
         </is>
       </c>
       <c r="J13" s="60" t="inlineStr">
         <is>
-          <t>米国の議会は、中国製のヒューマノイドロボットの軍事利用を禁止する防衛法案を進めており、国家安全保障やデータプライバシーの懸念から外国の自律システムの使用を制限する内容が含まれている。</t>
+          <t>Sometimes, what matters isn’t your output but what you put into the process. Think of it like work v the gym I teach public policy at the Harvard Kennedy School and the Munk School at the University of Toronto. And it will come as no surprise to you that my students regularly use AI to complete their writing assignments. Doing so is a waste of their tuition money. But if their entire career is going to include AI writing assistants, why shouldn’t they embrace their future? The best way I’ve found to explain the dilemma comes from the AI researcher Daniel Meissler: it’s the difference between work and the gym. Continue reading...</t>
         </is>
       </c>
       <c r="K13" s="60" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/tech/policy/article/3361622/us-eyes-ban-chinese-humanoid-robots-us-china-tech-rivalry-intensifies?utm_source=rss_feed</t>
+          <t>https://www.theguardian.com/commentisfree/2026/jul/24/should-you-use-ai</t>
         </is>
       </c>
       <c r="L13" s="60" t="inlineStr">
         <is>
-          <t>17c856708cfe91897e9a7d7c</t>
+          <t>d7259db0d54f48b0f5039bb8</t>
         </is>
       </c>
       <c r="M13" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:13:43+09:00</t>
+          <t>2026-07-26T20:19:15+09:00</t>
         </is>
       </c>
       <c r="N13" s="60" t="inlineStr">
@@ -1926,12 +1926,12 @@
     <row r="14" ht="42" customHeight="1">
       <c r="A14" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:13:43+09:00</t>
+          <t>2026-07-26T20:19:15+09:00</t>
         </is>
       </c>
       <c r="B14" s="75" t="inlineStr">
         <is>
-          <t>2026-07-23T10:00:17Z</t>
+          <t>2026-07-24T11:39:05Z</t>
         </is>
       </c>
       <c r="C14" s="60" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="D14" s="60" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>United Arab Emirates</t>
         </is>
       </c>
       <c r="E14" s="60" t="inlineStr">
@@ -1959,32 +1959,32 @@
       </c>
       <c r="H14" s="60" t="inlineStr">
         <is>
-          <t>South China Morning Post Technology</t>
+          <t>The National Technology</t>
         </is>
       </c>
       <c r="I14" s="60" t="inlineStr">
         <is>
-          <t>中国のテクノロジー企業、国内競争を背景にAIブームをチャンスに変える</t>
+          <t>Zoom launches live voice translation, with Arabic coming in late 2026</t>
         </is>
       </c>
       <c r="J14" s="60" t="inlineStr">
         <is>
-          <t>中国のテクノロジー企業は、AIへの投資が急増する中、国内の激しい競争を背景に国際的な展開を加速させている。特にクラウドベースのソフトウェアや基盤モデルを通じて、物理的な供給チェーンだけでなく、テクノロジーの輸出も増加している。</t>
+          <t>Zoom Technologies has launched a new live voice translation service, with Arabic support coming in the fourth quarter of this year. Five languages – English, Chinese, French, Japanese and Spanish – will initially be available, the California-based company said. A Zoom representative confirmed to The National that Arabic will be available in the fourth quarter, alongside German, Italian and Portuguese. Zoom launched a version of the service in April, after promoting it at its Zoomtopia conference last September. Using the live voice translation feature requires a Pro, Business, or Enterprise account, the artificial intelligence plug-in ZoomMate, or a stand-alone add-on. Zoom has posted instr…</t>
         </is>
       </c>
       <c r="K14" s="60" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/tech/tech-trends/article/3361596/chinas-tech-firms-turn-global-ai-boom-opportunity-amid-fierce-rivalry-home?utm_source=rss_feed</t>
+          <t>https://www.thenationalnews.com/future/technology/2026/07/24/zoom-launches-live-voice-translation-with-arabic-coming-in-late-2026/</t>
         </is>
       </c>
       <c r="L14" s="60" t="inlineStr">
         <is>
-          <t>2d5de96218ebc1a4b06e4e7c</t>
+          <t>9df818f0442aeef1a46447c7</t>
         </is>
       </c>
       <c r="M14" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:13:43+09:00</t>
+          <t>2026-07-26T20:19:15+09:00</t>
         </is>
       </c>
       <c r="N14" s="60" t="inlineStr">
@@ -1997,65 +1997,65 @@
     <row r="15" ht="42" customHeight="1">
       <c r="A15" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T20:19:15+09:00</t>
         </is>
       </c>
       <c r="B15" s="75" t="inlineStr">
         <is>
-          <t>2026-07-23T09:23:23Z</t>
+          <t>2026-07-24T11:00:03Z</t>
         </is>
       </c>
       <c r="C15" s="60" t="inlineStr">
         <is>
-          <t>EU &amp; Europe</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D15" s="60" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E15" s="60" t="inlineStr">
         <is>
-          <t>Innovation Policy</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="F15" s="76" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G15" s="60" t="inlineStr">
         <is>
-          <t>Policy Institute</t>
+          <t>Major Media</t>
         </is>
       </c>
       <c r="H15" s="60" t="inlineStr">
         <is>
-          <t>Bruegel</t>
+          <t>The New York Times Technology</t>
         </is>
       </c>
       <c r="I15" s="60" t="inlineStr">
         <is>
-          <t>EUの規制改善が競争力をもたらすか？</t>
+          <t>OpenAI Models Go Rogue + Kimi K3 Freakout + A.I. Superforecasting</t>
         </is>
       </c>
       <c r="J15" s="60" t="inlineStr">
         <is>
-          <t>EUの規制改善が競争力に与える影響についてのセッションが行われ、政策の重要性が議論されています。</t>
+          <t>“The story that we’re talking about in this segment was science fiction until Tuesday, OK?”</t>
         </is>
       </c>
       <c r="K15" s="60" t="inlineStr">
         <is>
-          <t>https://www.bruegel.org/node/12451</t>
+          <t>https://www.nytimes.com/2026/07/24/podcasts/hardfork-hugging-face-openai.html</t>
         </is>
       </c>
       <c r="L15" s="60" t="inlineStr">
         <is>
-          <t>90ef16bcfe1bd00925658dc5</t>
+          <t>1227687d6341c95d9729e93a</t>
         </is>
       </c>
       <c r="M15" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T20:19:15+09:00</t>
         </is>
       </c>
       <c r="N15" s="60" t="inlineStr">
@@ -2068,65 +2068,65 @@
     <row r="16" ht="42" customHeight="1">
       <c r="A16" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T20:19:15+09:00</t>
         </is>
       </c>
       <c r="B16" s="75" t="inlineStr">
         <is>
-          <t>2026-07-23T02:00:46Z</t>
+          <t>2026-07-24T06:30:46Z</t>
         </is>
       </c>
       <c r="C16" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D16" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="E16" s="60" t="inlineStr">
         <is>
-          <t>Semiconductors &amp; Telecom</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="F16" s="76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G16" s="60" t="inlineStr">
         <is>
-          <t>Official Company</t>
+          <t>Major Media</t>
         </is>
       </c>
       <c r="H16" s="60" t="inlineStr">
         <is>
-          <t>NVIDIA Blog</t>
+          <t>South China Morning Post Technology</t>
         </is>
       </c>
       <c r="I16" s="60" t="inlineStr">
         <is>
-          <t>NVIDIAのAIスパコンが海軍大学校で稼働開始</t>
+          <t>China’s Kimi K3 ‘significantly below’ US rivals in hacking power, study shows</t>
         </is>
       </c>
       <c r="J16" s="60" t="inlineStr">
         <is>
-          <t>NVIDIAの創業者が海軍大学校を訪れ、強力なAIプラットフォームを導入しました。これにより、学生や研究者が最新の技術を活用できる環境が整います。</t>
+          <t>Chinese unicorn Moonshot AI’s Kimi K3 model trails far behind top American rivals in its ability to launch cyberattacks, joint British-US government research shows, challenging Washington’s brewing anxiety over the rapid rise of Chinese open-source artificial intelligence. The model, currently considered China’s most powerful large language model, performs “significantly below the most recent frontier cyber-capable models”, according to a report published on Thursday by the UK Artificial...</t>
         </is>
       </c>
       <c r="K16" s="60" t="inlineStr">
         <is>
-          <t>https://blogs.nvidia.com/blog/naval-postgraduate-school-dgx-ai-supercomputer/</t>
+          <t>https://www.scmp.com/tech/tech-war/article/3361711/chinas-kimi-k3-significantly-below-us-rivals-hacking-power-uk-us-study-shows?utm_source=rss_feed</t>
         </is>
       </c>
       <c r="L16" s="60" t="inlineStr">
         <is>
-          <t>c174fc131c4d55cb839833e9</t>
+          <t>fc39eee8898a984a897b9824</t>
         </is>
       </c>
       <c r="M16" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T20:19:15+09:00</t>
         </is>
       </c>
       <c r="N16" s="60" t="inlineStr">
@@ -2139,12 +2139,12 @@
     <row r="17" ht="42" customHeight="1">
       <c r="A17" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:05:06+09:00</t>
+          <t>2026-07-26T20:19:15+09:00</t>
         </is>
       </c>
       <c r="B17" s="75" t="inlineStr">
         <is>
-          <t>2026-07-23T00:00:00Z</t>
+          <t>2026-07-23T20:58:35Z</t>
         </is>
       </c>
       <c r="C17" s="60" t="inlineStr">
@@ -2154,50 +2154,50 @@
       </c>
       <c r="D17" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="E17" s="60" t="inlineStr">
         <is>
-          <t>Innovation Policy</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="F17" s="76" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G17" s="60" t="inlineStr">
         <is>
-          <t>Policy Institute</t>
+          <t>Major Media</t>
         </is>
       </c>
       <c r="H17" s="60" t="inlineStr">
         <is>
-          <t>Brookings TechTank</t>
+          <t>BBC Technology</t>
         </is>
       </c>
       <c r="I17" s="60" t="inlineStr">
         <is>
-          <t>技術企業が雇用問題とスキル開発にどのように対処すべきか</t>
+          <t>Lawmakers push for AI 'kill switch' after OpenAI models go rogue</t>
         </is>
       </c>
       <c r="J17" s="60" t="inlineStr">
         <is>
-          <t>技術企業が直面する雇用問題とスキル開発に関する提言が行われ、政策的な視点からのアプローチが求められています。</t>
+          <t>A new bill would let the US government order the shutdown of AI models that pose a public threat.</t>
         </is>
       </c>
       <c r="K17" s="60" t="inlineStr">
         <is>
-          <t>https://www.brookings.edu/articles/how-tech-firms-should-address-job-concerns-and-skill-development/</t>
+          <t>https://www.bbc.co.uk/news/articles/cx2vqj2e9x8o?at_medium=RSS&amp;at_campaign=rss</t>
         </is>
       </c>
       <c r="L17" s="60" t="inlineStr">
         <is>
-          <t>0d48c18a0657c35e8abe7133</t>
+          <t>30744ac6eef4bc37b48358ce</t>
         </is>
       </c>
       <c r="M17" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:05:06+09:00</t>
+          <t>2026-07-26T20:19:15+09:00</t>
         </is>
       </c>
       <c r="N17" s="60" t="inlineStr">
@@ -2210,27 +2210,27 @@
     <row r="18" ht="42" customHeight="1">
       <c r="A18" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T20:19:15+09:00</t>
         </is>
       </c>
       <c r="B18" s="75" t="inlineStr">
         <is>
-          <t>2026-07-23T00:00:00Z</t>
+          <t>2026-07-23T15:27:52Z</t>
         </is>
       </c>
       <c r="C18" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D18" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="E18" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence | Healthcare</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="F18" s="76" t="n">
@@ -2238,37 +2238,37 @@
       </c>
       <c r="G18" s="60" t="inlineStr">
         <is>
-          <t>Official Company</t>
+          <t>Major Media</t>
         </is>
       </c>
       <c r="H18" s="60" t="inlineStr">
         <is>
-          <t>OpenAI News</t>
+          <t>The Guardian Technology</t>
         </is>
       </c>
       <c r="I18" s="60" t="inlineStr">
         <is>
-          <t>ChatGPTにおける健康機能の導入</t>
+          <t>Elon Musk says he got ‘carried away’ with Trump – but still holds on to contentious political views</t>
         </is>
       </c>
       <c r="J18" s="60" t="inlineStr">
         <is>
-          <t>ChatGPTが米国のユーザー向けに医療記録とApple Healthを安全に接続し、個別化された健康情報を提供する新機能を発表しました。</t>
+          <t>In interview, billionaire says instead of running ‘Doge’ he should’ve ‘worked on my companies’ and shares extreme predictions Elon Musk has admitted he became too consumed by politics during his volatile alliance with Donald Trump and his brief appointment as the president’s financial axman, running the so-called “department of government efficiency” (Doge). The world’s richest person, and briefly its first trillionaire after his SpaceX company floated on the New York stock exchange in June, made the confession in a wide-ranging interview with the Economist published on Thursday. He shared his positions on subjects from foreign wars to AI, and made a number of eye-opening predictions for th…</t>
         </is>
       </c>
       <c r="K18" s="60" t="inlineStr">
         <is>
-          <t>https://openai.com/index/health-in-chatgpt</t>
+          <t>https://www.theguardian.com/technology/2026/jul/23/elon-musk-regret-trump-doge-ai</t>
         </is>
       </c>
       <c r="L18" s="60" t="inlineStr">
         <is>
-          <t>bf70d809f9542eeef4af8727</t>
+          <t>5ab5ea23fbff158109e679af</t>
         </is>
       </c>
       <c r="M18" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T20:19:15+09:00</t>
         </is>
       </c>
       <c r="N18" s="60" t="inlineStr">
@@ -2281,22 +2281,22 @@
     <row r="19" ht="42" customHeight="1">
       <c r="A19" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T20:19:15+09:00</t>
         </is>
       </c>
       <c r="B19" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T14:21:46Z</t>
+          <t>2026-07-23T15:23:13Z</t>
         </is>
       </c>
       <c r="C19" s="60" t="inlineStr">
         <is>
-          <t>EU &amp; Europe</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D19" s="60" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E19" s="60" t="inlineStr">
@@ -2305,41 +2305,41 @@
         </is>
       </c>
       <c r="F19" s="76" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G19" s="60" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Major Media</t>
         </is>
       </c>
       <c r="H19" s="60" t="inlineStr">
         <is>
-          <t>UK DSIT</t>
+          <t>The New York Times Technology</t>
         </is>
       </c>
       <c r="I19" s="60" t="inlineStr">
         <is>
-          <t>研究における女性のための憲章に関するガイダンス</t>
+          <t>Lawsuit Against Meta Over Social Media Addiction Is Dropped</t>
         </is>
       </c>
       <c r="J19" s="60" t="inlineStr">
         <is>
-          <t>英国の研究システムにおける女性の成果を改善するための自主的な取り組みが提案され、研究資金提供者や研究機関に対する具体的な行動が示されています。</t>
+          <t>For Meta, the move was a reprieve after it and YouTube were found liable in another case in March of negligence and personal injury for their platforms’ addictive features.</t>
         </is>
       </c>
       <c r="K19" s="60" t="inlineStr">
         <is>
-          <t>https://www.gov.uk/government/publications/women-in-research-charter</t>
+          <t>https://www.nytimes.com/2026/07/22/technology/meta-social-media-lawsuit.html</t>
         </is>
       </c>
       <c r="L19" s="60" t="inlineStr">
         <is>
-          <t>1e9fd9033d38bacea37c0f42</t>
+          <t>1e298ac58555866955586e90</t>
         </is>
       </c>
       <c r="M19" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T20:19:15+09:00</t>
         </is>
       </c>
       <c r="N19" s="60" t="inlineStr">
@@ -2352,12 +2352,12 @@
     <row r="20" ht="42" customHeight="1">
       <c r="A20" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:05:06+09:00</t>
+          <t>2026-07-26T20:13:43+09:00</t>
         </is>
       </c>
       <c r="B20" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T14:12:14Z</t>
+          <t>2026-07-23T11:30:07Z</t>
         </is>
       </c>
       <c r="C20" s="60" t="inlineStr">
@@ -2367,50 +2367,50 @@
       </c>
       <c r="D20" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="E20" s="60" t="inlineStr">
         <is>
-          <t>Innovation Policy</t>
+          <t>Robotics | Innovation Policy</t>
         </is>
       </c>
       <c r="F20" s="76" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G20" s="60" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Major Media</t>
         </is>
       </c>
       <c r="H20" s="60" t="inlineStr">
         <is>
-          <t>DOE Office of Science News</t>
+          <t>South China Morning Post Technology</t>
         </is>
       </c>
       <c r="I20" s="60" t="inlineStr">
         <is>
-          <t>エネルギー長官クリス・ライトがAI駆動の科学的発見を加速するための最初のジェネシスミッションプロジェクトを発表</t>
+          <t>米国、中国製ヒューマノイドロボットの禁止を検討</t>
         </is>
       </c>
       <c r="J20" s="60" t="inlineStr">
         <is>
-          <t>エネルギー省は、全米から選ばれた約300のプロジェクトを発表し、エネルギー、発見科学、国家安全保障におけるブレークスルーを加速することを目指しています。</t>
+          <t>米国の議会は、中国製のヒューマノイドロボットの軍事利用を禁止する防衛法案を進めており、国家安全保障やデータプライバシーの懸念から外国の自律システムの使用を制限する内容が含まれている。</t>
         </is>
       </c>
       <c r="K20" s="60" t="inlineStr">
         <is>
-          <t>https://www.energy.gov/articles/secretary-energy-chris-wright-announces-first-genesis-mission-projects-selected-accelerate</t>
+          <t>https://www.scmp.com/tech/policy/article/3361622/us-eyes-ban-chinese-humanoid-robots-us-china-tech-rivalry-intensifies?utm_source=rss_feed</t>
         </is>
       </c>
       <c r="L20" s="60" t="inlineStr">
         <is>
-          <t>23fa1d6907c14d73ce3a41cd</t>
+          <t>17c856708cfe91897e9a7d7c</t>
         </is>
       </c>
       <c r="M20" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:05:06+09:00</t>
+          <t>2026-07-26T20:13:43+09:00</t>
         </is>
       </c>
       <c r="N20" s="60" t="inlineStr">
@@ -2423,12 +2423,12 @@
     <row r="21" ht="42" customHeight="1">
       <c r="A21" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T20:19:15+09:00</t>
         </is>
       </c>
       <c r="B21" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T14:12:00Z</t>
+          <t>2026-07-23T00:43:11Z</t>
         </is>
       </c>
       <c r="C21" s="60" t="inlineStr">
@@ -2443,45 +2443,45 @@
       </c>
       <c r="E21" s="60" t="inlineStr">
         <is>
-          <t>Innovation Policy | Artificial Intelligence</t>
+          <t>Innovation Policy</t>
         </is>
       </c>
       <c r="F21" s="76" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G21" s="60" t="inlineStr">
         <is>
-          <t>Policy Institute</t>
+          <t>Major Media</t>
         </is>
       </c>
       <c r="H21" s="60" t="inlineStr">
         <is>
-          <t>CSET</t>
+          <t>The New York Times Technology</t>
         </is>
       </c>
       <c r="I21" s="60" t="inlineStr">
         <is>
-          <t>人工知能と核戦争に関するグローバルノーベル賞受賞者会議での発言</t>
+          <t>Clarity Actが大統領の暗号販売禁止を巡る議論に巻き込まれる</t>
         </is>
       </c>
       <c r="J21" s="60" t="inlineStr">
         <is>
-          <t>CSETのシニアフェローがAIと核戦争に関する会議での経験を共有。</t>
+          <t>暗号産業が推進するClarity Actについて、民主党と共和党が議論を交わしており、上院での投票が近づいている。</t>
         </is>
       </c>
       <c r="K21" s="60" t="inlineStr">
         <is>
-          <t>https://cset.georgetown.edu/article/remarks-at-the-global-nobel-laureates-assembly-on-artificial-intelligence-and-nuclear-war/</t>
+          <t>https://www.nytimes.com/2026/07/22/technology/crypto-bill-trump.html</t>
         </is>
       </c>
       <c r="L21" s="60" t="inlineStr">
         <is>
-          <t>863086979e9f7f63c082cb57</t>
+          <t>3935aad326cb655427958fe7</t>
         </is>
       </c>
       <c r="M21" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T20:19:15+09:00</t>
         </is>
       </c>
       <c r="N21" s="60" t="inlineStr">
@@ -2499,7 +2499,7 @@
       </c>
       <c r="B22" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T13:58:00Z</t>
+          <t>2026-07-22T14:21:46Z</t>
         </is>
       </c>
       <c r="C22" s="60" t="inlineStr">
@@ -2532,22 +2532,22 @@
       </c>
       <c r="I22" s="60" t="inlineStr">
         <is>
-          <t>ガイダンス：Consultの利用登録</t>
+          <t>ガイダンス：研究における女性のチャーター</t>
         </is>
       </c>
       <c r="J22" s="60" t="inlineStr">
         <is>
-          <t>政府チームが公共の意見を分析するためのAIツールConsultの利用登録を呼びかけ。</t>
+          <t>英国の研究システムにおける女性の成果を改善するための自主的な取り組みが発表されました。</t>
         </is>
       </c>
       <c r="K22" s="60" t="inlineStr">
         <is>
-          <t>https://www.gov.uk/government/publications/consult-register-your-interest</t>
+          <t>https://www.gov.uk/government/publications/women-in-research-charter</t>
         </is>
       </c>
       <c r="L22" s="60" t="inlineStr">
         <is>
-          <t>a651f42eb5805e39f03fbebe</t>
+          <t>1e9fd9033d38bacea37c0f42</t>
         </is>
       </c>
       <c r="M22" s="75" t="inlineStr">
@@ -2570,7 +2570,7 @@
       </c>
       <c r="B23" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T13:53:19Z</t>
+          <t>2026-07-22T14:12:14Z</t>
         </is>
       </c>
       <c r="C23" s="60" t="inlineStr">
@@ -2585,11 +2585,11 @@
       </c>
       <c r="E23" s="60" t="inlineStr">
         <is>
-          <t>Innovation Policy | Artificial Intelligence</t>
+          <t>Innovation Policy</t>
         </is>
       </c>
       <c r="F23" s="76" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G23" s="60" t="inlineStr">
         <is>
@@ -2598,27 +2598,27 @@
       </c>
       <c r="H23" s="60" t="inlineStr">
         <is>
-          <t>National Science Foundation News</t>
+          <t>DOE Office of Science News</t>
         </is>
       </c>
       <c r="I23" s="60" t="inlineStr">
         <is>
-          <t>NSF長官代理によるAI優先事項の推進に関する声明</t>
+          <t>エネルギー長官がAI駆動の科学発見を加速するためのプロジェクトを発表</t>
         </is>
       </c>
       <c r="J23" s="60" t="inlineStr">
         <is>
-          <t>米国国立科学財団がホワイトハウスと連携し、AIに関する優先事項を推進することを発表。</t>
+          <t>エネルギー長官が、AI駆動の科学発見を加速するために選定された約300のプロジェクトを発表しました。</t>
         </is>
       </c>
       <c r="K23" s="60" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/news/statement-nsf-chief-staff-brian-stone-performing-duties-nsf-1</t>
+          <t>https://www.energy.gov/articles/secretary-energy-chris-wright-announces-first-genesis-mission-projects-selected-accelerate</t>
         </is>
       </c>
       <c r="L23" s="60" t="inlineStr">
         <is>
-          <t>123e2207578ca69c8f9c00a2</t>
+          <t>23fa1d6907c14d73ce3a41cd</t>
         </is>
       </c>
       <c r="M23" s="75" t="inlineStr">
@@ -2636,31 +2636,31 @@
     <row r="24" ht="42" customHeight="1">
       <c r="A24" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:05:06+09:00</t>
+          <t>2026-07-26T18:56:03+09:00</t>
         </is>
       </c>
       <c r="B24" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T13:53:12Z</t>
+          <t>2026-07-22T13:58:00Z</t>
         </is>
       </c>
       <c r="C24" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>EU &amp; Europe</t>
         </is>
       </c>
       <c r="D24" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="E24" s="60" t="inlineStr">
         <is>
-          <t>Innovation Policy | Artificial Intelligence</t>
+          <t>Innovation Policy</t>
         </is>
       </c>
       <c r="F24" s="76" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G24" s="60" t="inlineStr">
         <is>
@@ -2669,32 +2669,32 @@
       </c>
       <c r="H24" s="60" t="inlineStr">
         <is>
-          <t>National Science Foundation News</t>
+          <t>UK DSIT</t>
         </is>
       </c>
       <c r="I24" s="60" t="inlineStr">
         <is>
-          <t>新しいNSFイニシアチブがAIによる科学的発見のためのデータセットの価値を解放</t>
+          <t>ガイダンス：登録して関心を示す</t>
         </is>
       </c>
       <c r="J24" s="60" t="inlineStr">
         <is>
-          <t>米国国立科学財団がAIを活用した科学的発見を促進するための新しいプログラムを発表。</t>
+          <t>政府チームが公的相談の回答を分析するためのAIツール「Consult」の利用に関心を示すよう呼びかけています。</t>
         </is>
       </c>
       <c r="K24" s="60" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/news/new-nsf-initiative-aims-unlock-dataset-value-ai-enabled</t>
+          <t>https://www.gov.uk/government/publications/consult-register-your-interest</t>
         </is>
       </c>
       <c r="L24" s="60" t="inlineStr">
         <is>
-          <t>dcd819527d9b80141b26bcb8</t>
+          <t>a651f42eb5805e39f03fbebe</t>
         </is>
       </c>
       <c r="M24" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:05:06+09:00</t>
+          <t>2026-07-26T18:56:03+09:00</t>
         </is>
       </c>
       <c r="N24" s="60" t="inlineStr">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="B25" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T13:53:06Z</t>
+          <t>2026-07-22T13:53:19Z</t>
         </is>
       </c>
       <c r="C25" s="60" t="inlineStr">
@@ -2727,11 +2727,11 @@
       </c>
       <c r="E25" s="60" t="inlineStr">
         <is>
-          <t>Innovation Policy</t>
+          <t>Innovation Policy | Artificial Intelligence</t>
         </is>
       </c>
       <c r="F25" s="76" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G25" s="60" t="inlineStr">
         <is>
@@ -2745,22 +2745,22 @@
       </c>
       <c r="I25" s="60" t="inlineStr">
         <is>
-          <t>NSFがAI駆動の科学を進めるために8300万ドルの投資を発表</t>
+          <t>NSFのスタッフ長がAI優先事項を推進する声明を発表</t>
         </is>
       </c>
       <c r="J25" s="60" t="inlineStr">
         <is>
-          <t>米国国立科学財団が8300万ドルの助成金を発表し、研究者がデータインフラを利用できるようにする。</t>
+          <t>米国国立科学財団は、ホワイトハウスの科学技術政策室やエネルギー省と連携し、AIに関する優先事項を推進することを表明しました。</t>
         </is>
       </c>
       <c r="K25" s="60" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/news/nsf-announces-83m-investment-integrated-data-systems</t>
+          <t>https://www.nsf.gov/news/statement-nsf-chief-staff-brian-stone-performing-duties-nsf-1</t>
         </is>
       </c>
       <c r="L25" s="60" t="inlineStr">
         <is>
-          <t>018d40b7e6eb7aa4b8cfb5fa</t>
+          <t>123e2207578ca69c8f9c00a2</t>
         </is>
       </c>
       <c r="M25" s="75" t="inlineStr">
@@ -2778,17 +2778,17 @@
     <row r="26" ht="42" customHeight="1">
       <c r="A26" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T19:05:06+09:00</t>
         </is>
       </c>
       <c r="B26" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T13:00:00Z</t>
+          <t>2026-07-22T13:53:12Z</t>
         </is>
       </c>
       <c r="C26" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D26" s="60" t="inlineStr">
@@ -2798,45 +2798,45 @@
       </c>
       <c r="E26" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Innovation Policy | Artificial Intelligence</t>
         </is>
       </c>
       <c r="F26" s="76" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G26" s="60" t="inlineStr">
         <is>
-          <t>Official Company</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H26" s="60" t="inlineStr">
         <is>
-          <t>OpenAI News</t>
+          <t>National Science Foundation News</t>
         </is>
       </c>
       <c r="I26" s="60" t="inlineStr">
         <is>
-          <t>エフィンガム郡コミュニティとのAIインフラ構築</t>
+          <t>新しいNSFイニシアティブがAIを活用した科学的発見のためのデータセットの価値を引き出すことを目指す</t>
         </is>
       </c>
       <c r="J26" s="60" t="inlineStr">
         <is>
-          <t>OpenAIがエフィンガム郡でプロジェクトを発表し、責任あるエネルギー、地域投資、雇用、Codexへのアクセスを約束。</t>
+          <t>米国国立科学財団は、AIを活用した科学的発見を促進するための新しいプログラムを発表し、科学コミュニティのデータセットを活用することを目指しています。</t>
         </is>
       </c>
       <c r="K26" s="60" t="inlineStr">
         <is>
-          <t>https://openai.com/index/building-ai-infrastructure-with-the-effingham-county-community</t>
+          <t>https://www.nsf.gov/news/new-nsf-initiative-aims-unlock-dataset-value-ai-enabled</t>
         </is>
       </c>
       <c r="L26" s="60" t="inlineStr">
         <is>
-          <t>082c4173c70b04519142ea2a</t>
+          <t>dcd819527d9b80141b26bcb8</t>
         </is>
       </c>
       <c r="M26" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T19:05:06+09:00</t>
         </is>
       </c>
       <c r="N26" s="60" t="inlineStr">
@@ -2849,17 +2849,17 @@
     <row r="27" ht="42" customHeight="1">
       <c r="A27" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T19:05:06+09:00</t>
         </is>
       </c>
       <c r="B27" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T13:00:00Z</t>
+          <t>2026-07-22T13:53:06Z</t>
         </is>
       </c>
       <c r="C27" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D27" s="60" t="inlineStr">
@@ -2869,45 +2869,45 @@
       </c>
       <c r="E27" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Innovation Policy</t>
         </is>
       </c>
       <c r="F27" s="76" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G27" s="60" t="inlineStr">
         <is>
-          <t>Official Company</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H27" s="60" t="inlineStr">
         <is>
-          <t>OpenAI News</t>
+          <t>National Science Foundation News</t>
         </is>
       </c>
       <c r="I27" s="60" t="inlineStr">
         <is>
-          <t>ニュース組織がAIを活用して重要な使命を推進</t>
+          <t>NSFがAI駆動の科学を進めるために8300万ドルの投資を発表</t>
         </is>
       </c>
       <c r="J27" s="60" t="inlineStr">
         <is>
-          <t>ニュース組織がAIを利用して報道を強化し、オーディエンスを拡大し、ビジネス運営を改善している。</t>
+          <t>米国国立科学財団は、AI駆動の科学を進めるために8300万ドルの資金を発表し、研究者がデータインフラを利用できるようにすることを目指しています。</t>
         </is>
       </c>
       <c r="K27" s="60" t="inlineStr">
         <is>
-          <t>https://openai.com/index/how-news-organizations-are-using-ai</t>
+          <t>https://www.nsf.gov/news/nsf-announces-83m-investment-integrated-data-systems</t>
         </is>
       </c>
       <c r="L27" s="60" t="inlineStr">
         <is>
-          <t>932591afba7f1cf55372f3f4</t>
+          <t>018d40b7e6eb7aa4b8cfb5fa</t>
         </is>
       </c>
       <c r="M27" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T19:05:06+09:00</t>
         </is>
       </c>
       <c r="N27" s="60" t="inlineStr">
@@ -2958,12 +2958,12 @@
       </c>
       <c r="I28" s="60" t="inlineStr">
         <is>
-          <t>NIST、米国の中小製造業者を支援するための資金提供機会を発表</t>
+          <t>NISTが中小企業製造業者を支援するための資金提供機会を発表</t>
         </is>
       </c>
       <c r="J28" s="60" t="inlineStr">
         <is>
-          <t>NIST MEPは、米国の中小製造業者を支援するための資金提供機会についての情報ウェビナーを開催します。</t>
+          <t>NIST MEPが中小企業製造業者を支援するための資金提供機会についての情報ウェビナーを開催することを発表しました。</t>
         </is>
       </c>
       <c r="K28" s="60" t="inlineStr">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="B30" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T05:30:00Z</t>
+          <t>2026-07-21T19:44:19Z</t>
         </is>
       </c>
       <c r="C30" s="60" t="inlineStr">
@@ -3077,45 +3077,45 @@
       </c>
       <c r="D30" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="E30" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Innovation Policy | Fusion Energy</t>
         </is>
       </c>
       <c r="F30" s="76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G30" s="60" t="inlineStr">
         <is>
-          <t>Official Company</t>
+          <t>Industry Association</t>
         </is>
       </c>
       <c r="H30" s="60" t="inlineStr">
         <is>
-          <t>OpenAI News</t>
+          <t>Fusion Industry Association</t>
         </is>
       </c>
       <c r="I30" s="60" t="inlineStr">
         <is>
-          <t>OpenAI Presenceの紹介</t>
+          <t>FIAとクリーンエアタスクフォースがコードと基準に関する原則を発表</t>
         </is>
       </c>
       <c r="J30" s="60" t="inlineStr">
         <is>
-          <t>OpenAI Presenceは、組織が信頼できる音声およびチャットエージェントを展開するための企業向けAIエージェントプラットフォームです。</t>
+          <t>FIAとクリーンエアタスクフォースが、核融合の安全な展開を確保しつつ革新を促進するためのコードと基準に関する原則を発表しました。</t>
         </is>
       </c>
       <c r="K30" s="60" t="inlineStr">
         <is>
-          <t>https://openai.com/index/introducing-openai-presence</t>
+          <t>https://www.fusionindustryassociation.org/fia-and-clean-air-task-force-publish-principles-on-codes-and-standards/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=fia-and-clean-air-task-force-publish-principles-on-codes-and-standards</t>
         </is>
       </c>
       <c r="L30" s="60" t="inlineStr">
         <is>
-          <t>839f7a51d7b587ae6fb6fad7</t>
+          <t>2366dc909672b56b77a196bd</t>
         </is>
       </c>
       <c r="M30" s="75" t="inlineStr">
@@ -3138,55 +3138,55 @@
       </c>
       <c r="B31" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T00:00:00Z</t>
+          <t>2026-07-21T15:06:31Z</t>
         </is>
       </c>
       <c r="C31" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>EU &amp; Europe</t>
         </is>
       </c>
       <c r="D31" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="E31" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Innovation Policy</t>
         </is>
       </c>
       <c r="F31" s="76" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G31" s="60" t="inlineStr">
         <is>
-          <t>Official Company</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H31" s="60" t="inlineStr">
         <is>
-          <t>OpenAI News</t>
+          <t>UK DSIT</t>
         </is>
       </c>
       <c r="I31" s="60" t="inlineStr">
         <is>
-          <t>NTTデータグループ、Codexでインシデント分析を30分に短縮</t>
+          <t>TechFirst地域助成金プログラムのガイダンス</t>
         </is>
       </c>
       <c r="J31" s="60" t="inlineStr">
         <is>
-          <t>NTTデータグループは、ChatGPT EnterpriseとCodexを活用し、9,000人の従業員が業務を自動化し、インシデント分析を30分に短縮することに成功しました。</t>
+          <t>TechFirst地域助成金プログラムの詳細が記載されており、デジタルスキルを向上させ、技術職への支援を行います。</t>
         </is>
       </c>
       <c r="K31" s="60" t="inlineStr">
         <is>
-          <t>https://openai.com/index/ntt-data</t>
+          <t>https://www.gov.uk/government/publications/techlocal</t>
         </is>
       </c>
       <c r="L31" s="60" t="inlineStr">
         <is>
-          <t>389ebd02d2834f48054db326</t>
+          <t>88893e13a25a6efc42ed57ea</t>
         </is>
       </c>
       <c r="M31" s="75" t="inlineStr">
@@ -3209,55 +3209,55 @@
       </c>
       <c r="B32" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T00:00:00Z</t>
+          <t>2026-07-21T15:05:29Z</t>
         </is>
       </c>
       <c r="C32" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>EU &amp; Europe</t>
         </is>
       </c>
       <c r="D32" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="E32" s="60" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Innovation Policy</t>
         </is>
       </c>
       <c r="F32" s="76" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G32" s="60" t="inlineStr">
         <is>
-          <t>Scientific Publication</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H32" s="60" t="inlineStr">
         <is>
-          <t>Nature</t>
+          <t>UK DSIT</t>
         </is>
       </c>
       <c r="I32" s="60" t="inlineStr">
         <is>
-          <t>サブニュクレアゲノム区画化が二価クロマチン活性を制御</t>
+          <t>TechFirst PhDサポート</t>
         </is>
       </c>
       <c r="J32" s="60" t="inlineStr">
         <is>
-          <t>遺伝子の空間的な位置を理解することは、そのエピゲノム調節を理解するために必要です。</t>
+          <t>TechFirstの一環として、英国の急成長する技術セクターへの道を開く政府のスキルプログラムです。</t>
         </is>
       </c>
       <c r="K32" s="60" t="inlineStr">
         <is>
-          <t>https://www.nature.com/articles/s41586-026-10832-w</t>
+          <t>https://www.gov.uk/guidance/techexpert</t>
         </is>
       </c>
       <c r="L32" s="60" t="inlineStr">
         <is>
-          <t>f9bccca3cabb5ce19441f09d</t>
+          <t>406416679082f87595cbd50b</t>
         </is>
       </c>
       <c r="M32" s="75" t="inlineStr">
@@ -3280,55 +3280,55 @@
       </c>
       <c r="B33" s="75" t="inlineStr">
         <is>
-          <t>2026-07-21T22:35:45Z</t>
+          <t>2026-07-21T15:05:21Z</t>
         </is>
       </c>
       <c r="C33" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>EU &amp; Europe</t>
         </is>
       </c>
       <c r="D33" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="E33" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence | Semiconductors &amp; Telecom</t>
+          <t>Innovation Policy</t>
         </is>
       </c>
       <c r="F33" s="76" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G33" s="60" t="inlineStr">
         <is>
-          <t>Official Company</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H33" s="60" t="inlineStr">
         <is>
-          <t>NVIDIA Blog</t>
+          <t>UK DSIT</t>
         </is>
       </c>
       <c r="I33" s="60" t="inlineStr">
         <is>
-          <t>フォートワースにおけるウィストロンの先進製造工場開設</t>
+          <t>TechFirst：英国の技術スキルプログラム</t>
         </is>
       </c>
       <c r="J33" s="60" t="inlineStr">
         <is>
-          <t>ウィストロンがテキサス州フォートワースにAIシステム用の先進製造工場を開設しました。この工場では、世界のAIシステムの中心となるスーパーチップが生産されます。</t>
+          <t>TechFirstは、英国の急成長する技術セクターへの道を開く政府の主要な技術スキルプログラムであり、全国各地で機会を提供します。</t>
         </is>
       </c>
       <c r="K33" s="60" t="inlineStr">
         <is>
-          <t>https://blogs.nvidia.com/blog/wistron-manufacturing-texas/</t>
+          <t>https://www.gov.uk/guidance/techfirst</t>
         </is>
       </c>
       <c r="L33" s="60" t="inlineStr">
         <is>
-          <t>21f1e1f3e19b1a5bf0af3cb7</t>
+          <t>4ae9e496e9b66c66de074041</t>
         </is>
       </c>
       <c r="M33" s="75" t="inlineStr">
@@ -3351,55 +3351,55 @@
       </c>
       <c r="B34" s="75" t="inlineStr">
         <is>
-          <t>2026-07-21T19:44:19Z</t>
+          <t>2026-07-21T15:05:11Z</t>
         </is>
       </c>
       <c r="C34" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>EU &amp; Europe</t>
         </is>
       </c>
       <c r="D34" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="E34" s="60" t="inlineStr">
         <is>
-          <t>Innovation Policy | Fusion Energy</t>
+          <t>Innovation Policy | Semiconductors &amp; Telecom</t>
         </is>
       </c>
       <c r="F34" s="76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G34" s="60" t="inlineStr">
         <is>
-          <t>Industry Association</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H34" s="60" t="inlineStr">
         <is>
-          <t>Fusion Industry Association</t>
+          <t>UK DSIT</t>
         </is>
       </c>
       <c r="I34" s="60" t="inlineStr">
         <is>
-          <t>FIAとクリーンエアタスクフォースが核融合の原則を発表</t>
+          <t>固定通信近代化のための政策文書</t>
         </is>
       </c>
       <c r="J34" s="60" t="inlineStr">
         <is>
-          <t>核融合産業協会は、クリーンエアタスクフォースと協力して、核融合のコードと基準に関する原則を発表しました。</t>
+          <t>この文書は、通信事業者が現在および将来の固定通信の近代化を行う際に従うべきステップを示しています。</t>
         </is>
       </c>
       <c r="K34" s="60" t="inlineStr">
         <is>
-          <t>https://www.fusionindustryassociation.org/fia-and-clean-air-task-force-publish-principles-on-codes-and-standards/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=fia-and-clean-air-task-force-publish-principles-on-codes-and-standards</t>
+          <t>https://www.gov.uk/government/publications/fixed-telecoms-modernisation-charter</t>
         </is>
       </c>
       <c r="L34" s="60" t="inlineStr">
         <is>
-          <t>2366dc909672b56b77a196bd</t>
+          <t>d5e4431b57fcb4b6271f6c72</t>
         </is>
       </c>
       <c r="M34" s="75" t="inlineStr">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="B35" s="75" t="inlineStr">
         <is>
-          <t>2026-07-21T15:06:49Z</t>
+          <t>2026-07-21T14:48:28Z</t>
         </is>
       </c>
       <c r="C35" s="60" t="inlineStr">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="D35" s="60" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="E35" s="60" t="inlineStr">
         <is>
-          <t>Innovation Policy</t>
+          <t>Fusion Energy</t>
         </is>
       </c>
       <c r="F35" s="76" t="n">
@@ -3445,32 +3445,32 @@
       </c>
       <c r="G35" s="60" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Industry Association</t>
         </is>
       </c>
       <c r="H35" s="60" t="inlineStr">
         <is>
-          <t>UK DSIT</t>
+          <t>Fusion Industry Association</t>
         </is>
       </c>
       <c r="I35" s="60" t="inlineStr">
         <is>
-          <t>DSITの人材管理情報（2026年6月）</t>
+          <t>EUの核融合資金調達計画を示すFIA</t>
         </is>
       </c>
       <c r="J35" s="60" t="inlineStr">
         <is>
-          <t>部門のスタッフ数とコストに関する報告が行われています。</t>
+          <t>核融合産業協会は、商業核融合エネルギーのためのEU資金調達の実用的なロードマップを発表しました。研究から実証、商業展開に至る各段階で必要な資金調達手段の進化が求められています。</t>
         </is>
       </c>
       <c r="K35" s="60" t="inlineStr">
         <is>
-          <t>https://www.gov.uk/government/publications/dsit-workforce-management-information-june-2026</t>
+          <t>https://www.fusionindustryassociation.org/fia-outlines-eu-financing-pathway-for-fusion/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=fia-outlines-eu-financing-pathway-for-fusion</t>
         </is>
       </c>
       <c r="L35" s="60" t="inlineStr">
         <is>
-          <t>68c02c5c6a2ee3c9c91fc7f1</t>
+          <t>88af233d904d670250fa5a31</t>
         </is>
       </c>
       <c r="M35" s="75" t="inlineStr">
@@ -3493,55 +3493,55 @@
       </c>
       <c r="B36" s="75" t="inlineStr">
         <is>
-          <t>2026-07-21T15:06:31Z</t>
+          <t>2026-07-18T07:27:54Z</t>
         </is>
       </c>
       <c r="C36" s="60" t="inlineStr">
         <is>
-          <t>EU &amp; Europe</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D36" s="60" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="E36" s="60" t="inlineStr">
         <is>
-          <t>Innovation Policy</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="F36" s="76" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G36" s="60" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Intergovernmental</t>
         </is>
       </c>
       <c r="H36" s="60" t="inlineStr">
         <is>
-          <t>UK DSIT</t>
+          <t>WHO News</t>
         </is>
       </c>
       <c r="I36" s="60" t="inlineStr">
         <is>
-          <t>TechFirst地域支援プログラムの詳細</t>
+          <t>WHO加盟国が病原体アクセスと利益配分に関する交渉を継続</t>
         </is>
       </c>
       <c r="J36" s="60" t="inlineStr">
         <is>
-          <t>TechFirstの地域助成金プログラムの詳細が示されており、デジタルスキルを向上させ、テクノロジー職への支援を行います。</t>
+          <t>WHO加盟国は、パンデミック協定の中心要素である病原体アクセスと利益配分に関する交渉を進め、将来のパンデミックに対する迅速かつ効果的な対応を支える枠組みの最終化に向けた議論を行っています。</t>
         </is>
       </c>
       <c r="K36" s="60" t="inlineStr">
         <is>
-          <t>https://www.gov.uk/government/publications/techlocal</t>
+          <t>https://www.who.int/news/item/20-07-2026-who-member-states-continue-negotiations-on-the-pathogen-access-and-benefit-sharing-annex</t>
         </is>
       </c>
       <c r="L36" s="60" t="inlineStr">
         <is>
-          <t>88893e13a25a6efc42ed57ea</t>
+          <t>14dd15caca066d18dfcf2e34</t>
         </is>
       </c>
       <c r="M36" s="75" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="B37" s="75" t="inlineStr">
         <is>
-          <t>2026-07-21T15:05:29Z</t>
+          <t>2026-07-17T18:42:47Z</t>
         </is>
       </c>
       <c r="C37" s="60" t="inlineStr">
@@ -3574,45 +3574,45 @@
       </c>
       <c r="D37" s="60" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="E37" s="60" t="inlineStr">
         <is>
-          <t>Innovation Policy</t>
+          <t>Innovation Policy | Fusion Energy</t>
         </is>
       </c>
       <c r="F37" s="76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G37" s="60" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Industry Association</t>
         </is>
       </c>
       <c r="H37" s="60" t="inlineStr">
         <is>
-          <t>UK DSIT</t>
+          <t>Fusion Industry Association</t>
         </is>
       </c>
       <c r="I37" s="60" t="inlineStr">
         <is>
-          <t>TechFirstのPhD支援</t>
+          <t>EUの核融合競争力を確保する必要性に関する論文発表</t>
         </is>
       </c>
       <c r="J37" s="60" t="inlineStr">
         <is>
-          <t>TechFirstの一部として、UKの急成長するテクノロジーセクターへの道を開く政府のスキルプログラムです。</t>
+          <t>国際法専門家グループが発表した論文は、ヨーロッパが商業核融合において競争優位を持っているが、それを維持するために今行動する必要があると主張しています。</t>
         </is>
       </c>
       <c r="K37" s="60" t="inlineStr">
         <is>
-          <t>https://www.gov.uk/guidance/techexpert</t>
+          <t>https://www.fusionindustryassociation.org/international-legal-expert-group-publish-paper-on-the-need-for-the-eu-to-secure-its-competitive-fusion-advantage/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=international-legal-expert-group-publish-paper-on-the-need-for-the-eu-to-secure-its-competitive-fusion-advantage</t>
         </is>
       </c>
       <c r="L37" s="60" t="inlineStr">
         <is>
-          <t>406416679082f87595cbd50b</t>
+          <t>7ef6110ab078602757409abf</t>
         </is>
       </c>
       <c r="M37" s="75" t="inlineStr">
@@ -3635,22 +3635,22 @@
       </c>
       <c r="B38" s="75" t="inlineStr">
         <is>
-          <t>2026-07-21T15:05:21Z</t>
+          <t>2026-07-15T17:47:57Z</t>
         </is>
       </c>
       <c r="C38" s="60" t="inlineStr">
         <is>
-          <t>EU &amp; Europe</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="D38" s="60" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="E38" s="60" t="inlineStr">
         <is>
-          <t>Innovation Policy</t>
+          <t>Fusion Energy</t>
         </is>
       </c>
       <c r="F38" s="76" t="n">
@@ -3658,32 +3658,32 @@
       </c>
       <c r="G38" s="60" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Industry Association</t>
         </is>
       </c>
       <c r="H38" s="60" t="inlineStr">
         <is>
-          <t>UK DSIT</t>
+          <t>Fusion Industry Association</t>
         </is>
       </c>
       <c r="I38" s="60" t="inlineStr">
         <is>
-          <t>UKのテクノロジー分野を支援するTechFirst</t>
+          <t>スターロライトエンジンが60.6億円を調達</t>
         </is>
       </c>
       <c r="J38" s="60" t="inlineStr">
         <is>
-          <t>TechFirstは、UKの急成長するテクノロジーセクターへの道を開く政府の主力スキルプログラムです。</t>
+          <t>スターロライトエンジンは、FASTの開発を加速するために60.6億円の資金を調達しました。同社は、JT-60SAプログラムや国際的な取り組みを基にしたトカマク型核融合装置を開発しています。</t>
         </is>
       </c>
       <c r="K38" s="60" t="inlineStr">
         <is>
-          <t>https://www.gov.uk/guidance/techfirst</t>
+          <t>https://www.nikkei.com/article/DGXZQOUC152ET0V10C26A7000000/#new_tab?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=starlight-engine-raises-jpy-6-06-billion</t>
         </is>
       </c>
       <c r="L38" s="60" t="inlineStr">
         <is>
-          <t>4ae9e496e9b66c66de074041</t>
+          <t>2f29b005896c3737ab846738</t>
         </is>
       </c>
       <c r="M38" s="75" t="inlineStr">
@@ -3706,26 +3706,26 @@
       </c>
       <c r="B39" s="75" t="inlineStr">
         <is>
-          <t>2026-07-21T15:05:11Z</t>
+          <t>2026-07-14T12:00:00Z</t>
         </is>
       </c>
       <c r="C39" s="60" t="inlineStr">
         <is>
-          <t>EU &amp; Europe</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D39" s="60" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E39" s="60" t="inlineStr">
         <is>
-          <t>Innovation Policy | Semiconductors &amp; Telecom</t>
+          <t>Innovation Policy</t>
         </is>
       </c>
       <c r="F39" s="76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G39" s="60" t="inlineStr">
         <is>
@@ -3734,27 +3734,27 @@
       </c>
       <c r="H39" s="60" t="inlineStr">
         <is>
-          <t>UK DSIT</t>
+          <t>NIST News</t>
         </is>
       </c>
       <c r="I39" s="60" t="inlineStr">
         <is>
-          <t>固定通信近代化のための政策文書</t>
+          <t>NIST、微生物を殺す給湯器の新特許を取得</t>
         </is>
       </c>
       <c r="J39" s="60" t="inlineStr">
         <is>
-          <t>この文書は、通信事業者が現在および将来の固定通信の近代化を行う際に従うべきステップを示しています。</t>
+          <t>家庭の配管内の温水が有害な細菌の繁殖地となる可能性があることから、NISTが新たな特許を取得した。</t>
         </is>
       </c>
       <c r="K39" s="60" t="inlineStr">
         <is>
-          <t>https://www.gov.uk/government/publications/fixed-telecoms-modernisation-charter</t>
+          <t>https://www.nist.gov/news-events/news/2026/07/nist-receives-new-patent-microbe-killing-water-heater</t>
         </is>
       </c>
       <c r="L39" s="60" t="inlineStr">
         <is>
-          <t>d5e4431b57fcb4b6271f6c72</t>
+          <t>72b002f5a04f35d9ca1e9949</t>
         </is>
       </c>
       <c r="M39" s="75" t="inlineStr">
@@ -3777,22 +3777,22 @@
       </c>
       <c r="B40" s="75" t="inlineStr">
         <is>
-          <t>2026-07-21T14:48:28Z</t>
+          <t>2026-07-13T21:00:00Z</t>
         </is>
       </c>
       <c r="C40" s="60" t="inlineStr">
         <is>
-          <t>EU &amp; Europe</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D40" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E40" s="60" t="inlineStr">
         <is>
-          <t>Fusion Energy</t>
+          <t>Innovation Policy | Artificial Intelligence</t>
         </is>
       </c>
       <c r="F40" s="76" t="n">
@@ -3800,32 +3800,32 @@
       </c>
       <c r="G40" s="60" t="inlineStr">
         <is>
-          <t>Industry Association</t>
+          <t>Policy Institute</t>
         </is>
       </c>
       <c r="H40" s="60" t="inlineStr">
         <is>
-          <t>Fusion Industry Association</t>
+          <t>CSET</t>
         </is>
       </c>
       <c r="I40" s="60" t="inlineStr">
         <is>
-          <t>EUの核融合資金調達計画を示すFIA</t>
+          <t>米国、中国がAIを米国モデルで訓練するのを阻止しようとする</t>
         </is>
       </c>
       <c r="J40" s="60" t="inlineStr">
         <is>
-          <t>核融合産業協会は、商業核融合エネルギーのためのEU資金調達の実用的なロードマップを発表しました。研究から実証、商業展開に至る各段階で必要な資金調達手段の進化が求められています。</t>
+          <t>米国では、中国のAI企業が米国のシステムからの出力を使用してモデルを訓練することに対する懸念が高まっており、知的財産や競争、国家安全保障に関する議論が進んでいる。</t>
         </is>
       </c>
       <c r="K40" s="60" t="inlineStr">
         <is>
-          <t>https://www.fusionindustryassociation.org/fia-outlines-eu-financing-pathway-for-fusion/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=fia-outlines-eu-financing-pathway-for-fusion</t>
+          <t>https://cset.georgetown.edu/article/washington-is-looking-to-keep-china-from-training-its-ai-on-us-models/</t>
         </is>
       </c>
       <c r="L40" s="60" t="inlineStr">
         <is>
-          <t>88af233d904d670250fa5a31</t>
+          <t>e96177000536ef3f58f8fb3c</t>
         </is>
       </c>
       <c r="M40" s="75" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="B41" s="75" t="inlineStr">
         <is>
-          <t>2026-07-21T13:30:36Z</t>
+          <t>2026-07-13T12:00:41Z</t>
         </is>
       </c>
       <c r="C41" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D41" s="60" t="inlineStr">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="E41" s="60" t="inlineStr">
         <is>
-          <t>Innovation Policy | Artificial Intelligence</t>
+          <t>Semiconductors &amp; Telecom | Artificial Intelligence</t>
         </is>
       </c>
       <c r="F41" s="76" t="n">
@@ -3871,32 +3871,32 @@
       </c>
       <c r="G41" s="60" t="inlineStr">
         <is>
-          <t>Policy Institute</t>
+          <t>Official Company</t>
         </is>
       </c>
       <c r="H41" s="60" t="inlineStr">
         <is>
-          <t>CSET</t>
+          <t>Intel Newsroom</t>
         </is>
       </c>
       <c r="I41" s="60" t="inlineStr">
         <is>
-          <t>AIシステムはなぜ誤動作するのか？</t>
+          <t>インテル、ヨーロッパでの製造拡大に50億ユーロを投資</t>
         </is>
       </c>
       <c r="J41" s="60" t="inlineStr">
         <is>
-          <t>AIシステムの誤動作の原因を探るブログ記事で、政策的な視点からの考察が行われている。</t>
+          <t>インテルはアイルランドのLeixlipキャンパスに50億ユーロを投資し、AIと高性能コンピューティング向けの先進的なシリコンの需要に応えるための製造能力を拡大する。</t>
         </is>
       </c>
       <c r="K41" s="60" t="inlineStr">
         <is>
-          <t>https://cset.georgetown.edu/article/why-do-ai-systems-misbehave/</t>
+          <t>https://newsroom.intel.com/intel-foundry/intel-invests-5-billion-euro-to-expand-manufacturing-in-europe</t>
         </is>
       </c>
       <c r="L41" s="60" t="inlineStr">
         <is>
-          <t>3e1aa390ad965782cc86c386</t>
+          <t>297a8b5b279e5916cf45fddb</t>
         </is>
       </c>
       <c r="M41" s="75" t="inlineStr">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="B42" s="75" t="inlineStr">
         <is>
-          <t>2026-07-21T12:10:00Z</t>
+          <t>2026-07-12T21:00:00Z</t>
         </is>
       </c>
       <c r="C42" s="60" t="inlineStr">
@@ -3934,40 +3934,40 @@
       </c>
       <c r="E42" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Artificial Intelligence | Innovation Policy</t>
         </is>
       </c>
       <c r="F42" s="76" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G42" s="60" t="inlineStr">
         <is>
-          <t>Major Media</t>
+          <t>Policy Institute</t>
         </is>
       </c>
       <c r="H42" s="60" t="inlineStr">
         <is>
-          <t>MIT Technology Review</t>
+          <t>CSET</t>
         </is>
       </c>
       <c r="I42" s="60" t="inlineStr">
         <is>
-          <t>ダウンロード：中国のAIがホワイトハウスを分断し、記録的な著作権支払い</t>
+          <t>企業がコスト削減のために中国のAIモデルに注目</t>
         </is>
       </c>
       <c r="J42" s="60" t="inlineStr">
         <is>
-          <t>中国のAIモデルに関する議論が、トランプ政権のAI政策に影響を与えていることを報告。</t>
+          <t>企業がコスト削減を目的に中国のAIモデルを採用する動きが広がっており、低コストや改善された能力、オープンウェイトシステムの柔軟性がその要因とされている。</t>
         </is>
       </c>
       <c r="K42" s="60" t="inlineStr">
         <is>
-          <t>https://www.technologyreview.com/2026/07/21/1140685/the-download-chinese-ai-divides-white-house-anthropic-copyright-settlement/</t>
+          <t>https://cset.georgetown.edu/article/companies-turn-to-chinese-ai-models-to-cut-costs/</t>
         </is>
       </c>
       <c r="L42" s="60" t="inlineStr">
         <is>
-          <t>f9addf0904b9de5b7bcc326b</t>
+          <t>9e1bc06c29b61bed048d4f44</t>
         </is>
       </c>
       <c r="M42" s="75" t="inlineStr">
@@ -3982,1002 +3982,8 @@
       </c>
       <c r="O42" s="60" t="inlineStr"/>
     </row>
-    <row r="43" ht="42" customHeight="1">
-      <c r="A43" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="B43" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-21T07:00:00Z</t>
-        </is>
-      </c>
-      <c r="C43" s="60" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="D43" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E43" s="60" t="inlineStr">
-        <is>
-          <t>Artificial Intelligence</t>
-        </is>
-      </c>
-      <c r="F43" s="76" t="n">
-        <v>1</v>
-      </c>
-      <c r="G43" s="60" t="inlineStr">
-        <is>
-          <t>Official Company</t>
-        </is>
-      </c>
-      <c r="H43" s="60" t="inlineStr">
-        <is>
-          <t>OpenAI News</t>
-        </is>
-      </c>
-      <c r="I43" s="60" t="inlineStr">
-        <is>
-          <t>OpenAIとHugging Faceがモデル評価中のセキュリティインシデントに対処するために提携</t>
-        </is>
-      </c>
-      <c r="J43" s="60" t="inlineStr">
-        <is>
-          <t>OpenAIとHugging Faceは、AIモデル評価中のセキュリティインシデントに関する初期の調査結果を共有し、サイバー防御者への教訓を強調した。</t>
-        </is>
-      </c>
-      <c r="K43" s="60" t="inlineStr">
-        <is>
-          <t>https://openai.com/index/hugging-face-model-evaluation-security-incident</t>
-        </is>
-      </c>
-      <c r="L43" s="60" t="inlineStr">
-        <is>
-          <t>d925d8c91f460a44f07089c2</t>
-        </is>
-      </c>
-      <c r="M43" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="N43" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O43" s="60" t="inlineStr"/>
-    </row>
-    <row r="44" ht="42" customHeight="1">
-      <c r="A44" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="B44" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-20T15:55:00Z</t>
-        </is>
-      </c>
-      <c r="C44" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="D44" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E44" s="60" t="inlineStr">
-        <is>
-          <t>Semiconductors &amp; Telecom</t>
-        </is>
-      </c>
-      <c r="F44" s="76" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" s="60" t="inlineStr">
-        <is>
-          <t>Major Media</t>
-        </is>
-      </c>
-      <c r="H44" s="60" t="inlineStr">
-        <is>
-          <t>IEEE Spectrum</t>
-        </is>
-      </c>
-      <c r="I44" s="60" t="inlineStr">
-        <is>
-          <t>先端半導体故障分析のためのSEMガイド低電圧FIB仕上げ</t>
-        </is>
-      </c>
-      <c r="J44" s="60" t="inlineStr">
-        <is>
-          <t>ZEISS Crossbeam 750 FIBSEMが、精密TEMラメラ準備や高度なナノファブリケーションの新基準を設定し、故障分析を加速する方法を紹介。</t>
-        </is>
-      </c>
-      <c r="K44" s="60" t="inlineStr">
-        <is>
-          <t>https://event.on24.com/wcc/r/5418459/287E3D5B99470D34C830D69A24B3B207</t>
-        </is>
-      </c>
-      <c r="L44" s="60" t="inlineStr">
-        <is>
-          <t>73d0028e337a76c2cd00f1bc</t>
-        </is>
-      </c>
-      <c r="M44" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="N44" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O44" s="60" t="inlineStr"/>
-    </row>
-    <row r="45" ht="42" customHeight="1">
-      <c r="A45" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="B45" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-18T07:27:54Z</t>
-        </is>
-      </c>
-      <c r="C45" s="60" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="D45" s="60" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="E45" s="60" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-      <c r="F45" s="76" t="n">
-        <v>4</v>
-      </c>
-      <c r="G45" s="60" t="inlineStr">
-        <is>
-          <t>Intergovernmental</t>
-        </is>
-      </c>
-      <c r="H45" s="60" t="inlineStr">
-        <is>
-          <t>WHO News</t>
-        </is>
-      </c>
-      <c r="I45" s="60" t="inlineStr">
-        <is>
-          <t>WHO加盟国が病原体アクセスと利益配分に関する交渉を継続</t>
-        </is>
-      </c>
-      <c r="J45" s="60" t="inlineStr">
-        <is>
-          <t>WHO加盟国は、パンデミック協定の中心要素である病原体アクセスと利益配分に関する交渉を進め、将来のパンデミックに対する迅速かつ効果的な対応を支える枠組みの最終化に向けた議論を行っています。</t>
-        </is>
-      </c>
-      <c r="K45" s="60" t="inlineStr">
-        <is>
-          <t>https://www.who.int/news/item/20-07-2026-who-member-states-continue-negotiations-on-the-pathogen-access-and-benefit-sharing-annex</t>
-        </is>
-      </c>
-      <c r="L45" s="60" t="inlineStr">
-        <is>
-          <t>14dd15caca066d18dfcf2e34</t>
-        </is>
-      </c>
-      <c r="M45" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="N45" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O45" s="60" t="inlineStr"/>
-    </row>
-    <row r="46" ht="42" customHeight="1">
-      <c r="A46" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="B46" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-17T20:26:18Z</t>
-        </is>
-      </c>
-      <c r="C46" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="D46" s="60" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="E46" s="60" t="inlineStr">
-        <is>
-          <t>Fusion Energy</t>
-        </is>
-      </c>
-      <c r="F46" s="76" t="n">
-        <v>3</v>
-      </c>
-      <c r="G46" s="60" t="inlineStr">
-        <is>
-          <t>Industry Association</t>
-        </is>
-      </c>
-      <c r="H46" s="60" t="inlineStr">
-        <is>
-          <t>Fusion Industry Association</t>
-        </is>
-      </c>
-      <c r="I46" s="60" t="inlineStr">
-        <is>
-          <t>2026年グローバル核融合産業報告書の発表</t>
-        </is>
-      </c>
-      <c r="J46" s="60" t="inlineStr">
-        <is>
-          <t>核融合産業協会は、2026年グローバル核融合産業報告書を発表し、米国の政策に関連する議論を行いました。</t>
-        </is>
-      </c>
-      <c r="K46" s="60" t="inlineStr">
-        <is>
-          <t>https://www.fusionindustryassociation.org/fia-launches-the-2026-global-fusion-industry-report-in-new-york-city-washington-d-c-and-london/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=fia-launches-the-2026-global-fusion-industry-report-in-new-york-city-washington-d-c-and-london</t>
-        </is>
-      </c>
-      <c r="L46" s="60" t="inlineStr">
-        <is>
-          <t>186c1d4e76c09a864706432c</t>
-        </is>
-      </c>
-      <c r="M46" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="N46" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O46" s="60" t="inlineStr"/>
-    </row>
-    <row r="47" ht="42" customHeight="1">
-      <c r="A47" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="B47" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-17T18:42:47Z</t>
-        </is>
-      </c>
-      <c r="C47" s="60" t="inlineStr">
-        <is>
-          <t>EU &amp; Europe</t>
-        </is>
-      </c>
-      <c r="D47" s="60" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="E47" s="60" t="inlineStr">
-        <is>
-          <t>Innovation Policy | Fusion Energy</t>
-        </is>
-      </c>
-      <c r="F47" s="76" t="n">
-        <v>4</v>
-      </c>
-      <c r="G47" s="60" t="inlineStr">
-        <is>
-          <t>Industry Association</t>
-        </is>
-      </c>
-      <c r="H47" s="60" t="inlineStr">
-        <is>
-          <t>Fusion Industry Association</t>
-        </is>
-      </c>
-      <c r="I47" s="60" t="inlineStr">
-        <is>
-          <t>EUの核融合競争力を確保する必要性に関する論文発表</t>
-        </is>
-      </c>
-      <c r="J47" s="60" t="inlineStr">
-        <is>
-          <t>国際法専門家グループが発表した論文は、ヨーロッパが商業核融合において競争優位を持っているが、それを維持するために今行動する必要があると主張しています。</t>
-        </is>
-      </c>
-      <c r="K47" s="60" t="inlineStr">
-        <is>
-          <t>https://www.fusionindustryassociation.org/international-legal-expert-group-publish-paper-on-the-need-for-the-eu-to-secure-its-competitive-fusion-advantage/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=international-legal-expert-group-publish-paper-on-the-need-for-the-eu-to-secure-its-competitive-fusion-advantage</t>
-        </is>
-      </c>
-      <c r="L47" s="60" t="inlineStr">
-        <is>
-          <t>7ef6110ab078602757409abf</t>
-        </is>
-      </c>
-      <c r="M47" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="N47" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O47" s="60" t="inlineStr"/>
-    </row>
-    <row r="48" ht="42" customHeight="1">
-      <c r="A48" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="B48" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-15T21:00:00Z</t>
-        </is>
-      </c>
-      <c r="C48" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="D48" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E48" s="60" t="inlineStr">
-        <is>
-          <t>Artificial Intelligence | Innovation Policy</t>
-        </is>
-      </c>
-      <c r="F48" s="76" t="n">
-        <v>3</v>
-      </c>
-      <c r="G48" s="60" t="inlineStr">
-        <is>
-          <t>Policy Institute</t>
-        </is>
-      </c>
-      <c r="H48" s="60" t="inlineStr">
-        <is>
-          <t>CSET</t>
-        </is>
-      </c>
-      <c r="I48" s="60" t="inlineStr">
-        <is>
-          <t>GPT-Red：OpenAIが構築したAIスーパーハッカー</t>
-        </is>
-      </c>
-      <c r="J48" s="60" t="inlineStr">
-        <is>
-          <t>OpenAIが開発したGPT-Redは、大規模言語モデルの脆弱性を自動的に特定し、サイバー攻撃に対する防御を強化するためのAIスーパーハッカーです。</t>
-        </is>
-      </c>
-      <c r="K48" s="60" t="inlineStr">
-        <is>
-          <t>https://cset.georgetown.edu/article/meet-gpt-red-an-llm-super-hacker-openai-built-to-make-its-models-safer/</t>
-        </is>
-      </c>
-      <c r="L48" s="60" t="inlineStr">
-        <is>
-          <t>f64391d3daf689e78e7ac442</t>
-        </is>
-      </c>
-      <c r="M48" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="N48" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O48" s="60" t="inlineStr"/>
-    </row>
-    <row r="49" ht="42" customHeight="1">
-      <c r="A49" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="B49" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-15T17:47:57Z</t>
-        </is>
-      </c>
-      <c r="C49" s="60" t="inlineStr">
-        <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="D49" s="60" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="E49" s="60" t="inlineStr">
-        <is>
-          <t>Fusion Energy</t>
-        </is>
-      </c>
-      <c r="F49" s="76" t="n">
-        <v>3</v>
-      </c>
-      <c r="G49" s="60" t="inlineStr">
-        <is>
-          <t>Industry Association</t>
-        </is>
-      </c>
-      <c r="H49" s="60" t="inlineStr">
-        <is>
-          <t>Fusion Industry Association</t>
-        </is>
-      </c>
-      <c r="I49" s="60" t="inlineStr">
-        <is>
-          <t>スターロライトエンジンが60.6億円を調達</t>
-        </is>
-      </c>
-      <c r="J49" s="60" t="inlineStr">
-        <is>
-          <t>スターロライトエンジンは、FASTの開発を加速するために60.6億円の資金を調達しました。同社は、JT-60SAプログラムや国際的な取り組みを基にしたトカマク型核融合装置を開発しています。</t>
-        </is>
-      </c>
-      <c r="K49" s="60" t="inlineStr">
-        <is>
-          <t>https://www.nikkei.com/article/DGXZQOUC152ET0V10C26A7000000/#new_tab?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=starlight-engine-raises-jpy-6-06-billion</t>
-        </is>
-      </c>
-      <c r="L49" s="60" t="inlineStr">
-        <is>
-          <t>2f29b005896c3737ab846738</t>
-        </is>
-      </c>
-      <c r="M49" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="N49" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O49" s="60" t="inlineStr"/>
-    </row>
-    <row r="50" ht="42" customHeight="1">
-      <c r="A50" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="B50" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-15T17:43:32Z</t>
-        </is>
-      </c>
-      <c r="C50" s="60" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="D50" s="60" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="E50" s="60" t="inlineStr">
-        <is>
-          <t>Fusion Energy</t>
-        </is>
-      </c>
-      <c r="F50" s="76" t="n">
-        <v>0</v>
-      </c>
-      <c r="G50" s="60" t="inlineStr">
-        <is>
-          <t>Industry Association</t>
-        </is>
-      </c>
-      <c r="H50" s="60" t="inlineStr">
-        <is>
-          <t>Fusion Industry Association</t>
-        </is>
-      </c>
-      <c r="I50" s="60" t="inlineStr">
-        <is>
-          <t>マディソンの元オスカー・マイヤー工場に核融合研究センターが設立</t>
-        </is>
-      </c>
-      <c r="J50" s="60" t="inlineStr">
-        <is>
-          <t>Realta Fusionがマディソンに新しい本社と施設を設立し、核融合技術のプロトタイプを建設する計画を発表した。</t>
-        </is>
-      </c>
-      <c r="K50" s="60" t="inlineStr">
-        <is>
-          <t>https://www.jsonline.com/story/money/business/energy/2026/07/15/nuclear-fusion-facility-coming-to-madisons-oscar-mayer-factory-site/90900554007/?gnt-cfr=1&amp;gca-cat=p&amp;gca-uir=true&amp;gca-epti=z116463p117850l004150c117850e1157xxv116463d--54--b--54--&amp;gca-ft=178&amp;gca-ds=sophi#new_tab&amp;utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=fusion-research-center-coming-to-madisons-former-oscar-mayer-plant</t>
-        </is>
-      </c>
-      <c r="L50" s="60" t="inlineStr">
-        <is>
-          <t>aed2fa8a807fb17c3e6861e7</t>
-        </is>
-      </c>
-      <c r="M50" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="N50" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O50" s="60" t="inlineStr"/>
-    </row>
-    <row r="51" ht="42" customHeight="1">
-      <c r="A51" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="B51" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-15T00:01:54Z</t>
-        </is>
-      </c>
-      <c r="C51" s="60" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="D51" s="60" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="E51" s="60" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-      <c r="F51" s="76" t="n">
-        <v>1</v>
-      </c>
-      <c r="G51" s="60" t="inlineStr">
-        <is>
-          <t>Intergovernmental</t>
-        </is>
-      </c>
-      <c r="H51" s="60" t="inlineStr">
-        <is>
-          <t>WHO News</t>
-        </is>
-      </c>
-      <c r="I51" s="60" t="inlineStr">
-        <is>
-          <t>世界の子供の予防接種率が向上、紛争やためらいにもかかわらず</t>
-        </is>
-      </c>
-      <c r="J51" s="60" t="inlineStr">
-        <is>
-          <t>2025年には、世界で90%の乳児がジフテリア、破傷風、百日咳（DTP）ワクチンの少なくとも1回の接種を受け、85%が3回の接種を完了したとWHOとUNICEFの報告が示しています。しかし、依然として2019年の水準を下回っています。</t>
-        </is>
-      </c>
-      <c r="K51" s="60" t="inlineStr">
-        <is>
-          <t>https://www.who.int/news/item/15-07-2026-global-childhood-immunization-coverage-inches-forward-despite-conflict-and-hesitancy---unicef--who</t>
-        </is>
-      </c>
-      <c r="L51" s="60" t="inlineStr">
-        <is>
-          <t>03ea8728394fda1e18a57d66</t>
-        </is>
-      </c>
-      <c r="M51" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="N51" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O51" s="60" t="inlineStr"/>
-    </row>
-    <row r="52" ht="42" customHeight="1">
-      <c r="A52" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="B52" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-14T12:00:00Z</t>
-        </is>
-      </c>
-      <c r="C52" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="D52" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E52" s="60" t="inlineStr">
-        <is>
-          <t>Innovation Policy</t>
-        </is>
-      </c>
-      <c r="F52" s="76" t="n">
-        <v>4</v>
-      </c>
-      <c r="G52" s="60" t="inlineStr">
-        <is>
-          <t>Government</t>
-        </is>
-      </c>
-      <c r="H52" s="60" t="inlineStr">
-        <is>
-          <t>NIST News</t>
-        </is>
-      </c>
-      <c r="I52" s="60" t="inlineStr">
-        <is>
-          <t>NIST、微生物を殺す給湯器の新特許を取得</t>
-        </is>
-      </c>
-      <c r="J52" s="60" t="inlineStr">
-        <is>
-          <t>家庭の配管内の温水が有害な細菌の繁殖地となる可能性があることから、NISTが新たな特許を取得した。</t>
-        </is>
-      </c>
-      <c r="K52" s="60" t="inlineStr">
-        <is>
-          <t>https://www.nist.gov/news-events/news/2026/07/nist-receives-new-patent-microbe-killing-water-heater</t>
-        </is>
-      </c>
-      <c r="L52" s="60" t="inlineStr">
-        <is>
-          <t>72b002f5a04f35d9ca1e9949</t>
-        </is>
-      </c>
-      <c r="M52" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="N52" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O52" s="60" t="inlineStr"/>
-    </row>
-    <row r="53" ht="42" customHeight="1">
-      <c r="A53" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="B53" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-13T21:00:00Z</t>
-        </is>
-      </c>
-      <c r="C53" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="D53" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E53" s="60" t="inlineStr">
-        <is>
-          <t>Innovation Policy | Artificial Intelligence</t>
-        </is>
-      </c>
-      <c r="F53" s="76" t="n">
-        <v>3</v>
-      </c>
-      <c r="G53" s="60" t="inlineStr">
-        <is>
-          <t>Policy Institute</t>
-        </is>
-      </c>
-      <c r="H53" s="60" t="inlineStr">
-        <is>
-          <t>CSET</t>
-        </is>
-      </c>
-      <c r="I53" s="60" t="inlineStr">
-        <is>
-          <t>米国、中国がAIを米国モデルで訓練するのを阻止しようとする</t>
-        </is>
-      </c>
-      <c r="J53" s="60" t="inlineStr">
-        <is>
-          <t>米国では、中国のAI企業が米国のシステムからの出力を使用してモデルを訓練することに対する懸念が高まっており、知的財産や競争、国家安全保障に関する議論が進んでいる。</t>
-        </is>
-      </c>
-      <c r="K53" s="60" t="inlineStr">
-        <is>
-          <t>https://cset.georgetown.edu/article/washington-is-looking-to-keep-china-from-training-its-ai-on-us-models/</t>
-        </is>
-      </c>
-      <c r="L53" s="60" t="inlineStr">
-        <is>
-          <t>e96177000536ef3f58f8fb3c</t>
-        </is>
-      </c>
-      <c r="M53" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="N53" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O53" s="60" t="inlineStr"/>
-    </row>
-    <row r="54" ht="42" customHeight="1">
-      <c r="A54" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="B54" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-13T16:00:00Z</t>
-        </is>
-      </c>
-      <c r="C54" s="60" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="D54" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E54" s="60" t="inlineStr">
-        <is>
-          <t>Innovation Policy | Quantum</t>
-        </is>
-      </c>
-      <c r="F54" s="76" t="n">
-        <v>1</v>
-      </c>
-      <c r="G54" s="60" t="inlineStr">
-        <is>
-          <t>Official Company</t>
-        </is>
-      </c>
-      <c r="H54" s="60" t="inlineStr">
-        <is>
-          <t>Microsoft Research</t>
-        </is>
-      </c>
-      <c r="I54" s="60" t="inlineStr">
-        <is>
-          <t>SymCryptにおけるRust暗号の検証</t>
-        </is>
-      </c>
-      <c r="J54" s="60" t="inlineStr">
-        <is>
-          <t>新しい手法が開発者がコードを書く際にその検証を助け、実装と進化の過程で速度と適応性を保つことを可能にする。</t>
-        </is>
-      </c>
-      <c r="K54" s="60" t="inlineStr">
-        <is>
-          <t>https://www.microsoft.com/en-us/research/blog/verifying-rust-cryptography-in-symcrypt-from-standards-to-code/</t>
-        </is>
-      </c>
-      <c r="L54" s="60" t="inlineStr">
-        <is>
-          <t>a7866758cf94a3c5e9d26534</t>
-        </is>
-      </c>
-      <c r="M54" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="N54" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O54" s="60" t="inlineStr"/>
-    </row>
-    <row r="55" ht="42" customHeight="1">
-      <c r="A55" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="B55" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-13T12:00:41Z</t>
-        </is>
-      </c>
-      <c r="C55" s="60" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="D55" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E55" s="60" t="inlineStr">
-        <is>
-          <t>Semiconductors &amp; Telecom | Artificial Intelligence</t>
-        </is>
-      </c>
-      <c r="F55" s="76" t="n">
-        <v>3</v>
-      </c>
-      <c r="G55" s="60" t="inlineStr">
-        <is>
-          <t>Official Company</t>
-        </is>
-      </c>
-      <c r="H55" s="60" t="inlineStr">
-        <is>
-          <t>Intel Newsroom</t>
-        </is>
-      </c>
-      <c r="I55" s="60" t="inlineStr">
-        <is>
-          <t>インテル、ヨーロッパでの製造拡大に50億ユーロを投資</t>
-        </is>
-      </c>
-      <c r="J55" s="60" t="inlineStr">
-        <is>
-          <t>インテルはアイルランドのLeixlipキャンパスに50億ユーロを投資し、AIと高性能コンピューティング向けの先進的なシリコンの需要に応えるための製造能力を拡大する。</t>
-        </is>
-      </c>
-      <c r="K55" s="60" t="inlineStr">
-        <is>
-          <t>https://newsroom.intel.com/intel-foundry/intel-invests-5-billion-euro-to-expand-manufacturing-in-europe</t>
-        </is>
-      </c>
-      <c r="L55" s="60" t="inlineStr">
-        <is>
-          <t>297a8b5b279e5916cf45fddb</t>
-        </is>
-      </c>
-      <c r="M55" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="N55" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O55" s="60" t="inlineStr"/>
-    </row>
-    <row r="56" ht="42" customHeight="1">
-      <c r="A56" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="B56" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-12T21:00:00Z</t>
-        </is>
-      </c>
-      <c r="C56" s="60" t="inlineStr">
-        <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="D56" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E56" s="60" t="inlineStr">
-        <is>
-          <t>Artificial Intelligence | Innovation Policy</t>
-        </is>
-      </c>
-      <c r="F56" s="76" t="n">
-        <v>3</v>
-      </c>
-      <c r="G56" s="60" t="inlineStr">
-        <is>
-          <t>Policy Institute</t>
-        </is>
-      </c>
-      <c r="H56" s="60" t="inlineStr">
-        <is>
-          <t>CSET</t>
-        </is>
-      </c>
-      <c r="I56" s="60" t="inlineStr">
-        <is>
-          <t>企業がコスト削減のために中国のAIモデルに注目</t>
-        </is>
-      </c>
-      <c r="J56" s="60" t="inlineStr">
-        <is>
-          <t>企業がコスト削減を目的に中国のAIモデルを採用する動きが広がっており、低コストや改善された能力、オープンウェイトシステムの柔軟性がその要因とされている。</t>
-        </is>
-      </c>
-      <c r="K56" s="60" t="inlineStr">
-        <is>
-          <t>https://cset.georgetown.edu/article/companies-turn-to-chinese-ai-models-to-cut-costs/</t>
-        </is>
-      </c>
-      <c r="L56" s="60" t="inlineStr">
-        <is>
-          <t>9e1bc06c29b61bed048d4f44</t>
-        </is>
-      </c>
-      <c r="M56" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="N56" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O56" s="60" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A3:O56"/>
+  <autoFilter ref="A3:O42"/>
   <mergeCells count="2">
     <mergeCell ref="A1:O1"/>
     <mergeCell ref="A2:O2"/>
@@ -4995,7 +4001,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="N4:N56" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="N4:N42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"New,Reviewed,Follow-up,Archived"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5039,24 +4045,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K40" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K41" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K42" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K43" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K44" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K45" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K46" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K47" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K48" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K49" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K50" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K51" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K52" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K53" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K54" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K55" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K56" r:id="rId53"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId54"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId40"/>
   </tableParts>
 </worksheet>
 </file>
@@ -5067,7 +4059,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K37"/>
+  <dimension ref="A1:K41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5292,31 +4284,31 @@
       </c>
       <c r="D6" s="60" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Technology and innovation</t>
         </is>
       </c>
       <c r="E6" s="60" t="inlineStr">
         <is>
-          <t>The Guardian Technology</t>
+          <t>BBC Technology</t>
         </is>
       </c>
       <c r="F6" s="60" t="inlineStr">
         <is>
-          <t>Guardian News &amp; Media</t>
+          <t>BBC</t>
         </is>
       </c>
       <c r="G6" s="60" t="inlineStr">
         <is>
-          <t>https://www.theguardian.com/technology/rss</t>
+          <t>https://feeds.bbci.co.uk/news/technology/rss.xml</t>
         </is>
       </c>
       <c r="H6" s="60" t="inlineStr">
         <is>
-          <t>https://www.theguardian.com/technology</t>
+          <t>https://www.bbc.com/news/technology</t>
         </is>
       </c>
       <c r="I6" s="76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J6" s="60" t="inlineStr">
         <is>
@@ -5325,7 +4317,7 @@
       </c>
       <c r="K6" s="60" t="inlineStr">
         <is>
-          <t>Major media; strict topic filter is applied.</t>
+          <t>Official BBC technology feed; strict innovation-scope review is applied.</t>
         </is>
       </c>
     </row>
@@ -5337,7 +4329,7 @@
       </c>
       <c r="B7" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="C7" s="60" t="inlineStr">
@@ -5347,27 +4339,27 @@
       </c>
       <c r="D7" s="60" t="inlineStr">
         <is>
-          <t>Emerging technology</t>
+          <t>Technology and innovation</t>
         </is>
       </c>
       <c r="E7" s="60" t="inlineStr">
         <is>
-          <t>MIT Technology Review</t>
+          <t>The New York Times Technology</t>
         </is>
       </c>
       <c r="F7" s="60" t="inlineStr">
         <is>
-          <t>MIT Technology Review</t>
+          <t>The New York Times</t>
         </is>
       </c>
       <c r="G7" s="60" t="inlineStr">
         <is>
-          <t>https://www.technologyreview.com/feed/</t>
+          <t>https://rss.nytimes.com/services/xml/rss/nyt/Technology.xml</t>
         </is>
       </c>
       <c r="H7" s="60" t="inlineStr">
         <is>
-          <t>https://www.technologyreview.com/</t>
+          <t>https://www.nytimes.com/section/technology</t>
         </is>
       </c>
       <c r="I7" s="76" t="n">
@@ -5380,7 +4372,7 @@
       </c>
       <c r="K7" s="60" t="inlineStr">
         <is>
-          <t>Established specialist publication.</t>
+          <t>Official New York Times technology feed; strict innovation-scope review is applied.</t>
         </is>
       </c>
     </row>
@@ -5392,7 +4384,7 @@
       </c>
       <c r="B8" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="C8" s="60" t="inlineStr">
@@ -5402,27 +4394,27 @@
       </c>
       <c r="D8" s="60" t="inlineStr">
         <is>
-          <t>Engineering and technology</t>
+          <t>Science and research</t>
         </is>
       </c>
       <c r="E8" s="60" t="inlineStr">
         <is>
-          <t>IEEE Spectrum</t>
+          <t>The New York Times Science</t>
         </is>
       </c>
       <c r="F8" s="60" t="inlineStr">
         <is>
-          <t>IEEE</t>
+          <t>The New York Times</t>
         </is>
       </c>
       <c r="G8" s="60" t="inlineStr">
         <is>
-          <t>https://spectrum.ieee.org/feeds/feed.rss</t>
+          <t>https://rss.nytimes.com/services/xml/rss/nyt/Science.xml</t>
         </is>
       </c>
       <c r="H8" s="60" t="inlineStr">
         <is>
-          <t>https://spectrum.ieee.org/</t>
+          <t>https://www.nytimes.com/section/science</t>
         </is>
       </c>
       <c r="I8" s="76" t="n">
@@ -5435,7 +4427,7 @@
       </c>
       <c r="K8" s="60" t="inlineStr">
         <is>
-          <t>IEEE editorial publication.</t>
+          <t>Official New York Times science feed; strict innovation-scope review is applied.</t>
         </is>
       </c>
     </row>
@@ -5447,41 +4439,41 @@
       </c>
       <c r="B9" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="C9" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="D9" s="60" t="inlineStr">
         <is>
-          <t>Science</t>
+          <t>Science, technology and innovation policy</t>
         </is>
       </c>
       <c r="E9" s="60" t="inlineStr">
         <is>
-          <t>Nature</t>
+          <t>NISTEP Updates</t>
         </is>
       </c>
       <c r="F9" s="60" t="inlineStr">
         <is>
-          <t>Springer Nature</t>
+          <t>National Institute of Science and Technology Policy</t>
         </is>
       </c>
       <c r="G9" s="60" t="inlineStr">
         <is>
-          <t>https://www.nature.com/nature.rss</t>
+          <t>https://www.nistep.go.jp/feed</t>
         </is>
       </c>
       <c r="H9" s="60" t="inlineStr">
         <is>
-          <t>https://www.nature.com/</t>
+          <t>https://www.nistep.go.jp/</t>
         </is>
       </c>
       <c r="I9" s="76" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J9" s="60" t="inlineStr">
         <is>
@@ -5490,7 +4482,7 @@
       </c>
       <c r="K9" s="60" t="inlineStr">
         <is>
-          <t>Leading scientific publication; innovation-topic filter is applied.</t>
+          <t>Official Japanese science and technology policy institute feed.</t>
         </is>
       </c>
     </row>
@@ -5507,36 +4499,36 @@
       </c>
       <c r="C10" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="D10" s="60" t="inlineStr">
         <is>
-          <t>Science</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E10" s="60" t="inlineStr">
         <is>
-          <t>Science</t>
+          <t>The Guardian Technology</t>
         </is>
       </c>
       <c r="F10" s="60" t="inlineStr">
         <is>
-          <t>AAAS</t>
+          <t>Guardian News &amp; Media</t>
         </is>
       </c>
       <c r="G10" s="60" t="inlineStr">
         <is>
-          <t>https://www.science.org/action/showFeed?type=etoc&amp;feed=rss&amp;jc=science</t>
+          <t>https://www.theguardian.com/technology/rss</t>
         </is>
       </c>
       <c r="H10" s="60" t="inlineStr">
         <is>
-          <t>https://www.science.org/</t>
+          <t>https://www.theguardian.com/technology</t>
         </is>
       </c>
       <c r="I10" s="76" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J10" s="60" t="inlineStr">
         <is>
@@ -5545,7 +4537,7 @@
       </c>
       <c r="K10" s="60" t="inlineStr">
         <is>
-          <t>Leading scientific publication; the publisher may rate-limit automated access.</t>
+          <t>Major media; strict topic filter is applied.</t>
         </is>
       </c>
     </row>
@@ -5557,37 +4549,37 @@
       </c>
       <c r="B11" s="60" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="C11" s="60" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D11" s="60" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Emerging technology</t>
         </is>
       </c>
       <c r="E11" s="60" t="inlineStr">
         <is>
-          <t>South China Morning Post Technology</t>
+          <t>MIT Technology Review</t>
         </is>
       </c>
       <c r="F11" s="60" t="inlineStr">
         <is>
-          <t>South China Morning Post</t>
+          <t>MIT Technology Review</t>
         </is>
       </c>
       <c r="G11" s="60" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/rss/36/feed</t>
+          <t>https://www.technologyreview.com/feed/</t>
         </is>
       </c>
       <c r="H11" s="60" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/tech</t>
+          <t>https://www.technologyreview.com/</t>
         </is>
       </c>
       <c r="I11" s="76" t="n">
@@ -5600,7 +4592,7 @@
       </c>
       <c r="K11" s="60" t="inlineStr">
         <is>
-          <t>Major Asia-focused technology media; only /tech/ article URLs are accepted.</t>
+          <t>Established specialist publication.</t>
         </is>
       </c>
     </row>
@@ -5612,41 +4604,41 @@
       </c>
       <c r="B12" s="60" t="inlineStr">
         <is>
-          <t>Middle East</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="C12" s="60" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D12" s="60" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Engineering and technology</t>
         </is>
       </c>
       <c r="E12" s="60" t="inlineStr">
         <is>
-          <t>Arab News Technology</t>
+          <t>IEEE Spectrum</t>
         </is>
       </c>
       <c r="F12" s="60" t="inlineStr">
         <is>
-          <t>Arab News</t>
+          <t>IEEE</t>
         </is>
       </c>
       <c r="G12" s="60" t="inlineStr">
         <is>
-          <t>https://www.arabnews.com/taxonomy/term/2936/feed</t>
+          <t>https://spectrum.ieee.org/feeds/feed.rss</t>
         </is>
       </c>
       <c r="H12" s="60" t="inlineStr">
         <is>
-          <t>https://www.arabnews.com/tags/technology</t>
+          <t>https://spectrum.ieee.org/</t>
         </is>
       </c>
       <c r="I12" s="76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J12" s="60" t="inlineStr">
         <is>
@@ -5655,7 +4647,7 @@
       </c>
       <c r="K12" s="60" t="inlineStr">
         <is>
-          <t>Established regional media; topic filter is applied.</t>
+          <t>IEEE editorial publication.</t>
         </is>
       </c>
     </row>
@@ -5667,37 +4659,37 @@
       </c>
       <c r="B13" s="60" t="inlineStr">
         <is>
-          <t>Middle East</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="C13" s="60" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D13" s="60" t="inlineStr">
         <is>
-          <t>Technology and innovation</t>
+          <t>Science</t>
         </is>
       </c>
       <c r="E13" s="60" t="inlineStr">
         <is>
-          <t>The National Technology</t>
+          <t>Nature</t>
         </is>
       </c>
       <c r="F13" s="60" t="inlineStr">
         <is>
-          <t>The National</t>
+          <t>Springer Nature</t>
         </is>
       </c>
       <c r="G13" s="60" t="inlineStr">
         <is>
-          <t>https://www.thenationalnews.com/arc/outboundfeeds/rss/category/future/technology/?outputType=xml</t>
+          <t>https://www.nature.com/nature.rss</t>
         </is>
       </c>
       <c r="H13" s="60" t="inlineStr">
         <is>
-          <t>https://www.thenationalnews.com/future/technology/</t>
+          <t>https://www.nature.com/</t>
         </is>
       </c>
       <c r="I13" s="76" t="n">
@@ -5710,7 +4702,7 @@
       </c>
       <c r="K13" s="60" t="inlineStr">
         <is>
-          <t>Established UAE-based regional newspaper; official technology feed.</t>
+          <t>Leading scientific publication; innovation-topic filter is applied.</t>
         </is>
       </c>
     </row>
@@ -5722,7 +4714,7 @@
       </c>
       <c r="B14" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="C14" s="60" t="inlineStr">
@@ -5732,40 +4724,40 @@
       </c>
       <c r="D14" s="60" t="inlineStr">
         <is>
-          <t>Technology policy</t>
+          <t>Science</t>
         </is>
       </c>
       <c r="E14" s="60" t="inlineStr">
         <is>
-          <t>Brookings TechTank</t>
+          <t>Science</t>
         </is>
       </c>
       <c r="F14" s="60" t="inlineStr">
         <is>
-          <t>Brookings Institution</t>
+          <t>AAAS</t>
         </is>
       </c>
       <c r="G14" s="60" t="inlineStr">
         <is>
-          <t>https://www.brookings.edu/tags/techtank/</t>
+          <t>https://www.science.org/action/showFeed?type=etoc&amp;feed=rss&amp;jc=science</t>
         </is>
       </c>
       <c r="H14" s="60" t="inlineStr">
         <is>
-          <t>https://www.brookings.edu/tags/techtank/</t>
+          <t>https://www.science.org/</t>
         </is>
       </c>
       <c r="I14" s="76" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J14" s="60" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K14" s="60" t="inlineStr">
         <is>
-          <t>Technology-policy analysis from Brookings; official listing-page fallback.</t>
+          <t>Leading scientific publication; the publisher may rate-limit automated access.</t>
         </is>
       </c>
     </row>
@@ -5777,37 +4769,37 @@
       </c>
       <c r="B15" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="C15" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="D15" s="60" t="inlineStr">
         <is>
-          <t>Technology and industrial policy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E15" s="60" t="inlineStr">
         <is>
-          <t>CSIS Analysis</t>
+          <t>South China Morning Post Technology</t>
         </is>
       </c>
       <c r="F15" s="60" t="inlineStr">
         <is>
-          <t>Center for Strategic and International Studies</t>
+          <t>South China Morning Post</t>
         </is>
       </c>
       <c r="G15" s="60" t="inlineStr">
         <is>
-          <t>https://www.csis.org/rss.xml</t>
+          <t>https://www.scmp.com/rss/36/feed</t>
         </is>
       </c>
       <c r="H15" s="60" t="inlineStr">
         <is>
-          <t>https://www.csis.org/analysis</t>
+          <t>https://www.scmp.com/tech</t>
         </is>
       </c>
       <c r="I15" s="76" t="n">
@@ -5820,7 +4812,7 @@
       </c>
       <c r="K15" s="60" t="inlineStr">
         <is>
-          <t>Broad analysis feed; innovation-topic filter is applied.</t>
+          <t>Major Asia-focused technology media; only /tech/ article URLs are accepted.</t>
         </is>
       </c>
     </row>
@@ -5832,41 +4824,41 @@
       </c>
       <c r="B16" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Middle East</t>
         </is>
       </c>
       <c r="C16" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="D16" s="60" t="inlineStr">
         <is>
-          <t>Emerging technology policy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E16" s="60" t="inlineStr">
         <is>
-          <t>CSET</t>
+          <t>Arab News Technology</t>
         </is>
       </c>
       <c r="F16" s="60" t="inlineStr">
         <is>
-          <t>Center for Security and Emerging Technology</t>
+          <t>Arab News</t>
         </is>
       </c>
       <c r="G16" s="60" t="inlineStr">
         <is>
-          <t>https://cset.georgetown.edu/feed/</t>
+          <t>https://www.arabnews.com/taxonomy/term/2936/feed</t>
         </is>
       </c>
       <c r="H16" s="60" t="inlineStr">
         <is>
-          <t>https://cset.georgetown.edu/</t>
+          <t>https://www.arabnews.com/tags/technology</t>
         </is>
       </c>
       <c r="I16" s="76" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J16" s="60" t="inlineStr">
         <is>
@@ -5875,7 +4867,7 @@
       </c>
       <c r="K16" s="60" t="inlineStr">
         <is>
-          <t>University-based emerging-technology policy center.</t>
+          <t>Established regional media; topic filter is applied.</t>
         </is>
       </c>
     </row>
@@ -5887,37 +4879,37 @@
       </c>
       <c r="B17" s="60" t="inlineStr">
         <is>
-          <t>EU &amp; Europe</t>
+          <t>Middle East</t>
         </is>
       </c>
       <c r="C17" s="60" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>United Arab Emirates</t>
         </is>
       </c>
       <c r="D17" s="60" t="inlineStr">
         <is>
-          <t>Economic and innovation policy</t>
+          <t>Technology and innovation</t>
         </is>
       </c>
       <c r="E17" s="60" t="inlineStr">
         <is>
-          <t>Bruegel</t>
+          <t>The National Technology</t>
         </is>
       </c>
       <c r="F17" s="60" t="inlineStr">
         <is>
-          <t>Bruegel</t>
+          <t>The National</t>
         </is>
       </c>
       <c r="G17" s="60" t="inlineStr">
         <is>
-          <t>https://www.bruegel.org/rss.xml</t>
+          <t>https://www.thenationalnews.com/arc/outboundfeeds/rss/category/future/technology/?outputType=xml</t>
         </is>
       </c>
       <c r="H17" s="60" t="inlineStr">
         <is>
-          <t>https://www.bruegel.org/</t>
+          <t>https://www.thenationalnews.com/future/technology/</t>
         </is>
       </c>
       <c r="I17" s="76" t="n">
@@ -5930,7 +4922,7 @@
       </c>
       <c r="K17" s="60" t="inlineStr">
         <is>
-          <t>European economic-policy institute.</t>
+          <t>Established UAE-based regional newspaper; official technology feed.</t>
         </is>
       </c>
     </row>
@@ -5942,50 +4934,50 @@
       </c>
       <c r="B18" s="60" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="C18" s="60" t="inlineStr">
         <is>
-          <t>China / Germany</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D18" s="60" t="inlineStr">
         <is>
-          <t>China technology and industrial policy</t>
+          <t>Technology policy</t>
         </is>
       </c>
       <c r="E18" s="60" t="inlineStr">
         <is>
-          <t>MERICS</t>
+          <t>Brookings TechTank</t>
         </is>
       </c>
       <c r="F18" s="60" t="inlineStr">
         <is>
-          <t>Mercator Institute for China Studies</t>
+          <t>Brookings Institution</t>
         </is>
       </c>
       <c r="G18" s="60" t="inlineStr">
         <is>
-          <t>https://merics.org/en/rss.xml</t>
+          <t>https://www.brookings.edu/tags/techtank/</t>
         </is>
       </c>
       <c r="H18" s="60" t="inlineStr">
         <is>
-          <t>https://merics.org/en</t>
+          <t>https://www.brookings.edu/tags/techtank/</t>
         </is>
       </c>
       <c r="I18" s="76" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J18" s="60" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K18" s="60" t="inlineStr">
         <is>
-          <t>China-focused policy institute.</t>
+          <t>Technology-policy analysis from Brookings; official listing-page fallback.</t>
         </is>
       </c>
     </row>
@@ -6007,31 +4999,31 @@
       </c>
       <c r="D19" s="60" t="inlineStr">
         <is>
-          <t>Research policy and science</t>
+          <t>Technology and industrial policy</t>
         </is>
       </c>
       <c r="E19" s="60" t="inlineStr">
         <is>
-          <t>National Science Foundation News</t>
+          <t>CSIS Analysis</t>
         </is>
       </c>
       <c r="F19" s="60" t="inlineStr">
         <is>
-          <t>U.S. National Science Foundation</t>
+          <t>Center for Strategic and International Studies</t>
         </is>
       </c>
       <c r="G19" s="60" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/rss/rss_www_news.xml</t>
+          <t>https://www.csis.org/rss.xml</t>
         </is>
       </c>
       <c r="H19" s="60" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/news</t>
+          <t>https://www.csis.org/analysis</t>
         </is>
       </c>
       <c r="I19" s="76" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J19" s="60" t="inlineStr">
         <is>
@@ -6040,7 +5032,7 @@
       </c>
       <c r="K19" s="60" t="inlineStr">
         <is>
-          <t>Official U.S. government source.</t>
+          <t>Broad analysis feed; innovation-topic filter is applied.</t>
         </is>
       </c>
     </row>
@@ -6062,27 +5054,27 @@
       </c>
       <c r="D20" s="60" t="inlineStr">
         <is>
-          <t>Standards, science and industrial policy</t>
+          <t>Emerging technology policy</t>
         </is>
       </c>
       <c r="E20" s="60" t="inlineStr">
         <is>
-          <t>NIST News</t>
+          <t>CSET</t>
         </is>
       </c>
       <c r="F20" s="60" t="inlineStr">
         <is>
-          <t>National Institute of Standards and Technology</t>
+          <t>Center for Security and Emerging Technology</t>
         </is>
       </c>
       <c r="G20" s="60" t="inlineStr">
         <is>
-          <t>https://www.nist.gov/news-events/news/rss.xml</t>
+          <t>https://cset.georgetown.edu/feed/</t>
         </is>
       </c>
       <c r="H20" s="60" t="inlineStr">
         <is>
-          <t>https://www.nist.gov/news-events/news</t>
+          <t>https://cset.georgetown.edu/</t>
         </is>
       </c>
       <c r="I20" s="76" t="n">
@@ -6095,7 +5087,7 @@
       </c>
       <c r="K20" s="60" t="inlineStr">
         <is>
-          <t>Official U.S. government source.</t>
+          <t>University-based emerging-technology policy center.</t>
         </is>
       </c>
     </row>
@@ -6107,41 +5099,41 @@
       </c>
       <c r="B21" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>EU &amp; Europe</t>
         </is>
       </c>
       <c r="C21" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="D21" s="60" t="inlineStr">
         <is>
-          <t>Biotechnology and healthcare</t>
+          <t>Economic and innovation policy</t>
         </is>
       </c>
       <c r="E21" s="60" t="inlineStr">
         <is>
-          <t>NIH News Releases</t>
+          <t>Bruegel</t>
         </is>
       </c>
       <c r="F21" s="60" t="inlineStr">
         <is>
-          <t>U.S. National Institutes of Health</t>
+          <t>Bruegel</t>
         </is>
       </c>
       <c r="G21" s="60" t="inlineStr">
         <is>
-          <t>https://www.nih.gov/news-events/news-releases/rss.xml</t>
+          <t>https://www.bruegel.org/rss.xml</t>
         </is>
       </c>
       <c r="H21" s="60" t="inlineStr">
         <is>
-          <t>https://www.nih.gov/news-events/news-releases</t>
+          <t>https://www.bruegel.org/</t>
         </is>
       </c>
       <c r="I21" s="76" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J21" s="60" t="inlineStr">
         <is>
@@ -6150,7 +5142,7 @@
       </c>
       <c r="K21" s="60" t="inlineStr">
         <is>
-          <t>Official U.S. biomedical-research source.</t>
+          <t>European economic-policy institute.</t>
         </is>
       </c>
     </row>
@@ -6162,41 +5154,41 @@
       </c>
       <c r="B22" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="C22" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>China / Germany</t>
         </is>
       </c>
       <c r="D22" s="60" t="inlineStr">
         <is>
-          <t>Energy, quantum and research policy</t>
+          <t>China technology and industrial policy</t>
         </is>
       </c>
       <c r="E22" s="60" t="inlineStr">
         <is>
-          <t>DOE Office of Science News</t>
+          <t>MERICS</t>
         </is>
       </c>
       <c r="F22" s="60" t="inlineStr">
         <is>
-          <t>U.S. Department of Energy</t>
+          <t>Mercator Institute for China Studies</t>
         </is>
       </c>
       <c r="G22" s="60" t="inlineStr">
         <is>
-          <t>https://www.energy.gov/rss/science/3662436</t>
+          <t>https://merics.org/en/rss.xml</t>
         </is>
       </c>
       <c r="H22" s="60" t="inlineStr">
         <is>
-          <t>https://www.energy.gov/science/listings/office-science-news</t>
+          <t>https://merics.org/en</t>
         </is>
       </c>
       <c r="I22" s="76" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J22" s="60" t="inlineStr">
         <is>
@@ -6205,7 +5197,7 @@
       </c>
       <c r="K22" s="60" t="inlineStr">
         <is>
-          <t>Official U.S. government source; includes fusion and quantum policy.</t>
+          <t>China-focused policy institute.</t>
         </is>
       </c>
     </row>
@@ -6217,37 +5209,37 @@
       </c>
       <c r="B23" s="60" t="inlineStr">
         <is>
-          <t>EU &amp; Europe</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="C23" s="60" t="inlineStr">
         <is>
-          <t>European Union</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D23" s="60" t="inlineStr">
         <is>
-          <t>EU policy</t>
+          <t>Research policy and science</t>
         </is>
       </c>
       <c r="E23" s="60" t="inlineStr">
         <is>
-          <t>European Commission Press Corner</t>
+          <t>National Science Foundation News</t>
         </is>
       </c>
       <c r="F23" s="60" t="inlineStr">
         <is>
-          <t>European Commission</t>
+          <t>U.S. National Science Foundation</t>
         </is>
       </c>
       <c r="G23" s="60" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/commission/presscorner/api/rss?language=en&amp;documenttype=press_release</t>
+          <t>https://www.nsf.gov/rss/rss_www_news.xml</t>
         </is>
       </c>
       <c r="H23" s="60" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/commission/presscorner/home/en</t>
+          <t>https://www.nsf.gov/news</t>
         </is>
       </c>
       <c r="I23" s="76" t="n">
@@ -6260,7 +5252,7 @@
       </c>
       <c r="K23" s="60" t="inlineStr">
         <is>
-          <t>Official European Commission press releases.</t>
+          <t>Official U.S. government source.</t>
         </is>
       </c>
     </row>
@@ -6272,37 +5264,37 @@
       </c>
       <c r="B24" s="60" t="inlineStr">
         <is>
-          <t>EU &amp; Europe</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="C24" s="60" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D24" s="60" t="inlineStr">
         <is>
-          <t>Science and innovation policy</t>
+          <t>Standards, science and industrial policy</t>
         </is>
       </c>
       <c r="E24" s="60" t="inlineStr">
         <is>
-          <t>UK DSIT</t>
+          <t>NIST News</t>
         </is>
       </c>
       <c r="F24" s="60" t="inlineStr">
         <is>
-          <t>Department for Science, Innovation and Technology</t>
+          <t>National Institute of Standards and Technology</t>
         </is>
       </c>
       <c r="G24" s="60" t="inlineStr">
         <is>
-          <t>https://www.gov.uk/government/organisations/department-for-science-innovation-and-technology.atom</t>
+          <t>https://www.nist.gov/news-events/news/rss.xml</t>
         </is>
       </c>
       <c r="H24" s="60" t="inlineStr">
         <is>
-          <t>https://www.gov.uk/government/organisations/department-for-science-innovation-and-technology</t>
+          <t>https://www.nist.gov/news-events/news</t>
         </is>
       </c>
       <c r="I24" s="76" t="n">
@@ -6315,7 +5307,7 @@
       </c>
       <c r="K24" s="60" t="inlineStr">
         <is>
-          <t>Official UK government Atom feed.</t>
+          <t>Official U.S. government source.</t>
         </is>
       </c>
     </row>
@@ -6327,37 +5319,37 @@
       </c>
       <c r="B25" s="60" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="C25" s="60" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D25" s="60" t="inlineStr">
         <is>
-          <t>Industrial and innovation policy</t>
+          <t>Biotechnology and healthcare</t>
         </is>
       </c>
       <c r="E25" s="60" t="inlineStr">
         <is>
-          <t>METI Press Releases</t>
+          <t>NIH News Releases</t>
         </is>
       </c>
       <c r="F25" s="60" t="inlineStr">
         <is>
-          <t>Ministry of Economy, Trade and Industry</t>
+          <t>U.S. National Institutes of Health</t>
         </is>
       </c>
       <c r="G25" s="60" t="inlineStr">
         <is>
-          <t>https://www.meti.go.jp/english/press/index.rdf</t>
+          <t>https://www.nih.gov/news-events/news-releases/rss.xml</t>
         </is>
       </c>
       <c r="H25" s="60" t="inlineStr">
         <is>
-          <t>https://www.meti.go.jp/english/press/index.html</t>
+          <t>https://www.nih.gov/news-events/news-releases</t>
         </is>
       </c>
       <c r="I25" s="76" t="n">
@@ -6370,7 +5362,7 @@
       </c>
       <c r="K25" s="60" t="inlineStr">
         <is>
-          <t>Official Japanese government English-language feed.</t>
+          <t>Official U.S. biomedical-research source.</t>
         </is>
       </c>
     </row>
@@ -6382,41 +5374,41 @@
       </c>
       <c r="B26" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="C26" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D26" s="60" t="inlineStr">
         <is>
-          <t>Healthcare policy</t>
+          <t>Energy, quantum and research policy</t>
         </is>
       </c>
       <c r="E26" s="60" t="inlineStr">
         <is>
-          <t>WHO News</t>
+          <t>DOE Office of Science News</t>
         </is>
       </c>
       <c r="F26" s="60" t="inlineStr">
         <is>
-          <t>World Health Organization</t>
+          <t>U.S. Department of Energy</t>
         </is>
       </c>
       <c r="G26" s="60" t="inlineStr">
         <is>
-          <t>https://www.who.int/rss-feeds/news-english.xml</t>
+          <t>https://www.energy.gov/rss/science/3662436</t>
         </is>
       </c>
       <c r="H26" s="60" t="inlineStr">
         <is>
-          <t>https://www.who.int/news</t>
+          <t>https://www.energy.gov/science/listings/office-science-news</t>
         </is>
       </c>
       <c r="I26" s="76" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J26" s="60" t="inlineStr">
         <is>
@@ -6425,7 +5417,7 @@
       </c>
       <c r="K26" s="60" t="inlineStr">
         <is>
-          <t>Official international public-health source.</t>
+          <t>Official U.S. government source; includes fusion and quantum policy.</t>
         </is>
       </c>
     </row>
@@ -6437,41 +5429,41 @@
       </c>
       <c r="B27" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>EU &amp; Europe</t>
         </is>
       </c>
       <c r="C27" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>European Union</t>
         </is>
       </c>
       <c r="D27" s="60" t="inlineStr">
         <is>
-          <t>Energy technology and policy</t>
+          <t>EU policy</t>
         </is>
       </c>
       <c r="E27" s="60" t="inlineStr">
         <is>
-          <t>IEA News</t>
+          <t>European Commission Press Corner</t>
         </is>
       </c>
       <c r="F27" s="60" t="inlineStr">
         <is>
-          <t>International Energy Agency</t>
+          <t>European Commission</t>
         </is>
       </c>
       <c r="G27" s="60" t="inlineStr">
         <is>
-          <t>https://www.iea.org/rss/news.xml</t>
+          <t>https://ec.europa.eu/commission/presscorner/api/rss?language=en&amp;documenttype=press_release</t>
         </is>
       </c>
       <c r="H27" s="60" t="inlineStr">
         <is>
-          <t>https://www.iea.org/news</t>
+          <t>https://ec.europa.eu/commission/presscorner/home/en</t>
         </is>
       </c>
       <c r="I27" s="76" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J27" s="60" t="inlineStr">
         <is>
@@ -6480,7 +5472,7 @@
       </c>
       <c r="K27" s="60" t="inlineStr">
         <is>
-          <t>Official international energy-policy source.</t>
+          <t>Official European Commission press releases.</t>
         </is>
       </c>
     </row>
@@ -6492,41 +5484,41 @@
       </c>
       <c r="B28" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>EU &amp; Europe</t>
         </is>
       </c>
       <c r="C28" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="D28" s="60" t="inlineStr">
         <is>
-          <t>Economic, science and innovation policy</t>
+          <t>Science and innovation policy</t>
         </is>
       </c>
       <c r="E28" s="60" t="inlineStr">
         <is>
-          <t>OECD Newsroom</t>
+          <t>UK DSIT</t>
         </is>
       </c>
       <c r="F28" s="60" t="inlineStr">
         <is>
-          <t>OECD</t>
+          <t>Department for Science, Innovation and Technology</t>
         </is>
       </c>
       <c r="G28" s="60" t="inlineStr">
         <is>
-          <t>https://www.oecd.org/newsroom/rss.xml</t>
+          <t>https://www.gov.uk/government/organisations/department-for-science-innovation-and-technology.atom</t>
         </is>
       </c>
       <c r="H28" s="60" t="inlineStr">
         <is>
-          <t>https://www.oecd.org/newsroom/</t>
+          <t>https://www.gov.uk/government/organisations/department-for-science-innovation-and-technology</t>
         </is>
       </c>
       <c r="I28" s="76" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J28" s="60" t="inlineStr">
         <is>
@@ -6535,7 +5527,7 @@
       </c>
       <c r="K28" s="60" t="inlineStr">
         <is>
-          <t>Official OECD source.</t>
+          <t>Official UK government Atom feed.</t>
         </is>
       </c>
     </row>
@@ -6547,37 +5539,37 @@
       </c>
       <c r="B29" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="C29" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="D29" s="60" t="inlineStr">
         <is>
-          <t>Artificial intelligence</t>
+          <t>Industrial and innovation policy</t>
         </is>
       </c>
       <c r="E29" s="60" t="inlineStr">
         <is>
-          <t>OpenAI News</t>
+          <t>METI Press Releases</t>
         </is>
       </c>
       <c r="F29" s="60" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Ministry of Economy, Trade and Industry</t>
         </is>
       </c>
       <c r="G29" s="60" t="inlineStr">
         <is>
-          <t>https://openai.com/news/rss.xml</t>
+          <t>https://www.meti.go.jp/english/press/index.rdf</t>
         </is>
       </c>
       <c r="H29" s="60" t="inlineStr">
         <is>
-          <t>https://openai.com/news/</t>
+          <t>https://www.meti.go.jp/english/press/index.html</t>
         </is>
       </c>
       <c r="I29" s="76" t="n">
@@ -6590,7 +5582,7 @@
       </c>
       <c r="K29" s="60" t="inlineStr">
         <is>
-          <t>Official company newsroom.</t>
+          <t>Official Japanese government English-language feed.</t>
         </is>
       </c>
     </row>
@@ -6607,32 +5599,32 @@
       </c>
       <c r="C30" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D30" s="60" t="inlineStr">
         <is>
-          <t>Artificial intelligence</t>
+          <t>Healthcare policy</t>
         </is>
       </c>
       <c r="E30" s="60" t="inlineStr">
         <is>
-          <t>Google AI</t>
+          <t>WHO News</t>
         </is>
       </c>
       <c r="F30" s="60" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>World Health Organization</t>
         </is>
       </c>
       <c r="G30" s="60" t="inlineStr">
         <is>
-          <t>https://blog.google/technology/ai/rss/</t>
+          <t>https://www.who.int/rss-feeds/news-english.xml</t>
         </is>
       </c>
       <c r="H30" s="60" t="inlineStr">
         <is>
-          <t>https://blog.google/technology/ai/</t>
+          <t>https://www.who.int/news</t>
         </is>
       </c>
       <c r="I30" s="76" t="n">
@@ -6645,7 +5637,7 @@
       </c>
       <c r="K30" s="60" t="inlineStr">
         <is>
-          <t>Official company publication.</t>
+          <t>Official international public-health source.</t>
         </is>
       </c>
     </row>
@@ -6662,32 +5654,32 @@
       </c>
       <c r="C31" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D31" s="60" t="inlineStr">
         <is>
-          <t>AI and semiconductors</t>
+          <t>Energy technology and policy</t>
         </is>
       </c>
       <c r="E31" s="60" t="inlineStr">
         <is>
-          <t>NVIDIA Blog</t>
+          <t>IEA News</t>
         </is>
       </c>
       <c r="F31" s="60" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>International Energy Agency</t>
         </is>
       </c>
       <c r="G31" s="60" t="inlineStr">
         <is>
-          <t>https://blogs.nvidia.com/feed/</t>
+          <t>https://www.iea.org/rss/news.xml</t>
         </is>
       </c>
       <c r="H31" s="60" t="inlineStr">
         <is>
-          <t>https://blogs.nvidia.com/</t>
+          <t>https://www.iea.org/news</t>
         </is>
       </c>
       <c r="I31" s="76" t="n">
@@ -6700,7 +5692,7 @@
       </c>
       <c r="K31" s="60" t="inlineStr">
         <is>
-          <t>Official company publication.</t>
+          <t>Official international energy-policy source.</t>
         </is>
       </c>
     </row>
@@ -6717,32 +5709,32 @@
       </c>
       <c r="C32" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D32" s="60" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Economic, science and innovation policy</t>
         </is>
       </c>
       <c r="E32" s="60" t="inlineStr">
         <is>
-          <t>Intel Newsroom</t>
+          <t>OECD Newsroom</t>
         </is>
       </c>
       <c r="F32" s="60" t="inlineStr">
         <is>
-          <t>Intel</t>
+          <t>OECD</t>
         </is>
       </c>
       <c r="G32" s="60" t="inlineStr">
         <is>
-          <t>https://newsroom.intel.com/feed</t>
+          <t>https://www.oecd.org/newsroom/rss.xml</t>
         </is>
       </c>
       <c r="H32" s="60" t="inlineStr">
         <is>
-          <t>https://newsroom.intel.com/</t>
+          <t>https://www.oecd.org/newsroom/</t>
         </is>
       </c>
       <c r="I32" s="76" t="n">
@@ -6755,7 +5747,7 @@
       </c>
       <c r="K32" s="60" t="inlineStr">
         <is>
-          <t>Official company newsroom.</t>
+          <t>Official OECD source.</t>
         </is>
       </c>
     </row>
@@ -6777,31 +5769,31 @@
       </c>
       <c r="D33" s="60" t="inlineStr">
         <is>
-          <t>AI and quantum</t>
+          <t>Artificial intelligence</t>
         </is>
       </c>
       <c r="E33" s="60" t="inlineStr">
         <is>
-          <t>IBM Research</t>
+          <t>OpenAI News</t>
         </is>
       </c>
       <c r="F33" s="60" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="G33" s="60" t="inlineStr">
         <is>
-          <t>https://research.ibm.com/blog/rss.xml</t>
+          <t>https://openai.com/news/rss.xml</t>
         </is>
       </c>
       <c r="H33" s="60" t="inlineStr">
         <is>
-          <t>https://research.ibm.com/blog</t>
+          <t>https://openai.com/news/</t>
         </is>
       </c>
       <c r="I33" s="76" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J33" s="60" t="inlineStr">
         <is>
@@ -6810,7 +5802,7 @@
       </c>
       <c r="K33" s="60" t="inlineStr">
         <is>
-          <t>Official corporate research publication.</t>
+          <t>Official company newsroom.</t>
         </is>
       </c>
     </row>
@@ -6832,27 +5824,27 @@
       </c>
       <c r="D34" s="60" t="inlineStr">
         <is>
-          <t>AI, quantum and computing</t>
+          <t>Artificial intelligence</t>
         </is>
       </c>
       <c r="E34" s="60" t="inlineStr">
         <is>
-          <t>Microsoft Research</t>
+          <t>Google AI</t>
         </is>
       </c>
       <c r="F34" s="60" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="G34" s="60" t="inlineStr">
         <is>
-          <t>https://www.microsoft.com/en-us/research/feed/</t>
+          <t>https://blog.google/technology/ai/rss/</t>
         </is>
       </c>
       <c r="H34" s="60" t="inlineStr">
         <is>
-          <t>https://www.microsoft.com/en-us/research/blog/</t>
+          <t>https://blog.google/technology/ai/</t>
         </is>
       </c>
       <c r="I34" s="76" t="n">
@@ -6865,7 +5857,7 @@
       </c>
       <c r="K34" s="60" t="inlineStr">
         <is>
-          <t>Official corporate research publication.</t>
+          <t>Official company publication.</t>
         </is>
       </c>
     </row>
@@ -6877,37 +5869,37 @@
       </c>
       <c r="B35" s="60" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="C35" s="60" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D35" s="60" t="inlineStr">
         <is>
-          <t>Semiconductors, AI and telecom</t>
+          <t>AI and semiconductors</t>
         </is>
       </c>
       <c r="E35" s="60" t="inlineStr">
         <is>
-          <t>Samsung Global Newsroom</t>
+          <t>NVIDIA Blog</t>
         </is>
       </c>
       <c r="F35" s="60" t="inlineStr">
         <is>
-          <t>Samsung Electronics</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="G35" s="60" t="inlineStr">
         <is>
-          <t>https://news.samsung.com/global/feed</t>
+          <t>https://blogs.nvidia.com/feed/</t>
         </is>
       </c>
       <c r="H35" s="60" t="inlineStr">
         <is>
-          <t>https://news.samsung.com/global/</t>
+          <t>https://blogs.nvidia.com/</t>
         </is>
       </c>
       <c r="I35" s="76" t="n">
@@ -6920,7 +5912,7 @@
       </c>
       <c r="K35" s="60" t="inlineStr">
         <is>
-          <t>Official company newsroom.</t>
+          <t>Official company publication.</t>
         </is>
       </c>
     </row>
@@ -6932,50 +5924,50 @@
       </c>
       <c r="B36" s="60" t="inlineStr">
         <is>
-          <t>EU &amp; Europe</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="C36" s="60" t="inlineStr">
         <is>
-          <t>International / France</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D36" s="60" t="inlineStr">
         <is>
-          <t>Fusion energy</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="E36" s="60" t="inlineStr">
         <is>
-          <t>ITER News</t>
+          <t>Intel Newsroom</t>
         </is>
       </c>
       <c r="F36" s="60" t="inlineStr">
         <is>
-          <t>ITER Organization</t>
+          <t>Intel</t>
         </is>
       </c>
       <c r="G36" s="60" t="inlineStr">
         <is>
-          <t>https://www.iter.org/news</t>
+          <t>https://newsroom.intel.com/feed</t>
         </is>
       </c>
       <c r="H36" s="60" t="inlineStr">
         <is>
-          <t>https://www.iter.org/news</t>
+          <t>https://newsroom.intel.com/</t>
         </is>
       </c>
       <c r="I36" s="76" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J36" s="60" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K36" s="60" t="inlineStr">
         <is>
-          <t>Official international fusion project; official listing-page fallback.</t>
+          <t>Official company newsroom.</t>
         </is>
       </c>
     </row>
@@ -6992,50 +5984,270 @@
       </c>
       <c r="C37" s="60" t="inlineStr">
         <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D37" s="60" t="inlineStr">
+        <is>
+          <t>AI and quantum</t>
+        </is>
+      </c>
+      <c r="E37" s="60" t="inlineStr">
+        <is>
+          <t>IBM Research</t>
+        </is>
+      </c>
+      <c r="F37" s="60" t="inlineStr">
+        <is>
+          <t>IBM</t>
+        </is>
+      </c>
+      <c r="G37" s="60" t="inlineStr">
+        <is>
+          <t>https://research.ibm.com/blog/rss.xml</t>
+        </is>
+      </c>
+      <c r="H37" s="60" t="inlineStr">
+        <is>
+          <t>https://research.ibm.com/blog</t>
+        </is>
+      </c>
+      <c r="I37" s="76" t="n">
+        <v>4</v>
+      </c>
+      <c r="J37" s="60" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K37" s="60" t="inlineStr">
+        <is>
+          <t>Official corporate research publication.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="36" customHeight="1">
+      <c r="A38" s="60" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B38" s="60" t="inlineStr">
+        <is>
           <t>Global</t>
         </is>
       </c>
-      <c r="D37" s="60" t="inlineStr">
+      <c r="C38" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D38" s="60" t="inlineStr">
+        <is>
+          <t>AI, quantum and computing</t>
+        </is>
+      </c>
+      <c r="E38" s="60" t="inlineStr">
+        <is>
+          <t>Microsoft Research</t>
+        </is>
+      </c>
+      <c r="F38" s="60" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="G38" s="60" t="inlineStr">
+        <is>
+          <t>https://www.microsoft.com/en-us/research/feed/</t>
+        </is>
+      </c>
+      <c r="H38" s="60" t="inlineStr">
+        <is>
+          <t>https://www.microsoft.com/en-us/research/blog/</t>
+        </is>
+      </c>
+      <c r="I38" s="76" t="n">
+        <v>4</v>
+      </c>
+      <c r="J38" s="60" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K38" s="60" t="inlineStr">
+        <is>
+          <t>Official corporate research publication.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="36" customHeight="1">
+      <c r="A39" s="60" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B39" s="60" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="C39" s="60" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="D39" s="60" t="inlineStr">
+        <is>
+          <t>Semiconductors, AI and telecom</t>
+        </is>
+      </c>
+      <c r="E39" s="60" t="inlineStr">
+        <is>
+          <t>Samsung Global Newsroom</t>
+        </is>
+      </c>
+      <c r="F39" s="60" t="inlineStr">
+        <is>
+          <t>Samsung Electronics</t>
+        </is>
+      </c>
+      <c r="G39" s="60" t="inlineStr">
+        <is>
+          <t>https://news.samsung.com/global/feed</t>
+        </is>
+      </c>
+      <c r="H39" s="60" t="inlineStr">
+        <is>
+          <t>https://news.samsung.com/global/</t>
+        </is>
+      </c>
+      <c r="I39" s="76" t="n">
+        <v>4</v>
+      </c>
+      <c r="J39" s="60" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K39" s="60" t="inlineStr">
+        <is>
+          <t>Official company newsroom.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="36" customHeight="1">
+      <c r="A40" s="60" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B40" s="60" t="inlineStr">
+        <is>
+          <t>EU &amp; Europe</t>
+        </is>
+      </c>
+      <c r="C40" s="60" t="inlineStr">
+        <is>
+          <t>International / France</t>
+        </is>
+      </c>
+      <c r="D40" s="60" t="inlineStr">
         <is>
           <t>Fusion energy</t>
         </is>
       </c>
-      <c r="E37" s="60" t="inlineStr">
+      <c r="E40" s="60" t="inlineStr">
+        <is>
+          <t>ITER News</t>
+        </is>
+      </c>
+      <c r="F40" s="60" t="inlineStr">
+        <is>
+          <t>ITER Organization</t>
+        </is>
+      </c>
+      <c r="G40" s="60" t="inlineStr">
+        <is>
+          <t>https://www.iter.org/news</t>
+        </is>
+      </c>
+      <c r="H40" s="60" t="inlineStr">
+        <is>
+          <t>https://www.iter.org/news</t>
+        </is>
+      </c>
+      <c r="I40" s="76" t="n">
+        <v>5</v>
+      </c>
+      <c r="J40" s="60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K40" s="60" t="inlineStr">
+        <is>
+          <t>Official international fusion project; official listing-page fallback.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="36" customHeight="1">
+      <c r="A41" s="60" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B41" s="60" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C41" s="60" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="D41" s="60" t="inlineStr">
+        <is>
+          <t>Fusion energy</t>
+        </is>
+      </c>
+      <c r="E41" s="60" t="inlineStr">
         <is>
           <t>Fusion Industry Association</t>
         </is>
       </c>
-      <c r="F37" s="60" t="inlineStr">
+      <c r="F41" s="60" t="inlineStr">
         <is>
           <t>Fusion Industry Association</t>
         </is>
       </c>
-      <c r="G37" s="60" t="inlineStr">
+      <c r="G41" s="60" t="inlineStr">
         <is>
           <t>https://www.fusionindustryassociation.org/feed/</t>
         </is>
       </c>
-      <c r="H37" s="60" t="inlineStr">
+      <c r="H41" s="60" t="inlineStr">
         <is>
           <t>https://www.fusionindustryassociation.org/</t>
         </is>
       </c>
-      <c r="I37" s="76" t="n">
+      <c r="I41" s="76" t="n">
         <v>3</v>
       </c>
-      <c r="J37" s="60" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K37" s="60" t="inlineStr">
+      <c r="J41" s="60" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K41" s="60" t="inlineStr">
         <is>
           <t>Established industry association; company claims are clearly labeled by source.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:K37"/>
+  <autoFilter ref="A3:K41"/>
   <mergeCells count="2">
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A1:K1"/>
@@ -7114,10 +6326,18 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H36" r:id="rId66"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G37" r:id="rId67"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H37" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G38" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H38" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G39" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H39" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G40" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H40" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G41" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H41" r:id="rId76"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId69"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId77"/>
   </tableParts>
 </worksheet>
 </file>
@@ -7128,7 +6348,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7207,26 +6427,26 @@
     <row r="4" ht="42" customHeight="1">
       <c r="A4" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:13:43+09:00</t>
+          <t>2026-07-26T20:19:15+09:00</t>
         </is>
       </c>
       <c r="B4" s="77" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C4" s="77" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D4" s="77" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E4" s="77" t="n">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="F4" s="77" t="n">
         <v>10</v>
       </c>
       <c r="G4" s="77" t="n">
-        <v>162.46</v>
+        <v>134.05</v>
       </c>
       <c r="H4" s="60" t="inlineStr">
         <is>
@@ -7237,7 +6457,7 @@
     <row r="5">
       <c r="A5" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:00:03+09:00</t>
+          <t>2026-07-26T20:13:43+09:00</t>
         </is>
       </c>
       <c r="B5" s="77" t="n">
@@ -7247,16 +6467,16 @@
         <v>24</v>
       </c>
       <c r="D5" s="77" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E5" s="77" t="n">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="F5" s="77" t="n">
         <v>10</v>
       </c>
       <c r="G5" s="77" t="n">
-        <v>154.27</v>
+        <v>162.46</v>
       </c>
       <c r="H5" s="60" t="inlineStr">
         <is>
@@ -7267,7 +6487,7 @@
     <row r="6">
       <c r="A6" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:51:39+09:00</t>
+          <t>2026-07-26T20:00:03+09:00</t>
         </is>
       </c>
       <c r="B6" s="77" t="n">
@@ -7277,16 +6497,16 @@
         <v>24</v>
       </c>
       <c r="D6" s="77" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E6" s="77" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="F6" s="77" t="n">
         <v>10</v>
       </c>
       <c r="G6" s="77" t="n">
-        <v>11.55</v>
+        <v>154.27</v>
       </c>
       <c r="H6" s="60" t="inlineStr">
         <is>
@@ -7297,26 +6517,26 @@
     <row r="7">
       <c r="A7" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:10:55+09:00</t>
+          <t>2026-07-26T19:51:39+09:00</t>
         </is>
       </c>
       <c r="B7" s="77" t="n">
         <v>34</v>
       </c>
       <c r="C7" s="77" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D7" s="77" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E7" s="77" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F7" s="77" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G7" s="77" t="n">
-        <v>194.65</v>
+        <v>11.55</v>
       </c>
       <c r="H7" s="60" t="inlineStr">
         <is>
@@ -7327,26 +6547,26 @@
     <row r="8">
       <c r="A8" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:05:06+09:00</t>
+          <t>2026-07-26T19:10:55+09:00</t>
         </is>
       </c>
       <c r="B8" s="77" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C8" s="77" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D8" s="77" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E8" s="77" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="F8" s="77" t="n">
         <v>9</v>
       </c>
       <c r="G8" s="77" t="n">
-        <v>165.89</v>
+        <v>194.65</v>
       </c>
       <c r="H8" s="60" t="inlineStr">
         <is>
@@ -7357,35 +6577,65 @@
     <row r="9">
       <c r="A9" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T19:05:06+09:00</t>
         </is>
       </c>
       <c r="B9" s="77" t="n">
         <v>33</v>
       </c>
       <c r="C9" s="77" t="n">
+        <v>24</v>
+      </c>
+      <c r="D9" s="77" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" s="77" t="n">
+        <v>39</v>
+      </c>
+      <c r="F9" s="77" t="n">
+        <v>9</v>
+      </c>
+      <c r="G9" s="77" t="n">
+        <v>165.89</v>
+      </c>
+      <c r="H9" s="60" t="inlineStr">
+        <is>
+          <t>Daily update</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T18:56:03+09:00</t>
+        </is>
+      </c>
+      <c r="B10" s="77" t="n">
+        <v>33</v>
+      </c>
+      <c r="C10" s="77" t="n">
         <v>20</v>
       </c>
-      <c r="D9" s="77" t="n">
+      <c r="D10" s="77" t="n">
         <v>94</v>
       </c>
-      <c r="E9" s="77" t="n">
+      <c r="E10" s="77" t="n">
         <v>0</v>
       </c>
-      <c r="F9" s="77" t="n">
+      <c r="F10" s="77" t="n">
         <v>13</v>
       </c>
-      <c r="G9" s="77" t="n">
+      <c r="G10" s="77" t="n">
         <v>129.43</v>
       </c>
-      <c r="H9" s="60" t="inlineStr">
+      <c r="H10" s="60" t="inlineStr">
         <is>
           <t>Initial lookback</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:H9"/>
+  <autoFilter ref="A3:H10"/>
   <mergeCells count="2">
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>

--- a/docs/innovation_news_ledger.xlsx
+++ b/docs/innovation_news_ledger.xlsx
@@ -9,9 +9,9 @@
     <sheet name="Run Log" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'News Ledger'!$A$3:$O$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'News Ledger'!$A$3:$O$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Source Registry'!$A$3:$K$41</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Run Log'!$A$3:$H$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Run Log'!$A$3:$H$11</definedName>
   </definedNames>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -472,7 +472,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="NewsLedgerTable" displayName="NewsLedgerTable" ref="A3:O42" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="NewsLedgerTable" displayName="NewsLedgerTable" ref="A3:O17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <autoFilter ref="A3:O4"/>
   <tableColumns count="15">
     <tableColumn id="1" name="Collected At (JST)"/>
@@ -516,7 +516,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="RunLogTable" displayName="RunLogTable" ref="A3:H10" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="RunLogTable" displayName="RunLogTable" ref="A3:H11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <autoFilter ref="A3:H4"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Run Time (JST)"/>
@@ -800,7 +800,7 @@
       </c>
       <c r="B5" s="25" t="inlineStr">
         <is>
-          <t>2026-07-26T20:19:15+09:00</t>
+          <t>2026-07-26T20:24:57+09:00</t>
         </is>
       </c>
       <c r="C5" s="46" t="n"/>
@@ -1088,7 +1088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O42"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1282,70 +1282,74 @@
           <t>New</t>
         </is>
       </c>
-      <c r="O4" s="60" t="inlineStr"/>
+      <c r="O4" s="60" t="inlineStr">
+        <is>
+          <t>焦点: メモリおよびファウンドリ技術</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="42" customHeight="1">
       <c r="A5" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:19:15+09:00</t>
+          <t>2026-07-26T18:56:03+09:00</t>
         </is>
       </c>
       <c r="B5" s="75" t="inlineStr">
         <is>
-          <t>2026-07-24T19:55:05Z</t>
+          <t>2026-07-24T16:46:59Z</t>
         </is>
       </c>
       <c r="C5" s="60" t="inlineStr">
         <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D5" s="60" t="inlineStr">
+        <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="D5" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
       <c r="E5" s="60" t="inlineStr">
         <is>
-          <t>Innovation Policy</t>
+          <t>Semiconductors &amp; Telecom</t>
         </is>
       </c>
       <c r="F5" s="76" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G5" s="60" t="inlineStr">
         <is>
-          <t>Major Media</t>
+          <t>Official Company</t>
         </is>
       </c>
       <c r="H5" s="60" t="inlineStr">
         <is>
-          <t>The New York Times Science</t>
+          <t>Intel Newsroom</t>
         </is>
       </c>
       <c r="I5" s="60" t="inlineStr">
         <is>
-          <t>What to Know About Peptides the FDA Is Considering for Use</t>
+          <t>インテルとレンズテクノロジー、AI時代の先進半導体パッケージングを実現するために協力</t>
         </is>
       </c>
       <c r="J5" s="60" t="inlineStr">
         <is>
-          <t>The agency is considering whether compounding pharmacies should be allowed to produce BPC-157, TB-500 and other previously banned peptides.</t>
+          <t>インテルとレンズテクノロジーが、AI時代に向けた先進的な半導体パッケージング技術の開発を目指す戦略的コラボレーションを発表した。</t>
         </is>
       </c>
       <c r="K5" s="60" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/07/23/well/peptides-fda-research.html</t>
+          <t>https://newsroom.intel.com/new-technologies/intel-and-lens-technology-collaborate-to-enable-advanced-semiconductor-packaging-for-the-ai-era</t>
         </is>
       </c>
       <c r="L5" s="60" t="inlineStr">
         <is>
-          <t>2a99e80e122a0e1b78658c57</t>
+          <t>10eedf14d7d6b636e24e447d</t>
         </is>
       </c>
       <c r="M5" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:19:15+09:00</t>
+          <t>2026-07-26T18:56:03+09:00</t>
         </is>
       </c>
       <c r="N5" s="60" t="inlineStr">
@@ -1353,70 +1357,70 @@
           <t>New</t>
         </is>
       </c>
-      <c r="O5" s="60" t="inlineStr"/>
+      <c r="O5" s="60" t="inlineStr">
+        <is>
+          <t>枠: Technology Innovation / 焦点: 先進半導体パッケージング技術</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="42" customHeight="1">
       <c r="A6" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T20:24:57+09:00</t>
         </is>
       </c>
       <c r="B6" s="75" t="inlineStr">
         <is>
-          <t>2026-07-24T16:46:59Z</t>
+          <t>2026-07-24T15:25:30Z</t>
         </is>
       </c>
       <c r="C6" s="60" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>EU &amp; Europe</t>
         </is>
       </c>
       <c r="D6" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E6" s="60" t="inlineStr">
-        <is>
-          <t>Semiconductors &amp; Telecom</t>
-        </is>
-      </c>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="E6" s="60" t="inlineStr"/>
       <c r="F6" s="76" t="n">
         <v>3</v>
       </c>
       <c r="G6" s="60" t="inlineStr">
         <is>
-          <t>Official Company</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H6" s="60" t="inlineStr">
         <is>
-          <t>Intel Newsroom</t>
+          <t>UK DSIT</t>
         </is>
       </c>
       <c r="I6" s="60" t="inlineStr">
         <is>
-          <t>インテルとレンズテクノロジー、AI時代の先進半導体パッケージングを実現するために協力</t>
+          <t>Guidance: Cyber Resilience Pledge - list of signatories</t>
         </is>
       </c>
       <c r="J6" s="60" t="inlineStr">
         <is>
-          <t>インテルとレンズテクノロジーは、ガラス基板を用いた先進半導体パッケージング技術の開発を加速するための戦略的協力を発表しました。これにより、性能向上や相互接続密度の増加が期待されています。</t>
+          <t>Organisations that have signed the Cyber Resilience Pledge.</t>
         </is>
       </c>
       <c r="K6" s="60" t="inlineStr">
         <is>
-          <t>https://newsroom.intel.com/new-technologies/intel-and-lens-technology-collaborate-to-enable-advanced-semiconductor-packaging-for-the-ai-era</t>
+          <t>https://www.gov.uk/government/publications/cyber-resilience-pledge-list-of-signatories</t>
         </is>
       </c>
       <c r="L6" s="60" t="inlineStr">
         <is>
-          <t>10eedf14d7d6b636e24e447d</t>
+          <t>556f1cad5674dfe48a261c54</t>
         </is>
       </c>
       <c r="M6" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T20:24:57+09:00</t>
         </is>
       </c>
       <c r="N6" s="60" t="inlineStr">
@@ -1424,22 +1428,26 @@
           <t>New</t>
         </is>
       </c>
-      <c r="O6" s="60" t="inlineStr"/>
+      <c r="O6" s="60" t="inlineStr">
+        <is>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="42" customHeight="1">
       <c r="A7" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:19:15+09:00</t>
+          <t>2026-07-26T20:24:57+09:00</t>
         </is>
       </c>
       <c r="B7" s="75" t="inlineStr">
         <is>
-          <t>2026-07-24T14:46:32Z</t>
+          <t>2026-07-23T16:58:28Z</t>
         </is>
       </c>
       <c r="C7" s="60" t="inlineStr">
         <is>
-          <t>EU &amp; Europe</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D7" s="60" t="inlineStr">
@@ -1449,7 +1457,7 @@
       </c>
       <c r="E7" s="60" t="inlineStr">
         <is>
-          <t>Fusion Energy</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="F7" s="76" t="n">
@@ -1462,32 +1470,32 @@
       </c>
       <c r="H7" s="60" t="inlineStr">
         <is>
-          <t>The New York Times Science</t>
+          <t>MIT Technology Review</t>
         </is>
       </c>
       <c r="I7" s="60" t="inlineStr">
         <is>
-          <t>Life of Alan Turing Emerges in Richer Detail From Short Story</t>
+          <t>超冷却された腎臓が豚に移植される</t>
         </is>
       </c>
       <c r="J7" s="60" t="inlineStr">
         <is>
-          <t>A Cambridge professor has transcribed a handwritten story that the famous mathematician wrote in the year before his death, presenting a different side of him.</t>
+          <t>臓器移植において、超冷却された腎臓が豚に移植されるという重要な成果が報告されている。</t>
         </is>
       </c>
       <c r="K7" s="60" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/07/24/world/europe/alan-turing-short-story-cambridge.html</t>
+          <t>https://www.technologyreview.com/2026/07/23/1140765/supercooled-kidneys-have-been-transplanted-into-pigs-in-a-landmark-achievement/</t>
         </is>
       </c>
       <c r="L7" s="60" t="inlineStr">
         <is>
-          <t>72af9a1d3b7d7274dd0ca533</t>
+          <t>590a8cbd726d99d379ccecb1</t>
         </is>
       </c>
       <c r="M7" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:19:15+09:00</t>
+          <t>2026-07-26T20:24:57+09:00</t>
         </is>
       </c>
       <c r="N7" s="60" t="inlineStr">
@@ -1495,17 +1503,21 @@
           <t>New</t>
         </is>
       </c>
-      <c r="O7" s="60" t="inlineStr"/>
+      <c r="O7" s="60" t="inlineStr">
+        <is>
+          <t>枠: Technology Innovation / 焦点: 臓器移植技術</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="42" customHeight="1">
       <c r="A8" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:19:15+09:00</t>
+          <t>2026-07-26T20:24:57+09:00</t>
         </is>
       </c>
       <c r="B8" s="75" t="inlineStr">
         <is>
-          <t>2026-07-24T14:25:17Z</t>
+          <t>2026-07-23T12:30:11Z</t>
         </is>
       </c>
       <c r="C8" s="60" t="inlineStr">
@@ -1515,16 +1527,16 @@
       </c>
       <c r="D8" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="E8" s="60" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="F8" s="76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" s="60" t="inlineStr">
         <is>
@@ -1533,32 +1545,32 @@
       </c>
       <c r="H8" s="60" t="inlineStr">
         <is>
-          <t>The New York Times Science</t>
+          <t>South China Morning Post Technology</t>
         </is>
       </c>
       <c r="I8" s="60" t="inlineStr">
         <is>
-          <t>Health Care Agency Discontinues Dozens of Active Research Awards</t>
+          <t>米国の主張に対抗するAI専門家たち</t>
         </is>
       </c>
       <c r="J8" s="60" t="inlineStr">
         <is>
-          <t>The Agency for Healthcare Research and Quality slowed the awarding of new grants last year. Now it is stopping existing ones.</t>
+          <t>AIコミュニティが米国政府の知的財産権に関する主張に反論し、AIモデルの出力が著作権で保護されないことを指摘している。</t>
         </is>
       </c>
       <c r="K8" s="60" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/07/23/science/health-research-funding-ahrq.html</t>
+          <t>https://www.scmp.com/tech/tech-war/article/3361625/global-ai-experts-push-back-us-distillation-claims-against-moonshots-kimi-k3-model?utm_source=rss_feed</t>
         </is>
       </c>
       <c r="L8" s="60" t="inlineStr">
         <is>
-          <t>35ca7b9882d04ac7b97464b0</t>
+          <t>1ab937d4b6a64131b0a68bfc</t>
         </is>
       </c>
       <c r="M8" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:19:15+09:00</t>
+          <t>2026-07-26T20:24:57+09:00</t>
         </is>
       </c>
       <c r="N8" s="60" t="inlineStr">
@@ -1566,17 +1578,21 @@
           <t>New</t>
         </is>
       </c>
-      <c r="O8" s="60" t="inlineStr"/>
+      <c r="O8" s="60" t="inlineStr">
+        <is>
+          <t>枠: Innovation Policy / 政策分野: Patents &amp; Intellectual Property / 焦点: AIモデルの知的財産権</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="42" customHeight="1">
       <c r="A9" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:19:15+09:00</t>
+          <t>2026-07-26T20:13:43+09:00</t>
         </is>
       </c>
       <c r="B9" s="75" t="inlineStr">
         <is>
-          <t>2026-07-24T14:08:05Z</t>
+          <t>2026-07-23T11:30:07Z</t>
         </is>
       </c>
       <c r="C9" s="60" t="inlineStr">
@@ -1586,16 +1602,16 @@
       </c>
       <c r="D9" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="E9" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Robotics | Innovation Policy</t>
         </is>
       </c>
       <c r="F9" s="76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G9" s="60" t="inlineStr">
         <is>
@@ -1604,32 +1620,32 @@
       </c>
       <c r="H9" s="60" t="inlineStr">
         <is>
-          <t>The New York Times Technology</t>
+          <t>South China Morning Post Technology</t>
         </is>
       </c>
       <c r="I9" s="60" t="inlineStr">
         <is>
-          <t>An A.I. Music F.A.Q.: Can I Remix Madonna? Is This All Legal?</t>
+          <t>米国、中国製ヒューマノイドロボットの禁止を検討</t>
         </is>
       </c>
       <c r="J9" s="60" t="inlineStr">
         <is>
-          <t>Advances in A.I. are making it possible to create all kinds of music from scratch, but they also raise questions about what is legal and who will actually listen.</t>
+          <t>米国の議会は、中国製のヒューマノイドロボットの軍事利用を禁止する防衛法案を進めており、国家安全保障やデータプライバシーの懸念から外国の自律システムの使用を制限する内容が含まれている。</t>
         </is>
       </c>
       <c r="K9" s="60" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/07/24/arts/music/ai-music-faq.html</t>
+          <t>https://www.scmp.com/tech/policy/article/3361622/us-eyes-ban-chinese-humanoid-robots-us-china-tech-rivalry-intensifies?utm_source=rss_feed</t>
         </is>
       </c>
       <c r="L9" s="60" t="inlineStr">
         <is>
-          <t>7de4799418b19aa7b1ed024c</t>
+          <t>17c856708cfe91897e9a7d7c</t>
         </is>
       </c>
       <c r="M9" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:19:15+09:00</t>
+          <t>2026-07-26T20:13:43+09:00</t>
         </is>
       </c>
       <c r="N9" s="60" t="inlineStr">
@@ -1642,22 +1658,22 @@
     <row r="10" ht="42" customHeight="1">
       <c r="A10" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:19:15+09:00</t>
+          <t>2026-07-26T20:24:57+09:00</t>
         </is>
       </c>
       <c r="B10" s="75" t="inlineStr">
         <is>
-          <t>2026-07-24T13:32:42Z</t>
+          <t>2026-07-23T10:00:17Z</t>
         </is>
       </c>
       <c r="C10" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="D10" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="E10" s="60" t="inlineStr">
@@ -1675,32 +1691,32 @@
       </c>
       <c r="H10" s="60" t="inlineStr">
         <is>
-          <t>The New York Times Science</t>
+          <t>South China Morning Post Technology</t>
         </is>
       </c>
       <c r="I10" s="60" t="inlineStr">
         <is>
-          <t>Jacob Tsimerman Lives in Number Theory</t>
+          <t>China’s tech firms turn the global AI boom into opportunity amid fierce rivalry at home</t>
         </is>
       </c>
       <c r="J10" s="60" t="inlineStr">
         <is>
-          <t>Dr. Tsimerman won one of four Fields Medals, an award for top mathematicians under 40, for his work on the André-Oort conjecture, but is now changing his focus to artificial intelligence.</t>
+          <t>Driven by a global surge in AI spending and fierce competition at home, Chinese tech companies are rapidly expanding their international footprint, not just via physical supply chains, but increasingly through cloud-based software and foundation models. The broader push aligns with recent customs data from the first half of 2026 showing a sharp rise in physical tech exports. Integrated-circuit exports nearly doubled in value to US$177.3 billion, a 96 per cent year-on-year surge heavily inflated...</t>
         </is>
       </c>
       <c r="K10" s="60" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/07/23/science/jacob-tsimerman-fields-medal.html</t>
+          <t>https://www.scmp.com/tech/tech-trends/article/3361596/chinas-tech-firms-turn-global-ai-boom-opportunity-amid-fierce-rivalry-home?utm_source=rss_feed</t>
         </is>
       </c>
       <c r="L10" s="60" t="inlineStr">
         <is>
-          <t>7bc77efe108aea824dae5a1b</t>
+          <t>2d5de96218ebc1a4b06e4e7c</t>
         </is>
       </c>
       <c r="M10" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:19:15+09:00</t>
+          <t>2026-07-26T20:24:57+09:00</t>
         </is>
       </c>
       <c r="N10" s="60" t="inlineStr">
@@ -1708,32 +1724,36 @@
           <t>New</t>
         </is>
       </c>
-      <c r="O10" s="60" t="inlineStr"/>
+      <c r="O10" s="60" t="inlineStr">
+        <is>
+          <t>枠: Technology Innovation</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="42" customHeight="1">
       <c r="A11" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:19:15+09:00</t>
+          <t>2026-07-26T20:24:57+09:00</t>
         </is>
       </c>
       <c r="B11" s="75" t="inlineStr">
         <is>
-          <t>2026-07-24T13:29:44Z</t>
+          <t>2026-07-23T02:00:46Z</t>
         </is>
       </c>
       <c r="C11" s="60" t="inlineStr">
         <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="D11" s="60" t="inlineStr">
+        <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="D11" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
       <c r="E11" s="60" t="inlineStr">
         <is>
-          <t>Innovation Policy</t>
+          <t>Semiconductors &amp; Telecom</t>
         </is>
       </c>
       <c r="F11" s="76" t="n">
@@ -1741,37 +1761,37 @@
       </c>
       <c r="G11" s="60" t="inlineStr">
         <is>
-          <t>Major Media</t>
+          <t>Official Company</t>
         </is>
       </c>
       <c r="H11" s="60" t="inlineStr">
         <is>
-          <t>The New York Times Science</t>
+          <t>NVIDIA Blog</t>
         </is>
       </c>
       <c r="I11" s="60" t="inlineStr">
         <is>
-          <t>FDAパネルが4つのペプチドの制限解除を支持</t>
+          <t>NVIDIA AIスーパコンピュータが海軍大学院校で稼働開始</t>
         </is>
       </c>
       <c r="J11" s="60" t="inlineStr">
         <is>
-          <t>FDAのパネルは、3年前に禁止された未承認薬への広範なアクセスを許可することに反対する科学者たちの議論を行った。</t>
+          <t>NVIDIAが海軍大学院校にAIスーパコンピュータを導入し、学生や研究者に強力なAIプラットフォームを提供します。</t>
         </is>
       </c>
       <c r="K11" s="60" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/07/23/health/fda-scientists-rfk-peptides.html</t>
+          <t>https://blogs.nvidia.com/blog/naval-postgraduate-school-dgx-ai-supercomputer/</t>
         </is>
       </c>
       <c r="L11" s="60" t="inlineStr">
         <is>
-          <t>e6017b8b35489923d29a4728</t>
+          <t>c174fc131c4d55cb839833e9</t>
         </is>
       </c>
       <c r="M11" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:19:15+09:00</t>
+          <t>2026-07-26T20:24:57+09:00</t>
         </is>
       </c>
       <c r="N11" s="60" t="inlineStr">
@@ -1779,27 +1799,31 @@
           <t>New</t>
         </is>
       </c>
-      <c r="O11" s="60" t="inlineStr"/>
+      <c r="O11" s="60" t="inlineStr">
+        <is>
+          <t>枠: Technology Innovation / 焦点: NVIDIA DGX GB300システム</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="42" customHeight="1">
       <c r="A12" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:19:15+09:00</t>
+          <t>2026-07-26T20:24:57+09:00</t>
         </is>
       </c>
       <c r="B12" s="75" t="inlineStr">
         <is>
-          <t>2026-07-24T13:00:14Z</t>
+          <t>2026-07-22T14:12:00Z</t>
         </is>
       </c>
       <c r="C12" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D12" s="60" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E12" s="60" t="inlineStr">
@@ -1808,41 +1832,41 @@
         </is>
       </c>
       <c r="F12" s="76" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G12" s="60" t="inlineStr">
         <is>
-          <t>Major Media</t>
+          <t>Policy Institute</t>
         </is>
       </c>
       <c r="H12" s="60" t="inlineStr">
         <is>
-          <t>The Guardian Technology</t>
+          <t>CSET</t>
         </is>
       </c>
       <c r="I12" s="60" t="inlineStr">
         <is>
-          <t>Be skeptical of OpenAI’s rogue hacker agent story | John Thickstun</t>
+          <t>Remarks at the Global Nobel Laureates Assembly on Artificial Intelligence and Nuclear War in Borgo Laudato Si’, Vatican</t>
         </is>
       </c>
       <c r="J12" s="60" t="inlineStr">
         <is>
-          <t>If OpenAI loudly proclaims how dangerous AI is, investors will hear how powerful it is. And who benefits from that? On 14 February 2019, OpenAI announced a language model called GPT-2, the precursor to the models that power modern AI chatbots and agents such as ChatGPT and Claude. But OpenAI declared GPT-2 was too risky to release, citing concerns about safety and abuse. I recall being annoyed at the time that OpenAI would make such a useless announcement: the risks seemed overblown, and without access to the model there wasn’t much for a researcher like me to learn about GPT-2. Continue reading...</t>
+          <t>CSET Senior Fellow Emelia Probasco shares her experience and the remarks she gave at the Global Nobel Laureates Assembly on Artificial Intelligence and Nuclear War, which took place at Borgo Laudato Si’, Vatican. The post Remarks at the Global Nobel Laureates Assembly on Artificial Intelligence and Nuclear War in Borgo Laudato Si’, Vatican appeared first on Center for Security and Emerging Technology .</t>
         </is>
       </c>
       <c r="K12" s="60" t="inlineStr">
         <is>
-          <t>https://www.theguardian.com/technology/2026/jul/24/openai-rogue-hacker</t>
+          <t>https://cset.georgetown.edu/article/remarks-at-the-global-nobel-laureates-assembly-on-artificial-intelligence-and-nuclear-war/</t>
         </is>
       </c>
       <c r="L12" s="60" t="inlineStr">
         <is>
-          <t>ac01b28f85e133214755b7cc</t>
+          <t>863086979e9f7f63c082cb57</t>
         </is>
       </c>
       <c r="M12" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:19:15+09:00</t>
+          <t>2026-07-26T20:24:57+09:00</t>
         </is>
       </c>
       <c r="N12" s="60" t="inlineStr">
@@ -1850,27 +1874,31 @@
           <t>New</t>
         </is>
       </c>
-      <c r="O12" s="60" t="inlineStr"/>
+      <c r="O12" s="60" t="inlineStr">
+        <is>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="42" customHeight="1">
       <c r="A13" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:19:15+09:00</t>
+          <t>2026-07-26T19:05:06+09:00</t>
         </is>
       </c>
       <c r="B13" s="75" t="inlineStr">
         <is>
-          <t>2026-07-24T12:00:14Z</t>
+          <t>2026-07-22T13:53:19Z</t>
         </is>
       </c>
       <c r="C13" s="60" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D13" s="60" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E13" s="60" t="inlineStr">
@@ -1879,41 +1907,41 @@
         </is>
       </c>
       <c r="F13" s="76" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G13" s="60" t="inlineStr">
         <is>
-          <t>Major Media</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H13" s="60" t="inlineStr">
         <is>
-          <t>The Guardian Technology</t>
+          <t>National Science Foundation News</t>
         </is>
       </c>
       <c r="I13" s="60" t="inlineStr">
         <is>
-          <t>Should you use AI for a task? Here’s a simple way to decide | Bruce Schneier</t>
+          <t>NSF長官補のブライアン・ストーンによる声明：ジェネシスミッションを通じてAIの優先事項を進める</t>
         </is>
       </c>
       <c r="J13" s="60" t="inlineStr">
         <is>
-          <t>Sometimes, what matters isn’t your output but what you put into the process. Think of it like work v the gym I teach public policy at the Harvard Kennedy School and the Munk School at the University of Toronto. And it will come as no surprise to you that my students regularly use AI to complete their writing assignments. Doing so is a waste of their tuition money. But if their entire career is going to include AI writing assistants, why shouldn’t they embrace their future? The best way I’ve found to explain the dilemma comes from the AI researcher Daniel Meissler: it’s the difference between work and the gym. Continue reading...</t>
+          <t>米国国立科学財団がホワイトハウスと連携し、AIに関する優先事項を進める取り組みを発表。</t>
         </is>
       </c>
       <c r="K13" s="60" t="inlineStr">
         <is>
-          <t>https://www.theguardian.com/commentisfree/2026/jul/24/should-you-use-ai</t>
+          <t>https://www.nsf.gov/news/statement-nsf-chief-staff-brian-stone-performing-duties-nsf-1</t>
         </is>
       </c>
       <c r="L13" s="60" t="inlineStr">
         <is>
-          <t>d7259db0d54f48b0f5039bb8</t>
+          <t>123e2207578ca69c8f9c00a2</t>
         </is>
       </c>
       <c r="M13" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:19:15+09:00</t>
+          <t>2026-07-26T19:05:06+09:00</t>
         </is>
       </c>
       <c r="N13" s="60" t="inlineStr">
@@ -1921,27 +1949,31 @@
           <t>New</t>
         </is>
       </c>
-      <c r="O13" s="60" t="inlineStr"/>
+      <c r="O13" s="60" t="inlineStr">
+        <is>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 焦点: AIに関する国家戦略の推進</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="42" customHeight="1">
       <c r="A14" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:19:15+09:00</t>
+          <t>2026-07-26T19:05:06+09:00</t>
         </is>
       </c>
       <c r="B14" s="75" t="inlineStr">
         <is>
-          <t>2026-07-24T11:39:05Z</t>
+          <t>2026-07-22T13:53:12Z</t>
         </is>
       </c>
       <c r="C14" s="60" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D14" s="60" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E14" s="60" t="inlineStr">
@@ -1950,41 +1982,41 @@
         </is>
       </c>
       <c r="F14" s="76" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G14" s="60" t="inlineStr">
         <is>
-          <t>Major Media</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H14" s="60" t="inlineStr">
         <is>
-          <t>The National Technology</t>
+          <t>National Science Foundation News</t>
         </is>
       </c>
       <c r="I14" s="60" t="inlineStr">
         <is>
-          <t>Zoom launches live voice translation, with Arabic coming in late 2026</t>
+          <t>新しいNSFイニシアティブがAIを活用した科学的発見のためのデータセットの価値を引き出すことを目指す</t>
         </is>
       </c>
       <c r="J14" s="60" t="inlineStr">
         <is>
-          <t>Zoom Technologies has launched a new live voice translation service, with Arabic support coming in the fourth quarter of this year. Five languages – English, Chinese, French, Japanese and Spanish – will initially be available, the California-based company said. A Zoom representative confirmed to The National that Arabic will be available in the fourth quarter, alongside German, Italian and Portuguese. Zoom launched a version of the service in April, after promoting it at its Zoomtopia conference last September. Using the live voice translation feature requires a Pro, Business, or Enterprise account, the artificial intelligence plug-in ZoomMate, or a stand-alone add-on. Zoom has posted instr…</t>
+          <t>米国国立科学財団がAIを活用した科学的発見を促進するための新しいプログラムを発表し、データセットの価値を引き出すことを目指す。</t>
         </is>
       </c>
       <c r="K14" s="60" t="inlineStr">
         <is>
-          <t>https://www.thenationalnews.com/future/technology/2026/07/24/zoom-launches-live-voice-translation-with-arabic-coming-in-late-2026/</t>
+          <t>https://www.nsf.gov/news/new-nsf-initiative-aims-unlock-dataset-value-ai-enabled</t>
         </is>
       </c>
       <c r="L14" s="60" t="inlineStr">
         <is>
-          <t>9df818f0442aeef1a46447c7</t>
+          <t>dcd819527d9b80141b26bcb8</t>
         </is>
       </c>
       <c r="M14" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:19:15+09:00</t>
+          <t>2026-07-26T19:05:06+09:00</t>
         </is>
       </c>
       <c r="N14" s="60" t="inlineStr">
@@ -1992,70 +2024,74 @@
           <t>New</t>
         </is>
       </c>
-      <c r="O14" s="60" t="inlineStr"/>
+      <c r="O14" s="60" t="inlineStr">
+        <is>
+          <t>枠: Innovation Policy / 政策分野: R&amp;D Funding &amp; Tax Incentives / 焦点: AIを活用した科学的発見のためのデータセットの価値を引き出すプログラム</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="42" customHeight="1">
       <c r="A15" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:19:15+09:00</t>
+          <t>2026-07-26T18:56:03+09:00</t>
         </is>
       </c>
       <c r="B15" s="75" t="inlineStr">
         <is>
-          <t>2026-07-24T11:00:03Z</t>
+          <t>2026-07-21T14:48:28Z</t>
         </is>
       </c>
       <c r="C15" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>EU &amp; Europe</t>
         </is>
       </c>
       <c r="D15" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="E15" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Fusion Energy</t>
         </is>
       </c>
       <c r="F15" s="76" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G15" s="60" t="inlineStr">
         <is>
-          <t>Major Media</t>
+          <t>Industry Association</t>
         </is>
       </c>
       <c r="H15" s="60" t="inlineStr">
         <is>
-          <t>The New York Times Technology</t>
+          <t>Fusion Industry Association</t>
         </is>
       </c>
       <c r="I15" s="60" t="inlineStr">
         <is>
-          <t>OpenAI Models Go Rogue + Kimi K3 Freakout + A.I. Superforecasting</t>
+          <t>EUの核融合資金調達計画を示すFIA</t>
         </is>
       </c>
       <c r="J15" s="60" t="inlineStr">
         <is>
-          <t>“The story that we’re talking about in this segment was science fiction until Tuesday, OK?”</t>
+          <t>核融合産業協会は、商業核融合エネルギーのためのEU資金調達の実用的なロードマップを発表しました。研究から実証、商業展開に至る各段階で必要な資金調達手段の進化が求められています。</t>
         </is>
       </c>
       <c r="K15" s="60" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/07/24/podcasts/hardfork-hugging-face-openai.html</t>
+          <t>https://www.fusionindustryassociation.org/fia-outlines-eu-financing-pathway-for-fusion/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=fia-outlines-eu-financing-pathway-for-fusion</t>
         </is>
       </c>
       <c r="L15" s="60" t="inlineStr">
         <is>
-          <t>1227687d6341c95d9729e93a</t>
+          <t>88af233d904d670250fa5a31</t>
         </is>
       </c>
       <c r="M15" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:19:15+09:00</t>
+          <t>2026-07-26T18:56:03+09:00</t>
         </is>
       </c>
       <c r="N15" s="60" t="inlineStr">
@@ -2068,65 +2104,65 @@
     <row r="16" ht="42" customHeight="1">
       <c r="A16" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:19:15+09:00</t>
+          <t>2026-07-26T18:56:03+09:00</t>
         </is>
       </c>
       <c r="B16" s="75" t="inlineStr">
         <is>
-          <t>2026-07-24T06:30:46Z</t>
+          <t>2026-07-17T18:42:47Z</t>
         </is>
       </c>
       <c r="C16" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>EU &amp; Europe</t>
         </is>
       </c>
       <c r="D16" s="60" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="E16" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Innovation Policy | Fusion Energy</t>
         </is>
       </c>
       <c r="F16" s="76" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G16" s="60" t="inlineStr">
         <is>
-          <t>Major Media</t>
+          <t>Industry Association</t>
         </is>
       </c>
       <c r="H16" s="60" t="inlineStr">
         <is>
-          <t>South China Morning Post Technology</t>
+          <t>Fusion Industry Association</t>
         </is>
       </c>
       <c r="I16" s="60" t="inlineStr">
         <is>
-          <t>China’s Kimi K3 ‘significantly below’ US rivals in hacking power, study shows</t>
+          <t>EUの核融合競争力を確保する必要性に関する論文発表</t>
         </is>
       </c>
       <c r="J16" s="60" t="inlineStr">
         <is>
-          <t>Chinese unicorn Moonshot AI’s Kimi K3 model trails far behind top American rivals in its ability to launch cyberattacks, joint British-US government research shows, challenging Washington’s brewing anxiety over the rapid rise of Chinese open-source artificial intelligence. The model, currently considered China’s most powerful large language model, performs “significantly below the most recent frontier cyber-capable models”, according to a report published on Thursday by the UK Artificial...</t>
+          <t>国際法専門家グループが発表した論文は、ヨーロッパが商業核融合において競争優位を持っているが、それを維持するために今行動する必要があると主張しています。</t>
         </is>
       </c>
       <c r="K16" s="60" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/tech/tech-war/article/3361711/chinas-kimi-k3-significantly-below-us-rivals-hacking-power-uk-us-study-shows?utm_source=rss_feed</t>
+          <t>https://www.fusionindustryassociation.org/international-legal-expert-group-publish-paper-on-the-need-for-the-eu-to-secure-its-competitive-fusion-advantage/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=international-legal-expert-group-publish-paper-on-the-need-for-the-eu-to-secure-its-competitive-fusion-advantage</t>
         </is>
       </c>
       <c r="L16" s="60" t="inlineStr">
         <is>
-          <t>fc39eee8898a984a897b9824</t>
+          <t>7ef6110ab078602757409abf</t>
         </is>
       </c>
       <c r="M16" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:19:15+09:00</t>
+          <t>2026-07-26T18:56:03+09:00</t>
         </is>
       </c>
       <c r="N16" s="60" t="inlineStr">
@@ -2139,65 +2175,65 @@
     <row r="17" ht="42" customHeight="1">
       <c r="A17" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:19:15+09:00</t>
+          <t>2026-07-26T18:56:03+09:00</t>
         </is>
       </c>
       <c r="B17" s="75" t="inlineStr">
         <is>
-          <t>2026-07-23T20:58:35Z</t>
+          <t>2026-07-15T17:47:57Z</t>
         </is>
       </c>
       <c r="C17" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="D17" s="60" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="E17" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Fusion Energy</t>
         </is>
       </c>
       <c r="F17" s="76" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G17" s="60" t="inlineStr">
         <is>
-          <t>Major Media</t>
+          <t>Industry Association</t>
         </is>
       </c>
       <c r="H17" s="60" t="inlineStr">
         <is>
-          <t>BBC Technology</t>
+          <t>Fusion Industry Association</t>
         </is>
       </c>
       <c r="I17" s="60" t="inlineStr">
         <is>
-          <t>Lawmakers push for AI 'kill switch' after OpenAI models go rogue</t>
+          <t>スターロライトエンジンが60.6億円を調達</t>
         </is>
       </c>
       <c r="J17" s="60" t="inlineStr">
         <is>
-          <t>A new bill would let the US government order the shutdown of AI models that pose a public threat.</t>
+          <t>スターロライトエンジンは、FASTの開発を加速するために60.6億円の資金を調達しました。同社は、JT-60SAプログラムや国際的な取り組みを基にしたトカマク型核融合装置を開発しています。</t>
         </is>
       </c>
       <c r="K17" s="60" t="inlineStr">
         <is>
-          <t>https://www.bbc.co.uk/news/articles/cx2vqj2e9x8o?at_medium=RSS&amp;at_campaign=rss</t>
+          <t>https://www.nikkei.com/article/DGXZQOUC152ET0V10C26A7000000/#new_tab?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=starlight-engine-raises-jpy-6-06-billion</t>
         </is>
       </c>
       <c r="L17" s="60" t="inlineStr">
         <is>
-          <t>30744ac6eef4bc37b48358ce</t>
+          <t>2f29b005896c3737ab846738</t>
         </is>
       </c>
       <c r="M17" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:19:15+09:00</t>
+          <t>2026-07-26T18:56:03+09:00</t>
         </is>
       </c>
       <c r="N17" s="60" t="inlineStr">
@@ -2207,1783 +2243,8 @@
       </c>
       <c r="O17" s="60" t="inlineStr"/>
     </row>
-    <row r="18" ht="42" customHeight="1">
-      <c r="A18" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T20:19:15+09:00</t>
-        </is>
-      </c>
-      <c r="B18" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-23T15:27:52Z</t>
-        </is>
-      </c>
-      <c r="C18" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="D18" s="60" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="E18" s="60" t="inlineStr">
-        <is>
-          <t>Artificial Intelligence</t>
-        </is>
-      </c>
-      <c r="F18" s="76" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" s="60" t="inlineStr">
-        <is>
-          <t>Major Media</t>
-        </is>
-      </c>
-      <c r="H18" s="60" t="inlineStr">
-        <is>
-          <t>The Guardian Technology</t>
-        </is>
-      </c>
-      <c r="I18" s="60" t="inlineStr">
-        <is>
-          <t>Elon Musk says he got ‘carried away’ with Trump – but still holds on to contentious political views</t>
-        </is>
-      </c>
-      <c r="J18" s="60" t="inlineStr">
-        <is>
-          <t>In interview, billionaire says instead of running ‘Doge’ he should’ve ‘worked on my companies’ and shares extreme predictions Elon Musk has admitted he became too consumed by politics during his volatile alliance with Donald Trump and his brief appointment as the president’s financial axman, running the so-called “department of government efficiency” (Doge). The world’s richest person, and briefly its first trillionaire after his SpaceX company floated on the New York stock exchange in June, made the confession in a wide-ranging interview with the Economist published on Thursday. He shared his positions on subjects from foreign wars to AI, and made a number of eye-opening predictions for th…</t>
-        </is>
-      </c>
-      <c r="K18" s="60" t="inlineStr">
-        <is>
-          <t>https://www.theguardian.com/technology/2026/jul/23/elon-musk-regret-trump-doge-ai</t>
-        </is>
-      </c>
-      <c r="L18" s="60" t="inlineStr">
-        <is>
-          <t>5ab5ea23fbff158109e679af</t>
-        </is>
-      </c>
-      <c r="M18" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T20:19:15+09:00</t>
-        </is>
-      </c>
-      <c r="N18" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O18" s="60" t="inlineStr"/>
-    </row>
-    <row r="19" ht="42" customHeight="1">
-      <c r="A19" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T20:19:15+09:00</t>
-        </is>
-      </c>
-      <c r="B19" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-23T15:23:13Z</t>
-        </is>
-      </c>
-      <c r="C19" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="D19" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E19" s="60" t="inlineStr">
-        <is>
-          <t>Innovation Policy</t>
-        </is>
-      </c>
-      <c r="F19" s="76" t="n">
-        <v>1</v>
-      </c>
-      <c r="G19" s="60" t="inlineStr">
-        <is>
-          <t>Major Media</t>
-        </is>
-      </c>
-      <c r="H19" s="60" t="inlineStr">
-        <is>
-          <t>The New York Times Technology</t>
-        </is>
-      </c>
-      <c r="I19" s="60" t="inlineStr">
-        <is>
-          <t>Lawsuit Against Meta Over Social Media Addiction Is Dropped</t>
-        </is>
-      </c>
-      <c r="J19" s="60" t="inlineStr">
-        <is>
-          <t>For Meta, the move was a reprieve after it and YouTube were found liable in another case in March of negligence and personal injury for their platforms’ addictive features.</t>
-        </is>
-      </c>
-      <c r="K19" s="60" t="inlineStr">
-        <is>
-          <t>https://www.nytimes.com/2026/07/22/technology/meta-social-media-lawsuit.html</t>
-        </is>
-      </c>
-      <c r="L19" s="60" t="inlineStr">
-        <is>
-          <t>1e298ac58555866955586e90</t>
-        </is>
-      </c>
-      <c r="M19" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T20:19:15+09:00</t>
-        </is>
-      </c>
-      <c r="N19" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O19" s="60" t="inlineStr"/>
-    </row>
-    <row r="20" ht="42" customHeight="1">
-      <c r="A20" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T20:13:43+09:00</t>
-        </is>
-      </c>
-      <c r="B20" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-23T11:30:07Z</t>
-        </is>
-      </c>
-      <c r="C20" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="D20" s="60" t="inlineStr">
-        <is>
-          <t>Hong Kong</t>
-        </is>
-      </c>
-      <c r="E20" s="60" t="inlineStr">
-        <is>
-          <t>Robotics | Innovation Policy</t>
-        </is>
-      </c>
-      <c r="F20" s="76" t="n">
-        <v>2</v>
-      </c>
-      <c r="G20" s="60" t="inlineStr">
-        <is>
-          <t>Major Media</t>
-        </is>
-      </c>
-      <c r="H20" s="60" t="inlineStr">
-        <is>
-          <t>South China Morning Post Technology</t>
-        </is>
-      </c>
-      <c r="I20" s="60" t="inlineStr">
-        <is>
-          <t>米国、中国製ヒューマノイドロボットの禁止を検討</t>
-        </is>
-      </c>
-      <c r="J20" s="60" t="inlineStr">
-        <is>
-          <t>米国の議会は、中国製のヒューマノイドロボットの軍事利用を禁止する防衛法案を進めており、国家安全保障やデータプライバシーの懸念から外国の自律システムの使用を制限する内容が含まれている。</t>
-        </is>
-      </c>
-      <c r="K20" s="60" t="inlineStr">
-        <is>
-          <t>https://www.scmp.com/tech/policy/article/3361622/us-eyes-ban-chinese-humanoid-robots-us-china-tech-rivalry-intensifies?utm_source=rss_feed</t>
-        </is>
-      </c>
-      <c r="L20" s="60" t="inlineStr">
-        <is>
-          <t>17c856708cfe91897e9a7d7c</t>
-        </is>
-      </c>
-      <c r="M20" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T20:13:43+09:00</t>
-        </is>
-      </c>
-      <c r="N20" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O20" s="60" t="inlineStr"/>
-    </row>
-    <row r="21" ht="42" customHeight="1">
-      <c r="A21" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T20:19:15+09:00</t>
-        </is>
-      </c>
-      <c r="B21" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-23T00:43:11Z</t>
-        </is>
-      </c>
-      <c r="C21" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="D21" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E21" s="60" t="inlineStr">
-        <is>
-          <t>Innovation Policy</t>
-        </is>
-      </c>
-      <c r="F21" s="76" t="n">
-        <v>2</v>
-      </c>
-      <c r="G21" s="60" t="inlineStr">
-        <is>
-          <t>Major Media</t>
-        </is>
-      </c>
-      <c r="H21" s="60" t="inlineStr">
-        <is>
-          <t>The New York Times Technology</t>
-        </is>
-      </c>
-      <c r="I21" s="60" t="inlineStr">
-        <is>
-          <t>Clarity Actが大統領の暗号販売禁止を巡る議論に巻き込まれる</t>
-        </is>
-      </c>
-      <c r="J21" s="60" t="inlineStr">
-        <is>
-          <t>暗号産業が推進するClarity Actについて、民主党と共和党が議論を交わしており、上院での投票が近づいている。</t>
-        </is>
-      </c>
-      <c r="K21" s="60" t="inlineStr">
-        <is>
-          <t>https://www.nytimes.com/2026/07/22/technology/crypto-bill-trump.html</t>
-        </is>
-      </c>
-      <c r="L21" s="60" t="inlineStr">
-        <is>
-          <t>3935aad326cb655427958fe7</t>
-        </is>
-      </c>
-      <c r="M21" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T20:19:15+09:00</t>
-        </is>
-      </c>
-      <c r="N21" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O21" s="60" t="inlineStr"/>
-    </row>
-    <row r="22" ht="42" customHeight="1">
-      <c r="A22" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="B22" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-22T14:21:46Z</t>
-        </is>
-      </c>
-      <c r="C22" s="60" t="inlineStr">
-        <is>
-          <t>EU &amp; Europe</t>
-        </is>
-      </c>
-      <c r="D22" s="60" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="E22" s="60" t="inlineStr">
-        <is>
-          <t>Innovation Policy</t>
-        </is>
-      </c>
-      <c r="F22" s="76" t="n">
-        <v>3</v>
-      </c>
-      <c r="G22" s="60" t="inlineStr">
-        <is>
-          <t>Government</t>
-        </is>
-      </c>
-      <c r="H22" s="60" t="inlineStr">
-        <is>
-          <t>UK DSIT</t>
-        </is>
-      </c>
-      <c r="I22" s="60" t="inlineStr">
-        <is>
-          <t>ガイダンス：研究における女性のチャーター</t>
-        </is>
-      </c>
-      <c r="J22" s="60" t="inlineStr">
-        <is>
-          <t>英国の研究システムにおける女性の成果を改善するための自主的な取り組みが発表されました。</t>
-        </is>
-      </c>
-      <c r="K22" s="60" t="inlineStr">
-        <is>
-          <t>https://www.gov.uk/government/publications/women-in-research-charter</t>
-        </is>
-      </c>
-      <c r="L22" s="60" t="inlineStr">
-        <is>
-          <t>1e9fd9033d38bacea37c0f42</t>
-        </is>
-      </c>
-      <c r="M22" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="N22" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O22" s="60" t="inlineStr"/>
-    </row>
-    <row r="23" ht="42" customHeight="1">
-      <c r="A23" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T19:05:06+09:00</t>
-        </is>
-      </c>
-      <c r="B23" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-22T14:12:14Z</t>
-        </is>
-      </c>
-      <c r="C23" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="D23" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E23" s="60" t="inlineStr">
-        <is>
-          <t>Innovation Policy</t>
-        </is>
-      </c>
-      <c r="F23" s="76" t="n">
-        <v>3</v>
-      </c>
-      <c r="G23" s="60" t="inlineStr">
-        <is>
-          <t>Government</t>
-        </is>
-      </c>
-      <c r="H23" s="60" t="inlineStr">
-        <is>
-          <t>DOE Office of Science News</t>
-        </is>
-      </c>
-      <c r="I23" s="60" t="inlineStr">
-        <is>
-          <t>エネルギー長官がAI駆動の科学発見を加速するためのプロジェクトを発表</t>
-        </is>
-      </c>
-      <c r="J23" s="60" t="inlineStr">
-        <is>
-          <t>エネルギー長官が、AI駆動の科学発見を加速するために選定された約300のプロジェクトを発表しました。</t>
-        </is>
-      </c>
-      <c r="K23" s="60" t="inlineStr">
-        <is>
-          <t>https://www.energy.gov/articles/secretary-energy-chris-wright-announces-first-genesis-mission-projects-selected-accelerate</t>
-        </is>
-      </c>
-      <c r="L23" s="60" t="inlineStr">
-        <is>
-          <t>23fa1d6907c14d73ce3a41cd</t>
-        </is>
-      </c>
-      <c r="M23" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T19:05:06+09:00</t>
-        </is>
-      </c>
-      <c r="N23" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O23" s="60" t="inlineStr"/>
-    </row>
-    <row r="24" ht="42" customHeight="1">
-      <c r="A24" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="B24" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-22T13:58:00Z</t>
-        </is>
-      </c>
-      <c r="C24" s="60" t="inlineStr">
-        <is>
-          <t>EU &amp; Europe</t>
-        </is>
-      </c>
-      <c r="D24" s="60" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="E24" s="60" t="inlineStr">
-        <is>
-          <t>Innovation Policy</t>
-        </is>
-      </c>
-      <c r="F24" s="76" t="n">
-        <v>3</v>
-      </c>
-      <c r="G24" s="60" t="inlineStr">
-        <is>
-          <t>Government</t>
-        </is>
-      </c>
-      <c r="H24" s="60" t="inlineStr">
-        <is>
-          <t>UK DSIT</t>
-        </is>
-      </c>
-      <c r="I24" s="60" t="inlineStr">
-        <is>
-          <t>ガイダンス：登録して関心を示す</t>
-        </is>
-      </c>
-      <c r="J24" s="60" t="inlineStr">
-        <is>
-          <t>政府チームが公的相談の回答を分析するためのAIツール「Consult」の利用に関心を示すよう呼びかけています。</t>
-        </is>
-      </c>
-      <c r="K24" s="60" t="inlineStr">
-        <is>
-          <t>https://www.gov.uk/government/publications/consult-register-your-interest</t>
-        </is>
-      </c>
-      <c r="L24" s="60" t="inlineStr">
-        <is>
-          <t>a651f42eb5805e39f03fbebe</t>
-        </is>
-      </c>
-      <c r="M24" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="N24" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O24" s="60" t="inlineStr"/>
-    </row>
-    <row r="25" ht="42" customHeight="1">
-      <c r="A25" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T19:05:06+09:00</t>
-        </is>
-      </c>
-      <c r="B25" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-22T13:53:19Z</t>
-        </is>
-      </c>
-      <c r="C25" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="D25" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E25" s="60" t="inlineStr">
-        <is>
-          <t>Innovation Policy | Artificial Intelligence</t>
-        </is>
-      </c>
-      <c r="F25" s="76" t="n">
-        <v>5</v>
-      </c>
-      <c r="G25" s="60" t="inlineStr">
-        <is>
-          <t>Government</t>
-        </is>
-      </c>
-      <c r="H25" s="60" t="inlineStr">
-        <is>
-          <t>National Science Foundation News</t>
-        </is>
-      </c>
-      <c r="I25" s="60" t="inlineStr">
-        <is>
-          <t>NSFのスタッフ長がAI優先事項を推進する声明を発表</t>
-        </is>
-      </c>
-      <c r="J25" s="60" t="inlineStr">
-        <is>
-          <t>米国国立科学財団は、ホワイトハウスの科学技術政策室やエネルギー省と連携し、AIに関する優先事項を推進することを表明しました。</t>
-        </is>
-      </c>
-      <c r="K25" s="60" t="inlineStr">
-        <is>
-          <t>https://www.nsf.gov/news/statement-nsf-chief-staff-brian-stone-performing-duties-nsf-1</t>
-        </is>
-      </c>
-      <c r="L25" s="60" t="inlineStr">
-        <is>
-          <t>123e2207578ca69c8f9c00a2</t>
-        </is>
-      </c>
-      <c r="M25" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T19:05:06+09:00</t>
-        </is>
-      </c>
-      <c r="N25" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O25" s="60" t="inlineStr"/>
-    </row>
-    <row r="26" ht="42" customHeight="1">
-      <c r="A26" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T19:05:06+09:00</t>
-        </is>
-      </c>
-      <c r="B26" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-22T13:53:12Z</t>
-        </is>
-      </c>
-      <c r="C26" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="D26" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E26" s="60" t="inlineStr">
-        <is>
-          <t>Innovation Policy | Artificial Intelligence</t>
-        </is>
-      </c>
-      <c r="F26" s="76" t="n">
-        <v>4</v>
-      </c>
-      <c r="G26" s="60" t="inlineStr">
-        <is>
-          <t>Government</t>
-        </is>
-      </c>
-      <c r="H26" s="60" t="inlineStr">
-        <is>
-          <t>National Science Foundation News</t>
-        </is>
-      </c>
-      <c r="I26" s="60" t="inlineStr">
-        <is>
-          <t>新しいNSFイニシアティブがAIを活用した科学的発見のためのデータセットの価値を引き出すことを目指す</t>
-        </is>
-      </c>
-      <c r="J26" s="60" t="inlineStr">
-        <is>
-          <t>米国国立科学財団は、AIを活用した科学的発見を促進するための新しいプログラムを発表し、科学コミュニティのデータセットを活用することを目指しています。</t>
-        </is>
-      </c>
-      <c r="K26" s="60" t="inlineStr">
-        <is>
-          <t>https://www.nsf.gov/news/new-nsf-initiative-aims-unlock-dataset-value-ai-enabled</t>
-        </is>
-      </c>
-      <c r="L26" s="60" t="inlineStr">
-        <is>
-          <t>dcd819527d9b80141b26bcb8</t>
-        </is>
-      </c>
-      <c r="M26" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T19:05:06+09:00</t>
-        </is>
-      </c>
-      <c r="N26" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O26" s="60" t="inlineStr"/>
-    </row>
-    <row r="27" ht="42" customHeight="1">
-      <c r="A27" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T19:05:06+09:00</t>
-        </is>
-      </c>
-      <c r="B27" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-22T13:53:06Z</t>
-        </is>
-      </c>
-      <c r="C27" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="D27" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E27" s="60" t="inlineStr">
-        <is>
-          <t>Innovation Policy</t>
-        </is>
-      </c>
-      <c r="F27" s="76" t="n">
-        <v>3</v>
-      </c>
-      <c r="G27" s="60" t="inlineStr">
-        <is>
-          <t>Government</t>
-        </is>
-      </c>
-      <c r="H27" s="60" t="inlineStr">
-        <is>
-          <t>National Science Foundation News</t>
-        </is>
-      </c>
-      <c r="I27" s="60" t="inlineStr">
-        <is>
-          <t>NSFがAI駆動の科学を進めるために8300万ドルの投資を発表</t>
-        </is>
-      </c>
-      <c r="J27" s="60" t="inlineStr">
-        <is>
-          <t>米国国立科学財団は、AI駆動の科学を進めるために8300万ドルの資金を発表し、研究者がデータインフラを利用できるようにすることを目指しています。</t>
-        </is>
-      </c>
-      <c r="K27" s="60" t="inlineStr">
-        <is>
-          <t>https://www.nsf.gov/news/nsf-announces-83m-investment-integrated-data-systems</t>
-        </is>
-      </c>
-      <c r="L27" s="60" t="inlineStr">
-        <is>
-          <t>018d40b7e6eb7aa4b8cfb5fa</t>
-        </is>
-      </c>
-      <c r="M27" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T19:05:06+09:00</t>
-        </is>
-      </c>
-      <c r="N27" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O27" s="60" t="inlineStr"/>
-    </row>
-    <row r="28" ht="42" customHeight="1">
-      <c r="A28" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="B28" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-22T12:00:00Z</t>
-        </is>
-      </c>
-      <c r="C28" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="D28" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E28" s="60" t="inlineStr">
-        <is>
-          <t>Innovation Policy</t>
-        </is>
-      </c>
-      <c r="F28" s="76" t="n">
-        <v>5</v>
-      </c>
-      <c r="G28" s="60" t="inlineStr">
-        <is>
-          <t>Government</t>
-        </is>
-      </c>
-      <c r="H28" s="60" t="inlineStr">
-        <is>
-          <t>NIST News</t>
-        </is>
-      </c>
-      <c r="I28" s="60" t="inlineStr">
-        <is>
-          <t>NISTが中小企業製造業者を支援するための資金提供機会を発表</t>
-        </is>
-      </c>
-      <c r="J28" s="60" t="inlineStr">
-        <is>
-          <t>NIST MEPが中小企業製造業者を支援するための資金提供機会についての情報ウェビナーを開催することを発表しました。</t>
-        </is>
-      </c>
-      <c r="K28" s="60" t="inlineStr">
-        <is>
-          <t>https://www.nist.gov/news-events/news/2026/07/nist-announces-funding-opportunity-14-mep-centers-advance-small-and-medium</t>
-        </is>
-      </c>
-      <c r="L28" s="60" t="inlineStr">
-        <is>
-          <t>5aa9c93bc7040291c9f08bfa</t>
-        </is>
-      </c>
-      <c r="M28" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="N28" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O28" s="60" t="inlineStr"/>
-    </row>
-    <row r="29" ht="42" customHeight="1">
-      <c r="A29" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="B29" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-22T12:00:00Z</t>
-        </is>
-      </c>
-      <c r="C29" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="D29" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E29" s="60" t="inlineStr">
-        <is>
-          <t>Artificial Intelligence</t>
-        </is>
-      </c>
-      <c r="F29" s="76" t="n">
-        <v>2</v>
-      </c>
-      <c r="G29" s="60" t="inlineStr">
-        <is>
-          <t>Official Company</t>
-        </is>
-      </c>
-      <c r="H29" s="60" t="inlineStr">
-        <is>
-          <t>OpenAI News</t>
-        </is>
-      </c>
-      <c r="I29" s="60" t="inlineStr">
-        <is>
-          <t>国家科学の次の時代を進める</t>
-        </is>
-      </c>
-      <c r="J29" s="60" t="inlineStr">
-        <is>
-          <t>OpenAIは、米国エネルギー省や国立研究所と協力し、フロンティアAIを活用して発見を加速することにコミットしています。</t>
-        </is>
-      </c>
-      <c r="K29" s="60" t="inlineStr">
-        <is>
-          <t>https://openai.com/index/advancing-the-next-era-of-national-science</t>
-        </is>
-      </c>
-      <c r="L29" s="60" t="inlineStr">
-        <is>
-          <t>577ddf6b90e6d70b43383fc6</t>
-        </is>
-      </c>
-      <c r="M29" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="N29" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O29" s="60" t="inlineStr"/>
-    </row>
-    <row r="30" ht="42" customHeight="1">
-      <c r="A30" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="B30" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-21T19:44:19Z</t>
-        </is>
-      </c>
-      <c r="C30" s="60" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="D30" s="60" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="E30" s="60" t="inlineStr">
-        <is>
-          <t>Innovation Policy | Fusion Energy</t>
-        </is>
-      </c>
-      <c r="F30" s="76" t="n">
-        <v>2</v>
-      </c>
-      <c r="G30" s="60" t="inlineStr">
-        <is>
-          <t>Industry Association</t>
-        </is>
-      </c>
-      <c r="H30" s="60" t="inlineStr">
-        <is>
-          <t>Fusion Industry Association</t>
-        </is>
-      </c>
-      <c r="I30" s="60" t="inlineStr">
-        <is>
-          <t>FIAとクリーンエアタスクフォースがコードと基準に関する原則を発表</t>
-        </is>
-      </c>
-      <c r="J30" s="60" t="inlineStr">
-        <is>
-          <t>FIAとクリーンエアタスクフォースが、核融合の安全な展開を確保しつつ革新を促進するためのコードと基準に関する原則を発表しました。</t>
-        </is>
-      </c>
-      <c r="K30" s="60" t="inlineStr">
-        <is>
-          <t>https://www.fusionindustryassociation.org/fia-and-clean-air-task-force-publish-principles-on-codes-and-standards/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=fia-and-clean-air-task-force-publish-principles-on-codes-and-standards</t>
-        </is>
-      </c>
-      <c r="L30" s="60" t="inlineStr">
-        <is>
-          <t>2366dc909672b56b77a196bd</t>
-        </is>
-      </c>
-      <c r="M30" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="N30" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O30" s="60" t="inlineStr"/>
-    </row>
-    <row r="31" ht="42" customHeight="1">
-      <c r="A31" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="B31" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-21T15:06:31Z</t>
-        </is>
-      </c>
-      <c r="C31" s="60" t="inlineStr">
-        <is>
-          <t>EU &amp; Europe</t>
-        </is>
-      </c>
-      <c r="D31" s="60" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="E31" s="60" t="inlineStr">
-        <is>
-          <t>Innovation Policy</t>
-        </is>
-      </c>
-      <c r="F31" s="76" t="n">
-        <v>5</v>
-      </c>
-      <c r="G31" s="60" t="inlineStr">
-        <is>
-          <t>Government</t>
-        </is>
-      </c>
-      <c r="H31" s="60" t="inlineStr">
-        <is>
-          <t>UK DSIT</t>
-        </is>
-      </c>
-      <c r="I31" s="60" t="inlineStr">
-        <is>
-          <t>TechFirst地域助成金プログラムのガイダンス</t>
-        </is>
-      </c>
-      <c r="J31" s="60" t="inlineStr">
-        <is>
-          <t>TechFirst地域助成金プログラムの詳細が記載されており、デジタルスキルを向上させ、技術職への支援を行います。</t>
-        </is>
-      </c>
-      <c r="K31" s="60" t="inlineStr">
-        <is>
-          <t>https://www.gov.uk/government/publications/techlocal</t>
-        </is>
-      </c>
-      <c r="L31" s="60" t="inlineStr">
-        <is>
-          <t>88893e13a25a6efc42ed57ea</t>
-        </is>
-      </c>
-      <c r="M31" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="N31" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O31" s="60" t="inlineStr"/>
-    </row>
-    <row r="32" ht="42" customHeight="1">
-      <c r="A32" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="B32" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-21T15:05:29Z</t>
-        </is>
-      </c>
-      <c r="C32" s="60" t="inlineStr">
-        <is>
-          <t>EU &amp; Europe</t>
-        </is>
-      </c>
-      <c r="D32" s="60" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="E32" s="60" t="inlineStr">
-        <is>
-          <t>Innovation Policy</t>
-        </is>
-      </c>
-      <c r="F32" s="76" t="n">
-        <v>3</v>
-      </c>
-      <c r="G32" s="60" t="inlineStr">
-        <is>
-          <t>Government</t>
-        </is>
-      </c>
-      <c r="H32" s="60" t="inlineStr">
-        <is>
-          <t>UK DSIT</t>
-        </is>
-      </c>
-      <c r="I32" s="60" t="inlineStr">
-        <is>
-          <t>TechFirst PhDサポート</t>
-        </is>
-      </c>
-      <c r="J32" s="60" t="inlineStr">
-        <is>
-          <t>TechFirstの一環として、英国の急成長する技術セクターへの道を開く政府のスキルプログラムです。</t>
-        </is>
-      </c>
-      <c r="K32" s="60" t="inlineStr">
-        <is>
-          <t>https://www.gov.uk/guidance/techexpert</t>
-        </is>
-      </c>
-      <c r="L32" s="60" t="inlineStr">
-        <is>
-          <t>406416679082f87595cbd50b</t>
-        </is>
-      </c>
-      <c r="M32" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="N32" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O32" s="60" t="inlineStr"/>
-    </row>
-    <row r="33" ht="42" customHeight="1">
-      <c r="A33" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="B33" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-21T15:05:21Z</t>
-        </is>
-      </c>
-      <c r="C33" s="60" t="inlineStr">
-        <is>
-          <t>EU &amp; Europe</t>
-        </is>
-      </c>
-      <c r="D33" s="60" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="E33" s="60" t="inlineStr">
-        <is>
-          <t>Innovation Policy</t>
-        </is>
-      </c>
-      <c r="F33" s="76" t="n">
-        <v>3</v>
-      </c>
-      <c r="G33" s="60" t="inlineStr">
-        <is>
-          <t>Government</t>
-        </is>
-      </c>
-      <c r="H33" s="60" t="inlineStr">
-        <is>
-          <t>UK DSIT</t>
-        </is>
-      </c>
-      <c r="I33" s="60" t="inlineStr">
-        <is>
-          <t>TechFirst：英国の技術スキルプログラム</t>
-        </is>
-      </c>
-      <c r="J33" s="60" t="inlineStr">
-        <is>
-          <t>TechFirstは、英国の急成長する技術セクターへの道を開く政府の主要な技術スキルプログラムであり、全国各地で機会を提供します。</t>
-        </is>
-      </c>
-      <c r="K33" s="60" t="inlineStr">
-        <is>
-          <t>https://www.gov.uk/guidance/techfirst</t>
-        </is>
-      </c>
-      <c r="L33" s="60" t="inlineStr">
-        <is>
-          <t>4ae9e496e9b66c66de074041</t>
-        </is>
-      </c>
-      <c r="M33" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="N33" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O33" s="60" t="inlineStr"/>
-    </row>
-    <row r="34" ht="42" customHeight="1">
-      <c r="A34" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="B34" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-21T15:05:11Z</t>
-        </is>
-      </c>
-      <c r="C34" s="60" t="inlineStr">
-        <is>
-          <t>EU &amp; Europe</t>
-        </is>
-      </c>
-      <c r="D34" s="60" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="E34" s="60" t="inlineStr">
-        <is>
-          <t>Innovation Policy | Semiconductors &amp; Telecom</t>
-        </is>
-      </c>
-      <c r="F34" s="76" t="n">
-        <v>3</v>
-      </c>
-      <c r="G34" s="60" t="inlineStr">
-        <is>
-          <t>Government</t>
-        </is>
-      </c>
-      <c r="H34" s="60" t="inlineStr">
-        <is>
-          <t>UK DSIT</t>
-        </is>
-      </c>
-      <c r="I34" s="60" t="inlineStr">
-        <is>
-          <t>固定通信近代化のための政策文書</t>
-        </is>
-      </c>
-      <c r="J34" s="60" t="inlineStr">
-        <is>
-          <t>この文書は、通信事業者が現在および将来の固定通信の近代化を行う際に従うべきステップを示しています。</t>
-        </is>
-      </c>
-      <c r="K34" s="60" t="inlineStr">
-        <is>
-          <t>https://www.gov.uk/government/publications/fixed-telecoms-modernisation-charter</t>
-        </is>
-      </c>
-      <c r="L34" s="60" t="inlineStr">
-        <is>
-          <t>d5e4431b57fcb4b6271f6c72</t>
-        </is>
-      </c>
-      <c r="M34" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="N34" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O34" s="60" t="inlineStr"/>
-    </row>
-    <row r="35" ht="42" customHeight="1">
-      <c r="A35" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="B35" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-21T14:48:28Z</t>
-        </is>
-      </c>
-      <c r="C35" s="60" t="inlineStr">
-        <is>
-          <t>EU &amp; Europe</t>
-        </is>
-      </c>
-      <c r="D35" s="60" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="E35" s="60" t="inlineStr">
-        <is>
-          <t>Fusion Energy</t>
-        </is>
-      </c>
-      <c r="F35" s="76" t="n">
-        <v>3</v>
-      </c>
-      <c r="G35" s="60" t="inlineStr">
-        <is>
-          <t>Industry Association</t>
-        </is>
-      </c>
-      <c r="H35" s="60" t="inlineStr">
-        <is>
-          <t>Fusion Industry Association</t>
-        </is>
-      </c>
-      <c r="I35" s="60" t="inlineStr">
-        <is>
-          <t>EUの核融合資金調達計画を示すFIA</t>
-        </is>
-      </c>
-      <c r="J35" s="60" t="inlineStr">
-        <is>
-          <t>核融合産業協会は、商業核融合エネルギーのためのEU資金調達の実用的なロードマップを発表しました。研究から実証、商業展開に至る各段階で必要な資金調達手段の進化が求められています。</t>
-        </is>
-      </c>
-      <c r="K35" s="60" t="inlineStr">
-        <is>
-          <t>https://www.fusionindustryassociation.org/fia-outlines-eu-financing-pathway-for-fusion/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=fia-outlines-eu-financing-pathway-for-fusion</t>
-        </is>
-      </c>
-      <c r="L35" s="60" t="inlineStr">
-        <is>
-          <t>88af233d904d670250fa5a31</t>
-        </is>
-      </c>
-      <c r="M35" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="N35" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O35" s="60" t="inlineStr"/>
-    </row>
-    <row r="36" ht="42" customHeight="1">
-      <c r="A36" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="B36" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-18T07:27:54Z</t>
-        </is>
-      </c>
-      <c r="C36" s="60" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="D36" s="60" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="E36" s="60" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-      <c r="F36" s="76" t="n">
-        <v>4</v>
-      </c>
-      <c r="G36" s="60" t="inlineStr">
-        <is>
-          <t>Intergovernmental</t>
-        </is>
-      </c>
-      <c r="H36" s="60" t="inlineStr">
-        <is>
-          <t>WHO News</t>
-        </is>
-      </c>
-      <c r="I36" s="60" t="inlineStr">
-        <is>
-          <t>WHO加盟国が病原体アクセスと利益配分に関する交渉を継続</t>
-        </is>
-      </c>
-      <c r="J36" s="60" t="inlineStr">
-        <is>
-          <t>WHO加盟国は、パンデミック協定の中心要素である病原体アクセスと利益配分に関する交渉を進め、将来のパンデミックに対する迅速かつ効果的な対応を支える枠組みの最終化に向けた議論を行っています。</t>
-        </is>
-      </c>
-      <c r="K36" s="60" t="inlineStr">
-        <is>
-          <t>https://www.who.int/news/item/20-07-2026-who-member-states-continue-negotiations-on-the-pathogen-access-and-benefit-sharing-annex</t>
-        </is>
-      </c>
-      <c r="L36" s="60" t="inlineStr">
-        <is>
-          <t>14dd15caca066d18dfcf2e34</t>
-        </is>
-      </c>
-      <c r="M36" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="N36" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O36" s="60" t="inlineStr"/>
-    </row>
-    <row r="37" ht="42" customHeight="1">
-      <c r="A37" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="B37" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-17T18:42:47Z</t>
-        </is>
-      </c>
-      <c r="C37" s="60" t="inlineStr">
-        <is>
-          <t>EU &amp; Europe</t>
-        </is>
-      </c>
-      <c r="D37" s="60" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="E37" s="60" t="inlineStr">
-        <is>
-          <t>Innovation Policy | Fusion Energy</t>
-        </is>
-      </c>
-      <c r="F37" s="76" t="n">
-        <v>4</v>
-      </c>
-      <c r="G37" s="60" t="inlineStr">
-        <is>
-          <t>Industry Association</t>
-        </is>
-      </c>
-      <c r="H37" s="60" t="inlineStr">
-        <is>
-          <t>Fusion Industry Association</t>
-        </is>
-      </c>
-      <c r="I37" s="60" t="inlineStr">
-        <is>
-          <t>EUの核融合競争力を確保する必要性に関する論文発表</t>
-        </is>
-      </c>
-      <c r="J37" s="60" t="inlineStr">
-        <is>
-          <t>国際法専門家グループが発表した論文は、ヨーロッパが商業核融合において競争優位を持っているが、それを維持するために今行動する必要があると主張しています。</t>
-        </is>
-      </c>
-      <c r="K37" s="60" t="inlineStr">
-        <is>
-          <t>https://www.fusionindustryassociation.org/international-legal-expert-group-publish-paper-on-the-need-for-the-eu-to-secure-its-competitive-fusion-advantage/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=international-legal-expert-group-publish-paper-on-the-need-for-the-eu-to-secure-its-competitive-fusion-advantage</t>
-        </is>
-      </c>
-      <c r="L37" s="60" t="inlineStr">
-        <is>
-          <t>7ef6110ab078602757409abf</t>
-        </is>
-      </c>
-      <c r="M37" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="N37" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O37" s="60" t="inlineStr"/>
-    </row>
-    <row r="38" ht="42" customHeight="1">
-      <c r="A38" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="B38" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-15T17:47:57Z</t>
-        </is>
-      </c>
-      <c r="C38" s="60" t="inlineStr">
-        <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="D38" s="60" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="E38" s="60" t="inlineStr">
-        <is>
-          <t>Fusion Energy</t>
-        </is>
-      </c>
-      <c r="F38" s="76" t="n">
-        <v>3</v>
-      </c>
-      <c r="G38" s="60" t="inlineStr">
-        <is>
-          <t>Industry Association</t>
-        </is>
-      </c>
-      <c r="H38" s="60" t="inlineStr">
-        <is>
-          <t>Fusion Industry Association</t>
-        </is>
-      </c>
-      <c r="I38" s="60" t="inlineStr">
-        <is>
-          <t>スターロライトエンジンが60.6億円を調達</t>
-        </is>
-      </c>
-      <c r="J38" s="60" t="inlineStr">
-        <is>
-          <t>スターロライトエンジンは、FASTの開発を加速するために60.6億円の資金を調達しました。同社は、JT-60SAプログラムや国際的な取り組みを基にしたトカマク型核融合装置を開発しています。</t>
-        </is>
-      </c>
-      <c r="K38" s="60" t="inlineStr">
-        <is>
-          <t>https://www.nikkei.com/article/DGXZQOUC152ET0V10C26A7000000/#new_tab?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=starlight-engine-raises-jpy-6-06-billion</t>
-        </is>
-      </c>
-      <c r="L38" s="60" t="inlineStr">
-        <is>
-          <t>2f29b005896c3737ab846738</t>
-        </is>
-      </c>
-      <c r="M38" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="N38" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O38" s="60" t="inlineStr"/>
-    </row>
-    <row r="39" ht="42" customHeight="1">
-      <c r="A39" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="B39" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-14T12:00:00Z</t>
-        </is>
-      </c>
-      <c r="C39" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="D39" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E39" s="60" t="inlineStr">
-        <is>
-          <t>Innovation Policy</t>
-        </is>
-      </c>
-      <c r="F39" s="76" t="n">
-        <v>4</v>
-      </c>
-      <c r="G39" s="60" t="inlineStr">
-        <is>
-          <t>Government</t>
-        </is>
-      </c>
-      <c r="H39" s="60" t="inlineStr">
-        <is>
-          <t>NIST News</t>
-        </is>
-      </c>
-      <c r="I39" s="60" t="inlineStr">
-        <is>
-          <t>NIST、微生物を殺す給湯器の新特許を取得</t>
-        </is>
-      </c>
-      <c r="J39" s="60" t="inlineStr">
-        <is>
-          <t>家庭の配管内の温水が有害な細菌の繁殖地となる可能性があることから、NISTが新たな特許を取得した。</t>
-        </is>
-      </c>
-      <c r="K39" s="60" t="inlineStr">
-        <is>
-          <t>https://www.nist.gov/news-events/news/2026/07/nist-receives-new-patent-microbe-killing-water-heater</t>
-        </is>
-      </c>
-      <c r="L39" s="60" t="inlineStr">
-        <is>
-          <t>72b002f5a04f35d9ca1e9949</t>
-        </is>
-      </c>
-      <c r="M39" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="N39" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O39" s="60" t="inlineStr"/>
-    </row>
-    <row r="40" ht="42" customHeight="1">
-      <c r="A40" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="B40" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-13T21:00:00Z</t>
-        </is>
-      </c>
-      <c r="C40" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="D40" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E40" s="60" t="inlineStr">
-        <is>
-          <t>Innovation Policy | Artificial Intelligence</t>
-        </is>
-      </c>
-      <c r="F40" s="76" t="n">
-        <v>3</v>
-      </c>
-      <c r="G40" s="60" t="inlineStr">
-        <is>
-          <t>Policy Institute</t>
-        </is>
-      </c>
-      <c r="H40" s="60" t="inlineStr">
-        <is>
-          <t>CSET</t>
-        </is>
-      </c>
-      <c r="I40" s="60" t="inlineStr">
-        <is>
-          <t>米国、中国がAIを米国モデルで訓練するのを阻止しようとする</t>
-        </is>
-      </c>
-      <c r="J40" s="60" t="inlineStr">
-        <is>
-          <t>米国では、中国のAI企業が米国のシステムからの出力を使用してモデルを訓練することに対する懸念が高まっており、知的財産や競争、国家安全保障に関する議論が進んでいる。</t>
-        </is>
-      </c>
-      <c r="K40" s="60" t="inlineStr">
-        <is>
-          <t>https://cset.georgetown.edu/article/washington-is-looking-to-keep-china-from-training-its-ai-on-us-models/</t>
-        </is>
-      </c>
-      <c r="L40" s="60" t="inlineStr">
-        <is>
-          <t>e96177000536ef3f58f8fb3c</t>
-        </is>
-      </c>
-      <c r="M40" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="N40" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O40" s="60" t="inlineStr"/>
-    </row>
-    <row r="41" ht="42" customHeight="1">
-      <c r="A41" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="B41" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-13T12:00:41Z</t>
-        </is>
-      </c>
-      <c r="C41" s="60" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="D41" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E41" s="60" t="inlineStr">
-        <is>
-          <t>Semiconductors &amp; Telecom | Artificial Intelligence</t>
-        </is>
-      </c>
-      <c r="F41" s="76" t="n">
-        <v>3</v>
-      </c>
-      <c r="G41" s="60" t="inlineStr">
-        <is>
-          <t>Official Company</t>
-        </is>
-      </c>
-      <c r="H41" s="60" t="inlineStr">
-        <is>
-          <t>Intel Newsroom</t>
-        </is>
-      </c>
-      <c r="I41" s="60" t="inlineStr">
-        <is>
-          <t>インテル、ヨーロッパでの製造拡大に50億ユーロを投資</t>
-        </is>
-      </c>
-      <c r="J41" s="60" t="inlineStr">
-        <is>
-          <t>インテルはアイルランドのLeixlipキャンパスに50億ユーロを投資し、AIと高性能コンピューティング向けの先進的なシリコンの需要に応えるための製造能力を拡大する。</t>
-        </is>
-      </c>
-      <c r="K41" s="60" t="inlineStr">
-        <is>
-          <t>https://newsroom.intel.com/intel-foundry/intel-invests-5-billion-euro-to-expand-manufacturing-in-europe</t>
-        </is>
-      </c>
-      <c r="L41" s="60" t="inlineStr">
-        <is>
-          <t>297a8b5b279e5916cf45fddb</t>
-        </is>
-      </c>
-      <c r="M41" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="N41" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O41" s="60" t="inlineStr"/>
-    </row>
-    <row r="42" ht="42" customHeight="1">
-      <c r="A42" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="B42" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-12T21:00:00Z</t>
-        </is>
-      </c>
-      <c r="C42" s="60" t="inlineStr">
-        <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="D42" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E42" s="60" t="inlineStr">
-        <is>
-          <t>Artificial Intelligence | Innovation Policy</t>
-        </is>
-      </c>
-      <c r="F42" s="76" t="n">
-        <v>3</v>
-      </c>
-      <c r="G42" s="60" t="inlineStr">
-        <is>
-          <t>Policy Institute</t>
-        </is>
-      </c>
-      <c r="H42" s="60" t="inlineStr">
-        <is>
-          <t>CSET</t>
-        </is>
-      </c>
-      <c r="I42" s="60" t="inlineStr">
-        <is>
-          <t>企業がコスト削減のために中国のAIモデルに注目</t>
-        </is>
-      </c>
-      <c r="J42" s="60" t="inlineStr">
-        <is>
-          <t>企業がコスト削減を目的に中国のAIモデルを採用する動きが広がっており、低コストや改善された能力、オープンウェイトシステムの柔軟性がその要因とされている。</t>
-        </is>
-      </c>
-      <c r="K42" s="60" t="inlineStr">
-        <is>
-          <t>https://cset.georgetown.edu/article/companies-turn-to-chinese-ai-models-to-cut-costs/</t>
-        </is>
-      </c>
-      <c r="L42" s="60" t="inlineStr">
-        <is>
-          <t>9e1bc06c29b61bed048d4f44</t>
-        </is>
-      </c>
-      <c r="M42" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="N42" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O42" s="60" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A3:O42"/>
+  <autoFilter ref="A3:O17"/>
   <mergeCells count="2">
     <mergeCell ref="A1:O1"/>
     <mergeCell ref="A2:O2"/>
@@ -4001,7 +2262,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="N4:N42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="N4:N17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"New,Reviewed,Follow-up,Archived"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4020,35 +2281,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K33" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K35" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K37" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K38" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K39" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K40" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K41" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K42" r:id="rId39"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId40"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId15"/>
   </tableParts>
 </worksheet>
 </file>
@@ -6348,7 +4584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6427,7 +4663,7 @@
     <row r="4" ht="42" customHeight="1">
       <c r="A4" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:19:15+09:00</t>
+          <t>2026-07-26T20:24:57+09:00</t>
         </is>
       </c>
       <c r="B4" s="77" t="n">
@@ -6437,16 +4673,16 @@
         <v>28</v>
       </c>
       <c r="D4" s="77" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E4" s="77" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F4" s="77" t="n">
         <v>10</v>
       </c>
       <c r="G4" s="77" t="n">
-        <v>134.05</v>
+        <v>134.95</v>
       </c>
       <c r="H4" s="60" t="inlineStr">
         <is>
@@ -6457,26 +4693,26 @@
     <row r="5">
       <c r="A5" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:13:43+09:00</t>
+          <t>2026-07-26T20:19:15+09:00</t>
         </is>
       </c>
       <c r="B5" s="77" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C5" s="77" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D5" s="77" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E5" s="77" t="n">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="F5" s="77" t="n">
         <v>10</v>
       </c>
       <c r="G5" s="77" t="n">
-        <v>162.46</v>
+        <v>134.05</v>
       </c>
       <c r="H5" s="60" t="inlineStr">
         <is>
@@ -6487,7 +4723,7 @@
     <row r="6">
       <c r="A6" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:00:03+09:00</t>
+          <t>2026-07-26T20:13:43+09:00</t>
         </is>
       </c>
       <c r="B6" s="77" t="n">
@@ -6497,16 +4733,16 @@
         <v>24</v>
       </c>
       <c r="D6" s="77" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E6" s="77" t="n">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="F6" s="77" t="n">
         <v>10</v>
       </c>
       <c r="G6" s="77" t="n">
-        <v>154.27</v>
+        <v>162.46</v>
       </c>
       <c r="H6" s="60" t="inlineStr">
         <is>
@@ -6517,7 +4753,7 @@
     <row r="7">
       <c r="A7" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:51:39+09:00</t>
+          <t>2026-07-26T20:00:03+09:00</t>
         </is>
       </c>
       <c r="B7" s="77" t="n">
@@ -6527,16 +4763,16 @@
         <v>24</v>
       </c>
       <c r="D7" s="77" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E7" s="77" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="F7" s="77" t="n">
         <v>10</v>
       </c>
       <c r="G7" s="77" t="n">
-        <v>11.55</v>
+        <v>154.27</v>
       </c>
       <c r="H7" s="60" t="inlineStr">
         <is>
@@ -6547,26 +4783,26 @@
     <row r="8">
       <c r="A8" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:10:55+09:00</t>
+          <t>2026-07-26T19:51:39+09:00</t>
         </is>
       </c>
       <c r="B8" s="77" t="n">
         <v>34</v>
       </c>
       <c r="C8" s="77" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D8" s="77" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E8" s="77" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F8" s="77" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G8" s="77" t="n">
-        <v>194.65</v>
+        <v>11.55</v>
       </c>
       <c r="H8" s="60" t="inlineStr">
         <is>
@@ -6577,26 +4813,26 @@
     <row r="9">
       <c r="A9" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:05:06+09:00</t>
+          <t>2026-07-26T19:10:55+09:00</t>
         </is>
       </c>
       <c r="B9" s="77" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C9" s="77" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D9" s="77" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E9" s="77" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="F9" s="77" t="n">
         <v>9</v>
       </c>
       <c r="G9" s="77" t="n">
-        <v>165.89</v>
+        <v>194.65</v>
       </c>
       <c r="H9" s="60" t="inlineStr">
         <is>
@@ -6607,35 +4843,65 @@
     <row r="10">
       <c r="A10" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T19:05:06+09:00</t>
         </is>
       </c>
       <c r="B10" s="77" t="n">
         <v>33</v>
       </c>
       <c r="C10" s="77" t="n">
+        <v>24</v>
+      </c>
+      <c r="D10" s="77" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" s="77" t="n">
+        <v>39</v>
+      </c>
+      <c r="F10" s="77" t="n">
+        <v>9</v>
+      </c>
+      <c r="G10" s="77" t="n">
+        <v>165.89</v>
+      </c>
+      <c r="H10" s="60" t="inlineStr">
+        <is>
+          <t>Daily update</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T18:56:03+09:00</t>
+        </is>
+      </c>
+      <c r="B11" s="77" t="n">
+        <v>33</v>
+      </c>
+      <c r="C11" s="77" t="n">
         <v>20</v>
       </c>
-      <c r="D10" s="77" t="n">
+      <c r="D11" s="77" t="n">
         <v>94</v>
       </c>
-      <c r="E10" s="77" t="n">
+      <c r="E11" s="77" t="n">
         <v>0</v>
       </c>
-      <c r="F10" s="77" t="n">
+      <c r="F11" s="77" t="n">
         <v>13</v>
       </c>
-      <c r="G10" s="77" t="n">
+      <c r="G11" s="77" t="n">
         <v>129.43</v>
       </c>
-      <c r="H10" s="60" t="inlineStr">
+      <c r="H11" s="60" t="inlineStr">
         <is>
           <t>Initial lookback</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:H10"/>
+  <autoFilter ref="A3:H11"/>
   <mergeCells count="2">
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>

--- a/docs/innovation_news_ledger.xlsx
+++ b/docs/innovation_news_ledger.xlsx
@@ -9,9 +9,9 @@
     <sheet name="Run Log" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'News Ledger'!$A$3:$O$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'News Ledger'!$A$3:$O$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Source Registry'!$A$3:$K$41</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Run Log'!$A$3:$H$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Run Log'!$A$3:$H$12</definedName>
   </definedNames>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -472,7 +472,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="NewsLedgerTable" displayName="NewsLedgerTable" ref="A3:O17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="NewsLedgerTable" displayName="NewsLedgerTable" ref="A3:O14" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <autoFilter ref="A3:O4"/>
   <tableColumns count="15">
     <tableColumn id="1" name="Collected At (JST)"/>
@@ -516,7 +516,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="RunLogTable" displayName="RunLogTable" ref="A3:H11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="RunLogTable" displayName="RunLogTable" ref="A3:H12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <autoFilter ref="A3:H4"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Run Time (JST)"/>
@@ -800,7 +800,7 @@
       </c>
       <c r="B5" s="25" t="inlineStr">
         <is>
-          <t>2026-07-26T20:24:57+09:00</t>
+          <t>2026-07-26T20:29:40+09:00</t>
         </is>
       </c>
       <c r="C5" s="46" t="n"/>
@@ -1088,7 +1088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="F4" s="76" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G4" s="60" t="inlineStr">
         <is>
@@ -1254,12 +1254,12 @@
       </c>
       <c r="I4" s="60" t="inlineStr">
         <is>
-          <t>サムスン電子とブロードコム、メモリおよびファウンドリ技術での戦略的協力を拡大</t>
+          <t>サムスン電子とブロードコムがメモリおよびファウンドリ技術での戦略的協力を拡大</t>
         </is>
       </c>
       <c r="J4" s="60" t="inlineStr">
         <is>
-          <t>サムスン電子とブロードコムは、次世代AIインフラを支えるためのメモリおよびファウンドリ技術に関する戦略的協力を拡大するMOUを締結しました。</t>
+          <t>サムスン電子とブロードコムが、次世代のAIインフラを支えるためのメモリおよびファウンドリ技術に関する戦略的協力を拡大することを発表した。</t>
         </is>
       </c>
       <c r="K4" s="60" t="inlineStr">
@@ -1284,24 +1284,24 @@
       </c>
       <c r="O4" s="60" t="inlineStr">
         <is>
-          <t>焦点: メモリおよびファウンドリ技術</t>
+          <t>枠: Technology Innovation / 焦点: メモリおよびファウンドリ技術の協力</t>
         </is>
       </c>
     </row>
     <row r="5" ht="42" customHeight="1">
       <c r="A5" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T20:29:40+09:00</t>
         </is>
       </c>
       <c r="B5" s="75" t="inlineStr">
         <is>
-          <t>2026-07-24T16:46:59Z</t>
+          <t>2026-07-25T00:55:16Z</t>
         </is>
       </c>
       <c r="C5" s="60" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D5" s="60" t="inlineStr">
@@ -1311,45 +1311,45 @@
       </c>
       <c r="E5" s="60" t="inlineStr">
         <is>
-          <t>Semiconductors &amp; Telecom</t>
+          <t>Space</t>
         </is>
       </c>
       <c r="F5" s="76" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G5" s="60" t="inlineStr">
         <is>
-          <t>Official Company</t>
+          <t>Major Media</t>
         </is>
       </c>
       <c r="H5" s="60" t="inlineStr">
         <is>
-          <t>Intel Newsroom</t>
+          <t>The New York Times Science</t>
         </is>
       </c>
       <c r="I5" s="60" t="inlineStr">
         <is>
-          <t>インテルとレンズテクノロジー、AI時代の先進半導体パッケージングを実現するために協力</t>
+          <t>SpaceX、最新のStarship設計で着陸に成功</t>
         </is>
       </c>
       <c r="J5" s="60" t="inlineStr">
         <is>
-          <t>インテルとレンズテクノロジーが、AI時代に向けた先進的な半導体パッケージング技術の開発を目指す戦略的コラボレーションを発表した。</t>
+          <t>SpaceXはStarshipの13回目のテストで成功を収め、NASAの月計画に貢献することが期待されています。</t>
         </is>
       </c>
       <c r="K5" s="60" t="inlineStr">
         <is>
-          <t>https://newsroom.intel.com/new-technologies/intel-and-lens-technology-collaborate-to-enable-advanced-semiconductor-packaging-for-the-ai-era</t>
+          <t>https://www.nytimes.com/2026/07/24/science/spacex-starship-13th-test-flight.html</t>
         </is>
       </c>
       <c r="L5" s="60" t="inlineStr">
         <is>
-          <t>10eedf14d7d6b636e24e447d</t>
+          <t>a3a5c9efad44807da5223756</t>
         </is>
       </c>
       <c r="M5" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T20:29:40+09:00</t>
         </is>
       </c>
       <c r="N5" s="60" t="inlineStr">
@@ -1359,68 +1359,72 @@
       </c>
       <c r="O5" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 焦点: 先進半導体パッケージング技術</t>
+          <t>枠: Technology Innovation / 焦点: SpaceXのStarship設計</t>
         </is>
       </c>
     </row>
     <row r="6" ht="42" customHeight="1">
       <c r="A6" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:24:57+09:00</t>
+          <t>2026-07-26T18:56:03+09:00</t>
         </is>
       </c>
       <c r="B6" s="75" t="inlineStr">
         <is>
-          <t>2026-07-24T15:25:30Z</t>
+          <t>2026-07-24T16:46:59Z</t>
         </is>
       </c>
       <c r="C6" s="60" t="inlineStr">
         <is>
-          <t>EU &amp; Europe</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="D6" s="60" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="E6" s="60" t="inlineStr"/>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E6" s="60" t="inlineStr">
+        <is>
+          <t>Semiconductors &amp; Telecom</t>
+        </is>
+      </c>
       <c r="F6" s="76" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G6" s="60" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Official Company</t>
         </is>
       </c>
       <c r="H6" s="60" t="inlineStr">
         <is>
-          <t>UK DSIT</t>
+          <t>Intel Newsroom</t>
         </is>
       </c>
       <c r="I6" s="60" t="inlineStr">
         <is>
-          <t>Guidance: Cyber Resilience Pledge - list of signatories</t>
+          <t>インテルとレンズテクノロジーがAI時代の先進半導体パッケージングを実現するために協力</t>
         </is>
       </c>
       <c r="J6" s="60" t="inlineStr">
         <is>
-          <t>Organisations that have signed the Cyber Resilience Pledge.</t>
+          <t>インテルとレンズテクノロジーが、AI時代に向けた先進的な半導体パッケージング技術の開発に向けて戦略的な協力を発表した。</t>
         </is>
       </c>
       <c r="K6" s="60" t="inlineStr">
         <is>
-          <t>https://www.gov.uk/government/publications/cyber-resilience-pledge-list-of-signatories</t>
+          <t>https://newsroom.intel.com/new-technologies/intel-and-lens-technology-collaborate-to-enable-advanced-semiconductor-packaging-for-the-ai-era</t>
         </is>
       </c>
       <c r="L6" s="60" t="inlineStr">
         <is>
-          <t>556f1cad5674dfe48a261c54</t>
+          <t>10eedf14d7d6b636e24e447d</t>
         </is>
       </c>
       <c r="M6" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:24:57+09:00</t>
+          <t>2026-07-26T18:56:03+09:00</t>
         </is>
       </c>
       <c r="N6" s="60" t="inlineStr">
@@ -1430,34 +1434,34 @@
       </c>
       <c r="O6" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy</t>
+          <t>枠: Technology Innovation / 焦点: 先進半導体パッケージング技術</t>
         </is>
       </c>
     </row>
     <row r="7" ht="42" customHeight="1">
       <c r="A7" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:24:57+09:00</t>
+          <t>2026-07-26T20:29:40+09:00</t>
         </is>
       </c>
       <c r="B7" s="75" t="inlineStr">
         <is>
-          <t>2026-07-23T16:58:28Z</t>
+          <t>2026-07-24T02:35:52Z</t>
         </is>
       </c>
       <c r="C7" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="D7" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="E7" s="60" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Artificial Intelligence | Robotics</t>
         </is>
       </c>
       <c r="F7" s="76" t="n">
@@ -1470,32 +1474,32 @@
       </c>
       <c r="H7" s="60" t="inlineStr">
         <is>
-          <t>MIT Technology Review</t>
+          <t>South China Morning Post Technology</t>
         </is>
       </c>
       <c r="I7" s="60" t="inlineStr">
         <is>
-          <t>超冷却された腎臓が豚に移植される</t>
+          <t>中国のロボット共働者が増加中。AIコボットに挨拶を</t>
         </is>
       </c>
       <c r="J7" s="60" t="inlineStr">
         <is>
-          <t>臓器移植において、超冷却された腎臓が豚に移植されるという重要な成果が報告されている。</t>
+          <t>中国のヒューマノイドロボットや自動化工場が注目される中、協働ロボット（コボット）が進化している。最新モデルはコーディング知識を必要とせず、自然言語での指示に応じる。</t>
         </is>
       </c>
       <c r="K7" s="60" t="inlineStr">
         <is>
-          <t>https://www.technologyreview.com/2026/07/23/1140765/supercooled-kidneys-have-been-transplanted-into-pigs-in-a-landmark-achievement/</t>
+          <t>https://www.scmp.com/plus/tech/tech-trends/article/3361664/chinese-robot-co-workers-rise-say-hello-ai-cobots?utm_source=rss_feed</t>
         </is>
       </c>
       <c r="L7" s="60" t="inlineStr">
         <is>
-          <t>590a8cbd726d99d379ccecb1</t>
+          <t>00cfbfef6982b98ed0351899</t>
         </is>
       </c>
       <c r="M7" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:24:57+09:00</t>
+          <t>2026-07-26T20:29:40+09:00</t>
         </is>
       </c>
       <c r="N7" s="60" t="inlineStr">
@@ -1505,19 +1509,19 @@
       </c>
       <c r="O7" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 焦点: 臓器移植技術</t>
+          <t>枠: Technology Innovation / 焦点: 協働ロボット（コボット）</t>
         </is>
       </c>
     </row>
     <row r="8" ht="42" customHeight="1">
       <c r="A8" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:24:57+09:00</t>
+          <t>2026-07-26T20:29:40+09:00</t>
         </is>
       </c>
       <c r="B8" s="75" t="inlineStr">
         <is>
-          <t>2026-07-23T12:30:11Z</t>
+          <t>2026-07-23T20:58:35Z</t>
         </is>
       </c>
       <c r="C8" s="60" t="inlineStr">
@@ -1527,7 +1531,7 @@
       </c>
       <c r="D8" s="60" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="E8" s="60" t="inlineStr">
@@ -1545,32 +1549,32 @@
       </c>
       <c r="H8" s="60" t="inlineStr">
         <is>
-          <t>South China Morning Post Technology</t>
+          <t>BBC Technology</t>
         </is>
       </c>
       <c r="I8" s="60" t="inlineStr">
         <is>
-          <t>米国の主張に対抗するAI専門家たち</t>
+          <t>AIモデルのシャットダウンを許可する新法案が提案</t>
         </is>
       </c>
       <c r="J8" s="60" t="inlineStr">
         <is>
-          <t>AIコミュニティが米国政府の知的財産権に関する主張に反論し、AIモデルの出力が著作権で保護されないことを指摘している。</t>
+          <t>新たに提案された法案は、公共の脅威をもたらすAIモデルのシャットダウンを政府に許可する内容である。</t>
         </is>
       </c>
       <c r="K8" s="60" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/tech/tech-war/article/3361625/global-ai-experts-push-back-us-distillation-claims-against-moonshots-kimi-k3-model?utm_source=rss_feed</t>
+          <t>https://www.bbc.co.uk/news/articles/cx2vqj2e9x8o?at_medium=RSS&amp;at_campaign=rss</t>
         </is>
       </c>
       <c r="L8" s="60" t="inlineStr">
         <is>
-          <t>1ab937d4b6a64131b0a68bfc</t>
+          <t>30744ac6eef4bc37b48358ce</t>
         </is>
       </c>
       <c r="M8" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:24:57+09:00</t>
+          <t>2026-07-26T20:29:40+09:00</t>
         </is>
       </c>
       <c r="N8" s="60" t="inlineStr">
@@ -1580,72 +1584,68 @@
       </c>
       <c r="O8" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: Patents &amp; Intellectual Property / 焦点: AIモデルの知的財産権</t>
+          <t>枠: Innovation Policy / 政策分野: Regulation &amp; Governance / 焦点: AIモデルの規制</t>
         </is>
       </c>
     </row>
     <row r="9" ht="42" customHeight="1">
       <c r="A9" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:13:43+09:00</t>
+          <t>2026-07-26T20:29:40+09:00</t>
         </is>
       </c>
       <c r="B9" s="75" t="inlineStr">
         <is>
-          <t>2026-07-23T11:30:07Z</t>
+          <t>2026-07-22T14:21:46Z</t>
         </is>
       </c>
       <c r="C9" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>EU &amp; Europe</t>
         </is>
       </c>
       <c r="D9" s="60" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
-        </is>
-      </c>
-      <c r="E9" s="60" t="inlineStr">
-        <is>
-          <t>Robotics | Innovation Policy</t>
-        </is>
-      </c>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="E9" s="60" t="inlineStr"/>
       <c r="F9" s="76" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G9" s="60" t="inlineStr">
         <is>
-          <t>Major Media</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H9" s="60" t="inlineStr">
         <is>
-          <t>South China Morning Post Technology</t>
+          <t>UK DSIT</t>
         </is>
       </c>
       <c r="I9" s="60" t="inlineStr">
         <is>
-          <t>米国、中国製ヒューマノイドロボットの禁止を検討</t>
+          <t>ガイダンス：研究における女性のためのチャーター</t>
         </is>
       </c>
       <c r="J9" s="60" t="inlineStr">
         <is>
-          <t>米国の議会は、中国製のヒューマノイドロボットの軍事利用を禁止する防衛法案を進めており、国家安全保障やデータプライバシーの懸念から外国の自律システムの使用を制限する内容が含まれている。</t>
+          <t>UKの研究システムにおける女性の成果を改善するための自主的な取り組みが発表された。</t>
         </is>
       </c>
       <c r="K9" s="60" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/tech/policy/article/3361622/us-eyes-ban-chinese-humanoid-robots-us-china-tech-rivalry-intensifies?utm_source=rss_feed</t>
+          <t>https://www.gov.uk/government/publications/women-in-research-charter</t>
         </is>
       </c>
       <c r="L9" s="60" t="inlineStr">
         <is>
-          <t>17c856708cfe91897e9a7d7c</t>
+          <t>1e9fd9033d38bacea37c0f42</t>
         </is>
       </c>
       <c r="M9" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:13:43+09:00</t>
+          <t>2026-07-26T20:29:40+09:00</t>
         </is>
       </c>
       <c r="N9" s="60" t="inlineStr">
@@ -1653,70 +1653,74 @@
           <t>New</t>
         </is>
       </c>
-      <c r="O9" s="60" t="inlineStr"/>
+      <c r="O9" s="60" t="inlineStr">
+        <is>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy | Research System &amp; Talent / 焦点: 女性研究者の成果向上</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="42" customHeight="1">
       <c r="A10" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:24:57+09:00</t>
+          <t>2026-07-26T20:29:40+09:00</t>
         </is>
       </c>
       <c r="B10" s="75" t="inlineStr">
         <is>
-          <t>2026-07-23T10:00:17Z</t>
+          <t>2026-07-22T14:12:14Z</t>
         </is>
       </c>
       <c r="C10" s="60" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D10" s="60" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E10" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="F10" s="76" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G10" s="60" t="inlineStr">
         <is>
-          <t>Major Media</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H10" s="60" t="inlineStr">
         <is>
-          <t>South China Morning Post Technology</t>
+          <t>DOE Office of Science News</t>
         </is>
       </c>
       <c r="I10" s="60" t="inlineStr">
         <is>
-          <t>China’s tech firms turn the global AI boom into opportunity amid fierce rivalry at home</t>
+          <t>エネルギー長官クリス・ライト、AI駆動の科学発見を加速するための初のジェネシスミッションプロジェクトを発表</t>
         </is>
       </c>
       <c r="J10" s="60" t="inlineStr">
         <is>
-          <t>Driven by a global surge in AI spending and fierce competition at home, Chinese tech companies are rapidly expanding their international footprint, not just via physical supply chains, but increasingly through cloud-based software and foundation models. The broader push aligns with recent customs data from the first half of 2026 showing a sharp rise in physical tech exports. Integrated-circuit exports nearly doubled in value to US$177.3 billion, a 96 per cent year-on-year surge heavily inflated...</t>
+          <t>米国エネルギー省がAI駆動の科学発見を加速するために、全米から選ばれたプロジェクトを発表した。</t>
         </is>
       </c>
       <c r="K10" s="60" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/tech/tech-trends/article/3361596/chinas-tech-firms-turn-global-ai-boom-opportunity-amid-fierce-rivalry-home?utm_source=rss_feed</t>
+          <t>https://www.energy.gov/articles/secretary-energy-chris-wright-announces-first-genesis-mission-projects-selected-accelerate</t>
         </is>
       </c>
       <c r="L10" s="60" t="inlineStr">
         <is>
-          <t>2d5de96218ebc1a4b06e4e7c</t>
+          <t>23fa1d6907c14d73ce3a41cd</t>
         </is>
       </c>
       <c r="M10" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:24:57+09:00</t>
+          <t>2026-07-26T20:29:40+09:00</t>
         </is>
       </c>
       <c r="N10" s="60" t="inlineStr">
@@ -1726,24 +1730,24 @@
       </c>
       <c r="O10" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation</t>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 焦点: AI駆動の科学発見プロジェクト</t>
         </is>
       </c>
     </row>
     <row r="11" ht="42" customHeight="1">
       <c r="A11" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:24:57+09:00</t>
+          <t>2026-07-26T19:05:06+09:00</t>
         </is>
       </c>
       <c r="B11" s="75" t="inlineStr">
         <is>
-          <t>2026-07-23T02:00:46Z</t>
+          <t>2026-07-22T13:53:19Z</t>
         </is>
       </c>
       <c r="C11" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D11" s="60" t="inlineStr">
@@ -1753,45 +1757,45 @@
       </c>
       <c r="E11" s="60" t="inlineStr">
         <is>
-          <t>Semiconductors &amp; Telecom</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="F11" s="76" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G11" s="60" t="inlineStr">
         <is>
-          <t>Official Company</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H11" s="60" t="inlineStr">
         <is>
-          <t>NVIDIA Blog</t>
+          <t>National Science Foundation News</t>
         </is>
       </c>
       <c r="I11" s="60" t="inlineStr">
         <is>
-          <t>NVIDIA AIスーパコンピュータが海軍大学院校で稼働開始</t>
+          <t>NSFがAIに関する国家戦略を推進する声明を発表</t>
         </is>
       </c>
       <c r="J11" s="60" t="inlineStr">
         <is>
-          <t>NVIDIAが海軍大学院校にAIスーパコンピュータを導入し、学生や研究者に強力なAIプラットフォームを提供します。</t>
+          <t>米国科学財団（NSF）は、AIに関する国家戦略を推進するための声明を発表しました。</t>
         </is>
       </c>
       <c r="K11" s="60" t="inlineStr">
         <is>
-          <t>https://blogs.nvidia.com/blog/naval-postgraduate-school-dgx-ai-supercomputer/</t>
+          <t>https://www.nsf.gov/news/statement-nsf-chief-staff-brian-stone-performing-duties-nsf-1</t>
         </is>
       </c>
       <c r="L11" s="60" t="inlineStr">
         <is>
-          <t>c174fc131c4d55cb839833e9</t>
+          <t>123e2207578ca69c8f9c00a2</t>
         </is>
       </c>
       <c r="M11" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:24:57+09:00</t>
+          <t>2026-07-26T19:05:06+09:00</t>
         </is>
       </c>
       <c r="N11" s="60" t="inlineStr">
@@ -1801,19 +1805,19 @@
       </c>
       <c r="O11" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 焦点: NVIDIA DGX GB300システム</t>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 焦点: AIに関する国家戦略の推進</t>
         </is>
       </c>
     </row>
     <row r="12" ht="42" customHeight="1">
       <c r="A12" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:24:57+09:00</t>
+          <t>2026-07-26T19:05:06+09:00</t>
         </is>
       </c>
       <c r="B12" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T14:12:00Z</t>
+          <t>2026-07-22T13:53:12Z</t>
         </is>
       </c>
       <c r="C12" s="60" t="inlineStr">
@@ -1832,41 +1836,41 @@
         </is>
       </c>
       <c r="F12" s="76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G12" s="60" t="inlineStr">
         <is>
-          <t>Policy Institute</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H12" s="60" t="inlineStr">
         <is>
-          <t>CSET</t>
+          <t>National Science Foundation News</t>
         </is>
       </c>
       <c r="I12" s="60" t="inlineStr">
         <is>
-          <t>Remarks at the Global Nobel Laureates Assembly on Artificial Intelligence and Nuclear War in Borgo Laudato Si’, Vatican</t>
+          <t>NSFの新しい取り組みがAIによる科学的発見のためのデータセットの価値を引き出す</t>
         </is>
       </c>
       <c r="J12" s="60" t="inlineStr">
         <is>
-          <t>CSET Senior Fellow Emelia Probasco shares her experience and the remarks she gave at the Global Nobel Laureates Assembly on Artificial Intelligence and Nuclear War, which took place at Borgo Laudato Si’, Vatican. The post Remarks at the Global Nobel Laureates Assembly on Artificial Intelligence and Nuclear War in Borgo Laudato Si’, Vatican appeared first on Center for Security and Emerging Technology .</t>
+          <t>米国科学財団（NSF）は、AIを活用した科学的発見のためのデータセットの価値を引き出す新しいプログラムを発表しました。</t>
         </is>
       </c>
       <c r="K12" s="60" t="inlineStr">
         <is>
-          <t>https://cset.georgetown.edu/article/remarks-at-the-global-nobel-laureates-assembly-on-artificial-intelligence-and-nuclear-war/</t>
+          <t>https://www.nsf.gov/news/new-nsf-initiative-aims-unlock-dataset-value-ai-enabled</t>
         </is>
       </c>
       <c r="L12" s="60" t="inlineStr">
         <is>
-          <t>863086979e9f7f63c082cb57</t>
+          <t>dcd819527d9b80141b26bcb8</t>
         </is>
       </c>
       <c r="M12" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:24:57+09:00</t>
+          <t>2026-07-26T19:05:06+09:00</t>
         </is>
       </c>
       <c r="N12" s="60" t="inlineStr">
@@ -1876,19 +1880,19 @@
       </c>
       <c r="O12" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy</t>
+          <t>枠: Innovation Policy / 政策分野: R&amp;D Funding &amp; Tax Incentives / 焦点: AIを活用した科学的発見のためのデータセットの価値を引き出すプログラム</t>
         </is>
       </c>
     </row>
     <row r="13" ht="42" customHeight="1">
       <c r="A13" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:05:06+09:00</t>
+          <t>2026-07-26T20:29:40+09:00</t>
         </is>
       </c>
       <c r="B13" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T13:53:19Z</t>
+          <t>2026-07-22T13:53:06Z</t>
         </is>
       </c>
       <c r="C13" s="60" t="inlineStr">
@@ -1901,13 +1905,9 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="E13" s="60" t="inlineStr">
-        <is>
-          <t>Artificial Intelligence</t>
-        </is>
-      </c>
+      <c r="E13" s="60" t="inlineStr"/>
       <c r="F13" s="76" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G13" s="60" t="inlineStr">
         <is>
@@ -1921,27 +1921,27 @@
       </c>
       <c r="I13" s="60" t="inlineStr">
         <is>
-          <t>NSF長官補のブライアン・ストーンによる声明：ジェネシスミッションを通じてAIの優先事項を進める</t>
+          <t>NSF、AI駆動の科学を進展させるために8300万ドルの投資を発表</t>
         </is>
       </c>
       <c r="J13" s="60" t="inlineStr">
         <is>
-          <t>米国国立科学財団がホワイトハウスと連携し、AIに関する優先事項を進める取り組みを発表。</t>
+          <t>米国科学財団が8300万ドルの資金を通じて、AI駆動の科学を進展させるためのデータシステムとサービスの整備を発表した。</t>
         </is>
       </c>
       <c r="K13" s="60" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/news/statement-nsf-chief-staff-brian-stone-performing-duties-nsf-1</t>
+          <t>https://www.nsf.gov/news/nsf-announces-83m-investment-integrated-data-systems</t>
         </is>
       </c>
       <c r="L13" s="60" t="inlineStr">
         <is>
-          <t>123e2207578ca69c8f9c00a2</t>
+          <t>018d40b7e6eb7aa4b8cfb5fa</t>
         </is>
       </c>
       <c r="M13" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:05:06+09:00</t>
+          <t>2026-07-26T20:29:40+09:00</t>
         </is>
       </c>
       <c r="N13" s="60" t="inlineStr">
@@ -1951,19 +1951,19 @@
       </c>
       <c r="O13" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 焦点: AIに関する国家戦略の推進</t>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy | Research System &amp; Talent / 焦点: AI駆動の科学研究インフラ整備</t>
         </is>
       </c>
     </row>
     <row r="14" ht="42" customHeight="1">
       <c r="A14" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:05:06+09:00</t>
+          <t>2026-07-26T20:29:40+09:00</t>
         </is>
       </c>
       <c r="B14" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T13:53:12Z</t>
+          <t>2026-07-22T12:00:00Z</t>
         </is>
       </c>
       <c r="C14" s="60" t="inlineStr">
@@ -1976,11 +1976,7 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="E14" s="60" t="inlineStr">
-        <is>
-          <t>Artificial Intelligence</t>
-        </is>
-      </c>
+      <c r="E14" s="60" t="inlineStr"/>
       <c r="F14" s="76" t="n">
         <v>4</v>
       </c>
@@ -1991,32 +1987,32 @@
       </c>
       <c r="H14" s="60" t="inlineStr">
         <is>
-          <t>National Science Foundation News</t>
+          <t>NIST News</t>
         </is>
       </c>
       <c r="I14" s="60" t="inlineStr">
         <is>
-          <t>新しいNSFイニシアティブがAIを活用した科学的発見のためのデータセットの価値を引き出すことを目指す</t>
+          <t>NISTが中小企業向けの資金提供機会を発表</t>
         </is>
       </c>
       <c r="J14" s="60" t="inlineStr">
         <is>
-          <t>米国国立科学財団がAIを活用した科学的発見を促進するための新しいプログラムを発表し、データセットの価値を引き出すことを目指す。</t>
+          <t>NIST MEPは、米国の中小企業を支援するための資金提供機会を発表し、2026年7月28日にウェビナーを開催する予定です。</t>
         </is>
       </c>
       <c r="K14" s="60" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/news/new-nsf-initiative-aims-unlock-dataset-value-ai-enabled</t>
+          <t>https://www.nist.gov/news-events/news/2026/07/nist-announces-funding-opportunity-14-mep-centers-advance-small-and-medium</t>
         </is>
       </c>
       <c r="L14" s="60" t="inlineStr">
         <is>
-          <t>dcd819527d9b80141b26bcb8</t>
+          <t>5aa9c93bc7040291c9f08bfa</t>
         </is>
       </c>
       <c r="M14" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:05:06+09:00</t>
+          <t>2026-07-26T20:29:40+09:00</t>
         </is>
       </c>
       <c r="N14" s="60" t="inlineStr">
@@ -2026,225 +2022,12 @@
       </c>
       <c r="O14" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: R&amp;D Funding &amp; Tax Incentives / 焦点: AIを活用した科学的発見のためのデータセットの価値を引き出すプログラム</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="42" customHeight="1">
-      <c r="A15" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="B15" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-21T14:48:28Z</t>
-        </is>
-      </c>
-      <c r="C15" s="60" t="inlineStr">
-        <is>
-          <t>EU &amp; Europe</t>
-        </is>
-      </c>
-      <c r="D15" s="60" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="E15" s="60" t="inlineStr">
-        <is>
-          <t>Fusion Energy</t>
-        </is>
-      </c>
-      <c r="F15" s="76" t="n">
-        <v>3</v>
-      </c>
-      <c r="G15" s="60" t="inlineStr">
-        <is>
-          <t>Industry Association</t>
-        </is>
-      </c>
-      <c r="H15" s="60" t="inlineStr">
-        <is>
-          <t>Fusion Industry Association</t>
-        </is>
-      </c>
-      <c r="I15" s="60" t="inlineStr">
-        <is>
-          <t>EUの核融合資金調達計画を示すFIA</t>
-        </is>
-      </c>
-      <c r="J15" s="60" t="inlineStr">
-        <is>
-          <t>核融合産業協会は、商業核融合エネルギーのためのEU資金調達の実用的なロードマップを発表しました。研究から実証、商業展開に至る各段階で必要な資金調達手段の進化が求められています。</t>
-        </is>
-      </c>
-      <c r="K15" s="60" t="inlineStr">
-        <is>
-          <t>https://www.fusionindustryassociation.org/fia-outlines-eu-financing-pathway-for-fusion/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=fia-outlines-eu-financing-pathway-for-fusion</t>
-        </is>
-      </c>
-      <c r="L15" s="60" t="inlineStr">
-        <is>
-          <t>88af233d904d670250fa5a31</t>
-        </is>
-      </c>
-      <c r="M15" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="N15" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O15" s="60" t="inlineStr"/>
-    </row>
-    <row r="16" ht="42" customHeight="1">
-      <c r="A16" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="B16" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-17T18:42:47Z</t>
-        </is>
-      </c>
-      <c r="C16" s="60" t="inlineStr">
-        <is>
-          <t>EU &amp; Europe</t>
-        </is>
-      </c>
-      <c r="D16" s="60" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="E16" s="60" t="inlineStr">
-        <is>
-          <t>Innovation Policy | Fusion Energy</t>
-        </is>
-      </c>
-      <c r="F16" s="76" t="n">
-        <v>4</v>
-      </c>
-      <c r="G16" s="60" t="inlineStr">
-        <is>
-          <t>Industry Association</t>
-        </is>
-      </c>
-      <c r="H16" s="60" t="inlineStr">
-        <is>
-          <t>Fusion Industry Association</t>
-        </is>
-      </c>
-      <c r="I16" s="60" t="inlineStr">
-        <is>
-          <t>EUの核融合競争力を確保する必要性に関する論文発表</t>
-        </is>
-      </c>
-      <c r="J16" s="60" t="inlineStr">
-        <is>
-          <t>国際法専門家グループが発表した論文は、ヨーロッパが商業核融合において競争優位を持っているが、それを維持するために今行動する必要があると主張しています。</t>
-        </is>
-      </c>
-      <c r="K16" s="60" t="inlineStr">
-        <is>
-          <t>https://www.fusionindustryassociation.org/international-legal-expert-group-publish-paper-on-the-need-for-the-eu-to-secure-its-competitive-fusion-advantage/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=international-legal-expert-group-publish-paper-on-the-need-for-the-eu-to-secure-its-competitive-fusion-advantage</t>
-        </is>
-      </c>
-      <c r="L16" s="60" t="inlineStr">
-        <is>
-          <t>7ef6110ab078602757409abf</t>
-        </is>
-      </c>
-      <c r="M16" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="N16" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O16" s="60" t="inlineStr"/>
-    </row>
-    <row r="17" ht="42" customHeight="1">
-      <c r="A17" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="B17" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-15T17:47:57Z</t>
-        </is>
-      </c>
-      <c r="C17" s="60" t="inlineStr">
-        <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="D17" s="60" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="E17" s="60" t="inlineStr">
-        <is>
-          <t>Fusion Energy</t>
-        </is>
-      </c>
-      <c r="F17" s="76" t="n">
-        <v>3</v>
-      </c>
-      <c r="G17" s="60" t="inlineStr">
-        <is>
-          <t>Industry Association</t>
-        </is>
-      </c>
-      <c r="H17" s="60" t="inlineStr">
-        <is>
-          <t>Fusion Industry Association</t>
-        </is>
-      </c>
-      <c r="I17" s="60" t="inlineStr">
-        <is>
-          <t>スターロライトエンジンが60.6億円を調達</t>
-        </is>
-      </c>
-      <c r="J17" s="60" t="inlineStr">
-        <is>
-          <t>スターロライトエンジンは、FASTの開発を加速するために60.6億円の資金を調達しました。同社は、JT-60SAプログラムや国際的な取り組みを基にしたトカマク型核融合装置を開発しています。</t>
-        </is>
-      </c>
-      <c r="K17" s="60" t="inlineStr">
-        <is>
-          <t>https://www.nikkei.com/article/DGXZQOUC152ET0V10C26A7000000/#new_tab?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=starlight-engine-raises-jpy-6-06-billion</t>
-        </is>
-      </c>
-      <c r="L17" s="60" t="inlineStr">
-        <is>
-          <t>2f29b005896c3737ab846738</t>
-        </is>
-      </c>
-      <c r="M17" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:56:03+09:00</t>
-        </is>
-      </c>
-      <c r="N17" s="60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="O17" s="60" t="inlineStr"/>
+          <t>枠: Innovation Policy / 政策分野: R&amp;D Funding &amp; Tax Incentives | Public Procurement &amp; Industrial Policy / 焦点: 中小企業向けの資金提供</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:O17"/>
+  <autoFilter ref="A3:O14"/>
   <mergeCells count="2">
     <mergeCell ref="A1:O1"/>
     <mergeCell ref="A2:O2"/>
@@ -2262,7 +2045,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="N4:N17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="N4:N14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"New,Reviewed,Follow-up,Archived"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2278,13 +2061,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId15"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId12"/>
   </tableParts>
 </worksheet>
 </file>
@@ -4584,7 +4364,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4663,7 +4443,7 @@
     <row r="4" ht="42" customHeight="1">
       <c r="A4" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:24:57+09:00</t>
+          <t>2026-07-26T20:29:40+09:00</t>
         </is>
       </c>
       <c r="B4" s="77" t="n">
@@ -4673,16 +4453,16 @@
         <v>28</v>
       </c>
       <c r="D4" s="77" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E4" s="77" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="F4" s="77" t="n">
         <v>10</v>
       </c>
       <c r="G4" s="77" t="n">
-        <v>134.95</v>
+        <v>141.79</v>
       </c>
       <c r="H4" s="60" t="inlineStr">
         <is>
@@ -4693,7 +4473,7 @@
     <row r="5">
       <c r="A5" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:19:15+09:00</t>
+          <t>2026-07-26T20:24:57+09:00</t>
         </is>
       </c>
       <c r="B5" s="77" t="n">
@@ -4703,16 +4483,16 @@
         <v>28</v>
       </c>
       <c r="D5" s="77" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E5" s="77" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F5" s="77" t="n">
         <v>10</v>
       </c>
       <c r="G5" s="77" t="n">
-        <v>134.05</v>
+        <v>134.95</v>
       </c>
       <c r="H5" s="60" t="inlineStr">
         <is>
@@ -4723,26 +4503,26 @@
     <row r="6">
       <c r="A6" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:13:43+09:00</t>
+          <t>2026-07-26T20:19:15+09:00</t>
         </is>
       </c>
       <c r="B6" s="77" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C6" s="77" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D6" s="77" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E6" s="77" t="n">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="F6" s="77" t="n">
         <v>10</v>
       </c>
       <c r="G6" s="77" t="n">
-        <v>162.46</v>
+        <v>134.05</v>
       </c>
       <c r="H6" s="60" t="inlineStr">
         <is>
@@ -4753,7 +4533,7 @@
     <row r="7">
       <c r="A7" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:00:03+09:00</t>
+          <t>2026-07-26T20:13:43+09:00</t>
         </is>
       </c>
       <c r="B7" s="77" t="n">
@@ -4763,16 +4543,16 @@
         <v>24</v>
       </c>
       <c r="D7" s="77" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E7" s="77" t="n">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="F7" s="77" t="n">
         <v>10</v>
       </c>
       <c r="G7" s="77" t="n">
-        <v>154.27</v>
+        <v>162.46</v>
       </c>
       <c r="H7" s="60" t="inlineStr">
         <is>
@@ -4783,7 +4563,7 @@
     <row r="8">
       <c r="A8" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:51:39+09:00</t>
+          <t>2026-07-26T20:00:03+09:00</t>
         </is>
       </c>
       <c r="B8" s="77" t="n">
@@ -4793,16 +4573,16 @@
         <v>24</v>
       </c>
       <c r="D8" s="77" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E8" s="77" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="F8" s="77" t="n">
         <v>10</v>
       </c>
       <c r="G8" s="77" t="n">
-        <v>11.55</v>
+        <v>154.27</v>
       </c>
       <c r="H8" s="60" t="inlineStr">
         <is>
@@ -4813,26 +4593,26 @@
     <row r="9">
       <c r="A9" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:10:55+09:00</t>
+          <t>2026-07-26T19:51:39+09:00</t>
         </is>
       </c>
       <c r="B9" s="77" t="n">
         <v>34</v>
       </c>
       <c r="C9" s="77" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D9" s="77" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E9" s="77" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F9" s="77" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G9" s="77" t="n">
-        <v>194.65</v>
+        <v>11.55</v>
       </c>
       <c r="H9" s="60" t="inlineStr">
         <is>
@@ -4843,26 +4623,26 @@
     <row r="10">
       <c r="A10" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:05:06+09:00</t>
+          <t>2026-07-26T19:10:55+09:00</t>
         </is>
       </c>
       <c r="B10" s="77" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10" s="77" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D10" s="77" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E10" s="77" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="F10" s="77" t="n">
         <v>9</v>
       </c>
       <c r="G10" s="77" t="n">
-        <v>165.89</v>
+        <v>194.65</v>
       </c>
       <c r="H10" s="60" t="inlineStr">
         <is>
@@ -4873,35 +4653,65 @@
     <row r="11">
       <c r="A11" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T19:05:06+09:00</t>
         </is>
       </c>
       <c r="B11" s="77" t="n">
         <v>33</v>
       </c>
       <c r="C11" s="77" t="n">
+        <v>24</v>
+      </c>
+      <c r="D11" s="77" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" s="77" t="n">
+        <v>39</v>
+      </c>
+      <c r="F11" s="77" t="n">
+        <v>9</v>
+      </c>
+      <c r="G11" s="77" t="n">
+        <v>165.89</v>
+      </c>
+      <c r="H11" s="60" t="inlineStr">
+        <is>
+          <t>Daily update</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T18:56:03+09:00</t>
+        </is>
+      </c>
+      <c r="B12" s="77" t="n">
+        <v>33</v>
+      </c>
+      <c r="C12" s="77" t="n">
         <v>20</v>
       </c>
-      <c r="D11" s="77" t="n">
+      <c r="D12" s="77" t="n">
         <v>94</v>
       </c>
-      <c r="E11" s="77" t="n">
+      <c r="E12" s="77" t="n">
         <v>0</v>
       </c>
-      <c r="F11" s="77" t="n">
+      <c r="F12" s="77" t="n">
         <v>13</v>
       </c>
-      <c r="G11" s="77" t="n">
+      <c r="G12" s="77" t="n">
         <v>129.43</v>
       </c>
-      <c r="H11" s="60" t="inlineStr">
+      <c r="H12" s="60" t="inlineStr">
         <is>
           <t>Initial lookback</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:H11"/>
+  <autoFilter ref="A3:H12"/>
   <mergeCells count="2">
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>

--- a/docs/innovation_news_ledger.xlsx
+++ b/docs/innovation_news_ledger.xlsx
@@ -9,9 +9,9 @@
     <sheet name="Run Log" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'News Ledger'!$A$3:$O$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'News Ledger'!$A$3:$O$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Source Registry'!$A$3:$K$41</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Run Log'!$A$3:$H$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Run Log'!$A$3:$H$13</definedName>
   </definedNames>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -472,7 +472,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="NewsLedgerTable" displayName="NewsLedgerTable" ref="A3:O14" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="NewsLedgerTable" displayName="NewsLedgerTable" ref="A3:O16" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <autoFilter ref="A3:O4"/>
   <tableColumns count="15">
     <tableColumn id="1" name="Collected At (JST)"/>
@@ -516,7 +516,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="RunLogTable" displayName="RunLogTable" ref="A3:H12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="RunLogTable" displayName="RunLogTable" ref="A3:H13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <autoFilter ref="A3:H4"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Run Time (JST)"/>
@@ -800,7 +800,7 @@
       </c>
       <c r="B5" s="25" t="inlineStr">
         <is>
-          <t>2026-07-26T20:29:40+09:00</t>
+          <t>2026-07-26T20:34:08+09:00</t>
         </is>
       </c>
       <c r="C5" s="46" t="n"/>
@@ -1088,7 +1088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O14"/>
+  <dimension ref="A1:O16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1291,27 +1291,27 @@
     <row r="5" ht="42" customHeight="1">
       <c r="A5" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:29:40+09:00</t>
+          <t>2026-07-26T18:56:03+09:00</t>
         </is>
       </c>
       <c r="B5" s="75" t="inlineStr">
         <is>
-          <t>2026-07-25T00:55:16Z</t>
+          <t>2026-07-24T16:46:59Z</t>
         </is>
       </c>
       <c r="C5" s="60" t="inlineStr">
         <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D5" s="60" t="inlineStr">
+        <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="D5" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
       <c r="E5" s="60" t="inlineStr">
         <is>
-          <t>Space</t>
+          <t>Semiconductors &amp; Telecom</t>
         </is>
       </c>
       <c r="F5" s="76" t="n">
@@ -1319,37 +1319,37 @@
       </c>
       <c r="G5" s="60" t="inlineStr">
         <is>
-          <t>Major Media</t>
+          <t>Official Company</t>
         </is>
       </c>
       <c r="H5" s="60" t="inlineStr">
         <is>
-          <t>The New York Times Science</t>
+          <t>Intel Newsroom</t>
         </is>
       </c>
       <c r="I5" s="60" t="inlineStr">
         <is>
-          <t>SpaceX、最新のStarship設計で着陸に成功</t>
+          <t>インテルとレンズテクノロジーがAI時代の先進半導体パッケージングを実現するために協力</t>
         </is>
       </c>
       <c r="J5" s="60" t="inlineStr">
         <is>
-          <t>SpaceXはStarshipの13回目のテストで成功を収め、NASAの月計画に貢献することが期待されています。</t>
+          <t>インテルとレンズテクノロジーが、AI時代に向けた先進的な半導体パッケージング技術の開発に向けて戦略的な協力を発表した。</t>
         </is>
       </c>
       <c r="K5" s="60" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/07/24/science/spacex-starship-13th-test-flight.html</t>
+          <t>https://newsroom.intel.com/new-technologies/intel-and-lens-technology-collaborate-to-enable-advanced-semiconductor-packaging-for-the-ai-era</t>
         </is>
       </c>
       <c r="L5" s="60" t="inlineStr">
         <is>
-          <t>a3a5c9efad44807da5223756</t>
+          <t>10eedf14d7d6b636e24e447d</t>
         </is>
       </c>
       <c r="M5" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:29:40+09:00</t>
+          <t>2026-07-26T18:56:03+09:00</t>
         </is>
       </c>
       <c r="N5" s="60" t="inlineStr">
@@ -1359,19 +1359,19 @@
       </c>
       <c r="O5" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 焦点: SpaceXのStarship設計</t>
+          <t>枠: Technology Innovation / 焦点: 先進半導体パッケージング技術</t>
         </is>
       </c>
     </row>
     <row r="6" ht="42" customHeight="1">
       <c r="A6" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T20:29:40+09:00</t>
         </is>
       </c>
       <c r="B6" s="75" t="inlineStr">
         <is>
-          <t>2026-07-24T16:46:59Z</t>
+          <t>2026-07-24T02:35:52Z</t>
         </is>
       </c>
       <c r="C6" s="60" t="inlineStr">
@@ -1381,12 +1381,12 @@
       </c>
       <c r="D6" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="E6" s="60" t="inlineStr">
         <is>
-          <t>Semiconductors &amp; Telecom</t>
+          <t>Artificial Intelligence | Robotics</t>
         </is>
       </c>
       <c r="F6" s="76" t="n">
@@ -1394,37 +1394,37 @@
       </c>
       <c r="G6" s="60" t="inlineStr">
         <is>
-          <t>Official Company</t>
+          <t>Major Media</t>
         </is>
       </c>
       <c r="H6" s="60" t="inlineStr">
         <is>
-          <t>Intel Newsroom</t>
+          <t>South China Morning Post Technology</t>
         </is>
       </c>
       <c r="I6" s="60" t="inlineStr">
         <is>
-          <t>インテルとレンズテクノロジーがAI時代の先進半導体パッケージングを実現するために協力</t>
+          <t>中国のロボット共働者が増加中。AIコボットに挨拶を</t>
         </is>
       </c>
       <c r="J6" s="60" t="inlineStr">
         <is>
-          <t>インテルとレンズテクノロジーが、AI時代に向けた先進的な半導体パッケージング技術の開発に向けて戦略的な協力を発表した。</t>
+          <t>中国のヒューマノイドロボットや自動化工場が注目される中、協働ロボット（コボット）が進化している。最新モデルはコーディング知識を必要とせず、自然言語での指示に応じる。</t>
         </is>
       </c>
       <c r="K6" s="60" t="inlineStr">
         <is>
-          <t>https://newsroom.intel.com/new-technologies/intel-and-lens-technology-collaborate-to-enable-advanced-semiconductor-packaging-for-the-ai-era</t>
+          <t>https://www.scmp.com/plus/tech/tech-trends/article/3361664/chinese-robot-co-workers-rise-say-hello-ai-cobots?utm_source=rss_feed</t>
         </is>
       </c>
       <c r="L6" s="60" t="inlineStr">
         <is>
-          <t>10eedf14d7d6b636e24e447d</t>
+          <t>00cfbfef6982b98ed0351899</t>
         </is>
       </c>
       <c r="M6" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T20:29:40+09:00</t>
         </is>
       </c>
       <c r="N6" s="60" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="O6" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 焦点: 先進半導体パッケージング技術</t>
+          <t>枠: Technology Innovation / 焦点: 協働ロボット（コボット）</t>
         </is>
       </c>
     </row>
@@ -1446,26 +1446,26 @@
       </c>
       <c r="B7" s="75" t="inlineStr">
         <is>
-          <t>2026-07-24T02:35:52Z</t>
+          <t>2026-07-23T20:58:35Z</t>
         </is>
       </c>
       <c r="C7" s="60" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D7" s="60" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="E7" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence | Robotics</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="F7" s="76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" s="60" t="inlineStr">
         <is>
@@ -1474,27 +1474,27 @@
       </c>
       <c r="H7" s="60" t="inlineStr">
         <is>
-          <t>South China Morning Post Technology</t>
+          <t>BBC Technology</t>
         </is>
       </c>
       <c r="I7" s="60" t="inlineStr">
         <is>
-          <t>中国のロボット共働者が増加中。AIコボットに挨拶を</t>
+          <t>AIモデルのシャットダウンを許可する新法案が提案</t>
         </is>
       </c>
       <c r="J7" s="60" t="inlineStr">
         <is>
-          <t>中国のヒューマノイドロボットや自動化工場が注目される中、協働ロボット（コボット）が進化している。最新モデルはコーディング知識を必要とせず、自然言語での指示に応じる。</t>
+          <t>新たに提案された法案は、公共の脅威をもたらすAIモデルのシャットダウンを政府に許可する内容である。</t>
         </is>
       </c>
       <c r="K7" s="60" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/plus/tech/tech-trends/article/3361664/chinese-robot-co-workers-rise-say-hello-ai-cobots?utm_source=rss_feed</t>
+          <t>https://www.bbc.co.uk/news/articles/cx2vqj2e9x8o?at_medium=RSS&amp;at_campaign=rss</t>
         </is>
       </c>
       <c r="L7" s="60" t="inlineStr">
         <is>
-          <t>00cfbfef6982b98ed0351899</t>
+          <t>30744ac6eef4bc37b48358ce</t>
         </is>
       </c>
       <c r="M7" s="75" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="O7" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 焦点: 協働ロボット（コボット）</t>
+          <t>枠: Innovation Policy / 政策分野: Regulation &amp; Governance / 焦点: AIモデルの規制</t>
         </is>
       </c>
     </row>
@@ -1521,12 +1521,12 @@
       </c>
       <c r="B8" s="75" t="inlineStr">
         <is>
-          <t>2026-07-23T20:58:35Z</t>
+          <t>2026-07-22T14:21:46Z</t>
         </is>
       </c>
       <c r="C8" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>EU &amp; Europe</t>
         </is>
       </c>
       <c r="D8" s="60" t="inlineStr">
@@ -1534,42 +1534,38 @@
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="E8" s="60" t="inlineStr">
-        <is>
-          <t>Artificial Intelligence</t>
-        </is>
-      </c>
+      <c r="E8" s="60" t="inlineStr"/>
       <c r="F8" s="76" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G8" s="60" t="inlineStr">
         <is>
-          <t>Major Media</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H8" s="60" t="inlineStr">
         <is>
-          <t>BBC Technology</t>
+          <t>UK DSIT</t>
         </is>
       </c>
       <c r="I8" s="60" t="inlineStr">
         <is>
-          <t>AIモデルのシャットダウンを許可する新法案が提案</t>
+          <t>ガイダンス：研究における女性のためのチャーター</t>
         </is>
       </c>
       <c r="J8" s="60" t="inlineStr">
         <is>
-          <t>新たに提案された法案は、公共の脅威をもたらすAIモデルのシャットダウンを政府に許可する内容である。</t>
+          <t>UKの研究システムにおける女性の成果を改善するための自主的な取り組みが発表された。</t>
         </is>
       </c>
       <c r="K8" s="60" t="inlineStr">
         <is>
-          <t>https://www.bbc.co.uk/news/articles/cx2vqj2e9x8o?at_medium=RSS&amp;at_campaign=rss</t>
+          <t>https://www.gov.uk/government/publications/women-in-research-charter</t>
         </is>
       </c>
       <c r="L8" s="60" t="inlineStr">
         <is>
-          <t>30744ac6eef4bc37b48358ce</t>
+          <t>1e9fd9033d38bacea37c0f42</t>
         </is>
       </c>
       <c r="M8" s="75" t="inlineStr">
@@ -1584,7 +1580,7 @@
       </c>
       <c r="O8" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: Regulation &amp; Governance / 焦点: AIモデルの規制</t>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy | Research System &amp; Talent / 焦点: 女性研究者の成果向上</t>
         </is>
       </c>
     </row>
@@ -1596,22 +1592,22 @@
       </c>
       <c r="B9" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T14:21:46Z</t>
+          <t>2026-07-22T14:12:14Z</t>
         </is>
       </c>
       <c r="C9" s="60" t="inlineStr">
         <is>
-          <t>EU &amp; Europe</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D9" s="60" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E9" s="60" t="inlineStr"/>
       <c r="F9" s="76" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G9" s="60" t="inlineStr">
         <is>
@@ -1620,27 +1616,27 @@
       </c>
       <c r="H9" s="60" t="inlineStr">
         <is>
-          <t>UK DSIT</t>
+          <t>DOE Office of Science News</t>
         </is>
       </c>
       <c r="I9" s="60" t="inlineStr">
         <is>
-          <t>ガイダンス：研究における女性のためのチャーター</t>
+          <t>エネルギー長官クリス・ライト、AI駆動の科学発見を加速するための初のジェネシスミッションプロジェクトを発表</t>
         </is>
       </c>
       <c r="J9" s="60" t="inlineStr">
         <is>
-          <t>UKの研究システムにおける女性の成果を改善するための自主的な取り組みが発表された。</t>
+          <t>米国エネルギー省がAI駆動の科学発見を加速するために、全米から選ばれたプロジェクトを発表した。</t>
         </is>
       </c>
       <c r="K9" s="60" t="inlineStr">
         <is>
-          <t>https://www.gov.uk/government/publications/women-in-research-charter</t>
+          <t>https://www.energy.gov/articles/secretary-energy-chris-wright-announces-first-genesis-mission-projects-selected-accelerate</t>
         </is>
       </c>
       <c r="L9" s="60" t="inlineStr">
         <is>
-          <t>1e9fd9033d38bacea37c0f42</t>
+          <t>23fa1d6907c14d73ce3a41cd</t>
         </is>
       </c>
       <c r="M9" s="75" t="inlineStr">
@@ -1655,19 +1651,19 @@
       </c>
       <c r="O9" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy | Research System &amp; Talent / 焦点: 女性研究者の成果向上</t>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 焦点: AI駆動の科学発見プロジェクト</t>
         </is>
       </c>
     </row>
     <row r="10" ht="42" customHeight="1">
       <c r="A10" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:29:40+09:00</t>
+          <t>2026-07-26T19:05:06+09:00</t>
         </is>
       </c>
       <c r="B10" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T14:12:14Z</t>
+          <t>2026-07-22T13:53:19Z</t>
         </is>
       </c>
       <c r="C10" s="60" t="inlineStr">
@@ -1682,11 +1678,11 @@
       </c>
       <c r="E10" s="60" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="F10" s="76" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G10" s="60" t="inlineStr">
         <is>
@@ -1695,32 +1691,32 @@
       </c>
       <c r="H10" s="60" t="inlineStr">
         <is>
-          <t>DOE Office of Science News</t>
+          <t>National Science Foundation News</t>
         </is>
       </c>
       <c r="I10" s="60" t="inlineStr">
         <is>
-          <t>エネルギー長官クリス・ライト、AI駆動の科学発見を加速するための初のジェネシスミッションプロジェクトを発表</t>
+          <t>NSFがAIに関する国家戦略を推進する声明を発表</t>
         </is>
       </c>
       <c r="J10" s="60" t="inlineStr">
         <is>
-          <t>米国エネルギー省がAI駆動の科学発見を加速するために、全米から選ばれたプロジェクトを発表した。</t>
+          <t>米国科学財団（NSF）は、AIに関する国家戦略を推進するための声明を発表しました。</t>
         </is>
       </c>
       <c r="K10" s="60" t="inlineStr">
         <is>
-          <t>https://www.energy.gov/articles/secretary-energy-chris-wright-announces-first-genesis-mission-projects-selected-accelerate</t>
+          <t>https://www.nsf.gov/news/statement-nsf-chief-staff-brian-stone-performing-duties-nsf-1</t>
         </is>
       </c>
       <c r="L10" s="60" t="inlineStr">
         <is>
-          <t>23fa1d6907c14d73ce3a41cd</t>
+          <t>123e2207578ca69c8f9c00a2</t>
         </is>
       </c>
       <c r="M10" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:29:40+09:00</t>
+          <t>2026-07-26T19:05:06+09:00</t>
         </is>
       </c>
       <c r="N10" s="60" t="inlineStr">
@@ -1730,7 +1726,7 @@
       </c>
       <c r="O10" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 焦点: AI駆動の科学発見プロジェクト</t>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 焦点: AIに関する国家戦略の推進</t>
         </is>
       </c>
     </row>
@@ -1742,7 +1738,7 @@
       </c>
       <c r="B11" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T13:53:19Z</t>
+          <t>2026-07-22T13:53:12Z</t>
         </is>
       </c>
       <c r="C11" s="60" t="inlineStr">
@@ -1761,7 +1757,7 @@
         </is>
       </c>
       <c r="F11" s="76" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G11" s="60" t="inlineStr">
         <is>
@@ -1775,22 +1771,22 @@
       </c>
       <c r="I11" s="60" t="inlineStr">
         <is>
-          <t>NSFがAIに関する国家戦略を推進する声明を発表</t>
+          <t>NSFの新しい取り組みがAIによる科学的発見のためのデータセットの価値を引き出す</t>
         </is>
       </c>
       <c r="J11" s="60" t="inlineStr">
         <is>
-          <t>米国科学財団（NSF）は、AIに関する国家戦略を推進するための声明を発表しました。</t>
+          <t>米国科学財団（NSF）は、AIを活用した科学的発見のためのデータセットの価値を引き出す新しいプログラムを発表しました。</t>
         </is>
       </c>
       <c r="K11" s="60" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/news/statement-nsf-chief-staff-brian-stone-performing-duties-nsf-1</t>
+          <t>https://www.nsf.gov/news/new-nsf-initiative-aims-unlock-dataset-value-ai-enabled</t>
         </is>
       </c>
       <c r="L11" s="60" t="inlineStr">
         <is>
-          <t>123e2207578ca69c8f9c00a2</t>
+          <t>dcd819527d9b80141b26bcb8</t>
         </is>
       </c>
       <c r="M11" s="75" t="inlineStr">
@@ -1805,19 +1801,19 @@
       </c>
       <c r="O11" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 焦点: AIに関する国家戦略の推進</t>
+          <t>枠: Innovation Policy / 政策分野: R&amp;D Funding &amp; Tax Incentives / 焦点: AIを活用した科学的発見のためのデータセットの価値を引き出すプログラム</t>
         </is>
       </c>
     </row>
     <row r="12" ht="42" customHeight="1">
       <c r="A12" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:05:06+09:00</t>
+          <t>2026-07-26T20:29:40+09:00</t>
         </is>
       </c>
       <c r="B12" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T13:53:12Z</t>
+          <t>2026-07-22T13:53:06Z</t>
         </is>
       </c>
       <c r="C12" s="60" t="inlineStr">
@@ -1830,11 +1826,7 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="E12" s="60" t="inlineStr">
-        <is>
-          <t>Artificial Intelligence</t>
-        </is>
-      </c>
+      <c r="E12" s="60" t="inlineStr"/>
       <c r="F12" s="76" t="n">
         <v>4</v>
       </c>
@@ -1850,27 +1842,27 @@
       </c>
       <c r="I12" s="60" t="inlineStr">
         <is>
-          <t>NSFの新しい取り組みがAIによる科学的発見のためのデータセットの価値を引き出す</t>
+          <t>NSF、AI駆動の科学を進展させるために8300万ドルの投資を発表</t>
         </is>
       </c>
       <c r="J12" s="60" t="inlineStr">
         <is>
-          <t>米国科学財団（NSF）は、AIを活用した科学的発見のためのデータセットの価値を引き出す新しいプログラムを発表しました。</t>
+          <t>米国科学財団が8300万ドルの資金を通じて、AI駆動の科学を進展させるためのデータシステムとサービスの整備を発表した。</t>
         </is>
       </c>
       <c r="K12" s="60" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/news/new-nsf-initiative-aims-unlock-dataset-value-ai-enabled</t>
+          <t>https://www.nsf.gov/news/nsf-announces-83m-investment-integrated-data-systems</t>
         </is>
       </c>
       <c r="L12" s="60" t="inlineStr">
         <is>
-          <t>dcd819527d9b80141b26bcb8</t>
+          <t>018d40b7e6eb7aa4b8cfb5fa</t>
         </is>
       </c>
       <c r="M12" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:05:06+09:00</t>
+          <t>2026-07-26T20:29:40+09:00</t>
         </is>
       </c>
       <c r="N12" s="60" t="inlineStr">
@@ -1880,7 +1872,7 @@
       </c>
       <c r="O12" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: R&amp;D Funding &amp; Tax Incentives / 焦点: AIを活用した科学的発見のためのデータセットの価値を引き出すプログラム</t>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy | Research System &amp; Talent / 焦点: AI駆動の科学研究インフラ整備</t>
         </is>
       </c>
     </row>
@@ -1892,7 +1884,7 @@
       </c>
       <c r="B13" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T13:53:06Z</t>
+          <t>2026-07-22T12:00:00Z</t>
         </is>
       </c>
       <c r="C13" s="60" t="inlineStr">
@@ -1916,27 +1908,27 @@
       </c>
       <c r="H13" s="60" t="inlineStr">
         <is>
-          <t>National Science Foundation News</t>
+          <t>NIST News</t>
         </is>
       </c>
       <c r="I13" s="60" t="inlineStr">
         <is>
-          <t>NSF、AI駆動の科学を進展させるために8300万ドルの投資を発表</t>
+          <t>NISTが中小企業向けの資金提供機会を発表</t>
         </is>
       </c>
       <c r="J13" s="60" t="inlineStr">
         <is>
-          <t>米国科学財団が8300万ドルの資金を通じて、AI駆動の科学を進展させるためのデータシステムとサービスの整備を発表した。</t>
+          <t>NIST MEPは、米国の中小企業を支援するための資金提供機会を発表し、2026年7月28日にウェビナーを開催する予定です。</t>
         </is>
       </c>
       <c r="K13" s="60" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/news/nsf-announces-83m-investment-integrated-data-systems</t>
+          <t>https://www.nist.gov/news-events/news/2026/07/nist-announces-funding-opportunity-14-mep-centers-advance-small-and-medium</t>
         </is>
       </c>
       <c r="L13" s="60" t="inlineStr">
         <is>
-          <t>018d40b7e6eb7aa4b8cfb5fa</t>
+          <t>5aa9c93bc7040291c9f08bfa</t>
         </is>
       </c>
       <c r="M13" s="75" t="inlineStr">
@@ -1951,83 +1943,237 @@
       </c>
       <c r="O13" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy | Research System &amp; Talent / 焦点: AI駆動の科学研究インフラ整備</t>
+          <t>枠: Innovation Policy / 政策分野: R&amp;D Funding &amp; Tax Incentives | Public Procurement &amp; Industrial Policy / 焦点: 中小企業向けの資金提供</t>
         </is>
       </c>
     </row>
     <row r="14" ht="42" customHeight="1">
       <c r="A14" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:29:40+09:00</t>
+          <t>2026-07-26T18:56:03+09:00</t>
         </is>
       </c>
       <c r="B14" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T12:00:00Z</t>
+          <t>2026-07-21T14:48:28Z</t>
         </is>
       </c>
       <c r="C14" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>EU &amp; Europe</t>
         </is>
       </c>
       <c r="D14" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E14" s="60" t="inlineStr"/>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E14" s="60" t="inlineStr">
+        <is>
+          <t>Fusion Energy</t>
+        </is>
+      </c>
       <c r="F14" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="G14" s="60" t="inlineStr">
+        <is>
+          <t>Industry Association</t>
+        </is>
+      </c>
+      <c r="H14" s="60" t="inlineStr">
+        <is>
+          <t>Fusion Industry Association</t>
+        </is>
+      </c>
+      <c r="I14" s="60" t="inlineStr">
+        <is>
+          <t>FIAが核融合のためのEU資金調達の道筋を示す</t>
+        </is>
+      </c>
+      <c r="J14" s="60" t="inlineStr">
+        <is>
+          <t>核融合産業協会は、商業核融合エネルギーのための実用的なEU資金調達の道筋を示す論文を発表しました。核融合プロジェクトが研究から実証へ移行する際に必要な資金調達手段について論じています。</t>
+        </is>
+      </c>
+      <c r="K14" s="60" t="inlineStr">
+        <is>
+          <t>https://www.fusionindustryassociation.org/fia-outlines-eu-financing-pathway-for-fusion/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=fia-outlines-eu-financing-pathway-for-fusion</t>
+        </is>
+      </c>
+      <c r="L14" s="60" t="inlineStr">
+        <is>
+          <t>88af233d904d670250fa5a31</t>
+        </is>
+      </c>
+      <c r="M14" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T18:56:03+09:00</t>
+        </is>
+      </c>
+      <c r="N14" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O14" s="60" t="inlineStr">
+        <is>
+          <t>枠: Innovation Policy / 政策分野: R&amp;D Funding &amp; Tax Incentives / 焦点: 商業核融合エネルギーの資金調達</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="42" customHeight="1">
+      <c r="A15" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T18:56:03+09:00</t>
+        </is>
+      </c>
+      <c r="B15" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-17T18:42:47Z</t>
+        </is>
+      </c>
+      <c r="C15" s="60" t="inlineStr">
+        <is>
+          <t>EU &amp; Europe</t>
+        </is>
+      </c>
+      <c r="D15" s="60" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E15" s="60" t="inlineStr">
+        <is>
+          <t>Fusion Energy</t>
+        </is>
+      </c>
+      <c r="F15" s="76" t="n">
         <v>4</v>
       </c>
-      <c r="G14" s="60" t="inlineStr">
-        <is>
-          <t>Government</t>
-        </is>
-      </c>
-      <c r="H14" s="60" t="inlineStr">
-        <is>
-          <t>NIST News</t>
-        </is>
-      </c>
-      <c r="I14" s="60" t="inlineStr">
-        <is>
-          <t>NISTが中小企業向けの資金提供機会を発表</t>
-        </is>
-      </c>
-      <c r="J14" s="60" t="inlineStr">
-        <is>
-          <t>NIST MEPは、米国の中小企業を支援するための資金提供機会を発表し、2026年7月28日にウェビナーを開催する予定です。</t>
-        </is>
-      </c>
-      <c r="K14" s="60" t="inlineStr">
-        <is>
-          <t>https://www.nist.gov/news-events/news/2026/07/nist-announces-funding-opportunity-14-mep-centers-advance-small-and-medium</t>
-        </is>
-      </c>
-      <c r="L14" s="60" t="inlineStr">
-        <is>
-          <t>5aa9c93bc7040291c9f08bfa</t>
-        </is>
-      </c>
-      <c r="M14" s="75" t="inlineStr">
-        <is>
-          <t>2026-07-26T20:29:40+09:00</t>
-        </is>
-      </c>
-      <c r="N14" s="60" t="inlineStr">
+      <c r="G15" s="60" t="inlineStr">
+        <is>
+          <t>Industry Association</t>
+        </is>
+      </c>
+      <c r="H15" s="60" t="inlineStr">
+        <is>
+          <t>Fusion Industry Association</t>
+        </is>
+      </c>
+      <c r="I15" s="60" t="inlineStr">
+        <is>
+          <t>国際法専門家グループがEUの核融合競争力確保の必要性に関する論文を発表</t>
+        </is>
+      </c>
+      <c r="J15" s="60" t="inlineStr">
+        <is>
+          <t>国際法専門家グループが発表した論文は、EUが商業核融合において競争優位を持っているが、それを維持するためには今すぐ行動が必要であると主張しています。</t>
+        </is>
+      </c>
+      <c r="K15" s="60" t="inlineStr">
+        <is>
+          <t>https://www.fusionindustryassociation.org/international-legal-expert-group-publish-paper-on-the-need-for-the-eu-to-secure-its-competitive-fusion-advantage/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=international-legal-expert-group-publish-paper-on-the-need-for-the-eu-to-secure-its-competitive-fusion-advantage</t>
+        </is>
+      </c>
+      <c r="L15" s="60" t="inlineStr">
+        <is>
+          <t>7ef6110ab078602757409abf</t>
+        </is>
+      </c>
+      <c r="M15" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T18:56:03+09:00</t>
+        </is>
+      </c>
+      <c r="N15" s="60" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="O14" s="60" t="inlineStr">
-        <is>
-          <t>枠: Innovation Policy / 政策分野: R&amp;D Funding &amp; Tax Incentives | Public Procurement &amp; Industrial Policy / 焦点: 中小企業向けの資金提供</t>
+      <c r="O15" s="60" t="inlineStr">
+        <is>
+          <t>枠: Innovation Policy / 政策分野: Regulation &amp; Governance / 焦点: EUの核融合競争力の維持</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="42" customHeight="1">
+      <c r="A16" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T18:56:03+09:00</t>
+        </is>
+      </c>
+      <c r="B16" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-15T17:47:57Z</t>
+        </is>
+      </c>
+      <c r="C16" s="60" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D16" s="60" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E16" s="60" t="inlineStr">
+        <is>
+          <t>Fusion Energy</t>
+        </is>
+      </c>
+      <c r="F16" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="G16" s="60" t="inlineStr">
+        <is>
+          <t>Industry Association</t>
+        </is>
+      </c>
+      <c r="H16" s="60" t="inlineStr">
+        <is>
+          <t>Fusion Industry Association</t>
+        </is>
+      </c>
+      <c r="I16" s="60" t="inlineStr">
+        <is>
+          <t>スターロライトエンジンが60.6億円を調達</t>
+        </is>
+      </c>
+      <c r="J16" s="60" t="inlineStr">
+        <is>
+          <t>スターロライトエンジンは、FASTの開発を加速するために60.6億円を調達しました。この会社は、日本のJT-60SAプログラムや国際的な取り組みを基にしたトカマク型核融合機を開発しています。</t>
+        </is>
+      </c>
+      <c r="K16" s="60" t="inlineStr">
+        <is>
+          <t>https://www.nikkei.com/article/DGXZQOUC152ET0V10C26A7000000/#new_tab?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=starlight-engine-raises-jpy-6-06-billion</t>
+        </is>
+      </c>
+      <c r="L16" s="60" t="inlineStr">
+        <is>
+          <t>2f29b005896c3737ab846738</t>
+        </is>
+      </c>
+      <c r="M16" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T18:56:03+09:00</t>
+        </is>
+      </c>
+      <c r="N16" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O16" s="60" t="inlineStr">
+        <is>
+          <t>枠: Innovation Policy / 政策分野: R&amp;D Funding &amp; Tax Incentives / 焦点: トカマク型核融合機の開発</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:O14"/>
+  <autoFilter ref="A3:O16"/>
   <mergeCells count="2">
     <mergeCell ref="A1:O1"/>
     <mergeCell ref="A2:O2"/>
@@ -2045,7 +2191,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="N4:N14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="N4:N16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"New,Reviewed,Follow-up,Archived"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2061,10 +2207,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId13"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId12"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId14"/>
   </tableParts>
 </worksheet>
 </file>
@@ -4364,7 +4512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4443,7 +4591,7 @@
     <row r="4" ht="42" customHeight="1">
       <c r="A4" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:29:40+09:00</t>
+          <t>2026-07-26T20:34:08+09:00</t>
         </is>
       </c>
       <c r="B4" s="77" t="n">
@@ -4453,16 +4601,16 @@
         <v>28</v>
       </c>
       <c r="D4" s="77" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E4" s="77" t="n">
-        <v>11</v>
+        <v>74</v>
       </c>
       <c r="F4" s="77" t="n">
         <v>10</v>
       </c>
       <c r="G4" s="77" t="n">
-        <v>141.79</v>
+        <v>20.27</v>
       </c>
       <c r="H4" s="60" t="inlineStr">
         <is>
@@ -4473,7 +4621,7 @@
     <row r="5">
       <c r="A5" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:24:57+09:00</t>
+          <t>2026-07-26T20:29:40+09:00</t>
         </is>
       </c>
       <c r="B5" s="77" t="n">
@@ -4483,16 +4631,16 @@
         <v>28</v>
       </c>
       <c r="D5" s="77" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E5" s="77" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="F5" s="77" t="n">
         <v>10</v>
       </c>
       <c r="G5" s="77" t="n">
-        <v>134.95</v>
+        <v>141.79</v>
       </c>
       <c r="H5" s="60" t="inlineStr">
         <is>
@@ -4503,7 +4651,7 @@
     <row r="6">
       <c r="A6" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:19:15+09:00</t>
+          <t>2026-07-26T20:24:57+09:00</t>
         </is>
       </c>
       <c r="B6" s="77" t="n">
@@ -4513,16 +4661,16 @@
         <v>28</v>
       </c>
       <c r="D6" s="77" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E6" s="77" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F6" s="77" t="n">
         <v>10</v>
       </c>
       <c r="G6" s="77" t="n">
-        <v>134.05</v>
+        <v>134.95</v>
       </c>
       <c r="H6" s="60" t="inlineStr">
         <is>
@@ -4533,26 +4681,26 @@
     <row r="7">
       <c r="A7" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:13:43+09:00</t>
+          <t>2026-07-26T20:19:15+09:00</t>
         </is>
       </c>
       <c r="B7" s="77" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C7" s="77" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D7" s="77" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E7" s="77" t="n">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="F7" s="77" t="n">
         <v>10</v>
       </c>
       <c r="G7" s="77" t="n">
-        <v>162.46</v>
+        <v>134.05</v>
       </c>
       <c r="H7" s="60" t="inlineStr">
         <is>
@@ -4563,7 +4711,7 @@
     <row r="8">
       <c r="A8" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:00:03+09:00</t>
+          <t>2026-07-26T20:13:43+09:00</t>
         </is>
       </c>
       <c r="B8" s="77" t="n">
@@ -4573,16 +4721,16 @@
         <v>24</v>
       </c>
       <c r="D8" s="77" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E8" s="77" t="n">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="F8" s="77" t="n">
         <v>10</v>
       </c>
       <c r="G8" s="77" t="n">
-        <v>154.27</v>
+        <v>162.46</v>
       </c>
       <c r="H8" s="60" t="inlineStr">
         <is>
@@ -4593,7 +4741,7 @@
     <row r="9">
       <c r="A9" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:51:39+09:00</t>
+          <t>2026-07-26T20:00:03+09:00</t>
         </is>
       </c>
       <c r="B9" s="77" t="n">
@@ -4603,16 +4751,16 @@
         <v>24</v>
       </c>
       <c r="D9" s="77" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E9" s="77" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="F9" s="77" t="n">
         <v>10</v>
       </c>
       <c r="G9" s="77" t="n">
-        <v>11.55</v>
+        <v>154.27</v>
       </c>
       <c r="H9" s="60" t="inlineStr">
         <is>
@@ -4623,26 +4771,26 @@
     <row r="10">
       <c r="A10" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:10:55+09:00</t>
+          <t>2026-07-26T19:51:39+09:00</t>
         </is>
       </c>
       <c r="B10" s="77" t="n">
         <v>34</v>
       </c>
       <c r="C10" s="77" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D10" s="77" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E10" s="77" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F10" s="77" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G10" s="77" t="n">
-        <v>194.65</v>
+        <v>11.55</v>
       </c>
       <c r="H10" s="60" t="inlineStr">
         <is>
@@ -4653,26 +4801,26 @@
     <row r="11">
       <c r="A11" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:05:06+09:00</t>
+          <t>2026-07-26T19:10:55+09:00</t>
         </is>
       </c>
       <c r="B11" s="77" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C11" s="77" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D11" s="77" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E11" s="77" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="F11" s="77" t="n">
         <v>9</v>
       </c>
       <c r="G11" s="77" t="n">
-        <v>165.89</v>
+        <v>194.65</v>
       </c>
       <c r="H11" s="60" t="inlineStr">
         <is>
@@ -4683,35 +4831,65 @@
     <row r="12">
       <c r="A12" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T19:05:06+09:00</t>
         </is>
       </c>
       <c r="B12" s="77" t="n">
         <v>33</v>
       </c>
       <c r="C12" s="77" t="n">
+        <v>24</v>
+      </c>
+      <c r="D12" s="77" t="n">
+        <v>5</v>
+      </c>
+      <c r="E12" s="77" t="n">
+        <v>39</v>
+      </c>
+      <c r="F12" s="77" t="n">
+        <v>9</v>
+      </c>
+      <c r="G12" s="77" t="n">
+        <v>165.89</v>
+      </c>
+      <c r="H12" s="60" t="inlineStr">
+        <is>
+          <t>Daily update</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T18:56:03+09:00</t>
+        </is>
+      </c>
+      <c r="B13" s="77" t="n">
+        <v>33</v>
+      </c>
+      <c r="C13" s="77" t="n">
         <v>20</v>
       </c>
-      <c r="D12" s="77" t="n">
+      <c r="D13" s="77" t="n">
         <v>94</v>
       </c>
-      <c r="E12" s="77" t="n">
+      <c r="E13" s="77" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="77" t="n">
+      <c r="F13" s="77" t="n">
         <v>13</v>
       </c>
-      <c r="G12" s="77" t="n">
+      <c r="G13" s="77" t="n">
         <v>129.43</v>
       </c>
-      <c r="H12" s="60" t="inlineStr">
+      <c r="H13" s="60" t="inlineStr">
         <is>
           <t>Initial lookback</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:H12"/>
+  <autoFilter ref="A3:H13"/>
   <mergeCells count="2">
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>

--- a/docs/innovation_news_ledger.xlsx
+++ b/docs/innovation_news_ledger.xlsx
@@ -9,9 +9,9 @@
     <sheet name="Run Log" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'News Ledger'!$A$3:$O$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'News Ledger'!$A$3:$O$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Source Registry'!$A$3:$K$41</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Run Log'!$A$3:$H$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Run Log'!$A$3:$H$14</definedName>
   </definedNames>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -472,7 +472,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="NewsLedgerTable" displayName="NewsLedgerTable" ref="A3:O16" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="NewsLedgerTable" displayName="NewsLedgerTable" ref="A3:O17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <autoFilter ref="A3:O4"/>
   <tableColumns count="15">
     <tableColumn id="1" name="Collected At (JST)"/>
@@ -516,7 +516,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="RunLogTable" displayName="RunLogTable" ref="A3:H13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="RunLogTable" displayName="RunLogTable" ref="A3:H14" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <autoFilter ref="A3:H4"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Run Time (JST)"/>
@@ -800,7 +800,7 @@
       </c>
       <c r="B5" s="25" t="inlineStr">
         <is>
-          <t>2026-07-26T20:34:08+09:00</t>
+          <t>2026-07-26T20:36:29+09:00</t>
         </is>
       </c>
       <c r="C5" s="46" t="n"/>
@@ -1088,7 +1088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O16"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1441,12 +1441,12 @@
     <row r="7" ht="42" customHeight="1">
       <c r="A7" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:29:40+09:00</t>
+          <t>2026-07-26T20:36:29+09:00</t>
         </is>
       </c>
       <c r="B7" s="75" t="inlineStr">
         <is>
-          <t>2026-07-23T20:58:35Z</t>
+          <t>2026-07-24T00:00:00Z</t>
         </is>
       </c>
       <c r="C7" s="60" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="D7" s="60" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="E7" s="60" t="inlineStr">
@@ -1465,41 +1465,41 @@
         </is>
       </c>
       <c r="F7" s="76" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G7" s="60" t="inlineStr">
         <is>
-          <t>Major Media</t>
+          <t>Scientific Publication</t>
         </is>
       </c>
       <c r="H7" s="60" t="inlineStr">
         <is>
-          <t>BBC Technology</t>
+          <t>Nature</t>
         </is>
       </c>
       <c r="I7" s="60" t="inlineStr">
         <is>
-          <t>AIモデルのシャットダウンを許可する新法案が提案</t>
+          <t>ホワイトハウスがAI資金を発表 — 米国科学の新時代を示唆</t>
         </is>
       </c>
       <c r="J7" s="60" t="inlineStr">
         <is>
-          <t>新たに提案された法案は、公共の脅威をもたらすAIモデルのシャットダウンを政府に許可する内容である。</t>
+          <t>米国の科学顧問がAI研究を加速するための資金の見直しを呼びかけ、助成金を配布した。</t>
         </is>
       </c>
       <c r="K7" s="60" t="inlineStr">
         <is>
-          <t>https://www.bbc.co.uk/news/articles/cx2vqj2e9x8o?at_medium=RSS&amp;at_campaign=rss</t>
+          <t>https://www.nature.com/articles/d41586-026-02332-8</t>
         </is>
       </c>
       <c r="L7" s="60" t="inlineStr">
         <is>
-          <t>30744ac6eef4bc37b48358ce</t>
+          <t>856206151844f412d95b7a9b</t>
         </is>
       </c>
       <c r="M7" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:29:40+09:00</t>
+          <t>2026-07-26T20:36:29+09:00</t>
         </is>
       </c>
       <c r="N7" s="60" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="O7" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: Regulation &amp; Governance / 焦点: AIモデルの規制</t>
+          <t>枠: Innovation Policy / 政策分野: R&amp;D Funding &amp; Tax Incentives / 焦点: AI研究の助成金</t>
         </is>
       </c>
     </row>
@@ -1521,12 +1521,12 @@
       </c>
       <c r="B8" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T14:21:46Z</t>
+          <t>2026-07-23T20:58:35Z</t>
         </is>
       </c>
       <c r="C8" s="60" t="inlineStr">
         <is>
-          <t>EU &amp; Europe</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D8" s="60" t="inlineStr">
@@ -1534,38 +1534,42 @@
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="E8" s="60" t="inlineStr"/>
+      <c r="E8" s="60" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence</t>
+        </is>
+      </c>
       <c r="F8" s="76" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G8" s="60" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Major Media</t>
         </is>
       </c>
       <c r="H8" s="60" t="inlineStr">
         <is>
-          <t>UK DSIT</t>
+          <t>BBC Technology</t>
         </is>
       </c>
       <c r="I8" s="60" t="inlineStr">
         <is>
-          <t>ガイダンス：研究における女性のためのチャーター</t>
+          <t>AIモデルのシャットダウンを許可する新法案が提案</t>
         </is>
       </c>
       <c r="J8" s="60" t="inlineStr">
         <is>
-          <t>UKの研究システムにおける女性の成果を改善するための自主的な取り組みが発表された。</t>
+          <t>新たに提案された法案は、公共の脅威をもたらすAIモデルのシャットダウンを政府に許可する内容である。</t>
         </is>
       </c>
       <c r="K8" s="60" t="inlineStr">
         <is>
-          <t>https://www.gov.uk/government/publications/women-in-research-charter</t>
+          <t>https://www.bbc.co.uk/news/articles/cx2vqj2e9x8o?at_medium=RSS&amp;at_campaign=rss</t>
         </is>
       </c>
       <c r="L8" s="60" t="inlineStr">
         <is>
-          <t>1e9fd9033d38bacea37c0f42</t>
+          <t>30744ac6eef4bc37b48358ce</t>
         </is>
       </c>
       <c r="M8" s="75" t="inlineStr">
@@ -1580,7 +1584,7 @@
       </c>
       <c r="O8" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy | Research System &amp; Talent / 焦点: 女性研究者の成果向上</t>
+          <t>枠: Innovation Policy / 政策分野: Regulation &amp; Governance / 焦点: AIモデルの規制</t>
         </is>
       </c>
     </row>
@@ -1592,22 +1596,22 @@
       </c>
       <c r="B9" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T14:12:14Z</t>
+          <t>2026-07-22T14:21:46Z</t>
         </is>
       </c>
       <c r="C9" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>EU &amp; Europe</t>
         </is>
       </c>
       <c r="D9" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="E9" s="60" t="inlineStr"/>
       <c r="F9" s="76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G9" s="60" t="inlineStr">
         <is>
@@ -1616,27 +1620,27 @@
       </c>
       <c r="H9" s="60" t="inlineStr">
         <is>
-          <t>DOE Office of Science News</t>
+          <t>UK DSIT</t>
         </is>
       </c>
       <c r="I9" s="60" t="inlineStr">
         <is>
-          <t>エネルギー長官クリス・ライト、AI駆動の科学発見を加速するための初のジェネシスミッションプロジェクトを発表</t>
+          <t>ガイダンス：研究における女性のためのチャーター</t>
         </is>
       </c>
       <c r="J9" s="60" t="inlineStr">
         <is>
-          <t>米国エネルギー省がAI駆動の科学発見を加速するために、全米から選ばれたプロジェクトを発表した。</t>
+          <t>UKの研究システムにおける女性の成果を改善するための自主的な取り組みが発表された。</t>
         </is>
       </c>
       <c r="K9" s="60" t="inlineStr">
         <is>
-          <t>https://www.energy.gov/articles/secretary-energy-chris-wright-announces-first-genesis-mission-projects-selected-accelerate</t>
+          <t>https://www.gov.uk/government/publications/women-in-research-charter</t>
         </is>
       </c>
       <c r="L9" s="60" t="inlineStr">
         <is>
-          <t>23fa1d6907c14d73ce3a41cd</t>
+          <t>1e9fd9033d38bacea37c0f42</t>
         </is>
       </c>
       <c r="M9" s="75" t="inlineStr">
@@ -1651,19 +1655,19 @@
       </c>
       <c r="O9" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 焦点: AI駆動の科学発見プロジェクト</t>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy | Research System &amp; Talent / 焦点: 女性研究者の成果向上</t>
         </is>
       </c>
     </row>
     <row r="10" ht="42" customHeight="1">
       <c r="A10" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:05:06+09:00</t>
+          <t>2026-07-26T20:29:40+09:00</t>
         </is>
       </c>
       <c r="B10" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T13:53:19Z</t>
+          <t>2026-07-22T14:12:14Z</t>
         </is>
       </c>
       <c r="C10" s="60" t="inlineStr">
@@ -1682,7 +1686,7 @@
         </is>
       </c>
       <c r="F10" s="76" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G10" s="60" t="inlineStr">
         <is>
@@ -1691,32 +1695,32 @@
       </c>
       <c r="H10" s="60" t="inlineStr">
         <is>
-          <t>National Science Foundation News</t>
+          <t>DOE Office of Science News</t>
         </is>
       </c>
       <c r="I10" s="60" t="inlineStr">
         <is>
-          <t>NSFがAIに関する国家戦略を推進する声明を発表</t>
+          <t>エネルギー長官クリス・ライト、AI駆動の科学発見を加速するための初のジェネシスミッションプロジェクトを発表</t>
         </is>
       </c>
       <c r="J10" s="60" t="inlineStr">
         <is>
-          <t>米国科学財団（NSF）は、AIに関する国家戦略を推進するための声明を発表しました。</t>
+          <t>米国エネルギー省がAI駆動の科学発見を加速するために、全米から選ばれたプロジェクトを発表した。</t>
         </is>
       </c>
       <c r="K10" s="60" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/news/statement-nsf-chief-staff-brian-stone-performing-duties-nsf-1</t>
+          <t>https://www.energy.gov/articles/secretary-energy-chris-wright-announces-first-genesis-mission-projects-selected-accelerate</t>
         </is>
       </c>
       <c r="L10" s="60" t="inlineStr">
         <is>
-          <t>123e2207578ca69c8f9c00a2</t>
+          <t>23fa1d6907c14d73ce3a41cd</t>
         </is>
       </c>
       <c r="M10" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:05:06+09:00</t>
+          <t>2026-07-26T20:29:40+09:00</t>
         </is>
       </c>
       <c r="N10" s="60" t="inlineStr">
@@ -1726,7 +1730,7 @@
       </c>
       <c r="O10" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 焦点: AIに関する国家戦略の推進</t>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 焦点: AI駆動の科学発見プロジェクト</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1742,7 @@
       </c>
       <c r="B11" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T13:53:12Z</t>
+          <t>2026-07-22T13:53:19Z</t>
         </is>
       </c>
       <c r="C11" s="60" t="inlineStr">
@@ -1757,7 +1761,7 @@
         </is>
       </c>
       <c r="F11" s="76" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G11" s="60" t="inlineStr">
         <is>
@@ -1771,22 +1775,22 @@
       </c>
       <c r="I11" s="60" t="inlineStr">
         <is>
-          <t>NSFの新しい取り組みがAIによる科学的発見のためのデータセットの価値を引き出す</t>
+          <t>NSFがAIに関する国家戦略を推進する声明を発表</t>
         </is>
       </c>
       <c r="J11" s="60" t="inlineStr">
         <is>
-          <t>米国科学財団（NSF）は、AIを活用した科学的発見のためのデータセットの価値を引き出す新しいプログラムを発表しました。</t>
+          <t>米国科学財団（NSF）は、AIに関する国家戦略を推進するための声明を発表しました。</t>
         </is>
       </c>
       <c r="K11" s="60" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/news/new-nsf-initiative-aims-unlock-dataset-value-ai-enabled</t>
+          <t>https://www.nsf.gov/news/statement-nsf-chief-staff-brian-stone-performing-duties-nsf-1</t>
         </is>
       </c>
       <c r="L11" s="60" t="inlineStr">
         <is>
-          <t>dcd819527d9b80141b26bcb8</t>
+          <t>123e2207578ca69c8f9c00a2</t>
         </is>
       </c>
       <c r="M11" s="75" t="inlineStr">
@@ -1801,19 +1805,19 @@
       </c>
       <c r="O11" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: R&amp;D Funding &amp; Tax Incentives / 焦点: AIを活用した科学的発見のためのデータセットの価値を引き出すプログラム</t>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 焦点: AIに関する国家戦略の推進</t>
         </is>
       </c>
     </row>
     <row r="12" ht="42" customHeight="1">
       <c r="A12" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:29:40+09:00</t>
+          <t>2026-07-26T19:05:06+09:00</t>
         </is>
       </c>
       <c r="B12" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T13:53:06Z</t>
+          <t>2026-07-22T13:53:12Z</t>
         </is>
       </c>
       <c r="C12" s="60" t="inlineStr">
@@ -1826,7 +1830,11 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="E12" s="60" t="inlineStr"/>
+      <c r="E12" s="60" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence</t>
+        </is>
+      </c>
       <c r="F12" s="76" t="n">
         <v>4</v>
       </c>
@@ -1842,27 +1850,27 @@
       </c>
       <c r="I12" s="60" t="inlineStr">
         <is>
-          <t>NSF、AI駆動の科学を進展させるために8300万ドルの投資を発表</t>
+          <t>NSFの新しい取り組みがAIによる科学的発見のためのデータセットの価値を引き出す</t>
         </is>
       </c>
       <c r="J12" s="60" t="inlineStr">
         <is>
-          <t>米国科学財団が8300万ドルの資金を通じて、AI駆動の科学を進展させるためのデータシステムとサービスの整備を発表した。</t>
+          <t>米国科学財団（NSF）は、AIを活用した科学的発見のためのデータセットの価値を引き出す新しいプログラムを発表しました。</t>
         </is>
       </c>
       <c r="K12" s="60" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/news/nsf-announces-83m-investment-integrated-data-systems</t>
+          <t>https://www.nsf.gov/news/new-nsf-initiative-aims-unlock-dataset-value-ai-enabled</t>
         </is>
       </c>
       <c r="L12" s="60" t="inlineStr">
         <is>
-          <t>018d40b7e6eb7aa4b8cfb5fa</t>
+          <t>dcd819527d9b80141b26bcb8</t>
         </is>
       </c>
       <c r="M12" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:29:40+09:00</t>
+          <t>2026-07-26T19:05:06+09:00</t>
         </is>
       </c>
       <c r="N12" s="60" t="inlineStr">
@@ -1872,7 +1880,7 @@
       </c>
       <c r="O12" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy | Research System &amp; Talent / 焦点: AI駆動の科学研究インフラ整備</t>
+          <t>枠: Innovation Policy / 政策分野: R&amp;D Funding &amp; Tax Incentives / 焦点: AIを活用した科学的発見のためのデータセットの価値を引き出すプログラム</t>
         </is>
       </c>
     </row>
@@ -1884,7 +1892,7 @@
       </c>
       <c r="B13" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T12:00:00Z</t>
+          <t>2026-07-22T13:53:06Z</t>
         </is>
       </c>
       <c r="C13" s="60" t="inlineStr">
@@ -1897,7 +1905,11 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="E13" s="60" t="inlineStr"/>
+      <c r="E13" s="60" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence</t>
+        </is>
+      </c>
       <c r="F13" s="76" t="n">
         <v>4</v>
       </c>
@@ -1908,27 +1920,27 @@
       </c>
       <c r="H13" s="60" t="inlineStr">
         <is>
-          <t>NIST News</t>
+          <t>National Science Foundation News</t>
         </is>
       </c>
       <c r="I13" s="60" t="inlineStr">
         <is>
-          <t>NISTが中小企業向けの資金提供機会を発表</t>
+          <t>NSF、AI駆動の科学を進展させるために8300万ドルの投資を発表</t>
         </is>
       </c>
       <c r="J13" s="60" t="inlineStr">
         <is>
-          <t>NIST MEPは、米国の中小企業を支援するための資金提供機会を発表し、2026年7月28日にウェビナーを開催する予定です。</t>
+          <t>米国科学財団が8300万ドルの資金を通じて、AI駆動の科学を進展させるためのデータシステムとサービスの整備を発表した。</t>
         </is>
       </c>
       <c r="K13" s="60" t="inlineStr">
         <is>
-          <t>https://www.nist.gov/news-events/news/2026/07/nist-announces-funding-opportunity-14-mep-centers-advance-small-and-medium</t>
+          <t>https://www.nsf.gov/news/nsf-announces-83m-investment-integrated-data-systems</t>
         </is>
       </c>
       <c r="L13" s="60" t="inlineStr">
         <is>
-          <t>5aa9c93bc7040291c9f08bfa</t>
+          <t>018d40b7e6eb7aa4b8cfb5fa</t>
         </is>
       </c>
       <c r="M13" s="75" t="inlineStr">
@@ -1943,72 +1955,68 @@
       </c>
       <c r="O13" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: R&amp;D Funding &amp; Tax Incentives | Public Procurement &amp; Industrial Policy / 焦点: 中小企業向けの資金提供</t>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy | Research System &amp; Talent / 焦点: AI駆動の科学研究インフラ整備</t>
         </is>
       </c>
     </row>
     <row r="14" ht="42" customHeight="1">
       <c r="A14" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T20:29:40+09:00</t>
         </is>
       </c>
       <c r="B14" s="75" t="inlineStr">
         <is>
-          <t>2026-07-21T14:48:28Z</t>
+          <t>2026-07-22T12:00:00Z</t>
         </is>
       </c>
       <c r="C14" s="60" t="inlineStr">
         <is>
-          <t>EU &amp; Europe</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D14" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="E14" s="60" t="inlineStr">
-        <is>
-          <t>Fusion Energy</t>
-        </is>
-      </c>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E14" s="60" t="inlineStr"/>
       <c r="F14" s="76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G14" s="60" t="inlineStr">
         <is>
-          <t>Industry Association</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H14" s="60" t="inlineStr">
         <is>
-          <t>Fusion Industry Association</t>
+          <t>NIST News</t>
         </is>
       </c>
       <c r="I14" s="60" t="inlineStr">
         <is>
-          <t>FIAが核融合のためのEU資金調達の道筋を示す</t>
+          <t>NISTが中小企業向けの資金提供機会を発表</t>
         </is>
       </c>
       <c r="J14" s="60" t="inlineStr">
         <is>
-          <t>核融合産業協会は、商業核融合エネルギーのための実用的なEU資金調達の道筋を示す論文を発表しました。核融合プロジェクトが研究から実証へ移行する際に必要な資金調達手段について論じています。</t>
+          <t>NIST MEPは、米国の中小企業を支援するための資金提供機会を発表し、2026年7月28日にウェビナーを開催する予定です。</t>
         </is>
       </c>
       <c r="K14" s="60" t="inlineStr">
         <is>
-          <t>https://www.fusionindustryassociation.org/fia-outlines-eu-financing-pathway-for-fusion/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=fia-outlines-eu-financing-pathway-for-fusion</t>
+          <t>https://www.nist.gov/news-events/news/2026/07/nist-announces-funding-opportunity-14-mep-centers-advance-small-and-medium</t>
         </is>
       </c>
       <c r="L14" s="60" t="inlineStr">
         <is>
-          <t>88af233d904d670250fa5a31</t>
+          <t>5aa9c93bc7040291c9f08bfa</t>
         </is>
       </c>
       <c r="M14" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T20:29:40+09:00</t>
         </is>
       </c>
       <c r="N14" s="60" t="inlineStr">
@@ -2018,7 +2026,7 @@
       </c>
       <c r="O14" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: R&amp;D Funding &amp; Tax Incentives / 焦点: 商業核融合エネルギーの資金調達</t>
+          <t>枠: Innovation Policy / 政策分野: R&amp;D Funding &amp; Tax Incentives | Public Procurement &amp; Industrial Policy / 焦点: 中小企業向けの資金提供</t>
         </is>
       </c>
     </row>
@@ -2030,7 +2038,7 @@
       </c>
       <c r="B15" s="75" t="inlineStr">
         <is>
-          <t>2026-07-17T18:42:47Z</t>
+          <t>2026-07-21T14:48:28Z</t>
         </is>
       </c>
       <c r="C15" s="60" t="inlineStr">
@@ -2049,7 +2057,7 @@
         </is>
       </c>
       <c r="F15" s="76" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G15" s="60" t="inlineStr">
         <is>
@@ -2063,22 +2071,22 @@
       </c>
       <c r="I15" s="60" t="inlineStr">
         <is>
-          <t>国際法専門家グループがEUの核融合競争力確保の必要性に関する論文を発表</t>
+          <t>FIAが核融合のためのEU資金調達の道筋を示す</t>
         </is>
       </c>
       <c r="J15" s="60" t="inlineStr">
         <is>
-          <t>国際法専門家グループが発表した論文は、EUが商業核融合において競争優位を持っているが、それを維持するためには今すぐ行動が必要であると主張しています。</t>
+          <t>核融合産業協会は、商業核融合エネルギーのための実用的なEU資金調達の道筋を示す論文を発表しました。核融合プロジェクトが研究から実証へ移行する際に必要な資金調達手段について論じています。</t>
         </is>
       </c>
       <c r="K15" s="60" t="inlineStr">
         <is>
-          <t>https://www.fusionindustryassociation.org/international-legal-expert-group-publish-paper-on-the-need-for-the-eu-to-secure-its-competitive-fusion-advantage/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=international-legal-expert-group-publish-paper-on-the-need-for-the-eu-to-secure-its-competitive-fusion-advantage</t>
+          <t>https://www.fusionindustryassociation.org/fia-outlines-eu-financing-pathway-for-fusion/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=fia-outlines-eu-financing-pathway-for-fusion</t>
         </is>
       </c>
       <c r="L15" s="60" t="inlineStr">
         <is>
-          <t>7ef6110ab078602757409abf</t>
+          <t>88af233d904d670250fa5a31</t>
         </is>
       </c>
       <c r="M15" s="75" t="inlineStr">
@@ -2093,7 +2101,7 @@
       </c>
       <c r="O15" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: Regulation &amp; Governance / 焦点: EUの核融合競争力の維持</t>
+          <t>枠: Innovation Policy / 政策分野: R&amp;D Funding &amp; Tax Incentives / 焦点: 商業核融合エネルギーの資金調達</t>
         </is>
       </c>
     </row>
@@ -2105,75 +2113,150 @@
       </c>
       <c r="B16" s="75" t="inlineStr">
         <is>
+          <t>2026-07-17T18:42:47Z</t>
+        </is>
+      </c>
+      <c r="C16" s="60" t="inlineStr">
+        <is>
+          <t>EU &amp; Europe</t>
+        </is>
+      </c>
+      <c r="D16" s="60" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E16" s="60" t="inlineStr">
+        <is>
+          <t>Fusion Energy</t>
+        </is>
+      </c>
+      <c r="F16" s="76" t="n">
+        <v>4</v>
+      </c>
+      <c r="G16" s="60" t="inlineStr">
+        <is>
+          <t>Industry Association</t>
+        </is>
+      </c>
+      <c r="H16" s="60" t="inlineStr">
+        <is>
+          <t>Fusion Industry Association</t>
+        </is>
+      </c>
+      <c r="I16" s="60" t="inlineStr">
+        <is>
+          <t>国際法専門家グループがEUの核融合競争力確保の必要性に関する論文を発表</t>
+        </is>
+      </c>
+      <c r="J16" s="60" t="inlineStr">
+        <is>
+          <t>国際法専門家グループが発表した論文は、EUが商業核融合において競争優位を持っているが、それを維持するためには今すぐ行動が必要であると主張しています。</t>
+        </is>
+      </c>
+      <c r="K16" s="60" t="inlineStr">
+        <is>
+          <t>https://www.fusionindustryassociation.org/international-legal-expert-group-publish-paper-on-the-need-for-the-eu-to-secure-its-competitive-fusion-advantage/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=international-legal-expert-group-publish-paper-on-the-need-for-the-eu-to-secure-its-competitive-fusion-advantage</t>
+        </is>
+      </c>
+      <c r="L16" s="60" t="inlineStr">
+        <is>
+          <t>7ef6110ab078602757409abf</t>
+        </is>
+      </c>
+      <c r="M16" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T18:56:03+09:00</t>
+        </is>
+      </c>
+      <c r="N16" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O16" s="60" t="inlineStr">
+        <is>
+          <t>枠: Innovation Policy / 政策分野: Regulation &amp; Governance / 焦点: EUの核融合競争力の維持</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="42" customHeight="1">
+      <c r="A17" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T18:56:03+09:00</t>
+        </is>
+      </c>
+      <c r="B17" s="75" t="inlineStr">
+        <is>
           <t>2026-07-15T17:47:57Z</t>
         </is>
       </c>
-      <c r="C16" s="60" t="inlineStr">
+      <c r="C17" s="60" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="D16" s="60" t="inlineStr">
+      <c r="D17" s="60" t="inlineStr">
         <is>
           <t>Global</t>
         </is>
       </c>
-      <c r="E16" s="60" t="inlineStr">
+      <c r="E17" s="60" t="inlineStr">
         <is>
           <t>Fusion Energy</t>
         </is>
       </c>
-      <c r="F16" s="76" t="n">
+      <c r="F17" s="76" t="n">
         <v>3</v>
       </c>
-      <c r="G16" s="60" t="inlineStr">
+      <c r="G17" s="60" t="inlineStr">
         <is>
           <t>Industry Association</t>
         </is>
       </c>
-      <c r="H16" s="60" t="inlineStr">
+      <c r="H17" s="60" t="inlineStr">
         <is>
           <t>Fusion Industry Association</t>
         </is>
       </c>
-      <c r="I16" s="60" t="inlineStr">
+      <c r="I17" s="60" t="inlineStr">
         <is>
           <t>スターロライトエンジンが60.6億円を調達</t>
         </is>
       </c>
-      <c r="J16" s="60" t="inlineStr">
+      <c r="J17" s="60" t="inlineStr">
         <is>
           <t>スターロライトエンジンは、FASTの開発を加速するために60.6億円を調達しました。この会社は、日本のJT-60SAプログラムや国際的な取り組みを基にしたトカマク型核融合機を開発しています。</t>
         </is>
       </c>
-      <c r="K16" s="60" t="inlineStr">
+      <c r="K17" s="60" t="inlineStr">
         <is>
           <t>https://www.nikkei.com/article/DGXZQOUC152ET0V10C26A7000000/#new_tab?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=starlight-engine-raises-jpy-6-06-billion</t>
         </is>
       </c>
-      <c r="L16" s="60" t="inlineStr">
+      <c r="L17" s="60" t="inlineStr">
         <is>
           <t>2f29b005896c3737ab846738</t>
         </is>
       </c>
-      <c r="M16" s="75" t="inlineStr">
+      <c r="M17" s="75" t="inlineStr">
         <is>
           <t>2026-07-26T18:56:03+09:00</t>
         </is>
       </c>
-      <c r="N16" s="60" t="inlineStr">
+      <c r="N17" s="60" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="O16" s="60" t="inlineStr">
-        <is>
-          <t>枠: Innovation Policy / 政策分野: R&amp;D Funding &amp; Tax Incentives / 焦点: トカマク型核融合機の開発</t>
+      <c r="O17" s="60" t="inlineStr">
+        <is>
+          <t>枠: Technology Innovation / 焦点: トカマク型核融合機の開発</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:O16"/>
+  <autoFilter ref="A3:O17"/>
   <mergeCells count="2">
     <mergeCell ref="A1:O1"/>
     <mergeCell ref="A2:O2"/>
@@ -2191,7 +2274,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="N4:N16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="N4:N17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"New,Reviewed,Follow-up,Archived"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2209,10 +2292,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId14"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId15"/>
   </tableParts>
 </worksheet>
 </file>
@@ -4512,7 +4596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4591,7 +4675,7 @@
     <row r="4" ht="42" customHeight="1">
       <c r="A4" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:34:08+09:00</t>
+          <t>2026-07-26T20:36:29+09:00</t>
         </is>
       </c>
       <c r="B4" s="77" t="n">
@@ -4601,7 +4685,7 @@
         <v>28</v>
       </c>
       <c r="D4" s="77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" s="77" t="n">
         <v>74</v>
@@ -4610,7 +4694,7 @@
         <v>10</v>
       </c>
       <c r="G4" s="77" t="n">
-        <v>20.27</v>
+        <v>93.7</v>
       </c>
       <c r="H4" s="60" t="inlineStr">
         <is>
@@ -4621,7 +4705,7 @@
     <row r="5">
       <c r="A5" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:29:40+09:00</t>
+          <t>2026-07-26T20:34:08+09:00</t>
         </is>
       </c>
       <c r="B5" s="77" t="n">
@@ -4631,16 +4715,16 @@
         <v>28</v>
       </c>
       <c r="D5" s="77" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E5" s="77" t="n">
-        <v>11</v>
+        <v>74</v>
       </c>
       <c r="F5" s="77" t="n">
         <v>10</v>
       </c>
       <c r="G5" s="77" t="n">
-        <v>141.79</v>
+        <v>20.27</v>
       </c>
       <c r="H5" s="60" t="inlineStr">
         <is>
@@ -4651,7 +4735,7 @@
     <row r="6">
       <c r="A6" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:24:57+09:00</t>
+          <t>2026-07-26T20:29:40+09:00</t>
         </is>
       </c>
       <c r="B6" s="77" t="n">
@@ -4661,16 +4745,16 @@
         <v>28</v>
       </c>
       <c r="D6" s="77" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E6" s="77" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="F6" s="77" t="n">
         <v>10</v>
       </c>
       <c r="G6" s="77" t="n">
-        <v>134.95</v>
+        <v>141.79</v>
       </c>
       <c r="H6" s="60" t="inlineStr">
         <is>
@@ -4681,7 +4765,7 @@
     <row r="7">
       <c r="A7" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:19:15+09:00</t>
+          <t>2026-07-26T20:24:57+09:00</t>
         </is>
       </c>
       <c r="B7" s="77" t="n">
@@ -4691,16 +4775,16 @@
         <v>28</v>
       </c>
       <c r="D7" s="77" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E7" s="77" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F7" s="77" t="n">
         <v>10</v>
       </c>
       <c r="G7" s="77" t="n">
-        <v>134.05</v>
+        <v>134.95</v>
       </c>
       <c r="H7" s="60" t="inlineStr">
         <is>
@@ -4711,26 +4795,26 @@
     <row r="8">
       <c r="A8" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:13:43+09:00</t>
+          <t>2026-07-26T20:19:15+09:00</t>
         </is>
       </c>
       <c r="B8" s="77" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C8" s="77" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D8" s="77" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E8" s="77" t="n">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="F8" s="77" t="n">
         <v>10</v>
       </c>
       <c r="G8" s="77" t="n">
-        <v>162.46</v>
+        <v>134.05</v>
       </c>
       <c r="H8" s="60" t="inlineStr">
         <is>
@@ -4741,7 +4825,7 @@
     <row r="9">
       <c r="A9" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:00:03+09:00</t>
+          <t>2026-07-26T20:13:43+09:00</t>
         </is>
       </c>
       <c r="B9" s="77" t="n">
@@ -4751,16 +4835,16 @@
         <v>24</v>
       </c>
       <c r="D9" s="77" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E9" s="77" t="n">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="F9" s="77" t="n">
         <v>10</v>
       </c>
       <c r="G9" s="77" t="n">
-        <v>154.27</v>
+        <v>162.46</v>
       </c>
       <c r="H9" s="60" t="inlineStr">
         <is>
@@ -4771,7 +4855,7 @@
     <row r="10">
       <c r="A10" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:51:39+09:00</t>
+          <t>2026-07-26T20:00:03+09:00</t>
         </is>
       </c>
       <c r="B10" s="77" t="n">
@@ -4781,16 +4865,16 @@
         <v>24</v>
       </c>
       <c r="D10" s="77" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E10" s="77" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="F10" s="77" t="n">
         <v>10</v>
       </c>
       <c r="G10" s="77" t="n">
-        <v>11.55</v>
+        <v>154.27</v>
       </c>
       <c r="H10" s="60" t="inlineStr">
         <is>
@@ -4801,26 +4885,26 @@
     <row r="11">
       <c r="A11" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:10:55+09:00</t>
+          <t>2026-07-26T19:51:39+09:00</t>
         </is>
       </c>
       <c r="B11" s="77" t="n">
         <v>34</v>
       </c>
       <c r="C11" s="77" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D11" s="77" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E11" s="77" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F11" s="77" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G11" s="77" t="n">
-        <v>194.65</v>
+        <v>11.55</v>
       </c>
       <c r="H11" s="60" t="inlineStr">
         <is>
@@ -4831,26 +4915,26 @@
     <row r="12">
       <c r="A12" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:05:06+09:00</t>
+          <t>2026-07-26T19:10:55+09:00</t>
         </is>
       </c>
       <c r="B12" s="77" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C12" s="77" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D12" s="77" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E12" s="77" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="F12" s="77" t="n">
         <v>9</v>
       </c>
       <c r="G12" s="77" t="n">
-        <v>165.89</v>
+        <v>194.65</v>
       </c>
       <c r="H12" s="60" t="inlineStr">
         <is>
@@ -4861,35 +4945,65 @@
     <row r="13">
       <c r="A13" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T19:05:06+09:00</t>
         </is>
       </c>
       <c r="B13" s="77" t="n">
         <v>33</v>
       </c>
       <c r="C13" s="77" t="n">
+        <v>24</v>
+      </c>
+      <c r="D13" s="77" t="n">
+        <v>5</v>
+      </c>
+      <c r="E13" s="77" t="n">
+        <v>39</v>
+      </c>
+      <c r="F13" s="77" t="n">
+        <v>9</v>
+      </c>
+      <c r="G13" s="77" t="n">
+        <v>165.89</v>
+      </c>
+      <c r="H13" s="60" t="inlineStr">
+        <is>
+          <t>Daily update</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T18:56:03+09:00</t>
+        </is>
+      </c>
+      <c r="B14" s="77" t="n">
+        <v>33</v>
+      </c>
+      <c r="C14" s="77" t="n">
         <v>20</v>
       </c>
-      <c r="D13" s="77" t="n">
+      <c r="D14" s="77" t="n">
         <v>94</v>
       </c>
-      <c r="E13" s="77" t="n">
+      <c r="E14" s="77" t="n">
         <v>0</v>
       </c>
-      <c r="F13" s="77" t="n">
+      <c r="F14" s="77" t="n">
         <v>13</v>
       </c>
-      <c r="G13" s="77" t="n">
+      <c r="G14" s="77" t="n">
         <v>129.43</v>
       </c>
-      <c r="H13" s="60" t="inlineStr">
+      <c r="H14" s="60" t="inlineStr">
         <is>
           <t>Initial lookback</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:H13"/>
+  <autoFilter ref="A3:H14"/>
   <mergeCells count="2">
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>

--- a/docs/innovation_news_ledger.xlsx
+++ b/docs/innovation_news_ledger.xlsx
@@ -9,9 +9,9 @@
     <sheet name="Run Log" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'News Ledger'!$A$3:$O$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Source Registry'!$A$3:$K$41</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Run Log'!$A$3:$H$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'News Ledger'!$A$3:$O$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Source Registry'!$A$3:$K$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Run Log'!$A$3:$H$15</definedName>
   </definedNames>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -472,7 +472,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="NewsLedgerTable" displayName="NewsLedgerTable" ref="A3:O17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="NewsLedgerTable" displayName="NewsLedgerTable" ref="A3:O33" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <autoFilter ref="A3:O4"/>
   <tableColumns count="15">
     <tableColumn id="1" name="Collected At (JST)"/>
@@ -496,7 +496,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="SourceRegistryTable" displayName="SourceRegistryTable" ref="A3:K41" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="SourceRegistryTable" displayName="SourceRegistryTable" ref="A3:K44" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <autoFilter ref="A3:K37"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Active"/>
@@ -516,7 +516,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="RunLogTable" displayName="RunLogTable" ref="A3:H14" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="RunLogTable" displayName="RunLogTable" ref="A3:H15" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <autoFilter ref="A3:H4"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Run Time (JST)"/>
@@ -800,7 +800,7 @@
       </c>
       <c r="B5" s="25" t="inlineStr">
         <is>
-          <t>2026-07-26T20:36:29+09:00</t>
+          <t>2026-07-26T21:02:36+09:00</t>
         </is>
       </c>
       <c r="C5" s="46" t="n"/>
@@ -1088,7 +1088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:O33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1284,24 +1284,24 @@
       </c>
       <c r="O4" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 焦点: メモリおよびファウンドリ技術の協力</t>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: メモリおよびファウンドリ技術の協力</t>
         </is>
       </c>
     </row>
     <row r="5" ht="42" customHeight="1">
       <c r="A5" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T21:02:36+09:00</t>
         </is>
       </c>
       <c r="B5" s="75" t="inlineStr">
         <is>
-          <t>2026-07-24T16:46:59Z</t>
+          <t>2026-07-25T07:03:59Z</t>
         </is>
       </c>
       <c r="C5" s="60" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D5" s="60" t="inlineStr">
@@ -1311,11 +1311,11 @@
       </c>
       <c r="E5" s="60" t="inlineStr">
         <is>
-          <t>Semiconductors &amp; Telecom</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="F5" s="76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G5" s="60" t="inlineStr">
         <is>
@@ -1324,32 +1324,32 @@
       </c>
       <c r="H5" s="60" t="inlineStr">
         <is>
-          <t>Intel Newsroom</t>
+          <t>OpenAI News</t>
         </is>
       </c>
       <c r="I5" s="60" t="inlineStr">
         <is>
-          <t>インテルとレンズテクノロジーがAI時代の先進半導体パッケージングを実現するために協力</t>
+          <t>サイバーセキュリティ助成プログラムを通じて防御者を強化</t>
         </is>
       </c>
       <c r="J5" s="60" t="inlineStr">
         <is>
-          <t>インテルとレンズテクノロジーが、AI時代に向けた先進的な半導体パッケージング技術の開発に向けて戦略的な協力を発表した。</t>
+          <t>サイバーセキュリティにおける革新的な研究とAIの統合が強調されている助成プログラムについて報告。</t>
         </is>
       </c>
       <c r="K5" s="60" t="inlineStr">
         <is>
-          <t>https://newsroom.intel.com/new-technologies/intel-and-lens-technology-collaborate-to-enable-advanced-semiconductor-packaging-for-the-ai-era</t>
+          <t>https://openai.com/index/empowering-defenders-through-our-cybersecurity-grant-program</t>
         </is>
       </c>
       <c r="L5" s="60" t="inlineStr">
         <is>
-          <t>10eedf14d7d6b636e24e447d</t>
+          <t>c2c6b4643598298d6a0dbf2d</t>
         </is>
       </c>
       <c r="M5" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T21:02:36+09:00</t>
         </is>
       </c>
       <c r="N5" s="60" t="inlineStr">
@@ -1359,19 +1359,19 @@
       </c>
       <c r="O5" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 焦点: 先進半導体パッケージング技術</t>
+          <t>枠: Innovation Policy / 政策分野: R&amp;D Funding &amp; Tax Incentives / 学術区分: News &amp; Official Release / 焦点: サイバーセキュリティにおけるAI統合 / Historical backfill from an allowlisted source.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="42" customHeight="1">
       <c r="A6" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:29:40+09:00</t>
+          <t>2026-07-26T18:56:03+09:00</t>
         </is>
       </c>
       <c r="B6" s="75" t="inlineStr">
         <is>
-          <t>2026-07-24T02:35:52Z</t>
+          <t>2026-07-24T16:46:59Z</t>
         </is>
       </c>
       <c r="C6" s="60" t="inlineStr">
@@ -1381,12 +1381,12 @@
       </c>
       <c r="D6" s="60" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E6" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence | Robotics</t>
+          <t>Semiconductors &amp; Telecom</t>
         </is>
       </c>
       <c r="F6" s="76" t="n">
@@ -1394,37 +1394,37 @@
       </c>
       <c r="G6" s="60" t="inlineStr">
         <is>
-          <t>Major Media</t>
+          <t>Official Company</t>
         </is>
       </c>
       <c r="H6" s="60" t="inlineStr">
         <is>
-          <t>South China Morning Post Technology</t>
+          <t>Intel Newsroom</t>
         </is>
       </c>
       <c r="I6" s="60" t="inlineStr">
         <is>
-          <t>中国のロボット共働者が増加中。AIコボットに挨拶を</t>
+          <t>インテルとレンズテクノロジーがAI時代の先進半導体パッケージングを実現するために協力</t>
         </is>
       </c>
       <c r="J6" s="60" t="inlineStr">
         <is>
-          <t>中国のヒューマノイドロボットや自動化工場が注目される中、協働ロボット（コボット）が進化している。最新モデルはコーディング知識を必要とせず、自然言語での指示に応じる。</t>
+          <t>インテルとレンズテクノロジーが、AI時代に向けた先進的な半導体パッケージング技術の開発に向けて戦略的な協力を発表した。</t>
         </is>
       </c>
       <c r="K6" s="60" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/plus/tech/tech-trends/article/3361664/chinese-robot-co-workers-rise-say-hello-ai-cobots?utm_source=rss_feed</t>
+          <t>https://newsroom.intel.com/new-technologies/intel-and-lens-technology-collaborate-to-enable-advanced-semiconductor-packaging-for-the-ai-era</t>
         </is>
       </c>
       <c r="L6" s="60" t="inlineStr">
         <is>
-          <t>00cfbfef6982b98ed0351899</t>
+          <t>10eedf14d7d6b636e24e447d</t>
         </is>
       </c>
       <c r="M6" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:29:40+09:00</t>
+          <t>2026-07-26T18:56:03+09:00</t>
         </is>
       </c>
       <c r="N6" s="60" t="inlineStr">
@@ -1434,72 +1434,72 @@
       </c>
       <c r="O6" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 焦点: 協働ロボット（コボット）</t>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: 先進半導体パッケージング技術</t>
         </is>
       </c>
     </row>
     <row r="7" ht="42" customHeight="1">
       <c r="A7" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:36:29+09:00</t>
+          <t>2026-07-26T20:29:40+09:00</t>
         </is>
       </c>
       <c r="B7" s="75" t="inlineStr">
         <is>
-          <t>2026-07-24T00:00:00Z</t>
+          <t>2026-07-24T02:35:52Z</t>
         </is>
       </c>
       <c r="C7" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="D7" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="E7" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Artificial Intelligence | Robotics</t>
         </is>
       </c>
       <c r="F7" s="76" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G7" s="60" t="inlineStr">
         <is>
-          <t>Scientific Publication</t>
+          <t>Major Media</t>
         </is>
       </c>
       <c r="H7" s="60" t="inlineStr">
         <is>
-          <t>Nature</t>
+          <t>South China Morning Post Technology</t>
         </is>
       </c>
       <c r="I7" s="60" t="inlineStr">
         <is>
-          <t>ホワイトハウスがAI資金を発表 — 米国科学の新時代を示唆</t>
+          <t>中国のロボット共働者が増加中。AIコボットに挨拶を</t>
         </is>
       </c>
       <c r="J7" s="60" t="inlineStr">
         <is>
-          <t>米国の科学顧問がAI研究を加速するための資金の見直しを呼びかけ、助成金を配布した。</t>
+          <t>中国のヒューマノイドロボットや自動化工場が注目される中、協働ロボット（コボット）が進化している。最新モデルはコーディング知識を必要とせず、自然言語での指示に応じる。</t>
         </is>
       </c>
       <c r="K7" s="60" t="inlineStr">
         <is>
-          <t>https://www.nature.com/articles/d41586-026-02332-8</t>
+          <t>https://www.scmp.com/plus/tech/tech-trends/article/3361664/chinese-robot-co-workers-rise-say-hello-ai-cobots?utm_source=rss_feed</t>
         </is>
       </c>
       <c r="L7" s="60" t="inlineStr">
         <is>
-          <t>856206151844f412d95b7a9b</t>
+          <t>00cfbfef6982b98ed0351899</t>
         </is>
       </c>
       <c r="M7" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:36:29+09:00</t>
+          <t>2026-07-26T20:29:40+09:00</t>
         </is>
       </c>
       <c r="N7" s="60" t="inlineStr">
@@ -1509,19 +1509,19 @@
       </c>
       <c r="O7" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: R&amp;D Funding &amp; Tax Incentives / 焦点: AI研究の助成金</t>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: 協働ロボット（コボット）</t>
         </is>
       </c>
     </row>
     <row r="8" ht="42" customHeight="1">
       <c r="A8" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:29:40+09:00</t>
+          <t>2026-07-26T20:36:29+09:00</t>
         </is>
       </c>
       <c r="B8" s="75" t="inlineStr">
         <is>
-          <t>2026-07-23T20:58:35Z</t>
+          <t>2026-07-24T00:00:00Z</t>
         </is>
       </c>
       <c r="C8" s="60" t="inlineStr">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="D8" s="60" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="E8" s="60" t="inlineStr">
@@ -1540,41 +1540,41 @@
         </is>
       </c>
       <c r="F8" s="76" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G8" s="60" t="inlineStr">
         <is>
-          <t>Major Media</t>
+          <t>Scientific Publication</t>
         </is>
       </c>
       <c r="H8" s="60" t="inlineStr">
         <is>
-          <t>BBC Technology</t>
+          <t>Nature</t>
         </is>
       </c>
       <c r="I8" s="60" t="inlineStr">
         <is>
-          <t>AIモデルのシャットダウンを許可する新法案が提案</t>
+          <t>ホワイトハウスがAI資金を発表 — 米国科学の新時代を示唆</t>
         </is>
       </c>
       <c r="J8" s="60" t="inlineStr">
         <is>
-          <t>新たに提案された法案は、公共の脅威をもたらすAIモデルのシャットダウンを政府に許可する内容である。</t>
+          <t>米国の科学顧問がAI研究を加速するための資金の見直しを呼びかけ、助成金を配布した。</t>
         </is>
       </c>
       <c r="K8" s="60" t="inlineStr">
         <is>
-          <t>https://www.bbc.co.uk/news/articles/cx2vqj2e9x8o?at_medium=RSS&amp;at_campaign=rss</t>
+          <t>https://www.nature.com/articles/d41586-026-02332-8</t>
         </is>
       </c>
       <c r="L8" s="60" t="inlineStr">
         <is>
-          <t>30744ac6eef4bc37b48358ce</t>
+          <t>856206151844f412d95b7a9b</t>
         </is>
       </c>
       <c r="M8" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:29:40+09:00</t>
+          <t>2026-07-26T20:36:29+09:00</t>
         </is>
       </c>
       <c r="N8" s="60" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="O8" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: Regulation &amp; Governance / 焦点: AIモデルの規制</t>
+          <t>枠: Innovation Policy / 政策分野: R&amp;D Funding &amp; Tax Incentives / 学術区分: News &amp; Official Release / 焦点: AI研究の助成金</t>
         </is>
       </c>
     </row>
@@ -1596,12 +1596,12 @@
       </c>
       <c r="B9" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T14:21:46Z</t>
+          <t>2026-07-23T20:58:35Z</t>
         </is>
       </c>
       <c r="C9" s="60" t="inlineStr">
         <is>
-          <t>EU &amp; Europe</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D9" s="60" t="inlineStr">
@@ -1609,38 +1609,42 @@
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="E9" s="60" t="inlineStr"/>
+      <c r="E9" s="60" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence</t>
+        </is>
+      </c>
       <c r="F9" s="76" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G9" s="60" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Major Media</t>
         </is>
       </c>
       <c r="H9" s="60" t="inlineStr">
         <is>
-          <t>UK DSIT</t>
+          <t>BBC Technology</t>
         </is>
       </c>
       <c r="I9" s="60" t="inlineStr">
         <is>
-          <t>ガイダンス：研究における女性のためのチャーター</t>
+          <t>AIモデルのシャットダウンを許可する新法案が提案</t>
         </is>
       </c>
       <c r="J9" s="60" t="inlineStr">
         <is>
-          <t>UKの研究システムにおける女性の成果を改善するための自主的な取り組みが発表された。</t>
+          <t>新たに提案された法案は、公共の脅威をもたらすAIモデルのシャットダウンを政府に許可する内容である。</t>
         </is>
       </c>
       <c r="K9" s="60" t="inlineStr">
         <is>
-          <t>https://www.gov.uk/government/publications/women-in-research-charter</t>
+          <t>https://www.bbc.co.uk/news/articles/cx2vqj2e9x8o?at_medium=RSS&amp;at_campaign=rss</t>
         </is>
       </c>
       <c r="L9" s="60" t="inlineStr">
         <is>
-          <t>1e9fd9033d38bacea37c0f42</t>
+          <t>30744ac6eef4bc37b48358ce</t>
         </is>
       </c>
       <c r="M9" s="75" t="inlineStr">
@@ -1655,19 +1659,19 @@
       </c>
       <c r="O9" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy | Research System &amp; Talent / 焦点: 女性研究者の成果向上</t>
+          <t>枠: Innovation Policy / 政策分野: Regulation &amp; Governance / 学術区分: News &amp; Official Release / 焦点: AIモデルの規制</t>
         </is>
       </c>
     </row>
     <row r="10" ht="42" customHeight="1">
       <c r="A10" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:29:40+09:00</t>
+          <t>2026-07-26T21:02:36+09:00</t>
         </is>
       </c>
       <c r="B10" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T14:12:14Z</t>
+          <t>2026-07-23T17:13:03Z</t>
         </is>
       </c>
       <c r="C10" s="60" t="inlineStr">
@@ -1682,11 +1686,11 @@
       </c>
       <c r="E10" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Quantum | Healthcare</t>
         </is>
       </c>
       <c r="F10" s="76" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G10" s="60" t="inlineStr">
         <is>
@@ -1695,32 +1699,32 @@
       </c>
       <c r="H10" s="60" t="inlineStr">
         <is>
-          <t>DOE Office of Science News</t>
+          <t>NIH News Releases</t>
         </is>
       </c>
       <c r="I10" s="60" t="inlineStr">
         <is>
-          <t>エネルギー長官クリス・ライト、AI駆動の科学発見を加速するための初のジェネシスミッションプロジェクトを発表</t>
+          <t>NIH量子コンピューティングチャレンジ</t>
         </is>
       </c>
       <c r="J10" s="60" t="inlineStr">
         <is>
-          <t>米国エネルギー省がAI駆動の科学発見を加速するために、全米から選ばれたプロジェクトを発表した。</t>
+          <t>NIHの量子コンピューティングチャレンジは、既存の量子アルゴリズムを最適化し、医療問題に対する新しい解決策を開発することを目指しています。</t>
         </is>
       </c>
       <c r="K10" s="60" t="inlineStr">
         <is>
-          <t>https://www.energy.gov/articles/secretary-energy-chris-wright-announces-first-genesis-mission-projects-selected-accelerate</t>
+          <t>https://nih.gov/challenges/nih-quantum-computing-challenge</t>
         </is>
       </c>
       <c r="L10" s="60" t="inlineStr">
         <is>
-          <t>23fa1d6907c14d73ce3a41cd</t>
+          <t>a7fdeab66ca07d0508bd1ad7</t>
         </is>
       </c>
       <c r="M10" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:29:40+09:00</t>
+          <t>2026-07-26T21:02:36+09:00</t>
         </is>
       </c>
       <c r="N10" s="60" t="inlineStr">
@@ -1730,72 +1734,72 @@
       </c>
       <c r="O10" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 焦点: AI駆動の科学発見プロジェクト</t>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: 量子アルゴリズムの最適化と展開 / Historical backfill from an allowlisted source.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="42" customHeight="1">
       <c r="A11" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:05:06+09:00</t>
+          <t>2026-07-26T21:02:36+09:00</t>
         </is>
       </c>
       <c r="B11" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T13:53:19Z</t>
+          <t>2026-07-23T11:53:20Z</t>
         </is>
       </c>
       <c r="C11" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="D11" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>China / Germany</t>
         </is>
       </c>
       <c r="E11" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Semiconductors &amp; Telecom</t>
         </is>
       </c>
       <c r="F11" s="76" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G11" s="60" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Policy Institute</t>
         </is>
       </c>
       <c r="H11" s="60" t="inlineStr">
         <is>
-          <t>National Science Foundation News</t>
+          <t>MERICS</t>
         </is>
       </c>
       <c r="I11" s="60" t="inlineStr">
         <is>
-          <t>NSFがAIに関する国家戦略を推進する声明を発表</t>
+          <t>MERICS 閉鎖型ワークショップ: 中国の新しい半導体技術の進展とそれが欧州に与える影響</t>
         </is>
       </c>
       <c r="J11" s="60" t="inlineStr">
         <is>
-          <t>米国科学財団（NSF）は、AIに関する国家戦略を推進するための声明を発表しました。</t>
+          <t>MERICSは、中国の新しい半導体技術の進展とそれが欧州に与える影響についてのワークショップを開催しました。</t>
         </is>
       </c>
       <c r="K11" s="60" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/news/statement-nsf-chief-staff-brian-stone-performing-duties-nsf-1</t>
+          <t>https://merics.org/en/events/merics-closed-door-workshop-chinas-advancements-new-semiconductor-technologies-and-their</t>
         </is>
       </c>
       <c r="L11" s="60" t="inlineStr">
         <is>
-          <t>123e2207578ca69c8f9c00a2</t>
+          <t>f88b1d25b6392512e0a6bf5c</t>
         </is>
       </c>
       <c r="M11" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:05:06+09:00</t>
+          <t>2026-07-26T21:02:36+09:00</t>
         </is>
       </c>
       <c r="N11" s="60" t="inlineStr">
@@ -1805,72 +1809,72 @@
       </c>
       <c r="O11" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 焦点: AIに関する国家戦略の推進</t>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: 中国の半導体技術の進展 / Historical backfill from an allowlisted source.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="42" customHeight="1">
       <c r="A12" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:05:06+09:00</t>
+          <t>2026-07-26T21:02:36+09:00</t>
         </is>
       </c>
       <c r="B12" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T13:53:12Z</t>
+          <t>2026-07-23T08:00:10Z</t>
         </is>
       </c>
       <c r="C12" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="D12" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="E12" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Artificial Intelligence | Robotics</t>
         </is>
       </c>
       <c r="F12" s="76" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G12" s="60" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Major Media</t>
         </is>
       </c>
       <c r="H12" s="60" t="inlineStr">
         <is>
-          <t>National Science Foundation News</t>
+          <t>South China Morning Post Technology</t>
         </is>
       </c>
       <c r="I12" s="60" t="inlineStr">
         <is>
-          <t>NSFの新しい取り組みがAIによる科学的発見のためのデータセットの価値を引き出す</t>
+          <t>アリババのユニットが5-in-1 AIでロボットに統一された脳と体を提供</t>
         </is>
       </c>
       <c r="J12" s="60" t="inlineStr">
         <is>
-          <t>米国科学財団（NSF）は、AIを活用した科学的発見のためのデータセットの価値を引き出す新しいプログラムを発表しました。</t>
+          <t>アリババグループのマッピングユニットが、ロボットの各要素を統合する新しい技術フレームワークを発表しました。</t>
         </is>
       </c>
       <c r="K12" s="60" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/news/new-nsf-initiative-aims-unlock-dataset-value-ai-enabled</t>
+          <t>https://www.scmp.com/tech/big-tech/article/3361564/alibaba-unit-says-5-1-ai-gives-robots-unified-brain-body-and-limbs?utm_source=rss_feed</t>
         </is>
       </c>
       <c r="L12" s="60" t="inlineStr">
         <is>
-          <t>dcd819527d9b80141b26bcb8</t>
+          <t>9bbfcd1dad0cdcf2e946a9c2</t>
         </is>
       </c>
       <c r="M12" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:05:06+09:00</t>
+          <t>2026-07-26T21:02:36+09:00</t>
         </is>
       </c>
       <c r="N12" s="60" t="inlineStr">
@@ -1880,7 +1884,7 @@
       </c>
       <c r="O12" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: R&amp;D Funding &amp; Tax Incentives / 焦点: AIを活用した科学的発見のためのデータセットの価値を引き出すプログラム</t>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: ロボットの統合システム</t>
         </is>
       </c>
     </row>
@@ -1892,24 +1896,20 @@
       </c>
       <c r="B13" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T13:53:06Z</t>
+          <t>2026-07-22T14:21:46Z</t>
         </is>
       </c>
       <c r="C13" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>EU &amp; Europe</t>
         </is>
       </c>
       <c r="D13" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E13" s="60" t="inlineStr">
-        <is>
-          <t>Artificial Intelligence</t>
-        </is>
-      </c>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="E13" s="60" t="inlineStr"/>
       <c r="F13" s="76" t="n">
         <v>4</v>
       </c>
@@ -1920,27 +1920,27 @@
       </c>
       <c r="H13" s="60" t="inlineStr">
         <is>
-          <t>National Science Foundation News</t>
+          <t>UK DSIT</t>
         </is>
       </c>
       <c r="I13" s="60" t="inlineStr">
         <is>
-          <t>NSF、AI駆動の科学を進展させるために8300万ドルの投資を発表</t>
+          <t>ガイダンス：研究における女性のためのチャーター</t>
         </is>
       </c>
       <c r="J13" s="60" t="inlineStr">
         <is>
-          <t>米国科学財団が8300万ドルの資金を通じて、AI駆動の科学を進展させるためのデータシステムとサービスの整備を発表した。</t>
+          <t>UKの研究システムにおける女性の成果を改善するための自主的な取り組みが発表された。</t>
         </is>
       </c>
       <c r="K13" s="60" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/news/nsf-announces-83m-investment-integrated-data-systems</t>
+          <t>https://www.gov.uk/government/publications/women-in-research-charter</t>
         </is>
       </c>
       <c r="L13" s="60" t="inlineStr">
         <is>
-          <t>018d40b7e6eb7aa4b8cfb5fa</t>
+          <t>1e9fd9033d38bacea37c0f42</t>
         </is>
       </c>
       <c r="M13" s="75" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="O13" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy | Research System &amp; Talent / 焦点: AI駆動の科学研究インフラ整備</t>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy | Research System &amp; Talent / 学術区分: News &amp; Official Release / 焦点: 女性研究者の成果向上</t>
         </is>
       </c>
     </row>
@@ -1967,7 +1967,7 @@
       </c>
       <c r="B14" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T12:00:00Z</t>
+          <t>2026-07-22T14:12:14Z</t>
         </is>
       </c>
       <c r="C14" s="60" t="inlineStr">
@@ -1980,9 +1980,13 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="E14" s="60" t="inlineStr"/>
+      <c r="E14" s="60" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence</t>
+        </is>
+      </c>
       <c r="F14" s="76" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G14" s="60" t="inlineStr">
         <is>
@@ -1991,27 +1995,27 @@
       </c>
       <c r="H14" s="60" t="inlineStr">
         <is>
-          <t>NIST News</t>
+          <t>DOE Office of Science News</t>
         </is>
       </c>
       <c r="I14" s="60" t="inlineStr">
         <is>
-          <t>NISTが中小企業向けの資金提供機会を発表</t>
+          <t>エネルギー長官クリス・ライト、AI駆動の科学発見を加速するための初のジェネシスミッションプロジェクトを発表</t>
         </is>
       </c>
       <c r="J14" s="60" t="inlineStr">
         <is>
-          <t>NIST MEPは、米国の中小企業を支援するための資金提供機会を発表し、2026年7月28日にウェビナーを開催する予定です。</t>
+          <t>米国エネルギー省がAI駆動の科学発見を加速するために、全米から選ばれたプロジェクトを発表した。</t>
         </is>
       </c>
       <c r="K14" s="60" t="inlineStr">
         <is>
-          <t>https://www.nist.gov/news-events/news/2026/07/nist-announces-funding-opportunity-14-mep-centers-advance-small-and-medium</t>
+          <t>https://www.energy.gov/articles/secretary-energy-chris-wright-announces-first-genesis-mission-projects-selected-accelerate</t>
         </is>
       </c>
       <c r="L14" s="60" t="inlineStr">
         <is>
-          <t>5aa9c93bc7040291c9f08bfa</t>
+          <t>23fa1d6907c14d73ce3a41cd</t>
         </is>
       </c>
       <c r="M14" s="75" t="inlineStr">
@@ -2026,72 +2030,72 @@
       </c>
       <c r="O14" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: R&amp;D Funding &amp; Tax Incentives | Public Procurement &amp; Industrial Policy / 焦点: 中小企業向けの資金提供</t>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: AI駆動の科学発見プロジェクト</t>
         </is>
       </c>
     </row>
     <row r="15" ht="42" customHeight="1">
       <c r="A15" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T19:05:06+09:00</t>
         </is>
       </c>
       <c r="B15" s="75" t="inlineStr">
         <is>
-          <t>2026-07-21T14:48:28Z</t>
+          <t>2026-07-22T13:53:19Z</t>
         </is>
       </c>
       <c r="C15" s="60" t="inlineStr">
         <is>
-          <t>EU &amp; Europe</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D15" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E15" s="60" t="inlineStr">
         <is>
-          <t>Fusion Energy</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="F15" s="76" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G15" s="60" t="inlineStr">
         <is>
-          <t>Industry Association</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H15" s="60" t="inlineStr">
         <is>
-          <t>Fusion Industry Association</t>
+          <t>National Science Foundation News</t>
         </is>
       </c>
       <c r="I15" s="60" t="inlineStr">
         <is>
-          <t>FIAが核融合のためのEU資金調達の道筋を示す</t>
+          <t>NSFがAIに関する国家戦略を推進する声明を発表</t>
         </is>
       </c>
       <c r="J15" s="60" t="inlineStr">
         <is>
-          <t>核融合産業協会は、商業核融合エネルギーのための実用的なEU資金調達の道筋を示す論文を発表しました。核融合プロジェクトが研究から実証へ移行する際に必要な資金調達手段について論じています。</t>
+          <t>米国科学財団（NSF）は、AIに関する国家戦略を推進するための声明を発表しました。</t>
         </is>
       </c>
       <c r="K15" s="60" t="inlineStr">
         <is>
-          <t>https://www.fusionindustryassociation.org/fia-outlines-eu-financing-pathway-for-fusion/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=fia-outlines-eu-financing-pathway-for-fusion</t>
+          <t>https://www.nsf.gov/news/statement-nsf-chief-staff-brian-stone-performing-duties-nsf-1</t>
         </is>
       </c>
       <c r="L15" s="60" t="inlineStr">
         <is>
-          <t>88af233d904d670250fa5a31</t>
+          <t>123e2207578ca69c8f9c00a2</t>
         </is>
       </c>
       <c r="M15" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T19:05:06+09:00</t>
         </is>
       </c>
       <c r="N15" s="60" t="inlineStr">
@@ -2101,34 +2105,34 @@
       </c>
       <c r="O15" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: R&amp;D Funding &amp; Tax Incentives / 焦点: 商業核融合エネルギーの資金調達</t>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: AIに関する国家戦略の推進</t>
         </is>
       </c>
     </row>
     <row r="16" ht="42" customHeight="1">
       <c r="A16" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T19:05:06+09:00</t>
         </is>
       </c>
       <c r="B16" s="75" t="inlineStr">
         <is>
-          <t>2026-07-17T18:42:47Z</t>
+          <t>2026-07-22T13:53:12Z</t>
         </is>
       </c>
       <c r="C16" s="60" t="inlineStr">
         <is>
-          <t>EU &amp; Europe</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D16" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E16" s="60" t="inlineStr">
         <is>
-          <t>Fusion Energy</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="F16" s="76" t="n">
@@ -2136,37 +2140,37 @@
       </c>
       <c r="G16" s="60" t="inlineStr">
         <is>
-          <t>Industry Association</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H16" s="60" t="inlineStr">
         <is>
-          <t>Fusion Industry Association</t>
+          <t>National Science Foundation News</t>
         </is>
       </c>
       <c r="I16" s="60" t="inlineStr">
         <is>
-          <t>国際法専門家グループがEUの核融合競争力確保の必要性に関する論文を発表</t>
+          <t>NSFの新しい取り組みがAIによる科学的発見のためのデータセットの価値を引き出す</t>
         </is>
       </c>
       <c r="J16" s="60" t="inlineStr">
         <is>
-          <t>国際法専門家グループが発表した論文は、EUが商業核融合において競争優位を持っているが、それを維持するためには今すぐ行動が必要であると主張しています。</t>
+          <t>米国科学財団（NSF）は、AIを活用した科学的発見のためのデータセットの価値を引き出す新しいプログラムを発表しました。</t>
         </is>
       </c>
       <c r="K16" s="60" t="inlineStr">
         <is>
-          <t>https://www.fusionindustryassociation.org/international-legal-expert-group-publish-paper-on-the-need-for-the-eu-to-secure-its-competitive-fusion-advantage/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=international-legal-expert-group-publish-paper-on-the-need-for-the-eu-to-secure-its-competitive-fusion-advantage</t>
+          <t>https://www.nsf.gov/news/new-nsf-initiative-aims-unlock-dataset-value-ai-enabled</t>
         </is>
       </c>
       <c r="L16" s="60" t="inlineStr">
         <is>
-          <t>7ef6110ab078602757409abf</t>
+          <t>dcd819527d9b80141b26bcb8</t>
         </is>
       </c>
       <c r="M16" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T19:05:06+09:00</t>
         </is>
       </c>
       <c r="N16" s="60" t="inlineStr">
@@ -2176,87 +2180,1279 @@
       </c>
       <c r="O16" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: Regulation &amp; Governance / 焦点: EUの核融合競争力の維持</t>
+          <t>枠: Innovation Policy / 政策分野: R&amp;D Funding &amp; Tax Incentives / 学術区分: News &amp; Official Release / 焦点: AIを活用した科学的発見のためのデータセットの価値を引き出すプログラム</t>
         </is>
       </c>
     </row>
     <row r="17" ht="42" customHeight="1">
       <c r="A17" s="75" t="inlineStr">
         <is>
+          <t>2026-07-26T20:29:40+09:00</t>
+        </is>
+      </c>
+      <c r="B17" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-22T13:53:06Z</t>
+        </is>
+      </c>
+      <c r="C17" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D17" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E17" s="60" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="F17" s="76" t="n">
+        <v>4</v>
+      </c>
+      <c r="G17" s="60" t="inlineStr">
+        <is>
+          <t>Government</t>
+        </is>
+      </c>
+      <c r="H17" s="60" t="inlineStr">
+        <is>
+          <t>National Science Foundation News</t>
+        </is>
+      </c>
+      <c r="I17" s="60" t="inlineStr">
+        <is>
+          <t>NSF、AI駆動の科学を進展させるために8300万ドルの投資を発表</t>
+        </is>
+      </c>
+      <c r="J17" s="60" t="inlineStr">
+        <is>
+          <t>米国科学財団が8300万ドルの資金を通じて、AI駆動の科学を進展させるためのデータシステムとサービスの整備を発表した。</t>
+        </is>
+      </c>
+      <c r="K17" s="60" t="inlineStr">
+        <is>
+          <t>https://www.nsf.gov/news/nsf-announces-83m-investment-integrated-data-systems</t>
+        </is>
+      </c>
+      <c r="L17" s="60" t="inlineStr">
+        <is>
+          <t>018d40b7e6eb7aa4b8cfb5fa</t>
+        </is>
+      </c>
+      <c r="M17" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T20:29:40+09:00</t>
+        </is>
+      </c>
+      <c r="N17" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O17" s="60" t="inlineStr">
+        <is>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy | Research System &amp; Talent / 学術区分: News &amp; Official Release / 焦点: AI駆動の科学研究インフラ整備</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="42" customHeight="1">
+      <c r="A18" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T20:29:40+09:00</t>
+        </is>
+      </c>
+      <c r="B18" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-22T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="C18" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D18" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E18" s="60" t="inlineStr"/>
+      <c r="F18" s="76" t="n">
+        <v>4</v>
+      </c>
+      <c r="G18" s="60" t="inlineStr">
+        <is>
+          <t>Government</t>
+        </is>
+      </c>
+      <c r="H18" s="60" t="inlineStr">
+        <is>
+          <t>NIST News</t>
+        </is>
+      </c>
+      <c r="I18" s="60" t="inlineStr">
+        <is>
+          <t>NISTが中小企業向けの資金提供機会を発表</t>
+        </is>
+      </c>
+      <c r="J18" s="60" t="inlineStr">
+        <is>
+          <t>NIST MEPは、米国の中小企業を支援するための資金提供機会を発表し、2026年7月28日にウェビナーを開催する予定です。</t>
+        </is>
+      </c>
+      <c r="K18" s="60" t="inlineStr">
+        <is>
+          <t>https://www.nist.gov/news-events/news/2026/07/nist-announces-funding-opportunity-14-mep-centers-advance-small-and-medium</t>
+        </is>
+      </c>
+      <c r="L18" s="60" t="inlineStr">
+        <is>
+          <t>5aa9c93bc7040291c9f08bfa</t>
+        </is>
+      </c>
+      <c r="M18" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T20:29:40+09:00</t>
+        </is>
+      </c>
+      <c r="N18" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O18" s="60" t="inlineStr">
+        <is>
+          <t>枠: Innovation Policy / 政策分野: R&amp;D Funding &amp; Tax Incentives | Public Procurement &amp; Industrial Policy / 学術区分: News &amp; Official Release / 焦点: 中小企業向けの資金提供</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="42" customHeight="1">
+      <c r="A19" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T21:02:36+09:00</t>
+        </is>
+      </c>
+      <c r="B19" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-22T05:00:56Z</t>
+        </is>
+      </c>
+      <c r="C19" s="60" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D19" s="60" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="E19" s="60" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="F19" s="76" t="n">
+        <v>5</v>
+      </c>
+      <c r="G19" s="60" t="inlineStr">
+        <is>
+          <t>Government</t>
+        </is>
+      </c>
+      <c r="H19" s="60" t="inlineStr">
+        <is>
+          <t>NISTEP Updates</t>
+        </is>
+      </c>
+      <c r="I19" s="60" t="inlineStr">
+        <is>
+          <t>特定科学技術領域動向報告書 -AI（人工知能）- 研究開発インプット編を公表</t>
+        </is>
+      </c>
+      <c r="J19" s="60" t="inlineStr">
+        <is>
+          <t>我が国のAI分野における研究開発インプット状況を分析した報告書が公表され、科学技術政策に資する知見を提供。</t>
+        </is>
+      </c>
+      <c r="K19" s="60" t="inlineStr">
+        <is>
+          <t>https://www.nistep.go.jp/archives/63583/</t>
+        </is>
+      </c>
+      <c r="L19" s="60" t="inlineStr">
+        <is>
+          <t>6b6122461584a86ee7a1c595</t>
+        </is>
+      </c>
+      <c r="M19" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-22T14:00:56+09:00</t>
+        </is>
+      </c>
+      <c r="N19" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O19" s="60" t="inlineStr">
+        <is>
+          <t>枠: Technology Innovation | Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: 人工知能（AI）分野の研究開発インプット状況</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="42" customHeight="1">
+      <c r="A20" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T21:02:36+09:00</t>
+        </is>
+      </c>
+      <c r="B20" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-22T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="C20" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D20" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E20" s="60" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="F20" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="G20" s="60" t="inlineStr">
+        <is>
+          <t>Policy Institute</t>
+        </is>
+      </c>
+      <c r="H20" s="60" t="inlineStr">
+        <is>
+          <t>Brookings TechTank</t>
+        </is>
+      </c>
+      <c r="I20" s="60" t="inlineStr">
+        <is>
+          <t>政策がGen ZのAIへの信頼を決定する</t>
+        </is>
+      </c>
+      <c r="J20" s="60" t="inlineStr">
+        <is>
+          <t>Gen ZがAIを信頼するかどうかは、PRではなく政策によって決まると指摘されている。</t>
+        </is>
+      </c>
+      <c r="K20" s="60" t="inlineStr">
+        <is>
+          <t>https://www.brookings.edu/articles/policy-not-pr-will-determine-gen-zs-trust-in-ai/</t>
+        </is>
+      </c>
+      <c r="L20" s="60" t="inlineStr">
+        <is>
+          <t>61bd55f8ce5a2385a5420260</t>
+        </is>
+      </c>
+      <c r="M20" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-22T09:00:00+09:00</t>
+        </is>
+      </c>
+      <c r="N20" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O20" s="60" t="inlineStr">
+        <is>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: AIに関する政策</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T21:02:36+09:00</t>
+        </is>
+      </c>
+      <c r="B21" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-22T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="C21" s="60" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="D21" s="60" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E21" s="60" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="F21" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="60" t="inlineStr">
+        <is>
+          <t>Scientific Publication</t>
+        </is>
+      </c>
+      <c r="H21" s="60" t="inlineStr">
+        <is>
+          <t>Nature</t>
+        </is>
+      </c>
+      <c r="I21" s="60" t="inlineStr">
+        <is>
+          <t>AIによる設計が酵素進化を促進</t>
+        </is>
+      </c>
+      <c r="J21" s="60" t="inlineStr">
+        <is>
+          <t>AIを用いて設計された出発点を使用し、自然なタンパク質から進化したものよりも改善された特性を持つ酵素を進化させるワークフローが確立されました。</t>
+        </is>
+      </c>
+      <c r="K21" s="60" t="inlineStr">
+        <is>
+          <t>https://www.nature.com/articles/s41586-026-10820-0</t>
+        </is>
+      </c>
+      <c r="L21" s="60" t="inlineStr">
+        <is>
+          <t>6e9f79f12db784e010b0dad5</t>
+        </is>
+      </c>
+      <c r="M21" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-22T09:00:00+09:00</t>
+        </is>
+      </c>
+      <c r="N21" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O21" s="60" t="inlineStr">
+        <is>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: AIを用いた酵素進化</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T21:02:36+09:00</t>
+        </is>
+      </c>
+      <c r="B22" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-22T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="C22" s="60" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="D22" s="60" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E22" s="60" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="F22" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="60" t="inlineStr">
+        <is>
+          <t>Scientific Publication</t>
+        </is>
+      </c>
+      <c r="H22" s="60" t="inlineStr">
+        <is>
+          <t>Nature</t>
+        </is>
+      </c>
+      <c r="I22" s="60" t="inlineStr">
+        <is>
+          <t>量子パラ電気体SrTiO3におけるナノスケール極性テクスチャのイメージング</t>
+        </is>
+      </c>
+      <c r="J22" s="60" t="inlineStr">
+        <is>
+          <t>SrTiO3が105K以下で周期的な極性ナノドメインを形成し、40K以下でこれらが断片化することが示され、量子パラ電気性とナノスケールの極性秩序および無秩序に関連付けられています。</t>
+        </is>
+      </c>
+      <c r="K22" s="60" t="inlineStr">
+        <is>
+          <t>https://www.nature.com/articles/s41586-026-10823-x</t>
+        </is>
+      </c>
+      <c r="L22" s="60" t="inlineStr">
+        <is>
+          <t>f12f62aebb861877dd7a5cbf</t>
+        </is>
+      </c>
+      <c r="M22" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-22T09:00:00+09:00</t>
+        </is>
+      </c>
+      <c r="N22" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O22" s="60" t="inlineStr">
+        <is>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: 量子パラ電気体SrTiO3のナノスケール極性テクスチャ</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T21:02:36+09:00</t>
+        </is>
+      </c>
+      <c r="B23" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-21T19:44:19Z</t>
+        </is>
+      </c>
+      <c r="C23" s="60" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="D23" s="60" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E23" s="60" t="inlineStr"/>
+      <c r="F23" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="G23" s="60" t="inlineStr">
+        <is>
+          <t>Industry Association</t>
+        </is>
+      </c>
+      <c r="H23" s="60" t="inlineStr">
+        <is>
+          <t>Fusion Industry Association</t>
+        </is>
+      </c>
+      <c r="I23" s="60" t="inlineStr">
+        <is>
+          <t>FIAとクリーンエアタスクフォースが核融合の基準に関する原則を発表</t>
+        </is>
+      </c>
+      <c r="J23" s="60" t="inlineStr">
+        <is>
+          <t>FIAはクリーンエアタスクフォースと協力し、核融合のコードと基準に関する原則をまとめた文書を発表しました。核融合の展開に向けて、安全性を確保しつつ革新を促進するための基準が重要です。</t>
+        </is>
+      </c>
+      <c r="K23" s="60" t="inlineStr">
+        <is>
+          <t>https://www.fusionindustryassociation.org/fia-and-clean-air-task-force-publish-principles-on-codes-and-standards/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=fia-and-clean-air-task-force-publish-principles-on-codes-and-standards</t>
+        </is>
+      </c>
+      <c r="L23" s="60" t="inlineStr">
+        <is>
+          <t>2366dc909672b56b77a196bd</t>
+        </is>
+      </c>
+      <c r="M23" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-22T04:44:19+09:00</t>
+        </is>
+      </c>
+      <c r="N23" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O23" s="60" t="inlineStr">
+        <is>
+          <t>枠: Innovation Policy / 政策分野: Standards &amp; Safety / 学術区分: News &amp; Official Release / 焦点: 核融合技術のコードと基準</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T21:02:36+09:00</t>
+        </is>
+      </c>
+      <c r="B24" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-21T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="C24" s="60" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="D24" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E24" s="60" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="F24" s="76" t="n">
+        <v>2</v>
+      </c>
+      <c r="G24" s="60" t="inlineStr">
+        <is>
+          <t>Official Company</t>
+        </is>
+      </c>
+      <c r="H24" s="60" t="inlineStr">
+        <is>
+          <t>OpenAI News</t>
+        </is>
+      </c>
+      <c r="I24" s="60" t="inlineStr">
+        <is>
+          <t>OpenAIが中小企業向けChatGPTプログラムを発表</t>
+        </is>
+      </c>
+      <c r="J24" s="60" t="inlineStr">
+        <is>
+          <t>OpenAIは、中小企業がAIスキルを構築し、業務を自動化し、ChatGPTを活用して成長するためのプログラムを開始しました。</t>
+        </is>
+      </c>
+      <c r="K24" s="60" t="inlineStr">
+        <is>
+          <t>https://openai.com/index/introducing-chatgpt-small-business-program</t>
+        </is>
+      </c>
+      <c r="L24" s="60" t="inlineStr">
+        <is>
+          <t>3064e426d18ccd85acab9b00</t>
+        </is>
+      </c>
+      <c r="M24" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-22T02:00:00+09:00</t>
+        </is>
+      </c>
+      <c r="N24" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O24" s="60" t="inlineStr">
+        <is>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: 中小企業向けのAIスキル向上プログラム</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T21:02:36+09:00</t>
+        </is>
+      </c>
+      <c r="B25" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-21T15:05:11Z</t>
+        </is>
+      </c>
+      <c r="C25" s="60" t="inlineStr">
+        <is>
+          <t>EU &amp; Europe</t>
+        </is>
+      </c>
+      <c r="D25" s="60" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="E25" s="60" t="inlineStr">
+        <is>
+          <t>Semiconductors &amp; Telecom</t>
+        </is>
+      </c>
+      <c r="F25" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="G25" s="60" t="inlineStr">
+        <is>
+          <t>Government</t>
+        </is>
+      </c>
+      <c r="H25" s="60" t="inlineStr">
+        <is>
+          <t>UK DSIT</t>
+        </is>
+      </c>
+      <c r="I25" s="60" t="inlineStr">
+        <is>
+          <t>政策文書：固定通信近代化憲章</t>
+        </is>
+      </c>
+      <c r="J25" s="60" t="inlineStr">
+        <is>
+          <t>通信プロバイダーが現在および将来の固定通信近代化を行う際に従うべき手順を示す文書。</t>
+        </is>
+      </c>
+      <c r="K25" s="60" t="inlineStr">
+        <is>
+          <t>https://www.gov.uk/government/publications/fixed-telecoms-modernisation-charter</t>
+        </is>
+      </c>
+      <c r="L25" s="60" t="inlineStr">
+        <is>
+          <t>d5e4431b57fcb4b6271f6c72</t>
+        </is>
+      </c>
+      <c r="M25" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-22T00:05:11+09:00</t>
+        </is>
+      </c>
+      <c r="N25" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O25" s="60" t="inlineStr">
+        <is>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: 固定通信の近代化に関する手順</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T21:02:36+09:00</t>
+        </is>
+      </c>
+      <c r="B26" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-21T15:05:07Z</t>
+        </is>
+      </c>
+      <c r="C26" s="60" t="inlineStr">
+        <is>
+          <t>EU &amp; Europe</t>
+        </is>
+      </c>
+      <c r="D26" s="60" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="E26" s="60" t="inlineStr">
+        <is>
+          <t>Semiconductors &amp; Telecom</t>
+        </is>
+      </c>
+      <c r="F26" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="G26" s="60" t="inlineStr">
+        <is>
+          <t>Government</t>
+        </is>
+      </c>
+      <c r="H26" s="60" t="inlineStr">
+        <is>
+          <t>UK DSIT</t>
+        </is>
+      </c>
+      <c r="I26" s="60" t="inlineStr">
+        <is>
+          <t>政策文書：通信近代化：重要国家インフラ憲章</t>
+        </is>
+      </c>
+      <c r="J26" s="60" t="inlineStr">
+        <is>
+          <t>通信会社が通信近代化中に重要な国家インフラを保護するためのアプローチを示す文書。</t>
+        </is>
+      </c>
+      <c r="K26" s="60" t="inlineStr">
+        <is>
+          <t>https://www.gov.uk/government/publications/telecoms-modernisation-critical-national-infrastructure-charter</t>
+        </is>
+      </c>
+      <c r="L26" s="60" t="inlineStr">
+        <is>
+          <t>aafa3a246656ccda64dd93c4</t>
+        </is>
+      </c>
+      <c r="M26" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-22T00:05:07+09:00</t>
+        </is>
+      </c>
+      <c r="N26" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O26" s="60" t="inlineStr">
+        <is>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: 重要な国家インフラを保護するための通信会社のアプローチ</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T21:02:36+09:00</t>
+        </is>
+      </c>
+      <c r="B27" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-21T15:00:20Z</t>
+        </is>
+      </c>
+      <c r="C27" s="60" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="D27" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E27" s="60" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="F27" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="60" t="inlineStr">
+        <is>
+          <t>Official Company</t>
+        </is>
+      </c>
+      <c r="H27" s="60" t="inlineStr">
+        <is>
+          <t>NVIDIA Blog</t>
+        </is>
+      </c>
+      <c r="I27" s="60" t="inlineStr">
+        <is>
+          <t>Vera Rubin向けに構築されたNVIDIA Spectrum-6がギガスケールAIファクトリーに登場</t>
+        </is>
+      </c>
+      <c r="J27" s="60" t="inlineStr">
+        <is>
+          <t>NVIDIA Spectrum-6は、数十万のGPUとCPUを統合し、フロンティアモデルを訓練するためのギガスケールAIファクトリーを実現します。ネットワーキングが計算能力を向上させる重要な要素となっています。</t>
+        </is>
+      </c>
+      <c r="K27" s="60" t="inlineStr">
+        <is>
+          <t>https://blogs.nvidia.com/blog/nvidia-spectrum-six-arrives-in-gigascale-ai-factories/</t>
+        </is>
+      </c>
+      <c r="L27" s="60" t="inlineStr">
+        <is>
+          <t>6f3401cebeb5dc5a8f12a872</t>
+        </is>
+      </c>
+      <c r="M27" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-22T00:00:20+09:00</t>
+        </is>
+      </c>
+      <c r="N27" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O27" s="60" t="inlineStr">
+        <is>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: AIファクトリーの構築とネットワーキング技術</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="75" t="inlineStr">
+        <is>
           <t>2026-07-26T18:56:03+09:00</t>
         </is>
       </c>
-      <c r="B17" s="75" t="inlineStr">
+      <c r="B28" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-21T14:48:28Z</t>
+        </is>
+      </c>
+      <c r="C28" s="60" t="inlineStr">
+        <is>
+          <t>EU &amp; Europe</t>
+        </is>
+      </c>
+      <c r="D28" s="60" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E28" s="60" t="inlineStr">
+        <is>
+          <t>Fusion Energy</t>
+        </is>
+      </c>
+      <c r="F28" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="G28" s="60" t="inlineStr">
+        <is>
+          <t>Industry Association</t>
+        </is>
+      </c>
+      <c r="H28" s="60" t="inlineStr">
+        <is>
+          <t>Fusion Industry Association</t>
+        </is>
+      </c>
+      <c r="I28" s="60" t="inlineStr">
+        <is>
+          <t>FIAが核融合のためのEU資金調達の道筋を示す</t>
+        </is>
+      </c>
+      <c r="J28" s="60" t="inlineStr">
+        <is>
+          <t>核融合産業協会は、商業核融合エネルギーのための実用的なEU資金調達の道筋を示す論文を発表しました。核融合プロジェクトが研究から実証へ移行する際に必要な資金調達手段について論じています。</t>
+        </is>
+      </c>
+      <c r="K28" s="60" t="inlineStr">
+        <is>
+          <t>https://www.fusionindustryassociation.org/fia-outlines-eu-financing-pathway-for-fusion/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=fia-outlines-eu-financing-pathway-for-fusion</t>
+        </is>
+      </c>
+      <c r="L28" s="60" t="inlineStr">
+        <is>
+          <t>88af233d904d670250fa5a31</t>
+        </is>
+      </c>
+      <c r="M28" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T18:56:03+09:00</t>
+        </is>
+      </c>
+      <c r="N28" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O28" s="60" t="inlineStr">
+        <is>
+          <t>枠: Innovation Policy / 政策分野: R&amp;D Funding &amp; Tax Incentives / 学術区分: News &amp; Official Release / 焦点: 商業核融合エネルギーの資金調達</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T21:02:36+09:00</t>
+        </is>
+      </c>
+      <c r="B29" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-21T13:30:36Z</t>
+        </is>
+      </c>
+      <c r="C29" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D29" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E29" s="60" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="F29" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="G29" s="60" t="inlineStr">
+        <is>
+          <t>Policy Institute</t>
+        </is>
+      </c>
+      <c r="H29" s="60" t="inlineStr">
+        <is>
+          <t>CSET</t>
+        </is>
+      </c>
+      <c r="I29" s="60" t="inlineStr">
+        <is>
+          <t>AIシステムはなぜ誤動作するのか？</t>
+        </is>
+      </c>
+      <c r="J29" s="60" t="inlineStr">
+        <is>
+          <t>AIシステムの進化に伴い、その失敗の原因がますます謎となっています。このブログでは、AIの誤動作の原因について掘り下げています。</t>
+        </is>
+      </c>
+      <c r="K29" s="60" t="inlineStr">
+        <is>
+          <t>https://cset.georgetown.edu/article/why-do-ai-systems-misbehave/</t>
+        </is>
+      </c>
+      <c r="L29" s="60" t="inlineStr">
+        <is>
+          <t>3e1aa390ad965782cc86c386</t>
+        </is>
+      </c>
+      <c r="M29" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-21T22:30:36+09:00</t>
+        </is>
+      </c>
+      <c r="N29" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O29" s="60" t="inlineStr">
+        <is>
+          <t>枠: Technology Innovation | Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: AIシステムの誤動作の原因</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="42" customHeight="1">
+      <c r="A30" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T21:02:36+09:00</t>
+        </is>
+      </c>
+      <c r="B30" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-20T21:06:27Z</t>
+        </is>
+      </c>
+      <c r="C30" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D30" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E30" s="60" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="F30" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="G30" s="60" t="inlineStr">
+        <is>
+          <t>Policy Institute</t>
+        </is>
+      </c>
+      <c r="H30" s="60" t="inlineStr">
+        <is>
+          <t>Brookings TechTank</t>
+        </is>
+      </c>
+      <c r="I30" s="60" t="inlineStr">
+        <is>
+          <t>相続を返す：教育と研究政策がAIの借りた専門知識にどう対処できるか</t>
+        </is>
+      </c>
+      <c r="J30" s="60" t="inlineStr">
+        <is>
+          <t>教育と研究政策がAIの専門知識の借用にどのように対処すべきかについて論じられている。</t>
+        </is>
+      </c>
+      <c r="K30" s="60" t="inlineStr">
+        <is>
+          <t>https://brookings.edu/articles/repaying-the-inheritance-how-education-and-research-policy-can-address-ais-borrowed-expertise</t>
+        </is>
+      </c>
+      <c r="L30" s="60" t="inlineStr">
+        <is>
+          <t>42183313e1c951c0483c0d62</t>
+        </is>
+      </c>
+      <c r="M30" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-21T06:06:27+09:00</t>
+        </is>
+      </c>
+      <c r="N30" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O30" s="60" t="inlineStr">
+        <is>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: AIに関する教育政策 / Historical backfill from an allowlisted source.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="42" customHeight="1">
+      <c r="A31" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T21:02:36+09:00</t>
+        </is>
+      </c>
+      <c r="B31" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-20T15:55:00Z</t>
+        </is>
+      </c>
+      <c r="C31" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D31" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E31" s="60" t="inlineStr">
+        <is>
+          <t>Semiconductors &amp; Telecom</t>
+        </is>
+      </c>
+      <c r="F31" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="60" t="inlineStr">
+        <is>
+          <t>Major Media</t>
+        </is>
+      </c>
+      <c r="H31" s="60" t="inlineStr">
+        <is>
+          <t>IEEE Spectrum</t>
+        </is>
+      </c>
+      <c r="I31" s="60" t="inlineStr">
+        <is>
+          <t>先端半導体故障解析のためのSEMガイド低電圧FIB仕上げ</t>
+        </is>
+      </c>
+      <c r="J31" s="60" t="inlineStr">
+        <is>
+          <t>ZEISS Crossbeam 750 FIBSEMが、先端半導体の故障解析において新たな基準を設定する技術を紹介。精密なTEMラメラ準備やトモグラフィーを実現し、データ駆動の意思決定を加速させる。</t>
+        </is>
+      </c>
+      <c r="K31" s="60" t="inlineStr">
+        <is>
+          <t>https://event.on24.com/wcc/r/5418459/287E3D5B99470D34C830D69A24B3B207</t>
+        </is>
+      </c>
+      <c r="L31" s="60" t="inlineStr">
+        <is>
+          <t>73d0028e337a76c2cd00f1bc</t>
+        </is>
+      </c>
+      <c r="M31" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-21T00:55:00+09:00</t>
+        </is>
+      </c>
+      <c r="N31" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O31" s="60" t="inlineStr">
+        <is>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: 半導体故障解析のためのFIB技術</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="42" customHeight="1">
+      <c r="A32" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T18:56:03+09:00</t>
+        </is>
+      </c>
+      <c r="B32" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-17T18:42:47Z</t>
+        </is>
+      </c>
+      <c r="C32" s="60" t="inlineStr">
+        <is>
+          <t>EU &amp; Europe</t>
+        </is>
+      </c>
+      <c r="D32" s="60" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E32" s="60" t="inlineStr">
+        <is>
+          <t>Fusion Energy</t>
+        </is>
+      </c>
+      <c r="F32" s="76" t="n">
+        <v>4</v>
+      </c>
+      <c r="G32" s="60" t="inlineStr">
+        <is>
+          <t>Industry Association</t>
+        </is>
+      </c>
+      <c r="H32" s="60" t="inlineStr">
+        <is>
+          <t>Fusion Industry Association</t>
+        </is>
+      </c>
+      <c r="I32" s="60" t="inlineStr">
+        <is>
+          <t>国際法専門家グループがEUの核融合競争力確保の必要性に関する論文を発表</t>
+        </is>
+      </c>
+      <c r="J32" s="60" t="inlineStr">
+        <is>
+          <t>国際法専門家グループが発表した論文は、EUが商業核融合において競争優位を持っているが、それを維持するためには今すぐ行動が必要であると主張しています。</t>
+        </is>
+      </c>
+      <c r="K32" s="60" t="inlineStr">
+        <is>
+          <t>https://www.fusionindustryassociation.org/international-legal-expert-group-publish-paper-on-the-need-for-the-eu-to-secure-its-competitive-fusion-advantage/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=international-legal-expert-group-publish-paper-on-the-need-for-the-eu-to-secure-its-competitive-fusion-advantage</t>
+        </is>
+      </c>
+      <c r="L32" s="60" t="inlineStr">
+        <is>
+          <t>7ef6110ab078602757409abf</t>
+        </is>
+      </c>
+      <c r="M32" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T18:56:03+09:00</t>
+        </is>
+      </c>
+      <c r="N32" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O32" s="60" t="inlineStr">
+        <is>
+          <t>枠: Innovation Policy / 政策分野: Regulation &amp; Governance / 学術区分: News &amp; Official Release / 焦点: EUの核融合競争力の維持</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="42" customHeight="1">
+      <c r="A33" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T18:56:03+09:00</t>
+        </is>
+      </c>
+      <c r="B33" s="75" t="inlineStr">
         <is>
           <t>2026-07-15T17:47:57Z</t>
         </is>
       </c>
-      <c r="C17" s="60" t="inlineStr">
+      <c r="C33" s="60" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="D17" s="60" t="inlineStr">
+      <c r="D33" s="60" t="inlineStr">
         <is>
           <t>Global</t>
         </is>
       </c>
-      <c r="E17" s="60" t="inlineStr">
+      <c r="E33" s="60" t="inlineStr">
         <is>
           <t>Fusion Energy</t>
         </is>
       </c>
-      <c r="F17" s="76" t="n">
+      <c r="F33" s="76" t="n">
         <v>3</v>
       </c>
-      <c r="G17" s="60" t="inlineStr">
+      <c r="G33" s="60" t="inlineStr">
         <is>
           <t>Industry Association</t>
         </is>
       </c>
-      <c r="H17" s="60" t="inlineStr">
+      <c r="H33" s="60" t="inlineStr">
         <is>
           <t>Fusion Industry Association</t>
         </is>
       </c>
-      <c r="I17" s="60" t="inlineStr">
+      <c r="I33" s="60" t="inlineStr">
         <is>
           <t>スターロライトエンジンが60.6億円を調達</t>
         </is>
       </c>
-      <c r="J17" s="60" t="inlineStr">
+      <c r="J33" s="60" t="inlineStr">
         <is>
           <t>スターロライトエンジンは、FASTの開発を加速するために60.6億円を調達しました。この会社は、日本のJT-60SAプログラムや国際的な取り組みを基にしたトカマク型核融合機を開発しています。</t>
         </is>
       </c>
-      <c r="K17" s="60" t="inlineStr">
+      <c r="K33" s="60" t="inlineStr">
         <is>
           <t>https://www.nikkei.com/article/DGXZQOUC152ET0V10C26A7000000/#new_tab?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=starlight-engine-raises-jpy-6-06-billion</t>
         </is>
       </c>
-      <c r="L17" s="60" t="inlineStr">
+      <c r="L33" s="60" t="inlineStr">
         <is>
           <t>2f29b005896c3737ab846738</t>
         </is>
       </c>
-      <c r="M17" s="75" t="inlineStr">
+      <c r="M33" s="75" t="inlineStr">
         <is>
           <t>2026-07-26T18:56:03+09:00</t>
         </is>
       </c>
-      <c r="N17" s="60" t="inlineStr">
+      <c r="N33" s="60" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="O17" s="60" t="inlineStr">
-        <is>
-          <t>枠: Technology Innovation / 焦点: トカマク型核融合機の開発</t>
+      <c r="O33" s="60" t="inlineStr">
+        <is>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: トカマク型核融合機の開発</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:O17"/>
+  <autoFilter ref="A3:O33"/>
   <mergeCells count="2">
     <mergeCell ref="A1:O1"/>
     <mergeCell ref="A2:O2"/>
@@ -2274,7 +3470,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="N4:N17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="N4:N33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"New,Reviewed,Follow-up,Archived"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2293,10 +3489,26 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K33" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId15"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId31"/>
   </tableParts>
 </worksheet>
 </file>
@@ -2307,7 +3519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K41"/>
+  <dimension ref="A1:K44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4494,8 +5706,173 @@
         </is>
       </c>
     </row>
+    <row r="42" ht="36" customHeight="1">
+      <c r="A42" s="60" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B42" s="60" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C42" s="60" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="D42" s="60" t="inlineStr">
+        <is>
+          <t>Scholarly research</t>
+        </is>
+      </c>
+      <c r="E42" s="60" t="inlineStr">
+        <is>
+          <t>OpenAlex Journal Articles</t>
+        </is>
+      </c>
+      <c r="F42" s="60" t="inlineStr">
+        <is>
+          <t>OpenAlex</t>
+        </is>
+      </c>
+      <c r="G42" s="60" t="inlineStr">
+        <is>
+          <t>https://api.openalex.org/works</t>
+        </is>
+      </c>
+      <c r="H42" s="60" t="inlineStr">
+        <is>
+          <t>https://openalex.org/</t>
+        </is>
+      </c>
+      <c r="I42" s="76" t="n">
+        <v>4</v>
+      </c>
+      <c r="J42" s="60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K42" s="60" t="inlineStr">
+        <is>
+          <t>Scholarly metadata discovery. The card links to the DOI or OpenAlex record; peer-review status must be confirmed on the publisher page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="36" customHeight="1">
+      <c r="A43" s="60" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B43" s="60" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C43" s="60" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="D43" s="60" t="inlineStr">
+        <is>
+          <t>Conference proceedings</t>
+        </is>
+      </c>
+      <c r="E43" s="60" t="inlineStr">
+        <is>
+          <t>OpenAlex Conference Papers</t>
+        </is>
+      </c>
+      <c r="F43" s="60" t="inlineStr">
+        <is>
+          <t>OpenAlex</t>
+        </is>
+      </c>
+      <c r="G43" s="60" t="inlineStr">
+        <is>
+          <t>https://api.openalex.org/works</t>
+        </is>
+      </c>
+      <c r="H43" s="60" t="inlineStr">
+        <is>
+          <t>https://openalex.org/</t>
+        </is>
+      </c>
+      <c r="I43" s="76" t="n">
+        <v>4</v>
+      </c>
+      <c r="J43" s="60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K43" s="60" t="inlineStr">
+        <is>
+          <t>Official proceedings and conference-paper records discovered through OpenAlex. Review status varies by venue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="36" customHeight="1">
+      <c r="A44" s="60" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B44" s="60" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C44" s="60" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="D44" s="60" t="inlineStr">
+        <is>
+          <t>Preprints</t>
+        </is>
+      </c>
+      <c r="E44" s="60" t="inlineStr">
+        <is>
+          <t>OpenAlex Preprints</t>
+        </is>
+      </c>
+      <c r="F44" s="60" t="inlineStr">
+        <is>
+          <t>OpenAlex</t>
+        </is>
+      </c>
+      <c r="G44" s="60" t="inlineStr">
+        <is>
+          <t>https://api.openalex.org/works</t>
+        </is>
+      </c>
+      <c r="H44" s="60" t="inlineStr">
+        <is>
+          <t>https://openalex.org/</t>
+        </is>
+      </c>
+      <c r="I44" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="J44" s="60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K44" s="60" t="inlineStr">
+        <is>
+          <t>Preprints are displayed separately and must never be described as peer reviewed.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:K41"/>
+  <autoFilter ref="A3:K44"/>
   <mergeCells count="2">
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A1:K1"/>
@@ -4582,10 +5959,16 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H40" r:id="rId74"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G41" r:id="rId75"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H41" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G42" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H42" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G43" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H43" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G44" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H44" r:id="rId82"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId77"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId83"/>
   </tableParts>
 </worksheet>
 </file>
@@ -4596,7 +5979,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4675,37 +6058,37 @@
     <row r="4" ht="42" customHeight="1">
       <c r="A4" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:36:29+09:00</t>
+          <t>2026-07-26T21:02:36+09:00</t>
         </is>
       </c>
       <c r="B4" s="77" t="n">
-        <v>38</v>
+        <v>108</v>
       </c>
       <c r="C4" s="77" t="n">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="D4" s="77" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="E4" s="77" t="n">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="F4" s="77" t="n">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="G4" s="77" t="n">
-        <v>93.7</v>
+        <v>1376.15</v>
       </c>
       <c r="H4" s="60" t="inlineStr">
         <is>
-          <t>Daily update</t>
+          <t>Historical backfill: policy 365d / technology 183d</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:34:08+09:00</t>
+          <t>2026-07-26T20:36:29+09:00</t>
         </is>
       </c>
       <c r="B5" s="77" t="n">
@@ -4715,7 +6098,7 @@
         <v>28</v>
       </c>
       <c r="D5" s="77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" s="77" t="n">
         <v>74</v>
@@ -4724,7 +6107,7 @@
         <v>10</v>
       </c>
       <c r="G5" s="77" t="n">
-        <v>20.27</v>
+        <v>93.7</v>
       </c>
       <c r="H5" s="60" t="inlineStr">
         <is>
@@ -4735,7 +6118,7 @@
     <row r="6">
       <c r="A6" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:29:40+09:00</t>
+          <t>2026-07-26T20:34:08+09:00</t>
         </is>
       </c>
       <c r="B6" s="77" t="n">
@@ -4745,16 +6128,16 @@
         <v>28</v>
       </c>
       <c r="D6" s="77" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E6" s="77" t="n">
-        <v>11</v>
+        <v>74</v>
       </c>
       <c r="F6" s="77" t="n">
         <v>10</v>
       </c>
       <c r="G6" s="77" t="n">
-        <v>141.79</v>
+        <v>20.27</v>
       </c>
       <c r="H6" s="60" t="inlineStr">
         <is>
@@ -4765,7 +6148,7 @@
     <row r="7">
       <c r="A7" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:24:57+09:00</t>
+          <t>2026-07-26T20:29:40+09:00</t>
         </is>
       </c>
       <c r="B7" s="77" t="n">
@@ -4775,16 +6158,16 @@
         <v>28</v>
       </c>
       <c r="D7" s="77" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E7" s="77" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="F7" s="77" t="n">
         <v>10</v>
       </c>
       <c r="G7" s="77" t="n">
-        <v>134.95</v>
+        <v>141.79</v>
       </c>
       <c r="H7" s="60" t="inlineStr">
         <is>
@@ -4795,7 +6178,7 @@
     <row r="8">
       <c r="A8" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:19:15+09:00</t>
+          <t>2026-07-26T20:24:57+09:00</t>
         </is>
       </c>
       <c r="B8" s="77" t="n">
@@ -4805,16 +6188,16 @@
         <v>28</v>
       </c>
       <c r="D8" s="77" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E8" s="77" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F8" s="77" t="n">
         <v>10</v>
       </c>
       <c r="G8" s="77" t="n">
-        <v>134.05</v>
+        <v>134.95</v>
       </c>
       <c r="H8" s="60" t="inlineStr">
         <is>
@@ -4825,26 +6208,26 @@
     <row r="9">
       <c r="A9" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:13:43+09:00</t>
+          <t>2026-07-26T20:19:15+09:00</t>
         </is>
       </c>
       <c r="B9" s="77" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C9" s="77" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D9" s="77" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E9" s="77" t="n">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="F9" s="77" t="n">
         <v>10</v>
       </c>
       <c r="G9" s="77" t="n">
-        <v>162.46</v>
+        <v>134.05</v>
       </c>
       <c r="H9" s="60" t="inlineStr">
         <is>
@@ -4855,7 +6238,7 @@
     <row r="10">
       <c r="A10" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:00:03+09:00</t>
+          <t>2026-07-26T20:13:43+09:00</t>
         </is>
       </c>
       <c r="B10" s="77" t="n">
@@ -4865,16 +6248,16 @@
         <v>24</v>
       </c>
       <c r="D10" s="77" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E10" s="77" t="n">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="F10" s="77" t="n">
         <v>10</v>
       </c>
       <c r="G10" s="77" t="n">
-        <v>154.27</v>
+        <v>162.46</v>
       </c>
       <c r="H10" s="60" t="inlineStr">
         <is>
@@ -4885,7 +6268,7 @@
     <row r="11">
       <c r="A11" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:51:39+09:00</t>
+          <t>2026-07-26T20:00:03+09:00</t>
         </is>
       </c>
       <c r="B11" s="77" t="n">
@@ -4895,16 +6278,16 @@
         <v>24</v>
       </c>
       <c r="D11" s="77" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E11" s="77" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="F11" s="77" t="n">
         <v>10</v>
       </c>
       <c r="G11" s="77" t="n">
-        <v>11.55</v>
+        <v>154.27</v>
       </c>
       <c r="H11" s="60" t="inlineStr">
         <is>
@@ -4915,26 +6298,26 @@
     <row r="12">
       <c r="A12" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:10:55+09:00</t>
+          <t>2026-07-26T19:51:39+09:00</t>
         </is>
       </c>
       <c r="B12" s="77" t="n">
         <v>34</v>
       </c>
       <c r="C12" s="77" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D12" s="77" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E12" s="77" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F12" s="77" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G12" s="77" t="n">
-        <v>194.65</v>
+        <v>11.55</v>
       </c>
       <c r="H12" s="60" t="inlineStr">
         <is>
@@ -4945,26 +6328,26 @@
     <row r="13">
       <c r="A13" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:05:06+09:00</t>
+          <t>2026-07-26T19:10:55+09:00</t>
         </is>
       </c>
       <c r="B13" s="77" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C13" s="77" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D13" s="77" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E13" s="77" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="F13" s="77" t="n">
         <v>9</v>
       </c>
       <c r="G13" s="77" t="n">
-        <v>165.89</v>
+        <v>194.65</v>
       </c>
       <c r="H13" s="60" t="inlineStr">
         <is>
@@ -4975,35 +6358,65 @@
     <row r="14">
       <c r="A14" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T19:05:06+09:00</t>
         </is>
       </c>
       <c r="B14" s="77" t="n">
         <v>33</v>
       </c>
       <c r="C14" s="77" t="n">
+        <v>24</v>
+      </c>
+      <c r="D14" s="77" t="n">
+        <v>5</v>
+      </c>
+      <c r="E14" s="77" t="n">
+        <v>39</v>
+      </c>
+      <c r="F14" s="77" t="n">
+        <v>9</v>
+      </c>
+      <c r="G14" s="77" t="n">
+        <v>165.89</v>
+      </c>
+      <c r="H14" s="60" t="inlineStr">
+        <is>
+          <t>Daily update</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T18:56:03+09:00</t>
+        </is>
+      </c>
+      <c r="B15" s="77" t="n">
+        <v>33</v>
+      </c>
+      <c r="C15" s="77" t="n">
         <v>20</v>
       </c>
-      <c r="D14" s="77" t="n">
+      <c r="D15" s="77" t="n">
         <v>94</v>
       </c>
-      <c r="E14" s="77" t="n">
+      <c r="E15" s="77" t="n">
         <v>0</v>
       </c>
-      <c r="F14" s="77" t="n">
+      <c r="F15" s="77" t="n">
         <v>13</v>
       </c>
-      <c r="G14" s="77" t="n">
+      <c r="G15" s="77" t="n">
         <v>129.43</v>
       </c>
-      <c r="H14" s="60" t="inlineStr">
+      <c r="H15" s="60" t="inlineStr">
         <is>
           <t>Initial lookback</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:H14"/>
+  <autoFilter ref="A3:H15"/>
   <mergeCells count="2">
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>

--- a/docs/innovation_news_ledger.xlsx
+++ b/docs/innovation_news_ledger.xlsx
@@ -9,9 +9,9 @@
     <sheet name="Run Log" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'News Ledger'!$A$3:$O$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'News Ledger'!$A$3:$O$88</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Source Registry'!$A$3:$K$44</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Run Log'!$A$3:$H$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Run Log'!$A$3:$H$16</definedName>
   </definedNames>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -472,7 +472,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="NewsLedgerTable" displayName="NewsLedgerTable" ref="A3:O33" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="NewsLedgerTable" displayName="NewsLedgerTable" ref="A3:O88" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <autoFilter ref="A3:O4"/>
   <tableColumns count="15">
     <tableColumn id="1" name="Collected At (JST)"/>
@@ -516,7 +516,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="RunLogTable" displayName="RunLogTable" ref="A3:H15" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="RunLogTable" displayName="RunLogTable" ref="A3:H16" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <autoFilter ref="A3:H4"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Run Time (JST)"/>
@@ -800,7 +800,7 @@
       </c>
       <c r="B5" s="25" t="inlineStr">
         <is>
-          <t>2026-07-26T21:02:36+09:00</t>
+          <t>2026-07-26T21:29:09+09:00</t>
         </is>
       </c>
       <c r="C5" s="46" t="n"/>
@@ -1088,7 +1088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O33"/>
+  <dimension ref="A1:O88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1891,61 +1891,65 @@
     <row r="13" ht="42" customHeight="1">
       <c r="A13" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:29:40+09:00</t>
+          <t>2026-07-26T21:29:09+09:00</t>
         </is>
       </c>
       <c r="B13" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T14:21:46Z</t>
+          <t>2026-07-23T00:00:00Z</t>
         </is>
       </c>
       <c r="C13" s="60" t="inlineStr">
         <is>
-          <t>EU &amp; Europe</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="D13" s="60" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="E13" s="60" t="inlineStr"/>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E13" s="60" t="inlineStr">
+        <is>
+          <t>Robotics | Artificial Intelligence</t>
+        </is>
+      </c>
       <c r="F13" s="76" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G13" s="60" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Journal Article</t>
         </is>
       </c>
       <c r="H13" s="60" t="inlineStr">
         <is>
-          <t>UK DSIT</t>
+          <t>Frontiers in Neurorobotics</t>
         </is>
       </c>
       <c r="I13" s="60" t="inlineStr">
         <is>
-          <t>ガイダンス：研究における女性のためのチャーター</t>
+          <t>AI駆動の四足歩行ロボット：基本的な動作から高度な生物模倣行動まで</t>
         </is>
       </c>
       <c r="J13" s="60" t="inlineStr">
         <is>
-          <t>UKの研究システムにおける女性の成果を改善するための自主的な取り組みが発表された。</t>
+          <t>この研究は、四足歩行ロボットの動作制御や生物模倣行動に関するもので、ロボティクスとAIの融合を探求しています。</t>
         </is>
       </c>
       <c r="K13" s="60" t="inlineStr">
         <is>
-          <t>https://www.gov.uk/government/publications/women-in-research-charter</t>
+          <t>https://doi.org/10.3389/fnbot.2026.1855550</t>
         </is>
       </c>
       <c r="L13" s="60" t="inlineStr">
         <is>
-          <t>1e9fd9033d38bacea37c0f42</t>
+          <t>e165800add9d682af8ea2122</t>
         </is>
       </c>
       <c r="M13" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:29:40+09:00</t>
+          <t>2026-07-26T21:29:09+09:00</t>
         </is>
       </c>
       <c r="N13" s="60" t="inlineStr">
@@ -1955,72 +1959,72 @@
       </c>
       <c r="O13" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy | Research System &amp; Talent / 学術区分: News &amp; Official Release / 焦点: 女性研究者の成果向上</t>
+          <t>枠: Technology Innovation / 学術区分: Journal Article / 査読表示: Journal record — confirm peer review on publisher page / 掲載誌・学会: Frontiers in Neurorobotics / 焦点: 四足歩行ロボットの動作制御 / OpenAlex record; work type=article; citations=0</t>
         </is>
       </c>
     </row>
     <row r="14" ht="42" customHeight="1">
       <c r="A14" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:29:40+09:00</t>
+          <t>2026-07-26T21:29:09+09:00</t>
         </is>
       </c>
       <c r="B14" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T14:12:14Z</t>
+          <t>2026-07-23T00:00:00Z</t>
         </is>
       </c>
       <c r="C14" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D14" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="E14" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Fusion Energy</t>
         </is>
       </c>
       <c r="F14" s="76" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G14" s="60" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Journal Article</t>
         </is>
       </c>
       <c r="H14" s="60" t="inlineStr">
         <is>
-          <t>DOE Office of Science News</t>
+          <t>Nuclear Fusion</t>
         </is>
       </c>
       <c r="I14" s="60" t="inlineStr">
         <is>
-          <t>エネルギー長官クリス・ライト、AI駆動の科学発見を加速するための初のジェネシスミッションプロジェクトを発表</t>
+          <t>Wendelstein 7-X ステラレーターにおけるエネルギーイオンの閉じ込めにおける放射電場の役割</t>
         </is>
       </c>
       <c r="J14" s="60" t="inlineStr">
         <is>
-          <t>米国エネルギー省がAI駆動の科学発見を加速するために、全米から選ばれたプロジェクトを発表した。</t>
+          <t>この研究は、Wendelstein 7-X ステラレーターにおけるエネルギーイオンの閉じ込めにおける放射電場の役割を探求しています。</t>
         </is>
       </c>
       <c r="K14" s="60" t="inlineStr">
         <is>
-          <t>https://www.energy.gov/articles/secretary-energy-chris-wright-announces-first-genesis-mission-projects-selected-accelerate</t>
+          <t>https://doi.org/10.1088/1741-4326/ae8f55</t>
         </is>
       </c>
       <c r="L14" s="60" t="inlineStr">
         <is>
-          <t>23fa1d6907c14d73ce3a41cd</t>
+          <t>eef01d292bfb6d5bb3537528</t>
         </is>
       </c>
       <c r="M14" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:29:40+09:00</t>
+          <t>2026-07-26T21:29:09+09:00</t>
         </is>
       </c>
       <c r="N14" s="60" t="inlineStr">
@@ -2030,72 +2034,72 @@
       </c>
       <c r="O14" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: AI駆動の科学発見プロジェクト</t>
+          <t>枠: Technology Innovation / 学術区分: Journal Article / 査読表示: Journal record — confirm peer review on publisher page / 掲載誌・学会: Nuclear Fusion / 焦点: Wendelstein 7-X ステラレーターにおけるエネルギーイオンの閉じ込め / OpenAlex record; work type=article; citations=0</t>
         </is>
       </c>
     </row>
     <row r="15" ht="42" customHeight="1">
       <c r="A15" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:05:06+09:00</t>
+          <t>2026-07-26T21:29:09+09:00</t>
         </is>
       </c>
       <c r="B15" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T13:53:19Z</t>
+          <t>2026-07-23T00:00:00Z</t>
         </is>
       </c>
       <c r="C15" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D15" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="E15" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="F15" s="76" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G15" s="60" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Journal Article</t>
         </is>
       </c>
       <c r="H15" s="60" t="inlineStr">
         <is>
-          <t>National Science Foundation News</t>
+          <t>Scientific Reports</t>
         </is>
       </c>
       <c r="I15" s="60" t="inlineStr">
         <is>
-          <t>NSFがAIに関する国家戦略を推進する声明を発表</t>
+          <t>密なプラズマ焦点ホットスポットにおけるクーロン爆発の研究</t>
         </is>
       </c>
       <c r="J15" s="60" t="inlineStr">
         <is>
-          <t>米国科学財団（NSF）は、AIに関する国家戦略を推進するための声明を発表しました。</t>
+          <t>この研究は、密なプラズマ焦点におけるクーロン爆発をEPOCH粒子インセルシミュレーションコードを用いて探求しています。</t>
         </is>
       </c>
       <c r="K15" s="60" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/news/statement-nsf-chief-staff-brian-stone-performing-duties-nsf-1</t>
+          <t>https://doi.org/10.1038/s41598-026-63204-9</t>
         </is>
       </c>
       <c r="L15" s="60" t="inlineStr">
         <is>
-          <t>123e2207578ca69c8f9c00a2</t>
+          <t>fcf607380491b3f6666abab6</t>
         </is>
       </c>
       <c r="M15" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:05:06+09:00</t>
+          <t>2026-07-26T21:29:09+09:00</t>
         </is>
       </c>
       <c r="N15" s="60" t="inlineStr">
@@ -2105,72 +2109,72 @@
       </c>
       <c r="O15" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: AIに関する国家戦略の推進</t>
+          <t>枠: Technology Innovation / 学術区分: Journal Article / 査読表示: Journal record — confirm peer review on publisher page / 掲載誌・学会: Scientific Reports / 焦点: 密なプラズマ焦点におけるクーロン爆発の研究 / OpenAlex record; work type=article; citations=0</t>
         </is>
       </c>
     </row>
     <row r="16" ht="42" customHeight="1">
       <c r="A16" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:05:06+09:00</t>
+          <t>2026-07-26T21:29:09+09:00</t>
         </is>
       </c>
       <c r="B16" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T13:53:12Z</t>
+          <t>2026-07-23T00:00:00Z</t>
         </is>
       </c>
       <c r="C16" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D16" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="E16" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="F16" s="76" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G16" s="60" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Journal Article</t>
         </is>
       </c>
       <c r="H16" s="60" t="inlineStr">
         <is>
-          <t>National Science Foundation News</t>
+          <t>Frontiers in Microbiology</t>
         </is>
       </c>
       <c r="I16" s="60" t="inlineStr">
         <is>
-          <t>NSFの新しい取り組みがAIによる科学的発見のためのデータセットの価値を引き出す</t>
+          <t>バイオコントロールの可能性を持つ非モデルPseudoduganella株における全ゲノム配列と質量分析</t>
         </is>
       </c>
       <c r="J16" s="60" t="inlineStr">
         <is>
-          <t>米国科学財団（NSF）は、AIを活用した科学的発見のためのデータセットの価値を引き出す新しいプログラムを発表しました。</t>
+          <t>この研究は、バイオコントロールの可能性を持つ微生物の全ゲノム配列と質量分析に関するものです。</t>
         </is>
       </c>
       <c r="K16" s="60" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/news/new-nsf-initiative-aims-unlock-dataset-value-ai-enabled</t>
+          <t>https://doi.org/10.3389/fmicb.2026.1888443</t>
         </is>
       </c>
       <c r="L16" s="60" t="inlineStr">
         <is>
-          <t>dcd819527d9b80141b26bcb8</t>
+          <t>8e46c4e77352612582c695b8</t>
         </is>
       </c>
       <c r="M16" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:05:06+09:00</t>
+          <t>2026-07-26T21:29:09+09:00</t>
         </is>
       </c>
       <c r="N16" s="60" t="inlineStr">
@@ -2180,29 +2184,29 @@
       </c>
       <c r="O16" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: R&amp;D Funding &amp; Tax Incentives / 学術区分: News &amp; Official Release / 焦点: AIを活用した科学的発見のためのデータセットの価値を引き出すプログラム</t>
+          <t>枠: Technology Innovation / 学術区分: Journal Article / 査読表示: Journal record — confirm peer review on publisher page / 掲載誌・学会: Frontiers in Microbiology / 焦点: バイオコントロールの可能性を持つ微生物のゲノム解析 / OpenAlex record; work type=article; citations=0</t>
         </is>
       </c>
     </row>
     <row r="17" ht="42" customHeight="1">
       <c r="A17" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:29:40+09:00</t>
+          <t>2026-07-26T21:29:09+09:00</t>
         </is>
       </c>
       <c r="B17" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T13:53:06Z</t>
+          <t>2026-07-23T00:00:00Z</t>
         </is>
       </c>
       <c r="C17" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D17" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="E17" s="60" t="inlineStr">
@@ -2211,41 +2215,41 @@
         </is>
       </c>
       <c r="F17" s="76" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G17" s="60" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Journal Article</t>
         </is>
       </c>
       <c r="H17" s="60" t="inlineStr">
         <is>
-          <t>National Science Foundation News</t>
+          <t>OpenAlex Journal Articles</t>
         </is>
       </c>
       <c r="I17" s="60" t="inlineStr">
         <is>
-          <t>NSF、AI駆動の科学を進展させるために8300万ドルの投資を発表</t>
+          <t>人工知能による地磁気嵐の予測：レビュー、方法論的枠組み、シミュレーション事例研究</t>
         </is>
       </c>
       <c r="J17" s="60" t="inlineStr">
         <is>
-          <t>米国科学財団が8300万ドルの資金を通じて、AI駆動の科学を進展させるためのデータシステムとサービスの整備を発表した。</t>
+          <t>この研究は、人工知能を用いた地磁気嵐の予測に関する方法論的枠組みを提供しています。</t>
         </is>
       </c>
       <c r="K17" s="60" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/news/nsf-announces-83m-investment-integrated-data-systems</t>
+          <t>https://doi.org/10.64823/ijpcs.2601002</t>
         </is>
       </c>
       <c r="L17" s="60" t="inlineStr">
         <is>
-          <t>018d40b7e6eb7aa4b8cfb5fa</t>
+          <t>00fc3537b602e30057c2118d</t>
         </is>
       </c>
       <c r="M17" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:29:40+09:00</t>
+          <t>2026-07-26T21:29:09+09:00</t>
         </is>
       </c>
       <c r="N17" s="60" t="inlineStr">
@@ -2255,68 +2259,72 @@
       </c>
       <c r="O17" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy | Research System &amp; Talent / 学術区分: News &amp; Official Release / 焦点: AI駆動の科学研究インフラ整備</t>
+          <t>枠: Technology Innovation / 学術区分: Journal Article / 査読表示: Journal record — confirm peer review on publisher page / 焦点: 地磁気嵐の予測におけるAIの応用 / OpenAlex record; work type=article; citations=0</t>
         </is>
       </c>
     </row>
     <row r="18" ht="42" customHeight="1">
       <c r="A18" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:29:40+09:00</t>
+          <t>2026-07-26T21:29:09+09:00</t>
         </is>
       </c>
       <c r="B18" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T12:00:00Z</t>
+          <t>2026-07-23T00:00:00Z</t>
         </is>
       </c>
       <c r="C18" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D18" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E18" s="60" t="inlineStr"/>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E18" s="60" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
       <c r="F18" s="76" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G18" s="60" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Preprint</t>
         </is>
       </c>
       <c r="H18" s="60" t="inlineStr">
         <is>
-          <t>NIST News</t>
+          <t>Zenodo (CERN European Organization for Nuclear Research)</t>
         </is>
       </c>
       <c r="I18" s="60" t="inlineStr">
         <is>
-          <t>NISTが中小企業向けの資金提供機会を発表</t>
+          <t>Prim-Lex理論と量子技術ガバナンス：キュービットから量子主権へ</t>
         </is>
       </c>
       <c r="J18" s="60" t="inlineStr">
         <is>
-          <t>NIST MEPは、米国の中小企業を支援するための資金提供機会を発表し、2026年7月28日にウェビナーを開催する予定です。</t>
+          <t>この研究は、量子技術のガバナンスとその社会的影響について探求しています。</t>
         </is>
       </c>
       <c r="K18" s="60" t="inlineStr">
         <is>
-          <t>https://www.nist.gov/news-events/news/2026/07/nist-announces-funding-opportunity-14-mep-centers-advance-small-and-medium</t>
+          <t>https://doi.org/10.5281/zenodo.21512028</t>
         </is>
       </c>
       <c r="L18" s="60" t="inlineStr">
         <is>
-          <t>5aa9c93bc7040291c9f08bfa</t>
+          <t>61f1fcfb9afff652f523d019</t>
         </is>
       </c>
       <c r="M18" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:29:40+09:00</t>
+          <t>2026-07-26T21:29:09+09:00</t>
         </is>
       </c>
       <c r="N18" s="60" t="inlineStr">
@@ -2326,72 +2334,72 @@
       </c>
       <c r="O18" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: R&amp;D Funding &amp; Tax Incentives | Public Procurement &amp; Industrial Policy / 学術区分: News &amp; Official Release / 焦点: 中小企業向けの資金提供</t>
+          <t>枠: Technology Innovation / 学術区分: Preprint / 査読表示: Not peer reviewed / 掲載誌・学会: Zenodo (CERN European Organization for Nuclear Research) / 焦点: 量子技術のガバナンスと量子主権 / OpenAlex record; work type=preprint; citations=0</t>
         </is>
       </c>
     </row>
     <row r="19" ht="42" customHeight="1">
       <c r="A19" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T21:02:36+09:00</t>
+          <t>2026-07-26T21:29:09+09:00</t>
         </is>
       </c>
       <c r="B19" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T05:00:56Z</t>
+          <t>2026-07-23T00:00:00Z</t>
         </is>
       </c>
       <c r="C19" s="60" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D19" s="60" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="E19" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="F19" s="76" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G19" s="60" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Preprint</t>
         </is>
       </c>
       <c r="H19" s="60" t="inlineStr">
         <is>
-          <t>NISTEP Updates</t>
+          <t>bioRxiv (Cold Spring Harbor Laboratory)</t>
         </is>
       </c>
       <c r="I19" s="60" t="inlineStr">
         <is>
-          <t>特定科学技術領域動向報告書 -AI（人工知能）- 研究開発インプット編を公表</t>
+          <t>Aegilops speltoidesにおけるプログラムされた染色体除去とコヒーシンの過剰発現の相関</t>
         </is>
       </c>
       <c r="J19" s="60" t="inlineStr">
         <is>
-          <t>我が国のAI分野における研究開発インプット状況を分析した報告書が公表され、科学技術政策に資する知見を提供。</t>
+          <t>この研究は、植物の遺伝子と染色体の動態に関するものです。</t>
         </is>
       </c>
       <c r="K19" s="60" t="inlineStr">
         <is>
-          <t>https://www.nistep.go.jp/archives/63583/</t>
+          <t>https://doi.org/10.64898/2026.07.20.739560</t>
         </is>
       </c>
       <c r="L19" s="60" t="inlineStr">
         <is>
-          <t>6b6122461584a86ee7a1c595</t>
+          <t>90175c0dadf89da3e63d33a5</t>
         </is>
       </c>
       <c r="M19" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T14:00:56+09:00</t>
+          <t>2026-07-26T21:29:09+09:00</t>
         </is>
       </c>
       <c r="N19" s="60" t="inlineStr">
@@ -2401,72 +2409,68 @@
       </c>
       <c r="O19" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation | Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: 人工知能（AI）分野の研究開発インプット状況</t>
+          <t>枠: Technology Innovation / 学術区分: Preprint / 査読表示: Not peer reviewed / 掲載誌・学会: bioRxiv (Cold Spring Harbor Laboratory) / 焦点: 植物の遺伝子と染色体の研究 / OpenAlex record; work type=preprint; citations=0</t>
         </is>
       </c>
     </row>
     <row r="20" ht="42" customHeight="1">
       <c r="A20" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T21:02:36+09:00</t>
+          <t>2026-07-26T20:29:40+09:00</t>
         </is>
       </c>
       <c r="B20" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T00:00:00Z</t>
+          <t>2026-07-22T14:21:46Z</t>
         </is>
       </c>
       <c r="C20" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>EU &amp; Europe</t>
         </is>
       </c>
       <c r="D20" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E20" s="60" t="inlineStr">
-        <is>
-          <t>Artificial Intelligence</t>
-        </is>
-      </c>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="E20" s="60" t="inlineStr"/>
       <c r="F20" s="76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G20" s="60" t="inlineStr">
         <is>
-          <t>Policy Institute</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H20" s="60" t="inlineStr">
         <is>
-          <t>Brookings TechTank</t>
+          <t>UK DSIT</t>
         </is>
       </c>
       <c r="I20" s="60" t="inlineStr">
         <is>
-          <t>政策がGen ZのAIへの信頼を決定する</t>
+          <t>ガイダンス：研究における女性のためのチャーター</t>
         </is>
       </c>
       <c r="J20" s="60" t="inlineStr">
         <is>
-          <t>Gen ZがAIを信頼するかどうかは、PRではなく政策によって決まると指摘されている。</t>
+          <t>UKの研究システムにおける女性の成果を改善するための自主的な取り組みが発表された。</t>
         </is>
       </c>
       <c r="K20" s="60" t="inlineStr">
         <is>
-          <t>https://www.brookings.edu/articles/policy-not-pr-will-determine-gen-zs-trust-in-ai/</t>
+          <t>https://www.gov.uk/government/publications/women-in-research-charter</t>
         </is>
       </c>
       <c r="L20" s="60" t="inlineStr">
         <is>
-          <t>61bd55f8ce5a2385a5420260</t>
+          <t>1e9fd9033d38bacea37c0f42</t>
         </is>
       </c>
       <c r="M20" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T09:00:00+09:00</t>
+          <t>2026-07-26T20:29:40+09:00</t>
         </is>
       </c>
       <c r="N20" s="60" t="inlineStr">
@@ -2476,29 +2480,29 @@
       </c>
       <c r="O20" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: AIに関する政策</t>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy | Research System &amp; Talent / 学術区分: News &amp; Official Release / 焦点: 女性研究者の成果向上</t>
         </is>
       </c>
     </row>
     <row r="21" ht="42" customHeight="1">
       <c r="A21" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T21:02:36+09:00</t>
+          <t>2026-07-26T20:29:40+09:00</t>
         </is>
       </c>
       <c r="B21" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T00:00:00Z</t>
+          <t>2026-07-22T14:12:14Z</t>
         </is>
       </c>
       <c r="C21" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D21" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E21" s="60" t="inlineStr">
@@ -2507,41 +2511,41 @@
         </is>
       </c>
       <c r="F21" s="76" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G21" s="60" t="inlineStr">
         <is>
-          <t>Scientific Publication</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H21" s="60" t="inlineStr">
         <is>
-          <t>Nature</t>
+          <t>DOE Office of Science News</t>
         </is>
       </c>
       <c r="I21" s="60" t="inlineStr">
         <is>
-          <t>AIによる設計が酵素進化を促進</t>
+          <t>エネルギー長官クリス・ライト、AI駆動の科学発見を加速するための初のジェネシスミッションプロジェクトを発表</t>
         </is>
       </c>
       <c r="J21" s="60" t="inlineStr">
         <is>
-          <t>AIを用いて設計された出発点を使用し、自然なタンパク質から進化したものよりも改善された特性を持つ酵素を進化させるワークフローが確立されました。</t>
+          <t>米国エネルギー省がAI駆動の科学発見を加速するために、全米から選ばれたプロジェクトを発表した。</t>
         </is>
       </c>
       <c r="K21" s="60" t="inlineStr">
         <is>
-          <t>https://www.nature.com/articles/s41586-026-10820-0</t>
+          <t>https://www.energy.gov/articles/secretary-energy-chris-wright-announces-first-genesis-mission-projects-selected-accelerate</t>
         </is>
       </c>
       <c r="L21" s="60" t="inlineStr">
         <is>
-          <t>6e9f79f12db784e010b0dad5</t>
+          <t>23fa1d6907c14d73ce3a41cd</t>
         </is>
       </c>
       <c r="M21" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T09:00:00+09:00</t>
+          <t>2026-07-26T20:29:40+09:00</t>
         </is>
       </c>
       <c r="N21" s="60" t="inlineStr">
@@ -2551,72 +2555,72 @@
       </c>
       <c r="O21" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: AIを用いた酵素進化</t>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: AI駆動の科学発見プロジェクト</t>
         </is>
       </c>
     </row>
     <row r="22" ht="42" customHeight="1">
       <c r="A22" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T21:02:36+09:00</t>
+          <t>2026-07-26T19:05:06+09:00</t>
         </is>
       </c>
       <c r="B22" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T00:00:00Z</t>
+          <t>2026-07-22T13:53:19Z</t>
         </is>
       </c>
       <c r="C22" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D22" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E22" s="60" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="F22" s="76" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G22" s="60" t="inlineStr">
         <is>
-          <t>Scientific Publication</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H22" s="60" t="inlineStr">
         <is>
-          <t>Nature</t>
+          <t>National Science Foundation News</t>
         </is>
       </c>
       <c r="I22" s="60" t="inlineStr">
         <is>
-          <t>量子パラ電気体SrTiO3におけるナノスケール極性テクスチャのイメージング</t>
+          <t>NSFがAIに関する国家戦略を推進する声明を発表</t>
         </is>
       </c>
       <c r="J22" s="60" t="inlineStr">
         <is>
-          <t>SrTiO3が105K以下で周期的な極性ナノドメインを形成し、40K以下でこれらが断片化することが示され、量子パラ電気性とナノスケールの極性秩序および無秩序に関連付けられています。</t>
+          <t>米国科学財団（NSF）は、AIに関する国家戦略を推進するための声明を発表しました。</t>
         </is>
       </c>
       <c r="K22" s="60" t="inlineStr">
         <is>
-          <t>https://www.nature.com/articles/s41586-026-10823-x</t>
+          <t>https://www.nsf.gov/news/statement-nsf-chief-staff-brian-stone-performing-duties-nsf-1</t>
         </is>
       </c>
       <c r="L22" s="60" t="inlineStr">
         <is>
-          <t>f12f62aebb861877dd7a5cbf</t>
+          <t>123e2207578ca69c8f9c00a2</t>
         </is>
       </c>
       <c r="M22" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T09:00:00+09:00</t>
+          <t>2026-07-26T19:05:06+09:00</t>
         </is>
       </c>
       <c r="N22" s="60" t="inlineStr">
@@ -2626,68 +2630,72 @@
       </c>
       <c r="O22" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: 量子パラ電気体SrTiO3のナノスケール極性テクスチャ</t>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: AIに関する国家戦略の推進</t>
         </is>
       </c>
     </row>
     <row r="23" ht="42" customHeight="1">
       <c r="A23" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T21:02:36+09:00</t>
+          <t>2026-07-26T19:05:06+09:00</t>
         </is>
       </c>
       <c r="B23" s="75" t="inlineStr">
         <is>
-          <t>2026-07-21T19:44:19Z</t>
+          <t>2026-07-22T13:53:12Z</t>
         </is>
       </c>
       <c r="C23" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D23" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="E23" s="60" t="inlineStr"/>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E23" s="60" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence</t>
+        </is>
+      </c>
       <c r="F23" s="76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G23" s="60" t="inlineStr">
         <is>
-          <t>Industry Association</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H23" s="60" t="inlineStr">
         <is>
-          <t>Fusion Industry Association</t>
+          <t>National Science Foundation News</t>
         </is>
       </c>
       <c r="I23" s="60" t="inlineStr">
         <is>
-          <t>FIAとクリーンエアタスクフォースが核融合の基準に関する原則を発表</t>
+          <t>NSFの新しい取り組みがAIによる科学的発見のためのデータセットの価値を引き出す</t>
         </is>
       </c>
       <c r="J23" s="60" t="inlineStr">
         <is>
-          <t>FIAはクリーンエアタスクフォースと協力し、核融合のコードと基準に関する原則をまとめた文書を発表しました。核融合の展開に向けて、安全性を確保しつつ革新を促進するための基準が重要です。</t>
+          <t>米国科学財団（NSF）は、AIを活用した科学的発見のためのデータセットの価値を引き出す新しいプログラムを発表しました。</t>
         </is>
       </c>
       <c r="K23" s="60" t="inlineStr">
         <is>
-          <t>https://www.fusionindustryassociation.org/fia-and-clean-air-task-force-publish-principles-on-codes-and-standards/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=fia-and-clean-air-task-force-publish-principles-on-codes-and-standards</t>
+          <t>https://www.nsf.gov/news/new-nsf-initiative-aims-unlock-dataset-value-ai-enabled</t>
         </is>
       </c>
       <c r="L23" s="60" t="inlineStr">
         <is>
-          <t>2366dc909672b56b77a196bd</t>
+          <t>dcd819527d9b80141b26bcb8</t>
         </is>
       </c>
       <c r="M23" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T04:44:19+09:00</t>
+          <t>2026-07-26T19:05:06+09:00</t>
         </is>
       </c>
       <c r="N23" s="60" t="inlineStr">
@@ -2697,24 +2705,24 @@
       </c>
       <c r="O23" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: Standards &amp; Safety / 学術区分: News &amp; Official Release / 焦点: 核融合技術のコードと基準</t>
+          <t>枠: Innovation Policy / 政策分野: R&amp;D Funding &amp; Tax Incentives / 学術区分: News &amp; Official Release / 焦点: AIを活用した科学的発見のためのデータセットの価値を引き出すプログラム</t>
         </is>
       </c>
     </row>
     <row r="24" ht="42" customHeight="1">
       <c r="A24" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T21:02:36+09:00</t>
+          <t>2026-07-26T20:29:40+09:00</t>
         </is>
       </c>
       <c r="B24" s="75" t="inlineStr">
         <is>
-          <t>2026-07-21T17:00:00Z</t>
+          <t>2026-07-22T13:53:06Z</t>
         </is>
       </c>
       <c r="C24" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D24" s="60" t="inlineStr">
@@ -2728,41 +2736,41 @@
         </is>
       </c>
       <c r="F24" s="76" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G24" s="60" t="inlineStr">
         <is>
-          <t>Official Company</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H24" s="60" t="inlineStr">
         <is>
-          <t>OpenAI News</t>
+          <t>National Science Foundation News</t>
         </is>
       </c>
       <c r="I24" s="60" t="inlineStr">
         <is>
-          <t>OpenAIが中小企業向けChatGPTプログラムを発表</t>
+          <t>NSF、AI駆動の科学を進展させるために8300万ドルの投資を発表</t>
         </is>
       </c>
       <c r="J24" s="60" t="inlineStr">
         <is>
-          <t>OpenAIは、中小企業がAIスキルを構築し、業務を自動化し、ChatGPTを活用して成長するためのプログラムを開始しました。</t>
+          <t>米国科学財団が8300万ドルの資金を通じて、AI駆動の科学を進展させるためのデータシステムとサービスの整備を発表した。</t>
         </is>
       </c>
       <c r="K24" s="60" t="inlineStr">
         <is>
-          <t>https://openai.com/index/introducing-chatgpt-small-business-program</t>
+          <t>https://www.nsf.gov/news/nsf-announces-83m-investment-integrated-data-systems</t>
         </is>
       </c>
       <c r="L24" s="60" t="inlineStr">
         <is>
-          <t>3064e426d18ccd85acab9b00</t>
+          <t>018d40b7e6eb7aa4b8cfb5fa</t>
         </is>
       </c>
       <c r="M24" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T02:00:00+09:00</t>
+          <t>2026-07-26T20:29:40+09:00</t>
         </is>
       </c>
       <c r="N24" s="60" t="inlineStr">
@@ -2772,38 +2780,34 @@
       </c>
       <c r="O24" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: 中小企業向けのAIスキル向上プログラム</t>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy | Research System &amp; Talent / 学術区分: News &amp; Official Release / 焦点: AI駆動の科学研究インフラ整備</t>
         </is>
       </c>
     </row>
     <row r="25" ht="42" customHeight="1">
       <c r="A25" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T21:02:36+09:00</t>
+          <t>2026-07-26T20:29:40+09:00</t>
         </is>
       </c>
       <c r="B25" s="75" t="inlineStr">
         <is>
-          <t>2026-07-21T15:05:11Z</t>
+          <t>2026-07-22T12:00:00Z</t>
         </is>
       </c>
       <c r="C25" s="60" t="inlineStr">
         <is>
-          <t>EU &amp; Europe</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D25" s="60" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="E25" s="60" t="inlineStr">
-        <is>
-          <t>Semiconductors &amp; Telecom</t>
-        </is>
-      </c>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E25" s="60" t="inlineStr"/>
       <c r="F25" s="76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G25" s="60" t="inlineStr">
         <is>
@@ -2812,32 +2816,32 @@
       </c>
       <c r="H25" s="60" t="inlineStr">
         <is>
-          <t>UK DSIT</t>
+          <t>NIST News</t>
         </is>
       </c>
       <c r="I25" s="60" t="inlineStr">
         <is>
-          <t>政策文書：固定通信近代化憲章</t>
+          <t>NISTが中小企業向けの資金提供機会を発表</t>
         </is>
       </c>
       <c r="J25" s="60" t="inlineStr">
         <is>
-          <t>通信プロバイダーが現在および将来の固定通信近代化を行う際に従うべき手順を示す文書。</t>
+          <t>NIST MEPは、米国の中小企業を支援するための資金提供機会を発表し、2026年7月28日にウェビナーを開催する予定です。</t>
         </is>
       </c>
       <c r="K25" s="60" t="inlineStr">
         <is>
-          <t>https://www.gov.uk/government/publications/fixed-telecoms-modernisation-charter</t>
+          <t>https://www.nist.gov/news-events/news/2026/07/nist-announces-funding-opportunity-14-mep-centers-advance-small-and-medium</t>
         </is>
       </c>
       <c r="L25" s="60" t="inlineStr">
         <is>
-          <t>d5e4431b57fcb4b6271f6c72</t>
+          <t>5aa9c93bc7040291c9f08bfa</t>
         </is>
       </c>
       <c r="M25" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T00:05:11+09:00</t>
+          <t>2026-07-26T20:29:40+09:00</t>
         </is>
       </c>
       <c r="N25" s="60" t="inlineStr">
@@ -2847,7 +2851,7 @@
       </c>
       <c r="O25" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: 固定通信の近代化に関する手順</t>
+          <t>枠: Innovation Policy / 政策分野: R&amp;D Funding &amp; Tax Incentives | Public Procurement &amp; Industrial Policy / 学術区分: News &amp; Official Release / 焦点: 中小企業向けの資金提供</t>
         </is>
       </c>
     </row>
@@ -2859,26 +2863,26 @@
       </c>
       <c r="B26" s="75" t="inlineStr">
         <is>
-          <t>2026-07-21T15:05:07Z</t>
+          <t>2026-07-22T05:00:56Z</t>
         </is>
       </c>
       <c r="C26" s="60" t="inlineStr">
         <is>
-          <t>EU &amp; Europe</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="D26" s="60" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="E26" s="60" t="inlineStr">
         <is>
-          <t>Semiconductors &amp; Telecom</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="F26" s="76" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G26" s="60" t="inlineStr">
         <is>
@@ -2887,32 +2891,32 @@
       </c>
       <c r="H26" s="60" t="inlineStr">
         <is>
-          <t>UK DSIT</t>
+          <t>NISTEP Updates</t>
         </is>
       </c>
       <c r="I26" s="60" t="inlineStr">
         <is>
-          <t>政策文書：通信近代化：重要国家インフラ憲章</t>
+          <t>特定科学技術領域動向報告書 -AI（人工知能）- 研究開発インプット編を公表</t>
         </is>
       </c>
       <c r="J26" s="60" t="inlineStr">
         <is>
-          <t>通信会社が通信近代化中に重要な国家インフラを保護するためのアプローチを示す文書。</t>
+          <t>我が国のAI分野における研究開発インプット状況を分析した報告書が公表され、科学技術政策に資する知見を提供。</t>
         </is>
       </c>
       <c r="K26" s="60" t="inlineStr">
         <is>
-          <t>https://www.gov.uk/government/publications/telecoms-modernisation-critical-national-infrastructure-charter</t>
+          <t>https://www.nistep.go.jp/archives/63583/</t>
         </is>
       </c>
       <c r="L26" s="60" t="inlineStr">
         <is>
-          <t>aafa3a246656ccda64dd93c4</t>
+          <t>6b6122461584a86ee7a1c595</t>
         </is>
       </c>
       <c r="M26" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T00:05:07+09:00</t>
+          <t>2026-07-22T14:00:56+09:00</t>
         </is>
       </c>
       <c r="N26" s="60" t="inlineStr">
@@ -2922,7 +2926,7 @@
       </c>
       <c r="O26" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: 重要な国家インフラを保護するための通信会社のアプローチ</t>
+          <t>枠: Technology Innovation | Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: 人工知能（AI）分野の研究開発インプット状況</t>
         </is>
       </c>
     </row>
@@ -2934,12 +2938,12 @@
       </c>
       <c r="B27" s="75" t="inlineStr">
         <is>
-          <t>2026-07-21T15:00:20Z</t>
+          <t>2026-07-22T00:00:00Z</t>
         </is>
       </c>
       <c r="C27" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D27" s="60" t="inlineStr">
@@ -2953,41 +2957,41 @@
         </is>
       </c>
       <c r="F27" s="76" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G27" s="60" t="inlineStr">
         <is>
-          <t>Official Company</t>
+          <t>Policy Institute</t>
         </is>
       </c>
       <c r="H27" s="60" t="inlineStr">
         <is>
-          <t>NVIDIA Blog</t>
+          <t>Brookings TechTank</t>
         </is>
       </c>
       <c r="I27" s="60" t="inlineStr">
         <is>
-          <t>Vera Rubin向けに構築されたNVIDIA Spectrum-6がギガスケールAIファクトリーに登場</t>
+          <t>政策がGen ZのAIへの信頼を決定する</t>
         </is>
       </c>
       <c r="J27" s="60" t="inlineStr">
         <is>
-          <t>NVIDIA Spectrum-6は、数十万のGPUとCPUを統合し、フロンティアモデルを訓練するためのギガスケールAIファクトリーを実現します。ネットワーキングが計算能力を向上させる重要な要素となっています。</t>
+          <t>Gen ZがAIを信頼するかどうかは、PRではなく政策によって決まると指摘されている。</t>
         </is>
       </c>
       <c r="K27" s="60" t="inlineStr">
         <is>
-          <t>https://blogs.nvidia.com/blog/nvidia-spectrum-six-arrives-in-gigascale-ai-factories/</t>
+          <t>https://www.brookings.edu/articles/policy-not-pr-will-determine-gen-zs-trust-in-ai/</t>
         </is>
       </c>
       <c r="L27" s="60" t="inlineStr">
         <is>
-          <t>6f3401cebeb5dc5a8f12a872</t>
+          <t>61bd55f8ce5a2385a5420260</t>
         </is>
       </c>
       <c r="M27" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T00:00:20+09:00</t>
+          <t>2026-07-22T09:00:00+09:00</t>
         </is>
       </c>
       <c r="N27" s="60" t="inlineStr">
@@ -2997,24 +3001,24 @@
       </c>
       <c r="O27" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: AIファクトリーの構築とネットワーキング技術</t>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: AIに関する政策</t>
         </is>
       </c>
     </row>
     <row r="28" ht="42" customHeight="1">
       <c r="A28" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T21:02:36+09:00</t>
         </is>
       </c>
       <c r="B28" s="75" t="inlineStr">
         <is>
-          <t>2026-07-21T14:48:28Z</t>
+          <t>2026-07-22T00:00:00Z</t>
         </is>
       </c>
       <c r="C28" s="60" t="inlineStr">
         <is>
-          <t>EU &amp; Europe</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D28" s="60" t="inlineStr">
@@ -3024,45 +3028,45 @@
       </c>
       <c r="E28" s="60" t="inlineStr">
         <is>
-          <t>Fusion Energy</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="F28" s="76" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G28" s="60" t="inlineStr">
         <is>
-          <t>Industry Association</t>
+          <t>Scientific Publication</t>
         </is>
       </c>
       <c r="H28" s="60" t="inlineStr">
         <is>
-          <t>Fusion Industry Association</t>
+          <t>Nature</t>
         </is>
       </c>
       <c r="I28" s="60" t="inlineStr">
         <is>
-          <t>FIAが核融合のためのEU資金調達の道筋を示す</t>
+          <t>AIによる設計が酵素進化を促進</t>
         </is>
       </c>
       <c r="J28" s="60" t="inlineStr">
         <is>
-          <t>核融合産業協会は、商業核融合エネルギーのための実用的なEU資金調達の道筋を示す論文を発表しました。核融合プロジェクトが研究から実証へ移行する際に必要な資金調達手段について論じています。</t>
+          <t>AIを用いて設計された出発点を使用し、自然なタンパク質から進化したものよりも改善された特性を持つ酵素を進化させるワークフローが確立されました。</t>
         </is>
       </c>
       <c r="K28" s="60" t="inlineStr">
         <is>
-          <t>https://www.fusionindustryassociation.org/fia-outlines-eu-financing-pathway-for-fusion/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=fia-outlines-eu-financing-pathway-for-fusion</t>
+          <t>https://www.nature.com/articles/s41586-026-10820-0</t>
         </is>
       </c>
       <c r="L28" s="60" t="inlineStr">
         <is>
-          <t>88af233d904d670250fa5a31</t>
+          <t>6e9f79f12db784e010b0dad5</t>
         </is>
       </c>
       <c r="M28" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-22T09:00:00+09:00</t>
         </is>
       </c>
       <c r="N28" s="60" t="inlineStr">
@@ -3072,7 +3076,7 @@
       </c>
       <c r="O28" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: R&amp;D Funding &amp; Tax Incentives / 学術区分: News &amp; Official Release / 焦点: 商業核融合エネルギーの資金調達</t>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: AIを用いた酵素進化</t>
         </is>
       </c>
     </row>
@@ -3084,60 +3088,60 @@
       </c>
       <c r="B29" s="75" t="inlineStr">
         <is>
-          <t>2026-07-21T13:30:36Z</t>
+          <t>2026-07-22T00:00:00Z</t>
         </is>
       </c>
       <c r="C29" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D29" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="E29" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="F29" s="76" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G29" s="60" t="inlineStr">
         <is>
-          <t>Policy Institute</t>
+          <t>Scientific Publication</t>
         </is>
       </c>
       <c r="H29" s="60" t="inlineStr">
         <is>
-          <t>CSET</t>
+          <t>Nature</t>
         </is>
       </c>
       <c r="I29" s="60" t="inlineStr">
         <is>
-          <t>AIシステムはなぜ誤動作するのか？</t>
+          <t>量子パラ電気体SrTiO3におけるナノスケール極性テクスチャのイメージング</t>
         </is>
       </c>
       <c r="J29" s="60" t="inlineStr">
         <is>
-          <t>AIシステムの進化に伴い、その失敗の原因がますます謎となっています。このブログでは、AIの誤動作の原因について掘り下げています。</t>
+          <t>SrTiO3が105K以下で周期的な極性ナノドメインを形成し、40K以下でこれらが断片化することが示され、量子パラ電気性とナノスケールの極性秩序および無秩序に関連付けられています。</t>
         </is>
       </c>
       <c r="K29" s="60" t="inlineStr">
         <is>
-          <t>https://cset.georgetown.edu/article/why-do-ai-systems-misbehave/</t>
+          <t>https://www.nature.com/articles/s41586-026-10823-x</t>
         </is>
       </c>
       <c r="L29" s="60" t="inlineStr">
         <is>
-          <t>3e1aa390ad965782cc86c386</t>
+          <t>f12f62aebb861877dd7a5cbf</t>
         </is>
       </c>
       <c r="M29" s="75" t="inlineStr">
         <is>
-          <t>2026-07-21T22:30:36+09:00</t>
+          <t>2026-07-22T09:00:00+09:00</t>
         </is>
       </c>
       <c r="N29" s="60" t="inlineStr">
@@ -3147,7 +3151,7 @@
       </c>
       <c r="O29" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation | Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: AIシステムの誤動作の原因</t>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: 量子パラ電気体SrTiO3のナノスケール極性テクスチャ</t>
         </is>
       </c>
     </row>
@@ -3159,60 +3163,56 @@
       </c>
       <c r="B30" s="75" t="inlineStr">
         <is>
-          <t>2026-07-20T21:06:27Z</t>
+          <t>2026-07-21T19:44:19Z</t>
         </is>
       </c>
       <c r="C30" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D30" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E30" s="60" t="inlineStr">
-        <is>
-          <t>Artificial Intelligence</t>
-        </is>
-      </c>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E30" s="60" t="inlineStr"/>
       <c r="F30" s="76" t="n">
         <v>3</v>
       </c>
       <c r="G30" s="60" t="inlineStr">
         <is>
-          <t>Policy Institute</t>
+          <t>Industry Association</t>
         </is>
       </c>
       <c r="H30" s="60" t="inlineStr">
         <is>
-          <t>Brookings TechTank</t>
+          <t>Fusion Industry Association</t>
         </is>
       </c>
       <c r="I30" s="60" t="inlineStr">
         <is>
-          <t>相続を返す：教育と研究政策がAIの借りた専門知識にどう対処できるか</t>
+          <t>FIAとクリーンエアタスクフォースが核融合の基準に関する原則を発表</t>
         </is>
       </c>
       <c r="J30" s="60" t="inlineStr">
         <is>
-          <t>教育と研究政策がAIの専門知識の借用にどのように対処すべきかについて論じられている。</t>
+          <t>FIAはクリーンエアタスクフォースと協力し、核融合のコードと基準に関する原則をまとめた文書を発表しました。核融合の展開に向けて、安全性を確保しつつ革新を促進するための基準が重要です。</t>
         </is>
       </c>
       <c r="K30" s="60" t="inlineStr">
         <is>
-          <t>https://brookings.edu/articles/repaying-the-inheritance-how-education-and-research-policy-can-address-ais-borrowed-expertise</t>
+          <t>https://www.fusionindustryassociation.org/fia-and-clean-air-task-force-publish-principles-on-codes-and-standards/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=fia-and-clean-air-task-force-publish-principles-on-codes-and-standards</t>
         </is>
       </c>
       <c r="L30" s="60" t="inlineStr">
         <is>
-          <t>42183313e1c951c0483c0d62</t>
+          <t>2366dc909672b56b77a196bd</t>
         </is>
       </c>
       <c r="M30" s="75" t="inlineStr">
         <is>
-          <t>2026-07-21T06:06:27+09:00</t>
+          <t>2026-07-22T04:44:19+09:00</t>
         </is>
       </c>
       <c r="N30" s="60" t="inlineStr">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="O30" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: AIに関する教育政策 / Historical backfill from an allowlisted source.</t>
+          <t>枠: Innovation Policy / 政策分野: Standards &amp; Safety / 学術区分: News &amp; Official Release / 焦点: 核融合技術のコードと基準</t>
         </is>
       </c>
     </row>
@@ -3234,60 +3234,60 @@
       </c>
       <c r="B31" s="75" t="inlineStr">
         <is>
-          <t>2026-07-20T15:55:00Z</t>
+          <t>2026-07-21T17:00:00Z</t>
         </is>
       </c>
       <c r="C31" s="60" t="inlineStr">
         <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="D31" s="60" t="inlineStr">
+        <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="D31" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
       <c r="E31" s="60" t="inlineStr">
         <is>
-          <t>Semiconductors &amp; Telecom</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="F31" s="76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G31" s="60" t="inlineStr">
         <is>
-          <t>Major Media</t>
+          <t>Official Company</t>
         </is>
       </c>
       <c r="H31" s="60" t="inlineStr">
         <is>
-          <t>IEEE Spectrum</t>
+          <t>OpenAI News</t>
         </is>
       </c>
       <c r="I31" s="60" t="inlineStr">
         <is>
-          <t>先端半導体故障解析のためのSEMガイド低電圧FIB仕上げ</t>
+          <t>OpenAIが中小企業向けChatGPTプログラムを発表</t>
         </is>
       </c>
       <c r="J31" s="60" t="inlineStr">
         <is>
-          <t>ZEISS Crossbeam 750 FIBSEMが、先端半導体の故障解析において新たな基準を設定する技術を紹介。精密なTEMラメラ準備やトモグラフィーを実現し、データ駆動の意思決定を加速させる。</t>
+          <t>OpenAIは、中小企業がAIスキルを構築し、業務を自動化し、ChatGPTを活用して成長するためのプログラムを開始しました。</t>
         </is>
       </c>
       <c r="K31" s="60" t="inlineStr">
         <is>
-          <t>https://event.on24.com/wcc/r/5418459/287E3D5B99470D34C830D69A24B3B207</t>
+          <t>https://openai.com/index/introducing-chatgpt-small-business-program</t>
         </is>
       </c>
       <c r="L31" s="60" t="inlineStr">
         <is>
-          <t>73d0028e337a76c2cd00f1bc</t>
+          <t>3064e426d18ccd85acab9b00</t>
         </is>
       </c>
       <c r="M31" s="75" t="inlineStr">
         <is>
-          <t>2026-07-21T00:55:00+09:00</t>
+          <t>2026-07-22T02:00:00+09:00</t>
         </is>
       </c>
       <c r="N31" s="60" t="inlineStr">
@@ -3297,19 +3297,19 @@
       </c>
       <c r="O31" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: 半導体故障解析のためのFIB技術</t>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: 中小企業向けのAIスキル向上プログラム</t>
         </is>
       </c>
     </row>
     <row r="32" ht="42" customHeight="1">
       <c r="A32" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T21:02:36+09:00</t>
         </is>
       </c>
       <c r="B32" s="75" t="inlineStr">
         <is>
-          <t>2026-07-17T18:42:47Z</t>
+          <t>2026-07-21T15:05:11Z</t>
         </is>
       </c>
       <c r="C32" s="60" t="inlineStr">
@@ -3319,50 +3319,50 @@
       </c>
       <c r="D32" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="E32" s="60" t="inlineStr">
         <is>
-          <t>Fusion Energy</t>
+          <t>Semiconductors &amp; Telecom</t>
         </is>
       </c>
       <c r="F32" s="76" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G32" s="60" t="inlineStr">
         <is>
-          <t>Industry Association</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H32" s="60" t="inlineStr">
         <is>
-          <t>Fusion Industry Association</t>
+          <t>UK DSIT</t>
         </is>
       </c>
       <c r="I32" s="60" t="inlineStr">
         <is>
-          <t>国際法専門家グループがEUの核融合競争力確保の必要性に関する論文を発表</t>
+          <t>政策文書：固定通信近代化憲章</t>
         </is>
       </c>
       <c r="J32" s="60" t="inlineStr">
         <is>
-          <t>国際法専門家グループが発表した論文は、EUが商業核融合において競争優位を持っているが、それを維持するためには今すぐ行動が必要であると主張しています。</t>
+          <t>通信プロバイダーが現在および将来の固定通信近代化を行う際に従うべき手順を示す文書。</t>
         </is>
       </c>
       <c r="K32" s="60" t="inlineStr">
         <is>
-          <t>https://www.fusionindustryassociation.org/international-legal-expert-group-publish-paper-on-the-need-for-the-eu-to-secure-its-competitive-fusion-advantage/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=international-legal-expert-group-publish-paper-on-the-need-for-the-eu-to-secure-its-competitive-fusion-advantage</t>
+          <t>https://www.gov.uk/government/publications/fixed-telecoms-modernisation-charter</t>
         </is>
       </c>
       <c r="L32" s="60" t="inlineStr">
         <is>
-          <t>7ef6110ab078602757409abf</t>
+          <t>d5e4431b57fcb4b6271f6c72</t>
         </is>
       </c>
       <c r="M32" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-22T00:05:11+09:00</t>
         </is>
       </c>
       <c r="N32" s="60" t="inlineStr">
@@ -3372,34 +3372,34 @@
       </c>
       <c r="O32" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: Regulation &amp; Governance / 学術区分: News &amp; Official Release / 焦点: EUの核融合競争力の維持</t>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: 固定通信の近代化に関する手順</t>
         </is>
       </c>
     </row>
     <row r="33" ht="42" customHeight="1">
       <c r="A33" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T21:02:36+09:00</t>
         </is>
       </c>
       <c r="B33" s="75" t="inlineStr">
         <is>
-          <t>2026-07-15T17:47:57Z</t>
+          <t>2026-07-21T15:05:07Z</t>
         </is>
       </c>
       <c r="C33" s="60" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>EU &amp; Europe</t>
         </is>
       </c>
       <c r="D33" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="E33" s="60" t="inlineStr">
         <is>
-          <t>Fusion Energy</t>
+          <t>Semiconductors &amp; Telecom</t>
         </is>
       </c>
       <c r="F33" s="76" t="n">
@@ -3407,52 +3407,4129 @@
       </c>
       <c r="G33" s="60" t="inlineStr">
         <is>
+          <t>Government</t>
+        </is>
+      </c>
+      <c r="H33" s="60" t="inlineStr">
+        <is>
+          <t>UK DSIT</t>
+        </is>
+      </c>
+      <c r="I33" s="60" t="inlineStr">
+        <is>
+          <t>政策文書：通信近代化：重要国家インフラ憲章</t>
+        </is>
+      </c>
+      <c r="J33" s="60" t="inlineStr">
+        <is>
+          <t>通信会社が通信近代化中に重要な国家インフラを保護するためのアプローチを示す文書。</t>
+        </is>
+      </c>
+      <c r="K33" s="60" t="inlineStr">
+        <is>
+          <t>https://www.gov.uk/government/publications/telecoms-modernisation-critical-national-infrastructure-charter</t>
+        </is>
+      </c>
+      <c r="L33" s="60" t="inlineStr">
+        <is>
+          <t>aafa3a246656ccda64dd93c4</t>
+        </is>
+      </c>
+      <c r="M33" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-22T00:05:07+09:00</t>
+        </is>
+      </c>
+      <c r="N33" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O33" s="60" t="inlineStr">
+        <is>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: 重要な国家インフラを保護するための通信会社のアプローチ</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="42" customHeight="1">
+      <c r="A34" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T21:02:36+09:00</t>
+        </is>
+      </c>
+      <c r="B34" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-21T15:00:20Z</t>
+        </is>
+      </c>
+      <c r="C34" s="60" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="D34" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E34" s="60" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="F34" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="60" t="inlineStr">
+        <is>
+          <t>Official Company</t>
+        </is>
+      </c>
+      <c r="H34" s="60" t="inlineStr">
+        <is>
+          <t>NVIDIA Blog</t>
+        </is>
+      </c>
+      <c r="I34" s="60" t="inlineStr">
+        <is>
+          <t>Vera Rubin向けに構築されたNVIDIA Spectrum-6がギガスケールAIファクトリーに登場</t>
+        </is>
+      </c>
+      <c r="J34" s="60" t="inlineStr">
+        <is>
+          <t>NVIDIA Spectrum-6は、数十万のGPUとCPUを統合し、フロンティアモデルを訓練するためのギガスケールAIファクトリーを実現します。ネットワーキングが計算能力を向上させる重要な要素となっています。</t>
+        </is>
+      </c>
+      <c r="K34" s="60" t="inlineStr">
+        <is>
+          <t>https://blogs.nvidia.com/blog/nvidia-spectrum-six-arrives-in-gigascale-ai-factories/</t>
+        </is>
+      </c>
+      <c r="L34" s="60" t="inlineStr">
+        <is>
+          <t>6f3401cebeb5dc5a8f12a872</t>
+        </is>
+      </c>
+      <c r="M34" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-22T00:00:20+09:00</t>
+        </is>
+      </c>
+      <c r="N34" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O34" s="60" t="inlineStr">
+        <is>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: AIファクトリーの構築とネットワーキング技術</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="42" customHeight="1">
+      <c r="A35" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T18:56:03+09:00</t>
+        </is>
+      </c>
+      <c r="B35" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-21T14:48:28Z</t>
+        </is>
+      </c>
+      <c r="C35" s="60" t="inlineStr">
+        <is>
+          <t>EU &amp; Europe</t>
+        </is>
+      </c>
+      <c r="D35" s="60" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E35" s="60" t="inlineStr">
+        <is>
+          <t>Fusion Energy</t>
+        </is>
+      </c>
+      <c r="F35" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="G35" s="60" t="inlineStr">
+        <is>
           <t>Industry Association</t>
         </is>
       </c>
-      <c r="H33" s="60" t="inlineStr">
+      <c r="H35" s="60" t="inlineStr">
         <is>
           <t>Fusion Industry Association</t>
         </is>
       </c>
-      <c r="I33" s="60" t="inlineStr">
+      <c r="I35" s="60" t="inlineStr">
+        <is>
+          <t>FIAが核融合のためのEU資金調達の道筋を示す</t>
+        </is>
+      </c>
+      <c r="J35" s="60" t="inlineStr">
+        <is>
+          <t>核融合産業協会は、商業核融合エネルギーのための実用的なEU資金調達の道筋を示す論文を発表しました。核融合プロジェクトが研究から実証へ移行する際に必要な資金調達手段について論じています。</t>
+        </is>
+      </c>
+      <c r="K35" s="60" t="inlineStr">
+        <is>
+          <t>https://www.fusionindustryassociation.org/fia-outlines-eu-financing-pathway-for-fusion/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=fia-outlines-eu-financing-pathway-for-fusion</t>
+        </is>
+      </c>
+      <c r="L35" s="60" t="inlineStr">
+        <is>
+          <t>88af233d904d670250fa5a31</t>
+        </is>
+      </c>
+      <c r="M35" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T18:56:03+09:00</t>
+        </is>
+      </c>
+      <c r="N35" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O35" s="60" t="inlineStr">
+        <is>
+          <t>枠: Innovation Policy / 政策分野: R&amp;D Funding &amp; Tax Incentives / 学術区分: News &amp; Official Release / 焦点: 商業核融合エネルギーの資金調達</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="42" customHeight="1">
+      <c r="A36" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T21:02:36+09:00</t>
+        </is>
+      </c>
+      <c r="B36" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-21T13:30:36Z</t>
+        </is>
+      </c>
+      <c r="C36" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D36" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E36" s="60" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="F36" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="G36" s="60" t="inlineStr">
+        <is>
+          <t>Policy Institute</t>
+        </is>
+      </c>
+      <c r="H36" s="60" t="inlineStr">
+        <is>
+          <t>CSET</t>
+        </is>
+      </c>
+      <c r="I36" s="60" t="inlineStr">
+        <is>
+          <t>AIシステムはなぜ誤動作するのか？</t>
+        </is>
+      </c>
+      <c r="J36" s="60" t="inlineStr">
+        <is>
+          <t>AIシステムの進化に伴い、その失敗の原因がますます謎となっています。このブログでは、AIの誤動作の原因について掘り下げています。</t>
+        </is>
+      </c>
+      <c r="K36" s="60" t="inlineStr">
+        <is>
+          <t>https://cset.georgetown.edu/article/why-do-ai-systems-misbehave/</t>
+        </is>
+      </c>
+      <c r="L36" s="60" t="inlineStr">
+        <is>
+          <t>3e1aa390ad965782cc86c386</t>
+        </is>
+      </c>
+      <c r="M36" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-21T22:30:36+09:00</t>
+        </is>
+      </c>
+      <c r="N36" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O36" s="60" t="inlineStr">
+        <is>
+          <t>枠: Technology Innovation | Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: AIシステムの誤動作の原因</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="42" customHeight="1">
+      <c r="A37" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T21:02:36+09:00</t>
+        </is>
+      </c>
+      <c r="B37" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-20T21:06:27Z</t>
+        </is>
+      </c>
+      <c r="C37" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D37" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E37" s="60" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="F37" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="G37" s="60" t="inlineStr">
+        <is>
+          <t>Policy Institute</t>
+        </is>
+      </c>
+      <c r="H37" s="60" t="inlineStr">
+        <is>
+          <t>Brookings TechTank</t>
+        </is>
+      </c>
+      <c r="I37" s="60" t="inlineStr">
+        <is>
+          <t>相続を返す：教育と研究政策がAIの借りた専門知識にどう対処できるか</t>
+        </is>
+      </c>
+      <c r="J37" s="60" t="inlineStr">
+        <is>
+          <t>教育と研究政策がAIの専門知識の借用にどのように対処すべきかについて論じられている。</t>
+        </is>
+      </c>
+      <c r="K37" s="60" t="inlineStr">
+        <is>
+          <t>https://brookings.edu/articles/repaying-the-inheritance-how-education-and-research-policy-can-address-ais-borrowed-expertise</t>
+        </is>
+      </c>
+      <c r="L37" s="60" t="inlineStr">
+        <is>
+          <t>42183313e1c951c0483c0d62</t>
+        </is>
+      </c>
+      <c r="M37" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-21T06:06:27+09:00</t>
+        </is>
+      </c>
+      <c r="N37" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O37" s="60" t="inlineStr">
+        <is>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: AIに関する教育政策 / Historical backfill from an allowlisted source.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="42" customHeight="1">
+      <c r="A38" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T21:02:36+09:00</t>
+        </is>
+      </c>
+      <c r="B38" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-20T15:55:00Z</t>
+        </is>
+      </c>
+      <c r="C38" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D38" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E38" s="60" t="inlineStr">
+        <is>
+          <t>Semiconductors &amp; Telecom</t>
+        </is>
+      </c>
+      <c r="F38" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="60" t="inlineStr">
+        <is>
+          <t>Major Media</t>
+        </is>
+      </c>
+      <c r="H38" s="60" t="inlineStr">
+        <is>
+          <t>IEEE Spectrum</t>
+        </is>
+      </c>
+      <c r="I38" s="60" t="inlineStr">
+        <is>
+          <t>先端半導体故障解析のためのSEMガイド低電圧FIB仕上げ</t>
+        </is>
+      </c>
+      <c r="J38" s="60" t="inlineStr">
+        <is>
+          <t>ZEISS Crossbeam 750 FIBSEMが、先端半導体の故障解析において新たな基準を設定する技術を紹介。精密なTEMラメラ準備やトモグラフィーを実現し、データ駆動の意思決定を加速させる。</t>
+        </is>
+      </c>
+      <c r="K38" s="60" t="inlineStr">
+        <is>
+          <t>https://event.on24.com/wcc/r/5418459/287E3D5B99470D34C830D69A24B3B207</t>
+        </is>
+      </c>
+      <c r="L38" s="60" t="inlineStr">
+        <is>
+          <t>73d0028e337a76c2cd00f1bc</t>
+        </is>
+      </c>
+      <c r="M38" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-21T00:55:00+09:00</t>
+        </is>
+      </c>
+      <c r="N38" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O38" s="60" t="inlineStr">
+        <is>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: 半導体故障解析のためのFIB技術</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="42" customHeight="1">
+      <c r="A39" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T18:56:03+09:00</t>
+        </is>
+      </c>
+      <c r="B39" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-17T18:42:47Z</t>
+        </is>
+      </c>
+      <c r="C39" s="60" t="inlineStr">
+        <is>
+          <t>EU &amp; Europe</t>
+        </is>
+      </c>
+      <c r="D39" s="60" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E39" s="60" t="inlineStr">
+        <is>
+          <t>Fusion Energy</t>
+        </is>
+      </c>
+      <c r="F39" s="76" t="n">
+        <v>4</v>
+      </c>
+      <c r="G39" s="60" t="inlineStr">
+        <is>
+          <t>Industry Association</t>
+        </is>
+      </c>
+      <c r="H39" s="60" t="inlineStr">
+        <is>
+          <t>Fusion Industry Association</t>
+        </is>
+      </c>
+      <c r="I39" s="60" t="inlineStr">
+        <is>
+          <t>国際法専門家グループがEUの核融合競争力確保の必要性に関する論文を発表</t>
+        </is>
+      </c>
+      <c r="J39" s="60" t="inlineStr">
+        <is>
+          <t>国際法専門家グループが発表した論文は、EUが商業核融合において競争優位を持っているが、それを維持するためには今すぐ行動が必要であると主張しています。</t>
+        </is>
+      </c>
+      <c r="K39" s="60" t="inlineStr">
+        <is>
+          <t>https://www.fusionindustryassociation.org/international-legal-expert-group-publish-paper-on-the-need-for-the-eu-to-secure-its-competitive-fusion-advantage/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=international-legal-expert-group-publish-paper-on-the-need-for-the-eu-to-secure-its-competitive-fusion-advantage</t>
+        </is>
+      </c>
+      <c r="L39" s="60" t="inlineStr">
+        <is>
+          <t>7ef6110ab078602757409abf</t>
+        </is>
+      </c>
+      <c r="M39" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T18:56:03+09:00</t>
+        </is>
+      </c>
+      <c r="N39" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O39" s="60" t="inlineStr">
+        <is>
+          <t>枠: Innovation Policy / 政策分野: Regulation &amp; Governance / 学術区分: News &amp; Official Release / 焦点: EUの核融合競争力の維持</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="42" customHeight="1">
+      <c r="A40" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T21:02:36+09:00</t>
+        </is>
+      </c>
+      <c r="B40" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-17T15:00:03Z</t>
+        </is>
+      </c>
+      <c r="C40" s="60" t="inlineStr">
+        <is>
+          <t>EU &amp; Europe</t>
+        </is>
+      </c>
+      <c r="D40" s="60" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="E40" s="60" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="F40" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="G40" s="60" t="inlineStr">
+        <is>
+          <t>Government</t>
+        </is>
+      </c>
+      <c r="H40" s="60" t="inlineStr">
+        <is>
+          <t>UK DSIT</t>
+        </is>
+      </c>
+      <c r="I40" s="60" t="inlineStr">
+        <is>
+          <t>ガイダンス：AI研究資源</t>
+        </is>
+      </c>
+      <c r="J40" s="60" t="inlineStr">
+        <is>
+          <t>AI研究資源（AIRR）は、研究者や産業にAI専門の計算能力を提供する先進的なスパコンのスイートである。</t>
+        </is>
+      </c>
+      <c r="K40" s="60" t="inlineStr">
+        <is>
+          <t>https://www.gov.uk/government/publications/ai-research-resource</t>
+        </is>
+      </c>
+      <c r="L40" s="60" t="inlineStr">
+        <is>
+          <t>579a0b7ad2d471608fff5049</t>
+        </is>
+      </c>
+      <c r="M40" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-18T00:00:03+09:00</t>
+        </is>
+      </c>
+      <c r="N40" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O40" s="60" t="inlineStr">
+        <is>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: AI研究資源の提供</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="42" customHeight="1">
+      <c r="A41" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T21:02:36+09:00</t>
+        </is>
+      </c>
+      <c r="B41" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-17T12:00:04Z</t>
+        </is>
+      </c>
+      <c r="C41" s="60" t="inlineStr">
+        <is>
+          <t>EU &amp; Europe</t>
+        </is>
+      </c>
+      <c r="D41" s="60" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="E41" s="60" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="F41" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="G41" s="60" t="inlineStr">
+        <is>
+          <t>Government</t>
+        </is>
+      </c>
+      <c r="H41" s="60" t="inlineStr">
+        <is>
+          <t>UK DSIT</t>
+        </is>
+      </c>
+      <c r="I41" s="60" t="inlineStr">
+        <is>
+          <t>通知：AIRR異種スーパーコンピュータホストサイト選定に関する関心表明</t>
+        </is>
+      </c>
+      <c r="J41" s="60" t="inlineStr">
+        <is>
+          <t>UKの次のAIスパコンのホストサイト選定に関する関心表明が行われた。</t>
+        </is>
+      </c>
+      <c r="K41" s="60" t="inlineStr">
+        <is>
+          <t>https://www.gov.uk/government/publications/expression-of-interest-airr-heterogeneous-supercomputer-host-site-selection</t>
+        </is>
+      </c>
+      <c r="L41" s="60" t="inlineStr">
+        <is>
+          <t>27d607577c2759c8d53f9ddf</t>
+        </is>
+      </c>
+      <c r="M41" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-17T21:00:04+09:00</t>
+        </is>
+      </c>
+      <c r="N41" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O41" s="60" t="inlineStr">
+        <is>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: AIスパコンのホストサイト選定</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="42" customHeight="1">
+      <c r="A42" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T21:02:36+09:00</t>
+        </is>
+      </c>
+      <c r="B42" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-16T14:20:57Z</t>
+        </is>
+      </c>
+      <c r="C42" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D42" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E42" s="60" t="inlineStr"/>
+      <c r="F42" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="G42" s="60" t="inlineStr">
+        <is>
+          <t>Government</t>
+        </is>
+      </c>
+      <c r="H42" s="60" t="inlineStr">
+        <is>
+          <t>DOE Office of Science News</t>
+        </is>
+      </c>
+      <c r="I42" s="60" t="inlineStr">
+        <is>
+          <t>科学を発見する：2027年春の学部インターンシップの応募受付中</t>
+        </is>
+      </c>
+      <c r="J42" s="60" t="inlineStr">
+        <is>
+          <t>学生と新卒者がDOE国立研究所で研究や技術プロジェクトを行うインターンシップの応募が始まった。</t>
+        </is>
+      </c>
+      <c r="K42" s="60" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov/science/articles/discover-science-applications-open-spring-2027-undergraduate-internships</t>
+        </is>
+      </c>
+      <c r="L42" s="60" t="inlineStr">
+        <is>
+          <t>8fc860c00020615caa679423</t>
+        </is>
+      </c>
+      <c r="M42" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-16T23:20:57+09:00</t>
+        </is>
+      </c>
+      <c r="N42" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O42" s="60" t="inlineStr">
+        <is>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: 学生の研究機会</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="42" customHeight="1">
+      <c r="A43" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T21:02:36+09:00</t>
+        </is>
+      </c>
+      <c r="B43" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-16T13:35:15Z</t>
+        </is>
+      </c>
+      <c r="C43" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D43" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E43" s="60" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="F43" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="G43" s="60" t="inlineStr">
+        <is>
+          <t>Government</t>
+        </is>
+      </c>
+      <c r="H43" s="60" t="inlineStr">
+        <is>
+          <t>DOE Office of Science News</t>
+        </is>
+      </c>
+      <c r="I43" s="60" t="inlineStr">
+        <is>
+          <t>ノイズを抑える：DOEが次世代量子情報科学を支える同位体供給チェーンのブレークスルーを発表</t>
+        </is>
+      </c>
+      <c r="J43" s="60" t="inlineStr">
+        <is>
+          <t>DOEが次世代量子情報科学を支えるための重要な同位体供給に関する成果を発表。</t>
+        </is>
+      </c>
+      <c r="K43" s="60" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov/science/articles/silencing-noise-doe-unveils-breakthrough-domestic-silicon-and-germanium-isotope</t>
+        </is>
+      </c>
+      <c r="L43" s="60" t="inlineStr">
+        <is>
+          <t>17ffa424cf814d722a951c64</t>
+        </is>
+      </c>
+      <c r="M43" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-16T22:35:15+09:00</t>
+        </is>
+      </c>
+      <c r="N43" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O43" s="60" t="inlineStr">
+        <is>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: 量子情報科学のための同位体供給</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="42" customHeight="1">
+      <c r="A44" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T18:56:03+09:00</t>
+        </is>
+      </c>
+      <c r="B44" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-15T17:47:57Z</t>
+        </is>
+      </c>
+      <c r="C44" s="60" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D44" s="60" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E44" s="60" t="inlineStr">
+        <is>
+          <t>Fusion Energy</t>
+        </is>
+      </c>
+      <c r="F44" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="G44" s="60" t="inlineStr">
+        <is>
+          <t>Industry Association</t>
+        </is>
+      </c>
+      <c r="H44" s="60" t="inlineStr">
+        <is>
+          <t>Fusion Industry Association</t>
+        </is>
+      </c>
+      <c r="I44" s="60" t="inlineStr">
         <is>
           <t>スターロライトエンジンが60.6億円を調達</t>
         </is>
       </c>
-      <c r="J33" s="60" t="inlineStr">
+      <c r="J44" s="60" t="inlineStr">
         <is>
           <t>スターロライトエンジンは、FASTの開発を加速するために60.6億円を調達しました。この会社は、日本のJT-60SAプログラムや国際的な取り組みを基にしたトカマク型核融合機を開発しています。</t>
         </is>
       </c>
-      <c r="K33" s="60" t="inlineStr">
+      <c r="K44" s="60" t="inlineStr">
         <is>
           <t>https://www.nikkei.com/article/DGXZQOUC152ET0V10C26A7000000/#new_tab?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=starlight-engine-raises-jpy-6-06-billion</t>
         </is>
       </c>
-      <c r="L33" s="60" t="inlineStr">
+      <c r="L44" s="60" t="inlineStr">
         <is>
           <t>2f29b005896c3737ab846738</t>
         </is>
       </c>
-      <c r="M33" s="75" t="inlineStr">
+      <c r="M44" s="75" t="inlineStr">
         <is>
           <t>2026-07-26T18:56:03+09:00</t>
         </is>
       </c>
-      <c r="N33" s="60" t="inlineStr">
+      <c r="N44" s="60" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="O33" s="60" t="inlineStr">
+      <c r="O44" s="60" t="inlineStr">
         <is>
           <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: トカマク型核融合機の開発</t>
         </is>
       </c>
     </row>
+    <row r="45" ht="42" customHeight="1">
+      <c r="A45" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T21:02:36+09:00</t>
+        </is>
+      </c>
+      <c r="B45" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-15T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="C45" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D45" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E45" s="60" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="F45" s="76" t="n">
+        <v>2</v>
+      </c>
+      <c r="G45" s="60" t="inlineStr">
+        <is>
+          <t>Official Company</t>
+        </is>
+      </c>
+      <c r="H45" s="60" t="inlineStr">
+        <is>
+          <t>OpenAI News</t>
+        </is>
+      </c>
+      <c r="I45" s="60" t="inlineStr">
+        <is>
+          <t>米国が州と連邦の行動を通じてAIの安全性を進める</t>
+        </is>
+      </c>
+      <c r="J45" s="60" t="inlineStr">
+        <is>
+          <t>OpenAIは、州法が安全で民主的なAIのための国家的な枠組みを構築する「逆連邦主義」アプローチを概説しています。</t>
+        </is>
+      </c>
+      <c r="K45" s="60" t="inlineStr">
+        <is>
+          <t>https://openai.com/index/advancing-ai-safety-through-state-and-federal-action</t>
+        </is>
+      </c>
+      <c r="L45" s="60" t="inlineStr">
+        <is>
+          <t>23b1197c74335456a9552d5a</t>
+        </is>
+      </c>
+      <c r="M45" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-15T21:00:00+09:00</t>
+        </is>
+      </c>
+      <c r="N45" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O45" s="60" t="inlineStr">
+        <is>
+          <t>枠: Innovation Policy / 政策分野: Regulation &amp; Governance / 学術区分: News &amp; Official Release / 焦点: AIガバナンスの国家フレームワーク</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="42" customHeight="1">
+      <c r="A46" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T21:02:36+09:00</t>
+        </is>
+      </c>
+      <c r="B46" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-14T16:00:08Z</t>
+        </is>
+      </c>
+      <c r="C46" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D46" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E46" s="60" t="inlineStr"/>
+      <c r="F46" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="G46" s="60" t="inlineStr">
+        <is>
+          <t>Government</t>
+        </is>
+      </c>
+      <c r="H46" s="60" t="inlineStr">
+        <is>
+          <t>National Science Foundation News</t>
+        </is>
+      </c>
+      <c r="I46" s="60" t="inlineStr">
+        <is>
+          <t>NSF、全国の研究、雇用、経済成長を促進するために12の新しい地域イノベーションエンジンを授与</t>
+        </is>
+      </c>
+      <c r="J46" s="60" t="inlineStr">
+        <is>
+          <t>米国科学財団が12の地域イノベーションエンジンに助成を行い、イノベーションクラスターの構築と拡大を目指す。</t>
+        </is>
+      </c>
+      <c r="K46" s="60" t="inlineStr">
+        <is>
+          <t>https://www.nsf.gov/news/nsf-awards-12-new-regional-innovation-engines-fuel-research</t>
+        </is>
+      </c>
+      <c r="L46" s="60" t="inlineStr">
+        <is>
+          <t>de4a8c6972dcbf82c2e445b3</t>
+        </is>
+      </c>
+      <c r="M46" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-15T01:00:08+09:00</t>
+        </is>
+      </c>
+      <c r="N46" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O46" s="60" t="inlineStr">
+        <is>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: 地域イノベーションエンジン</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="42" customHeight="1">
+      <c r="A47" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T21:02:36+09:00</t>
+        </is>
+      </c>
+      <c r="B47" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-10T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="C47" s="60" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="D47" s="60" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E47" s="60" t="inlineStr">
+        <is>
+          <t>Fusion Energy</t>
+        </is>
+      </c>
+      <c r="F47" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="60" t="inlineStr">
+        <is>
+          <t>Journal Article</t>
+        </is>
+      </c>
+      <c r="H47" s="60" t="inlineStr">
+        <is>
+          <t>Nuclear Fusion</t>
+        </is>
+      </c>
+      <c r="I47" s="60" t="inlineStr">
+        <is>
+          <t>ST-E1核融合発電プラントのための統合物理と磁石設計</t>
+        </is>
+      </c>
+      <c r="J47" s="60" t="inlineStr">
+        <is>
+          <t>ST-E1核融合発電プラントにおける超伝導材料やトカマクの物理に関する研究が紹介されている。</t>
+        </is>
+      </c>
+      <c r="K47" s="60" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1088/1741-4326/ae773b</t>
+        </is>
+      </c>
+      <c r="L47" s="60" t="inlineStr">
+        <is>
+          <t>a0ed06f7d374240814073762</t>
+        </is>
+      </c>
+      <c r="M47" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-10T09:00:00+09:00</t>
+        </is>
+      </c>
+      <c r="N47" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O47" s="60" t="inlineStr">
+        <is>
+          <t>枠: Technology Innovation / 学術区分: Journal Article / 査読表示: Journal record — confirm peer review on publisher page / 掲載誌・学会: Nuclear Fusion / 焦点: 核融合発電プラントの物理と磁石設計 / OpenAlex record; work type=article; citations=9</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="42" customHeight="1">
+      <c r="A48" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T21:02:36+09:00</t>
+        </is>
+      </c>
+      <c r="B48" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-09T06:09:17Z</t>
+        </is>
+      </c>
+      <c r="C48" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D48" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E48" s="60" t="inlineStr"/>
+      <c r="F48" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="G48" s="60" t="inlineStr">
+        <is>
+          <t>Government</t>
+        </is>
+      </c>
+      <c r="H48" s="60" t="inlineStr">
+        <is>
+          <t>DOE Office of Science News</t>
+        </is>
+      </c>
+      <c r="I48" s="60" t="inlineStr">
+        <is>
+          <t>米エネルギー省、オークリッジ国立研究所で安定同位体生産能力を拡大</t>
+        </is>
+      </c>
+      <c r="J48" s="60" t="inlineStr">
+        <is>
+          <t>米エネルギー省がオークリッジ国立研究所での安定同位体生産能力を再構築し、革新を進めている。</t>
+        </is>
+      </c>
+      <c r="K48" s="60" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov/science/articles/doe-expands-stable-isotope-production-capabilities-oak-ridge-national-laboratory</t>
+        </is>
+      </c>
+      <c r="L48" s="60" t="inlineStr">
+        <is>
+          <t>da263a0637b63a97e7adcb02</t>
+        </is>
+      </c>
+      <c r="M48" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-09T15:09:17+09:00</t>
+        </is>
+      </c>
+      <c r="N48" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O48" s="60" t="inlineStr">
+        <is>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: 安定同位体生産能力</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="42" customHeight="1">
+      <c r="A49" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T21:02:36+09:00</t>
+        </is>
+      </c>
+      <c r="B49" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-07T18:00:07Z</t>
+        </is>
+      </c>
+      <c r="C49" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D49" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E49" s="60" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="F49" s="76" t="n">
+        <v>4</v>
+      </c>
+      <c r="G49" s="60" t="inlineStr">
+        <is>
+          <t>Government</t>
+        </is>
+      </c>
+      <c r="H49" s="60" t="inlineStr">
+        <is>
+          <t>National Science Foundation News</t>
+        </is>
+      </c>
+      <c r="I49" s="60" t="inlineStr">
+        <is>
+          <t>NSFが量子技術を進展させるProject Triadを発表</t>
+        </is>
+      </c>
+      <c r="J49" s="60" t="inlineStr">
+        <is>
+          <t>米国科学財団が量子センシング、ネットワーキング、コンピューティングを統合する新たなプロジェクトを発表した。</t>
+        </is>
+      </c>
+      <c r="K49" s="60" t="inlineStr">
+        <is>
+          <t>https://www.nsf.gov/news/nsf-launches-project-triad-advance-quantum-technology-real</t>
+        </is>
+      </c>
+      <c r="L49" s="60" t="inlineStr">
+        <is>
+          <t>2d4a226d3ce7cc9e366e902d</t>
+        </is>
+      </c>
+      <c r="M49" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-08T03:00:07+09:00</t>
+        </is>
+      </c>
+      <c r="N49" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O49" s="60" t="inlineStr">
+        <is>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: 量子センシング、量子ネットワーキング、量子コンピューティングの統合</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="42" customHeight="1">
+      <c r="A50" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T21:02:36+09:00</t>
+        </is>
+      </c>
+      <c r="B50" s="75" t="inlineStr">
+        <is>
+          <t>2026-06-29T21:14:22Z</t>
+        </is>
+      </c>
+      <c r="C50" s="60" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="D50" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E50" s="60" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="F50" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="60" t="inlineStr">
+        <is>
+          <t>Official Company</t>
+        </is>
+      </c>
+      <c r="H50" s="60" t="inlineStr">
+        <is>
+          <t>Microsoft Research</t>
+        </is>
+      </c>
+      <c r="I50" s="60" t="inlineStr">
+        <is>
+          <t>Memora：抽象性と特異性のバランスを取る調和的メモリ表現</t>
+        </is>
+      </c>
+      <c r="J50" s="60" t="inlineStr">
+        <is>
+          <t>AIエージェントの効率的なメモリシステムに関する新しいアプローチが提案されている。</t>
+        </is>
+      </c>
+      <c r="K50" s="60" t="inlineStr">
+        <is>
+          <t>https://www.microsoft.com/en-us/research/blog/memora-a-harmonic-memory-representation-balancing-abstraction-and-specificity/</t>
+        </is>
+      </c>
+      <c r="L50" s="60" t="inlineStr">
+        <is>
+          <t>6c035ef4d4202a4874e60b97</t>
+        </is>
+      </c>
+      <c r="M50" s="75" t="inlineStr">
+        <is>
+          <t>2026-06-30T06:14:22+09:00</t>
+        </is>
+      </c>
+      <c r="N50" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O50" s="60" t="inlineStr">
+        <is>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: AIエージェントのメモリシステム</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="42" customHeight="1">
+      <c r="A51" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T21:02:36+09:00</t>
+        </is>
+      </c>
+      <c r="B51" s="75" t="inlineStr">
+        <is>
+          <t>2026-06-29T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="C51" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D51" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E51" s="60" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="F51" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="G51" s="60" t="inlineStr">
+        <is>
+          <t>Government</t>
+        </is>
+      </c>
+      <c r="H51" s="60" t="inlineStr">
+        <is>
+          <t>NIST News</t>
+        </is>
+      </c>
+      <c r="I51" s="60" t="inlineStr">
+        <is>
+          <t>NISTが量子技術の製造を推進するセンターを設立</t>
+        </is>
+      </c>
+      <c r="J51" s="60" t="inlineStr">
+        <is>
+          <t>NISTが量子製造工学センターを設立することを発表し、量子技術の製造を推進する。</t>
+        </is>
+      </c>
+      <c r="K51" s="60" t="inlineStr">
+        <is>
+          <t>https://www.nist.gov/news-events/news/2026/06/nist-launches-center-drive-manufacture-quantum-technologies</t>
+        </is>
+      </c>
+      <c r="L51" s="60" t="inlineStr">
+        <is>
+          <t>2d90197d96166b4d1d7f7c11</t>
+        </is>
+      </c>
+      <c r="M51" s="75" t="inlineStr">
+        <is>
+          <t>2026-06-29T21:00:00+09:00</t>
+        </is>
+      </c>
+      <c r="N51" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O51" s="60" t="inlineStr">
+        <is>
+          <t>枠: Innovation Policy / 政策分野: Public Procurement &amp; Industrial Policy / 学術区分: News &amp; Official Release / 焦点: 量子製造技術の推進</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="42" customHeight="1">
+      <c r="A52" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T21:02:36+09:00</t>
+        </is>
+      </c>
+      <c r="B52" s="75" t="inlineStr">
+        <is>
+          <t>2026-06-27T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="C52" s="60" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="D52" s="60" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E52" s="60" t="inlineStr">
+        <is>
+          <t>Biotechnology</t>
+        </is>
+      </c>
+      <c r="F52" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" s="60" t="inlineStr">
+        <is>
+          <t>Preprint</t>
+        </is>
+      </c>
+      <c r="H52" s="60" t="inlineStr">
+        <is>
+          <t>bioRxiv (Cold Spring Harbor Laboratory)</t>
+        </is>
+      </c>
+      <c r="I52" s="60" t="inlineStr">
+        <is>
+          <t>必須および防御遺伝子の共同ターゲティングによるCRISPR-Cas抗微生物剤の相乗効果</t>
+        </is>
+      </c>
+      <c r="J52" s="60" t="inlineStr">
+        <is>
+          <t>CRISPR技術に関する新しい研究成果が示されている。</t>
+        </is>
+      </c>
+      <c r="K52" s="60" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.64898/2026.06.25.734632</t>
+        </is>
+      </c>
+      <c r="L52" s="60" t="inlineStr">
+        <is>
+          <t>6e3725303a7713be5a875629</t>
+        </is>
+      </c>
+      <c r="M52" s="75" t="inlineStr">
+        <is>
+          <t>2026-06-27T09:00:00+09:00</t>
+        </is>
+      </c>
+      <c r="N52" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O52" s="60" t="inlineStr">
+        <is>
+          <t>枠: Technology Innovation / 学術区分: Preprint / 査読表示: Not peer reviewed / 掲載誌・学会: bioRxiv (Cold Spring Harbor Laboratory) / 焦点: CRISPR技術の新しい応用 / OpenAlex record; work type=preprint; citations=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="42" customHeight="1">
+      <c r="A53" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T21:02:36+09:00</t>
+        </is>
+      </c>
+      <c r="B53" s="75" t="inlineStr">
+        <is>
+          <t>2026-06-26T14:45:17Z</t>
+        </is>
+      </c>
+      <c r="C53" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D53" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E53" s="60" t="inlineStr">
+        <is>
+          <t>Robotics</t>
+        </is>
+      </c>
+      <c r="F53" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" s="60" t="inlineStr">
+        <is>
+          <t>Government</t>
+        </is>
+      </c>
+      <c r="H53" s="60" t="inlineStr">
+        <is>
+          <t>National Science Foundation News</t>
+        </is>
+      </c>
+      <c r="I53" s="60" t="inlineStr">
+        <is>
+          <t>ポッドキャスト：脳-コンピュータインターフェースが外骨格を制御</t>
+        </is>
+      </c>
+      <c r="J53" s="60" t="inlineStr">
+        <is>
+          <t>Payam Heydariが脊髄損傷を持つ人々の生活を変える可能性のある脳-コンピュータインターフェースのブレークスルーについて語ります。</t>
+        </is>
+      </c>
+      <c r="K53" s="60" t="inlineStr">
+        <is>
+          <t>https://www.nsf.gov/news/podcast-brain-computer-interface-controls-exoskeleton</t>
+        </is>
+      </c>
+      <c r="L53" s="60" t="inlineStr">
+        <is>
+          <t>37ad9acbe021f897aeaac025</t>
+        </is>
+      </c>
+      <c r="M53" s="75" t="inlineStr">
+        <is>
+          <t>2026-06-26T23:45:17+09:00</t>
+        </is>
+      </c>
+      <c r="N53" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O53" s="60" t="inlineStr">
+        <is>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: 脳-コンピュータインターフェースとロボット外骨格</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="42" customHeight="1">
+      <c r="A54" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T21:02:36+09:00</t>
+        </is>
+      </c>
+      <c r="B54" s="75" t="inlineStr">
+        <is>
+          <t>2026-06-25T05:26:14Z</t>
+        </is>
+      </c>
+      <c r="C54" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D54" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E54" s="60" t="inlineStr"/>
+      <c r="F54" s="76" t="n">
+        <v>4</v>
+      </c>
+      <c r="G54" s="60" t="inlineStr">
+        <is>
+          <t>Government</t>
+        </is>
+      </c>
+      <c r="H54" s="60" t="inlineStr">
+        <is>
+          <t>DOE Office of Science News</t>
+        </is>
+      </c>
+      <c r="I54" s="60" t="inlineStr">
+        <is>
+          <t>エネルギー省がアメリカのエネルギーと製造の国内供給網を強化</t>
+        </is>
+      </c>
+      <c r="J54" s="60" t="inlineStr">
+        <is>
+          <t>エネルギー省は、構造的完全性テストに使用される放射性同位体イリジウム-192の国内生産能力を確立する手助けをしました。</t>
+        </is>
+      </c>
+      <c r="K54" s="60" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov/science/articles/doe-strengthens-domestic-supply-chain-american-energy-and-manufacturing</t>
+        </is>
+      </c>
+      <c r="L54" s="60" t="inlineStr">
+        <is>
+          <t>62854e5795f9fac8f0427e2f</t>
+        </is>
+      </c>
+      <c r="M54" s="75" t="inlineStr">
+        <is>
+          <t>2026-06-25T14:26:14+09:00</t>
+        </is>
+      </c>
+      <c r="N54" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O54" s="60" t="inlineStr">
+        <is>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: イリジウム-192の国内生産能力</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="42" customHeight="1">
+      <c r="A55" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T21:02:36+09:00</t>
+        </is>
+      </c>
+      <c r="B55" s="75" t="inlineStr">
+        <is>
+          <t>2026-06-25T04:00:24Z</t>
+        </is>
+      </c>
+      <c r="C55" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D55" s="60" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="E55" s="60" t="inlineStr"/>
+      <c r="F55" s="76" t="n">
+        <v>4</v>
+      </c>
+      <c r="G55" s="60" t="inlineStr">
+        <is>
+          <t>Government</t>
+        </is>
+      </c>
+      <c r="H55" s="60" t="inlineStr">
+        <is>
+          <t>NISTEP Updates</t>
+        </is>
+      </c>
+      <c r="I55" s="60" t="inlineStr">
+        <is>
+          <t>「STI Horizon（エスティーアイ ホライズン）」誌2026夏号を公表</t>
+        </is>
+      </c>
+      <c r="J55" s="60" t="inlineStr">
+        <is>
+          <t>科学技術・学術政策研究所（NISTEP）が、科学技術・イノベーション政策に関する情報を幅広く掲載したSTI Horizon 2026夏号を公表しました。</t>
+        </is>
+      </c>
+      <c r="K55" s="60" t="inlineStr">
+        <is>
+          <t>https://www.nistep.go.jp/archives/63155/</t>
+        </is>
+      </c>
+      <c r="L55" s="60" t="inlineStr">
+        <is>
+          <t>79d88af79ddda07d59b28e08</t>
+        </is>
+      </c>
+      <c r="M55" s="75" t="inlineStr">
+        <is>
+          <t>2026-06-25T13:00:24+09:00</t>
+        </is>
+      </c>
+      <c r="N55" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O55" s="60" t="inlineStr">
+        <is>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: 科学技術・イノベーション政策に関する情報</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="42" customHeight="1">
+      <c r="A56" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T21:02:36+09:00</t>
+        </is>
+      </c>
+      <c r="B56" s="75" t="inlineStr">
+        <is>
+          <t>2026-06-23T14:26:00Z</t>
+        </is>
+      </c>
+      <c r="C56" s="60" t="inlineStr">
+        <is>
+          <t>EU &amp; Europe</t>
+        </is>
+      </c>
+      <c r="D56" s="60" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="E56" s="60" t="inlineStr">
+        <is>
+          <t>Robotics</t>
+        </is>
+      </c>
+      <c r="F56" s="76" t="n">
+        <v>2</v>
+      </c>
+      <c r="G56" s="60" t="inlineStr">
+        <is>
+          <t>Government</t>
+        </is>
+      </c>
+      <c r="H56" s="60" t="inlineStr">
+        <is>
+          <t>UK DSIT</t>
+        </is>
+      </c>
+      <c r="I56" s="60" t="inlineStr">
+        <is>
+          <t>Sellafieldの清掃を助ける新しいロボット</t>
+        </is>
+      </c>
+      <c r="J56" s="60" t="inlineStr">
+        <is>
+          <t>リモート操作された機械が、Sellafieldの最も危険な核廃棄物保管所に初めて送られました。</t>
+        </is>
+      </c>
+      <c r="K56" s="60" t="inlineStr">
+        <is>
+          <t>https://gov.uk/government/news/the-new-robot-helping-clean-up-sellafield</t>
+        </is>
+      </c>
+      <c r="L56" s="60" t="inlineStr">
+        <is>
+          <t>132391c846d95677d6ca86ff</t>
+        </is>
+      </c>
+      <c r="M56" s="75" t="inlineStr">
+        <is>
+          <t>2026-06-23T23:26:00+09:00</t>
+        </is>
+      </c>
+      <c r="N56" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O56" s="60" t="inlineStr">
+        <is>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: 危険な核廃棄物の清掃に使用されるロボット / Historical backfill from an allowlisted source.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="42" customHeight="1">
+      <c r="A57" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T21:02:36+09:00</t>
+        </is>
+      </c>
+      <c r="B57" s="75" t="inlineStr">
+        <is>
+          <t>2026-06-22T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="C57" s="60" t="inlineStr">
+        <is>
+          <t>EU &amp; Europe</t>
+        </is>
+      </c>
+      <c r="D57" s="60" t="inlineStr">
+        <is>
+          <t>International / France</t>
+        </is>
+      </c>
+      <c r="E57" s="60" t="inlineStr">
+        <is>
+          <t>Fusion Energy</t>
+        </is>
+      </c>
+      <c r="F57" s="76" t="n">
+        <v>2</v>
+      </c>
+      <c r="G57" s="60" t="inlineStr">
+        <is>
+          <t>Intergovernmental</t>
+        </is>
+      </c>
+      <c r="H57" s="60" t="inlineStr">
+        <is>
+          <t>ITER News</t>
+        </is>
+      </c>
+      <c r="I57" s="60" t="inlineStr">
+        <is>
+          <t>溶接技術の向上を目指す核融合知識の構築</t>
+        </is>
+      </c>
+      <c r="J57" s="60" t="inlineStr">
+        <is>
+          <t>ITERの溶接技術者が、初のコンポーネントのための溶接手順を開発し、トカマクの狭い空間での溶接戦略を考案しています。</t>
+        </is>
+      </c>
+      <c r="K57" s="60" t="inlineStr">
+        <is>
+          <t>https://www.iter.org/node/20687/building-fusion-knowledge-one-weld-time</t>
+        </is>
+      </c>
+      <c r="L57" s="60" t="inlineStr">
+        <is>
+          <t>a918d75ead8fb4248ac7e87a</t>
+        </is>
+      </c>
+      <c r="M57" s="75" t="inlineStr">
+        <is>
+          <t>2026-06-22T09:00:00+09:00</t>
+        </is>
+      </c>
+      <c r="N57" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O57" s="60" t="inlineStr">
+        <is>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: 核融合コンポーネントの溶接手法</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="42" customHeight="1">
+      <c r="A58" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T21:02:36+09:00</t>
+        </is>
+      </c>
+      <c r="B58" s="75" t="inlineStr">
+        <is>
+          <t>2026-06-15T15:23:31Z</t>
+        </is>
+      </c>
+      <c r="C58" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D58" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E58" s="60" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="F58" s="76" t="n">
+        <v>4</v>
+      </c>
+      <c r="G58" s="60" t="inlineStr">
+        <is>
+          <t>Government</t>
+        </is>
+      </c>
+      <c r="H58" s="60" t="inlineStr">
+        <is>
+          <t>NIH News Releases</t>
+        </is>
+      </c>
+      <c r="I58" s="60" t="inlineStr">
+        <is>
+          <t>研究影響を高めるための再現性向上イニシアティブ</t>
+        </is>
+      </c>
+      <c r="J58" s="60" t="inlineStr">
+        <is>
+          <t>新しい生物医学研究が人間の健康理解を進め、病気治療の新たな方法を提供する中、独立した再現が研究者にとって重要であることを強調したイニシアティブ。</t>
+        </is>
+      </c>
+      <c r="K58" s="60" t="inlineStr">
+        <is>
+          <t>https://nih.gov/common-fund/common-fund-programs/replication-enhance-research-impact-initiative</t>
+        </is>
+      </c>
+      <c r="L58" s="60" t="inlineStr">
+        <is>
+          <t>1b5e51bc8d4c51589eee5027</t>
+        </is>
+      </c>
+      <c r="M58" s="75" t="inlineStr">
+        <is>
+          <t>2026-06-16T00:23:31+09:00</t>
+        </is>
+      </c>
+      <c r="N58" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O58" s="60" t="inlineStr">
+        <is>
+          <t>枠: Innovation Policy / 政策分野: Patents &amp; Intellectual Property / 学術区分: News &amp; Official Release / 焦点: 医療研究の再現性向上 / Historical backfill from an allowlisted source.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="42" customHeight="1">
+      <c r="A59" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T21:02:36+09:00</t>
+        </is>
+      </c>
+      <c r="B59" s="75" t="inlineStr">
+        <is>
+          <t>2026-06-15T05:00:30Z</t>
+        </is>
+      </c>
+      <c r="C59" s="60" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D59" s="60" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="E59" s="60" t="inlineStr"/>
+      <c r="F59" s="76" t="n">
+        <v>4</v>
+      </c>
+      <c r="G59" s="60" t="inlineStr">
+        <is>
+          <t>Government</t>
+        </is>
+      </c>
+      <c r="H59" s="60" t="inlineStr">
+        <is>
+          <t>NISTEP Updates</t>
+        </is>
+      </c>
+      <c r="I59" s="60" t="inlineStr">
+        <is>
+          <t>日本の大学における研究活動の構造変化</t>
+        </is>
+      </c>
+      <c r="J59" s="60" t="inlineStr">
+        <is>
+          <t>日本の大学における研究活動の変化を分析し、外部資金の活用が研究の活性化に寄与していることを示した調査研究。</t>
+        </is>
+      </c>
+      <c r="K59" s="60" t="inlineStr">
+        <is>
+          <t>https://www.nistep.go.jp/archives/63067/</t>
+        </is>
+      </c>
+      <c r="L59" s="60" t="inlineStr">
+        <is>
+          <t>aff9dcbd77c489cb20aa6fdd</t>
+        </is>
+      </c>
+      <c r="M59" s="75" t="inlineStr">
+        <is>
+          <t>2026-06-15T14:00:30+09:00</t>
+        </is>
+      </c>
+      <c r="N59" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O59" s="60" t="inlineStr">
+        <is>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: 大学の研究活動の構造変化</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="42" customHeight="1">
+      <c r="A60" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T21:02:36+09:00</t>
+        </is>
+      </c>
+      <c r="B60" s="75" t="inlineStr">
+        <is>
+          <t>2026-06-15T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="C60" s="60" t="inlineStr">
+        <is>
+          <t>EU &amp; Europe</t>
+        </is>
+      </c>
+      <c r="D60" s="60" t="inlineStr">
+        <is>
+          <t>International / France</t>
+        </is>
+      </c>
+      <c r="E60" s="60" t="inlineStr">
+        <is>
+          <t>Fusion Energy</t>
+        </is>
+      </c>
+      <c r="F60" s="76" t="n">
+        <v>2</v>
+      </c>
+      <c r="G60" s="60" t="inlineStr">
+        <is>
+          <t>Intergovernmental</t>
+        </is>
+      </c>
+      <c r="H60" s="60" t="inlineStr">
+        <is>
+          <t>ITER News</t>
+        </is>
+      </c>
+      <c r="I60" s="60" t="inlineStr">
+        <is>
+          <t>世界中から一つのアセンブリラインへ</t>
+        </is>
+      </c>
+      <c r="J60" s="60" t="inlineStr">
+        <is>
+          <t>ITERのダイバータが新たな統合段階に入り、設計と製造の数十年にわたる努力が実を結んでいる。</t>
+        </is>
+      </c>
+      <c r="K60" s="60" t="inlineStr">
+        <is>
+          <t>https://www.iter.org/node/20687/around-world-one-assembly-line</t>
+        </is>
+      </c>
+      <c r="L60" s="60" t="inlineStr">
+        <is>
+          <t>ac71361e131ee1a80ac51837</t>
+        </is>
+      </c>
+      <c r="M60" s="75" t="inlineStr">
+        <is>
+          <t>2026-06-15T09:00:00+09:00</t>
+        </is>
+      </c>
+      <c r="N60" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O60" s="60" t="inlineStr">
+        <is>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: ITERのダイバータの統合</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="42" customHeight="1">
+      <c r="A61" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T21:02:36+09:00</t>
+        </is>
+      </c>
+      <c r="B61" s="75" t="inlineStr">
+        <is>
+          <t>2026-06-15T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="C61" s="60" t="inlineStr">
+        <is>
+          <t>EU &amp; Europe</t>
+        </is>
+      </c>
+      <c r="D61" s="60" t="inlineStr">
+        <is>
+          <t>International / France</t>
+        </is>
+      </c>
+      <c r="E61" s="60" t="inlineStr">
+        <is>
+          <t>Fusion Energy</t>
+        </is>
+      </c>
+      <c r="F61" s="76" t="n">
+        <v>2</v>
+      </c>
+      <c r="G61" s="60" t="inlineStr">
+        <is>
+          <t>Intergovernmental</t>
+        </is>
+      </c>
+      <c r="H61" s="60" t="inlineStr">
+        <is>
+          <t>ITER News</t>
+        </is>
+      </c>
+      <c r="I61" s="60" t="inlineStr">
+        <is>
+          <t>馬の年に先を行く</t>
+        </is>
+      </c>
+      <c r="J61" s="60" t="inlineStr">
+        <is>
+          <t>ITERにおける真空容器の組立が予定よりも早く進行中で、経験と調整の利点が示されている。</t>
+        </is>
+      </c>
+      <c r="K61" s="60" t="inlineStr">
+        <is>
+          <t>https://www.iter.org/node/20687/galloping-ahead-year-horse</t>
+        </is>
+      </c>
+      <c r="L61" s="60" t="inlineStr">
+        <is>
+          <t>47f993ca6a92c4175db656f6</t>
+        </is>
+      </c>
+      <c r="M61" s="75" t="inlineStr">
+        <is>
+          <t>2026-06-15T09:00:00+09:00</t>
+        </is>
+      </c>
+      <c r="N61" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O61" s="60" t="inlineStr">
+        <is>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: ITERの真空容器の組立</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="42" customHeight="1">
+      <c r="A62" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T21:02:36+09:00</t>
+        </is>
+      </c>
+      <c r="B62" s="75" t="inlineStr">
+        <is>
+          <t>2026-06-15T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="C62" s="60" t="inlineStr">
+        <is>
+          <t>EU &amp; Europe</t>
+        </is>
+      </c>
+      <c r="D62" s="60" t="inlineStr">
+        <is>
+          <t>International / France</t>
+        </is>
+      </c>
+      <c r="E62" s="60" t="inlineStr">
+        <is>
+          <t>Fusion Energy</t>
+        </is>
+      </c>
+      <c r="F62" s="76" t="n">
+        <v>2</v>
+      </c>
+      <c r="G62" s="60" t="inlineStr">
+        <is>
+          <t>Intergovernmental</t>
+        </is>
+      </c>
+      <c r="H62" s="60" t="inlineStr">
+        <is>
+          <t>ITER News</t>
+        </is>
+      </c>
+      <c r="I62" s="60" t="inlineStr">
+        <is>
+          <t>ロシアのクルチャトフ研究所との協定を締結</t>
+        </is>
+      </c>
+      <c r="J62" s="60" t="inlineStr">
+        <is>
+          <t>ITERがロシアのクルチャトフ研究所との間で科学的交流と共同研究プログラムの実施に関する協定を締結。</t>
+        </is>
+      </c>
+      <c r="K62" s="60" t="inlineStr">
+        <is>
+          <t>https://www.iter.org/node/20687/iter-signs-agreement-russias-kurchatov-institute</t>
+        </is>
+      </c>
+      <c r="L62" s="60" t="inlineStr">
+        <is>
+          <t>bef2ae98b3b6e9a710e28c9f</t>
+        </is>
+      </c>
+      <c r="M62" s="75" t="inlineStr">
+        <is>
+          <t>2026-06-15T09:00:00+09:00</t>
+        </is>
+      </c>
+      <c r="N62" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O62" s="60" t="inlineStr">
+        <is>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: ロシアのクルチャトフ研究所との協定</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="42" customHeight="1">
+      <c r="A63" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T21:02:36+09:00</t>
+        </is>
+      </c>
+      <c r="B63" s="75" t="inlineStr">
+        <is>
+          <t>2026-06-11T17:39:29Z</t>
+        </is>
+      </c>
+      <c r="C63" s="60" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="D63" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E63" s="60" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="F63" s="76" t="n">
+        <v>2</v>
+      </c>
+      <c r="G63" s="60" t="inlineStr">
+        <is>
+          <t>Official Company</t>
+        </is>
+      </c>
+      <c r="H63" s="60" t="inlineStr">
+        <is>
+          <t>OpenAI News</t>
+        </is>
+      </c>
+      <c r="I63" s="60" t="inlineStr">
+        <is>
+          <t>特許に関する私たちのアプローチ</t>
+        </is>
+      </c>
+      <c r="J63" s="60" t="inlineStr">
+        <is>
+          <t>OpenAIは、AIに関する特許の広範なアクセス、協力、安全性の原則を重視している。</t>
+        </is>
+      </c>
+      <c r="K63" s="60" t="inlineStr">
+        <is>
+          <t>https://openai.com/approach-to-patents</t>
+        </is>
+      </c>
+      <c r="L63" s="60" t="inlineStr">
+        <is>
+          <t>15bd5956a07021e966ca1264</t>
+        </is>
+      </c>
+      <c r="M63" s="75" t="inlineStr">
+        <is>
+          <t>2026-06-12T02:39:29+09:00</t>
+        </is>
+      </c>
+      <c r="N63" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O63" s="60" t="inlineStr">
+        <is>
+          <t>枠: Innovation Policy / 政策分野: Patents &amp; Intellectual Property / 学術区分: News &amp; Official Release / 焦点: AIに関する特許の方針 / Historical backfill from an allowlisted source.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="42" customHeight="1">
+      <c r="A64" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T21:02:36+09:00</t>
+        </is>
+      </c>
+      <c r="B64" s="75" t="inlineStr">
+        <is>
+          <t>2026-06-09T19:00:00Z</t>
+        </is>
+      </c>
+      <c r="C64" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D64" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E64" s="60" t="inlineStr">
+        <is>
+          <t>Fusion Energy</t>
+        </is>
+      </c>
+      <c r="F64" s="76" t="n">
+        <v>5</v>
+      </c>
+      <c r="G64" s="60" t="inlineStr">
+        <is>
+          <t>Government</t>
+        </is>
+      </c>
+      <c r="H64" s="60" t="inlineStr">
+        <is>
+          <t>DOE Office of Science News</t>
+        </is>
+      </c>
+      <c r="I64" s="60" t="inlineStr">
+        <is>
+          <t>エネルギー省が商業核融合電力を加速するための最終化されたロードマップを発表</t>
+        </is>
+      </c>
+      <c r="J64" s="60" t="inlineStr">
+        <is>
+          <t>米国エネルギー省が核融合エネルギーの開発と商業化を加速するための国家戦略を発表した。</t>
+        </is>
+      </c>
+      <c r="K64" s="60" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov/articles/energy-department-releases-finalized-fusion-science-and-technology-roadmap-accelerate</t>
+        </is>
+      </c>
+      <c r="L64" s="60" t="inlineStr">
+        <is>
+          <t>bf24d6f8eb27dabbbe4e196e</t>
+        </is>
+      </c>
+      <c r="M64" s="75" t="inlineStr">
+        <is>
+          <t>2026-06-10T04:00:00+09:00</t>
+        </is>
+      </c>
+      <c r="N64" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O64" s="60" t="inlineStr">
+        <is>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy | Patents &amp; Intellectual Property / 学術区分: News &amp; Official Release / 焦点: 核融合エネルギーの商業化に向けた戦略</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="42" customHeight="1">
+      <c r="A65" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T21:02:36+09:00</t>
+        </is>
+      </c>
+      <c r="B65" s="75" t="inlineStr">
+        <is>
+          <t>2026-06-09T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="C65" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D65" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E65" s="60" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="F65" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="G65" s="60" t="inlineStr">
+        <is>
+          <t>Government</t>
+        </is>
+      </c>
+      <c r="H65" s="60" t="inlineStr">
+        <is>
+          <t>NIST News</t>
+        </is>
+      </c>
+      <c r="I65" s="60" t="inlineStr">
+        <is>
+          <t>NISTの数学的証明がAIシステムのセキュリティモデルへの移行を支持</t>
+        </is>
+      </c>
+      <c r="J65" s="60" t="inlineStr">
+        <is>
+          <t>NISTがAIシステムのための新しいセキュリティモデルに関する数学的証明を発表した。</t>
+        </is>
+      </c>
+      <c r="K65" s="60" t="inlineStr">
+        <is>
+          <t>https://www.nist.gov/news-events/news/2026/06/nist-mathematical-proof-supports-transition-continuous-monitor-and-update</t>
+        </is>
+      </c>
+      <c r="L65" s="60" t="inlineStr">
+        <is>
+          <t>edf1c2446b6ba41114d4bc6b</t>
+        </is>
+      </c>
+      <c r="M65" s="75" t="inlineStr">
+        <is>
+          <t>2026-06-09T21:00:00+09:00</t>
+        </is>
+      </c>
+      <c r="N65" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O65" s="60" t="inlineStr">
+        <is>
+          <t>枠: Innovation Policy / 政策分野: Public Procurement &amp; Industrial Policy / 学術区分: News &amp; Official Release / 焦点: AIシステムのセキュリティモデル</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="42" customHeight="1">
+      <c r="A66" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T21:02:36+09:00</t>
+        </is>
+      </c>
+      <c r="B66" s="75" t="inlineStr">
+        <is>
+          <t>2026-06-08T13:36:33Z</t>
+        </is>
+      </c>
+      <c r="C66" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D66" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E66" s="60" t="inlineStr"/>
+      <c r="F66" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="G66" s="60" t="inlineStr">
+        <is>
+          <t>Government</t>
+        </is>
+      </c>
+      <c r="H66" s="60" t="inlineStr">
+        <is>
+          <t>DOE Office of Science News</t>
+        </is>
+      </c>
+      <c r="I66" s="60" t="inlineStr">
+        <is>
+          <t>研究ニュースアップデート：2026年6月8日</t>
+        </is>
+      </c>
+      <c r="J66" s="60" t="inlineStr">
+        <is>
+          <t>米国エネルギー省が量子技術に関する国家戦略を発表した。</t>
+        </is>
+      </c>
+      <c r="K66" s="60" t="inlineStr">
+        <is>
+          <t>https://content.govdelivery.com/accounts/USDOEOS/bulletins/41affd7</t>
+        </is>
+      </c>
+      <c r="L66" s="60" t="inlineStr">
+        <is>
+          <t>a9f82cc8c9f6fc70090055af</t>
+        </is>
+      </c>
+      <c r="M66" s="75" t="inlineStr">
+        <is>
+          <t>2026-06-08T22:36:33+09:00</t>
+        </is>
+      </c>
+      <c r="N66" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O66" s="60" t="inlineStr">
+        <is>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: 量子技術に関する国家戦略</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="42" customHeight="1">
+      <c r="A67" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T21:02:36+09:00</t>
+        </is>
+      </c>
+      <c r="B67" s="75" t="inlineStr">
+        <is>
+          <t>2026-06-08T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="C67" s="60" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="D67" s="60" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E67" s="60" t="inlineStr">
+        <is>
+          <t>Space</t>
+        </is>
+      </c>
+      <c r="F67" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" s="60" t="inlineStr">
+        <is>
+          <t>Conference Paper</t>
+        </is>
+      </c>
+      <c r="H67" s="60" t="inlineStr">
+        <is>
+          <t>Proceedings of the International Conference on Automated Planning and Scheduling</t>
+        </is>
+      </c>
+      <c r="I67" s="60" t="inlineStr">
+        <is>
+          <t>NASAのキャルサーズ地球コロナ観測ミッションのための長期運用スケジューリングに関する深層強化学習</t>
+        </is>
+      </c>
+      <c r="J67" s="60" t="inlineStr">
+        <is>
+          <t>NASAの観測ミッションにおける長期運用スケジューリングに関する深層強化学習の研究が発表された。</t>
+        </is>
+      </c>
+      <c r="K67" s="60" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1609/icaps.v36i1.42871</t>
+        </is>
+      </c>
+      <c r="L67" s="60" t="inlineStr">
+        <is>
+          <t>c180becba22f98a3320c630d</t>
+        </is>
+      </c>
+      <c r="M67" s="75" t="inlineStr">
+        <is>
+          <t>2026-06-08T09:00:00+09:00</t>
+        </is>
+      </c>
+      <c r="N67" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O67" s="60" t="inlineStr">
+        <is>
+          <t>枠: Technology Innovation / 学術区分: Conference Paper / 査読表示: Conference proceedings — review status varies / 掲載誌・学会: Proceedings of the International Conference on Automated Planning and Scheduling / 焦点: 宇宙船のダイナミクスと制御、強化学習 / OpenAlex record; work type=conference-paper; citations=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="42" customHeight="1">
+      <c r="A68" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T21:02:36+09:00</t>
+        </is>
+      </c>
+      <c r="B68" s="75" t="inlineStr">
+        <is>
+          <t>2026-06-05T12:28:26Z</t>
+        </is>
+      </c>
+      <c r="C68" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D68" s="60" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E68" s="60" t="inlineStr"/>
+      <c r="F68" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="G68" s="60" t="inlineStr">
+        <is>
+          <t>Intergovernmental</t>
+        </is>
+      </c>
+      <c r="H68" s="60" t="inlineStr">
+        <is>
+          <t>WHO News</t>
+        </is>
+      </c>
+      <c r="I68" s="60" t="inlineStr">
+        <is>
+          <t>アフリカCDCとWHOが共同で大陸的エボラ対応計画を発表</t>
+        </is>
+      </c>
+      <c r="J68" s="60" t="inlineStr">
+        <is>
+          <t>アフリカCDCとWHOがエボラ出血熱の対応計画を発表し、518百万ドルの資金を調達することを目指している。</t>
+        </is>
+      </c>
+      <c r="K68" s="60" t="inlineStr">
+        <is>
+          <t>https://www.who.int/news/item/05-06-2026-africa-cdc-and-who-launch-joint-continental-ebola-response-plan</t>
+        </is>
+      </c>
+      <c r="L68" s="60" t="inlineStr">
+        <is>
+          <t>41c465a6eca3591002d781ba</t>
+        </is>
+      </c>
+      <c r="M68" s="75" t="inlineStr">
+        <is>
+          <t>2026-06-05T21:28:26+09:00</t>
+        </is>
+      </c>
+      <c r="N68" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O68" s="60" t="inlineStr">
+        <is>
+          <t>枠: Innovation Policy / 政策分野: Public Procurement &amp; Industrial Policy / 学術区分: News &amp; Official Release / 焦点: エボラ出血熱に対する準備と対応計画</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="42" customHeight="1">
+      <c r="A69" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T21:02:36+09:00</t>
+        </is>
+      </c>
+      <c r="B69" s="75" t="inlineStr">
+        <is>
+          <t>2026-06-04T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="C69" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D69" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E69" s="60" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="F69" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="G69" s="60" t="inlineStr">
+        <is>
+          <t>Government</t>
+        </is>
+      </c>
+      <c r="H69" s="60" t="inlineStr">
+        <is>
+          <t>NIST News</t>
+        </is>
+      </c>
+      <c r="I69" s="60" t="inlineStr">
+        <is>
+          <t>新しいAIモデルが火災時の安全な避難経路を特定</t>
+        </is>
+      </c>
+      <c r="J69" s="60" t="inlineStr">
+        <is>
+          <t>NIST主導のチームが、火災時に安全な避難経路を特定する新しいAIモデルを作成した。</t>
+        </is>
+      </c>
+      <c r="K69" s="60" t="inlineStr">
+        <is>
+          <t>https://www.nist.gov/news-events/news/2026/06/new-ai-model-shows-how-evacuate-fires-one-safe-step-time</t>
+        </is>
+      </c>
+      <c r="L69" s="60" t="inlineStr">
+        <is>
+          <t>434bb62e0a1e48aca17e1405</t>
+        </is>
+      </c>
+      <c r="M69" s="75" t="inlineStr">
+        <is>
+          <t>2026-06-04T21:00:00+09:00</t>
+        </is>
+      </c>
+      <c r="N69" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O69" s="60" t="inlineStr">
+        <is>
+          <t>枠: Innovation Policy / 政策分野: Public Procurement &amp; Industrial Policy / 学術区分: News &amp; Official Release / 焦点: 火災時の安全な避難経路の特定</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="42" customHeight="1">
+      <c r="A70" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T21:02:36+09:00</t>
+        </is>
+      </c>
+      <c r="B70" s="75" t="inlineStr">
+        <is>
+          <t>2026-06-04T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="C70" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D70" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E70" s="60" t="inlineStr"/>
+      <c r="F70" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="G70" s="60" t="inlineStr">
+        <is>
+          <t>Government</t>
+        </is>
+      </c>
+      <c r="H70" s="60" t="inlineStr">
+        <is>
+          <t>NIST News</t>
+        </is>
+      </c>
+      <c r="I70" s="60" t="inlineStr">
+        <is>
+          <t>NIST研究者がレーザーを用いた合金の結合方法を発見</t>
+        </is>
+      </c>
+      <c r="J70" s="60" t="inlineStr">
+        <is>
+          <t>NISTが3Dプリンティング中の金属の原子構造をリアルタイムで研究する方法を改善した。</t>
+        </is>
+      </c>
+      <c r="K70" s="60" t="inlineStr">
+        <is>
+          <t>https://www.nist.gov/news-events/news/2026/06/nist-researchers-discover-new-way-whisk-alloys-together-lasers</t>
+        </is>
+      </c>
+      <c r="L70" s="60" t="inlineStr">
+        <is>
+          <t>a03605c38ac072e4b77247db</t>
+        </is>
+      </c>
+      <c r="M70" s="75" t="inlineStr">
+        <is>
+          <t>2026-06-04T21:00:00+09:00</t>
+        </is>
+      </c>
+      <c r="N70" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O70" s="60" t="inlineStr">
+        <is>
+          <t>枠: Innovation Policy / 政策分野: Public Procurement &amp; Industrial Policy / 学術区分: News &amp; Official Release / 焦点: レーザーを用いた合金の結合方法</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="42" customHeight="1">
+      <c r="A71" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T21:02:36+09:00</t>
+        </is>
+      </c>
+      <c r="B71" s="75" t="inlineStr">
+        <is>
+          <t>2026-06-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="C71" s="60" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="D71" s="60" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E71" s="60" t="inlineStr">
+        <is>
+          <t>Space</t>
+        </is>
+      </c>
+      <c r="F71" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" s="60" t="inlineStr">
+        <is>
+          <t>Conference Paper</t>
+        </is>
+      </c>
+      <c r="H71" s="60" t="inlineStr">
+        <is>
+          <t>Journal of Physics Conference Series</t>
+        </is>
+      </c>
+      <c r="I71" s="60" t="inlineStr">
+        <is>
+          <t>異なる操縦条件下における四タンクシステムの液体スロッシング特性の分析</t>
+        </is>
+      </c>
+      <c r="J71" s="60" t="inlineStr">
+        <is>
+          <t>異なる操縦条件下での四タンクシステムにおける液体スロッシング特性を分析した研究。</t>
+        </is>
+      </c>
+      <c r="K71" s="60" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1088/1742-6596/3256/1/012058</t>
+        </is>
+      </c>
+      <c r="L71" s="60" t="inlineStr">
+        <is>
+          <t>f1249e075d80a29b98de0c87</t>
+        </is>
+      </c>
+      <c r="M71" s="75" t="inlineStr">
+        <is>
+          <t>2026-06-01T09:00:00+09:00</t>
+        </is>
+      </c>
+      <c r="N71" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O71" s="60" t="inlineStr">
+        <is>
+          <t>枠: Technology Innovation / 学術区分: Conference Paper / 査読表示: Conference proceedings — review status varies / 掲載誌・学会: Journal of Physics Conference Series / 焦点: 液体スロッシング特性 / OpenAlex record; work type=conference-paper; citations=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="42" customHeight="1">
+      <c r="A72" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T21:02:36+09:00</t>
+        </is>
+      </c>
+      <c r="B72" s="75" t="inlineStr">
+        <is>
+          <t>2026-05-20T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="C72" s="60" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="D72" s="60" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E72" s="60" t="inlineStr">
+        <is>
+          <t>Biotechnology</t>
+        </is>
+      </c>
+      <c r="F72" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" s="60" t="inlineStr">
+        <is>
+          <t>Conference Paper</t>
+        </is>
+      </c>
+      <c r="H72" s="60" t="inlineStr">
+        <is>
+          <t>Exploring Science Academic Conference Series</t>
+        </is>
+      </c>
+      <c r="I72" s="60" t="inlineStr">
+        <is>
+          <t>ベンチからベッドサイドへ：CRISPR遺伝子編集の多次元臨床応用と課題</t>
+        </is>
+      </c>
+      <c r="J72" s="60" t="inlineStr">
+        <is>
+          <t>CRISPR遺伝子編集技術の臨床応用とその課題についての研究が報告されている。</t>
+        </is>
+      </c>
+      <c r="K72" s="60" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.70267/shbe.20262633</t>
+        </is>
+      </c>
+      <c r="L72" s="60" t="inlineStr">
+        <is>
+          <t>f3ffddf94d57c4580e4df687</t>
+        </is>
+      </c>
+      <c r="M72" s="75" t="inlineStr">
+        <is>
+          <t>2026-05-20T09:00:00+09:00</t>
+        </is>
+      </c>
+      <c r="N72" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O72" s="60" t="inlineStr">
+        <is>
+          <t>枠: Technology Innovation / 学術区分: Conference Paper / 査読表示: Conference proceedings — review status varies / 掲載誌・学会: Exploring Science Academic Conference Series / 焦点: CRISPR遺伝子編集技術 / OpenAlex record; work type=conference-paper; citations=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="42" customHeight="1">
+      <c r="A73" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T21:02:36+09:00</t>
+        </is>
+      </c>
+      <c r="B73" s="75" t="inlineStr">
+        <is>
+          <t>2026-05-18T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="C73" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D73" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E73" s="60" t="inlineStr">
+        <is>
+          <t>Space</t>
+        </is>
+      </c>
+      <c r="F73" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="G73" s="60" t="inlineStr">
+        <is>
+          <t>Government</t>
+        </is>
+      </c>
+      <c r="H73" s="60" t="inlineStr">
+        <is>
+          <t>NIST News</t>
+        </is>
+      </c>
+      <c r="I73" s="60" t="inlineStr">
+        <is>
+          <t>月を目指す：暗いクレーターにおける超安定レーザーが月面ナビゲーション、精密時間計測、新しい科学を可能にする</t>
+        </is>
+      </c>
+      <c r="J73" s="60" t="inlineStr">
+        <is>
+          <t>月面の暗いクレーターにおいて、最も安定した光学レーザーを構築する可能性についての研究が報告されている。</t>
+        </is>
+      </c>
+      <c r="K73" s="60" t="inlineStr">
+        <is>
+          <t>https://www.nist.gov/news-events/news/2026/05/shooting-moon-ultrastable-lasers-dark-craters-could-enable-lunar-navigation</t>
+        </is>
+      </c>
+      <c r="L73" s="60" t="inlineStr">
+        <is>
+          <t>99f664278415a42538163a5c</t>
+        </is>
+      </c>
+      <c r="M73" s="75" t="inlineStr">
+        <is>
+          <t>2026-05-18T21:00:00+09:00</t>
+        </is>
+      </c>
+      <c r="N73" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O73" s="60" t="inlineStr">
+        <is>
+          <t>枠: Innovation Policy / 政策分野: Public Procurement &amp; Industrial Policy / 学術区分: News &amp; Official Release / 焦点: 月面での超安定レーザー技術</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="42" customHeight="1">
+      <c r="A74" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T21:02:36+09:00</t>
+        </is>
+      </c>
+      <c r="B74" s="75" t="inlineStr">
+        <is>
+          <t>2026-04-20T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="C74" s="60" t="inlineStr">
+        <is>
+          <t>EU &amp; Europe</t>
+        </is>
+      </c>
+      <c r="D74" s="60" t="inlineStr">
+        <is>
+          <t>International / France</t>
+        </is>
+      </c>
+      <c r="E74" s="60" t="inlineStr">
+        <is>
+          <t>Fusion Energy</t>
+        </is>
+      </c>
+      <c r="F74" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="G74" s="60" t="inlineStr">
+        <is>
+          <t>Intergovernmental</t>
+        </is>
+      </c>
+      <c r="H74" s="60" t="inlineStr">
+        <is>
+          <t>ITER News</t>
+        </is>
+      </c>
+      <c r="I74" s="60" t="inlineStr">
+        <is>
+          <t>ITER容器に関する重要な判決が核融合の規制アプローチを強化</t>
+        </is>
+      </c>
+      <c r="J74" s="60" t="inlineStr">
+        <is>
+          <t>フランスの原子力安全局がITERの真空容器を圧力機器規則から除外することを承認し、核融合デバイスに特化した規制枠組みの重要な一歩となりました。</t>
+        </is>
+      </c>
+      <c r="K74" s="60" t="inlineStr">
+        <is>
+          <t>https://iter.org/actualites-iter/key-ruling-iter-vessel-strengthens-fit-purpose-fusion-regulatory-approach</t>
+        </is>
+      </c>
+      <c r="L74" s="60" t="inlineStr">
+        <is>
+          <t>4783b0d9acc14b70e803cc06</t>
+        </is>
+      </c>
+      <c r="M74" s="75" t="inlineStr">
+        <is>
+          <t>2026-04-20T09:00:00+09:00</t>
+        </is>
+      </c>
+      <c r="N74" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O74" s="60" t="inlineStr">
+        <is>
+          <t>枠: Innovation Policy / 政策分野: Regulation &amp; Governance / 学術区分: News &amp; Official Release / 焦点: ITERプロジェクトの真空容器に関する規制 / Historical backfill from an allowlisted source.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="42" customHeight="1">
+      <c r="A75" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T21:02:36+09:00</t>
+        </is>
+      </c>
+      <c r="B75" s="75" t="inlineStr">
+        <is>
+          <t>2026-04-15T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="C75" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D75" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E75" s="60" t="inlineStr">
+        <is>
+          <t>Semiconductors &amp; Telecom</t>
+        </is>
+      </c>
+      <c r="F75" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="G75" s="60" t="inlineStr">
+        <is>
+          <t>Government</t>
+        </is>
+      </c>
+      <c r="H75" s="60" t="inlineStr">
+        <is>
+          <t>NIST News</t>
+        </is>
+      </c>
+      <c r="I75" s="60" t="inlineStr">
+        <is>
+          <t>NIST科学者が小型回路で「任意の波長」レーザーを作成</t>
+        </is>
+      </c>
+      <c r="J75" s="60" t="inlineStr">
+        <is>
+          <t>NISTの科学者が光用の集積回路を作成する新しい方法を開発しました。</t>
+        </is>
+      </c>
+      <c r="K75" s="60" t="inlineStr">
+        <is>
+          <t>https://www.nist.gov/news-events/news/2026/04/any-color-you-nist-scientists-create-any-wavelength-lasers-tiny-circuits</t>
+        </is>
+      </c>
+      <c r="L75" s="60" t="inlineStr">
+        <is>
+          <t>4fba34d8f0d0bf2d1a725c46</t>
+        </is>
+      </c>
+      <c r="M75" s="75" t="inlineStr">
+        <is>
+          <t>2026-04-15T21:00:00+09:00</t>
+        </is>
+      </c>
+      <c r="N75" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O75" s="60" t="inlineStr">
+        <is>
+          <t>枠: Technology Innovation | Innovation Policy / 政策分野: Public Procurement &amp; Industrial Policy / 学術区分: News &amp; Official Release / 焦点: 光用の集積回路の製造方法</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="42" customHeight="1">
+      <c r="A76" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T21:02:36+09:00</t>
+        </is>
+      </c>
+      <c r="B76" s="75" t="inlineStr">
+        <is>
+          <t>2026-03-31T19:31:10Z</t>
+        </is>
+      </c>
+      <c r="C76" s="60" t="inlineStr">
+        <is>
+          <t>EU &amp; Europe</t>
+        </is>
+      </c>
+      <c r="D76" s="60" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="E76" s="60" t="inlineStr"/>
+      <c r="F76" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="G76" s="60" t="inlineStr">
+        <is>
+          <t>Government</t>
+        </is>
+      </c>
+      <c r="H76" s="60" t="inlineStr">
+        <is>
+          <t>UK DSIT</t>
+        </is>
+      </c>
+      <c r="I76" s="60" t="inlineStr">
+        <is>
+          <t>R&amp;D税制の改革に関するHMRC内部マニュアル</t>
+        </is>
+      </c>
+      <c r="J76" s="60" t="inlineStr">
+        <is>
+          <t>HMRCがR&amp;D税制の改革に関する内部マニュアルを発表。具体的な内容は不明。</t>
+        </is>
+      </c>
+      <c r="K76" s="60" t="inlineStr">
+        <is>
+          <t>https://gov.uk/hmrc-internal-manuals/corporate-intangibles-research-and-development-manual/cird191000</t>
+        </is>
+      </c>
+      <c r="L76" s="60" t="inlineStr">
+        <is>
+          <t>33ac5f715280bf2f800578ec</t>
+        </is>
+      </c>
+      <c r="M76" s="75" t="inlineStr">
+        <is>
+          <t>2026-04-01T04:31:10+09:00</t>
+        </is>
+      </c>
+      <c r="N76" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O76" s="60" t="inlineStr">
+        <is>
+          <t>枠: Innovation Policy / 政策分野: R&amp;D Funding &amp; Tax Incentives / 学術区分: News &amp; Official Release / 焦点: R&amp;D税制の改革 / Historical backfill from an allowlisted source.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="42" customHeight="1">
+      <c r="A77" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T21:02:36+09:00</t>
+        </is>
+      </c>
+      <c r="B77" s="75" t="inlineStr">
+        <is>
+          <t>2026-03-31T18:45:30Z</t>
+        </is>
+      </c>
+      <c r="C77" s="60" t="inlineStr">
+        <is>
+          <t>EU &amp; Europe</t>
+        </is>
+      </c>
+      <c r="D77" s="60" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="E77" s="60" t="inlineStr"/>
+      <c r="F77" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="G77" s="60" t="inlineStr">
+        <is>
+          <t>Government</t>
+        </is>
+      </c>
+      <c r="H77" s="60" t="inlineStr">
+        <is>
+          <t>UK DSIT</t>
+        </is>
+      </c>
+      <c r="I77" s="60" t="inlineStr">
+        <is>
+          <t>認証に関するHMRC内部マニュアル</t>
+        </is>
+      </c>
+      <c r="J77" s="60" t="inlineStr">
+        <is>
+          <t>HMRCが認証に関する基準を定めた内部マニュアルを発表。具体的な内容は不明。</t>
+        </is>
+      </c>
+      <c r="K77" s="60" t="inlineStr">
+        <is>
+          <t>https://gov.uk/hmrc-internal-manuals/insurance-policyholder-taxation-manual/iptm8305</t>
+        </is>
+      </c>
+      <c r="L77" s="60" t="inlineStr">
+        <is>
+          <t>1065a54c9ab4490b2df8079f</t>
+        </is>
+      </c>
+      <c r="M77" s="75" t="inlineStr">
+        <is>
+          <t>2026-04-01T03:45:30+09:00</t>
+        </is>
+      </c>
+      <c r="N77" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O77" s="60" t="inlineStr">
+        <is>
+          <t>枠: Innovation Policy / 政策分野: Standards &amp; Safety / 学術区分: News &amp; Official Release / 焦点: 認証に関する基準 / Historical backfill from an allowlisted source.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="42" customHeight="1">
+      <c r="A78" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T21:02:36+09:00</t>
+        </is>
+      </c>
+      <c r="B78" s="75" t="inlineStr">
+        <is>
+          <t>2026-03-30T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="C78" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D78" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E78" s="60" t="inlineStr"/>
+      <c r="F78" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="G78" s="60" t="inlineStr">
+        <is>
+          <t>Government</t>
+        </is>
+      </c>
+      <c r="H78" s="60" t="inlineStr">
+        <is>
+          <t>NIST News</t>
+        </is>
+      </c>
+      <c r="I78" s="60" t="inlineStr">
+        <is>
+          <t>極限環境に耐えるフォトニックチップのパッケージング技術</t>
+        </is>
+      </c>
+      <c r="J78" s="60" t="inlineStr">
+        <is>
+          <t>NISTが極限環境に耐えるフォトニックチップのパッケージング技術を開発。具体的な応用範囲が示されている。</t>
+        </is>
+      </c>
+      <c r="K78" s="60" t="inlineStr">
+        <is>
+          <t>https://www.nist.gov/news-events/news/2026/03/nist-researchers-develop-photonic-chip-packaging-can-withstand-extreme</t>
+        </is>
+      </c>
+      <c r="L78" s="60" t="inlineStr">
+        <is>
+          <t>d0ce8f269bfecebfea5fffc2</t>
+        </is>
+      </c>
+      <c r="M78" s="75" t="inlineStr">
+        <is>
+          <t>2026-03-30T21:00:00+09:00</t>
+        </is>
+      </c>
+      <c r="N78" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O78" s="60" t="inlineStr">
+        <is>
+          <t>枠: Innovation Policy / 政策分野: Public Procurement &amp; Industrial Policy / 学術区分: News &amp; Official Release / 焦点: フォトニックチップのパッケージング技術</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="42" customHeight="1">
+      <c r="A79" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T21:02:36+09:00</t>
+        </is>
+      </c>
+      <c r="B79" s="75" t="inlineStr">
+        <is>
+          <t>2026-03-30T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="C79" s="60" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="D79" s="60" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E79" s="60" t="inlineStr">
+        <is>
+          <t>Fusion Energy</t>
+        </is>
+      </c>
+      <c r="F79" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" s="60" t="inlineStr">
+        <is>
+          <t>Journal Article</t>
+        </is>
+      </c>
+      <c r="H79" s="60" t="inlineStr">
+        <is>
+          <t>Physical review. E</t>
+        </is>
+      </c>
+      <c r="I79" s="60" t="inlineStr">
+        <is>
+          <t>最適化されたステラレーターWendelstein 7-Xにおけるトカマクレベルの性能</t>
+        </is>
+      </c>
+      <c r="J79" s="60" t="inlineStr">
+        <is>
+          <t>Wendelstein 7-Xにおける安定したピーク密度プロファイルを持つトカマクレベルの性能に関する研究が報告されている。</t>
+        </is>
+      </c>
+      <c r="K79" s="60" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1103/q59k-8m26</t>
+        </is>
+      </c>
+      <c r="L79" s="60" t="inlineStr">
+        <is>
+          <t>5f9127127dab71cd54ecf2d1</t>
+        </is>
+      </c>
+      <c r="M79" s="75" t="inlineStr">
+        <is>
+          <t>2026-03-30T09:00:00+09:00</t>
+        </is>
+      </c>
+      <c r="N79" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O79" s="60" t="inlineStr">
+        <is>
+          <t>枠: Technology Innovation / 学術区分: Journal Article / 査読表示: Journal record — confirm peer review on publisher page / 掲載誌・学会: Physical review. E / 焦点: 核融合技術 / OpenAlex record; work type=article; citations=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="42" customHeight="1">
+      <c r="A80" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T21:02:36+09:00</t>
+        </is>
+      </c>
+      <c r="B80" s="75" t="inlineStr">
+        <is>
+          <t>2026-03-20T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="C80" s="60" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="D80" s="60" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E80" s="60" t="inlineStr">
+        <is>
+          <t>Space</t>
+        </is>
+      </c>
+      <c r="F80" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" s="60" t="inlineStr">
+        <is>
+          <t>Journal Article</t>
+        </is>
+      </c>
+      <c r="H80" s="60" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="I80" s="60" t="inlineStr">
+        <is>
+          <t>FedLTN-CubeSat: 低軌道キューブサットコンステレーションにおける侵入検知のための神経シンボリック連合学習</t>
+        </is>
+      </c>
+      <c r="J80" s="60" t="inlineStr">
+        <is>
+          <t>低軌道キューブサットにおける侵入検知システムに関する研究が報告されている。</t>
+        </is>
+      </c>
+      <c r="K80" s="60" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.3390/math14061047</t>
+        </is>
+      </c>
+      <c r="L80" s="60" t="inlineStr">
+        <is>
+          <t>5d6fe2faeaa63e58b36b981e</t>
+        </is>
+      </c>
+      <c r="M80" s="75" t="inlineStr">
+        <is>
+          <t>2026-03-20T09:00:00+09:00</t>
+        </is>
+      </c>
+      <c r="N80" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O80" s="60" t="inlineStr">
+        <is>
+          <t>枠: Technology Innovation / 学術区分: Journal Article / 査読表示: Journal record — confirm peer review on publisher page / 掲載誌・学会: Mathematics / 焦点: 宇宙通信システム / OpenAlex record; work type=article; citations=7</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="42" customHeight="1">
+      <c r="A81" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T21:02:36+09:00</t>
+        </is>
+      </c>
+      <c r="B81" s="75" t="inlineStr">
+        <is>
+          <t>2026-03-10T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="C81" s="60" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="D81" s="60" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E81" s="60" t="inlineStr">
+        <is>
+          <t>Space</t>
+        </is>
+      </c>
+      <c r="F81" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" s="60" t="inlineStr">
+        <is>
+          <t>Journal Article</t>
+        </is>
+      </c>
+      <c r="H81" s="60" t="inlineStr">
+        <is>
+          <t>Virtual and Physical Prototyping</t>
+        </is>
+      </c>
+      <c r="I81" s="60" t="inlineStr">
+        <is>
+          <t>宇宙製造のためのデジタルツイン：フレームワークから未来への包括的レビュー</t>
+        </is>
+      </c>
+      <c r="J81" s="60" t="inlineStr">
+        <is>
+          <t>宇宙製造におけるデジタルツイン技術についての包括的なレビューを提供する。</t>
+        </is>
+      </c>
+      <c r="K81" s="60" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1080/17452759.2026.2639147</t>
+        </is>
+      </c>
+      <c r="L81" s="60" t="inlineStr">
+        <is>
+          <t>885d28facd82d772f140e913</t>
+        </is>
+      </c>
+      <c r="M81" s="75" t="inlineStr">
+        <is>
+          <t>2026-03-10T09:00:00+09:00</t>
+        </is>
+      </c>
+      <c r="N81" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O81" s="60" t="inlineStr">
+        <is>
+          <t>枠: Technology Innovation / 学術区分: Journal Article / 査読表示: Journal record — confirm peer review on publisher page / 掲載誌・学会: Virtual and Physical Prototyping / 焦点: 宇宙製造におけるデジタルツイン技術 / OpenAlex record; work type=article; citations=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="42" customHeight="1">
+      <c r="A82" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T21:02:36+09:00</t>
+        </is>
+      </c>
+      <c r="B82" s="75" t="inlineStr">
+        <is>
+          <t>2026-03-10T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="C82" s="60" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="D82" s="60" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E82" s="60" t="inlineStr">
+        <is>
+          <t>Robotics | Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="F82" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" s="60" t="inlineStr">
+        <is>
+          <t>Conference Paper</t>
+        </is>
+      </c>
+      <c r="H82" s="60" t="inlineStr">
+        <is>
+          <t>OpenAlex Conference Papers</t>
+        </is>
+      </c>
+      <c r="I82" s="60" t="inlineStr">
+        <is>
+          <t>Spotとのポップアップ体験：ロボットに対する公衆の認識を形成する</t>
+        </is>
+      </c>
+      <c r="J82" s="60" t="inlineStr">
+        <is>
+          <t>ロボットに対する公衆の認識を形成するための体験に関する研究。</t>
+        </is>
+      </c>
+      <c r="K82" s="60" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1145/3757279.3785600</t>
+        </is>
+      </c>
+      <c r="L82" s="60" t="inlineStr">
+        <is>
+          <t>921d3c21d3095bd95d28b7e4</t>
+        </is>
+      </c>
+      <c r="M82" s="75" t="inlineStr">
+        <is>
+          <t>2026-03-10T09:00:00+09:00</t>
+        </is>
+      </c>
+      <c r="N82" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O82" s="60" t="inlineStr">
+        <is>
+          <t>枠: Technology Innovation / 学術区分: Conference Paper / 査読表示: Conference proceedings — review status varies / 焦点: ロボットと人間の相互作用 / OpenAlex record; work type=conference-paper; citations=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="42" customHeight="1">
+      <c r="A83" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T21:02:36+09:00</t>
+        </is>
+      </c>
+      <c r="B83" s="75" t="inlineStr">
+        <is>
+          <t>2026-02-25T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="C83" s="60" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D83" s="60" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E83" s="60" t="inlineStr">
+        <is>
+          <t>Fusion Energy</t>
+        </is>
+      </c>
+      <c r="F83" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" s="60" t="inlineStr">
+        <is>
+          <t>Journal Article</t>
+        </is>
+      </c>
+      <c r="H83" s="60" t="inlineStr">
+        <is>
+          <t>Cryo</t>
+        </is>
+      </c>
+      <c r="I83" s="60" t="inlineStr">
+        <is>
+          <t>中国の超伝導トカマク戦略に基づく核融合磁石技術の概要</t>
+        </is>
+      </c>
+      <c r="J83" s="60" t="inlineStr">
+        <is>
+          <t>中国の超伝導トカマク戦略に基づく核融合磁石技術についての研究が紹介されており、超伝導材料や核融合発電に関連する技術が議論されています。</t>
+        </is>
+      </c>
+      <c r="K83" s="60" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.3390/cryo2010003</t>
+        </is>
+      </c>
+      <c r="L83" s="60" t="inlineStr">
+        <is>
+          <t>05022994d11a8d44cf509354</t>
+        </is>
+      </c>
+      <c r="M83" s="75" t="inlineStr">
+        <is>
+          <t>2026-02-25T09:00:00+09:00</t>
+        </is>
+      </c>
+      <c r="N83" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O83" s="60" t="inlineStr">
+        <is>
+          <t>枠: Technology Innovation / 学術区分: Journal Article / 査読表示: Journal record — confirm peer review on publisher page / 掲載誌・学会: Cryo / 焦点: 核融合技術 / OpenAlex record; work type=article; citations=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="42" customHeight="1">
+      <c r="A84" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T21:02:36+09:00</t>
+        </is>
+      </c>
+      <c r="B84" s="75" t="inlineStr">
+        <is>
+          <t>2026-02-17T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="C84" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D84" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E84" s="60" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="F84" s="76" t="n">
+        <v>4</v>
+      </c>
+      <c r="G84" s="60" t="inlineStr">
+        <is>
+          <t>Government</t>
+        </is>
+      </c>
+      <c r="H84" s="60" t="inlineStr">
+        <is>
+          <t>NIST News</t>
+        </is>
+      </c>
+      <c r="I84" s="60" t="inlineStr">
+        <is>
+          <t>相互運用可能で安全な革新のためのAIエージェント標準イニシアティブの発表</t>
+        </is>
+      </c>
+      <c r="J84" s="60" t="inlineStr">
+        <is>
+          <t>次世代AIの安全性と相互運用性を確保するためのイニシアティブが発表されました。</t>
+        </is>
+      </c>
+      <c r="K84" s="60" t="inlineStr">
+        <is>
+          <t>https://www.nist.gov/news-events/news/2026/02/announcing-ai-agent-standards-initiative-interoperable-and-secure</t>
+        </is>
+      </c>
+      <c r="L84" s="60" t="inlineStr">
+        <is>
+          <t>f2546cdceb249a312eaf9fa2</t>
+        </is>
+      </c>
+      <c r="M84" s="75" t="inlineStr">
+        <is>
+          <t>2026-02-17T21:00:00+09:00</t>
+        </is>
+      </c>
+      <c r="N84" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O84" s="60" t="inlineStr">
+        <is>
+          <t>枠: Innovation Policy / 政策分野: Public Procurement &amp; Industrial Policy / 学術区分: News &amp; Official Release / 焦点: AIの標準化と相互運用性</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="42" customHeight="1">
+      <c r="A85" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T21:02:36+09:00</t>
+        </is>
+      </c>
+      <c r="B85" s="75" t="inlineStr">
+        <is>
+          <t>2026-02-12T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="C85" s="60" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="D85" s="60" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E85" s="60" t="inlineStr">
+        <is>
+          <t>Semiconductors &amp; Telecom</t>
+        </is>
+      </c>
+      <c r="F85" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" s="60" t="inlineStr">
+        <is>
+          <t>Journal Article</t>
+        </is>
+      </c>
+      <c r="H85" s="60" t="inlineStr">
+        <is>
+          <t>Advanced Materials</t>
+        </is>
+      </c>
+      <c r="I85" s="60" t="inlineStr">
+        <is>
+          <t>地球を超えて：宇宙における準2次元ペロブスカイト太陽電池の耐久性</t>
+        </is>
+      </c>
+      <c r="J85" s="60" t="inlineStr">
+        <is>
+          <t>この研究は、宇宙環境におけるペロブスカイト太陽電池の性能最適化と耐久性に焦点を当てています。</t>
+        </is>
+      </c>
+      <c r="K85" s="60" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1002/adma.202520433</t>
+        </is>
+      </c>
+      <c r="L85" s="60" t="inlineStr">
+        <is>
+          <t>9a620b53ec8eae21b841cb1c</t>
+        </is>
+      </c>
+      <c r="M85" s="75" t="inlineStr">
+        <is>
+          <t>2026-02-12T09:00:00+09:00</t>
+        </is>
+      </c>
+      <c r="N85" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O85" s="60" t="inlineStr">
+        <is>
+          <t>枠: Technology Innovation / 学術区分: Journal Article / 査読表示: Journal record — confirm peer review on publisher page / 掲載誌・学会: Advanced Materials / 焦点: ペロブスカイト太陽電池 / OpenAlex record; work type=article; citations=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="42" customHeight="1">
+      <c r="A86" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T21:02:36+09:00</t>
+        </is>
+      </c>
+      <c r="B86" s="75" t="inlineStr">
+        <is>
+          <t>2026-02-10T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="C86" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D86" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E86" s="60" t="inlineStr">
+        <is>
+          <t>Biotechnology | Artificial Intelligence | Semiconductors &amp; Telecom | Quantum</t>
+        </is>
+      </c>
+      <c r="F86" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="G86" s="60" t="inlineStr">
+        <is>
+          <t>Government</t>
+        </is>
+      </c>
+      <c r="H86" s="60" t="inlineStr">
+        <is>
+          <t>NIST News</t>
+        </is>
+      </c>
+      <c r="I86" s="60" t="inlineStr">
+        <is>
+          <t>NISTがAI、バイオテクノロジー、半導体、量子などを進める小規模企業に300万ドル以上を配分</t>
+        </is>
+      </c>
+      <c r="J86" s="60" t="inlineStr">
+        <is>
+          <t>NISTはSBIRプログラムを通じて、AIやバイオテクノロジーなどの分野で8つの小規模企業に資金を配分しています。</t>
+        </is>
+      </c>
+      <c r="K86" s="60" t="inlineStr">
+        <is>
+          <t>https://www.nist.gov/news-events/news/2026/02/nist-allocates-over-3-million-small-businesses-advancing-ai-biotechnology</t>
+        </is>
+      </c>
+      <c r="L86" s="60" t="inlineStr">
+        <is>
+          <t>2700025a185e7f6eb2253ff3</t>
+        </is>
+      </c>
+      <c r="M86" s="75" t="inlineStr">
+        <is>
+          <t>2026-02-10T21:00:00+09:00</t>
+        </is>
+      </c>
+      <c r="N86" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O86" s="60" t="inlineStr">
+        <is>
+          <t>枠: Innovation Policy / 政策分野: Public Procurement &amp; Industrial Policy / 学術区分: News &amp; Official Release / 焦点: 小規模企業への資金配分</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="42" customHeight="1">
+      <c r="A87" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T21:02:36+09:00</t>
+        </is>
+      </c>
+      <c r="B87" s="75" t="inlineStr">
+        <is>
+          <t>2026-02-09T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="C87" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D87" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E87" s="60" t="inlineStr">
+        <is>
+          <t>Space</t>
+        </is>
+      </c>
+      <c r="F87" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="G87" s="60" t="inlineStr">
+        <is>
+          <t>Government</t>
+        </is>
+      </c>
+      <c r="H87" s="60" t="inlineStr">
+        <is>
+          <t>NIST News</t>
+        </is>
+      </c>
+      <c r="I87" s="60" t="inlineStr">
+        <is>
+          <t>宇宙：標準の最前線</t>
+        </is>
+      </c>
+      <c r="J87" s="60" t="inlineStr">
+        <is>
+          <t>NISTが国際宇宙ステーションに送った7つの標準材料についての報告です。</t>
+        </is>
+      </c>
+      <c r="K87" s="60" t="inlineStr">
+        <is>
+          <t>https://www.nist.gov/news-events/news/2026/02/space-final-frontier-standards</t>
+        </is>
+      </c>
+      <c r="L87" s="60" t="inlineStr">
+        <is>
+          <t>c1c40b3a2acf0b54aefa63ef</t>
+        </is>
+      </c>
+      <c r="M87" s="75" t="inlineStr">
+        <is>
+          <t>2026-02-09T21:00:00+09:00</t>
+        </is>
+      </c>
+      <c r="N87" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O87" s="60" t="inlineStr">
+        <is>
+          <t>枠: Innovation Policy / 政策分野: Public Procurement &amp; Industrial Policy / 学術区分: News &amp; Official Release / 焦点: 宇宙での標準材料の使用</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="42" customHeight="1">
+      <c r="A88" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T21:02:36+09:00</t>
+        </is>
+      </c>
+      <c r="B88" s="75" t="inlineStr">
+        <is>
+          <t>2026-01-30T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="C88" s="60" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="D88" s="60" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E88" s="60" t="inlineStr">
+        <is>
+          <t>Healthcare | Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="F88" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" s="60" t="inlineStr">
+        <is>
+          <t>Journal Article</t>
+        </is>
+      </c>
+      <c r="H88" s="60" t="inlineStr">
+        <is>
+          <t>Critical Reviews in Oncology/Hematology</t>
+        </is>
+      </c>
+      <c r="I88" s="60" t="inlineStr">
+        <is>
+          <t>がん治療におけるデジタルツイン：予測モデルから個別化治療戦略へ</t>
+        </is>
+      </c>
+      <c r="J88" s="60" t="inlineStr">
+        <is>
+          <t>がん治療におけるデジタルツイン技術の応用について、予測モデルから個別化治療戦略への進展を探る。</t>
+        </is>
+      </c>
+      <c r="K88" s="60" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.critrevonc.2026.105171</t>
+        </is>
+      </c>
+      <c r="L88" s="60" t="inlineStr">
+        <is>
+          <t>8ef56dd4b5b959ec5be3808b</t>
+        </is>
+      </c>
+      <c r="M88" s="75" t="inlineStr">
+        <is>
+          <t>2026-01-30T09:00:00+09:00</t>
+        </is>
+      </c>
+      <c r="N88" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O88" s="60" t="inlineStr">
+        <is>
+          <t>枠: Technology Innovation / 学術区分: Journal Article / 査読表示: Journal record — confirm peer review on publisher page / 掲載誌・学会: Critical Reviews in Oncology/Hematology / 焦点: デジタルツイン技術を用いたがん治療 / OpenAlex record; work type=article; citations=23</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:O33"/>
+  <autoFilter ref="A3:O88"/>
   <mergeCells count="2">
     <mergeCell ref="A1:O1"/>
     <mergeCell ref="A2:O2"/>
@@ -3470,7 +7547,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="N4:N33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="N4:N88" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"New,Reviewed,Follow-up,Archived"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3505,10 +7582,65 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K33" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K35" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K37" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K38" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K39" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K40" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K41" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K42" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K43" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K44" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K45" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K46" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K47" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K48" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K49" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K50" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K51" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K52" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K53" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K54" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K55" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K56" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K57" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K58" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K59" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K60" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K61" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K62" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K63" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K64" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K65" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K66" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K67" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K68" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K69" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K70" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K71" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K72" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K73" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K74" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K75" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K76" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K77" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K78" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K79" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K80" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K81" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K82" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K83" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K84" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K85" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K86" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K87" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K88" r:id="rId85"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId31"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId86"/>
   </tableParts>
 </worksheet>
 </file>
@@ -5979,7 +10111,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6058,67 +10190,67 @@
     <row r="4" ht="42" customHeight="1">
       <c r="A4" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T21:02:36+09:00</t>
+          <t>2026-07-26T21:29:09+09:00</t>
         </is>
       </c>
       <c r="B4" s="77" t="n">
-        <v>108</v>
+        <v>41</v>
       </c>
       <c r="C4" s="77" t="n">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="D4" s="77" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E4" s="77" t="n">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="F4" s="77" t="n">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="G4" s="77" t="n">
-        <v>1376.15</v>
+        <v>832.08</v>
       </c>
       <c r="H4" s="60" t="inlineStr">
         <is>
-          <t>Historical backfill: policy 365d / technology 183d</t>
+          <t>Daily update</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:36:29+09:00</t>
+          <t>2026-07-26T21:02:36+09:00</t>
         </is>
       </c>
       <c r="B5" s="77" t="n">
-        <v>38</v>
+        <v>108</v>
       </c>
       <c r="C5" s="77" t="n">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="D5" s="77" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="E5" s="77" t="n">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="F5" s="77" t="n">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="G5" s="77" t="n">
-        <v>93.7</v>
+        <v>1376.15</v>
       </c>
       <c r="H5" s="60" t="inlineStr">
         <is>
-          <t>Daily update</t>
+          <t>Historical backfill: policy 365d / technology 183d</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:34:08+09:00</t>
+          <t>2026-07-26T20:36:29+09:00</t>
         </is>
       </c>
       <c r="B6" s="77" t="n">
@@ -6128,7 +10260,7 @@
         <v>28</v>
       </c>
       <c r="D6" s="77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" s="77" t="n">
         <v>74</v>
@@ -6137,7 +10269,7 @@
         <v>10</v>
       </c>
       <c r="G6" s="77" t="n">
-        <v>20.27</v>
+        <v>93.7</v>
       </c>
       <c r="H6" s="60" t="inlineStr">
         <is>
@@ -6148,7 +10280,7 @@
     <row r="7">
       <c r="A7" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:29:40+09:00</t>
+          <t>2026-07-26T20:34:08+09:00</t>
         </is>
       </c>
       <c r="B7" s="77" t="n">
@@ -6158,16 +10290,16 @@
         <v>28</v>
       </c>
       <c r="D7" s="77" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E7" s="77" t="n">
-        <v>11</v>
+        <v>74</v>
       </c>
       <c r="F7" s="77" t="n">
         <v>10</v>
       </c>
       <c r="G7" s="77" t="n">
-        <v>141.79</v>
+        <v>20.27</v>
       </c>
       <c r="H7" s="60" t="inlineStr">
         <is>
@@ -6178,7 +10310,7 @@
     <row r="8">
       <c r="A8" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:24:57+09:00</t>
+          <t>2026-07-26T20:29:40+09:00</t>
         </is>
       </c>
       <c r="B8" s="77" t="n">
@@ -6188,16 +10320,16 @@
         <v>28</v>
       </c>
       <c r="D8" s="77" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E8" s="77" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="F8" s="77" t="n">
         <v>10</v>
       </c>
       <c r="G8" s="77" t="n">
-        <v>134.95</v>
+        <v>141.79</v>
       </c>
       <c r="H8" s="60" t="inlineStr">
         <is>
@@ -6208,7 +10340,7 @@
     <row r="9">
       <c r="A9" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:19:15+09:00</t>
+          <t>2026-07-26T20:24:57+09:00</t>
         </is>
       </c>
       <c r="B9" s="77" t="n">
@@ -6218,16 +10350,16 @@
         <v>28</v>
       </c>
       <c r="D9" s="77" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E9" s="77" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F9" s="77" t="n">
         <v>10</v>
       </c>
       <c r="G9" s="77" t="n">
-        <v>134.05</v>
+        <v>134.95</v>
       </c>
       <c r="H9" s="60" t="inlineStr">
         <is>
@@ -6238,26 +10370,26 @@
     <row r="10">
       <c r="A10" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:13:43+09:00</t>
+          <t>2026-07-26T20:19:15+09:00</t>
         </is>
       </c>
       <c r="B10" s="77" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C10" s="77" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D10" s="77" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E10" s="77" t="n">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="F10" s="77" t="n">
         <v>10</v>
       </c>
       <c r="G10" s="77" t="n">
-        <v>162.46</v>
+        <v>134.05</v>
       </c>
       <c r="H10" s="60" t="inlineStr">
         <is>
@@ -6268,7 +10400,7 @@
     <row r="11">
       <c r="A11" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:00:03+09:00</t>
+          <t>2026-07-26T20:13:43+09:00</t>
         </is>
       </c>
       <c r="B11" s="77" t="n">
@@ -6278,16 +10410,16 @@
         <v>24</v>
       </c>
       <c r="D11" s="77" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E11" s="77" t="n">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="F11" s="77" t="n">
         <v>10</v>
       </c>
       <c r="G11" s="77" t="n">
-        <v>154.27</v>
+        <v>162.46</v>
       </c>
       <c r="H11" s="60" t="inlineStr">
         <is>
@@ -6298,7 +10430,7 @@
     <row r="12">
       <c r="A12" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:51:39+09:00</t>
+          <t>2026-07-26T20:00:03+09:00</t>
         </is>
       </c>
       <c r="B12" s="77" t="n">
@@ -6308,16 +10440,16 @@
         <v>24</v>
       </c>
       <c r="D12" s="77" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E12" s="77" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="F12" s="77" t="n">
         <v>10</v>
       </c>
       <c r="G12" s="77" t="n">
-        <v>11.55</v>
+        <v>154.27</v>
       </c>
       <c r="H12" s="60" t="inlineStr">
         <is>
@@ -6328,26 +10460,26 @@
     <row r="13">
       <c r="A13" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:10:55+09:00</t>
+          <t>2026-07-26T19:51:39+09:00</t>
         </is>
       </c>
       <c r="B13" s="77" t="n">
         <v>34</v>
       </c>
       <c r="C13" s="77" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D13" s="77" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E13" s="77" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F13" s="77" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G13" s="77" t="n">
-        <v>194.65</v>
+        <v>11.55</v>
       </c>
       <c r="H13" s="60" t="inlineStr">
         <is>
@@ -6358,26 +10490,26 @@
     <row r="14">
       <c r="A14" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:05:06+09:00</t>
+          <t>2026-07-26T19:10:55+09:00</t>
         </is>
       </c>
       <c r="B14" s="77" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C14" s="77" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D14" s="77" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E14" s="77" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="F14" s="77" t="n">
         <v>9</v>
       </c>
       <c r="G14" s="77" t="n">
-        <v>165.89</v>
+        <v>194.65</v>
       </c>
       <c r="H14" s="60" t="inlineStr">
         <is>
@@ -6388,35 +10520,65 @@
     <row r="15">
       <c r="A15" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T19:05:06+09:00</t>
         </is>
       </c>
       <c r="B15" s="77" t="n">
         <v>33</v>
       </c>
       <c r="C15" s="77" t="n">
+        <v>24</v>
+      </c>
+      <c r="D15" s="77" t="n">
+        <v>5</v>
+      </c>
+      <c r="E15" s="77" t="n">
+        <v>39</v>
+      </c>
+      <c r="F15" s="77" t="n">
+        <v>9</v>
+      </c>
+      <c r="G15" s="77" t="n">
+        <v>165.89</v>
+      </c>
+      <c r="H15" s="60" t="inlineStr">
+        <is>
+          <t>Daily update</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T18:56:03+09:00</t>
+        </is>
+      </c>
+      <c r="B16" s="77" t="n">
+        <v>33</v>
+      </c>
+      <c r="C16" s="77" t="n">
         <v>20</v>
       </c>
-      <c r="D15" s="77" t="n">
+      <c r="D16" s="77" t="n">
         <v>94</v>
       </c>
-      <c r="E15" s="77" t="n">
+      <c r="E16" s="77" t="n">
         <v>0</v>
       </c>
-      <c r="F15" s="77" t="n">
+      <c r="F16" s="77" t="n">
         <v>13</v>
       </c>
-      <c r="G15" s="77" t="n">
+      <c r="G16" s="77" t="n">
         <v>129.43</v>
       </c>
-      <c r="H15" s="60" t="inlineStr">
+      <c r="H16" s="60" t="inlineStr">
         <is>
           <t>Initial lookback</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:H15"/>
+  <autoFilter ref="A3:H16"/>
   <mergeCells count="2">
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>

--- a/docs/innovation_news_ledger.xlsx
+++ b/docs/innovation_news_ledger.xlsx
@@ -9,9 +9,9 @@
     <sheet name="Run Log" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'News Ledger'!$A$3:$O$91</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Source Registry'!$A$3:$K$50</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Run Log'!$A$3:$H$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'News Ledger'!$A$3:$O$94</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Source Registry'!$A$3:$K$58</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Run Log'!$A$3:$H$19</definedName>
   </definedNames>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -472,7 +472,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="NewsLedgerTable" displayName="NewsLedgerTable" ref="A3:O91" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="NewsLedgerTable" displayName="NewsLedgerTable" ref="A3:O94" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <autoFilter ref="A3:O4"/>
   <tableColumns count="15">
     <tableColumn id="1" name="Collected At (JST)"/>
@@ -496,7 +496,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="SourceRegistryTable" displayName="SourceRegistryTable" ref="A3:K50" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="SourceRegistryTable" displayName="SourceRegistryTable" ref="A3:K58" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <autoFilter ref="A3:K37"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Active"/>
@@ -516,7 +516,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="RunLogTable" displayName="RunLogTable" ref="A3:H18" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="RunLogTable" displayName="RunLogTable" ref="A3:H19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <autoFilter ref="A3:H4"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Run Time (JST)"/>
@@ -800,7 +800,7 @@
       </c>
       <c r="B5" s="25" t="inlineStr">
         <is>
-          <t>2026-07-26T22:13:31+09:00</t>
+          <t>2026-07-26T22:54:37+09:00</t>
         </is>
       </c>
       <c r="C5" s="46" t="n"/>
@@ -1088,7 +1088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O91"/>
+  <dimension ref="A1:O94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1362,7 +1362,7 @@
     <row r="6" ht="42" customHeight="1">
       <c r="A6" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T21:29:09+09:00</t>
+          <t>2026-07-26T20:36:29+09:00</t>
         </is>
       </c>
       <c r="B6" s="75" t="inlineStr">
@@ -1372,55 +1372,55 @@
       </c>
       <c r="C6" s="60" t="inlineStr">
         <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D6" s="60" t="inlineStr">
+        <is>
           <t>Global</t>
         </is>
       </c>
-      <c r="D6" s="60" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
       <c r="E6" s="60" t="inlineStr">
         <is>
-          <t>Healthcare | Artificial Intelligence</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="F6" s="76" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G6" s="60" t="inlineStr">
         <is>
-          <t>Journal Article</t>
+          <t>Scientific Publication</t>
         </is>
       </c>
       <c r="H6" s="60" t="inlineStr">
         <is>
-          <t>Frontiers in Oral Health</t>
+          <t>Nature</t>
         </is>
       </c>
       <c r="I6" s="60" t="inlineStr">
         <is>
-          <t>リモートスクリーニングから精密予防へ：リスク予測と公平な口腔医療のための責任あるマルチモーダルAI</t>
+          <t>ホワイトハウスがAI資金を発表 — 米国科学の新時代を示唆</t>
         </is>
       </c>
       <c r="J6" s="60" t="inlineStr">
         <is>
-          <t>AIの口腔医療への応用が進展し、診断性能が向上しているが、バイアスや外部検証の不足などの課題が残る。</t>
+          <t>米国の科学顧問が資金調達の改革を呼びかけ、AIを用いた研究を加速するための助成金を配布した。</t>
         </is>
       </c>
       <c r="K6" s="60" t="inlineStr">
         <is>
-          <t>https://doi.org/10.3389/froh.2026.1878692</t>
+          <t>https://www.nature.com/articles/d41586-026-02332-8</t>
         </is>
       </c>
       <c r="L6" s="60" t="inlineStr">
         <is>
-          <t>7c510b60fabb7257c2f4eca5</t>
+          <t>856206151844f412d95b7a9b</t>
         </is>
       </c>
       <c r="M6" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T21:29:09+09:00</t>
+          <t>2026-07-26T20:36:29+09:00</t>
         </is>
       </c>
       <c r="N6" s="60" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="O6" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: Journal Article / 査読表示: Journal record — confirm peer review on publisher page / 掲載誌・学会: Frontiers in Oral Health / 焦点: AIを用いた口腔医療におけるリスク予測 / OpenAlex record; work type=article; citations=0</t>
+          <t>枠: Innovation Policy / 政策分野: R&amp;D Funding &amp; Tax Incentives / 学術区分: News &amp; Official Release / 焦点: AI研究の資金調達</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="E8" s="60" t="inlineStr">
         <is>
-          <t>Fusion Energy</t>
+          <t>Robotics</t>
         </is>
       </c>
       <c r="F8" s="76" t="n">
@@ -1541,27 +1541,27 @@
       </c>
       <c r="H8" s="60" t="inlineStr">
         <is>
-          <t>Nuclear Fusion</t>
+          <t>Science Advances</t>
         </is>
       </c>
       <c r="I8" s="60" t="inlineStr">
         <is>
-          <t>Wendelstein 7-Xにおける高速イオンの閉じ込めにおける放射電場の役割</t>
+          <t>自己探求によるロボットの行動と言語の発展</t>
         </is>
       </c>
       <c r="J8" s="60" t="inlineStr">
         <is>
-          <t>Wendelstein 7-Xの磁気構成が高速イオンの閉じ込めを改善することが期待されるが、その検証は難しい。</t>
+          <t>ロボットが自己探求を通じて行動と言語を学ぶ過程を探る研究が行われた。</t>
         </is>
       </c>
       <c r="K8" s="60" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1088/1741-4326/ae8f55</t>
+          <t>https://doi.org/10.1126/sciadv.aee7533</t>
         </is>
       </c>
       <c r="L8" s="60" t="inlineStr">
         <is>
-          <t>eef01d292bfb6d5bb3537528</t>
+          <t>c833fd421c298cf895263644</t>
         </is>
       </c>
       <c r="M8" s="75" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="O8" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: Journal Article / 査読表示: Journal record — confirm peer review on publisher page / 掲載誌・学会: Nuclear Fusion / 焦点: Wendelstein 7-Xの高速イオンの閉じ込めにおける放射電場の役割 / OpenAlex record; work type=article; citations=0</t>
+          <t>枠: Technology Innovation / 学術区分: Journal Article / 査読表示: Journal record — confirm peer review on publisher page / 掲載誌・学会: Science Advances / 焦点: ロボットの自己探求による行動と言語の発展 / OpenAlex record; work type=article; citations=1</t>
         </is>
       </c>
     </row>
@@ -1593,17 +1593,17 @@
       </c>
       <c r="C9" s="60" t="inlineStr">
         <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D9" s="60" t="inlineStr">
+        <is>
           <t>Global</t>
         </is>
       </c>
-      <c r="D9" s="60" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
       <c r="E9" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Robotics | Artificial Intelligence</t>
         </is>
       </c>
       <c r="F9" s="76" t="n">
@@ -1616,27 +1616,27 @@
       </c>
       <c r="H9" s="60" t="inlineStr">
         <is>
-          <t>OpenAlex Journal Articles</t>
+          <t>Frontiers in Neurorobotics</t>
         </is>
       </c>
       <c r="I9" s="60" t="inlineStr">
         <is>
-          <t>人工知能による地磁気嵐の予測：レビュー、方法論的枠組み、シミュレーション事例研究</t>
+          <t>AI駆動の四足ロボット：基本的な移動から高度な生物模倣行動まで</t>
         </is>
       </c>
       <c r="J9" s="60" t="inlineStr">
         <is>
-          <t>地磁気嵐の予測において、人工知能技術が従来のモデルよりも高い精度を示すことをレビューし、AI駆動の予測システムの構築方法を提案する。</t>
+          <t>四足ロボットの技術開発に関する文献レビューが行われ、AIの進展がその能力を拡張していることが示された。</t>
         </is>
       </c>
       <c r="K9" s="60" t="inlineStr">
         <is>
-          <t>https://doi.org/10.64823/ijpcs.2601002</t>
+          <t>https://doi.org/10.3389/fnbot.2026.1855550</t>
         </is>
       </c>
       <c r="L9" s="60" t="inlineStr">
         <is>
-          <t>00fc3537b602e30057c2118d</t>
+          <t>e165800add9d682af8ea2122</t>
         </is>
       </c>
       <c r="M9" s="75" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="O9" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: Journal Article / 査読表示: Journal record — confirm peer review on publisher page / 焦点: 地磁気嵐予測におけるAI技術 / OpenAlex record; work type=article; citations=0</t>
+          <t>枠: Technology Innovation / 学術区分: Journal Article / 査読表示: Journal record — confirm peer review on publisher page / 掲載誌・学会: Frontiers in Neurorobotics / 焦点: AI駆動の四足ロボット / OpenAlex record; work type=article; citations=0</t>
         </is>
       </c>
     </row>
@@ -1678,40 +1678,40 @@
       </c>
       <c r="E10" s="60" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Fusion Energy</t>
         </is>
       </c>
       <c r="F10" s="76" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G10" s="60" t="inlineStr">
         <is>
-          <t>Preprint</t>
+          <t>Journal Article</t>
         </is>
       </c>
       <c r="H10" s="60" t="inlineStr">
         <is>
-          <t>Zenodo (CERN European Organization for Nuclear Research)</t>
+          <t>Nuclear Fusion</t>
         </is>
       </c>
       <c r="I10" s="60" t="inlineStr">
         <is>
-          <t>量子技術ガバナンスに関するPrim-Lex理論：キュービットから量子主権へ</t>
+          <t>Wendelstein 7-Xにおける高速イオンの閉じ込めにおける放射電場の役割</t>
         </is>
       </c>
       <c r="J10" s="60" t="inlineStr">
         <is>
-          <t>OECDが量子技術に関する初の国際的な標準を採択し、量子技術のガバナンスが学術的議論から制度的構築へと移行したことを示す。</t>
+          <t>Wendelstein 7-Xにおける高速イオンの閉じ込めに関する研究が行われ、放射電場の影響が分析された。</t>
         </is>
       </c>
       <c r="K10" s="60" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5281/zenodo.21512028</t>
+          <t>https://doi.org/10.1088/1741-4326/ae8f55</t>
         </is>
       </c>
       <c r="L10" s="60" t="inlineStr">
         <is>
-          <t>61f1fcfb9afff652f523d019</t>
+          <t>eef01d292bfb6d5bb3537528</t>
         </is>
       </c>
       <c r="M10" s="75" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="O10" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation | Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: Preprint / 査読表示: Not peer reviewed / 掲載誌・学会: Zenodo (CERN European Organization for Nuclear Research) / 焦点: 量子技術のガバナンスと国際標準 / OpenAlex record; work type=preprint; citations=0</t>
+          <t>枠: Technology Innovation / 学術区分: Journal Article / 査読表示: Journal record — confirm peer review on publisher page / 掲載誌・学会: Nuclear Fusion / 焦点: Wendelstein 7-Xの高速イオンの閉じ込め / OpenAlex record; work type=article; citations=0</t>
         </is>
       </c>
     </row>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="E11" s="60" t="inlineStr">
         <is>
-          <t>Space</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="F11" s="76" t="n">
@@ -1761,32 +1761,32 @@
       </c>
       <c r="G11" s="60" t="inlineStr">
         <is>
-          <t>Preprint</t>
+          <t>Journal Article</t>
         </is>
       </c>
       <c r="H11" s="60" t="inlineStr">
         <is>
-          <t>Research Square</t>
+          <t>Scientific Reports</t>
         </is>
       </c>
       <c r="I11" s="60" t="inlineStr">
         <is>
-          <t>軸対称液体貯蔵タンクのスロッシング等価パラメータに関するモデル化手法</t>
+          <t>密なプラズマフォーカスにおけるクーロン爆発の研究</t>
         </is>
       </c>
       <c r="J11" s="60" t="inlineStr">
         <is>
-          <t>液体貯蔵タンクのスロッシングに関する新しいモデル化手法を提案し、流体力学的なシミュレーションを行う。</t>
+          <t>密なプラズマフォーカスにおけるクーロン爆発のシミュレーション研究が行われ、極端な条件下での挙動が分析された。</t>
         </is>
       </c>
       <c r="K11" s="60" t="inlineStr">
         <is>
-          <t>https://doi.org/10.21203/rs.3.rs-10191620/v1</t>
+          <t>https://doi.org/10.1038/s41598-026-63204-9</t>
         </is>
       </c>
       <c r="L11" s="60" t="inlineStr">
         <is>
-          <t>5dcc87029750dfedd91e620a</t>
+          <t>fcf607380491b3f6666abab6</t>
         </is>
       </c>
       <c r="M11" s="75" t="inlineStr">
@@ -1801,34 +1801,34 @@
       </c>
       <c r="O11" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: Preprint / 査読表示: Not peer reviewed / 掲載誌・学会: Research Square / 焦点: 液体貯蔵タンクのスロッシングモデル / OpenAlex record; work type=preprint; citations=0</t>
+          <t>枠: Technology Innovation / 学術区分: Journal Article / 査読表示: Journal record — confirm peer review on publisher page / 掲載誌・学会: Scientific Reports / 焦点: 密なプラズマフォーカスにおけるクーロン爆発の研究 / OpenAlex record; work type=article; citations=0</t>
         </is>
       </c>
     </row>
     <row r="12" ht="42" customHeight="1">
       <c r="A12" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:05:06+09:00</t>
+          <t>2026-07-26T21:29:09+09:00</t>
         </is>
       </c>
       <c r="B12" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T13:53:12Z</t>
+          <t>2026-07-23T00:00:00Z</t>
         </is>
       </c>
       <c r="C12" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D12" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="E12" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="F12" s="76" t="n">
@@ -1836,37 +1836,37 @@
       </c>
       <c r="G12" s="60" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Preprint</t>
         </is>
       </c>
       <c r="H12" s="60" t="inlineStr">
         <is>
-          <t>National Science Foundation News</t>
+          <t>Zenodo (CERN European Organization for Nuclear Research)</t>
         </is>
       </c>
       <c r="I12" s="60" t="inlineStr">
         <is>
-          <t>NSFがAIによる科学的発見のためのデータセット価値を解放する新プログラムを発表</t>
+          <t>プライム・レックス理論と量子技術ガバナンス：キュービットから量子主権へ</t>
         </is>
       </c>
       <c r="J12" s="60" t="inlineStr">
         <is>
-          <t>米国国立科学財団は、AIを活用した科学的発見のためのデータセット価値を解放するプログラムを発表しました。</t>
+          <t>OECDが採択した量子技術に関する提言を基に、量子技術のガバナンスの枠組みを構築する方法を探求した。</t>
         </is>
       </c>
       <c r="K12" s="60" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/news/new-nsf-initiative-aims-unlock-dataset-value-ai-enabled</t>
+          <t>https://doi.org/10.5281/zenodo.21512028</t>
         </is>
       </c>
       <c r="L12" s="60" t="inlineStr">
         <is>
-          <t>dcd819527d9b80141b26bcb8</t>
+          <t>61f1fcfb9afff652f523d019</t>
         </is>
       </c>
       <c r="M12" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:05:06+09:00</t>
+          <t>2026-07-26T21:29:09+09:00</t>
         </is>
       </c>
       <c r="N12" s="60" t="inlineStr">
@@ -1876,19 +1876,19 @@
       </c>
       <c r="O12" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: R&amp;D Funding &amp; Tax Incentives / 学術区分: News &amp; Official Release / 焦点: AIを活用した科学的発見のためのデータセット</t>
+          <t>枠: Technology Innovation | Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: Preprint / 査読表示: Not peer reviewed / 掲載誌・学会: Zenodo (CERN European Organization for Nuclear Research) / 焦点: 量子技術のガバナンスとOECDの提言 / OpenAlex record; work type=preprint; citations=0</t>
         </is>
       </c>
     </row>
     <row r="13" ht="42" customHeight="1">
       <c r="A13" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:29:40+09:00</t>
+          <t>2026-07-26T21:02:36+09:00</t>
         </is>
       </c>
       <c r="B13" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T13:53:06Z</t>
+          <t>2026-07-23T00:00:00Z</t>
         </is>
       </c>
       <c r="C13" s="60" t="inlineStr">
@@ -1903,45 +1903,45 @@
       </c>
       <c r="E13" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="F13" s="76" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G13" s="60" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Official Company</t>
         </is>
       </c>
       <c r="H13" s="60" t="inlineStr">
         <is>
-          <t>National Science Foundation News</t>
+          <t>OpenAI News</t>
         </is>
       </c>
       <c r="I13" s="60" t="inlineStr">
         <is>
-          <t>NSFがAI駆動の科学を進展させるために8300万ドルの投資を発表</t>
+          <t>AdventHealthがOpenAIを活用して全人的ケアを進める</t>
         </is>
       </c>
       <c r="J13" s="60" t="inlineStr">
         <is>
-          <t>米国国立科学財団は、AI駆動の科学を進展させるために8300万ドルの投資を発表しました。</t>
+          <t>AdventHealthがChatGPTを利用して業務を効率化し、患者ケアにより多くの時間を戻す取り組みを行っている。</t>
         </is>
       </c>
       <c r="K13" s="60" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/news/nsf-announces-83m-investment-integrated-data-systems</t>
+          <t>https://openai.com/index/adventhealth</t>
         </is>
       </c>
       <c r="L13" s="60" t="inlineStr">
         <is>
-          <t>018d40b7e6eb7aa4b8cfb5fa</t>
+          <t>57b488d288c298008e72a574</t>
         </is>
       </c>
       <c r="M13" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:29:40+09:00</t>
+          <t>2026-07-26T21:02:36+09:00</t>
         </is>
       </c>
       <c r="N13" s="60" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="O13" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy | Research System &amp; Talent / 学術区分: News &amp; Official Release / 焦点: AI駆動の科学のためのデータシステム</t>
+          <t>枠: Technology Innovation | Innovation Policy / 政策分野: Public Procurement &amp; Industrial Policy / 学術区分: News &amp; Official Release / 焦点: ChatGPTを用いたヘルスケアの業務効率化 / Historical backfill from an allowlisted source.</t>
         </is>
       </c>
     </row>
@@ -1963,51 +1963,55 @@
       </c>
       <c r="B14" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T12:00:00Z</t>
+          <t>2026-07-23T00:00:00Z</t>
         </is>
       </c>
       <c r="C14" s="60" t="inlineStr">
         <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="D14" s="60" t="inlineStr">
+        <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="D14" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E14" s="60" t="inlineStr"/>
+      <c r="E14" s="60" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
       <c r="F14" s="76" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G14" s="60" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Official Company</t>
         </is>
       </c>
       <c r="H14" s="60" t="inlineStr">
         <is>
-          <t>NIST News</t>
+          <t>OpenAI News</t>
         </is>
       </c>
       <c r="I14" s="60" t="inlineStr">
         <is>
-          <t>NIST、中小企業向けの資金提供機会を発表</t>
+          <t>ChatGPTにおけるヘルスケア機能の開始</t>
         </is>
       </c>
       <c r="J14" s="60" t="inlineStr">
         <is>
-          <t>NIST MEPが中小企業向けの資金提供機会を発表し、2026年7月28日にウェビナーを開催する予定。</t>
+          <t>ChatGPTの新機能により、米国の利用者は医療記録とApple Healthを安全に接続し、より個別化された健康情報を得ることができるようになった。</t>
         </is>
       </c>
       <c r="K14" s="60" t="inlineStr">
         <is>
-          <t>https://www.nist.gov/news-events/news/2026/07/nist-announces-funding-opportunity-14-mep-centers-advance-small-and-medium</t>
+          <t>https://openai.com/index/health-in-chatgpt</t>
         </is>
       </c>
       <c r="L14" s="60" t="inlineStr">
         <is>
-          <t>5aa9c93bc7040291c9f08bfa</t>
+          <t>bf70d809f9542eeef4af8727</t>
         </is>
       </c>
       <c r="M14" s="75" t="inlineStr">
@@ -2022,29 +2026,29 @@
       </c>
       <c r="O14" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: R&amp;D Funding &amp; Tax Incentives | Public Procurement &amp; Industrial Policy / 学術区分: News &amp; Official Release / 焦点: 中小企業向けの資金提供機会</t>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: ChatGPTのヘルスケア機能</t>
         </is>
       </c>
     </row>
     <row r="15" ht="42" customHeight="1">
       <c r="A15" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T21:02:36+09:00</t>
+          <t>2026-07-26T20:29:40+09:00</t>
         </is>
       </c>
       <c r="B15" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T05:00:56Z</t>
+          <t>2026-07-22T14:12:14Z</t>
         </is>
       </c>
       <c r="C15" s="60" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D15" s="60" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E15" s="60" t="inlineStr">
@@ -2053,7 +2057,7 @@
         </is>
       </c>
       <c r="F15" s="76" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G15" s="60" t="inlineStr">
         <is>
@@ -2062,32 +2066,32 @@
       </c>
       <c r="H15" s="60" t="inlineStr">
         <is>
-          <t>NISTEP Updates</t>
+          <t>DOE Office of Science News</t>
         </is>
       </c>
       <c r="I15" s="60" t="inlineStr">
         <is>
-          <t>特定科学技術領域動向報告書 -AI（人工知能）- 研究開発インプット編を公表</t>
+          <t>エネルギー長官がAI駆動の科学的発見を加速するプロジェクトを発表</t>
         </is>
       </c>
       <c r="J15" s="60" t="inlineStr">
         <is>
-          <t>AI分野における研究開発状況を分析し、基礎データをまとめた報告書を公表。</t>
+          <t>エネルギー長官クリス・ライトが、全米から選ばれた300のプロジェクトを発表し、エネルギーや発見科学、国家安全保障の分野でのブレークスルーを促進する。</t>
         </is>
       </c>
       <c r="K15" s="60" t="inlineStr">
         <is>
-          <t>https://www.nistep.go.jp/archives/63583/</t>
+          <t>https://www.energy.gov/articles/secretary-energy-chris-wright-announces-first-genesis-mission-projects-selected-accelerate</t>
         </is>
       </c>
       <c r="L15" s="60" t="inlineStr">
         <is>
-          <t>6b6122461584a86ee7a1c595</t>
+          <t>23fa1d6907c14d73ce3a41cd</t>
         </is>
       </c>
       <c r="M15" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T14:00:56+09:00</t>
+          <t>2026-07-26T20:29:40+09:00</t>
         </is>
       </c>
       <c r="N15" s="60" t="inlineStr">
@@ -2097,72 +2101,72 @@
       </c>
       <c r="O15" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation | Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: 人工知能（AI）分野の研究開発インプット</t>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: AI駆動の科学的発見を加速するプロジェクト</t>
         </is>
       </c>
     </row>
     <row r="16" ht="42" customHeight="1">
       <c r="A16" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T21:02:36+09:00</t>
+          <t>2026-07-26T19:05:06+09:00</t>
         </is>
       </c>
       <c r="B16" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T00:00:00Z</t>
+          <t>2026-07-22T13:53:19Z</t>
         </is>
       </c>
       <c r="C16" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D16" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E16" s="60" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="F16" s="76" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G16" s="60" t="inlineStr">
         <is>
-          <t>Scientific Publication</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H16" s="60" t="inlineStr">
         <is>
-          <t>Nature</t>
+          <t>National Science Foundation News</t>
         </is>
       </c>
       <c r="I16" s="60" t="inlineStr">
         <is>
-          <t>ブラウンブルヘッドキャットフィッシュのメラノーマは新しい伝染性がんを示す</t>
+          <t>NSFがAI優先事項の推進に関する声明を発表</t>
         </is>
       </c>
       <c r="J16" s="60" t="inlineStr">
         <is>
-          <t>ブラウンブルヘッドキャットフィッシュの腫瘍と非腫瘍組織の全ゲノム配列解析により、自然に発生する伝染性がんの一種が明らかになった。</t>
+          <t>米国国家科学財団が、ホワイトハウスの科学技術政策室やエネルギー省と連携し、AIに関する優先事項を進めることを発表した。</t>
         </is>
       </c>
       <c r="K16" s="60" t="inlineStr">
         <is>
-          <t>https://www.nature.com/articles/s41586-026-10832-w</t>
+          <t>https://www.nsf.gov/news/statement-nsf-chief-staff-brian-stone-performing-duties-nsf-1</t>
         </is>
       </c>
       <c r="L16" s="60" t="inlineStr">
         <is>
-          <t>f9bccca3cabb5ce19441f09d</t>
+          <t>123e2207578ca69c8f9c00a2</t>
         </is>
       </c>
       <c r="M16" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T09:00:00+09:00</t>
+          <t>2026-07-26T19:05:06+09:00</t>
         </is>
       </c>
       <c r="N16" s="60" t="inlineStr">
@@ -2172,72 +2176,72 @@
       </c>
       <c r="O16" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: トランスミッシブルがん</t>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: AI優先事項の推進</t>
         </is>
       </c>
     </row>
     <row r="17" ht="42" customHeight="1">
       <c r="A17" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T21:02:36+09:00</t>
+          <t>2026-07-26T19:05:06+09:00</t>
         </is>
       </c>
       <c r="B17" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T00:00:00Z</t>
+          <t>2026-07-22T13:53:12Z</t>
         </is>
       </c>
       <c r="C17" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D17" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E17" s="60" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="F17" s="76" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G17" s="60" t="inlineStr">
         <is>
-          <t>Scientific Publication</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H17" s="60" t="inlineStr">
         <is>
-          <t>Nature</t>
+          <t>National Science Foundation News</t>
         </is>
       </c>
       <c r="I17" s="60" t="inlineStr">
         <is>
-          <t>量子パラエレクトリックSrTiO3におけるナノスケール極性テクスチャのイメージング</t>
+          <t>NSFがAIによる科学的発見のためのデータセット価値を解放する新プログラムを発表</t>
         </is>
       </c>
       <c r="J17" s="60" t="inlineStr">
         <is>
-          <t>Cryo-STEMを用いて、SrTiO3が105K以下で周期的な極性ナノドメインを形成することが明らかになった。</t>
+          <t>米国国立科学財団は、AIを活用した科学的発見のためのデータセット価値を解放するプログラムを発表しました。</t>
         </is>
       </c>
       <c r="K17" s="60" t="inlineStr">
         <is>
-          <t>https://www.nature.com/articles/s41586-026-10823-x</t>
+          <t>https://www.nsf.gov/news/new-nsf-initiative-aims-unlock-dataset-value-ai-enabled</t>
         </is>
       </c>
       <c r="L17" s="60" t="inlineStr">
         <is>
-          <t>f12f62aebb861877dd7a5cbf</t>
+          <t>dcd819527d9b80141b26bcb8</t>
         </is>
       </c>
       <c r="M17" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T09:00:00+09:00</t>
+          <t>2026-07-26T19:05:06+09:00</t>
         </is>
       </c>
       <c r="N17" s="60" t="inlineStr">
@@ -2247,72 +2251,72 @@
       </c>
       <c r="O17" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: 量子パラエレクトリックSrTiO3のナノスケール極性テクスチャのイメージング</t>
+          <t>枠: Innovation Policy / 政策分野: R&amp;D Funding &amp; Tax Incentives / 学術区分: News &amp; Official Release / 焦点: AIを活用した科学的発見のためのデータセット</t>
         </is>
       </c>
     </row>
     <row r="18" ht="42" customHeight="1">
       <c r="A18" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T21:02:36+09:00</t>
+          <t>2026-07-26T20:29:40+09:00</t>
         </is>
       </c>
       <c r="B18" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T00:00:00Z</t>
+          <t>2026-07-22T13:53:06Z</t>
         </is>
       </c>
       <c r="C18" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D18" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E18" s="60" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="F18" s="76" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G18" s="60" t="inlineStr">
         <is>
-          <t>Scientific Publication</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H18" s="60" t="inlineStr">
         <is>
-          <t>Nature</t>
+          <t>National Science Foundation News</t>
         </is>
       </c>
       <c r="I18" s="60" t="inlineStr">
         <is>
-          <t>ブラウンブルヘッドキャットフィッシュのメラノーマは新しい伝染性がんを示す</t>
+          <t>NSFがAI駆動の科学を進展させるために8300万ドルの投資を発表</t>
         </is>
       </c>
       <c r="J18" s="60" t="inlineStr">
         <is>
-          <t>ブラウンブルヘッドキャットフィッシュの腫瘍と非腫瘍組織の全ゲノム配列解析により、自然に発生する伝染性がんの一種が明らかになった。</t>
+          <t>米国国立科学財団は、AI駆動の科学を進展させるために8300万ドルの投資を発表しました。</t>
         </is>
       </c>
       <c r="K18" s="60" t="inlineStr">
         <is>
-          <t>https://www.nature.com/articles/s41586-026-10828-6</t>
+          <t>https://www.nsf.gov/news/nsf-announces-83m-investment-integrated-data-systems</t>
         </is>
       </c>
       <c r="L18" s="60" t="inlineStr">
         <is>
-          <t>3c774b8bd5e287725e43b3b5</t>
+          <t>018d40b7e6eb7aa4b8cfb5fa</t>
         </is>
       </c>
       <c r="M18" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T09:00:00+09:00</t>
+          <t>2026-07-26T20:29:40+09:00</t>
         </is>
       </c>
       <c r="N18" s="60" t="inlineStr">
@@ -2322,72 +2326,68 @@
       </c>
       <c r="O18" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: トランスミッシブルがんの発見</t>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy | Research System &amp; Talent / 学術区分: News &amp; Official Release / 焦点: AI駆動の科学のためのデータシステム</t>
         </is>
       </c>
     </row>
     <row r="19" ht="42" customHeight="1">
       <c r="A19" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T21:02:36+09:00</t>
+          <t>2026-07-26T20:29:40+09:00</t>
         </is>
       </c>
       <c r="B19" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T00:00:00Z</t>
+          <t>2026-07-22T12:00:00Z</t>
         </is>
       </c>
       <c r="C19" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D19" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="E19" s="60" t="inlineStr">
-        <is>
-          <t>Artificial Intelligence</t>
-        </is>
-      </c>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E19" s="60" t="inlineStr"/>
       <c r="F19" s="76" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G19" s="60" t="inlineStr">
         <is>
-          <t>Scientific Publication</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H19" s="60" t="inlineStr">
         <is>
-          <t>Nature</t>
+          <t>NIST News</t>
         </is>
       </c>
       <c r="I19" s="60" t="inlineStr">
         <is>
-          <t>AIを使って数分でグラフィカルアブストラクトを作成する方法</t>
+          <t>NIST、中小企業向けの資金提供機会を発表</t>
         </is>
       </c>
       <c r="J19" s="60" t="inlineStr">
         <is>
-          <t>人工知能は、グラフィックデザインの経験がない人々にとって民主化の力となる。</t>
+          <t>NIST MEPが中小企業向けの資金提供機会を発表し、2026年7月28日にウェビナーを開催する予定。</t>
         </is>
       </c>
       <c r="K19" s="60" t="inlineStr">
         <is>
-          <t>https://www.nature.com/articles/d41586-026-02072-9</t>
+          <t>https://www.nist.gov/news-events/news/2026/07/nist-announces-funding-opportunity-14-mep-centers-advance-small-and-medium</t>
         </is>
       </c>
       <c r="L19" s="60" t="inlineStr">
         <is>
-          <t>b2a4fe860295587fbfbde689</t>
+          <t>5aa9c93bc7040291c9f08bfa</t>
         </is>
       </c>
       <c r="M19" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T09:00:00+09:00</t>
+          <t>2026-07-26T20:29:40+09:00</t>
         </is>
       </c>
       <c r="N19" s="60" t="inlineStr">
@@ -2397,7 +2397,7 @@
       </c>
       <c r="O19" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: AIを用いたグラフィカルアブストラクトの作成</t>
+          <t>枠: Innovation Policy / 政策分野: R&amp;D Funding &amp; Tax Incentives | Public Procurement &amp; Industrial Policy / 学術区分: News &amp; Official Release / 焦点: 中小企業向けの資金提供機会</t>
         </is>
       </c>
     </row>
@@ -2409,17 +2409,17 @@
       </c>
       <c r="B20" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T00:00:00Z</t>
+          <t>2026-07-22T05:00:56Z</t>
         </is>
       </c>
       <c r="C20" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="D20" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="E20" s="60" t="inlineStr">
@@ -2428,41 +2428,41 @@
         </is>
       </c>
       <c r="F20" s="76" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G20" s="60" t="inlineStr">
         <is>
-          <t>Scientific Publication</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H20" s="60" t="inlineStr">
         <is>
-          <t>Nature</t>
+          <t>NISTEP Updates</t>
         </is>
       </c>
       <c r="I20" s="60" t="inlineStr">
         <is>
-          <t>「良いデザインには熟練が必要」：科学的イラストレーターがAIの未来を描く</t>
+          <t>特定科学技術領域動向報告書 -AI（人工知能）- 研究開発インプット編を公表</t>
         </is>
       </c>
       <c r="J20" s="60" t="inlineStr">
         <is>
-          <t>Natureが5人のアーティストに科学を視覚的に伝えるアプローチについてインタビューした。</t>
+          <t>AI分野における研究開発状況を分析し、基礎データをまとめた報告書を公表。</t>
         </is>
       </c>
       <c r="K20" s="60" t="inlineStr">
         <is>
-          <t>https://www.nature.com/articles/d41586-026-02230-z</t>
+          <t>https://www.nistep.go.jp/archives/63583/</t>
         </is>
       </c>
       <c r="L20" s="60" t="inlineStr">
         <is>
-          <t>108461ddd7bd10edd9652aef</t>
+          <t>6b6122461584a86ee7a1c595</t>
         </is>
       </c>
       <c r="M20" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T09:00:00+09:00</t>
+          <t>2026-07-22T14:00:56+09:00</t>
         </is>
       </c>
       <c r="N20" s="60" t="inlineStr">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="O20" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: 科学的イラストレーションにおけるAIの未来</t>
+          <t>枠: Technology Innovation | Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: 人工知能（AI）分野の研究開発インプット</t>
         </is>
       </c>
     </row>
@@ -2489,50 +2489,50 @@
       </c>
       <c r="C21" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D21" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E21" s="60" t="inlineStr">
         <is>
-          <t>Biotechnology | Artificial Intelligence</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="F21" s="76" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G21" s="60" t="inlineStr">
         <is>
-          <t>Scientific Publication</t>
+          <t>Policy Institute</t>
         </is>
       </c>
       <c r="H21" s="60" t="inlineStr">
         <is>
-          <t>Nature</t>
+          <t>Brookings TechTank</t>
         </is>
       </c>
       <c r="I21" s="60" t="inlineStr">
         <is>
-          <t>AIがCRISPR複合体の相互作用を特定し、DNA編集の特異性を向上させる</t>
+          <t>政策が世代ZのAIへの信頼を決定する</t>
         </is>
       </c>
       <c r="J21" s="60" t="inlineStr">
         <is>
-          <t>AlphaFold3による分子接触の予測が、DNAターゲット配列に対する酵素の選択性を改善するために使用された。</t>
+          <t>世代ZのAIに対する信頼は、PRではなく政策によって決まると論じられている。</t>
         </is>
       </c>
       <c r="K21" s="60" t="inlineStr">
         <is>
-          <t>https://www.nature.com/articles/d41586-026-02042-1</t>
+          <t>https://www.brookings.edu/articles/policy-not-pr-will-determine-gen-zs-trust-in-ai/</t>
         </is>
       </c>
       <c r="L21" s="60" t="inlineStr">
         <is>
-          <t>ab4fcaf4ee310e08612eba0d</t>
+          <t>61bd55f8ce5a2385a5420260</t>
         </is>
       </c>
       <c r="M21" s="75" t="inlineStr">
@@ -2547,7 +2547,7 @@
       </c>
       <c r="O21" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: CRISPR複合体における相互作用の特定</t>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: AIに対する信頼の構築</t>
         </is>
       </c>
     </row>
@@ -2592,22 +2592,22 @@
       </c>
       <c r="I22" s="60" t="inlineStr">
         <is>
-          <t>背景遺伝子と新しい変異ががん進化を導く</t>
+          <t>ブラウンブルヘッドキャットフィッシュのメラノーマは新しい伝染性がんを示す</t>
         </is>
       </c>
       <c r="J22" s="60" t="inlineStr">
         <is>
-          <t>マウスでの腫瘍進化の再実行により、DNA損傷後のがんの発展が示された。</t>
+          <t>ブラウンブルヘッドキャットフィッシュの腫瘍と非腫瘍組織の全ゲノム配列解析により、自然に発生する伝染性がんの一種が明らかになった。</t>
         </is>
       </c>
       <c r="K22" s="60" t="inlineStr">
         <is>
-          <t>https://www.nature.com/articles/d41586-026-02155-7</t>
+          <t>https://www.nature.com/articles/s41586-026-10832-w</t>
         </is>
       </c>
       <c r="L22" s="60" t="inlineStr">
         <is>
-          <t>74243d6e7e201860f4f79008</t>
+          <t>f9bccca3cabb5ce19441f09d</t>
         </is>
       </c>
       <c r="M22" s="75" t="inlineStr">
@@ -2622,7 +2622,7 @@
       </c>
       <c r="O22" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: がん進化における背景遺伝子と新しい変異の相互作用</t>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: トランスミッシブルがん</t>
         </is>
       </c>
     </row>
@@ -2649,7 +2649,7 @@
       </c>
       <c r="E23" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="F23" s="76" t="n">
@@ -2667,22 +2667,22 @@
       </c>
       <c r="I23" s="60" t="inlineStr">
         <is>
-          <t>科学におけるAI画像のミスを避けるための3つのヒント</t>
+          <t>量子パラエレクトリックSrTiO3におけるナノスケール極性テクスチャのイメージング</t>
         </is>
       </c>
       <c r="J23" s="60" t="inlineStr">
         <is>
-          <t>AIツールはグラフィック作成に役立つが、エラーを引き起こす可能性がある。</t>
+          <t>Cryo-STEMを用いて、SrTiO3が105K以下で周期的な極性ナノドメインを形成することが明らかになった。</t>
         </is>
       </c>
       <c r="K23" s="60" t="inlineStr">
         <is>
-          <t>https://www.nature.com/articles/d41586-026-02233-w</t>
+          <t>https://www.nature.com/articles/s41586-026-10823-x</t>
         </is>
       </c>
       <c r="L23" s="60" t="inlineStr">
         <is>
-          <t>3333c16762502cf03b987a99</t>
+          <t>f12f62aebb861877dd7a5cbf</t>
         </is>
       </c>
       <c r="M23" s="75" t="inlineStr">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="O23" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: 科学におけるAI画像のミスを避けるためのヒント</t>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: 量子パラエレクトリックSrTiO3のナノスケール極性テクスチャのイメージング</t>
         </is>
       </c>
     </row>
@@ -2724,7 +2724,7 @@
       </c>
       <c r="E24" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="F24" s="76" t="n">
@@ -2742,22 +2742,22 @@
       </c>
       <c r="I24" s="60" t="inlineStr">
         <is>
-          <t>日々のブリーフィング：世界はついにポリオを根絶できるか？</t>
+          <t>ブラウンブルヘッドキャットフィッシュのメラノーマは新しい伝染性がんを示す</t>
         </is>
       </c>
       <c r="J24" s="60" t="inlineStr">
         <is>
-          <t>一部の研究者は、現在の根絶戦略が時代遅れであると考えている。</t>
+          <t>ブラウンブルヘッドキャットフィッシュの腫瘍と非腫瘍組織の全ゲノム配列解析により、自然に発生する伝染性がんの一種が明らかになった。</t>
         </is>
       </c>
       <c r="K24" s="60" t="inlineStr">
         <is>
-          <t>https://www.nature.com/articles/d41586-026-02302-0</t>
+          <t>https://www.nature.com/articles/s41586-026-10828-6</t>
         </is>
       </c>
       <c r="L24" s="60" t="inlineStr">
         <is>
-          <t>a6bb3e839151ea803a445830</t>
+          <t>3c774b8bd5e287725e43b3b5</t>
         </is>
       </c>
       <c r="M24" s="75" t="inlineStr">
@@ -2772,7 +2772,7 @@
       </c>
       <c r="O24" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: ポリオ根絶に関する研究</t>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: トランスミッシブルがんの発見</t>
         </is>
       </c>
     </row>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="B25" s="75" t="inlineStr">
         <is>
-          <t>2026-07-21T22:35:45Z</t>
+          <t>2026-07-22T00:00:00Z</t>
         </is>
       </c>
       <c r="C25" s="60" t="inlineStr">
@@ -2794,7 +2794,7 @@
       </c>
       <c r="D25" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="E25" s="60" t="inlineStr">
@@ -2807,37 +2807,37 @@
       </c>
       <c r="G25" s="60" t="inlineStr">
         <is>
-          <t>Official Company</t>
+          <t>Scientific Publication</t>
         </is>
       </c>
       <c r="H25" s="60" t="inlineStr">
         <is>
-          <t>NVIDIA Blog</t>
+          <t>Nature</t>
         </is>
       </c>
       <c r="I25" s="60" t="inlineStr">
         <is>
-          <t>フォートワースにて：WistronがNVIDIA AIシステムを生産するための先進的製造工場を開設</t>
+          <t>AIを使って数分でグラフィカルアブストラクトを作成する方法</t>
         </is>
       </c>
       <c r="J25" s="60" t="inlineStr">
         <is>
-          <t>Wistronがテキサス州フォートワースに324,000平方フィートの製造施設を開設し、AIシステムのためのスーパーチップを生産する。</t>
+          <t>人工知能は、グラフィックデザインの経験がない人々にとって民主化の力となる。</t>
         </is>
       </c>
       <c r="K25" s="60" t="inlineStr">
         <is>
-          <t>https://blogs.nvidia.com/blog/wistron-manufacturing-texas/</t>
+          <t>https://www.nature.com/articles/d41586-026-02072-9</t>
         </is>
       </c>
       <c r="L25" s="60" t="inlineStr">
         <is>
-          <t>21f1e1f3e19b1a5bf0af3cb7</t>
+          <t>b2a4fe860295587fbfbde689</t>
         </is>
       </c>
       <c r="M25" s="75" t="inlineStr">
         <is>
-          <t>2026-07-22T07:35:45+09:00</t>
+          <t>2026-07-22T09:00:00+09:00</t>
         </is>
       </c>
       <c r="N25" s="60" t="inlineStr">
@@ -2847,24 +2847,24 @@
       </c>
       <c r="O25" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: NVIDIA AIシステムの製造</t>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: AIを用いたグラフィカルアブストラクトの作成</t>
         </is>
       </c>
     </row>
     <row r="26" ht="42" customHeight="1">
       <c r="A26" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T21:02:36+09:00</t>
         </is>
       </c>
       <c r="B26" s="75" t="inlineStr">
         <is>
-          <t>2026-07-21T14:48:28Z</t>
+          <t>2026-07-22T00:00:00Z</t>
         </is>
       </c>
       <c r="C26" s="60" t="inlineStr">
         <is>
-          <t>EU &amp; Europe</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D26" s="60" t="inlineStr">
@@ -2874,45 +2874,45 @@
       </c>
       <c r="E26" s="60" t="inlineStr">
         <is>
-          <t>Fusion Energy</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="F26" s="76" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G26" s="60" t="inlineStr">
         <is>
-          <t>Industry Association</t>
+          <t>Scientific Publication</t>
         </is>
       </c>
       <c r="H26" s="60" t="inlineStr">
         <is>
-          <t>Fusion Industry Association</t>
+          <t>Nature</t>
         </is>
       </c>
       <c r="I26" s="60" t="inlineStr">
         <is>
-          <t>FIA、核融合のためのEU資金調達の道筋を示す</t>
+          <t>「良いデザインには熟練が必要」：科学的イラストレーターがAIの未来を描く</t>
         </is>
       </c>
       <c r="J26" s="60" t="inlineStr">
         <is>
-          <t>Fusion Industry Associationが商業核融合エネルギーのためのEU資金調達のロードマップを発表。</t>
+          <t>Natureが5人のアーティストに科学を視覚的に伝えるアプローチについてインタビューした。</t>
         </is>
       </c>
       <c r="K26" s="60" t="inlineStr">
         <is>
-          <t>https://www.fusionindustryassociation.org/fia-outlines-eu-financing-pathway-for-fusion/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=fia-outlines-eu-financing-pathway-for-fusion</t>
+          <t>https://www.nature.com/articles/d41586-026-02230-z</t>
         </is>
       </c>
       <c r="L26" s="60" t="inlineStr">
         <is>
-          <t>88af233d904d670250fa5a31</t>
+          <t>108461ddd7bd10edd9652aef</t>
         </is>
       </c>
       <c r="M26" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-22T09:00:00+09:00</t>
         </is>
       </c>
       <c r="N26" s="60" t="inlineStr">
@@ -2922,7 +2922,7 @@
       </c>
       <c r="O26" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: R&amp;D Funding &amp; Tax Incentives / 学術区分: News &amp; Official Release / 焦点: EUの核融合エネルギー商業化に向けた資金調達</t>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: 科学的イラストレーションにおけるAIの未来</t>
         </is>
       </c>
     </row>
@@ -2934,7 +2934,7 @@
       </c>
       <c r="B27" s="75" t="inlineStr">
         <is>
-          <t>2026-07-21T00:00:00Z</t>
+          <t>2026-07-22T00:00:00Z</t>
         </is>
       </c>
       <c r="C27" s="60" t="inlineStr">
@@ -2949,7 +2949,7 @@
       </c>
       <c r="E27" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence | Quantum</t>
+          <t>Biotechnology | Artificial Intelligence</t>
         </is>
       </c>
       <c r="F27" s="76" t="n">
@@ -2957,37 +2957,37 @@
       </c>
       <c r="G27" s="60" t="inlineStr">
         <is>
-          <t>Conference Paper</t>
+          <t>Scientific Publication</t>
         </is>
       </c>
       <c r="H27" s="60" t="inlineStr">
         <is>
-          <t>OpenAlex Conference Papers</t>
+          <t>Nature</t>
         </is>
       </c>
       <c r="I27" s="60" t="inlineStr">
         <is>
-          <t>心血管疾患リスク予測のための量子機械学習</t>
+          <t>AIがCRISPR複合体の相互作用を特定し、DNA編集の特異性を向上させる</t>
         </is>
       </c>
       <c r="J27" s="60" t="inlineStr">
         <is>
-          <t>量子コンピュータを用いた心血管疾患リスク予測に関する研究が進められている。</t>
+          <t>AlphaFold3による分子接触の予測が、DNAターゲット配列に対する酵素の選択性を改善するために使用された。</t>
         </is>
       </c>
       <c r="K27" s="60" t="inlineStr">
         <is>
-          <t>https://doi.org/10.3390/engproc2026150039</t>
+          <t>https://www.nature.com/articles/d41586-026-02042-1</t>
         </is>
       </c>
       <c r="L27" s="60" t="inlineStr">
         <is>
-          <t>1cd467f8ebb1388daedc245f</t>
+          <t>ab4fcaf4ee310e08612eba0d</t>
         </is>
       </c>
       <c r="M27" s="75" t="inlineStr">
         <is>
-          <t>2026-07-21T09:00:00+09:00</t>
+          <t>2026-07-22T09:00:00+09:00</t>
         </is>
       </c>
       <c r="N27" s="60" t="inlineStr">
@@ -2997,7 +2997,7 @@
       </c>
       <c r="O27" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: Conference Paper / 査読表示: Conference proceedings — review status varies / 焦点: 量子機械学習と心血管疾患リスク予測 / OpenAlex record; work type=conference-paper; citations=0</t>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: CRISPR複合体における相互作用の特定</t>
         </is>
       </c>
     </row>
@@ -3009,7 +3009,7 @@
       </c>
       <c r="B28" s="75" t="inlineStr">
         <is>
-          <t>2026-07-20T15:00:53Z</t>
+          <t>2026-07-22T00:00:00Z</t>
         </is>
       </c>
       <c r="C28" s="60" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="D28" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="E28" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence | Robotics</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="F28" s="76" t="n">
@@ -3032,37 +3032,37 @@
       </c>
       <c r="G28" s="60" t="inlineStr">
         <is>
-          <t>Official Company</t>
+          <t>Scientific Publication</t>
         </is>
       </c>
       <c r="H28" s="60" t="inlineStr">
         <is>
-          <t>NVIDIA Blog</t>
+          <t>Nature</t>
         </is>
       </c>
       <c r="I28" s="60" t="inlineStr">
         <is>
-          <t>SIGGRAPHでNVIDIAがエージェントAIと物理AIでグラフィックスとシミュレーションを進展</t>
+          <t>背景遺伝子と新しい変異ががん進化を導く</t>
         </is>
       </c>
       <c r="J28" s="60" t="inlineStr">
         <is>
-          <t>NVIDIAはSIGGRAPHで、オープンモデルからリアルタイムシミュレーションまで、AIとグラフィックスの革新がメディア、コンテンツ制作、ロボティクスを変革していることを発表した。</t>
+          <t>マウスでの腫瘍進化の再実行により、DNA損傷後のがんの発展が示された。</t>
         </is>
       </c>
       <c r="K28" s="60" t="inlineStr">
         <is>
-          <t>https://blogs.nvidia.com/blog/siggraph-news-2026/</t>
+          <t>https://www.nature.com/articles/d41586-026-02155-7</t>
         </is>
       </c>
       <c r="L28" s="60" t="inlineStr">
         <is>
-          <t>70c1acaa81ba6cd1c84a673d</t>
+          <t>74243d6e7e201860f4f79008</t>
         </is>
       </c>
       <c r="M28" s="75" t="inlineStr">
         <is>
-          <t>2026-07-21T00:00:53+09:00</t>
+          <t>2026-07-22T09:00:00+09:00</t>
         </is>
       </c>
       <c r="N28" s="60" t="inlineStr">
@@ -3072,7 +3072,7 @@
       </c>
       <c r="O28" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: エージェントAIと物理AIの進展</t>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: がん進化における背景遺伝子と新しい変異の相互作用</t>
         </is>
       </c>
     </row>
@@ -3084,60 +3084,60 @@
       </c>
       <c r="B29" s="75" t="inlineStr">
         <is>
-          <t>2026-07-20T13:30:06Z</t>
+          <t>2026-07-22T00:00:00Z</t>
         </is>
       </c>
       <c r="C29" s="60" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D29" s="60" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="E29" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence | Semiconductors &amp; Telecom</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="F29" s="76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G29" s="60" t="inlineStr">
         <is>
-          <t>Major Media</t>
+          <t>Scientific Publication</t>
         </is>
       </c>
       <c r="H29" s="60" t="inlineStr">
         <is>
-          <t>South China Morning Post Technology</t>
+          <t>Nature</t>
         </is>
       </c>
       <c r="I29" s="60" t="inlineStr">
         <is>
-          <t>トークン経済からタスク経済へ？SenseTimeがAIの商業化に賭ける</t>
+          <t>科学におけるAI画像のミスを避けるための3つのヒント</t>
         </is>
       </c>
       <c r="J29" s="60" t="inlineStr">
         <is>
-          <t>中国のAI企業SenseTimeは、トークン価格の低下に伴い、AIの商業化が「トークン経済」から「タスク経済」へ移行する見込みであると述べた。</t>
+          <t>AIツールはグラフィック作成に役立つが、エラーを引き起こす可能性がある。</t>
         </is>
       </c>
       <c r="K29" s="60" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/tech/big-tech/article/3361242/no-longer-token-economy-sensetime-bets-task-economy-token-prices-set-drop?utm_source=rss_feed</t>
+          <t>https://www.nature.com/articles/d41586-026-02233-w</t>
         </is>
       </c>
       <c r="L29" s="60" t="inlineStr">
         <is>
-          <t>cd5b1ea310d8a65d00ad1ad9</t>
+          <t>3333c16762502cf03b987a99</t>
         </is>
       </c>
       <c r="M29" s="75" t="inlineStr">
         <is>
-          <t>2026-07-20T22:30:06+09:00</t>
+          <t>2026-07-22T09:00:00+09:00</t>
         </is>
       </c>
       <c r="N29" s="60" t="inlineStr">
@@ -3147,7 +3147,7 @@
       </c>
       <c r="O29" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation | Innovation Policy / 政策分野: Patents &amp; Intellectual Property / 学術区分: News &amp; Official Release / 焦点: AIの商業化の移行</t>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: 科学におけるAI画像のミスを避けるためのヒント</t>
         </is>
       </c>
     </row>
@@ -3159,7 +3159,7 @@
       </c>
       <c r="B30" s="75" t="inlineStr">
         <is>
-          <t>2026-07-20T10:59:23Z</t>
+          <t>2026-07-22T00:00:00Z</t>
         </is>
       </c>
       <c r="C30" s="60" t="inlineStr">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="D30" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="E30" s="60" t="inlineStr">
@@ -3182,37 +3182,37 @@
       </c>
       <c r="G30" s="60" t="inlineStr">
         <is>
-          <t>Official Company</t>
+          <t>Scientific Publication</t>
         </is>
       </c>
       <c r="H30" s="60" t="inlineStr">
         <is>
-          <t>NVIDIA Blog</t>
+          <t>Nature</t>
         </is>
       </c>
       <c r="I30" s="60" t="inlineStr">
         <is>
-          <t>Bristol Myers Squibbがライフサイエンス業界で最も先進的なAI工場を構築</t>
+          <t>日々のブリーフィング：世界はついにポリオを根絶できるか？</t>
         </is>
       </c>
       <c r="J30" s="60" t="inlineStr">
         <is>
-          <t>Bristol Myers Squibbは、ライフサイエンス分野でのAIクラスターを拡大し、成果を上げていることを発表した。</t>
+          <t>一部の研究者は、現在の根絶戦略が時代遅れであると考えている。</t>
         </is>
       </c>
       <c r="K30" s="60" t="inlineStr">
         <is>
-          <t>https://blogs.nvidia.com/blog/bristol-myers-squibb-building-life-science-industrys-most-advanced-ai-factory-on-nvidia-vera-rubin/</t>
+          <t>https://www.nature.com/articles/d41586-026-02302-0</t>
         </is>
       </c>
       <c r="L30" s="60" t="inlineStr">
         <is>
-          <t>b4ddc90482832cbb50579f2a</t>
+          <t>a6bb3e839151ea803a445830</t>
         </is>
       </c>
       <c r="M30" s="75" t="inlineStr">
         <is>
-          <t>2026-07-20T19:59:23+09:00</t>
+          <t>2026-07-22T09:00:00+09:00</t>
         </is>
       </c>
       <c r="N30" s="60" t="inlineStr">
@@ -3222,72 +3222,72 @@
       </c>
       <c r="O30" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: AIクラスターの展開</t>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: ポリオ根絶に関する研究</t>
         </is>
       </c>
     </row>
     <row r="31" ht="42" customHeight="1">
       <c r="A31" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T21:02:36+09:00</t>
         </is>
       </c>
       <c r="B31" s="75" t="inlineStr">
         <is>
-          <t>2026-07-17T18:42:47Z</t>
+          <t>2026-07-21T22:35:45Z</t>
         </is>
       </c>
       <c r="C31" s="60" t="inlineStr">
         <is>
-          <t>EU &amp; Europe</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D31" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E31" s="60" t="inlineStr">
         <is>
-          <t>Fusion Energy</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="F31" s="76" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G31" s="60" t="inlineStr">
         <is>
-          <t>Industry Association</t>
+          <t>Official Company</t>
         </is>
       </c>
       <c r="H31" s="60" t="inlineStr">
         <is>
-          <t>Fusion Industry Association</t>
+          <t>NVIDIA Blog</t>
         </is>
       </c>
       <c r="I31" s="60" t="inlineStr">
         <is>
-          <t>国際法専門家グループ、EUの核融合競争優位性確保の必要性に関する論文を発表</t>
+          <t>フォートワースにて：WistronがNVIDIA AIシステムを生産するための先進的製造工場を開設</t>
         </is>
       </c>
       <c r="J31" s="60" t="inlineStr">
         <is>
-          <t>国際法専門家グループがEUの核融合エネルギーに関する競争優位性を確保する必要性を論じた。</t>
+          <t>Wistronがテキサス州フォートワースに324,000平方フィートの製造施設を開設し、AIシステムのためのスーパーチップを生産する。</t>
         </is>
       </c>
       <c r="K31" s="60" t="inlineStr">
         <is>
-          <t>https://www.fusionindustryassociation.org/international-legal-expert-group-publish-paper-on-the-need-for-the-eu-to-secure-its-competitive-fusion-advantage/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=international-legal-expert-group-publish-paper-on-the-need-for-the-eu-to-secure-its-competitive-fusion-advantage</t>
+          <t>https://blogs.nvidia.com/blog/wistron-manufacturing-texas/</t>
         </is>
       </c>
       <c r="L31" s="60" t="inlineStr">
         <is>
-          <t>7ef6110ab078602757409abf</t>
+          <t>21f1e1f3e19b1a5bf0af3cb7</t>
         </is>
       </c>
       <c r="M31" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-22T07:35:45+09:00</t>
         </is>
       </c>
       <c r="N31" s="60" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="O31" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: Regulation &amp; Governance / 学術区分: News &amp; Official Release / 焦点: EUの核融合エネルギーに関する規制とガバナンス</t>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: NVIDIA AIシステムの製造</t>
         </is>
       </c>
     </row>
@@ -3309,7 +3309,7 @@
       </c>
       <c r="B32" s="75" t="inlineStr">
         <is>
-          <t>2026-07-17T15:00:03Z</t>
+          <t>2026-07-21T15:05:11Z</t>
         </is>
       </c>
       <c r="C32" s="60" t="inlineStr">
@@ -3324,7 +3324,7 @@
       </c>
       <c r="E32" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Semiconductors &amp; Telecom</t>
         </is>
       </c>
       <c r="F32" s="76" t="n">
@@ -3342,27 +3342,27 @@
       </c>
       <c r="I32" s="60" t="inlineStr">
         <is>
-          <t>AI研究資源に関するガイダンス</t>
+          <t>固定通信近代化憲章に関する政策文書</t>
         </is>
       </c>
       <c r="J32" s="60" t="inlineStr">
         <is>
-          <t>AI研究資源（AIRR）は、研究者や産業にAI専門の計算能力を提供するスーパーコンピュータのスイートです。</t>
+          <t>通信事業者が現在および将来の固定通信近代化を実施する際に従うべき手順を示した文書。</t>
         </is>
       </c>
       <c r="K32" s="60" t="inlineStr">
         <is>
-          <t>https://www.gov.uk/government/publications/ai-research-resource</t>
+          <t>https://www.gov.uk/government/publications/fixed-telecoms-modernisation-charter</t>
         </is>
       </c>
       <c r="L32" s="60" t="inlineStr">
         <is>
-          <t>579a0b7ad2d471608fff5049</t>
+          <t>d5e4431b57fcb4b6271f6c72</t>
         </is>
       </c>
       <c r="M32" s="75" t="inlineStr">
         <is>
-          <t>2026-07-18T00:00:03+09:00</t>
+          <t>2026-07-22T00:05:11+09:00</t>
         </is>
       </c>
       <c r="N32" s="60" t="inlineStr">
@@ -3372,19 +3372,19 @@
       </c>
       <c r="O32" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: AI研究資源（AIRR）</t>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: 固定通信の近代化手順</t>
         </is>
       </c>
     </row>
     <row r="33" ht="42" customHeight="1">
       <c r="A33" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T21:45:54+09:00</t>
+          <t>2026-07-26T21:02:36+09:00</t>
         </is>
       </c>
       <c r="B33" s="75" t="inlineStr">
         <is>
-          <t>2026-07-17T14:48:00Z</t>
+          <t>2026-07-21T15:05:07Z</t>
         </is>
       </c>
       <c r="C33" s="60" t="inlineStr">
@@ -3394,46 +3394,50 @@
       </c>
       <c r="D33" s="60" t="inlineStr">
         <is>
-          <t>European Patent Organisation</t>
-        </is>
-      </c>
-      <c r="E33" s="60" t="inlineStr"/>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="E33" s="60" t="inlineStr">
+        <is>
+          <t>Semiconductors &amp; Telecom</t>
+        </is>
+      </c>
       <c r="F33" s="76" t="n">
         <v>3</v>
       </c>
       <c r="G33" s="60" t="inlineStr">
         <is>
-          <t>Intergovernmental</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H33" s="60" t="inlineStr">
         <is>
-          <t>European Patent Office News</t>
+          <t>UK DSIT</t>
         </is>
       </c>
       <c r="I33" s="60" t="inlineStr">
         <is>
-          <t>技術革新を加速するための特許と標準</t>
+          <t>通信近代化：重要国家インフラ憲章に関する政策文書</t>
         </is>
       </c>
       <c r="J33" s="60" t="inlineStr">
         <is>
-          <t>特許と標準が技術革新を加速するための重要な要素であることについての情報。</t>
+          <t>通信事業者が通信近代化中に重要国家インフラを保護するためのアプローチを示した文書。</t>
         </is>
       </c>
       <c r="K33" s="60" t="inlineStr">
         <is>
-          <t>https://epo.org/en/about-us/observatory-patents-and-technology/policy-and-funding/patents-and-standards</t>
+          <t>https://www.gov.uk/government/publications/telecoms-modernisation-critical-national-infrastructure-charter</t>
         </is>
       </c>
       <c r="L33" s="60" t="inlineStr">
         <is>
-          <t>a0d096f59b7771ee7e91da7b</t>
+          <t>aafa3a246656ccda64dd93c4</t>
         </is>
       </c>
       <c r="M33" s="75" t="inlineStr">
         <is>
-          <t>2026-07-17T23:48:00+09:00</t>
+          <t>2026-07-22T00:05:07+09:00</t>
         </is>
       </c>
       <c r="N33" s="60" t="inlineStr">
@@ -3443,19 +3447,19 @@
       </c>
       <c r="O33" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: Patents &amp; Intellectual Property / 学術区分: News &amp; Official Release / 焦点: 技術革新を加速するための特許と標準 / Historical backfill from an allowlisted source.</t>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: 重要国家インフラの保護方針</t>
         </is>
       </c>
     </row>
     <row r="34" ht="42" customHeight="1">
       <c r="A34" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T21:02:36+09:00</t>
+          <t>2026-07-26T18:56:03+09:00</t>
         </is>
       </c>
       <c r="B34" s="75" t="inlineStr">
         <is>
-          <t>2026-07-17T13:42:16Z</t>
+          <t>2026-07-21T14:48:28Z</t>
         </is>
       </c>
       <c r="C34" s="60" t="inlineStr">
@@ -3465,46 +3469,50 @@
       </c>
       <c r="D34" s="60" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="E34" s="60" t="inlineStr"/>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E34" s="60" t="inlineStr">
+        <is>
+          <t>Fusion Energy</t>
+        </is>
+      </c>
       <c r="F34" s="76" t="n">
         <v>3</v>
       </c>
       <c r="G34" s="60" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Industry Association</t>
         </is>
       </c>
       <c r="H34" s="60" t="inlineStr">
         <is>
-          <t>UK DSIT</t>
+          <t>Fusion Industry Association</t>
         </is>
       </c>
       <c r="I34" s="60" t="inlineStr">
         <is>
-          <t>デジタルサービスの改善に関する公開書簡</t>
+          <t>FIA、核融合のためのEU資金調達の道筋を示す</t>
         </is>
       </c>
       <c r="J34" s="60" t="inlineStr">
         <is>
-          <t>業界リーダーに向けて、デジタルサービスの改善に関する公開書簡が送られた。</t>
+          <t>Fusion Industry Associationが商業核融合エネルギーのためのEU資金調達のロードマップを発表。</t>
         </is>
       </c>
       <c r="K34" s="60" t="inlineStr">
         <is>
-          <t>https://www.gov.uk/government/publications/improving-access-to-and-use-of-digital-services-open-letter-to-business-leaders</t>
+          <t>https://www.fusionindustryassociation.org/fia-outlines-eu-financing-pathway-for-fusion/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=fia-outlines-eu-financing-pathway-for-fusion</t>
         </is>
       </c>
       <c r="L34" s="60" t="inlineStr">
         <is>
-          <t>d136ac8a836994c6ce5e35c6</t>
+          <t>88af233d904d670250fa5a31</t>
         </is>
       </c>
       <c r="M34" s="75" t="inlineStr">
         <is>
-          <t>2026-07-17T22:42:16+09:00</t>
+          <t>2026-07-26T18:56:03+09:00</t>
         </is>
       </c>
       <c r="N34" s="60" t="inlineStr">
@@ -3514,7 +3522,7 @@
       </c>
       <c r="O34" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: デジタルサービスの改善</t>
+          <t>枠: Innovation Policy / 政策分野: R&amp;D Funding &amp; Tax Incentives / 学術区分: News &amp; Official Release / 焦点: EUの核融合エネルギー商業化に向けた資金調達</t>
         </is>
       </c>
     </row>
@@ -3526,60 +3534,60 @@
       </c>
       <c r="B35" s="75" t="inlineStr">
         <is>
-          <t>2026-07-17T12:00:04Z</t>
+          <t>2026-07-21T00:00:00Z</t>
         </is>
       </c>
       <c r="C35" s="60" t="inlineStr">
         <is>
-          <t>EU &amp; Europe</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D35" s="60" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="E35" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="F35" s="76" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G35" s="60" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Conference Paper</t>
         </is>
       </c>
       <c r="H35" s="60" t="inlineStr">
         <is>
-          <t>UK DSIT</t>
+          <t>OpenAlex Conference Papers</t>
         </is>
       </c>
       <c r="I35" s="60" t="inlineStr">
         <is>
-          <t>AIスーパーコンピュータホストサイト選定に関する表明</t>
+          <t>量子機械学習による心血管疾患リスク予測の向上</t>
         </is>
       </c>
       <c r="J35" s="60" t="inlineStr">
         <is>
-          <t>UKの次のAIスーパーコンピュータのホストサイト選定に関する表明が行われた。</t>
+          <t>この研究は、量子アルゴリズムを用いて心血管疾患の予測を行うモデルを探求しており、量子サポートベクターマシンや量子ニューラルネットワークを活用しています。</t>
         </is>
       </c>
       <c r="K35" s="60" t="inlineStr">
         <is>
-          <t>https://www.gov.uk/government/publications/expression-of-interest-airr-heterogeneous-supercomputer-host-site-selection</t>
+          <t>https://doi.org/10.3390/engproc2026150039</t>
         </is>
       </c>
       <c r="L35" s="60" t="inlineStr">
         <is>
-          <t>27d607577c2759c8d53f9ddf</t>
+          <t>1cd467f8ebb1388daedc245f</t>
         </is>
       </c>
       <c r="M35" s="75" t="inlineStr">
         <is>
-          <t>2026-07-17T21:00:04+09:00</t>
+          <t>2026-07-21T09:00:00+09:00</t>
         </is>
       </c>
       <c r="N35" s="60" t="inlineStr">
@@ -3589,7 +3597,7 @@
       </c>
       <c r="O35" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: AIスーパーコンピュータのホストサイト選定</t>
+          <t>枠: Technology Innovation / 学術区分: Conference Paper / 査読表示: Conference proceedings — review status varies / 焦点: 量子機械学習による心血管疾患リスク予測 / OpenAlex record; work type=conference-paper; citations=0</t>
         </is>
       </c>
     </row>
@@ -3601,56 +3609,60 @@
       </c>
       <c r="B36" s="75" t="inlineStr">
         <is>
-          <t>2026-07-17T07:59:22Z</t>
+          <t>2026-07-20T21:06:27Z</t>
         </is>
       </c>
       <c r="C36" s="60" t="inlineStr">
         <is>
-          <t>EU &amp; Europe</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D36" s="60" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="E36" s="60" t="inlineStr"/>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E36" s="60" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence</t>
+        </is>
+      </c>
       <c r="F36" s="76" t="n">
         <v>3</v>
       </c>
       <c r="G36" s="60" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Policy Institute</t>
         </is>
       </c>
       <c r="H36" s="60" t="inlineStr">
         <is>
-          <t>UK DSIT</t>
+          <t>Brookings TechTank</t>
         </is>
       </c>
       <c r="I36" s="60" t="inlineStr">
         <is>
-          <t>子供のオンライン保護に関する新ルール</t>
+          <t>AIの借りた専門知識に対処する教育と研究政策</t>
         </is>
       </c>
       <c r="J36" s="60" t="inlineStr">
         <is>
-          <t>UK政府が16歳未満の子供に対するソーシャルメディア禁止を発表した。</t>
+          <t>教育政策が短期的な生産性と長期的な認知発展の間の緊張にどのように対応すべきかについて論じています。</t>
         </is>
       </c>
       <c r="K36" s="60" t="inlineStr">
         <is>
-          <t>https://www.gov.uk/government/publications/fact-sheet-new-rules-to-protect-children-online</t>
+          <t>https://brookings.edu/articles/repaying-the-inheritance-how-education-and-research-policy-can-address-ais-borrowed-expertise</t>
         </is>
       </c>
       <c r="L36" s="60" t="inlineStr">
         <is>
-          <t>371ff53aa8f9007fcb1ddddf</t>
+          <t>42183313e1c951c0483c0d62</t>
         </is>
       </c>
       <c r="M36" s="75" t="inlineStr">
         <is>
-          <t>2026-07-17T16:59:22+09:00</t>
+          <t>2026-07-21T06:06:27+09:00</t>
         </is>
       </c>
       <c r="N36" s="60" t="inlineStr">
@@ -3660,7 +3672,7 @@
       </c>
       <c r="O36" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: 子供のオンライン保護に関する新ルール</t>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: AIに関する教育政策の変革 / Historical backfill from an allowlisted source.</t>
         </is>
       </c>
     </row>
@@ -3672,7 +3684,7 @@
       </c>
       <c r="B37" s="75" t="inlineStr">
         <is>
-          <t>2026-07-16T13:35:15Z</t>
+          <t>2026-07-20T15:55:00Z</t>
         </is>
       </c>
       <c r="C37" s="60" t="inlineStr">
@@ -3687,45 +3699,45 @@
       </c>
       <c r="E37" s="60" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Semiconductors &amp; Telecom</t>
         </is>
       </c>
       <c r="F37" s="76" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G37" s="60" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Major Media</t>
         </is>
       </c>
       <c r="H37" s="60" t="inlineStr">
         <is>
-          <t>DOE Office of Science News</t>
+          <t>IEEE Spectrum</t>
         </is>
       </c>
       <c r="I37" s="60" t="inlineStr">
         <is>
-          <t>ノイズを消す：DOEが次世代量子情報科学を支える国内シリコンとゲルマニウムイソトープ供給のブレークスルーを発表</t>
+          <t>先進半導体故障解析のためのSEMガイド低電圧FIB仕上げ</t>
         </is>
       </c>
       <c r="J37" s="60" t="inlineStr">
         <is>
-          <t>DOEが、次世代量子情報科学を加速するために、商業ソースよりも100倍以上の純度を持つイソトープを生産する成果を発表した。</t>
+          <t>ZEISS Crossbeam 750 FIBSEMが先進的な半導体故障解析の新しい基準を設定する方法について説明しています。</t>
         </is>
       </c>
       <c r="K37" s="60" t="inlineStr">
         <is>
-          <t>https://www.energy.gov/science/articles/silencing-noise-doe-unveils-breakthrough-domestic-silicon-and-germanium-isotope</t>
+          <t>https://event.on24.com/wcc/r/5418459/287E3D5B99470D34C830D69A24B3B207</t>
         </is>
       </c>
       <c r="L37" s="60" t="inlineStr">
         <is>
-          <t>17ffa424cf814d722a951c64</t>
+          <t>73d0028e337a76c2cd00f1bc</t>
         </is>
       </c>
       <c r="M37" s="75" t="inlineStr">
         <is>
-          <t>2026-07-16T22:35:15+09:00</t>
+          <t>2026-07-21T00:55:00+09:00</t>
         </is>
       </c>
       <c r="N37" s="60" t="inlineStr">
@@ -3735,7 +3747,7 @@
       </c>
       <c r="O37" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation | Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: 量子情報科学におけるイソトープ供給</t>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: 先進半導体の故障解析技術</t>
         </is>
       </c>
     </row>
@@ -3747,7 +3759,7 @@
       </c>
       <c r="B38" s="75" t="inlineStr">
         <is>
-          <t>2026-07-15T23:00:54Z</t>
+          <t>2026-07-20T15:00:53Z</t>
         </is>
       </c>
       <c r="C38" s="60" t="inlineStr">
@@ -3780,27 +3792,27 @@
       </c>
       <c r="I38" s="60" t="inlineStr">
         <is>
-          <t>NVIDIAがロボティクスとエッジAIを進展させる新しいJetson Thorコンピュータを発表</t>
+          <t>SIGGRAPHでNVIDIAがエージェントAIと物理AIでグラフィックスとシミュレーションを進展</t>
         </is>
       </c>
       <c r="J38" s="60" t="inlineStr">
         <is>
-          <t>NVIDIAが新しいJetson Thorコンピュータを発表し、一般向けロボットとエッジAIの需要に応える。</t>
+          <t>NVIDIAはSIGGRAPHで、オープンモデルからリアルタイムシミュレーションまで、AIとグラフィックスの革新がメディア、コンテンツ制作、ロボティクスを変革していることを発表した。</t>
         </is>
       </c>
       <c r="K38" s="60" t="inlineStr">
         <is>
-          <t>https://blogs.nvidia.com/blog/jetson-thor-robotics-edge-ai-agent/</t>
+          <t>https://blogs.nvidia.com/blog/siggraph-news-2026/</t>
         </is>
       </c>
       <c r="L38" s="60" t="inlineStr">
         <is>
-          <t>85f482f3f904d00f68946a80</t>
+          <t>70c1acaa81ba6cd1c84a673d</t>
         </is>
       </c>
       <c r="M38" s="75" t="inlineStr">
         <is>
-          <t>2026-07-16T08:00:54+09:00</t>
+          <t>2026-07-21T00:00:53+09:00</t>
         </is>
       </c>
       <c r="N38" s="60" t="inlineStr">
@@ -3810,7 +3822,7 @@
       </c>
       <c r="O38" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: AIスーパコンピュータモジュール</t>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: エージェントAIと物理AIの進展</t>
         </is>
       </c>
     </row>
@@ -3822,22 +3834,22 @@
       </c>
       <c r="B39" s="75" t="inlineStr">
         <is>
-          <t>2026-07-15T10:00:00Z</t>
+          <t>2026-07-20T13:30:06Z</t>
         </is>
       </c>
       <c r="C39" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="D39" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="E39" s="60" t="inlineStr">
         <is>
-          <t>Healthcare | Artificial Intelligence</t>
+          <t>Artificial Intelligence | Semiconductors &amp; Telecom</t>
         </is>
       </c>
       <c r="F39" s="76" t="n">
@@ -3845,37 +3857,37 @@
       </c>
       <c r="G39" s="60" t="inlineStr">
         <is>
-          <t>Official Company</t>
+          <t>Major Media</t>
         </is>
       </c>
       <c r="H39" s="60" t="inlineStr">
         <is>
-          <t>OpenAI News</t>
+          <t>South China Morning Post Technology</t>
         </is>
       </c>
       <c r="I39" s="60" t="inlineStr">
         <is>
-          <t>Penda HealthとのAI臨床コパイロットの開発</t>
+          <t>トークン経済からタスク経済へ？SenseTimeがAIの商業化に賭ける</t>
         </is>
       </c>
       <c r="J39" s="60" t="inlineStr">
         <is>
-          <t>OpenAIとPenda Healthが共同でAI臨床コパイロットを発表し、実際の使用で診断エラーを16%削減した。</t>
+          <t>中国のAI企業SenseTimeは、トークン価格の低下に伴い、AIの商業化が「トークン経済」から「タスク経済」へ移行する見込みであると述べた。</t>
         </is>
       </c>
       <c r="K39" s="60" t="inlineStr">
         <is>
-          <t>https://openai.com/index/ai-clinical-copilot-penda-health</t>
+          <t>https://www.scmp.com/tech/big-tech/article/3361242/no-longer-token-economy-sensetime-bets-task-economy-token-prices-set-drop?utm_source=rss_feed</t>
         </is>
       </c>
       <c r="L39" s="60" t="inlineStr">
         <is>
-          <t>85bbe066139c673fbb76100c</t>
+          <t>cd5b1ea310d8a65d00ad1ad9</t>
         </is>
       </c>
       <c r="M39" s="75" t="inlineStr">
         <is>
-          <t>2026-07-15T19:00:00+09:00</t>
+          <t>2026-07-20T22:30:06+09:00</t>
         </is>
       </c>
       <c r="N39" s="60" t="inlineStr">
@@ -3885,7 +3897,7 @@
       </c>
       <c r="O39" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: AI臨床コパイロット / Historical backfill from an allowlisted source.</t>
+          <t>枠: Technology Innovation | Innovation Policy / 政策分野: Patents &amp; Intellectual Property / 学術区分: News &amp; Official Release / 焦点: AIの商業化の移行</t>
         </is>
       </c>
     </row>
@@ -3897,17 +3909,17 @@
       </c>
       <c r="B40" s="75" t="inlineStr">
         <is>
-          <t>2026-07-14T16:00:08Z</t>
+          <t>2026-07-20T11:29:00Z</t>
         </is>
       </c>
       <c r="C40" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>EU &amp; Europe</t>
         </is>
       </c>
       <c r="D40" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="E40" s="60" t="inlineStr"/>
@@ -3921,32 +3933,32 @@
       </c>
       <c r="H40" s="60" t="inlineStr">
         <is>
-          <t>National Science Foundation News</t>
+          <t>UK DSIT</t>
         </is>
       </c>
       <c r="I40" s="60" t="inlineStr">
         <is>
-          <t>NSFが全国の研究、雇用、経済成長を促進するために12の新しい地域イノベーションエンジンを授与</t>
+          <t>透明性データ：契約されたおよび建設された施設、プロジェクトギガビット契約</t>
         </is>
       </c>
       <c r="J40" s="60" t="inlineStr">
         <is>
-          <t>米国科学財団は、全国の20州にわたる12のチームに新しいNSF地域イノベーションエンジンの助成を発表した。これにより、イノベーションクラスターの構築とスケールアップを目指す。</t>
+          <t>デジタルUKがプロジェクトギガビット契約に基づく契約状況を報告しています。</t>
         </is>
       </c>
       <c r="K40" s="60" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/news/nsf-awards-12-new-regional-innovation-engines-fuel-research</t>
+          <t>https://www.gov.uk/government/publications/premises-contracted-and-built-project-gigabit-contracts</t>
         </is>
       </c>
       <c r="L40" s="60" t="inlineStr">
         <is>
-          <t>de4a8c6972dcbf82c2e445b3</t>
+          <t>d643b4b81f6998869b340654</t>
         </is>
       </c>
       <c r="M40" s="75" t="inlineStr">
         <is>
-          <t>2026-07-15T01:00:08+09:00</t>
+          <t>2026-07-20T20:29:00+09:00</t>
         </is>
       </c>
       <c r="N40" s="60" t="inlineStr">
@@ -3956,7 +3968,7 @@
       </c>
       <c r="O40" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: 地域イノベーションエンジン</t>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: デジタルインフラ整備に関する国家戦略</t>
         </is>
       </c>
     </row>
@@ -3968,7 +3980,7 @@
       </c>
       <c r="B41" s="75" t="inlineStr">
         <is>
-          <t>2026-07-10T00:00:00Z</t>
+          <t>2026-07-20T10:59:23Z</t>
         </is>
       </c>
       <c r="C41" s="60" t="inlineStr">
@@ -3978,12 +3990,12 @@
       </c>
       <c r="D41" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E41" s="60" t="inlineStr">
         <is>
-          <t>Fusion Energy</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="F41" s="76" t="n">
@@ -3991,37 +4003,37 @@
       </c>
       <c r="G41" s="60" t="inlineStr">
         <is>
-          <t>Journal Article</t>
+          <t>Official Company</t>
         </is>
       </c>
       <c r="H41" s="60" t="inlineStr">
         <is>
-          <t>Nuclear Fusion</t>
+          <t>NVIDIA Blog</t>
         </is>
       </c>
       <c r="I41" s="60" t="inlineStr">
         <is>
-          <t>ST-E1核融合発電プラントのための統合物理と磁石設計</t>
+          <t>Bristol Myers Squibbがライフサイエンス業界で最も先進的なAI工場を構築</t>
         </is>
       </c>
       <c r="J41" s="60" t="inlineStr">
         <is>
-          <t>ST-E1核融合発電プラントにおける超伝導材料やトカマクの物理に関する研究が紹介されている。</t>
+          <t>Bristol Myers Squibbは、ライフサイエンス分野でのAIクラスターを拡大し、成果を上げていることを発表した。</t>
         </is>
       </c>
       <c r="K41" s="60" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1088/1741-4326/ae773b</t>
+          <t>https://blogs.nvidia.com/blog/bristol-myers-squibb-building-life-science-industrys-most-advanced-ai-factory-on-nvidia-vera-rubin/</t>
         </is>
       </c>
       <c r="L41" s="60" t="inlineStr">
         <is>
-          <t>a0ed06f7d374240814073762</t>
+          <t>b4ddc90482832cbb50579f2a</t>
         </is>
       </c>
       <c r="M41" s="75" t="inlineStr">
         <is>
-          <t>2026-07-10T09:00:00+09:00</t>
+          <t>2026-07-20T19:59:23+09:00</t>
         </is>
       </c>
       <c r="N41" s="60" t="inlineStr">
@@ -4031,7 +4043,7 @@
       </c>
       <c r="O41" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: Journal Article / 査読表示: Journal record — confirm peer review on publisher page / 掲載誌・学会: Nuclear Fusion / 焦点: 核融合発電プラントの物理と磁石設計 / OpenAlex record; work type=article; citations=9</t>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: AIクラスターの展開</t>
         </is>
       </c>
     </row>
@@ -4043,22 +4055,22 @@
       </c>
       <c r="B42" s="75" t="inlineStr">
         <is>
-          <t>2026-07-08T08:00:00Z</t>
+          <t>2026-07-20T00:00:00Z</t>
         </is>
       </c>
       <c r="C42" s="60" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D42" s="60" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="E42" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Artificial Intelligence | Healthcare</t>
         </is>
       </c>
       <c r="F42" s="76" t="n">
@@ -4066,37 +4078,37 @@
       </c>
       <c r="G42" s="60" t="inlineStr">
         <is>
-          <t>Official Company</t>
+          <t>Journal Article</t>
         </is>
       </c>
       <c r="H42" s="60" t="inlineStr">
         <is>
-          <t>Samsung Global Newsroom</t>
+          <t>Machine Intelligence Research</t>
         </is>
       </c>
       <c r="I42" s="60" t="inlineStr">
         <is>
-          <t>サムスン、次世代AIインフラ向けに最適化されたPM1763 SSDの量産を開始</t>
+          <t>M2SNet: 医療画像セグメンテーションのためのマルチスケール減算ネットワーク</t>
         </is>
       </c>
       <c r="J42" s="60" t="inlineStr">
         <is>
-          <t>サムスン電子は、次世代AIおよびHPCサーバー環境向けに最適化されたPCIe® 6.0ベースの企業向けSSD、PM1763の量産を開始した。</t>
+          <t>M2SNetは、医療画像のセグメンテーションを改善するために、異なるレベルの特徴を効果的に融合する新しい手法を提案します。</t>
         </is>
       </c>
       <c r="K42" s="60" t="inlineStr">
         <is>
-          <t>https://news.samsung.com/global/samsung-begins-mass-production-of-pm1763-ssd-optimized-for-next-generation-ai-infrastructure</t>
+          <t>https://doi.org/10.1007/s11633-026-1662-9</t>
         </is>
       </c>
       <c r="L42" s="60" t="inlineStr">
         <is>
-          <t>ffa2f59ee7918b4bbfdce082</t>
+          <t>bffca1cc322e28515452081a</t>
         </is>
       </c>
       <c r="M42" s="75" t="inlineStr">
         <is>
-          <t>2026-07-08T17:00:00+09:00</t>
+          <t>2026-07-20T09:00:00+09:00</t>
         </is>
       </c>
       <c r="N42" s="60" t="inlineStr">
@@ -4106,34 +4118,34 @@
       </c>
       <c r="O42" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: PM1763 SSD</t>
+          <t>枠: Technology Innovation / 学術区分: Journal Article / 査読表示: Journal record — confirm peer review on publisher page / 掲載誌・学会: Machine Intelligence Research / 焦点: 医療画像セグメンテーション技術 / OpenAlex record; work type=article; citations=79</t>
         </is>
       </c>
     </row>
     <row r="43" ht="42" customHeight="1">
       <c r="A43" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T21:02:36+09:00</t>
+          <t>2026-07-26T18:56:03+09:00</t>
         </is>
       </c>
       <c r="B43" s="75" t="inlineStr">
         <is>
-          <t>2026-07-07T18:00:07Z</t>
+          <t>2026-07-17T18:42:47Z</t>
         </is>
       </c>
       <c r="C43" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>EU &amp; Europe</t>
         </is>
       </c>
       <c r="D43" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="E43" s="60" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Fusion Energy</t>
         </is>
       </c>
       <c r="F43" s="76" t="n">
@@ -4141,37 +4153,37 @@
       </c>
       <c r="G43" s="60" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Industry Association</t>
         </is>
       </c>
       <c r="H43" s="60" t="inlineStr">
         <is>
-          <t>National Science Foundation News</t>
+          <t>Fusion Industry Association</t>
         </is>
       </c>
       <c r="I43" s="60" t="inlineStr">
         <is>
-          <t>NSF、実用的な量子技術を進展させるProject Triadを開始</t>
+          <t>国際法専門家グループ、EUの核融合競争優位性確保の必要性に関する論文を発表</t>
         </is>
       </c>
       <c r="J43" s="60" t="inlineStr">
         <is>
-          <t>米国国立科学財団が量子技術を統合する新たなイニシアティブ、Project Triadを発表した。</t>
+          <t>国際法専門家グループがEUの核融合エネルギーに関する競争優位性を確保する必要性を論じた。</t>
         </is>
       </c>
       <c r="K43" s="60" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/news/nsf-launches-project-triad-advance-quantum-technology-real</t>
+          <t>https://www.fusionindustryassociation.org/international-legal-expert-group-publish-paper-on-the-need-for-the-eu-to-secure-its-competitive-fusion-advantage/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=international-legal-expert-group-publish-paper-on-the-need-for-the-eu-to-secure-its-competitive-fusion-advantage</t>
         </is>
       </c>
       <c r="L43" s="60" t="inlineStr">
         <is>
-          <t>2d4a226d3ce7cc9e366e902d</t>
+          <t>7ef6110ab078602757409abf</t>
         </is>
       </c>
       <c r="M43" s="75" t="inlineStr">
         <is>
-          <t>2026-07-08T03:00:07+09:00</t>
+          <t>2026-07-26T18:56:03+09:00</t>
         </is>
       </c>
       <c r="N43" s="60" t="inlineStr">
@@ -4181,72 +4193,72 @@
       </c>
       <c r="O43" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: Project Triad</t>
+          <t>枠: Innovation Policy / 政策分野: Regulation &amp; Governance / 学術区分: News &amp; Official Release / 焦点: EUの核融合エネルギーに関する規制とガバナンス</t>
         </is>
       </c>
     </row>
     <row r="44" ht="42" customHeight="1">
       <c r="A44" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T21:45:54+09:00</t>
+          <t>2026-07-26T21:02:36+09:00</t>
         </is>
       </c>
       <c r="B44" s="75" t="inlineStr">
         <is>
-          <t>2026-06-30T00:00:00Z</t>
+          <t>2026-07-17T15:00:03Z</t>
         </is>
       </c>
       <c r="C44" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>EU &amp; Europe</t>
         </is>
       </c>
       <c r="D44" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="E44" s="60" t="inlineStr">
         <is>
-          <t>Robotics</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="F44" s="76" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G44" s="60" t="inlineStr">
         <is>
-          <t>Preprint</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H44" s="60" t="inlineStr">
         <is>
-          <t>arXiv (Cornell University)</t>
+          <t>UK DSIT</t>
         </is>
       </c>
       <c r="I44" s="60" t="inlineStr">
         <is>
-          <t>CoDex: デモなしでの機能的操作の学習</t>
+          <t>AI研究資源に関するガイダンス</t>
         </is>
       </c>
       <c r="J44" s="60" t="inlineStr">
         <is>
-          <t>デモなしで機能的操作を学習するための新しいアプローチが提案されている。</t>
+          <t>AI研究資源（AIRR）は、研究者や産業にAI専門の計算能力を提供するスーパーコンピュータのスイートです。</t>
         </is>
       </c>
       <c r="K44" s="60" t="inlineStr">
         <is>
-          <t>https://openalex.org/W7167154222</t>
+          <t>https://www.gov.uk/government/publications/ai-research-resource</t>
         </is>
       </c>
       <c r="L44" s="60" t="inlineStr">
         <is>
-          <t>35d402b402a9608c13756e83</t>
+          <t>579a0b7ad2d471608fff5049</t>
         </is>
       </c>
       <c r="M44" s="75" t="inlineStr">
         <is>
-          <t>2026-06-30T09:00:00+09:00</t>
+          <t>2026-07-18T00:00:03+09:00</t>
         </is>
       </c>
       <c r="N44" s="60" t="inlineStr">
@@ -4256,72 +4268,68 @@
       </c>
       <c r="O44" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: Preprint / 査読表示: Not peer reviewed / 掲載誌・学会: arXiv (Cornell University) / 焦点: ロボット操作と学習に関する研究 / OpenAlex record; work type=preprint; citations=0</t>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: AI研究資源（AIRR）</t>
         </is>
       </c>
     </row>
     <row r="45" ht="42" customHeight="1">
       <c r="A45" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T21:02:36+09:00</t>
+          <t>2026-07-26T21:45:54+09:00</t>
         </is>
       </c>
       <c r="B45" s="75" t="inlineStr">
         <is>
-          <t>2026-06-29T21:14:22Z</t>
+          <t>2026-07-17T14:48:00Z</t>
         </is>
       </c>
       <c r="C45" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>EU &amp; Europe</t>
         </is>
       </c>
       <c r="D45" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E45" s="60" t="inlineStr">
-        <is>
-          <t>Artificial Intelligence</t>
-        </is>
-      </c>
+          <t>European Patent Organisation</t>
+        </is>
+      </c>
+      <c r="E45" s="60" t="inlineStr"/>
       <c r="F45" s="76" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G45" s="60" t="inlineStr">
         <is>
-          <t>Official Company</t>
+          <t>Intergovernmental</t>
         </is>
       </c>
       <c r="H45" s="60" t="inlineStr">
         <is>
-          <t>Microsoft Research</t>
+          <t>European Patent Office News</t>
         </is>
       </c>
       <c r="I45" s="60" t="inlineStr">
         <is>
-          <t>Memora: 抽象と特異性のバランスを取る調和的メモリ表現</t>
+          <t>技術革新を加速するための特許と標準</t>
         </is>
       </c>
       <c r="J45" s="60" t="inlineStr">
         <is>
-          <t>AIエージェントが過去の会話を記憶できない問題を解決するために、Memoraがスケーラブルなメモリシステムを提案した。</t>
+          <t>特許と標準が技術革新を加速するための重要な要素であることについての情報。</t>
         </is>
       </c>
       <c r="K45" s="60" t="inlineStr">
         <is>
-          <t>https://www.microsoft.com/en-us/research/blog/memora-a-harmonic-memory-representation-balancing-abstraction-and-specificity/</t>
+          <t>https://epo.org/en/about-us/observatory-patents-and-technology/policy-and-funding/patents-and-standards</t>
         </is>
       </c>
       <c r="L45" s="60" t="inlineStr">
         <is>
-          <t>6c035ef4d4202a4874e60b97</t>
+          <t>a0d096f59b7771ee7e91da7b</t>
         </is>
       </c>
       <c r="M45" s="75" t="inlineStr">
         <is>
-          <t>2026-06-30T06:14:22+09:00</t>
+          <t>2026-07-17T23:48:00+09:00</t>
         </is>
       </c>
       <c r="N45" s="60" t="inlineStr">
@@ -4331,72 +4339,68 @@
       </c>
       <c r="O45" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: AIメモリシステム</t>
+          <t>枠: Innovation Policy / 政策分野: Patents &amp; Intellectual Property / 学術区分: News &amp; Official Release / 焦点: 技術革新を加速するための特許と標準 / Historical backfill from an allowlisted source.</t>
         </is>
       </c>
     </row>
     <row r="46" ht="42" customHeight="1">
       <c r="A46" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T21:45:54+09:00</t>
+          <t>2026-07-26T21:02:36+09:00</t>
         </is>
       </c>
       <c r="B46" s="75" t="inlineStr">
         <is>
-          <t>2026-06-29T00:00:00Z</t>
+          <t>2026-07-17T13:42:16Z</t>
         </is>
       </c>
       <c r="C46" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>EU &amp; Europe</t>
         </is>
       </c>
       <c r="D46" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="E46" s="60" t="inlineStr">
-        <is>
-          <t>Fusion Energy</t>
-        </is>
-      </c>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="E46" s="60" t="inlineStr"/>
       <c r="F46" s="76" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G46" s="60" t="inlineStr">
         <is>
-          <t>Preprint</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H46" s="60" t="inlineStr">
         <is>
-          <t>arXiv (Cornell University)</t>
+          <t>UK DSIT</t>
         </is>
       </c>
       <c r="I46" s="60" t="inlineStr">
         <is>
-          <t>トロイダル中性流を利用したダイバータ粒子排出の強化</t>
+          <t>デジタルサービスの改善に関する公開書簡</t>
         </is>
       </c>
       <c r="J46" s="60" t="inlineStr">
         <is>
-          <t>核融合研究におけるトロイダル中性流の利用に関する研究が発表された。</t>
+          <t>業界リーダーに向けて、デジタルサービスの改善に関する公開書簡が送られた。</t>
         </is>
       </c>
       <c r="K46" s="60" t="inlineStr">
         <is>
-          <t>https://openalex.org/W7166900160</t>
+          <t>https://www.gov.uk/government/publications/improving-access-to-and-use-of-digital-services-open-letter-to-business-leaders</t>
         </is>
       </c>
       <c r="L46" s="60" t="inlineStr">
         <is>
-          <t>c0f8dfb2d641935c085b9cd5</t>
+          <t>d136ac8a836994c6ce5e35c6</t>
         </is>
       </c>
       <c r="M46" s="75" t="inlineStr">
         <is>
-          <t>2026-06-29T09:00:00+09:00</t>
+          <t>2026-07-17T22:42:16+09:00</t>
         </is>
       </c>
       <c r="N46" s="60" t="inlineStr">
@@ -4406,72 +4410,72 @@
       </c>
       <c r="O46" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: Preprint / 査読表示: Not peer reviewed / 掲載誌・学会: arXiv (Cornell University) / 焦点: 核融合材料と技術 / OpenAlex record; work type=preprint; citations=0</t>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: デジタルサービスの改善</t>
         </is>
       </c>
     </row>
     <row r="47" ht="42" customHeight="1">
       <c r="A47" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T21:45:54+09:00</t>
+          <t>2026-07-26T21:02:36+09:00</t>
         </is>
       </c>
       <c r="B47" s="75" t="inlineStr">
         <is>
-          <t>2026-06-29T00:00:00Z</t>
+          <t>2026-07-17T12:00:04Z</t>
         </is>
       </c>
       <c r="C47" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>EU &amp; Europe</t>
         </is>
       </c>
       <c r="D47" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="E47" s="60" t="inlineStr">
         <is>
-          <t>Fusion Energy | Quantum</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="F47" s="76" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G47" s="60" t="inlineStr">
         <is>
-          <t>Preprint</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H47" s="60" t="inlineStr">
         <is>
-          <t>arXiv (Cornell University)</t>
+          <t>UK DSIT</t>
         </is>
       </c>
       <c r="I47" s="60" t="inlineStr">
         <is>
-          <t>核融合ブランケット溶融塩における量子計算</t>
+          <t>AIスーパーコンピュータホストサイト選定に関する表明</t>
         </is>
       </c>
       <c r="J47" s="60" t="inlineStr">
         <is>
-          <t>核融合ブランケットに関連する量子計算に関する研究が発表された。</t>
+          <t>UKの次のAIスーパーコンピュータのホストサイト選定に関する表明が行われた。</t>
         </is>
       </c>
       <c r="K47" s="60" t="inlineStr">
         <is>
-          <t>https://openalex.org/W7166900467</t>
+          <t>https://www.gov.uk/government/publications/expression-of-interest-airr-heterogeneous-supercomputer-host-site-selection</t>
         </is>
       </c>
       <c r="L47" s="60" t="inlineStr">
         <is>
-          <t>a13bde138787eb63bed73f80</t>
+          <t>27d607577c2759c8d53f9ddf</t>
         </is>
       </c>
       <c r="M47" s="75" t="inlineStr">
         <is>
-          <t>2026-06-29T09:00:00+09:00</t>
+          <t>2026-07-17T21:00:04+09:00</t>
         </is>
       </c>
       <c r="N47" s="60" t="inlineStr">
@@ -4481,7 +4485,7 @@
       </c>
       <c r="O47" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: Preprint / 査読表示: Not peer reviewed / 掲載誌・学会: arXiv (Cornell University) / 焦点: 核融合ブランケットと量子計算 / OpenAlex record; work type=preprint; citations=0</t>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: AIスーパーコンピュータのホストサイト選定</t>
         </is>
       </c>
     </row>
@@ -4493,22 +4497,22 @@
       </c>
       <c r="B48" s="75" t="inlineStr">
         <is>
-          <t>2026-06-26T04:47:39Z</t>
+          <t>2026-07-17T07:59:22Z</t>
         </is>
       </c>
       <c r="C48" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>EU &amp; Europe</t>
         </is>
       </c>
       <c r="D48" s="60" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="E48" s="60" t="inlineStr"/>
       <c r="F48" s="76" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G48" s="60" t="inlineStr">
         <is>
@@ -4517,32 +4521,32 @@
       </c>
       <c r="H48" s="60" t="inlineStr">
         <is>
-          <t>NISTEP Updates</t>
+          <t>UK DSIT</t>
         </is>
       </c>
       <c r="I48" s="60" t="inlineStr">
         <is>
-          <t>研究文化をめぐる対話と展開に関する資料公開</t>
+          <t>子供のオンライン保護に関する新ルール</t>
         </is>
       </c>
       <c r="J48" s="60" t="inlineStr">
         <is>
-          <t>文部科学省が研究者対象のウェルビーイングと研究文化に関する全国調査の準備を進めています。</t>
+          <t>UK政府が16歳未満の子供に対するソーシャルメディア禁止を発表した。</t>
         </is>
       </c>
       <c r="K48" s="60" t="inlineStr">
         <is>
-          <t>https://www.nistep.go.jp/archives/63398/</t>
+          <t>https://www.gov.uk/government/publications/fact-sheet-new-rules-to-protect-children-online</t>
         </is>
       </c>
       <c r="L48" s="60" t="inlineStr">
         <is>
-          <t>ff67a3172cc526b012791921</t>
+          <t>371ff53aa8f9007fcb1ddddf</t>
         </is>
       </c>
       <c r="M48" s="75" t="inlineStr">
         <is>
-          <t>2026-06-26T13:47:39+09:00</t>
+          <t>2026-07-17T16:59:22+09:00</t>
         </is>
       </c>
       <c r="N48" s="60" t="inlineStr">
@@ -4552,7 +4556,7 @@
       </c>
       <c r="O48" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: 研究者のウェルビーイングと研究文化</t>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: 子供のオンライン保護に関する新ルール</t>
         </is>
       </c>
     </row>
@@ -4564,22 +4568,26 @@
       </c>
       <c r="B49" s="75" t="inlineStr">
         <is>
-          <t>2026-06-26T01:30:26Z</t>
+          <t>2026-07-16T13:35:15Z</t>
         </is>
       </c>
       <c r="C49" s="60" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D49" s="60" t="inlineStr">
         <is>
-          <t>Japan</t>
-        </is>
-      </c>
-      <c r="E49" s="60" t="inlineStr"/>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E49" s="60" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
       <c r="F49" s="76" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G49" s="60" t="inlineStr">
         <is>
@@ -4588,32 +4596,32 @@
       </c>
       <c r="H49" s="60" t="inlineStr">
         <is>
-          <t>NISTEP Updates</t>
+          <t>DOE Office of Science News</t>
         </is>
       </c>
       <c r="I49" s="60" t="inlineStr">
         <is>
-          <t>親子企業間の資源再配分と特許活動の特性</t>
+          <t>ノイズを消す：DOEが次世代量子情報科学を支える国内シリコンとゲルマニウムイソトープ供給のブレークスルーを発表</t>
         </is>
       </c>
       <c r="J49" s="60" t="inlineStr">
         <is>
-          <t>親子企業間での研究開発資源の移動に関する特許活動の特性についての実証分析が行われました。</t>
+          <t>DOEが、次世代量子情報科学を加速するために、商業ソースよりも100倍以上の純度を持つイソトープを生産する成果を発表した。</t>
         </is>
       </c>
       <c r="K49" s="60" t="inlineStr">
         <is>
-          <t>https://www.nistep.go.jp/archives/63333/</t>
+          <t>https://www.energy.gov/science/articles/silencing-noise-doe-unveils-breakthrough-domestic-silicon-and-germanium-isotope</t>
         </is>
       </c>
       <c r="L49" s="60" t="inlineStr">
         <is>
-          <t>25352f245236dac75576baa7</t>
+          <t>17ffa424cf814d722a951c64</t>
         </is>
       </c>
       <c r="M49" s="75" t="inlineStr">
         <is>
-          <t>2026-06-26T10:30:26+09:00</t>
+          <t>2026-07-16T22:35:15+09:00</t>
         </is>
       </c>
       <c r="N49" s="60" t="inlineStr">
@@ -4623,7 +4631,7 @@
       </c>
       <c r="O49" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy | Patents &amp; Intellectual Property / 学術区分: News &amp; Official Release / 焦点: 親子企業間の資源再配分と特許活動</t>
+          <t>枠: Technology Innovation | Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: 量子情報科学におけるイソトープ供給</t>
         </is>
       </c>
     </row>
@@ -4635,56 +4643,60 @@
       </c>
       <c r="B50" s="75" t="inlineStr">
         <is>
-          <t>2026-06-25T05:26:14Z</t>
+          <t>2026-07-15T23:00:54Z</t>
         </is>
       </c>
       <c r="C50" s="60" t="inlineStr">
         <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="D50" s="60" t="inlineStr">
+        <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="D50" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E50" s="60" t="inlineStr"/>
+      <c r="E50" s="60" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence | Robotics</t>
+        </is>
+      </c>
       <c r="F50" s="76" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G50" s="60" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Official Company</t>
         </is>
       </c>
       <c r="H50" s="60" t="inlineStr">
         <is>
-          <t>DOE Office of Science News</t>
+          <t>NVIDIA Blog</t>
         </is>
       </c>
       <c r="I50" s="60" t="inlineStr">
         <is>
-          <t>米国エネルギー省が国内供給網を強化</t>
+          <t>NVIDIAがロボティクスとエッジAIを進展させる新しいJetson Thorコンピュータを発表</t>
         </is>
       </c>
       <c r="J50" s="60" t="inlineStr">
         <is>
-          <t>米国エネルギー省がイリジウム-192の国内生産能力を確立しました。</t>
+          <t>NVIDIAが新しいJetson Thorコンピュータを発表し、一般向けロボットとエッジAIの需要に応える。</t>
         </is>
       </c>
       <c r="K50" s="60" t="inlineStr">
         <is>
-          <t>https://www.energy.gov/science/articles/doe-strengthens-domestic-supply-chain-american-energy-and-manufacturing</t>
+          <t>https://blogs.nvidia.com/blog/jetson-thor-robotics-edge-ai-agent/</t>
         </is>
       </c>
       <c r="L50" s="60" t="inlineStr">
         <is>
-          <t>62854e5795f9fac8f0427e2f</t>
+          <t>85f482f3f904d00f68946a80</t>
         </is>
       </c>
       <c r="M50" s="75" t="inlineStr">
         <is>
-          <t>2026-06-25T14:26:14+09:00</t>
+          <t>2026-07-16T08:00:54+09:00</t>
         </is>
       </c>
       <c r="N50" s="60" t="inlineStr">
@@ -4694,7 +4706,7 @@
       </c>
       <c r="O50" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: イリジウム-192の国内生産能力</t>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: AIスーパコンピュータモジュール</t>
         </is>
       </c>
     </row>
@@ -4706,7 +4718,7 @@
       </c>
       <c r="B51" s="75" t="inlineStr">
         <is>
-          <t>2026-06-25T04:00:24Z</t>
+          <t>2026-07-15T21:00:00Z</t>
         </is>
       </c>
       <c r="C51" s="60" t="inlineStr">
@@ -4716,46 +4728,50 @@
       </c>
       <c r="D51" s="60" t="inlineStr">
         <is>
-          <t>Japan</t>
-        </is>
-      </c>
-      <c r="E51" s="60" t="inlineStr"/>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E51" s="60" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence</t>
+        </is>
+      </c>
       <c r="F51" s="76" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G51" s="60" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Policy Institute</t>
         </is>
       </c>
       <c r="H51" s="60" t="inlineStr">
         <is>
-          <t>NISTEP Updates</t>
+          <t>CSET</t>
         </is>
       </c>
       <c r="I51" s="60" t="inlineStr">
         <is>
-          <t>STI Horizon誌2026夏号の公表</t>
+          <t>GPT-Red: OpenAIが構築したモデルの安全性向上のためのAI</t>
         </is>
       </c>
       <c r="J51" s="60" t="inlineStr">
         <is>
-          <t>NISTEPが科学技術・イノベーション政策に関する情報を幅広く掲載したSTI Horizon 2026夏号を公表しました。</t>
+          <t>OpenAIが開発したGPT-Redは、大規模言語モデルの脆弱性を自動的に特定し、サイバー攻撃に対する防御を強化するためのAIです。</t>
         </is>
       </c>
       <c r="K51" s="60" t="inlineStr">
         <is>
-          <t>https://www.nistep.go.jp/archives/63155/</t>
+          <t>https://cset.georgetown.edu/article/meet-gpt-red-an-llm-super-hacker-openai-built-to-make-its-models-safer/</t>
         </is>
       </c>
       <c r="L51" s="60" t="inlineStr">
         <is>
-          <t>79d88af79ddda07d59b28e08</t>
+          <t>f64391d3daf689e78e7ac442</t>
         </is>
       </c>
       <c r="M51" s="75" t="inlineStr">
         <is>
-          <t>2026-06-25T13:00:24+09:00</t>
+          <t>2026-07-16T06:00:00+09:00</t>
         </is>
       </c>
       <c r="N51" s="60" t="inlineStr">
@@ -4765,7 +4781,7 @@
       </c>
       <c r="O51" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: 科学技術・イノベーション政策</t>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: AIの脆弱性を特定する技術</t>
         </is>
       </c>
     </row>
@@ -4777,22 +4793,22 @@
       </c>
       <c r="B52" s="75" t="inlineStr">
         <is>
-          <t>2026-06-23T14:26:00Z</t>
+          <t>2026-07-15T12:00:00Z</t>
         </is>
       </c>
       <c r="C52" s="60" t="inlineStr">
         <is>
-          <t>EU &amp; Europe</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D52" s="60" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E52" s="60" t="inlineStr">
         <is>
-          <t>Robotics</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="F52" s="76" t="n">
@@ -4800,37 +4816,37 @@
       </c>
       <c r="G52" s="60" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Official Company</t>
         </is>
       </c>
       <c r="H52" s="60" t="inlineStr">
         <is>
-          <t>UK DSIT</t>
+          <t>OpenAI News</t>
         </is>
       </c>
       <c r="I52" s="60" t="inlineStr">
         <is>
-          <t>Sellafieldの清掃を助ける新しいロボット</t>
+          <t>米国、州と連邦の行動を通じてAI安全性を推進</t>
         </is>
       </c>
       <c r="J52" s="60" t="inlineStr">
         <is>
-          <t>リモート操作された機械がSellafieldの最も危険な核廃棄物保管所に初めて送られ、清掃作業を支援している。</t>
+          <t>OpenAIは、州法が安全で民主的なAIのための国家的フレームワークを構築する「逆連邦主義」アプローチを概説しています。</t>
         </is>
       </c>
       <c r="K52" s="60" t="inlineStr">
         <is>
-          <t>https://gov.uk/government/news/the-new-robot-helping-clean-up-sellafield</t>
+          <t>https://openai.com/index/advancing-ai-safety-through-state-and-federal-action</t>
         </is>
       </c>
       <c r="L52" s="60" t="inlineStr">
         <is>
-          <t>132391c846d95677d6ca86ff</t>
+          <t>23b1197c74335456a9552d5a</t>
         </is>
       </c>
       <c r="M52" s="75" t="inlineStr">
         <is>
-          <t>2026-06-23T23:26:00+09:00</t>
+          <t>2026-07-15T21:00:00+09:00</t>
         </is>
       </c>
       <c r="N52" s="60" t="inlineStr">
@@ -4840,7 +4856,7 @@
       </c>
       <c r="O52" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: Sellafieldでのロボットの使用 / Historical backfill from an allowlisted source.</t>
+          <t>枠: Innovation Policy / 政策分野: Regulation &amp; Governance / 学術区分: News &amp; Official Release / 焦点: AIガバナンス</t>
         </is>
       </c>
     </row>
@@ -4852,60 +4868,60 @@
       </c>
       <c r="B53" s="75" t="inlineStr">
         <is>
-          <t>2026-06-23T11:43:57Z</t>
+          <t>2026-07-15T10:00:00Z</t>
         </is>
       </c>
       <c r="C53" s="60" t="inlineStr">
         <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="D53" s="60" t="inlineStr">
+        <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="D53" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
       <c r="E53" s="60" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Healthcare | Artificial Intelligence</t>
         </is>
       </c>
       <c r="F53" s="76" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G53" s="60" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Official Company</t>
         </is>
       </c>
       <c r="H53" s="60" t="inlineStr">
         <is>
-          <t>DOE Office of Science News</t>
+          <t>OpenAI News</t>
         </is>
       </c>
       <c r="I53" s="60" t="inlineStr">
         <is>
-          <t>エネルギー省、科学的に関連する耐障害量子コンピュータの創出と展開に関するイニシアティブを発表</t>
+          <t>Penda HealthとのAI臨床コパイロットの開発</t>
         </is>
       </c>
       <c r="J53" s="60" t="inlineStr">
         <is>
-          <t>米国エネルギー省が、科学的に関連する耐障害量子コンピュータを創出し展開するためのイニシアティブを発表した。</t>
+          <t>OpenAIとPenda Healthが共同でAI臨床コパイロットを発表し、実際の使用で診断エラーを16%削減した。</t>
         </is>
       </c>
       <c r="K53" s="60" t="inlineStr">
         <is>
-          <t>https://www.energy.gov/science/articles/energy-department-announces-initiative-create-and-deploy-worlds-first</t>
+          <t>https://openai.com/index/ai-clinical-copilot-penda-health</t>
         </is>
       </c>
       <c r="L53" s="60" t="inlineStr">
         <is>
-          <t>9e1d8ad5a7ac944965b9f2bd</t>
+          <t>85bbe066139c673fbb76100c</t>
         </is>
       </c>
       <c r="M53" s="75" t="inlineStr">
         <is>
-          <t>2026-06-23T20:43:57+09:00</t>
+          <t>2026-07-15T19:00:00+09:00</t>
         </is>
       </c>
       <c r="N53" s="60" t="inlineStr">
@@ -4915,7 +4931,7 @@
       </c>
       <c r="O53" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: 量子コンピュータの開発</t>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: AI臨床コパイロット / Historical backfill from an allowlisted source.</t>
         </is>
       </c>
     </row>
@@ -4927,7 +4943,7 @@
       </c>
       <c r="B54" s="75" t="inlineStr">
         <is>
-          <t>2026-06-15T15:23:31Z</t>
+          <t>2026-07-14T16:00:08Z</t>
         </is>
       </c>
       <c r="C54" s="60" t="inlineStr">
@@ -4940,13 +4956,9 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="E54" s="60" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
+      <c r="E54" s="60" t="inlineStr"/>
       <c r="F54" s="76" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G54" s="60" t="inlineStr">
         <is>
@@ -4955,32 +4967,32 @@
       </c>
       <c r="H54" s="60" t="inlineStr">
         <is>
-          <t>NIH News Releases</t>
+          <t>National Science Foundation News</t>
         </is>
       </c>
       <c r="I54" s="60" t="inlineStr">
         <is>
-          <t>研究影響を高めるための再現性向上イニシアティブ</t>
+          <t>NSFが全国の研究、雇用、経済成長を促進するために12の新しい地域イノベーションエンジンを授与</t>
         </is>
       </c>
       <c r="J54" s="60" t="inlineStr">
         <is>
-          <t>新しい生物医学研究が人間の健康に関する理解を深め、病気治療の新たな方法を提供することを目指す。独立した再現は、研究者に追加データを提供し、将来の研究プロジェクトの基盤を強化する。</t>
+          <t>米国科学財団は、全国の20州にわたる12のチームに新しいNSF地域イノベーションエンジンの助成を発表した。これにより、イノベーションクラスターの構築とスケールアップを目指す。</t>
         </is>
       </c>
       <c r="K54" s="60" t="inlineStr">
         <is>
-          <t>https://nih.gov/common-fund/common-fund-programs/replication-enhance-research-impact-initiative</t>
+          <t>https://www.nsf.gov/news/nsf-awards-12-new-regional-innovation-engines-fuel-research</t>
         </is>
       </c>
       <c r="L54" s="60" t="inlineStr">
         <is>
-          <t>1b5e51bc8d4c51589eee5027</t>
+          <t>de4a8c6972dcbf82c2e445b3</t>
         </is>
       </c>
       <c r="M54" s="75" t="inlineStr">
         <is>
-          <t>2026-06-16T00:23:31+09:00</t>
+          <t>2026-07-15T01:00:08+09:00</t>
         </is>
       </c>
       <c r="N54" s="60" t="inlineStr">
@@ -4990,7 +5002,7 @@
       </c>
       <c r="O54" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 政策分野: Patents &amp; Intellectual Property / 学術区分: News &amp; Official Release / 焦点: 生物医学研究の再現性 / Historical backfill from an allowlisted source.</t>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: 地域イノベーションエンジン</t>
         </is>
       </c>
     </row>
@@ -5002,17 +5014,17 @@
       </c>
       <c r="B55" s="75" t="inlineStr">
         <is>
-          <t>2026-06-15T00:00:00Z</t>
+          <t>2026-07-10T00:00:00Z</t>
         </is>
       </c>
       <c r="C55" s="60" t="inlineStr">
         <is>
-          <t>EU &amp; Europe</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D55" s="60" t="inlineStr">
         <is>
-          <t>International / France</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="E55" s="60" t="inlineStr">
@@ -5021,41 +5033,41 @@
         </is>
       </c>
       <c r="F55" s="76" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G55" s="60" t="inlineStr">
         <is>
-          <t>Intergovernmental</t>
+          <t>Journal Article</t>
         </is>
       </c>
       <c r="H55" s="60" t="inlineStr">
         <is>
-          <t>ITER News</t>
+          <t>Nuclear Fusion</t>
         </is>
       </c>
       <c r="I55" s="60" t="inlineStr">
         <is>
-          <t>世界中から一つのアセンブリラインへ</t>
+          <t>ST-E1核融合発電プラントの統合物理と磁石設計</t>
         </is>
       </c>
       <c r="J55" s="60" t="inlineStr">
         <is>
-          <t>ITERダイバータが新たな統合段階に入り、設計・製造の数十年を経て新しいフェーズに突入した。</t>
+          <t>ST-E1は、トカマクエナジーの商業競争力のある核融合発電プラント設計であり、ハイテクスーパコンダクターマグネットケージを特徴としています。</t>
         </is>
       </c>
       <c r="K55" s="60" t="inlineStr">
         <is>
-          <t>https://www.iter.org/node/20687/around-world-one-assembly-line</t>
+          <t>https://doi.org/10.1088/1741-4326/ae773b</t>
         </is>
       </c>
       <c r="L55" s="60" t="inlineStr">
         <is>
-          <t>ac71361e131ee1a80ac51837</t>
+          <t>a0ed06f7d374240814073762</t>
         </is>
       </c>
       <c r="M55" s="75" t="inlineStr">
         <is>
-          <t>2026-06-15T09:00:00+09:00</t>
+          <t>2026-07-10T09:00:00+09:00</t>
         </is>
       </c>
       <c r="N55" s="60" t="inlineStr">
@@ -5065,7 +5077,7 @@
       </c>
       <c r="O55" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: ITERダイバータの統合</t>
+          <t>枠: Technology Innovation / 学術区分: Journal Article / 査読表示: Journal record — confirm peer review on publisher page / 掲載誌・学会: Nuclear Fusion / 焦点: 核融合技術 / OpenAlex record; work type=article; citations=9</t>
         </is>
       </c>
     </row>
@@ -5077,60 +5089,60 @@
       </c>
       <c r="B56" s="75" t="inlineStr">
         <is>
-          <t>2026-06-15T00:00:00Z</t>
+          <t>2026-07-08T08:00:00Z</t>
         </is>
       </c>
       <c r="C56" s="60" t="inlineStr">
         <is>
-          <t>EU &amp; Europe</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="D56" s="60" t="inlineStr">
         <is>
-          <t>International / France</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="E56" s="60" t="inlineStr">
         <is>
-          <t>Fusion Energy</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="F56" s="76" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G56" s="60" t="inlineStr">
         <is>
-          <t>Intergovernmental</t>
+          <t>Official Company</t>
         </is>
       </c>
       <c r="H56" s="60" t="inlineStr">
         <is>
-          <t>ITER News</t>
+          <t>Samsung Global Newsroom</t>
         </is>
       </c>
       <c r="I56" s="60" t="inlineStr">
         <is>
-          <t>馬の年に先を行く</t>
+          <t>サムスン、次世代AIインフラ向けに最適化されたPM1763 SSDの量産を開始</t>
         </is>
       </c>
       <c r="J56" s="60" t="inlineStr">
         <is>
-          <t>ITERでの真空容器の組立が予定よりも早く進行中で、経験と調整の利点が示されている。</t>
+          <t>サムスン電子は、次世代AIおよびHPCサーバー環境向けに最適化されたPCIe® 6.0ベースの企業向けSSD、PM1763の量産を開始した。</t>
         </is>
       </c>
       <c r="K56" s="60" t="inlineStr">
         <is>
-          <t>https://www.iter.org/node/20687/galloping-ahead-year-horse</t>
+          <t>https://news.samsung.com/global/samsung-begins-mass-production-of-pm1763-ssd-optimized-for-next-generation-ai-infrastructure</t>
         </is>
       </c>
       <c r="L56" s="60" t="inlineStr">
         <is>
-          <t>47f993ca6a92c4175db656f6</t>
+          <t>ffa2f59ee7918b4bbfdce082</t>
         </is>
       </c>
       <c r="M56" s="75" t="inlineStr">
         <is>
-          <t>2026-06-15T09:00:00+09:00</t>
+          <t>2026-07-08T17:00:00+09:00</t>
         </is>
       </c>
       <c r="N56" s="60" t="inlineStr">
@@ -5140,7 +5152,7 @@
       </c>
       <c r="O56" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: 真空容器の組立</t>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: PM1763 SSD</t>
         </is>
       </c>
     </row>
@@ -5152,60 +5164,60 @@
       </c>
       <c r="B57" s="75" t="inlineStr">
         <is>
-          <t>2026-06-15T00:00:00Z</t>
+          <t>2026-07-07T18:00:07Z</t>
         </is>
       </c>
       <c r="C57" s="60" t="inlineStr">
         <is>
-          <t>EU &amp; Europe</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D57" s="60" t="inlineStr">
         <is>
-          <t>International / France</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E57" s="60" t="inlineStr">
         <is>
-          <t>Fusion Energy</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="F57" s="76" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G57" s="60" t="inlineStr">
         <is>
-          <t>Intergovernmental</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H57" s="60" t="inlineStr">
         <is>
-          <t>ITER News</t>
+          <t>National Science Foundation News</t>
         </is>
       </c>
       <c r="I57" s="60" t="inlineStr">
         <is>
-          <t>ロシアのクルチャトフ研究所との協定を締結</t>
+          <t>NSF、実用的な量子技術を進展させるProject Triadを開始</t>
         </is>
       </c>
       <c r="J57" s="60" t="inlineStr">
         <is>
-          <t>ITERがロシアのクルチャトフ研究所との間で科学的交流や共同研究プログラムの実施に関する協定を締結した。</t>
+          <t>米国国立科学財団が量子技術を統合する新たなイニシアティブ、Project Triadを発表した。</t>
         </is>
       </c>
       <c r="K57" s="60" t="inlineStr">
         <is>
-          <t>https://www.iter.org/node/20687/iter-signs-agreement-russias-kurchatov-institute</t>
+          <t>https://www.nsf.gov/news/nsf-launches-project-triad-advance-quantum-technology-real</t>
         </is>
       </c>
       <c r="L57" s="60" t="inlineStr">
         <is>
-          <t>bef2ae98b3b6e9a710e28c9f</t>
+          <t>2d4a226d3ce7cc9e366e902d</t>
         </is>
       </c>
       <c r="M57" s="75" t="inlineStr">
         <is>
-          <t>2026-06-15T09:00:00+09:00</t>
+          <t>2026-07-08T03:00:07+09:00</t>
         </is>
       </c>
       <c r="N57" s="60" t="inlineStr">
@@ -5215,7 +5227,7 @@
       </c>
       <c r="O57" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: ロシアのクルチャトフ研究所との協定</t>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: Project Triad</t>
         </is>
       </c>
     </row>
@@ -5227,7 +5239,7 @@
       </c>
       <c r="B58" s="75" t="inlineStr">
         <is>
-          <t>2026-06-11T17:39:29Z</t>
+          <t>2026-06-29T21:14:22Z</t>
         </is>
       </c>
       <c r="C58" s="60" t="inlineStr">
@@ -5246,7 +5258,7 @@
         </is>
       </c>
       <c r="F58" s="76" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G58" s="60" t="inlineStr">
         <is>
@@ -5255,32 +5267,32 @@
       </c>
       <c r="H58" s="60" t="inlineStr">
         <is>
-          <t>OpenAI News</t>
+          <t>Microsoft Research</t>
         </is>
       </c>
       <c r="I58" s="60" t="inlineStr">
         <is>
-          <t>特許に関する私たちのアプローチ</t>
+          <t>Memora: 抽象と特異性のバランスを取る調和的メモリ表現</t>
         </is>
       </c>
       <c r="J58" s="60" t="inlineStr">
         <is>
-          <t>OpenAIは、AIのための広範なアクセス、協力、安全性の原則にコミットしています。</t>
+          <t>AIエージェントが過去の会話を記憶できない問題を解決するために、Memoraがスケーラブルなメモリシステムを提案した。</t>
         </is>
       </c>
       <c r="K58" s="60" t="inlineStr">
         <is>
-          <t>https://openai.com/approach-to-patents</t>
+          <t>https://www.microsoft.com/en-us/research/blog/memora-a-harmonic-memory-representation-balancing-abstraction-and-specificity/</t>
         </is>
       </c>
       <c r="L58" s="60" t="inlineStr">
         <is>
-          <t>15bd5956a07021e966ca1264</t>
+          <t>6c035ef4d4202a4874e60b97</t>
         </is>
       </c>
       <c r="M58" s="75" t="inlineStr">
         <is>
-          <t>2026-06-12T02:39:29+09:00</t>
+          <t>2026-06-30T06:14:22+09:00</t>
         </is>
       </c>
       <c r="N58" s="60" t="inlineStr">
@@ -5290,7 +5302,7 @@
       </c>
       <c r="O58" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: Patents &amp; Intellectual Property / 学術区分: News &amp; Official Release / 焦点: AIに関する特許の方針 / Historical backfill from an allowlisted source.</t>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: AIメモリシステム</t>
         </is>
       </c>
     </row>
@@ -5302,7 +5314,7 @@
       </c>
       <c r="B59" s="75" t="inlineStr">
         <is>
-          <t>2026-06-09T19:00:00Z</t>
+          <t>2026-06-29T12:00:00Z</t>
         </is>
       </c>
       <c r="C59" s="60" t="inlineStr">
@@ -5317,11 +5329,11 @@
       </c>
       <c r="E59" s="60" t="inlineStr">
         <is>
-          <t>Fusion Energy</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="F59" s="76" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G59" s="60" t="inlineStr">
         <is>
@@ -5330,32 +5342,32 @@
       </c>
       <c r="H59" s="60" t="inlineStr">
         <is>
-          <t>DOE Office of Science News</t>
+          <t>NIST News</t>
         </is>
       </c>
       <c r="I59" s="60" t="inlineStr">
         <is>
-          <t>エネルギー省が核融合科学と技術のロードマップを発表</t>
+          <t>NIST、量子技術の製造を推進するセンターを設立</t>
         </is>
       </c>
       <c r="J59" s="60" t="inlineStr">
         <is>
-          <t>米国エネルギー省は、核融合エネルギーの開発と商業化を加速するための戦略を発表しました。</t>
+          <t>NISTは、量子製造工学センター（QMEC）を設立するためにSRIインターナショナルとの合意を発表した。</t>
         </is>
       </c>
       <c r="K59" s="60" t="inlineStr">
         <is>
-          <t>https://www.energy.gov/articles/energy-department-releases-finalized-fusion-science-and-technology-roadmap-accelerate</t>
+          <t>https://www.nist.gov/news-events/news/2026/06/nist-launches-center-drive-manufacture-quantum-technologies</t>
         </is>
       </c>
       <c r="L59" s="60" t="inlineStr">
         <is>
-          <t>bf24d6f8eb27dabbbe4e196e</t>
+          <t>2d90197d96166b4d1d7f7c11</t>
         </is>
       </c>
       <c r="M59" s="75" t="inlineStr">
         <is>
-          <t>2026-06-10T04:00:00+09:00</t>
+          <t>2026-06-29T21:00:00+09:00</t>
         </is>
       </c>
       <c r="N59" s="60" t="inlineStr">
@@ -5365,7 +5377,7 @@
       </c>
       <c r="O59" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy | Patents &amp; Intellectual Property / 学術区分: News &amp; Official Release / 焦点: 核融合エネルギーの商業化に向けた戦略</t>
+          <t>枠: Innovation Policy / 政策分野: Public Procurement &amp; Industrial Policy / 学術区分: News &amp; Official Release / 焦点: 量子製造工学センターの設立</t>
         </is>
       </c>
     </row>
@@ -5377,7 +5389,7 @@
       </c>
       <c r="B60" s="75" t="inlineStr">
         <is>
-          <t>2026-06-09T12:00:00Z</t>
+          <t>2026-06-26T04:47:39Z</t>
         </is>
       </c>
       <c r="C60" s="60" t="inlineStr">
@@ -5387,16 +5399,12 @@
       </c>
       <c r="D60" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E60" s="60" t="inlineStr">
-        <is>
-          <t>Artificial Intelligence</t>
-        </is>
-      </c>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="E60" s="60" t="inlineStr"/>
       <c r="F60" s="76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G60" s="60" t="inlineStr">
         <is>
@@ -5405,32 +5413,32 @@
       </c>
       <c r="H60" s="60" t="inlineStr">
         <is>
-          <t>NIST News</t>
+          <t>NISTEP Updates</t>
         </is>
       </c>
       <c r="I60" s="60" t="inlineStr">
         <is>
-          <t>NISTの数学的証明がAIシステムのセキュリティモデルへの移行を支持</t>
+          <t>研究文化をめぐる対話と展開に関する資料公開</t>
         </is>
       </c>
       <c r="J60" s="60" t="inlineStr">
         <is>
-          <t>NISTは、AIシステムのための継続的な監視と更新のセキュリティモデルへの移行を支持する数学的証明を発表しました。</t>
+          <t>文部科学省が研究者対象のウェルビーイングと研究文化に関する全国調査の準備を進めています。</t>
         </is>
       </c>
       <c r="K60" s="60" t="inlineStr">
         <is>
-          <t>https://www.nist.gov/news-events/news/2026/06/nist-mathematical-proof-supports-transition-continuous-monitor-and-update</t>
+          <t>https://www.nistep.go.jp/archives/63398/</t>
         </is>
       </c>
       <c r="L60" s="60" t="inlineStr">
         <is>
-          <t>edf1c2446b6ba41114d4bc6b</t>
+          <t>ff67a3172cc526b012791921</t>
         </is>
       </c>
       <c r="M60" s="75" t="inlineStr">
         <is>
-          <t>2026-06-09T21:00:00+09:00</t>
+          <t>2026-06-26T13:47:39+09:00</t>
         </is>
       </c>
       <c r="N60" s="60" t="inlineStr">
@@ -5440,7 +5448,7 @@
       </c>
       <c r="O60" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: Public Procurement &amp; Industrial Policy / 学術区分: News &amp; Official Release / 焦点: AIシステムのセキュリティモデル</t>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: 研究者のウェルビーイングと研究文化</t>
         </is>
       </c>
     </row>
@@ -5452,60 +5460,56 @@
       </c>
       <c r="B61" s="75" t="inlineStr">
         <is>
-          <t>2026-06-08T00:00:00Z</t>
+          <t>2026-06-26T01:30:26Z</t>
         </is>
       </c>
       <c r="C61" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="D61" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="E61" s="60" t="inlineStr">
-        <is>
-          <t>Space</t>
-        </is>
-      </c>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="E61" s="60" t="inlineStr"/>
       <c r="F61" s="76" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G61" s="60" t="inlineStr">
         <is>
-          <t>Conference Paper</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H61" s="60" t="inlineStr">
         <is>
-          <t>Proceedings of the International Conference on Automated Planning and Scheduling</t>
+          <t>NISTEP Updates</t>
         </is>
       </c>
       <c r="I61" s="60" t="inlineStr">
         <is>
-          <t>NASAの観測ミッションにおける深層強化学習</t>
+          <t>親子企業間の資源再配分と特許活動の特性</t>
         </is>
       </c>
       <c r="J61" s="60" t="inlineStr">
         <is>
-          <t>NASAのキャルサーズ地球コロナ観測ミッションにおける長期運用スケジューリングのための深層強化学習が紹介されている。</t>
+          <t>親子企業間での研究開発資源の移動に関する特許活動の特性についての実証分析が行われました。</t>
         </is>
       </c>
       <c r="K61" s="60" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1609/icaps.v36i1.42871</t>
+          <t>https://www.nistep.go.jp/archives/63333/</t>
         </is>
       </c>
       <c r="L61" s="60" t="inlineStr">
         <is>
-          <t>c180becba22f98a3320c630d</t>
+          <t>25352f245236dac75576baa7</t>
         </is>
       </c>
       <c r="M61" s="75" t="inlineStr">
         <is>
-          <t>2026-06-08T09:00:00+09:00</t>
+          <t>2026-06-26T10:30:26+09:00</t>
         </is>
       </c>
       <c r="N61" s="60" t="inlineStr">
@@ -5515,7 +5519,7 @@
       </c>
       <c r="O61" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: Conference Paper / 査読表示: Conference proceedings — review status varies / 掲載誌・学会: Proceedings of the International Conference on Automated Planning and Scheduling / 焦点: NASAの観測ミッションにおける運用スケジューリング / OpenAlex record; work type=conference-paper; citations=0</t>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy | Patents &amp; Intellectual Property / 学術区分: News &amp; Official Release / 焦点: 親子企業間の資源再配分と特許活動</t>
         </is>
       </c>
     </row>
@@ -5527,7 +5531,7 @@
       </c>
       <c r="B62" s="75" t="inlineStr">
         <is>
-          <t>2026-06-05T12:28:26Z</t>
+          <t>2026-06-25T05:26:14Z</t>
         </is>
       </c>
       <c r="C62" s="60" t="inlineStr">
@@ -5537,46 +5541,46 @@
       </c>
       <c r="D62" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E62" s="60" t="inlineStr"/>
       <c r="F62" s="76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G62" s="60" t="inlineStr">
         <is>
-          <t>Intergovernmental</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H62" s="60" t="inlineStr">
         <is>
-          <t>WHO News</t>
+          <t>DOE Office of Science News</t>
         </is>
       </c>
       <c r="I62" s="60" t="inlineStr">
         <is>
-          <t>アフリカCDCとWHOが共同でエボラ対応計画を発表</t>
+          <t>米国エネルギー省が国内供給網を強化</t>
         </is>
       </c>
       <c r="J62" s="60" t="inlineStr">
         <is>
-          <t>アフリカCDCとWHOがエボラウイルスの対応計画を発表し、5億1800万ドルの資金を目指す。</t>
+          <t>米国エネルギー省がイリジウム-192の国内生産能力を確立しました。</t>
         </is>
       </c>
       <c r="K62" s="60" t="inlineStr">
         <is>
-          <t>https://www.who.int/news/item/05-06-2026-africa-cdc-and-who-launch-joint-continental-ebola-response-plan</t>
+          <t>https://www.energy.gov/science/articles/doe-strengthens-domestic-supply-chain-american-energy-and-manufacturing</t>
         </is>
       </c>
       <c r="L62" s="60" t="inlineStr">
         <is>
-          <t>41c465a6eca3591002d781ba</t>
+          <t>62854e5795f9fac8f0427e2f</t>
         </is>
       </c>
       <c r="M62" s="75" t="inlineStr">
         <is>
-          <t>2026-06-05T21:28:26+09:00</t>
+          <t>2026-06-25T14:26:14+09:00</t>
         </is>
       </c>
       <c r="N62" s="60" t="inlineStr">
@@ -5586,7 +5590,7 @@
       </c>
       <c r="O62" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: Public Procurement &amp; Industrial Policy / 学術区分: News &amp; Official Release / 焦点: エボラウイルスに対する対応計画</t>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: イリジウム-192の国内生産能力</t>
         </is>
       </c>
     </row>
@@ -5598,7 +5602,7 @@
       </c>
       <c r="B63" s="75" t="inlineStr">
         <is>
-          <t>2026-06-04T12:00:00Z</t>
+          <t>2026-06-25T04:00:24Z</t>
         </is>
       </c>
       <c r="C63" s="60" t="inlineStr">
@@ -5608,16 +5612,12 @@
       </c>
       <c r="D63" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E63" s="60" t="inlineStr">
-        <is>
-          <t>Artificial Intelligence</t>
-        </is>
-      </c>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="E63" s="60" t="inlineStr"/>
       <c r="F63" s="76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G63" s="60" t="inlineStr">
         <is>
@@ -5626,32 +5626,32 @@
       </c>
       <c r="H63" s="60" t="inlineStr">
         <is>
-          <t>NIST News</t>
+          <t>NISTEP Updates</t>
         </is>
       </c>
       <c r="I63" s="60" t="inlineStr">
         <is>
-          <t>新しいAIモデルが火災時の避難経路を特定</t>
+          <t>STI Horizon誌2026夏号の公表</t>
         </is>
       </c>
       <c r="J63" s="60" t="inlineStr">
         <is>
-          <t>NISTが火災時に安全な避難経路を特定する新しいAIモデルを作成した。</t>
+          <t>NISTEPが科学技術・イノベーション政策に関する情報を幅広く掲載したSTI Horizon 2026夏号を公表しました。</t>
         </is>
       </c>
       <c r="K63" s="60" t="inlineStr">
         <is>
-          <t>https://www.nist.gov/news-events/news/2026/06/new-ai-model-shows-how-evacuate-fires-one-safe-step-time</t>
+          <t>https://www.nistep.go.jp/archives/63155/</t>
         </is>
       </c>
       <c r="L63" s="60" t="inlineStr">
         <is>
-          <t>434bb62e0a1e48aca17e1405</t>
+          <t>79d88af79ddda07d59b28e08</t>
         </is>
       </c>
       <c r="M63" s="75" t="inlineStr">
         <is>
-          <t>2026-06-04T21:00:00+09:00</t>
+          <t>2026-06-25T13:00:24+09:00</t>
         </is>
       </c>
       <c r="N63" s="60" t="inlineStr">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="O63" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: Public Procurement &amp; Industrial Policy / 学術区分: News &amp; Official Release / 焦点: 火災時の避難経路を特定するAIモデル</t>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: 科学技術・イノベーション政策</t>
         </is>
       </c>
     </row>
@@ -5673,22 +5673,26 @@
       </c>
       <c r="B64" s="75" t="inlineStr">
         <is>
-          <t>2026-06-04T12:00:00Z</t>
+          <t>2026-06-23T14:26:00Z</t>
         </is>
       </c>
       <c r="C64" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>EU &amp; Europe</t>
         </is>
       </c>
       <c r="D64" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E64" s="60" t="inlineStr"/>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="E64" s="60" t="inlineStr">
+        <is>
+          <t>Robotics</t>
+        </is>
+      </c>
       <c r="F64" s="76" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G64" s="60" t="inlineStr">
         <is>
@@ -5697,32 +5701,32 @@
       </c>
       <c r="H64" s="60" t="inlineStr">
         <is>
-          <t>NIST News</t>
+          <t>UK DSIT</t>
         </is>
       </c>
       <c r="I64" s="60" t="inlineStr">
         <is>
-          <t>NISTがレーザーを用いた合金の結合方法を発見</t>
+          <t>Sellafieldの清掃を助ける新しいロボット</t>
         </is>
       </c>
       <c r="J64" s="60" t="inlineStr">
         <is>
-          <t>NISTが3Dプリンティング中の金属の原子構造をリアルタイムで研究する方法を改善した。</t>
+          <t>リモート操作された機械がSellafieldの最も危険な核廃棄物保管所に初めて送られ、清掃作業を支援している。</t>
         </is>
       </c>
       <c r="K64" s="60" t="inlineStr">
         <is>
-          <t>https://www.nist.gov/news-events/news/2026/06/nist-researchers-discover-new-way-whisk-alloys-together-lasers</t>
+          <t>https://gov.uk/government/news/the-new-robot-helping-clean-up-sellafield</t>
         </is>
       </c>
       <c r="L64" s="60" t="inlineStr">
         <is>
-          <t>a03605c38ac072e4b77247db</t>
+          <t>132391c846d95677d6ca86ff</t>
         </is>
       </c>
       <c r="M64" s="75" t="inlineStr">
         <is>
-          <t>2026-06-04T21:00:00+09:00</t>
+          <t>2026-06-23T23:26:00+09:00</t>
         </is>
       </c>
       <c r="N64" s="60" t="inlineStr">
@@ -5732,7 +5736,7 @@
       </c>
       <c r="O64" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: Public Procurement &amp; Industrial Policy / 学術区分: News &amp; Official Release / 焦点: レーザーを用いた合金の結合方法</t>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: Sellafieldでのロボットの使用 / Historical backfill from an allowlisted source.</t>
         </is>
       </c>
     </row>
@@ -5744,12 +5748,12 @@
       </c>
       <c r="B65" s="75" t="inlineStr">
         <is>
-          <t>2026-06-03T03:00:33Z</t>
+          <t>2026-06-23T11:43:57Z</t>
         </is>
       </c>
       <c r="C65" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D65" s="60" t="inlineStr">
@@ -5759,45 +5763,45 @@
       </c>
       <c r="E65" s="60" t="inlineStr">
         <is>
-          <t>Semiconductors &amp; Telecom</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="F65" s="76" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G65" s="60" t="inlineStr">
         <is>
-          <t>Official Company</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H65" s="60" t="inlineStr">
         <is>
-          <t>Intel Newsroom</t>
+          <t>DOE Office of Science News</t>
         </is>
       </c>
       <c r="I65" s="60" t="inlineStr">
         <is>
-          <t>インテル、企業向けEthernet E835ネットワーク制御装置を発表</t>
+          <t>エネルギー省、科学的に関連する耐障害量子コンピュータの創出と展開に関するイニシアティブを発表</t>
         </is>
       </c>
       <c r="J65" s="60" t="inlineStr">
         <is>
-          <t>インテルは、データセンターや企業、AI、テレコムモバイルコアアプリケーション向けに高密度環境の帯域幅とスケーラビリティの要求に応えるEthernet E835ネットワーク制御装置とアダプタを発表した。</t>
+          <t>米国エネルギー省が、科学的に関連する耐障害量子コンピュータを創出し展開するためのイニシアティブを発表した。</t>
         </is>
       </c>
       <c r="K65" s="60" t="inlineStr">
         <is>
-          <t>https://newsroom.intel.com/pt/data-cente/intel-apresenta-controladores-e-adaptadores-de-rede-ethernet-e835-para-infraestruturas-corporativas-de-borda-e-telecomunicacoes</t>
+          <t>https://www.energy.gov/science/articles/energy-department-announces-initiative-create-and-deploy-worlds-first</t>
         </is>
       </c>
       <c r="L65" s="60" t="inlineStr">
         <is>
-          <t>c78a2a348fa6a57f7ff2f7c3</t>
+          <t>9e1d8ad5a7ac944965b9f2bd</t>
         </is>
       </c>
       <c r="M65" s="75" t="inlineStr">
         <is>
-          <t>2026-06-03T12:00:33+09:00</t>
+          <t>2026-06-23T20:43:57+09:00</t>
         </is>
       </c>
       <c r="N65" s="60" t="inlineStr">
@@ -5807,72 +5811,68 @@
       </c>
       <c r="O65" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: Ethernetネットワーク用の制御装置とアダプタ / Historical backfill from an allowlisted source.</t>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: 量子コンピュータの開発</t>
         </is>
       </c>
     </row>
     <row r="66" ht="42" customHeight="1">
       <c r="A66" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T21:02:36+09:00</t>
+          <t>2026-07-26T22:54:37+09:00</t>
         </is>
       </c>
       <c r="B66" s="75" t="inlineStr">
         <is>
-          <t>2026-06-01T00:00:00Z</t>
+          <t>2026-06-17T00:00:00Z</t>
         </is>
       </c>
       <c r="C66" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>EU &amp; Europe</t>
         </is>
       </c>
       <c r="D66" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="E66" s="60" t="inlineStr">
-        <is>
-          <t>Fusion Energy</t>
-        </is>
-      </c>
+          <t>European Union</t>
+        </is>
+      </c>
+      <c r="E66" s="60" t="inlineStr"/>
       <c r="F66" s="76" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G66" s="60" t="inlineStr">
         <is>
-          <t>Journal Article</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H66" s="60" t="inlineStr">
         <is>
-          <t>Journal of Plasma Physics</t>
+          <t>European Innovation Council Policy Benchmarks</t>
         </is>
       </c>
       <c r="I66" s="60" t="inlineStr">
         <is>
-          <t>ARC核融合発電所の物理的基盤の概要</t>
+          <t>EIC、14億ユーロ超の2026年ワークプログラムを改定</t>
         </is>
       </c>
       <c r="J66" s="60" t="inlineStr">
         <is>
-          <t>ARC核融合発電所に関する物理的基盤を概説した研究であり、核融合技術に関連する具体的な内容が含まれている。</t>
+          <t>欧州イノベーション会議は、総額14億ユーロ超の2026年ワークプログラムを改定した。Pathfinder、Transition、Accelerator、STEP Scale Upなどで研究から事業拡大までを支援し、防衛・デュアルユース技術も対象に加えた。</t>
         </is>
       </c>
       <c r="K66" s="60" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1017/s0022377826101706</t>
+          <t>https://eic.ec.europa.eu/eic-funding-opportunities/eic-2026-work-programme_en</t>
         </is>
       </c>
       <c r="L66" s="60" t="inlineStr">
         <is>
-          <t>4c3553fe5b06c01ca071e28f</t>
+          <t>d4c7b12d61b3d909256f0d10</t>
         </is>
       </c>
       <c r="M66" s="75" t="inlineStr">
         <is>
-          <t>2026-06-01T09:00:00+09:00</t>
+          <t>2026-06-17T09:00:00+09:00</t>
         </is>
       </c>
       <c r="N66" s="60" t="inlineStr">
@@ -5882,7 +5882,7 @@
       </c>
       <c r="O66" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: Journal Article / 査読表示: Journal record — confirm peer review on publisher page / 掲載誌・学会: Journal of Plasma Physics / 焦点: ARC核融合発電所の物理的基盤 / OpenAlex record; work type=article; citations=5</t>
+          <t>枠: Innovation Policy / 政策分野: R&amp;D Funding &amp; Tax Incentives | National Programs &amp; Strategy | Public Procurement &amp; Industrial Policy / 学術区分: News &amp; Official Release / 焦点: EUの研究・ディープテック事業化・スケールアップ支援 / Pinned official policy benchmark.</t>
         </is>
       </c>
     </row>
@@ -5894,60 +5894,60 @@
       </c>
       <c r="B67" s="75" t="inlineStr">
         <is>
-          <t>2026-06-01T00:00:00Z</t>
+          <t>2026-06-15T15:23:31Z</t>
         </is>
       </c>
       <c r="C67" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D67" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E67" s="60" t="inlineStr">
         <is>
-          <t>Fusion Energy</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="F67" s="76" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G67" s="60" t="inlineStr">
         <is>
-          <t>Journal Article</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H67" s="60" t="inlineStr">
         <is>
-          <t>Physics of Plasmas</t>
+          <t>NIH News Releases</t>
         </is>
       </c>
       <c r="I67" s="60" t="inlineStr">
         <is>
-          <t>ステラレーター平衡最適化のための柔軟で微分可能なコイルプロキシ</t>
+          <t>研究影響を高めるための再現性向上イニシアティブ</t>
         </is>
       </c>
       <c r="J67" s="60" t="inlineStr">
         <is>
-          <t>ステラレーターの平衡最適化に関する研究で、核融合技術に関連する具体的な内容が含まれている。</t>
+          <t>新しい生物医学研究が人間の健康に関する理解を深め、病気治療の新たな方法を提供することを目指す。独立した再現は、研究者に追加データを提供し、将来の研究プロジェクトの基盤を強化する。</t>
         </is>
       </c>
       <c r="K67" s="60" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1063/5.0307710</t>
+          <t>https://nih.gov/common-fund/common-fund-programs/replication-enhance-research-impact-initiative</t>
         </is>
       </c>
       <c r="L67" s="60" t="inlineStr">
         <is>
-          <t>aa6e411aac0ccc5f00d72fac</t>
+          <t>1b5e51bc8d4c51589eee5027</t>
         </is>
       </c>
       <c r="M67" s="75" t="inlineStr">
         <is>
-          <t>2026-06-01T09:00:00+09:00</t>
+          <t>2026-06-16T00:23:31+09:00</t>
         </is>
       </c>
       <c r="N67" s="60" t="inlineStr">
@@ -5957,7 +5957,7 @@
       </c>
       <c r="O67" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: Journal Article / 査読表示: Journal record — confirm peer review on publisher page / 掲載誌・学会: Physics of Plasmas / 焦点: ステラレーターの平衡最適化に関する研究 / OpenAlex record; work type=article; citations=1</t>
+          <t>枠: Technology Innovation / 政策分野: Patents &amp; Intellectual Property / 学術区分: News &amp; Official Release / 焦点: 生物医学研究の再現性 / Historical backfill from an allowlisted source.</t>
         </is>
       </c>
     </row>
@@ -5969,60 +5969,60 @@
       </c>
       <c r="B68" s="75" t="inlineStr">
         <is>
-          <t>2026-05-20T00:00:00Z</t>
+          <t>2026-06-15T00:00:00Z</t>
         </is>
       </c>
       <c r="C68" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>EU &amp; Europe</t>
         </is>
       </c>
       <c r="D68" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>International / France</t>
         </is>
       </c>
       <c r="E68" s="60" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Fusion Energy</t>
         </is>
       </c>
       <c r="F68" s="76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G68" s="60" t="inlineStr">
         <is>
-          <t>Conference Paper</t>
+          <t>Intergovernmental</t>
         </is>
       </c>
       <c r="H68" s="60" t="inlineStr">
         <is>
-          <t>Exploring Science Academic Conference Series</t>
+          <t>ITER News</t>
         </is>
       </c>
       <c r="I68" s="60" t="inlineStr">
         <is>
-          <t>ベンチからベッドサイドへ：CRISPR遺伝子編集の多次元臨床応用と課題</t>
+          <t>世界中から一つのアセンブリラインへ</t>
         </is>
       </c>
       <c r="J68" s="60" t="inlineStr">
         <is>
-          <t>CRISPR遺伝子編集技術の臨床応用とその課題について議論する。</t>
+          <t>ITERダイバータが新たな統合段階に入り、設計・製造の数十年を経て新しいフェーズに突入した。</t>
         </is>
       </c>
       <c r="K68" s="60" t="inlineStr">
         <is>
-          <t>https://doi.org/10.70267/shbe.20262633</t>
+          <t>https://www.iter.org/node/20687/around-world-one-assembly-line</t>
         </is>
       </c>
       <c r="L68" s="60" t="inlineStr">
         <is>
-          <t>f3ffddf94d57c4580e4df687</t>
+          <t>ac71361e131ee1a80ac51837</t>
         </is>
       </c>
       <c r="M68" s="75" t="inlineStr">
         <is>
-          <t>2026-05-20T09:00:00+09:00</t>
+          <t>2026-06-15T09:00:00+09:00</t>
         </is>
       </c>
       <c r="N68" s="60" t="inlineStr">
@@ -6032,7 +6032,7 @@
       </c>
       <c r="O68" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: Conference Paper / 査読表示: Conference proceedings — review status varies / 掲載誌・学会: Exploring Science Academic Conference Series / 焦点: CRISPR遺伝子編集 / OpenAlex record; work type=conference-paper; citations=0</t>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: ITERダイバータの統合</t>
         </is>
       </c>
     </row>
@@ -6044,60 +6044,60 @@
       </c>
       <c r="B69" s="75" t="inlineStr">
         <is>
-          <t>2026-05-09T00:00:00Z</t>
+          <t>2026-06-15T00:00:00Z</t>
         </is>
       </c>
       <c r="C69" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>EU &amp; Europe</t>
         </is>
       </c>
       <c r="D69" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>International / France</t>
         </is>
       </c>
       <c r="E69" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Fusion Energy</t>
         </is>
       </c>
       <c r="F69" s="76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G69" s="60" t="inlineStr">
         <is>
-          <t>Journal Article</t>
+          <t>Intergovernmental</t>
         </is>
       </c>
       <c r="H69" s="60" t="inlineStr">
         <is>
-          <t>Frontiers of Computer Science</t>
+          <t>ITER News</t>
         </is>
       </c>
       <c r="I69" s="60" t="inlineStr">
         <is>
-          <t>大規模言語モデルの調査</t>
+          <t>馬の年に先を行く</t>
         </is>
       </c>
       <c r="J69" s="60" t="inlineStr">
         <is>
-          <t>大規模言語モデルに関する調査を行い、自然言語処理技術やデータサイエンスの関連性を探る。</t>
+          <t>ITERでの真空容器の組立が予定よりも早く進行中で、経験と調整の利点が示されている。</t>
         </is>
       </c>
       <c r="K69" s="60" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1007/s11704-026-60308-3</t>
+          <t>https://www.iter.org/node/20687/galloping-ahead-year-horse</t>
         </is>
       </c>
       <c r="L69" s="60" t="inlineStr">
         <is>
-          <t>a9e3f3eff30c6762c76be864</t>
+          <t>47f993ca6a92c4175db656f6</t>
         </is>
       </c>
       <c r="M69" s="75" t="inlineStr">
         <is>
-          <t>2026-05-09T09:00:00+09:00</t>
+          <t>2026-06-15T09:00:00+09:00</t>
         </is>
       </c>
       <c r="N69" s="60" t="inlineStr">
@@ -6107,7 +6107,7 @@
       </c>
       <c r="O69" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: Journal Article / 査読表示: Journal record — confirm peer review on publisher page / 掲載誌・学会: Frontiers of Computer Science / 焦点: 大規模言語モデル / OpenAlex record; work type=article; citations=1421</t>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: 真空容器の組立</t>
         </is>
       </c>
     </row>
@@ -6119,60 +6119,60 @@
       </c>
       <c r="B70" s="75" t="inlineStr">
         <is>
-          <t>2026-05-09T00:00:00Z</t>
+          <t>2026-06-15T00:00:00Z</t>
         </is>
       </c>
       <c r="C70" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>EU &amp; Europe</t>
         </is>
       </c>
       <c r="D70" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>International / France</t>
         </is>
       </c>
       <c r="E70" s="60" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Fusion Energy</t>
         </is>
       </c>
       <c r="F70" s="76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G70" s="60" t="inlineStr">
         <is>
-          <t>Journal Article</t>
+          <t>Intergovernmental</t>
         </is>
       </c>
       <c r="H70" s="60" t="inlineStr">
         <is>
-          <t>Physical Review Research</t>
+          <t>ITER News</t>
         </is>
       </c>
       <c r="I70" s="60" t="inlineStr">
         <is>
-          <t>量子選択された構成相互作用</t>
+          <t>ロシアのクルチャトフ研究所との協定を締結</t>
         </is>
       </c>
       <c r="J70" s="60" t="inlineStr">
         <is>
-          <t>量子コンピュータによるハミルトニアンの古典的対角化に関する研究を行う。</t>
+          <t>ITERがロシアのクルチャトフ研究所との間で科学的交流や共同研究プログラムの実施に関する協定を締結した。</t>
         </is>
       </c>
       <c r="K70" s="60" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1103/dmn4-snfx</t>
+          <t>https://www.iter.org/node/20687/iter-signs-agreement-russias-kurchatov-institute</t>
         </is>
       </c>
       <c r="L70" s="60" t="inlineStr">
         <is>
-          <t>52e598aac1c8b58d44fc6c10</t>
+          <t>bef2ae98b3b6e9a710e28c9f</t>
         </is>
       </c>
       <c r="M70" s="75" t="inlineStr">
         <is>
-          <t>2026-05-09T09:00:00+09:00</t>
+          <t>2026-06-15T09:00:00+09:00</t>
         </is>
       </c>
       <c r="N70" s="60" t="inlineStr">
@@ -6182,7 +6182,7 @@
       </c>
       <c r="O70" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: Journal Article / 査読表示: Journal record — confirm peer review on publisher page / 掲載誌・学会: Physical Review Research / 焦点: 量子選択された構成相互作用 / OpenAlex record; work type=article; citations=19</t>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: ロシアのクルチャトフ研究所との協定</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="B71" s="75" t="inlineStr">
         <is>
-          <t>2026-05-01T00:00:00Z</t>
+          <t>2026-06-11T17:39:29Z</t>
         </is>
       </c>
       <c r="C71" s="60" t="inlineStr">
@@ -6204,7 +6204,7 @@
       </c>
       <c r="D71" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E71" s="60" t="inlineStr">
@@ -6213,41 +6213,41 @@
         </is>
       </c>
       <c r="F71" s="76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G71" s="60" t="inlineStr">
         <is>
-          <t>Journal Article</t>
+          <t>Official Company</t>
         </is>
       </c>
       <c r="H71" s="60" t="inlineStr">
         <is>
-          <t>Fundamental Research</t>
+          <t>OpenAI News</t>
         </is>
       </c>
       <c r="I71" s="60" t="inlineStr">
         <is>
-          <t>役割に基づく専門家アーキテクチャに基づくマルチエージェント法務アシスタント</t>
+          <t>特許に関する私たちのアプローチ</t>
         </is>
       </c>
       <c r="J71" s="60" t="inlineStr">
         <is>
-          <t>AIを法務に応用したマルチエージェントシステムの研究を行う。</t>
+          <t>OpenAIは、AIのための広範なアクセス、協力、安全性の原則にコミットしています。</t>
         </is>
       </c>
       <c r="K71" s="60" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.fmre.2026.03.026</t>
+          <t>https://openai.com/approach-to-patents</t>
         </is>
       </c>
       <c r="L71" s="60" t="inlineStr">
         <is>
-          <t>5b8d24eb7beb412006e619c4</t>
+          <t>15bd5956a07021e966ca1264</t>
         </is>
       </c>
       <c r="M71" s="75" t="inlineStr">
         <is>
-          <t>2026-05-01T09:00:00+09:00</t>
+          <t>2026-06-12T02:39:29+09:00</t>
         </is>
       </c>
       <c r="N71" s="60" t="inlineStr">
@@ -6257,7 +6257,7 @@
       </c>
       <c r="O71" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: Journal Article / 査読表示: Journal record — confirm peer review on publisher page / 掲載誌・学会: Fundamental Research / 焦点: 役割に基づく専門家アーキテクチャのマルチエージェント法務アシスタント / OpenAlex record; work type=article; citations=92</t>
+          <t>枠: Innovation Policy / 政策分野: Patents &amp; Intellectual Property / 学術区分: News &amp; Official Release / 焦点: AIに関する特許の方針 / Historical backfill from an allowlisted source.</t>
         </is>
       </c>
     </row>
@@ -6269,60 +6269,60 @@
       </c>
       <c r="B72" s="75" t="inlineStr">
         <is>
-          <t>2026-04-28T00:00:00Z</t>
+          <t>2026-06-09T19:00:00Z</t>
         </is>
       </c>
       <c r="C72" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D72" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E72" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Fusion Energy</t>
         </is>
       </c>
       <c r="F72" s="76" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G72" s="60" t="inlineStr">
         <is>
-          <t>Journal Article</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H72" s="60" t="inlineStr">
         <is>
-          <t>IEEE Transactions on Neural Networks and Learning Systems</t>
+          <t>DOE Office of Science News</t>
         </is>
       </c>
       <c r="I72" s="60" t="inlineStr">
         <is>
-          <t>視覚-言語-行動モデルに関する調査</t>
+          <t>エネルギー省が核融合科学と技術のロードマップを発表</t>
         </is>
       </c>
       <c r="J72" s="60" t="inlineStr">
         <is>
-          <t>ロボティクスにおける視覚と言語の相互作用に関する研究を行う。</t>
+          <t>米国エネルギー省は、核融合エネルギーの開発と商業化を加速するための戦略を発表しました。</t>
         </is>
       </c>
       <c r="K72" s="60" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1109/tnnls.2025.3650584</t>
+          <t>https://www.energy.gov/articles/energy-department-releases-finalized-fusion-science-and-technology-roadmap-accelerate</t>
         </is>
       </c>
       <c r="L72" s="60" t="inlineStr">
         <is>
-          <t>eb939baa1db14f16d9107554</t>
+          <t>bf24d6f8eb27dabbbe4e196e</t>
         </is>
       </c>
       <c r="M72" s="75" t="inlineStr">
         <is>
-          <t>2026-04-28T09:00:00+09:00</t>
+          <t>2026-06-10T04:00:00+09:00</t>
         </is>
       </c>
       <c r="N72" s="60" t="inlineStr">
@@ -6332,7 +6332,7 @@
       </c>
       <c r="O72" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: Journal Article / 査読表示: Journal record — confirm peer review on publisher page / 掲載誌・学会: IEEE Transactions on Neural Networks and Learning Systems / 焦点: 視覚-言語-行動モデル / OpenAlex record; work type=article; citations=15</t>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy | Patents &amp; Intellectual Property / 学術区分: News &amp; Official Release / 焦点: 核融合エネルギーの商業化に向けた戦略</t>
         </is>
       </c>
     </row>
@@ -6344,60 +6344,60 @@
       </c>
       <c r="B73" s="75" t="inlineStr">
         <is>
-          <t>2026-04-28T00:00:00Z</t>
+          <t>2026-06-09T12:00:00Z</t>
         </is>
       </c>
       <c r="C73" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D73" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E73" s="60" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="F73" s="76" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G73" s="60" t="inlineStr">
         <is>
-          <t>Preprint</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H73" s="60" t="inlineStr">
         <is>
-          <t>eLife</t>
+          <t>NIST News</t>
         </is>
       </c>
       <c r="I73" s="60" t="inlineStr">
         <is>
-          <t>DNAバーコード近接グラフによる形状、画像、体積の再構成</t>
+          <t>NISTの数学的証明がAIシステムのセキュリティモデルへの移行を支持</t>
         </is>
       </c>
       <c r="J73" s="60" t="inlineStr">
         <is>
-          <t>DNAバーコードを用いた新しい再構成手法に関する研究を行う。</t>
+          <t>NISTは、AIシステムのための継続的な監視と更新のセキュリティモデルへの移行を支持する数学的証明を発表しました。</t>
         </is>
       </c>
       <c r="K73" s="60" t="inlineStr">
         <is>
-          <t>https://doi.org/10.7554/elife.110436.1</t>
+          <t>https://www.nist.gov/news-events/news/2026/06/nist-mathematical-proof-supports-transition-continuous-monitor-and-update</t>
         </is>
       </c>
       <c r="L73" s="60" t="inlineStr">
         <is>
-          <t>164a3e5a84e9828ecbb1d8ba</t>
+          <t>edf1c2446b6ba41114d4bc6b</t>
         </is>
       </c>
       <c r="M73" s="75" t="inlineStr">
         <is>
-          <t>2026-04-28T09:00:00+09:00</t>
+          <t>2026-06-09T21:00:00+09:00</t>
         </is>
       </c>
       <c r="N73" s="60" t="inlineStr">
@@ -6407,7 +6407,7 @@
       </c>
       <c r="O73" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: Preprint / 査読表示: Not peer reviewed / 掲載誌・学会: eLife / 焦点: DNAバーコード近接グラフによる形状、画像、体積の再構成 / OpenAlex record; work type=preprint; citations=1</t>
+          <t>枠: Innovation Policy / 政策分野: Public Procurement &amp; Industrial Policy / 学術区分: News &amp; Official Release / 焦点: AIシステムのセキュリティモデル</t>
         </is>
       </c>
     </row>
@@ -6419,60 +6419,56 @@
       </c>
       <c r="B74" s="75" t="inlineStr">
         <is>
-          <t>2026-04-21T00:00:00Z</t>
+          <t>2026-06-05T12:28:26Z</t>
         </is>
       </c>
       <c r="C74" s="60" t="inlineStr">
         <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D74" s="60" t="inlineStr">
+        <is>
           <t>Global</t>
         </is>
       </c>
-      <c r="D74" s="60" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="E74" s="60" t="inlineStr">
-        <is>
-          <t>Robotics</t>
-        </is>
-      </c>
+      <c r="E74" s="60" t="inlineStr"/>
       <c r="F74" s="76" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G74" s="60" t="inlineStr">
         <is>
-          <t>Preprint</t>
+          <t>Intergovernmental</t>
         </is>
       </c>
       <c r="H74" s="60" t="inlineStr">
         <is>
-          <t>Research Square</t>
+          <t>WHO News</t>
         </is>
       </c>
       <c r="I74" s="60" t="inlineStr">
         <is>
-          <t>スケーラブルなロボティック制御のためのオンライン拡散ポリシーRLアルゴリズムのレビュー</t>
+          <t>アフリカCDCとWHOが共同でエボラ対応計画を発表</t>
         </is>
       </c>
       <c r="J74" s="60" t="inlineStr">
         <is>
-          <t>強化学習を用いたロボティクス制御に関する研究レビュー。</t>
+          <t>アフリカCDCとWHOがエボラウイルスの対応計画を発表し、5億1800万ドルの資金を目指す。</t>
         </is>
       </c>
       <c r="K74" s="60" t="inlineStr">
         <is>
-          <t>https://doi.org/10.21203/rs.3.rs-9346251/v1</t>
+          <t>https://www.who.int/news/item/05-06-2026-africa-cdc-and-who-launch-joint-continental-ebola-response-plan</t>
         </is>
       </c>
       <c r="L74" s="60" t="inlineStr">
         <is>
-          <t>08661e9ba2f7468a7d1c0a57</t>
+          <t>41c465a6eca3591002d781ba</t>
         </is>
       </c>
       <c r="M74" s="75" t="inlineStr">
         <is>
-          <t>2026-04-21T09:00:00+09:00</t>
+          <t>2026-06-05T21:28:26+09:00</t>
         </is>
       </c>
       <c r="N74" s="60" t="inlineStr">
@@ -6482,7 +6478,7 @@
       </c>
       <c r="O74" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: Preprint / 査読表示: Not peer reviewed / 掲載誌・学会: Research Square / 焦点: 強化学習を用いたロボティクスの制御 / OpenAlex record; work type=preprint; citations=1</t>
+          <t>枠: Innovation Policy / 政策分野: Public Procurement &amp; Industrial Policy / 学術区分: News &amp; Official Release / 焦点: エボラウイルスに対する対応計画</t>
         </is>
       </c>
     </row>
@@ -6494,7 +6490,7 @@
       </c>
       <c r="B75" s="75" t="inlineStr">
         <is>
-          <t>2026-04-15T12:00:00Z</t>
+          <t>2026-06-04T12:00:00Z</t>
         </is>
       </c>
       <c r="C75" s="60" t="inlineStr">
@@ -6509,11 +6505,11 @@
       </c>
       <c r="E75" s="60" t="inlineStr">
         <is>
-          <t>Semiconductors &amp; Telecom</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="F75" s="76" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G75" s="60" t="inlineStr">
         <is>
@@ -6527,27 +6523,27 @@
       </c>
       <c r="I75" s="60" t="inlineStr">
         <is>
-          <t>好きな色を選べる：NIST科学者が小型回路で「任意の波長」レーザーを作成</t>
+          <t>新しいAIモデルが火災時の避難経路を特定</t>
         </is>
       </c>
       <c r="J75" s="60" t="inlineStr">
         <is>
-          <t>NISTの科学者たちが、シリコンウェハ上に特殊材料の複雑なパターンを堆積することで、光のための集積回路を作成する方法を開発した。</t>
+          <t>NISTが火災時に安全な避難経路を特定する新しいAIモデルを作成した。</t>
         </is>
       </c>
       <c r="K75" s="60" t="inlineStr">
         <is>
-          <t>https://www.nist.gov/news-events/news/2026/04/any-color-you-nist-scientists-create-any-wavelength-lasers-tiny-circuits</t>
+          <t>https://www.nist.gov/news-events/news/2026/06/new-ai-model-shows-how-evacuate-fires-one-safe-step-time</t>
         </is>
       </c>
       <c r="L75" s="60" t="inlineStr">
         <is>
-          <t>4fba34d8f0d0bf2d1a725c46</t>
+          <t>434bb62e0a1e48aca17e1405</t>
         </is>
       </c>
       <c r="M75" s="75" t="inlineStr">
         <is>
-          <t>2026-04-15T21:00:00+09:00</t>
+          <t>2026-06-04T21:00:00+09:00</t>
         </is>
       </c>
       <c r="N75" s="60" t="inlineStr">
@@ -6557,7 +6553,7 @@
       </c>
       <c r="O75" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: 集積回路の光学技術</t>
+          <t>枠: Innovation Policy / 政策分野: Public Procurement &amp; Industrial Policy / 学術区分: News &amp; Official Release / 焦点: 火災時の避難経路を特定するAIモデル</t>
         </is>
       </c>
     </row>
@@ -6569,12 +6565,12 @@
       </c>
       <c r="B76" s="75" t="inlineStr">
         <is>
-          <t>2026-04-10T00:00:00Z</t>
+          <t>2026-06-04T12:00:00Z</t>
         </is>
       </c>
       <c r="C76" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D76" s="60" t="inlineStr">
@@ -6582,47 +6578,43 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="E76" s="60" t="inlineStr">
-        <is>
-          <t>Artificial Intelligence | Healthcare</t>
-        </is>
-      </c>
+      <c r="E76" s="60" t="inlineStr"/>
       <c r="F76" s="76" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G76" s="60" t="inlineStr">
         <is>
-          <t>Official Company</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H76" s="60" t="inlineStr">
         <is>
-          <t>OpenAI News</t>
+          <t>NIST News</t>
         </is>
       </c>
       <c r="I76" s="60" t="inlineStr">
         <is>
-          <t>医療におけるAIの活用</t>
+          <t>NISTがレーザーを用いた合金の結合方法を発見</t>
         </is>
       </c>
       <c r="J76" s="60" t="inlineStr">
         <is>
-          <t>医療現場でのChatGPTの活用により、診断や文書作成、患者ケアを支援する方法が探求されている。</t>
+          <t>NISTが3Dプリンティング中の金属の原子構造をリアルタイムで研究する方法を改善した。</t>
         </is>
       </c>
       <c r="K76" s="60" t="inlineStr">
         <is>
-          <t>https://openai.com/academy/healthcare</t>
+          <t>https://www.nist.gov/news-events/news/2026/06/nist-researchers-discover-new-way-whisk-alloys-together-lasers</t>
         </is>
       </c>
       <c r="L76" s="60" t="inlineStr">
         <is>
-          <t>66439e0ac0aedcb0a787347c</t>
+          <t>a03605c38ac072e4b77247db</t>
         </is>
       </c>
       <c r="M76" s="75" t="inlineStr">
         <is>
-          <t>2026-04-10T09:00:00+09:00</t>
+          <t>2026-06-04T21:00:00+09:00</t>
         </is>
       </c>
       <c r="N76" s="60" t="inlineStr">
@@ -6632,7 +6624,7 @@
       </c>
       <c r="O76" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: AIを用いた診断支援ツール / Historical backfill from an allowlisted source.</t>
+          <t>枠: Innovation Policy / 政策分野: Public Procurement &amp; Industrial Policy / 学術区分: News &amp; Official Release / 焦点: レーザーを用いた合金の結合方法</t>
         </is>
       </c>
     </row>
@@ -6644,7 +6636,7 @@
       </c>
       <c r="B77" s="75" t="inlineStr">
         <is>
-          <t>2026-03-30T00:00:00Z</t>
+          <t>2026-06-03T03:00:33Z</t>
         </is>
       </c>
       <c r="C77" s="60" t="inlineStr">
@@ -6654,12 +6646,12 @@
       </c>
       <c r="D77" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E77" s="60" t="inlineStr">
         <is>
-          <t>Fusion Energy</t>
+          <t>Semiconductors &amp; Telecom</t>
         </is>
       </c>
       <c r="F77" s="76" t="n">
@@ -6667,37 +6659,37 @@
       </c>
       <c r="G77" s="60" t="inlineStr">
         <is>
-          <t>Journal Article</t>
+          <t>Official Company</t>
         </is>
       </c>
       <c r="H77" s="60" t="inlineStr">
         <is>
-          <t>Physical review. E</t>
+          <t>Intel Newsroom</t>
         </is>
       </c>
       <c r="I77" s="60" t="inlineStr">
         <is>
-          <t>最適化されたステラレーターWendelstein 7-Xにおけるトカマク性能</t>
+          <t>インテル、企業向けEthernet E835ネットワーク制御装置を発表</t>
         </is>
       </c>
       <c r="J77" s="60" t="inlineStr">
         <is>
-          <t>Wendelstein 7-Xにおけるトカマクの性能が最適化され、安定したピーク密度プロファイルが確認されました。</t>
+          <t>インテルは、データセンターや企業、AI、テレコムモバイルコアアプリケーション向けに高密度環境の帯域幅とスケーラビリティの要求に応えるEthernet E835ネットワーク制御装置とアダプタを発表した。</t>
         </is>
       </c>
       <c r="K77" s="60" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1103/q59k-8m26</t>
+          <t>https://newsroom.intel.com/pt/data-cente/intel-apresenta-controladores-e-adaptadores-de-rede-ethernet-e835-para-infraestruturas-corporativas-de-borda-e-telecomunicacoes</t>
         </is>
       </c>
       <c r="L77" s="60" t="inlineStr">
         <is>
-          <t>5f9127127dab71cd54ecf2d1</t>
+          <t>c78a2a348fa6a57f7ff2f7c3</t>
         </is>
       </c>
       <c r="M77" s="75" t="inlineStr">
         <is>
-          <t>2026-03-30T09:00:00+09:00</t>
+          <t>2026-06-03T12:00:33+09:00</t>
         </is>
       </c>
       <c r="N77" s="60" t="inlineStr">
@@ -6707,7 +6699,7 @@
       </c>
       <c r="O77" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: Journal Article / 査読表示: Journal record — confirm peer review on publisher page / 掲載誌・学会: Physical review. E / 焦点: Wendelstein 7-Xのトカマク性能 / OpenAlex record; work type=article; citations=2</t>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: Ethernetネットワーク用の制御装置とアダプタ / Historical backfill from an allowlisted source.</t>
         </is>
       </c>
     </row>
@@ -6719,7 +6711,7 @@
       </c>
       <c r="B78" s="75" t="inlineStr">
         <is>
-          <t>2026-03-20T00:00:00Z</t>
+          <t>2026-05-19T00:00:00Z</t>
         </is>
       </c>
       <c r="C78" s="60" t="inlineStr">
@@ -6734,7 +6726,7 @@
       </c>
       <c r="E78" s="60" t="inlineStr">
         <is>
-          <t>Space</t>
+          <t>Artificial Intelligence | Healthcare | Biotechnology</t>
         </is>
       </c>
       <c r="F78" s="76" t="n">
@@ -6747,32 +6739,32 @@
       </c>
       <c r="H78" s="60" t="inlineStr">
         <is>
-          <t>Mathematics</t>
+          <t>Nature</t>
         </is>
       </c>
       <c r="I78" s="60" t="inlineStr">
         <is>
-          <t>FedLTN-CubeSat: 低軌道キューブサットコンステレーションにおける侵入検知のための神経シンボリック連合学習</t>
+          <t>Co-Scientistによる科学的発見の加速</t>
         </is>
       </c>
       <c r="J78" s="60" t="inlineStr">
         <is>
-          <t>この研究は、低軌道キューブサットコンステレーションにおける侵入検知のための神経シンボリック連合学習を提案しています。</t>
+          <t>Co-Scientistは、科学者の研究目的に基づいて新しい研究仮説を生成するAIシステムで、特にバイオメディカル分野での応用が示されています。</t>
         </is>
       </c>
       <c r="K78" s="60" t="inlineStr">
         <is>
-          <t>https://doi.org/10.3390/math14061047</t>
+          <t>https://doi.org/10.1038/s41586-026-10644-y</t>
         </is>
       </c>
       <c r="L78" s="60" t="inlineStr">
         <is>
-          <t>5d6fe2faeaa63e58b36b981e</t>
+          <t>21dce88bdeef80bd3133e790</t>
         </is>
       </c>
       <c r="M78" s="75" t="inlineStr">
         <is>
-          <t>2026-03-20T09:00:00+09:00</t>
+          <t>2026-05-19T09:00:00+09:00</t>
         </is>
       </c>
       <c r="N78" s="60" t="inlineStr">
@@ -6782,7 +6774,7 @@
       </c>
       <c r="O78" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: Journal Article / 査読表示: Journal record — confirm peer review on publisher page / 掲載誌・学会: Mathematics / 焦点: 宇宙通信システムと侵入検知システム / OpenAlex record; work type=article; citations=7</t>
+          <t>枠: Technology Innovation / 学術区分: Journal Article / 査読表示: Journal record — confirm peer review on publisher page / 掲載誌・学会: Nature / 焦点: AIによる科学的発見の加速 / OpenAlex record; work type=article; citations=56</t>
         </is>
       </c>
     </row>
@@ -6794,7 +6786,7 @@
       </c>
       <c r="B79" s="75" t="inlineStr">
         <is>
-          <t>2026-03-19T12:00:00Z</t>
+          <t>2026-05-18T12:00:00Z</t>
         </is>
       </c>
       <c r="C79" s="60" t="inlineStr">
@@ -6807,9 +6799,13 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="E79" s="60" t="inlineStr"/>
+      <c r="E79" s="60" t="inlineStr">
+        <is>
+          <t>Space</t>
+        </is>
+      </c>
       <c r="F79" s="76" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G79" s="60" t="inlineStr">
         <is>
@@ -6823,27 +6819,27 @@
       </c>
       <c r="I79" s="60" t="inlineStr">
         <is>
-          <t>NISTが議会にFY 2025の国家建設安全チーム調査の進捗を報告</t>
+          <t>月面探査に向けた超安定レーザー技術の可能性</t>
         </is>
       </c>
       <c r="J79" s="60" t="inlineStr">
         <is>
-          <t>NISTは、Champlain Towers Southの調査に関する作業の概要を含む報告書を議会に提出しました。</t>
+          <t>月面の永久影にあるクレーターは、これまでにないほど安定した光学レーザーを構築する理想的な場所となる可能性がある。</t>
         </is>
       </c>
       <c r="K79" s="60" t="inlineStr">
         <is>
-          <t>https://www.nist.gov/news-events/news/2026/03/nist-submits-annual-report-congress-summarizing-fy-2025-progress-national</t>
+          <t>https://www.nist.gov/news-events/news/2026/05/shooting-moon-ultrastable-lasers-dark-craters-could-enable-lunar-navigation</t>
         </is>
       </c>
       <c r="L79" s="60" t="inlineStr">
         <is>
-          <t>e322af74bfc6d82e04e94180</t>
+          <t>99f664278415a42538163a5c</t>
         </is>
       </c>
       <c r="M79" s="75" t="inlineStr">
         <is>
-          <t>2026-03-19T21:00:00+09:00</t>
+          <t>2026-05-18T21:00:00+09:00</t>
         </is>
       </c>
       <c r="N79" s="60" t="inlineStr">
@@ -6853,72 +6849,68 @@
       </c>
       <c r="O79" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: Public Procurement &amp; Industrial Policy / 学術区分: News &amp; Official Release / 焦点: 国家建設安全チームの調査進捗</t>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: 超安定レーザー技術</t>
         </is>
       </c>
     </row>
     <row r="80" ht="42" customHeight="1">
       <c r="A80" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T21:02:36+09:00</t>
+          <t>2026-07-26T22:54:37+09:00</t>
         </is>
       </c>
       <c r="B80" s="75" t="inlineStr">
         <is>
-          <t>2026-03-14T00:00:00Z</t>
+          <t>2026-05-14T00:00:00Z</t>
         </is>
       </c>
       <c r="C80" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D80" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="E80" s="60" t="inlineStr">
-        <is>
-          <t>Healthcare | Artificial Intelligence</t>
-        </is>
-      </c>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E80" s="60" t="inlineStr"/>
       <c r="F80" s="76" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G80" s="60" t="inlineStr">
         <is>
-          <t>Conference Paper</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H80" s="60" t="inlineStr">
         <is>
-          <t>Proceedings of the AAAI Conference on Artificial Intelligence</t>
+          <t>NSF Policy Benchmarks</t>
         </is>
       </c>
       <c r="I80" s="60" t="inlineStr">
         <is>
-          <t>医療における大規模言語モデルのベンチマーク</t>
+          <t>NSF、15億ドルのX-Labs構想を発表</t>
         </is>
       </c>
       <c r="J80" s="60" t="inlineStr">
         <is>
-          <t>医療における複雑なタスクに対する大規模言語モデルのベンチマークに関する研究が発表されました。</t>
+          <t>米国NSFは15億ドル規模の「NSF X-Labs」を発表した。従来型機関の外で独立研究組織を立ち上げ・拡大し、世代を画する科学的ブレークスルーを長期・大規模に追求する。</t>
         </is>
       </c>
       <c r="K80" s="60" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1609/aaai.v40i45.41243</t>
+          <t>https://www.nsf.gov/news/nsf-announces-15b-nsf-x-labs-initiative-pursue-generational</t>
         </is>
       </c>
       <c r="L80" s="60" t="inlineStr">
         <is>
-          <t>2ea42bfe0d086c8df38f95ce</t>
+          <t>770e8a385a4790aa084a1d15</t>
         </is>
       </c>
       <c r="M80" s="75" t="inlineStr">
         <is>
-          <t>2026-03-14T09:00:00+09:00</t>
+          <t>2026-05-14T09:00:00+09:00</t>
         </is>
       </c>
       <c r="N80" s="60" t="inlineStr">
@@ -6928,7 +6920,7 @@
       </c>
       <c r="O80" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: Conference Paper / 査読表示: Conference proceedings — review status varies / 掲載誌・学会: Proceedings of the AAAI Conference on Artificial Intelligence / 焦点: 医療におけるAIの活用 / OpenAlex record; work type=conference-paper; citations=1</t>
+          <t>枠: Innovation Policy / 政策分野: R&amp;D Funding &amp; Tax Incentives | National Programs &amp; Strategy | Research System &amp; Talent / 学術区分: News &amp; Official Release / 焦点: 独立研究組織を通じた大型・長期の基礎研究支援 / Pinned official policy benchmark.</t>
         </is>
       </c>
     </row>
@@ -6940,22 +6932,22 @@
       </c>
       <c r="B81" s="75" t="inlineStr">
         <is>
-          <t>2026-03-14T00:00:00Z</t>
+          <t>2026-04-15T12:00:00Z</t>
         </is>
       </c>
       <c r="C81" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D81" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E81" s="60" t="inlineStr">
         <is>
-          <t>Healthcare | Artificial Intelligence</t>
+          <t>Semiconductors &amp; Telecom</t>
         </is>
       </c>
       <c r="F81" s="76" t="n">
@@ -6963,37 +6955,37 @@
       </c>
       <c r="G81" s="60" t="inlineStr">
         <is>
-          <t>Conference Paper</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H81" s="60" t="inlineStr">
         <is>
-          <t>Proceedings of the AAAI Conference on Artificial Intelligence</t>
+          <t>NIST News</t>
         </is>
       </c>
       <c r="I81" s="60" t="inlineStr">
         <is>
-          <t>希少疾患の診断と治療のための自律型多分野チーム</t>
+          <t>好きな色を選べる：NIST科学者が小型回路で「任意の波長」レーザーを作成</t>
         </is>
       </c>
       <c r="J81" s="60" t="inlineStr">
         <is>
-          <t>希少疾患の診断と治療に向けた自律型多分野チームの研究が発表されました。</t>
+          <t>NISTの科学者たちが、シリコンウェハ上に特殊材料の複雑なパターンを堆積することで、光のための集積回路を作成する方法を開発した。</t>
         </is>
       </c>
       <c r="K81" s="60" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1609/aaai.v40i1.36969</t>
+          <t>https://www.nist.gov/news-events/news/2026/04/any-color-you-nist-scientists-create-any-wavelength-lasers-tiny-circuits</t>
         </is>
       </c>
       <c r="L81" s="60" t="inlineStr">
         <is>
-          <t>819111de6bdbb056ff23a177</t>
+          <t>4fba34d8f0d0bf2d1a725c46</t>
         </is>
       </c>
       <c r="M81" s="75" t="inlineStr">
         <is>
-          <t>2026-03-14T09:00:00+09:00</t>
+          <t>2026-04-15T21:00:00+09:00</t>
         </is>
       </c>
       <c r="N81" s="60" t="inlineStr">
@@ -7003,7 +6995,7 @@
       </c>
       <c r="O81" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: Conference Paper / 査読表示: Conference proceedings — review status varies / 掲載誌・学会: Proceedings of the AAAI Conference on Artificial Intelligence / 焦点: 希少疾患の診断と治療におけるAIの活用 / OpenAlex record; work type=conference-paper; citations=1</t>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: 集積回路の光学技術</t>
         </is>
       </c>
     </row>
@@ -7015,7 +7007,7 @@
       </c>
       <c r="B82" s="75" t="inlineStr">
         <is>
-          <t>2026-03-13T00:00:00Z</t>
+          <t>2026-04-10T00:00:00Z</t>
         </is>
       </c>
       <c r="C82" s="60" t="inlineStr">
@@ -7025,50 +7017,50 @@
       </c>
       <c r="D82" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E82" s="60" t="inlineStr">
         <is>
-          <t>Space</t>
+          <t>Artificial Intelligence | Healthcare</t>
         </is>
       </c>
       <c r="F82" s="76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G82" s="60" t="inlineStr">
         <is>
-          <t>Preprint</t>
+          <t>Official Company</t>
         </is>
       </c>
       <c r="H82" s="60" t="inlineStr">
         <is>
-          <t>arXiv (Cornell University)</t>
+          <t>OpenAI News</t>
         </is>
       </c>
       <c r="I82" s="60" t="inlineStr">
         <is>
-          <t>太陽風における宇宙船の後流</t>
+          <t>医療におけるAIの活用</t>
         </is>
       </c>
       <c r="J82" s="60" t="inlineStr">
         <is>
-          <t>太陽風における宇宙船の後流に関する研究が発表されました。</t>
+          <t>医療現場でのChatGPTの活用により、診断や文書作成、患者ケアを支援する方法が探求されている。</t>
         </is>
       </c>
       <c r="K82" s="60" t="inlineStr">
         <is>
-          <t>https://doi.org/10.48550/arxiv.2603.12860</t>
+          <t>https://openai.com/academy/healthcare</t>
         </is>
       </c>
       <c r="L82" s="60" t="inlineStr">
         <is>
-          <t>46df327edbda9cbcb65c531c</t>
+          <t>66439e0ac0aedcb0a787347c</t>
         </is>
       </c>
       <c r="M82" s="75" t="inlineStr">
         <is>
-          <t>2026-03-13T09:00:00+09:00</t>
+          <t>2026-04-10T09:00:00+09:00</t>
         </is>
       </c>
       <c r="N82" s="60" t="inlineStr">
@@ -7078,72 +7070,68 @@
       </c>
       <c r="O82" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: Preprint / 査読表示: Not peer reviewed / 掲載誌・学会: arXiv (Cornell University) / 焦点: 宇宙プラズマダイナミクス / OpenAlex record; work type=preprint; citations=6</t>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: AIを用いた診断支援ツール / Historical backfill from an allowlisted source.</t>
         </is>
       </c>
     </row>
     <row r="83" ht="42" customHeight="1">
       <c r="A83" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T21:02:36+09:00</t>
+          <t>2026-07-26T22:54:37+09:00</t>
         </is>
       </c>
       <c r="B83" s="75" t="inlineStr">
         <is>
-          <t>2026-03-11T00:00:00Z</t>
+          <t>2026-03-24T00:00:00Z</t>
         </is>
       </c>
       <c r="C83" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="D83" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="E83" s="60" t="inlineStr">
-        <is>
-          <t>Semiconductors &amp; Telecom</t>
-        </is>
-      </c>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E83" s="60" t="inlineStr"/>
       <c r="F83" s="76" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G83" s="60" t="inlineStr">
         <is>
-          <t>Journal Article</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H83" s="60" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>China Innovation Policy Benchmarks</t>
         </is>
       </c>
       <c r="I83" s="60" t="inlineStr">
         <is>
-          <t>6G通信アンテナ技術の研究進展</t>
+          <t>中国、大学・研究機関の特許130万件を審査し事業化候補68万件を企業へ接続</t>
         </is>
       </c>
       <c r="J83" s="60" t="inlineStr">
         <is>
-          <t>6G通信におけるアンテナ技術の研究進展についてのレビューが発表されました。</t>
+          <t>中国は大学・研究機関が保有する130万件超の特許を全国審査し、事業化可能性の高い発明特許68万件を特定して46万社へ接続した。国務院の特許転化・活用行動計画に基づき、評価、マッチング、研究者報酬、技術移転人材を整備する。</t>
         </is>
       </c>
       <c r="K83" s="60" t="inlineStr">
         <is>
-          <t>https://doi.org/10.3390/electronics15061173</t>
+          <t>https://english.www.gov.cn/news/202603/24/content_WS69c1edb6c6d00ca5f9a0a13c.html</t>
         </is>
       </c>
       <c r="L83" s="60" t="inlineStr">
         <is>
-          <t>57024341e7150ff310f53441</t>
+          <t>56bcce956cacb3b5f73edbdd</t>
         </is>
       </c>
       <c r="M83" s="75" t="inlineStr">
         <is>
-          <t>2026-03-11T09:00:00+09:00</t>
+          <t>2026-03-24T09:00:00+09:00</t>
         </is>
       </c>
       <c r="N83" s="60" t="inlineStr">
@@ -7153,7 +7141,7 @@
       </c>
       <c r="O83" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: Journal Article / 査読表示: Journal record — confirm peer review on publisher page / 掲載誌・学会: Electronics / 焦点: 6G通信アンテナ技術の研究進展 / OpenAlex record; work type=article; citations=1</t>
+          <t>枠: Innovation Policy / 政策分野: Patents &amp; Intellectual Property | Public Procurement &amp; Industrial Policy / 学術区分: News &amp; Official Release / 焦点: 大学・研究機関の特許評価、企業マッチング、技術移転 / Pinned official policy benchmark.</t>
         </is>
       </c>
     </row>
@@ -7165,60 +7153,56 @@
       </c>
       <c r="B84" s="75" t="inlineStr">
         <is>
-          <t>2026-03-10T00:00:00Z</t>
+          <t>2026-03-19T12:00:00Z</t>
         </is>
       </c>
       <c r="C84" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D84" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="E84" s="60" t="inlineStr">
-        <is>
-          <t>Space</t>
-        </is>
-      </c>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E84" s="60" t="inlineStr"/>
       <c r="F84" s="76" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G84" s="60" t="inlineStr">
         <is>
-          <t>Journal Article</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H84" s="60" t="inlineStr">
         <is>
-          <t>Virtual and Physical Prototyping</t>
+          <t>NIST News</t>
         </is>
       </c>
       <c r="I84" s="60" t="inlineStr">
         <is>
-          <t>宇宙製造におけるデジタルツインの包括的レビュー</t>
+          <t>NISTが議会にFY 2025の国家建設安全チーム調査の進捗を報告</t>
         </is>
       </c>
       <c r="J84" s="60" t="inlineStr">
         <is>
-          <t>宇宙製造におけるデジタルツインの活用に関する包括的なレビューが発表されました。</t>
+          <t>NISTは、Champlain Towers Southの調査に関する作業の概要を含む報告書を議会に提出しました。</t>
         </is>
       </c>
       <c r="K84" s="60" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1080/17452759.2026.2639147</t>
+          <t>https://www.nist.gov/news-events/news/2026/03/nist-submits-annual-report-congress-summarizing-fy-2025-progress-national</t>
         </is>
       </c>
       <c r="L84" s="60" t="inlineStr">
         <is>
-          <t>885d28facd82d772f140e913</t>
+          <t>e322af74bfc6d82e04e94180</t>
         </is>
       </c>
       <c r="M84" s="75" t="inlineStr">
         <is>
-          <t>2026-03-10T09:00:00+09:00</t>
+          <t>2026-03-19T21:00:00+09:00</t>
         </is>
       </c>
       <c r="N84" s="60" t="inlineStr">
@@ -7228,7 +7212,7 @@
       </c>
       <c r="O84" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: Journal Article / 査読表示: Journal record — confirm peer review on publisher page / 掲載誌・学会: Virtual and Physical Prototyping / 焦点: 宇宙製造におけるデジタルツインの活用 / OpenAlex record; work type=article; citations=2</t>
+          <t>枠: Innovation Policy / 政策分野: Public Procurement &amp; Industrial Policy / 学術区分: News &amp; Official Release / 焦点: 国家建設安全チームの調査進捗</t>
         </is>
       </c>
     </row>
@@ -7240,60 +7224,60 @@
       </c>
       <c r="B85" s="75" t="inlineStr">
         <is>
-          <t>2026-03-10T00:00:00Z</t>
+          <t>2026-03-04T14:57:24Z</t>
         </is>
       </c>
       <c r="C85" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>EU &amp; Europe</t>
         </is>
       </c>
       <c r="D85" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>China / Germany</t>
         </is>
       </c>
       <c r="E85" s="60" t="inlineStr">
         <is>
-          <t>Robotics | Artificial Intelligence</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="F85" s="76" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G85" s="60" t="inlineStr">
         <is>
-          <t>Conference Paper</t>
+          <t>Policy Institute</t>
         </is>
       </c>
       <c r="H85" s="60" t="inlineStr">
         <is>
-          <t>OpenAlex Conference Papers</t>
+          <t>MERICS</t>
         </is>
       </c>
       <c r="I85" s="60" t="inlineStr">
         <is>
-          <t>ロボットとの対話による公衆の認識形成</t>
+          <t>アストラゼネカ、中国を製薬イノベーションのハブに</t>
         </is>
       </c>
       <c r="J85" s="60" t="inlineStr">
         <is>
-          <t>ロボットとの対話を通じて公衆の認識を形成する研究が発表されました。</t>
+          <t>アストラゼネカが2030年までに中国の研究開発に150億ドルを投資する計画を発表。</t>
         </is>
       </c>
       <c r="K85" s="60" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1145/3757279.3785600</t>
+          <t>https://merics.org/en/comment/astrazenecas-rd-bet-makes-china-pharma-innovation-hub</t>
         </is>
       </c>
       <c r="L85" s="60" t="inlineStr">
         <is>
-          <t>921d3c21d3095bd95d28b7e4</t>
+          <t>1c2d02bf178504dd287a6106</t>
         </is>
       </c>
       <c r="M85" s="75" t="inlineStr">
         <is>
-          <t>2026-03-10T09:00:00+09:00</t>
+          <t>2026-03-04T23:57:24+09:00</t>
         </is>
       </c>
       <c r="N85" s="60" t="inlineStr">
@@ -7303,72 +7287,68 @@
       </c>
       <c r="O85" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: Conference Paper / 査読表示: Conference proceedings — review status varies / 焦点: ロボットとの対話における公衆の認識 / OpenAlex record; work type=conference-paper; citations=2</t>
+          <t>枠: Innovation Policy / 政策分野: Regulation &amp; Governance / 学術区分: News &amp; Official Release / 焦点: バイオテクノロジー産業の規制 / Historical backfill from an allowlisted source.</t>
         </is>
       </c>
     </row>
     <row r="86" ht="42" customHeight="1">
       <c r="A86" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T21:02:36+09:00</t>
+          <t>2026-07-26T22:54:37+09:00</t>
         </is>
       </c>
       <c r="B86" s="75" t="inlineStr">
         <is>
-          <t>2026-03-04T14:57:24Z</t>
+          <t>2026-02-17T00:00:00Z</t>
         </is>
       </c>
       <c r="C86" s="60" t="inlineStr">
         <is>
-          <t>EU &amp; Europe</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D86" s="60" t="inlineStr">
         <is>
-          <t>China / Germany</t>
-        </is>
-      </c>
-      <c r="E86" s="60" t="inlineStr">
-        <is>
-          <t>Biotechnology</t>
-        </is>
-      </c>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E86" s="60" t="inlineStr"/>
       <c r="F86" s="76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G86" s="60" t="inlineStr">
         <is>
-          <t>Policy Institute</t>
+          <t>Intergovernmental</t>
         </is>
       </c>
       <c r="H86" s="60" t="inlineStr">
         <is>
-          <t>MERICS</t>
+          <t>WIPO Policy Benchmarks</t>
         </is>
       </c>
       <c r="I86" s="60" t="inlineStr">
         <is>
-          <t>アストラゼネカ、中国を製薬イノベーションのハブに</t>
+          <t>WIPO「世界知的財産報告書2026」、技術普及を左右する4要因を分析</t>
         </is>
       </c>
       <c r="J86" s="60" t="inlineStr">
         <is>
-          <t>アストラゼネカが2030年までに中国の研究開発に150億ドルを投資する計画を発表。</t>
+          <t>WIPOは「世界知的財産報告書2026」で、技術の性質、情報流通、受容能力、政策・知財制度の4要因が技術普及の速度と範囲を左右すると分析した。特許と科学論文のデータから各国の普及格差を示す。</t>
         </is>
       </c>
       <c r="K86" s="60" t="inlineStr">
         <is>
-          <t>https://merics.org/en/comment/astrazenecas-rd-bet-makes-china-pharma-innovation-hub</t>
+          <t>https://www.wipo.int/web-publications/world-intellectual-property-report-2026/en/index.html</t>
         </is>
       </c>
       <c r="L86" s="60" t="inlineStr">
         <is>
-          <t>1c2d02bf178504dd287a6106</t>
+          <t>424d3f7436d98c3c4ec35b6d</t>
         </is>
       </c>
       <c r="M86" s="75" t="inlineStr">
         <is>
-          <t>2026-03-04T23:57:24+09:00</t>
+          <t>2026-02-17T09:00:00+09:00</t>
         </is>
       </c>
       <c r="N86" s="60" t="inlineStr">
@@ -7378,72 +7358,68 @@
       </c>
       <c r="O86" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: Regulation &amp; Governance / 学術区分: News &amp; Official Release / 焦点: バイオテクノロジー産業の規制 / Historical backfill from an allowlisted source.</t>
+          <t>枠: Innovation Policy / 政策分野: Patents &amp; Intellectual Property | National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: 知的財産制度と技術普及の関係 / Pinned official policy benchmark.</t>
         </is>
       </c>
     </row>
     <row r="87" ht="42" customHeight="1">
       <c r="A87" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T21:02:36+09:00</t>
+          <t>2026-07-26T22:54:37+09:00</t>
         </is>
       </c>
       <c r="B87" s="75" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00Z</t>
+          <t>2026-02-12T00:00:00Z</t>
         </is>
       </c>
       <c r="C87" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="D87" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="E87" s="60" t="inlineStr">
-        <is>
-          <t>Semiconductors &amp; Telecom</t>
-        </is>
-      </c>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="E87" s="60" t="inlineStr"/>
       <c r="F87" s="76" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G87" s="60" t="inlineStr">
         <is>
-          <t>Journal Article</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H87" s="60" t="inlineStr">
         <is>
-          <t>Light Science &amp; Applications</t>
+          <t>Korea Innovation Policy Benchmarks</t>
         </is>
       </c>
       <c r="I87" s="60" t="inlineStr">
         <is>
-          <t>共振器強化型分散ブラッグ反射器レーザー</t>
+          <t>韓国、大型国家R&amp;Dの事前評価を18年ぶりに全面改革</t>
         </is>
       </c>
       <c r="J87" s="60" t="inlineStr">
         <is>
-          <t>分散ブラッグ反射器レーザーに関する先進的な技術について述べる。</t>
+          <t>韓国は大型国家R&amp;Dの投資審査制度を18年ぶりに全面改革する。事前評価の対象基準を500億ウォンから1,000億ウォンへ引き上げ、研究型には計画審査、研究インフラ型には企画から完成までの全ライフサイクル審査を導入する。</t>
         </is>
       </c>
       <c r="K87" s="60" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1038/s41377-026-02249-x</t>
+          <t>https://www.msit.go.kr/eng/bbs/view.do?bbsSeqNo=42&amp;mId=4&amp;nttSeqNo=1227&amp;sCode=eng</t>
         </is>
       </c>
       <c r="L87" s="60" t="inlineStr">
         <is>
-          <t>2b68603f6c27927e4e6fbcdf</t>
+          <t>d1549e57df1e4381c7594af7</t>
         </is>
       </c>
       <c r="M87" s="75" t="inlineStr">
         <is>
-          <t>2026-03-03T09:00:00+09:00</t>
+          <t>2026-02-12T09:00:00+09:00</t>
         </is>
       </c>
       <c r="N87" s="60" t="inlineStr">
@@ -7453,7 +7429,7 @@
       </c>
       <c r="O87" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: Journal Article / 査読表示: Journal record — confirm peer review on publisher page / 掲載誌・学会: Light Science &amp; Applications / 焦点: 分散ブラッグ反射器レーザー / OpenAlex record; work type=article; citations=1</t>
+          <t>枠: Innovation Policy / 政策分野: R&amp;D Funding &amp; Tax Incentives | National Programs &amp; Strategy | Regulation &amp; Governance / 学術区分: News &amp; Official Release / 焦点: 大型国家R&amp;Dプロジェクトの投資審査と全ライフサイクル管理 / Pinned official policy benchmark.</t>
         </is>
       </c>
     </row>
@@ -7465,60 +7441,60 @@
       </c>
       <c r="B88" s="75" t="inlineStr">
         <is>
-          <t>2026-03-02T00:00:00Z</t>
+          <t>2026-02-10T12:00:00Z</t>
         </is>
       </c>
       <c r="C88" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D88" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E88" s="60" t="inlineStr">
         <is>
-          <t>Semiconductors &amp; Telecom</t>
+          <t>Biotechnology | Artificial Intelligence | Semiconductors &amp; Telecom | Quantum</t>
         </is>
       </c>
       <c r="F88" s="76" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G88" s="60" t="inlineStr">
         <is>
-          <t>Journal Article</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H88" s="60" t="inlineStr">
         <is>
-          <t>Sensors</t>
+          <t>NIST News</t>
         </is>
       </c>
       <c r="I88" s="60" t="inlineStr">
         <is>
-          <t>VIS–NIRスペクトルで動作する光学ガスセンサーの進展</t>
+          <t>NISTがAI、バイオテクノロジー、半導体、量子技術を進展させる小規模企業に300万ドル以上を配分</t>
         </is>
       </c>
       <c r="J88" s="60" t="inlineStr">
         <is>
-          <t>光学ガスセンサーの構造、材料、性能に関する進展を述べる。</t>
+          <t>NISTはSBIRプログラムの下で、7つの州にある8つの小規模企業に資金を配分することを発表した。</t>
         </is>
       </c>
       <c r="K88" s="60" t="inlineStr">
         <is>
-          <t>https://doi.org/10.3390/s26051568</t>
+          <t>https://www.nist.gov/news-events/news/2026/02/nist-allocates-over-3-million-small-businesses-advancing-ai-biotechnology</t>
         </is>
       </c>
       <c r="L88" s="60" t="inlineStr">
         <is>
-          <t>2c9e1a33e74e24a3f068c18e</t>
+          <t>2700025a185e7f6eb2253ff3</t>
         </is>
       </c>
       <c r="M88" s="75" t="inlineStr">
         <is>
-          <t>2026-03-02T09:00:00+09:00</t>
+          <t>2026-02-10T21:00:00+09:00</t>
         </is>
       </c>
       <c r="N88" s="60" t="inlineStr">
@@ -7528,29 +7504,29 @@
       </c>
       <c r="O88" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: Journal Article / 査読表示: Journal record — confirm peer review on publisher page / 掲載誌・学会: Sensors / 焦点: 光学ガスセンサー / OpenAlex record; work type=article; citations=1</t>
+          <t>枠: Innovation Policy / 政策分野: Public Procurement &amp; Industrial Policy / 学術区分: News &amp; Official Release / 焦点: AI、バイオテクノロジー、半導体、量子技術に関する資金配分</t>
         </is>
       </c>
     </row>
     <row r="89" ht="42" customHeight="1">
       <c r="A89" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T21:02:36+09:00</t>
+          <t>2026-07-26T22:54:37+09:00</t>
         </is>
       </c>
       <c r="B89" s="75" t="inlineStr">
         <is>
-          <t>2026-02-28T00:00:00Z</t>
+          <t>2025-11-24T00:00:00Z</t>
         </is>
       </c>
       <c r="C89" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D89" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E89" s="60" t="inlineStr">
@@ -7559,41 +7535,41 @@
         </is>
       </c>
       <c r="F89" s="76" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G89" s="60" t="inlineStr">
         <is>
-          <t>Journal Article</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H89" s="60" t="inlineStr">
         <is>
-          <t>Future Internet</t>
+          <t>White House Science Policy Benchmarks</t>
         </is>
       </c>
       <c r="I89" s="60" t="inlineStr">
         <is>
-          <t>マルチチャネル空中レーダーシステムにおけるAIベースの攻撃検出</t>
+          <t>米国、AIで科学発見を加速する「Genesis Mission」を開始</t>
         </is>
       </c>
       <c r="J89" s="60" t="inlineStr">
         <is>
-          <t>AIを用いたLED VLCにおける攻撃検出技術について述べる。</t>
+          <t>米国は大統領令で「Genesis Mission」を開始した。連邦の科学データ、スーパーコンピューター、AI、研究施設を統合し、科学基盤モデルとAIエージェントで仮説検証や研究工程を自動化する国家計画である。</t>
         </is>
       </c>
       <c r="K89" s="60" t="inlineStr">
         <is>
-          <t>https://doi.org/10.3390/fi18030124</t>
+          <t>https://www.whitehouse.gov/presidential-actions/2025/11/launching-the-genesis-mission/</t>
         </is>
       </c>
       <c r="L89" s="60" t="inlineStr">
         <is>
-          <t>72abc9f1c55ab781464c0667</t>
+          <t>f224687901952d4c32603531</t>
         </is>
       </c>
       <c r="M89" s="75" t="inlineStr">
         <is>
-          <t>2026-02-28T09:00:00+09:00</t>
+          <t>2025-11-24T09:00:00+09:00</t>
         </is>
       </c>
       <c r="N89" s="60" t="inlineStr">
@@ -7603,72 +7579,68 @@
       </c>
       <c r="O89" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: Journal Article / 査読表示: Journal record — confirm peer review on publisher page / 掲載誌・学会: Future Internet / 焦点: AIを用いた攻撃検出技術 / OpenAlex record; work type=article; citations=13</t>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy | Research System &amp; Talent / 学術区分: News &amp; Official Release / 焦点: AI、連邦科学データ、国立研究所を統合する国家研究基盤 / Pinned official policy benchmark.</t>
         </is>
       </c>
     </row>
     <row r="90" ht="42" customHeight="1">
       <c r="A90" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T21:02:36+09:00</t>
+          <t>2026-07-26T22:54:37+09:00</t>
         </is>
       </c>
       <c r="B90" s="75" t="inlineStr">
         <is>
-          <t>2026-02-20T00:00:00Z</t>
+          <t>2025-11-24T00:00:00Z</t>
         </is>
       </c>
       <c r="C90" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>EU &amp; Europe</t>
         </is>
       </c>
       <c r="D90" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="E90" s="60" t="inlineStr">
-        <is>
-          <t>Biotechnology</t>
-        </is>
-      </c>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="E90" s="60" t="inlineStr"/>
       <c r="F90" s="76" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G90" s="60" t="inlineStr">
         <is>
-          <t>Journal Article</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H90" s="60" t="inlineStr">
         <is>
-          <t>Frontiers in Microbiology</t>
+          <t>United Kingdom Innovation Policy Benchmarks</t>
         </is>
       </c>
       <c r="I90" s="60" t="inlineStr">
         <is>
-          <t>植物-土壌-微生物相互作用：持続可能な農業と健康な生態系におけるメカニズム、進展、課題</t>
+          <t>英国、UKRIの386億ポンドを戦略分野と企業成長へ重点配分</t>
         </is>
       </c>
       <c r="J90" s="60" t="inlineStr">
         <is>
-          <t>持続可能な農業における植物と土壌、微生物の相互作用についての研究をまとめた。</t>
+          <t>英国政府はUKRIの総額386億ポンドの研究資金を重点化する。政府優先課題に80億ポンド、革新的企業の成長に70億ポンドを振り向け、量子などの戦略技術、研究成果の事業化、国際研究人材を支援する。</t>
         </is>
       </c>
       <c r="K90" s="60" t="inlineStr">
         <is>
-          <t>https://doi.org/10.3389/fmicb.2026.1762743</t>
+          <t>https://www.gov.uk/government/news/more-targeted-rd-investment-towards-driving-uk-growth-and-jobs-unveiled-by-technology-secretary</t>
         </is>
       </c>
       <c r="L90" s="60" t="inlineStr">
         <is>
-          <t>1d30f53f097ef24f90c091cf</t>
+          <t>352d511ffda7b190e7b5b71f</t>
         </is>
       </c>
       <c r="M90" s="75" t="inlineStr">
         <is>
-          <t>2026-02-20T09:00:00+09:00</t>
+          <t>2025-11-24T09:00:00+09:00</t>
         </is>
       </c>
       <c r="N90" s="60" t="inlineStr">
@@ -7678,87 +7650,308 @@
       </c>
       <c r="O90" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: Journal Article / 査読表示: Journal record — confirm peer review on publisher page / 掲載誌・学会: Frontiers in Microbiology / 焦点: 植物-土壌-微生物相互作用 / OpenAlex record; work type=article; citations=10</t>
+          <t>枠: Innovation Policy / 政策分野: R&amp;D Funding &amp; Tax Incentives | National Programs &amp; Strategy | Public Procurement &amp; Industrial Policy | Research System &amp; Talent / 学術区分: News &amp; Official Release / 焦点: 公的R&amp;D資金の戦略分野・企業成長・研究人材への重点配分 / Pinned official policy benchmark.</t>
         </is>
       </c>
     </row>
     <row r="91" ht="42" customHeight="1">
       <c r="A91" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T21:02:36+09:00</t>
+          <t>2026-07-26T22:54:37+09:00</t>
         </is>
       </c>
       <c r="B91" s="75" t="inlineStr">
         <is>
-          <t>2026-02-10T12:00:00Z</t>
+          <t>2025-11-20T00:00:00Z</t>
         </is>
       </c>
       <c r="C91" s="60" t="inlineStr">
         <is>
+          <t>EU &amp; Europe</t>
+        </is>
+      </c>
+      <c r="D91" s="60" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="E91" s="60" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="F91" s="76" t="n">
+        <v>5</v>
+      </c>
+      <c r="G91" s="60" t="inlineStr">
+        <is>
+          <t>Government</t>
+        </is>
+      </c>
+      <c r="H91" s="60" t="inlineStr">
+        <is>
+          <t>United Kingdom Innovation Policy Benchmarks</t>
+        </is>
+      </c>
+      <c r="I91" s="60" t="inlineStr">
+        <is>
+          <t>英国、「AI for Science Strategy」で計算資源・データ・自律実験を一体支援</t>
+        </is>
+      </c>
+      <c r="J91" s="60" t="inlineStr">
+        <is>
+          <t>英国はAIによる科学発見を加速する15施策を公表した。公共計算資源AIRR、研究データへの安全なアクセス、自律実験室、AIサイエンティストを一体で整備し、大型研究には6か月で20万～100万GPU時間を配分する。</t>
+        </is>
+      </c>
+      <c r="K91" s="60" t="inlineStr">
+        <is>
+          <t>https://www.gov.uk/government/publications/ai-for-science-strategy/ai-for-science-strategy</t>
+        </is>
+      </c>
+      <c r="L91" s="60" t="inlineStr">
+        <is>
+          <t>216920d93f7a73f79a84dad1</t>
+        </is>
+      </c>
+      <c r="M91" s="75" t="inlineStr">
+        <is>
+          <t>2025-11-20T09:00:00+09:00</t>
+        </is>
+      </c>
+      <c r="N91" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O91" s="60" t="inlineStr">
+        <is>
+          <t>枠: Innovation Policy / 政策分野: R&amp;D Funding &amp; Tax Incentives | National Programs &amp; Strategy | Research System &amp; Talent / 学術区分: News &amp; Official Release / 焦点: AI計算資源、研究データ、自律実験室を統合した科学研究基盤 / Pinned official policy benchmark.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="42" customHeight="1">
+      <c r="A92" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T22:54:37+09:00</t>
+        </is>
+      </c>
+      <c r="B92" s="75" t="inlineStr">
+        <is>
+          <t>2025-09-15T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="C92" s="60" t="inlineStr">
+        <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="D91" s="60" t="inlineStr">
+      <c r="D92" s="60" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="E91" s="60" t="inlineStr">
-        <is>
-          <t>Biotechnology | Artificial Intelligence | Semiconductors &amp; Telecom | Quantum</t>
-        </is>
-      </c>
-      <c r="F91" s="76" t="n">
-        <v>3</v>
-      </c>
-      <c r="G91" s="60" t="inlineStr">
+      <c r="E92" s="60" t="inlineStr"/>
+      <c r="F92" s="76" t="n">
+        <v>5</v>
+      </c>
+      <c r="G92" s="60" t="inlineStr">
         <is>
           <t>Government</t>
         </is>
       </c>
-      <c r="H91" s="60" t="inlineStr">
-        <is>
-          <t>NIST News</t>
-        </is>
-      </c>
-      <c r="I91" s="60" t="inlineStr">
-        <is>
-          <t>NISTがAI、バイオテクノロジー、半導体、量子技術を進展させる小規模企業に300万ドル以上を配分</t>
-        </is>
-      </c>
-      <c r="J91" s="60" t="inlineStr">
-        <is>
-          <t>NISTはSBIRプログラムの下で、7つの州にある8つの小規模企業に資金を配分することを発表した。</t>
-        </is>
-      </c>
-      <c r="K91" s="60" t="inlineStr">
-        <is>
-          <t>https://www.nist.gov/news-events/news/2026/02/nist-allocates-over-3-million-small-businesses-advancing-ai-biotechnology</t>
-        </is>
-      </c>
-      <c r="L91" s="60" t="inlineStr">
-        <is>
-          <t>2700025a185e7f6eb2253ff3</t>
-        </is>
-      </c>
-      <c r="M91" s="75" t="inlineStr">
-        <is>
-          <t>2026-02-10T21:00:00+09:00</t>
-        </is>
-      </c>
-      <c r="N91" s="60" t="inlineStr">
+      <c r="H92" s="60" t="inlineStr">
+        <is>
+          <t>United States R&amp;D Tax Policy Benchmarks</t>
+        </is>
+      </c>
+      <c r="I92" s="60" t="inlineStr">
+        <is>
+          <t>米国、国内R&amp;D費の即時控除を認める新Section 174Aの実施手続きを公表</t>
+        </is>
+      </c>
+      <c r="J92" s="60" t="inlineStr">
+        <is>
+          <t>米国IRSは新設された内国歳入法Section 174Aの実施手続きを示した。2024年12月31日後に始まる課税年度の国内研究・実験費は原則即時控除できる一方、国外R&amp;D費は15年償却を継続し、過年度の国内R&amp;D費には移行措置を設ける。</t>
+        </is>
+      </c>
+      <c r="K92" s="60" t="inlineStr">
+        <is>
+          <t>https://www.irs.gov/irb/2025-38_IRB</t>
+        </is>
+      </c>
+      <c r="L92" s="60" t="inlineStr">
+        <is>
+          <t>f5062cb90623083863eb5adc</t>
+        </is>
+      </c>
+      <c r="M92" s="75" t="inlineStr">
+        <is>
+          <t>2025-09-15T09:00:00+09:00</t>
+        </is>
+      </c>
+      <c r="N92" s="60" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="O91" s="60" t="inlineStr">
-        <is>
-          <t>枠: Innovation Policy / 政策分野: Public Procurement &amp; Industrial Policy / 学術区分: News &amp; Official Release / 焦点: AI、バイオテクノロジー、半導体、量子技術に関する資金配分</t>
+      <c r="O92" s="60" t="inlineStr">
+        <is>
+          <t>枠: Innovation Policy / 政策分野: R&amp;D Funding &amp; Tax Incentives / 学術区分: News &amp; Official Release / 焦点: 企業の国内研究開発費に対する即時控除と国外R&amp;D費の償却 / Pinned official policy benchmark.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="42" customHeight="1">
+      <c r="A93" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T22:54:37+09:00</t>
+        </is>
+      </c>
+      <c r="B93" s="75" t="inlineStr">
+        <is>
+          <t>2025-08-27T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="C93" s="60" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D93" s="60" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E93" s="60" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="F93" s="76" t="n">
+        <v>5</v>
+      </c>
+      <c r="G93" s="60" t="inlineStr">
+        <is>
+          <t>Government</t>
+        </is>
+      </c>
+      <c r="H93" s="60" t="inlineStr">
+        <is>
+          <t>China Innovation Policy Benchmarks</t>
+        </is>
+      </c>
+      <c r="I93" s="60" t="inlineStr">
+        <is>
+          <t>中国国務院、「AI Plus」指針で6分野へのAI統合目標を設定</t>
+        </is>
+      </c>
+      <c r="J93" s="60" t="inlineStr">
+        <is>
+          <t>中国国務院は「AI Plus」指針を公表し、科学技術、産業、消費、民生、ガバナンス、国際協力の6分野にAIを統合する。次世代スマート端末・AIエージェントの普及率を2027年に70％超、2030年に90％超へ引き上げる目標を置いた。</t>
+        </is>
+      </c>
+      <c r="K93" s="60" t="inlineStr">
+        <is>
+          <t>https://english.www.gov.cn/policies/latestreleases/202508/27/content_WS68ae7976c6d0868f4e8f51a0.html</t>
+        </is>
+      </c>
+      <c r="L93" s="60" t="inlineStr">
+        <is>
+          <t>234d256bd362cd224236af3c</t>
+        </is>
+      </c>
+      <c r="M93" s="75" t="inlineStr">
+        <is>
+          <t>2025-08-27T09:00:00+09:00</t>
+        </is>
+      </c>
+      <c r="N93" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O93" s="60" t="inlineStr">
+        <is>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy | Public Procurement &amp; Industrial Policy / 学術区分: News &amp; Official Release / 焦点: AIの研究・産業・公共部門への国家的な普及と実装 / Pinned official policy benchmark.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="42" customHeight="1">
+      <c r="A94" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T22:54:37+09:00</t>
+        </is>
+      </c>
+      <c r="B94" s="75" t="inlineStr">
+        <is>
+          <t>2025-08-05T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="C94" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D94" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E94" s="60" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence | Biotechnology</t>
+        </is>
+      </c>
+      <c r="F94" s="76" t="n">
+        <v>5</v>
+      </c>
+      <c r="G94" s="60" t="inlineStr">
+        <is>
+          <t>Government</t>
+        </is>
+      </c>
+      <c r="H94" s="60" t="inlineStr">
+        <is>
+          <t>NSF Policy Benchmarks</t>
+        </is>
+      </c>
+      <c r="I94" s="60" t="inlineStr">
+        <is>
+          <t>NSF、AIプログラマブル・クラウド研究所の全米ネットワークへ投資</t>
+        </is>
+      </c>
+      <c r="J94" s="60" t="inlineStr">
+        <is>
+          <t>米国NSFは、遠隔利用できるAIプログラマブル・クラウド研究所の全米ネットワークに投資する。初期対象はバイオテクノロジーと材料科学で、実験自動化と技術移転の加速を狙う。</t>
+        </is>
+      </c>
+      <c r="K94" s="60" t="inlineStr">
+        <is>
+          <t>https://www.nsf.gov/news/nsf-invest-new-national-network-ai-programmable-cloud</t>
+        </is>
+      </c>
+      <c r="L94" s="60" t="inlineStr">
+        <is>
+          <t>f5dc59710a410021bae58dc4</t>
+        </is>
+      </c>
+      <c r="M94" s="75" t="inlineStr">
+        <is>
+          <t>2025-08-05T09:00:00+09:00</t>
+        </is>
+      </c>
+      <c r="N94" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O94" s="60" t="inlineStr">
+        <is>
+          <t>枠: Innovation Policy / 政策分野: R&amp;D Funding &amp; Tax Incentives | National Programs &amp; Strategy | Research System &amp; Talent / 学術区分: News &amp; Official Release / 焦点: AIで遠隔操作する研究施設ネットワーク / Pinned official policy benchmark.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:O91"/>
+  <autoFilter ref="A3:O94"/>
   <mergeCells count="2">
     <mergeCell ref="A1:O1"/>
     <mergeCell ref="A2:O2"/>
@@ -7776,7 +7969,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="N4:N91" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="N4:N94" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"New,Reviewed,Follow-up,Archived"</formula1>
     </dataValidation>
   </dataValidations>
@@ -7869,10 +8062,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K89" r:id="rId86"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K90" r:id="rId87"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K91" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K92" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K93" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K94" r:id="rId91"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId89"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId92"/>
   </tableParts>
 </worksheet>
 </file>
@@ -7883,7 +8079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K50"/>
+  <dimension ref="A1:K58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -10408,41 +10604,41 @@
       </c>
       <c r="B48" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="C48" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D48" s="60" t="inlineStr">
         <is>
-          <t>Scholarly research</t>
+          <t>National research programs and funding</t>
         </is>
       </c>
       <c r="E48" s="60" t="inlineStr">
         <is>
-          <t>OpenAlex Journal Articles</t>
+          <t>NSF Policy Benchmarks</t>
         </is>
       </c>
       <c r="F48" s="60" t="inlineStr">
         <is>
-          <t>OpenAlex</t>
+          <t>U.S. National Science Foundation</t>
         </is>
       </c>
       <c r="G48" s="60" t="inlineStr">
         <is>
-          <t>https://api.openalex.org/works</t>
+          <t>https://www.nsf.gov/news</t>
         </is>
       </c>
       <c r="H48" s="60" t="inlineStr">
         <is>
-          <t>https://openalex.org/</t>
+          <t>https://www.nsf.gov/news</t>
         </is>
       </c>
       <c r="I48" s="76" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J48" s="60" t="inlineStr">
         <is>
@@ -10451,7 +10647,7 @@
       </c>
       <c r="K48" s="60" t="inlineStr">
         <is>
-          <t>Scholarly metadata discovery. The card links to the DOI or OpenAlex record; peer-review status must be confirmed on the publisher page.</t>
+          <t>Reviewed primary-source benchmarks for major NSF research programs.</t>
         </is>
       </c>
     </row>
@@ -10463,41 +10659,41 @@
       </c>
       <c r="B49" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="C49" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D49" s="60" t="inlineStr">
         <is>
-          <t>Conference proceedings</t>
+          <t>National science, technology and research policy</t>
         </is>
       </c>
       <c r="E49" s="60" t="inlineStr">
         <is>
-          <t>OpenAlex Conference Papers</t>
+          <t>White House Science Policy Benchmarks</t>
         </is>
       </c>
       <c r="F49" s="60" t="inlineStr">
         <is>
-          <t>OpenAlex</t>
+          <t>The White House</t>
         </is>
       </c>
       <c r="G49" s="60" t="inlineStr">
         <is>
-          <t>https://api.openalex.org/works</t>
+          <t>https://www.whitehouse.gov/ostp/news/</t>
         </is>
       </c>
       <c r="H49" s="60" t="inlineStr">
         <is>
-          <t>https://openalex.org/</t>
+          <t>https://www.whitehouse.gov/ostp/</t>
         </is>
       </c>
       <c r="I49" s="76" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J49" s="60" t="inlineStr">
         <is>
@@ -10506,7 +10702,7 @@
       </c>
       <c r="K49" s="60" t="inlineStr">
         <is>
-          <t>Official proceedings and conference-paper records discovered through OpenAlex. Review status varies by venue.</t>
+          <t>Reviewed primary-source benchmark for a major U.S. national science mission.</t>
         </is>
       </c>
     </row>
@@ -10518,55 +10714,495 @@
       </c>
       <c r="B50" s="60" t="inlineStr">
         <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="C50" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D50" s="60" t="inlineStr">
+        <is>
+          <t>Research and development tax policy</t>
+        </is>
+      </c>
+      <c r="E50" s="60" t="inlineStr">
+        <is>
+          <t>United States R&amp;D Tax Policy Benchmarks</t>
+        </is>
+      </c>
+      <c r="F50" s="60" t="inlineStr">
+        <is>
+          <t>Internal Revenue Service</t>
+        </is>
+      </c>
+      <c r="G50" s="60" t="inlineStr">
+        <is>
+          <t>https://www.irs.gov/irb/2025-38_IRB</t>
+        </is>
+      </c>
+      <c r="H50" s="60" t="inlineStr">
+        <is>
+          <t>https://www.irs.gov/</t>
+        </is>
+      </c>
+      <c r="I50" s="76" t="n">
+        <v>5</v>
+      </c>
+      <c r="J50" s="60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K50" s="60" t="inlineStr">
+        <is>
+          <t>Reviewed primary-source benchmark for a material change in U.S. R&amp;D tax treatment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="36" customHeight="1">
+      <c r="A51" s="60" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B51" s="60" t="inlineStr">
+        <is>
+          <t>EU &amp; Europe</t>
+        </is>
+      </c>
+      <c r="C51" s="60" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="D51" s="60" t="inlineStr">
+        <is>
+          <t>National research strategy, funding and research infrastructure</t>
+        </is>
+      </c>
+      <c r="E51" s="60" t="inlineStr">
+        <is>
+          <t>United Kingdom Innovation Policy Benchmarks</t>
+        </is>
+      </c>
+      <c r="F51" s="60" t="inlineStr">
+        <is>
+          <t>UK Department for Science, Innovation and Technology</t>
+        </is>
+      </c>
+      <c r="G51" s="60" t="inlineStr">
+        <is>
+          <t>https://www.gov.uk/government/organisations/department-for-science-innovation-and-technology</t>
+        </is>
+      </c>
+      <c r="H51" s="60" t="inlineStr">
+        <is>
+          <t>https://www.gov.uk/government/organisations/department-for-science-innovation-and-technology</t>
+        </is>
+      </c>
+      <c r="I51" s="76" t="n">
+        <v>5</v>
+      </c>
+      <c r="J51" s="60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K51" s="60" t="inlineStr">
+        <is>
+          <t>Reviewed primary-source benchmarks for UK research strategy and funding allocation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="36" customHeight="1">
+      <c r="A52" s="60" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B52" s="60" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="C52" s="60" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="D52" s="60" t="inlineStr">
+        <is>
+          <t>National technology strategy and patent commercialization policy</t>
+        </is>
+      </c>
+      <c r="E52" s="60" t="inlineStr">
+        <is>
+          <t>China Innovation Policy Benchmarks</t>
+        </is>
+      </c>
+      <c r="F52" s="60" t="inlineStr">
+        <is>
+          <t>State Council of the People's Republic of China</t>
+        </is>
+      </c>
+      <c r="G52" s="60" t="inlineStr">
+        <is>
+          <t>https://english.www.gov.cn/policies/</t>
+        </is>
+      </c>
+      <c r="H52" s="60" t="inlineStr">
+        <is>
+          <t>https://english.www.gov.cn/</t>
+        </is>
+      </c>
+      <c r="I52" s="76" t="n">
+        <v>5</v>
+      </c>
+      <c r="J52" s="60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K52" s="60" t="inlineStr">
+        <is>
+          <t>Reviewed official benchmarks for China's technology deployment and patent-commercialization policy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="36" customHeight="1">
+      <c r="A53" s="60" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B53" s="60" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="C53" s="60" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="D53" s="60" t="inlineStr">
+        <is>
+          <t>National R&amp;D investment and project governance</t>
+        </is>
+      </c>
+      <c r="E53" s="60" t="inlineStr">
+        <is>
+          <t>Korea Innovation Policy Benchmarks</t>
+        </is>
+      </c>
+      <c r="F53" s="60" t="inlineStr">
+        <is>
+          <t>Ministry of Science and ICT, Republic of Korea</t>
+        </is>
+      </c>
+      <c r="G53" s="60" t="inlineStr">
+        <is>
+          <t>https://www.msit.go.kr/eng/bbs/list.do?bbsSeqNo=42&amp;mId=4</t>
+        </is>
+      </c>
+      <c r="H53" s="60" t="inlineStr">
+        <is>
+          <t>https://www.msit.go.kr/eng/</t>
+        </is>
+      </c>
+      <c r="I53" s="76" t="n">
+        <v>5</v>
+      </c>
+      <c r="J53" s="60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K53" s="60" t="inlineStr">
+        <is>
+          <t>Reviewed primary-source benchmark for Korea's large-scale national R&amp;D investment system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="36" customHeight="1">
+      <c r="A54" s="60" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B54" s="60" t="inlineStr">
+        <is>
+          <t>EU &amp; Europe</t>
+        </is>
+      </c>
+      <c r="C54" s="60" t="inlineStr">
+        <is>
+          <t>European Union</t>
+        </is>
+      </c>
+      <c r="D54" s="60" t="inlineStr">
+        <is>
+          <t>European research and innovation funding policy</t>
+        </is>
+      </c>
+      <c r="E54" s="60" t="inlineStr">
+        <is>
+          <t>European Innovation Council Policy Benchmarks</t>
+        </is>
+      </c>
+      <c r="F54" s="60" t="inlineStr">
+        <is>
+          <t>European Innovation Council</t>
+        </is>
+      </c>
+      <c r="G54" s="60" t="inlineStr">
+        <is>
+          <t>https://eic.ec.europa.eu/eic-funding-opportunities/eic-2026-work-programme_en</t>
+        </is>
+      </c>
+      <c r="H54" s="60" t="inlineStr">
+        <is>
+          <t>https://eic.ec.europa.eu/</t>
+        </is>
+      </c>
+      <c r="I54" s="76" t="n">
+        <v>5</v>
+      </c>
+      <c r="J54" s="60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K54" s="60" t="inlineStr">
+        <is>
+          <t>Reviewed primary-source benchmark for the EIC's 2026 funding programme.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="36" customHeight="1">
+      <c r="A55" s="60" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B55" s="60" t="inlineStr">
+        <is>
           <t>Global</t>
         </is>
       </c>
-      <c r="C50" s="60" t="inlineStr">
+      <c r="C55" s="60" t="inlineStr">
         <is>
           <t>Global</t>
         </is>
       </c>
-      <c r="D50" s="60" t="inlineStr">
+      <c r="D55" s="60" t="inlineStr">
+        <is>
+          <t>Intellectual property and innovation policy evidence</t>
+        </is>
+      </c>
+      <c r="E55" s="60" t="inlineStr">
+        <is>
+          <t>WIPO Policy Benchmarks</t>
+        </is>
+      </c>
+      <c r="F55" s="60" t="inlineStr">
+        <is>
+          <t>World Intellectual Property Organization</t>
+        </is>
+      </c>
+      <c r="G55" s="60" t="inlineStr">
+        <is>
+          <t>https://www.wipo.int/web-publications/world-intellectual-property-report-2026/en/index.html</t>
+        </is>
+      </c>
+      <c r="H55" s="60" t="inlineStr">
+        <is>
+          <t>https://www.wipo.int/en/web/world-ip-report</t>
+        </is>
+      </c>
+      <c r="I55" s="76" t="n">
+        <v>5</v>
+      </c>
+      <c r="J55" s="60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K55" s="60" t="inlineStr">
+        <is>
+          <t>Reviewed WIPO evidence benchmark for patent and technology-diffusion policy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="36" customHeight="1">
+      <c r="A56" s="60" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B56" s="60" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C56" s="60" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="D56" s="60" t="inlineStr">
+        <is>
+          <t>Scholarly research</t>
+        </is>
+      </c>
+      <c r="E56" s="60" t="inlineStr">
+        <is>
+          <t>OpenAlex Journal Articles</t>
+        </is>
+      </c>
+      <c r="F56" s="60" t="inlineStr">
+        <is>
+          <t>OpenAlex</t>
+        </is>
+      </c>
+      <c r="G56" s="60" t="inlineStr">
+        <is>
+          <t>https://api.openalex.org/works</t>
+        </is>
+      </c>
+      <c r="H56" s="60" t="inlineStr">
+        <is>
+          <t>https://openalex.org/</t>
+        </is>
+      </c>
+      <c r="I56" s="76" t="n">
+        <v>4</v>
+      </c>
+      <c r="J56" s="60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K56" s="60" t="inlineStr">
+        <is>
+          <t>Scholarly metadata discovery. The card links to the DOI or OpenAlex record; peer-review status must be confirmed on the publisher page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="36" customHeight="1">
+      <c r="A57" s="60" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B57" s="60" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C57" s="60" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="D57" s="60" t="inlineStr">
+        <is>
+          <t>Conference proceedings</t>
+        </is>
+      </c>
+      <c r="E57" s="60" t="inlineStr">
+        <is>
+          <t>OpenAlex Conference Papers</t>
+        </is>
+      </c>
+      <c r="F57" s="60" t="inlineStr">
+        <is>
+          <t>OpenAlex</t>
+        </is>
+      </c>
+      <c r="G57" s="60" t="inlineStr">
+        <is>
+          <t>https://api.openalex.org/works</t>
+        </is>
+      </c>
+      <c r="H57" s="60" t="inlineStr">
+        <is>
+          <t>https://openalex.org/</t>
+        </is>
+      </c>
+      <c r="I57" s="76" t="n">
+        <v>4</v>
+      </c>
+      <c r="J57" s="60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K57" s="60" t="inlineStr">
+        <is>
+          <t>Official proceedings and conference-paper records discovered through OpenAlex. Review status varies by venue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="36" customHeight="1">
+      <c r="A58" s="60" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B58" s="60" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C58" s="60" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="D58" s="60" t="inlineStr">
         <is>
           <t>Preprints</t>
         </is>
       </c>
-      <c r="E50" s="60" t="inlineStr">
+      <c r="E58" s="60" t="inlineStr">
         <is>
           <t>OpenAlex Preprints</t>
         </is>
       </c>
-      <c r="F50" s="60" t="inlineStr">
+      <c r="F58" s="60" t="inlineStr">
         <is>
           <t>OpenAlex</t>
         </is>
       </c>
-      <c r="G50" s="60" t="inlineStr">
+      <c r="G58" s="60" t="inlineStr">
         <is>
           <t>https://api.openalex.org/works</t>
         </is>
       </c>
-      <c r="H50" s="60" t="inlineStr">
+      <c r="H58" s="60" t="inlineStr">
         <is>
           <t>https://openalex.org/</t>
         </is>
       </c>
-      <c r="I50" s="76" t="n">
+      <c r="I58" s="76" t="n">
         <v>3</v>
       </c>
-      <c r="J50" s="60" t="inlineStr">
+      <c r="J58" s="60" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="K50" s="60" t="inlineStr">
+      <c r="K58" s="60" t="inlineStr">
         <is>
           <t>Preprints are displayed separately and must never be described as peer reviewed.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:K50"/>
+  <autoFilter ref="A3:K58"/>
   <mergeCells count="2">
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A1:K1"/>
@@ -10671,10 +11307,26 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H49" r:id="rId92"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G50" r:id="rId93"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H50" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G51" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H51" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G52" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H52" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G53" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H53" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G54" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H54" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G55" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H55" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G56" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H56" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G57" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H57" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G58" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H58" r:id="rId110"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId95"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId111"/>
   </tableParts>
 </worksheet>
 </file>
@@ -10685,7 +11337,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -10764,26 +11416,26 @@
     <row r="4" ht="42" customHeight="1">
       <c r="A4" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T22:13:31+09:00</t>
+          <t>2026-07-26T22:54:37+09:00</t>
         </is>
       </c>
       <c r="B4" s="77" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="C4" s="77" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="D4" s="77" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E4" s="77" t="n">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F4" s="77" t="n">
         <v>10</v>
       </c>
       <c r="G4" s="77" t="n">
-        <v>1655.72</v>
+        <v>3379.75</v>
       </c>
       <c r="H4" s="60" t="inlineStr">
         <is>
@@ -10794,127 +11446,127 @@
     <row r="5">
       <c r="A5" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T21:45:54+09:00</t>
+          <t>2026-07-26T22:13:31+09:00</t>
         </is>
       </c>
       <c r="B5" s="77" t="n">
-        <v>128</v>
+        <v>47</v>
       </c>
       <c r="C5" s="77" t="n">
-        <v>73</v>
+        <v>37</v>
       </c>
       <c r="D5" s="77" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E5" s="77" t="n">
-        <v>603</v>
+        <v>124</v>
       </c>
       <c r="F5" s="77" t="n">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="G5" s="77" t="n">
-        <v>1492.56</v>
+        <v>1655.72</v>
       </c>
       <c r="H5" s="60" t="inlineStr">
         <is>
-          <t>Historical backfill: policy 365d / technology 183d</t>
+          <t>Daily update</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T21:29:09+09:00</t>
+          <t>2026-07-26T21:45:54+09:00</t>
         </is>
       </c>
       <c r="B6" s="77" t="n">
-        <v>41</v>
+        <v>128</v>
       </c>
       <c r="C6" s="77" t="n">
-        <v>31</v>
+        <v>73</v>
       </c>
       <c r="D6" s="77" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E6" s="77" t="n">
-        <v>76</v>
+        <v>603</v>
       </c>
       <c r="F6" s="77" t="n">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="G6" s="77" t="n">
-        <v>832.08</v>
+        <v>1492.56</v>
       </c>
       <c r="H6" s="60" t="inlineStr">
         <is>
-          <t>Daily update</t>
+          <t>Historical backfill: policy 365d / technology 183d</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T21:02:36+09:00</t>
+          <t>2026-07-26T21:29:09+09:00</t>
         </is>
       </c>
       <c r="B7" s="77" t="n">
-        <v>108</v>
+        <v>41</v>
       </c>
       <c r="C7" s="77" t="n">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="D7" s="77" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E7" s="77" t="n">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="F7" s="77" t="n">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="G7" s="77" t="n">
-        <v>1376.15</v>
+        <v>832.08</v>
       </c>
       <c r="H7" s="60" t="inlineStr">
         <is>
-          <t>Historical backfill: policy 365d / technology 183d</t>
+          <t>Daily update</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:36:29+09:00</t>
+          <t>2026-07-26T21:02:36+09:00</t>
         </is>
       </c>
       <c r="B8" s="77" t="n">
-        <v>38</v>
+        <v>108</v>
       </c>
       <c r="C8" s="77" t="n">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="D8" s="77" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="E8" s="77" t="n">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="F8" s="77" t="n">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="G8" s="77" t="n">
-        <v>93.7</v>
+        <v>1376.15</v>
       </c>
       <c r="H8" s="60" t="inlineStr">
         <is>
-          <t>Daily update</t>
+          <t>Historical backfill: policy 365d / technology 183d</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:34:08+09:00</t>
+          <t>2026-07-26T20:36:29+09:00</t>
         </is>
       </c>
       <c r="B9" s="77" t="n">
@@ -10924,7 +11576,7 @@
         <v>28</v>
       </c>
       <c r="D9" s="77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" s="77" t="n">
         <v>74</v>
@@ -10933,7 +11585,7 @@
         <v>10</v>
       </c>
       <c r="G9" s="77" t="n">
-        <v>20.27</v>
+        <v>93.7</v>
       </c>
       <c r="H9" s="60" t="inlineStr">
         <is>
@@ -10944,7 +11596,7 @@
     <row r="10">
       <c r="A10" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:29:40+09:00</t>
+          <t>2026-07-26T20:34:08+09:00</t>
         </is>
       </c>
       <c r="B10" s="77" t="n">
@@ -10954,16 +11606,16 @@
         <v>28</v>
       </c>
       <c r="D10" s="77" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E10" s="77" t="n">
-        <v>11</v>
+        <v>74</v>
       </c>
       <c r="F10" s="77" t="n">
         <v>10</v>
       </c>
       <c r="G10" s="77" t="n">
-        <v>141.79</v>
+        <v>20.27</v>
       </c>
       <c r="H10" s="60" t="inlineStr">
         <is>
@@ -10974,7 +11626,7 @@
     <row r="11">
       <c r="A11" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:24:57+09:00</t>
+          <t>2026-07-26T20:29:40+09:00</t>
         </is>
       </c>
       <c r="B11" s="77" t="n">
@@ -10984,16 +11636,16 @@
         <v>28</v>
       </c>
       <c r="D11" s="77" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E11" s="77" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="F11" s="77" t="n">
         <v>10</v>
       </c>
       <c r="G11" s="77" t="n">
-        <v>134.95</v>
+        <v>141.79</v>
       </c>
       <c r="H11" s="60" t="inlineStr">
         <is>
@@ -11004,7 +11656,7 @@
     <row r="12">
       <c r="A12" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:19:15+09:00</t>
+          <t>2026-07-26T20:24:57+09:00</t>
         </is>
       </c>
       <c r="B12" s="77" t="n">
@@ -11014,16 +11666,16 @@
         <v>28</v>
       </c>
       <c r="D12" s="77" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E12" s="77" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F12" s="77" t="n">
         <v>10</v>
       </c>
       <c r="G12" s="77" t="n">
-        <v>134.05</v>
+        <v>134.95</v>
       </c>
       <c r="H12" s="60" t="inlineStr">
         <is>
@@ -11034,26 +11686,26 @@
     <row r="13">
       <c r="A13" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:13:43+09:00</t>
+          <t>2026-07-26T20:19:15+09:00</t>
         </is>
       </c>
       <c r="B13" s="77" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C13" s="77" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D13" s="77" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E13" s="77" t="n">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="F13" s="77" t="n">
         <v>10</v>
       </c>
       <c r="G13" s="77" t="n">
-        <v>162.46</v>
+        <v>134.05</v>
       </c>
       <c r="H13" s="60" t="inlineStr">
         <is>
@@ -11064,7 +11716,7 @@
     <row r="14">
       <c r="A14" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T20:00:03+09:00</t>
+          <t>2026-07-26T20:13:43+09:00</t>
         </is>
       </c>
       <c r="B14" s="77" t="n">
@@ -11074,16 +11726,16 @@
         <v>24</v>
       </c>
       <c r="D14" s="77" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E14" s="77" t="n">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="F14" s="77" t="n">
         <v>10</v>
       </c>
       <c r="G14" s="77" t="n">
-        <v>154.27</v>
+        <v>162.46</v>
       </c>
       <c r="H14" s="60" t="inlineStr">
         <is>
@@ -11094,7 +11746,7 @@
     <row r="15">
       <c r="A15" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:51:39+09:00</t>
+          <t>2026-07-26T20:00:03+09:00</t>
         </is>
       </c>
       <c r="B15" s="77" t="n">
@@ -11104,16 +11756,16 @@
         <v>24</v>
       </c>
       <c r="D15" s="77" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E15" s="77" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="F15" s="77" t="n">
         <v>10</v>
       </c>
       <c r="G15" s="77" t="n">
-        <v>11.55</v>
+        <v>154.27</v>
       </c>
       <c r="H15" s="60" t="inlineStr">
         <is>
@@ -11124,26 +11776,26 @@
     <row r="16">
       <c r="A16" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:10:55+09:00</t>
+          <t>2026-07-26T19:51:39+09:00</t>
         </is>
       </c>
       <c r="B16" s="77" t="n">
         <v>34</v>
       </c>
       <c r="C16" s="77" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D16" s="77" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E16" s="77" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F16" s="77" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G16" s="77" t="n">
-        <v>194.65</v>
+        <v>11.55</v>
       </c>
       <c r="H16" s="60" t="inlineStr">
         <is>
@@ -11154,26 +11806,26 @@
     <row r="17">
       <c r="A17" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T19:05:06+09:00</t>
+          <t>2026-07-26T19:10:55+09:00</t>
         </is>
       </c>
       <c r="B17" s="77" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C17" s="77" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D17" s="77" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E17" s="77" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="F17" s="77" t="n">
         <v>9</v>
       </c>
       <c r="G17" s="77" t="n">
-        <v>165.89</v>
+        <v>194.65</v>
       </c>
       <c r="H17" s="60" t="inlineStr">
         <is>
@@ -11184,35 +11836,65 @@
     <row r="18">
       <c r="A18" s="75" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T19:05:06+09:00</t>
         </is>
       </c>
       <c r="B18" s="77" t="n">
         <v>33</v>
       </c>
       <c r="C18" s="77" t="n">
+        <v>24</v>
+      </c>
+      <c r="D18" s="77" t="n">
+        <v>5</v>
+      </c>
+      <c r="E18" s="77" t="n">
+        <v>39</v>
+      </c>
+      <c r="F18" s="77" t="n">
+        <v>9</v>
+      </c>
+      <c r="G18" s="77" t="n">
+        <v>165.89</v>
+      </c>
+      <c r="H18" s="60" t="inlineStr">
+        <is>
+          <t>Daily update</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="75" t="inlineStr">
+        <is>
+          <t>2026-07-26T18:56:03+09:00</t>
+        </is>
+      </c>
+      <c r="B19" s="77" t="n">
+        <v>33</v>
+      </c>
+      <c r="C19" s="77" t="n">
         <v>20</v>
       </c>
-      <c r="D18" s="77" t="n">
+      <c r="D19" s="77" t="n">
         <v>94</v>
       </c>
-      <c r="E18" s="77" t="n">
+      <c r="E19" s="77" t="n">
         <v>0</v>
       </c>
-      <c r="F18" s="77" t="n">
+      <c r="F19" s="77" t="n">
         <v>13</v>
       </c>
-      <c r="G18" s="77" t="n">
+      <c r="G19" s="77" t="n">
         <v>129.43</v>
       </c>
-      <c r="H18" s="60" t="inlineStr">
+      <c r="H19" s="60" t="inlineStr">
         <is>
           <t>Initial lookback</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:H18"/>
+  <autoFilter ref="A3:H19"/>
   <mergeCells count="2">
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>

--- a/docs/innovation_news_ledger.xlsx
+++ b/docs/innovation_news_ledger.xlsx
@@ -11,7 +11,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'News Ledger'!$A$3:$O$87</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Source Registry'!$A$3:$N$263</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Run Log'!$A$3:$H$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Run Log'!$A$3:$H$25</definedName>
   </definedNames>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -667,7 +667,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="RunLogTable" displayName="RunLogTable" ref="A3:H24" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="RunLogTable" displayName="RunLogTable" ref="A3:H25" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <autoFilter ref="A3:H4"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Run Time (JST)"/>
@@ -951,7 +951,7 @@
       </c>
       <c r="B5" s="25" t="inlineStr">
         <is>
-          <t>2026-07-27T19:18:32+09:00</t>
+          <t>2026-07-27T20:03:17+09:00</t>
         </is>
       </c>
       <c r="C5" s="46" t="n"/>
@@ -26390,7 +26390,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -26469,7 +26469,7 @@
     <row r="4" ht="42" customHeight="1">
       <c r="A4" s="106" t="inlineStr">
         <is>
-          <t>2026-07-27T19:18:32+09:00</t>
+          <t>2026-07-27T20:03:17+09:00</t>
         </is>
       </c>
       <c r="B4" s="108" t="n">
@@ -26479,16 +26479,16 @@
         <v>226</v>
       </c>
       <c r="D4" s="108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" s="108" t="n">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="F4" s="108" t="n">
         <v>26</v>
       </c>
       <c r="G4" s="108" t="n">
-        <v>2017.45</v>
+        <v>762.3200000000001</v>
       </c>
       <c r="H4" s="60" t="inlineStr">
         <is>
@@ -26499,26 +26499,26 @@
     <row r="5">
       <c r="A5" s="106" t="inlineStr">
         <is>
-          <t>2026-07-27T18:40:11+09:00</t>
+          <t>2026-07-27T19:18:32+09:00</t>
         </is>
       </c>
       <c r="B5" s="108" t="n">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C5" s="108" t="n">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D5" s="108" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="108" t="n">
-        <v>471</v>
+        <v>492</v>
       </c>
       <c r="F5" s="108" t="n">
         <v>26</v>
       </c>
       <c r="G5" s="108" t="n">
-        <v>1984.46</v>
+        <v>2017.45</v>
       </c>
       <c r="H5" s="60" t="inlineStr">
         <is>
@@ -26529,67 +26529,67 @@
     <row r="6">
       <c r="A6" s="106" t="inlineStr">
         <is>
-          <t>2026-07-27T11:51:54+09:00</t>
+          <t>2026-07-27T18:40:11+09:00</t>
         </is>
       </c>
       <c r="B6" s="108" t="n">
-        <v>347</v>
+        <v>253</v>
       </c>
       <c r="C6" s="108" t="n">
-        <v>263</v>
+        <v>227</v>
       </c>
       <c r="D6" s="108" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="108" t="n">
-        <v>1087</v>
+        <v>471</v>
       </c>
       <c r="F6" s="108" t="n">
-        <v>84</v>
+        <v>26</v>
       </c>
       <c r="G6" s="108" t="n">
-        <v>4784.36</v>
+        <v>1984.46</v>
       </c>
       <c r="H6" s="60" t="inlineStr">
         <is>
-          <t>Historical backfill: policy 365d / technology 183d</t>
+          <t>Daily update</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="106" t="inlineStr">
         <is>
-          <t>2026-07-27T07:11:33+09:00</t>
+          <t>2026-07-27T11:51:54+09:00</t>
         </is>
       </c>
       <c r="B7" s="108" t="n">
-        <v>89</v>
+        <v>347</v>
       </c>
       <c r="C7" s="108" t="n">
-        <v>76</v>
+        <v>263</v>
       </c>
       <c r="D7" s="108" t="n">
         <v>0</v>
       </c>
       <c r="E7" s="108" t="n">
-        <v>187</v>
+        <v>1087</v>
       </c>
       <c r="F7" s="108" t="n">
-        <v>13</v>
+        <v>84</v>
       </c>
       <c r="G7" s="108" t="n">
-        <v>1975.42</v>
+        <v>4784.36</v>
       </c>
       <c r="H7" s="60" t="inlineStr">
         <is>
-          <t>Daily update</t>
+          <t>Historical backfill: policy 365d / technology 183d</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="106" t="inlineStr">
         <is>
-          <t>2026-07-27T06:32:05+09:00</t>
+          <t>2026-07-27T07:11:33+09:00</t>
         </is>
       </c>
       <c r="B8" s="108" t="n">
@@ -26602,13 +26602,13 @@
         <v>0</v>
       </c>
       <c r="E8" s="108" t="n">
-        <v>115</v>
+        <v>187</v>
       </c>
       <c r="F8" s="108" t="n">
         <v>13</v>
       </c>
       <c r="G8" s="108" t="n">
-        <v>1988.98</v>
+        <v>1975.42</v>
       </c>
       <c r="H8" s="60" t="inlineStr">
         <is>
@@ -26619,26 +26619,26 @@
     <row r="9">
       <c r="A9" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T22:54:37+09:00</t>
+          <t>2026-07-27T06:32:05+09:00</t>
         </is>
       </c>
       <c r="B9" s="108" t="n">
-        <v>55</v>
+        <v>89</v>
       </c>
       <c r="C9" s="108" t="n">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="D9" s="108" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E9" s="108" t="n">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="F9" s="108" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G9" s="108" t="n">
-        <v>3379.75</v>
+        <v>1988.98</v>
       </c>
       <c r="H9" s="60" t="inlineStr">
         <is>
@@ -26649,26 +26649,26 @@
     <row r="10">
       <c r="A10" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T22:13:31+09:00</t>
+          <t>2026-07-26T22:54:37+09:00</t>
         </is>
       </c>
       <c r="B10" s="108" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="C10" s="108" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="D10" s="108" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E10" s="108" t="n">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F10" s="108" t="n">
         <v>10</v>
       </c>
       <c r="G10" s="108" t="n">
-        <v>1655.72</v>
+        <v>3379.75</v>
       </c>
       <c r="H10" s="60" t="inlineStr">
         <is>
@@ -26679,127 +26679,127 @@
     <row r="11">
       <c r="A11" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T21:45:54+09:00</t>
+          <t>2026-07-26T22:13:31+09:00</t>
         </is>
       </c>
       <c r="B11" s="108" t="n">
-        <v>128</v>
+        <v>47</v>
       </c>
       <c r="C11" s="108" t="n">
-        <v>73</v>
+        <v>37</v>
       </c>
       <c r="D11" s="108" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E11" s="108" t="n">
-        <v>603</v>
+        <v>124</v>
       </c>
       <c r="F11" s="108" t="n">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="G11" s="108" t="n">
-        <v>1492.56</v>
+        <v>1655.72</v>
       </c>
       <c r="H11" s="60" t="inlineStr">
         <is>
-          <t>Historical backfill: policy 365d / technology 183d</t>
+          <t>Daily update</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T21:29:09+09:00</t>
+          <t>2026-07-26T21:45:54+09:00</t>
         </is>
       </c>
       <c r="B12" s="108" t="n">
-        <v>41</v>
+        <v>128</v>
       </c>
       <c r="C12" s="108" t="n">
-        <v>31</v>
+        <v>73</v>
       </c>
       <c r="D12" s="108" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E12" s="108" t="n">
-        <v>76</v>
+        <v>603</v>
       </c>
       <c r="F12" s="108" t="n">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="G12" s="108" t="n">
-        <v>832.08</v>
+        <v>1492.56</v>
       </c>
       <c r="H12" s="60" t="inlineStr">
         <is>
-          <t>Daily update</t>
+          <t>Historical backfill: policy 365d / technology 183d</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T21:02:36+09:00</t>
+          <t>2026-07-26T21:29:09+09:00</t>
         </is>
       </c>
       <c r="B13" s="108" t="n">
-        <v>108</v>
+        <v>41</v>
       </c>
       <c r="C13" s="108" t="n">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="D13" s="108" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E13" s="108" t="n">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="F13" s="108" t="n">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="G13" s="108" t="n">
-        <v>1376.15</v>
+        <v>832.08</v>
       </c>
       <c r="H13" s="60" t="inlineStr">
         <is>
-          <t>Historical backfill: policy 365d / technology 183d</t>
+          <t>Daily update</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T20:36:29+09:00</t>
+          <t>2026-07-26T21:02:36+09:00</t>
         </is>
       </c>
       <c r="B14" s="108" t="n">
-        <v>38</v>
+        <v>108</v>
       </c>
       <c r="C14" s="108" t="n">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="D14" s="108" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="E14" s="108" t="n">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="F14" s="108" t="n">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="G14" s="108" t="n">
-        <v>93.7</v>
+        <v>1376.15</v>
       </c>
       <c r="H14" s="60" t="inlineStr">
         <is>
-          <t>Daily update</t>
+          <t>Historical backfill: policy 365d / technology 183d</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T20:34:08+09:00</t>
+          <t>2026-07-26T20:36:29+09:00</t>
         </is>
       </c>
       <c r="B15" s="108" t="n">
@@ -26809,7 +26809,7 @@
         <v>28</v>
       </c>
       <c r="D15" s="108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15" s="108" t="n">
         <v>74</v>
@@ -26818,7 +26818,7 @@
         <v>10</v>
       </c>
       <c r="G15" s="108" t="n">
-        <v>20.27</v>
+        <v>93.7</v>
       </c>
       <c r="H15" s="60" t="inlineStr">
         <is>
@@ -26829,7 +26829,7 @@
     <row r="16">
       <c r="A16" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T20:29:40+09:00</t>
+          <t>2026-07-26T20:34:08+09:00</t>
         </is>
       </c>
       <c r="B16" s="108" t="n">
@@ -26839,16 +26839,16 @@
         <v>28</v>
       </c>
       <c r="D16" s="108" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E16" s="108" t="n">
-        <v>11</v>
+        <v>74</v>
       </c>
       <c r="F16" s="108" t="n">
         <v>10</v>
       </c>
       <c r="G16" s="108" t="n">
-        <v>141.79</v>
+        <v>20.27</v>
       </c>
       <c r="H16" s="60" t="inlineStr">
         <is>
@@ -26859,7 +26859,7 @@
     <row r="17">
       <c r="A17" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T20:24:57+09:00</t>
+          <t>2026-07-26T20:29:40+09:00</t>
         </is>
       </c>
       <c r="B17" s="108" t="n">
@@ -26869,16 +26869,16 @@
         <v>28</v>
       </c>
       <c r="D17" s="108" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E17" s="108" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="F17" s="108" t="n">
         <v>10</v>
       </c>
       <c r="G17" s="108" t="n">
-        <v>134.95</v>
+        <v>141.79</v>
       </c>
       <c r="H17" s="60" t="inlineStr">
         <is>
@@ -26889,7 +26889,7 @@
     <row r="18">
       <c r="A18" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T20:19:15+09:00</t>
+          <t>2026-07-26T20:24:57+09:00</t>
         </is>
       </c>
       <c r="B18" s="108" t="n">
@@ -26899,16 +26899,16 @@
         <v>28</v>
       </c>
       <c r="D18" s="108" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E18" s="108" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F18" s="108" t="n">
         <v>10</v>
       </c>
       <c r="G18" s="108" t="n">
-        <v>134.05</v>
+        <v>134.95</v>
       </c>
       <c r="H18" s="60" t="inlineStr">
         <is>
@@ -26919,26 +26919,26 @@
     <row r="19">
       <c r="A19" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T20:13:43+09:00</t>
+          <t>2026-07-26T20:19:15+09:00</t>
         </is>
       </c>
       <c r="B19" s="108" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C19" s="108" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D19" s="108" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E19" s="108" t="n">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="F19" s="108" t="n">
         <v>10</v>
       </c>
       <c r="G19" s="108" t="n">
-        <v>162.46</v>
+        <v>134.05</v>
       </c>
       <c r="H19" s="60" t="inlineStr">
         <is>
@@ -26949,7 +26949,7 @@
     <row r="20">
       <c r="A20" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T20:00:03+09:00</t>
+          <t>2026-07-26T20:13:43+09:00</t>
         </is>
       </c>
       <c r="B20" s="108" t="n">
@@ -26959,16 +26959,16 @@
         <v>24</v>
       </c>
       <c r="D20" s="108" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E20" s="108" t="n">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="F20" s="108" t="n">
         <v>10</v>
       </c>
       <c r="G20" s="108" t="n">
-        <v>154.27</v>
+        <v>162.46</v>
       </c>
       <c r="H20" s="60" t="inlineStr">
         <is>
@@ -26979,7 +26979,7 @@
     <row r="21">
       <c r="A21" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T19:51:39+09:00</t>
+          <t>2026-07-26T20:00:03+09:00</t>
         </is>
       </c>
       <c r="B21" s="108" t="n">
@@ -26989,16 +26989,16 @@
         <v>24</v>
       </c>
       <c r="D21" s="108" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E21" s="108" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="F21" s="108" t="n">
         <v>10</v>
       </c>
       <c r="G21" s="108" t="n">
-        <v>11.55</v>
+        <v>154.27</v>
       </c>
       <c r="H21" s="60" t="inlineStr">
         <is>
@@ -27009,26 +27009,26 @@
     <row r="22">
       <c r="A22" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T19:10:55+09:00</t>
+          <t>2026-07-26T19:51:39+09:00</t>
         </is>
       </c>
       <c r="B22" s="108" t="n">
         <v>34</v>
       </c>
       <c r="C22" s="108" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D22" s="108" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E22" s="108" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F22" s="108" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G22" s="108" t="n">
-        <v>194.65</v>
+        <v>11.55</v>
       </c>
       <c r="H22" s="60" t="inlineStr">
         <is>
@@ -27039,26 +27039,26 @@
     <row r="23">
       <c r="A23" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T19:05:06+09:00</t>
+          <t>2026-07-26T19:10:55+09:00</t>
         </is>
       </c>
       <c r="B23" s="108" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C23" s="108" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D23" s="108" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E23" s="108" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="F23" s="108" t="n">
         <v>9</v>
       </c>
       <c r="G23" s="108" t="n">
-        <v>165.89</v>
+        <v>194.65</v>
       </c>
       <c r="H23" s="60" t="inlineStr">
         <is>
@@ -27069,35 +27069,65 @@
     <row r="24">
       <c r="A24" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T19:05:06+09:00</t>
         </is>
       </c>
       <c r="B24" s="108" t="n">
         <v>33</v>
       </c>
       <c r="C24" s="108" t="n">
+        <v>24</v>
+      </c>
+      <c r="D24" s="108" t="n">
+        <v>5</v>
+      </c>
+      <c r="E24" s="108" t="n">
+        <v>39</v>
+      </c>
+      <c r="F24" s="108" t="n">
+        <v>9</v>
+      </c>
+      <c r="G24" s="108" t="n">
+        <v>165.89</v>
+      </c>
+      <c r="H24" s="60" t="inlineStr">
+        <is>
+          <t>Daily update</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="106" t="inlineStr">
+        <is>
+          <t>2026-07-26T18:56:03+09:00</t>
+        </is>
+      </c>
+      <c r="B25" s="108" t="n">
+        <v>33</v>
+      </c>
+      <c r="C25" s="108" t="n">
         <v>20</v>
       </c>
-      <c r="D24" s="108" t="n">
+      <c r="D25" s="108" t="n">
         <v>94</v>
       </c>
-      <c r="E24" s="108" t="n">
+      <c r="E25" s="108" t="n">
         <v>0</v>
       </c>
-      <c r="F24" s="108" t="n">
+      <c r="F25" s="108" t="n">
         <v>13</v>
       </c>
-      <c r="G24" s="108" t="n">
+      <c r="G25" s="108" t="n">
         <v>129.43</v>
       </c>
-      <c r="H24" s="60" t="inlineStr">
+      <c r="H25" s="60" t="inlineStr">
         <is>
           <t>Initial lookback</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:H24"/>
+  <autoFilter ref="A3:H25"/>
   <mergeCells count="2">
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>

--- a/docs/innovation_news_ledger.xlsx
+++ b/docs/innovation_news_ledger.xlsx
@@ -11,7 +11,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'News Ledger'!$A$3:$O$87</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Source Registry'!$A$3:$N$263</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Run Log'!$A$3:$H$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Run Log'!$A$3:$H$26</definedName>
   </definedNames>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -667,7 +667,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="RunLogTable" displayName="RunLogTable" ref="A3:H25" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="RunLogTable" displayName="RunLogTable" ref="A3:H26" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <autoFilter ref="A3:H4"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Run Time (JST)"/>
@@ -951,7 +951,7 @@
       </c>
       <c r="B5" s="25" t="inlineStr">
         <is>
-          <t>2026-07-27T20:03:17+09:00</t>
+          <t>2026-07-27T23:07:45+09:00</t>
         </is>
       </c>
       <c r="C5" s="46" t="n"/>
@@ -8641,12 +8641,12 @@
       </c>
       <c r="G16" s="60" t="inlineStr">
         <is>
-          <t>https://www.arabnews.com/tags/technology</t>
+          <t>https://www.arabnews.com/category/tags/technology</t>
         </is>
       </c>
       <c r="H16" s="60" t="inlineStr">
         <is>
-          <t>https://www.arabnews.com/tags/technology</t>
+          <t>https://www.arabnews.com/category/tags/technology</t>
         </is>
       </c>
       <c r="I16" s="107" t="n">
@@ -8804,7 +8804,11 @@
           <t>Daily</t>
         </is>
       </c>
-      <c r="N18" s="95" t="inlineStr"/>
+      <c r="N18" s="95" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence | Robotics | Semiconductors &amp; Telecom | Quantum | Fusion Energy | Biotechnology | Healthcare | Space</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="36" customHeight="1">
       <c r="A19" s="60" t="inlineStr">
@@ -8870,7 +8874,11 @@
           <t>Daily</t>
         </is>
       </c>
-      <c r="N19" s="95" t="inlineStr"/>
+      <c r="N19" s="95" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence | Robotics | Semiconductors &amp; Telecom | Quantum | Fusion Energy | Biotechnology | Healthcare | Space</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="36" customHeight="1">
       <c r="A20" s="60" t="inlineStr">
@@ -9076,7 +9084,11 @@
           <t>Daily</t>
         </is>
       </c>
-      <c r="N22" s="95" t="inlineStr"/>
+      <c r="N22" s="95" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence | Robotics | Semiconductors &amp; Telecom | Quantum | Fusion Energy | Biotechnology | Healthcare | Space</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="36" customHeight="1">
       <c r="A23" s="60" t="inlineStr">
@@ -9111,12 +9123,12 @@
       </c>
       <c r="G23" s="60" t="inlineStr">
         <is>
-          <t>https://www.bruegel.org/analysis</t>
+          <t>https://www.bruegel.org/feed/analysis</t>
         </is>
       </c>
       <c r="H23" s="60" t="inlineStr">
         <is>
-          <t>https://www.bruegel.org/analysis</t>
+          <t>https://www.bruegel.org/publications/analyses</t>
         </is>
       </c>
       <c r="I23" s="107" t="n">
@@ -9124,12 +9136,12 @@
       </c>
       <c r="J23" s="60" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K23" s="60" t="inlineStr">
         <is>
-          <t>European economic-policy institute; scans the official analysis page.</t>
+          <t>European economic-policy institute; official analysis RSS.</t>
         </is>
       </c>
       <c r="L23" s="94" t="inlineStr">
@@ -9142,7 +9154,11 @@
           <t>Daily</t>
         </is>
       </c>
-      <c r="N23" s="95" t="inlineStr"/>
+      <c r="N23" s="95" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence | Robotics | Semiconductors &amp; Telecom | Quantum | Fusion Energy | Biotechnology | Healthcare | Space</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="36" customHeight="1">
       <c r="A24" s="60" t="inlineStr">
@@ -9208,7 +9224,11 @@
           <t>Daily</t>
         </is>
       </c>
-      <c r="N24" s="95" t="inlineStr"/>
+      <c r="N24" s="95" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence | Robotics | Semiconductors &amp; Telecom | Quantum | Fusion Energy | Biotechnology | Healthcare | Space</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="36" customHeight="1">
       <c r="A25" s="60" t="inlineStr">
@@ -10405,12 +10425,12 @@
       </c>
       <c r="G42" s="60" t="inlineStr">
         <is>
-          <t>https://deepmind.google/discover/blog/</t>
+          <t>https://deepmind.google/blog/rss.xml</t>
         </is>
       </c>
       <c r="H42" s="60" t="inlineStr">
         <is>
-          <t>https://deepmind.google/discover/blog/</t>
+          <t>https://deepmind.google/blog/</t>
         </is>
       </c>
       <c r="I42" s="107" t="n">
@@ -10418,12 +10438,12 @@
       </c>
       <c r="J42" s="60" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K42" s="60" t="inlineStr">
         <is>
-          <t>Official corporate research publication.</t>
+          <t>Official corporate research RSS.</t>
         </is>
       </c>
       <c r="L42" s="94" t="inlineStr">
@@ -10825,12 +10845,12 @@
       </c>
       <c r="G48" s="60" t="inlineStr">
         <is>
-          <t>https://new.abb.com/news</t>
+          <t>https://www.abb.com/global/en/areas/robotics</t>
         </is>
       </c>
       <c r="H48" s="60" t="inlineStr">
         <is>
-          <t>https://new.abb.com/products/robotics</t>
+          <t>https://www.abb.com/global/en/areas/robotics</t>
         </is>
       </c>
       <c r="I48" s="107" t="n">
@@ -10843,7 +10863,7 @@
       </c>
       <c r="K48" s="60" t="inlineStr">
         <is>
-          <t>Official ABB releases; the technology filter retains robotics and automation R&amp;D.</t>
+          <t>Official ABB Robotics all-stories feed exposed by ABB's NewsBank JSON service.</t>
         </is>
       </c>
       <c r="L48" s="94" t="inlineStr">
@@ -11385,12 +11405,12 @@
       </c>
       <c r="G56" s="60" t="inlineStr">
         <is>
-          <t>https://www.nokia.com/about-us/newsroom/</t>
+          <t>https://www.nokia.com/newsroom/tagfeed/en-us/tags/press__releases</t>
         </is>
       </c>
       <c r="H56" s="60" t="inlineStr">
         <is>
-          <t>https://www.nokia.com/about-us/newsroom/</t>
+          <t>https://www.nokia.com/newsroom/</t>
         </is>
       </c>
       <c r="I56" s="107" t="n">
@@ -11398,12 +11418,12 @@
       </c>
       <c r="J56" s="60" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K56" s="60" t="inlineStr">
         <is>
-          <t>Official telecommunications research and technology newsroom.</t>
+          <t>Official telecommunications press-release RSS.</t>
         </is>
       </c>
       <c r="L56" s="94" t="inlineStr">
@@ -12015,12 +12035,12 @@
       </c>
       <c r="G65" s="60" t="inlineStr">
         <is>
-          <t>https://www.modernatx.com/media-center/all-media</t>
+          <t>https://news.modernatx.com/</t>
         </is>
       </c>
       <c r="H65" s="60" t="inlineStr">
         <is>
-          <t>https://www.modernatx.com/media-center/all-media</t>
+          <t>https://news.modernatx.com/</t>
         </is>
       </c>
       <c r="I65" s="107" t="n">
@@ -12033,7 +12053,7 @@
       </c>
       <c r="K65" s="60" t="inlineStr">
         <is>
-          <t>Official biotechnology company newsroom; financial-only releases are excluded.</t>
+          <t>Official biotechnology company press releases from the structured feed used by Moderna's newsroom; financial-only releases are excluded.</t>
         </is>
       </c>
       <c r="L65" s="94" t="inlineStr">
@@ -12118,7 +12138,7 @@
       </c>
       <c r="N66" s="95" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Biotechnology | Healthcare</t>
         </is>
       </c>
     </row>
@@ -12383,7 +12403,7 @@
       </c>
       <c r="K70" s="60" t="inlineStr">
         <is>
-          <t>Official launch-vehicle and spacecraft engineering updates.</t>
+          <t>Official launch-vehicle and spacecraft engineering updates from the SpaceX website CMS.</t>
         </is>
       </c>
       <c r="L70" s="94" t="inlineStr">
@@ -13018,7 +13038,11 @@
           <t>Daily</t>
         </is>
       </c>
-      <c r="N79" s="95" t="inlineStr"/>
+      <c r="N79" s="95" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence | Robotics | Semiconductors &amp; Telecom | Quantum | Fusion Energy | Biotechnology | Healthcare | Space</t>
+        </is>
+      </c>
     </row>
     <row r="80" ht="36" customHeight="1">
       <c r="A80" s="60" t="inlineStr">
@@ -15327,7 +15351,7 @@
       </c>
       <c r="G113" s="60" t="inlineStr">
         <is>
-          <t>https://kikaku.ai-gakkai.or.jp/category/news/feed</t>
+          <t>https://www.ai-gakkai.or.jp/feed/</t>
         </is>
       </c>
       <c r="H113" s="60" t="inlineStr">
@@ -15887,7 +15911,7 @@
       </c>
       <c r="G121" s="60" t="inlineStr">
         <is>
-          <t>https://eetimes.itmedia.co.jp/ee/rss/index.rdf</t>
+          <t>https://rss.itmedia.co.jp/rss/2.0/eetimes.xml</t>
         </is>
       </c>
       <c r="H121" s="60" t="inlineStr">
@@ -16395,7 +16419,7 @@
       </c>
       <c r="K128" s="60" t="inlineStr">
         <is>
-          <t>Weekly B-tier specialist analysis; only public metadata and pages are collected.</t>
+          <t>Weekly B-tier specialist analysis from the JSON endpoint used by the official public frontend.</t>
         </is>
       </c>
       <c r="L128" s="94" t="inlineStr">
@@ -20092,7 +20116,7 @@
       </c>
       <c r="H181" s="60" t="inlineStr">
         <is>
-          <t>https://www.nationalacademies.org/step</t>
+          <t>https://www.nationalacademies.org/units/PGA-STEP-22-P-460</t>
         </is>
       </c>
       <c r="I181" s="107" t="n">
@@ -20157,7 +20181,7 @@
       </c>
       <c r="G182" s="60" t="inlineStr">
         <is>
-          <t>https://www.federalregister.gov/documents/search.rss?conditions%5Bsections%5D%5B%5D=science-and-technology</t>
+          <t>https://www.federalregister.gov/api/v1/documents.json</t>
         </is>
       </c>
       <c r="H182" s="60" t="inlineStr">
@@ -20170,12 +20194,12 @@
       </c>
       <c r="J182" s="60" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K182" s="60" t="inlineStr">
         <is>
-          <t>Official Federal Register science-and-technology RSS with strict topic and policy filtering.</t>
+          <t>Official Federal Register science-and-technology JSON API with strict topic and policy filtering.</t>
         </is>
       </c>
       <c r="L182" s="94" t="inlineStr">
@@ -22467,7 +22491,7 @@
       </c>
       <c r="G215" s="60" t="inlineStr">
         <is>
-          <t>https://www.renesas.com/en/about/press-room</t>
+          <t>https://www.renesas.com/en/about/newsroom</t>
         </is>
       </c>
       <c r="H215" s="60" t="inlineStr">
@@ -26390,7 +26414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -26469,26 +26493,26 @@
     <row r="4" ht="42" customHeight="1">
       <c r="A4" s="106" t="inlineStr">
         <is>
-          <t>2026-07-27T20:03:17+09:00</t>
+          <t>2026-07-27T23:07:45+09:00</t>
         </is>
       </c>
       <c r="B4" s="108" t="n">
         <v>252</v>
       </c>
       <c r="C4" s="108" t="n">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D4" s="108" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E4" s="108" t="n">
-        <v>493</v>
+        <v>466</v>
       </c>
       <c r="F4" s="108" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G4" s="108" t="n">
-        <v>762.3200000000001</v>
+        <v>819.04</v>
       </c>
       <c r="H4" s="60" t="inlineStr">
         <is>
@@ -26499,7 +26523,7 @@
     <row r="5">
       <c r="A5" s="106" t="inlineStr">
         <is>
-          <t>2026-07-27T19:18:32+09:00</t>
+          <t>2026-07-27T20:03:17+09:00</t>
         </is>
       </c>
       <c r="B5" s="108" t="n">
@@ -26509,16 +26533,16 @@
         <v>226</v>
       </c>
       <c r="D5" s="108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" s="108" t="n">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="F5" s="108" t="n">
         <v>26</v>
       </c>
       <c r="G5" s="108" t="n">
-        <v>2017.45</v>
+        <v>762.3200000000001</v>
       </c>
       <c r="H5" s="60" t="inlineStr">
         <is>
@@ -26529,26 +26553,26 @@
     <row r="6">
       <c r="A6" s="106" t="inlineStr">
         <is>
-          <t>2026-07-27T18:40:11+09:00</t>
+          <t>2026-07-27T19:18:32+09:00</t>
         </is>
       </c>
       <c r="B6" s="108" t="n">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C6" s="108" t="n">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D6" s="108" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="108" t="n">
-        <v>471</v>
+        <v>492</v>
       </c>
       <c r="F6" s="108" t="n">
         <v>26</v>
       </c>
       <c r="G6" s="108" t="n">
-        <v>1984.46</v>
+        <v>2017.45</v>
       </c>
       <c r="H6" s="60" t="inlineStr">
         <is>
@@ -26559,67 +26583,67 @@
     <row r="7">
       <c r="A7" s="106" t="inlineStr">
         <is>
-          <t>2026-07-27T11:51:54+09:00</t>
+          <t>2026-07-27T18:40:11+09:00</t>
         </is>
       </c>
       <c r="B7" s="108" t="n">
-        <v>347</v>
+        <v>253</v>
       </c>
       <c r="C7" s="108" t="n">
-        <v>263</v>
+        <v>227</v>
       </c>
       <c r="D7" s="108" t="n">
         <v>0</v>
       </c>
       <c r="E7" s="108" t="n">
-        <v>1087</v>
+        <v>471</v>
       </c>
       <c r="F7" s="108" t="n">
-        <v>84</v>
+        <v>26</v>
       </c>
       <c r="G7" s="108" t="n">
-        <v>4784.36</v>
+        <v>1984.46</v>
       </c>
       <c r="H7" s="60" t="inlineStr">
         <is>
-          <t>Historical backfill: policy 365d / technology 183d</t>
+          <t>Daily update</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="106" t="inlineStr">
         <is>
-          <t>2026-07-27T07:11:33+09:00</t>
+          <t>2026-07-27T11:51:54+09:00</t>
         </is>
       </c>
       <c r="B8" s="108" t="n">
-        <v>89</v>
+        <v>347</v>
       </c>
       <c r="C8" s="108" t="n">
-        <v>76</v>
+        <v>263</v>
       </c>
       <c r="D8" s="108" t="n">
         <v>0</v>
       </c>
       <c r="E8" s="108" t="n">
-        <v>187</v>
+        <v>1087</v>
       </c>
       <c r="F8" s="108" t="n">
-        <v>13</v>
+        <v>84</v>
       </c>
       <c r="G8" s="108" t="n">
-        <v>1975.42</v>
+        <v>4784.36</v>
       </c>
       <c r="H8" s="60" t="inlineStr">
         <is>
-          <t>Daily update</t>
+          <t>Historical backfill: policy 365d / technology 183d</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="106" t="inlineStr">
         <is>
-          <t>2026-07-27T06:32:05+09:00</t>
+          <t>2026-07-27T07:11:33+09:00</t>
         </is>
       </c>
       <c r="B9" s="108" t="n">
@@ -26632,13 +26656,13 @@
         <v>0</v>
       </c>
       <c r="E9" s="108" t="n">
-        <v>115</v>
+        <v>187</v>
       </c>
       <c r="F9" s="108" t="n">
         <v>13</v>
       </c>
       <c r="G9" s="108" t="n">
-        <v>1988.98</v>
+        <v>1975.42</v>
       </c>
       <c r="H9" s="60" t="inlineStr">
         <is>
@@ -26649,26 +26673,26 @@
     <row r="10">
       <c r="A10" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T22:54:37+09:00</t>
+          <t>2026-07-27T06:32:05+09:00</t>
         </is>
       </c>
       <c r="B10" s="108" t="n">
-        <v>55</v>
+        <v>89</v>
       </c>
       <c r="C10" s="108" t="n">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="D10" s="108" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E10" s="108" t="n">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="F10" s="108" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G10" s="108" t="n">
-        <v>3379.75</v>
+        <v>1988.98</v>
       </c>
       <c r="H10" s="60" t="inlineStr">
         <is>
@@ -26679,26 +26703,26 @@
     <row r="11">
       <c r="A11" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T22:13:31+09:00</t>
+          <t>2026-07-26T22:54:37+09:00</t>
         </is>
       </c>
       <c r="B11" s="108" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="C11" s="108" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="D11" s="108" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E11" s="108" t="n">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F11" s="108" t="n">
         <v>10</v>
       </c>
       <c r="G11" s="108" t="n">
-        <v>1655.72</v>
+        <v>3379.75</v>
       </c>
       <c r="H11" s="60" t="inlineStr">
         <is>
@@ -26709,127 +26733,127 @@
     <row r="12">
       <c r="A12" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T21:45:54+09:00</t>
+          <t>2026-07-26T22:13:31+09:00</t>
         </is>
       </c>
       <c r="B12" s="108" t="n">
-        <v>128</v>
+        <v>47</v>
       </c>
       <c r="C12" s="108" t="n">
-        <v>73</v>
+        <v>37</v>
       </c>
       <c r="D12" s="108" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E12" s="108" t="n">
-        <v>603</v>
+        <v>124</v>
       </c>
       <c r="F12" s="108" t="n">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="G12" s="108" t="n">
-        <v>1492.56</v>
+        <v>1655.72</v>
       </c>
       <c r="H12" s="60" t="inlineStr">
         <is>
-          <t>Historical backfill: policy 365d / technology 183d</t>
+          <t>Daily update</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T21:29:09+09:00</t>
+          <t>2026-07-26T21:45:54+09:00</t>
         </is>
       </c>
       <c r="B13" s="108" t="n">
-        <v>41</v>
+        <v>128</v>
       </c>
       <c r="C13" s="108" t="n">
-        <v>31</v>
+        <v>73</v>
       </c>
       <c r="D13" s="108" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E13" s="108" t="n">
-        <v>76</v>
+        <v>603</v>
       </c>
       <c r="F13" s="108" t="n">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="G13" s="108" t="n">
-        <v>832.08</v>
+        <v>1492.56</v>
       </c>
       <c r="H13" s="60" t="inlineStr">
         <is>
-          <t>Daily update</t>
+          <t>Historical backfill: policy 365d / technology 183d</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T21:02:36+09:00</t>
+          <t>2026-07-26T21:29:09+09:00</t>
         </is>
       </c>
       <c r="B14" s="108" t="n">
-        <v>108</v>
+        <v>41</v>
       </c>
       <c r="C14" s="108" t="n">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="D14" s="108" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E14" s="108" t="n">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="F14" s="108" t="n">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="G14" s="108" t="n">
-        <v>1376.15</v>
+        <v>832.08</v>
       </c>
       <c r="H14" s="60" t="inlineStr">
         <is>
-          <t>Historical backfill: policy 365d / technology 183d</t>
+          <t>Daily update</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T20:36:29+09:00</t>
+          <t>2026-07-26T21:02:36+09:00</t>
         </is>
       </c>
       <c r="B15" s="108" t="n">
-        <v>38</v>
+        <v>108</v>
       </c>
       <c r="C15" s="108" t="n">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="D15" s="108" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="E15" s="108" t="n">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="F15" s="108" t="n">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="G15" s="108" t="n">
-        <v>93.7</v>
+        <v>1376.15</v>
       </c>
       <c r="H15" s="60" t="inlineStr">
         <is>
-          <t>Daily update</t>
+          <t>Historical backfill: policy 365d / technology 183d</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T20:34:08+09:00</t>
+          <t>2026-07-26T20:36:29+09:00</t>
         </is>
       </c>
       <c r="B16" s="108" t="n">
@@ -26839,7 +26863,7 @@
         <v>28</v>
       </c>
       <c r="D16" s="108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E16" s="108" t="n">
         <v>74</v>
@@ -26848,7 +26872,7 @@
         <v>10</v>
       </c>
       <c r="G16" s="108" t="n">
-        <v>20.27</v>
+        <v>93.7</v>
       </c>
       <c r="H16" s="60" t="inlineStr">
         <is>
@@ -26859,7 +26883,7 @@
     <row r="17">
       <c r="A17" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T20:29:40+09:00</t>
+          <t>2026-07-26T20:34:08+09:00</t>
         </is>
       </c>
       <c r="B17" s="108" t="n">
@@ -26869,16 +26893,16 @@
         <v>28</v>
       </c>
       <c r="D17" s="108" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E17" s="108" t="n">
-        <v>11</v>
+        <v>74</v>
       </c>
       <c r="F17" s="108" t="n">
         <v>10</v>
       </c>
       <c r="G17" s="108" t="n">
-        <v>141.79</v>
+        <v>20.27</v>
       </c>
       <c r="H17" s="60" t="inlineStr">
         <is>
@@ -26889,7 +26913,7 @@
     <row r="18">
       <c r="A18" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T20:24:57+09:00</t>
+          <t>2026-07-26T20:29:40+09:00</t>
         </is>
       </c>
       <c r="B18" s="108" t="n">
@@ -26899,16 +26923,16 @@
         <v>28</v>
       </c>
       <c r="D18" s="108" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E18" s="108" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="F18" s="108" t="n">
         <v>10</v>
       </c>
       <c r="G18" s="108" t="n">
-        <v>134.95</v>
+        <v>141.79</v>
       </c>
       <c r="H18" s="60" t="inlineStr">
         <is>
@@ -26919,7 +26943,7 @@
     <row r="19">
       <c r="A19" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T20:19:15+09:00</t>
+          <t>2026-07-26T20:24:57+09:00</t>
         </is>
       </c>
       <c r="B19" s="108" t="n">
@@ -26929,16 +26953,16 @@
         <v>28</v>
       </c>
       <c r="D19" s="108" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E19" s="108" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F19" s="108" t="n">
         <v>10</v>
       </c>
       <c r="G19" s="108" t="n">
-        <v>134.05</v>
+        <v>134.95</v>
       </c>
       <c r="H19" s="60" t="inlineStr">
         <is>
@@ -26949,26 +26973,26 @@
     <row r="20">
       <c r="A20" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T20:13:43+09:00</t>
+          <t>2026-07-26T20:19:15+09:00</t>
         </is>
       </c>
       <c r="B20" s="108" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C20" s="108" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D20" s="108" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E20" s="108" t="n">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="F20" s="108" t="n">
         <v>10</v>
       </c>
       <c r="G20" s="108" t="n">
-        <v>162.46</v>
+        <v>134.05</v>
       </c>
       <c r="H20" s="60" t="inlineStr">
         <is>
@@ -26979,7 +27003,7 @@
     <row r="21">
       <c r="A21" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T20:00:03+09:00</t>
+          <t>2026-07-26T20:13:43+09:00</t>
         </is>
       </c>
       <c r="B21" s="108" t="n">
@@ -26989,16 +27013,16 @@
         <v>24</v>
       </c>
       <c r="D21" s="108" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E21" s="108" t="n">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="F21" s="108" t="n">
         <v>10</v>
       </c>
       <c r="G21" s="108" t="n">
-        <v>154.27</v>
+        <v>162.46</v>
       </c>
       <c r="H21" s="60" t="inlineStr">
         <is>
@@ -27009,7 +27033,7 @@
     <row r="22">
       <c r="A22" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T19:51:39+09:00</t>
+          <t>2026-07-26T20:00:03+09:00</t>
         </is>
       </c>
       <c r="B22" s="108" t="n">
@@ -27019,16 +27043,16 @@
         <v>24</v>
       </c>
       <c r="D22" s="108" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E22" s="108" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="F22" s="108" t="n">
         <v>10</v>
       </c>
       <c r="G22" s="108" t="n">
-        <v>11.55</v>
+        <v>154.27</v>
       </c>
       <c r="H22" s="60" t="inlineStr">
         <is>
@@ -27039,26 +27063,26 @@
     <row r="23">
       <c r="A23" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T19:10:55+09:00</t>
+          <t>2026-07-26T19:51:39+09:00</t>
         </is>
       </c>
       <c r="B23" s="108" t="n">
         <v>34</v>
       </c>
       <c r="C23" s="108" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D23" s="108" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E23" s="108" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F23" s="108" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G23" s="108" t="n">
-        <v>194.65</v>
+        <v>11.55</v>
       </c>
       <c r="H23" s="60" t="inlineStr">
         <is>
@@ -27069,26 +27093,26 @@
     <row r="24">
       <c r="A24" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T19:05:06+09:00</t>
+          <t>2026-07-26T19:10:55+09:00</t>
         </is>
       </c>
       <c r="B24" s="108" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C24" s="108" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D24" s="108" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E24" s="108" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="F24" s="108" t="n">
         <v>9</v>
       </c>
       <c r="G24" s="108" t="n">
-        <v>165.89</v>
+        <v>194.65</v>
       </c>
       <c r="H24" s="60" t="inlineStr">
         <is>
@@ -27099,35 +27123,65 @@
     <row r="25">
       <c r="A25" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T19:05:06+09:00</t>
         </is>
       </c>
       <c r="B25" s="108" t="n">
         <v>33</v>
       </c>
       <c r="C25" s="108" t="n">
+        <v>24</v>
+      </c>
+      <c r="D25" s="108" t="n">
+        <v>5</v>
+      </c>
+      <c r="E25" s="108" t="n">
+        <v>39</v>
+      </c>
+      <c r="F25" s="108" t="n">
+        <v>9</v>
+      </c>
+      <c r="G25" s="108" t="n">
+        <v>165.89</v>
+      </c>
+      <c r="H25" s="60" t="inlineStr">
+        <is>
+          <t>Daily update</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="106" t="inlineStr">
+        <is>
+          <t>2026-07-26T18:56:03+09:00</t>
+        </is>
+      </c>
+      <c r="B26" s="108" t="n">
+        <v>33</v>
+      </c>
+      <c r="C26" s="108" t="n">
         <v>20</v>
       </c>
-      <c r="D25" s="108" t="n">
+      <c r="D26" s="108" t="n">
         <v>94</v>
       </c>
-      <c r="E25" s="108" t="n">
+      <c r="E26" s="108" t="n">
         <v>0</v>
       </c>
-      <c r="F25" s="108" t="n">
+      <c r="F26" s="108" t="n">
         <v>13</v>
       </c>
-      <c r="G25" s="108" t="n">
+      <c r="G26" s="108" t="n">
         <v>129.43</v>
       </c>
-      <c r="H25" s="60" t="inlineStr">
+      <c r="H26" s="60" t="inlineStr">
         <is>
           <t>Initial lookback</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:H25"/>
+  <autoFilter ref="A3:H26"/>
   <mergeCells count="2">
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>

--- a/docs/innovation_news_ledger.xlsx
+++ b/docs/innovation_news_ledger.xlsx
@@ -9,9 +9,9 @@
     <sheet name="Run Log" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'News Ledger'!$A$3:$O$146</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'News Ledger'!$A$3:$O$175</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Source Registry'!$A$3:$N$263</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Run Log'!$A$3:$H$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Run Log'!$A$3:$H$29</definedName>
   </definedNames>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -620,7 +620,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="NewsLedgerTable" displayName="NewsLedgerTable" ref="A3:O146" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="NewsLedgerTable" displayName="NewsLedgerTable" ref="A3:O175" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <autoFilter ref="A3:O4"/>
   <tableColumns count="15">
     <tableColumn id="1" name="Collected At (JST)"/>
@@ -667,7 +667,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="RunLogTable" displayName="RunLogTable" ref="A3:H28" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="RunLogTable" displayName="RunLogTable" ref="A3:H29" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <autoFilter ref="A3:H4"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Run Time (JST)"/>
@@ -951,7 +951,7 @@
       </c>
       <c r="B5" s="25" t="inlineStr">
         <is>
-          <t>2026-07-28T01:34:11+09:00</t>
+          <t>2026-07-28T01:39:30+09:00</t>
         </is>
       </c>
       <c r="C5" s="46" t="n"/>
@@ -1239,7 +1239,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O146"/>
+  <dimension ref="A1:O175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -5776,61 +5776,65 @@
     <row r="63" ht="42" customHeight="1">
       <c r="A63" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T21:45:54+09:00</t>
+          <t>2026-07-28T01:39:30+09:00</t>
         </is>
       </c>
       <c r="B63" s="106" t="inlineStr">
         <is>
-          <t>2026-07-24T01:25:22Z</t>
+          <t>2026-07-24T17:59:57Z</t>
         </is>
       </c>
       <c r="C63" s="60" t="inlineStr">
         <is>
-          <t>EU &amp; Europe</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D63" s="60" t="inlineStr">
         <is>
-          <t>European Patent Organisation</t>
-        </is>
-      </c>
-      <c r="E63" s="60" t="inlineStr"/>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E63" s="60" t="inlineStr">
+        <is>
+          <t>Robotics</t>
+        </is>
+      </c>
       <c r="F63" s="107" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G63" s="60" t="inlineStr">
         <is>
-          <t>Intergovernmental</t>
+          <t>Preprint</t>
         </is>
       </c>
       <c r="H63" s="60" t="inlineStr">
         <is>
-          <t>European Patent Office News</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="I63" s="60" t="inlineStr">
         <is>
-          <t>EPOが2037年までPCT権限を継続</t>
+          <t>ロボットレンダリングによるロボット因子化世界モデル</t>
         </is>
       </c>
       <c r="J63" s="60" t="inlineStr">
         <is>
-          <t>PCT総会はEPOを国際調査および予備審査機関として再任した。</t>
+          <t>行動条件付きのビデオ世界モデルが、ロボットの動作を予測する新しいアプローチを提案している。</t>
         </is>
       </c>
       <c r="K63" s="60" t="inlineStr">
         <is>
-          <t>https://www.epo.org/en/news-events/news/epo-continue-key-role-pct-authority-until-2037</t>
+          <t>https://arxiv.org/abs/2607.22535v1</t>
         </is>
       </c>
       <c r="L63" s="60" t="inlineStr">
         <is>
-          <t>0709c55767ed6dbd79c145c1</t>
+          <t>67e85214fe27170085cdf258</t>
         </is>
       </c>
       <c r="M63" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T21:45:54+09:00</t>
+          <t>2026-07-28T01:39:30+09:00</t>
         </is>
       </c>
       <c r="N63" s="60" t="inlineStr">
@@ -5840,24 +5844,24 @@
       </c>
       <c r="O63" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: Patents &amp; Intellectual Property / 学術区分: News &amp; Official Release / 焦点: PCTにおけるEPOの役割</t>
+          <t>枠: Technology Innovation / 学術区分: Preprint / 査読表示: Not peer reviewed / 焦点: ロボットの行動条件付きビデオ世界モデル</t>
         </is>
       </c>
     </row>
     <row r="64" ht="42" customHeight="1">
       <c r="A64" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T20:36:29+09:00</t>
+          <t>2026-07-28T01:39:30+09:00</t>
         </is>
       </c>
       <c r="B64" s="106" t="inlineStr">
         <is>
-          <t>2026-07-24T00:00:00Z</t>
+          <t>2026-07-24T17:59:51Z</t>
         </is>
       </c>
       <c r="C64" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D64" s="60" t="inlineStr">
@@ -5871,41 +5875,41 @@
         </is>
       </c>
       <c r="F64" s="107" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G64" s="60" t="inlineStr">
         <is>
-          <t>Scientific Publication</t>
+          <t>Preprint</t>
         </is>
       </c>
       <c r="H64" s="60" t="inlineStr">
         <is>
-          <t>Nature</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="I64" s="60" t="inlineStr">
         <is>
-          <t>ホワイトハウスがAI資金を発表 — 米国科学の新時代を示唆</t>
+          <t>SM4RT: 4D再構築のための構造化運動幾何学の学習</t>
         </is>
       </c>
       <c r="J64" s="60" t="inlineStr">
         <is>
-          <t>米国の科学顧問が資金調達の改革を呼びかけ、AIを用いた研究を加速するための助成金を配布した。</t>
+          <t>幾何学基盤モデルがモノキュラー3D再構築を進展させ、4D動的理解への拡張を目指している。</t>
         </is>
       </c>
       <c r="K64" s="60" t="inlineStr">
         <is>
-          <t>https://www.nature.com/articles/d41586-026-02332-8</t>
+          <t>https://arxiv.org/abs/2607.22534v1</t>
         </is>
       </c>
       <c r="L64" s="60" t="inlineStr">
         <is>
-          <t>856206151844f412d95b7a9b</t>
+          <t>9274a8e28ab44e70e244fb9d</t>
         </is>
       </c>
       <c r="M64" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T20:36:29+09:00</t>
+          <t>2026-07-28T01:39:30+09:00</t>
         </is>
       </c>
       <c r="N64" s="60" t="inlineStr">
@@ -5915,68 +5919,72 @@
       </c>
       <c r="O64" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: R&amp;D Funding &amp; Tax Incentives / 学術区分: News &amp; Official Release / 焦点: AI研究の資金調達</t>
+          <t>枠: Technology Innovation / 学術区分: Preprint / 査読表示: Not peer reviewed / 焦点: 4D再構築のための構造化運動幾何学</t>
         </is>
       </c>
     </row>
     <row r="65" ht="42" customHeight="1">
       <c r="A65" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T21:45:54+09:00</t>
+          <t>2026-07-28T01:39:30+09:00</t>
         </is>
       </c>
       <c r="B65" s="106" t="inlineStr">
         <is>
-          <t>2026-07-23T04:00:01Z</t>
+          <t>2026-07-24T17:59:33Z</t>
         </is>
       </c>
       <c r="C65" s="60" t="inlineStr">
         <is>
-          <t>EU &amp; Europe</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D65" s="60" t="inlineStr">
         <is>
-          <t>European Patent Organisation</t>
-        </is>
-      </c>
-      <c r="E65" s="60" t="inlineStr"/>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E65" s="60" t="inlineStr">
+        <is>
+          <t>Robotics</t>
+        </is>
+      </c>
       <c r="F65" s="107" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G65" s="60" t="inlineStr">
         <is>
-          <t>Intergovernmental</t>
+          <t>Preprint</t>
         </is>
       </c>
       <c r="H65" s="60" t="inlineStr">
         <is>
-          <t>European Patent Office News</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="I65" s="60" t="inlineStr">
         <is>
-          <t>特許付与プロセスが2027年4月1日から完全デジタル化</t>
+          <t>ViTacWorld: 接触豊富なロボット操作のためのビジュオタクティル世界モデルの拡張</t>
         </is>
       </c>
       <c r="J65" s="60" t="inlineStr">
         <is>
-          <t>EPOは、ユーザーとの密接な協力のもとで数年間のデジタル変革を経て、特許のデジタル申請と通知を義務化する準備を進めている。</t>
+          <t>接触豊富なロボット操作に必要な物理的相互作用の手がかりを提供する新しいモデルが開発されている。</t>
         </is>
       </c>
       <c r="K65" s="60" t="inlineStr">
         <is>
-          <t>https://www.epo.org/en/news-events/news/patent-granting-process-fully-digital-1-april-2027</t>
+          <t>https://arxiv.org/abs/2607.22530v1</t>
         </is>
       </c>
       <c r="L65" s="60" t="inlineStr">
         <is>
-          <t>0f53b9e079b5f01ec34debad</t>
+          <t>e9a68a9d11693ead04f5ff62</t>
         </is>
       </c>
       <c r="M65" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T21:45:54+09:00</t>
+          <t>2026-07-28T01:39:30+09:00</t>
         </is>
       </c>
       <c r="N65" s="60" t="inlineStr">
@@ -5986,19 +5994,19 @@
       </c>
       <c r="O65" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: Patents &amp; Intellectual Property / 学術区分: News &amp; Official Release / 焦点: 特許のデジタル申請および通知の義務化</t>
+          <t>枠: Technology Innovation / 学術区分: Preprint / 査読表示: Not peer reviewed / 焦点: 接触豊富なロボット操作のためのビジュオタクティル世界モデル</t>
         </is>
       </c>
     </row>
     <row r="66" ht="42" customHeight="1">
       <c r="A66" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T21:29:09+09:00</t>
+          <t>2026-07-28T01:39:30+09:00</t>
         </is>
       </c>
       <c r="B66" s="106" t="inlineStr">
         <is>
-          <t>2026-07-23T00:00:00Z</t>
+          <t>2026-07-24T17:16:19Z</t>
         </is>
       </c>
       <c r="C66" s="60" t="inlineStr">
@@ -6013,7 +6021,7 @@
       </c>
       <c r="E66" s="60" t="inlineStr">
         <is>
-          <t>Robotics</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="F66" s="107" t="n">
@@ -6021,37 +6029,37 @@
       </c>
       <c r="G66" s="60" t="inlineStr">
         <is>
-          <t>Journal Article</t>
+          <t>Preprint</t>
         </is>
       </c>
       <c r="H66" s="60" t="inlineStr">
         <is>
-          <t>Science Advances</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="I66" s="60" t="inlineStr">
         <is>
-          <t>自己探求によるロボットの行動と言語の発展</t>
+          <t>安定器コードにおける相関コヒーレントエラー：一般的なキュムラントフレームワークと干渉ベースのエラー抑制</t>
         </is>
       </c>
       <c r="J66" s="60" t="inlineStr">
         <is>
-          <t>ロボットが自己探求を通じて行動と言語を学ぶ過程を探る研究が行われた。</t>
+          <t>安定器コードにおけるコヒーレントエラーの相関を解析し、量子エラー訂正サイクルにおける論理チャネルを導出する新しい枠組みを提案。</t>
         </is>
       </c>
       <c r="K66" s="60" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1126/sciadv.aee7533</t>
+          <t>https://arxiv.org/abs/2607.22503v1</t>
         </is>
       </c>
       <c r="L66" s="60" t="inlineStr">
         <is>
-          <t>c833fd421c298cf895263644</t>
+          <t>913276e450c52ac5e38f6962</t>
         </is>
       </c>
       <c r="M66" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T21:29:09+09:00</t>
+          <t>2026-07-28T01:39:30+09:00</t>
         </is>
       </c>
       <c r="N66" s="60" t="inlineStr">
@@ -6061,24 +6069,24 @@
       </c>
       <c r="O66" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: Journal Article / 査読表示: Journal record — confirm peer review on publisher page / 掲載誌・学会: Science Advances / 焦点: ロボットの自己探求による行動と言語の発展 / OpenAlex record; work type=article; citations=1</t>
+          <t>枠: Technology Innovation / 学術区分: Preprint / 査読表示: Not peer reviewed / 焦点: 量子エラー訂正</t>
         </is>
       </c>
     </row>
     <row r="67" ht="42" customHeight="1">
       <c r="A67" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T21:29:09+09:00</t>
+          <t>2026-07-28T01:39:30+09:00</t>
         </is>
       </c>
       <c r="B67" s="106" t="inlineStr">
         <is>
-          <t>2026-07-23T00:00:00Z</t>
+          <t>2026-07-24T17:13:24Z</t>
         </is>
       </c>
       <c r="C67" s="60" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D67" s="60" t="inlineStr">
@@ -6088,7 +6096,7 @@
       </c>
       <c r="E67" s="60" t="inlineStr">
         <is>
-          <t>Robotics | Artificial Intelligence</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="F67" s="107" t="n">
@@ -6096,37 +6104,37 @@
       </c>
       <c r="G67" s="60" t="inlineStr">
         <is>
-          <t>Journal Article</t>
+          <t>Preprint</t>
         </is>
       </c>
       <c r="H67" s="60" t="inlineStr">
         <is>
-          <t>Frontiers in Neurorobotics</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="I67" s="60" t="inlineStr">
         <is>
-          <t>AI駆動の四足ロボット：基本的な移動から高度な生物模倣行動まで</t>
+          <t>Kalb-Ramondスカラー電磁気学における1ループ効果的ポテンシャル</t>
         </is>
       </c>
       <c r="J67" s="60" t="inlineStr">
         <is>
-          <t>四足ロボットの技術開発に関する文献レビューが行われ、AIの進展がその能力を拡張していることが示された。</t>
+          <t>Kalb-Ramondスカラー電磁気学における1ループの効果的ポテンシャルを計算し、量子補正を導出する手法を示す。</t>
         </is>
       </c>
       <c r="K67" s="60" t="inlineStr">
         <is>
-          <t>https://doi.org/10.3389/fnbot.2026.1855550</t>
+          <t>https://arxiv.org/abs/2607.22501v1</t>
         </is>
       </c>
       <c r="L67" s="60" t="inlineStr">
         <is>
-          <t>e165800add9d682af8ea2122</t>
+          <t>77d754d5d6e27f112a68b696</t>
         </is>
       </c>
       <c r="M67" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T21:29:09+09:00</t>
+          <t>2026-07-28T01:39:30+09:00</t>
         </is>
       </c>
       <c r="N67" s="60" t="inlineStr">
@@ -6136,19 +6144,19 @@
       </c>
       <c r="O67" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: Journal Article / 査読表示: Journal record — confirm peer review on publisher page / 掲載誌・学会: Frontiers in Neurorobotics / 焦点: AI駆動の四足ロボット / OpenAlex record; work type=article; citations=0</t>
+          <t>枠: Technology Innovation / 学術区分: Preprint / 査読表示: Not peer reviewed / 焦点: 量子電磁気学の効果的ポテンシャル</t>
         </is>
       </c>
     </row>
     <row r="68" ht="42" customHeight="1">
       <c r="A68" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T21:29:09+09:00</t>
+          <t>2026-07-28T01:39:30+09:00</t>
         </is>
       </c>
       <c r="B68" s="106" t="inlineStr">
         <is>
-          <t>2026-07-23T00:00:00Z</t>
+          <t>2026-07-24T17:11:09Z</t>
         </is>
       </c>
       <c r="C68" s="60" t="inlineStr">
@@ -6163,7 +6171,7 @@
       </c>
       <c r="E68" s="60" t="inlineStr">
         <is>
-          <t>Fusion Energy</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="F68" s="107" t="n">
@@ -6171,37 +6179,37 @@
       </c>
       <c r="G68" s="60" t="inlineStr">
         <is>
-          <t>Journal Article</t>
+          <t>Preprint</t>
         </is>
       </c>
       <c r="H68" s="60" t="inlineStr">
         <is>
-          <t>Nuclear Fusion</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="I68" s="60" t="inlineStr">
         <is>
-          <t>Wendelstein 7-Xにおける高速イオンの閉じ込めにおける放射電場の役割</t>
+          <t>整数線形計画法を用いた自動フラグベースの故障耐性状態準備</t>
         </is>
       </c>
       <c r="J68" s="60" t="inlineStr">
         <is>
-          <t>Wendelstein 7-Xにおける高速イオンの閉じ込めに関する研究が行われ、放射電場の影響が分析された。</t>
+          <t>故障耐性量子計算における状態準備の自動化手法を提案し、ゲート数の削減を目指す。</t>
         </is>
       </c>
       <c r="K68" s="60" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1088/1741-4326/ae8f55</t>
+          <t>https://arxiv.org/abs/2607.22498v1</t>
         </is>
       </c>
       <c r="L68" s="60" t="inlineStr">
         <is>
-          <t>eef01d292bfb6d5bb3537528</t>
+          <t>0396bbeabfb025762de79b3a</t>
         </is>
       </c>
       <c r="M68" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T21:29:09+09:00</t>
+          <t>2026-07-28T01:39:30+09:00</t>
         </is>
       </c>
       <c r="N68" s="60" t="inlineStr">
@@ -6211,19 +6219,19 @@
       </c>
       <c r="O68" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: Journal Article / 査読表示: Journal record — confirm peer review on publisher page / 掲載誌・学会: Nuclear Fusion / 焦点: Wendelstein 7-Xの高速イオンの閉じ込め / OpenAlex record; work type=article; citations=0</t>
+          <t>枠: Technology Innovation / 学術区分: Preprint / 査読表示: Not peer reviewed / 焦点: 量子状態準備の自動化</t>
         </is>
       </c>
     </row>
     <row r="69" ht="42" customHeight="1">
       <c r="A69" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T21:29:09+09:00</t>
+          <t>2026-07-28T01:39:30+09:00</t>
         </is>
       </c>
       <c r="B69" s="106" t="inlineStr">
         <is>
-          <t>2026-07-23T00:00:00Z</t>
+          <t>2026-07-24T17:09:16Z</t>
         </is>
       </c>
       <c r="C69" s="60" t="inlineStr">
@@ -6238,7 +6246,7 @@
       </c>
       <c r="E69" s="60" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="F69" s="107" t="n">
@@ -6246,37 +6254,37 @@
       </c>
       <c r="G69" s="60" t="inlineStr">
         <is>
-          <t>Journal Article</t>
+          <t>Preprint</t>
         </is>
       </c>
       <c r="H69" s="60" t="inlineStr">
         <is>
-          <t>Scientific Reports</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="I69" s="60" t="inlineStr">
         <is>
-          <t>密なプラズマフォーカスにおけるクーロン爆発の研究</t>
+          <t>ホログラフィーにおけるダイラトン状態、相転移、臨界性</t>
         </is>
       </c>
       <c r="J69" s="60" t="inlineStr">
         <is>
-          <t>密なプラズマフォーカスにおけるクーロン爆発のシミュレーション研究が行われ、極端な条件下での挙動が分析された。</t>
+          <t>ダイラトンの存在と相転移に関する新しい理論的考察を行い、量子場理論における重要な問題を探求。</t>
         </is>
       </c>
       <c r="K69" s="60" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1038/s41598-026-63204-9</t>
+          <t>https://arxiv.org/abs/2607.22497v1</t>
         </is>
       </c>
       <c r="L69" s="60" t="inlineStr">
         <is>
-          <t>fcf607380491b3f6666abab6</t>
+          <t>690d6e9559cc67ddc5ce55ae</t>
         </is>
       </c>
       <c r="M69" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T21:29:09+09:00</t>
+          <t>2026-07-28T01:39:30+09:00</t>
         </is>
       </c>
       <c r="N69" s="60" t="inlineStr">
@@ -6286,19 +6294,19 @@
       </c>
       <c r="O69" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: Journal Article / 査読表示: Journal record — confirm peer review on publisher page / 掲載誌・学会: Scientific Reports / 焦点: 密なプラズマフォーカスにおけるクーロン爆発の研究 / OpenAlex record; work type=article; citations=0</t>
+          <t>枠: Technology Innovation / 学術区分: Preprint / 査読表示: Not peer reviewed / 焦点: ホログラフィーにおけるダイラトンと相転移</t>
         </is>
       </c>
     </row>
     <row r="70" ht="42" customHeight="1">
       <c r="A70" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T21:29:09+09:00</t>
+          <t>2026-07-28T01:39:30+09:00</t>
         </is>
       </c>
       <c r="B70" s="106" t="inlineStr">
         <is>
-          <t>2026-07-23T00:00:00Z</t>
+          <t>2026-07-24T17:06:05Z</t>
         </is>
       </c>
       <c r="C70" s="60" t="inlineStr">
@@ -6317,7 +6325,7 @@
         </is>
       </c>
       <c r="F70" s="107" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G70" s="60" t="inlineStr">
         <is>
@@ -6326,32 +6334,32 @@
       </c>
       <c r="H70" s="60" t="inlineStr">
         <is>
-          <t>Zenodo (CERN European Organization for Nuclear Research)</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="I70" s="60" t="inlineStr">
         <is>
-          <t>プライム・レックス理論と量子技術ガバナンス：キュービットから量子主権へ</t>
+          <t>フラクタル量子多体スカーとZX計算からのハミルトニアン逆設計</t>
         </is>
       </c>
       <c r="J70" s="60" t="inlineStr">
         <is>
-          <t>OECDが採択した量子技術に関する提言を基に、量子技術のガバナンスの枠組みを構築する方法を探求した。</t>
+          <t>ZX計算を用いてフラクタル多体状態を構築する新しい手法を提案し、量子プロセスの理解を深める。</t>
         </is>
       </c>
       <c r="K70" s="60" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5281/zenodo.21512028</t>
+          <t>https://arxiv.org/abs/2607.22495v1</t>
         </is>
       </c>
       <c r="L70" s="60" t="inlineStr">
         <is>
-          <t>61f1fcfb9afff652f523d019</t>
+          <t>0382e06bbc9f67fed6530b29</t>
         </is>
       </c>
       <c r="M70" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T21:29:09+09:00</t>
+          <t>2026-07-28T01:39:30+09:00</t>
         </is>
       </c>
       <c r="N70" s="60" t="inlineStr">
@@ -6361,72 +6369,72 @@
       </c>
       <c r="O70" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation | Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: Preprint / 査読表示: Not peer reviewed / 掲載誌・学会: Zenodo (CERN European Organization for Nuclear Research) / 焦点: 量子技術のガバナンスとOECDの提言 / OpenAlex record; work type=preprint; citations=0</t>
+          <t>枠: Technology Innovation / 学術区分: Preprint / 査読表示: Not peer reviewed / 焦点: 量子多体スカー状態の構築</t>
         </is>
       </c>
     </row>
     <row r="71" ht="42" customHeight="1">
       <c r="A71" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T20:29:40+09:00</t>
+          <t>2026-07-28T01:39:30+09:00</t>
         </is>
       </c>
       <c r="B71" s="106" t="inlineStr">
         <is>
-          <t>2026-07-22T14:12:14Z</t>
+          <t>2026-07-24T17:02:03Z</t>
         </is>
       </c>
       <c r="C71" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D71" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="E71" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="F71" s="107" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G71" s="60" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Preprint</t>
         </is>
       </c>
       <c r="H71" s="60" t="inlineStr">
         <is>
-          <t>DOE Office of Science News</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="I71" s="60" t="inlineStr">
         <is>
-          <t>エネルギー長官がAI駆動の科学的発見を加速するプロジェクトを発表</t>
+          <t>正の密度におけるハートリーからブラソフへの半古典的限界：強い時間一様収束と散乱</t>
         </is>
       </c>
       <c r="J71" s="60" t="inlineStr">
         <is>
-          <t>エネルギー長官クリス・ライトが、全米から選ばれた300のプロジェクトを発表し、エネルギーや発見科学、国家安全保障の分野でのブレークスルーを促進する。</t>
+          <t>ハートリー方程式からブラソフ方程式への強い収束を示し、量子と古典の初期摂動の整合性を探求。</t>
         </is>
       </c>
       <c r="K71" s="60" t="inlineStr">
         <is>
-          <t>https://www.energy.gov/articles/secretary-energy-chris-wright-announces-first-genesis-mission-projects-selected-accelerate</t>
+          <t>https://arxiv.org/abs/2607.22490v1</t>
         </is>
       </c>
       <c r="L71" s="60" t="inlineStr">
         <is>
-          <t>23fa1d6907c14d73ce3a41cd</t>
+          <t>e0cca36441c6165cea694240</t>
         </is>
       </c>
       <c r="M71" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T20:29:40+09:00</t>
+          <t>2026-07-28T01:39:30+09:00</t>
         </is>
       </c>
       <c r="N71" s="60" t="inlineStr">
@@ -6436,72 +6444,72 @@
       </c>
       <c r="O71" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: AI駆動の科学的発見を加速するプロジェクト</t>
+          <t>枠: Technology Innovation / 学術区分: Preprint / 査読表示: Not peer reviewed / 焦点: ハートリーからブラソフへの半古典的収束</t>
         </is>
       </c>
     </row>
     <row r="72" ht="42" customHeight="1">
       <c r="A72" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T19:05:06+09:00</t>
+          <t>2026-07-28T01:39:30+09:00</t>
         </is>
       </c>
       <c r="B72" s="106" t="inlineStr">
         <is>
-          <t>2026-07-22T13:53:19Z</t>
+          <t>2026-07-24T17:00:28Z</t>
         </is>
       </c>
       <c r="C72" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D72" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="E72" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="F72" s="107" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G72" s="60" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Preprint</t>
         </is>
       </c>
       <c r="H72" s="60" t="inlineStr">
         <is>
-          <t>National Science Foundation News</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="I72" s="60" t="inlineStr">
         <is>
-          <t>NSFがAI優先事項の推進に関する声明を発表</t>
+          <t>強相関または古典的限界における対称破れ自己相互作用補正の正確性：ハーモニウムによる実証</t>
         </is>
       </c>
       <c r="J72" s="60" t="inlineStr">
         <is>
-          <t>米国国家科学財団が、ホワイトハウスの科学技術政策室やエネルギー省と連携し、AIに関する優先事項を進めることを発表した。</t>
+          <t>強相関電子系における自己相互作用補正の理論的考察を行い、量子力学の限界を探求。</t>
         </is>
       </c>
       <c r="K72" s="60" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/news/statement-nsf-chief-staff-brian-stone-performing-duties-nsf-1</t>
+          <t>https://arxiv.org/abs/2607.22488v1</t>
         </is>
       </c>
       <c r="L72" s="60" t="inlineStr">
         <is>
-          <t>123e2207578ca69c8f9c00a2</t>
+          <t>fd78af21b1fceb9fc9041fff</t>
         </is>
       </c>
       <c r="M72" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T19:05:06+09:00</t>
+          <t>2026-07-28T01:39:30+09:00</t>
         </is>
       </c>
       <c r="N72" s="60" t="inlineStr">
@@ -6511,72 +6519,72 @@
       </c>
       <c r="O72" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: AI優先事項の推進</t>
+          <t>枠: Technology Innovation / 学術区分: Preprint / 査読表示: Not peer reviewed / 焦点: 強相関電子系における自己相互作用補正</t>
         </is>
       </c>
     </row>
     <row r="73" ht="42" customHeight="1">
       <c r="A73" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T19:05:06+09:00</t>
+          <t>2026-07-28T01:39:30+09:00</t>
         </is>
       </c>
       <c r="B73" s="106" t="inlineStr">
         <is>
-          <t>2026-07-22T13:53:12Z</t>
+          <t>2026-07-24T16:57:03Z</t>
         </is>
       </c>
       <c r="C73" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D73" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="E73" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="F73" s="107" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G73" s="60" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Preprint</t>
         </is>
       </c>
       <c r="H73" s="60" t="inlineStr">
         <is>
-          <t>National Science Foundation News</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="I73" s="60" t="inlineStr">
         <is>
-          <t>NSFがAIによる科学的発見のためのデータセット価値を解放する新プログラムを発表</t>
+          <t>量子材料を研究するための準粒子干渉</t>
         </is>
       </c>
       <c r="J73" s="60" t="inlineStr">
         <is>
-          <t>米国国立科学財団は、AIを活用した科学的発見のためのデータセット価値を解放するプログラムを発表しました。</t>
+          <t>量子材料の特性を理解するためには、材料の低エネルギー電子構造の詳細な知識が重要です。電子構造の詳細は、電子的不安定性や相関効果、新しい電子秩序に影響を与え、量子材料の特性を制御・設計するための現実的かつ詳細な理解が必要です。</t>
         </is>
       </c>
       <c r="K73" s="60" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/news/new-nsf-initiative-aims-unlock-dataset-value-ai-enabled</t>
+          <t>https://arxiv.org/abs/2607.22487v1</t>
         </is>
       </c>
       <c r="L73" s="60" t="inlineStr">
         <is>
-          <t>dcd819527d9b80141b26bcb8</t>
+          <t>4913b471343464799295241b</t>
         </is>
       </c>
       <c r="M73" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T19:05:06+09:00</t>
+          <t>2026-07-28T01:39:30+09:00</t>
         </is>
       </c>
       <c r="N73" s="60" t="inlineStr">
@@ -6586,72 +6594,72 @@
       </c>
       <c r="O73" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: R&amp;D Funding &amp; Tax Incentives / 学術区分: News &amp; Official Release / 焦点: AIを活用した科学的発見のためのデータセット</t>
+          <t>枠: Technology Innovation / 学術区分: Preprint / 査読表示: Not peer reviewed / 焦点: 量子材料の電子構造</t>
         </is>
       </c>
     </row>
     <row r="74" ht="42" customHeight="1">
       <c r="A74" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T20:29:40+09:00</t>
+          <t>2026-07-28T01:39:30+09:00</t>
         </is>
       </c>
       <c r="B74" s="106" t="inlineStr">
         <is>
-          <t>2026-07-22T13:53:06Z</t>
+          <t>2026-07-24T16:53:51Z</t>
         </is>
       </c>
       <c r="C74" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D74" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="E74" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Robotics</t>
         </is>
       </c>
       <c r="F74" s="107" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G74" s="60" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Preprint</t>
         </is>
       </c>
       <c r="H74" s="60" t="inlineStr">
         <is>
-          <t>National Science Foundation News</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="I74" s="60" t="inlineStr">
         <is>
-          <t>NSFがAI駆動の科学を進展させるために8300万ドルの投資を発表</t>
+          <t>モジュラーオンライン可変インピーダンスのためのフレームワーク</t>
         </is>
       </c>
       <c r="J74" s="60" t="inlineStr">
         <is>
-          <t>米国国立科学財団は、AI駆動の科学を進展させるために8300万ドルの投資を発表しました。</t>
+          <t>本論文では、異なるマニピュレーターに対して再利用可能なインフラを提供するロボット非依存のコンプライアンス制御フレームワークを提案します。プラグインベースのアーキテクチャにより、制御インフラと制御法の実装を分離しています。</t>
         </is>
       </c>
       <c r="K74" s="60" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/news/nsf-announces-83m-investment-integrated-data-systems</t>
+          <t>https://arxiv.org/abs/2607.22483v1</t>
         </is>
       </c>
       <c r="L74" s="60" t="inlineStr">
         <is>
-          <t>018d40b7e6eb7aa4b8cfb5fa</t>
+          <t>d8729b048d413ebb261721be</t>
         </is>
       </c>
       <c r="M74" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T20:29:40+09:00</t>
+          <t>2026-07-28T01:39:30+09:00</t>
         </is>
       </c>
       <c r="N74" s="60" t="inlineStr">
@@ -6661,68 +6669,72 @@
       </c>
       <c r="O74" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy | Research System &amp; Talent / 学術区分: News &amp; Official Release / 焦点: AI駆動の科学のためのデータシステム</t>
+          <t>枠: Technology Innovation / 学術区分: Preprint / 査読表示: Not peer reviewed / 焦点: ロボットのコンプライアンス制御フレームワーク</t>
         </is>
       </c>
     </row>
     <row r="75" ht="42" customHeight="1">
       <c r="A75" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T20:29:40+09:00</t>
+          <t>2026-07-28T01:39:30+09:00</t>
         </is>
       </c>
       <c r="B75" s="106" t="inlineStr">
         <is>
-          <t>2026-07-22T12:00:00Z</t>
+          <t>2026-07-24T16:39:06Z</t>
         </is>
       </c>
       <c r="C75" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D75" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E75" s="60" t="inlineStr"/>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E75" s="60" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence</t>
+        </is>
+      </c>
       <c r="F75" s="107" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G75" s="60" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Preprint</t>
         </is>
       </c>
       <c r="H75" s="60" t="inlineStr">
         <is>
-          <t>NIST News</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="I75" s="60" t="inlineStr">
         <is>
-          <t>NIST、中小企業向けの資金提供機会を発表</t>
+          <t>テストケース品質マイニングによる信頼性の高いコード生成</t>
         </is>
       </c>
       <c r="J75" s="60" t="inlineStr">
         <is>
-          <t>NIST MEPが中小企業向けの資金提供機会を発表し、2026年7月28日にウェビナーを開催する予定。</t>
+          <t>本論文では、自然言語要件のみで機能する自動テスト生成の課題に対処するため、相互検証に基づく閉ループのテスト駆動開発フレームワークを提案します。</t>
         </is>
       </c>
       <c r="K75" s="60" t="inlineStr">
         <is>
-          <t>https://www.nist.gov/news-events/news/2026/07/nist-announces-funding-opportunity-14-mep-centers-advance-small-and-medium</t>
+          <t>https://arxiv.org/abs/2607.22471v1</t>
         </is>
       </c>
       <c r="L75" s="60" t="inlineStr">
         <is>
-          <t>5aa9c93bc7040291c9f08bfa</t>
+          <t>68bbe68a19f8607f9b8c2513</t>
         </is>
       </c>
       <c r="M75" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T20:29:40+09:00</t>
+          <t>2026-07-28T01:39:30+09:00</t>
         </is>
       </c>
       <c r="N75" s="60" t="inlineStr">
@@ -6732,72 +6744,72 @@
       </c>
       <c r="O75" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: R&amp;D Funding &amp; Tax Incentives | Public Procurement &amp; Industrial Policy / 学術区分: News &amp; Official Release / 焦点: 中小企業向けの資金提供機会</t>
+          <t>枠: Technology Innovation / 学術区分: Preprint / 査読表示: Not peer reviewed / 焦点: テスト駆動開発におけるコード生成</t>
         </is>
       </c>
     </row>
     <row r="76" ht="42" customHeight="1">
       <c r="A76" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T21:02:36+09:00</t>
+          <t>2026-07-28T01:39:30+09:00</t>
         </is>
       </c>
       <c r="B76" s="106" t="inlineStr">
         <is>
-          <t>2026-07-22T05:00:56Z</t>
+          <t>2026-07-24T16:32:40Z</t>
         </is>
       </c>
       <c r="C76" s="60" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D76" s="60" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="E76" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Artificial Intelligence | Quantum | Fusion Energy</t>
         </is>
       </c>
       <c r="F76" s="107" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G76" s="60" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Preprint</t>
         </is>
       </c>
       <c r="H76" s="60" t="inlineStr">
         <is>
-          <t>NISTEP Updates</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="I76" s="60" t="inlineStr">
         <is>
-          <t>特定科学技術領域動向報告書 -AI（人工知能）- 研究開発インプット編を公表</t>
+          <t>トランスフォーマーモデルによる分子基底状態の準備</t>
         </is>
       </c>
       <c r="J76" s="60" t="inlineStr">
         <is>
-          <t>AI分野における研究開発状況を分析し、基礎データをまとめた報告書を公表。</t>
+          <t>量子状態準備は多くの量子アルゴリズムの重要な要素です。本研究では、電子構造計算のための基底状態準備回路を合成する生成AIフレームワークADAPT-GQEを紹介します。</t>
         </is>
       </c>
       <c r="K76" s="60" t="inlineStr">
         <is>
-          <t>https://www.nistep.go.jp/archives/63583/</t>
+          <t>https://arxiv.org/abs/2607.22468v1</t>
         </is>
       </c>
       <c r="L76" s="60" t="inlineStr">
         <is>
-          <t>6b6122461584a86ee7a1c595</t>
+          <t>84e66964299ab6d6bfe75723</t>
         </is>
       </c>
       <c r="M76" s="106" t="inlineStr">
         <is>
-          <t>2026-07-22T14:00:56+09:00</t>
+          <t>2026-07-28T01:39:30+09:00</t>
         </is>
       </c>
       <c r="N76" s="60" t="inlineStr">
@@ -6807,72 +6819,68 @@
       </c>
       <c r="O76" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation | Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: 人工知能（AI）分野の研究開発インプット</t>
+          <t>枠: Technology Innovation / 学術区分: Preprint / 査読表示: Not peer reviewed / 焦点: 量子状態準備のためのAIフレームワーク</t>
         </is>
       </c>
     </row>
     <row r="77" ht="42" customHeight="1">
       <c r="A77" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T21:02:36+09:00</t>
+          <t>2026-07-26T21:45:54+09:00</t>
         </is>
       </c>
       <c r="B77" s="106" t="inlineStr">
         <is>
-          <t>2026-07-22T00:00:00Z</t>
+          <t>2026-07-24T01:25:22Z</t>
         </is>
       </c>
       <c r="C77" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>EU &amp; Europe</t>
         </is>
       </c>
       <c r="D77" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E77" s="60" t="inlineStr">
-        <is>
-          <t>Artificial Intelligence</t>
-        </is>
-      </c>
+          <t>European Patent Organisation</t>
+        </is>
+      </c>
+      <c r="E77" s="60" t="inlineStr"/>
       <c r="F77" s="107" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G77" s="60" t="inlineStr">
         <is>
-          <t>Policy Institute</t>
+          <t>Intergovernmental</t>
         </is>
       </c>
       <c r="H77" s="60" t="inlineStr">
         <is>
-          <t>Brookings TechTank</t>
+          <t>European Patent Office News</t>
         </is>
       </c>
       <c r="I77" s="60" t="inlineStr">
         <is>
-          <t>政策が世代ZのAIへの信頼を決定する</t>
+          <t>EPOが2037年までPCT権限を継続</t>
         </is>
       </c>
       <c r="J77" s="60" t="inlineStr">
         <is>
-          <t>世代ZのAIに対する信頼は、PRではなく政策によって決まると論じられている。</t>
+          <t>PCT総会はEPOを国際調査および予備審査機関として再任した。</t>
         </is>
       </c>
       <c r="K77" s="60" t="inlineStr">
         <is>
-          <t>https://www.brookings.edu/articles/policy-not-pr-will-determine-gen-zs-trust-in-ai/</t>
+          <t>https://www.epo.org/en/news-events/news/epo-continue-key-role-pct-authority-until-2037</t>
         </is>
       </c>
       <c r="L77" s="60" t="inlineStr">
         <is>
-          <t>61bd55f8ce5a2385a5420260</t>
+          <t>0709c55767ed6dbd79c145c1</t>
         </is>
       </c>
       <c r="M77" s="106" t="inlineStr">
         <is>
-          <t>2026-07-22T09:00:00+09:00</t>
+          <t>2026-07-26T21:45:54+09:00</t>
         </is>
       </c>
       <c r="N77" s="60" t="inlineStr">
@@ -6882,38 +6890,38 @@
       </c>
       <c r="O77" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: AIに対する信頼の構築</t>
+          <t>枠: Innovation Policy / 政策分野: Patents &amp; Intellectual Property / 学術区分: News &amp; Official Release / 焦点: PCTにおけるEPOの役割</t>
         </is>
       </c>
     </row>
     <row r="78" ht="42" customHeight="1">
       <c r="A78" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T21:02:36+09:00</t>
+          <t>2026-07-26T20:36:29+09:00</t>
         </is>
       </c>
       <c r="B78" s="106" t="inlineStr">
         <is>
-          <t>2026-07-22T00:00:00Z</t>
+          <t>2026-07-24T00:00:00Z</t>
         </is>
       </c>
       <c r="C78" s="60" t="inlineStr">
         <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D78" s="60" t="inlineStr">
+        <is>
           <t>Global</t>
         </is>
       </c>
-      <c r="D78" s="60" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
       <c r="E78" s="60" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="F78" s="107" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G78" s="60" t="inlineStr">
         <is>
@@ -6927,27 +6935,27 @@
       </c>
       <c r="I78" s="60" t="inlineStr">
         <is>
-          <t>ブラウンブルヘッドキャットフィッシュのメラノーマは新しい伝染性がんを示す</t>
+          <t>ホワイトハウスがAI資金を発表 — 米国科学の新時代を示唆</t>
         </is>
       </c>
       <c r="J78" s="60" t="inlineStr">
         <is>
-          <t>ブラウンブルヘッドキャットフィッシュの腫瘍と非腫瘍組織の全ゲノム配列解析により、自然に発生する伝染性がんの一種が明らかになった。</t>
+          <t>米国の科学顧問が資金調達の改革を呼びかけ、AIを用いた研究を加速するための助成金を配布した。</t>
         </is>
       </c>
       <c r="K78" s="60" t="inlineStr">
         <is>
-          <t>https://www.nature.com/articles/s41586-026-10832-w</t>
+          <t>https://www.nature.com/articles/d41586-026-02332-8</t>
         </is>
       </c>
       <c r="L78" s="60" t="inlineStr">
         <is>
-          <t>f9bccca3cabb5ce19441f09d</t>
+          <t>856206151844f412d95b7a9b</t>
         </is>
       </c>
       <c r="M78" s="106" t="inlineStr">
         <is>
-          <t>2026-07-22T09:00:00+09:00</t>
+          <t>2026-07-26T20:36:29+09:00</t>
         </is>
       </c>
       <c r="N78" s="60" t="inlineStr">
@@ -6957,72 +6965,68 @@
       </c>
       <c r="O78" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: トランスミッシブルがん</t>
+          <t>枠: Innovation Policy / 政策分野: R&amp;D Funding &amp; Tax Incentives / 学術区分: News &amp; Official Release / 焦点: AI研究の資金調達</t>
         </is>
       </c>
     </row>
     <row r="79" ht="42" customHeight="1">
       <c r="A79" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T21:02:36+09:00</t>
+          <t>2026-07-26T21:45:54+09:00</t>
         </is>
       </c>
       <c r="B79" s="106" t="inlineStr">
         <is>
-          <t>2026-07-22T00:00:00Z</t>
+          <t>2026-07-23T04:00:01Z</t>
         </is>
       </c>
       <c r="C79" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>EU &amp; Europe</t>
         </is>
       </c>
       <c r="D79" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="E79" s="60" t="inlineStr">
-        <is>
-          <t>Quantum</t>
-        </is>
-      </c>
+          <t>European Patent Organisation</t>
+        </is>
+      </c>
+      <c r="E79" s="60" t="inlineStr"/>
       <c r="F79" s="107" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G79" s="60" t="inlineStr">
         <is>
-          <t>Scientific Publication</t>
+          <t>Intergovernmental</t>
         </is>
       </c>
       <c r="H79" s="60" t="inlineStr">
         <is>
-          <t>Nature</t>
+          <t>European Patent Office News</t>
         </is>
       </c>
       <c r="I79" s="60" t="inlineStr">
         <is>
-          <t>量子パラエレクトリックSrTiO3におけるナノスケール極性テクスチャのイメージング</t>
+          <t>特許付与プロセスが2027年4月1日から完全デジタル化</t>
         </is>
       </c>
       <c r="J79" s="60" t="inlineStr">
         <is>
-          <t>Cryo-STEMを用いて、SrTiO3が105K以下で周期的な極性ナノドメインを形成することが明らかになった。</t>
+          <t>EPOは、ユーザーとの密接な協力のもとで数年間のデジタル変革を経て、特許のデジタル申請と通知を義務化する準備を進めている。</t>
         </is>
       </c>
       <c r="K79" s="60" t="inlineStr">
         <is>
-          <t>https://www.nature.com/articles/s41586-026-10823-x</t>
+          <t>https://www.epo.org/en/news-events/news/patent-granting-process-fully-digital-1-april-2027</t>
         </is>
       </c>
       <c r="L79" s="60" t="inlineStr">
         <is>
-          <t>f12f62aebb861877dd7a5cbf</t>
+          <t>0f53b9e079b5f01ec34debad</t>
         </is>
       </c>
       <c r="M79" s="106" t="inlineStr">
         <is>
-          <t>2026-07-22T09:00:00+09:00</t>
+          <t>2026-07-26T21:45:54+09:00</t>
         </is>
       </c>
       <c r="N79" s="60" t="inlineStr">
@@ -7032,19 +7036,19 @@
       </c>
       <c r="O79" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: 量子パラエレクトリックSrTiO3のナノスケール極性テクスチャのイメージング</t>
+          <t>枠: Innovation Policy / 政策分野: Patents &amp; Intellectual Property / 学術区分: News &amp; Official Release / 焦点: 特許のデジタル申請および通知の義務化</t>
         </is>
       </c>
     </row>
     <row r="80" ht="42" customHeight="1">
       <c r="A80" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T21:02:36+09:00</t>
+          <t>2026-07-26T21:29:09+09:00</t>
         </is>
       </c>
       <c r="B80" s="106" t="inlineStr">
         <is>
-          <t>2026-07-22T00:00:00Z</t>
+          <t>2026-07-23T00:00:00Z</t>
         </is>
       </c>
       <c r="C80" s="60" t="inlineStr">
@@ -7059,7 +7063,7 @@
       </c>
       <c r="E80" s="60" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Robotics</t>
         </is>
       </c>
       <c r="F80" s="107" t="n">
@@ -7067,37 +7071,37 @@
       </c>
       <c r="G80" s="60" t="inlineStr">
         <is>
-          <t>Scientific Publication</t>
+          <t>Journal Article</t>
         </is>
       </c>
       <c r="H80" s="60" t="inlineStr">
         <is>
-          <t>Nature</t>
+          <t>Science Advances</t>
         </is>
       </c>
       <c r="I80" s="60" t="inlineStr">
         <is>
-          <t>ブラウンブルヘッドキャットフィッシュのメラノーマは新しい伝染性がんを示す</t>
+          <t>自己探求によるロボットの行動と言語の発展</t>
         </is>
       </c>
       <c r="J80" s="60" t="inlineStr">
         <is>
-          <t>ブラウンブルヘッドキャットフィッシュの腫瘍と非腫瘍組織の全ゲノム配列解析により、自然に発生する伝染性がんの一種が明らかになった。</t>
+          <t>ロボットが自己探求を通じて行動と言語を学ぶ過程を探る研究が行われた。</t>
         </is>
       </c>
       <c r="K80" s="60" t="inlineStr">
         <is>
-          <t>https://www.nature.com/articles/s41586-026-10828-6</t>
+          <t>https://doi.org/10.1126/sciadv.aee7533</t>
         </is>
       </c>
       <c r="L80" s="60" t="inlineStr">
         <is>
-          <t>3c774b8bd5e287725e43b3b5</t>
+          <t>c833fd421c298cf895263644</t>
         </is>
       </c>
       <c r="M80" s="106" t="inlineStr">
         <is>
-          <t>2026-07-22T09:00:00+09:00</t>
+          <t>2026-07-26T21:29:09+09:00</t>
         </is>
       </c>
       <c r="N80" s="60" t="inlineStr">
@@ -7107,34 +7111,34 @@
       </c>
       <c r="O80" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: トランスミッシブルがんの発見</t>
+          <t>枠: Technology Innovation / 学術区分: Journal Article / 査読表示: Journal record — confirm peer review on publisher page / 掲載誌・学会: Science Advances / 焦点: ロボットの自己探求による行動と言語の発展 / OpenAlex record; work type=article; citations=1</t>
         </is>
       </c>
     </row>
     <row r="81" ht="42" customHeight="1">
       <c r="A81" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T21:02:36+09:00</t>
+          <t>2026-07-26T21:29:09+09:00</t>
         </is>
       </c>
       <c r="B81" s="106" t="inlineStr">
         <is>
-          <t>2026-07-22T00:00:00Z</t>
+          <t>2026-07-23T00:00:00Z</t>
         </is>
       </c>
       <c r="C81" s="60" t="inlineStr">
         <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D81" s="60" t="inlineStr">
+        <is>
           <t>Global</t>
         </is>
       </c>
-      <c r="D81" s="60" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
       <c r="E81" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Robotics | Artificial Intelligence</t>
         </is>
       </c>
       <c r="F81" s="107" t="n">
@@ -7142,37 +7146,37 @@
       </c>
       <c r="G81" s="60" t="inlineStr">
         <is>
-          <t>Scientific Publication</t>
+          <t>Journal Article</t>
         </is>
       </c>
       <c r="H81" s="60" t="inlineStr">
         <is>
-          <t>Nature</t>
+          <t>Frontiers in Neurorobotics</t>
         </is>
       </c>
       <c r="I81" s="60" t="inlineStr">
         <is>
-          <t>AIを使って数分でグラフィカルアブストラクトを作成する方法</t>
+          <t>AI駆動の四足ロボット：基本的な移動から高度な生物模倣行動まで</t>
         </is>
       </c>
       <c r="J81" s="60" t="inlineStr">
         <is>
-          <t>人工知能は、グラフィックデザインの経験がない人々にとって民主化の力となる。</t>
+          <t>四足ロボットの技術開発に関する文献レビューが行われ、AIの進展がその能力を拡張していることが示された。</t>
         </is>
       </c>
       <c r="K81" s="60" t="inlineStr">
         <is>
-          <t>https://www.nature.com/articles/d41586-026-02072-9</t>
+          <t>https://doi.org/10.3389/fnbot.2026.1855550</t>
         </is>
       </c>
       <c r="L81" s="60" t="inlineStr">
         <is>
-          <t>b2a4fe860295587fbfbde689</t>
+          <t>e165800add9d682af8ea2122</t>
         </is>
       </c>
       <c r="M81" s="106" t="inlineStr">
         <is>
-          <t>2026-07-22T09:00:00+09:00</t>
+          <t>2026-07-26T21:29:09+09:00</t>
         </is>
       </c>
       <c r="N81" s="60" t="inlineStr">
@@ -7182,19 +7186,19 @@
       </c>
       <c r="O81" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: AIを用いたグラフィカルアブストラクトの作成</t>
+          <t>枠: Technology Innovation / 学術区分: Journal Article / 査読表示: Journal record — confirm peer review on publisher page / 掲載誌・学会: Frontiers in Neurorobotics / 焦点: AI駆動の四足ロボット / OpenAlex record; work type=article; citations=0</t>
         </is>
       </c>
     </row>
     <row r="82" ht="42" customHeight="1">
       <c r="A82" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T21:02:36+09:00</t>
+          <t>2026-07-26T21:29:09+09:00</t>
         </is>
       </c>
       <c r="B82" s="106" t="inlineStr">
         <is>
-          <t>2026-07-22T00:00:00Z</t>
+          <t>2026-07-23T00:00:00Z</t>
         </is>
       </c>
       <c r="C82" s="60" t="inlineStr">
@@ -7209,7 +7213,7 @@
       </c>
       <c r="E82" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Fusion Energy</t>
         </is>
       </c>
       <c r="F82" s="107" t="n">
@@ -7217,37 +7221,37 @@
       </c>
       <c r="G82" s="60" t="inlineStr">
         <is>
-          <t>Scientific Publication</t>
+          <t>Journal Article</t>
         </is>
       </c>
       <c r="H82" s="60" t="inlineStr">
         <is>
-          <t>Nature</t>
+          <t>Nuclear Fusion</t>
         </is>
       </c>
       <c r="I82" s="60" t="inlineStr">
         <is>
-          <t>「良いデザインには熟練が必要」：科学的イラストレーターがAIの未来を描く</t>
+          <t>Wendelstein 7-Xにおける高速イオンの閉じ込めにおける放射電場の役割</t>
         </is>
       </c>
       <c r="J82" s="60" t="inlineStr">
         <is>
-          <t>Natureが5人のアーティストに科学を視覚的に伝えるアプローチについてインタビューした。</t>
+          <t>Wendelstein 7-Xにおける高速イオンの閉じ込めに関する研究が行われ、放射電場の影響が分析された。</t>
         </is>
       </c>
       <c r="K82" s="60" t="inlineStr">
         <is>
-          <t>https://www.nature.com/articles/d41586-026-02230-z</t>
+          <t>https://doi.org/10.1088/1741-4326/ae8f55</t>
         </is>
       </c>
       <c r="L82" s="60" t="inlineStr">
         <is>
-          <t>108461ddd7bd10edd9652aef</t>
+          <t>eef01d292bfb6d5bb3537528</t>
         </is>
       </c>
       <c r="M82" s="106" t="inlineStr">
         <is>
-          <t>2026-07-22T09:00:00+09:00</t>
+          <t>2026-07-26T21:29:09+09:00</t>
         </is>
       </c>
       <c r="N82" s="60" t="inlineStr">
@@ -7257,19 +7261,19 @@
       </c>
       <c r="O82" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: 科学的イラストレーションにおけるAIの未来</t>
+          <t>枠: Technology Innovation / 学術区分: Journal Article / 査読表示: Journal record — confirm peer review on publisher page / 掲載誌・学会: Nuclear Fusion / 焦点: Wendelstein 7-Xの高速イオンの閉じ込め / OpenAlex record; work type=article; citations=0</t>
         </is>
       </c>
     </row>
     <row r="83" ht="42" customHeight="1">
       <c r="A83" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T21:02:36+09:00</t>
+          <t>2026-07-26T21:29:09+09:00</t>
         </is>
       </c>
       <c r="B83" s="106" t="inlineStr">
         <is>
-          <t>2026-07-22T00:00:00Z</t>
+          <t>2026-07-23T00:00:00Z</t>
         </is>
       </c>
       <c r="C83" s="60" t="inlineStr">
@@ -7284,7 +7288,7 @@
       </c>
       <c r="E83" s="60" t="inlineStr">
         <is>
-          <t>Biotechnology | Artificial Intelligence</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="F83" s="107" t="n">
@@ -7292,37 +7296,37 @@
       </c>
       <c r="G83" s="60" t="inlineStr">
         <is>
-          <t>Scientific Publication</t>
+          <t>Journal Article</t>
         </is>
       </c>
       <c r="H83" s="60" t="inlineStr">
         <is>
-          <t>Nature</t>
+          <t>Scientific Reports</t>
         </is>
       </c>
       <c r="I83" s="60" t="inlineStr">
         <is>
-          <t>AIがCRISPR複合体の相互作用を特定し、DNA編集の特異性を向上させる</t>
+          <t>密なプラズマフォーカスにおけるクーロン爆発の研究</t>
         </is>
       </c>
       <c r="J83" s="60" t="inlineStr">
         <is>
-          <t>AlphaFold3による分子接触の予測が、DNAターゲット配列に対する酵素の選択性を改善するために使用された。</t>
+          <t>密なプラズマフォーカスにおけるクーロン爆発のシミュレーション研究が行われ、極端な条件下での挙動が分析された。</t>
         </is>
       </c>
       <c r="K83" s="60" t="inlineStr">
         <is>
-          <t>https://www.nature.com/articles/d41586-026-02042-1</t>
+          <t>https://doi.org/10.1038/s41598-026-63204-9</t>
         </is>
       </c>
       <c r="L83" s="60" t="inlineStr">
         <is>
-          <t>ab4fcaf4ee310e08612eba0d</t>
+          <t>fcf607380491b3f6666abab6</t>
         </is>
       </c>
       <c r="M83" s="106" t="inlineStr">
         <is>
-          <t>2026-07-22T09:00:00+09:00</t>
+          <t>2026-07-26T21:29:09+09:00</t>
         </is>
       </c>
       <c r="N83" s="60" t="inlineStr">
@@ -7332,19 +7336,19 @@
       </c>
       <c r="O83" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: CRISPR複合体における相互作用の特定</t>
+          <t>枠: Technology Innovation / 学術区分: Journal Article / 査読表示: Journal record — confirm peer review on publisher page / 掲載誌・学会: Scientific Reports / 焦点: 密なプラズマフォーカスにおけるクーロン爆発の研究 / OpenAlex record; work type=article; citations=0</t>
         </is>
       </c>
     </row>
     <row r="84" ht="42" customHeight="1">
       <c r="A84" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T21:02:36+09:00</t>
+          <t>2026-07-26T21:29:09+09:00</t>
         </is>
       </c>
       <c r="B84" s="106" t="inlineStr">
         <is>
-          <t>2026-07-22T00:00:00Z</t>
+          <t>2026-07-23T00:00:00Z</t>
         </is>
       </c>
       <c r="C84" s="60" t="inlineStr">
@@ -7359,45 +7363,45 @@
       </c>
       <c r="E84" s="60" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="F84" s="107" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G84" s="60" t="inlineStr">
         <is>
-          <t>Scientific Publication</t>
+          <t>Preprint</t>
         </is>
       </c>
       <c r="H84" s="60" t="inlineStr">
         <is>
-          <t>Nature</t>
+          <t>Zenodo (CERN European Organization for Nuclear Research)</t>
         </is>
       </c>
       <c r="I84" s="60" t="inlineStr">
         <is>
-          <t>背景遺伝子と新しい変異ががん進化を導く</t>
+          <t>プライム・レックス理論と量子技術ガバナンス：キュービットから量子主権へ</t>
         </is>
       </c>
       <c r="J84" s="60" t="inlineStr">
         <is>
-          <t>マウスでの腫瘍進化の再実行により、DNA損傷後のがんの発展が示された。</t>
+          <t>OECDが採択した量子技術に関する提言を基に、量子技術のガバナンスの枠組みを構築する方法を探求した。</t>
         </is>
       </c>
       <c r="K84" s="60" t="inlineStr">
         <is>
-          <t>https://www.nature.com/articles/d41586-026-02155-7</t>
+          <t>https://doi.org/10.5281/zenodo.21512028</t>
         </is>
       </c>
       <c r="L84" s="60" t="inlineStr">
         <is>
-          <t>74243d6e7e201860f4f79008</t>
+          <t>61f1fcfb9afff652f523d019</t>
         </is>
       </c>
       <c r="M84" s="106" t="inlineStr">
         <is>
-          <t>2026-07-22T09:00:00+09:00</t>
+          <t>2026-07-26T21:29:09+09:00</t>
         </is>
       </c>
       <c r="N84" s="60" t="inlineStr">
@@ -7407,29 +7411,29 @@
       </c>
       <c r="O84" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: がん進化における背景遺伝子と新しい変異の相互作用</t>
+          <t>枠: Technology Innovation | Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: Preprint / 査読表示: Not peer reviewed / 掲載誌・学会: Zenodo (CERN European Organization for Nuclear Research) / 焦点: 量子技術のガバナンスとOECDの提言 / OpenAlex record; work type=preprint; citations=0</t>
         </is>
       </c>
     </row>
     <row r="85" ht="42" customHeight="1">
       <c r="A85" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T21:02:36+09:00</t>
+          <t>2026-07-26T20:29:40+09:00</t>
         </is>
       </c>
       <c r="B85" s="106" t="inlineStr">
         <is>
-          <t>2026-07-22T00:00:00Z</t>
+          <t>2026-07-22T14:12:14Z</t>
         </is>
       </c>
       <c r="C85" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D85" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E85" s="60" t="inlineStr">
@@ -7438,41 +7442,41 @@
         </is>
       </c>
       <c r="F85" s="107" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G85" s="60" t="inlineStr">
         <is>
-          <t>Scientific Publication</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H85" s="60" t="inlineStr">
         <is>
-          <t>Nature</t>
+          <t>DOE Office of Science News</t>
         </is>
       </c>
       <c r="I85" s="60" t="inlineStr">
         <is>
-          <t>科学におけるAI画像のミスを避けるための3つのヒント</t>
+          <t>エネルギー長官がAI駆動の科学的発見を加速するプロジェクトを発表</t>
         </is>
       </c>
       <c r="J85" s="60" t="inlineStr">
         <is>
-          <t>AIツールはグラフィック作成に役立つが、エラーを引き起こす可能性がある。</t>
+          <t>エネルギー長官クリス・ライトが、全米から選ばれた300のプロジェクトを発表し、エネルギーや発見科学、国家安全保障の分野でのブレークスルーを促進する。</t>
         </is>
       </c>
       <c r="K85" s="60" t="inlineStr">
         <is>
-          <t>https://www.nature.com/articles/d41586-026-02233-w</t>
+          <t>https://www.energy.gov/articles/secretary-energy-chris-wright-announces-first-genesis-mission-projects-selected-accelerate</t>
         </is>
       </c>
       <c r="L85" s="60" t="inlineStr">
         <is>
-          <t>3333c16762502cf03b987a99</t>
+          <t>23fa1d6907c14d73ce3a41cd</t>
         </is>
       </c>
       <c r="M85" s="106" t="inlineStr">
         <is>
-          <t>2026-07-22T09:00:00+09:00</t>
+          <t>2026-07-26T20:29:40+09:00</t>
         </is>
       </c>
       <c r="N85" s="60" t="inlineStr">
@@ -7482,29 +7486,29 @@
       </c>
       <c r="O85" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: 科学におけるAI画像のミスを避けるためのヒント</t>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: AI駆動の科学的発見を加速するプロジェクト</t>
         </is>
       </c>
     </row>
     <row r="86" ht="42" customHeight="1">
       <c r="A86" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T21:02:36+09:00</t>
+          <t>2026-07-26T19:05:06+09:00</t>
         </is>
       </c>
       <c r="B86" s="106" t="inlineStr">
         <is>
-          <t>2026-07-22T00:00:00Z</t>
+          <t>2026-07-22T13:53:19Z</t>
         </is>
       </c>
       <c r="C86" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D86" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E86" s="60" t="inlineStr">
@@ -7513,41 +7517,41 @@
         </is>
       </c>
       <c r="F86" s="107" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G86" s="60" t="inlineStr">
         <is>
-          <t>Scientific Publication</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H86" s="60" t="inlineStr">
         <is>
-          <t>Nature</t>
+          <t>National Science Foundation News</t>
         </is>
       </c>
       <c r="I86" s="60" t="inlineStr">
         <is>
-          <t>日々のブリーフィング：世界はついにポリオを根絶できるか？</t>
+          <t>NSFがAI優先事項の推進に関する声明を発表</t>
         </is>
       </c>
       <c r="J86" s="60" t="inlineStr">
         <is>
-          <t>一部の研究者は、現在の根絶戦略が時代遅れであると考えている。</t>
+          <t>米国国家科学財団が、ホワイトハウスの科学技術政策室やエネルギー省と連携し、AIに関する優先事項を進めることを発表した。</t>
         </is>
       </c>
       <c r="K86" s="60" t="inlineStr">
         <is>
-          <t>https://www.nature.com/articles/d41586-026-02302-0</t>
+          <t>https://www.nsf.gov/news/statement-nsf-chief-staff-brian-stone-performing-duties-nsf-1</t>
         </is>
       </c>
       <c r="L86" s="60" t="inlineStr">
         <is>
-          <t>a6bb3e839151ea803a445830</t>
+          <t>123e2207578ca69c8f9c00a2</t>
         </is>
       </c>
       <c r="M86" s="106" t="inlineStr">
         <is>
-          <t>2026-07-22T09:00:00+09:00</t>
+          <t>2026-07-26T19:05:06+09:00</t>
         </is>
       </c>
       <c r="N86" s="60" t="inlineStr">
@@ -7557,24 +7561,24 @@
       </c>
       <c r="O86" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: ポリオ根絶に関する研究</t>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: AI優先事項の推進</t>
         </is>
       </c>
     </row>
     <row r="87" ht="42" customHeight="1">
       <c r="A87" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T21:02:36+09:00</t>
+          <t>2026-07-26T19:05:06+09:00</t>
         </is>
       </c>
       <c r="B87" s="106" t="inlineStr">
         <is>
-          <t>2026-07-21T22:35:45Z</t>
+          <t>2026-07-22T13:53:12Z</t>
         </is>
       </c>
       <c r="C87" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D87" s="60" t="inlineStr">
@@ -7588,41 +7592,41 @@
         </is>
       </c>
       <c r="F87" s="107" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G87" s="60" t="inlineStr">
         <is>
-          <t>Official Company</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H87" s="60" t="inlineStr">
         <is>
-          <t>NVIDIA Blog</t>
+          <t>National Science Foundation News</t>
         </is>
       </c>
       <c r="I87" s="60" t="inlineStr">
         <is>
-          <t>フォートワースにて：WistronがNVIDIA AIシステムを生産するための先進的製造工場を開設</t>
+          <t>NSFがAIによる科学的発見のためのデータセット価値を解放する新プログラムを発表</t>
         </is>
       </c>
       <c r="J87" s="60" t="inlineStr">
         <is>
-          <t>Wistronがテキサス州フォートワースに324,000平方フィートの製造施設を開設し、AIシステムのためのスーパーチップを生産する。</t>
+          <t>米国国立科学財団は、AIを活用した科学的発見のためのデータセット価値を解放するプログラムを発表しました。</t>
         </is>
       </c>
       <c r="K87" s="60" t="inlineStr">
         <is>
-          <t>https://blogs.nvidia.com/blog/wistron-manufacturing-texas/</t>
+          <t>https://www.nsf.gov/news/new-nsf-initiative-aims-unlock-dataset-value-ai-enabled</t>
         </is>
       </c>
       <c r="L87" s="60" t="inlineStr">
         <is>
-          <t>21f1e1f3e19b1a5bf0af3cb7</t>
+          <t>dcd819527d9b80141b26bcb8</t>
         </is>
       </c>
       <c r="M87" s="106" t="inlineStr">
         <is>
-          <t>2026-07-22T07:35:45+09:00</t>
+          <t>2026-07-26T19:05:06+09:00</t>
         </is>
       </c>
       <c r="N87" s="60" t="inlineStr">
@@ -7632,38 +7636,38 @@
       </c>
       <c r="O87" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: NVIDIA AIシステムの製造</t>
+          <t>枠: Innovation Policy / 政策分野: R&amp;D Funding &amp; Tax Incentives / 学術区分: News &amp; Official Release / 焦点: AIを活用した科学的発見のためのデータセット</t>
         </is>
       </c>
     </row>
     <row r="88" ht="42" customHeight="1">
       <c r="A88" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T21:02:36+09:00</t>
+          <t>2026-07-26T20:29:40+09:00</t>
         </is>
       </c>
       <c r="B88" s="106" t="inlineStr">
         <is>
-          <t>2026-07-21T15:05:11Z</t>
+          <t>2026-07-22T13:53:06Z</t>
         </is>
       </c>
       <c r="C88" s="60" t="inlineStr">
         <is>
-          <t>EU &amp; Europe</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D88" s="60" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E88" s="60" t="inlineStr">
         <is>
-          <t>Semiconductors &amp; Telecom</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="F88" s="107" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G88" s="60" t="inlineStr">
         <is>
@@ -7672,32 +7676,32 @@
       </c>
       <c r="H88" s="60" t="inlineStr">
         <is>
-          <t>UK DSIT</t>
+          <t>National Science Foundation News</t>
         </is>
       </c>
       <c r="I88" s="60" t="inlineStr">
         <is>
-          <t>固定通信近代化憲章に関する政策文書</t>
+          <t>NSFがAI駆動の科学を進展させるために8300万ドルの投資を発表</t>
         </is>
       </c>
       <c r="J88" s="60" t="inlineStr">
         <is>
-          <t>通信事業者が現在および将来の固定通信近代化を実施する際に従うべき手順を示した文書。</t>
+          <t>米国国立科学財団は、AI駆動の科学を進展させるために8300万ドルの投資を発表しました。</t>
         </is>
       </c>
       <c r="K88" s="60" t="inlineStr">
         <is>
-          <t>https://www.gov.uk/government/publications/fixed-telecoms-modernisation-charter</t>
+          <t>https://www.nsf.gov/news/nsf-announces-83m-investment-integrated-data-systems</t>
         </is>
       </c>
       <c r="L88" s="60" t="inlineStr">
         <is>
-          <t>d5e4431b57fcb4b6271f6c72</t>
+          <t>018d40b7e6eb7aa4b8cfb5fa</t>
         </is>
       </c>
       <c r="M88" s="106" t="inlineStr">
         <is>
-          <t>2026-07-22T00:05:11+09:00</t>
+          <t>2026-07-26T20:29:40+09:00</t>
         </is>
       </c>
       <c r="N88" s="60" t="inlineStr">
@@ -7707,72 +7711,72 @@
       </c>
       <c r="O88" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: 固定通信の近代化手順</t>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy | Research System &amp; Talent / 学術区分: News &amp; Official Release / 焦点: AI駆動の科学のためのデータシステム</t>
         </is>
       </c>
     </row>
     <row r="89" ht="42" customHeight="1">
       <c r="A89" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T21:02:36+09:00</t>
+          <t>2026-07-28T01:39:30+09:00</t>
         </is>
       </c>
       <c r="B89" s="106" t="inlineStr">
         <is>
-          <t>2026-07-21T15:05:07Z</t>
+          <t>2026-07-22T13:18:55Z</t>
         </is>
       </c>
       <c r="C89" s="60" t="inlineStr">
         <is>
-          <t>EU &amp; Europe</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="D89" s="60" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="E89" s="60" t="inlineStr">
         <is>
-          <t>Semiconductors &amp; Telecom</t>
+          <t>Fusion Energy</t>
         </is>
       </c>
       <c r="F89" s="107" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G89" s="60" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Industry Association</t>
         </is>
       </c>
       <c r="H89" s="60" t="inlineStr">
         <is>
-          <t>UK DSIT</t>
+          <t>Fusion Industry Association</t>
         </is>
       </c>
       <c r="I89" s="60" t="inlineStr">
         <is>
-          <t>通信近代化：重要国家インフラ憲章に関する政策文書</t>
+          <t>韓国、世界最大の核融合炉ITERの核心部品を完成</t>
         </is>
       </c>
       <c r="J89" s="60" t="inlineStr">
         <is>
-          <t>通信事業者が通信近代化中に重要国家インフラを保護するためのアプローチを示した文書。</t>
+          <t>韓国は、世界最大の核融合プロジェクトであるITERの最終反応器コンポーネントの製造と設置を完了しました。この成果は、核融合技術と大規模な先進製造における国の専門性の向上を示しています。</t>
         </is>
       </c>
       <c r="K89" s="60" t="inlineStr">
         <is>
-          <t>https://www.gov.uk/government/publications/telecoms-modernisation-critical-national-infrastructure-charter</t>
+          <t>https://www.asiae.co.kr/en/article/science/2026072213475928139?mc_cid=ed1acc7bef&amp;mc_eid=01cd8fe465#new_tab&amp;utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=korea-completes-core-of-worlds-largest-fusion-reactor-iter</t>
         </is>
       </c>
       <c r="L89" s="60" t="inlineStr">
         <is>
-          <t>aafa3a246656ccda64dd93c4</t>
+          <t>55b5e71d5f2f13411a2b039b</t>
         </is>
       </c>
       <c r="M89" s="106" t="inlineStr">
         <is>
-          <t>2026-07-22T00:05:07+09:00</t>
+          <t>2026-07-28T01:39:30+09:00</t>
         </is>
       </c>
       <c r="N89" s="60" t="inlineStr">
@@ -7782,72 +7786,68 @@
       </c>
       <c r="O89" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: 重要国家インフラの保護方針</t>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: 核融合技術</t>
         </is>
       </c>
     </row>
     <row r="90" ht="42" customHeight="1">
       <c r="A90" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T20:29:40+09:00</t>
         </is>
       </c>
       <c r="B90" s="106" t="inlineStr">
         <is>
-          <t>2026-07-21T14:48:28Z</t>
+          <t>2026-07-22T12:00:00Z</t>
         </is>
       </c>
       <c r="C90" s="60" t="inlineStr">
         <is>
-          <t>EU &amp; Europe</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D90" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="E90" s="60" t="inlineStr">
-        <is>
-          <t>Fusion Energy</t>
-        </is>
-      </c>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E90" s="60" t="inlineStr"/>
       <c r="F90" s="107" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G90" s="60" t="inlineStr">
         <is>
-          <t>Industry Association</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H90" s="60" t="inlineStr">
         <is>
-          <t>Fusion Industry Association</t>
+          <t>NIST News</t>
         </is>
       </c>
       <c r="I90" s="60" t="inlineStr">
         <is>
-          <t>FIA、核融合のためのEU資金調達の道筋を示す</t>
+          <t>NIST、中小企業向けの資金提供機会を発表</t>
         </is>
       </c>
       <c r="J90" s="60" t="inlineStr">
         <is>
-          <t>Fusion Industry Associationが商業核融合エネルギーのためのEU資金調達のロードマップを発表。</t>
+          <t>NIST MEPが中小企業向けの資金提供機会を発表し、2026年7月28日にウェビナーを開催する予定。</t>
         </is>
       </c>
       <c r="K90" s="60" t="inlineStr">
         <is>
-          <t>https://www.fusionindustryassociation.org/fia-outlines-eu-financing-pathway-for-fusion/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=fia-outlines-eu-financing-pathway-for-fusion</t>
+          <t>https://www.nist.gov/news-events/news/2026/07/nist-announces-funding-opportunity-14-mep-centers-advance-small-and-medium</t>
         </is>
       </c>
       <c r="L90" s="60" t="inlineStr">
         <is>
-          <t>88af233d904d670250fa5a31</t>
+          <t>5aa9c93bc7040291c9f08bfa</t>
         </is>
       </c>
       <c r="M90" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T20:29:40+09:00</t>
         </is>
       </c>
       <c r="N90" s="60" t="inlineStr">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="O90" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: R&amp;D Funding &amp; Tax Incentives / 学術区分: News &amp; Official Release / 焦点: EUの核融合エネルギー商業化に向けた資金調達</t>
+          <t>枠: Innovation Policy / 政策分野: R&amp;D Funding &amp; Tax Incentives | Public Procurement &amp; Industrial Policy / 学術区分: News &amp; Official Release / 焦点: 中小企業向けの資金提供機会</t>
         </is>
       </c>
     </row>
@@ -7869,60 +7869,60 @@
       </c>
       <c r="B91" s="106" t="inlineStr">
         <is>
-          <t>2026-07-21T00:00:00Z</t>
+          <t>2026-07-22T05:00:56Z</t>
         </is>
       </c>
       <c r="C91" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="D91" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="E91" s="60" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="F91" s="107" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G91" s="60" t="inlineStr">
         <is>
-          <t>Conference Paper</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H91" s="60" t="inlineStr">
         <is>
-          <t>OpenAlex Conference Papers</t>
+          <t>NISTEP Updates</t>
         </is>
       </c>
       <c r="I91" s="60" t="inlineStr">
         <is>
-          <t>量子機械学習による心血管疾患リスク予測の向上</t>
+          <t>特定科学技術領域動向報告書 -AI（人工知能）- 研究開発インプット編を公表</t>
         </is>
       </c>
       <c r="J91" s="60" t="inlineStr">
         <is>
-          <t>この研究は、量子アルゴリズムを用いて心血管疾患の予測を行うモデルを探求しており、量子サポートベクターマシンや量子ニューラルネットワークを活用しています。</t>
+          <t>AI分野における研究開発状況を分析し、基礎データをまとめた報告書を公表。</t>
         </is>
       </c>
       <c r="K91" s="60" t="inlineStr">
         <is>
-          <t>https://doi.org/10.3390/engproc2026150039</t>
+          <t>https://www.nistep.go.jp/archives/63583/</t>
         </is>
       </c>
       <c r="L91" s="60" t="inlineStr">
         <is>
-          <t>1cd467f8ebb1388daedc245f</t>
+          <t>6b6122461584a86ee7a1c595</t>
         </is>
       </c>
       <c r="M91" s="106" t="inlineStr">
         <is>
-          <t>2026-07-21T09:00:00+09:00</t>
+          <t>2026-07-22T14:00:56+09:00</t>
         </is>
       </c>
       <c r="N91" s="60" t="inlineStr">
@@ -7932,7 +7932,7 @@
       </c>
       <c r="O91" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: Conference Paper / 査読表示: Conference proceedings — review status varies / 焦点: 量子機械学習による心血管疾患リスク予測 / OpenAlex record; work type=conference-paper; citations=0</t>
+          <t>枠: Technology Innovation | Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: 人工知能（AI）分野の研究開発インプット</t>
         </is>
       </c>
     </row>
@@ -7944,7 +7944,7 @@
       </c>
       <c r="B92" s="106" t="inlineStr">
         <is>
-          <t>2026-07-20T21:06:27Z</t>
+          <t>2026-07-22T00:00:00Z</t>
         </is>
       </c>
       <c r="C92" s="60" t="inlineStr">
@@ -7977,27 +7977,27 @@
       </c>
       <c r="I92" s="60" t="inlineStr">
         <is>
-          <t>AIの借りた専門知識に対処する教育と研究政策</t>
+          <t>政策が世代ZのAIへの信頼を決定する</t>
         </is>
       </c>
       <c r="J92" s="60" t="inlineStr">
         <is>
-          <t>教育政策が短期的な生産性と長期的な認知発展の間の緊張にどのように対応すべきかについて論じています。</t>
+          <t>世代ZのAIに対する信頼は、PRではなく政策によって決まると論じられている。</t>
         </is>
       </c>
       <c r="K92" s="60" t="inlineStr">
         <is>
-          <t>https://brookings.edu/articles/repaying-the-inheritance-how-education-and-research-policy-can-address-ais-borrowed-expertise</t>
+          <t>https://www.brookings.edu/articles/policy-not-pr-will-determine-gen-zs-trust-in-ai/</t>
         </is>
       </c>
       <c r="L92" s="60" t="inlineStr">
         <is>
-          <t>42183313e1c951c0483c0d62</t>
+          <t>61bd55f8ce5a2385a5420260</t>
         </is>
       </c>
       <c r="M92" s="106" t="inlineStr">
         <is>
-          <t>2026-07-21T06:06:27+09:00</t>
+          <t>2026-07-22T09:00:00+09:00</t>
         </is>
       </c>
       <c r="N92" s="60" t="inlineStr">
@@ -8007,7 +8007,7 @@
       </c>
       <c r="O92" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: AIに関する教育政策の変革 / Historical backfill from an allowlisted source.</t>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: AIに対する信頼の構築</t>
         </is>
       </c>
     </row>
@@ -8019,22 +8019,22 @@
       </c>
       <c r="B93" s="106" t="inlineStr">
         <is>
-          <t>2026-07-20T15:55:00Z</t>
+          <t>2026-07-22T00:00:00Z</t>
         </is>
       </c>
       <c r="C93" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D93" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="E93" s="60" t="inlineStr">
         <is>
-          <t>Semiconductors &amp; Telecom</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="F93" s="107" t="n">
@@ -8042,37 +8042,37 @@
       </c>
       <c r="G93" s="60" t="inlineStr">
         <is>
-          <t>Major Media</t>
+          <t>Scientific Publication</t>
         </is>
       </c>
       <c r="H93" s="60" t="inlineStr">
         <is>
-          <t>IEEE Spectrum</t>
+          <t>Nature</t>
         </is>
       </c>
       <c r="I93" s="60" t="inlineStr">
         <is>
-          <t>先進半導体故障解析のためのSEMガイド低電圧FIB仕上げ</t>
+          <t>ブラウンブルヘッドキャットフィッシュのメラノーマは新しい伝染性がんを示す</t>
         </is>
       </c>
       <c r="J93" s="60" t="inlineStr">
         <is>
-          <t>ZEISS Crossbeam 750 FIBSEMが先進的な半導体故障解析の新しい基準を設定する方法について説明しています。</t>
+          <t>ブラウンブルヘッドキャットフィッシュの腫瘍と非腫瘍組織の全ゲノム配列解析により、自然に発生する伝染性がんの一種が明らかになった。</t>
         </is>
       </c>
       <c r="K93" s="60" t="inlineStr">
         <is>
-          <t>https://event.on24.com/wcc/r/5418459/287E3D5B99470D34C830D69A24B3B207</t>
+          <t>https://www.nature.com/articles/s41586-026-10832-w</t>
         </is>
       </c>
       <c r="L93" s="60" t="inlineStr">
         <is>
-          <t>73d0028e337a76c2cd00f1bc</t>
+          <t>f9bccca3cabb5ce19441f09d</t>
         </is>
       </c>
       <c r="M93" s="106" t="inlineStr">
         <is>
-          <t>2026-07-21T00:55:00+09:00</t>
+          <t>2026-07-22T09:00:00+09:00</t>
         </is>
       </c>
       <c r="N93" s="60" t="inlineStr">
@@ -8082,7 +8082,7 @@
       </c>
       <c r="O93" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: 先進半導体の故障解析技術</t>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: トランスミッシブルがん</t>
         </is>
       </c>
     </row>
@@ -8094,7 +8094,7 @@
       </c>
       <c r="B94" s="106" t="inlineStr">
         <is>
-          <t>2026-07-20T15:00:53Z</t>
+          <t>2026-07-22T00:00:00Z</t>
         </is>
       </c>
       <c r="C94" s="60" t="inlineStr">
@@ -8104,12 +8104,12 @@
       </c>
       <c r="D94" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="E94" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence | Robotics</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="F94" s="107" t="n">
@@ -8117,37 +8117,37 @@
       </c>
       <c r="G94" s="60" t="inlineStr">
         <is>
-          <t>Official Company</t>
+          <t>Scientific Publication</t>
         </is>
       </c>
       <c r="H94" s="60" t="inlineStr">
         <is>
-          <t>NVIDIA Blog</t>
+          <t>Nature</t>
         </is>
       </c>
       <c r="I94" s="60" t="inlineStr">
         <is>
-          <t>SIGGRAPHでNVIDIAがエージェントAIと物理AIでグラフィックスとシミュレーションを進展</t>
+          <t>量子パラエレクトリックSrTiO3におけるナノスケール極性テクスチャのイメージング</t>
         </is>
       </c>
       <c r="J94" s="60" t="inlineStr">
         <is>
-          <t>NVIDIAはSIGGRAPHで、オープンモデルからリアルタイムシミュレーションまで、AIとグラフィックスの革新がメディア、コンテンツ制作、ロボティクスを変革していることを発表した。</t>
+          <t>Cryo-STEMを用いて、SrTiO3が105K以下で周期的な極性ナノドメインを形成することが明らかになった。</t>
         </is>
       </c>
       <c r="K94" s="60" t="inlineStr">
         <is>
-          <t>https://blogs.nvidia.com/blog/siggraph-news-2026/</t>
+          <t>https://www.nature.com/articles/s41586-026-10823-x</t>
         </is>
       </c>
       <c r="L94" s="60" t="inlineStr">
         <is>
-          <t>70c1acaa81ba6cd1c84a673d</t>
+          <t>f12f62aebb861877dd7a5cbf</t>
         </is>
       </c>
       <c r="M94" s="106" t="inlineStr">
         <is>
-          <t>2026-07-21T00:00:53+09:00</t>
+          <t>2026-07-22T09:00:00+09:00</t>
         </is>
       </c>
       <c r="N94" s="60" t="inlineStr">
@@ -8157,7 +8157,7 @@
       </c>
       <c r="O94" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: エージェントAIと物理AIの進展</t>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: 量子パラエレクトリックSrTiO3のナノスケール極性テクスチャのイメージング</t>
         </is>
       </c>
     </row>
@@ -8169,60 +8169,60 @@
       </c>
       <c r="B95" s="106" t="inlineStr">
         <is>
-          <t>2026-07-20T13:30:06Z</t>
+          <t>2026-07-22T00:00:00Z</t>
         </is>
       </c>
       <c r="C95" s="60" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D95" s="60" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="E95" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence | Semiconductors &amp; Telecom</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="F95" s="107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G95" s="60" t="inlineStr">
         <is>
-          <t>Major Media</t>
+          <t>Scientific Publication</t>
         </is>
       </c>
       <c r="H95" s="60" t="inlineStr">
         <is>
-          <t>South China Morning Post Technology</t>
+          <t>Nature</t>
         </is>
       </c>
       <c r="I95" s="60" t="inlineStr">
         <is>
-          <t>トークン経済からタスク経済へ？SenseTimeがAIの商業化に賭ける</t>
+          <t>ブラウンブルヘッドキャットフィッシュのメラノーマは新しい伝染性がんを示す</t>
         </is>
       </c>
       <c r="J95" s="60" t="inlineStr">
         <is>
-          <t>中国のAI企業SenseTimeは、トークン価格の低下に伴い、AIの商業化が「トークン経済」から「タスク経済」へ移行する見込みであると述べた。</t>
+          <t>ブラウンブルヘッドキャットフィッシュの腫瘍と非腫瘍組織の全ゲノム配列解析により、自然に発生する伝染性がんの一種が明らかになった。</t>
         </is>
       </c>
       <c r="K95" s="60" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/tech/big-tech/article/3361242/no-longer-token-economy-sensetime-bets-task-economy-token-prices-set-drop?utm_source=rss_feed</t>
+          <t>https://www.nature.com/articles/s41586-026-10828-6</t>
         </is>
       </c>
       <c r="L95" s="60" t="inlineStr">
         <is>
-          <t>cd5b1ea310d8a65d00ad1ad9</t>
+          <t>3c774b8bd5e287725e43b3b5</t>
         </is>
       </c>
       <c r="M95" s="106" t="inlineStr">
         <is>
-          <t>2026-07-20T22:30:06+09:00</t>
+          <t>2026-07-22T09:00:00+09:00</t>
         </is>
       </c>
       <c r="N95" s="60" t="inlineStr">
@@ -8232,7 +8232,7 @@
       </c>
       <c r="O95" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation | Innovation Policy / 政策分野: Patents &amp; Intellectual Property / 学術区分: News &amp; Official Release / 焦点: AIの商業化の移行</t>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: トランスミッシブルがんの発見</t>
         </is>
       </c>
     </row>
@@ -8244,56 +8244,60 @@
       </c>
       <c r="B96" s="106" t="inlineStr">
         <is>
-          <t>2026-07-20T11:29:00Z</t>
+          <t>2026-07-22T00:00:00Z</t>
         </is>
       </c>
       <c r="C96" s="60" t="inlineStr">
         <is>
-          <t>EU &amp; Europe</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D96" s="60" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="E96" s="60" t="inlineStr"/>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E96" s="60" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence</t>
+        </is>
+      </c>
       <c r="F96" s="107" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G96" s="60" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Scientific Publication</t>
         </is>
       </c>
       <c r="H96" s="60" t="inlineStr">
         <is>
-          <t>UK DSIT</t>
+          <t>Nature</t>
         </is>
       </c>
       <c r="I96" s="60" t="inlineStr">
         <is>
-          <t>透明性データ：契約されたおよび建設された施設、プロジェクトギガビット契約</t>
+          <t>AIを使って数分でグラフィカルアブストラクトを作成する方法</t>
         </is>
       </c>
       <c r="J96" s="60" t="inlineStr">
         <is>
-          <t>デジタルUKがプロジェクトギガビット契約に基づく契約状況を報告しています。</t>
+          <t>人工知能は、グラフィックデザインの経験がない人々にとって民主化の力となる。</t>
         </is>
       </c>
       <c r="K96" s="60" t="inlineStr">
         <is>
-          <t>https://www.gov.uk/government/publications/premises-contracted-and-built-project-gigabit-contracts</t>
+          <t>https://www.nature.com/articles/d41586-026-02072-9</t>
         </is>
       </c>
       <c r="L96" s="60" t="inlineStr">
         <is>
-          <t>d643b4b81f6998869b340654</t>
+          <t>b2a4fe860295587fbfbde689</t>
         </is>
       </c>
       <c r="M96" s="106" t="inlineStr">
         <is>
-          <t>2026-07-20T20:29:00+09:00</t>
+          <t>2026-07-22T09:00:00+09:00</t>
         </is>
       </c>
       <c r="N96" s="60" t="inlineStr">
@@ -8303,7 +8307,7 @@
       </c>
       <c r="O96" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: デジタルインフラ整備に関する国家戦略</t>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: AIを用いたグラフィカルアブストラクトの作成</t>
         </is>
       </c>
     </row>
@@ -8315,7 +8319,7 @@
       </c>
       <c r="B97" s="106" t="inlineStr">
         <is>
-          <t>2026-07-20T10:59:23Z</t>
+          <t>2026-07-22T00:00:00Z</t>
         </is>
       </c>
       <c r="C97" s="60" t="inlineStr">
@@ -8325,7 +8329,7 @@
       </c>
       <c r="D97" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="E97" s="60" t="inlineStr">
@@ -8338,37 +8342,37 @@
       </c>
       <c r="G97" s="60" t="inlineStr">
         <is>
-          <t>Official Company</t>
+          <t>Scientific Publication</t>
         </is>
       </c>
       <c r="H97" s="60" t="inlineStr">
         <is>
-          <t>NVIDIA Blog</t>
+          <t>Nature</t>
         </is>
       </c>
       <c r="I97" s="60" t="inlineStr">
         <is>
-          <t>Bristol Myers Squibbがライフサイエンス業界で最も先進的なAI工場を構築</t>
+          <t>「良いデザインには熟練が必要」：科学的イラストレーターがAIの未来を描く</t>
         </is>
       </c>
       <c r="J97" s="60" t="inlineStr">
         <is>
-          <t>Bristol Myers Squibbは、ライフサイエンス分野でのAIクラスターを拡大し、成果を上げていることを発表した。</t>
+          <t>Natureが5人のアーティストに科学を視覚的に伝えるアプローチについてインタビューした。</t>
         </is>
       </c>
       <c r="K97" s="60" t="inlineStr">
         <is>
-          <t>https://blogs.nvidia.com/blog/bristol-myers-squibb-building-life-science-industrys-most-advanced-ai-factory-on-nvidia-vera-rubin/</t>
+          <t>https://www.nature.com/articles/d41586-026-02230-z</t>
         </is>
       </c>
       <c r="L97" s="60" t="inlineStr">
         <is>
-          <t>b4ddc90482832cbb50579f2a</t>
+          <t>108461ddd7bd10edd9652aef</t>
         </is>
       </c>
       <c r="M97" s="106" t="inlineStr">
         <is>
-          <t>2026-07-20T19:59:23+09:00</t>
+          <t>2026-07-22T09:00:00+09:00</t>
         </is>
       </c>
       <c r="N97" s="60" t="inlineStr">
@@ -8378,7 +8382,7 @@
       </c>
       <c r="O97" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: AIクラスターの展開</t>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: 科学的イラストレーションにおけるAIの未来</t>
         </is>
       </c>
     </row>
@@ -8390,7 +8394,7 @@
       </c>
       <c r="B98" s="106" t="inlineStr">
         <is>
-          <t>2026-07-20T00:00:00Z</t>
+          <t>2026-07-22T00:00:00Z</t>
         </is>
       </c>
       <c r="C98" s="60" t="inlineStr">
@@ -8405,7 +8409,7 @@
       </c>
       <c r="E98" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence | Healthcare</t>
+          <t>Biotechnology | Artificial Intelligence</t>
         </is>
       </c>
       <c r="F98" s="107" t="n">
@@ -8413,37 +8417,37 @@
       </c>
       <c r="G98" s="60" t="inlineStr">
         <is>
-          <t>Journal Article</t>
+          <t>Scientific Publication</t>
         </is>
       </c>
       <c r="H98" s="60" t="inlineStr">
         <is>
-          <t>Machine Intelligence Research</t>
+          <t>Nature</t>
         </is>
       </c>
       <c r="I98" s="60" t="inlineStr">
         <is>
-          <t>M2SNet: 医療画像セグメンテーションのためのマルチスケール減算ネットワーク</t>
+          <t>AIがCRISPR複合体の相互作用を特定し、DNA編集の特異性を向上させる</t>
         </is>
       </c>
       <c r="J98" s="60" t="inlineStr">
         <is>
-          <t>M2SNetは、医療画像のセグメンテーションを改善するために、異なるレベルの特徴を効果的に融合する新しい手法を提案します。</t>
+          <t>AlphaFold3による分子接触の予測が、DNAターゲット配列に対する酵素の選択性を改善するために使用された。</t>
         </is>
       </c>
       <c r="K98" s="60" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1007/s11633-026-1662-9</t>
+          <t>https://www.nature.com/articles/d41586-026-02042-1</t>
         </is>
       </c>
       <c r="L98" s="60" t="inlineStr">
         <is>
-          <t>bffca1cc322e28515452081a</t>
+          <t>ab4fcaf4ee310e08612eba0d</t>
         </is>
       </c>
       <c r="M98" s="106" t="inlineStr">
         <is>
-          <t>2026-07-20T09:00:00+09:00</t>
+          <t>2026-07-22T09:00:00+09:00</t>
         </is>
       </c>
       <c r="N98" s="60" t="inlineStr">
@@ -8453,24 +8457,24 @@
       </c>
       <c r="O98" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: Journal Article / 査読表示: Journal record — confirm peer review on publisher page / 掲載誌・学会: Machine Intelligence Research / 焦点: 医療画像セグメンテーション技術 / OpenAlex record; work type=article; citations=79</t>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: CRISPR複合体における相互作用の特定</t>
         </is>
       </c>
     </row>
     <row r="99" ht="42" customHeight="1">
       <c r="A99" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T21:02:36+09:00</t>
         </is>
       </c>
       <c r="B99" s="106" t="inlineStr">
         <is>
-          <t>2026-07-17T18:42:47Z</t>
+          <t>2026-07-22T00:00:00Z</t>
         </is>
       </c>
       <c r="C99" s="60" t="inlineStr">
         <is>
-          <t>EU &amp; Europe</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D99" s="60" t="inlineStr">
@@ -8480,45 +8484,45 @@
       </c>
       <c r="E99" s="60" t="inlineStr">
         <is>
-          <t>Fusion Energy</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="F99" s="107" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G99" s="60" t="inlineStr">
         <is>
-          <t>Industry Association</t>
+          <t>Scientific Publication</t>
         </is>
       </c>
       <c r="H99" s="60" t="inlineStr">
         <is>
-          <t>Fusion Industry Association</t>
+          <t>Nature</t>
         </is>
       </c>
       <c r="I99" s="60" t="inlineStr">
         <is>
-          <t>国際法専門家グループ、EUの核融合競争優位性確保の必要性に関する論文を発表</t>
+          <t>背景遺伝子と新しい変異ががん進化を導く</t>
         </is>
       </c>
       <c r="J99" s="60" t="inlineStr">
         <is>
-          <t>国際法専門家グループがEUの核融合エネルギーに関する競争優位性を確保する必要性を論じた。</t>
+          <t>マウスでの腫瘍進化の再実行により、DNA損傷後のがんの発展が示された。</t>
         </is>
       </c>
       <c r="K99" s="60" t="inlineStr">
         <is>
-          <t>https://www.fusionindustryassociation.org/international-legal-expert-group-publish-paper-on-the-need-for-the-eu-to-secure-its-competitive-fusion-advantage/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=international-legal-expert-group-publish-paper-on-the-need-for-the-eu-to-secure-its-competitive-fusion-advantage</t>
+          <t>https://www.nature.com/articles/d41586-026-02155-7</t>
         </is>
       </c>
       <c r="L99" s="60" t="inlineStr">
         <is>
-          <t>7ef6110ab078602757409abf</t>
+          <t>74243d6e7e201860f4f79008</t>
         </is>
       </c>
       <c r="M99" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-22T09:00:00+09:00</t>
         </is>
       </c>
       <c r="N99" s="60" t="inlineStr">
@@ -8528,7 +8532,7 @@
       </c>
       <c r="O99" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: Regulation &amp; Governance / 学術区分: News &amp; Official Release / 焦点: EUの核融合エネルギーに関する規制とガバナンス</t>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: がん進化における背景遺伝子と新しい変異の相互作用</t>
         </is>
       </c>
     </row>
@@ -8540,17 +8544,17 @@
       </c>
       <c r="B100" s="106" t="inlineStr">
         <is>
-          <t>2026-07-17T15:00:03Z</t>
+          <t>2026-07-22T00:00:00Z</t>
         </is>
       </c>
       <c r="C100" s="60" t="inlineStr">
         <is>
-          <t>EU &amp; Europe</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D100" s="60" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="E100" s="60" t="inlineStr">
@@ -8559,41 +8563,41 @@
         </is>
       </c>
       <c r="F100" s="107" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G100" s="60" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Scientific Publication</t>
         </is>
       </c>
       <c r="H100" s="60" t="inlineStr">
         <is>
-          <t>UK DSIT</t>
+          <t>Nature</t>
         </is>
       </c>
       <c r="I100" s="60" t="inlineStr">
         <is>
-          <t>AI研究資源に関するガイダンス</t>
+          <t>科学におけるAI画像のミスを避けるための3つのヒント</t>
         </is>
       </c>
       <c r="J100" s="60" t="inlineStr">
         <is>
-          <t>AI研究資源（AIRR）は、研究者や産業にAI専門の計算能力を提供するスーパーコンピュータのスイートです。</t>
+          <t>AIツールはグラフィック作成に役立つが、エラーを引き起こす可能性がある。</t>
         </is>
       </c>
       <c r="K100" s="60" t="inlineStr">
         <is>
-          <t>https://www.gov.uk/government/publications/ai-research-resource</t>
+          <t>https://www.nature.com/articles/d41586-026-02233-w</t>
         </is>
       </c>
       <c r="L100" s="60" t="inlineStr">
         <is>
-          <t>579a0b7ad2d471608fff5049</t>
+          <t>3333c16762502cf03b987a99</t>
         </is>
       </c>
       <c r="M100" s="106" t="inlineStr">
         <is>
-          <t>2026-07-18T00:00:03+09:00</t>
+          <t>2026-07-22T09:00:00+09:00</t>
         </is>
       </c>
       <c r="N100" s="60" t="inlineStr">
@@ -8603,68 +8607,72 @@
       </c>
       <c r="O100" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: AI研究資源（AIRR）</t>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: 科学におけるAI画像のミスを避けるためのヒント</t>
         </is>
       </c>
     </row>
     <row r="101" ht="42" customHeight="1">
       <c r="A101" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T21:45:54+09:00</t>
+          <t>2026-07-26T21:02:36+09:00</t>
         </is>
       </c>
       <c r="B101" s="106" t="inlineStr">
         <is>
-          <t>2026-07-17T14:48:00Z</t>
+          <t>2026-07-22T00:00:00Z</t>
         </is>
       </c>
       <c r="C101" s="60" t="inlineStr">
         <is>
-          <t>EU &amp; Europe</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D101" s="60" t="inlineStr">
         <is>
-          <t>European Patent Organisation</t>
-        </is>
-      </c>
-      <c r="E101" s="60" t="inlineStr"/>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E101" s="60" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence</t>
+        </is>
+      </c>
       <c r="F101" s="107" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G101" s="60" t="inlineStr">
         <is>
-          <t>Intergovernmental</t>
+          <t>Scientific Publication</t>
         </is>
       </c>
       <c r="H101" s="60" t="inlineStr">
         <is>
-          <t>European Patent Office News</t>
+          <t>Nature</t>
         </is>
       </c>
       <c r="I101" s="60" t="inlineStr">
         <is>
-          <t>技術革新を加速するための特許と標準</t>
+          <t>日々のブリーフィング：世界はついにポリオを根絶できるか？</t>
         </is>
       </c>
       <c r="J101" s="60" t="inlineStr">
         <is>
-          <t>特許と標準が技術革新を加速するための重要な要素であることについての情報。</t>
+          <t>一部の研究者は、現在の根絶戦略が時代遅れであると考えている。</t>
         </is>
       </c>
       <c r="K101" s="60" t="inlineStr">
         <is>
-          <t>https://epo.org/en/about-us/observatory-patents-and-technology/policy-and-funding/patents-and-standards</t>
+          <t>https://www.nature.com/articles/d41586-026-02302-0</t>
         </is>
       </c>
       <c r="L101" s="60" t="inlineStr">
         <is>
-          <t>a0d096f59b7771ee7e91da7b</t>
+          <t>a6bb3e839151ea803a445830</t>
         </is>
       </c>
       <c r="M101" s="106" t="inlineStr">
         <is>
-          <t>2026-07-17T23:48:00+09:00</t>
+          <t>2026-07-22T09:00:00+09:00</t>
         </is>
       </c>
       <c r="N101" s="60" t="inlineStr">
@@ -8674,7 +8682,7 @@
       </c>
       <c r="O101" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: Patents &amp; Intellectual Property / 学術区分: News &amp; Official Release / 焦点: 技術革新を加速するための特許と標準 / Historical backfill from an allowlisted source.</t>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: ポリオ根絶に関する研究</t>
         </is>
       </c>
     </row>
@@ -8686,56 +8694,60 @@
       </c>
       <c r="B102" s="106" t="inlineStr">
         <is>
-          <t>2026-07-17T13:42:16Z</t>
+          <t>2026-07-21T22:35:45Z</t>
         </is>
       </c>
       <c r="C102" s="60" t="inlineStr">
         <is>
-          <t>EU &amp; Europe</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D102" s="60" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="E102" s="60" t="inlineStr"/>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E102" s="60" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence</t>
+        </is>
+      </c>
       <c r="F102" s="107" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G102" s="60" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Official Company</t>
         </is>
       </c>
       <c r="H102" s="60" t="inlineStr">
         <is>
-          <t>UK DSIT</t>
+          <t>NVIDIA Blog</t>
         </is>
       </c>
       <c r="I102" s="60" t="inlineStr">
         <is>
-          <t>デジタルサービスの改善に関する公開書簡</t>
+          <t>フォートワースにて：WistronがNVIDIA AIシステムを生産するための先進的製造工場を開設</t>
         </is>
       </c>
       <c r="J102" s="60" t="inlineStr">
         <is>
-          <t>業界リーダーに向けて、デジタルサービスの改善に関する公開書簡が送られた。</t>
+          <t>Wistronがテキサス州フォートワースに324,000平方フィートの製造施設を開設し、AIシステムのためのスーパーチップを生産する。</t>
         </is>
       </c>
       <c r="K102" s="60" t="inlineStr">
         <is>
-          <t>https://www.gov.uk/government/publications/improving-access-to-and-use-of-digital-services-open-letter-to-business-leaders</t>
+          <t>https://blogs.nvidia.com/blog/wistron-manufacturing-texas/</t>
         </is>
       </c>
       <c r="L102" s="60" t="inlineStr">
         <is>
-          <t>d136ac8a836994c6ce5e35c6</t>
+          <t>21f1e1f3e19b1a5bf0af3cb7</t>
         </is>
       </c>
       <c r="M102" s="106" t="inlineStr">
         <is>
-          <t>2026-07-17T22:42:16+09:00</t>
+          <t>2026-07-22T07:35:45+09:00</t>
         </is>
       </c>
       <c r="N102" s="60" t="inlineStr">
@@ -8745,7 +8757,7 @@
       </c>
       <c r="O102" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: デジタルサービスの改善</t>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: NVIDIA AIシステムの製造</t>
         </is>
       </c>
     </row>
@@ -8757,7 +8769,7 @@
       </c>
       <c r="B103" s="106" t="inlineStr">
         <is>
-          <t>2026-07-17T12:00:04Z</t>
+          <t>2026-07-21T15:05:11Z</t>
         </is>
       </c>
       <c r="C103" s="60" t="inlineStr">
@@ -8772,7 +8784,7 @@
       </c>
       <c r="E103" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Semiconductors &amp; Telecom</t>
         </is>
       </c>
       <c r="F103" s="107" t="n">
@@ -8790,27 +8802,27 @@
       </c>
       <c r="I103" s="60" t="inlineStr">
         <is>
-          <t>AIスーパーコンピュータホストサイト選定に関する表明</t>
+          <t>固定通信近代化憲章に関する政策文書</t>
         </is>
       </c>
       <c r="J103" s="60" t="inlineStr">
         <is>
-          <t>UKの次のAIスーパーコンピュータのホストサイト選定に関する表明が行われた。</t>
+          <t>通信事業者が現在および将来の固定通信近代化を実施する際に従うべき手順を示した文書。</t>
         </is>
       </c>
       <c r="K103" s="60" t="inlineStr">
         <is>
-          <t>https://www.gov.uk/government/publications/expression-of-interest-airr-heterogeneous-supercomputer-host-site-selection</t>
+          <t>https://www.gov.uk/government/publications/fixed-telecoms-modernisation-charter</t>
         </is>
       </c>
       <c r="L103" s="60" t="inlineStr">
         <is>
-          <t>27d607577c2759c8d53f9ddf</t>
+          <t>d5e4431b57fcb4b6271f6c72</t>
         </is>
       </c>
       <c r="M103" s="106" t="inlineStr">
         <is>
-          <t>2026-07-17T21:00:04+09:00</t>
+          <t>2026-07-22T00:05:11+09:00</t>
         </is>
       </c>
       <c r="N103" s="60" t="inlineStr">
@@ -8820,7 +8832,7 @@
       </c>
       <c r="O103" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: AIスーパーコンピュータのホストサイト選定</t>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: 固定通信の近代化手順</t>
         </is>
       </c>
     </row>
@@ -8832,7 +8844,7 @@
       </c>
       <c r="B104" s="106" t="inlineStr">
         <is>
-          <t>2026-07-17T07:59:22Z</t>
+          <t>2026-07-21T15:05:07Z</t>
         </is>
       </c>
       <c r="C104" s="60" t="inlineStr">
@@ -8845,7 +8857,11 @@
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="E104" s="60" t="inlineStr"/>
+      <c r="E104" s="60" t="inlineStr">
+        <is>
+          <t>Semiconductors &amp; Telecom</t>
+        </is>
+      </c>
       <c r="F104" s="107" t="n">
         <v>3</v>
       </c>
@@ -8861,27 +8877,27 @@
       </c>
       <c r="I104" s="60" t="inlineStr">
         <is>
-          <t>子供のオンライン保護に関する新ルール</t>
+          <t>通信近代化：重要国家インフラ憲章に関する政策文書</t>
         </is>
       </c>
       <c r="J104" s="60" t="inlineStr">
         <is>
-          <t>UK政府が16歳未満の子供に対するソーシャルメディア禁止を発表した。</t>
+          <t>通信事業者が通信近代化中に重要国家インフラを保護するためのアプローチを示した文書。</t>
         </is>
       </c>
       <c r="K104" s="60" t="inlineStr">
         <is>
-          <t>https://www.gov.uk/government/publications/fact-sheet-new-rules-to-protect-children-online</t>
+          <t>https://www.gov.uk/government/publications/telecoms-modernisation-critical-national-infrastructure-charter</t>
         </is>
       </c>
       <c r="L104" s="60" t="inlineStr">
         <is>
-          <t>371ff53aa8f9007fcb1ddddf</t>
+          <t>aafa3a246656ccda64dd93c4</t>
         </is>
       </c>
       <c r="M104" s="106" t="inlineStr">
         <is>
-          <t>2026-07-17T16:59:22+09:00</t>
+          <t>2026-07-22T00:05:07+09:00</t>
         </is>
       </c>
       <c r="N104" s="60" t="inlineStr">
@@ -8891,34 +8907,34 @@
       </c>
       <c r="O104" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: 子供のオンライン保護に関する新ルール</t>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: 重要国家インフラの保護方針</t>
         </is>
       </c>
     </row>
     <row r="105" ht="42" customHeight="1">
       <c r="A105" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T21:02:36+09:00</t>
+          <t>2026-07-26T18:56:03+09:00</t>
         </is>
       </c>
       <c r="B105" s="106" t="inlineStr">
         <is>
-          <t>2026-07-16T13:35:15Z</t>
+          <t>2026-07-21T14:48:28Z</t>
         </is>
       </c>
       <c r="C105" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>EU &amp; Europe</t>
         </is>
       </c>
       <c r="D105" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="E105" s="60" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Fusion Energy</t>
         </is>
       </c>
       <c r="F105" s="107" t="n">
@@ -8926,37 +8942,37 @@
       </c>
       <c r="G105" s="60" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Industry Association</t>
         </is>
       </c>
       <c r="H105" s="60" t="inlineStr">
         <is>
-          <t>DOE Office of Science News</t>
+          <t>Fusion Industry Association</t>
         </is>
       </c>
       <c r="I105" s="60" t="inlineStr">
         <is>
-          <t>ノイズを消す：DOEが次世代量子情報科学を支える国内シリコンとゲルマニウムイソトープ供給のブレークスルーを発表</t>
+          <t>FIA、核融合のためのEU資金調達の道筋を示す</t>
         </is>
       </c>
       <c r="J105" s="60" t="inlineStr">
         <is>
-          <t>DOEが、次世代量子情報科学を加速するために、商業ソースよりも100倍以上の純度を持つイソトープを生産する成果を発表した。</t>
+          <t>Fusion Industry Associationが商業核融合エネルギーのためのEU資金調達のロードマップを発表。</t>
         </is>
       </c>
       <c r="K105" s="60" t="inlineStr">
         <is>
-          <t>https://www.energy.gov/science/articles/silencing-noise-doe-unveils-breakthrough-domestic-silicon-and-germanium-isotope</t>
+          <t>https://www.fusionindustryassociation.org/fia-outlines-eu-financing-pathway-for-fusion/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=fia-outlines-eu-financing-pathway-for-fusion</t>
         </is>
       </c>
       <c r="L105" s="60" t="inlineStr">
         <is>
-          <t>17ffa424cf814d722a951c64</t>
+          <t>88af233d904d670250fa5a31</t>
         </is>
       </c>
       <c r="M105" s="106" t="inlineStr">
         <is>
-          <t>2026-07-16T22:35:15+09:00</t>
+          <t>2026-07-26T18:56:03+09:00</t>
         </is>
       </c>
       <c r="N105" s="60" t="inlineStr">
@@ -8966,7 +8982,7 @@
       </c>
       <c r="O105" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation | Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: 量子情報科学におけるイソトープ供給</t>
+          <t>枠: Innovation Policy / 政策分野: R&amp;D Funding &amp; Tax Incentives / 学術区分: News &amp; Official Release / 焦点: EUの核融合エネルギー商業化に向けた資金調達</t>
         </is>
       </c>
     </row>
@@ -8978,7 +8994,7 @@
       </c>
       <c r="B106" s="106" t="inlineStr">
         <is>
-          <t>2026-07-15T23:00:54Z</t>
+          <t>2026-07-21T00:00:00Z</t>
         </is>
       </c>
       <c r="C106" s="60" t="inlineStr">
@@ -8988,12 +9004,12 @@
       </c>
       <c r="D106" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="E106" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence | Robotics</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="F106" s="107" t="n">
@@ -9001,37 +9017,37 @@
       </c>
       <c r="G106" s="60" t="inlineStr">
         <is>
-          <t>Official Company</t>
+          <t>Conference Paper</t>
         </is>
       </c>
       <c r="H106" s="60" t="inlineStr">
         <is>
-          <t>NVIDIA Blog</t>
+          <t>OpenAlex Conference Papers</t>
         </is>
       </c>
       <c r="I106" s="60" t="inlineStr">
         <is>
-          <t>NVIDIAがロボティクスとエッジAIを進展させる新しいJetson Thorコンピュータを発表</t>
+          <t>量子機械学習による心血管疾患リスク予測の向上</t>
         </is>
       </c>
       <c r="J106" s="60" t="inlineStr">
         <is>
-          <t>NVIDIAが新しいJetson Thorコンピュータを発表し、一般向けロボットとエッジAIの需要に応える。</t>
+          <t>この研究は、量子アルゴリズムを用いて心血管疾患の予測を行うモデルを探求しており、量子サポートベクターマシンや量子ニューラルネットワークを活用しています。</t>
         </is>
       </c>
       <c r="K106" s="60" t="inlineStr">
         <is>
-          <t>https://blogs.nvidia.com/blog/jetson-thor-robotics-edge-ai-agent/</t>
+          <t>https://doi.org/10.3390/engproc2026150039</t>
         </is>
       </c>
       <c r="L106" s="60" t="inlineStr">
         <is>
-          <t>85f482f3f904d00f68946a80</t>
+          <t>1cd467f8ebb1388daedc245f</t>
         </is>
       </c>
       <c r="M106" s="106" t="inlineStr">
         <is>
-          <t>2026-07-16T08:00:54+09:00</t>
+          <t>2026-07-21T09:00:00+09:00</t>
         </is>
       </c>
       <c r="N106" s="60" t="inlineStr">
@@ -9041,7 +9057,7 @@
       </c>
       <c r="O106" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: AIスーパコンピュータモジュール</t>
+          <t>枠: Technology Innovation / 学術区分: Conference Paper / 査読表示: Conference proceedings — review status varies / 焦点: 量子機械学習による心血管疾患リスク予測 / OpenAlex record; work type=conference-paper; citations=0</t>
         </is>
       </c>
     </row>
@@ -9053,7 +9069,7 @@
       </c>
       <c r="B107" s="106" t="inlineStr">
         <is>
-          <t>2026-07-15T21:00:00Z</t>
+          <t>2026-07-20T21:06:27Z</t>
         </is>
       </c>
       <c r="C107" s="60" t="inlineStr">
@@ -9072,7 +9088,7 @@
         </is>
       </c>
       <c r="F107" s="107" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G107" s="60" t="inlineStr">
         <is>
@@ -9081,32 +9097,32 @@
       </c>
       <c r="H107" s="60" t="inlineStr">
         <is>
-          <t>CSET</t>
+          <t>Brookings TechTank</t>
         </is>
       </c>
       <c r="I107" s="60" t="inlineStr">
         <is>
-          <t>GPT-Red: OpenAIが構築したモデルの安全性向上のためのAI</t>
+          <t>AIの借りた専門知識に対処する教育と研究政策</t>
         </is>
       </c>
       <c r="J107" s="60" t="inlineStr">
         <is>
-          <t>OpenAIが開発したGPT-Redは、大規模言語モデルの脆弱性を自動的に特定し、サイバー攻撃に対する防御を強化するためのAIです。</t>
+          <t>教育政策が短期的な生産性と長期的な認知発展の間の緊張にどのように対応すべきかについて論じています。</t>
         </is>
       </c>
       <c r="K107" s="60" t="inlineStr">
         <is>
-          <t>https://cset.georgetown.edu/article/meet-gpt-red-an-llm-super-hacker-openai-built-to-make-its-models-safer/</t>
+          <t>https://brookings.edu/articles/repaying-the-inheritance-how-education-and-research-policy-can-address-ais-borrowed-expertise</t>
         </is>
       </c>
       <c r="L107" s="60" t="inlineStr">
         <is>
-          <t>f64391d3daf689e78e7ac442</t>
+          <t>42183313e1c951c0483c0d62</t>
         </is>
       </c>
       <c r="M107" s="106" t="inlineStr">
         <is>
-          <t>2026-07-16T06:00:00+09:00</t>
+          <t>2026-07-21T06:06:27+09:00</t>
         </is>
       </c>
       <c r="N107" s="60" t="inlineStr">
@@ -9116,7 +9132,7 @@
       </c>
       <c r="O107" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: AIの脆弱性を特定する技術</t>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: AIに関する教育政策の変革 / Historical backfill from an allowlisted source.</t>
         </is>
       </c>
     </row>
@@ -9128,7 +9144,7 @@
       </c>
       <c r="B108" s="106" t="inlineStr">
         <is>
-          <t>2026-07-14T16:00:08Z</t>
+          <t>2026-07-20T15:55:00Z</t>
         </is>
       </c>
       <c r="C108" s="60" t="inlineStr">
@@ -9141,43 +9157,47 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="E108" s="60" t="inlineStr"/>
+      <c r="E108" s="60" t="inlineStr">
+        <is>
+          <t>Semiconductors &amp; Telecom</t>
+        </is>
+      </c>
       <c r="F108" s="107" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G108" s="60" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Major Media</t>
         </is>
       </c>
       <c r="H108" s="60" t="inlineStr">
         <is>
-          <t>National Science Foundation News</t>
+          <t>IEEE Spectrum</t>
         </is>
       </c>
       <c r="I108" s="60" t="inlineStr">
         <is>
-          <t>NSFが全国の研究、雇用、経済成長を促進するために12の新しい地域イノベーションエンジンを授与</t>
+          <t>先進半導体故障解析のためのSEMガイド低電圧FIB仕上げ</t>
         </is>
       </c>
       <c r="J108" s="60" t="inlineStr">
         <is>
-          <t>米国科学財団は、全国の20州にわたる12のチームに新しいNSF地域イノベーションエンジンの助成を発表した。これにより、イノベーションクラスターの構築とスケールアップを目指す。</t>
+          <t>ZEISS Crossbeam 750 FIBSEMが先進的な半導体故障解析の新しい基準を設定する方法について説明しています。</t>
         </is>
       </c>
       <c r="K108" s="60" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/news/nsf-awards-12-new-regional-innovation-engines-fuel-research</t>
+          <t>https://event.on24.com/wcc/r/5418459/287E3D5B99470D34C830D69A24B3B207</t>
         </is>
       </c>
       <c r="L108" s="60" t="inlineStr">
         <is>
-          <t>de4a8c6972dcbf82c2e445b3</t>
+          <t>73d0028e337a76c2cd00f1bc</t>
         </is>
       </c>
       <c r="M108" s="106" t="inlineStr">
         <is>
-          <t>2026-07-15T01:00:08+09:00</t>
+          <t>2026-07-21T00:55:00+09:00</t>
         </is>
       </c>
       <c r="N108" s="60" t="inlineStr">
@@ -9187,7 +9207,7 @@
       </c>
       <c r="O108" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: 地域イノベーションエンジン</t>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: 先進半導体の故障解析技術</t>
         </is>
       </c>
     </row>
@@ -9199,7 +9219,7 @@
       </c>
       <c r="B109" s="106" t="inlineStr">
         <is>
-          <t>2026-07-10T00:00:00Z</t>
+          <t>2026-07-20T15:00:53Z</t>
         </is>
       </c>
       <c r="C109" s="60" t="inlineStr">
@@ -9209,12 +9229,12 @@
       </c>
       <c r="D109" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E109" s="60" t="inlineStr">
         <is>
-          <t>Fusion Energy</t>
+          <t>Artificial Intelligence | Robotics</t>
         </is>
       </c>
       <c r="F109" s="107" t="n">
@@ -9222,37 +9242,37 @@
       </c>
       <c r="G109" s="60" t="inlineStr">
         <is>
-          <t>Journal Article</t>
+          <t>Official Company</t>
         </is>
       </c>
       <c r="H109" s="60" t="inlineStr">
         <is>
-          <t>Nuclear Fusion</t>
+          <t>NVIDIA Blog</t>
         </is>
       </c>
       <c r="I109" s="60" t="inlineStr">
         <is>
-          <t>ST-E1核融合発電プラントの統合物理と磁石設計</t>
+          <t>SIGGRAPHでNVIDIAがエージェントAIと物理AIでグラフィックスとシミュレーションを進展</t>
         </is>
       </c>
       <c r="J109" s="60" t="inlineStr">
         <is>
-          <t>ST-E1は、トカマクエナジーの商業競争力のある核融合発電プラント設計であり、ハイテクスーパコンダクターマグネットケージを特徴としています。</t>
+          <t>NVIDIAはSIGGRAPHで、オープンモデルからリアルタイムシミュレーションまで、AIとグラフィックスの革新がメディア、コンテンツ制作、ロボティクスを変革していることを発表した。</t>
         </is>
       </c>
       <c r="K109" s="60" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1088/1741-4326/ae773b</t>
+          <t>https://blogs.nvidia.com/blog/siggraph-news-2026/</t>
         </is>
       </c>
       <c r="L109" s="60" t="inlineStr">
         <is>
-          <t>a0ed06f7d374240814073762</t>
+          <t>70c1acaa81ba6cd1c84a673d</t>
         </is>
       </c>
       <c r="M109" s="106" t="inlineStr">
         <is>
-          <t>2026-07-10T09:00:00+09:00</t>
+          <t>2026-07-21T00:00:53+09:00</t>
         </is>
       </c>
       <c r="N109" s="60" t="inlineStr">
@@ -9262,7 +9282,7 @@
       </c>
       <c r="O109" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: Journal Article / 査読表示: Journal record — confirm peer review on publisher page / 掲載誌・学会: Nuclear Fusion / 焦点: 核融合技術 / OpenAlex record; work type=article; citations=9</t>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: エージェントAIと物理AIの進展</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9294,7 @@
       </c>
       <c r="B110" s="106" t="inlineStr">
         <is>
-          <t>2026-07-08T08:00:00Z</t>
+          <t>2026-07-20T13:30:06Z</t>
         </is>
       </c>
       <c r="C110" s="60" t="inlineStr">
@@ -9284,50 +9304,50 @@
       </c>
       <c r="D110" s="60" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="E110" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Artificial Intelligence | Semiconductors &amp; Telecom</t>
         </is>
       </c>
       <c r="F110" s="107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G110" s="60" t="inlineStr">
         <is>
-          <t>Official Company</t>
+          <t>Major Media</t>
         </is>
       </c>
       <c r="H110" s="60" t="inlineStr">
         <is>
-          <t>Samsung Global Newsroom</t>
+          <t>South China Morning Post Technology</t>
         </is>
       </c>
       <c r="I110" s="60" t="inlineStr">
         <is>
-          <t>サムスン、次世代AIインフラ向けに最適化されたPM1763 SSDの量産を開始</t>
+          <t>トークン経済からタスク経済へ？SenseTimeがAIの商業化に賭ける</t>
         </is>
       </c>
       <c r="J110" s="60" t="inlineStr">
         <is>
-          <t>サムスン電子は、次世代AIおよびHPCサーバー環境向けに最適化されたPCIe® 6.0ベースの企業向けSSD、PM1763の量産を開始した。</t>
+          <t>中国のAI企業SenseTimeは、トークン価格の低下に伴い、AIの商業化が「トークン経済」から「タスク経済」へ移行する見込みであると述べた。</t>
         </is>
       </c>
       <c r="K110" s="60" t="inlineStr">
         <is>
-          <t>https://news.samsung.com/global/samsung-begins-mass-production-of-pm1763-ssd-optimized-for-next-generation-ai-infrastructure</t>
+          <t>https://www.scmp.com/tech/big-tech/article/3361242/no-longer-token-economy-sensetime-bets-task-economy-token-prices-set-drop?utm_source=rss_feed</t>
         </is>
       </c>
       <c r="L110" s="60" t="inlineStr">
         <is>
-          <t>ffa2f59ee7918b4bbfdce082</t>
+          <t>cd5b1ea310d8a65d00ad1ad9</t>
         </is>
       </c>
       <c r="M110" s="106" t="inlineStr">
         <is>
-          <t>2026-07-08T17:00:00+09:00</t>
+          <t>2026-07-20T22:30:06+09:00</t>
         </is>
       </c>
       <c r="N110" s="60" t="inlineStr">
@@ -9337,72 +9357,72 @@
       </c>
       <c r="O110" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: PM1763 SSD</t>
+          <t>枠: Technology Innovation | Innovation Policy / 政策分野: Patents &amp; Intellectual Property / 学術区分: News &amp; Official Release / 焦点: AIの商業化の移行</t>
         </is>
       </c>
     </row>
     <row r="111" ht="42" customHeight="1">
       <c r="A111" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T21:02:36+09:00</t>
+          <t>2026-07-28T01:39:30+09:00</t>
         </is>
       </c>
       <c r="B111" s="106" t="inlineStr">
         <is>
-          <t>2026-07-07T18:00:07Z</t>
+          <t>2026-07-20T13:21:36Z</t>
         </is>
       </c>
       <c r="C111" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D111" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="E111" s="60" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Fusion Energy</t>
         </is>
       </c>
       <c r="F111" s="107" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G111" s="60" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Industry Association</t>
         </is>
       </c>
       <c r="H111" s="60" t="inlineStr">
         <is>
-          <t>National Science Foundation News</t>
+          <t>Fusion Industry Association</t>
         </is>
       </c>
       <c r="I111" s="60" t="inlineStr">
         <is>
-          <t>NSF、実用的な量子技術を進展させるProject Triadを開始</t>
+          <t>LLNLとPacific Fusion、Siriusパルスパワープロトタイプで3,000回のテスト達成</t>
         </is>
       </c>
       <c r="J111" s="60" t="inlineStr">
         <is>
-          <t>米国国立科学財団が量子技術を統合する新たなイニシアティブ、Project Triadを発表した。</t>
+          <t>ローレンス・リバモア国立研究所とPacific Fusionは、Siriusパルスパワープロトタイプの3,000回の成功テストを達成しました。この成果は、核融合エネルギーの大規模デモンストレーションに向けた重要な進展を示しています。</t>
         </is>
       </c>
       <c r="K111" s="60" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/news/nsf-launches-project-triad-advance-quantum-technology-real</t>
+          <t>https://www.ans.org/news/article-8217/llnl-and-pacific-fusion-achieve-3000shot-milestone-with-sirius-pulsedpower-prototype/?mc_cid=ed1acc7bef&amp;mc_eid=01cd8fe465#new_tab&amp;utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=llnl-and-pacific-fusion-achieve-3000-shot-milestone-with-sirius-pulsed-power-prototype</t>
         </is>
       </c>
       <c r="L111" s="60" t="inlineStr">
         <is>
-          <t>2d4a226d3ce7cc9e366e902d</t>
+          <t>c654a0d44a7fcbda5490cd6d</t>
         </is>
       </c>
       <c r="M111" s="106" t="inlineStr">
         <is>
-          <t>2026-07-08T03:00:07+09:00</t>
+          <t>2026-07-28T01:39:30+09:00</t>
         </is>
       </c>
       <c r="N111" s="60" t="inlineStr">
@@ -9412,19 +9432,19 @@
       </c>
       <c r="O111" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: Project Triad</t>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: 核融合エネルギー技術</t>
         </is>
       </c>
     </row>
     <row r="112" ht="42" customHeight="1">
       <c r="A112" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T21:02:36+09:00</t>
+          <t>2026-07-28T01:39:30+09:00</t>
         </is>
       </c>
       <c r="B112" s="106" t="inlineStr">
         <is>
-          <t>2026-06-29T21:14:22Z</t>
+          <t>2026-07-20T13:17:02Z</t>
         </is>
       </c>
       <c r="C112" s="60" t="inlineStr">
@@ -9434,12 +9454,12 @@
       </c>
       <c r="D112" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="E112" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Fusion Energy | Quantum</t>
         </is>
       </c>
       <c r="F112" s="107" t="n">
@@ -9447,37 +9467,37 @@
       </c>
       <c r="G112" s="60" t="inlineStr">
         <is>
-          <t>Official Company</t>
+          <t>Industry Association</t>
         </is>
       </c>
       <c r="H112" s="60" t="inlineStr">
         <is>
-          <t>Microsoft Research</t>
+          <t>Fusion Industry Association</t>
         </is>
       </c>
       <c r="I112" s="60" t="inlineStr">
         <is>
-          <t>Memora: 抽象と特異性のバランスを取る調和的メモリ表現</t>
+          <t>量子材料の発見が核融合用電子機器の進展を促進する可能性</t>
         </is>
       </c>
       <c r="J112" s="60" t="inlineStr">
         <is>
-          <t>AIエージェントが過去の会話を記憶できない問題を解決するために、Memoraがスケーラブルなメモリシステムを提案した。</t>
+          <t>アリゾナ大学の研究者は、グラフェンナノリボンが将来の核融合発電所の放射線センサーとして機能する可能性を示しました。この技術は、既存のセンサーよりも反応器コアに近いリアルタイムモニタリングを可能にするかもしれません。</t>
         </is>
       </c>
       <c r="K112" s="60" t="inlineStr">
         <is>
-          <t>https://www.microsoft.com/en-us/research/blog/memora-a-harmonic-memory-representation-balancing-abstraction-and-specificity/</t>
+          <t>https://thequantuminsider.com/2026/07/20/quantum-materials-discovery-could-advance-electronics-for-extreme-environments/?mc_cid=ed1acc7bef&amp;mc_eid=01cd8fe465#new_tab&amp;utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=quantum-materials-discovery-could-advance-electronics-for-fusion</t>
         </is>
       </c>
       <c r="L112" s="60" t="inlineStr">
         <is>
-          <t>6c035ef4d4202a4874e60b97</t>
+          <t>1d37727752cb4b098b374ef4</t>
         </is>
       </c>
       <c r="M112" s="106" t="inlineStr">
         <is>
-          <t>2026-06-30T06:14:22+09:00</t>
+          <t>2026-07-28T01:39:30+09:00</t>
         </is>
       </c>
       <c r="N112" s="60" t="inlineStr">
@@ -9487,7 +9507,7 @@
       </c>
       <c r="O112" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: AIメモリシステム</t>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: 量子材料と核融合技術</t>
         </is>
       </c>
     </row>
@@ -9499,24 +9519,20 @@
       </c>
       <c r="B113" s="106" t="inlineStr">
         <is>
-          <t>2026-06-29T12:00:00Z</t>
+          <t>2026-07-20T11:29:00Z</t>
         </is>
       </c>
       <c r="C113" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>EU &amp; Europe</t>
         </is>
       </c>
       <c r="D113" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E113" s="60" t="inlineStr">
-        <is>
-          <t>Quantum</t>
-        </is>
-      </c>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="E113" s="60" t="inlineStr"/>
       <c r="F113" s="107" t="n">
         <v>3</v>
       </c>
@@ -9527,32 +9543,32 @@
       </c>
       <c r="H113" s="60" t="inlineStr">
         <is>
-          <t>NIST News</t>
+          <t>UK DSIT</t>
         </is>
       </c>
       <c r="I113" s="60" t="inlineStr">
         <is>
-          <t>NIST、量子技術の製造を推進するセンターを設立</t>
+          <t>透明性データ：契約されたおよび建設された施設、プロジェクトギガビット契約</t>
         </is>
       </c>
       <c r="J113" s="60" t="inlineStr">
         <is>
-          <t>NISTは、量子製造工学センター（QMEC）を設立するためにSRIインターナショナルとの合意を発表した。</t>
+          <t>デジタルUKがプロジェクトギガビット契約に基づく契約状況を報告しています。</t>
         </is>
       </c>
       <c r="K113" s="60" t="inlineStr">
         <is>
-          <t>https://www.nist.gov/news-events/news/2026/06/nist-launches-center-drive-manufacture-quantum-technologies</t>
+          <t>https://www.gov.uk/government/publications/premises-contracted-and-built-project-gigabit-contracts</t>
         </is>
       </c>
       <c r="L113" s="60" t="inlineStr">
         <is>
-          <t>2d90197d96166b4d1d7f7c11</t>
+          <t>d643b4b81f6998869b340654</t>
         </is>
       </c>
       <c r="M113" s="106" t="inlineStr">
         <is>
-          <t>2026-06-29T21:00:00+09:00</t>
+          <t>2026-07-20T20:29:00+09:00</t>
         </is>
       </c>
       <c r="N113" s="60" t="inlineStr">
@@ -9562,7 +9578,7 @@
       </c>
       <c r="O113" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: Public Procurement &amp; Industrial Policy / 学術区分: News &amp; Official Release / 焦点: 量子製造工学センターの設立</t>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: デジタルインフラ整備に関する国家戦略</t>
         </is>
       </c>
     </row>
@@ -9574,56 +9590,60 @@
       </c>
       <c r="B114" s="106" t="inlineStr">
         <is>
-          <t>2026-06-26T04:47:39Z</t>
+          <t>2026-07-20T10:59:23Z</t>
         </is>
       </c>
       <c r="C114" s="60" t="inlineStr">
         <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="D114" s="60" t="inlineStr">
+        <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="D114" s="60" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
-      </c>
-      <c r="E114" s="60" t="inlineStr"/>
+      <c r="E114" s="60" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence</t>
+        </is>
+      </c>
       <c r="F114" s="107" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G114" s="60" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Official Company</t>
         </is>
       </c>
       <c r="H114" s="60" t="inlineStr">
         <is>
-          <t>NISTEP Updates</t>
+          <t>NVIDIA Blog</t>
         </is>
       </c>
       <c r="I114" s="60" t="inlineStr">
         <is>
-          <t>研究文化をめぐる対話と展開に関する資料公開</t>
+          <t>Bristol Myers Squibbがライフサイエンス業界で最も先進的なAI工場を構築</t>
         </is>
       </c>
       <c r="J114" s="60" t="inlineStr">
         <is>
-          <t>文部科学省が研究者対象のウェルビーイングと研究文化に関する全国調査の準備を進めています。</t>
+          <t>Bristol Myers Squibbは、ライフサイエンス分野でのAIクラスターを拡大し、成果を上げていることを発表した。</t>
         </is>
       </c>
       <c r="K114" s="60" t="inlineStr">
         <is>
-          <t>https://www.nistep.go.jp/archives/63398/</t>
+          <t>https://blogs.nvidia.com/blog/bristol-myers-squibb-building-life-science-industrys-most-advanced-ai-factory-on-nvidia-vera-rubin/</t>
         </is>
       </c>
       <c r="L114" s="60" t="inlineStr">
         <is>
-          <t>ff67a3172cc526b012791921</t>
+          <t>b4ddc90482832cbb50579f2a</t>
         </is>
       </c>
       <c r="M114" s="106" t="inlineStr">
         <is>
-          <t>2026-06-26T13:47:39+09:00</t>
+          <t>2026-07-20T19:59:23+09:00</t>
         </is>
       </c>
       <c r="N114" s="60" t="inlineStr">
@@ -9633,7 +9653,7 @@
       </c>
       <c r="O114" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: 研究者のウェルビーイングと研究文化</t>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: AIクラスターの展開</t>
         </is>
       </c>
     </row>
@@ -9645,56 +9665,60 @@
       </c>
       <c r="B115" s="106" t="inlineStr">
         <is>
-          <t>2026-06-26T01:30:26Z</t>
+          <t>2026-07-20T00:00:00Z</t>
         </is>
       </c>
       <c r="C115" s="60" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D115" s="60" t="inlineStr">
         <is>
-          <t>Japan</t>
-        </is>
-      </c>
-      <c r="E115" s="60" t="inlineStr"/>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E115" s="60" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence | Healthcare</t>
+        </is>
+      </c>
       <c r="F115" s="107" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G115" s="60" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Journal Article</t>
         </is>
       </c>
       <c r="H115" s="60" t="inlineStr">
         <is>
-          <t>NISTEP Updates</t>
+          <t>Machine Intelligence Research</t>
         </is>
       </c>
       <c r="I115" s="60" t="inlineStr">
         <is>
-          <t>親子企業間の資源再配分と特許活動の特性</t>
+          <t>M2SNet: 医療画像セグメンテーションのためのマルチスケール減算ネットワーク</t>
         </is>
       </c>
       <c r="J115" s="60" t="inlineStr">
         <is>
-          <t>親子企業間での研究開発資源の移動に関する特許活動の特性についての実証分析が行われました。</t>
+          <t>M2SNetは、医療画像のセグメンテーションを改善するために、異なるレベルの特徴を効果的に融合する新しい手法を提案します。</t>
         </is>
       </c>
       <c r="K115" s="60" t="inlineStr">
         <is>
-          <t>https://www.nistep.go.jp/archives/63333/</t>
+          <t>https://doi.org/10.1007/s11633-026-1662-9</t>
         </is>
       </c>
       <c r="L115" s="60" t="inlineStr">
         <is>
-          <t>25352f245236dac75576baa7</t>
+          <t>bffca1cc322e28515452081a</t>
         </is>
       </c>
       <c r="M115" s="106" t="inlineStr">
         <is>
-          <t>2026-06-26T10:30:26+09:00</t>
+          <t>2026-07-20T09:00:00+09:00</t>
         </is>
       </c>
       <c r="N115" s="60" t="inlineStr">
@@ -9704,68 +9728,72 @@
       </c>
       <c r="O115" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy | Patents &amp; Intellectual Property / 学術区分: News &amp; Official Release / 焦点: 親子企業間の資源再配分と特許活動</t>
+          <t>枠: Technology Innovation / 学術区分: Journal Article / 査読表示: Journal record — confirm peer review on publisher page / 掲載誌・学会: Machine Intelligence Research / 焦点: 医療画像セグメンテーション技術 / OpenAlex record; work type=article; citations=79</t>
         </is>
       </c>
     </row>
     <row r="116" ht="42" customHeight="1">
       <c r="A116" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T21:02:36+09:00</t>
+          <t>2026-07-26T18:56:03+09:00</t>
         </is>
       </c>
       <c r="B116" s="106" t="inlineStr">
         <is>
-          <t>2026-06-25T05:26:14Z</t>
+          <t>2026-07-17T18:42:47Z</t>
         </is>
       </c>
       <c r="C116" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>EU &amp; Europe</t>
         </is>
       </c>
       <c r="D116" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E116" s="60" t="inlineStr"/>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E116" s="60" t="inlineStr">
+        <is>
+          <t>Fusion Energy</t>
+        </is>
+      </c>
       <c r="F116" s="107" t="n">
         <v>4</v>
       </c>
       <c r="G116" s="60" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Industry Association</t>
         </is>
       </c>
       <c r="H116" s="60" t="inlineStr">
         <is>
-          <t>DOE Office of Science News</t>
+          <t>Fusion Industry Association</t>
         </is>
       </c>
       <c r="I116" s="60" t="inlineStr">
         <is>
-          <t>米国エネルギー省が国内供給網を強化</t>
+          <t>国際法専門家グループ、EUの核融合競争優位性確保の必要性に関する論文を発表</t>
         </is>
       </c>
       <c r="J116" s="60" t="inlineStr">
         <is>
-          <t>米国エネルギー省がイリジウム-192の国内生産能力を確立しました。</t>
+          <t>国際法専門家グループがEUの核融合エネルギーに関する競争優位性を確保する必要性を論じた。</t>
         </is>
       </c>
       <c r="K116" s="60" t="inlineStr">
         <is>
-          <t>https://www.energy.gov/science/articles/doe-strengthens-domestic-supply-chain-american-energy-and-manufacturing</t>
+          <t>https://www.fusionindustryassociation.org/international-legal-expert-group-publish-paper-on-the-need-for-the-eu-to-secure-its-competitive-fusion-advantage/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=international-legal-expert-group-publish-paper-on-the-need-for-the-eu-to-secure-its-competitive-fusion-advantage</t>
         </is>
       </c>
       <c r="L116" s="60" t="inlineStr">
         <is>
-          <t>62854e5795f9fac8f0427e2f</t>
+          <t>7ef6110ab078602757409abf</t>
         </is>
       </c>
       <c r="M116" s="106" t="inlineStr">
         <is>
-          <t>2026-06-25T14:26:14+09:00</t>
+          <t>2026-07-26T18:56:03+09:00</t>
         </is>
       </c>
       <c r="N116" s="60" t="inlineStr">
@@ -9775,7 +9803,7 @@
       </c>
       <c r="O116" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: イリジウム-192の国内生産能力</t>
+          <t>枠: Innovation Policy / 政策分野: Regulation &amp; Governance / 学術区分: News &amp; Official Release / 焦点: EUの核融合エネルギーに関する規制とガバナンス</t>
         </is>
       </c>
     </row>
@@ -9787,22 +9815,26 @@
       </c>
       <c r="B117" s="106" t="inlineStr">
         <is>
-          <t>2026-06-25T04:00:24Z</t>
+          <t>2026-07-17T15:00:03Z</t>
         </is>
       </c>
       <c r="C117" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>EU &amp; Europe</t>
         </is>
       </c>
       <c r="D117" s="60" t="inlineStr">
         <is>
-          <t>Japan</t>
-        </is>
-      </c>
-      <c r="E117" s="60" t="inlineStr"/>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="E117" s="60" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence</t>
+        </is>
+      </c>
       <c r="F117" s="107" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G117" s="60" t="inlineStr">
         <is>
@@ -9811,32 +9843,32 @@
       </c>
       <c r="H117" s="60" t="inlineStr">
         <is>
-          <t>NISTEP Updates</t>
+          <t>UK DSIT</t>
         </is>
       </c>
       <c r="I117" s="60" t="inlineStr">
         <is>
-          <t>STI Horizon誌2026夏号の公表</t>
+          <t>AI研究資源に関するガイダンス</t>
         </is>
       </c>
       <c r="J117" s="60" t="inlineStr">
         <is>
-          <t>NISTEPが科学技術・イノベーション政策に関する情報を幅広く掲載したSTI Horizon 2026夏号を公表しました。</t>
+          <t>AI研究資源（AIRR）は、研究者や産業にAI専門の計算能力を提供するスーパーコンピュータのスイートです。</t>
         </is>
       </c>
       <c r="K117" s="60" t="inlineStr">
         <is>
-          <t>https://www.nistep.go.jp/archives/63155/</t>
+          <t>https://www.gov.uk/government/publications/ai-research-resource</t>
         </is>
       </c>
       <c r="L117" s="60" t="inlineStr">
         <is>
-          <t>79d88af79ddda07d59b28e08</t>
+          <t>579a0b7ad2d471608fff5049</t>
         </is>
       </c>
       <c r="M117" s="106" t="inlineStr">
         <is>
-          <t>2026-06-25T13:00:24+09:00</t>
+          <t>2026-07-18T00:00:03+09:00</t>
         </is>
       </c>
       <c r="N117" s="60" t="inlineStr">
@@ -9846,19 +9878,19 @@
       </c>
       <c r="O117" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: 科学技術・イノベーション政策</t>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: AI研究資源（AIRR）</t>
         </is>
       </c>
     </row>
     <row r="118" ht="42" customHeight="1">
       <c r="A118" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T21:02:36+09:00</t>
+          <t>2026-07-26T21:45:54+09:00</t>
         </is>
       </c>
       <c r="B118" s="106" t="inlineStr">
         <is>
-          <t>2026-06-23T14:26:00Z</t>
+          <t>2026-07-17T14:48:00Z</t>
         </is>
       </c>
       <c r="C118" s="60" t="inlineStr">
@@ -9868,50 +9900,46 @@
       </c>
       <c r="D118" s="60" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="E118" s="60" t="inlineStr">
-        <is>
-          <t>Robotics</t>
-        </is>
-      </c>
+          <t>European Patent Organisation</t>
+        </is>
+      </c>
+      <c r="E118" s="60" t="inlineStr"/>
       <c r="F118" s="107" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G118" s="60" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Intergovernmental</t>
         </is>
       </c>
       <c r="H118" s="60" t="inlineStr">
         <is>
-          <t>UK DSIT</t>
+          <t>European Patent Office News</t>
         </is>
       </c>
       <c r="I118" s="60" t="inlineStr">
         <is>
-          <t>Sellafieldの清掃を助ける新しいロボット</t>
+          <t>技術革新を加速するための特許と標準</t>
         </is>
       </c>
       <c r="J118" s="60" t="inlineStr">
         <is>
-          <t>リモート操作された機械がSellafieldの最も危険な核廃棄物保管所に初めて送られ、清掃作業を支援している。</t>
+          <t>特許と標準が技術革新を加速するための重要な要素であることについての情報。</t>
         </is>
       </c>
       <c r="K118" s="60" t="inlineStr">
         <is>
-          <t>https://gov.uk/government/news/the-new-robot-helping-clean-up-sellafield</t>
+          <t>https://epo.org/en/about-us/observatory-patents-and-technology/policy-and-funding/patents-and-standards</t>
         </is>
       </c>
       <c r="L118" s="60" t="inlineStr">
         <is>
-          <t>132391c846d95677d6ca86ff</t>
+          <t>a0d096f59b7771ee7e91da7b</t>
         </is>
       </c>
       <c r="M118" s="106" t="inlineStr">
         <is>
-          <t>2026-06-23T23:26:00+09:00</t>
+          <t>2026-07-17T23:48:00+09:00</t>
         </is>
       </c>
       <c r="N118" s="60" t="inlineStr">
@@ -9921,7 +9949,7 @@
       </c>
       <c r="O118" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: Sellafieldでのロボットの使用 / Historical backfill from an allowlisted source.</t>
+          <t>枠: Innovation Policy / 政策分野: Patents &amp; Intellectual Property / 学術区分: News &amp; Official Release / 焦点: 技術革新を加速するための特許と標準 / Historical backfill from an allowlisted source.</t>
         </is>
       </c>
     </row>
@@ -9933,26 +9961,22 @@
       </c>
       <c r="B119" s="106" t="inlineStr">
         <is>
-          <t>2026-06-23T11:43:57Z</t>
+          <t>2026-07-17T13:42:16Z</t>
         </is>
       </c>
       <c r="C119" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>EU &amp; Europe</t>
         </is>
       </c>
       <c r="D119" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E119" s="60" t="inlineStr">
-        <is>
-          <t>Quantum</t>
-        </is>
-      </c>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="E119" s="60" t="inlineStr"/>
       <c r="F119" s="107" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G119" s="60" t="inlineStr">
         <is>
@@ -9961,32 +9985,32 @@
       </c>
       <c r="H119" s="60" t="inlineStr">
         <is>
-          <t>DOE Office of Science News</t>
+          <t>UK DSIT</t>
         </is>
       </c>
       <c r="I119" s="60" t="inlineStr">
         <is>
-          <t>エネルギー省、科学的に関連する耐障害量子コンピュータの創出と展開に関するイニシアティブを発表</t>
+          <t>デジタルサービスの改善に関する公開書簡</t>
         </is>
       </c>
       <c r="J119" s="60" t="inlineStr">
         <is>
-          <t>米国エネルギー省が、科学的に関連する耐障害量子コンピュータを創出し展開するためのイニシアティブを発表した。</t>
+          <t>業界リーダーに向けて、デジタルサービスの改善に関する公開書簡が送られた。</t>
         </is>
       </c>
       <c r="K119" s="60" t="inlineStr">
         <is>
-          <t>https://www.energy.gov/science/articles/energy-department-announces-initiative-create-and-deploy-worlds-first</t>
+          <t>https://www.gov.uk/government/publications/improving-access-to-and-use-of-digital-services-open-letter-to-business-leaders</t>
         </is>
       </c>
       <c r="L119" s="60" t="inlineStr">
         <is>
-          <t>9e1d8ad5a7ac944965b9f2bd</t>
+          <t>d136ac8a836994c6ce5e35c6</t>
         </is>
       </c>
       <c r="M119" s="106" t="inlineStr">
         <is>
-          <t>2026-06-23T20:43:57+09:00</t>
+          <t>2026-07-17T22:42:16+09:00</t>
         </is>
       </c>
       <c r="N119" s="60" t="inlineStr">
@@ -9996,19 +10020,19 @@
       </c>
       <c r="O119" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: 量子コンピュータの開発</t>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: デジタルサービスの改善</t>
         </is>
       </c>
     </row>
     <row r="120" ht="42" customHeight="1">
       <c r="A120" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T22:54:37+09:00</t>
+          <t>2026-07-26T21:02:36+09:00</t>
         </is>
       </c>
       <c r="B120" s="106" t="inlineStr">
         <is>
-          <t>2026-06-17T00:00:00Z</t>
+          <t>2026-07-17T12:00:04Z</t>
         </is>
       </c>
       <c r="C120" s="60" t="inlineStr">
@@ -10018,12 +10042,16 @@
       </c>
       <c r="D120" s="60" t="inlineStr">
         <is>
-          <t>European Union</t>
-        </is>
-      </c>
-      <c r="E120" s="60" t="inlineStr"/>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="E120" s="60" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence</t>
+        </is>
+      </c>
       <c r="F120" s="107" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G120" s="60" t="inlineStr">
         <is>
@@ -10032,32 +10060,32 @@
       </c>
       <c r="H120" s="60" t="inlineStr">
         <is>
-          <t>European Innovation Council Policy Benchmarks</t>
+          <t>UK DSIT</t>
         </is>
       </c>
       <c r="I120" s="60" t="inlineStr">
         <is>
-          <t>EIC、14億ユーロ超の2026年ワークプログラムを改定</t>
+          <t>AIスーパーコンピュータホストサイト選定に関する表明</t>
         </is>
       </c>
       <c r="J120" s="60" t="inlineStr">
         <is>
-          <t>欧州イノベーション会議は、総額14億ユーロ超の2026年ワークプログラムを改定した。Pathfinder、Transition、Accelerator、STEP Scale Upなどで研究から事業拡大までを支援し、防衛・デュアルユース技術も対象に加えた。</t>
+          <t>UKの次のAIスーパーコンピュータのホストサイト選定に関する表明が行われた。</t>
         </is>
       </c>
       <c r="K120" s="60" t="inlineStr">
         <is>
-          <t>https://eic.ec.europa.eu/eic-funding-opportunities/eic-2026-work-programme_en</t>
+          <t>https://www.gov.uk/government/publications/expression-of-interest-airr-heterogeneous-supercomputer-host-site-selection</t>
         </is>
       </c>
       <c r="L120" s="60" t="inlineStr">
         <is>
-          <t>d4c7b12d61b3d909256f0d10</t>
+          <t>27d607577c2759c8d53f9ddf</t>
         </is>
       </c>
       <c r="M120" s="106" t="inlineStr">
         <is>
-          <t>2026-06-17T09:00:00+09:00</t>
+          <t>2026-07-17T21:00:04+09:00</t>
         </is>
       </c>
       <c r="N120" s="60" t="inlineStr">
@@ -10067,7 +10095,7 @@
       </c>
       <c r="O120" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: R&amp;D Funding &amp; Tax Incentives | National Programs &amp; Strategy | Public Procurement &amp; Industrial Policy / 学術区分: News &amp; Official Release / 焦点: EUの研究・ディープテック事業化・スケールアップ支援 / Pinned official policy benchmark.</t>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: AIスーパーコンピュータのホストサイト選定</t>
         </is>
       </c>
     </row>
@@ -10079,26 +10107,22 @@
       </c>
       <c r="B121" s="106" t="inlineStr">
         <is>
-          <t>2026-06-15T15:23:31Z</t>
+          <t>2026-07-17T07:59:22Z</t>
         </is>
       </c>
       <c r="C121" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>EU &amp; Europe</t>
         </is>
       </c>
       <c r="D121" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E121" s="60" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="E121" s="60" t="inlineStr"/>
       <c r="F121" s="107" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G121" s="60" t="inlineStr">
         <is>
@@ -10107,32 +10131,32 @@
       </c>
       <c r="H121" s="60" t="inlineStr">
         <is>
-          <t>NIH News Releases</t>
+          <t>UK DSIT</t>
         </is>
       </c>
       <c r="I121" s="60" t="inlineStr">
         <is>
-          <t>研究影響を高めるための再現性向上イニシアティブ</t>
+          <t>子供のオンライン保護に関する新ルール</t>
         </is>
       </c>
       <c r="J121" s="60" t="inlineStr">
         <is>
-          <t>新しい生物医学研究が人間の健康に関する理解を深め、病気治療の新たな方法を提供することを目指す。独立した再現は、研究者に追加データを提供し、将来の研究プロジェクトの基盤を強化する。</t>
+          <t>UK政府が16歳未満の子供に対するソーシャルメディア禁止を発表した。</t>
         </is>
       </c>
       <c r="K121" s="60" t="inlineStr">
         <is>
-          <t>https://nih.gov/common-fund/common-fund-programs/replication-enhance-research-impact-initiative</t>
+          <t>https://www.gov.uk/government/publications/fact-sheet-new-rules-to-protect-children-online</t>
         </is>
       </c>
       <c r="L121" s="60" t="inlineStr">
         <is>
-          <t>1b5e51bc8d4c51589eee5027</t>
+          <t>371ff53aa8f9007fcb1ddddf</t>
         </is>
       </c>
       <c r="M121" s="106" t="inlineStr">
         <is>
-          <t>2026-06-16T00:23:31+09:00</t>
+          <t>2026-07-17T16:59:22+09:00</t>
         </is>
       </c>
       <c r="N121" s="60" t="inlineStr">
@@ -10142,7 +10166,7 @@
       </c>
       <c r="O121" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 政策分野: Patents &amp; Intellectual Property / 学術区分: News &amp; Official Release / 焦点: 生物医学研究の再現性 / Historical backfill from an allowlisted source.</t>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: 子供のオンライン保護に関する新ルール</t>
         </is>
       </c>
     </row>
@@ -10154,60 +10178,60 @@
       </c>
       <c r="B122" s="106" t="inlineStr">
         <is>
-          <t>2026-06-15T00:00:00Z</t>
+          <t>2026-07-16T13:35:15Z</t>
         </is>
       </c>
       <c r="C122" s="60" t="inlineStr">
         <is>
-          <t>EU &amp; Europe</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D122" s="60" t="inlineStr">
         <is>
-          <t>International / France</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E122" s="60" t="inlineStr">
         <is>
-          <t>Fusion Energy</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="F122" s="107" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G122" s="60" t="inlineStr">
         <is>
-          <t>Intergovernmental</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H122" s="60" t="inlineStr">
         <is>
-          <t>ITER News</t>
+          <t>DOE Office of Science News</t>
         </is>
       </c>
       <c r="I122" s="60" t="inlineStr">
         <is>
-          <t>世界中から一つのアセンブリラインへ</t>
+          <t>ノイズを消す：DOEが次世代量子情報科学を支える国内シリコンとゲルマニウムイソトープ供給のブレークスルーを発表</t>
         </is>
       </c>
       <c r="J122" s="60" t="inlineStr">
         <is>
-          <t>ITERダイバータが新たな統合段階に入り、設計・製造の数十年を経て新しいフェーズに突入した。</t>
+          <t>DOEが、次世代量子情報科学を加速するために、商業ソースよりも100倍以上の純度を持つイソトープを生産する成果を発表した。</t>
         </is>
       </c>
       <c r="K122" s="60" t="inlineStr">
         <is>
-          <t>https://www.iter.org/node/20687/around-world-one-assembly-line</t>
+          <t>https://www.energy.gov/science/articles/silencing-noise-doe-unveils-breakthrough-domestic-silicon-and-germanium-isotope</t>
         </is>
       </c>
       <c r="L122" s="60" t="inlineStr">
         <is>
-          <t>ac71361e131ee1a80ac51837</t>
+          <t>17ffa424cf814d722a951c64</t>
         </is>
       </c>
       <c r="M122" s="106" t="inlineStr">
         <is>
-          <t>2026-06-15T09:00:00+09:00</t>
+          <t>2026-07-16T22:35:15+09:00</t>
         </is>
       </c>
       <c r="N122" s="60" t="inlineStr">
@@ -10217,7 +10241,7 @@
       </c>
       <c r="O122" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: ITERダイバータの統合</t>
+          <t>枠: Technology Innovation | Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: 量子情報科学におけるイソトープ供給</t>
         </is>
       </c>
     </row>
@@ -10229,60 +10253,60 @@
       </c>
       <c r="B123" s="106" t="inlineStr">
         <is>
-          <t>2026-06-15T00:00:00Z</t>
+          <t>2026-07-15T23:00:54Z</t>
         </is>
       </c>
       <c r="C123" s="60" t="inlineStr">
         <is>
-          <t>EU &amp; Europe</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D123" s="60" t="inlineStr">
         <is>
-          <t>International / France</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E123" s="60" t="inlineStr">
         <is>
-          <t>Fusion Energy</t>
+          <t>Artificial Intelligence | Robotics</t>
         </is>
       </c>
       <c r="F123" s="107" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G123" s="60" t="inlineStr">
         <is>
-          <t>Intergovernmental</t>
+          <t>Official Company</t>
         </is>
       </c>
       <c r="H123" s="60" t="inlineStr">
         <is>
-          <t>ITER News</t>
+          <t>NVIDIA Blog</t>
         </is>
       </c>
       <c r="I123" s="60" t="inlineStr">
         <is>
-          <t>馬の年に先を行く</t>
+          <t>NVIDIAがロボティクスとエッジAIを進展させる新しいJetson Thorコンピュータを発表</t>
         </is>
       </c>
       <c r="J123" s="60" t="inlineStr">
         <is>
-          <t>ITERでの真空容器の組立が予定よりも早く進行中で、経験と調整の利点が示されている。</t>
+          <t>NVIDIAが新しいJetson Thorコンピュータを発表し、一般向けロボットとエッジAIの需要に応える。</t>
         </is>
       </c>
       <c r="K123" s="60" t="inlineStr">
         <is>
-          <t>https://www.iter.org/node/20687/galloping-ahead-year-horse</t>
+          <t>https://blogs.nvidia.com/blog/jetson-thor-robotics-edge-ai-agent/</t>
         </is>
       </c>
       <c r="L123" s="60" t="inlineStr">
         <is>
-          <t>47f993ca6a92c4175db656f6</t>
+          <t>85f482f3f904d00f68946a80</t>
         </is>
       </c>
       <c r="M123" s="106" t="inlineStr">
         <is>
-          <t>2026-06-15T09:00:00+09:00</t>
+          <t>2026-07-16T08:00:54+09:00</t>
         </is>
       </c>
       <c r="N123" s="60" t="inlineStr">
@@ -10292,7 +10316,7 @@
       </c>
       <c r="O123" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: 真空容器の組立</t>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: AIスーパコンピュータモジュール</t>
         </is>
       </c>
     </row>
@@ -10304,60 +10328,60 @@
       </c>
       <c r="B124" s="106" t="inlineStr">
         <is>
-          <t>2026-06-15T00:00:00Z</t>
+          <t>2026-07-15T21:00:00Z</t>
         </is>
       </c>
       <c r="C124" s="60" t="inlineStr">
         <is>
-          <t>EU &amp; Europe</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D124" s="60" t="inlineStr">
         <is>
-          <t>International / France</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E124" s="60" t="inlineStr">
         <is>
-          <t>Fusion Energy</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="F124" s="107" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G124" s="60" t="inlineStr">
         <is>
-          <t>Intergovernmental</t>
+          <t>Policy Institute</t>
         </is>
       </c>
       <c r="H124" s="60" t="inlineStr">
         <is>
-          <t>ITER News</t>
+          <t>CSET</t>
         </is>
       </c>
       <c r="I124" s="60" t="inlineStr">
         <is>
-          <t>ロシアのクルチャトフ研究所との協定を締結</t>
+          <t>GPT-Red: OpenAIが構築したモデルの安全性向上のためのAI</t>
         </is>
       </c>
       <c r="J124" s="60" t="inlineStr">
         <is>
-          <t>ITERがロシアのクルチャトフ研究所との間で科学的交流や共同研究プログラムの実施に関する協定を締結した。</t>
+          <t>OpenAIが開発したGPT-Redは、大規模言語モデルの脆弱性を自動的に特定し、サイバー攻撃に対する防御を強化するためのAIです。</t>
         </is>
       </c>
       <c r="K124" s="60" t="inlineStr">
         <is>
-          <t>https://www.iter.org/node/20687/iter-signs-agreement-russias-kurchatov-institute</t>
+          <t>https://cset.georgetown.edu/article/meet-gpt-red-an-llm-super-hacker-openai-built-to-make-its-models-safer/</t>
         </is>
       </c>
       <c r="L124" s="60" t="inlineStr">
         <is>
-          <t>bef2ae98b3b6e9a710e28c9f</t>
+          <t>f64391d3daf689e78e7ac442</t>
         </is>
       </c>
       <c r="M124" s="106" t="inlineStr">
         <is>
-          <t>2026-06-15T09:00:00+09:00</t>
+          <t>2026-07-16T06:00:00+09:00</t>
         </is>
       </c>
       <c r="N124" s="60" t="inlineStr">
@@ -10367,7 +10391,7 @@
       </c>
       <c r="O124" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: ロシアのクルチャトフ研究所との協定</t>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: AIの脆弱性を特定する技術</t>
         </is>
       </c>
     </row>
@@ -10379,7 +10403,7 @@
       </c>
       <c r="B125" s="106" t="inlineStr">
         <is>
-          <t>2026-06-09T19:00:00Z</t>
+          <t>2026-07-14T16:00:08Z</t>
         </is>
       </c>
       <c r="C125" s="60" t="inlineStr">
@@ -10392,13 +10416,9 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="E125" s="60" t="inlineStr">
-        <is>
-          <t>Fusion Energy</t>
-        </is>
-      </c>
+      <c r="E125" s="60" t="inlineStr"/>
       <c r="F125" s="107" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G125" s="60" t="inlineStr">
         <is>
@@ -10407,32 +10427,32 @@
       </c>
       <c r="H125" s="60" t="inlineStr">
         <is>
-          <t>DOE Office of Science News</t>
+          <t>National Science Foundation News</t>
         </is>
       </c>
       <c r="I125" s="60" t="inlineStr">
         <is>
-          <t>エネルギー省が核融合科学と技術のロードマップを発表</t>
+          <t>NSFが全国の研究、雇用、経済成長を促進するために12の新しい地域イノベーションエンジンを授与</t>
         </is>
       </c>
       <c r="J125" s="60" t="inlineStr">
         <is>
-          <t>米国エネルギー省は、核融合エネルギーの開発と商業化を加速するための戦略を発表しました。</t>
+          <t>米国科学財団は、全国の20州にわたる12のチームに新しいNSF地域イノベーションエンジンの助成を発表した。これにより、イノベーションクラスターの構築とスケールアップを目指す。</t>
         </is>
       </c>
       <c r="K125" s="60" t="inlineStr">
         <is>
-          <t>https://www.energy.gov/articles/energy-department-releases-finalized-fusion-science-and-technology-roadmap-accelerate</t>
+          <t>https://www.nsf.gov/news/nsf-awards-12-new-regional-innovation-engines-fuel-research</t>
         </is>
       </c>
       <c r="L125" s="60" t="inlineStr">
         <is>
-          <t>bf24d6f8eb27dabbbe4e196e</t>
+          <t>de4a8c6972dcbf82c2e445b3</t>
         </is>
       </c>
       <c r="M125" s="106" t="inlineStr">
         <is>
-          <t>2026-06-10T04:00:00+09:00</t>
+          <t>2026-07-15T01:00:08+09:00</t>
         </is>
       </c>
       <c r="N125" s="60" t="inlineStr">
@@ -10442,7 +10462,7 @@
       </c>
       <c r="O125" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy | Patents &amp; Intellectual Property / 学術区分: News &amp; Official Release / 焦点: 核融合エネルギーの商業化に向けた戦略</t>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: 地域イノベーションエンジン</t>
         </is>
       </c>
     </row>
@@ -10454,60 +10474,60 @@
       </c>
       <c r="B126" s="106" t="inlineStr">
         <is>
-          <t>2026-06-09T12:00:00Z</t>
+          <t>2026-07-10T00:00:00Z</t>
         </is>
       </c>
       <c r="C126" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D126" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="E126" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Fusion Energy</t>
         </is>
       </c>
       <c r="F126" s="107" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G126" s="60" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Journal Article</t>
         </is>
       </c>
       <c r="H126" s="60" t="inlineStr">
         <is>
-          <t>NIST News</t>
+          <t>Nuclear Fusion</t>
         </is>
       </c>
       <c r="I126" s="60" t="inlineStr">
         <is>
-          <t>NISTの数学的証明がAIシステムのセキュリティモデルへの移行を支持</t>
+          <t>ST-E1核融合発電プラントの統合物理と磁石設計</t>
         </is>
       </c>
       <c r="J126" s="60" t="inlineStr">
         <is>
-          <t>NISTは、AIシステムのための継続的な監視と更新のセキュリティモデルへの移行を支持する数学的証明を発表しました。</t>
+          <t>ST-E1は、トカマクエナジーの商業競争力のある核融合発電プラント設計であり、ハイテクスーパコンダクターマグネットケージを特徴としています。</t>
         </is>
       </c>
       <c r="K126" s="60" t="inlineStr">
         <is>
-          <t>https://www.nist.gov/news-events/news/2026/06/nist-mathematical-proof-supports-transition-continuous-monitor-and-update</t>
+          <t>https://doi.org/10.1088/1741-4326/ae773b</t>
         </is>
       </c>
       <c r="L126" s="60" t="inlineStr">
         <is>
-          <t>edf1c2446b6ba41114d4bc6b</t>
+          <t>a0ed06f7d374240814073762</t>
         </is>
       </c>
       <c r="M126" s="106" t="inlineStr">
         <is>
-          <t>2026-06-09T21:00:00+09:00</t>
+          <t>2026-07-10T09:00:00+09:00</t>
         </is>
       </c>
       <c r="N126" s="60" t="inlineStr">
@@ -10517,7 +10537,7 @@
       </c>
       <c r="O126" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: Public Procurement &amp; Industrial Policy / 学術区分: News &amp; Official Release / 焦点: AIシステムのセキュリティモデル</t>
+          <t>枠: Technology Innovation / 学術区分: Journal Article / 査読表示: Journal record — confirm peer review on publisher page / 掲載誌・学会: Nuclear Fusion / 焦点: 核融合技術 / OpenAlex record; work type=article; citations=9</t>
         </is>
       </c>
     </row>
@@ -10529,56 +10549,60 @@
       </c>
       <c r="B127" s="106" t="inlineStr">
         <is>
-          <t>2026-06-05T12:28:26Z</t>
+          <t>2026-07-08T08:00:00Z</t>
         </is>
       </c>
       <c r="C127" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="D127" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="E127" s="60" t="inlineStr"/>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="E127" s="60" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence</t>
+        </is>
+      </c>
       <c r="F127" s="107" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G127" s="60" t="inlineStr">
         <is>
-          <t>Intergovernmental</t>
+          <t>Official Company</t>
         </is>
       </c>
       <c r="H127" s="60" t="inlineStr">
         <is>
-          <t>WHO News</t>
+          <t>Samsung Global Newsroom</t>
         </is>
       </c>
       <c r="I127" s="60" t="inlineStr">
         <is>
-          <t>アフリカCDCとWHOが共同でエボラ対応計画を発表</t>
+          <t>サムスン、次世代AIインフラ向けに最適化されたPM1763 SSDの量産を開始</t>
         </is>
       </c>
       <c r="J127" s="60" t="inlineStr">
         <is>
-          <t>アフリカCDCとWHOがエボラウイルスの対応計画を発表し、5億1800万ドルの資金を目指す。</t>
+          <t>サムスン電子は、次世代AIおよびHPCサーバー環境向けに最適化されたPCIe® 6.0ベースの企業向けSSD、PM1763の量産を開始した。</t>
         </is>
       </c>
       <c r="K127" s="60" t="inlineStr">
         <is>
-          <t>https://www.who.int/news/item/05-06-2026-africa-cdc-and-who-launch-joint-continental-ebola-response-plan</t>
+          <t>https://news.samsung.com/global/samsung-begins-mass-production-of-pm1763-ssd-optimized-for-next-generation-ai-infrastructure</t>
         </is>
       </c>
       <c r="L127" s="60" t="inlineStr">
         <is>
-          <t>41c465a6eca3591002d781ba</t>
+          <t>ffa2f59ee7918b4bbfdce082</t>
         </is>
       </c>
       <c r="M127" s="106" t="inlineStr">
         <is>
-          <t>2026-06-05T21:28:26+09:00</t>
+          <t>2026-07-08T17:00:00+09:00</t>
         </is>
       </c>
       <c r="N127" s="60" t="inlineStr">
@@ -10588,7 +10612,7 @@
       </c>
       <c r="O127" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: Public Procurement &amp; Industrial Policy / 学術区分: News &amp; Official Release / 焦点: エボラウイルスに対する対応計画</t>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: PM1763 SSD</t>
         </is>
       </c>
     </row>
@@ -10600,7 +10624,7 @@
       </c>
       <c r="B128" s="106" t="inlineStr">
         <is>
-          <t>2026-06-04T12:00:00Z</t>
+          <t>2026-07-07T18:00:07Z</t>
         </is>
       </c>
       <c r="C128" s="60" t="inlineStr">
@@ -10615,11 +10639,11 @@
       </c>
       <c r="E128" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="F128" s="107" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G128" s="60" t="inlineStr">
         <is>
@@ -10628,32 +10652,32 @@
       </c>
       <c r="H128" s="60" t="inlineStr">
         <is>
-          <t>NIST News</t>
+          <t>National Science Foundation News</t>
         </is>
       </c>
       <c r="I128" s="60" t="inlineStr">
         <is>
-          <t>新しいAIモデルが火災時の避難経路を特定</t>
+          <t>NSF、実用的な量子技術を進展させるProject Triadを開始</t>
         </is>
       </c>
       <c r="J128" s="60" t="inlineStr">
         <is>
-          <t>NISTが火災時に安全な避難経路を特定する新しいAIモデルを作成した。</t>
+          <t>米国国立科学財団が量子技術を統合する新たなイニシアティブ、Project Triadを発表した。</t>
         </is>
       </c>
       <c r="K128" s="60" t="inlineStr">
         <is>
-          <t>https://www.nist.gov/news-events/news/2026/06/new-ai-model-shows-how-evacuate-fires-one-safe-step-time</t>
+          <t>https://www.nsf.gov/news/nsf-launches-project-triad-advance-quantum-technology-real</t>
         </is>
       </c>
       <c r="L128" s="60" t="inlineStr">
         <is>
-          <t>434bb62e0a1e48aca17e1405</t>
+          <t>2d4a226d3ce7cc9e366e902d</t>
         </is>
       </c>
       <c r="M128" s="106" t="inlineStr">
         <is>
-          <t>2026-06-04T21:00:00+09:00</t>
+          <t>2026-07-08T03:00:07+09:00</t>
         </is>
       </c>
       <c r="N128" s="60" t="inlineStr">
@@ -10663,7 +10687,7 @@
       </c>
       <c r="O128" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: Public Procurement &amp; Industrial Policy / 学術区分: News &amp; Official Release / 焦点: 火災時の避難経路を特定するAIモデル</t>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: Project Triad</t>
         </is>
       </c>
     </row>
@@ -10675,56 +10699,60 @@
       </c>
       <c r="B129" s="106" t="inlineStr">
         <is>
-          <t>2026-06-04T12:00:00Z</t>
+          <t>2026-06-29T21:14:22Z</t>
         </is>
       </c>
       <c r="C129" s="60" t="inlineStr">
         <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="D129" s="60" t="inlineStr">
+        <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="D129" s="60" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E129" s="60" t="inlineStr"/>
+      <c r="E129" s="60" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence</t>
+        </is>
+      </c>
       <c r="F129" s="107" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G129" s="60" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Official Company</t>
         </is>
       </c>
       <c r="H129" s="60" t="inlineStr">
         <is>
-          <t>NIST News</t>
+          <t>Microsoft Research</t>
         </is>
       </c>
       <c r="I129" s="60" t="inlineStr">
         <is>
-          <t>NISTがレーザーを用いた合金の結合方法を発見</t>
+          <t>Memora: 抽象と特異性のバランスを取る調和的メモリ表現</t>
         </is>
       </c>
       <c r="J129" s="60" t="inlineStr">
         <is>
-          <t>NISTが3Dプリンティング中の金属の原子構造をリアルタイムで研究する方法を改善した。</t>
+          <t>AIエージェントが過去の会話を記憶できない問題を解決するために、Memoraがスケーラブルなメモリシステムを提案した。</t>
         </is>
       </c>
       <c r="K129" s="60" t="inlineStr">
         <is>
-          <t>https://www.nist.gov/news-events/news/2026/06/nist-researchers-discover-new-way-whisk-alloys-together-lasers</t>
+          <t>https://www.microsoft.com/en-us/research/blog/memora-a-harmonic-memory-representation-balancing-abstraction-and-specificity/</t>
         </is>
       </c>
       <c r="L129" s="60" t="inlineStr">
         <is>
-          <t>a03605c38ac072e4b77247db</t>
+          <t>6c035ef4d4202a4874e60b97</t>
         </is>
       </c>
       <c r="M129" s="106" t="inlineStr">
         <is>
-          <t>2026-06-04T21:00:00+09:00</t>
+          <t>2026-06-30T06:14:22+09:00</t>
         </is>
       </c>
       <c r="N129" s="60" t="inlineStr">
@@ -10734,7 +10762,7 @@
       </c>
       <c r="O129" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: Public Procurement &amp; Industrial Policy / 学術区分: News &amp; Official Release / 焦点: レーザーを用いた合金の結合方法</t>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: AIメモリシステム</t>
         </is>
       </c>
     </row>
@@ -10746,12 +10774,12 @@
       </c>
       <c r="B130" s="106" t="inlineStr">
         <is>
-          <t>2026-06-03T03:00:33Z</t>
+          <t>2026-06-29T12:00:00Z</t>
         </is>
       </c>
       <c r="C130" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D130" s="60" t="inlineStr">
@@ -10761,45 +10789,45 @@
       </c>
       <c r="E130" s="60" t="inlineStr">
         <is>
-          <t>Semiconductors &amp; Telecom</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="F130" s="107" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G130" s="60" t="inlineStr">
         <is>
-          <t>Official Company</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H130" s="60" t="inlineStr">
         <is>
-          <t>Intel Newsroom</t>
+          <t>NIST News</t>
         </is>
       </c>
       <c r="I130" s="60" t="inlineStr">
         <is>
-          <t>インテル、企業向けEthernet E835ネットワーク制御装置を発表</t>
+          <t>NIST、量子技術の製造を推進するセンターを設立</t>
         </is>
       </c>
       <c r="J130" s="60" t="inlineStr">
         <is>
-          <t>インテルは、データセンターや企業、AI、テレコムモバイルコアアプリケーション向けに高密度環境の帯域幅とスケーラビリティの要求に応えるEthernet E835ネットワーク制御装置とアダプタを発表した。</t>
+          <t>NISTは、量子製造工学センター（QMEC）を設立するためにSRIインターナショナルとの合意を発表した。</t>
         </is>
       </c>
       <c r="K130" s="60" t="inlineStr">
         <is>
-          <t>https://newsroom.intel.com/pt/data-cente/intel-apresenta-controladores-e-adaptadores-de-rede-ethernet-e835-para-infraestruturas-corporativas-de-borda-e-telecomunicacoes</t>
+          <t>https://www.nist.gov/news-events/news/2026/06/nist-launches-center-drive-manufacture-quantum-technologies</t>
         </is>
       </c>
       <c r="L130" s="60" t="inlineStr">
         <is>
-          <t>c78a2a348fa6a57f7ff2f7c3</t>
+          <t>2d90197d96166b4d1d7f7c11</t>
         </is>
       </c>
       <c r="M130" s="106" t="inlineStr">
         <is>
-          <t>2026-06-03T12:00:33+09:00</t>
+          <t>2026-06-29T21:00:00+09:00</t>
         </is>
       </c>
       <c r="N130" s="60" t="inlineStr">
@@ -10809,7 +10837,7 @@
       </c>
       <c r="O130" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: Ethernetネットワーク用の制御装置とアダプタ / Historical backfill from an allowlisted source.</t>
+          <t>枠: Innovation Policy / 政策分野: Public Procurement &amp; Industrial Policy / 学術区分: News &amp; Official Release / 焦点: 量子製造工学センターの設立</t>
         </is>
       </c>
     </row>
@@ -10821,60 +10849,56 @@
       </c>
       <c r="B131" s="106" t="inlineStr">
         <is>
-          <t>2026-05-19T00:00:00Z</t>
+          <t>2026-06-26T04:47:39Z</t>
         </is>
       </c>
       <c r="C131" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D131" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="E131" s="60" t="inlineStr">
-        <is>
-          <t>Artificial Intelligence | Healthcare | Biotechnology</t>
-        </is>
-      </c>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="E131" s="60" t="inlineStr"/>
       <c r="F131" s="107" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G131" s="60" t="inlineStr">
         <is>
-          <t>Journal Article</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H131" s="60" t="inlineStr">
         <is>
-          <t>Nature</t>
+          <t>NISTEP Updates</t>
         </is>
       </c>
       <c r="I131" s="60" t="inlineStr">
         <is>
-          <t>Co-Scientistによる科学的発見の加速</t>
+          <t>研究文化をめぐる対話と展開に関する資料公開</t>
         </is>
       </c>
       <c r="J131" s="60" t="inlineStr">
         <is>
-          <t>Co-Scientistは、科学者の研究目的に基づいて新しい研究仮説を生成するAIシステムで、特にバイオメディカル分野での応用が示されています。</t>
+          <t>文部科学省が研究者対象のウェルビーイングと研究文化に関する全国調査の準備を進めています。</t>
         </is>
       </c>
       <c r="K131" s="60" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1038/s41586-026-10644-y</t>
+          <t>https://www.nistep.go.jp/archives/63398/</t>
         </is>
       </c>
       <c r="L131" s="60" t="inlineStr">
         <is>
-          <t>21dce88bdeef80bd3133e790</t>
+          <t>ff67a3172cc526b012791921</t>
         </is>
       </c>
       <c r="M131" s="106" t="inlineStr">
         <is>
-          <t>2026-05-19T09:00:00+09:00</t>
+          <t>2026-06-26T13:47:39+09:00</t>
         </is>
       </c>
       <c r="N131" s="60" t="inlineStr">
@@ -10884,7 +10908,7 @@
       </c>
       <c r="O131" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: Journal Article / 査読表示: Journal record — confirm peer review on publisher page / 掲載誌・学会: Nature / 焦点: AIによる科学的発見の加速 / OpenAlex record; work type=article; citations=56</t>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: 研究者のウェルビーイングと研究文化</t>
         </is>
       </c>
     </row>
@@ -10896,26 +10920,22 @@
       </c>
       <c r="B132" s="106" t="inlineStr">
         <is>
-          <t>2026-05-18T12:00:00Z</t>
+          <t>2026-06-26T01:30:26Z</t>
         </is>
       </c>
       <c r="C132" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="D132" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E132" s="60" t="inlineStr">
-        <is>
-          <t>Space</t>
-        </is>
-      </c>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="E132" s="60" t="inlineStr"/>
       <c r="F132" s="107" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G132" s="60" t="inlineStr">
         <is>
@@ -10924,32 +10944,32 @@
       </c>
       <c r="H132" s="60" t="inlineStr">
         <is>
-          <t>NIST News</t>
+          <t>NISTEP Updates</t>
         </is>
       </c>
       <c r="I132" s="60" t="inlineStr">
         <is>
-          <t>月面探査に向けた超安定レーザー技術の可能性</t>
+          <t>親子企業間の資源再配分と特許活動の特性</t>
         </is>
       </c>
       <c r="J132" s="60" t="inlineStr">
         <is>
-          <t>月面の永久影にあるクレーターは、これまでにないほど安定した光学レーザーを構築する理想的な場所となる可能性がある。</t>
+          <t>親子企業間での研究開発資源の移動に関する特許活動の特性についての実証分析が行われました。</t>
         </is>
       </c>
       <c r="K132" s="60" t="inlineStr">
         <is>
-          <t>https://www.nist.gov/news-events/news/2026/05/shooting-moon-ultrastable-lasers-dark-craters-could-enable-lunar-navigation</t>
+          <t>https://www.nistep.go.jp/archives/63333/</t>
         </is>
       </c>
       <c r="L132" s="60" t="inlineStr">
         <is>
-          <t>99f664278415a42538163a5c</t>
+          <t>25352f245236dac75576baa7</t>
         </is>
       </c>
       <c r="M132" s="106" t="inlineStr">
         <is>
-          <t>2026-05-18T21:00:00+09:00</t>
+          <t>2026-06-26T10:30:26+09:00</t>
         </is>
       </c>
       <c r="N132" s="60" t="inlineStr">
@@ -10959,19 +10979,19 @@
       </c>
       <c r="O132" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: 超安定レーザー技術</t>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy | Patents &amp; Intellectual Property / 学術区分: News &amp; Official Release / 焦点: 親子企業間の資源再配分と特許活動</t>
         </is>
       </c>
     </row>
     <row r="133" ht="42" customHeight="1">
       <c r="A133" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T22:54:37+09:00</t>
+          <t>2026-07-26T21:02:36+09:00</t>
         </is>
       </c>
       <c r="B133" s="106" t="inlineStr">
         <is>
-          <t>2026-05-14T00:00:00Z</t>
+          <t>2026-06-25T05:26:14Z</t>
         </is>
       </c>
       <c r="C133" s="60" t="inlineStr">
@@ -10986,7 +11006,7 @@
       </c>
       <c r="E133" s="60" t="inlineStr"/>
       <c r="F133" s="107" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G133" s="60" t="inlineStr">
         <is>
@@ -10995,32 +11015,32 @@
       </c>
       <c r="H133" s="60" t="inlineStr">
         <is>
-          <t>NSF Policy Benchmarks</t>
+          <t>DOE Office of Science News</t>
         </is>
       </c>
       <c r="I133" s="60" t="inlineStr">
         <is>
-          <t>NSF、15億ドルのX-Labs構想を発表</t>
+          <t>米国エネルギー省が国内供給網を強化</t>
         </is>
       </c>
       <c r="J133" s="60" t="inlineStr">
         <is>
-          <t>米国NSFは15億ドル規模の「NSF X-Labs」を発表した。従来型機関の外で独立研究組織を立ち上げ・拡大し、世代を画する科学的ブレークスルーを長期・大規模に追求する。</t>
+          <t>米国エネルギー省がイリジウム-192の国内生産能力を確立しました。</t>
         </is>
       </c>
       <c r="K133" s="60" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/news/nsf-announces-15b-nsf-x-labs-initiative-pursue-generational</t>
+          <t>https://www.energy.gov/science/articles/doe-strengthens-domestic-supply-chain-american-energy-and-manufacturing</t>
         </is>
       </c>
       <c r="L133" s="60" t="inlineStr">
         <is>
-          <t>770e8a385a4790aa084a1d15</t>
+          <t>62854e5795f9fac8f0427e2f</t>
         </is>
       </c>
       <c r="M133" s="106" t="inlineStr">
         <is>
-          <t>2026-05-14T09:00:00+09:00</t>
+          <t>2026-06-25T14:26:14+09:00</t>
         </is>
       </c>
       <c r="N133" s="60" t="inlineStr">
@@ -11030,7 +11050,7 @@
       </c>
       <c r="O133" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: R&amp;D Funding &amp; Tax Incentives | National Programs &amp; Strategy | Research System &amp; Talent / 学術区分: News &amp; Official Release / 焦点: 独立研究組織を通じた大型・長期の基礎研究支援 / Pinned official policy benchmark.</t>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: イリジウム-192の国内生産能力</t>
         </is>
       </c>
     </row>
@@ -11042,7 +11062,7 @@
       </c>
       <c r="B134" s="106" t="inlineStr">
         <is>
-          <t>2026-04-15T12:00:00Z</t>
+          <t>2026-06-25T04:00:24Z</t>
         </is>
       </c>
       <c r="C134" s="60" t="inlineStr">
@@ -11052,16 +11072,12 @@
       </c>
       <c r="D134" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E134" s="60" t="inlineStr">
-        <is>
-          <t>Semiconductors &amp; Telecom</t>
-        </is>
-      </c>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="E134" s="60" t="inlineStr"/>
       <c r="F134" s="107" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G134" s="60" t="inlineStr">
         <is>
@@ -11070,32 +11086,32 @@
       </c>
       <c r="H134" s="60" t="inlineStr">
         <is>
-          <t>NIST News</t>
+          <t>NISTEP Updates</t>
         </is>
       </c>
       <c r="I134" s="60" t="inlineStr">
         <is>
-          <t>好きな色を選べる：NIST科学者が小型回路で「任意の波長」レーザーを作成</t>
+          <t>STI Horizon誌2026夏号の公表</t>
         </is>
       </c>
       <c r="J134" s="60" t="inlineStr">
         <is>
-          <t>NISTの科学者たちが、シリコンウェハ上に特殊材料の複雑なパターンを堆積することで、光のための集積回路を作成する方法を開発した。</t>
+          <t>NISTEPが科学技術・イノベーション政策に関する情報を幅広く掲載したSTI Horizon 2026夏号を公表しました。</t>
         </is>
       </c>
       <c r="K134" s="60" t="inlineStr">
         <is>
-          <t>https://www.nist.gov/news-events/news/2026/04/any-color-you-nist-scientists-create-any-wavelength-lasers-tiny-circuits</t>
+          <t>https://www.nistep.go.jp/archives/63155/</t>
         </is>
       </c>
       <c r="L134" s="60" t="inlineStr">
         <is>
-          <t>4fba34d8f0d0bf2d1a725c46</t>
+          <t>79d88af79ddda07d59b28e08</t>
         </is>
       </c>
       <c r="M134" s="106" t="inlineStr">
         <is>
-          <t>2026-04-15T21:00:00+09:00</t>
+          <t>2026-06-25T13:00:24+09:00</t>
         </is>
       </c>
       <c r="N134" s="60" t="inlineStr">
@@ -11105,34 +11121,38 @@
       </c>
       <c r="O134" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: 集積回路の光学技術</t>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: 科学技術・イノベーション政策</t>
         </is>
       </c>
     </row>
     <row r="135" ht="42" customHeight="1">
       <c r="A135" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T22:54:37+09:00</t>
+          <t>2026-07-26T21:02:36+09:00</t>
         </is>
       </c>
       <c r="B135" s="106" t="inlineStr">
         <is>
-          <t>2026-03-24T00:00:00Z</t>
+          <t>2026-06-23T14:26:00Z</t>
         </is>
       </c>
       <c r="C135" s="60" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>EU &amp; Europe</t>
         </is>
       </c>
       <c r="D135" s="60" t="inlineStr">
         <is>
-          <t>China</t>
-        </is>
-      </c>
-      <c r="E135" s="60" t="inlineStr"/>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="E135" s="60" t="inlineStr">
+        <is>
+          <t>Robotics</t>
+        </is>
+      </c>
       <c r="F135" s="107" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G135" s="60" t="inlineStr">
         <is>
@@ -11141,32 +11161,32 @@
       </c>
       <c r="H135" s="60" t="inlineStr">
         <is>
-          <t>China Innovation Policy Benchmarks</t>
+          <t>UK DSIT</t>
         </is>
       </c>
       <c r="I135" s="60" t="inlineStr">
         <is>
-          <t>中国、大学・研究機関の特許130万件を審査し事業化候補68万件を企業へ接続</t>
+          <t>Sellafieldの清掃を助ける新しいロボット</t>
         </is>
       </c>
       <c r="J135" s="60" t="inlineStr">
         <is>
-          <t>中国は大学・研究機関が保有する130万件超の特許を全国審査し、事業化可能性の高い発明特許68万件を特定して46万社へ接続した。国務院の特許転化・活用行動計画に基づき、評価、マッチング、研究者報酬、技術移転人材を整備する。</t>
+          <t>リモート操作された機械がSellafieldの最も危険な核廃棄物保管所に初めて送られ、清掃作業を支援している。</t>
         </is>
       </c>
       <c r="K135" s="60" t="inlineStr">
         <is>
-          <t>https://english.www.gov.cn/news/202603/24/content_WS69c1edb6c6d00ca5f9a0a13c.html</t>
+          <t>https://gov.uk/government/news/the-new-robot-helping-clean-up-sellafield</t>
         </is>
       </c>
       <c r="L135" s="60" t="inlineStr">
         <is>
-          <t>56bcce956cacb3b5f73edbdd</t>
+          <t>132391c846d95677d6ca86ff</t>
         </is>
       </c>
       <c r="M135" s="106" t="inlineStr">
         <is>
-          <t>2026-03-24T09:00:00+09:00</t>
+          <t>2026-06-23T23:26:00+09:00</t>
         </is>
       </c>
       <c r="N135" s="60" t="inlineStr">
@@ -11176,7 +11196,7 @@
       </c>
       <c r="O135" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: Patents &amp; Intellectual Property | Public Procurement &amp; Industrial Policy / 学術区分: News &amp; Official Release / 焦点: 大学・研究機関の特許評価、企業マッチング、技術移転 / Pinned official policy benchmark.</t>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: Sellafieldでのロボットの使用 / Historical backfill from an allowlisted source.</t>
         </is>
       </c>
     </row>
@@ -11188,7 +11208,7 @@
       </c>
       <c r="B136" s="106" t="inlineStr">
         <is>
-          <t>2026-03-19T12:00:00Z</t>
+          <t>2026-06-23T11:43:57Z</t>
         </is>
       </c>
       <c r="C136" s="60" t="inlineStr">
@@ -11201,9 +11221,13 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="E136" s="60" t="inlineStr"/>
+      <c r="E136" s="60" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
       <c r="F136" s="107" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G136" s="60" t="inlineStr">
         <is>
@@ -11212,32 +11236,32 @@
       </c>
       <c r="H136" s="60" t="inlineStr">
         <is>
-          <t>NIST News</t>
+          <t>DOE Office of Science News</t>
         </is>
       </c>
       <c r="I136" s="60" t="inlineStr">
         <is>
-          <t>NISTが議会にFY 2025の国家建設安全チーム調査の進捗を報告</t>
+          <t>エネルギー省、科学的に関連する耐障害量子コンピュータの創出と展開に関するイニシアティブを発表</t>
         </is>
       </c>
       <c r="J136" s="60" t="inlineStr">
         <is>
-          <t>NISTは、Champlain Towers Southの調査に関する作業の概要を含む報告書を議会に提出しました。</t>
+          <t>米国エネルギー省が、科学的に関連する耐障害量子コンピュータを創出し展開するためのイニシアティブを発表した。</t>
         </is>
       </c>
       <c r="K136" s="60" t="inlineStr">
         <is>
-          <t>https://www.nist.gov/news-events/news/2026/03/nist-submits-annual-report-congress-summarizing-fy-2025-progress-national</t>
+          <t>https://www.energy.gov/science/articles/energy-department-announces-initiative-create-and-deploy-worlds-first</t>
         </is>
       </c>
       <c r="L136" s="60" t="inlineStr">
         <is>
-          <t>e322af74bfc6d82e04e94180</t>
+          <t>9e1d8ad5a7ac944965b9f2bd</t>
         </is>
       </c>
       <c r="M136" s="106" t="inlineStr">
         <is>
-          <t>2026-03-19T21:00:00+09:00</t>
+          <t>2026-06-23T20:43:57+09:00</t>
         </is>
       </c>
       <c r="N136" s="60" t="inlineStr">
@@ -11247,19 +11271,19 @@
       </c>
       <c r="O136" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: Public Procurement &amp; Industrial Policy / 学術区分: News &amp; Official Release / 焦点: 国家建設安全チームの調査進捗</t>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: 量子コンピュータの開発</t>
         </is>
       </c>
     </row>
     <row r="137" ht="42" customHeight="1">
       <c r="A137" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T21:02:36+09:00</t>
+          <t>2026-07-26T22:54:37+09:00</t>
         </is>
       </c>
       <c r="B137" s="106" t="inlineStr">
         <is>
-          <t>2026-03-04T14:57:24Z</t>
+          <t>2026-06-17T00:00:00Z</t>
         </is>
       </c>
       <c r="C137" s="60" t="inlineStr">
@@ -11269,50 +11293,46 @@
       </c>
       <c r="D137" s="60" t="inlineStr">
         <is>
-          <t>China / Germany</t>
-        </is>
-      </c>
-      <c r="E137" s="60" t="inlineStr">
-        <is>
-          <t>Biotechnology</t>
-        </is>
-      </c>
+          <t>European Union</t>
+        </is>
+      </c>
+      <c r="E137" s="60" t="inlineStr"/>
       <c r="F137" s="107" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G137" s="60" t="inlineStr">
         <is>
-          <t>Policy Institute</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H137" s="60" t="inlineStr">
         <is>
-          <t>MERICS</t>
+          <t>European Innovation Council Policy Benchmarks</t>
         </is>
       </c>
       <c r="I137" s="60" t="inlineStr">
         <is>
-          <t>アストラゼネカ、中国を製薬イノベーションのハブに</t>
+          <t>EIC、14億ユーロ超の2026年ワークプログラムを改定</t>
         </is>
       </c>
       <c r="J137" s="60" t="inlineStr">
         <is>
-          <t>アストラゼネカが2030年までに中国の研究開発に150億ドルを投資する計画を発表。</t>
+          <t>欧州イノベーション会議は、総額14億ユーロ超の2026年ワークプログラムを改定した。Pathfinder、Transition、Accelerator、STEP Scale Upなどで研究から事業拡大までを支援し、防衛・デュアルユース技術も対象に加えた。</t>
         </is>
       </c>
       <c r="K137" s="60" t="inlineStr">
         <is>
-          <t>https://merics.org/en/comment/astrazenecas-rd-bet-makes-china-pharma-innovation-hub</t>
+          <t>https://eic.ec.europa.eu/eic-funding-opportunities/eic-2026-work-programme_en</t>
         </is>
       </c>
       <c r="L137" s="60" t="inlineStr">
         <is>
-          <t>1c2d02bf178504dd287a6106</t>
+          <t>d4c7b12d61b3d909256f0d10</t>
         </is>
       </c>
       <c r="M137" s="106" t="inlineStr">
         <is>
-          <t>2026-03-04T23:57:24+09:00</t>
+          <t>2026-06-17T09:00:00+09:00</t>
         </is>
       </c>
       <c r="N137" s="60" t="inlineStr">
@@ -11322,68 +11342,72 @@
       </c>
       <c r="O137" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: Regulation &amp; Governance / 学術区分: News &amp; Official Release / 焦点: バイオテクノロジー産業の規制 / Historical backfill from an allowlisted source.</t>
+          <t>枠: Innovation Policy / 政策分野: R&amp;D Funding &amp; Tax Incentives | National Programs &amp; Strategy | Public Procurement &amp; Industrial Policy / 学術区分: News &amp; Official Release / 焦点: EUの研究・ディープテック事業化・スケールアップ支援 / Pinned official policy benchmark.</t>
         </is>
       </c>
     </row>
     <row r="138" ht="42" customHeight="1">
       <c r="A138" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T22:54:37+09:00</t>
+          <t>2026-07-26T21:02:36+09:00</t>
         </is>
       </c>
       <c r="B138" s="106" t="inlineStr">
         <is>
-          <t>2026-02-17T00:00:00Z</t>
+          <t>2026-06-15T15:23:31Z</t>
         </is>
       </c>
       <c r="C138" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D138" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="E138" s="60" t="inlineStr"/>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E138" s="60" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
       <c r="F138" s="107" t="n">
         <v>4</v>
       </c>
       <c r="G138" s="60" t="inlineStr">
         <is>
-          <t>Intergovernmental</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H138" s="60" t="inlineStr">
         <is>
-          <t>WIPO Policy Benchmarks</t>
+          <t>NIH News Releases</t>
         </is>
       </c>
       <c r="I138" s="60" t="inlineStr">
         <is>
-          <t>WIPO「世界知的財産報告書2026」、技術普及を左右する4要因を分析</t>
+          <t>研究影響を高めるための再現性向上イニシアティブ</t>
         </is>
       </c>
       <c r="J138" s="60" t="inlineStr">
         <is>
-          <t>WIPOは「世界知的財産報告書2026」で、技術の性質、情報流通、受容能力、政策・知財制度の4要因が技術普及の速度と範囲を左右すると分析した。特許と科学論文のデータから各国の普及格差を示す。</t>
+          <t>新しい生物医学研究が人間の健康に関する理解を深め、病気治療の新たな方法を提供することを目指す。独立した再現は、研究者に追加データを提供し、将来の研究プロジェクトの基盤を強化する。</t>
         </is>
       </c>
       <c r="K138" s="60" t="inlineStr">
         <is>
-          <t>https://www.wipo.int/web-publications/world-intellectual-property-report-2026/en/index.html</t>
+          <t>https://nih.gov/common-fund/common-fund-programs/replication-enhance-research-impact-initiative</t>
         </is>
       </c>
       <c r="L138" s="60" t="inlineStr">
         <is>
-          <t>424d3f7436d98c3c4ec35b6d</t>
+          <t>1b5e51bc8d4c51589eee5027</t>
         </is>
       </c>
       <c r="M138" s="106" t="inlineStr">
         <is>
-          <t>2026-02-17T09:00:00+09:00</t>
+          <t>2026-06-16T00:23:31+09:00</t>
         </is>
       </c>
       <c r="N138" s="60" t="inlineStr">
@@ -11393,68 +11417,72 @@
       </c>
       <c r="O138" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: Patents &amp; Intellectual Property | National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: 知的財産制度と技術普及の関係 / Pinned official policy benchmark.</t>
+          <t>枠: Technology Innovation / 政策分野: Patents &amp; Intellectual Property / 学術区分: News &amp; Official Release / 焦点: 生物医学研究の再現性 / Historical backfill from an allowlisted source.</t>
         </is>
       </c>
     </row>
     <row r="139" ht="42" customHeight="1">
       <c r="A139" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T22:54:37+09:00</t>
+          <t>2026-07-26T21:02:36+09:00</t>
         </is>
       </c>
       <c r="B139" s="106" t="inlineStr">
         <is>
-          <t>2026-02-12T00:00:00Z</t>
+          <t>2026-06-15T00:00:00Z</t>
         </is>
       </c>
       <c r="C139" s="60" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>EU &amp; Europe</t>
         </is>
       </c>
       <c r="D139" s="60" t="inlineStr">
         <is>
-          <t>South Korea</t>
-        </is>
-      </c>
-      <c r="E139" s="60" t="inlineStr"/>
+          <t>International / France</t>
+        </is>
+      </c>
+      <c r="E139" s="60" t="inlineStr">
+        <is>
+          <t>Fusion Energy</t>
+        </is>
+      </c>
       <c r="F139" s="107" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G139" s="60" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Intergovernmental</t>
         </is>
       </c>
       <c r="H139" s="60" t="inlineStr">
         <is>
-          <t>Korea Innovation Policy Benchmarks</t>
+          <t>ITER News</t>
         </is>
       </c>
       <c r="I139" s="60" t="inlineStr">
         <is>
-          <t>韓国、大型国家R&amp;Dの事前評価を18年ぶりに全面改革</t>
+          <t>世界中から一つのアセンブリラインへ</t>
         </is>
       </c>
       <c r="J139" s="60" t="inlineStr">
         <is>
-          <t>韓国は大型国家R&amp;Dの投資審査制度を18年ぶりに全面改革する。事前評価の対象基準を500億ウォンから1,000億ウォンへ引き上げ、研究型には計画審査、研究インフラ型には企画から完成までの全ライフサイクル審査を導入する。</t>
+          <t>ITERダイバータが新たな統合段階に入り、設計・製造の数十年を経て新しいフェーズに突入した。</t>
         </is>
       </c>
       <c r="K139" s="60" t="inlineStr">
         <is>
-          <t>https://www.msit.go.kr/eng/bbs/view.do?bbsSeqNo=42&amp;mId=4&amp;nttSeqNo=1227&amp;sCode=eng</t>
+          <t>https://www.iter.org/node/20687/around-world-one-assembly-line</t>
         </is>
       </c>
       <c r="L139" s="60" t="inlineStr">
         <is>
-          <t>d1549e57df1e4381c7594af7</t>
+          <t>ac71361e131ee1a80ac51837</t>
         </is>
       </c>
       <c r="M139" s="106" t="inlineStr">
         <is>
-          <t>2026-02-12T09:00:00+09:00</t>
+          <t>2026-06-15T09:00:00+09:00</t>
         </is>
       </c>
       <c r="N139" s="60" t="inlineStr">
@@ -11464,7 +11492,7 @@
       </c>
       <c r="O139" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: R&amp;D Funding &amp; Tax Incentives | National Programs &amp; Strategy | Regulation &amp; Governance / 学術区分: News &amp; Official Release / 焦点: 大型国家R&amp;Dプロジェクトの投資審査と全ライフサイクル管理 / Pinned official policy benchmark.</t>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: ITERダイバータの統合</t>
         </is>
       </c>
     </row>
@@ -11476,60 +11504,60 @@
       </c>
       <c r="B140" s="106" t="inlineStr">
         <is>
-          <t>2026-02-10T12:00:00Z</t>
+          <t>2026-06-15T00:00:00Z</t>
         </is>
       </c>
       <c r="C140" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>EU &amp; Europe</t>
         </is>
       </c>
       <c r="D140" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>International / France</t>
         </is>
       </c>
       <c r="E140" s="60" t="inlineStr">
         <is>
-          <t>Biotechnology | Artificial Intelligence | Semiconductors &amp; Telecom | Quantum</t>
+          <t>Fusion Energy</t>
         </is>
       </c>
       <c r="F140" s="107" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G140" s="60" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Intergovernmental</t>
         </is>
       </c>
       <c r="H140" s="60" t="inlineStr">
         <is>
-          <t>NIST News</t>
+          <t>ITER News</t>
         </is>
       </c>
       <c r="I140" s="60" t="inlineStr">
         <is>
-          <t>NISTがAI、バイオテクノロジー、半導体、量子技術を進展させる小規模企業に300万ドル以上を配分</t>
+          <t>馬の年に先を行く</t>
         </is>
       </c>
       <c r="J140" s="60" t="inlineStr">
         <is>
-          <t>NISTはSBIRプログラムの下で、7つの州にある8つの小規模企業に資金を配分することを発表した。</t>
+          <t>ITERでの真空容器の組立が予定よりも早く進行中で、経験と調整の利点が示されている。</t>
         </is>
       </c>
       <c r="K140" s="60" t="inlineStr">
         <is>
-          <t>https://www.nist.gov/news-events/news/2026/02/nist-allocates-over-3-million-small-businesses-advancing-ai-biotechnology</t>
+          <t>https://www.iter.org/node/20687/galloping-ahead-year-horse</t>
         </is>
       </c>
       <c r="L140" s="60" t="inlineStr">
         <is>
-          <t>2700025a185e7f6eb2253ff3</t>
+          <t>47f993ca6a92c4175db656f6</t>
         </is>
       </c>
       <c r="M140" s="106" t="inlineStr">
         <is>
-          <t>2026-02-10T21:00:00+09:00</t>
+          <t>2026-06-15T09:00:00+09:00</t>
         </is>
       </c>
       <c r="N140" s="60" t="inlineStr">
@@ -11539,72 +11567,72 @@
       </c>
       <c r="O140" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: Public Procurement &amp; Industrial Policy / 学術区分: News &amp; Official Release / 焦点: AI、バイオテクノロジー、半導体、量子技術に関する資金配分</t>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: 真空容器の組立</t>
         </is>
       </c>
     </row>
     <row r="141" ht="42" customHeight="1">
       <c r="A141" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T22:54:37+09:00</t>
+          <t>2026-07-26T21:02:36+09:00</t>
         </is>
       </c>
       <c r="B141" s="106" t="inlineStr">
         <is>
-          <t>2025-11-24T00:00:00Z</t>
+          <t>2026-06-15T00:00:00Z</t>
         </is>
       </c>
       <c r="C141" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>EU &amp; Europe</t>
         </is>
       </c>
       <c r="D141" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>International / France</t>
         </is>
       </c>
       <c r="E141" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Fusion Energy</t>
         </is>
       </c>
       <c r="F141" s="107" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G141" s="60" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Intergovernmental</t>
         </is>
       </c>
       <c r="H141" s="60" t="inlineStr">
         <is>
-          <t>White House Science Policy Benchmarks</t>
+          <t>ITER News</t>
         </is>
       </c>
       <c r="I141" s="60" t="inlineStr">
         <is>
-          <t>米国、AIで科学発見を加速する「Genesis Mission」を開始</t>
+          <t>ロシアのクルチャトフ研究所との協定を締結</t>
         </is>
       </c>
       <c r="J141" s="60" t="inlineStr">
         <is>
-          <t>米国は大統領令で「Genesis Mission」を開始した。連邦の科学データ、スーパーコンピューター、AI、研究施設を統合し、科学基盤モデルとAIエージェントで仮説検証や研究工程を自動化する国家計画である。</t>
+          <t>ITERがロシアのクルチャトフ研究所との間で科学的交流や共同研究プログラムの実施に関する協定を締結した。</t>
         </is>
       </c>
       <c r="K141" s="60" t="inlineStr">
         <is>
-          <t>https://www.whitehouse.gov/presidential-actions/2025/11/launching-the-genesis-mission/</t>
+          <t>https://www.iter.org/node/20687/iter-signs-agreement-russias-kurchatov-institute</t>
         </is>
       </c>
       <c r="L141" s="60" t="inlineStr">
         <is>
-          <t>f224687901952d4c32603531</t>
+          <t>bef2ae98b3b6e9a710e28c9f</t>
         </is>
       </c>
       <c r="M141" s="106" t="inlineStr">
         <is>
-          <t>2025-11-24T09:00:00+09:00</t>
+          <t>2026-06-15T09:00:00+09:00</t>
         </is>
       </c>
       <c r="N141" s="60" t="inlineStr">
@@ -11614,32 +11642,36 @@
       </c>
       <c r="O141" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy | Research System &amp; Talent / 学術区分: News &amp; Official Release / 焦点: AI、連邦科学データ、国立研究所を統合する国家研究基盤 / Pinned official policy benchmark.</t>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: ロシアのクルチャトフ研究所との協定</t>
         </is>
       </c>
     </row>
     <row r="142" ht="42" customHeight="1">
       <c r="A142" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T22:54:37+09:00</t>
+          <t>2026-07-26T21:02:36+09:00</t>
         </is>
       </c>
       <c r="B142" s="106" t="inlineStr">
         <is>
-          <t>2025-11-24T00:00:00Z</t>
+          <t>2026-06-09T19:00:00Z</t>
         </is>
       </c>
       <c r="C142" s="60" t="inlineStr">
         <is>
-          <t>EU &amp; Europe</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D142" s="60" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="E142" s="60" t="inlineStr"/>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E142" s="60" t="inlineStr">
+        <is>
+          <t>Fusion Energy</t>
+        </is>
+      </c>
       <c r="F142" s="107" t="n">
         <v>5</v>
       </c>
@@ -11650,32 +11682,32 @@
       </c>
       <c r="H142" s="60" t="inlineStr">
         <is>
-          <t>United Kingdom Innovation Policy Benchmarks</t>
+          <t>DOE Office of Science News</t>
         </is>
       </c>
       <c r="I142" s="60" t="inlineStr">
         <is>
-          <t>英国、UKRIの386億ポンドを戦略分野と企業成長へ重点配分</t>
+          <t>エネルギー省が核融合科学と技術のロードマップを発表</t>
         </is>
       </c>
       <c r="J142" s="60" t="inlineStr">
         <is>
-          <t>英国政府はUKRIの総額386億ポンドの研究資金を重点化する。政府優先課題に80億ポンド、革新的企業の成長に70億ポンドを振り向け、量子などの戦略技術、研究成果の事業化、国際研究人材を支援する。</t>
+          <t>米国エネルギー省は、核融合エネルギーの開発と商業化を加速するための戦略を発表しました。</t>
         </is>
       </c>
       <c r="K142" s="60" t="inlineStr">
         <is>
-          <t>https://www.gov.uk/government/news/more-targeted-rd-investment-towards-driving-uk-growth-and-jobs-unveiled-by-technology-secretary</t>
+          <t>https://www.energy.gov/articles/energy-department-releases-finalized-fusion-science-and-technology-roadmap-accelerate</t>
         </is>
       </c>
       <c r="L142" s="60" t="inlineStr">
         <is>
-          <t>352d511ffda7b190e7b5b71f</t>
+          <t>bf24d6f8eb27dabbbe4e196e</t>
         </is>
       </c>
       <c r="M142" s="106" t="inlineStr">
         <is>
-          <t>2025-11-24T09:00:00+09:00</t>
+          <t>2026-06-10T04:00:00+09:00</t>
         </is>
       </c>
       <c r="N142" s="60" t="inlineStr">
@@ -11685,29 +11717,29 @@
       </c>
       <c r="O142" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: R&amp;D Funding &amp; Tax Incentives | National Programs &amp; Strategy | Public Procurement &amp; Industrial Policy | Research System &amp; Talent / 学術区分: News &amp; Official Release / 焦点: 公的R&amp;D資金の戦略分野・企業成長・研究人材への重点配分 / Pinned official policy benchmark.</t>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy | Patents &amp; Intellectual Property / 学術区分: News &amp; Official Release / 焦点: 核融合エネルギーの商業化に向けた戦略</t>
         </is>
       </c>
     </row>
     <row r="143" ht="42" customHeight="1">
       <c r="A143" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T22:54:37+09:00</t>
+          <t>2026-07-26T21:02:36+09:00</t>
         </is>
       </c>
       <c r="B143" s="106" t="inlineStr">
         <is>
-          <t>2025-11-20T00:00:00Z</t>
+          <t>2026-06-09T12:00:00Z</t>
         </is>
       </c>
       <c r="C143" s="60" t="inlineStr">
         <is>
-          <t>EU &amp; Europe</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D143" s="60" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E143" s="60" t="inlineStr">
@@ -11716,7 +11748,7 @@
         </is>
       </c>
       <c r="F143" s="107" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G143" s="60" t="inlineStr">
         <is>
@@ -11725,32 +11757,32 @@
       </c>
       <c r="H143" s="60" t="inlineStr">
         <is>
-          <t>United Kingdom Innovation Policy Benchmarks</t>
+          <t>NIST News</t>
         </is>
       </c>
       <c r="I143" s="60" t="inlineStr">
         <is>
-          <t>英国、「AI for Science Strategy」で計算資源・データ・自律実験を一体支援</t>
+          <t>NISTの数学的証明がAIシステムのセキュリティモデルへの移行を支持</t>
         </is>
       </c>
       <c r="J143" s="60" t="inlineStr">
         <is>
-          <t>英国はAIによる科学発見を加速する15施策を公表した。公共計算資源AIRR、研究データへの安全なアクセス、自律実験室、AIサイエンティストを一体で整備し、大型研究には6か月で20万～100万GPU時間を配分する。</t>
+          <t>NISTは、AIシステムのための継続的な監視と更新のセキュリティモデルへの移行を支持する数学的証明を発表しました。</t>
         </is>
       </c>
       <c r="K143" s="60" t="inlineStr">
         <is>
-          <t>https://www.gov.uk/government/publications/ai-for-science-strategy/ai-for-science-strategy</t>
+          <t>https://www.nist.gov/news-events/news/2026/06/nist-mathematical-proof-supports-transition-continuous-monitor-and-update</t>
         </is>
       </c>
       <c r="L143" s="60" t="inlineStr">
         <is>
-          <t>216920d93f7a73f79a84dad1</t>
+          <t>edf1c2446b6ba41114d4bc6b</t>
         </is>
       </c>
       <c r="M143" s="106" t="inlineStr">
         <is>
-          <t>2025-11-20T09:00:00+09:00</t>
+          <t>2026-06-09T21:00:00+09:00</t>
         </is>
       </c>
       <c r="N143" s="60" t="inlineStr">
@@ -11760,19 +11792,19 @@
       </c>
       <c r="O143" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: R&amp;D Funding &amp; Tax Incentives | National Programs &amp; Strategy | Research System &amp; Talent / 学術区分: News &amp; Official Release / 焦点: AI計算資源、研究データ、自律実験室を統合した科学研究基盤 / Pinned official policy benchmark.</t>
+          <t>枠: Innovation Policy / 政策分野: Public Procurement &amp; Industrial Policy / 学術区分: News &amp; Official Release / 焦点: AIシステムのセキュリティモデル</t>
         </is>
       </c>
     </row>
     <row r="144" ht="42" customHeight="1">
       <c r="A144" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T22:54:37+09:00</t>
+          <t>2026-07-26T21:02:36+09:00</t>
         </is>
       </c>
       <c r="B144" s="106" t="inlineStr">
         <is>
-          <t>2025-09-15T00:00:00Z</t>
+          <t>2026-06-05T12:28:26Z</t>
         </is>
       </c>
       <c r="C144" s="60" t="inlineStr">
@@ -11782,46 +11814,46 @@
       </c>
       <c r="D144" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="E144" s="60" t="inlineStr"/>
       <c r="F144" s="107" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G144" s="60" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Intergovernmental</t>
         </is>
       </c>
       <c r="H144" s="60" t="inlineStr">
         <is>
-          <t>United States R&amp;D Tax Policy Benchmarks</t>
+          <t>WHO News</t>
         </is>
       </c>
       <c r="I144" s="60" t="inlineStr">
         <is>
-          <t>米国、国内R&amp;D費の即時控除を認める新Section 174Aの実施手続きを公表</t>
+          <t>アフリカCDCとWHOが共同でエボラ対応計画を発表</t>
         </is>
       </c>
       <c r="J144" s="60" t="inlineStr">
         <is>
-          <t>米国IRSは新設された内国歳入法Section 174Aの実施手続きを示した。2024年12月31日後に始まる課税年度の国内研究・実験費は原則即時控除できる一方、国外R&amp;D費は15年償却を継続し、過年度の国内R&amp;D費には移行措置を設ける。</t>
+          <t>アフリカCDCとWHOがエボラウイルスの対応計画を発表し、5億1800万ドルの資金を目指す。</t>
         </is>
       </c>
       <c r="K144" s="60" t="inlineStr">
         <is>
-          <t>https://www.irs.gov/irb/2025-38_IRB</t>
+          <t>https://www.who.int/news/item/05-06-2026-africa-cdc-and-who-launch-joint-continental-ebola-response-plan</t>
         </is>
       </c>
       <c r="L144" s="60" t="inlineStr">
         <is>
-          <t>f5062cb90623083863eb5adc</t>
+          <t>41c465a6eca3591002d781ba</t>
         </is>
       </c>
       <c r="M144" s="106" t="inlineStr">
         <is>
-          <t>2025-09-15T09:00:00+09:00</t>
+          <t>2026-06-05T21:28:26+09:00</t>
         </is>
       </c>
       <c r="N144" s="60" t="inlineStr">
@@ -11831,29 +11863,29 @@
       </c>
       <c r="O144" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: R&amp;D Funding &amp; Tax Incentives / 学術区分: News &amp; Official Release / 焦点: 企業の国内研究開発費に対する即時控除と国外R&amp;D費の償却 / Pinned official policy benchmark.</t>
+          <t>枠: Innovation Policy / 政策分野: Public Procurement &amp; Industrial Policy / 学術区分: News &amp; Official Release / 焦点: エボラウイルスに対する対応計画</t>
         </is>
       </c>
     </row>
     <row r="145" ht="42" customHeight="1">
       <c r="A145" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T22:54:37+09:00</t>
+          <t>2026-07-26T21:02:36+09:00</t>
         </is>
       </c>
       <c r="B145" s="106" t="inlineStr">
         <is>
-          <t>2025-08-27T00:00:00Z</t>
+          <t>2026-06-04T12:00:00Z</t>
         </is>
       </c>
       <c r="C145" s="60" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D145" s="60" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E145" s="60" t="inlineStr">
@@ -11862,7 +11894,7 @@
         </is>
       </c>
       <c r="F145" s="107" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G145" s="60" t="inlineStr">
         <is>
@@ -11871,32 +11903,32 @@
       </c>
       <c r="H145" s="60" t="inlineStr">
         <is>
-          <t>China Innovation Policy Benchmarks</t>
+          <t>NIST News</t>
         </is>
       </c>
       <c r="I145" s="60" t="inlineStr">
         <is>
-          <t>中国国務院、「AI Plus」指針で6分野へのAI統合目標を設定</t>
+          <t>新しいAIモデルが火災時の避難経路を特定</t>
         </is>
       </c>
       <c r="J145" s="60" t="inlineStr">
         <is>
-          <t>中国国務院は「AI Plus」指針を公表し、科学技術、産業、消費、民生、ガバナンス、国際協力の6分野にAIを統合する。次世代スマート端末・AIエージェントの普及率を2027年に70％超、2030年に90％超へ引き上げる目標を置いた。</t>
+          <t>NISTが火災時に安全な避難経路を特定する新しいAIモデルを作成した。</t>
         </is>
       </c>
       <c r="K145" s="60" t="inlineStr">
         <is>
-          <t>https://english.www.gov.cn/policies/latestreleases/202508/27/content_WS68ae7976c6d0868f4e8f51a0.html</t>
+          <t>https://www.nist.gov/news-events/news/2026/06/new-ai-model-shows-how-evacuate-fires-one-safe-step-time</t>
         </is>
       </c>
       <c r="L145" s="60" t="inlineStr">
         <is>
-          <t>234d256bd362cd224236af3c</t>
+          <t>434bb62e0a1e48aca17e1405</t>
         </is>
       </c>
       <c r="M145" s="106" t="inlineStr">
         <is>
-          <t>2025-08-27T09:00:00+09:00</t>
+          <t>2026-06-04T21:00:00+09:00</t>
         </is>
       </c>
       <c r="N145" s="60" t="inlineStr">
@@ -11906,87 +11938,2230 @@
       </c>
       <c r="O145" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy | Public Procurement &amp; Industrial Policy / 学術区分: News &amp; Official Release / 焦点: AIの研究・産業・公共部門への国家的な普及と実装 / Pinned official policy benchmark.</t>
+          <t>枠: Innovation Policy / 政策分野: Public Procurement &amp; Industrial Policy / 学術区分: News &amp; Official Release / 焦点: 火災時の避難経路を特定するAIモデル</t>
         </is>
       </c>
     </row>
     <row r="146" ht="42" customHeight="1">
       <c r="A146" s="106" t="inlineStr">
         <is>
+          <t>2026-07-26T21:02:36+09:00</t>
+        </is>
+      </c>
+      <c r="B146" s="106" t="inlineStr">
+        <is>
+          <t>2026-06-04T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="C146" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D146" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E146" s="60" t="inlineStr"/>
+      <c r="F146" s="107" t="n">
+        <v>3</v>
+      </c>
+      <c r="G146" s="60" t="inlineStr">
+        <is>
+          <t>Government</t>
+        </is>
+      </c>
+      <c r="H146" s="60" t="inlineStr">
+        <is>
+          <t>NIST News</t>
+        </is>
+      </c>
+      <c r="I146" s="60" t="inlineStr">
+        <is>
+          <t>NISTがレーザーを用いた合金の結合方法を発見</t>
+        </is>
+      </c>
+      <c r="J146" s="60" t="inlineStr">
+        <is>
+          <t>NISTが3Dプリンティング中の金属の原子構造をリアルタイムで研究する方法を改善した。</t>
+        </is>
+      </c>
+      <c r="K146" s="60" t="inlineStr">
+        <is>
+          <t>https://www.nist.gov/news-events/news/2026/06/nist-researchers-discover-new-way-whisk-alloys-together-lasers</t>
+        </is>
+      </c>
+      <c r="L146" s="60" t="inlineStr">
+        <is>
+          <t>a03605c38ac072e4b77247db</t>
+        </is>
+      </c>
+      <c r="M146" s="106" t="inlineStr">
+        <is>
+          <t>2026-06-04T21:00:00+09:00</t>
+        </is>
+      </c>
+      <c r="N146" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O146" s="60" t="inlineStr">
+        <is>
+          <t>枠: Innovation Policy / 政策分野: Public Procurement &amp; Industrial Policy / 学術区分: News &amp; Official Release / 焦点: レーザーを用いた合金の結合方法</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="42" customHeight="1">
+      <c r="A147" s="106" t="inlineStr">
+        <is>
+          <t>2026-07-26T21:02:36+09:00</t>
+        </is>
+      </c>
+      <c r="B147" s="106" t="inlineStr">
+        <is>
+          <t>2026-06-03T03:00:33Z</t>
+        </is>
+      </c>
+      <c r="C147" s="60" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="D147" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E147" s="60" t="inlineStr">
+        <is>
+          <t>Semiconductors &amp; Telecom</t>
+        </is>
+      </c>
+      <c r="F147" s="107" t="n">
+        <v>0</v>
+      </c>
+      <c r="G147" s="60" t="inlineStr">
+        <is>
+          <t>Official Company</t>
+        </is>
+      </c>
+      <c r="H147" s="60" t="inlineStr">
+        <is>
+          <t>Intel Newsroom</t>
+        </is>
+      </c>
+      <c r="I147" s="60" t="inlineStr">
+        <is>
+          <t>インテル、企業向けEthernet E835ネットワーク制御装置を発表</t>
+        </is>
+      </c>
+      <c r="J147" s="60" t="inlineStr">
+        <is>
+          <t>インテルは、データセンターや企業、AI、テレコムモバイルコアアプリケーション向けに高密度環境の帯域幅とスケーラビリティの要求に応えるEthernet E835ネットワーク制御装置とアダプタを発表した。</t>
+        </is>
+      </c>
+      <c r="K147" s="60" t="inlineStr">
+        <is>
+          <t>https://newsroom.intel.com/pt/data-cente/intel-apresenta-controladores-e-adaptadores-de-rede-ethernet-e835-para-infraestruturas-corporativas-de-borda-e-telecomunicacoes</t>
+        </is>
+      </c>
+      <c r="L147" s="60" t="inlineStr">
+        <is>
+          <t>c78a2a348fa6a57f7ff2f7c3</t>
+        </is>
+      </c>
+      <c r="M147" s="106" t="inlineStr">
+        <is>
+          <t>2026-06-03T12:00:33+09:00</t>
+        </is>
+      </c>
+      <c r="N147" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O147" s="60" t="inlineStr">
+        <is>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: Ethernetネットワーク用の制御装置とアダプタ / Historical backfill from an allowlisted source.</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="42" customHeight="1">
+      <c r="A148" s="106" t="inlineStr">
+        <is>
+          <t>2026-07-26T21:02:36+09:00</t>
+        </is>
+      </c>
+      <c r="B148" s="106" t="inlineStr">
+        <is>
+          <t>2026-05-19T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="C148" s="60" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="D148" s="60" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E148" s="60" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence | Healthcare | Biotechnology</t>
+        </is>
+      </c>
+      <c r="F148" s="107" t="n">
+        <v>0</v>
+      </c>
+      <c r="G148" s="60" t="inlineStr">
+        <is>
+          <t>Journal Article</t>
+        </is>
+      </c>
+      <c r="H148" s="60" t="inlineStr">
+        <is>
+          <t>Nature</t>
+        </is>
+      </c>
+      <c r="I148" s="60" t="inlineStr">
+        <is>
+          <t>Co-Scientistによる科学的発見の加速</t>
+        </is>
+      </c>
+      <c r="J148" s="60" t="inlineStr">
+        <is>
+          <t>Co-Scientistは、科学者の研究目的に基づいて新しい研究仮説を生成するAIシステムで、特にバイオメディカル分野での応用が示されています。</t>
+        </is>
+      </c>
+      <c r="K148" s="60" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1038/s41586-026-10644-y</t>
+        </is>
+      </c>
+      <c r="L148" s="60" t="inlineStr">
+        <is>
+          <t>21dce88bdeef80bd3133e790</t>
+        </is>
+      </c>
+      <c r="M148" s="106" t="inlineStr">
+        <is>
+          <t>2026-05-19T09:00:00+09:00</t>
+        </is>
+      </c>
+      <c r="N148" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O148" s="60" t="inlineStr">
+        <is>
+          <t>枠: Technology Innovation / 学術区分: Journal Article / 査読表示: Journal record — confirm peer review on publisher page / 掲載誌・学会: Nature / 焦点: AIによる科学的発見の加速 / OpenAlex record; work type=article; citations=56</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="42" customHeight="1">
+      <c r="A149" s="106" t="inlineStr">
+        <is>
+          <t>2026-07-26T21:02:36+09:00</t>
+        </is>
+      </c>
+      <c r="B149" s="106" t="inlineStr">
+        <is>
+          <t>2026-05-18T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="C149" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D149" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E149" s="60" t="inlineStr">
+        <is>
+          <t>Space</t>
+        </is>
+      </c>
+      <c r="F149" s="107" t="n">
+        <v>0</v>
+      </c>
+      <c r="G149" s="60" t="inlineStr">
+        <is>
+          <t>Government</t>
+        </is>
+      </c>
+      <c r="H149" s="60" t="inlineStr">
+        <is>
+          <t>NIST News</t>
+        </is>
+      </c>
+      <c r="I149" s="60" t="inlineStr">
+        <is>
+          <t>月面探査に向けた超安定レーザー技術の可能性</t>
+        </is>
+      </c>
+      <c r="J149" s="60" t="inlineStr">
+        <is>
+          <t>月面の永久影にあるクレーターは、これまでにないほど安定した光学レーザーを構築する理想的な場所となる可能性がある。</t>
+        </is>
+      </c>
+      <c r="K149" s="60" t="inlineStr">
+        <is>
+          <t>https://www.nist.gov/news-events/news/2026/05/shooting-moon-ultrastable-lasers-dark-craters-could-enable-lunar-navigation</t>
+        </is>
+      </c>
+      <c r="L149" s="60" t="inlineStr">
+        <is>
+          <t>99f664278415a42538163a5c</t>
+        </is>
+      </c>
+      <c r="M149" s="106" t="inlineStr">
+        <is>
+          <t>2026-05-18T21:00:00+09:00</t>
+        </is>
+      </c>
+      <c r="N149" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O149" s="60" t="inlineStr">
+        <is>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: 超安定レーザー技術</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="42" customHeight="1">
+      <c r="A150" s="106" t="inlineStr">
+        <is>
           <t>2026-07-26T22:54:37+09:00</t>
         </is>
       </c>
-      <c r="B146" s="106" t="inlineStr">
+      <c r="B150" s="106" t="inlineStr">
+        <is>
+          <t>2026-05-14T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="C150" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D150" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E150" s="60" t="inlineStr"/>
+      <c r="F150" s="107" t="n">
+        <v>5</v>
+      </c>
+      <c r="G150" s="60" t="inlineStr">
+        <is>
+          <t>Government</t>
+        </is>
+      </c>
+      <c r="H150" s="60" t="inlineStr">
+        <is>
+          <t>NSF Policy Benchmarks</t>
+        </is>
+      </c>
+      <c r="I150" s="60" t="inlineStr">
+        <is>
+          <t>NSF、15億ドルのX-Labs構想を発表</t>
+        </is>
+      </c>
+      <c r="J150" s="60" t="inlineStr">
+        <is>
+          <t>米国NSFは15億ドル規模の「NSF X-Labs」を発表した。従来型機関の外で独立研究組織を立ち上げ・拡大し、世代を画する科学的ブレークスルーを長期・大規模に追求する。</t>
+        </is>
+      </c>
+      <c r="K150" s="60" t="inlineStr">
+        <is>
+          <t>https://www.nsf.gov/news/nsf-announces-15b-nsf-x-labs-initiative-pursue-generational</t>
+        </is>
+      </c>
+      <c r="L150" s="60" t="inlineStr">
+        <is>
+          <t>770e8a385a4790aa084a1d15</t>
+        </is>
+      </c>
+      <c r="M150" s="106" t="inlineStr">
+        <is>
+          <t>2026-05-14T09:00:00+09:00</t>
+        </is>
+      </c>
+      <c r="N150" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O150" s="60" t="inlineStr">
+        <is>
+          <t>枠: Innovation Policy / 政策分野: R&amp;D Funding &amp; Tax Incentives | National Programs &amp; Strategy | Research System &amp; Talent / 学術区分: News &amp; Official Release / 焦点: 独立研究組織を通じた大型・長期の基礎研究支援 / Pinned official policy benchmark.</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="42" customHeight="1">
+      <c r="A151" s="106" t="inlineStr">
+        <is>
+          <t>2026-07-26T21:02:36+09:00</t>
+        </is>
+      </c>
+      <c r="B151" s="106" t="inlineStr">
+        <is>
+          <t>2026-04-15T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="C151" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D151" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E151" s="60" t="inlineStr">
+        <is>
+          <t>Semiconductors &amp; Telecom</t>
+        </is>
+      </c>
+      <c r="F151" s="107" t="n">
+        <v>0</v>
+      </c>
+      <c r="G151" s="60" t="inlineStr">
+        <is>
+          <t>Government</t>
+        </is>
+      </c>
+      <c r="H151" s="60" t="inlineStr">
+        <is>
+          <t>NIST News</t>
+        </is>
+      </c>
+      <c r="I151" s="60" t="inlineStr">
+        <is>
+          <t>好きな色を選べる：NIST科学者が小型回路で「任意の波長」レーザーを作成</t>
+        </is>
+      </c>
+      <c r="J151" s="60" t="inlineStr">
+        <is>
+          <t>NISTの科学者たちが、シリコンウェハ上に特殊材料の複雑なパターンを堆積することで、光のための集積回路を作成する方法を開発した。</t>
+        </is>
+      </c>
+      <c r="K151" s="60" t="inlineStr">
+        <is>
+          <t>https://www.nist.gov/news-events/news/2026/04/any-color-you-nist-scientists-create-any-wavelength-lasers-tiny-circuits</t>
+        </is>
+      </c>
+      <c r="L151" s="60" t="inlineStr">
+        <is>
+          <t>4fba34d8f0d0bf2d1a725c46</t>
+        </is>
+      </c>
+      <c r="M151" s="106" t="inlineStr">
+        <is>
+          <t>2026-04-15T21:00:00+09:00</t>
+        </is>
+      </c>
+      <c r="N151" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O151" s="60" t="inlineStr">
+        <is>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: 集積回路の光学技術</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="42" customHeight="1">
+      <c r="A152" s="106" t="inlineStr">
+        <is>
+          <t>2026-07-26T22:54:37+09:00</t>
+        </is>
+      </c>
+      <c r="B152" s="106" t="inlineStr">
+        <is>
+          <t>2026-03-24T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="C152" s="60" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D152" s="60" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E152" s="60" t="inlineStr"/>
+      <c r="F152" s="107" t="n">
+        <v>5</v>
+      </c>
+      <c r="G152" s="60" t="inlineStr">
+        <is>
+          <t>Government</t>
+        </is>
+      </c>
+      <c r="H152" s="60" t="inlineStr">
+        <is>
+          <t>China Innovation Policy Benchmarks</t>
+        </is>
+      </c>
+      <c r="I152" s="60" t="inlineStr">
+        <is>
+          <t>中国、大学・研究機関の特許130万件を審査し事業化候補68万件を企業へ接続</t>
+        </is>
+      </c>
+      <c r="J152" s="60" t="inlineStr">
+        <is>
+          <t>中国は大学・研究機関が保有する130万件超の特許を全国審査し、事業化可能性の高い発明特許68万件を特定して46万社へ接続した。国務院の特許転化・活用行動計画に基づき、評価、マッチング、研究者報酬、技術移転人材を整備する。</t>
+        </is>
+      </c>
+      <c r="K152" s="60" t="inlineStr">
+        <is>
+          <t>https://english.www.gov.cn/news/202603/24/content_WS69c1edb6c6d00ca5f9a0a13c.html</t>
+        </is>
+      </c>
+      <c r="L152" s="60" t="inlineStr">
+        <is>
+          <t>56bcce956cacb3b5f73edbdd</t>
+        </is>
+      </c>
+      <c r="M152" s="106" t="inlineStr">
+        <is>
+          <t>2026-03-24T09:00:00+09:00</t>
+        </is>
+      </c>
+      <c r="N152" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O152" s="60" t="inlineStr">
+        <is>
+          <t>枠: Innovation Policy / 政策分野: Patents &amp; Intellectual Property | Public Procurement &amp; Industrial Policy / 学術区分: News &amp; Official Release / 焦点: 大学・研究機関の特許評価、企業マッチング、技術移転 / Pinned official policy benchmark.</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="42" customHeight="1">
+      <c r="A153" s="106" t="inlineStr">
+        <is>
+          <t>2026-07-26T21:02:36+09:00</t>
+        </is>
+      </c>
+      <c r="B153" s="106" t="inlineStr">
+        <is>
+          <t>2026-03-19T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="C153" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D153" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E153" s="60" t="inlineStr"/>
+      <c r="F153" s="107" t="n">
+        <v>4</v>
+      </c>
+      <c r="G153" s="60" t="inlineStr">
+        <is>
+          <t>Government</t>
+        </is>
+      </c>
+      <c r="H153" s="60" t="inlineStr">
+        <is>
+          <t>NIST News</t>
+        </is>
+      </c>
+      <c r="I153" s="60" t="inlineStr">
+        <is>
+          <t>NISTが議会にFY 2025の国家建設安全チーム調査の進捗を報告</t>
+        </is>
+      </c>
+      <c r="J153" s="60" t="inlineStr">
+        <is>
+          <t>NISTは、Champlain Towers Southの調査に関する作業の概要を含む報告書を議会に提出しました。</t>
+        </is>
+      </c>
+      <c r="K153" s="60" t="inlineStr">
+        <is>
+          <t>https://www.nist.gov/news-events/news/2026/03/nist-submits-annual-report-congress-summarizing-fy-2025-progress-national</t>
+        </is>
+      </c>
+      <c r="L153" s="60" t="inlineStr">
+        <is>
+          <t>e322af74bfc6d82e04e94180</t>
+        </is>
+      </c>
+      <c r="M153" s="106" t="inlineStr">
+        <is>
+          <t>2026-03-19T21:00:00+09:00</t>
+        </is>
+      </c>
+      <c r="N153" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O153" s="60" t="inlineStr">
+        <is>
+          <t>枠: Innovation Policy / 政策分野: Public Procurement &amp; Industrial Policy / 学術区分: News &amp; Official Release / 焦点: 国家建設安全チームの調査進捗</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="42" customHeight="1">
+      <c r="A154" s="106" t="inlineStr">
+        <is>
+          <t>2026-07-28T01:39:30+09:00</t>
+        </is>
+      </c>
+      <c r="B154" s="106" t="inlineStr">
+        <is>
+          <t>2026-03-17T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="C154" s="60" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="D154" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E154" s="60" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="F154" s="107" t="n">
+        <v>0</v>
+      </c>
+      <c r="G154" s="60" t="inlineStr">
+        <is>
+          <t>Conference Paper</t>
+        </is>
+      </c>
+      <c r="H154" s="60" t="inlineStr">
+        <is>
+          <t>AAAI Proceedings</t>
+        </is>
+      </c>
+      <c r="I154" s="60" t="inlineStr">
+        <is>
+          <t>リソース効率的な睡眠段階分類のためのマルチレベルマスキングとプロンプト学習</t>
+        </is>
+      </c>
+      <c r="J154" s="60" t="inlineStr">
+        <is>
+          <t>自動睡眠段階分類は睡眠の質評価に重要であり、リソース制約のあるシステム向けに信頼性のある分類性能を維持しつつ信号収集量を削減する手法を提案。</t>
+        </is>
+      </c>
+      <c r="K154" s="60" t="inlineStr">
+        <is>
+          <t>https://ojs.aaai.org/index.php/AAAI/article/view/36958</t>
+        </is>
+      </c>
+      <c r="L154" s="60" t="inlineStr">
+        <is>
+          <t>e1652868b00b3d1b3ade9afe</t>
+        </is>
+      </c>
+      <c r="M154" s="106" t="inlineStr">
+        <is>
+          <t>2026-03-17T09:00:00+09:00</t>
+        </is>
+      </c>
+      <c r="N154" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O154" s="60" t="inlineStr">
+        <is>
+          <t>枠: Technology Innovation / 学術区分: Conference Paper / 査読表示: Conference proceedings — review status varies / 焦点: 自動睡眠段階分類</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="42" customHeight="1">
+      <c r="A155" s="106" t="inlineStr">
+        <is>
+          <t>2026-07-28T01:39:30+09:00</t>
+        </is>
+      </c>
+      <c r="B155" s="106" t="inlineStr">
+        <is>
+          <t>2026-03-14T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="C155" s="60" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="D155" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E155" s="60" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="F155" s="107" t="n">
+        <v>0</v>
+      </c>
+      <c r="G155" s="60" t="inlineStr">
+        <is>
+          <t>Conference Paper</t>
+        </is>
+      </c>
+      <c r="H155" s="60" t="inlineStr">
+        <is>
+          <t>AAAI Proceedings</t>
+        </is>
+      </c>
+      <c r="I155" s="60" t="inlineStr">
+        <is>
+          <t>パラ言語的手がかりを取り入れた包括的なスピーチ有害性データセットと検出フレームワーク</t>
+        </is>
+      </c>
+      <c r="J155" s="60" t="inlineStr">
+        <is>
+          <t>有害なスピーチ検出のために、感情やイントネーションなどのパラ言語的手がかりを考慮した新しい音声データセットを提案。</t>
+        </is>
+      </c>
+      <c r="K155" s="60" t="inlineStr">
+        <is>
+          <t>https://ojs.aaai.org/index.php/AAAI/article/view/36960</t>
+        </is>
+      </c>
+      <c r="L155" s="60" t="inlineStr">
+        <is>
+          <t>deaa1c45519ca1e04067d6e6</t>
+        </is>
+      </c>
+      <c r="M155" s="106" t="inlineStr">
+        <is>
+          <t>2026-03-14T09:00:00+09:00</t>
+        </is>
+      </c>
+      <c r="N155" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O155" s="60" t="inlineStr">
+        <is>
+          <t>枠: Technology Innovation / 学術区分: Conference Paper / 査読表示: Conference proceedings — review status varies / 焦点: 有害なスピーチ検出のための音声データセット</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="42" customHeight="1">
+      <c r="A156" s="106" t="inlineStr">
+        <is>
+          <t>2026-07-28T01:39:30+09:00</t>
+        </is>
+      </c>
+      <c r="B156" s="106" t="inlineStr">
+        <is>
+          <t>2026-03-14T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="C156" s="60" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="D156" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E156" s="60" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="F156" s="107" t="n">
+        <v>0</v>
+      </c>
+      <c r="G156" s="60" t="inlineStr">
+        <is>
+          <t>Conference Paper</t>
+        </is>
+      </c>
+      <c r="H156" s="60" t="inlineStr">
+        <is>
+          <t>AAAI Proceedings</t>
+        </is>
+      </c>
+      <c r="I156" s="60" t="inlineStr">
+        <is>
+          <t>変調ベースのバックドア攻撃：スピーカー認識への攻撃手法</t>
+        </is>
+      </c>
+      <c r="J156" s="60" t="inlineStr">
+        <is>
+          <t>スピーカー認識における深層ニューラルネットワークの脆弱性を利用した新しいバックドア攻撃手法を提案。</t>
+        </is>
+      </c>
+      <c r="K156" s="60" t="inlineStr">
+        <is>
+          <t>https://ojs.aaai.org/index.php/AAAI/article/view/36961</t>
+        </is>
+      </c>
+      <c r="L156" s="60" t="inlineStr">
+        <is>
+          <t>7f87b9dff63ad19c353fe7a6</t>
+        </is>
+      </c>
+      <c r="M156" s="106" t="inlineStr">
+        <is>
+          <t>2026-03-14T09:00:00+09:00</t>
+        </is>
+      </c>
+      <c r="N156" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O156" s="60" t="inlineStr">
+        <is>
+          <t>枠: Technology Innovation / 学術区分: Conference Paper / 査読表示: Conference proceedings — review status varies / 焦点: スピーカー認識に対するバックドア攻撃</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="42" customHeight="1">
+      <c r="A157" s="106" t="inlineStr">
+        <is>
+          <t>2026-07-28T01:39:30+09:00</t>
+        </is>
+      </c>
+      <c r="B157" s="106" t="inlineStr">
+        <is>
+          <t>2026-03-14T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="C157" s="60" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="D157" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E157" s="60" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="F157" s="107" t="n">
+        <v>0</v>
+      </c>
+      <c r="G157" s="60" t="inlineStr">
+        <is>
+          <t>Conference Paper</t>
+        </is>
+      </c>
+      <c r="H157" s="60" t="inlineStr">
+        <is>
+          <t>AAAI Proceedings</t>
+        </is>
+      </c>
+      <c r="I157" s="60" t="inlineStr">
+        <is>
+          <t>ロスレスDNAストレージのための構造的に安定化された表現学習</t>
+        </is>
+      </c>
+      <c r="J157" s="60" t="inlineStr">
+        <is>
+          <t>DNAデータストレージのための新しい表現学習モデルを提案し、エラー訂正と構造生物学を組み合わせた手法を示す。</t>
+        </is>
+      </c>
+      <c r="K157" s="60" t="inlineStr">
+        <is>
+          <t>https://ojs.aaai.org/index.php/AAAI/article/view/36962</t>
+        </is>
+      </c>
+      <c r="L157" s="60" t="inlineStr">
+        <is>
+          <t>96301baa1f5f933139a5efb6</t>
+        </is>
+      </c>
+      <c r="M157" s="106" t="inlineStr">
+        <is>
+          <t>2026-03-14T09:00:00+09:00</t>
+        </is>
+      </c>
+      <c r="N157" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O157" s="60" t="inlineStr">
+        <is>
+          <t>枠: Technology Innovation / 学術区分: Conference Paper / 査読表示: Conference proceedings — review status varies / 焦点: DNAデータストレージのための表現学習</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="42" customHeight="1">
+      <c r="A158" s="106" t="inlineStr">
+        <is>
+          <t>2026-07-28T01:39:30+09:00</t>
+        </is>
+      </c>
+      <c r="B158" s="106" t="inlineStr">
+        <is>
+          <t>2026-03-14T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="C158" s="60" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="D158" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E158" s="60" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="F158" s="107" t="n">
+        <v>0</v>
+      </c>
+      <c r="G158" s="60" t="inlineStr">
+        <is>
+          <t>Conference Paper</t>
+        </is>
+      </c>
+      <c r="H158" s="60" t="inlineStr">
+        <is>
+          <t>AAAI Proceedings</t>
+        </is>
+      </c>
+      <c r="I158" s="60" t="inlineStr">
+        <is>
+          <t>動画に配慮したグラフ検索強化生成のためのハイブリッド推論</t>
+        </is>
+      </c>
+      <c r="J158" s="60" t="inlineStr">
+        <is>
+          <t>長文動画理解における情報検索強化生成の新しいアプローチを提案し、ユーザーのクエリに動的に対応する手法を示す。</t>
+        </is>
+      </c>
+      <c r="K158" s="60" t="inlineStr">
+        <is>
+          <t>https://ojs.aaai.org/index.php/AAAI/article/view/36963</t>
+        </is>
+      </c>
+      <c r="L158" s="60" t="inlineStr">
+        <is>
+          <t>c710dc62c45272645e1fd328</t>
+        </is>
+      </c>
+      <c r="M158" s="106" t="inlineStr">
+        <is>
+          <t>2026-03-14T09:00:00+09:00</t>
+        </is>
+      </c>
+      <c r="N158" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O158" s="60" t="inlineStr">
+        <is>
+          <t>枠: Technology Innovation / 学術区分: Conference Paper / 査読表示: Conference proceedings — review status varies / 焦点: 動画理解のための情報検索強化生成</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="42" customHeight="1">
+      <c r="A159" s="106" t="inlineStr">
+        <is>
+          <t>2026-07-28T01:39:30+09:00</t>
+        </is>
+      </c>
+      <c r="B159" s="106" t="inlineStr">
+        <is>
+          <t>2026-03-14T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="C159" s="60" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="D159" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E159" s="60" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="F159" s="107" t="n">
+        <v>0</v>
+      </c>
+      <c r="G159" s="60" t="inlineStr">
+        <is>
+          <t>Conference Paper</t>
+        </is>
+      </c>
+      <c r="H159" s="60" t="inlineStr">
+        <is>
+          <t>AAAI Proceedings</t>
+        </is>
+      </c>
+      <c r="I159" s="60" t="inlineStr">
+        <is>
+          <t>コードモデルに対する移植可能なバックドア攻撃</t>
+        </is>
+      </c>
+      <c r="J159" s="60" t="inlineStr">
+        <is>
+          <t>ソフトウェア開発におけるコードモデルの脆弱性を利用した新しいバックドア攻撃手法を提案。</t>
+        </is>
+      </c>
+      <c r="K159" s="60" t="inlineStr">
+        <is>
+          <t>https://ojs.aaai.org/index.php/AAAI/article/view/36964</t>
+        </is>
+      </c>
+      <c r="L159" s="60" t="inlineStr">
+        <is>
+          <t>e0b15ef165b8ccd8e09d4daa</t>
+        </is>
+      </c>
+      <c r="M159" s="106" t="inlineStr">
+        <is>
+          <t>2026-03-14T09:00:00+09:00</t>
+        </is>
+      </c>
+      <c r="N159" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O159" s="60" t="inlineStr">
+        <is>
+          <t>枠: Technology Innovation / 学術区分: Conference Paper / 査読表示: Conference proceedings — review status varies / 焦点: コードモデルに対するバックドア攻撃</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="42" customHeight="1">
+      <c r="A160" s="106" t="inlineStr">
+        <is>
+          <t>2026-07-28T01:39:30+09:00</t>
+        </is>
+      </c>
+      <c r="B160" s="106" t="inlineStr">
+        <is>
+          <t>2026-03-14T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="C160" s="60" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="D160" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E160" s="60" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="F160" s="107" t="n">
+        <v>0</v>
+      </c>
+      <c r="G160" s="60" t="inlineStr">
+        <is>
+          <t>Conference Paper</t>
+        </is>
+      </c>
+      <c r="H160" s="60" t="inlineStr">
+        <is>
+          <t>AAAI Proceedings</t>
+        </is>
+      </c>
+      <c r="I160" s="60" t="inlineStr">
+        <is>
+          <t>物理的正則化階層生成モデルによる金属ガラス構造生成とエネルギー予測</t>
+        </is>
+      </c>
+      <c r="J160" s="60" t="inlineStr">
+        <is>
+          <t>金属ガラスの構造生成とエネルギー予測のために、階層的グラフ変分オートエンコーダーを導入し、効率的な生成を実現する。</t>
+        </is>
+      </c>
+      <c r="K160" s="60" t="inlineStr">
+        <is>
+          <t>https://ojs.aaai.org/index.php/AAAI/article/view/36967</t>
+        </is>
+      </c>
+      <c r="L160" s="60" t="inlineStr">
+        <is>
+          <t>c5d1c7f73a68899ac8993922</t>
+        </is>
+      </c>
+      <c r="M160" s="106" t="inlineStr">
+        <is>
+          <t>2026-03-14T09:00:00+09:00</t>
+        </is>
+      </c>
+      <c r="N160" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O160" s="60" t="inlineStr">
+        <is>
+          <t>枠: Technology Innovation / 学術区分: Conference Paper / 査読表示: Conference proceedings — review status varies / 焦点: グラスVAEによる構造生成とエネルギー予測</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" ht="42" customHeight="1">
+      <c r="A161" s="106" t="inlineStr">
+        <is>
+          <t>2026-07-28T01:39:30+09:00</t>
+        </is>
+      </c>
+      <c r="B161" s="106" t="inlineStr">
+        <is>
+          <t>2026-03-14T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="C161" s="60" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="D161" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E161" s="60" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="F161" s="107" t="n">
+        <v>0</v>
+      </c>
+      <c r="G161" s="60" t="inlineStr">
+        <is>
+          <t>Conference Paper</t>
+        </is>
+      </c>
+      <c r="H161" s="60" t="inlineStr">
+        <is>
+          <t>AAAI Proceedings</t>
+        </is>
+      </c>
+      <c r="I161" s="60" t="inlineStr">
+        <is>
+          <t>明示的質量制御による新規ペプチド配列決定のための回帰ガイド拡散モデル</t>
+        </is>
+      </c>
+      <c r="J161" s="60" t="inlineStr">
+        <is>
+          <t>質量の一貫性を強制する新しい回帰ガイド拡散モデルを導入し、ペプチド配列決定の精度を向上させる。</t>
+        </is>
+      </c>
+      <c r="K161" s="60" t="inlineStr">
+        <is>
+          <t>https://ojs.aaai.org/index.php/AAAI/article/view/36968</t>
+        </is>
+      </c>
+      <c r="L161" s="60" t="inlineStr">
+        <is>
+          <t>a1a589afc3b0f55410ca9c79</t>
+        </is>
+      </c>
+      <c r="M161" s="106" t="inlineStr">
+        <is>
+          <t>2026-03-14T09:00:00+09:00</t>
+        </is>
+      </c>
+      <c r="N161" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O161" s="60" t="inlineStr">
+        <is>
+          <t>枠: Technology Innovation / 学術区分: Conference Paper / 査読表示: Conference proceedings — review status varies / 焦点: DiffuNovoによる新しいペプチド配列決定</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="42" customHeight="1">
+      <c r="A162" s="106" t="inlineStr">
+        <is>
+          <t>2026-07-28T01:39:30+09:00</t>
+        </is>
+      </c>
+      <c r="B162" s="106" t="inlineStr">
+        <is>
+          <t>2026-03-14T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="C162" s="60" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="D162" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E162" s="60" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence | Robotics</t>
+        </is>
+      </c>
+      <c r="F162" s="107" t="n">
+        <v>0</v>
+      </c>
+      <c r="G162" s="60" t="inlineStr">
+        <is>
+          <t>Conference Paper</t>
+        </is>
+      </c>
+      <c r="H162" s="60" t="inlineStr">
+        <is>
+          <t>AAAI Proceedings</t>
+        </is>
+      </c>
+      <c r="I162" s="60" t="inlineStr">
+        <is>
+          <t>因果運転パターン転送による一般化可能な交通シミュレーション</t>
+        </is>
+      </c>
+      <c r="J162" s="60" t="inlineStr">
+        <is>
+          <t>自動運転システムの安全性を検証するための新しい交通シミュレーション手法を提案し、一般化能力を向上させる。</t>
+        </is>
+      </c>
+      <c r="K162" s="60" t="inlineStr">
+        <is>
+          <t>https://ojs.aaai.org/index.php/AAAI/article/view/36970</t>
+        </is>
+      </c>
+      <c r="L162" s="60" t="inlineStr">
+        <is>
+          <t>1fe557d3d0075af262b50ffd</t>
+        </is>
+      </c>
+      <c r="M162" s="106" t="inlineStr">
+        <is>
+          <t>2026-03-14T09:00:00+09:00</t>
+        </is>
+      </c>
+      <c r="N162" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O162" s="60" t="inlineStr">
+        <is>
+          <t>枠: Technology Innovation / 学術区分: Conference Paper / 査読表示: Conference proceedings — review status varies / 焦点: 因果運転パターン転送による交通シミュレーション</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="42" customHeight="1">
+      <c r="A163" s="106" t="inlineStr">
+        <is>
+          <t>2026-07-28T01:39:30+09:00</t>
+        </is>
+      </c>
+      <c r="B163" s="106" t="inlineStr">
+        <is>
+          <t>2026-03-14T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="C163" s="60" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="D163" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E163" s="60" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence | Robotics</t>
+        </is>
+      </c>
+      <c r="F163" s="107" t="n">
+        <v>0</v>
+      </c>
+      <c r="G163" s="60" t="inlineStr">
+        <is>
+          <t>Conference Paper</t>
+        </is>
+      </c>
+      <c r="H163" s="60" t="inlineStr">
+        <is>
+          <t>AAAI Proceedings</t>
+        </is>
+      </c>
+      <c r="I163" s="60" t="inlineStr">
+        <is>
+          <t>TRACE: 反応条件予測のための変換認識型グラフ精製</t>
+        </is>
+      </c>
+      <c r="J163" s="60" t="inlineStr">
+        <is>
+          <t>化学合成における反応条件を予測するための新しいフレームワークTRACEを提案し、精度を向上させる。</t>
+        </is>
+      </c>
+      <c r="K163" s="60" t="inlineStr">
+        <is>
+          <t>https://ojs.aaai.org/index.php/AAAI/article/view/36971</t>
+        </is>
+      </c>
+      <c r="L163" s="60" t="inlineStr">
+        <is>
+          <t>3ff817a57a7c27892949e83d</t>
+        </is>
+      </c>
+      <c r="M163" s="106" t="inlineStr">
+        <is>
+          <t>2026-03-14T09:00:00+09:00</t>
+        </is>
+      </c>
+      <c r="N163" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O163" s="60" t="inlineStr">
+        <is>
+          <t>枠: Technology Innovation / 学術区分: Conference Paper / 査読表示: Conference proceedings — review status varies / 焦点: TRACEによる反応条件予測</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="42" customHeight="1">
+      <c r="A164" s="106" t="inlineStr">
+        <is>
+          <t>2026-07-28T01:39:30+09:00</t>
+        </is>
+      </c>
+      <c r="B164" s="106" t="inlineStr">
+        <is>
+          <t>2026-03-14T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="C164" s="60" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="D164" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E164" s="60" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence | Robotics</t>
+        </is>
+      </c>
+      <c r="F164" s="107" t="n">
+        <v>0</v>
+      </c>
+      <c r="G164" s="60" t="inlineStr">
+        <is>
+          <t>Conference Paper</t>
+        </is>
+      </c>
+      <c r="H164" s="60" t="inlineStr">
+        <is>
+          <t>AAAI Proceedings</t>
+        </is>
+      </c>
+      <c r="I164" s="60" t="inlineStr">
+        <is>
+          <t>DyC-STG: IoTにおけるリアルタイムデータ信頼性分析のための動的因果空間-時間グラフネットワーク</t>
+        </is>
+      </c>
+      <c r="J164" s="60" t="inlineStr">
+        <is>
+          <t>IoTセンサーからのデータ信頼性を分析するための新しい手法を提案し、動的環境における課題を解決する。</t>
+        </is>
+      </c>
+      <c r="K164" s="60" t="inlineStr">
+        <is>
+          <t>https://ojs.aaai.org/index.php/AAAI/article/view/36973</t>
+        </is>
+      </c>
+      <c r="L164" s="60" t="inlineStr">
+        <is>
+          <t>6805dbddb3826be7ebe147b8</t>
+        </is>
+      </c>
+      <c r="M164" s="106" t="inlineStr">
+        <is>
+          <t>2026-03-14T09:00:00+09:00</t>
+        </is>
+      </c>
+      <c r="N164" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O164" s="60" t="inlineStr">
+        <is>
+          <t>枠: Technology Innovation / 学術区分: Conference Paper / 査読表示: Conference proceedings — review status varies / 焦点: DyC-STGによるデータ信頼性分析</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="42" customHeight="1">
+      <c r="A165" s="106" t="inlineStr">
+        <is>
+          <t>2026-07-28T01:39:30+09:00</t>
+        </is>
+      </c>
+      <c r="B165" s="106" t="inlineStr">
+        <is>
+          <t>2026-03-14T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="C165" s="60" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="D165" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E165" s="60" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence | Robotics</t>
+        </is>
+      </c>
+      <c r="F165" s="107" t="n">
+        <v>0</v>
+      </c>
+      <c r="G165" s="60" t="inlineStr">
+        <is>
+          <t>Conference Paper</t>
+        </is>
+      </c>
+      <c r="H165" s="60" t="inlineStr">
+        <is>
+          <t>AAAI Proceedings</t>
+        </is>
+      </c>
+      <c r="I165" s="60" t="inlineStr">
+        <is>
+          <t>ProAR: 分子動力学のための確率的オート回帰モデリング</t>
+        </is>
+      </c>
+      <c r="J165" s="60" t="inlineStr">
+        <is>
+          <t>生体分子の構造動態を理解するための新しい確率的オート回帰フレームワークを導入し、軌道生成を効率化する。</t>
+        </is>
+      </c>
+      <c r="K165" s="60" t="inlineStr">
+        <is>
+          <t>https://ojs.aaai.org/index.php/AAAI/article/view/36974</t>
+        </is>
+      </c>
+      <c r="L165" s="60" t="inlineStr">
+        <is>
+          <t>ce37fe13ab81476b177efd29</t>
+        </is>
+      </c>
+      <c r="M165" s="106" t="inlineStr">
+        <is>
+          <t>2026-03-14T09:00:00+09:00</t>
+        </is>
+      </c>
+      <c r="N165" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O165" s="60" t="inlineStr">
+        <is>
+          <t>枠: Technology Innovation / 学術区分: Conference Paper / 査読表示: Conference proceedings — review status varies / 焦点: ProARによる分子動力学のモデリング</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="42" customHeight="1">
+      <c r="A166" s="106" t="inlineStr">
+        <is>
+          <t>2026-07-26T21:02:36+09:00</t>
+        </is>
+      </c>
+      <c r="B166" s="106" t="inlineStr">
+        <is>
+          <t>2026-03-04T14:57:24Z</t>
+        </is>
+      </c>
+      <c r="C166" s="60" t="inlineStr">
+        <is>
+          <t>EU &amp; Europe</t>
+        </is>
+      </c>
+      <c r="D166" s="60" t="inlineStr">
+        <is>
+          <t>China / Germany</t>
+        </is>
+      </c>
+      <c r="E166" s="60" t="inlineStr">
+        <is>
+          <t>Biotechnology</t>
+        </is>
+      </c>
+      <c r="F166" s="107" t="n">
+        <v>3</v>
+      </c>
+      <c r="G166" s="60" t="inlineStr">
+        <is>
+          <t>Policy Institute</t>
+        </is>
+      </c>
+      <c r="H166" s="60" t="inlineStr">
+        <is>
+          <t>MERICS</t>
+        </is>
+      </c>
+      <c r="I166" s="60" t="inlineStr">
+        <is>
+          <t>アストラゼネカ、中国を製薬イノベーションのハブに</t>
+        </is>
+      </c>
+      <c r="J166" s="60" t="inlineStr">
+        <is>
+          <t>アストラゼネカが2030年までに中国の研究開発に150億ドルを投資する計画を発表。</t>
+        </is>
+      </c>
+      <c r="K166" s="60" t="inlineStr">
+        <is>
+          <t>https://merics.org/en/comment/astrazenecas-rd-bet-makes-china-pharma-innovation-hub</t>
+        </is>
+      </c>
+      <c r="L166" s="60" t="inlineStr">
+        <is>
+          <t>1c2d02bf178504dd287a6106</t>
+        </is>
+      </c>
+      <c r="M166" s="106" t="inlineStr">
+        <is>
+          <t>2026-03-04T23:57:24+09:00</t>
+        </is>
+      </c>
+      <c r="N166" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O166" s="60" t="inlineStr">
+        <is>
+          <t>枠: Innovation Policy / 政策分野: Regulation &amp; Governance / 学術区分: News &amp; Official Release / 焦点: バイオテクノロジー産業の規制 / Historical backfill from an allowlisted source.</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="42" customHeight="1">
+      <c r="A167" s="106" t="inlineStr">
+        <is>
+          <t>2026-07-26T22:54:37+09:00</t>
+        </is>
+      </c>
+      <c r="B167" s="106" t="inlineStr">
+        <is>
+          <t>2026-02-17T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="C167" s="60" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="D167" s="60" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E167" s="60" t="inlineStr"/>
+      <c r="F167" s="107" t="n">
+        <v>4</v>
+      </c>
+      <c r="G167" s="60" t="inlineStr">
+        <is>
+          <t>Intergovernmental</t>
+        </is>
+      </c>
+      <c r="H167" s="60" t="inlineStr">
+        <is>
+          <t>WIPO Policy Benchmarks</t>
+        </is>
+      </c>
+      <c r="I167" s="60" t="inlineStr">
+        <is>
+          <t>WIPO「世界知的財産報告書2026」、技術普及を左右する4要因を分析</t>
+        </is>
+      </c>
+      <c r="J167" s="60" t="inlineStr">
+        <is>
+          <t>WIPOは「世界知的財産報告書2026」で、技術の性質、情報流通、受容能力、政策・知財制度の4要因が技術普及の速度と範囲を左右すると分析した。特許と科学論文のデータから各国の普及格差を示す。</t>
+        </is>
+      </c>
+      <c r="K167" s="60" t="inlineStr">
+        <is>
+          <t>https://www.wipo.int/web-publications/world-intellectual-property-report-2026/en/index.html</t>
+        </is>
+      </c>
+      <c r="L167" s="60" t="inlineStr">
+        <is>
+          <t>424d3f7436d98c3c4ec35b6d</t>
+        </is>
+      </c>
+      <c r="M167" s="106" t="inlineStr">
+        <is>
+          <t>2026-02-17T09:00:00+09:00</t>
+        </is>
+      </c>
+      <c r="N167" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O167" s="60" t="inlineStr">
+        <is>
+          <t>枠: Innovation Policy / 政策分野: Patents &amp; Intellectual Property | National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: 知的財産制度と技術普及の関係 / Pinned official policy benchmark.</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="42" customHeight="1">
+      <c r="A168" s="106" t="inlineStr">
+        <is>
+          <t>2026-07-26T22:54:37+09:00</t>
+        </is>
+      </c>
+      <c r="B168" s="106" t="inlineStr">
+        <is>
+          <t>2026-02-12T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="C168" s="60" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D168" s="60" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="E168" s="60" t="inlineStr"/>
+      <c r="F168" s="107" t="n">
+        <v>5</v>
+      </c>
+      <c r="G168" s="60" t="inlineStr">
+        <is>
+          <t>Government</t>
+        </is>
+      </c>
+      <c r="H168" s="60" t="inlineStr">
+        <is>
+          <t>Korea Innovation Policy Benchmarks</t>
+        </is>
+      </c>
+      <c r="I168" s="60" t="inlineStr">
+        <is>
+          <t>韓国、大型国家R&amp;Dの事前評価を18年ぶりに全面改革</t>
+        </is>
+      </c>
+      <c r="J168" s="60" t="inlineStr">
+        <is>
+          <t>韓国は大型国家R&amp;Dの投資審査制度を18年ぶりに全面改革する。事前評価の対象基準を500億ウォンから1,000億ウォンへ引き上げ、研究型には計画審査、研究インフラ型には企画から完成までの全ライフサイクル審査を導入する。</t>
+        </is>
+      </c>
+      <c r="K168" s="60" t="inlineStr">
+        <is>
+          <t>https://www.msit.go.kr/eng/bbs/view.do?bbsSeqNo=42&amp;mId=4&amp;nttSeqNo=1227&amp;sCode=eng</t>
+        </is>
+      </c>
+      <c r="L168" s="60" t="inlineStr">
+        <is>
+          <t>d1549e57df1e4381c7594af7</t>
+        </is>
+      </c>
+      <c r="M168" s="106" t="inlineStr">
+        <is>
+          <t>2026-02-12T09:00:00+09:00</t>
+        </is>
+      </c>
+      <c r="N168" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O168" s="60" t="inlineStr">
+        <is>
+          <t>枠: Innovation Policy / 政策分野: R&amp;D Funding &amp; Tax Incentives | National Programs &amp; Strategy | Regulation &amp; Governance / 学術区分: News &amp; Official Release / 焦点: 大型国家R&amp;Dプロジェクトの投資審査と全ライフサイクル管理 / Pinned official policy benchmark.</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="42" customHeight="1">
+      <c r="A169" s="106" t="inlineStr">
+        <is>
+          <t>2026-07-26T21:02:36+09:00</t>
+        </is>
+      </c>
+      <c r="B169" s="106" t="inlineStr">
+        <is>
+          <t>2026-02-10T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="C169" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D169" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E169" s="60" t="inlineStr">
+        <is>
+          <t>Biotechnology | Artificial Intelligence | Semiconductors &amp; Telecom | Quantum</t>
+        </is>
+      </c>
+      <c r="F169" s="107" t="n">
+        <v>3</v>
+      </c>
+      <c r="G169" s="60" t="inlineStr">
+        <is>
+          <t>Government</t>
+        </is>
+      </c>
+      <c r="H169" s="60" t="inlineStr">
+        <is>
+          <t>NIST News</t>
+        </is>
+      </c>
+      <c r="I169" s="60" t="inlineStr">
+        <is>
+          <t>NISTがAI、バイオテクノロジー、半導体、量子技術を進展させる小規模企業に300万ドル以上を配分</t>
+        </is>
+      </c>
+      <c r="J169" s="60" t="inlineStr">
+        <is>
+          <t>NISTはSBIRプログラムの下で、7つの州にある8つの小規模企業に資金を配分することを発表した。</t>
+        </is>
+      </c>
+      <c r="K169" s="60" t="inlineStr">
+        <is>
+          <t>https://www.nist.gov/news-events/news/2026/02/nist-allocates-over-3-million-small-businesses-advancing-ai-biotechnology</t>
+        </is>
+      </c>
+      <c r="L169" s="60" t="inlineStr">
+        <is>
+          <t>2700025a185e7f6eb2253ff3</t>
+        </is>
+      </c>
+      <c r="M169" s="106" t="inlineStr">
+        <is>
+          <t>2026-02-10T21:00:00+09:00</t>
+        </is>
+      </c>
+      <c r="N169" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O169" s="60" t="inlineStr">
+        <is>
+          <t>枠: Innovation Policy / 政策分野: Public Procurement &amp; Industrial Policy / 学術区分: News &amp; Official Release / 焦点: AI、バイオテクノロジー、半導体、量子技術に関する資金配分</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="42" customHeight="1">
+      <c r="A170" s="106" t="inlineStr">
+        <is>
+          <t>2026-07-26T22:54:37+09:00</t>
+        </is>
+      </c>
+      <c r="B170" s="106" t="inlineStr">
+        <is>
+          <t>2025-11-24T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="C170" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D170" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E170" s="60" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="F170" s="107" t="n">
+        <v>5</v>
+      </c>
+      <c r="G170" s="60" t="inlineStr">
+        <is>
+          <t>Government</t>
+        </is>
+      </c>
+      <c r="H170" s="60" t="inlineStr">
+        <is>
+          <t>White House Science Policy Benchmarks</t>
+        </is>
+      </c>
+      <c r="I170" s="60" t="inlineStr">
+        <is>
+          <t>米国、AIで科学発見を加速する「Genesis Mission」を開始</t>
+        </is>
+      </c>
+      <c r="J170" s="60" t="inlineStr">
+        <is>
+          <t>米国は大統領令で「Genesis Mission」を開始した。連邦の科学データ、スーパーコンピューター、AI、研究施設を統合し、科学基盤モデルとAIエージェントで仮説検証や研究工程を自動化する国家計画である。</t>
+        </is>
+      </c>
+      <c r="K170" s="60" t="inlineStr">
+        <is>
+          <t>https://www.whitehouse.gov/presidential-actions/2025/11/launching-the-genesis-mission/</t>
+        </is>
+      </c>
+      <c r="L170" s="60" t="inlineStr">
+        <is>
+          <t>f224687901952d4c32603531</t>
+        </is>
+      </c>
+      <c r="M170" s="106" t="inlineStr">
+        <is>
+          <t>2025-11-24T09:00:00+09:00</t>
+        </is>
+      </c>
+      <c r="N170" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O170" s="60" t="inlineStr">
+        <is>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy | Research System &amp; Talent / 学術区分: News &amp; Official Release / 焦点: AI、連邦科学データ、国立研究所を統合する国家研究基盤 / Pinned official policy benchmark.</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="42" customHeight="1">
+      <c r="A171" s="106" t="inlineStr">
+        <is>
+          <t>2026-07-26T22:54:37+09:00</t>
+        </is>
+      </c>
+      <c r="B171" s="106" t="inlineStr">
+        <is>
+          <t>2025-11-24T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="C171" s="60" t="inlineStr">
+        <is>
+          <t>EU &amp; Europe</t>
+        </is>
+      </c>
+      <c r="D171" s="60" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="E171" s="60" t="inlineStr"/>
+      <c r="F171" s="107" t="n">
+        <v>5</v>
+      </c>
+      <c r="G171" s="60" t="inlineStr">
+        <is>
+          <t>Government</t>
+        </is>
+      </c>
+      <c r="H171" s="60" t="inlineStr">
+        <is>
+          <t>United Kingdom Innovation Policy Benchmarks</t>
+        </is>
+      </c>
+      <c r="I171" s="60" t="inlineStr">
+        <is>
+          <t>英国、UKRIの386億ポンドを戦略分野と企業成長へ重点配分</t>
+        </is>
+      </c>
+      <c r="J171" s="60" t="inlineStr">
+        <is>
+          <t>英国政府はUKRIの総額386億ポンドの研究資金を重点化する。政府優先課題に80億ポンド、革新的企業の成長に70億ポンドを振り向け、量子などの戦略技術、研究成果の事業化、国際研究人材を支援する。</t>
+        </is>
+      </c>
+      <c r="K171" s="60" t="inlineStr">
+        <is>
+          <t>https://www.gov.uk/government/news/more-targeted-rd-investment-towards-driving-uk-growth-and-jobs-unveiled-by-technology-secretary</t>
+        </is>
+      </c>
+      <c r="L171" s="60" t="inlineStr">
+        <is>
+          <t>352d511ffda7b190e7b5b71f</t>
+        </is>
+      </c>
+      <c r="M171" s="106" t="inlineStr">
+        <is>
+          <t>2025-11-24T09:00:00+09:00</t>
+        </is>
+      </c>
+      <c r="N171" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O171" s="60" t="inlineStr">
+        <is>
+          <t>枠: Innovation Policy / 政策分野: R&amp;D Funding &amp; Tax Incentives | National Programs &amp; Strategy | Public Procurement &amp; Industrial Policy | Research System &amp; Talent / 学術区分: News &amp; Official Release / 焦点: 公的R&amp;D資金の戦略分野・企業成長・研究人材への重点配分 / Pinned official policy benchmark.</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="42" customHeight="1">
+      <c r="A172" s="106" t="inlineStr">
+        <is>
+          <t>2026-07-26T22:54:37+09:00</t>
+        </is>
+      </c>
+      <c r="B172" s="106" t="inlineStr">
+        <is>
+          <t>2025-11-20T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="C172" s="60" t="inlineStr">
+        <is>
+          <t>EU &amp; Europe</t>
+        </is>
+      </c>
+      <c r="D172" s="60" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="E172" s="60" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="F172" s="107" t="n">
+        <v>5</v>
+      </c>
+      <c r="G172" s="60" t="inlineStr">
+        <is>
+          <t>Government</t>
+        </is>
+      </c>
+      <c r="H172" s="60" t="inlineStr">
+        <is>
+          <t>United Kingdom Innovation Policy Benchmarks</t>
+        </is>
+      </c>
+      <c r="I172" s="60" t="inlineStr">
+        <is>
+          <t>英国、「AI for Science Strategy」で計算資源・データ・自律実験を一体支援</t>
+        </is>
+      </c>
+      <c r="J172" s="60" t="inlineStr">
+        <is>
+          <t>英国はAIによる科学発見を加速する15施策を公表した。公共計算資源AIRR、研究データへの安全なアクセス、自律実験室、AIサイエンティストを一体で整備し、大型研究には6か月で20万～100万GPU時間を配分する。</t>
+        </is>
+      </c>
+      <c r="K172" s="60" t="inlineStr">
+        <is>
+          <t>https://www.gov.uk/government/publications/ai-for-science-strategy/ai-for-science-strategy</t>
+        </is>
+      </c>
+      <c r="L172" s="60" t="inlineStr">
+        <is>
+          <t>216920d93f7a73f79a84dad1</t>
+        </is>
+      </c>
+      <c r="M172" s="106" t="inlineStr">
+        <is>
+          <t>2025-11-20T09:00:00+09:00</t>
+        </is>
+      </c>
+      <c r="N172" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O172" s="60" t="inlineStr">
+        <is>
+          <t>枠: Innovation Policy / 政策分野: R&amp;D Funding &amp; Tax Incentives | National Programs &amp; Strategy | Research System &amp; Talent / 学術区分: News &amp; Official Release / 焦点: AI計算資源、研究データ、自律実験室を統合した科学研究基盤 / Pinned official policy benchmark.</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="42" customHeight="1">
+      <c r="A173" s="106" t="inlineStr">
+        <is>
+          <t>2026-07-26T22:54:37+09:00</t>
+        </is>
+      </c>
+      <c r="B173" s="106" t="inlineStr">
+        <is>
+          <t>2025-09-15T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="C173" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D173" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E173" s="60" t="inlineStr"/>
+      <c r="F173" s="107" t="n">
+        <v>5</v>
+      </c>
+      <c r="G173" s="60" t="inlineStr">
+        <is>
+          <t>Government</t>
+        </is>
+      </c>
+      <c r="H173" s="60" t="inlineStr">
+        <is>
+          <t>United States R&amp;D Tax Policy Benchmarks</t>
+        </is>
+      </c>
+      <c r="I173" s="60" t="inlineStr">
+        <is>
+          <t>米国、国内R&amp;D費の即時控除を認める新Section 174Aの実施手続きを公表</t>
+        </is>
+      </c>
+      <c r="J173" s="60" t="inlineStr">
+        <is>
+          <t>米国IRSは新設された内国歳入法Section 174Aの実施手続きを示した。2024年12月31日後に始まる課税年度の国内研究・実験費は原則即時控除できる一方、国外R&amp;D費は15年償却を継続し、過年度の国内R&amp;D費には移行措置を設ける。</t>
+        </is>
+      </c>
+      <c r="K173" s="60" t="inlineStr">
+        <is>
+          <t>https://www.irs.gov/irb/2025-38_IRB</t>
+        </is>
+      </c>
+      <c r="L173" s="60" t="inlineStr">
+        <is>
+          <t>f5062cb90623083863eb5adc</t>
+        </is>
+      </c>
+      <c r="M173" s="106" t="inlineStr">
+        <is>
+          <t>2025-09-15T09:00:00+09:00</t>
+        </is>
+      </c>
+      <c r="N173" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O173" s="60" t="inlineStr">
+        <is>
+          <t>枠: Innovation Policy / 政策分野: R&amp;D Funding &amp; Tax Incentives / 学術区分: News &amp; Official Release / 焦点: 企業の国内研究開発費に対する即時控除と国外R&amp;D費の償却 / Pinned official policy benchmark.</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="42" customHeight="1">
+      <c r="A174" s="106" t="inlineStr">
+        <is>
+          <t>2026-07-26T22:54:37+09:00</t>
+        </is>
+      </c>
+      <c r="B174" s="106" t="inlineStr">
+        <is>
+          <t>2025-08-27T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="C174" s="60" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D174" s="60" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E174" s="60" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="F174" s="107" t="n">
+        <v>5</v>
+      </c>
+      <c r="G174" s="60" t="inlineStr">
+        <is>
+          <t>Government</t>
+        </is>
+      </c>
+      <c r="H174" s="60" t="inlineStr">
+        <is>
+          <t>China Innovation Policy Benchmarks</t>
+        </is>
+      </c>
+      <c r="I174" s="60" t="inlineStr">
+        <is>
+          <t>中国国務院、「AI Plus」指針で6分野へのAI統合目標を設定</t>
+        </is>
+      </c>
+      <c r="J174" s="60" t="inlineStr">
+        <is>
+          <t>中国国務院は「AI Plus」指針を公表し、科学技術、産業、消費、民生、ガバナンス、国際協力の6分野にAIを統合する。次世代スマート端末・AIエージェントの普及率を2027年に70％超、2030年に90％超へ引き上げる目標を置いた。</t>
+        </is>
+      </c>
+      <c r="K174" s="60" t="inlineStr">
+        <is>
+          <t>https://english.www.gov.cn/policies/latestreleases/202508/27/content_WS68ae7976c6d0868f4e8f51a0.html</t>
+        </is>
+      </c>
+      <c r="L174" s="60" t="inlineStr">
+        <is>
+          <t>234d256bd362cd224236af3c</t>
+        </is>
+      </c>
+      <c r="M174" s="106" t="inlineStr">
+        <is>
+          <t>2025-08-27T09:00:00+09:00</t>
+        </is>
+      </c>
+      <c r="N174" s="60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O174" s="60" t="inlineStr">
+        <is>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy | Public Procurement &amp; Industrial Policy / 学術区分: News &amp; Official Release / 焦点: AIの研究・産業・公共部門への国家的な普及と実装 / Pinned official policy benchmark.</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="42" customHeight="1">
+      <c r="A175" s="106" t="inlineStr">
+        <is>
+          <t>2026-07-26T22:54:37+09:00</t>
+        </is>
+      </c>
+      <c r="B175" s="106" t="inlineStr">
         <is>
           <t>2025-08-05T00:00:00Z</t>
         </is>
       </c>
-      <c r="C146" s="60" t="inlineStr">
+      <c r="C175" s="60" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="D146" s="60" t="inlineStr">
+      <c r="D175" s="60" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="E146" s="60" t="inlineStr">
+      <c r="E175" s="60" t="inlineStr">
         <is>
           <t>Artificial Intelligence | Biotechnology</t>
         </is>
       </c>
-      <c r="F146" s="107" t="n">
+      <c r="F175" s="107" t="n">
         <v>5</v>
       </c>
-      <c r="G146" s="60" t="inlineStr">
+      <c r="G175" s="60" t="inlineStr">
         <is>
           <t>Government</t>
         </is>
       </c>
-      <c r="H146" s="60" t="inlineStr">
+      <c r="H175" s="60" t="inlineStr">
         <is>
           <t>NSF Policy Benchmarks</t>
         </is>
       </c>
-      <c r="I146" s="60" t="inlineStr">
+      <c r="I175" s="60" t="inlineStr">
         <is>
           <t>NSF、AIプログラマブル・クラウド研究所の全米ネットワークへ投資</t>
         </is>
       </c>
-      <c r="J146" s="60" t="inlineStr">
+      <c r="J175" s="60" t="inlineStr">
         <is>
           <t>米国NSFは、遠隔利用できるAIプログラマブル・クラウド研究所の全米ネットワークに投資する。初期対象はバイオテクノロジーと材料科学で、実験自動化と技術移転の加速を狙う。</t>
         </is>
       </c>
-      <c r="K146" s="60" t="inlineStr">
+      <c r="K175" s="60" t="inlineStr">
         <is>
           <t>https://www.nsf.gov/news/nsf-invest-new-national-network-ai-programmable-cloud</t>
         </is>
       </c>
-      <c r="L146" s="60" t="inlineStr">
+      <c r="L175" s="60" t="inlineStr">
         <is>
           <t>f5dc59710a410021bae58dc4</t>
         </is>
       </c>
-      <c r="M146" s="106" t="inlineStr">
+      <c r="M175" s="106" t="inlineStr">
         <is>
           <t>2025-08-05T09:00:00+09:00</t>
         </is>
       </c>
-      <c r="N146" s="60" t="inlineStr">
+      <c r="N175" s="60" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="O146" s="60" t="inlineStr">
+      <c r="O175" s="60" t="inlineStr">
         <is>
           <t>枠: Innovation Policy / 政策分野: R&amp;D Funding &amp; Tax Incentives | National Programs &amp; Strategy | Research System &amp; Talent / 学術区分: News &amp; Official Release / 焦点: AIで遠隔操作する研究施設ネットワーク / Pinned official policy benchmark.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:O146"/>
+  <autoFilter ref="A3:O175"/>
   <mergeCells count="2">
     <mergeCell ref="A1:O1"/>
     <mergeCell ref="A2:O2"/>
@@ -12004,7 +14179,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="N4:N146" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="N4:N175" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"New,Reviewed,Follow-up,Archived"</formula1>
     </dataValidation>
   </dataValidations>
@@ -12152,10 +14327,39 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K144" r:id="rId141"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K145" r:id="rId142"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K146" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K147" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K148" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K149" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K150" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K151" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K152" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K153" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K154" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K155" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K156" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K157" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K158" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K159" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K160" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K161" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K162" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K163" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K164" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K165" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K166" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K167" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K168" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K169" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K170" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K171" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K172" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K173" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K174" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K175" r:id="rId172"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId144"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId173"/>
   </tableParts>
 </worksheet>
 </file>
@@ -30882,7 +33086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -30961,56 +33165,56 @@
     <row r="4" ht="42" customHeight="1">
       <c r="A4" s="106" t="inlineStr">
         <is>
-          <t>2026-07-28T01:34:11+09:00</t>
+          <t>2026-07-28T01:39:30+09:00</t>
         </is>
       </c>
       <c r="B4" s="108" t="n">
-        <v>252</v>
+        <v>8</v>
       </c>
       <c r="C4" s="108" t="n">
-        <v>232</v>
+        <v>7</v>
       </c>
       <c r="D4" s="108" t="n">
+        <v>29</v>
+      </c>
+      <c r="E4" s="108" t="n">
+        <v>51</v>
+      </c>
+      <c r="F4" s="108" t="n">
         <v>1</v>
       </c>
-      <c r="E4" s="108" t="n">
-        <v>490</v>
-      </c>
-      <c r="F4" s="108" t="n">
-        <v>20</v>
-      </c>
       <c r="G4" s="108" t="n">
-        <v>241.51</v>
+        <v>253.27</v>
       </c>
       <c r="H4" s="60" t="inlineStr">
         <is>
-          <t>Daily update</t>
+          <t>Historical backfill: policy 365d / technology 183d</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="106" t="inlineStr">
         <is>
-          <t>2026-07-27T23:37:06+09:00</t>
+          <t>2026-07-28T01:34:11+09:00</t>
         </is>
       </c>
       <c r="B5" s="108" t="n">
         <v>252</v>
       </c>
       <c r="C5" s="108" t="n">
-        <v>199</v>
+        <v>232</v>
       </c>
       <c r="D5" s="108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" s="108" t="n">
-        <v>440</v>
+        <v>490</v>
       </c>
       <c r="F5" s="108" t="n">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="G5" s="108" t="n">
-        <v>856.75</v>
+        <v>241.51</v>
       </c>
       <c r="H5" s="60" t="inlineStr">
         <is>
@@ -31021,26 +33225,26 @@
     <row r="6">
       <c r="A6" s="106" t="inlineStr">
         <is>
-          <t>2026-07-27T23:07:45+09:00</t>
+          <t>2026-07-27T23:37:06+09:00</t>
         </is>
       </c>
       <c r="B6" s="108" t="n">
         <v>252</v>
       </c>
       <c r="C6" s="108" t="n">
-        <v>228</v>
+        <v>199</v>
       </c>
       <c r="D6" s="108" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E6" s="108" t="n">
-        <v>466</v>
+        <v>440</v>
       </c>
       <c r="F6" s="108" t="n">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="G6" s="108" t="n">
-        <v>819.04</v>
+        <v>856.75</v>
       </c>
       <c r="H6" s="60" t="inlineStr">
         <is>
@@ -31051,26 +33255,26 @@
     <row r="7">
       <c r="A7" s="106" t="inlineStr">
         <is>
-          <t>2026-07-27T20:03:17+09:00</t>
+          <t>2026-07-27T23:07:45+09:00</t>
         </is>
       </c>
       <c r="B7" s="108" t="n">
         <v>252</v>
       </c>
       <c r="C7" s="108" t="n">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D7" s="108" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E7" s="108" t="n">
-        <v>493</v>
+        <v>466</v>
       </c>
       <c r="F7" s="108" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G7" s="108" t="n">
-        <v>762.3200000000001</v>
+        <v>819.04</v>
       </c>
       <c r="H7" s="60" t="inlineStr">
         <is>
@@ -31081,7 +33285,7 @@
     <row r="8">
       <c r="A8" s="106" t="inlineStr">
         <is>
-          <t>2026-07-27T19:18:32+09:00</t>
+          <t>2026-07-27T20:03:17+09:00</t>
         </is>
       </c>
       <c r="B8" s="108" t="n">
@@ -31091,16 +33295,16 @@
         <v>226</v>
       </c>
       <c r="D8" s="108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" s="108" t="n">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="F8" s="108" t="n">
         <v>26</v>
       </c>
       <c r="G8" s="108" t="n">
-        <v>2017.45</v>
+        <v>762.3200000000001</v>
       </c>
       <c r="H8" s="60" t="inlineStr">
         <is>
@@ -31111,26 +33315,26 @@
     <row r="9">
       <c r="A9" s="106" t="inlineStr">
         <is>
-          <t>2026-07-27T18:40:11+09:00</t>
+          <t>2026-07-27T19:18:32+09:00</t>
         </is>
       </c>
       <c r="B9" s="108" t="n">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C9" s="108" t="n">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D9" s="108" t="n">
         <v>0</v>
       </c>
       <c r="E9" s="108" t="n">
-        <v>471</v>
+        <v>492</v>
       </c>
       <c r="F9" s="108" t="n">
         <v>26</v>
       </c>
       <c r="G9" s="108" t="n">
-        <v>1984.46</v>
+        <v>2017.45</v>
       </c>
       <c r="H9" s="60" t="inlineStr">
         <is>
@@ -31141,67 +33345,67 @@
     <row r="10">
       <c r="A10" s="106" t="inlineStr">
         <is>
-          <t>2026-07-27T11:51:54+09:00</t>
+          <t>2026-07-27T18:40:11+09:00</t>
         </is>
       </c>
       <c r="B10" s="108" t="n">
-        <v>347</v>
+        <v>253</v>
       </c>
       <c r="C10" s="108" t="n">
-        <v>263</v>
+        <v>227</v>
       </c>
       <c r="D10" s="108" t="n">
         <v>0</v>
       </c>
       <c r="E10" s="108" t="n">
-        <v>1087</v>
+        <v>471</v>
       </c>
       <c r="F10" s="108" t="n">
-        <v>84</v>
+        <v>26</v>
       </c>
       <c r="G10" s="108" t="n">
-        <v>4784.36</v>
+        <v>1984.46</v>
       </c>
       <c r="H10" s="60" t="inlineStr">
         <is>
-          <t>Historical backfill: policy 365d / technology 183d</t>
+          <t>Daily update</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="106" t="inlineStr">
         <is>
-          <t>2026-07-27T07:11:33+09:00</t>
+          <t>2026-07-27T11:51:54+09:00</t>
         </is>
       </c>
       <c r="B11" s="108" t="n">
-        <v>89</v>
+        <v>347</v>
       </c>
       <c r="C11" s="108" t="n">
-        <v>76</v>
+        <v>263</v>
       </c>
       <c r="D11" s="108" t="n">
         <v>0</v>
       </c>
       <c r="E11" s="108" t="n">
-        <v>187</v>
+        <v>1087</v>
       </c>
       <c r="F11" s="108" t="n">
-        <v>13</v>
+        <v>84</v>
       </c>
       <c r="G11" s="108" t="n">
-        <v>1975.42</v>
+        <v>4784.36</v>
       </c>
       <c r="H11" s="60" t="inlineStr">
         <is>
-          <t>Daily update</t>
+          <t>Historical backfill: policy 365d / technology 183d</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="106" t="inlineStr">
         <is>
-          <t>2026-07-27T06:32:05+09:00</t>
+          <t>2026-07-27T07:11:33+09:00</t>
         </is>
       </c>
       <c r="B12" s="108" t="n">
@@ -31214,13 +33418,13 @@
         <v>0</v>
       </c>
       <c r="E12" s="108" t="n">
-        <v>115</v>
+        <v>187</v>
       </c>
       <c r="F12" s="108" t="n">
         <v>13</v>
       </c>
       <c r="G12" s="108" t="n">
-        <v>1988.98</v>
+        <v>1975.42</v>
       </c>
       <c r="H12" s="60" t="inlineStr">
         <is>
@@ -31231,26 +33435,26 @@
     <row r="13">
       <c r="A13" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T22:54:37+09:00</t>
+          <t>2026-07-27T06:32:05+09:00</t>
         </is>
       </c>
       <c r="B13" s="108" t="n">
-        <v>55</v>
+        <v>89</v>
       </c>
       <c r="C13" s="108" t="n">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="D13" s="108" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E13" s="108" t="n">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="F13" s="108" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G13" s="108" t="n">
-        <v>3379.75</v>
+        <v>1988.98</v>
       </c>
       <c r="H13" s="60" t="inlineStr">
         <is>
@@ -31261,26 +33465,26 @@
     <row r="14">
       <c r="A14" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T22:13:31+09:00</t>
+          <t>2026-07-26T22:54:37+09:00</t>
         </is>
       </c>
       <c r="B14" s="108" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="C14" s="108" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="D14" s="108" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E14" s="108" t="n">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F14" s="108" t="n">
         <v>10</v>
       </c>
       <c r="G14" s="108" t="n">
-        <v>1655.72</v>
+        <v>3379.75</v>
       </c>
       <c r="H14" s="60" t="inlineStr">
         <is>
@@ -31291,127 +33495,127 @@
     <row r="15">
       <c r="A15" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T21:45:54+09:00</t>
+          <t>2026-07-26T22:13:31+09:00</t>
         </is>
       </c>
       <c r="B15" s="108" t="n">
-        <v>128</v>
+        <v>47</v>
       </c>
       <c r="C15" s="108" t="n">
-        <v>73</v>
+        <v>37</v>
       </c>
       <c r="D15" s="108" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E15" s="108" t="n">
-        <v>603</v>
+        <v>124</v>
       </c>
       <c r="F15" s="108" t="n">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="G15" s="108" t="n">
-        <v>1492.56</v>
+        <v>1655.72</v>
       </c>
       <c r="H15" s="60" t="inlineStr">
         <is>
-          <t>Historical backfill: policy 365d / technology 183d</t>
+          <t>Daily update</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T21:29:09+09:00</t>
+          <t>2026-07-26T21:45:54+09:00</t>
         </is>
       </c>
       <c r="B16" s="108" t="n">
-        <v>41</v>
+        <v>128</v>
       </c>
       <c r="C16" s="108" t="n">
-        <v>31</v>
+        <v>73</v>
       </c>
       <c r="D16" s="108" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E16" s="108" t="n">
-        <v>76</v>
+        <v>603</v>
       </c>
       <c r="F16" s="108" t="n">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="G16" s="108" t="n">
-        <v>832.08</v>
+        <v>1492.56</v>
       </c>
       <c r="H16" s="60" t="inlineStr">
         <is>
-          <t>Daily update</t>
+          <t>Historical backfill: policy 365d / technology 183d</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T21:02:36+09:00</t>
+          <t>2026-07-26T21:29:09+09:00</t>
         </is>
       </c>
       <c r="B17" s="108" t="n">
-        <v>108</v>
+        <v>41</v>
       </c>
       <c r="C17" s="108" t="n">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="D17" s="108" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E17" s="108" t="n">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="F17" s="108" t="n">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="G17" s="108" t="n">
-        <v>1376.15</v>
+        <v>832.08</v>
       </c>
       <c r="H17" s="60" t="inlineStr">
         <is>
-          <t>Historical backfill: policy 365d / technology 183d</t>
+          <t>Daily update</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T20:36:29+09:00</t>
+          <t>2026-07-26T21:02:36+09:00</t>
         </is>
       </c>
       <c r="B18" s="108" t="n">
-        <v>38</v>
+        <v>108</v>
       </c>
       <c r="C18" s="108" t="n">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="D18" s="108" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="E18" s="108" t="n">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="F18" s="108" t="n">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="G18" s="108" t="n">
-        <v>93.7</v>
+        <v>1376.15</v>
       </c>
       <c r="H18" s="60" t="inlineStr">
         <is>
-          <t>Daily update</t>
+          <t>Historical backfill: policy 365d / technology 183d</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T20:34:08+09:00</t>
+          <t>2026-07-26T20:36:29+09:00</t>
         </is>
       </c>
       <c r="B19" s="108" t="n">
@@ -31421,7 +33625,7 @@
         <v>28</v>
       </c>
       <c r="D19" s="108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19" s="108" t="n">
         <v>74</v>
@@ -31430,7 +33634,7 @@
         <v>10</v>
       </c>
       <c r="G19" s="108" t="n">
-        <v>20.27</v>
+        <v>93.7</v>
       </c>
       <c r="H19" s="60" t="inlineStr">
         <is>
@@ -31441,7 +33645,7 @@
     <row r="20">
       <c r="A20" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T20:29:40+09:00</t>
+          <t>2026-07-26T20:34:08+09:00</t>
         </is>
       </c>
       <c r="B20" s="108" t="n">
@@ -31451,16 +33655,16 @@
         <v>28</v>
       </c>
       <c r="D20" s="108" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E20" s="108" t="n">
-        <v>11</v>
+        <v>74</v>
       </c>
       <c r="F20" s="108" t="n">
         <v>10</v>
       </c>
       <c r="G20" s="108" t="n">
-        <v>141.79</v>
+        <v>20.27</v>
       </c>
       <c r="H20" s="60" t="inlineStr">
         <is>
@@ -31471,7 +33675,7 @@
     <row r="21">
       <c r="A21" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T20:24:57+09:00</t>
+          <t>2026-07-26T20:29:40+09:00</t>
         </is>
       </c>
       <c r="B21" s="108" t="n">
@@ -31481,16 +33685,16 @@
         <v>28</v>
       </c>
       <c r="D21" s="108" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E21" s="108" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="F21" s="108" t="n">
         <v>10</v>
       </c>
       <c r="G21" s="108" t="n">
-        <v>134.95</v>
+        <v>141.79</v>
       </c>
       <c r="H21" s="60" t="inlineStr">
         <is>
@@ -31501,7 +33705,7 @@
     <row r="22">
       <c r="A22" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T20:19:15+09:00</t>
+          <t>2026-07-26T20:24:57+09:00</t>
         </is>
       </c>
       <c r="B22" s="108" t="n">
@@ -31511,16 +33715,16 @@
         <v>28</v>
       </c>
       <c r="D22" s="108" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E22" s="108" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F22" s="108" t="n">
         <v>10</v>
       </c>
       <c r="G22" s="108" t="n">
-        <v>134.05</v>
+        <v>134.95</v>
       </c>
       <c r="H22" s="60" t="inlineStr">
         <is>
@@ -31531,26 +33735,26 @@
     <row r="23">
       <c r="A23" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T20:13:43+09:00</t>
+          <t>2026-07-26T20:19:15+09:00</t>
         </is>
       </c>
       <c r="B23" s="108" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C23" s="108" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D23" s="108" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E23" s="108" t="n">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="F23" s="108" t="n">
         <v>10</v>
       </c>
       <c r="G23" s="108" t="n">
-        <v>162.46</v>
+        <v>134.05</v>
       </c>
       <c r="H23" s="60" t="inlineStr">
         <is>
@@ -31561,7 +33765,7 @@
     <row r="24">
       <c r="A24" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T20:00:03+09:00</t>
+          <t>2026-07-26T20:13:43+09:00</t>
         </is>
       </c>
       <c r="B24" s="108" t="n">
@@ -31571,16 +33775,16 @@
         <v>24</v>
       </c>
       <c r="D24" s="108" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E24" s="108" t="n">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="F24" s="108" t="n">
         <v>10</v>
       </c>
       <c r="G24" s="108" t="n">
-        <v>154.27</v>
+        <v>162.46</v>
       </c>
       <c r="H24" s="60" t="inlineStr">
         <is>
@@ -31591,7 +33795,7 @@
     <row r="25">
       <c r="A25" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T19:51:39+09:00</t>
+          <t>2026-07-26T20:00:03+09:00</t>
         </is>
       </c>
       <c r="B25" s="108" t="n">
@@ -31601,16 +33805,16 @@
         <v>24</v>
       </c>
       <c r="D25" s="108" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E25" s="108" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="F25" s="108" t="n">
         <v>10</v>
       </c>
       <c r="G25" s="108" t="n">
-        <v>11.55</v>
+        <v>154.27</v>
       </c>
       <c r="H25" s="60" t="inlineStr">
         <is>
@@ -31621,26 +33825,26 @@
     <row r="26">
       <c r="A26" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T19:10:55+09:00</t>
+          <t>2026-07-26T19:51:39+09:00</t>
         </is>
       </c>
       <c r="B26" s="108" t="n">
         <v>34</v>
       </c>
       <c r="C26" s="108" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D26" s="108" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E26" s="108" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F26" s="108" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G26" s="108" t="n">
-        <v>194.65</v>
+        <v>11.55</v>
       </c>
       <c r="H26" s="60" t="inlineStr">
         <is>
@@ -31651,26 +33855,26 @@
     <row r="27">
       <c r="A27" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T19:05:06+09:00</t>
+          <t>2026-07-26T19:10:55+09:00</t>
         </is>
       </c>
       <c r="B27" s="108" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C27" s="108" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D27" s="108" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E27" s="108" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="F27" s="108" t="n">
         <v>9</v>
       </c>
       <c r="G27" s="108" t="n">
-        <v>165.89</v>
+        <v>194.65</v>
       </c>
       <c r="H27" s="60" t="inlineStr">
         <is>
@@ -31681,35 +33885,65 @@
     <row r="28">
       <c r="A28" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T19:05:06+09:00</t>
         </is>
       </c>
       <c r="B28" s="108" t="n">
         <v>33</v>
       </c>
       <c r="C28" s="108" t="n">
+        <v>24</v>
+      </c>
+      <c r="D28" s="108" t="n">
+        <v>5</v>
+      </c>
+      <c r="E28" s="108" t="n">
+        <v>39</v>
+      </c>
+      <c r="F28" s="108" t="n">
+        <v>9</v>
+      </c>
+      <c r="G28" s="108" t="n">
+        <v>165.89</v>
+      </c>
+      <c r="H28" s="60" t="inlineStr">
+        <is>
+          <t>Daily update</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="106" t="inlineStr">
+        <is>
+          <t>2026-07-26T18:56:03+09:00</t>
+        </is>
+      </c>
+      <c r="B29" s="108" t="n">
+        <v>33</v>
+      </c>
+      <c r="C29" s="108" t="n">
         <v>20</v>
       </c>
-      <c r="D28" s="108" t="n">
+      <c r="D29" s="108" t="n">
         <v>94</v>
       </c>
-      <c r="E28" s="108" t="n">
+      <c r="E29" s="108" t="n">
         <v>0</v>
       </c>
-      <c r="F28" s="108" t="n">
+      <c r="F29" s="108" t="n">
         <v>13</v>
       </c>
-      <c r="G28" s="108" t="n">
+      <c r="G29" s="108" t="n">
         <v>129.43</v>
       </c>
-      <c r="H28" s="60" t="inlineStr">
+      <c r="H29" s="60" t="inlineStr">
         <is>
           <t>Initial lookback</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:H28"/>
+  <autoFilter ref="A3:H29"/>
   <mergeCells count="2">
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>

--- a/docs/innovation_news_ledger.xlsx
+++ b/docs/innovation_news_ledger.xlsx
@@ -9,9 +9,9 @@
     <sheet name="Run Log" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'News Ledger'!$A$3:$O$175</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'News Ledger'!$A$3:$O$148</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Source Registry'!$A$3:$N$263</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Run Log'!$A$3:$H$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Run Log'!$A$3:$H$30</definedName>
   </definedNames>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -620,7 +620,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="NewsLedgerTable" displayName="NewsLedgerTable" ref="A3:O175" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="NewsLedgerTable" displayName="NewsLedgerTable" ref="A3:O148" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <autoFilter ref="A3:O4"/>
   <tableColumns count="15">
     <tableColumn id="1" name="Collected At (JST)"/>
@@ -667,7 +667,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="RunLogTable" displayName="RunLogTable" ref="A3:H29" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="RunLogTable" displayName="RunLogTable" ref="A3:H30" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <autoFilter ref="A3:H4"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Run Time (JST)"/>
@@ -951,7 +951,7 @@
       </c>
       <c r="B5" s="25" t="inlineStr">
         <is>
-          <t>2026-07-28T01:39:30+09:00</t>
+          <t>2026-07-28T01:46:34+09:00</t>
         </is>
       </c>
       <c r="C5" s="46" t="n"/>
@@ -1239,7 +1239,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O175"/>
+  <dimension ref="A1:O148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -7006,12 +7006,12 @@
       </c>
       <c r="I79" s="60" t="inlineStr">
         <is>
-          <t>特許付与プロセスが2027年4月1日から完全デジタル化</t>
+          <t>2027年4月1日から特許付与プロセスが完全デジタル化</t>
         </is>
       </c>
       <c r="J79" s="60" t="inlineStr">
         <is>
-          <t>EPOは、ユーザーとの密接な協力のもとで数年間のデジタル変革を経て、特許のデジタル申請と通知を義務化する準備を進めている。</t>
+          <t>数年にわたるデジタルトランスフォーメーションの後、EPOはデジタル提出と通知を義務化する準備を進めている。</t>
         </is>
       </c>
       <c r="K79" s="60" t="inlineStr">
@@ -7036,7 +7036,7 @@
       </c>
       <c r="O79" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: Patents &amp; Intellectual Property / 学術区分: News &amp; Official Release / 焦点: 特許のデジタル申請および通知の義務化</t>
+          <t>枠: Innovation Policy / 政策分野: Patents &amp; Intellectual Property / 学術区分: News &amp; Official Release / 焦点: 特許付与プロセスのデジタル化</t>
         </is>
       </c>
     </row>
@@ -7063,40 +7063,40 @@
       </c>
       <c r="E80" s="60" t="inlineStr">
         <is>
-          <t>Robotics</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="F80" s="107" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G80" s="60" t="inlineStr">
         <is>
-          <t>Journal Article</t>
+          <t>Preprint</t>
         </is>
       </c>
       <c r="H80" s="60" t="inlineStr">
         <is>
-          <t>Science Advances</t>
+          <t>Zenodo (CERN European Organization for Nuclear Research)</t>
         </is>
       </c>
       <c r="I80" s="60" t="inlineStr">
         <is>
-          <t>自己探求によるロボットの行動と言語の発展</t>
+          <t>Prim-Lex理論と量子技術ガバナンス：キュービットから量子主権へ</t>
         </is>
       </c>
       <c r="J80" s="60" t="inlineStr">
         <is>
-          <t>ロボットが自己探求を通じて行動と言語を学ぶ過程を探る研究が行われた。</t>
+          <t>量子技術のガバナンスに関する研究を扱ったプレプリントです。</t>
         </is>
       </c>
       <c r="K80" s="60" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1126/sciadv.aee7533</t>
+          <t>https://doi.org/10.5281/zenodo.21512028</t>
         </is>
       </c>
       <c r="L80" s="60" t="inlineStr">
         <is>
-          <t>c833fd421c298cf895263644</t>
+          <t>61f1fcfb9afff652f523d019</t>
         </is>
       </c>
       <c r="M80" s="106" t="inlineStr">
@@ -7111,34 +7111,34 @@
       </c>
       <c r="O80" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: Journal Article / 査読表示: Journal record — confirm peer review on publisher page / 掲載誌・学会: Science Advances / 焦点: ロボットの自己探求による行動と言語の発展 / OpenAlex record; work type=article; citations=1</t>
+          <t>枠: Technology Innovation | Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: Preprint / 査読表示: Not peer reviewed / 掲載誌・学会: Zenodo (CERN European Organization for Nuclear Research) / 焦点: 量子技術のガバナンス / OpenAlex record; work type=preprint; citations=0</t>
         </is>
       </c>
     </row>
     <row r="81" ht="42" customHeight="1">
       <c r="A81" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T21:29:09+09:00</t>
+          <t>2026-07-26T20:29:40+09:00</t>
         </is>
       </c>
       <c r="B81" s="106" t="inlineStr">
         <is>
-          <t>2026-07-23T00:00:00Z</t>
+          <t>2026-07-22T14:12:14Z</t>
         </is>
       </c>
       <c r="C81" s="60" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D81" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E81" s="60" t="inlineStr">
         <is>
-          <t>Robotics | Artificial Intelligence</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="F81" s="107" t="n">
@@ -7146,37 +7146,37 @@
       </c>
       <c r="G81" s="60" t="inlineStr">
         <is>
-          <t>Journal Article</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H81" s="60" t="inlineStr">
         <is>
-          <t>Frontiers in Neurorobotics</t>
+          <t>DOE Office of Science News</t>
         </is>
       </c>
       <c r="I81" s="60" t="inlineStr">
         <is>
-          <t>AI駆動の四足ロボット：基本的な移動から高度な生物模倣行動まで</t>
+          <t>エネルギー長官クリス・ライトがAI駆動の科学的発見を加速するための最初のジェネシスミッションプロジェクトを発表</t>
         </is>
       </c>
       <c r="J81" s="60" t="inlineStr">
         <is>
-          <t>四足ロボットの技術開発に関する文献レビューが行われ、AIの進展がその能力を拡張していることが示された。</t>
+          <t>エネルギー長官クリス・ライトは、全米50州からの歴史的なRFA応答から選ばれた約300のプロジェクトを発表し、エネルギー、発見科学、国家安全保障におけるブレークスルーを加速することを目指している。</t>
         </is>
       </c>
       <c r="K81" s="60" t="inlineStr">
         <is>
-          <t>https://doi.org/10.3389/fnbot.2026.1855550</t>
+          <t>https://www.energy.gov/articles/secretary-energy-chris-wright-announces-first-genesis-mission-projects-selected-accelerate</t>
         </is>
       </c>
       <c r="L81" s="60" t="inlineStr">
         <is>
-          <t>e165800add9d682af8ea2122</t>
+          <t>23fa1d6907c14d73ce3a41cd</t>
         </is>
       </c>
       <c r="M81" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T21:29:09+09:00</t>
+          <t>2026-07-26T20:29:40+09:00</t>
         </is>
       </c>
       <c r="N81" s="60" t="inlineStr">
@@ -7186,72 +7186,72 @@
       </c>
       <c r="O81" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: Journal Article / 査読表示: Journal record — confirm peer review on publisher page / 掲載誌・学会: Frontiers in Neurorobotics / 焦点: AI駆動の四足ロボット / OpenAlex record; work type=article; citations=0</t>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: AIを用いた科学的発見の加速</t>
         </is>
       </c>
     </row>
     <row r="82" ht="42" customHeight="1">
       <c r="A82" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T21:29:09+09:00</t>
+          <t>2026-07-26T19:05:06+09:00</t>
         </is>
       </c>
       <c r="B82" s="106" t="inlineStr">
         <is>
-          <t>2026-07-23T00:00:00Z</t>
+          <t>2026-07-22T13:53:19Z</t>
         </is>
       </c>
       <c r="C82" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D82" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E82" s="60" t="inlineStr">
         <is>
-          <t>Fusion Energy</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="F82" s="107" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G82" s="60" t="inlineStr">
         <is>
-          <t>Journal Article</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H82" s="60" t="inlineStr">
         <is>
-          <t>Nuclear Fusion</t>
+          <t>National Science Foundation News</t>
         </is>
       </c>
       <c r="I82" s="60" t="inlineStr">
         <is>
-          <t>Wendelstein 7-Xにおける高速イオンの閉じ込めにおける放射電場の役割</t>
+          <t>NSF長官補のブライアン・ストーンによるAI優先事項推進に関する声明</t>
         </is>
       </c>
       <c r="J82" s="60" t="inlineStr">
         <is>
-          <t>Wendelstein 7-Xにおける高速イオンの閉じ込めに関する研究が行われ、放射電場の影響が分析された。</t>
+          <t>米国科学財団の長官補ブライアン・ストーンが、ホワイトハウスやエネルギー省と連携し、AIに関する行政の優先事項を推進することを発表。</t>
         </is>
       </c>
       <c r="K82" s="60" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1088/1741-4326/ae8f55</t>
+          <t>https://www.nsf.gov/news/statement-nsf-chief-staff-brian-stone-performing-duties-nsf-1</t>
         </is>
       </c>
       <c r="L82" s="60" t="inlineStr">
         <is>
-          <t>eef01d292bfb6d5bb3537528</t>
+          <t>123e2207578ca69c8f9c00a2</t>
         </is>
       </c>
       <c r="M82" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T21:29:09+09:00</t>
+          <t>2026-07-26T19:05:06+09:00</t>
         </is>
       </c>
       <c r="N82" s="60" t="inlineStr">
@@ -7261,72 +7261,72 @@
       </c>
       <c r="O82" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: Journal Article / 査読表示: Journal record — confirm peer review on publisher page / 掲載誌・学会: Nuclear Fusion / 焦点: Wendelstein 7-Xの高速イオンの閉じ込め / OpenAlex record; work type=article; citations=0</t>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: AI政策の推進</t>
         </is>
       </c>
     </row>
     <row r="83" ht="42" customHeight="1">
       <c r="A83" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T21:29:09+09:00</t>
+          <t>2026-07-26T19:05:06+09:00</t>
         </is>
       </c>
       <c r="B83" s="106" t="inlineStr">
         <is>
-          <t>2026-07-23T00:00:00Z</t>
+          <t>2026-07-22T13:53:12Z</t>
         </is>
       </c>
       <c r="C83" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D83" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E83" s="60" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="F83" s="107" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G83" s="60" t="inlineStr">
         <is>
-          <t>Journal Article</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H83" s="60" t="inlineStr">
         <is>
-          <t>Scientific Reports</t>
+          <t>National Science Foundation News</t>
         </is>
       </c>
       <c r="I83" s="60" t="inlineStr">
         <is>
-          <t>密なプラズマフォーカスにおけるクーロン爆発の研究</t>
+          <t>新しいNSFイニシアティブがAIによる科学的発見のためのデータセット価値を解放</t>
         </is>
       </c>
       <c r="J83" s="60" t="inlineStr">
         <is>
-          <t>密なプラズマフォーカスにおけるクーロン爆発のシミュレーション研究が行われ、極端な条件下での挙動が分析された。</t>
+          <t>米国国立科学財団は、AIを活用した科学的発見のためのデータセット価値を解放するプログラムを発表し、科学コミュニティのデータセットを進展させるための新たな投資を行う。</t>
         </is>
       </c>
       <c r="K83" s="60" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1038/s41598-026-63204-9</t>
+          <t>https://www.nsf.gov/news/new-nsf-initiative-aims-unlock-dataset-value-ai-enabled</t>
         </is>
       </c>
       <c r="L83" s="60" t="inlineStr">
         <is>
-          <t>fcf607380491b3f6666abab6</t>
+          <t>dcd819527d9b80141b26bcb8</t>
         </is>
       </c>
       <c r="M83" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T21:29:09+09:00</t>
+          <t>2026-07-26T19:05:06+09:00</t>
         </is>
       </c>
       <c r="N83" s="60" t="inlineStr">
@@ -7336,34 +7336,34 @@
       </c>
       <c r="O83" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: Journal Article / 査読表示: Journal record — confirm peer review on publisher page / 掲載誌・学会: Scientific Reports / 焦点: 密なプラズマフォーカスにおけるクーロン爆発の研究 / OpenAlex record; work type=article; citations=0</t>
+          <t>枠: Innovation Policy / 政策分野: R&amp;D Funding &amp; Tax Incentives / 学術区分: News &amp; Official Release / 焦点: AIを活用した科学的発見のためのデータセット</t>
         </is>
       </c>
     </row>
     <row r="84" ht="42" customHeight="1">
       <c r="A84" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T21:29:09+09:00</t>
+          <t>2026-07-26T20:29:40+09:00</t>
         </is>
       </c>
       <c r="B84" s="106" t="inlineStr">
         <is>
-          <t>2026-07-23T00:00:00Z</t>
+          <t>2026-07-22T13:53:06Z</t>
         </is>
       </c>
       <c r="C84" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D84" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E84" s="60" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="F84" s="107" t="n">
@@ -7371,37 +7371,37 @@
       </c>
       <c r="G84" s="60" t="inlineStr">
         <is>
-          <t>Preprint</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H84" s="60" t="inlineStr">
         <is>
-          <t>Zenodo (CERN European Organization for Nuclear Research)</t>
+          <t>National Science Foundation News</t>
         </is>
       </c>
       <c r="I84" s="60" t="inlineStr">
         <is>
-          <t>プライム・レックス理論と量子技術ガバナンス：キュービットから量子主権へ</t>
+          <t>NSFがAI駆動の科学を進展させるために8300万ドルの投資を発表</t>
         </is>
       </c>
       <c r="J84" s="60" t="inlineStr">
         <is>
-          <t>OECDが採択した量子技術に関する提言を基に、量子技術のガバナンスの枠組みを構築する方法を探求した。</t>
+          <t>米国国立科学財団は、AI駆動の科学を進展させるために8300万ドルの投資を発表しました。</t>
         </is>
       </c>
       <c r="K84" s="60" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5281/zenodo.21512028</t>
+          <t>https://www.nsf.gov/news/nsf-announces-83m-investment-integrated-data-systems</t>
         </is>
       </c>
       <c r="L84" s="60" t="inlineStr">
         <is>
-          <t>61f1fcfb9afff652f523d019</t>
+          <t>018d40b7e6eb7aa4b8cfb5fa</t>
         </is>
       </c>
       <c r="M84" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T21:29:09+09:00</t>
+          <t>2026-07-26T20:29:40+09:00</t>
         </is>
       </c>
       <c r="N84" s="60" t="inlineStr">
@@ -7411,72 +7411,72 @@
       </c>
       <c r="O84" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation | Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: Preprint / 査読表示: Not peer reviewed / 掲載誌・学会: Zenodo (CERN European Organization for Nuclear Research) / 焦点: 量子技術のガバナンスとOECDの提言 / OpenAlex record; work type=preprint; citations=0</t>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy | Research System &amp; Talent / 学術区分: News &amp; Official Release / 焦点: AI駆動の科学のためのデータシステム</t>
         </is>
       </c>
     </row>
     <row r="85" ht="42" customHeight="1">
       <c r="A85" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T20:29:40+09:00</t>
+          <t>2026-07-28T01:39:30+09:00</t>
         </is>
       </c>
       <c r="B85" s="106" t="inlineStr">
         <is>
-          <t>2026-07-22T14:12:14Z</t>
+          <t>2026-07-22T13:18:55Z</t>
         </is>
       </c>
       <c r="C85" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="D85" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="E85" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Fusion Energy</t>
         </is>
       </c>
       <c r="F85" s="107" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G85" s="60" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Industry Association</t>
         </is>
       </c>
       <c r="H85" s="60" t="inlineStr">
         <is>
-          <t>DOE Office of Science News</t>
+          <t>Fusion Industry Association</t>
         </is>
       </c>
       <c r="I85" s="60" t="inlineStr">
         <is>
-          <t>エネルギー長官がAI駆動の科学的発見を加速するプロジェクトを発表</t>
+          <t>韓国、世界最大の核融合炉ITERの核心部品を完成</t>
         </is>
       </c>
       <c r="J85" s="60" t="inlineStr">
         <is>
-          <t>エネルギー長官クリス・ライトが、全米から選ばれた300のプロジェクトを発表し、エネルギーや発見科学、国家安全保障の分野でのブレークスルーを促進する。</t>
+          <t>韓国は、世界最大の核融合プロジェクトであるITERの最終反応器コンポーネントの製造と設置を完了しました。この成果は、核融合技術と大規模な先進製造における国の専門性の向上を示しています。</t>
         </is>
       </c>
       <c r="K85" s="60" t="inlineStr">
         <is>
-          <t>https://www.energy.gov/articles/secretary-energy-chris-wright-announces-first-genesis-mission-projects-selected-accelerate</t>
+          <t>https://www.asiae.co.kr/en/article/science/2026072213475928139?mc_cid=ed1acc7bef&amp;mc_eid=01cd8fe465#new_tab&amp;utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=korea-completes-core-of-worlds-largest-fusion-reactor-iter</t>
         </is>
       </c>
       <c r="L85" s="60" t="inlineStr">
         <is>
-          <t>23fa1d6907c14d73ce3a41cd</t>
+          <t>55b5e71d5f2f13411a2b039b</t>
         </is>
       </c>
       <c r="M85" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T20:29:40+09:00</t>
+          <t>2026-07-28T01:39:30+09:00</t>
         </is>
       </c>
       <c r="N85" s="60" t="inlineStr">
@@ -7486,29 +7486,29 @@
       </c>
       <c r="O85" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: AI駆動の科学的発見を加速するプロジェクト</t>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: 核融合技術</t>
         </is>
       </c>
     </row>
     <row r="86" ht="42" customHeight="1">
       <c r="A86" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T19:05:06+09:00</t>
+          <t>2026-07-26T21:02:36+09:00</t>
         </is>
       </c>
       <c r="B86" s="106" t="inlineStr">
         <is>
-          <t>2026-07-22T13:53:19Z</t>
+          <t>2026-07-22T05:00:56Z</t>
         </is>
       </c>
       <c r="C86" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="D86" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="E86" s="60" t="inlineStr">
@@ -7526,32 +7526,32 @@
       </c>
       <c r="H86" s="60" t="inlineStr">
         <is>
-          <t>National Science Foundation News</t>
+          <t>NISTEP Updates</t>
         </is>
       </c>
       <c r="I86" s="60" t="inlineStr">
         <is>
-          <t>NSFがAI優先事項の推進に関する声明を発表</t>
+          <t>特定科学技術領域動向報告書 -AI（人工知能）- 研究開発インプット編を公表</t>
         </is>
       </c>
       <c r="J86" s="60" t="inlineStr">
         <is>
-          <t>米国国家科学財団が、ホワイトハウスの科学技術政策室やエネルギー省と連携し、AIに関する優先事項を進めることを発表した。</t>
+          <t>人工知能（AI）の研究開発インプット状況を分析し、我が国のAI分野における科学技術政策に資する知見を提供する報告書を公表。</t>
         </is>
       </c>
       <c r="K86" s="60" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/news/statement-nsf-chief-staff-brian-stone-performing-duties-nsf-1</t>
+          <t>https://www.nistep.go.jp/archives/63583/</t>
         </is>
       </c>
       <c r="L86" s="60" t="inlineStr">
         <is>
-          <t>123e2207578ca69c8f9c00a2</t>
+          <t>6b6122461584a86ee7a1c595</t>
         </is>
       </c>
       <c r="M86" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T19:05:06+09:00</t>
+          <t>2026-07-22T14:00:56+09:00</t>
         </is>
       </c>
       <c r="N86" s="60" t="inlineStr">
@@ -7561,72 +7561,72 @@
       </c>
       <c r="O86" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: AI優先事項の推進</t>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: AI研究開発インプット状況</t>
         </is>
       </c>
     </row>
     <row r="87" ht="42" customHeight="1">
       <c r="A87" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T19:05:06+09:00</t>
+          <t>2026-07-26T21:02:36+09:00</t>
         </is>
       </c>
       <c r="B87" s="106" t="inlineStr">
         <is>
-          <t>2026-07-22T13:53:12Z</t>
+          <t>2026-07-22T00:00:00Z</t>
         </is>
       </c>
       <c r="C87" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D87" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="E87" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="F87" s="107" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G87" s="60" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Scientific Publication</t>
         </is>
       </c>
       <c r="H87" s="60" t="inlineStr">
         <is>
-          <t>National Science Foundation News</t>
+          <t>Nature</t>
         </is>
       </c>
       <c r="I87" s="60" t="inlineStr">
         <is>
-          <t>NSFがAIによる科学的発見のためのデータセット価値を解放する新プログラムを発表</t>
+          <t>量子パラエレクトリックSrTiO3におけるナノスケール極性テクスチャのイメージング</t>
         </is>
       </c>
       <c r="J87" s="60" t="inlineStr">
         <is>
-          <t>米国国立科学財団は、AIを活用した科学的発見のためのデータセット価値を解放するプログラムを発表しました。</t>
+          <t>Cryo-STEMを用いて、SrTiO3が105K以下で周期的な極性ナノドメインを形成することが明らかになった。</t>
         </is>
       </c>
       <c r="K87" s="60" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/news/new-nsf-initiative-aims-unlock-dataset-value-ai-enabled</t>
+          <t>https://www.nature.com/articles/s41586-026-10823-x</t>
         </is>
       </c>
       <c r="L87" s="60" t="inlineStr">
         <is>
-          <t>dcd819527d9b80141b26bcb8</t>
+          <t>f12f62aebb861877dd7a5cbf</t>
         </is>
       </c>
       <c r="M87" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T19:05:06+09:00</t>
+          <t>2026-07-22T09:00:00+09:00</t>
         </is>
       </c>
       <c r="N87" s="60" t="inlineStr">
@@ -7636,72 +7636,72 @@
       </c>
       <c r="O87" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: R&amp;D Funding &amp; Tax Incentives / 学術区分: News &amp; Official Release / 焦点: AIを活用した科学的発見のためのデータセット</t>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: 量子パラエレクトリックSrTiO3のナノスケール極性テクスチャのイメージング</t>
         </is>
       </c>
     </row>
     <row r="88" ht="42" customHeight="1">
       <c r="A88" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T20:29:40+09:00</t>
+          <t>2026-07-26T21:02:36+09:00</t>
         </is>
       </c>
       <c r="B88" s="106" t="inlineStr">
         <is>
-          <t>2026-07-22T13:53:06Z</t>
+          <t>2026-07-22T00:00:00Z</t>
         </is>
       </c>
       <c r="C88" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D88" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="E88" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="F88" s="107" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G88" s="60" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Scientific Publication</t>
         </is>
       </c>
       <c r="H88" s="60" t="inlineStr">
         <is>
-          <t>National Science Foundation News</t>
+          <t>Nature</t>
         </is>
       </c>
       <c r="I88" s="60" t="inlineStr">
         <is>
-          <t>NSFがAI駆動の科学を進展させるために8300万ドルの投資を発表</t>
+          <t>ブラウンブルヘッドキャットフィッシュのメラノーマは新しい伝染性がんを示す</t>
         </is>
       </c>
       <c r="J88" s="60" t="inlineStr">
         <is>
-          <t>米国国立科学財団は、AI駆動の科学を進展させるために8300万ドルの投資を発表しました。</t>
+          <t>ブラウンブルヘッドキャットフィッシュの腫瘍と非腫瘍組織の全ゲノム配列解析により、自然に発生する伝染性がんの一種が明らかになった。</t>
         </is>
       </c>
       <c r="K88" s="60" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/news/nsf-announces-83m-investment-integrated-data-systems</t>
+          <t>https://www.nature.com/articles/s41586-026-10828-6</t>
         </is>
       </c>
       <c r="L88" s="60" t="inlineStr">
         <is>
-          <t>018d40b7e6eb7aa4b8cfb5fa</t>
+          <t>3c774b8bd5e287725e43b3b5</t>
         </is>
       </c>
       <c r="M88" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T20:29:40+09:00</t>
+          <t>2026-07-22T09:00:00+09:00</t>
         </is>
       </c>
       <c r="N88" s="60" t="inlineStr">
@@ -7711,24 +7711,24 @@
       </c>
       <c r="O88" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy | Research System &amp; Talent / 学術区分: News &amp; Official Release / 焦点: AI駆動の科学のためのデータシステム</t>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: トランスミッシブルがんの発見</t>
         </is>
       </c>
     </row>
     <row r="89" ht="42" customHeight="1">
       <c r="A89" s="106" t="inlineStr">
         <is>
-          <t>2026-07-28T01:39:30+09:00</t>
+          <t>2026-07-26T21:02:36+09:00</t>
         </is>
       </c>
       <c r="B89" s="106" t="inlineStr">
         <is>
-          <t>2026-07-22T13:18:55Z</t>
+          <t>2026-07-22T00:00:00Z</t>
         </is>
       </c>
       <c r="C89" s="60" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D89" s="60" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="E89" s="60" t="inlineStr">
         <is>
-          <t>Fusion Energy</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="F89" s="107" t="n">
@@ -7746,37 +7746,37 @@
       </c>
       <c r="G89" s="60" t="inlineStr">
         <is>
-          <t>Industry Association</t>
+          <t>Scientific Publication</t>
         </is>
       </c>
       <c r="H89" s="60" t="inlineStr">
         <is>
-          <t>Fusion Industry Association</t>
+          <t>Nature</t>
         </is>
       </c>
       <c r="I89" s="60" t="inlineStr">
         <is>
-          <t>韓国、世界最大の核融合炉ITERの核心部品を完成</t>
+          <t>AIを使って数分でグラフィカルアブストラクトを作成する方法</t>
         </is>
       </c>
       <c r="J89" s="60" t="inlineStr">
         <is>
-          <t>韓国は、世界最大の核融合プロジェクトであるITERの最終反応器コンポーネントの製造と設置を完了しました。この成果は、核融合技術と大規模な先進製造における国の専門性の向上を示しています。</t>
+          <t>人工知能は、グラフィックデザインの経験がない人々にとって民主化の力となる。</t>
         </is>
       </c>
       <c r="K89" s="60" t="inlineStr">
         <is>
-          <t>https://www.asiae.co.kr/en/article/science/2026072213475928139?mc_cid=ed1acc7bef&amp;mc_eid=01cd8fe465#new_tab&amp;utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=korea-completes-core-of-worlds-largest-fusion-reactor-iter</t>
+          <t>https://www.nature.com/articles/d41586-026-02072-9</t>
         </is>
       </c>
       <c r="L89" s="60" t="inlineStr">
         <is>
-          <t>55b5e71d5f2f13411a2b039b</t>
+          <t>b2a4fe860295587fbfbde689</t>
         </is>
       </c>
       <c r="M89" s="106" t="inlineStr">
         <is>
-          <t>2026-07-28T01:39:30+09:00</t>
+          <t>2026-07-22T09:00:00+09:00</t>
         </is>
       </c>
       <c r="N89" s="60" t="inlineStr">
@@ -7786,68 +7786,72 @@
       </c>
       <c r="O89" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: 核融合技術</t>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: AIを用いたグラフィカルアブストラクトの作成</t>
         </is>
       </c>
     </row>
     <row r="90" ht="42" customHeight="1">
       <c r="A90" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T20:29:40+09:00</t>
+          <t>2026-07-26T21:02:36+09:00</t>
         </is>
       </c>
       <c r="B90" s="106" t="inlineStr">
         <is>
-          <t>2026-07-22T12:00:00Z</t>
+          <t>2026-07-22T00:00:00Z</t>
         </is>
       </c>
       <c r="C90" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D90" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E90" s="60" t="inlineStr"/>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E90" s="60" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence</t>
+        </is>
+      </c>
       <c r="F90" s="107" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G90" s="60" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Scientific Publication</t>
         </is>
       </c>
       <c r="H90" s="60" t="inlineStr">
         <is>
-          <t>NIST News</t>
+          <t>Nature</t>
         </is>
       </c>
       <c r="I90" s="60" t="inlineStr">
         <is>
-          <t>NIST、中小企業向けの資金提供機会を発表</t>
+          <t>「良いデザインには熟練が必要」：科学的イラストレーターがAIの未来を描く</t>
         </is>
       </c>
       <c r="J90" s="60" t="inlineStr">
         <is>
-          <t>NIST MEPが中小企業向けの資金提供機会を発表し、2026年7月28日にウェビナーを開催する予定。</t>
+          <t>Natureが5人のアーティストに科学を視覚的に伝えるアプローチについてインタビューした。</t>
         </is>
       </c>
       <c r="K90" s="60" t="inlineStr">
         <is>
-          <t>https://www.nist.gov/news-events/news/2026/07/nist-announces-funding-opportunity-14-mep-centers-advance-small-and-medium</t>
+          <t>https://www.nature.com/articles/d41586-026-02230-z</t>
         </is>
       </c>
       <c r="L90" s="60" t="inlineStr">
         <is>
-          <t>5aa9c93bc7040291c9f08bfa</t>
+          <t>108461ddd7bd10edd9652aef</t>
         </is>
       </c>
       <c r="M90" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T20:29:40+09:00</t>
+          <t>2026-07-22T09:00:00+09:00</t>
         </is>
       </c>
       <c r="N90" s="60" t="inlineStr">
@@ -7857,7 +7861,7 @@
       </c>
       <c r="O90" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: R&amp;D Funding &amp; Tax Incentives | Public Procurement &amp; Industrial Policy / 学術区分: News &amp; Official Release / 焦点: 中小企業向けの資金提供機会</t>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: 科学的イラストレーションにおけるAIの未来</t>
         </is>
       </c>
     </row>
@@ -7869,60 +7873,60 @@
       </c>
       <c r="B91" s="106" t="inlineStr">
         <is>
-          <t>2026-07-22T05:00:56Z</t>
+          <t>2026-07-22T00:00:00Z</t>
         </is>
       </c>
       <c r="C91" s="60" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D91" s="60" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="E91" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Biotechnology | Artificial Intelligence</t>
         </is>
       </c>
       <c r="F91" s="107" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G91" s="60" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Scientific Publication</t>
         </is>
       </c>
       <c r="H91" s="60" t="inlineStr">
         <is>
-          <t>NISTEP Updates</t>
+          <t>Nature</t>
         </is>
       </c>
       <c r="I91" s="60" t="inlineStr">
         <is>
-          <t>特定科学技術領域動向報告書 -AI（人工知能）- 研究開発インプット編を公表</t>
+          <t>AIがCRISPR複合体の相互作用を特定し、DNA編集の特異性を向上させる</t>
         </is>
       </c>
       <c r="J91" s="60" t="inlineStr">
         <is>
-          <t>AI分野における研究開発状況を分析し、基礎データをまとめた報告書を公表。</t>
+          <t>AlphaFold3による分子接触の予測が、DNAターゲット配列に対する酵素の選択性を改善するために使用された。</t>
         </is>
       </c>
       <c r="K91" s="60" t="inlineStr">
         <is>
-          <t>https://www.nistep.go.jp/archives/63583/</t>
+          <t>https://www.nature.com/articles/d41586-026-02042-1</t>
         </is>
       </c>
       <c r="L91" s="60" t="inlineStr">
         <is>
-          <t>6b6122461584a86ee7a1c595</t>
+          <t>ab4fcaf4ee310e08612eba0d</t>
         </is>
       </c>
       <c r="M91" s="106" t="inlineStr">
         <is>
-          <t>2026-07-22T14:00:56+09:00</t>
+          <t>2026-07-22T09:00:00+09:00</t>
         </is>
       </c>
       <c r="N91" s="60" t="inlineStr">
@@ -7932,7 +7936,7 @@
       </c>
       <c r="O91" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation | Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: 人工知能（AI）分野の研究開発インプット</t>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: CRISPR複合体における相互作用の特定</t>
         </is>
       </c>
     </row>
@@ -7949,50 +7953,50 @@
       </c>
       <c r="C92" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D92" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="E92" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="F92" s="107" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G92" s="60" t="inlineStr">
         <is>
-          <t>Policy Institute</t>
+          <t>Scientific Publication</t>
         </is>
       </c>
       <c r="H92" s="60" t="inlineStr">
         <is>
-          <t>Brookings TechTank</t>
+          <t>Nature</t>
         </is>
       </c>
       <c r="I92" s="60" t="inlineStr">
         <is>
-          <t>政策が世代ZのAIへの信頼を決定する</t>
+          <t>背景遺伝子と新しい変異ががん進化を導く</t>
         </is>
       </c>
       <c r="J92" s="60" t="inlineStr">
         <is>
-          <t>世代ZのAIに対する信頼は、PRではなく政策によって決まると論じられている。</t>
+          <t>マウスでの腫瘍進化の再実行により、DNA損傷後のがんの発展が示された。</t>
         </is>
       </c>
       <c r="K92" s="60" t="inlineStr">
         <is>
-          <t>https://www.brookings.edu/articles/policy-not-pr-will-determine-gen-zs-trust-in-ai/</t>
+          <t>https://www.nature.com/articles/d41586-026-02155-7</t>
         </is>
       </c>
       <c r="L92" s="60" t="inlineStr">
         <is>
-          <t>61bd55f8ce5a2385a5420260</t>
+          <t>74243d6e7e201860f4f79008</t>
         </is>
       </c>
       <c r="M92" s="106" t="inlineStr">
@@ -8007,7 +8011,7 @@
       </c>
       <c r="O92" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: AIに対する信頼の構築</t>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: がん進化における背景遺伝子と新しい変異の相互作用</t>
         </is>
       </c>
     </row>
@@ -8034,7 +8038,7 @@
       </c>
       <c r="E93" s="60" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="F93" s="107" t="n">
@@ -8052,22 +8056,22 @@
       </c>
       <c r="I93" s="60" t="inlineStr">
         <is>
-          <t>ブラウンブルヘッドキャットフィッシュのメラノーマは新しい伝染性がんを示す</t>
+          <t>科学におけるAI画像のミスを避けるための3つのヒント</t>
         </is>
       </c>
       <c r="J93" s="60" t="inlineStr">
         <is>
-          <t>ブラウンブルヘッドキャットフィッシュの腫瘍と非腫瘍組織の全ゲノム配列解析により、自然に発生する伝染性がんの一種が明らかになった。</t>
+          <t>AIツールはグラフィック作成に役立つが、エラーを引き起こす可能性がある。</t>
         </is>
       </c>
       <c r="K93" s="60" t="inlineStr">
         <is>
-          <t>https://www.nature.com/articles/s41586-026-10832-w</t>
+          <t>https://www.nature.com/articles/d41586-026-02233-w</t>
         </is>
       </c>
       <c r="L93" s="60" t="inlineStr">
         <is>
-          <t>f9bccca3cabb5ce19441f09d</t>
+          <t>3333c16762502cf03b987a99</t>
         </is>
       </c>
       <c r="M93" s="106" t="inlineStr">
@@ -8082,7 +8086,7 @@
       </c>
       <c r="O93" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: トランスミッシブルがん</t>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: 科学におけるAI画像のミスを避けるためのヒント</t>
         </is>
       </c>
     </row>
@@ -8109,7 +8113,7 @@
       </c>
       <c r="E94" s="60" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="F94" s="107" t="n">
@@ -8127,22 +8131,22 @@
       </c>
       <c r="I94" s="60" t="inlineStr">
         <is>
-          <t>量子パラエレクトリックSrTiO3におけるナノスケール極性テクスチャのイメージング</t>
+          <t>日々のブリーフィング：世界はついにポリオを根絶できるか？</t>
         </is>
       </c>
       <c r="J94" s="60" t="inlineStr">
         <is>
-          <t>Cryo-STEMを用いて、SrTiO3が105K以下で周期的な極性ナノドメインを形成することが明らかになった。</t>
+          <t>一部の研究者は、現在の根絶戦略が時代遅れであると考えている。</t>
         </is>
       </c>
       <c r="K94" s="60" t="inlineStr">
         <is>
-          <t>https://www.nature.com/articles/s41586-026-10823-x</t>
+          <t>https://www.nature.com/articles/d41586-026-02302-0</t>
         </is>
       </c>
       <c r="L94" s="60" t="inlineStr">
         <is>
-          <t>f12f62aebb861877dd7a5cbf</t>
+          <t>a6bb3e839151ea803a445830</t>
         </is>
       </c>
       <c r="M94" s="106" t="inlineStr">
@@ -8157,7 +8161,7 @@
       </c>
       <c r="O94" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: 量子パラエレクトリックSrTiO3のナノスケール極性テクスチャのイメージング</t>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: ポリオ根絶に関する研究</t>
         </is>
       </c>
     </row>
@@ -8169,7 +8173,7 @@
       </c>
       <c r="B95" s="106" t="inlineStr">
         <is>
-          <t>2026-07-22T00:00:00Z</t>
+          <t>2026-07-21T22:35:45Z</t>
         </is>
       </c>
       <c r="C95" s="60" t="inlineStr">
@@ -8179,12 +8183,12 @@
       </c>
       <c r="D95" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E95" s="60" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="F95" s="107" t="n">
@@ -8192,37 +8196,37 @@
       </c>
       <c r="G95" s="60" t="inlineStr">
         <is>
-          <t>Scientific Publication</t>
+          <t>Official Company</t>
         </is>
       </c>
       <c r="H95" s="60" t="inlineStr">
         <is>
-          <t>Nature</t>
+          <t>NVIDIA Blog</t>
         </is>
       </c>
       <c r="I95" s="60" t="inlineStr">
         <is>
-          <t>ブラウンブルヘッドキャットフィッシュのメラノーマは新しい伝染性がんを示す</t>
+          <t>フォートワースにて：ウィストロンがNVIDIA AIシステムを生産する先進的製造工場を開設</t>
         </is>
       </c>
       <c r="J95" s="60" t="inlineStr">
         <is>
-          <t>ブラウンブルヘッドキャットフィッシュの腫瘍と非腫瘍組織の全ゲノム配列解析により、自然に発生する伝染性がんの一種が明らかになった。</t>
+          <t>ウィストロンがテキサス州フォートワースに新たな製造施設を開設し、AIシステムの中心となるスーパーチップを生産する。</t>
         </is>
       </c>
       <c r="K95" s="60" t="inlineStr">
         <is>
-          <t>https://www.nature.com/articles/s41586-026-10828-6</t>
+          <t>https://blogs.nvidia.com/blog/wistron-manufacturing-texas/</t>
         </is>
       </c>
       <c r="L95" s="60" t="inlineStr">
         <is>
-          <t>3c774b8bd5e287725e43b3b5</t>
+          <t>21f1e1f3e19b1a5bf0af3cb7</t>
         </is>
       </c>
       <c r="M95" s="106" t="inlineStr">
         <is>
-          <t>2026-07-22T09:00:00+09:00</t>
+          <t>2026-07-22T07:35:45+09:00</t>
         </is>
       </c>
       <c r="N95" s="60" t="inlineStr">
@@ -8232,7 +8236,7 @@
       </c>
       <c r="O95" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: トランスミッシブルがんの発見</t>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: NVIDIA AIシステムの製造</t>
         </is>
       </c>
     </row>
@@ -8244,60 +8248,60 @@
       </c>
       <c r="B96" s="106" t="inlineStr">
         <is>
-          <t>2026-07-22T00:00:00Z</t>
+          <t>2026-07-21T15:05:11Z</t>
         </is>
       </c>
       <c r="C96" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>EU &amp; Europe</t>
         </is>
       </c>
       <c r="D96" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="E96" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Semiconductors &amp; Telecom</t>
         </is>
       </c>
       <c r="F96" s="107" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G96" s="60" t="inlineStr">
         <is>
-          <t>Scientific Publication</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H96" s="60" t="inlineStr">
         <is>
-          <t>Nature</t>
+          <t>UK DSIT</t>
         </is>
       </c>
       <c r="I96" s="60" t="inlineStr">
         <is>
-          <t>AIを使って数分でグラフィカルアブストラクトを作成する方法</t>
+          <t>政策文書：固定通信近代化チャーター</t>
         </is>
       </c>
       <c r="J96" s="60" t="inlineStr">
         <is>
-          <t>人工知能は、グラフィックデザインの経験がない人々にとって民主化の力となる。</t>
+          <t>この文書は、通信事業者が現在および将来の固定通信の近代化を行う際に従うべき手順を示している。</t>
         </is>
       </c>
       <c r="K96" s="60" t="inlineStr">
         <is>
-          <t>https://www.nature.com/articles/d41586-026-02072-9</t>
+          <t>https://www.gov.uk/government/publications/fixed-telecoms-modernisation-charter</t>
         </is>
       </c>
       <c r="L96" s="60" t="inlineStr">
         <is>
-          <t>b2a4fe860295587fbfbde689</t>
+          <t>d5e4431b57fcb4b6271f6c72</t>
         </is>
       </c>
       <c r="M96" s="106" t="inlineStr">
         <is>
-          <t>2026-07-22T09:00:00+09:00</t>
+          <t>2026-07-22T00:05:11+09:00</t>
         </is>
       </c>
       <c r="N96" s="60" t="inlineStr">
@@ -8307,7 +8311,7 @@
       </c>
       <c r="O96" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: AIを用いたグラフィカルアブストラクトの作成</t>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: 固定通信の近代化</t>
         </is>
       </c>
     </row>
@@ -8319,60 +8323,60 @@
       </c>
       <c r="B97" s="106" t="inlineStr">
         <is>
-          <t>2026-07-22T00:00:00Z</t>
+          <t>2026-07-21T15:05:07Z</t>
         </is>
       </c>
       <c r="C97" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>EU &amp; Europe</t>
         </is>
       </c>
       <c r="D97" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="E97" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Semiconductors &amp; Telecom</t>
         </is>
       </c>
       <c r="F97" s="107" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G97" s="60" t="inlineStr">
         <is>
-          <t>Scientific Publication</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H97" s="60" t="inlineStr">
         <is>
-          <t>Nature</t>
+          <t>UK DSIT</t>
         </is>
       </c>
       <c r="I97" s="60" t="inlineStr">
         <is>
-          <t>「良いデザインには熟練が必要」：科学的イラストレーターがAIの未来を描く</t>
+          <t>政策文書：通信の近代化に関する重要国家インフラ憲章</t>
         </is>
       </c>
       <c r="J97" s="60" t="inlineStr">
         <is>
-          <t>Natureが5人のアーティストに科学を視覚的に伝えるアプローチについてインタビューした。</t>
+          <t>この文書は、通信会社が通信の近代化において重要国家インフラを保護するためのアプローチを示している。</t>
         </is>
       </c>
       <c r="K97" s="60" t="inlineStr">
         <is>
-          <t>https://www.nature.com/articles/d41586-026-02230-z</t>
+          <t>https://www.gov.uk/government/publications/telecoms-modernisation-critical-national-infrastructure-charter</t>
         </is>
       </c>
       <c r="L97" s="60" t="inlineStr">
         <is>
-          <t>108461ddd7bd10edd9652aef</t>
+          <t>aafa3a246656ccda64dd93c4</t>
         </is>
       </c>
       <c r="M97" s="106" t="inlineStr">
         <is>
-          <t>2026-07-22T09:00:00+09:00</t>
+          <t>2026-07-22T00:05:07+09:00</t>
         </is>
       </c>
       <c r="N97" s="60" t="inlineStr">
@@ -8382,72 +8386,72 @@
       </c>
       <c r="O97" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: 科学的イラストレーションにおけるAIの未来</t>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: 通信会社の重要国家インフラ保護のアプローチ</t>
         </is>
       </c>
     </row>
     <row r="98" ht="42" customHeight="1">
       <c r="A98" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T21:02:36+09:00</t>
+          <t>2026-07-26T18:56:03+09:00</t>
         </is>
       </c>
       <c r="B98" s="106" t="inlineStr">
         <is>
-          <t>2026-07-22T00:00:00Z</t>
+          <t>2026-07-21T14:48:28Z</t>
         </is>
       </c>
       <c r="C98" s="60" t="inlineStr">
         <is>
+          <t>EU &amp; Europe</t>
+        </is>
+      </c>
+      <c r="D98" s="60" t="inlineStr">
+        <is>
           <t>Global</t>
         </is>
       </c>
-      <c r="D98" s="60" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
       <c r="E98" s="60" t="inlineStr">
         <is>
-          <t>Biotechnology | Artificial Intelligence</t>
+          <t>Fusion Energy</t>
         </is>
       </c>
       <c r="F98" s="107" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G98" s="60" t="inlineStr">
         <is>
-          <t>Scientific Publication</t>
+          <t>Industry Association</t>
         </is>
       </c>
       <c r="H98" s="60" t="inlineStr">
         <is>
-          <t>Nature</t>
+          <t>Fusion Industry Association</t>
         </is>
       </c>
       <c r="I98" s="60" t="inlineStr">
         <is>
-          <t>AIがCRISPR複合体の相互作用を特定し、DNA編集の特異性を向上させる</t>
+          <t>FIA、核融合のためのEU資金調達の道筋を示す</t>
         </is>
       </c>
       <c r="J98" s="60" t="inlineStr">
         <is>
-          <t>AlphaFold3による分子接触の予測が、DNAターゲット配列に対する酵素の選択性を改善するために使用された。</t>
+          <t>Fusion Industry Associationが商業核融合エネルギーのためのEU資金調達のロードマップを発表。</t>
         </is>
       </c>
       <c r="K98" s="60" t="inlineStr">
         <is>
-          <t>https://www.nature.com/articles/d41586-026-02042-1</t>
+          <t>https://www.fusionindustryassociation.org/fia-outlines-eu-financing-pathway-for-fusion/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=fia-outlines-eu-financing-pathway-for-fusion</t>
         </is>
       </c>
       <c r="L98" s="60" t="inlineStr">
         <is>
-          <t>ab4fcaf4ee310e08612eba0d</t>
+          <t>88af233d904d670250fa5a31</t>
         </is>
       </c>
       <c r="M98" s="106" t="inlineStr">
         <is>
-          <t>2026-07-22T09:00:00+09:00</t>
+          <t>2026-07-26T18:56:03+09:00</t>
         </is>
       </c>
       <c r="N98" s="60" t="inlineStr">
@@ -8457,7 +8461,7 @@
       </c>
       <c r="O98" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: CRISPR複合体における相互作用の特定</t>
+          <t>枠: Innovation Policy / 政策分野: R&amp;D Funding &amp; Tax Incentives / 学術区分: News &amp; Official Release / 焦点: EUの核融合エネルギー商業化に向けた資金調達</t>
         </is>
       </c>
     </row>
@@ -8469,7 +8473,7 @@
       </c>
       <c r="B99" s="106" t="inlineStr">
         <is>
-          <t>2026-07-22T00:00:00Z</t>
+          <t>2026-07-21T00:00:00Z</t>
         </is>
       </c>
       <c r="C99" s="60" t="inlineStr">
@@ -8484,7 +8488,7 @@
       </c>
       <c r="E99" s="60" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="F99" s="107" t="n">
@@ -8492,37 +8496,37 @@
       </c>
       <c r="G99" s="60" t="inlineStr">
         <is>
-          <t>Scientific Publication</t>
+          <t>Conference Paper</t>
         </is>
       </c>
       <c r="H99" s="60" t="inlineStr">
         <is>
-          <t>Nature</t>
+          <t>OpenAlex Conference Papers</t>
         </is>
       </c>
       <c r="I99" s="60" t="inlineStr">
         <is>
-          <t>背景遺伝子と新しい変異ががん進化を導く</t>
+          <t>心血管疾患リスク予測のための量子機械学習</t>
         </is>
       </c>
       <c r="J99" s="60" t="inlineStr">
         <is>
-          <t>マウスでの腫瘍進化の再実行により、DNA損傷後のがんの発展が示された。</t>
+          <t>量子機械学習を用いた心血管疾患リスク予測に関する研究が発表されました。</t>
         </is>
       </c>
       <c r="K99" s="60" t="inlineStr">
         <is>
-          <t>https://www.nature.com/articles/d41586-026-02155-7</t>
+          <t>https://doi.org/10.3390/engproc2026150039</t>
         </is>
       </c>
       <c r="L99" s="60" t="inlineStr">
         <is>
-          <t>74243d6e7e201860f4f79008</t>
+          <t>1cd467f8ebb1388daedc245f</t>
         </is>
       </c>
       <c r="M99" s="106" t="inlineStr">
         <is>
-          <t>2026-07-22T09:00:00+09:00</t>
+          <t>2026-07-21T09:00:00+09:00</t>
         </is>
       </c>
       <c r="N99" s="60" t="inlineStr">
@@ -8532,7 +8536,7 @@
       </c>
       <c r="O99" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: がん進化における背景遺伝子と新しい変異の相互作用</t>
+          <t>枠: Technology Innovation / 学術区分: Conference Paper / 査読表示: Conference proceedings — review status varies / 焦点: 量子機械学習 / OpenAlex record; work type=conference-paper; citations=0</t>
         </is>
       </c>
     </row>
@@ -8544,17 +8548,17 @@
       </c>
       <c r="B100" s="106" t="inlineStr">
         <is>
-          <t>2026-07-22T00:00:00Z</t>
+          <t>2026-07-20T21:06:27Z</t>
         </is>
       </c>
       <c r="C100" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D100" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E100" s="60" t="inlineStr">
@@ -8563,41 +8567,41 @@
         </is>
       </c>
       <c r="F100" s="107" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G100" s="60" t="inlineStr">
         <is>
-          <t>Scientific Publication</t>
+          <t>Policy Institute</t>
         </is>
       </c>
       <c r="H100" s="60" t="inlineStr">
         <is>
-          <t>Nature</t>
+          <t>Brookings TechTank</t>
         </is>
       </c>
       <c r="I100" s="60" t="inlineStr">
         <is>
-          <t>科学におけるAI画像のミスを避けるための3つのヒント</t>
+          <t>相続を返す：教育と研究政策がAIの借りた専門知識にどう対処できるか</t>
         </is>
       </c>
       <c r="J100" s="60" t="inlineStr">
         <is>
-          <t>AIツールはグラフィック作成に役立つが、エラーを引き起こす可能性がある。</t>
+          <t>ニアム・ヤラギが、短期的な生産性と長期的な認知発展の間の緊張の中で教育がどのように変わるべきかを論じている。</t>
         </is>
       </c>
       <c r="K100" s="60" t="inlineStr">
         <is>
-          <t>https://www.nature.com/articles/d41586-026-02233-w</t>
+          <t>https://brookings.edu/articles/repaying-the-inheritance-how-education-and-research-policy-can-address-ais-borrowed-expertise</t>
         </is>
       </c>
       <c r="L100" s="60" t="inlineStr">
         <is>
-          <t>3333c16762502cf03b987a99</t>
+          <t>42183313e1c951c0483c0d62</t>
         </is>
       </c>
       <c r="M100" s="106" t="inlineStr">
         <is>
-          <t>2026-07-22T09:00:00+09:00</t>
+          <t>2026-07-21T06:06:27+09:00</t>
         </is>
       </c>
       <c r="N100" s="60" t="inlineStr">
@@ -8607,7 +8611,7 @@
       </c>
       <c r="O100" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: 科学におけるAI画像のミスを避けるためのヒント</t>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: AIの専門知識に関する教育と研究政策 / Historical backfill from an allowlisted source.</t>
         </is>
       </c>
     </row>
@@ -8619,22 +8623,22 @@
       </c>
       <c r="B101" s="106" t="inlineStr">
         <is>
-          <t>2026-07-22T00:00:00Z</t>
+          <t>2026-07-20T15:55:00Z</t>
         </is>
       </c>
       <c r="C101" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D101" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E101" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Semiconductors &amp; Telecom</t>
         </is>
       </c>
       <c r="F101" s="107" t="n">
@@ -8642,37 +8646,37 @@
       </c>
       <c r="G101" s="60" t="inlineStr">
         <is>
-          <t>Scientific Publication</t>
+          <t>Major Media</t>
         </is>
       </c>
       <c r="H101" s="60" t="inlineStr">
         <is>
-          <t>Nature</t>
+          <t>IEEE Spectrum</t>
         </is>
       </c>
       <c r="I101" s="60" t="inlineStr">
         <is>
-          <t>日々のブリーフィング：世界はついにポリオを根絶できるか？</t>
+          <t>先端半導体故障解析のためのSEMガイド低電圧FIB仕上げ</t>
         </is>
       </c>
       <c r="J101" s="60" t="inlineStr">
         <is>
-          <t>一部の研究者は、現在の根絶戦略が時代遅れであると考えている。</t>
+          <t>ZEISS Crossbeam 750 FIBSEMを用いた先端半導体故障解析の新技術が発表されました。</t>
         </is>
       </c>
       <c r="K101" s="60" t="inlineStr">
         <is>
-          <t>https://www.nature.com/articles/d41586-026-02302-0</t>
+          <t>https://event.on24.com/wcc/r/5418459/287E3D5B99470D34C830D69A24B3B207</t>
         </is>
       </c>
       <c r="L101" s="60" t="inlineStr">
         <is>
-          <t>a6bb3e839151ea803a445830</t>
+          <t>73d0028e337a76c2cd00f1bc</t>
         </is>
       </c>
       <c r="M101" s="106" t="inlineStr">
         <is>
-          <t>2026-07-22T09:00:00+09:00</t>
+          <t>2026-07-21T00:55:00+09:00</t>
         </is>
       </c>
       <c r="N101" s="60" t="inlineStr">
@@ -8682,19 +8686,19 @@
       </c>
       <c r="O101" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: ポリオ根絶に関する研究</t>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: 半導体故障解析のためのFIB技術</t>
         </is>
       </c>
     </row>
     <row r="102" ht="42" customHeight="1">
       <c r="A102" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T21:02:36+09:00</t>
+          <t>2026-07-28T01:39:30+09:00</t>
         </is>
       </c>
       <c r="B102" s="106" t="inlineStr">
         <is>
-          <t>2026-07-21T22:35:45Z</t>
+          <t>2026-07-20T13:21:36Z</t>
         </is>
       </c>
       <c r="C102" s="60" t="inlineStr">
@@ -8704,12 +8708,12 @@
       </c>
       <c r="D102" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="E102" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Fusion Energy</t>
         </is>
       </c>
       <c r="F102" s="107" t="n">
@@ -8717,37 +8721,37 @@
       </c>
       <c r="G102" s="60" t="inlineStr">
         <is>
-          <t>Official Company</t>
+          <t>Industry Association</t>
         </is>
       </c>
       <c r="H102" s="60" t="inlineStr">
         <is>
-          <t>NVIDIA Blog</t>
+          <t>Fusion Industry Association</t>
         </is>
       </c>
       <c r="I102" s="60" t="inlineStr">
         <is>
-          <t>フォートワースにて：WistronがNVIDIA AIシステムを生産するための先進的製造工場を開設</t>
+          <t>LLNLとPacific Fusion、Siriusパルスパワープロトタイプで3,000回のテスト達成</t>
         </is>
       </c>
       <c r="J102" s="60" t="inlineStr">
         <is>
-          <t>Wistronがテキサス州フォートワースに324,000平方フィートの製造施設を開設し、AIシステムのためのスーパーチップを生産する。</t>
+          <t>ローレンス・リバモア国立研究所とPacific Fusionは、Siriusパルスパワープロトタイプの3,000回の成功テストを達成しました。この成果は、核融合エネルギーの大規模デモンストレーションに向けた重要な進展を示しています。</t>
         </is>
       </c>
       <c r="K102" s="60" t="inlineStr">
         <is>
-          <t>https://blogs.nvidia.com/blog/wistron-manufacturing-texas/</t>
+          <t>https://www.ans.org/news/article-8217/llnl-and-pacific-fusion-achieve-3000shot-milestone-with-sirius-pulsedpower-prototype/?mc_cid=ed1acc7bef&amp;mc_eid=01cd8fe465#new_tab&amp;utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=llnl-and-pacific-fusion-achieve-3000-shot-milestone-with-sirius-pulsed-power-prototype</t>
         </is>
       </c>
       <c r="L102" s="60" t="inlineStr">
         <is>
-          <t>21f1e1f3e19b1a5bf0af3cb7</t>
+          <t>c654a0d44a7fcbda5490cd6d</t>
         </is>
       </c>
       <c r="M102" s="106" t="inlineStr">
         <is>
-          <t>2026-07-22T07:35:45+09:00</t>
+          <t>2026-07-28T01:39:30+09:00</t>
         </is>
       </c>
       <c r="N102" s="60" t="inlineStr">
@@ -8757,72 +8761,72 @@
       </c>
       <c r="O102" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: NVIDIA AIシステムの製造</t>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: 核融合エネルギー技術</t>
         </is>
       </c>
     </row>
     <row r="103" ht="42" customHeight="1">
       <c r="A103" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T21:02:36+09:00</t>
+          <t>2026-07-28T01:39:30+09:00</t>
         </is>
       </c>
       <c r="B103" s="106" t="inlineStr">
         <is>
-          <t>2026-07-21T15:05:11Z</t>
+          <t>2026-07-20T13:17:02Z</t>
         </is>
       </c>
       <c r="C103" s="60" t="inlineStr">
         <is>
-          <t>EU &amp; Europe</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D103" s="60" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="E103" s="60" t="inlineStr">
         <is>
-          <t>Semiconductors &amp; Telecom</t>
+          <t>Fusion Energy | Quantum</t>
         </is>
       </c>
       <c r="F103" s="107" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G103" s="60" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Industry Association</t>
         </is>
       </c>
       <c r="H103" s="60" t="inlineStr">
         <is>
-          <t>UK DSIT</t>
+          <t>Fusion Industry Association</t>
         </is>
       </c>
       <c r="I103" s="60" t="inlineStr">
         <is>
-          <t>固定通信近代化憲章に関する政策文書</t>
+          <t>量子材料の発見が核融合用電子機器の進展を促進する可能性</t>
         </is>
       </c>
       <c r="J103" s="60" t="inlineStr">
         <is>
-          <t>通信事業者が現在および将来の固定通信近代化を実施する際に従うべき手順を示した文書。</t>
+          <t>アリゾナ大学の研究者は、グラフェンナノリボンが将来の核融合発電所の放射線センサーとして機能する可能性を示しました。この技術は、既存のセンサーよりも反応器コアに近いリアルタイムモニタリングを可能にするかもしれません。</t>
         </is>
       </c>
       <c r="K103" s="60" t="inlineStr">
         <is>
-          <t>https://www.gov.uk/government/publications/fixed-telecoms-modernisation-charter</t>
+          <t>https://thequantuminsider.com/2026/07/20/quantum-materials-discovery-could-advance-electronics-for-extreme-environments/?mc_cid=ed1acc7bef&amp;mc_eid=01cd8fe465#new_tab&amp;utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=quantum-materials-discovery-could-advance-electronics-for-fusion</t>
         </is>
       </c>
       <c r="L103" s="60" t="inlineStr">
         <is>
-          <t>d5e4431b57fcb4b6271f6c72</t>
+          <t>1d37727752cb4b098b374ef4</t>
         </is>
       </c>
       <c r="M103" s="106" t="inlineStr">
         <is>
-          <t>2026-07-22T00:05:11+09:00</t>
+          <t>2026-07-28T01:39:30+09:00</t>
         </is>
       </c>
       <c r="N103" s="60" t="inlineStr">
@@ -8832,7 +8836,7 @@
       </c>
       <c r="O103" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: 固定通信の近代化手順</t>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: 量子材料と核融合技術</t>
         </is>
       </c>
     </row>
@@ -8844,60 +8848,60 @@
       </c>
       <c r="B104" s="106" t="inlineStr">
         <is>
-          <t>2026-07-21T15:05:07Z</t>
+          <t>2026-07-20T00:00:00Z</t>
         </is>
       </c>
       <c r="C104" s="60" t="inlineStr">
         <is>
-          <t>EU &amp; Europe</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D104" s="60" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="E104" s="60" t="inlineStr">
         <is>
-          <t>Semiconductors &amp; Telecom</t>
+          <t>Artificial Intelligence | Healthcare</t>
         </is>
       </c>
       <c r="F104" s="107" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G104" s="60" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Journal Article</t>
         </is>
       </c>
       <c r="H104" s="60" t="inlineStr">
         <is>
-          <t>UK DSIT</t>
+          <t>Machine Intelligence Research</t>
         </is>
       </c>
       <c r="I104" s="60" t="inlineStr">
         <is>
-          <t>通信近代化：重要国家インフラ憲章に関する政策文書</t>
+          <t>医療画像セグメンテーションのための多スケールネットワーク</t>
         </is>
       </c>
       <c r="J104" s="60" t="inlineStr">
         <is>
-          <t>通信事業者が通信近代化中に重要国家インフラを保護するためのアプローチを示した文書。</t>
+          <t>医療画像セグメンテーションのための新しいAI技術M2SNetが発表されました。</t>
         </is>
       </c>
       <c r="K104" s="60" t="inlineStr">
         <is>
-          <t>https://www.gov.uk/government/publications/telecoms-modernisation-critical-national-infrastructure-charter</t>
+          <t>https://doi.org/10.1007/s11633-026-1662-9</t>
         </is>
       </c>
       <c r="L104" s="60" t="inlineStr">
         <is>
-          <t>aafa3a246656ccda64dd93c4</t>
+          <t>bffca1cc322e28515452081a</t>
         </is>
       </c>
       <c r="M104" s="106" t="inlineStr">
         <is>
-          <t>2026-07-22T00:05:07+09:00</t>
+          <t>2026-07-20T09:00:00+09:00</t>
         </is>
       </c>
       <c r="N104" s="60" t="inlineStr">
@@ -8907,7 +8911,7 @@
       </c>
       <c r="O104" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: 重要国家インフラの保護方針</t>
+          <t>枠: Technology Innovation / 学術区分: Journal Article / 査読表示: Journal record — confirm peer review on publisher page / 掲載誌・学会: Machine Intelligence Research / 焦点: 医療画像セグメンテーションのためのAI技術 / OpenAlex record; work type=article; citations=79</t>
         </is>
       </c>
     </row>
@@ -8919,7 +8923,7 @@
       </c>
       <c r="B105" s="106" t="inlineStr">
         <is>
-          <t>2026-07-21T14:48:28Z</t>
+          <t>2026-07-17T18:42:47Z</t>
         </is>
       </c>
       <c r="C105" s="60" t="inlineStr">
@@ -8938,7 +8942,7 @@
         </is>
       </c>
       <c r="F105" s="107" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G105" s="60" t="inlineStr">
         <is>
@@ -8952,22 +8956,22 @@
       </c>
       <c r="I105" s="60" t="inlineStr">
         <is>
-          <t>FIA、核融合のためのEU資金調達の道筋を示す</t>
+          <t>国際法専門家グループ、EUの核融合競争優位性確保の必要性に関する論文を発表</t>
         </is>
       </c>
       <c r="J105" s="60" t="inlineStr">
         <is>
-          <t>Fusion Industry Associationが商業核融合エネルギーのためのEU資金調達のロードマップを発表。</t>
+          <t>国際法専門家グループがEUの核融合エネルギーに関する競争優位性を確保する必要性を論じた。</t>
         </is>
       </c>
       <c r="K105" s="60" t="inlineStr">
         <is>
-          <t>https://www.fusionindustryassociation.org/fia-outlines-eu-financing-pathway-for-fusion/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=fia-outlines-eu-financing-pathway-for-fusion</t>
+          <t>https://www.fusionindustryassociation.org/international-legal-expert-group-publish-paper-on-the-need-for-the-eu-to-secure-its-competitive-fusion-advantage/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=international-legal-expert-group-publish-paper-on-the-need-for-the-eu-to-secure-its-competitive-fusion-advantage</t>
         </is>
       </c>
       <c r="L105" s="60" t="inlineStr">
         <is>
-          <t>88af233d904d670250fa5a31</t>
+          <t>7ef6110ab078602757409abf</t>
         </is>
       </c>
       <c r="M105" s="106" t="inlineStr">
@@ -8982,7 +8986,7 @@
       </c>
       <c r="O105" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: R&amp;D Funding &amp; Tax Incentives / 学術区分: News &amp; Official Release / 焦点: EUの核融合エネルギー商業化に向けた資金調達</t>
+          <t>枠: Innovation Policy / 政策分野: Regulation &amp; Governance / 学術区分: News &amp; Official Release / 焦点: EUの核融合エネルギーに関する規制とガバナンス</t>
         </is>
       </c>
     </row>
@@ -8994,60 +8998,60 @@
       </c>
       <c r="B106" s="106" t="inlineStr">
         <is>
-          <t>2026-07-21T00:00:00Z</t>
+          <t>2026-07-17T15:00:03Z</t>
         </is>
       </c>
       <c r="C106" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>EU &amp; Europe</t>
         </is>
       </c>
       <c r="D106" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="E106" s="60" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="F106" s="107" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G106" s="60" t="inlineStr">
         <is>
-          <t>Conference Paper</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H106" s="60" t="inlineStr">
         <is>
-          <t>OpenAlex Conference Papers</t>
+          <t>UK DSIT</t>
         </is>
       </c>
       <c r="I106" s="60" t="inlineStr">
         <is>
-          <t>量子機械学習による心血管疾患リスク予測の向上</t>
+          <t>AI研究資源に関するガイダンス</t>
         </is>
       </c>
       <c r="J106" s="60" t="inlineStr">
         <is>
-          <t>この研究は、量子アルゴリズムを用いて心血管疾患の予測を行うモデルを探求しており、量子サポートベクターマシンや量子ニューラルネットワークを活用しています。</t>
+          <t>AI研究資源（AIRR）は、研究者や産業にAI専門の計算能力を提供するスーパーコンピュータのスイートです。</t>
         </is>
       </c>
       <c r="K106" s="60" t="inlineStr">
         <is>
-          <t>https://doi.org/10.3390/engproc2026150039</t>
+          <t>https://www.gov.uk/government/publications/ai-research-resource</t>
         </is>
       </c>
       <c r="L106" s="60" t="inlineStr">
         <is>
-          <t>1cd467f8ebb1388daedc245f</t>
+          <t>579a0b7ad2d471608fff5049</t>
         </is>
       </c>
       <c r="M106" s="106" t="inlineStr">
         <is>
-          <t>2026-07-21T09:00:00+09:00</t>
+          <t>2026-07-18T00:00:03+09:00</t>
         </is>
       </c>
       <c r="N106" s="60" t="inlineStr">
@@ -9057,72 +9061,68 @@
       </c>
       <c r="O106" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: Conference Paper / 査読表示: Conference proceedings — review status varies / 焦点: 量子機械学習による心血管疾患リスク予測 / OpenAlex record; work type=conference-paper; citations=0</t>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: AI研究資源（AIRR）</t>
         </is>
       </c>
     </row>
     <row r="107" ht="42" customHeight="1">
       <c r="A107" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T21:02:36+09:00</t>
+          <t>2026-07-26T21:45:54+09:00</t>
         </is>
       </c>
       <c r="B107" s="106" t="inlineStr">
         <is>
-          <t>2026-07-20T21:06:27Z</t>
+          <t>2026-07-17T14:48:00Z</t>
         </is>
       </c>
       <c r="C107" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>EU &amp; Europe</t>
         </is>
       </c>
       <c r="D107" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E107" s="60" t="inlineStr">
-        <is>
-          <t>Artificial Intelligence</t>
-        </is>
-      </c>
+          <t>European Patent Organisation</t>
+        </is>
+      </c>
+      <c r="E107" s="60" t="inlineStr"/>
       <c r="F107" s="107" t="n">
         <v>3</v>
       </c>
       <c r="G107" s="60" t="inlineStr">
         <is>
-          <t>Policy Institute</t>
+          <t>Intergovernmental</t>
         </is>
       </c>
       <c r="H107" s="60" t="inlineStr">
         <is>
-          <t>Brookings TechTank</t>
+          <t>European Patent Office News</t>
         </is>
       </c>
       <c r="I107" s="60" t="inlineStr">
         <is>
-          <t>AIの借りた専門知識に対処する教育と研究政策</t>
+          <t>技術革新を加速するための特許と標準</t>
         </is>
       </c>
       <c r="J107" s="60" t="inlineStr">
         <is>
-          <t>教育政策が短期的な生産性と長期的な認知発展の間の緊張にどのように対応すべきかについて論じています。</t>
+          <t>特許と標準が技術革新を加速するための重要な要素であることについての情報。</t>
         </is>
       </c>
       <c r="K107" s="60" t="inlineStr">
         <is>
-          <t>https://brookings.edu/articles/repaying-the-inheritance-how-education-and-research-policy-can-address-ais-borrowed-expertise</t>
+          <t>https://epo.org/en/about-us/observatory-patents-and-technology/policy-and-funding/patents-and-standards</t>
         </is>
       </c>
       <c r="L107" s="60" t="inlineStr">
         <is>
-          <t>42183313e1c951c0483c0d62</t>
+          <t>a0d096f59b7771ee7e91da7b</t>
         </is>
       </c>
       <c r="M107" s="106" t="inlineStr">
         <is>
-          <t>2026-07-21T06:06:27+09:00</t>
+          <t>2026-07-17T23:48:00+09:00</t>
         </is>
       </c>
       <c r="N107" s="60" t="inlineStr">
@@ -9132,7 +9132,7 @@
       </c>
       <c r="O107" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: AIに関する教育政策の変革 / Historical backfill from an allowlisted source.</t>
+          <t>枠: Innovation Policy / 政策分野: Patents &amp; Intellectual Property / 学術区分: News &amp; Official Release / 焦点: 技術革新を加速するための特許と標準 / Historical backfill from an allowlisted source.</t>
         </is>
       </c>
     </row>
@@ -9144,60 +9144,56 @@
       </c>
       <c r="B108" s="106" t="inlineStr">
         <is>
-          <t>2026-07-20T15:55:00Z</t>
+          <t>2026-07-17T13:42:16Z</t>
         </is>
       </c>
       <c r="C108" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>EU &amp; Europe</t>
         </is>
       </c>
       <c r="D108" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E108" s="60" t="inlineStr">
-        <is>
-          <t>Semiconductors &amp; Telecom</t>
-        </is>
-      </c>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="E108" s="60" t="inlineStr"/>
       <c r="F108" s="107" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G108" s="60" t="inlineStr">
         <is>
-          <t>Major Media</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H108" s="60" t="inlineStr">
         <is>
-          <t>IEEE Spectrum</t>
+          <t>UK DSIT</t>
         </is>
       </c>
       <c r="I108" s="60" t="inlineStr">
         <is>
-          <t>先進半導体故障解析のためのSEMガイド低電圧FIB仕上げ</t>
+          <t>デジタルサービスの改善に関する公開書簡</t>
         </is>
       </c>
       <c r="J108" s="60" t="inlineStr">
         <is>
-          <t>ZEISS Crossbeam 750 FIBSEMが先進的な半導体故障解析の新しい基準を設定する方法について説明しています。</t>
+          <t>業界リーダーに向けて、デジタルサービスの改善に関する公開書簡が送られた。</t>
         </is>
       </c>
       <c r="K108" s="60" t="inlineStr">
         <is>
-          <t>https://event.on24.com/wcc/r/5418459/287E3D5B99470D34C830D69A24B3B207</t>
+          <t>https://www.gov.uk/government/publications/improving-access-to-and-use-of-digital-services-open-letter-to-business-leaders</t>
         </is>
       </c>
       <c r="L108" s="60" t="inlineStr">
         <is>
-          <t>73d0028e337a76c2cd00f1bc</t>
+          <t>d136ac8a836994c6ce5e35c6</t>
         </is>
       </c>
       <c r="M108" s="106" t="inlineStr">
         <is>
-          <t>2026-07-21T00:55:00+09:00</t>
+          <t>2026-07-17T22:42:16+09:00</t>
         </is>
       </c>
       <c r="N108" s="60" t="inlineStr">
@@ -9207,7 +9203,7 @@
       </c>
       <c r="O108" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: 先進半導体の故障解析技術</t>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: デジタルサービスの改善</t>
         </is>
       </c>
     </row>
@@ -9219,60 +9215,60 @@
       </c>
       <c r="B109" s="106" t="inlineStr">
         <is>
-          <t>2026-07-20T15:00:53Z</t>
+          <t>2026-07-17T12:00:04Z</t>
         </is>
       </c>
       <c r="C109" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>EU &amp; Europe</t>
         </is>
       </c>
       <c r="D109" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="E109" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence | Robotics</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="F109" s="107" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G109" s="60" t="inlineStr">
         <is>
-          <t>Official Company</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H109" s="60" t="inlineStr">
         <is>
-          <t>NVIDIA Blog</t>
+          <t>UK DSIT</t>
         </is>
       </c>
       <c r="I109" s="60" t="inlineStr">
         <is>
-          <t>SIGGRAPHでNVIDIAがエージェントAIと物理AIでグラフィックスとシミュレーションを進展</t>
+          <t>AIスーパーコンピュータホストサイト選定に関する表明</t>
         </is>
       </c>
       <c r="J109" s="60" t="inlineStr">
         <is>
-          <t>NVIDIAはSIGGRAPHで、オープンモデルからリアルタイムシミュレーションまで、AIとグラフィックスの革新がメディア、コンテンツ制作、ロボティクスを変革していることを発表した。</t>
+          <t>UKの次のAIスーパーコンピュータのホストサイト選定に関する表明が行われた。</t>
         </is>
       </c>
       <c r="K109" s="60" t="inlineStr">
         <is>
-          <t>https://blogs.nvidia.com/blog/siggraph-news-2026/</t>
+          <t>https://www.gov.uk/government/publications/expression-of-interest-airr-heterogeneous-supercomputer-host-site-selection</t>
         </is>
       </c>
       <c r="L109" s="60" t="inlineStr">
         <is>
-          <t>70c1acaa81ba6cd1c84a673d</t>
+          <t>27d607577c2759c8d53f9ddf</t>
         </is>
       </c>
       <c r="M109" s="106" t="inlineStr">
         <is>
-          <t>2026-07-21T00:00:53+09:00</t>
+          <t>2026-07-17T21:00:04+09:00</t>
         </is>
       </c>
       <c r="N109" s="60" t="inlineStr">
@@ -9282,7 +9278,7 @@
       </c>
       <c r="O109" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: エージェントAIと物理AIの進展</t>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: AIスーパーコンピュータのホストサイト選定</t>
         </is>
       </c>
     </row>
@@ -9294,60 +9290,56 @@
       </c>
       <c r="B110" s="106" t="inlineStr">
         <is>
-          <t>2026-07-20T13:30:06Z</t>
+          <t>2026-07-17T07:59:22Z</t>
         </is>
       </c>
       <c r="C110" s="60" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>EU &amp; Europe</t>
         </is>
       </c>
       <c r="D110" s="60" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
-        </is>
-      </c>
-      <c r="E110" s="60" t="inlineStr">
-        <is>
-          <t>Artificial Intelligence | Semiconductors &amp; Telecom</t>
-        </is>
-      </c>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="E110" s="60" t="inlineStr"/>
       <c r="F110" s="107" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G110" s="60" t="inlineStr">
         <is>
-          <t>Major Media</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H110" s="60" t="inlineStr">
         <is>
-          <t>South China Morning Post Technology</t>
+          <t>UK DSIT</t>
         </is>
       </c>
       <c r="I110" s="60" t="inlineStr">
         <is>
-          <t>トークン経済からタスク経済へ？SenseTimeがAIの商業化に賭ける</t>
+          <t>子供のオンライン保護に関する新ルール</t>
         </is>
       </c>
       <c r="J110" s="60" t="inlineStr">
         <is>
-          <t>中国のAI企業SenseTimeは、トークン価格の低下に伴い、AIの商業化が「トークン経済」から「タスク経済」へ移行する見込みであると述べた。</t>
+          <t>UK政府が16歳未満の子供に対するソーシャルメディア禁止を発表した。</t>
         </is>
       </c>
       <c r="K110" s="60" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/tech/big-tech/article/3361242/no-longer-token-economy-sensetime-bets-task-economy-token-prices-set-drop?utm_source=rss_feed</t>
+          <t>https://www.gov.uk/government/publications/fact-sheet-new-rules-to-protect-children-online</t>
         </is>
       </c>
       <c r="L110" s="60" t="inlineStr">
         <is>
-          <t>cd5b1ea310d8a65d00ad1ad9</t>
+          <t>371ff53aa8f9007fcb1ddddf</t>
         </is>
       </c>
       <c r="M110" s="106" t="inlineStr">
         <is>
-          <t>2026-07-20T22:30:06+09:00</t>
+          <t>2026-07-17T16:59:22+09:00</t>
         </is>
       </c>
       <c r="N110" s="60" t="inlineStr">
@@ -9357,72 +9349,72 @@
       </c>
       <c r="O110" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation | Innovation Policy / 政策分野: Patents &amp; Intellectual Property / 学術区分: News &amp; Official Release / 焦点: AIの商業化の移行</t>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: 子供のオンライン保護に関する新ルール</t>
         </is>
       </c>
     </row>
     <row r="111" ht="42" customHeight="1">
       <c r="A111" s="106" t="inlineStr">
         <is>
-          <t>2026-07-28T01:39:30+09:00</t>
+          <t>2026-07-26T21:02:36+09:00</t>
         </is>
       </c>
       <c r="B111" s="106" t="inlineStr">
         <is>
-          <t>2026-07-20T13:21:36Z</t>
+          <t>2026-07-16T13:35:15Z</t>
         </is>
       </c>
       <c r="C111" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D111" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E111" s="60" t="inlineStr">
         <is>
-          <t>Fusion Energy</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="F111" s="107" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G111" s="60" t="inlineStr">
         <is>
-          <t>Industry Association</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H111" s="60" t="inlineStr">
         <is>
-          <t>Fusion Industry Association</t>
+          <t>DOE Office of Science News</t>
         </is>
       </c>
       <c r="I111" s="60" t="inlineStr">
         <is>
-          <t>LLNLとPacific Fusion、Siriusパルスパワープロトタイプで3,000回のテスト達成</t>
+          <t>ノイズを消す：DOEが次世代量子情報科学を支える同位体供給チェーンの突破口を発表</t>
         </is>
       </c>
       <c r="J111" s="60" t="inlineStr">
         <is>
-          <t>ローレンス・リバモア国立研究所とPacific Fusionは、Siriusパルスパワープロトタイプの3,000回の成功テストを達成しました。この成果は、核融合エネルギーの大規模デモンストレーションに向けた重要な進展を示しています。</t>
+          <t>DOEが、次世代量子情報科学を加速するために、商業ソースよりも100倍以上純度の高い同位体を供給する成果を発表した。</t>
         </is>
       </c>
       <c r="K111" s="60" t="inlineStr">
         <is>
-          <t>https://www.ans.org/news/article-8217/llnl-and-pacific-fusion-achieve-3000shot-milestone-with-sirius-pulsedpower-prototype/?mc_cid=ed1acc7bef&amp;mc_eid=01cd8fe465#new_tab&amp;utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=llnl-and-pacific-fusion-achieve-3000-shot-milestone-with-sirius-pulsed-power-prototype</t>
+          <t>https://www.energy.gov/science/articles/silencing-noise-doe-unveils-breakthrough-domestic-silicon-and-germanium-isotope</t>
         </is>
       </c>
       <c r="L111" s="60" t="inlineStr">
         <is>
-          <t>c654a0d44a7fcbda5490cd6d</t>
+          <t>17ffa424cf814d722a951c64</t>
         </is>
       </c>
       <c r="M111" s="106" t="inlineStr">
         <is>
-          <t>2026-07-28T01:39:30+09:00</t>
+          <t>2026-07-16T22:35:15+09:00</t>
         </is>
       </c>
       <c r="N111" s="60" t="inlineStr">
@@ -9432,19 +9424,19 @@
       </c>
       <c r="O111" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: 核融合エネルギー技術</t>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: 量子情報科学のための同位体供給チェーン</t>
         </is>
       </c>
     </row>
     <row r="112" ht="42" customHeight="1">
       <c r="A112" s="106" t="inlineStr">
         <is>
-          <t>2026-07-28T01:39:30+09:00</t>
+          <t>2026-07-26T21:02:36+09:00</t>
         </is>
       </c>
       <c r="B112" s="106" t="inlineStr">
         <is>
-          <t>2026-07-20T13:17:02Z</t>
+          <t>2026-07-15T23:00:54Z</t>
         </is>
       </c>
       <c r="C112" s="60" t="inlineStr">
@@ -9454,12 +9446,12 @@
       </c>
       <c r="D112" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E112" s="60" t="inlineStr">
         <is>
-          <t>Fusion Energy | Quantum</t>
+          <t>Artificial Intelligence | Robotics</t>
         </is>
       </c>
       <c r="F112" s="107" t="n">
@@ -9467,37 +9459,37 @@
       </c>
       <c r="G112" s="60" t="inlineStr">
         <is>
-          <t>Industry Association</t>
+          <t>Official Company</t>
         </is>
       </c>
       <c r="H112" s="60" t="inlineStr">
         <is>
-          <t>Fusion Industry Association</t>
+          <t>NVIDIA Blog</t>
         </is>
       </c>
       <c r="I112" s="60" t="inlineStr">
         <is>
-          <t>量子材料の発見が核融合用電子機器の進展を促進する可能性</t>
+          <t>NVIDIAがロボティクスとエッジAIを進展させる新しいJetson Thorコンピュータを発表</t>
         </is>
       </c>
       <c r="J112" s="60" t="inlineStr">
         <is>
-          <t>アリゾナ大学の研究者は、グラフェンナノリボンが将来の核融合発電所の放射線センサーとして機能する可能性を示しました。この技術は、既存のセンサーよりも反応器コアに近いリアルタイムモニタリングを可能にするかもしれません。</t>
+          <t>NVIDIAが新しいJetson Thorコンピュータを発表し、一般向けロボットとエッジAIの需要に応える。</t>
         </is>
       </c>
       <c r="K112" s="60" t="inlineStr">
         <is>
-          <t>https://thequantuminsider.com/2026/07/20/quantum-materials-discovery-could-advance-electronics-for-extreme-environments/?mc_cid=ed1acc7bef&amp;mc_eid=01cd8fe465#new_tab&amp;utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=quantum-materials-discovery-could-advance-electronics-for-fusion</t>
+          <t>https://blogs.nvidia.com/blog/jetson-thor-robotics-edge-ai-agent/</t>
         </is>
       </c>
       <c r="L112" s="60" t="inlineStr">
         <is>
-          <t>1d37727752cb4b098b374ef4</t>
+          <t>85f482f3f904d00f68946a80</t>
         </is>
       </c>
       <c r="M112" s="106" t="inlineStr">
         <is>
-          <t>2026-07-28T01:39:30+09:00</t>
+          <t>2026-07-16T08:00:54+09:00</t>
         </is>
       </c>
       <c r="N112" s="60" t="inlineStr">
@@ -9507,7 +9499,7 @@
       </c>
       <c r="O112" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: 量子材料と核融合技術</t>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: AIスーパコンピュータモジュール</t>
         </is>
       </c>
     </row>
@@ -9519,56 +9511,60 @@
       </c>
       <c r="B113" s="106" t="inlineStr">
         <is>
-          <t>2026-07-20T11:29:00Z</t>
+          <t>2026-07-15T21:00:00Z</t>
         </is>
       </c>
       <c r="C113" s="60" t="inlineStr">
         <is>
-          <t>EU &amp; Europe</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D113" s="60" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="E113" s="60" t="inlineStr"/>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E113" s="60" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence</t>
+        </is>
+      </c>
       <c r="F113" s="107" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G113" s="60" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Policy Institute</t>
         </is>
       </c>
       <c r="H113" s="60" t="inlineStr">
         <is>
-          <t>UK DSIT</t>
+          <t>CSET</t>
         </is>
       </c>
       <c r="I113" s="60" t="inlineStr">
         <is>
-          <t>透明性データ：契約されたおよび建設された施設、プロジェクトギガビット契約</t>
+          <t>AIモデルの安全性を高めるためのGPT-Red</t>
         </is>
       </c>
       <c r="J113" s="60" t="inlineStr">
         <is>
-          <t>デジタルUKがプロジェクトギガビット契約に基づく契約状況を報告しています。</t>
+          <t>OpenAIが開発したAIスーパーハッカーGPT-Redが、AIモデルの脆弱性を自動的に特定する技術を発表しました。</t>
         </is>
       </c>
       <c r="K113" s="60" t="inlineStr">
         <is>
-          <t>https://www.gov.uk/government/publications/premises-contracted-and-built-project-gigabit-contracts</t>
+          <t>https://cset.georgetown.edu/article/meet-gpt-red-an-llm-super-hacker-openai-built-to-make-its-models-safer/</t>
         </is>
       </c>
       <c r="L113" s="60" t="inlineStr">
         <is>
-          <t>d643b4b81f6998869b340654</t>
+          <t>f64391d3daf689e78e7ac442</t>
         </is>
       </c>
       <c r="M113" s="106" t="inlineStr">
         <is>
-          <t>2026-07-20T20:29:00+09:00</t>
+          <t>2026-07-16T06:00:00+09:00</t>
         </is>
       </c>
       <c r="N113" s="60" t="inlineStr">
@@ -9578,7 +9574,7 @@
       </c>
       <c r="O113" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: デジタルインフラ整備に関する国家戦略</t>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: AIモデルの脆弱性検出技術</t>
         </is>
       </c>
     </row>
@@ -9590,7 +9586,7 @@
       </c>
       <c r="B114" s="106" t="inlineStr">
         <is>
-          <t>2026-07-20T10:59:23Z</t>
+          <t>2026-07-10T00:00:00Z</t>
         </is>
       </c>
       <c r="C114" s="60" t="inlineStr">
@@ -9600,12 +9596,12 @@
       </c>
       <c r="D114" s="60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="E114" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Fusion Energy</t>
         </is>
       </c>
       <c r="F114" s="107" t="n">
@@ -9613,37 +9609,37 @@
       </c>
       <c r="G114" s="60" t="inlineStr">
         <is>
-          <t>Official Company</t>
+          <t>Journal Article</t>
         </is>
       </c>
       <c r="H114" s="60" t="inlineStr">
         <is>
-          <t>NVIDIA Blog</t>
+          <t>Nuclear Fusion</t>
         </is>
       </c>
       <c r="I114" s="60" t="inlineStr">
         <is>
-          <t>Bristol Myers Squibbがライフサイエンス業界で最も先進的なAI工場を構築</t>
+          <t>ST-E1核融合発電プラントのための統合物理と磁石設計</t>
         </is>
       </c>
       <c r="J114" s="60" t="inlineStr">
         <is>
-          <t>Bristol Myers Squibbは、ライフサイエンス分野でのAIクラスターを拡大し、成果を上げていることを発表した。</t>
+          <t>超伝導材料やトカマクに関する研究が行われている。</t>
         </is>
       </c>
       <c r="K114" s="60" t="inlineStr">
         <is>
-          <t>https://blogs.nvidia.com/blog/bristol-myers-squibb-building-life-science-industrys-most-advanced-ai-factory-on-nvidia-vera-rubin/</t>
+          <t>https://doi.org/10.1088/1741-4326/ae773b</t>
         </is>
       </c>
       <c r="L114" s="60" t="inlineStr">
         <is>
-          <t>b4ddc90482832cbb50579f2a</t>
+          <t>a0ed06f7d374240814073762</t>
         </is>
       </c>
       <c r="M114" s="106" t="inlineStr">
         <is>
-          <t>2026-07-20T19:59:23+09:00</t>
+          <t>2026-07-10T09:00:00+09:00</t>
         </is>
       </c>
       <c r="N114" s="60" t="inlineStr">
@@ -9653,7 +9649,7 @@
       </c>
       <c r="O114" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: AIクラスターの展開</t>
+          <t>枠: Technology Innovation / 学術区分: Journal Article / 査読表示: Journal record — confirm peer review on publisher page / 掲載誌・学会: Nuclear Fusion / 焦点: ST-E1核融合発電プラントの物理と磁石設計 / OpenAlex record; work type=article; citations=9</t>
         </is>
       </c>
     </row>
@@ -9665,22 +9661,22 @@
       </c>
       <c r="B115" s="106" t="inlineStr">
         <is>
-          <t>2026-07-20T00:00:00Z</t>
+          <t>2026-07-08T08:00:00Z</t>
         </is>
       </c>
       <c r="C115" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="D115" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="E115" s="60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence | Healthcare</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="F115" s="107" t="n">
@@ -9688,37 +9684,37 @@
       </c>
       <c r="G115" s="60" t="inlineStr">
         <is>
-          <t>Journal Article</t>
+          <t>Official Company</t>
         </is>
       </c>
       <c r="H115" s="60" t="inlineStr">
         <is>
-          <t>Machine Intelligence Research</t>
+          <t>Samsung Global Newsroom</t>
         </is>
       </c>
       <c r="I115" s="60" t="inlineStr">
         <is>
-          <t>M2SNet: 医療画像セグメンテーションのためのマルチスケール減算ネットワーク</t>
+          <t>サムスン、次世代AIインフラ向けに最適化されたPM1763 SSDの量産を開始</t>
         </is>
       </c>
       <c r="J115" s="60" t="inlineStr">
         <is>
-          <t>M2SNetは、医療画像のセグメンテーションを改善するために、異なるレベルの特徴を効果的に融合する新しい手法を提案します。</t>
+          <t>サムスンが次世代AIおよびHPCサーバー環境向けに最適化されたSSDの量産を開始した。</t>
         </is>
       </c>
       <c r="K115" s="60" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1007/s11633-026-1662-9</t>
+          <t>https://news.samsung.com/global/samsung-begins-mass-production-of-pm1763-ssd-optimized-for-next-generation-ai-infrastructure</t>
         </is>
       </c>
       <c r="L115" s="60" t="inlineStr">
         <is>
-          <t>bffca1cc322e28515452081a</t>
+          <t>ffa2f59ee7918b4bbfdce082</t>
         </is>
       </c>
       <c r="M115" s="106" t="inlineStr">
         <is>
-          <t>2026-07-20T09:00:00+09:00</t>
+          <t>2026-07-08T17:00:00+09:00</t>
         </is>
       </c>
       <c r="N115" s="60" t="inlineStr">
@@ -9728,34 +9724,34 @@
       </c>
       <c r="O115" s="60" t="inlineStr">
         <is>
-          <t>枠: Technology Innovation / 学術区分: Journal Article / 査読表示: Journal record — confirm peer review on publisher page / 掲載誌・学会: Machine Intelligence Research / 焦点: 医療画像セグメンテーション技術 / OpenAlex record; work type=article; citations=79</t>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: 次世代AIインフラ向けのSSD</t>
         </is>
       </c>
     </row>
     <row r="116" ht="42" customHeight="1">
       <c r="A116" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-26T21:02:36+09:00</t>
         </is>
       </c>
       <c r="B116" s="106" t="inlineStr">
         <is>
-          <t>2026-07-17T18:42:47Z</t>
+          <t>2026-07-07T18:00:07Z</t>
         </is>
       </c>
       <c r="C116" s="60" t="inlineStr">
         <is>
-          <t>EU &amp; Europe</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D116" s="60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E116" s="60" t="inlineStr">
         <is>
-          <t>Fusion Energy</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="F116" s="107" t="n">
@@ -9763,37 +9759,37 @@
       </c>
       <c r="G116" s="60" t="inlineStr">
         <is>
-          <t>Industry Association</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H116" s="60" t="inlineStr">
         <is>
-          <t>Fusion Industry Association</t>
+          <t>National Science Foundation News</t>
         </is>
       </c>
       <c r="I116" s="60" t="inlineStr">
         <is>
-          <t>国際法専門家グループ、EUの核融合競争優位性確保の必要性に関する論文を発表</t>
+          <t>NSF、実用的な量子技術を進展させるProject Triadを開始</t>
         </is>
       </c>
       <c r="J116" s="60" t="inlineStr">
         <is>
-          <t>国際法専門家グループがEUの核融合エネルギーに関する競争優位性を確保する必要性を論じた。</t>
+          <t>米国国立科学財団が量子技術を統合する新たなイニシアティブ、Project Triadを発表した。</t>
         </is>
       </c>
       <c r="K116" s="60" t="inlineStr">
         <is>
-          <t>https://www.fusionindustryassociation.org/international-legal-expert-group-publish-paper-on-the-need-for-the-eu-to-secure-its-competitive-fusion-advantage/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=international-legal-expert-group-publish-paper-on-the-need-for-the-eu-to-secure-its-competitive-fusion-advantage</t>
+          <t>https://www.nsf.gov/news/nsf-launches-project-triad-advance-quantum-technology-real</t>
         </is>
       </c>
       <c r="L116" s="60" t="inlineStr">
         <is>
-          <t>7ef6110ab078602757409abf</t>
+          <t>2d4a226d3ce7cc9e366e902d</t>
         </is>
       </c>
       <c r="M116" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T18:56:03+09:00</t>
+          <t>2026-07-08T03:00:07+09:00</t>
         </is>
       </c>
       <c r="N116" s="60" t="inlineStr">
@@ -9803,7 +9799,7 @@
       </c>
       <c r="O116" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: Regulation &amp; Governance / 学術区分: News &amp; Official Release / 焦点: EUの核融合エネルギーに関する規制とガバナンス</t>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: Project Triad</t>
         </is>
       </c>
     </row>
@@ -9815,17 +9811,17 @@
       </c>
       <c r="B117" s="106" t="inlineStr">
         <is>
-          <t>2026-07-17T15:00:03Z</t>
+          <t>2026-06-29T21:14:22Z</t>
         </is>
       </c>
       <c r="C117" s="60" t="inlineStr">
         <is>
-          <t>EU &amp; Europe</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D117" s="60" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E117" s="60" t="inlineStr">
@@ -9834,41 +9830,41 @@
         </is>
       </c>
       <c r="F117" s="107" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G117" s="60" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Official Company</t>
         </is>
       </c>
       <c r="H117" s="60" t="inlineStr">
         <is>
-          <t>UK DSIT</t>
+          <t>Microsoft Research</t>
         </is>
       </c>
       <c r="I117" s="60" t="inlineStr">
         <is>
-          <t>AI研究資源に関するガイダンス</t>
+          <t>抽象性と特異性のバランスを取る記憶表現Memora</t>
         </is>
       </c>
       <c r="J117" s="60" t="inlineStr">
         <is>
-          <t>AI研究資源（AIRR）は、研究者や産業にAI専門の計算能力を提供するスーパーコンピュータのスイートです。</t>
+          <t>AIエージェントの効率的な記憶システムMemoraが発表されました。</t>
         </is>
       </c>
       <c r="K117" s="60" t="inlineStr">
         <is>
-          <t>https://www.gov.uk/government/publications/ai-research-resource</t>
+          <t>https://www.microsoft.com/en-us/research/blog/memora-a-harmonic-memory-representation-balancing-abstraction-and-specificity/</t>
         </is>
       </c>
       <c r="L117" s="60" t="inlineStr">
         <is>
-          <t>579a0b7ad2d471608fff5049</t>
+          <t>6c035ef4d4202a4874e60b97</t>
         </is>
       </c>
       <c r="M117" s="106" t="inlineStr">
         <is>
-          <t>2026-07-18T00:00:03+09:00</t>
+          <t>2026-06-30T06:14:22+09:00</t>
         </is>
       </c>
       <c r="N117" s="60" t="inlineStr">
@@ -9878,68 +9874,72 @@
       </c>
       <c r="O117" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: AI研究資源（AIRR）</t>
+          <t>枠: Technology Innovation / 学術区分: News &amp; Official Release / 焦点: AIエージェントの記憶システム</t>
         </is>
       </c>
     </row>
     <row r="118" ht="42" customHeight="1">
       <c r="A118" s="106" t="inlineStr">
         <is>
-          <t>2026-07-26T21:45:54+09:00</t>
+          <t>2026-07-26T21:02:36+09:00</t>
         </is>
       </c>
       <c r="B118" s="106" t="inlineStr">
         <is>
-          <t>2026-07-17T14:48:00Z</t>
+          <t>2026-06-29T12:00:00Z</t>
         </is>
       </c>
       <c r="C118" s="60" t="inlineStr">
         <is>
-          <t>EU &amp; Europe</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D118" s="60" t="inlineStr">
         <is>
-          <t>European Patent Organisation</t>
-        </is>
-      </c>
-      <c r="E118" s="60" t="inlineStr"/>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E118" s="60" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
       <c r="F118" s="107" t="n">
         <v>3</v>
       </c>
       <c r="G118" s="60" t="inlineStr">
         <is>
-          <t>Intergovernmental</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="H118" s="60" t="inlineStr">
         <is>
-          <t>European Patent Office News</t>
+          <t>NIST News</t>
         </is>
       </c>
       <c r="I118" s="60" t="inlineStr">
         <is>
-          <t>技術革新を加速するための特許と標準</t>
+          <t>NIST、量子技術の製造を推進するセンターを設立</t>
         </is>
       </c>
       <c r="J118" s="60" t="inlineStr">
         <is>
-          <t>特許と標準が技術革新を加速するための重要な要素であることについての情報。</t>
+          <t>NISTは、量子製造工学センター（QMEC）を設立するためにSRIインターナショナルとの合意を発表した。</t>
         </is>
       </c>
       <c r="K118" s="60" t="inlineStr">
         <is>
-          <t>https://epo.org/en/about-us/observatory-patents-and-technology/policy-and-funding/patents-and-standards</t>
+          <t>https://www.nist.gov/news-events/news/2026/06/nist-launches-center-drive-manufacture-quantum-technologies</t>
         </is>
       </c>
       <c r="L118" s="60" t="inlineStr">
         <is>
-          <t>a0d096f59b7771ee7e91da7b</t>
+          <t>2d90197d96166b4d1d7f7c11</t>
         </is>
       </c>
       <c r="M118" s="106" t="inlineStr">
         <is>
-          <t>2026-07-17T23:48:00+09:00</t>
+          <t>2026-06-29T21:00:00+09:00</t>
         </is>
       </c>
       <c r="N118" s="60" t="inlineStr">
@@ -9949,7 +9949,7 @@
       </c>
       <c r="O118" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: Patents &amp; Intellectual Property / 学術区分: News &amp; Official Release / 焦点: 技術革新を加速するための特許と標準 / Historical backfill from an allowlisted source.</t>
+          <t>枠: Innovation Policy / 政策分野: Public Procurement &amp; Industrial Policy / 学術区分: News &amp; Official Release / 焦点: 量子製造工学センターの設立</t>
         </is>
       </c>
     </row>
@@ -9961,22 +9961,22 @@
       </c>
       <c r="B119" s="106" t="inlineStr">
         <is>
-          <t>2026-07-17T13:42:16Z</t>
+          <t>2026-06-26T01:30:26Z</t>
         </is>
       </c>
       <c r="C119" s="60" t="inlineStr">
         <is>
-          <t>EU &amp; Europe</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="D119" s="60" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="E119" s="60" t="inlineStr"/>
       <c r="F119" s="107" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G119" s="60" t="inlineStr">
         <is>
@@ -9985,32 +9985,32 @@
       </c>
       <c r="H119" s="60" t="inlineStr">
         <is>
-          <t>UK DSIT</t>
+          <t>NISTEP Updates</t>
         </is>
       </c>
       <c r="I119" s="60" t="inlineStr">
         <is>
-          <t>デジタルサービスの改善に関する公開書簡</t>
+          <t>親子企業間の資源再配分と特許活動の特性</t>
         </is>
       </c>
       <c r="J119" s="60" t="inlineStr">
         <is>
-          <t>業界リーダーに向けて、デジタルサービスの改善に関する公開書簡が送られた。</t>
+          <t>親子企業間での研究開発資源の移動に関する特許活動の特性についての実証分析が行われました。</t>
         </is>
       </c>
       <c r="K119" s="60" t="inlineStr">
         <is>
-          <t>https://www.gov.uk/government/publications/improving-access-to-and-use-of-digital-services-open-letter-to-business-leaders</t>
+          <t>https://www.nistep.go.jp/archives/63333/</t>
         </is>
       </c>
       <c r="L119" s="60" t="inlineStr">
         <is>
-          <t>d136ac8a836994c6ce5e35c6</t>
+          <t>25352f245236dac75576baa7</t>
         </is>
       </c>
       <c r="M119" s="106" t="inlineStr">
         <is>
-          <t>2026-07-17T22:42:16+09:00</t>
+          <t>2026-06-26T10:30:26+09:00</t>
         </is>
       </c>
       <c r="N119" s="60" t="inlineStr">
@@ -10020,7 +10020,7 @@
       </c>
       <c r="O119" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: デジタルサービスの改善</t>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy | Patents &amp; Intellectual Property / 学術区分: News &amp; Official Release / 焦点: 親子企業間の資源再配分と特許活動</t>
         </is>
       </c>
     </row>
@@ -10032,26 +10032,22 @@
       </c>
       <c r="B120" s="106" t="inlineStr">
         <is>
-          <t>2026-07-17T12:00:04Z</t>
+          <t>2026-06-25T05:26:14Z</t>
         </is>
       </c>
       <c r="C120" s="60" t="inlineStr">
         <is>
-          <t>EU &amp; Europe</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D120" s="60" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="E120" s="60" t="inlineStr">
-        <is>
-          <t>Artificial Intelligence</t>
-        </is>
-      </c>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E120" s="60" t="inlineStr"/>
       <c r="F120" s="107" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G120" s="60" t="inlineStr">
         <is>
@@ -10060,32 +10056,32 @@
       </c>
       <c r="H120" s="60" t="inlineStr">
         <is>
-          <t>UK DSIT</t>
+          <t>DOE Office of Science News</t>
         </is>
       </c>
       <c r="I120" s="60" t="inlineStr">
         <is>
-          <t>AIスーパーコンピュータホストサイト選定に関する表明</t>
+          <t>米国エネルギー省が国内供給網を強化</t>
         </is>
       </c>
       <c r="J120" s="60" t="inlineStr">
         <is>
-          <t>UKの次のAIスーパーコンピュータのホストサイト選定に関する表明が行われた。</t>
+          <t>米国エネルギー省がイリジウム-192の国内生産能力を確立しました。</t>
         </is>
       </c>
       <c r="K120" s="60" t="inlineStr">
         <is>
-          <t>https://www.gov.uk/government/publications/expression-of-interest-airr-heterogeneous-supercomputer-host-site-selection</t>
+          <t>https://www.energy.gov/science/articles/doe-strengthens-domestic-supply-chain-american-energy-and-manufacturing</t>
         </is>
       </c>
       <c r="L120" s="60" t="inlineStr">
         <is>
-          <t>27d607577c2759c8d53f9ddf</t>
+          <t>62854e5795f9fac8f0427e2f</t>
         </is>
       </c>
       <c r="M120" s="106" t="inlineStr">
         <is>
-          <t>2026-07-17T21:00:04+09:00</t>
+          <t>2026-06-25T14:26:14+09:00</t>
         </is>
       </c>
       <c r="N120" s="60" t="inlineStr">
@@ -10095,7 +10091,7 @@
       </c>
       <c r="O120" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: AIスーパーコンピュータのホストサイト選定</t>
+          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: イリジウム-192の国内生産能力</t>
         </is>
       </c>
     </row>
@@ -10107,22 +10103,22 @@
       </c>
       <c r="B121" s="106" t="inlineStr">
         <is>
-          <t>2026-07-17T07:59:22Z</t>
+          <t>2026-06-25T04:00:24Z</t>
         </is>
       </c>
       <c r="C121" s="60" t="inlineStr">
         <is>
-          <t>EU &amp; Europe</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D121" s="60" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="E121" s="60" t="inlineStr"/>
       <c r="F121" s="107" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G121" s="60" t="inlineStr">
         <is>
@@ -10131,32 +10127,32 @@
       </c>
       <c r="H121" s="60" t="inlineStr">
         <is>
-          <t>UK DSIT</t>
+          <t>NISTEP Updates</t>
         </is>
       </c>
       <c r="I121" s="60" t="inlineStr">
         <is>
-          <t>子供のオンライン保護に関する新ルール</t>
+          <t>STI Horizon誌2026夏号の公表</t>
         </is>
       </c>
       <c r="J121" s="60" t="inlineStr">
         <is>
-          <t>UK政府が16歳未満の子供に対するソーシャルメディア禁止を発表した。</t>
+          <t>NISTEPが科学技術・イノベーション政策に関する情報を幅広く掲載したSTI Horizon 2026夏号を公表しました。</t>
         </is>
       </c>
       <c r="K121" s="60" t="inlineStr">
         <is>
-          <t>https://www.gov.uk/government/publications/fact-sheet-new-rules-to-protect-children-online</t>
+          <t>https://www.nistep.go.jp/archives/63155/</t>
         </is>
       </c>
       <c r="L121" s="60" t="inlineStr">
         <is>
-          <t>371ff53aa8f9007fcb1ddddf</t>
+          <t>79d88af79ddda07d59b28e08</t>
         </is>
       </c>
       <c r="M121" s="106" t="inlineStr">
         <is>
-          <t>2026-07-17T16:59:22+09:00</t>
+          <t>2026-06-25T13:00:24+09:00</t>
         </is>
       </c>
       <c r="N121" s="60" t="inlineStr">
@@ -10166,7 +10162,7 @@
       </c>
       <c r="O121" s="60" t="inlineStr">
         <is>
-          <t>枠: Innovation Policy / 政策分野: National Programs &amp; Strategy / 学術区分: News &amp; Official Release / 焦点: 子供のオンライン保護に関する新ルール</t>
+          <t>枠: Innovation Policy / 政策分野